--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,13 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D543"/>
+  <dimension ref="A1:E543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,10 +439,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>price_00:30</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -457,9 +463,12 @@
         <v>70545.39999999999</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>70545.39999999999</v>
+        <v>70623.2</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>70623.2</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -473,9 +482,12 @@
         <v>2072.31</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>2072.31</v>
+        <v>2074.4</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>2074.4</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -489,9 +501,12 @@
         <v>86.72</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>86.72</v>
+        <v>86.86</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -505,11 +520,14 @@
         <v>4.039</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>4.039</v>
+        <v>4.022</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>4.039</v>
       </c>
+      <c r="E5" s="1" t="n">
+        <v>4.022</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -521,9 +539,12 @@
         <v>0.09485</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.09485</v>
+        <v>0.09515</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>0.09515</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>0.09485</v>
       </c>
     </row>
@@ -537,9 +558,12 @@
         <v>1.388</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1.388</v>
+        <v>1.3892</v>
       </c>
       <c r="D7" s="1" t="n">
+        <v>1.3892</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -553,11 +577,14 @@
         <v>22.657</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>22.657</v>
+        <v>22.485</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>22.657</v>
       </c>
+      <c r="E8" s="1" t="n">
+        <v>22.485</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -569,9 +596,12 @@
         <v>0.002119</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>0.002119</v>
+        <v>0.00215</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>0.002119</v>
       </c>
     </row>
@@ -585,11 +615,14 @@
         <v>0.01067</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>0.01067</v>
+        <v>0.009129</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>0.01067</v>
       </c>
+      <c r="E10" s="1" t="n">
+        <v>0.009129</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,11 +634,14 @@
         <v>0.1709</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.1709</v>
+        <v>0.16978</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0.1709</v>
       </c>
+      <c r="E11" s="1" t="n">
+        <v>0.16978</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -617,9 +653,12 @@
         <v>0.01197</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>0.01197</v>
+        <v>0.012009</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>0.012009</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>0.01197</v>
       </c>
     </row>
@@ -633,9 +672,12 @@
         <v>37.988</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>37.988</v>
+        <v>38.402</v>
       </c>
       <c r="D13" s="1" t="n">
+        <v>38.402</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -649,9 +691,12 @@
         <v>652.8</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>652.8</v>
+        <v>653.52</v>
       </c>
       <c r="D14" s="1" t="n">
+        <v>653.52</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -665,9 +710,12 @@
         <v>209.13</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>209.13</v>
+        <v>209.41</v>
       </c>
       <c r="D15" s="1" t="n">
+        <v>209.41</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -681,9 +729,12 @@
         <v>0.0033417</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>0.0033417</v>
+        <v>0.0033503</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>0.0033503</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>0.0033417</v>
       </c>
     </row>
@@ -697,9 +748,12 @@
         <v>234.47</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>234.47</v>
+        <v>235.2</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>235.2</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -713,9 +767,12 @@
         <v>0.987</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.987</v>
+        <v>0.9913</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>0.9913</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -729,11 +786,14 @@
         <v>1.0322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>1.0322</v>
+        <v>1.0184</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1.0322</v>
       </c>
+      <c r="E19" s="1" t="n">
+        <v>1.0184</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -745,9 +805,12 @@
         <v>0.2608</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>0.2608</v>
+        <v>0.2612</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>0.2608</v>
       </c>
     </row>
@@ -761,11 +824,14 @@
         <v>0.60985</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.60985</v>
+        <v>0.60434</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>0.60985</v>
       </c>
+      <c r="E21" s="1" t="n">
+        <v>0.60434</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -777,9 +843,12 @@
         <v>8.991</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>8.991</v>
+        <v>9.013</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>9.013</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -793,9 +862,12 @@
         <v>0.02425</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>0.02425</v>
+        <v>0.02441</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>0.02441</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>0.02425</v>
       </c>
     </row>
@@ -809,9 +881,12 @@
         <v>9.555999999999999</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>9.555999999999999</v>
+        <v>9.579000000000001</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>9.579000000000001</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -825,9 +900,12 @@
         <v>1.218</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>1.218</v>
+        <v>1.222</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -841,11 +919,14 @@
         <v>0.07160999999999999</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.07160999999999999</v>
+        <v>0.07106</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>0.07160999999999999</v>
       </c>
+      <c r="E26" s="1" t="n">
+        <v>0.07106</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -862,6 +943,9 @@
       <c r="D27" s="1" t="n">
         <v>1.428</v>
       </c>
+      <c r="E27" s="1" t="n">
+        <v>1.428</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -873,9 +957,12 @@
         <v>1.309</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>1.309</v>
+        <v>1.312</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -889,9 +976,12 @@
         <v>461.74</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>461.74</v>
+        <v>461.93</v>
       </c>
       <c r="D29" s="1" t="n">
+        <v>461.93</v>
+      </c>
+      <c r="E29" s="1" t="n">
         <v>461.74</v>
       </c>
     </row>
@@ -905,9 +995,12 @@
         <v>1.2764</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>1.2764</v>
+        <v>1.2786</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>1.2786</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -921,11 +1014,14 @@
         <v>5024.91</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>5024.91</v>
+        <v>5022.05</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>5024.91</v>
       </c>
+      <c r="E31" s="1" t="n">
+        <v>5022.05</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -937,9 +1033,12 @@
         <v>0.867</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.867</v>
+        <v>0.872</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="E32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -953,9 +1052,12 @@
         <v>0.001971</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.001971</v>
+        <v>0.001981</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>0.001981</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -969,11 +1071,14 @@
         <v>0.17091</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>0.17091</v>
+        <v>0.16678</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>0.17091</v>
       </c>
+      <c r="E34" s="1" t="n">
+        <v>0.16678</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -985,9 +1090,12 @@
         <v>0.2982</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>0.2982</v>
+        <v>0.29856</v>
       </c>
       <c r="D35" s="1" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>0.2982</v>
       </c>
     </row>
@@ -1001,11 +1109,14 @@
         <v>1.793</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>1.793</v>
+        <v>1.787</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>1.793</v>
       </c>
+      <c r="E36" s="1" t="n">
+        <v>1.787</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1017,9 +1128,12 @@
         <v>110.25</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>110.25</v>
+        <v>110.66</v>
       </c>
       <c r="D37" s="1" t="n">
+        <v>110.66</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1033,9 +1147,12 @@
         <v>0.22651</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>0.22651</v>
+        <v>0.22687</v>
       </c>
       <c r="D38" s="1" t="n">
+        <v>0.22687</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>0.22651</v>
       </c>
     </row>
@@ -1049,9 +1166,12 @@
         <v>0.1078</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.1078</v>
+        <v>0.1082</v>
       </c>
       <c r="D39" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="E39" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -1065,9 +1185,12 @@
         <v>0.37042</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>0.37042</v>
+        <v>0.37297</v>
       </c>
       <c r="D40" s="1" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="E40" s="1" t="n">
         <v>0.37042</v>
       </c>
     </row>
@@ -1081,9 +1204,12 @@
         <v>54.45</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>54.45</v>
+        <v>54.52</v>
       </c>
       <c r="D41" s="1" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="E41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1097,11 +1223,14 @@
         <v>0.0010838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.0010838</v>
+        <v>0.0010793</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>0.0010838</v>
       </c>
+      <c r="E42" s="1" t="n">
+        <v>0.0010793</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1113,11 +1242,14 @@
         <v>6.588</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>6.588</v>
+        <v>6.531</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>6.588</v>
       </c>
+      <c r="E43" s="1" t="n">
+        <v>6.531</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1129,9 +1261,12 @@
         <v>0.6409</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.6409</v>
+        <v>0.6451</v>
       </c>
       <c r="D44" s="1" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>0.6409</v>
       </c>
     </row>
@@ -1145,9 +1280,12 @@
         <v>0.3539</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0.3539</v>
+        <v>0.354</v>
       </c>
       <c r="D45" s="1" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -1161,11 +1299,14 @@
         <v>0.0326</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.0326</v>
+        <v>0.03257</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>0.0326</v>
       </c>
+      <c r="E46" s="1" t="n">
+        <v>0.03257</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1177,11 +1318,14 @@
         <v>0.07371</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.07371</v>
+        <v>0.07321</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>0.07371</v>
       </c>
+      <c r="E47" s="1" t="n">
+        <v>0.07321</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1193,9 +1337,12 @@
         <v>0.7008</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.7008</v>
+        <v>0.7035</v>
       </c>
       <c r="D48" s="1" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="E48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -1209,11 +1356,14 @@
         <v>0.00463</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.00463</v>
+        <v>0.00462</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>0.00463</v>
       </c>
+      <c r="E49" s="1" t="n">
+        <v>0.00462</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1225,9 +1375,12 @@
         <v>0.1041</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.1041</v>
+        <v>0.1043</v>
       </c>
       <c r="D50" s="1" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="E50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -1241,9 +1394,12 @@
         <v>0.04036</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>0.04036</v>
+        <v>0.04047</v>
       </c>
       <c r="D51" s="1" t="n">
+        <v>0.04047</v>
+      </c>
+      <c r="E51" s="1" t="n">
         <v>0.04036</v>
       </c>
     </row>
@@ -1257,9 +1413,12 @@
         <v>0.1667</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.1667</v>
+        <v>0.1672</v>
       </c>
       <c r="D52" s="1" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>0.1667</v>
       </c>
     </row>
@@ -1273,9 +1432,12 @@
         <v>0.02164</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>0.02164</v>
+        <v>0.0222</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -1289,9 +1451,12 @@
         <v>0.007221</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.007221</v>
+        <v>0.007229</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>0.007229</v>
+      </c>
+      <c r="E54" s="1" t="n">
         <v>0.007221</v>
       </c>
     </row>
@@ -1305,9 +1470,12 @@
         <v>3.925</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>3.925</v>
+        <v>3.933</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>3.925</v>
       </c>
     </row>
@@ -1321,11 +1489,14 @@
         <v>0.017208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0.017208</v>
+        <v>0.017126</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>0.017208</v>
       </c>
+      <c r="E56" s="1" t="n">
+        <v>0.017126</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1337,9 +1508,12 @@
         <v>0.1095</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0.1095</v>
+        <v>0.1103</v>
       </c>
       <c r="D57" s="1" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="E57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -1353,9 +1527,12 @@
         <v>2.643</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>2.643</v>
+        <v>2.656</v>
       </c>
       <c r="D58" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -1369,9 +1546,12 @@
         <v>0.1593</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0.1593</v>
+        <v>0.16</v>
       </c>
       <c r="D59" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -1385,9 +1565,12 @@
         <v>0.005914</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0.005914</v>
+        <v>0.005918</v>
       </c>
       <c r="D60" s="1" t="n">
+        <v>0.005918</v>
+      </c>
+      <c r="E60" s="1" t="n">
         <v>0.005914</v>
       </c>
     </row>
@@ -1401,9 +1584,12 @@
         <v>0.09204</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.09204</v>
+        <v>0.09209000000000001</v>
       </c>
       <c r="D61" s="1" t="n">
+        <v>0.09209000000000001</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>0.09204</v>
       </c>
     </row>
@@ -1417,9 +1603,12 @@
         <v>0.9118000000000001</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9151</v>
       </c>
       <c r="D62" s="1" t="n">
+        <v>0.9151</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -1438,6 +1627,9 @@
       <c r="D63" s="1" t="n">
         <v>0.774</v>
       </c>
+      <c r="E63" s="1" t="n">
+        <v>0.774</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1449,9 +1641,12 @@
         <v>0.04674</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0.04674</v>
+        <v>0.04677</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>0.04677</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>0.04674</v>
       </c>
     </row>
@@ -1465,9 +1660,12 @@
         <v>355.34</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>355.34</v>
+        <v>357.03</v>
       </c>
       <c r="D65" s="1" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="E65" s="1" t="n">
         <v>355.34</v>
       </c>
     </row>
@@ -1481,9 +1679,12 @@
         <v>0.12788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0.12788</v>
+        <v>0.12814</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>0.12814</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -1497,11 +1698,14 @@
         <v>0.2446</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0.2446</v>
+        <v>0.2418</v>
       </c>
       <c r="D67" s="1" t="n">
         <v>0.2446</v>
       </c>
+      <c r="E67" s="1" t="n">
+        <v>0.2418</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1513,9 +1717,12 @@
         <v>0.0034</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>0.0034</v>
+        <v>0.00342</v>
       </c>
       <c r="D68" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="E68" s="1" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -1529,9 +1736,12 @@
         <v>0.1759</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0.1759</v>
+        <v>0.1762</v>
       </c>
       <c r="D69" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="E69" s="1" t="n">
         <v>0.1759</v>
       </c>
     </row>
@@ -1545,9 +1755,12 @@
         <v>0.16422</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>0.16422</v>
+        <v>0.16434</v>
       </c>
       <c r="D70" s="1" t="n">
+        <v>0.16434</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>0.16422</v>
       </c>
     </row>
@@ -1561,11 +1774,14 @@
         <v>0.3541</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>0.3541</v>
+        <v>0.3523</v>
       </c>
       <c r="D71" s="1" t="n">
         <v>0.3541</v>
       </c>
+      <c r="E71" s="1" t="n">
+        <v>0.3523</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1577,9 +1793,12 @@
         <v>0.7043</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>0.7043</v>
+        <v>0.7067</v>
       </c>
       <c r="D72" s="1" t="n">
+        <v>0.7067</v>
+      </c>
+      <c r="E72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -1593,11 +1812,14 @@
         <v>0.00861</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>0.00861</v>
+        <v>0.00859</v>
       </c>
       <c r="D73" s="1" t="n">
         <v>0.00861</v>
       </c>
+      <c r="E73" s="1" t="n">
+        <v>0.00859</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1609,9 +1831,12 @@
         <v>0.006002</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0.006002</v>
+        <v>0.006005</v>
       </c>
       <c r="D74" s="1" t="n">
+        <v>0.006005</v>
+      </c>
+      <c r="E74" s="1" t="n">
         <v>0.006002</v>
       </c>
     </row>
@@ -1630,6 +1855,9 @@
       <c r="D75" s="1" t="n">
         <v>0.226</v>
       </c>
+      <c r="E75" s="1" t="n">
+        <v>0.226</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1641,11 +1869,14 @@
         <v>0.3033</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>0.3033</v>
+        <v>0.3025</v>
       </c>
       <c r="D76" s="1" t="n">
         <v>0.3033</v>
       </c>
+      <c r="E76" s="1" t="n">
+        <v>0.3025</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1657,9 +1888,12 @@
         <v>0.1001</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>0.1001</v>
+        <v>0.1003</v>
       </c>
       <c r="D77" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="E77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -1673,9 +1907,12 @@
         <v>0.1227</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>0.1227</v>
+        <v>0.1231</v>
       </c>
       <c r="D78" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -1689,11 +1926,14 @@
         <v>0.06877999999999999</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>0.06877999999999999</v>
+        <v>0.06873</v>
       </c>
       <c r="D79" s="1" t="n">
         <v>0.06877999999999999</v>
       </c>
+      <c r="E79" s="1" t="n">
+        <v>0.06873</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1705,11 +1945,14 @@
         <v>0.04696</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>0.04696</v>
+        <v>0.04659</v>
       </c>
       <c r="D80" s="1" t="n">
         <v>0.04696</v>
       </c>
+      <c r="E80" s="1" t="n">
+        <v>0.04659</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1721,11 +1964,14 @@
         <v>0.000234</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>0.000234</v>
+        <v>0.000232</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>0.000234</v>
       </c>
+      <c r="E81" s="1" t="n">
+        <v>0.000232</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1737,9 +1983,12 @@
         <v>8.215</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>8.215</v>
+        <v>8.231</v>
       </c>
       <c r="D82" s="1" t="n">
+        <v>8.231</v>
+      </c>
+      <c r="E82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -1753,11 +2002,14 @@
         <v>0.0006002</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>0.0006002</v>
+        <v>0.0005992</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>0.0006002</v>
       </c>
+      <c r="E83" s="1" t="n">
+        <v>0.0005992</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1769,11 +2021,14 @@
         <v>0.4212</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>0.4212</v>
+        <v>0.4158</v>
       </c>
       <c r="D84" s="1" t="n">
         <v>0.4212</v>
       </c>
+      <c r="E84" s="1" t="n">
+        <v>0.4158</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1785,9 +2040,12 @@
         <v>0.06243</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>0.06243</v>
+        <v>0.06254</v>
       </c>
       <c r="D85" s="1" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="E85" s="1" t="n">
         <v>0.06243</v>
       </c>
     </row>
@@ -1801,11 +2059,14 @@
         <v>0.05509</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>0.05509</v>
+        <v>0.05465</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>0.05509</v>
       </c>
+      <c r="E86" s="1" t="n">
+        <v>0.05465</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1817,9 +2078,12 @@
         <v>0.003329</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>0.003329</v>
+        <v>0.003345</v>
       </c>
       <c r="D87" s="1" t="n">
+        <v>0.003345</v>
+      </c>
+      <c r="E87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -1833,11 +2097,14 @@
         <v>0.04971</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>0.04971</v>
+        <v>0.04964</v>
       </c>
       <c r="D88" s="1" t="n">
         <v>0.04971</v>
       </c>
+      <c r="E88" s="1" t="n">
+        <v>0.04964</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1849,9 +2116,12 @@
         <v>0.03031</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>0.03031</v>
+        <v>0.03065</v>
       </c>
       <c r="D89" s="1" t="n">
+        <v>0.03065</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -1865,9 +2135,12 @@
         <v>0.3473</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>0.3473</v>
+        <v>0.3483</v>
       </c>
       <c r="D90" s="1" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="E90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -1881,11 +2154,14 @@
         <v>0.06078</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>0.06078</v>
+        <v>0.06074</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>0.06078</v>
       </c>
+      <c r="E91" s="1" t="n">
+        <v>0.06074</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1897,9 +2173,12 @@
         <v>0.3421</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>0.3421</v>
+        <v>0.3454</v>
       </c>
       <c r="D92" s="1" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="E92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -1913,9 +2192,12 @@
         <v>1.966</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>1.966</v>
+        <v>1.9716</v>
       </c>
       <c r="D93" s="1" t="n">
+        <v>1.9716</v>
+      </c>
+      <c r="E93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -1929,9 +2211,12 @@
         <v>0.2589</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>0.2589</v>
+        <v>0.2596</v>
       </c>
       <c r="D94" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="E94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -1945,11 +2230,14 @@
         <v>0.04525</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>0.04525</v>
+        <v>0.04516</v>
       </c>
       <c r="D95" s="1" t="n">
         <v>0.04525</v>
       </c>
+      <c r="E95" s="1" t="n">
+        <v>0.04516</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1961,9 +2249,12 @@
         <v>0.005831</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>0.005831</v>
+        <v>0.006006</v>
       </c>
       <c r="D96" s="1" t="n">
+        <v>0.006006</v>
+      </c>
+      <c r="E96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -1977,9 +2268,12 @@
         <v>0.001746</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>0.001746</v>
+        <v>0.001748</v>
       </c>
       <c r="D97" s="1" t="n">
+        <v>0.001748</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>0.001746</v>
       </c>
     </row>
@@ -1993,11 +2287,14 @@
         <v>5.284</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>5.284</v>
+        <v>5.251</v>
       </c>
       <c r="D98" s="1" t="n">
         <v>5.284</v>
       </c>
+      <c r="E98" s="1" t="n">
+        <v>5.251</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2009,9 +2306,12 @@
         <v>0.01514</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>0.01514</v>
+        <v>0.01516</v>
       </c>
       <c r="D99" s="1" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="E99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -2025,9 +2325,12 @@
         <v>0.5508999999999999</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5515</v>
       </c>
       <c r="D100" s="1" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -2041,11 +2344,14 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0912</v>
       </c>
       <c r="D101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
+      <c r="E101" s="1" t="n">
+        <v>0.0912</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2057,9 +2363,12 @@
         <v>32.48</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>32.48</v>
+        <v>32.53</v>
       </c>
       <c r="D102" s="1" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="E102" s="1" t="n">
         <v>32.48</v>
       </c>
     </row>
@@ -2073,9 +2382,12 @@
         <v>0.032</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>0.032</v>
+        <v>0.03251</v>
       </c>
       <c r="D103" s="1" t="n">
+        <v>0.03251</v>
+      </c>
+      <c r="E103" s="1" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -2089,9 +2401,12 @@
         <v>0.06582</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>0.06582</v>
+        <v>0.06598999999999999</v>
       </c>
       <c r="D104" s="1" t="n">
+        <v>0.06598999999999999</v>
+      </c>
+      <c r="E104" s="1" t="n">
         <v>0.06582</v>
       </c>
     </row>
@@ -2105,9 +2420,12 @@
         <v>1.2981</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>1.2981</v>
+        <v>1.3037</v>
       </c>
       <c r="D105" s="1" t="n">
+        <v>1.3037</v>
+      </c>
+      <c r="E105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -2121,11 +2439,14 @@
         <v>0.1186</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>0.1186</v>
+        <v>0.1183</v>
       </c>
       <c r="D106" s="1" t="n">
         <v>0.1186</v>
       </c>
+      <c r="E106" s="1" t="n">
+        <v>0.1183</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2142,6 +2463,9 @@
       <c r="D107" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="E107" s="1" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2153,9 +2477,12 @@
         <v>0.09589</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0.09589</v>
+        <v>0.09616</v>
       </c>
       <c r="D108" s="1" t="n">
+        <v>0.09616</v>
+      </c>
+      <c r="E108" s="1" t="n">
         <v>0.09589</v>
       </c>
     </row>
@@ -2169,11 +2496,14 @@
         <v>0.14276</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0.14276</v>
+        <v>0.14064</v>
       </c>
       <c r="D109" s="1" t="n">
         <v>0.14276</v>
       </c>
+      <c r="E109" s="1" t="n">
+        <v>0.14064</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2185,9 +2515,12 @@
         <v>5.546</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>5.546</v>
+        <v>5.57</v>
       </c>
       <c r="D110" s="1" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -2201,9 +2534,12 @@
         <v>1.082</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>1.082</v>
+        <v>1.092</v>
       </c>
       <c r="D111" s="1" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="E111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -2217,9 +2553,12 @@
         <v>0.029692</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0.029692</v>
+        <v>0.029743</v>
       </c>
       <c r="D112" s="1" t="n">
+        <v>0.029743</v>
+      </c>
+      <c r="E112" s="1" t="n">
         <v>0.029692</v>
       </c>
     </row>
@@ -2233,9 +2572,12 @@
         <v>1.874</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>1.874</v>
+        <v>1.879</v>
       </c>
       <c r="D113" s="1" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -2249,11 +2591,14 @@
         <v>0.06108</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0.06108</v>
+        <v>0.06009</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>0.06108</v>
       </c>
+      <c r="E114" s="1" t="n">
+        <v>0.06009</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2265,9 +2610,12 @@
         <v>0.12932</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0.12932</v>
+        <v>0.12981</v>
       </c>
       <c r="D115" s="1" t="n">
+        <v>0.12981</v>
+      </c>
+      <c r="E115" s="1" t="n">
         <v>0.12932</v>
       </c>
     </row>
@@ -2281,9 +2629,12 @@
         <v>1.1095</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>1.1095</v>
+        <v>1.1135</v>
       </c>
       <c r="D116" s="1" t="n">
+        <v>1.1135</v>
+      </c>
+      <c r="E116" s="1" t="n">
         <v>1.1095</v>
       </c>
     </row>
@@ -2297,11 +2648,14 @@
         <v>0.156</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0.156</v>
+        <v>0.1537</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>0.156</v>
       </c>
+      <c r="E117" s="1" t="n">
+        <v>0.1537</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2313,11 +2667,14 @@
         <v>0.1584</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0.1584</v>
+        <v>0.1582</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>0.1584</v>
       </c>
+      <c r="E118" s="1" t="n">
+        <v>0.1582</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2329,11 +2686,14 @@
         <v>0.04587</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0.04587</v>
+        <v>0.04566</v>
       </c>
       <c r="D119" s="1" t="n">
         <v>0.04587</v>
       </c>
+      <c r="E119" s="1" t="n">
+        <v>0.04566</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2345,9 +2705,12 @@
         <v>3.018</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>3.018</v>
+        <v>3.022</v>
       </c>
       <c r="D120" s="1" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="E120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -2361,9 +2724,12 @@
         <v>0.2957</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>0.2957</v>
+        <v>0.297</v>
       </c>
       <c r="D121" s="1" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="E121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -2377,9 +2743,12 @@
         <v>0.5826</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>0.5826</v>
+        <v>0.5831</v>
       </c>
       <c r="D122" s="1" t="n">
+        <v>0.5831</v>
+      </c>
+      <c r="E122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -2398,6 +2767,9 @@
       <c r="D123" s="1" t="n">
         <v>0.01263</v>
       </c>
+      <c r="E123" s="1" t="n">
+        <v>0.01263</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2409,9 +2781,12 @@
         <v>0.1584</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>0.1584</v>
+        <v>0.1591</v>
       </c>
       <c r="D124" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="E124" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -2425,9 +2800,12 @@
         <v>0.001778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>0.001778</v>
+        <v>0.001783</v>
       </c>
       <c r="D125" s="1" t="n">
+        <v>0.001783</v>
+      </c>
+      <c r="E125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -2441,9 +2819,12 @@
         <v>0.0004894</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>0.0004894</v>
+        <v>0.0004906</v>
       </c>
       <c r="D126" s="1" t="n">
+        <v>0.0004906</v>
+      </c>
+      <c r="E126" s="1" t="n">
         <v>0.0004894</v>
       </c>
     </row>
@@ -2457,9 +2838,12 @@
         <v>0.02949</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>0.02949</v>
+        <v>0.02957</v>
       </c>
       <c r="D127" s="1" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="E127" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -2473,9 +2857,12 @@
         <v>0.04119</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>0.04119</v>
+        <v>0.04122</v>
       </c>
       <c r="D128" s="1" t="n">
+        <v>0.04122</v>
+      </c>
+      <c r="E128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -2489,11 +2876,14 @@
         <v>0.04887</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>0.04887</v>
+        <v>0.04871</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>0.04887</v>
       </c>
+      <c r="E129" s="1" t="n">
+        <v>0.04871</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2510,6 +2900,9 @@
       <c r="D130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
+      <c r="E130" s="1" t="n">
+        <v>1.24e-05</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2521,11 +2914,14 @@
         <v>7.2e-06</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>7.2e-06</v>
+        <v>7.1e-06</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
+      <c r="E131" s="1" t="n">
+        <v>7.1e-06</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2542,6 +2938,9 @@
       <c r="D132" s="1" t="n">
         <v>0.007</v>
       </c>
+      <c r="E132" s="1" t="n">
+        <v>0.007</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2553,9 +2952,12 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0969</v>
       </c>
       <c r="D133" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="E133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -2569,9 +2971,12 @@
         <v>0.0004099</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>0.0004099</v>
+        <v>0.0004113</v>
       </c>
       <c r="D134" s="1" t="n">
+        <v>0.0004113</v>
+      </c>
+      <c r="E134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -2585,11 +2990,14 @@
         <v>0.08391999999999999</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>0.08391999999999999</v>
+        <v>0.08344</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>0.08391999999999999</v>
       </c>
+      <c r="E135" s="1" t="n">
+        <v>0.08344</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2601,9 +3009,12 @@
         <v>0.007984</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>0.007984</v>
+        <v>0.007990000000000001</v>
       </c>
       <c r="D136" s="1" t="n">
+        <v>0.007990000000000001</v>
+      </c>
+      <c r="E136" s="1" t="n">
         <v>0.007984</v>
       </c>
     </row>
@@ -2617,9 +3028,12 @@
         <v>0.000816</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>0.000816</v>
+        <v>0.0008262</v>
       </c>
       <c r="D137" s="1" t="n">
+        <v>0.0008262</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -2633,9 +3047,12 @@
         <v>0.1483</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>0.1483</v>
+        <v>0.1484</v>
       </c>
       <c r="D138" s="1" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="E138" s="1" t="n">
         <v>0.1483</v>
       </c>
     </row>
@@ -2649,11 +3066,14 @@
         <v>0.006726</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>0.006726</v>
+        <v>0.006725</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>0.006726</v>
       </c>
+      <c r="E139" s="1" t="n">
+        <v>0.006725</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2665,9 +3085,12 @@
         <v>0.01387</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>0.01387</v>
+        <v>0.01389</v>
       </c>
       <c r="D140" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="E140" s="1" t="n">
         <v>0.01387</v>
       </c>
     </row>
@@ -2681,11 +3104,14 @@
         <v>0.09848999999999999</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>0.09848999999999999</v>
+        <v>0.09816</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
+      <c r="E141" s="1" t="n">
+        <v>0.09816</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2697,9 +3123,12 @@
         <v>0.05405</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>0.05405</v>
+        <v>0.05415</v>
       </c>
       <c r="D142" s="1" t="n">
+        <v>0.05415</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -2713,9 +3142,12 @@
         <v>0.3237</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>0.3237</v>
+        <v>0.3241</v>
       </c>
       <c r="D143" s="1" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="E143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -2729,9 +3161,12 @@
         <v>0.02576</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>0.02576</v>
+        <v>0.02586</v>
       </c>
       <c r="D144" s="1" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.02576</v>
       </c>
     </row>
@@ -2745,11 +3180,14 @@
         <v>0.238</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>0.238</v>
+        <v>0.2378</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>0.238</v>
       </c>
+      <c r="E145" s="1" t="n">
+        <v>0.2378</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2761,9 +3199,12 @@
         <v>0.007066</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>0.007066</v>
+        <v>0.0071</v>
       </c>
       <c r="D146" s="1" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="E146" s="1" t="n">
         <v>0.007066</v>
       </c>
     </row>
@@ -2777,9 +3218,12 @@
         <v>0.08695</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>0.08695</v>
+        <v>0.08721</v>
       </c>
       <c r="D147" s="1" t="n">
+        <v>0.08721</v>
+      </c>
+      <c r="E147" s="1" t="n">
         <v>0.08695</v>
       </c>
     </row>
@@ -2793,9 +3237,12 @@
         <v>0.05024</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>0.05024</v>
+        <v>0.05072</v>
       </c>
       <c r="D148" s="1" t="n">
+        <v>0.05072</v>
+      </c>
+      <c r="E148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -2809,11 +3256,14 @@
         <v>0.02394</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>0.02394</v>
+        <v>0.02393</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>0.02394</v>
       </c>
+      <c r="E149" s="1" t="n">
+        <v>0.02393</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2825,9 +3275,12 @@
         <v>0.08646</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>0.08646</v>
+        <v>0.0867</v>
       </c>
       <c r="D150" s="1" t="n">
+        <v>0.0867</v>
+      </c>
+      <c r="E150" s="1" t="n">
         <v>0.08646</v>
       </c>
     </row>
@@ -2841,9 +3294,12 @@
         <v>0.02341</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>0.02341</v>
+        <v>0.02352</v>
       </c>
       <c r="D151" s="1" t="n">
+        <v>0.02352</v>
+      </c>
+      <c r="E151" s="1" t="n">
         <v>0.02341</v>
       </c>
     </row>
@@ -2857,9 +3313,12 @@
         <v>0.02577</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>0.02577</v>
+        <v>0.02586</v>
       </c>
       <c r="D152" s="1" t="n">
+        <v>0.02586</v>
+      </c>
+      <c r="E152" s="1" t="n">
         <v>0.02577</v>
       </c>
     </row>
@@ -2873,11 +3332,14 @@
         <v>0.0002102</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>0.0002102</v>
+        <v>0.0002082</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>0.0002102</v>
       </c>
+      <c r="E153" s="1" t="n">
+        <v>0.0002082</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2889,9 +3351,12 @@
         <v>0.4406</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>0.4406</v>
+        <v>0.4419</v>
       </c>
       <c r="D154" s="1" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="E154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -2905,11 +3370,14 @@
         <v>0.06741999999999999</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>0.06741999999999999</v>
+        <v>0.06714000000000001</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
+      <c r="E155" s="1" t="n">
+        <v>0.06714000000000001</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2921,9 +3389,12 @@
         <v>0.12825</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>0.12825</v>
+        <v>0.12859</v>
       </c>
       <c r="D156" s="1" t="n">
+        <v>0.12859</v>
+      </c>
+      <c r="E156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -2937,9 +3408,12 @@
         <v>0.4844</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>0.4844</v>
+        <v>0.4847</v>
       </c>
       <c r="D157" s="1" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="E157" s="1" t="n">
         <v>0.4844</v>
       </c>
     </row>
@@ -2953,9 +3427,12 @@
         <v>0.4465</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>0.4465</v>
+        <v>0.4479</v>
       </c>
       <c r="D158" s="1" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="E158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -2969,9 +3446,12 @@
         <v>0.007528</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>0.007528</v>
+        <v>0.007557</v>
       </c>
       <c r="D159" s="1" t="n">
+        <v>0.007557</v>
+      </c>
+      <c r="E159" s="1" t="n">
         <v>0.007528</v>
       </c>
     </row>
@@ -2985,9 +3465,12 @@
         <v>0.004628</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>0.004628</v>
+        <v>0.004641</v>
       </c>
       <c r="D160" s="1" t="n">
+        <v>0.004641</v>
+      </c>
+      <c r="E160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -3001,9 +3484,12 @@
         <v>0.004294</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>0.004294</v>
+        <v>0.004306</v>
       </c>
       <c r="D161" s="1" t="n">
+        <v>0.004306</v>
+      </c>
+      <c r="E161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -3017,9 +3503,12 @@
         <v>0.0958</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>0.0958</v>
+        <v>0.0961</v>
       </c>
       <c r="D162" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="E162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -3033,9 +3522,12 @@
         <v>0.2859</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>0.2859</v>
+        <v>0.286</v>
       </c>
       <c r="D163" s="1" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="E163" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -3049,9 +3541,12 @@
         <v>0.1145</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>0.1145</v>
+        <v>0.1148</v>
       </c>
       <c r="D164" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="E164" s="1" t="n">
         <v>0.1145</v>
       </c>
     </row>
@@ -3065,9 +3560,12 @@
         <v>0.1756</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>0.1756</v>
+        <v>0.1758</v>
       </c>
       <c r="D165" s="1" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="E165" s="1" t="n">
         <v>0.1756</v>
       </c>
     </row>
@@ -3081,9 +3579,12 @@
         <v>0.01006</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>0.01006</v>
+        <v>0.01008</v>
       </c>
       <c r="D166" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="E166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -3097,11 +3598,14 @@
         <v>1.829</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>1.829</v>
+        <v>1.827</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>1.829</v>
       </c>
+      <c r="E167" s="1" t="n">
+        <v>1.827</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3113,11 +3617,14 @@
         <v>1.339</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>1.339</v>
+        <v>1.337</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>1.339</v>
       </c>
+      <c r="E168" s="1" t="n">
+        <v>1.337</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3129,9 +3636,12 @@
         <v>0.007321</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>0.007321</v>
+        <v>0.007328</v>
       </c>
       <c r="D169" s="1" t="n">
+        <v>0.007328</v>
+      </c>
+      <c r="E169" s="1" t="n">
         <v>0.007321</v>
       </c>
     </row>
@@ -3145,9 +3655,12 @@
         <v>0.0116</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>0.0116</v>
+        <v>0.0117</v>
       </c>
       <c r="D170" s="1" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="E170" s="1" t="n">
         <v>0.0116</v>
       </c>
     </row>
@@ -3161,9 +3674,12 @@
         <v>0.005796</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>0.005796</v>
+        <v>0.005805</v>
       </c>
       <c r="D171" s="1" t="n">
+        <v>0.005805</v>
+      </c>
+      <c r="E171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -3177,9 +3693,12 @@
         <v>0.14615</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>0.14615</v>
+        <v>0.14704</v>
       </c>
       <c r="D172" s="1" t="n">
+        <v>0.14704</v>
+      </c>
+      <c r="E172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -3193,9 +3712,12 @@
         <v>4.871</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>4.871</v>
+        <v>4.886</v>
       </c>
       <c r="D173" s="1" t="n">
+        <v>4.886</v>
+      </c>
+      <c r="E173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -3209,9 +3731,12 @@
         <v>0.07868</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>0.07868</v>
+        <v>0.07912</v>
       </c>
       <c r="D174" s="1" t="n">
+        <v>0.07912</v>
+      </c>
+      <c r="E174" s="1" t="n">
         <v>0.07868</v>
       </c>
     </row>
@@ -3225,9 +3750,12 @@
         <v>0.007488</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>0.007488</v>
+        <v>0.007513</v>
       </c>
       <c r="D175" s="1" t="n">
+        <v>0.007513</v>
+      </c>
+      <c r="E175" s="1" t="n">
         <v>0.007488</v>
       </c>
     </row>
@@ -3241,11 +3769,14 @@
         <v>0.2023</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>0.2023</v>
+        <v>0.202</v>
       </c>
       <c r="D176" s="1" t="n">
         <v>0.2023</v>
       </c>
+      <c r="E176" s="1" t="n">
+        <v>0.202</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3257,9 +3788,12 @@
         <v>0.05175</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>0.05175</v>
+        <v>0.05187</v>
       </c>
       <c r="D177" s="1" t="n">
+        <v>0.05187</v>
+      </c>
+      <c r="E177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -3273,9 +3807,12 @@
         <v>0.05458</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>0.05458</v>
+        <v>0.05465</v>
       </c>
       <c r="D178" s="1" t="n">
+        <v>0.05465</v>
+      </c>
+      <c r="E178" s="1" t="n">
         <v>0.05458</v>
       </c>
     </row>
@@ -3289,11 +3826,14 @@
         <v>0.02338</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>0.02338</v>
+        <v>0.02332</v>
       </c>
       <c r="D179" s="1" t="n">
         <v>0.02338</v>
       </c>
+      <c r="E179" s="1" t="n">
+        <v>0.02332</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3305,9 +3845,12 @@
         <v>0.694</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>0.694</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="D180" s="1" t="n">
+        <v>0.6951000000000001</v>
+      </c>
+      <c r="E180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -3321,9 +3864,12 @@
         <v>0.0003727</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>0.0003727</v>
+        <v>0.0003731</v>
       </c>
       <c r="D181" s="1" t="n">
+        <v>0.0003731</v>
+      </c>
+      <c r="E181" s="1" t="n">
         <v>0.0003727</v>
       </c>
     </row>
@@ -3337,11 +3883,14 @@
         <v>0.01287</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>0.01287</v>
+        <v>0.01273</v>
       </c>
       <c r="D182" s="1" t="n">
         <v>0.01287</v>
       </c>
+      <c r="E182" s="1" t="n">
+        <v>0.01273</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3353,11 +3902,14 @@
         <v>4.271</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>4.271</v>
+        <v>4.265</v>
       </c>
       <c r="D183" s="1" t="n">
         <v>4.271</v>
       </c>
+      <c r="E183" s="1" t="n">
+        <v>4.265</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3369,9 +3921,12 @@
         <v>0.2382</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>0.2382</v>
+        <v>0.2392</v>
       </c>
       <c r="D184" s="1" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="E184" s="1" t="n">
         <v>0.2382</v>
       </c>
     </row>
@@ -3385,11 +3940,14 @@
         <v>0.03782</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>0.03782</v>
+        <v>0.03769</v>
       </c>
       <c r="D185" s="1" t="n">
         <v>0.03782</v>
       </c>
+      <c r="E185" s="1" t="n">
+        <v>0.03769</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3401,11 +3959,14 @@
         <v>0.11619</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>0.11619</v>
+        <v>0.11591</v>
       </c>
       <c r="D186" s="1" t="n">
         <v>0.11619</v>
       </c>
+      <c r="E186" s="1" t="n">
+        <v>0.11591</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3417,11 +3978,14 @@
         <v>0.009277000000000001</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>0.009277000000000001</v>
+        <v>0.009265000000000001</v>
       </c>
       <c r="D187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
+      <c r="E187" s="1" t="n">
+        <v>0.009265000000000001</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3433,9 +3997,12 @@
         <v>0.0975</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>0.0975</v>
+        <v>0.0977</v>
       </c>
       <c r="D188" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="E188" s="1" t="n">
         <v>0.0975</v>
       </c>
     </row>
@@ -3449,9 +4016,12 @@
         <v>0.02774</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>0.02774</v>
+        <v>0.02801</v>
       </c>
       <c r="D189" s="1" t="n">
+        <v>0.02801</v>
+      </c>
+      <c r="E189" s="1" t="n">
         <v>0.02774</v>
       </c>
     </row>
@@ -3465,11 +4035,14 @@
         <v>0.008840000000000001</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>0.008840000000000001</v>
+        <v>0.00873</v>
       </c>
       <c r="D190" s="1" t="n">
         <v>0.008840000000000001</v>
       </c>
+      <c r="E190" s="1" t="n">
+        <v>0.00873</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3481,9 +4054,12 @@
         <v>0.001949</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>0.001949</v>
+        <v>0.001953</v>
       </c>
       <c r="D191" s="1" t="n">
+        <v>0.001953</v>
+      </c>
+      <c r="E191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -3497,9 +4073,12 @@
         <v>0.1003</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>0.1003</v>
+        <v>0.1005</v>
       </c>
       <c r="D192" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="E192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -3513,9 +4092,12 @@
         <v>0.02325</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>0.02325</v>
+        <v>0.02334</v>
       </c>
       <c r="D193" s="1" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="E193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -3529,9 +4111,12 @@
         <v>0.01349</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>0.01349</v>
+        <v>0.01351</v>
       </c>
       <c r="D194" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="E194" s="1" t="n">
         <v>0.01349</v>
       </c>
     </row>
@@ -3545,9 +4130,12 @@
         <v>0.02103</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>0.02103</v>
+        <v>0.02105</v>
       </c>
       <c r="D195" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="E195" s="1" t="n">
         <v>0.02103</v>
       </c>
     </row>
@@ -3561,9 +4149,12 @@
         <v>0.1698</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>0.1698</v>
+        <v>0.17003</v>
       </c>
       <c r="D196" s="1" t="n">
+        <v>0.17003</v>
+      </c>
+      <c r="E196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -3577,9 +4168,12 @@
         <v>0.007454</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>0.007454</v>
+        <v>0.007482</v>
       </c>
       <c r="D197" s="1" t="n">
+        <v>0.007482</v>
+      </c>
+      <c r="E197" s="1" t="n">
         <v>0.007454</v>
       </c>
     </row>
@@ -3593,9 +4187,12 @@
         <v>0.01904</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>0.01904</v>
+        <v>0.01908</v>
       </c>
       <c r="D198" s="1" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="E198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -3609,11 +4206,14 @@
         <v>0.0164</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>0.0164</v>
+        <v>0.01639</v>
       </c>
       <c r="D199" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="E199" s="1" t="n">
+        <v>0.01639</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3625,9 +4225,12 @@
         <v>0.2966</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>0.2966</v>
+        <v>0.2975</v>
       </c>
       <c r="D200" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="E200" s="1" t="n">
         <v>0.2966</v>
       </c>
     </row>
@@ -3641,9 +4244,12 @@
         <v>0.006231</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>0.006231</v>
+        <v>0.006237</v>
       </c>
       <c r="D201" s="1" t="n">
+        <v>0.006237</v>
+      </c>
+      <c r="E201" s="1" t="n">
         <v>0.006231</v>
       </c>
     </row>
@@ -3657,9 +4263,12 @@
         <v>0.0004448</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>0.0004448</v>
+        <v>0.0004463</v>
       </c>
       <c r="D202" s="1" t="n">
+        <v>0.0004463</v>
+      </c>
+      <c r="E202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -3673,9 +4282,12 @@
         <v>0.007312</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>0.007312</v>
+        <v>0.007344</v>
       </c>
       <c r="D203" s="1" t="n">
+        <v>0.007344</v>
+      </c>
+      <c r="E203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -3689,9 +4301,12 @@
         <v>0.1282</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>0.1282</v>
+        <v>0.1286</v>
       </c>
       <c r="D204" s="1" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="E204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -3705,11 +4320,14 @@
         <v>0.01457</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>0.01457</v>
+        <v>0.01446</v>
       </c>
       <c r="D205" s="1" t="n">
         <v>0.01457</v>
       </c>
+      <c r="E205" s="1" t="n">
+        <v>0.01446</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3721,9 +4339,12 @@
         <v>0.003605</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>0.003605</v>
+        <v>0.00361</v>
       </c>
       <c r="D206" s="1" t="n">
+        <v>0.00361</v>
+      </c>
+      <c r="E206" s="1" t="n">
         <v>0.003605</v>
       </c>
     </row>
@@ -3737,11 +4358,14 @@
         <v>0.05944</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>0.05944</v>
+        <v>0.0594</v>
       </c>
       <c r="D207" s="1" t="n">
         <v>0.05944</v>
       </c>
+      <c r="E207" s="1" t="n">
+        <v>0.0594</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3753,9 +4377,12 @@
         <v>15.35</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>15.35</v>
+        <v>15.4</v>
       </c>
       <c r="D208" s="1" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -3769,11 +4396,14 @@
         <v>5186.2</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>5186.2</v>
+        <v>5185.6</v>
       </c>
       <c r="D209" s="1" t="n">
         <v>5186.2</v>
       </c>
+      <c r="E209" s="1" t="n">
+        <v>5185.6</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3785,9 +4415,12 @@
         <v>0.11988</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>0.11988</v>
+        <v>0.12039</v>
       </c>
       <c r="D210" s="1" t="n">
+        <v>0.12039</v>
+      </c>
+      <c r="E210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -3801,11 +4434,14 @@
         <v>0.1838</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>0.1838</v>
+        <v>0.1832</v>
       </c>
       <c r="D211" s="1" t="n">
         <v>0.1838</v>
       </c>
+      <c r="E211" s="1" t="n">
+        <v>0.1832</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3817,9 +4453,12 @@
         <v>0.0301</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>0.0301</v>
+        <v>0.0302</v>
       </c>
       <c r="D212" s="1" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="E212" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -3833,9 +4472,12 @@
         <v>1.3921</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>1.3921</v>
+        <v>1.3958</v>
       </c>
       <c r="D213" s="1" t="n">
+        <v>1.3958</v>
+      </c>
+      <c r="E213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -3849,11 +4491,14 @@
         <v>0.05661</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>0.05661</v>
+        <v>0.05658</v>
       </c>
       <c r="D214" s="1" t="n">
         <v>0.05661</v>
       </c>
+      <c r="E214" s="1" t="n">
+        <v>0.05658</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3865,9 +4510,12 @@
         <v>0.0437</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>0.0437</v>
+        <v>0.04376</v>
       </c>
       <c r="D215" s="1" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="E215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -3881,11 +4529,14 @@
         <v>0.15121</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>0.15121</v>
+        <v>0.15102</v>
       </c>
       <c r="D216" s="1" t="n">
         <v>0.15121</v>
       </c>
+      <c r="E216" s="1" t="n">
+        <v>0.15102</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3902,6 +4553,9 @@
       <c r="D217" s="1" t="n">
         <v>0.073</v>
       </c>
+      <c r="E217" s="1" t="n">
+        <v>0.073</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3913,9 +4567,12 @@
         <v>0.00266</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>0.00266</v>
+        <v>0.00267</v>
       </c>
       <c r="D218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="E218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -3929,9 +4586,12 @@
         <v>0.01716</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>0.01716</v>
+        <v>0.01721</v>
       </c>
       <c r="D219" s="1" t="n">
+        <v>0.01721</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>0.01716</v>
       </c>
     </row>
@@ -3945,9 +4605,12 @@
         <v>0.05509</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>0.05509</v>
+        <v>0.05524</v>
       </c>
       <c r="D220" s="1" t="n">
+        <v>0.05524</v>
+      </c>
+      <c r="E220" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -3961,9 +4624,12 @@
         <v>0.02182</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>0.02182</v>
+        <v>0.02189</v>
       </c>
       <c r="D221" s="1" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="E221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -3977,9 +4643,12 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.00942</v>
       </c>
       <c r="D222" s="1" t="n">
+        <v>0.00942</v>
+      </c>
+      <c r="E222" s="1" t="n">
         <v>0.009379999999999999</v>
       </c>
     </row>
@@ -3998,6 +4667,9 @@
       <c r="D223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="E223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4009,11 +4681,14 @@
         <v>0.038</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>0.038</v>
+        <v>0.03797</v>
       </c>
       <c r="D224" s="1" t="n">
         <v>0.038</v>
       </c>
+      <c r="E224" s="1" t="n">
+        <v>0.03797</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4025,9 +4700,12 @@
         <v>0.001526</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>0.001526</v>
+        <v>0.001529</v>
       </c>
       <c r="D225" s="1" t="n">
+        <v>0.001529</v>
+      </c>
+      <c r="E225" s="1" t="n">
         <v>0.001526</v>
       </c>
     </row>
@@ -4041,11 +4719,14 @@
         <v>27.12</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>27.12</v>
+        <v>27.1</v>
       </c>
       <c r="D226" s="1" t="n">
         <v>27.12</v>
       </c>
+      <c r="E226" s="1" t="n">
+        <v>27.1</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4057,9 +4738,12 @@
         <v>0.0702</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>0.0702</v>
+        <v>0.07020999999999999</v>
       </c>
       <c r="D227" s="1" t="n">
+        <v>0.07020999999999999</v>
+      </c>
+      <c r="E227" s="1" t="n">
         <v>0.0702</v>
       </c>
     </row>
@@ -4073,9 +4757,12 @@
         <v>0.3111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>0.3111</v>
+        <v>0.3131</v>
       </c>
       <c r="D228" s="1" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="E228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -4089,9 +4776,12 @@
         <v>18.42</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>18.42</v>
+        <v>18.46</v>
       </c>
       <c r="D229" s="1" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="E229" s="1" t="n">
         <v>18.42</v>
       </c>
     </row>
@@ -4105,9 +4795,12 @@
         <v>0.01947</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>0.01947</v>
+        <v>0.01952</v>
       </c>
       <c r="D230" s="1" t="n">
+        <v>0.01952</v>
+      </c>
+      <c r="E230" s="1" t="n">
         <v>0.01947</v>
       </c>
     </row>
@@ -4121,9 +4814,12 @@
         <v>0.01221</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>0.01221</v>
+        <v>0.01222</v>
       </c>
       <c r="D231" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="E231" s="1" t="n">
         <v>0.01221</v>
       </c>
     </row>
@@ -4137,9 +4833,12 @@
         <v>0.2285</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>0.2285</v>
+        <v>0.229</v>
       </c>
       <c r="D232" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="E232" s="1" t="n">
         <v>0.2285</v>
       </c>
     </row>
@@ -4153,9 +4852,12 @@
         <v>0.07113999999999999</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>0.07113999999999999</v>
+        <v>0.07124999999999999</v>
       </c>
       <c r="D233" s="1" t="n">
+        <v>0.07124999999999999</v>
+      </c>
+      <c r="E233" s="1" t="n">
         <v>0.07113999999999999</v>
       </c>
     </row>
@@ -4169,9 +4871,12 @@
         <v>0.1701</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>0.1701</v>
+        <v>0.1704</v>
       </c>
       <c r="D234" s="1" t="n">
+        <v>0.1704</v>
+      </c>
+      <c r="E234" s="1" t="n">
         <v>0.1701</v>
       </c>
     </row>
@@ -4185,9 +4890,12 @@
         <v>0.0252</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>0.0252</v>
+        <v>0.0253</v>
       </c>
       <c r="D235" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="E235" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -4206,6 +4914,9 @@
       <c r="D236" s="1" t="n">
         <v>0.03006</v>
       </c>
+      <c r="E236" s="1" t="n">
+        <v>0.03006</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4217,9 +4928,12 @@
         <v>1.984</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>1.984</v>
+        <v>1.987</v>
       </c>
       <c r="D237" s="1" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="E237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -4233,11 +4947,14 @@
         <v>0.4281</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>0.4281</v>
+        <v>0.4268</v>
       </c>
       <c r="D238" s="1" t="n">
         <v>0.4281</v>
       </c>
+      <c r="E238" s="1" t="n">
+        <v>0.4268</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4249,11 +4966,14 @@
         <v>0.03376</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>0.03376</v>
+        <v>0.03367</v>
       </c>
       <c r="D239" s="1" t="n">
         <v>0.03376</v>
       </c>
+      <c r="E239" s="1" t="n">
+        <v>0.03367</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4265,9 +4985,12 @@
         <v>0.0338</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>0.0338</v>
+        <v>0.03391</v>
       </c>
       <c r="D240" s="1" t="n">
+        <v>0.03391</v>
+      </c>
+      <c r="E240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -4286,6 +5009,9 @@
       <c r="D241" s="1" t="n">
         <v>0.0007509</v>
       </c>
+      <c r="E241" s="1" t="n">
+        <v>0.0007509</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4297,9 +5023,12 @@
         <v>0.1829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>0.1829</v>
+        <v>0.1834</v>
       </c>
       <c r="D242" s="1" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="E242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -4313,9 +5042,12 @@
         <v>0.014827</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>0.014827</v>
+        <v>0.014839</v>
       </c>
       <c r="D243" s="1" t="n">
+        <v>0.014839</v>
+      </c>
+      <c r="E243" s="1" t="n">
         <v>0.014827</v>
       </c>
     </row>
@@ -4329,9 +5061,12 @@
         <v>3.08e-05</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>3.08e-05</v>
+        <v>3.09e-05</v>
       </c>
       <c r="D244" s="1" t="n">
+        <v>3.09e-05</v>
+      </c>
+      <c r="E244" s="1" t="n">
         <v>3.08e-05</v>
       </c>
     </row>
@@ -4345,9 +5080,12 @@
         <v>0.03521</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>0.03521</v>
+        <v>0.03543</v>
       </c>
       <c r="D245" s="1" t="n">
+        <v>0.03543</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>0.03521</v>
       </c>
     </row>
@@ -4361,11 +5099,14 @@
         <v>0.08046</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>0.08046</v>
+        <v>0.08039</v>
       </c>
       <c r="D246" s="1" t="n">
         <v>0.08046</v>
       </c>
+      <c r="E246" s="1" t="n">
+        <v>0.08039</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4377,9 +5118,12 @@
         <v>0.007518</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>0.007518</v>
+        <v>0.007522</v>
       </c>
       <c r="D247" s="1" t="n">
+        <v>0.007522</v>
+      </c>
+      <c r="E247" s="1" t="n">
         <v>0.007518</v>
       </c>
     </row>
@@ -4393,11 +5137,14 @@
         <v>0.09798999999999999</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>0.09798999999999999</v>
+        <v>0.09717000000000001</v>
       </c>
       <c r="D248" s="1" t="n">
         <v>0.09798999999999999</v>
       </c>
+      <c r="E248" s="1" t="n">
+        <v>0.09717000000000001</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4409,11 +5156,14 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
+      <c r="E249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4425,9 +5175,12 @@
         <v>0.03504</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>0.03504</v>
+        <v>0.0351</v>
       </c>
       <c r="D250" s="1" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="E250" s="1" t="n">
         <v>0.03504</v>
       </c>
     </row>
@@ -4441,9 +5194,12 @@
         <v>0.04058</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>0.04058</v>
+        <v>0.04079</v>
       </c>
       <c r="D251" s="1" t="n">
+        <v>0.04079</v>
+      </c>
+      <c r="E251" s="1" t="n">
         <v>0.04058</v>
       </c>
     </row>
@@ -4457,9 +5213,12 @@
         <v>0.0891</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>0.0891</v>
+        <v>0.0893</v>
       </c>
       <c r="D252" s="1" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="E252" s="1" t="n">
         <v>0.0891</v>
       </c>
     </row>
@@ -4473,9 +5232,12 @@
         <v>4.058</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>4.058</v>
+        <v>4.071</v>
       </c>
       <c r="D253" s="1" t="n">
+        <v>4.071</v>
+      </c>
+      <c r="E253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -4489,9 +5251,12 @@
         <v>0.1866</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>0.1866</v>
+        <v>0.1872</v>
       </c>
       <c r="D254" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="E254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -4505,9 +5270,12 @@
         <v>0.07278</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>0.07278</v>
+        <v>0.07283000000000001</v>
       </c>
       <c r="D255" s="1" t="n">
+        <v>0.07283000000000001</v>
+      </c>
+      <c r="E255" s="1" t="n">
         <v>0.07278</v>
       </c>
     </row>
@@ -4521,11 +5289,14 @@
         <v>0.01817</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>0.01817</v>
+        <v>0.01816</v>
       </c>
       <c r="D256" s="1" t="n">
         <v>0.01817</v>
       </c>
+      <c r="E256" s="1" t="n">
+        <v>0.01816</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4537,9 +5308,12 @@
         <v>5.942</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>5.942</v>
+        <v>5.956</v>
       </c>
       <c r="D257" s="1" t="n">
+        <v>5.956</v>
+      </c>
+      <c r="E257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -4553,9 +5327,12 @@
         <v>0.2617</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>0.2617</v>
+        <v>0.2639</v>
       </c>
       <c r="D258" s="1" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="E258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -4569,9 +5346,12 @@
         <v>0.1361</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>0.1361</v>
+        <v>0.1364</v>
       </c>
       <c r="D259" s="1" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="E259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -4585,11 +5365,14 @@
         <v>0.30595</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>0.30595</v>
+        <v>0.30555</v>
       </c>
       <c r="D260" s="1" t="n">
         <v>0.30595</v>
       </c>
+      <c r="E260" s="1" t="n">
+        <v>0.30555</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -4601,11 +5384,14 @@
         <v>0.09809</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>0.09809</v>
+        <v>0.09787</v>
       </c>
       <c r="D261" s="1" t="n">
         <v>0.09809</v>
       </c>
+      <c r="E261" s="1" t="n">
+        <v>0.09787</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4617,9 +5403,12 @@
         <v>0.5409</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>0.5409</v>
+        <v>0.5422</v>
       </c>
       <c r="D262" s="1" t="n">
+        <v>0.5422</v>
+      </c>
+      <c r="E262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -4633,9 +5422,12 @@
         <v>0.2923</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>0.2923</v>
+        <v>0.293</v>
       </c>
       <c r="D263" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="E263" s="1" t="n">
         <v>0.2923</v>
       </c>
     </row>
@@ -4649,9 +5441,12 @@
         <v>0.948</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="D264" s="1" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="E264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -4665,9 +5460,12 @@
         <v>0.5427999999999999</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5431</v>
       </c>
       <c r="D265" s="1" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="E265" s="1" t="n">
         <v>0.5427999999999999</v>
       </c>
     </row>
@@ -4681,9 +5479,12 @@
         <v>0.07371</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>0.07371</v>
+        <v>0.07381</v>
       </c>
       <c r="D266" s="1" t="n">
+        <v>0.07381</v>
+      </c>
+      <c r="E266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -4697,11 +5498,14 @@
         <v>0.0213</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>0.0213</v>
+        <v>0.02127</v>
       </c>
       <c r="D267" s="1" t="n">
         <v>0.0213</v>
       </c>
+      <c r="E267" s="1" t="n">
+        <v>0.02127</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4713,9 +5517,12 @@
         <v>0.01606</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>0.01606</v>
+        <v>0.01622</v>
       </c>
       <c r="D268" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -4729,11 +5536,14 @@
         <v>0.003717</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>0.003717</v>
+        <v>0.003715</v>
       </c>
       <c r="D269" s="1" t="n">
         <v>0.003717</v>
       </c>
+      <c r="E269" s="1" t="n">
+        <v>0.003715</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -4745,11 +5555,14 @@
         <v>0.00787</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>0.00787</v>
+        <v>0.0078</v>
       </c>
       <c r="D270" s="1" t="n">
         <v>0.00787</v>
       </c>
+      <c r="E270" s="1" t="n">
+        <v>0.0078</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4761,9 +5574,12 @@
         <v>0.05495</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>0.05495</v>
+        <v>0.05509</v>
       </c>
       <c r="D271" s="1" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="E271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -4782,6 +5598,9 @@
       <c r="D272" s="1" t="n">
         <v>2.3</v>
       </c>
+      <c r="E272" s="1" t="n">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -4793,9 +5612,12 @@
         <v>0.05431</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>0.05431</v>
+        <v>0.05452</v>
       </c>
       <c r="D273" s="1" t="n">
+        <v>0.05452</v>
+      </c>
+      <c r="E273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -4809,9 +5631,12 @@
         <v>0.02286</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>0.02286</v>
+        <v>0.02289</v>
       </c>
       <c r="D274" s="1" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="E274" s="1" t="n">
         <v>0.02286</v>
       </c>
     </row>
@@ -4825,9 +5650,12 @@
         <v>1.185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>1.185</v>
+        <v>1.19</v>
       </c>
       <c r="D275" s="1" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E275" s="1" t="n">
         <v>1.185</v>
       </c>
     </row>
@@ -4841,9 +5669,12 @@
         <v>0.2728</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>0.2728</v>
+        <v>0.2731</v>
       </c>
       <c r="D276" s="1" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="E276" s="1" t="n">
         <v>0.2728</v>
       </c>
     </row>
@@ -4857,9 +5688,12 @@
         <v>0.953</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>0.953</v>
+        <v>0.956</v>
       </c>
       <c r="D277" s="1" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="E277" s="1" t="n">
         <v>0.953</v>
       </c>
     </row>
@@ -4873,9 +5707,12 @@
         <v>0.6228</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>0.6228</v>
+        <v>0.6248</v>
       </c>
       <c r="D278" s="1" t="n">
+        <v>0.6248</v>
+      </c>
+      <c r="E278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -4894,6 +5731,9 @@
       <c r="D279" s="1" t="n">
         <v>0.00135</v>
       </c>
+      <c r="E279" s="1" t="n">
+        <v>0.00135</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4905,9 +5745,12 @@
         <v>0.00554</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>0.00554</v>
+        <v>0.005551</v>
       </c>
       <c r="D280" s="1" t="n">
+        <v>0.005551</v>
+      </c>
+      <c r="E280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -4921,9 +5764,12 @@
         <v>1.522</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>1.522</v>
+        <v>1.525</v>
       </c>
       <c r="D281" s="1" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="E281" s="1" t="n">
         <v>1.522</v>
       </c>
     </row>
@@ -4937,9 +5783,12 @@
         <v>28.36</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>28.36</v>
+        <v>28.47</v>
       </c>
       <c r="D282" s="1" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="E282" s="1" t="n">
         <v>28.36</v>
       </c>
     </row>
@@ -4953,9 +5802,12 @@
         <v>0.12935</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>0.12935</v>
+        <v>0.12939</v>
       </c>
       <c r="D283" s="1" t="n">
+        <v>0.12939</v>
+      </c>
+      <c r="E283" s="1" t="n">
         <v>0.12935</v>
       </c>
     </row>
@@ -4969,9 +5821,12 @@
         <v>0.01111</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>0.01111</v>
+        <v>0.01113</v>
       </c>
       <c r="D284" s="1" t="n">
+        <v>0.01113</v>
+      </c>
+      <c r="E284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -4985,9 +5840,12 @@
         <v>6.487</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>6.487</v>
+        <v>6.501</v>
       </c>
       <c r="D285" s="1" t="n">
+        <v>6.501</v>
+      </c>
+      <c r="E285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -5001,11 +5859,14 @@
         <v>0.01849</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>0.01849</v>
+        <v>0.01848</v>
       </c>
       <c r="D286" s="1" t="n">
         <v>0.01849</v>
       </c>
+      <c r="E286" s="1" t="n">
+        <v>0.01848</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5017,9 +5878,12 @@
         <v>0.008477</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>0.008477</v>
+        <v>0.008486</v>
       </c>
       <c r="D287" s="1" t="n">
+        <v>0.008486</v>
+      </c>
+      <c r="E287" s="1" t="n">
         <v>0.008477</v>
       </c>
     </row>
@@ -5033,11 +5897,14 @@
         <v>0.3929</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>0.3929</v>
+        <v>0.3917</v>
       </c>
       <c r="D288" s="1" t="n">
         <v>0.3929</v>
       </c>
+      <c r="E288" s="1" t="n">
+        <v>0.3917</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5049,9 +5916,12 @@
         <v>0.010535</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>0.010535</v>
+        <v>0.010539</v>
       </c>
       <c r="D289" s="1" t="n">
+        <v>0.010539</v>
+      </c>
+      <c r="E289" s="1" t="n">
         <v>0.010535</v>
       </c>
     </row>
@@ -5065,9 +5935,12 @@
         <v>0.02613</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>0.02613</v>
+        <v>0.0262</v>
       </c>
       <c r="D290" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="E290" s="1" t="n">
         <v>0.02613</v>
       </c>
     </row>
@@ -5081,9 +5954,12 @@
         <v>0.096</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="D291" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -5097,9 +5973,12 @@
         <v>0.28585</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>0.28585</v>
+        <v>0.2861</v>
       </c>
       <c r="D292" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="E292" s="1" t="n">
         <v>0.28585</v>
       </c>
     </row>
@@ -5113,9 +5992,12 @@
         <v>0.01533</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>0.01533</v>
+        <v>0.01548</v>
       </c>
       <c r="D293" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="E293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -5129,9 +6011,12 @@
         <v>0.003412</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>0.003412</v>
+        <v>0.003416</v>
       </c>
       <c r="D294" s="1" t="n">
+        <v>0.003416</v>
+      </c>
+      <c r="E294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -5145,9 +6030,12 @@
         <v>0.043493</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>0.043493</v>
+        <v>0.043723</v>
       </c>
       <c r="D295" s="1" t="n">
+        <v>0.043723</v>
+      </c>
+      <c r="E295" s="1" t="n">
         <v>0.043493</v>
       </c>
     </row>
@@ -5161,9 +6049,12 @@
         <v>0.02953</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>0.02953</v>
+        <v>0.03007</v>
       </c>
       <c r="D296" s="1" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="E296" s="1" t="n">
         <v>0.02953</v>
       </c>
     </row>
@@ -5177,11 +6068,14 @@
         <v>0.0401</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>0.0401</v>
+        <v>0.03983</v>
       </c>
       <c r="D297" s="1" t="n">
         <v>0.0401</v>
       </c>
+      <c r="E297" s="1" t="n">
+        <v>0.03983</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5193,9 +6087,12 @@
         <v>0.08326</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>0.08326</v>
+        <v>0.08359</v>
       </c>
       <c r="D298" s="1" t="n">
+        <v>0.08359</v>
+      </c>
+      <c r="E298" s="1" t="n">
         <v>0.08326</v>
       </c>
     </row>
@@ -5209,9 +6106,12 @@
         <v>0.00762</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>0.00762</v>
+        <v>0.00764</v>
       </c>
       <c r="D299" s="1" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="E299" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -5225,9 +6125,12 @@
         <v>0.01519</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>0.01519</v>
+        <v>0.01524</v>
       </c>
       <c r="D300" s="1" t="n">
+        <v>0.01524</v>
+      </c>
+      <c r="E300" s="1" t="n">
         <v>0.01519</v>
       </c>
     </row>
@@ -5241,9 +6144,12 @@
         <v>0.1416</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>0.1416</v>
+        <v>0.142</v>
       </c>
       <c r="D301" s="1" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E301" s="1" t="n">
         <v>0.1416</v>
       </c>
     </row>
@@ -5257,11 +6163,14 @@
         <v>0.0006538</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>0.0006538</v>
+        <v>0.0006511000000000001</v>
       </c>
       <c r="D302" s="1" t="n">
         <v>0.0006538</v>
       </c>
+      <c r="E302" s="1" t="n">
+        <v>0.0006511000000000001</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5273,9 +6182,12 @@
         <v>0.0621</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>0.0621</v>
+        <v>0.06235</v>
       </c>
       <c r="D303" s="1" t="n">
+        <v>0.06235</v>
+      </c>
+      <c r="E303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -5289,9 +6201,12 @@
         <v>0.0001634</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>0.0001634</v>
+        <v>0.0001639</v>
       </c>
       <c r="D304" s="1" t="n">
+        <v>0.0001639</v>
+      </c>
+      <c r="E304" s="1" t="n">
         <v>0.0001634</v>
       </c>
     </row>
@@ -5305,9 +6220,12 @@
         <v>0.06086</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>0.06086</v>
+        <v>0.0609</v>
       </c>
       <c r="D305" s="1" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="E305" s="1" t="n">
         <v>0.06086</v>
       </c>
     </row>
@@ -5321,9 +6239,12 @@
         <v>0.02265</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>0.02265</v>
+        <v>0.022667</v>
       </c>
       <c r="D306" s="1" t="n">
+        <v>0.022667</v>
+      </c>
+      <c r="E306" s="1" t="n">
         <v>0.02265</v>
       </c>
     </row>
@@ -5337,9 +6258,12 @@
         <v>0.02388</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>0.02388</v>
+        <v>0.02414</v>
       </c>
       <c r="D307" s="1" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="E307" s="1" t="n">
         <v>0.02388</v>
       </c>
     </row>
@@ -5358,6 +6282,9 @@
       <c r="D308" s="1" t="n">
         <v>0.000411</v>
       </c>
+      <c r="E308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5369,11 +6296,14 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0898</v>
       </c>
       <c r="D309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
+      <c r="E309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5385,9 +6315,12 @@
         <v>0.387</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>0.387</v>
+        <v>0.3882</v>
       </c>
       <c r="D310" s="1" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="E310" s="1" t="n">
         <v>0.387</v>
       </c>
     </row>
@@ -5406,6 +6339,9 @@
       <c r="D311" s="1" t="n">
         <v>0.0357</v>
       </c>
+      <c r="E311" s="1" t="n">
+        <v>0.0357</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5422,6 +6358,9 @@
       <c r="D312" s="1" t="n">
         <v>0.02445</v>
       </c>
+      <c r="E312" s="1" t="n">
+        <v>0.02445</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -5433,9 +6372,12 @@
         <v>0.04143</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>0.04143</v>
+        <v>0.04147</v>
       </c>
       <c r="D313" s="1" t="n">
+        <v>0.04147</v>
+      </c>
+      <c r="E313" s="1" t="n">
         <v>0.04143</v>
       </c>
     </row>
@@ -5449,9 +6391,12 @@
         <v>3.998</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>3.998</v>
+        <v>4.009</v>
       </c>
       <c r="D314" s="1" t="n">
+        <v>4.009</v>
+      </c>
+      <c r="E314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -5465,9 +6410,12 @@
         <v>0.1595</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>0.1595</v>
+        <v>0.1601</v>
       </c>
       <c r="D315" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="E315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -5481,11 +6429,14 @@
         <v>0.08852</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>0.08852</v>
+        <v>0.08825</v>
       </c>
       <c r="D316" s="1" t="n">
         <v>0.08852</v>
       </c>
+      <c r="E316" s="1" t="n">
+        <v>0.08825</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5497,11 +6448,14 @@
         <v>0.06827999999999999</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>0.06827999999999999</v>
+        <v>0.06814000000000001</v>
       </c>
       <c r="D317" s="1" t="n">
         <v>0.06827999999999999</v>
       </c>
+      <c r="E317" s="1" t="n">
+        <v>0.06814000000000001</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -5513,11 +6467,14 @@
         <v>0.01272</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>0.01272</v>
+        <v>0.012661</v>
       </c>
       <c r="D318" s="1" t="n">
         <v>0.01272</v>
       </c>
+      <c r="E318" s="1" t="n">
+        <v>0.012661</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -5534,6 +6491,9 @@
       <c r="D319" s="1" t="n">
         <v>0.001135</v>
       </c>
+      <c r="E319" s="1" t="n">
+        <v>0.001135</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5550,6 +6510,9 @@
       <c r="D320" s="1" t="n">
         <v>0.063</v>
       </c>
+      <c r="E320" s="1" t="n">
+        <v>0.063</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5561,9 +6524,12 @@
         <v>0.00523</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>0.00523</v>
+        <v>0.00524</v>
       </c>
       <c r="D321" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="E321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -5577,11 +6543,14 @@
         <v>0.1116</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>0.1116</v>
+        <v>0.1115</v>
       </c>
       <c r="D322" s="1" t="n">
         <v>0.1116</v>
       </c>
+      <c r="E322" s="1" t="n">
+        <v>0.1115</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5593,9 +6562,12 @@
         <v>0.04171</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>0.04171</v>
+        <v>0.04225</v>
       </c>
       <c r="D323" s="1" t="n">
+        <v>0.04225</v>
+      </c>
+      <c r="E323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -5609,9 +6581,12 @@
         <v>0.01768</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>0.01768</v>
+        <v>0.01777</v>
       </c>
       <c r="D324" s="1" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="E324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -5625,11 +6600,14 @@
         <v>0.005695</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>0.005695</v>
+        <v>0.00569</v>
       </c>
       <c r="D325" s="1" t="n">
         <v>0.005695</v>
       </c>
+      <c r="E325" s="1" t="n">
+        <v>0.00569</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5641,9 +6619,12 @@
         <v>0.001771</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>0.001771</v>
+        <v>0.001779</v>
       </c>
       <c r="D326" s="1" t="n">
+        <v>0.001779</v>
+      </c>
+      <c r="E326" s="1" t="n">
         <v>0.001771</v>
       </c>
     </row>
@@ -5657,9 +6638,12 @@
         <v>0.04076</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>0.04076</v>
+        <v>0.04083</v>
       </c>
       <c r="D327" s="1" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="E327" s="1" t="n">
         <v>0.04076</v>
       </c>
     </row>
@@ -5673,11 +6657,14 @@
         <v>0.053964</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>0.053964</v>
+        <v>0.05395</v>
       </c>
       <c r="D328" s="1" t="n">
         <v>0.053964</v>
       </c>
+      <c r="E328" s="1" t="n">
+        <v>0.05395</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -5689,9 +6676,12 @@
         <v>0.2779</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>0.2779</v>
+        <v>0.2789</v>
       </c>
       <c r="D329" s="1" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="E329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -5705,9 +6695,12 @@
         <v>0.1593</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>0.1593</v>
+        <v>0.1599</v>
       </c>
       <c r="D330" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="E330" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -5721,9 +6714,12 @@
         <v>0.05348</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>0.05348</v>
+        <v>0.05356</v>
       </c>
       <c r="D331" s="1" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="E331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -5737,9 +6733,12 @@
         <v>0.3594</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>0.3594</v>
+        <v>0.3607</v>
       </c>
       <c r="D332" s="1" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="E332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -5753,9 +6752,12 @@
         <v>0.03041</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>0.03041</v>
+        <v>0.03046</v>
       </c>
       <c r="D333" s="1" t="n">
+        <v>0.03046</v>
+      </c>
+      <c r="E333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -5769,9 +6771,12 @@
         <v>0.01756</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>0.01756</v>
+        <v>0.01766</v>
       </c>
       <c r="D334" s="1" t="n">
+        <v>0.01766</v>
+      </c>
+      <c r="E334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -5785,9 +6790,12 @@
         <v>0.0574</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>0.0574</v>
+        <v>0.0577</v>
       </c>
       <c r="D335" s="1" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="E335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -5801,9 +6809,12 @@
         <v>0.09117</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>0.09117</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="D336" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="E336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -5817,11 +6828,14 @@
         <v>0.17619</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>0.17619</v>
+        <v>0.17441</v>
       </c>
       <c r="D337" s="1" t="n">
         <v>0.17619</v>
       </c>
+      <c r="E337" s="1" t="n">
+        <v>0.17441</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -5833,11 +6847,14 @@
         <v>0.02135</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>0.02135</v>
+        <v>0.02134</v>
       </c>
       <c r="D338" s="1" t="n">
         <v>0.02135</v>
       </c>
+      <c r="E338" s="1" t="n">
+        <v>0.02134</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -5849,9 +6866,12 @@
         <v>0.1313</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>0.1313</v>
+        <v>0.1315</v>
       </c>
       <c r="D339" s="1" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="E339" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -5865,9 +6885,12 @@
         <v>0.008108000000000001</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>0.008108000000000001</v>
+        <v>0.008114</v>
       </c>
       <c r="D340" s="1" t="n">
+        <v>0.008114</v>
+      </c>
+      <c r="E340" s="1" t="n">
         <v>0.008108000000000001</v>
       </c>
     </row>
@@ -5881,9 +6904,12 @@
         <v>4.382</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>4.382</v>
+        <v>4.393</v>
       </c>
       <c r="D341" s="1" t="n">
+        <v>4.393</v>
+      </c>
+      <c r="E341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -5897,9 +6923,12 @@
         <v>0.19148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>0.19148</v>
+        <v>0.19353</v>
       </c>
       <c r="D342" s="1" t="n">
+        <v>0.19353</v>
+      </c>
+      <c r="E342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -5913,9 +6942,12 @@
         <v>0.08266999999999999</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>0.08266999999999999</v>
+        <v>0.08291999999999999</v>
       </c>
       <c r="D343" s="1" t="n">
+        <v>0.08291999999999999</v>
+      </c>
+      <c r="E343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -5929,9 +6961,12 @@
         <v>0.1829</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>0.1829</v>
+        <v>0.183</v>
       </c>
       <c r="D344" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="E344" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -5945,9 +6980,12 @@
         <v>0.003245</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>0.003245</v>
+        <v>0.00325</v>
       </c>
       <c r="D345" s="1" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="E345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -5961,9 +6999,12 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.09085</v>
       </c>
       <c r="D346" s="1" t="n">
+        <v>0.09085</v>
+      </c>
+      <c r="E346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -5977,9 +7018,12 @@
         <v>2.254</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>2.254</v>
+        <v>2.258</v>
       </c>
       <c r="D347" s="1" t="n">
+        <v>2.258</v>
+      </c>
+      <c r="E347" s="1" t="n">
         <v>2.254</v>
       </c>
     </row>
@@ -5993,11 +7037,14 @@
         <v>0.304</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>0.304</v>
+        <v>0.3038</v>
       </c>
       <c r="D348" s="1" t="n">
         <v>0.304</v>
       </c>
+      <c r="E348" s="1" t="n">
+        <v>0.3038</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6009,11 +7056,14 @@
         <v>0.02991</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>0.02991</v>
+        <v>0.02987</v>
       </c>
       <c r="D349" s="1" t="n">
         <v>0.02991</v>
       </c>
+      <c r="E349" s="1" t="n">
+        <v>0.02987</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6025,9 +7075,12 @@
         <v>0.1271</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>0.1271</v>
+        <v>0.1277</v>
       </c>
       <c r="D350" s="1" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="E350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -6041,9 +7094,12 @@
         <v>0.06689000000000001</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>0.06689000000000001</v>
+        <v>0.06696000000000001</v>
       </c>
       <c r="D351" s="1" t="n">
+        <v>0.06696000000000001</v>
+      </c>
+      <c r="E351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -6057,9 +7113,12 @@
         <v>0.06236</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>0.06236</v>
+        <v>0.06244</v>
       </c>
       <c r="D352" s="1" t="n">
+        <v>0.06244</v>
+      </c>
+      <c r="E352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -6073,9 +7132,12 @@
         <v>0.06375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>0.06375</v>
+        <v>0.06387</v>
       </c>
       <c r="D353" s="1" t="n">
+        <v>0.06387</v>
+      </c>
+      <c r="E353" s="1" t="n">
         <v>0.06375</v>
       </c>
     </row>
@@ -6089,9 +7151,12 @@
         <v>0.10405</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>0.10405</v>
+        <v>0.10433</v>
       </c>
       <c r="D354" s="1" t="n">
+        <v>0.10433</v>
+      </c>
+      <c r="E354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -6105,9 +7170,12 @@
         <v>0.0901</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>0.0901</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="D355" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="E355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -6121,9 +7189,12 @@
         <v>0.07036000000000001</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>0.07036000000000001</v>
+        <v>0.07054000000000001</v>
       </c>
       <c r="D356" s="1" t="n">
+        <v>0.07054000000000001</v>
+      </c>
+      <c r="E356" s="1" t="n">
         <v>0.07036000000000001</v>
       </c>
     </row>
@@ -6137,9 +7208,12 @@
         <v>0.4523</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>0.4523</v>
+        <v>0.4541</v>
       </c>
       <c r="D357" s="1" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="E357" s="1" t="n">
         <v>0.4523</v>
       </c>
     </row>
@@ -6153,9 +7227,12 @@
         <v>0.03517</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>0.03517</v>
+        <v>0.03527</v>
       </c>
       <c r="D358" s="1" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="E358" s="1" t="n">
         <v>0.03517</v>
       </c>
     </row>
@@ -6169,9 +7246,12 @@
         <v>0.01476</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>0.01476</v>
+        <v>0.01481</v>
       </c>
       <c r="D359" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="E359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -6185,11 +7265,14 @@
         <v>0.13306</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>0.13306</v>
+        <v>0.13283</v>
       </c>
       <c r="D360" s="1" t="n">
         <v>0.13306</v>
       </c>
+      <c r="E360" s="1" t="n">
+        <v>0.13283</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6201,9 +7284,12 @@
         <v>0.0005848</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>0.0005848</v>
+        <v>0.000587</v>
       </c>
       <c r="D361" s="1" t="n">
+        <v>0.000587</v>
+      </c>
+      <c r="E361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -6217,11 +7303,14 @@
         <v>0.03893</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>0.03893</v>
+        <v>0.03878</v>
       </c>
       <c r="D362" s="1" t="n">
         <v>0.03893</v>
       </c>
+      <c r="E362" s="1" t="n">
+        <v>0.03878</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6233,11 +7322,14 @@
         <v>3.223</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>3.223</v>
+        <v>3.214</v>
       </c>
       <c r="D363" s="1" t="n">
         <v>3.223</v>
       </c>
+      <c r="E363" s="1" t="n">
+        <v>3.214</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6249,9 +7341,12 @@
         <v>0.1657</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>0.1657</v>
+        <v>0.1663</v>
       </c>
       <c r="D364" s="1" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="E364" s="1" t="n">
         <v>0.1657</v>
       </c>
     </row>
@@ -6265,9 +7360,12 @@
         <v>0.1129</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>0.1129</v>
+        <v>0.1133</v>
       </c>
       <c r="D365" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="E365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -6281,9 +7379,12 @@
         <v>0.0006419</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>0.0006419</v>
+        <v>0.0006434</v>
       </c>
       <c r="D366" s="1" t="n">
+        <v>0.0006434</v>
+      </c>
+      <c r="E366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -6297,9 +7398,12 @@
         <v>0.05956</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>0.05956</v>
+        <v>0.05961</v>
       </c>
       <c r="D367" s="1" t="n">
+        <v>0.05961</v>
+      </c>
+      <c r="E367" s="1" t="n">
         <v>0.05956</v>
       </c>
     </row>
@@ -6313,9 +7417,12 @@
         <v>0.0825</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>0.0825</v>
+        <v>0.08289000000000001</v>
       </c>
       <c r="D368" s="1" t="n">
+        <v>0.08289000000000001</v>
+      </c>
+      <c r="E368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -6329,9 +7436,12 @@
         <v>0.03979</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>0.03979</v>
+        <v>0.0398</v>
       </c>
       <c r="D369" s="1" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="E369" s="1" t="n">
         <v>0.03979</v>
       </c>
     </row>
@@ -6345,11 +7455,14 @@
         <v>3.727</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>3.727</v>
+        <v>3.709</v>
       </c>
       <c r="D370" s="1" t="n">
         <v>3.727</v>
       </c>
+      <c r="E370" s="1" t="n">
+        <v>3.709</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -6361,9 +7474,12 @@
         <v>0.1226</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>0.1226</v>
+        <v>0.1227</v>
       </c>
       <c r="D371" s="1" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="E371" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -6377,9 +7493,12 @@
         <v>0.01471</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>0.01471</v>
+        <v>0.01473</v>
       </c>
       <c r="D372" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="E372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -6393,9 +7512,12 @@
         <v>0.02197</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>0.02197</v>
+        <v>0.02205</v>
       </c>
       <c r="D373" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="E373" s="1" t="n">
         <v>0.02197</v>
       </c>
     </row>
@@ -6409,9 +7531,12 @@
         <v>1.8539</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>1.8539</v>
+        <v>1.8584</v>
       </c>
       <c r="D374" s="1" t="n">
+        <v>1.8584</v>
+      </c>
+      <c r="E374" s="1" t="n">
         <v>1.8539</v>
       </c>
     </row>
@@ -6425,9 +7550,12 @@
         <v>0.02095</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>0.02095</v>
+        <v>0.02106</v>
       </c>
       <c r="D375" s="1" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="E375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -6441,9 +7569,12 @@
         <v>1.296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>1.296</v>
+        <v>1.301</v>
       </c>
       <c r="D376" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="E376" s="1" t="n">
         <v>1.296</v>
       </c>
     </row>
@@ -6457,11 +7588,14 @@
         <v>0.2845</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>0.2845</v>
+        <v>0.2837</v>
       </c>
       <c r="D377" s="1" t="n">
         <v>0.2845</v>
       </c>
+      <c r="E377" s="1" t="n">
+        <v>0.2837</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6473,11 +7607,14 @@
         <v>0.01573</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>0.01573</v>
+        <v>0.01567</v>
       </c>
       <c r="D378" s="1" t="n">
         <v>0.01573</v>
       </c>
+      <c r="E378" s="1" t="n">
+        <v>0.01567</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6489,11 +7626,14 @@
         <v>1.5349</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>1.5349</v>
+        <v>1.5325</v>
       </c>
       <c r="D379" s="1" t="n">
         <v>1.5349</v>
       </c>
+      <c r="E379" s="1" t="n">
+        <v>1.5325</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6505,9 +7645,12 @@
         <v>6.962e-05</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>6.962e-05</v>
+        <v>6.969000000000001e-05</v>
       </c>
       <c r="D380" s="1" t="n">
+        <v>6.969000000000001e-05</v>
+      </c>
+      <c r="E380" s="1" t="n">
         <v>6.962e-05</v>
       </c>
     </row>
@@ -6521,9 +7664,12 @@
         <v>2.551</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>2.551</v>
+        <v>2.555</v>
       </c>
       <c r="D381" s="1" t="n">
+        <v>2.555</v>
+      </c>
+      <c r="E381" s="1" t="n">
         <v>2.551</v>
       </c>
     </row>
@@ -6537,9 +7683,12 @@
         <v>0.06745</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>0.06745</v>
+        <v>0.06753000000000001</v>
       </c>
       <c r="D382" s="1" t="n">
+        <v>0.06753000000000001</v>
+      </c>
+      <c r="E382" s="1" t="n">
         <v>0.06745</v>
       </c>
     </row>
@@ -6553,9 +7702,12 @@
         <v>0.01745</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>0.01745</v>
+        <v>0.01758</v>
       </c>
       <c r="D383" s="1" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="E383" s="1" t="n">
         <v>0.01745</v>
       </c>
     </row>
@@ -6569,11 +7721,14 @@
         <v>0.05065</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>0.05065</v>
+        <v>0.05055</v>
       </c>
       <c r="D384" s="1" t="n">
         <v>0.05065</v>
       </c>
+      <c r="E384" s="1" t="n">
+        <v>0.05055</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -6585,9 +7740,12 @@
         <v>7.554</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>7.554</v>
+        <v>7.572</v>
       </c>
       <c r="D385" s="1" t="n">
+        <v>7.572</v>
+      </c>
+      <c r="E385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -6601,9 +7759,12 @@
         <v>0.00327</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>0.00327</v>
+        <v>0.003292</v>
       </c>
       <c r="D386" s="1" t="n">
+        <v>0.003292</v>
+      </c>
+      <c r="E386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -6617,9 +7778,12 @@
         <v>0.0003838</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>0.0003838</v>
+        <v>0.0003847</v>
       </c>
       <c r="D387" s="1" t="n">
+        <v>0.0003847</v>
+      </c>
+      <c r="E387" s="1" t="n">
         <v>0.0003838</v>
       </c>
     </row>
@@ -6633,9 +7797,12 @@
         <v>0.009769999999999999</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>0.009769999999999999</v>
+        <v>0.009889999999999999</v>
       </c>
       <c r="D388" s="1" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="E388" s="1" t="n">
         <v>0.009769999999999999</v>
       </c>
     </row>
@@ -6649,9 +7816,12 @@
         <v>0.2889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>0.2889</v>
+        <v>0.2891</v>
       </c>
       <c r="D389" s="1" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="E389" s="1" t="n">
         <v>0.2889</v>
       </c>
     </row>
@@ -6665,11 +7835,14 @@
         <v>0.0249</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>0.0249</v>
+        <v>0.0248</v>
       </c>
       <c r="D390" s="1" t="n">
         <v>0.0249</v>
       </c>
+      <c r="E390" s="1" t="n">
+        <v>0.0248</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -6681,9 +7854,12 @@
         <v>2.815</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>2.815</v>
+        <v>2.818</v>
       </c>
       <c r="D391" s="1" t="n">
+        <v>2.818</v>
+      </c>
+      <c r="E391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -6697,9 +7873,12 @@
         <v>0.01343</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>0.01343</v>
+        <v>0.01351</v>
       </c>
       <c r="D392" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="E392" s="1" t="n">
         <v>0.01343</v>
       </c>
     </row>
@@ -6718,6 +7897,9 @@
       <c r="D393" s="1" t="n">
         <v>0.00235</v>
       </c>
+      <c r="E393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -6729,9 +7911,12 @@
         <v>0.05922</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>0.05922</v>
+        <v>0.05951</v>
       </c>
       <c r="D394" s="1" t="n">
+        <v>0.05951</v>
+      </c>
+      <c r="E394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -6750,6 +7935,9 @@
       <c r="D395" s="1" t="n">
         <v>0.0405</v>
       </c>
+      <c r="E395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -6761,9 +7949,12 @@
         <v>0.09127</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>0.09127</v>
+        <v>0.09134</v>
       </c>
       <c r="D396" s="1" t="n">
+        <v>0.09134</v>
+      </c>
+      <c r="E396" s="1" t="n">
         <v>0.09127</v>
       </c>
     </row>
@@ -6777,9 +7968,12 @@
         <v>0.1517</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>0.1517</v>
+        <v>0.1521</v>
       </c>
       <c r="D397" s="1" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="E397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -6793,9 +7987,12 @@
         <v>0.925</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>0.925</v>
+        <v>0.926</v>
       </c>
       <c r="D398" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="E398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -6809,9 +8006,12 @@
         <v>0.05215</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>0.05215</v>
+        <v>0.05242</v>
       </c>
       <c r="D399" s="1" t="n">
+        <v>0.05242</v>
+      </c>
+      <c r="E399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -6825,9 +8025,12 @@
         <v>2.517</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>2.517</v>
+        <v>2.523</v>
       </c>
       <c r="D400" s="1" t="n">
+        <v>2.523</v>
+      </c>
+      <c r="E400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -6841,9 +8044,12 @@
         <v>0.01788</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>0.01788</v>
+        <v>0.01814</v>
       </c>
       <c r="D401" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="E401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -6857,9 +8063,12 @@
         <v>0.07953</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>0.07953</v>
+        <v>0.07958999999999999</v>
       </c>
       <c r="D402" s="1" t="n">
+        <v>0.07958999999999999</v>
+      </c>
+      <c r="E402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -6873,9 +8082,12 @@
         <v>1.2484</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>1.2484</v>
+        <v>1.2515</v>
       </c>
       <c r="D403" s="1" t="n">
+        <v>1.2515</v>
+      </c>
+      <c r="E403" s="1" t="n">
         <v>1.2484</v>
       </c>
     </row>
@@ -6889,11 +8101,14 @@
         <v>0.00716</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>0.00716</v>
+        <v>0.00715</v>
       </c>
       <c r="D404" s="1" t="n">
         <v>0.00716</v>
       </c>
+      <c r="E404" s="1" t="n">
+        <v>0.00715</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -6905,9 +8120,12 @@
         <v>0.4987</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>0.4987</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="D405" s="1" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>0.4987</v>
       </c>
     </row>
@@ -6921,11 +8139,14 @@
         <v>0.01151</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>0.01151</v>
+        <v>0.01146</v>
       </c>
       <c r="D406" s="1" t="n">
         <v>0.01151</v>
       </c>
+      <c r="E406" s="1" t="n">
+        <v>0.01146</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -6937,9 +8158,12 @@
         <v>0.0464</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>0.0464</v>
+        <v>0.04649</v>
       </c>
       <c r="D407" s="1" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="E407" s="1" t="n">
         <v>0.0464</v>
       </c>
     </row>
@@ -6953,9 +8177,12 @@
         <v>0.03947</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>0.03947</v>
+        <v>0.03955</v>
       </c>
       <c r="D408" s="1" t="n">
+        <v>0.03955</v>
+      </c>
+      <c r="E408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -6969,9 +8196,12 @@
         <v>0.05276</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>0.05276</v>
+        <v>0.05283</v>
       </c>
       <c r="D409" s="1" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="E409" s="1" t="n">
         <v>0.05276</v>
       </c>
     </row>
@@ -6985,9 +8215,12 @@
         <v>0.01247</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>0.01247</v>
+        <v>0.01256</v>
       </c>
       <c r="D410" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="E410" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -7001,9 +8234,12 @@
         <v>0.06378</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>0.06378</v>
+        <v>0.06396</v>
       </c>
       <c r="D411" s="1" t="n">
+        <v>0.06396</v>
+      </c>
+      <c r="E411" s="1" t="n">
         <v>0.06378</v>
       </c>
     </row>
@@ -7017,9 +8253,12 @@
         <v>0.0414</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>0.0414</v>
+        <v>0.04144</v>
       </c>
       <c r="D412" s="1" t="n">
+        <v>0.04144</v>
+      </c>
+      <c r="E412" s="1" t="n">
         <v>0.0414</v>
       </c>
     </row>
@@ -7033,9 +8272,12 @@
         <v>1.117</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>1.117</v>
+        <v>1.118</v>
       </c>
       <c r="D413" s="1" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="E413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -7049,9 +8291,12 @@
         <v>0.2639</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>0.2639</v>
+        <v>0.2644</v>
       </c>
       <c r="D414" s="1" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="E414" s="1" t="n">
         <v>0.2639</v>
       </c>
     </row>
@@ -7065,11 +8310,14 @@
         <v>0.001222</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>0.001222</v>
+        <v>0.001221</v>
       </c>
       <c r="D415" s="1" t="n">
         <v>0.001222</v>
       </c>
+      <c r="E415" s="1" t="n">
+        <v>0.001221</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7081,11 +8329,14 @@
         <v>0.03196</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>0.03196</v>
+        <v>0.0319</v>
       </c>
       <c r="D416" s="1" t="n">
         <v>0.03196</v>
       </c>
+      <c r="E416" s="1" t="n">
+        <v>0.0319</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7097,11 +8348,14 @@
         <v>0.01473</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>0.01473</v>
+        <v>0.01454</v>
       </c>
       <c r="D417" s="1" t="n">
         <v>0.01473</v>
       </c>
+      <c r="E417" s="1" t="n">
+        <v>0.01454</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -7113,9 +8367,12 @@
         <v>0.1479</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>0.1479</v>
+        <v>0.148</v>
       </c>
       <c r="D418" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="E418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -7129,9 +8386,12 @@
         <v>0.04862</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>0.04862</v>
+        <v>0.04884</v>
       </c>
       <c r="D419" s="1" t="n">
+        <v>0.04884</v>
+      </c>
+      <c r="E419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -7145,9 +8405,12 @@
         <v>65.70999999999999</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>65.70999999999999</v>
+        <v>66</v>
       </c>
       <c r="D420" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="E420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -7166,6 +8429,9 @@
       <c r="D421" s="1" t="n">
         <v>0.875</v>
       </c>
+      <c r="E421" s="1" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -7177,11 +8443,14 @@
         <v>0.012972</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>0.012972</v>
+        <v>0.012969</v>
       </c>
       <c r="D422" s="1" t="n">
         <v>0.012972</v>
       </c>
+      <c r="E422" s="1" t="n">
+        <v>0.012969</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -7193,9 +8462,12 @@
         <v>0.01594</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>0.01594</v>
+        <v>0.01597</v>
       </c>
       <c r="D423" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="E423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -7209,11 +8481,14 @@
         <v>0.26036</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>0.26036</v>
+        <v>0.25951</v>
       </c>
       <c r="D424" s="1" t="n">
         <v>0.26036</v>
       </c>
+      <c r="E424" s="1" t="n">
+        <v>0.25951</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -7225,9 +8500,12 @@
         <v>0.599</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>0.599</v>
+        <v>0.6007</v>
       </c>
       <c r="D425" s="1" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="E425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -7241,11 +8519,14 @@
         <v>0.005657</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>0.005657</v>
+        <v>0.005653</v>
       </c>
       <c r="D426" s="1" t="n">
         <v>0.005657</v>
       </c>
+      <c r="E426" s="1" t="n">
+        <v>0.005653</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -7257,9 +8538,12 @@
         <v>0.04899</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>0.04899</v>
+        <v>0.04916</v>
       </c>
       <c r="D427" s="1" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="E427" s="1" t="n">
         <v>0.04899</v>
       </c>
     </row>
@@ -7273,9 +8557,12 @@
         <v>0.1254</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>0.1254</v>
+        <v>0.1259</v>
       </c>
       <c r="D428" s="1" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="E428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -7289,9 +8576,12 @@
         <v>0.003197</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>0.003197</v>
+        <v>0.0032</v>
       </c>
       <c r="D429" s="1" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="E429" s="1" t="n">
         <v>0.003197</v>
       </c>
     </row>
@@ -7305,9 +8595,12 @@
         <v>0.03673</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>0.03673</v>
+        <v>0.03678</v>
       </c>
       <c r="D430" s="1" t="n">
+        <v>0.03678</v>
+      </c>
+      <c r="E430" s="1" t="n">
         <v>0.03673</v>
       </c>
     </row>
@@ -7321,9 +8614,12 @@
         <v>0.401</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>0.401</v>
+        <v>0.4011</v>
       </c>
       <c r="D431" s="1" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="E431" s="1" t="n">
         <v>0.401</v>
       </c>
     </row>
@@ -7337,9 +8633,12 @@
         <v>0.004519</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>0.004519</v>
+        <v>0.004542</v>
       </c>
       <c r="D432" s="1" t="n">
+        <v>0.004542</v>
+      </c>
+      <c r="E432" s="1" t="n">
         <v>0.004519</v>
       </c>
     </row>
@@ -7358,6 +8657,9 @@
       <c r="D433" s="1" t="n">
         <v>0.0978</v>
       </c>
+      <c r="E433" s="1" t="n">
+        <v>0.0978</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -7369,9 +8671,12 @@
         <v>0.01238</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>0.01238</v>
+        <v>0.01239</v>
       </c>
       <c r="D434" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="E434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -7385,9 +8690,12 @@
         <v>1.968</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>1.968</v>
+        <v>1.978</v>
       </c>
       <c r="D435" s="1" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="E435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -7401,11 +8709,14 @@
         <v>0.001848</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>0.001848</v>
+        <v>0.001833</v>
       </c>
       <c r="D436" s="1" t="n">
         <v>0.001848</v>
       </c>
+      <c r="E436" s="1" t="n">
+        <v>0.001833</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -7417,9 +8728,12 @@
         <v>0.4417</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>0.4417</v>
+        <v>0.4423</v>
       </c>
       <c r="D437" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="E437" s="1" t="n">
         <v>0.4417</v>
       </c>
     </row>
@@ -7433,9 +8747,12 @@
         <v>0.00534</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>0.00534</v>
+        <v>0.00535</v>
       </c>
       <c r="D438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="E438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -7454,6 +8771,9 @@
       <c r="D439" s="1" t="n">
         <v>0.1033</v>
       </c>
+      <c r="E439" s="1" t="n">
+        <v>0.1033</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -7465,9 +8785,12 @@
         <v>0.0342</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>0.0342</v>
+        <v>0.03431</v>
       </c>
       <c r="D440" s="1" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="E440" s="1" t="n">
         <v>0.0342</v>
       </c>
     </row>
@@ -7481,9 +8804,12 @@
         <v>0.08201</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>0.08201</v>
+        <v>0.08209</v>
       </c>
       <c r="D441" s="1" t="n">
+        <v>0.08209</v>
+      </c>
+      <c r="E441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -7497,11 +8823,14 @@
         <v>1.307</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>1.307</v>
+        <v>1.305</v>
       </c>
       <c r="D442" s="1" t="n">
         <v>1.307</v>
       </c>
+      <c r="E442" s="1" t="n">
+        <v>1.305</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -7513,9 +8842,12 @@
         <v>0.07550999999999999</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>0.07550999999999999</v>
+        <v>0.07571</v>
       </c>
       <c r="D443" s="1" t="n">
+        <v>0.07571</v>
+      </c>
+      <c r="E443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -7529,9 +8861,12 @@
         <v>0.07661</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>0.07661</v>
+        <v>0.07692</v>
       </c>
       <c r="D444" s="1" t="n">
+        <v>0.07692</v>
+      </c>
+      <c r="E444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -7545,9 +8880,12 @@
         <v>0.04357</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>0.04357</v>
+        <v>0.04377</v>
       </c>
       <c r="D445" s="1" t="n">
+        <v>0.04377</v>
+      </c>
+      <c r="E445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -7561,9 +8899,12 @@
         <v>0.0216</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>0.0216</v>
+        <v>0.0217</v>
       </c>
       <c r="D446" s="1" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="E446" s="1" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -7577,9 +8918,12 @@
         <v>0.2795</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>0.2795</v>
+        <v>0.2797</v>
       </c>
       <c r="D447" s="1" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="E447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -7593,9 +8937,12 @@
         <v>0.03141</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>0.03141</v>
+        <v>0.03146</v>
       </c>
       <c r="D448" s="1" t="n">
+        <v>0.03146</v>
+      </c>
+      <c r="E448" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -7609,9 +8956,12 @@
         <v>0.00642</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>0.00642</v>
+        <v>0.00644</v>
       </c>
       <c r="D449" s="1" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="E449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -7625,9 +8975,12 @@
         <v>0.022879</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>0.022879</v>
+        <v>0.022916</v>
       </c>
       <c r="D450" s="1" t="n">
+        <v>0.022916</v>
+      </c>
+      <c r="E450" s="1" t="n">
         <v>0.022879</v>
       </c>
     </row>
@@ -7641,9 +8994,12 @@
         <v>0.04223</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>0.04223</v>
+        <v>0.04232</v>
       </c>
       <c r="D451" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -7657,11 +9013,14 @@
         <v>0.07363</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>0.07363</v>
+        <v>0.07346999999999999</v>
       </c>
       <c r="D452" s="1" t="n">
         <v>0.07363</v>
       </c>
+      <c r="E452" s="1" t="n">
+        <v>0.07346999999999999</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -7673,9 +9032,12 @@
         <v>0.0005925</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>0.0005925</v>
+        <v>0.0005931000000000001</v>
       </c>
       <c r="D453" s="1" t="n">
+        <v>0.0005931000000000001</v>
+      </c>
+      <c r="E453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -7694,6 +9056,9 @@
       <c r="D454" s="1" t="n">
         <v>0.307</v>
       </c>
+      <c r="E454" s="1" t="n">
+        <v>0.307</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -7705,9 +9070,12 @@
         <v>0.004208</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>0.004208</v>
+        <v>0.004228</v>
       </c>
       <c r="D455" s="1" t="n">
+        <v>0.004228</v>
+      </c>
+      <c r="E455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -7721,9 +9089,12 @@
         <v>0.1835</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>0.1835</v>
+        <v>0.1843</v>
       </c>
       <c r="D456" s="1" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="E456" s="1" t="n">
         <v>0.1835</v>
       </c>
     </row>
@@ -7737,9 +9108,12 @@
         <v>0.04278</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>0.04278</v>
+        <v>0.04284</v>
       </c>
       <c r="D457" s="1" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="E457" s="1" t="n">
         <v>0.04278</v>
       </c>
     </row>
@@ -7753,9 +9127,12 @@
         <v>0.1459</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>0.1459</v>
+        <v>0.1463</v>
       </c>
       <c r="D458" s="1" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="E458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -7769,9 +9146,12 @@
         <v>0.008574</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>0.008574</v>
+        <v>0.008583</v>
       </c>
       <c r="D459" s="1" t="n">
+        <v>0.008583</v>
+      </c>
+      <c r="E459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -7785,11 +9165,14 @@
         <v>0.007521</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>0.007521</v>
+        <v>0.007458</v>
       </c>
       <c r="D460" s="1" t="n">
         <v>0.007521</v>
       </c>
+      <c r="E460" s="1" t="n">
+        <v>0.007458</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -7801,9 +9184,12 @@
         <v>0.0001722</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>0.0001722</v>
+        <v>0.0001736</v>
       </c>
       <c r="D461" s="1" t="n">
+        <v>0.0001736</v>
+      </c>
+      <c r="E461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -7817,9 +9203,12 @@
         <v>0.02244</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>0.02244</v>
+        <v>0.02246</v>
       </c>
       <c r="D462" s="1" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="E462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -7833,9 +9222,12 @@
         <v>0.0374</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>0.0374</v>
+        <v>0.03777</v>
       </c>
       <c r="D463" s="1" t="n">
+        <v>0.03777</v>
+      </c>
+      <c r="E463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -7849,9 +9241,12 @@
         <v>0.3031</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>0.3031</v>
+        <v>0.3038</v>
       </c>
       <c r="D464" s="1" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="E464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -7870,6 +9265,9 @@
       <c r="D465" s="1" t="n">
         <v>0.03923</v>
       </c>
+      <c r="E465" s="1" t="n">
+        <v>0.03923</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -7881,9 +9279,12 @@
         <v>2.682</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>2.682</v>
+        <v>2.687</v>
       </c>
       <c r="D466" s="1" t="n">
+        <v>2.687</v>
+      </c>
+      <c r="E466" s="1" t="n">
         <v>2.682</v>
       </c>
     </row>
@@ -7897,9 +9298,12 @@
         <v>0.0337</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>0.0337</v>
+        <v>0.03394</v>
       </c>
       <c r="D467" s="1" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="E467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -7913,9 +9317,12 @@
         <v>0.176</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>0.176</v>
+        <v>0.1763</v>
       </c>
       <c r="D468" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="E468" s="1" t="n">
         <v>0.176</v>
       </c>
     </row>
@@ -7929,9 +9336,12 @@
         <v>0.0956</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>0.0956</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="D469" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="E469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -7945,11 +9355,14 @@
         <v>0.06748999999999999</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>0.06748999999999999</v>
+        <v>0.06745</v>
       </c>
       <c r="D470" s="1" t="n">
         <v>0.06748999999999999</v>
       </c>
+      <c r="E470" s="1" t="n">
+        <v>0.06745</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -7961,9 +9374,12 @@
         <v>0.03978</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>0.03978</v>
+        <v>0.03983</v>
       </c>
       <c r="D471" s="1" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="E471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -7977,9 +9393,12 @@
         <v>0.2477</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>0.2477</v>
+        <v>0.2481</v>
       </c>
       <c r="D472" s="1" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="E472" s="1" t="n">
         <v>0.2477</v>
       </c>
     </row>
@@ -7993,11 +9412,14 @@
         <v>0.016588</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>0.016588</v>
+        <v>0.016545</v>
       </c>
       <c r="D473" s="1" t="n">
         <v>0.016588</v>
       </c>
+      <c r="E473" s="1" t="n">
+        <v>0.016545</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8009,9 +9431,12 @@
         <v>0.1148</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>0.1148</v>
+        <v>0.1149</v>
       </c>
       <c r="D474" s="1" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="E474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -8025,9 +9450,12 @@
         <v>0.04264</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>0.04264</v>
+        <v>0.04293</v>
       </c>
       <c r="D475" s="1" t="n">
+        <v>0.04293</v>
+      </c>
+      <c r="E475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -8041,9 +9469,12 @@
         <v>0.2071</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>0.2071</v>
+        <v>0.2075</v>
       </c>
       <c r="D476" s="1" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="E476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -8057,11 +9488,14 @@
         <v>0.00682</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>0.00682</v>
+        <v>0.006817</v>
       </c>
       <c r="D477" s="1" t="n">
         <v>0.00682</v>
       </c>
+      <c r="E477" s="1" t="n">
+        <v>0.006817</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -8078,6 +9512,9 @@
       <c r="D478" s="1" t="n">
         <v>0.01814</v>
       </c>
+      <c r="E478" s="1" t="n">
+        <v>0.01814</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -8089,9 +9526,12 @@
         <v>0.0473</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>0.0473</v>
+        <v>0.04738</v>
       </c>
       <c r="D479" s="1" t="n">
+        <v>0.04738</v>
+      </c>
+      <c r="E479" s="1" t="n">
         <v>0.0473</v>
       </c>
     </row>
@@ -8105,9 +9545,12 @@
         <v>0.25884</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>0.25884</v>
+        <v>0.25959</v>
       </c>
       <c r="D480" s="1" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="E480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -8121,9 +9564,12 @@
         <v>0.01241</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>0.01241</v>
+        <v>0.01253</v>
       </c>
       <c r="D481" s="1" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="E481" s="1" t="n">
         <v>0.01241</v>
       </c>
     </row>
@@ -8137,9 +9583,12 @@
         <v>0.004063</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>0.004063</v>
+        <v>0.004069</v>
       </c>
       <c r="D482" s="1" t="n">
+        <v>0.004069</v>
+      </c>
+      <c r="E482" s="1" t="n">
         <v>0.004063</v>
       </c>
     </row>
@@ -8153,9 +9602,12 @@
         <v>0.123</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>0.123</v>
+        <v>0.1232</v>
       </c>
       <c r="D483" s="1" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="E483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -8169,11 +9621,14 @@
         <v>0.02166</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>0.02166</v>
+        <v>0.02164</v>
       </c>
       <c r="D484" s="1" t="n">
         <v>0.02166</v>
       </c>
+      <c r="E484" s="1" t="n">
+        <v>0.02164</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -8185,11 +9640,14 @@
         <v>0.04638</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>0.04638</v>
+        <v>0.04607</v>
       </c>
       <c r="D485" s="1" t="n">
         <v>0.04638</v>
       </c>
+      <c r="E485" s="1" t="n">
+        <v>0.04607</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -8201,9 +9659,12 @@
         <v>0.1732</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>0.1732</v>
+        <v>0.1734</v>
       </c>
       <c r="D486" s="1" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="E486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -8217,9 +9678,12 @@
         <v>0.273</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>0.273</v>
+        <v>0.2733</v>
       </c>
       <c r="D487" s="1" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="E487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -8233,9 +9697,12 @@
         <v>0.04625</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>0.04625</v>
+        <v>0.04628</v>
       </c>
       <c r="D488" s="1" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="E488" s="1" t="n">
         <v>0.04625</v>
       </c>
     </row>
@@ -8249,9 +9716,12 @@
         <v>0.0002151</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>0.0002151</v>
+        <v>0.0002152</v>
       </c>
       <c r="D489" s="1" t="n">
+        <v>0.0002152</v>
+      </c>
+      <c r="E489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -8265,11 +9735,14 @@
         <v>1.762</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>1.762</v>
+        <v>1.761</v>
       </c>
       <c r="D490" s="1" t="n">
         <v>1.762</v>
       </c>
+      <c r="E490" s="1" t="n">
+        <v>1.761</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -8281,9 +9754,12 @@
         <v>15.996</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>15.996</v>
+        <v>16.049</v>
       </c>
       <c r="D491" s="1" t="n">
+        <v>16.049</v>
+      </c>
+      <c r="E491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -8297,9 +9773,12 @@
         <v>0.06648</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>0.06648</v>
+        <v>0.06664</v>
       </c>
       <c r="D492" s="1" t="n">
+        <v>0.06664</v>
+      </c>
+      <c r="E492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -8313,9 +9792,12 @@
         <v>0.06734999999999999</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>0.06734999999999999</v>
+        <v>0.06766</v>
       </c>
       <c r="D493" s="1" t="n">
+        <v>0.06766</v>
+      </c>
+      <c r="E493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -8329,9 +9811,12 @@
         <v>0.009375</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>0.009375</v>
+        <v>0.009416000000000001</v>
       </c>
       <c r="D494" s="1" t="n">
+        <v>0.009416000000000001</v>
+      </c>
+      <c r="E494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -8345,9 +9830,12 @@
         <v>0.005936</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>0.005936</v>
+        <v>0.006116</v>
       </c>
       <c r="D495" s="1" t="n">
+        <v>0.006116</v>
+      </c>
+      <c r="E495" s="1" t="n">
         <v>0.005936</v>
       </c>
     </row>
@@ -8361,9 +9849,12 @@
         <v>0.00992</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>0.00992</v>
+        <v>0.00993</v>
       </c>
       <c r="D496" s="1" t="n">
+        <v>0.00993</v>
+      </c>
+      <c r="E496" s="1" t="n">
         <v>0.00992</v>
       </c>
     </row>
@@ -8377,9 +9868,12 @@
         <v>0.04394</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>0.04394</v>
+        <v>0.04395</v>
       </c>
       <c r="D497" s="1" t="n">
+        <v>0.04395</v>
+      </c>
+      <c r="E497" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -8398,6 +9892,9 @@
       <c r="D498" s="1" t="n">
         <v>0.006405</v>
       </c>
+      <c r="E498" s="1" t="n">
+        <v>0.006405</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -8409,9 +9906,12 @@
         <v>0.01044</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>0.01044</v>
+        <v>0.01047</v>
       </c>
       <c r="D499" s="1" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="E499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -8425,9 +9925,12 @@
         <v>0.5089</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>0.5089</v>
+        <v>0.5122</v>
       </c>
       <c r="D500" s="1" t="n">
+        <v>0.5122</v>
+      </c>
+      <c r="E500" s="1" t="n">
         <v>0.5089</v>
       </c>
     </row>
@@ -8441,9 +9944,12 @@
         <v>0.03205</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>0.03205</v>
+        <v>0.03212</v>
       </c>
       <c r="D501" s="1" t="n">
+        <v>0.03212</v>
+      </c>
+      <c r="E501" s="1" t="n">
         <v>0.03205</v>
       </c>
     </row>
@@ -8457,11 +9963,14 @@
         <v>0.4359</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>0.4359</v>
+        <v>0.4356</v>
       </c>
       <c r="D502" s="1" t="n">
         <v>0.4359</v>
       </c>
+      <c r="E502" s="1" t="n">
+        <v>0.4356</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -8473,11 +9982,14 @@
         <v>0.999401</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>0.999401</v>
+        <v>0.9994</v>
       </c>
       <c r="D503" s="1" t="n">
         <v>0.999401</v>
       </c>
+      <c r="E503" s="1" t="n">
+        <v>0.9994</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -8489,11 +10001,14 @@
         <v>0.03534</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>0.03534</v>
+        <v>0.03525</v>
       </c>
       <c r="D504" s="1" t="n">
         <v>0.03534</v>
       </c>
+      <c r="E504" s="1" t="n">
+        <v>0.03525</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -8505,9 +10020,12 @@
         <v>0.004893</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>0.004893</v>
+        <v>0.004926</v>
       </c>
       <c r="D505" s="1" t="n">
+        <v>0.004926</v>
+      </c>
+      <c r="E505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -8521,9 +10039,12 @@
         <v>0.01389</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>0.01389</v>
+        <v>0.01394</v>
       </c>
       <c r="D506" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="E506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -8537,11 +10058,14 @@
         <v>0.003478</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>0.003478</v>
+        <v>0.00347</v>
       </c>
       <c r="D507" s="1" t="n">
         <v>0.003478</v>
       </c>
+      <c r="E507" s="1" t="n">
+        <v>0.00347</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -8553,9 +10077,12 @@
         <v>1.417</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>1.417</v>
+        <v>1.42</v>
       </c>
       <c r="D508" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -8569,9 +10096,12 @@
         <v>0.005102</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>0.005102</v>
+        <v>0.005124</v>
       </c>
       <c r="D509" s="1" t="n">
+        <v>0.005124</v>
+      </c>
+      <c r="E509" s="1" t="n">
         <v>0.005102</v>
       </c>
     </row>
@@ -8585,9 +10115,12 @@
         <v>0.01572</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>0.01572</v>
+        <v>0.01576</v>
       </c>
       <c r="D510" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="E510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -8601,11 +10134,14 @@
         <v>0.08361</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>0.08361</v>
+        <v>0.08319</v>
       </c>
       <c r="D511" s="1" t="n">
         <v>0.08361</v>
       </c>
+      <c r="E511" s="1" t="n">
+        <v>0.08319</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -8617,9 +10153,12 @@
         <v>0.007105</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>0.007105</v>
+        <v>0.007112</v>
       </c>
       <c r="D512" s="1" t="n">
+        <v>0.007112</v>
+      </c>
+      <c r="E512" s="1" t="n">
         <v>0.007105</v>
       </c>
     </row>
@@ -8633,11 +10172,14 @@
         <v>0.01469</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>0.01469</v>
+        <v>0.01468</v>
       </c>
       <c r="D513" s="1" t="n">
         <v>0.01469</v>
       </c>
+      <c r="E513" s="1" t="n">
+        <v>0.01468</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -8649,9 +10191,12 @@
         <v>0.04768</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>0.04768</v>
+        <v>0.04787</v>
       </c>
       <c r="D514" s="1" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="E514" s="1" t="n">
         <v>0.04768</v>
       </c>
     </row>
@@ -8665,9 +10210,12 @@
         <v>0.01824</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>0.01824</v>
+        <v>0.01826</v>
       </c>
       <c r="D515" s="1" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="E515" s="1" t="n">
         <v>0.01824</v>
       </c>
     </row>
@@ -8681,9 +10229,12 @@
         <v>0.0005792</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>0.0005792</v>
+        <v>0.0005801</v>
       </c>
       <c r="D516" s="1" t="n">
+        <v>0.0005801</v>
+      </c>
+      <c r="E516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -8697,9 +10248,12 @@
         <v>0.07829</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>0.07829</v>
+        <v>0.07869</v>
       </c>
       <c r="D517" s="1" t="n">
+        <v>0.07869</v>
+      </c>
+      <c r="E517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -8713,9 +10267,12 @@
         <v>0.006386</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>0.006386</v>
+        <v>0.006392</v>
       </c>
       <c r="D518" s="1" t="n">
+        <v>0.006392</v>
+      </c>
+      <c r="E518" s="1" t="n">
         <v>0.006386</v>
       </c>
     </row>
@@ -8729,9 +10286,12 @@
         <v>0.05803</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>0.05803</v>
+        <v>0.0581</v>
       </c>
       <c r="D519" s="1" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="E519" s="1" t="n">
         <v>0.05803</v>
       </c>
     </row>
@@ -8745,9 +10305,12 @@
         <v>0.10496</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>0.10496</v>
+        <v>0.10531</v>
       </c>
       <c r="D520" s="1" t="n">
+        <v>0.10531</v>
+      </c>
+      <c r="E520" s="1" t="n">
         <v>0.10496</v>
       </c>
     </row>
@@ -8761,9 +10324,12 @@
         <v>0.01787</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>0.01787</v>
+        <v>0.01793</v>
       </c>
       <c r="D521" s="1" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="E521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -8777,9 +10343,12 @@
         <v>0.01644</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>0.01644</v>
+        <v>0.0165</v>
       </c>
       <c r="D522" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="E522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -8793,9 +10362,12 @@
         <v>0.01083</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>0.01083</v>
+        <v>0.01085</v>
       </c>
       <c r="D523" s="1" t="n">
+        <v>0.01085</v>
+      </c>
+      <c r="E523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -8809,9 +10381,12 @@
         <v>0.006771</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>0.006771</v>
+        <v>0.006859</v>
       </c>
       <c r="D524" s="1" t="n">
+        <v>0.006859</v>
+      </c>
+      <c r="E524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -8825,11 +10400,14 @@
         <v>0.005998</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>0.005998</v>
+        <v>0.005997</v>
       </c>
       <c r="D525" s="1" t="n">
         <v>0.005998</v>
       </c>
+      <c r="E525" s="1" t="n">
+        <v>0.005997</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -8841,11 +10419,14 @@
         <v>0.001449</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>0.001449</v>
+        <v>0.001437</v>
       </c>
       <c r="D526" s="1" t="n">
         <v>0.001449</v>
       </c>
+      <c r="E526" s="1" t="n">
+        <v>0.001437</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -8862,6 +10443,9 @@
       <c r="D527" s="1" t="n">
         <v>0.372</v>
       </c>
+      <c r="E527" s="1" t="n">
+        <v>0.372</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -8873,9 +10457,12 @@
         <v>0.005138</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>0.005138</v>
+        <v>0.005159</v>
       </c>
       <c r="D528" s="1" t="n">
+        <v>0.005159</v>
+      </c>
+      <c r="E528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -8889,9 +10476,12 @@
         <v>2.917</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>2.917</v>
+        <v>2.918</v>
       </c>
       <c r="D529" s="1" t="n">
+        <v>2.918</v>
+      </c>
+      <c r="E529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -8905,9 +10495,12 @@
         <v>0.1554</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>0.1554</v>
+        <v>0.1559</v>
       </c>
       <c r="D530" s="1" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="E530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -8921,9 +10514,12 @@
         <v>2540</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="D531" s="1" t="n">
+        <v>2544</v>
+      </c>
+      <c r="E531" s="1" t="n">
         <v>2540</v>
       </c>
     </row>
@@ -8937,9 +10533,12 @@
         <v>0.03927</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>0.03927</v>
+        <v>0.03928</v>
       </c>
       <c r="D532" s="1" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="E532" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -8953,9 +10552,12 @@
         <v>0.02157</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>0.02157</v>
+        <v>0.02183</v>
       </c>
       <c r="D533" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="E533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -8969,9 +10571,12 @@
         <v>0.07267</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>0.07267</v>
+        <v>0.0727</v>
       </c>
       <c r="D534" s="1" t="n">
+        <v>0.0727</v>
+      </c>
+      <c r="E534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -8985,9 +10590,12 @@
         <v>0.007766</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>0.007766</v>
+        <v>0.007801</v>
       </c>
       <c r="D535" s="1" t="n">
+        <v>0.007801</v>
+      </c>
+      <c r="E535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -9001,9 +10609,12 @@
         <v>0.05002</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>0.05002</v>
+        <v>0.0504</v>
       </c>
       <c r="D536" s="1" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="E536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -9022,6 +10633,9 @@
       <c r="D537" s="1" t="n">
         <v>0.00406</v>
       </c>
+      <c r="E537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -9033,9 +10647,12 @@
         <v>0.08284</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>0.08284</v>
+        <v>0.0832</v>
       </c>
       <c r="D538" s="1" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="E538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -9049,9 +10666,12 @@
         <v>0.02499</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>0.02499</v>
+        <v>0.02502</v>
       </c>
       <c r="D539" s="1" t="n">
+        <v>0.02502</v>
+      </c>
+      <c r="E539" s="1" t="n">
         <v>0.02499</v>
       </c>
     </row>
@@ -9065,9 +10685,12 @@
         <v>0.08461</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>0.08461</v>
+        <v>0.08469</v>
       </c>
       <c r="D540" s="1" t="n">
+        <v>0.08469</v>
+      </c>
+      <c r="E540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -9081,9 +10704,12 @@
         <v>0.01896</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>0.01896</v>
+        <v>0.019</v>
       </c>
       <c r="D541" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E541" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -9102,6 +10728,9 @@
       <c r="D542" s="1" t="n">
         <v>0.01698</v>
       </c>
+      <c r="E542" s="1" t="n">
+        <v>0.01698</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -9113,9 +10742,12 @@
         <v>0.1047</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>0.1047</v>
+        <v>0.1049</v>
       </c>
       <c r="D543" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="E543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,15 +416,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F543"/>
+  <dimension ref="A1:G543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,10 +451,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>price_01:00</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -475,9 +481,12 @@
         <v>70610</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>70623.2</v>
+        <v>70644.2</v>
       </c>
       <c r="F2" s="1" t="n">
+        <v>70644.2</v>
+      </c>
+      <c r="G2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -497,9 +506,12 @@
         <v>2074.43</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2074.43</v>
+        <v>2076.36</v>
       </c>
       <c r="F3" s="1" t="n">
+        <v>2076.36</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -519,9 +531,12 @@
         <v>86.89</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>86.89</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>87.01000000000001</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -541,9 +556,12 @@
         <v>4.033</v>
       </c>
       <c r="E5" s="1" t="n">
+        <v>4.028</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>4.039</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -563,9 +581,12 @@
         <v>0.09519</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.09519</v>
+        <v>0.09528</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>0.09528</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>0.09485</v>
       </c>
     </row>
@@ -585,9 +606,12 @@
         <v>1.3902</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1.3902</v>
+        <v>1.3922</v>
       </c>
       <c r="F7" s="1" t="n">
+        <v>1.3922</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -607,9 +631,12 @@
         <v>22.204</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>22.657</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -629,9 +656,12 @@
         <v>0.002135</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>0.00215</v>
+        <v>0.002175</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>0.002175</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>0.002119</v>
       </c>
     </row>
@@ -651,9 +681,12 @@
         <v>0.010041</v>
       </c>
       <c r="E10" s="1" t="n">
+        <v>0.010265</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -673,9 +706,12 @@
         <v>0.17048</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.1709</v>
+        <v>0.17111</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>0.17111</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>0.16978</v>
       </c>
     </row>
@@ -695,10 +731,13 @@
         <v>0.011888</v>
       </c>
       <c r="E12" s="1" t="n">
+        <v>0.011847</v>
+      </c>
+      <c r="F12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>0.011888</v>
+      <c r="G12" s="1" t="n">
+        <v>0.011847</v>
       </c>
     </row>
     <row r="13">
@@ -717,9 +756,12 @@
         <v>38.306</v>
       </c>
       <c r="E13" s="1" t="n">
+        <v>38.333</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -739,9 +781,12 @@
         <v>653.8099999999999</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>653.8099999999999</v>
+        <v>654.02</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>654.02</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -761,9 +806,12 @@
         <v>209.91</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>209.91</v>
+        <v>209.93</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>209.93</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -783,9 +831,12 @@
         <v>0.0033535</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.0033535</v>
+        <v>0.0033537</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>0.0033537</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>0.0033417</v>
       </c>
     </row>
@@ -805,9 +856,12 @@
         <v>237</v>
       </c>
       <c r="E17" s="1" t="n">
+        <v>236.48</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>237</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="G17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -827,9 +881,12 @@
         <v>0.9943</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.9943</v>
+        <v>0.9959</v>
       </c>
       <c r="F18" s="1" t="n">
+        <v>0.9959</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -849,9 +906,12 @@
         <v>1.0722</v>
       </c>
       <c r="E19" s="1" t="n">
+        <v>1.0555</v>
+      </c>
+      <c r="F19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="G19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -874,6 +934,9 @@
         <v>0.2612</v>
       </c>
       <c r="F20" s="1" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>0.2608</v>
       </c>
     </row>
@@ -893,9 +956,12 @@
         <v>0.60529</v>
       </c>
       <c r="E21" s="1" t="n">
+        <v>0.6065700000000001</v>
+      </c>
+      <c r="F21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="G21" s="1" t="n">
         <v>0.60434</v>
       </c>
     </row>
@@ -915,9 +981,12 @@
         <v>9.026999999999999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>9.026999999999999</v>
+        <v>9.032999999999999</v>
       </c>
       <c r="F22" s="1" t="n">
+        <v>9.032999999999999</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -937,9 +1006,12 @@
         <v>0.02421</v>
       </c>
       <c r="E23" s="1" t="n">
+        <v>0.02422</v>
+      </c>
+      <c r="F23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>0.02421</v>
       </c>
     </row>
@@ -959,9 +1031,12 @@
         <v>9.586</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>9.586</v>
+        <v>9.599</v>
       </c>
       <c r="F24" s="1" t="n">
+        <v>9.599</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -981,9 +1056,12 @@
         <v>1.224</v>
       </c>
       <c r="E25" s="1" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="F25" s="1" t="n">
         <v>1.224</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="G25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1003,10 +1081,13 @@
         <v>0.07076</v>
       </c>
       <c r="E26" s="1" t="n">
+        <v>0.07024</v>
+      </c>
+      <c r="F26" s="1" t="n">
         <v>0.07160999999999999</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>0.07076</v>
+      <c r="G26" s="1" t="n">
+        <v>0.07024</v>
       </c>
     </row>
     <row r="27">
@@ -1025,9 +1106,12 @@
         <v>1.424</v>
       </c>
       <c r="E27" s="1" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="F27" s="1" t="n">
         <v>1.428</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="G27" s="1" t="n">
         <v>1.424</v>
       </c>
     </row>
@@ -1050,6 +1134,9 @@
         <v>1.312</v>
       </c>
       <c r="F28" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -1069,9 +1156,12 @@
         <v>462.18</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>462.18</v>
+        <v>462.44</v>
       </c>
       <c r="F29" s="1" t="n">
+        <v>462.44</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>461.74</v>
       </c>
     </row>
@@ -1091,9 +1181,12 @@
         <v>1.2767</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>1.2786</v>
+        <v>1.279</v>
       </c>
       <c r="F30" s="1" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1113,10 +1206,13 @@
         <v>5023.41</v>
       </c>
       <c r="E31" s="1" t="n">
+        <v>5021.33</v>
+      </c>
+      <c r="F31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="F31" s="1" t="n">
-        <v>5022.05</v>
+      <c r="G31" s="1" t="n">
+        <v>5021.33</v>
       </c>
     </row>
     <row r="32">
@@ -1135,9 +1231,12 @@
         <v>0.873</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>0.873</v>
+        <v>0.877</v>
       </c>
       <c r="F32" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1157,9 +1256,12 @@
         <v>0.00198</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.001981</v>
+        <v>0.001983</v>
       </c>
       <c r="F33" s="1" t="n">
+        <v>0.001983</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1179,9 +1281,12 @@
         <v>0.16972</v>
       </c>
       <c r="E34" s="1" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="F34" s="1" t="n">
         <v>0.17091</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="G34" s="1" t="n">
         <v>0.16678</v>
       </c>
     </row>
@@ -1201,9 +1306,12 @@
         <v>0.29839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>0.29856</v>
+        <v>0.29866</v>
       </c>
       <c r="F35" s="1" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>0.2982</v>
       </c>
     </row>
@@ -1223,9 +1331,12 @@
         <v>1.788</v>
       </c>
       <c r="E36" s="1" t="n">
+        <v>1.789</v>
+      </c>
+      <c r="F36" s="1" t="n">
         <v>1.793</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="G36" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1245,9 +1356,12 @@
         <v>110.86</v>
       </c>
       <c r="E37" s="1" t="n">
+        <v>110.78</v>
+      </c>
+      <c r="F37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="G37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1267,9 +1381,12 @@
         <v>0.22488</v>
       </c>
       <c r="E38" s="1" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="F38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="G38" s="1" t="n">
         <v>0.22488</v>
       </c>
     </row>
@@ -1289,9 +1406,12 @@
         <v>0.1082</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.1082</v>
+        <v>0.1083</v>
       </c>
       <c r="F39" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="G39" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -1311,9 +1431,12 @@
         <v>0.37392</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.37392</v>
+        <v>0.37507</v>
       </c>
       <c r="F40" s="1" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>0.37042</v>
       </c>
     </row>
@@ -1333,9 +1456,12 @@
         <v>54.53</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>54.53</v>
+        <v>54.58</v>
       </c>
       <c r="F41" s="1" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1355,10 +1481,13 @@
         <v>0.001081</v>
       </c>
       <c r="E42" s="1" t="n">
+        <v>0.0010772</v>
+      </c>
+      <c r="F42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="F42" s="1" t="n">
-        <v>0.0010793</v>
+      <c r="G42" s="1" t="n">
+        <v>0.0010772</v>
       </c>
     </row>
     <row r="43">
@@ -1377,10 +1506,13 @@
         <v>6.462</v>
       </c>
       <c r="E43" s="1" t="n">
+        <v>6.443</v>
+      </c>
+      <c r="F43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="F43" s="1" t="n">
-        <v>6.462</v>
+      <c r="G43" s="1" t="n">
+        <v>6.443</v>
       </c>
     </row>
     <row r="44">
@@ -1399,9 +1531,12 @@
         <v>0.6401</v>
       </c>
       <c r="E44" s="1" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="F44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="G44" s="1" t="n">
         <v>0.6401</v>
       </c>
     </row>
@@ -1421,9 +1556,12 @@
         <v>0.3552</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.3552</v>
+        <v>0.3556</v>
       </c>
       <c r="F45" s="1" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="G45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -1443,9 +1581,12 @@
         <v>0.03237</v>
       </c>
       <c r="E46" s="1" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="F46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="G46" s="1" t="n">
         <v>0.03237</v>
       </c>
     </row>
@@ -1465,10 +1606,13 @@
         <v>0.07267</v>
       </c>
       <c r="E47" s="1" t="n">
+        <v>0.07242999999999999</v>
+      </c>
+      <c r="F47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="F47" s="1" t="n">
-        <v>0.07267</v>
+      <c r="G47" s="1" t="n">
+        <v>0.07242999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1487,9 +1631,12 @@
         <v>0.7027</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.7035</v>
+        <v>0.7057</v>
       </c>
       <c r="F48" s="1" t="n">
+        <v>0.7057</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -1509,9 +1656,12 @@
         <v>0.004564</v>
       </c>
       <c r="E49" s="1" t="n">
+        <v>0.004571</v>
+      </c>
+      <c r="F49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="G49" s="1" t="n">
         <v>0.004564</v>
       </c>
     </row>
@@ -1531,9 +1681,12 @@
         <v>0.1049</v>
       </c>
       <c r="E50" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="F50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="G50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -1553,9 +1706,12 @@
         <v>0.04023</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>0.04033</v>
+      </c>
+      <c r="F51" s="1" t="n">
         <v>0.04047</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="G51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -1575,9 +1731,12 @@
         <v>0.1688</v>
       </c>
       <c r="E52" s="1" t="n">
+        <v>0.1676</v>
+      </c>
+      <c r="F52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="G52" s="1" t="n">
         <v>0.1667</v>
       </c>
     </row>
@@ -1597,9 +1756,12 @@
         <v>0.02186</v>
       </c>
       <c r="E53" s="1" t="n">
+        <v>0.02167</v>
+      </c>
+      <c r="F53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="G53" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -1619,9 +1781,12 @@
         <v>0.007261</v>
       </c>
       <c r="E54" s="1" t="n">
+        <v>0.007258</v>
+      </c>
+      <c r="F54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="G54" s="1" t="n">
         <v>0.007221</v>
       </c>
     </row>
@@ -1641,9 +1806,12 @@
         <v>3.93</v>
       </c>
       <c r="E55" s="1" t="n">
+        <v>3.929</v>
+      </c>
+      <c r="F55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="G55" s="1" t="n">
         <v>3.925</v>
       </c>
     </row>
@@ -1663,9 +1831,12 @@
         <v>0.017082</v>
       </c>
       <c r="E56" s="1" t="n">
+        <v>0.017116</v>
+      </c>
+      <c r="F56" s="1" t="n">
         <v>0.017208</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="G56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -1685,9 +1856,12 @@
         <v>0.111</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>0.111</v>
+        <v>0.1117</v>
       </c>
       <c r="F57" s="1" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -1707,9 +1881,12 @@
         <v>2.659</v>
       </c>
       <c r="E58" s="1" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="F58" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -1729,9 +1906,12 @@
         <v>0.1604</v>
       </c>
       <c r="E59" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -1751,9 +1931,12 @@
         <v>0.005915</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>0.005918</v>
+        <v>0.00593</v>
       </c>
       <c r="F60" s="1" t="n">
+        <v>0.00593</v>
+      </c>
+      <c r="G60" s="1" t="n">
         <v>0.005914</v>
       </c>
     </row>
@@ -1773,9 +1956,12 @@
         <v>0.09209000000000001</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>0.09209000000000001</v>
+        <v>0.09215</v>
       </c>
       <c r="F61" s="1" t="n">
+        <v>0.09215</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>0.09204</v>
       </c>
     </row>
@@ -1798,6 +1984,9 @@
         <v>0.9154</v>
       </c>
       <c r="F62" s="1" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -1820,6 +2009,9 @@
         <v>0.779</v>
       </c>
       <c r="F63" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="G63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -1839,9 +2031,12 @@
         <v>0.04623</v>
       </c>
       <c r="E64" s="1" t="n">
+        <v>0.04671</v>
+      </c>
+      <c r="F64" s="1" t="n">
         <v>0.04677</v>
       </c>
-      <c r="F64" s="1" t="n">
+      <c r="G64" s="1" t="n">
         <v>0.04623</v>
       </c>
     </row>
@@ -1861,10 +2056,13 @@
         <v>357.66</v>
       </c>
       <c r="E65" s="1" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="F65" s="1" t="n">
         <v>357.66</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>355.34</v>
+      <c r="G65" s="1" t="n">
+        <v>355.08</v>
       </c>
     </row>
     <row r="66">
@@ -1883,10 +2081,13 @@
         <v>0.12782</v>
       </c>
       <c r="E66" s="1" t="n">
+        <v>0.12558</v>
+      </c>
+      <c r="F66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="F66" s="1" t="n">
-        <v>0.12782</v>
+      <c r="G66" s="1" t="n">
+        <v>0.12558</v>
       </c>
     </row>
     <row r="67">
@@ -1905,9 +2106,12 @@
         <v>0.2428</v>
       </c>
       <c r="E67" s="1" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="F67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="G67" s="1" t="n">
         <v>0.2418</v>
       </c>
     </row>
@@ -1930,6 +2134,9 @@
         <v>0.00343</v>
       </c>
       <c r="F68" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="G68" s="1" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -1949,9 +2156,12 @@
         <v>0.1761</v>
       </c>
       <c r="E69" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="F69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="F69" s="1" t="n">
+      <c r="G69" s="1" t="n">
         <v>0.1759</v>
       </c>
     </row>
@@ -1971,9 +2181,12 @@
         <v>0.16421</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>0.16434</v>
+        <v>0.16485</v>
       </c>
       <c r="F70" s="1" t="n">
+        <v>0.16485</v>
+      </c>
+      <c r="G70" s="1" t="n">
         <v>0.16421</v>
       </c>
     </row>
@@ -1993,9 +2206,12 @@
         <v>0.3517</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>0.3541</v>
+        <v>0.3554</v>
       </c>
       <c r="F71" s="1" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G71" s="1" t="n">
         <v>0.3517</v>
       </c>
     </row>
@@ -2015,9 +2231,12 @@
         <v>0.7078</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>0.7078</v>
+        <v>0.7083</v>
       </c>
       <c r="F72" s="1" t="n">
+        <v>0.7083</v>
+      </c>
+      <c r="G72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -2037,9 +2256,12 @@
         <v>0.00873</v>
       </c>
       <c r="E73" s="1" t="n">
+        <v>0.008630000000000001</v>
+      </c>
+      <c r="F73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="F73" s="1" t="n">
+      <c r="G73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -2062,6 +2284,9 @@
         <v>0.006018</v>
       </c>
       <c r="F74" s="1" t="n">
+        <v>0.006018</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>0.006002</v>
       </c>
     </row>
@@ -2081,9 +2306,12 @@
         <v>0.227</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="F75" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="G75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -2103,9 +2331,12 @@
         <v>0.3074</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>0.3074</v>
+        <v>0.3084</v>
       </c>
       <c r="F76" s="1" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="G76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -2125,9 +2356,12 @@
         <v>0.1006</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>0.1006</v>
+        <v>0.1007</v>
       </c>
       <c r="F77" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="G77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -2150,6 +2384,9 @@
         <v>0.1233</v>
       </c>
       <c r="F78" s="1" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="G78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -2169,9 +2406,12 @@
         <v>0.06933</v>
       </c>
       <c r="E79" s="1" t="n">
+        <v>0.06891</v>
+      </c>
+      <c r="F79" s="1" t="n">
         <v>0.06933</v>
       </c>
-      <c r="F79" s="1" t="n">
+      <c r="G79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -2191,9 +2431,12 @@
         <v>0.04655</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>0.04696</v>
+        <v>0.04699</v>
       </c>
       <c r="F80" s="1" t="n">
+        <v>0.04699</v>
+      </c>
+      <c r="G80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -2213,9 +2456,12 @@
         <v>0.000231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>0.000234</v>
+        <v>0.000235</v>
       </c>
       <c r="F81" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="G81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -2235,9 +2481,12 @@
         <v>8.231999999999999</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>8.231999999999999</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="F82" s="1" t="n">
+        <v>8.244999999999999</v>
+      </c>
+      <c r="G82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -2257,10 +2506,13 @@
         <v>0.000594</v>
       </c>
       <c r="E83" s="1" t="n">
+        <v>0.0005892</v>
+      </c>
+      <c r="F83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="F83" s="1" t="n">
-        <v>0.000594</v>
+      <c r="G83" s="1" t="n">
+        <v>0.0005892</v>
       </c>
     </row>
     <row r="84">
@@ -2279,9 +2531,12 @@
         <v>0.4149</v>
       </c>
       <c r="E84" s="1" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="F84" s="1" t="n">
         <v>0.4212</v>
       </c>
-      <c r="F84" s="1" t="n">
+      <c r="G84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -2301,9 +2556,12 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.06279</v>
       </c>
       <c r="F85" s="1" t="n">
+        <v>0.06279</v>
+      </c>
+      <c r="G85" s="1" t="n">
         <v>0.06243</v>
       </c>
     </row>
@@ -2323,10 +2581,13 @@
         <v>0.05455</v>
       </c>
       <c r="E86" s="1" t="n">
+        <v>0.05447</v>
+      </c>
+      <c r="F86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="F86" s="1" t="n">
-        <v>0.05455</v>
+      <c r="G86" s="1" t="n">
+        <v>0.05447</v>
       </c>
     </row>
     <row r="87">
@@ -2345,9 +2606,12 @@
         <v>0.003353</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>0.003353</v>
+        <v>0.003356</v>
       </c>
       <c r="F87" s="1" t="n">
+        <v>0.003356</v>
+      </c>
+      <c r="G87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -2367,9 +2631,12 @@
         <v>0.04994</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>0.04994</v>
+        <v>0.05045</v>
       </c>
       <c r="F88" s="1" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="G88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -2389,9 +2656,12 @@
         <v>0.03077</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>0.03077</v>
+        <v>0.03086</v>
       </c>
       <c r="F89" s="1" t="n">
+        <v>0.03086</v>
+      </c>
+      <c r="G89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -2411,9 +2681,12 @@
         <v>0.3491</v>
       </c>
       <c r="E90" s="1" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="F90" s="1" t="n">
         <v>0.3491</v>
       </c>
-      <c r="F90" s="1" t="n">
+      <c r="G90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -2433,9 +2706,12 @@
         <v>0.061</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>0.061</v>
+        <v>0.06122</v>
       </c>
       <c r="F91" s="1" t="n">
+        <v>0.06122</v>
+      </c>
+      <c r="G91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -2455,9 +2731,12 @@
         <v>0.3527</v>
       </c>
       <c r="E92" s="1" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="F92" s="1" t="n">
         <v>0.3527</v>
       </c>
-      <c r="F92" s="1" t="n">
+      <c r="G92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -2477,9 +2756,12 @@
         <v>1.9716</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>1.9716</v>
+        <v>1.9753</v>
       </c>
       <c r="F93" s="1" t="n">
+        <v>1.9753</v>
+      </c>
+      <c r="G93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -2502,6 +2784,9 @@
         <v>0.2599</v>
       </c>
       <c r="F94" s="1" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="G94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -2521,9 +2806,12 @@
         <v>0.045</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>0.04525</v>
+        <v>0.04542</v>
       </c>
       <c r="F95" s="1" t="n">
+        <v>0.04542</v>
+      </c>
+      <c r="G95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -2543,9 +2831,12 @@
         <v>0.006176</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>0.006176</v>
+        <v>0.006343</v>
       </c>
       <c r="F96" s="1" t="n">
+        <v>0.006343</v>
+      </c>
+      <c r="G96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -2565,10 +2856,13 @@
         <v>0.001739</v>
       </c>
       <c r="E97" s="1" t="n">
+        <v>0.001732</v>
+      </c>
+      <c r="F97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="F97" s="1" t="n">
-        <v>0.001739</v>
+      <c r="G97" s="1" t="n">
+        <v>0.001732</v>
       </c>
     </row>
     <row r="98">
@@ -2587,10 +2881,13 @@
         <v>5.255</v>
       </c>
       <c r="E98" s="1" t="n">
+        <v>5.221</v>
+      </c>
+      <c r="F98" s="1" t="n">
         <v>5.284</v>
       </c>
-      <c r="F98" s="1" t="n">
-        <v>5.251</v>
+      <c r="G98" s="1" t="n">
+        <v>5.221</v>
       </c>
     </row>
     <row r="99">
@@ -2609,9 +2906,12 @@
         <v>0.01523</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>0.01523</v>
+        <v>0.0153</v>
       </c>
       <c r="F99" s="1" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="G99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -2634,6 +2934,9 @@
         <v>0.552</v>
       </c>
       <c r="F100" s="1" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="G100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -2653,9 +2956,12 @@
         <v>0.091</v>
       </c>
       <c r="E101" s="1" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="F101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="F101" s="1" t="n">
+      <c r="G101" s="1" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -2675,9 +2981,12 @@
         <v>32.59</v>
       </c>
       <c r="E102" s="1" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="F102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="F102" s="1" t="n">
+      <c r="G102" s="1" t="n">
         <v>32.48</v>
       </c>
     </row>
@@ -2700,6 +3009,9 @@
         <v>0.03258</v>
       </c>
       <c r="F103" s="1" t="n">
+        <v>0.03258</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -2719,9 +3031,12 @@
         <v>0.06614</v>
       </c>
       <c r="E104" s="1" t="n">
+        <v>0.06612</v>
+      </c>
+      <c r="F104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="F104" s="1" t="n">
+      <c r="G104" s="1" t="n">
         <v>0.06582</v>
       </c>
     </row>
@@ -2741,9 +3056,12 @@
         <v>1.3036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>1.3037</v>
+        <v>1.3041</v>
       </c>
       <c r="F105" s="1" t="n">
+        <v>1.3041</v>
+      </c>
+      <c r="G105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -2763,9 +3081,12 @@
         <v>0.119</v>
       </c>
       <c r="E106" s="1" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="F106" s="1" t="n">
         <v>0.119</v>
       </c>
-      <c r="F106" s="1" t="n">
+      <c r="G106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -2790,6 +3111,9 @@
       <c r="F107" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="G107" s="1" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2807,9 +3131,12 @@
         <v>0.09593</v>
       </c>
       <c r="E108" s="1" t="n">
+        <v>0.09606000000000001</v>
+      </c>
+      <c r="F108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="F108" s="1" t="n">
+      <c r="G108" s="1" t="n">
         <v>0.09589</v>
       </c>
     </row>
@@ -2829,9 +3156,12 @@
         <v>0.13861</v>
       </c>
       <c r="E109" s="1" t="n">
+        <v>0.13987</v>
+      </c>
+      <c r="F109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="F109" s="1" t="n">
+      <c r="G109" s="1" t="n">
         <v>0.13861</v>
       </c>
     </row>
@@ -2851,9 +3181,12 @@
         <v>5.566</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>5.57</v>
+        <v>5.578</v>
       </c>
       <c r="F110" s="1" t="n">
+        <v>5.578</v>
+      </c>
+      <c r="G110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -2873,9 +3206,12 @@
         <v>1.109</v>
       </c>
       <c r="E111" s="1" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="F111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="F111" s="1" t="n">
+      <c r="G111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -2895,10 +3231,13 @@
         <v>0.029647</v>
       </c>
       <c r="E112" s="1" t="n">
+        <v>0.029477</v>
+      </c>
+      <c r="F112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="F112" s="1" t="n">
-        <v>0.029647</v>
+      <c r="G112" s="1" t="n">
+        <v>0.029477</v>
       </c>
     </row>
     <row r="113">
@@ -2917,9 +3256,12 @@
         <v>1.877</v>
       </c>
       <c r="E113" s="1" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="F113" s="1" t="n">
         <v>1.879</v>
       </c>
-      <c r="F113" s="1" t="n">
+      <c r="G113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -2939,10 +3281,13 @@
         <v>0.05997</v>
       </c>
       <c r="E114" s="1" t="n">
+        <v>0.05906</v>
+      </c>
+      <c r="F114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="F114" s="1" t="n">
-        <v>0.05997</v>
+      <c r="G114" s="1" t="n">
+        <v>0.05906</v>
       </c>
     </row>
     <row r="115">
@@ -2961,10 +3306,13 @@
         <v>0.12862</v>
       </c>
       <c r="E115" s="1" t="n">
+        <v>0.12799</v>
+      </c>
+      <c r="F115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="F115" s="1" t="n">
-        <v>0.12862</v>
+      <c r="G115" s="1" t="n">
+        <v>0.12799</v>
       </c>
     </row>
     <row r="116">
@@ -2983,10 +3331,13 @@
         <v>1.1128</v>
       </c>
       <c r="E116" s="1" t="n">
+        <v>1.1055</v>
+      </c>
+      <c r="F116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="F116" s="1" t="n">
-        <v>1.1095</v>
+      <c r="G116" s="1" t="n">
+        <v>1.1055</v>
       </c>
     </row>
     <row r="117">
@@ -3005,9 +3356,12 @@
         <v>0.1561</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>0.1561</v>
+        <v>0.1612</v>
       </c>
       <c r="F117" s="1" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="G117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -3027,9 +3381,12 @@
         <v>0.1583</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>0.1584</v>
+        <v>0.1585</v>
       </c>
       <c r="F118" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="G118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -3049,9 +3406,12 @@
         <v>0.04588</v>
       </c>
       <c r="E119" s="1" t="n">
+        <v>0.04573</v>
+      </c>
+      <c r="F119" s="1" t="n">
         <v>0.04588</v>
       </c>
-      <c r="F119" s="1" t="n">
+      <c r="G119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -3071,9 +3431,12 @@
         <v>3.029</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>3.029</v>
+        <v>3.033</v>
       </c>
       <c r="F120" s="1" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="G120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -3093,9 +3456,12 @@
         <v>0.2972</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>0.2972</v>
+        <v>0.2976</v>
       </c>
       <c r="F121" s="1" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="G121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -3115,9 +3481,12 @@
         <v>0.585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>0.585</v>
+        <v>0.5857</v>
       </c>
       <c r="F122" s="1" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="G122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -3137,10 +3506,13 @@
         <v>0.01261</v>
       </c>
       <c r="E123" s="1" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="F123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="F123" s="1" t="n">
-        <v>0.01261</v>
+      <c r="G123" s="1" t="n">
+        <v>0.0126</v>
       </c>
     </row>
     <row r="124">
@@ -3159,9 +3531,12 @@
         <v>0.1595</v>
       </c>
       <c r="E124" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="F124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="F124" s="1" t="n">
+      <c r="G124" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -3181,9 +3556,12 @@
         <v>0.001783</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>0.001783</v>
+        <v>0.001785</v>
       </c>
       <c r="F125" s="1" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="G125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -3203,10 +3581,13 @@
         <v>0.0004903</v>
       </c>
       <c r="E126" s="1" t="n">
+        <v>0.000489</v>
+      </c>
+      <c r="F126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="F126" s="1" t="n">
-        <v>0.0004894</v>
+      <c r="G126" s="1" t="n">
+        <v>0.000489</v>
       </c>
     </row>
     <row r="127">
@@ -3225,9 +3606,12 @@
         <v>0.02958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>0.02958</v>
+        <v>0.02959</v>
       </c>
       <c r="F127" s="1" t="n">
+        <v>0.02959</v>
+      </c>
+      <c r="G127" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -3247,9 +3631,12 @@
         <v>0.04128</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>0.04128</v>
+        <v>0.04131</v>
       </c>
       <c r="F128" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="G128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -3269,10 +3656,13 @@
         <v>0.0488</v>
       </c>
       <c r="E129" s="1" t="n">
+        <v>0.04858</v>
+      </c>
+      <c r="F129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="F129" s="1" t="n">
-        <v>0.04871</v>
+      <c r="G129" s="1" t="n">
+        <v>0.04858</v>
       </c>
     </row>
     <row r="130">
@@ -3294,6 +3684,9 @@
         <v>1.25e-05</v>
       </c>
       <c r="F130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="G130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -3313,9 +3706,12 @@
         <v>6.7e-06</v>
       </c>
       <c r="E131" s="1" t="n">
+        <v>6.8e-06</v>
+      </c>
+      <c r="F131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="F131" s="1" t="n">
+      <c r="G131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -3335,9 +3731,12 @@
         <v>0.00702</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>0.00702</v>
+        <v>0.00703</v>
       </c>
       <c r="F132" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="G132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -3357,9 +3756,12 @@
         <v>0.097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>0.097</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="F133" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="G133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -3379,9 +3781,12 @@
         <v>0.0004104</v>
       </c>
       <c r="E134" s="1" t="n">
+        <v>0.0004108</v>
+      </c>
+      <c r="F134" s="1" t="n">
         <v>0.0004113</v>
       </c>
-      <c r="F134" s="1" t="n">
+      <c r="G134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -3401,9 +3806,12 @@
         <v>0.08408</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>0.08408</v>
+        <v>0.08426</v>
       </c>
       <c r="F135" s="1" t="n">
+        <v>0.08426</v>
+      </c>
+      <c r="G135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -3423,10 +3831,13 @@
         <v>0.008005</v>
       </c>
       <c r="E136" s="1" t="n">
+        <v>0.007962</v>
+      </c>
+      <c r="F136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="F136" s="1" t="n">
-        <v>0.007984</v>
+      <c r="G136" s="1" t="n">
+        <v>0.007962</v>
       </c>
     </row>
     <row r="137">
@@ -3445,9 +3856,12 @@
         <v>0.0008195</v>
       </c>
       <c r="E137" s="1" t="n">
+        <v>0.0008222</v>
+      </c>
+      <c r="F137" s="1" t="n">
         <v>0.0008262</v>
       </c>
-      <c r="F137" s="1" t="n">
+      <c r="G137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -3467,9 +3881,12 @@
         <v>0.1484</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>0.1484</v>
+        <v>0.1487</v>
       </c>
       <c r="F138" s="1" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="G138" s="1" t="n">
         <v>0.1483</v>
       </c>
     </row>
@@ -3489,9 +3906,12 @@
         <v>0.00673</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>0.00673</v>
+        <v>0.00674</v>
       </c>
       <c r="F139" s="1" t="n">
+        <v>0.00674</v>
+      </c>
+      <c r="G139" s="1" t="n">
         <v>0.006725</v>
       </c>
     </row>
@@ -3511,9 +3931,12 @@
         <v>0.01391</v>
       </c>
       <c r="E140" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="F140" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="F140" s="1" t="n">
+      <c r="G140" s="1" t="n">
         <v>0.01387</v>
       </c>
     </row>
@@ -3533,10 +3956,13 @@
         <v>0.09807</v>
       </c>
       <c r="E141" s="1" t="n">
+        <v>0.09772</v>
+      </c>
+      <c r="F141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="F141" s="1" t="n">
-        <v>0.09807</v>
+      <c r="G141" s="1" t="n">
+        <v>0.09772</v>
       </c>
     </row>
     <row r="142">
@@ -3555,9 +3981,12 @@
         <v>0.05416</v>
       </c>
       <c r="E142" s="1" t="n">
+        <v>0.05413</v>
+      </c>
+      <c r="F142" s="1" t="n">
         <v>0.05416</v>
       </c>
-      <c r="F142" s="1" t="n">
+      <c r="G142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -3577,9 +4006,12 @@
         <v>0.3256</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>0.3256</v>
+        <v>0.3262</v>
       </c>
       <c r="F143" s="1" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="G143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -3599,9 +4031,12 @@
         <v>0.02583</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>0.02586</v>
+        <v>0.02588</v>
       </c>
       <c r="F144" s="1" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="G144" s="1" t="n">
         <v>0.02576</v>
       </c>
     </row>
@@ -3621,9 +4056,12 @@
         <v>0.2377</v>
       </c>
       <c r="E145" s="1" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="F145" s="1" t="n">
         <v>0.238</v>
       </c>
-      <c r="F145" s="1" t="n">
+      <c r="G145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -3643,9 +4081,12 @@
         <v>0.007125</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>0.007125</v>
+        <v>0.007129</v>
       </c>
       <c r="F146" s="1" t="n">
+        <v>0.007129</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>0.007066</v>
       </c>
     </row>
@@ -3665,9 +4106,12 @@
         <v>0.08734</v>
       </c>
       <c r="E147" s="1" t="n">
+        <v>0.08703</v>
+      </c>
+      <c r="F147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="F147" s="1" t="n">
+      <c r="G147" s="1" t="n">
         <v>0.08695</v>
       </c>
     </row>
@@ -3687,9 +4131,12 @@
         <v>0.05045</v>
       </c>
       <c r="E148" s="1" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="F148" s="1" t="n">
         <v>0.05072</v>
       </c>
-      <c r="F148" s="1" t="n">
+      <c r="G148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -3709,9 +4156,12 @@
         <v>0.02391</v>
       </c>
       <c r="E149" s="1" t="n">
+        <v>0.02393</v>
+      </c>
+      <c r="F149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="F149" s="1" t="n">
+      <c r="G149" s="1" t="n">
         <v>0.02391</v>
       </c>
     </row>
@@ -3731,10 +4181,13 @@
         <v>0.08608</v>
       </c>
       <c r="E150" s="1" t="n">
+        <v>0.08606999999999999</v>
+      </c>
+      <c r="F150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="F150" s="1" t="n">
-        <v>0.08608</v>
+      <c r="G150" s="1" t="n">
+        <v>0.08606999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -3753,10 +4206,13 @@
         <v>0.02341</v>
       </c>
       <c r="E151" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="F151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="F151" s="1" t="n">
-        <v>0.02341</v>
+      <c r="G151" s="1" t="n">
+        <v>0.02329</v>
       </c>
     </row>
     <row r="152">
@@ -3775,9 +4231,12 @@
         <v>0.02579</v>
       </c>
       <c r="E152" s="1" t="n">
+        <v>0.02582</v>
+      </c>
+      <c r="F152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="F152" s="1" t="n">
+      <c r="G152" s="1" t="n">
         <v>0.02577</v>
       </c>
     </row>
@@ -3797,9 +4256,12 @@
         <v>0.0002098</v>
       </c>
       <c r="E153" s="1" t="n">
+        <v>0.0002098</v>
+      </c>
+      <c r="F153" s="1" t="n">
         <v>0.0002102</v>
       </c>
-      <c r="F153" s="1" t="n">
+      <c r="G153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -3819,9 +4281,12 @@
         <v>0.4442</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>0.4442</v>
+        <v>0.4457</v>
       </c>
       <c r="F154" s="1" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="G154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -3841,10 +4306,13 @@
         <v>0.06693</v>
       </c>
       <c r="E155" s="1" t="n">
+        <v>0.06662999999999999</v>
+      </c>
+      <c r="F155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="F155" s="1" t="n">
-        <v>0.06693</v>
+      <c r="G155" s="1" t="n">
+        <v>0.06662999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -3863,9 +4331,12 @@
         <v>0.12833</v>
       </c>
       <c r="E156" s="1" t="n">
+        <v>0.12848</v>
+      </c>
+      <c r="F156" s="1" t="n">
         <v>0.12859</v>
       </c>
-      <c r="F156" s="1" t="n">
+      <c r="G156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -3885,9 +4356,12 @@
         <v>0.4844</v>
       </c>
       <c r="E157" s="1" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="F157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="F157" s="1" t="n">
+      <c r="G157" s="1" t="n">
         <v>0.4844</v>
       </c>
     </row>
@@ -3907,9 +4381,12 @@
         <v>0.4476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>0.4479</v>
+        <v>0.4523</v>
       </c>
       <c r="F158" s="1" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -3929,9 +4406,12 @@
         <v>0.007533</v>
       </c>
       <c r="E159" s="1" t="n">
+        <v>0.007552</v>
+      </c>
+      <c r="F159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="F159" s="1" t="n">
+      <c r="G159" s="1" t="n">
         <v>0.007528</v>
       </c>
     </row>
@@ -3951,9 +4431,12 @@
         <v>0.00465</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>0.00465</v>
+        <v>0.004655</v>
       </c>
       <c r="F160" s="1" t="n">
+        <v>0.004655</v>
+      </c>
+      <c r="G160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -3973,9 +4456,12 @@
         <v>0.004304</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>0.004306</v>
+        <v>0.004314</v>
       </c>
       <c r="F161" s="1" t="n">
+        <v>0.004314</v>
+      </c>
+      <c r="G161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -3995,9 +4481,12 @@
         <v>0.0964</v>
       </c>
       <c r="E162" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="F162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="F162" s="1" t="n">
+      <c r="G162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -4017,9 +4506,12 @@
         <v>0.2861</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>0.2861</v>
+        <v>0.2865</v>
       </c>
       <c r="F163" s="1" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -4039,9 +4531,12 @@
         <v>0.1146</v>
       </c>
       <c r="E164" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="F164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="F164" s="1" t="n">
+      <c r="G164" s="1" t="n">
         <v>0.1145</v>
       </c>
     </row>
@@ -4061,9 +4556,12 @@
         <v>0.1758</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>0.1758</v>
+        <v>0.1761</v>
       </c>
       <c r="F165" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="G165" s="1" t="n">
         <v>0.1756</v>
       </c>
     </row>
@@ -4086,6 +4584,9 @@
         <v>0.01008</v>
       </c>
       <c r="F166" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="G166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -4105,9 +4606,12 @@
         <v>1.834</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>1.834</v>
+        <v>1.836</v>
       </c>
       <c r="F167" s="1" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>1.827</v>
       </c>
     </row>
@@ -4127,9 +4631,12 @@
         <v>1.35</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>1.35</v>
+        <v>1.363</v>
       </c>
       <c r="F168" s="1" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="G168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -4149,9 +4656,12 @@
         <v>0.007333</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>0.007333</v>
+        <v>0.007335</v>
       </c>
       <c r="F169" s="1" t="n">
+        <v>0.007335</v>
+      </c>
+      <c r="G169" s="1" t="n">
         <v>0.007321</v>
       </c>
     </row>
@@ -4171,10 +4681,13 @@
         <v>0.0116</v>
       </c>
       <c r="E170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="F170" s="1" t="n">
-        <v>0.0116</v>
+      <c r="G170" s="1" t="n">
+        <v>0.0115</v>
       </c>
     </row>
     <row r="171">
@@ -4193,9 +4706,12 @@
         <v>0.005827</v>
       </c>
       <c r="E171" s="1" t="n">
+        <v>0.005816</v>
+      </c>
+      <c r="F171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="F171" s="1" t="n">
+      <c r="G171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -4215,9 +4731,12 @@
         <v>0.14737</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>0.14737</v>
+        <v>0.14796</v>
       </c>
       <c r="F172" s="1" t="n">
+        <v>0.14796</v>
+      </c>
+      <c r="G172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -4237,9 +4756,12 @@
         <v>4.9</v>
       </c>
       <c r="E173" s="1" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="F173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="F173" s="1" t="n">
+      <c r="G173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -4259,9 +4781,12 @@
         <v>0.07982</v>
       </c>
       <c r="E174" s="1" t="n">
+        <v>0.07924</v>
+      </c>
+      <c r="F174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="F174" s="1" t="n">
+      <c r="G174" s="1" t="n">
         <v>0.07868</v>
       </c>
     </row>
@@ -4281,9 +4806,12 @@
         <v>0.007502</v>
       </c>
       <c r="E175" s="1" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="F175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="F175" s="1" t="n">
+      <c r="G175" s="1" t="n">
         <v>0.007488</v>
       </c>
     </row>
@@ -4303,9 +4831,12 @@
         <v>0.2016</v>
       </c>
       <c r="E176" s="1" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="F176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="F176" s="1" t="n">
+      <c r="G176" s="1" t="n">
         <v>0.2016</v>
       </c>
     </row>
@@ -4325,9 +4856,12 @@
         <v>0.0519</v>
       </c>
       <c r="E177" s="1" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="F177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="F177" s="1" t="n">
+      <c r="G177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -4347,9 +4881,12 @@
         <v>0.05455</v>
       </c>
       <c r="E178" s="1" t="n">
+        <v>0.05464</v>
+      </c>
+      <c r="F178" s="1" t="n">
         <v>0.05465</v>
       </c>
-      <c r="F178" s="1" t="n">
+      <c r="G178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -4369,9 +4906,12 @@
         <v>0.02324</v>
       </c>
       <c r="E179" s="1" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="F179" s="1" t="n">
+      <c r="G179" s="1" t="n">
         <v>0.02324</v>
       </c>
     </row>
@@ -4391,9 +4931,12 @@
         <v>0.6946</v>
       </c>
       <c r="E180" s="1" t="n">
+        <v>0.6941000000000001</v>
+      </c>
+      <c r="F180" s="1" t="n">
         <v>0.6951000000000001</v>
       </c>
-      <c r="F180" s="1" t="n">
+      <c r="G180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -4413,9 +4956,12 @@
         <v>0.0003724</v>
       </c>
       <c r="E181" s="1" t="n">
+        <v>0.0003727</v>
+      </c>
+      <c r="F181" s="1" t="n">
         <v>0.0003731</v>
       </c>
-      <c r="F181" s="1" t="n">
+      <c r="G181" s="1" t="n">
         <v>0.0003724</v>
       </c>
     </row>
@@ -4435,10 +4981,13 @@
         <v>0.01274</v>
       </c>
       <c r="E182" s="1" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="F182" s="1" t="n">
-        <v>0.01273</v>
+      <c r="G182" s="1" t="n">
+        <v>0.0127</v>
       </c>
     </row>
     <row r="183">
@@ -4457,9 +5006,12 @@
         <v>4.277</v>
       </c>
       <c r="E183" s="1" t="n">
+        <v>4.266</v>
+      </c>
+      <c r="F183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="F183" s="1" t="n">
+      <c r="G183" s="1" t="n">
         <v>4.265</v>
       </c>
     </row>
@@ -4479,10 +5031,13 @@
         <v>0.2369</v>
       </c>
       <c r="E184" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="F184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="F184" s="1" t="n">
-        <v>0.2369</v>
+      <c r="G184" s="1" t="n">
+        <v>0.2368</v>
       </c>
     </row>
     <row r="185">
@@ -4501,9 +5056,12 @@
         <v>0.03772</v>
       </c>
       <c r="E185" s="1" t="n">
+        <v>0.03774</v>
+      </c>
+      <c r="F185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="F185" s="1" t="n">
+      <c r="G185" s="1" t="n">
         <v>0.03769</v>
       </c>
     </row>
@@ -4523,9 +5081,12 @@
         <v>0.11573</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>0.11619</v>
+        <v>0.11628</v>
       </c>
       <c r="F186" s="1" t="n">
+        <v>0.11628</v>
+      </c>
+      <c r="G186" s="1" t="n">
         <v>0.11573</v>
       </c>
     </row>
@@ -4545,9 +5106,12 @@
         <v>0.009131</v>
       </c>
       <c r="E187" s="1" t="n">
+        <v>0.009186</v>
+      </c>
+      <c r="F187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="F187" s="1" t="n">
+      <c r="G187" s="1" t="n">
         <v>0.009131</v>
       </c>
     </row>
@@ -4567,9 +5131,12 @@
         <v>0.0977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>0.0977</v>
+        <v>0.0978</v>
       </c>
       <c r="F188" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="G188" s="1" t="n">
         <v>0.0975</v>
       </c>
     </row>
@@ -4589,9 +5156,12 @@
         <v>0.02808</v>
       </c>
       <c r="E189" s="1" t="n">
+        <v>0.02796</v>
+      </c>
+      <c r="F189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="F189" s="1" t="n">
+      <c r="G189" s="1" t="n">
         <v>0.02774</v>
       </c>
     </row>
@@ -4611,9 +5181,12 @@
         <v>0.00877</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>0.008840000000000001</v>
+        <v>0.00886</v>
       </c>
       <c r="F190" s="1" t="n">
+        <v>0.00886</v>
+      </c>
+      <c r="G190" s="1" t="n">
         <v>0.00873</v>
       </c>
     </row>
@@ -4633,9 +5206,12 @@
         <v>0.001956</v>
       </c>
       <c r="E191" s="1" t="n">
+        <v>0.001954</v>
+      </c>
+      <c r="F191" s="1" t="n">
         <v>0.001956</v>
       </c>
-      <c r="F191" s="1" t="n">
+      <c r="G191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -4655,9 +5231,12 @@
         <v>0.1003</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>0.1005</v>
+        <v>0.1009</v>
       </c>
       <c r="F192" s="1" t="n">
+        <v>0.1009</v>
+      </c>
+      <c r="G192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -4677,9 +5256,12 @@
         <v>0.02325</v>
       </c>
       <c r="E193" s="1" t="n">
+        <v>0.02333</v>
+      </c>
+      <c r="F193" s="1" t="n">
         <v>0.02334</v>
       </c>
-      <c r="F193" s="1" t="n">
+      <c r="G193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -4699,9 +5281,12 @@
         <v>0.01351</v>
       </c>
       <c r="E194" s="1" t="n">
+        <v>0.01349</v>
+      </c>
+      <c r="F194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="F194" s="1" t="n">
+      <c r="G194" s="1" t="n">
         <v>0.01349</v>
       </c>
     </row>
@@ -4721,9 +5306,12 @@
         <v>0.02095</v>
       </c>
       <c r="E195" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="F195" s="1" t="n">
+      <c r="G195" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -4743,9 +5331,12 @@
         <v>0.17143</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>0.17143</v>
+        <v>0.17221</v>
       </c>
       <c r="F196" s="1" t="n">
+        <v>0.17221</v>
+      </c>
+      <c r="G196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -4765,10 +5356,13 @@
         <v>0.007351</v>
       </c>
       <c r="E197" s="1" t="n">
+        <v>0.007292</v>
+      </c>
+      <c r="F197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="F197" s="1" t="n">
-        <v>0.007351</v>
+      <c r="G197" s="1" t="n">
+        <v>0.007292</v>
       </c>
     </row>
     <row r="198">
@@ -4787,9 +5381,12 @@
         <v>0.01909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>0.01909</v>
+        <v>0.0191</v>
       </c>
       <c r="F198" s="1" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="G198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -4809,10 +5406,13 @@
         <v>0.01634</v>
       </c>
       <c r="E199" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="F199" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="F199" s="1" t="n">
-        <v>0.01634</v>
+      <c r="G199" s="1" t="n">
+        <v>0.01631</v>
       </c>
     </row>
     <row r="200">
@@ -4834,6 +5434,9 @@
         <v>0.2975</v>
       </c>
       <c r="F200" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="G200" s="1" t="n">
         <v>0.2966</v>
       </c>
     </row>
@@ -4853,10 +5456,13 @@
         <v>0.006235</v>
       </c>
       <c r="E201" s="1" t="n">
+        <v>0.006223</v>
+      </c>
+      <c r="F201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="F201" s="1" t="n">
-        <v>0.006231</v>
+      <c r="G201" s="1" t="n">
+        <v>0.006223</v>
       </c>
     </row>
     <row r="202">
@@ -4875,9 +5481,12 @@
         <v>0.0004457</v>
       </c>
       <c r="E202" s="1" t="n">
+        <v>0.0004461</v>
+      </c>
+      <c r="F202" s="1" t="n">
         <v>0.0004463</v>
       </c>
-      <c r="F202" s="1" t="n">
+      <c r="G202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -4897,9 +5506,12 @@
         <v>0.007385</v>
       </c>
       <c r="E203" s="1" t="n">
+        <v>0.007375</v>
+      </c>
+      <c r="F203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="F203" s="1" t="n">
+      <c r="G203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -4919,9 +5531,12 @@
         <v>0.1289</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>0.1289</v>
+        <v>0.1294</v>
       </c>
       <c r="F204" s="1" t="n">
+        <v>0.1294</v>
+      </c>
+      <c r="G204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -4941,9 +5556,12 @@
         <v>0.01444</v>
       </c>
       <c r="E205" s="1" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="F205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="F205" s="1" t="n">
+      <c r="G205" s="1" t="n">
         <v>0.01444</v>
       </c>
     </row>
@@ -4963,10 +5581,13 @@
         <v>0.003599</v>
       </c>
       <c r="E206" s="1" t="n">
+        <v>0.003566</v>
+      </c>
+      <c r="F206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="F206" s="1" t="n">
-        <v>0.003599</v>
+      <c r="G206" s="1" t="n">
+        <v>0.003566</v>
       </c>
     </row>
     <row r="207">
@@ -4985,9 +5606,12 @@
         <v>0.05974</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>0.05974</v>
+        <v>0.05999</v>
       </c>
       <c r="F207" s="1" t="n">
+        <v>0.05999</v>
+      </c>
+      <c r="G207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -5007,9 +5631,12 @@
         <v>15.42</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>15.42</v>
+        <v>15.45</v>
       </c>
       <c r="F208" s="1" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="G208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -5029,10 +5656,13 @@
         <v>5185.7</v>
       </c>
       <c r="E209" s="1" t="n">
+        <v>5184.2</v>
+      </c>
+      <c r="F209" s="1" t="n">
         <v>5186.2</v>
       </c>
-      <c r="F209" s="1" t="n">
-        <v>5185.6</v>
+      <c r="G209" s="1" t="n">
+        <v>5184.2</v>
       </c>
     </row>
     <row r="210">
@@ -5051,9 +5681,12 @@
         <v>0.12006</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>0.12039</v>
+        <v>0.12042</v>
       </c>
       <c r="F210" s="1" t="n">
+        <v>0.12042</v>
+      </c>
+      <c r="G210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -5073,10 +5706,13 @@
         <v>0.1839</v>
       </c>
       <c r="E211" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="F211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="F211" s="1" t="n">
-        <v>0.1832</v>
+      <c r="G211" s="1" t="n">
+        <v>0.1828</v>
       </c>
     </row>
     <row r="212">
@@ -5095,9 +5731,12 @@
         <v>0.0298</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>0.0302</v>
+        <v>0.0303</v>
       </c>
       <c r="F212" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="G212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -5117,9 +5756,12 @@
         <v>1.3966</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>1.3966</v>
+        <v>1.3976</v>
       </c>
       <c r="F213" s="1" t="n">
+        <v>1.3976</v>
+      </c>
+      <c r="G213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -5139,9 +5781,12 @@
         <v>0.0566</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>0.05661</v>
+        <v>0.05662</v>
       </c>
       <c r="F214" s="1" t="n">
+        <v>0.05662</v>
+      </c>
+      <c r="G214" s="1" t="n">
         <v>0.05658</v>
       </c>
     </row>
@@ -5161,9 +5806,12 @@
         <v>0.04385</v>
       </c>
       <c r="E215" s="1" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="F215" s="1" t="n">
         <v>0.04385</v>
       </c>
-      <c r="F215" s="1" t="n">
+      <c r="G215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -5183,9 +5831,12 @@
         <v>0.15108</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>0.15121</v>
+        <v>0.15123</v>
       </c>
       <c r="F216" s="1" t="n">
+        <v>0.15123</v>
+      </c>
+      <c r="G216" s="1" t="n">
         <v>0.15102</v>
       </c>
     </row>
@@ -5205,9 +5856,12 @@
         <v>0.074</v>
       </c>
       <c r="E217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="F217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="F217" s="1" t="n">
+      <c r="G217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -5227,9 +5881,12 @@
         <v>0.00267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>0.00267</v>
+        <v>0.00268</v>
       </c>
       <c r="F218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="G218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -5249,9 +5906,12 @@
         <v>0.01719</v>
       </c>
       <c r="E219" s="1" t="n">
+        <v>0.01719</v>
+      </c>
+      <c r="F219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="F219" s="1" t="n">
+      <c r="G219" s="1" t="n">
         <v>0.01716</v>
       </c>
     </row>
@@ -5271,9 +5931,12 @@
         <v>0.05533</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>0.05533</v>
+        <v>0.05535</v>
       </c>
       <c r="F220" s="1" t="n">
+        <v>0.05535</v>
+      </c>
+      <c r="G220" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -5293,9 +5956,12 @@
         <v>0.0219</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>0.0219</v>
+        <v>0.02196</v>
       </c>
       <c r="F221" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="G221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -5315,9 +5981,12 @@
         <v>0.0094</v>
       </c>
       <c r="E222" s="1" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="F222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="F222" s="1" t="n">
+      <c r="G222" s="1" t="n">
         <v>0.009379999999999999</v>
       </c>
     </row>
@@ -5342,6 +6011,9 @@
       <c r="F223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="G223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5359,9 +6031,12 @@
         <v>0.0383</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>0.0383</v>
+        <v>0.03841</v>
       </c>
       <c r="F224" s="1" t="n">
+        <v>0.03841</v>
+      </c>
+      <c r="G224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -5381,9 +6056,12 @@
         <v>0.00153</v>
       </c>
       <c r="E225" s="1" t="n">
+        <v>0.001529</v>
+      </c>
+      <c r="F225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="F225" s="1" t="n">
+      <c r="G225" s="1" t="n">
         <v>0.001526</v>
       </c>
     </row>
@@ -5403,10 +6081,13 @@
         <v>27.18</v>
       </c>
       <c r="E226" s="1" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="F226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="F226" s="1" t="n">
-        <v>27.1</v>
+      <c r="G226" s="1" t="n">
+        <v>27.05</v>
       </c>
     </row>
     <row r="227">
@@ -5425,9 +6106,12 @@
         <v>0.07027</v>
       </c>
       <c r="E227" s="1" t="n">
+        <v>0.07023</v>
+      </c>
+      <c r="F227" s="1" t="n">
         <v>0.07027</v>
       </c>
-      <c r="F227" s="1" t="n">
+      <c r="G227" s="1" t="n">
         <v>0.0702</v>
       </c>
     </row>
@@ -5447,9 +6131,12 @@
         <v>0.3121</v>
       </c>
       <c r="E228" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="F228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="F228" s="1" t="n">
+      <c r="G228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -5472,6 +6159,9 @@
         <v>18.46</v>
       </c>
       <c r="F229" s="1" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="G229" s="1" t="n">
         <v>18.42</v>
       </c>
     </row>
@@ -5491,10 +6181,13 @@
         <v>0.01946</v>
       </c>
       <c r="E230" s="1" t="n">
+        <v>0.01939</v>
+      </c>
+      <c r="F230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="F230" s="1" t="n">
-        <v>0.01946</v>
+      <c r="G230" s="1" t="n">
+        <v>0.01939</v>
       </c>
     </row>
     <row r="231">
@@ -5513,9 +6206,12 @@
         <v>0.01224</v>
       </c>
       <c r="E231" s="1" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="F231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="F231" s="1" t="n">
+      <c r="G231" s="1" t="n">
         <v>0.01221</v>
       </c>
     </row>
@@ -5535,9 +6231,12 @@
         <v>0.2293</v>
       </c>
       <c r="E232" s="1" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="F232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="F232" s="1" t="n">
+      <c r="G232" s="1" t="n">
         <v>0.2285</v>
       </c>
     </row>
@@ -5557,9 +6256,12 @@
         <v>0.0713</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>0.0713</v>
+        <v>0.07136000000000001</v>
       </c>
       <c r="F233" s="1" t="n">
+        <v>0.07136000000000001</v>
+      </c>
+      <c r="G233" s="1" t="n">
         <v>0.07113999999999999</v>
       </c>
     </row>
@@ -5579,9 +6281,12 @@
         <v>0.1704</v>
       </c>
       <c r="E234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="F234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="F234" s="1" t="n">
+      <c r="G234" s="1" t="n">
         <v>0.1701</v>
       </c>
     </row>
@@ -5604,6 +6309,9 @@
         <v>0.0253</v>
       </c>
       <c r="F235" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="G235" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -5623,9 +6331,12 @@
         <v>0.03013</v>
       </c>
       <c r="E236" s="1" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="F236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="F236" s="1" t="n">
+      <c r="G236" s="1" t="n">
         <v>0.03006</v>
       </c>
     </row>
@@ -5645,9 +6356,12 @@
         <v>1.987</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>1.987</v>
+        <v>1.993</v>
       </c>
       <c r="F237" s="1" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="G237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -5667,9 +6381,12 @@
         <v>0.4295</v>
       </c>
       <c r="E238" s="1" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="F238" s="1" t="n">
         <v>0.4295</v>
       </c>
-      <c r="F238" s="1" t="n">
+      <c r="G238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -5689,10 +6406,13 @@
         <v>0.03374</v>
       </c>
       <c r="E239" s="1" t="n">
+        <v>0.03363</v>
+      </c>
+      <c r="F239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="F239" s="1" t="n">
-        <v>0.03367</v>
+      <c r="G239" s="1" t="n">
+        <v>0.03363</v>
       </c>
     </row>
     <row r="240">
@@ -5711,9 +6431,12 @@
         <v>0.03408</v>
       </c>
       <c r="E240" s="1" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="F240" s="1" t="n">
         <v>0.03408</v>
       </c>
-      <c r="F240" s="1" t="n">
+      <c r="G240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -5733,9 +6456,12 @@
         <v>0.0007551</v>
       </c>
       <c r="E241" s="1" t="n">
+        <v>0.0007534</v>
+      </c>
+      <c r="F241" s="1" t="n">
         <v>0.0007551</v>
       </c>
-      <c r="F241" s="1" t="n">
+      <c r="G241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -5755,9 +6481,12 @@
         <v>0.1839</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>0.1839</v>
+        <v>0.1847</v>
       </c>
       <c r="F242" s="1" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="G242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -5777,10 +6506,13 @@
         <v>0.014828</v>
       </c>
       <c r="E243" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="F243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="F243" s="1" t="n">
-        <v>0.014827</v>
+      <c r="G243" s="1" t="n">
+        <v>0.01482</v>
       </c>
     </row>
     <row r="244">
@@ -5799,9 +6531,12 @@
         <v>3.08e-05</v>
       </c>
       <c r="E244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="F244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="F244" s="1" t="n">
+      <c r="G244" s="1" t="n">
         <v>3.08e-05</v>
       </c>
     </row>
@@ -5821,9 +6556,12 @@
         <v>0.03523</v>
       </c>
       <c r="E245" s="1" t="n">
+        <v>0.03525</v>
+      </c>
+      <c r="F245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="F245" s="1" t="n">
+      <c r="G245" s="1" t="n">
         <v>0.03521</v>
       </c>
     </row>
@@ -5843,9 +6581,12 @@
         <v>0.08066</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>0.08066</v>
+        <v>0.08076</v>
       </c>
       <c r="F246" s="1" t="n">
+        <v>0.08076</v>
+      </c>
+      <c r="G246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -5865,9 +6606,12 @@
         <v>0.007318</v>
       </c>
       <c r="E247" s="1" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="F247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="F247" s="1" t="n">
+      <c r="G247" s="1" t="n">
         <v>0.007318</v>
       </c>
     </row>
@@ -5887,9 +6631,12 @@
         <v>0.09855999999999999</v>
       </c>
       <c r="E248" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="F248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="F248" s="1" t="n">
+      <c r="G248" s="1" t="n">
         <v>0.09717000000000001</v>
       </c>
     </row>
@@ -5912,6 +6659,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="F249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="G249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -5931,9 +6681,12 @@
         <v>0.03516</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>0.03516</v>
+        <v>0.03521</v>
       </c>
       <c r="F250" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="G250" s="1" t="n">
         <v>0.03504</v>
       </c>
     </row>
@@ -5953,9 +6706,12 @@
         <v>0.04086</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>0.04086</v>
+        <v>0.04087</v>
       </c>
       <c r="F251" s="1" t="n">
+        <v>0.04087</v>
+      </c>
+      <c r="G251" s="1" t="n">
         <v>0.04058</v>
       </c>
     </row>
@@ -5975,9 +6731,12 @@
         <v>0.0891</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>0.0893</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="F252" s="1" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="G252" s="1" t="n">
         <v>0.0891</v>
       </c>
     </row>
@@ -5997,9 +6756,12 @@
         <v>4.085</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>4.085</v>
+        <v>4.088</v>
       </c>
       <c r="F253" s="1" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="G253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -6019,9 +6781,12 @@
         <v>0.1874</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>0.1874</v>
+        <v>0.1875</v>
       </c>
       <c r="F254" s="1" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="G254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -6041,10 +6806,13 @@
         <v>0.07275</v>
       </c>
       <c r="E255" s="1" t="n">
+        <v>0.07273</v>
+      </c>
+      <c r="F255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="F255" s="1" t="n">
-        <v>0.07275</v>
+      <c r="G255" s="1" t="n">
+        <v>0.07273</v>
       </c>
     </row>
     <row r="256">
@@ -6063,9 +6831,12 @@
         <v>0.01817</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>0.01817</v>
+        <v>0.01828</v>
       </c>
       <c r="F256" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="G256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -6085,9 +6856,12 @@
         <v>5.955</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>5.956</v>
+        <v>5.957</v>
       </c>
       <c r="F257" s="1" t="n">
+        <v>5.957</v>
+      </c>
+      <c r="G257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -6107,9 +6881,12 @@
         <v>0.2636</v>
       </c>
       <c r="E258" s="1" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="F258" s="1" t="n">
         <v>0.2639</v>
       </c>
-      <c r="F258" s="1" t="n">
+      <c r="G258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -6129,9 +6906,12 @@
         <v>0.1365</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>0.1365</v>
+        <v>0.1369</v>
       </c>
       <c r="F259" s="1" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="G259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -6151,9 +6931,12 @@
         <v>0.30537</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>0.30595</v>
+        <v>0.30606</v>
       </c>
       <c r="F260" s="1" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="G260" s="1" t="n">
         <v>0.30537</v>
       </c>
     </row>
@@ -6173,9 +6956,12 @@
         <v>0.09828000000000001</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>0.09828000000000001</v>
+        <v>0.09862</v>
       </c>
       <c r="F261" s="1" t="n">
+        <v>0.09862</v>
+      </c>
+      <c r="G261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -6195,9 +6981,12 @@
         <v>0.544</v>
       </c>
       <c r="E262" s="1" t="n">
+        <v>0.5434</v>
+      </c>
+      <c r="F262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="F262" s="1" t="n">
+      <c r="G262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -6217,9 +7006,12 @@
         <v>0.2925</v>
       </c>
       <c r="E263" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="F263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="F263" s="1" t="n">
+      <c r="G263" s="1" t="n">
         <v>0.2923</v>
       </c>
     </row>
@@ -6239,9 +7031,12 @@
         <v>0.951</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>0.951</v>
+        <v>0.953</v>
       </c>
       <c r="F264" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="G264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -6261,9 +7056,12 @@
         <v>0.5405</v>
       </c>
       <c r="E265" s="1" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="F265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="F265" s="1" t="n">
+      <c r="G265" s="1" t="n">
         <v>0.5405</v>
       </c>
     </row>
@@ -6283,9 +7081,12 @@
         <v>0.07388</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>0.07388</v>
+        <v>0.074</v>
       </c>
       <c r="F266" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="G266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -6305,9 +7106,12 @@
         <v>0.02142</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>0.02142</v>
+        <v>0.02151</v>
       </c>
       <c r="F267" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="G267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -6327,9 +7131,12 @@
         <v>0.01613</v>
       </c>
       <c r="E268" s="1" t="n">
+        <v>0.01609</v>
+      </c>
+      <c r="F268" s="1" t="n">
         <v>0.01622</v>
       </c>
-      <c r="F268" s="1" t="n">
+      <c r="G268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -6349,9 +7156,12 @@
         <v>0.003708</v>
       </c>
       <c r="E269" s="1" t="n">
+        <v>0.003709</v>
+      </c>
+      <c r="F269" s="1" t="n">
         <v>0.003717</v>
       </c>
-      <c r="F269" s="1" t="n">
+      <c r="G269" s="1" t="n">
         <v>0.003708</v>
       </c>
     </row>
@@ -6371,10 +7181,13 @@
         <v>0.00779</v>
       </c>
       <c r="E270" s="1" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="F270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="F270" s="1" t="n">
-        <v>0.00779</v>
+      <c r="G270" s="1" t="n">
+        <v>0.00769</v>
       </c>
     </row>
     <row r="271">
@@ -6393,9 +7206,12 @@
         <v>0.0551</v>
       </c>
       <c r="E271" s="1" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="F271" s="1" t="n">
         <v>0.0551</v>
       </c>
-      <c r="F271" s="1" t="n">
+      <c r="G271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -6415,9 +7231,12 @@
         <v>2.301</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>2.301</v>
+        <v>2.311</v>
       </c>
       <c r="F272" s="1" t="n">
+        <v>2.311</v>
+      </c>
+      <c r="G272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -6437,9 +7256,12 @@
         <v>0.05464</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>0.05464</v>
+        <v>0.0547</v>
       </c>
       <c r="F273" s="1" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="G273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -6459,9 +7281,12 @@
         <v>0.02291</v>
       </c>
       <c r="E274" s="1" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="F274" s="1" t="n">
         <v>0.02291</v>
       </c>
-      <c r="F274" s="1" t="n">
+      <c r="G274" s="1" t="n">
         <v>0.02286</v>
       </c>
     </row>
@@ -6481,9 +7306,12 @@
         <v>1.193</v>
       </c>
       <c r="E275" s="1" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="F275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="F275" s="1" t="n">
+      <c r="G275" s="1" t="n">
         <v>1.185</v>
       </c>
     </row>
@@ -6503,10 +7331,13 @@
         <v>0.2732</v>
       </c>
       <c r="E276" s="1" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="F276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="F276" s="1" t="n">
-        <v>0.2728</v>
+      <c r="G276" s="1" t="n">
+        <v>0.2723</v>
       </c>
     </row>
     <row r="277">
@@ -6525,10 +7356,13 @@
         <v>0.95</v>
       </c>
       <c r="E277" s="1" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="F277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="F277" s="1" t="n">
-        <v>0.95</v>
+      <c r="G277" s="1" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="278">
@@ -6547,9 +7381,12 @@
         <v>0.6256</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>0.6256</v>
+        <v>0.6257</v>
       </c>
       <c r="F278" s="1" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="G278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -6569,9 +7406,12 @@
         <v>0.001353</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>0.001353</v>
+        <v>0.001362</v>
       </c>
       <c r="F279" s="1" t="n">
+        <v>0.001362</v>
+      </c>
+      <c r="G279" s="1" t="n">
         <v>0.00135</v>
       </c>
     </row>
@@ -6591,9 +7431,12 @@
         <v>0.005553</v>
       </c>
       <c r="E280" s="1" t="n">
+        <v>0.005546</v>
+      </c>
+      <c r="F280" s="1" t="n">
         <v>0.005553</v>
       </c>
-      <c r="F280" s="1" t="n">
+      <c r="G280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -6613,9 +7456,12 @@
         <v>1.525</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>1.525</v>
+        <v>1.526</v>
       </c>
       <c r="F281" s="1" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="G281" s="1" t="n">
         <v>1.522</v>
       </c>
     </row>
@@ -6635,9 +7481,12 @@
         <v>28.42</v>
       </c>
       <c r="E282" s="1" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="F282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="F282" s="1" t="n">
+      <c r="G282" s="1" t="n">
         <v>28.36</v>
       </c>
     </row>
@@ -6657,9 +7506,12 @@
         <v>0.12942</v>
       </c>
       <c r="E283" s="1" t="n">
+        <v>0.12935</v>
+      </c>
+      <c r="F283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="F283" s="1" t="n">
+      <c r="G283" s="1" t="n">
         <v>0.12935</v>
       </c>
     </row>
@@ -6679,9 +7531,12 @@
         <v>0.01112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>0.01113</v>
+        <v>0.01114</v>
       </c>
       <c r="F284" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="G284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -6701,9 +7556,12 @@
         <v>6.509</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>6.509</v>
+        <v>6.544</v>
       </c>
       <c r="F285" s="1" t="n">
+        <v>6.544</v>
+      </c>
+      <c r="G285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -6726,6 +7584,9 @@
         <v>0.01857</v>
       </c>
       <c r="F286" s="1" t="n">
+        <v>0.01857</v>
+      </c>
+      <c r="G286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -6745,10 +7606,13 @@
         <v>0.008437999999999999</v>
       </c>
       <c r="E287" s="1" t="n">
+        <v>0.008432</v>
+      </c>
+      <c r="F287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="F287" s="1" t="n">
-        <v>0.008437999999999999</v>
+      <c r="G287" s="1" t="n">
+        <v>0.008432</v>
       </c>
     </row>
     <row r="288">
@@ -6767,10 +7631,13 @@
         <v>0.3894</v>
       </c>
       <c r="E288" s="1" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="F288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="F288" s="1" t="n">
-        <v>0.3894</v>
+      <c r="G288" s="1" t="n">
+        <v>0.3879</v>
       </c>
     </row>
     <row r="289">
@@ -6789,10 +7656,13 @@
         <v>0.010496</v>
       </c>
       <c r="E289" s="1" t="n">
+        <v>0.010495</v>
+      </c>
+      <c r="F289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="F289" s="1" t="n">
-        <v>0.010496</v>
+      <c r="G289" s="1" t="n">
+        <v>0.010495</v>
       </c>
     </row>
     <row r="290">
@@ -6811,9 +7681,12 @@
         <v>0.02626</v>
       </c>
       <c r="E290" s="1" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="F290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="F290" s="1" t="n">
+      <c r="G290" s="1" t="n">
         <v>0.02613</v>
       </c>
     </row>
@@ -6836,6 +7709,9 @@
         <v>0.097</v>
       </c>
       <c r="F291" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="G291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -6855,9 +7731,12 @@
         <v>0.28557</v>
       </c>
       <c r="E292" s="1" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="F292" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="F292" s="1" t="n">
+      <c r="G292" s="1" t="n">
         <v>0.28557</v>
       </c>
     </row>
@@ -6877,9 +7756,12 @@
         <v>0.01544</v>
       </c>
       <c r="E293" s="1" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="F293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="F293" s="1" t="n">
+      <c r="G293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -6899,9 +7781,12 @@
         <v>0.003416</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>0.003416</v>
+        <v>0.003417</v>
       </c>
       <c r="F294" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="G294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -6921,9 +7806,12 @@
         <v>0.043601</v>
       </c>
       <c r="E295" s="1" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="F295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="F295" s="1" t="n">
+      <c r="G295" s="1" t="n">
         <v>0.043493</v>
       </c>
     </row>
@@ -6943,9 +7831,12 @@
         <v>0.02943</v>
       </c>
       <c r="E296" s="1" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="F296" s="1" t="n">
         <v>0.03007</v>
       </c>
-      <c r="F296" s="1" t="n">
+      <c r="G296" s="1" t="n">
         <v>0.02943</v>
       </c>
     </row>
@@ -6965,10 +7856,13 @@
         <v>0.03994</v>
       </c>
       <c r="E297" s="1" t="n">
+        <v>0.03975</v>
+      </c>
+      <c r="F297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="F297" s="1" t="n">
-        <v>0.03983</v>
+      <c r="G297" s="1" t="n">
+        <v>0.03975</v>
       </c>
     </row>
     <row r="298">
@@ -6987,9 +7881,12 @@
         <v>0.08338</v>
       </c>
       <c r="E298" s="1" t="n">
+        <v>0.08334999999999999</v>
+      </c>
+      <c r="F298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="F298" s="1" t="n">
+      <c r="G298" s="1" t="n">
         <v>0.08326</v>
       </c>
     </row>
@@ -7012,6 +7909,9 @@
         <v>0.00766</v>
       </c>
       <c r="F299" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="G299" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -7031,9 +7931,12 @@
         <v>0.01532</v>
       </c>
       <c r="E300" s="1" t="n">
+        <v>0.01528</v>
+      </c>
+      <c r="F300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="F300" s="1" t="n">
+      <c r="G300" s="1" t="n">
         <v>0.01519</v>
       </c>
     </row>
@@ -7053,10 +7956,13 @@
         <v>0.1416</v>
       </c>
       <c r="E301" s="1" t="n">
+        <v>0.1413</v>
+      </c>
+      <c r="F301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="F301" s="1" t="n">
-        <v>0.1416</v>
+      <c r="G301" s="1" t="n">
+        <v>0.1413</v>
       </c>
     </row>
     <row r="302">
@@ -7075,10 +7981,13 @@
         <v>0.0006518</v>
       </c>
       <c r="E302" s="1" t="n">
+        <v>0.000641</v>
+      </c>
+      <c r="F302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="F302" s="1" t="n">
-        <v>0.0006511000000000001</v>
+      <c r="G302" s="1" t="n">
+        <v>0.000641</v>
       </c>
     </row>
     <row r="303">
@@ -7097,9 +8006,12 @@
         <v>0.06232</v>
       </c>
       <c r="E303" s="1" t="n">
+        <v>0.06234</v>
+      </c>
+      <c r="F303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="F303" s="1" t="n">
+      <c r="G303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -7119,10 +8031,13 @@
         <v>0.0001638</v>
       </c>
       <c r="E304" s="1" t="n">
+        <v>0.0001632</v>
+      </c>
+      <c r="F304" s="1" t="n">
         <v>0.0001639</v>
       </c>
-      <c r="F304" s="1" t="n">
-        <v>0.0001634</v>
+      <c r="G304" s="1" t="n">
+        <v>0.0001632</v>
       </c>
     </row>
     <row r="305">
@@ -7141,9 +8056,12 @@
         <v>0.06078</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>0.0609</v>
+        <v>0.06134</v>
       </c>
       <c r="F305" s="1" t="n">
+        <v>0.06134</v>
+      </c>
+      <c r="G305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -7163,10 +8081,13 @@
         <v>0.022477</v>
       </c>
       <c r="E306" s="1" t="n">
+        <v>0.022332</v>
+      </c>
+      <c r="F306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="F306" s="1" t="n">
-        <v>0.022477</v>
+      <c r="G306" s="1" t="n">
+        <v>0.022332</v>
       </c>
     </row>
     <row r="307">
@@ -7185,9 +8106,12 @@
         <v>0.02367</v>
       </c>
       <c r="E307" s="1" t="n">
+        <v>0.02374</v>
+      </c>
+      <c r="F307" s="1" t="n">
         <v>0.02414</v>
       </c>
-      <c r="F307" s="1" t="n">
+      <c r="G307" s="1" t="n">
         <v>0.02367</v>
       </c>
     </row>
@@ -7210,6 +8134,9 @@
         <v>0.000412</v>
       </c>
       <c r="F308" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="G308" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -7229,9 +8156,12 @@
         <v>0.0898</v>
       </c>
       <c r="E309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="F309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="F309" s="1" t="n">
+      <c r="G309" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -7251,9 +8181,12 @@
         <v>0.3831</v>
       </c>
       <c r="E310" s="1" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="F310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="F310" s="1" t="n">
+      <c r="G310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -7276,6 +8209,9 @@
         <v>0.0358</v>
       </c>
       <c r="F311" s="1" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="G311" s="1" t="n">
         <v>0.0357</v>
       </c>
     </row>
@@ -7295,9 +8231,12 @@
         <v>0.02458</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>0.02458</v>
+        <v>0.02471</v>
       </c>
       <c r="F312" s="1" t="n">
+        <v>0.02471</v>
+      </c>
+      <c r="G312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -7317,9 +8256,12 @@
         <v>0.04139</v>
       </c>
       <c r="E313" s="1" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="F313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="F313" s="1" t="n">
+      <c r="G313" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -7339,9 +8281,12 @@
         <v>4.015</v>
       </c>
       <c r="E314" s="1" t="n">
+        <v>4.007</v>
+      </c>
+      <c r="F314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="F314" s="1" t="n">
+      <c r="G314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -7361,9 +8306,12 @@
         <v>0.1604</v>
       </c>
       <c r="E315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="F315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="F315" s="1" t="n">
+      <c r="G315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -7383,10 +8331,13 @@
         <v>0.08819</v>
       </c>
       <c r="E316" s="1" t="n">
+        <v>0.08805</v>
+      </c>
+      <c r="F316" s="1" t="n">
         <v>0.08852</v>
       </c>
-      <c r="F316" s="1" t="n">
-        <v>0.08819</v>
+      <c r="G316" s="1" t="n">
+        <v>0.08805</v>
       </c>
     </row>
     <row r="317">
@@ -7405,9 +8356,12 @@
         <v>0.06816</v>
       </c>
       <c r="E317" s="1" t="n">
+        <v>0.06827</v>
+      </c>
+      <c r="F317" s="1" t="n">
         <v>0.06827999999999999</v>
       </c>
-      <c r="F317" s="1" t="n">
+      <c r="G317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -7427,9 +8381,12 @@
         <v>0.012643</v>
       </c>
       <c r="E318" s="1" t="n">
+        <v>0.012664</v>
+      </c>
+      <c r="F318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="F318" s="1" t="n">
+      <c r="G318" s="1" t="n">
         <v>0.012643</v>
       </c>
     </row>
@@ -7449,9 +8406,12 @@
         <v>0.001136</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>0.001136</v>
+        <v>0.001138</v>
       </c>
       <c r="F319" s="1" t="n">
+        <v>0.001138</v>
+      </c>
+      <c r="G319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -7471,9 +8431,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="F320" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="G320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -7496,6 +8459,9 @@
         <v>0.00525</v>
       </c>
       <c r="F321" s="1" t="n">
+        <v>0.00525</v>
+      </c>
+      <c r="G321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -7518,6 +8484,9 @@
         <v>0.1116</v>
       </c>
       <c r="F322" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="G322" s="1" t="n">
         <v>0.1114</v>
       </c>
     </row>
@@ -7537,9 +8506,12 @@
         <v>0.04246</v>
       </c>
       <c r="E323" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="F323" s="1" t="n">
         <v>0.04246</v>
       </c>
-      <c r="F323" s="1" t="n">
+      <c r="G323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -7559,9 +8531,12 @@
         <v>0.01776</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>0.01777</v>
+        <v>0.0178</v>
       </c>
       <c r="F324" s="1" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="G324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -7581,10 +8556,13 @@
         <v>0.00569</v>
       </c>
       <c r="E325" s="1" t="n">
+        <v>0.005689</v>
+      </c>
+      <c r="F325" s="1" t="n">
         <v>0.005695</v>
       </c>
-      <c r="F325" s="1" t="n">
-        <v>0.00569</v>
+      <c r="G325" s="1" t="n">
+        <v>0.005689</v>
       </c>
     </row>
     <row r="326">
@@ -7603,9 +8581,12 @@
         <v>0.001767</v>
       </c>
       <c r="E326" s="1" t="n">
+        <v>0.001768</v>
+      </c>
+      <c r="F326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="F326" s="1" t="n">
+      <c r="G326" s="1" t="n">
         <v>0.001767</v>
       </c>
     </row>
@@ -7625,9 +8606,12 @@
         <v>0.04085</v>
       </c>
       <c r="E327" s="1" t="n">
+        <v>0.04082</v>
+      </c>
+      <c r="F327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="F327" s="1" t="n">
+      <c r="G327" s="1" t="n">
         <v>0.04076</v>
       </c>
     </row>
@@ -7647,9 +8631,12 @@
         <v>0.054034</v>
       </c>
       <c r="E328" s="1" t="n">
+        <v>0.054032</v>
+      </c>
+      <c r="F328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="F328" s="1" t="n">
+      <c r="G328" s="1" t="n">
         <v>0.05395</v>
       </c>
     </row>
@@ -7669,9 +8656,12 @@
         <v>0.279</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>0.279</v>
+        <v>0.2795</v>
       </c>
       <c r="F329" s="1" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="G329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -7691,9 +8681,12 @@
         <v>0.1601</v>
       </c>
       <c r="E330" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="F330" s="1" t="n">
+      <c r="G330" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -7713,9 +8706,12 @@
         <v>0.05355</v>
       </c>
       <c r="E331" s="1" t="n">
+        <v>0.05354</v>
+      </c>
+      <c r="F331" s="1" t="n">
         <v>0.05356</v>
       </c>
-      <c r="F331" s="1" t="n">
+      <c r="G331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -7735,9 +8731,12 @@
         <v>0.3603</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>0.3607</v>
+        <v>0.361</v>
       </c>
       <c r="F332" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="G332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -7760,6 +8759,9 @@
         <v>0.03048</v>
       </c>
       <c r="F333" s="1" t="n">
+        <v>0.03048</v>
+      </c>
+      <c r="G333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -7779,9 +8781,12 @@
         <v>0.01797</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>0.01797</v>
+        <v>0.01832</v>
       </c>
       <c r="F334" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="G334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -7801,9 +8806,12 @@
         <v>0.0579</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>0.0579</v>
+        <v>0.0581</v>
       </c>
       <c r="F335" s="1" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="G335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -7823,9 +8831,12 @@
         <v>0.09182</v>
       </c>
       <c r="E336" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="F336" s="1" t="n">
         <v>0.09182</v>
       </c>
-      <c r="F336" s="1" t="n">
+      <c r="G336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -7845,9 +8856,12 @@
         <v>0.17548</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>0.17619</v>
+        <v>0.1777</v>
       </c>
       <c r="F337" s="1" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="G337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -7867,10 +8881,13 @@
         <v>0.02122</v>
       </c>
       <c r="E338" s="1" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="F338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="F338" s="1" t="n">
-        <v>0.02122</v>
+      <c r="G338" s="1" t="n">
+        <v>0.0212</v>
       </c>
     </row>
     <row r="339">
@@ -7889,9 +8906,12 @@
         <v>0.1315</v>
       </c>
       <c r="E339" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="F339" s="1" t="n">
         <v>0.1315</v>
       </c>
-      <c r="F339" s="1" t="n">
+      <c r="G339" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -7911,10 +8931,13 @@
         <v>0.0081</v>
       </c>
       <c r="E340" s="1" t="n">
+        <v>0.008014</v>
+      </c>
+      <c r="F340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="F340" s="1" t="n">
-        <v>0.0081</v>
+      <c r="G340" s="1" t="n">
+        <v>0.008014</v>
       </c>
     </row>
     <row r="341">
@@ -7933,9 +8956,12 @@
         <v>4.401</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>4.401</v>
+        <v>4.403</v>
       </c>
       <c r="F341" s="1" t="n">
+        <v>4.403</v>
+      </c>
+      <c r="G341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -7955,9 +8981,12 @@
         <v>0.19496</v>
       </c>
       <c r="E342" s="1" t="n">
+        <v>0.19423</v>
+      </c>
+      <c r="F342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="F342" s="1" t="n">
+      <c r="G342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -7977,9 +9006,12 @@
         <v>0.08325</v>
       </c>
       <c r="E343" s="1" t="n">
+        <v>0.08316999999999999</v>
+      </c>
+      <c r="F343" s="1" t="n">
         <v>0.08325</v>
       </c>
-      <c r="F343" s="1" t="n">
+      <c r="G343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -7999,9 +9031,12 @@
         <v>0.1829</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>0.183</v>
+        <v>0.1835</v>
       </c>
       <c r="F344" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="G344" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -8021,9 +9056,12 @@
         <v>0.003252</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>0.003252</v>
+        <v>0.003265</v>
       </c>
       <c r="F345" s="1" t="n">
+        <v>0.003265</v>
+      </c>
+      <c r="G345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -8043,9 +9081,12 @@
         <v>0.09118</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>0.09118</v>
+        <v>0.09121</v>
       </c>
       <c r="F346" s="1" t="n">
+        <v>0.09121</v>
+      </c>
+      <c r="G346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -8065,9 +9106,12 @@
         <v>2.259</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>2.259</v>
+        <v>2.26</v>
       </c>
       <c r="F347" s="1" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G347" s="1" t="n">
         <v>2.254</v>
       </c>
     </row>
@@ -8087,9 +9131,12 @@
         <v>0.3041</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>0.3041</v>
+        <v>0.3049</v>
       </c>
       <c r="F348" s="1" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="G348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -8109,9 +9156,12 @@
         <v>0.02982</v>
       </c>
       <c r="E349" s="1" t="n">
+        <v>0.02983</v>
+      </c>
+      <c r="F349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="F349" s="1" t="n">
+      <c r="G349" s="1" t="n">
         <v>0.02982</v>
       </c>
     </row>
@@ -8131,9 +9181,12 @@
         <v>0.1281</v>
       </c>
       <c r="E350" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="F350" s="1" t="n">
+      <c r="G350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -8153,9 +9206,12 @@
         <v>0.0677</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>0.0677</v>
+        <v>0.06804</v>
       </c>
       <c r="F351" s="1" t="n">
+        <v>0.06804</v>
+      </c>
+      <c r="G351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -8175,9 +9231,12 @@
         <v>0.06251</v>
       </c>
       <c r="E352" s="1" t="n">
+        <v>0.06247</v>
+      </c>
+      <c r="F352" s="1" t="n">
         <v>0.06251</v>
       </c>
-      <c r="F352" s="1" t="n">
+      <c r="G352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -8197,9 +9256,12 @@
         <v>0.0639</v>
       </c>
       <c r="E353" s="1" t="n">
+        <v>0.06388000000000001</v>
+      </c>
+      <c r="F353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="F353" s="1" t="n">
+      <c r="G353" s="1" t="n">
         <v>0.06375</v>
       </c>
     </row>
@@ -8219,9 +9281,12 @@
         <v>0.10425</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>0.10433</v>
+        <v>0.10569</v>
       </c>
       <c r="F354" s="1" t="n">
+        <v>0.10569</v>
+      </c>
+      <c r="G354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -8244,6 +9309,9 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="F355" s="1" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="G355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -8263,10 +9331,13 @@
         <v>0.06997</v>
       </c>
       <c r="E356" s="1" t="n">
+        <v>0.06988</v>
+      </c>
+      <c r="F356" s="1" t="n">
         <v>0.07054000000000001</v>
       </c>
-      <c r="F356" s="1" t="n">
-        <v>0.06997</v>
+      <c r="G356" s="1" t="n">
+        <v>0.06988</v>
       </c>
     </row>
     <row r="357">
@@ -8285,9 +9356,12 @@
         <v>0.4538</v>
       </c>
       <c r="E357" s="1" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="F357" s="1" t="n">
         <v>0.4541</v>
       </c>
-      <c r="F357" s="1" t="n">
+      <c r="G357" s="1" t="n">
         <v>0.4523</v>
       </c>
     </row>
@@ -8307,10 +9381,13 @@
         <v>0.03517</v>
       </c>
       <c r="E358" s="1" t="n">
+        <v>0.03467</v>
+      </c>
+      <c r="F358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="F358" s="1" t="n">
-        <v>0.03517</v>
+      <c r="G358" s="1" t="n">
+        <v>0.03467</v>
       </c>
     </row>
     <row r="359">
@@ -8329,9 +9406,12 @@
         <v>0.01479</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>0.01481</v>
+        <v>0.01482</v>
       </c>
       <c r="F359" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="G359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -8351,10 +9431,13 @@
         <v>0.13299</v>
       </c>
       <c r="E360" s="1" t="n">
+        <v>0.13282</v>
+      </c>
+      <c r="F360" s="1" t="n">
         <v>0.13306</v>
       </c>
-      <c r="F360" s="1" t="n">
-        <v>0.13283</v>
+      <c r="G360" s="1" t="n">
+        <v>0.13282</v>
       </c>
     </row>
     <row r="361">
@@ -8373,9 +9456,12 @@
         <v>0.0005883</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>0.0005883</v>
+        <v>0.0005885</v>
       </c>
       <c r="F361" s="1" t="n">
+        <v>0.0005885</v>
+      </c>
+      <c r="G361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -8395,10 +9481,13 @@
         <v>0.03881</v>
       </c>
       <c r="E362" s="1" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="F362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="F362" s="1" t="n">
-        <v>0.03878</v>
+      <c r="G362" s="1" t="n">
+        <v>0.0386</v>
       </c>
     </row>
     <row r="363">
@@ -8417,9 +9506,12 @@
         <v>3.208</v>
       </c>
       <c r="E363" s="1" t="n">
+        <v>3.214</v>
+      </c>
+      <c r="F363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="F363" s="1" t="n">
+      <c r="G363" s="1" t="n">
         <v>3.208</v>
       </c>
     </row>
@@ -8439,9 +9531,12 @@
         <v>0.1661</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>0.1663</v>
+        <v>0.1664</v>
       </c>
       <c r="F364" s="1" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="G364" s="1" t="n">
         <v>0.1657</v>
       </c>
     </row>
@@ -8461,9 +9556,12 @@
         <v>0.1135</v>
       </c>
       <c r="E365" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="F365" s="1" t="n">
         <v>0.1135</v>
       </c>
-      <c r="F365" s="1" t="n">
+      <c r="G365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -8483,9 +9581,12 @@
         <v>0.0006438</v>
       </c>
       <c r="E366" s="1" t="n">
+        <v>0.0006437</v>
+      </c>
+      <c r="F366" s="1" t="n">
         <v>0.0006438</v>
       </c>
-      <c r="F366" s="1" t="n">
+      <c r="G366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -8505,9 +9606,12 @@
         <v>0.05979</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>0.05979</v>
+        <v>0.05998</v>
       </c>
       <c r="F367" s="1" t="n">
+        <v>0.05998</v>
+      </c>
+      <c r="G367" s="1" t="n">
         <v>0.05956</v>
       </c>
     </row>
@@ -8527,9 +9631,12 @@
         <v>0.08298</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>0.08298</v>
+        <v>0.08323</v>
       </c>
       <c r="F368" s="1" t="n">
+        <v>0.08323</v>
+      </c>
+      <c r="G368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -8549,9 +9656,12 @@
         <v>0.04</v>
       </c>
       <c r="E369" s="1" t="n">
+        <v>0.03997</v>
+      </c>
+      <c r="F369" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="F369" s="1" t="n">
+      <c r="G369" s="1" t="n">
         <v>0.03979</v>
       </c>
     </row>
@@ -8571,9 +9681,12 @@
         <v>3.713</v>
       </c>
       <c r="E370" s="1" t="n">
+        <v>3.723</v>
+      </c>
+      <c r="F370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="F370" s="1" t="n">
+      <c r="G370" s="1" t="n">
         <v>3.709</v>
       </c>
     </row>
@@ -8593,9 +9706,12 @@
         <v>0.1226</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>0.1227</v>
+        <v>0.123</v>
       </c>
       <c r="F371" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="G371" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -8615,9 +9731,12 @@
         <v>0.01474</v>
       </c>
       <c r="E372" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="F372" s="1" t="n">
         <v>0.01474</v>
       </c>
-      <c r="F372" s="1" t="n">
+      <c r="G372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -8637,10 +9756,13 @@
         <v>0.02204</v>
       </c>
       <c r="E373" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="F373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="F373" s="1" t="n">
-        <v>0.02197</v>
+      <c r="G373" s="1" t="n">
+        <v>0.02196</v>
       </c>
     </row>
     <row r="374">
@@ -8659,9 +9781,12 @@
         <v>1.8537</v>
       </c>
       <c r="E374" s="1" t="n">
+        <v>1.8566</v>
+      </c>
+      <c r="F374" s="1" t="n">
         <v>1.8584</v>
       </c>
-      <c r="F374" s="1" t="n">
+      <c r="G374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -8681,9 +9806,12 @@
         <v>0.02102</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>0.02106</v>
+        <v>0.02108</v>
       </c>
       <c r="F375" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="G375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -8703,10 +9831,13 @@
         <v>1.297</v>
       </c>
       <c r="E376" s="1" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="F376" s="1" t="n">
         <v>1.301</v>
       </c>
-      <c r="F376" s="1" t="n">
-        <v>1.296</v>
+      <c r="G376" s="1" t="n">
+        <v>1.294</v>
       </c>
     </row>
     <row r="377">
@@ -8725,9 +9856,12 @@
         <v>0.2841</v>
       </c>
       <c r="E377" s="1" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="F377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="F377" s="1" t="n">
+      <c r="G377" s="1" t="n">
         <v>0.2837</v>
       </c>
     </row>
@@ -8747,10 +9881,13 @@
         <v>0.01563</v>
       </c>
       <c r="E378" s="1" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="F378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="F378" s="1" t="n">
-        <v>0.01563</v>
+      <c r="G378" s="1" t="n">
+        <v>0.01561</v>
       </c>
     </row>
     <row r="379">
@@ -8769,9 +9906,12 @@
         <v>1.5275</v>
       </c>
       <c r="E379" s="1" t="n">
+        <v>1.5291</v>
+      </c>
+      <c r="F379" s="1" t="n">
         <v>1.5349</v>
       </c>
-      <c r="F379" s="1" t="n">
+      <c r="G379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -8791,9 +9931,12 @@
         <v>6.972e-05</v>
       </c>
       <c r="E380" s="1" t="n">
+        <v>6.969000000000001e-05</v>
+      </c>
+      <c r="F380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="F380" s="1" t="n">
+      <c r="G380" s="1" t="n">
         <v>6.962e-05</v>
       </c>
     </row>
@@ -8813,9 +9956,12 @@
         <v>2.559</v>
       </c>
       <c r="E381" s="1" t="n">
+        <v>2.552</v>
+      </c>
+      <c r="F381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="F381" s="1" t="n">
+      <c r="G381" s="1" t="n">
         <v>2.551</v>
       </c>
     </row>
@@ -8835,10 +9981,13 @@
         <v>0.0675</v>
       </c>
       <c r="E382" s="1" t="n">
+        <v>0.06738</v>
+      </c>
+      <c r="F382" s="1" t="n">
         <v>0.06753000000000001</v>
       </c>
-      <c r="F382" s="1" t="n">
-        <v>0.06745</v>
+      <c r="G382" s="1" t="n">
+        <v>0.06738</v>
       </c>
     </row>
     <row r="383">
@@ -8857,10 +10006,13 @@
         <v>0.01716</v>
       </c>
       <c r="E383" s="1" t="n">
+        <v>0.01713</v>
+      </c>
+      <c r="F383" s="1" t="n">
         <v>0.01758</v>
       </c>
-      <c r="F383" s="1" t="n">
-        <v>0.01716</v>
+      <c r="G383" s="1" t="n">
+        <v>0.01713</v>
       </c>
     </row>
     <row r="384">
@@ -8879,9 +10031,12 @@
         <v>0.05066</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>0.05066</v>
+        <v>0.05068</v>
       </c>
       <c r="F384" s="1" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="G384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -8901,9 +10056,12 @@
         <v>7.576</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>7.576</v>
+        <v>7.585</v>
       </c>
       <c r="F385" s="1" t="n">
+        <v>7.585</v>
+      </c>
+      <c r="G385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -8923,9 +10081,12 @@
         <v>0.003299</v>
       </c>
       <c r="E386" s="1" t="n">
+        <v>0.003295</v>
+      </c>
+      <c r="F386" s="1" t="n">
         <v>0.003299</v>
       </c>
-      <c r="F386" s="1" t="n">
+      <c r="G386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -8945,9 +10106,12 @@
         <v>0.0003848</v>
       </c>
       <c r="E387" s="1" t="n">
+        <v>0.0003846</v>
+      </c>
+      <c r="F387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="F387" s="1" t="n">
+      <c r="G387" s="1" t="n">
         <v>0.0003838</v>
       </c>
     </row>
@@ -8967,10 +10131,13 @@
         <v>0.00984</v>
       </c>
       <c r="E388" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="F388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="F388" s="1" t="n">
-        <v>0.009769999999999999</v>
+      <c r="G388" s="1" t="n">
+        <v>0.00967</v>
       </c>
     </row>
     <row r="389">
@@ -8989,10 +10156,13 @@
         <v>0.2888</v>
       </c>
       <c r="E389" s="1" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="F389" s="1" t="n">
         <v>0.2891</v>
       </c>
-      <c r="F389" s="1" t="n">
-        <v>0.2888</v>
+      <c r="G389" s="1" t="n">
+        <v>0.2883</v>
       </c>
     </row>
     <row r="390">
@@ -9011,9 +10181,12 @@
         <v>0.0247</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>0.0249</v>
+        <v>0.025</v>
       </c>
       <c r="F390" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -9033,9 +10206,12 @@
         <v>2.819</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>2.819</v>
+        <v>2.829</v>
       </c>
       <c r="F391" s="1" t="n">
+        <v>2.829</v>
+      </c>
+      <c r="G391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -9058,6 +10234,9 @@
         <v>0.01351</v>
       </c>
       <c r="F392" s="1" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="G392" s="1" t="n">
         <v>0.01343</v>
       </c>
     </row>
@@ -9080,6 +10259,9 @@
         <v>0.00236</v>
       </c>
       <c r="F393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="G393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -9099,9 +10281,12 @@
         <v>0.05949</v>
       </c>
       <c r="E394" s="1" t="n">
+        <v>0.05946</v>
+      </c>
+      <c r="F394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="F394" s="1" t="n">
+      <c r="G394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -9126,6 +10311,9 @@
       <c r="F395" s="1" t="n">
         <v>0.0405</v>
       </c>
+      <c r="G395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9143,9 +10331,12 @@
         <v>0.09107999999999999</v>
       </c>
       <c r="E396" s="1" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="F396" s="1" t="n">
         <v>0.09134</v>
       </c>
-      <c r="F396" s="1" t="n">
+      <c r="G396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -9165,9 +10356,12 @@
         <v>0.152</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>0.1521</v>
+        <v>0.1522</v>
       </c>
       <c r="F397" s="1" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="G397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -9187,9 +10381,12 @@
         <v>0.928</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="F398" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="G398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -9209,9 +10406,12 @@
         <v>0.05241</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>0.05242</v>
+        <v>0.0525</v>
       </c>
       <c r="F399" s="1" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="G399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -9234,6 +10434,9 @@
         <v>2.525</v>
       </c>
       <c r="F400" s="1" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="G400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -9253,9 +10456,12 @@
         <v>0.01797</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>0.01814</v>
+        <v>0.01819</v>
       </c>
       <c r="F401" s="1" t="n">
+        <v>0.01819</v>
+      </c>
+      <c r="G401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -9275,9 +10481,12 @@
         <v>0.08044999999999999</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>0.08044999999999999</v>
+        <v>0.08097</v>
       </c>
       <c r="F402" s="1" t="n">
+        <v>0.08097</v>
+      </c>
+      <c r="G402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -9297,9 +10506,12 @@
         <v>1.252</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>1.252</v>
+        <v>1.2526</v>
       </c>
       <c r="F403" s="1" t="n">
+        <v>1.2526</v>
+      </c>
+      <c r="G403" s="1" t="n">
         <v>1.2484</v>
       </c>
     </row>
@@ -9319,9 +10531,12 @@
         <v>0.00717</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>0.00717</v>
+        <v>0.00719</v>
       </c>
       <c r="F404" s="1" t="n">
+        <v>0.00719</v>
+      </c>
+      <c r="G404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -9341,10 +10556,13 @@
         <v>0.4966</v>
       </c>
       <c r="E405" s="1" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="F405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="F405" s="1" t="n">
-        <v>0.4966</v>
+      <c r="G405" s="1" t="n">
+        <v>0.4945</v>
       </c>
     </row>
     <row r="406">
@@ -9366,6 +10584,9 @@
         <v>0.01151</v>
       </c>
       <c r="F406" s="1" t="n">
+        <v>0.01151</v>
+      </c>
+      <c r="G406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -9385,9 +10606,12 @@
         <v>0.0465</v>
       </c>
       <c r="E407" s="1" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="F407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="F407" s="1" t="n">
+      <c r="G407" s="1" t="n">
         <v>0.0464</v>
       </c>
     </row>
@@ -9410,6 +10634,9 @@
         <v>0.03964</v>
       </c>
       <c r="F408" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -9429,10 +10656,13 @@
         <v>0.05285</v>
       </c>
       <c r="E409" s="1" t="n">
+        <v>0.05274</v>
+      </c>
+      <c r="F409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="F409" s="1" t="n">
-        <v>0.05276</v>
+      <c r="G409" s="1" t="n">
+        <v>0.05274</v>
       </c>
     </row>
     <row r="410">
@@ -9454,6 +10684,9 @@
         <v>0.01256</v>
       </c>
       <c r="F410" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="G410" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -9473,9 +10706,12 @@
         <v>0.06401</v>
       </c>
       <c r="E411" s="1" t="n">
+        <v>0.06399000000000001</v>
+      </c>
+      <c r="F411" s="1" t="n">
         <v>0.06401</v>
       </c>
-      <c r="F411" s="1" t="n">
+      <c r="G411" s="1" t="n">
         <v>0.06378</v>
       </c>
     </row>
@@ -9495,9 +10731,12 @@
         <v>0.04146</v>
       </c>
       <c r="E412" s="1" t="n">
+        <v>0.04141</v>
+      </c>
+      <c r="F412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="F412" s="1" t="n">
+      <c r="G412" s="1" t="n">
         <v>0.0414</v>
       </c>
     </row>
@@ -9520,6 +10759,9 @@
         <v>1.122</v>
       </c>
       <c r="F413" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="G413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -9539,9 +10781,12 @@
         <v>0.2637</v>
       </c>
       <c r="E414" s="1" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="F414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="F414" s="1" t="n">
+      <c r="G414" s="1" t="n">
         <v>0.2637</v>
       </c>
     </row>
@@ -9561,9 +10806,12 @@
         <v>0.001223</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>0.001223</v>
+        <v>0.001261</v>
       </c>
       <c r="F415" s="1" t="n">
+        <v>0.001261</v>
+      </c>
+      <c r="G415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -9583,9 +10831,12 @@
         <v>0.03179</v>
       </c>
       <c r="E416" s="1" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="F416" s="1" t="n">
         <v>0.03196</v>
       </c>
-      <c r="F416" s="1" t="n">
+      <c r="G416" s="1" t="n">
         <v>0.03179</v>
       </c>
     </row>
@@ -9605,9 +10856,12 @@
         <v>0.01462</v>
       </c>
       <c r="E417" s="1" t="n">
+        <v>0.01462</v>
+      </c>
+      <c r="F417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="F417" s="1" t="n">
+      <c r="G417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -9627,9 +10881,12 @@
         <v>0.1482</v>
       </c>
       <c r="E418" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="F418" s="1" t="n">
         <v>0.1482</v>
       </c>
-      <c r="F418" s="1" t="n">
+      <c r="G418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -9649,9 +10906,12 @@
         <v>0.04869</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>0.04884</v>
+        <v>0.04887</v>
       </c>
       <c r="F419" s="1" t="n">
+        <v>0.04887</v>
+      </c>
+      <c r="G419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -9671,9 +10931,12 @@
         <v>66.34</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>66.34</v>
+        <v>66.38</v>
       </c>
       <c r="F420" s="1" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="G420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -9693,9 +10956,12 @@
         <v>0.879</v>
       </c>
       <c r="E421" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="F421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="F421" s="1" t="n">
+      <c r="G421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -9715,10 +10981,13 @@
         <v>0.012932</v>
       </c>
       <c r="E422" s="1" t="n">
+        <v>0.012896</v>
+      </c>
+      <c r="F422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="F422" s="1" t="n">
-        <v>0.012932</v>
+      <c r="G422" s="1" t="n">
+        <v>0.012896</v>
       </c>
     </row>
     <row r="423">
@@ -9737,9 +11006,12 @@
         <v>0.01597</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>0.01597</v>
+        <v>0.01599</v>
       </c>
       <c r="F423" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="G423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -9759,9 +11031,12 @@
         <v>0.26204</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>0.26204</v>
+        <v>0.26551</v>
       </c>
       <c r="F424" s="1" t="n">
+        <v>0.26551</v>
+      </c>
+      <c r="G424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -9781,9 +11056,12 @@
         <v>0.601</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>0.601</v>
+        <v>0.6018</v>
       </c>
       <c r="F425" s="1" t="n">
+        <v>0.6018</v>
+      </c>
+      <c r="G425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -9803,10 +11081,13 @@
         <v>0.005617</v>
       </c>
       <c r="E426" s="1" t="n">
+        <v>0.005596</v>
+      </c>
+      <c r="F426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="F426" s="1" t="n">
-        <v>0.005617</v>
+      <c r="G426" s="1" t="n">
+        <v>0.005596</v>
       </c>
     </row>
     <row r="427">
@@ -9825,10 +11106,13 @@
         <v>0.04892</v>
       </c>
       <c r="E427" s="1" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="F427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="F427" s="1" t="n">
-        <v>0.04892</v>
+      <c r="G427" s="1" t="n">
+        <v>0.0489</v>
       </c>
     </row>
     <row r="428">
@@ -9850,6 +11134,9 @@
         <v>0.1261</v>
       </c>
       <c r="F428" s="1" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="G428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -9869,10 +11156,13 @@
         <v>0.003197</v>
       </c>
       <c r="E429" s="1" t="n">
+        <v>0.003193</v>
+      </c>
+      <c r="F429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="F429" s="1" t="n">
-        <v>0.003197</v>
+      <c r="G429" s="1" t="n">
+        <v>0.003193</v>
       </c>
     </row>
     <row r="430">
@@ -9891,9 +11181,12 @@
         <v>0.03655</v>
       </c>
       <c r="E430" s="1" t="n">
+        <v>0.03663</v>
+      </c>
+      <c r="F430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="F430" s="1" t="n">
+      <c r="G430" s="1" t="n">
         <v>0.03655</v>
       </c>
     </row>
@@ -9913,10 +11206,13 @@
         <v>0.4009</v>
       </c>
       <c r="E431" s="1" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="F431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="F431" s="1" t="n">
-        <v>0.4009</v>
+      <c r="G431" s="1" t="n">
+        <v>0.4008</v>
       </c>
     </row>
     <row r="432">
@@ -9935,9 +11231,12 @@
         <v>0.004542</v>
       </c>
       <c r="E432" s="1" t="n">
+        <v>0.004532</v>
+      </c>
+      <c r="F432" s="1" t="n">
         <v>0.004542</v>
       </c>
-      <c r="F432" s="1" t="n">
+      <c r="G432" s="1" t="n">
         <v>0.004519</v>
       </c>
     </row>
@@ -9957,9 +11256,12 @@
         <v>0.098</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>0.098</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="F433" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="G433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -9982,6 +11284,9 @@
         <v>0.01244</v>
       </c>
       <c r="F434" s="1" t="n">
+        <v>0.01244</v>
+      </c>
+      <c r="G434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -10001,9 +11306,12 @@
         <v>1.981</v>
       </c>
       <c r="E435" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F435" s="1" t="n">
         <v>1.981</v>
       </c>
-      <c r="F435" s="1" t="n">
+      <c r="G435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -10023,9 +11331,12 @@
         <v>0.001839</v>
       </c>
       <c r="E436" s="1" t="n">
+        <v>0.001844</v>
+      </c>
+      <c r="F436" s="1" t="n">
         <v>0.001848</v>
       </c>
-      <c r="F436" s="1" t="n">
+      <c r="G436" s="1" t="n">
         <v>0.001833</v>
       </c>
     </row>
@@ -10045,9 +11356,12 @@
         <v>0.4423</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>0.4423</v>
+        <v>0.4427</v>
       </c>
       <c r="F437" s="1" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="G437" s="1" t="n">
         <v>0.4417</v>
       </c>
     </row>
@@ -10067,9 +11381,12 @@
         <v>0.00537</v>
       </c>
       <c r="E438" s="1" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="F438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="F438" s="1" t="n">
+      <c r="G438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -10089,9 +11406,12 @@
         <v>0.1034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>0.1034</v>
+        <v>0.1035</v>
       </c>
       <c r="F439" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="G439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -10111,10 +11431,13 @@
         <v>0.03423</v>
       </c>
       <c r="E440" s="1" t="n">
+        <v>0.03417</v>
+      </c>
+      <c r="F440" s="1" t="n">
         <v>0.03431</v>
       </c>
-      <c r="F440" s="1" t="n">
-        <v>0.0342</v>
+      <c r="G440" s="1" t="n">
+        <v>0.03417</v>
       </c>
     </row>
     <row r="441">
@@ -10133,9 +11456,12 @@
         <v>0.08215</v>
       </c>
       <c r="E441" s="1" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="F441" s="1" t="n">
         <v>0.08215</v>
       </c>
-      <c r="F441" s="1" t="n">
+      <c r="G441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -10155,9 +11481,12 @@
         <v>1.308</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>1.308</v>
+        <v>1.315</v>
       </c>
       <c r="F442" s="1" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="G442" s="1" t="n">
         <v>1.305</v>
       </c>
     </row>
@@ -10177,9 +11506,12 @@
         <v>0.07566000000000001</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>0.07571</v>
+        <v>0.07573000000000001</v>
       </c>
       <c r="F443" s="1" t="n">
+        <v>0.07573000000000001</v>
+      </c>
+      <c r="G443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -10199,9 +11531,12 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="E444" s="1" t="n">
+        <v>0.07679</v>
+      </c>
+      <c r="F444" s="1" t="n">
         <v>0.07692</v>
       </c>
-      <c r="F444" s="1" t="n">
+      <c r="G444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -10221,9 +11556,12 @@
         <v>0.04386</v>
       </c>
       <c r="E445" s="1" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="F445" s="1" t="n">
         <v>0.04386</v>
       </c>
-      <c r="F445" s="1" t="n">
+      <c r="G445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -10243,9 +11581,12 @@
         <v>0.02154</v>
       </c>
       <c r="E446" s="1" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="F446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="F446" s="1" t="n">
+      <c r="G446" s="1" t="n">
         <v>0.02154</v>
       </c>
     </row>
@@ -10265,9 +11606,12 @@
         <v>0.2806</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>0.2806</v>
+        <v>0.2811</v>
       </c>
       <c r="F447" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="G447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -10287,10 +11631,13 @@
         <v>0.03144</v>
       </c>
       <c r="E448" s="1" t="n">
+        <v>0.03137</v>
+      </c>
+      <c r="F448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="F448" s="1" t="n">
-        <v>0.03141</v>
+      <c r="G448" s="1" t="n">
+        <v>0.03137</v>
       </c>
     </row>
     <row r="449">
@@ -10312,6 +11659,9 @@
         <v>0.00646</v>
       </c>
       <c r="F449" s="1" t="n">
+        <v>0.00646</v>
+      </c>
+      <c r="G449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -10331,9 +11681,12 @@
         <v>0.022996</v>
       </c>
       <c r="E450" s="1" t="n">
+        <v>0.022942</v>
+      </c>
+      <c r="F450" s="1" t="n">
         <v>0.022996</v>
       </c>
-      <c r="F450" s="1" t="n">
+      <c r="G450" s="1" t="n">
         <v>0.022879</v>
       </c>
     </row>
@@ -10353,9 +11706,12 @@
         <v>0.0423</v>
       </c>
       <c r="E451" s="1" t="n">
+        <v>0.04225</v>
+      </c>
+      <c r="F451" s="1" t="n">
         <v>0.04232</v>
       </c>
-      <c r="F451" s="1" t="n">
+      <c r="G451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -10375,10 +11731,13 @@
         <v>0.07319000000000001</v>
       </c>
       <c r="E452" s="1" t="n">
+        <v>0.07253999999999999</v>
+      </c>
+      <c r="F452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="F452" s="1" t="n">
-        <v>0.07319000000000001</v>
+      <c r="G452" s="1" t="n">
+        <v>0.07253999999999999</v>
       </c>
     </row>
     <row r="453">
@@ -10397,9 +11756,12 @@
         <v>0.0005935</v>
       </c>
       <c r="E453" s="1" t="n">
+        <v>0.0005932</v>
+      </c>
+      <c r="F453" s="1" t="n">
         <v>0.0005935</v>
       </c>
-      <c r="F453" s="1" t="n">
+      <c r="G453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -10419,9 +11781,12 @@
         <v>0.308</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>0.308</v>
+        <v>0.309</v>
       </c>
       <c r="F454" s="1" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="G454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -10441,9 +11806,12 @@
         <v>0.004249</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>0.004249</v>
+        <v>0.004265</v>
       </c>
       <c r="F455" s="1" t="n">
+        <v>0.004265</v>
+      </c>
+      <c r="G455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -10463,9 +11831,12 @@
         <v>0.1844</v>
       </c>
       <c r="E456" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="F456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="F456" s="1" t="n">
+      <c r="G456" s="1" t="n">
         <v>0.1835</v>
       </c>
     </row>
@@ -10485,9 +11856,12 @@
         <v>0.04284</v>
       </c>
       <c r="E457" s="1" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="F457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="F457" s="1" t="n">
+      <c r="G457" s="1" t="n">
         <v>0.04278</v>
       </c>
     </row>
@@ -10510,6 +11884,9 @@
         <v>0.1465</v>
       </c>
       <c r="F458" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="G458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -10532,6 +11909,9 @@
         <v>0.008600999999999999</v>
       </c>
       <c r="F459" s="1" t="n">
+        <v>0.008600999999999999</v>
+      </c>
+      <c r="G459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -10551,9 +11931,12 @@
         <v>0.007494</v>
       </c>
       <c r="E460" s="1" t="n">
+        <v>0.007473</v>
+      </c>
+      <c r="F460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="F460" s="1" t="n">
+      <c r="G460" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -10573,9 +11956,12 @@
         <v>0.0001727</v>
       </c>
       <c r="E461" s="1" t="n">
+        <v>0.0001727</v>
+      </c>
+      <c r="F461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="F461" s="1" t="n">
+      <c r="G461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -10595,9 +11981,12 @@
         <v>0.02256</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>0.02256</v>
+        <v>0.02262</v>
       </c>
       <c r="F462" s="1" t="n">
+        <v>0.02262</v>
+      </c>
+      <c r="G462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -10617,9 +12006,12 @@
         <v>0.03762</v>
       </c>
       <c r="E463" s="1" t="n">
+        <v>0.03763</v>
+      </c>
+      <c r="F463" s="1" t="n">
         <v>0.03777</v>
       </c>
-      <c r="F463" s="1" t="n">
+      <c r="G463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -10639,9 +12031,12 @@
         <v>0.3037</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>0.3038</v>
+        <v>0.3043</v>
       </c>
       <c r="F464" s="1" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="G464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -10661,10 +12056,13 @@
         <v>0.03911</v>
       </c>
       <c r="E465" s="1" t="n">
+        <v>0.03905</v>
+      </c>
+      <c r="F465" s="1" t="n">
         <v>0.03923</v>
       </c>
-      <c r="F465" s="1" t="n">
-        <v>0.03911</v>
+      <c r="G465" s="1" t="n">
+        <v>0.03905</v>
       </c>
     </row>
     <row r="466">
@@ -10683,9 +12081,12 @@
         <v>2.685</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>2.687</v>
+        <v>2.691</v>
       </c>
       <c r="F466" s="1" t="n">
+        <v>2.691</v>
+      </c>
+      <c r="G466" s="1" t="n">
         <v>2.682</v>
       </c>
     </row>
@@ -10705,9 +12106,12 @@
         <v>0.03397</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>0.03397</v>
+        <v>0.03435</v>
       </c>
       <c r="F467" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="G467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -10727,9 +12131,12 @@
         <v>0.1762</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>0.1763</v>
+        <v>0.1765</v>
       </c>
       <c r="F468" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="G468" s="1" t="n">
         <v>0.176</v>
       </c>
     </row>
@@ -10749,9 +12156,12 @@
         <v>0.0956</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0958</v>
       </c>
       <c r="F469" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="G469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -10771,9 +12181,12 @@
         <v>0.06757000000000001</v>
       </c>
       <c r="E470" s="1" t="n">
+        <v>0.06753000000000001</v>
+      </c>
+      <c r="F470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="F470" s="1" t="n">
+      <c r="G470" s="1" t="n">
         <v>0.06745</v>
       </c>
     </row>
@@ -10793,9 +12206,12 @@
         <v>0.03996</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>0.03996</v>
+        <v>0.03998</v>
       </c>
       <c r="F471" s="1" t="n">
+        <v>0.03998</v>
+      </c>
+      <c r="G471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -10815,9 +12231,12 @@
         <v>0.2475</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>0.2481</v>
+        <v>0.2484</v>
       </c>
       <c r="F472" s="1" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="G472" s="1" t="n">
         <v>0.2475</v>
       </c>
     </row>
@@ -10837,9 +12256,12 @@
         <v>0.016522</v>
       </c>
       <c r="E473" s="1" t="n">
+        <v>0.016554</v>
+      </c>
+      <c r="F473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="F473" s="1" t="n">
+      <c r="G473" s="1" t="n">
         <v>0.016522</v>
       </c>
     </row>
@@ -10859,9 +12281,12 @@
         <v>0.1152</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>0.1152</v>
+        <v>0.1154</v>
       </c>
       <c r="F474" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="G474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -10881,9 +12306,12 @@
         <v>0.04304</v>
       </c>
       <c r="E475" s="1" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="F475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="F475" s="1" t="n">
+      <c r="G475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -10903,9 +12331,12 @@
         <v>0.2078</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>0.2078</v>
+        <v>0.2081</v>
       </c>
       <c r="F476" s="1" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="G476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -10925,9 +12356,12 @@
         <v>0.006833</v>
       </c>
       <c r="E477" s="1" t="n">
+        <v>0.006826</v>
+      </c>
+      <c r="F477" s="1" t="n">
         <v>0.006833</v>
       </c>
-      <c r="F477" s="1" t="n">
+      <c r="G477" s="1" t="n">
         <v>0.006817</v>
       </c>
     </row>
@@ -10950,6 +12384,9 @@
         <v>0.01814</v>
       </c>
       <c r="F478" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="G478" s="1" t="n">
         <v>0.01811</v>
       </c>
     </row>
@@ -10969,10 +12406,13 @@
         <v>0.04731</v>
       </c>
       <c r="E479" s="1" t="n">
+        <v>0.04698</v>
+      </c>
+      <c r="F479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="F479" s="1" t="n">
-        <v>0.0473</v>
+      <c r="G479" s="1" t="n">
+        <v>0.04698</v>
       </c>
     </row>
     <row r="480">
@@ -10991,9 +12431,12 @@
         <v>0.26054</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>0.26054</v>
+        <v>0.26166</v>
       </c>
       <c r="F480" s="1" t="n">
+        <v>0.26166</v>
+      </c>
+      <c r="G480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -11013,9 +12456,12 @@
         <v>0.01235</v>
       </c>
       <c r="E481" s="1" t="n">
+        <v>0.01235</v>
+      </c>
+      <c r="F481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="F481" s="1" t="n">
+      <c r="G481" s="1" t="n">
         <v>0.01235</v>
       </c>
     </row>
@@ -11035,10 +12481,13 @@
         <v>0.004066</v>
       </c>
       <c r="E482" s="1" t="n">
+        <v>0.004061</v>
+      </c>
+      <c r="F482" s="1" t="n">
         <v>0.004069</v>
       </c>
-      <c r="F482" s="1" t="n">
-        <v>0.004063</v>
+      <c r="G482" s="1" t="n">
+        <v>0.004061</v>
       </c>
     </row>
     <row r="483">
@@ -11057,9 +12506,12 @@
         <v>0.1232</v>
       </c>
       <c r="E483" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="F483" s="1" t="n">
         <v>0.1232</v>
       </c>
-      <c r="F483" s="1" t="n">
+      <c r="G483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -11079,9 +12531,12 @@
         <v>0.02187</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>0.02187</v>
+        <v>0.02201</v>
       </c>
       <c r="F484" s="1" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="G484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -11101,10 +12556,13 @@
         <v>0.04616</v>
       </c>
       <c r="E485" s="1" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="F485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="F485" s="1" t="n">
-        <v>0.04607</v>
+      <c r="G485" s="1" t="n">
+        <v>0.04574</v>
       </c>
     </row>
     <row r="486">
@@ -11123,9 +12581,12 @@
         <v>0.1735</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>0.1735</v>
+        <v>0.1736</v>
       </c>
       <c r="F486" s="1" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="G486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -11145,9 +12606,12 @@
         <v>0.2735</v>
       </c>
       <c r="E487" s="1" t="n">
+        <v>0.2734</v>
+      </c>
+      <c r="F487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="F487" s="1" t="n">
+      <c r="G487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -11167,9 +12631,12 @@
         <v>0.0463</v>
       </c>
       <c r="E488" s="1" t="n">
+        <v>0.04625</v>
+      </c>
+      <c r="F488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="F488" s="1" t="n">
+      <c r="G488" s="1" t="n">
         <v>0.04625</v>
       </c>
     </row>
@@ -11189,9 +12656,12 @@
         <v>0.0002158</v>
       </c>
       <c r="E489" s="1" t="n">
+        <v>0.0002156</v>
+      </c>
+      <c r="F489" s="1" t="n">
         <v>0.0002158</v>
       </c>
-      <c r="F489" s="1" t="n">
+      <c r="G489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -11211,9 +12681,12 @@
         <v>1.759</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>1.762</v>
+        <v>1.765</v>
       </c>
       <c r="F490" s="1" t="n">
+        <v>1.765</v>
+      </c>
+      <c r="G490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -11233,9 +12706,12 @@
         <v>16.062</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>16.062</v>
+        <v>16.083</v>
       </c>
       <c r="F491" s="1" t="n">
+        <v>16.083</v>
+      </c>
+      <c r="G491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -11255,9 +12731,12 @@
         <v>0.06673999999999999</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>0.06673999999999999</v>
+        <v>0.06680999999999999</v>
       </c>
       <c r="F492" s="1" t="n">
+        <v>0.06680999999999999</v>
+      </c>
+      <c r="G492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -11277,9 +12756,12 @@
         <v>0.06768</v>
       </c>
       <c r="E493" s="1" t="n">
+        <v>0.06763</v>
+      </c>
+      <c r="F493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="F493" s="1" t="n">
+      <c r="G493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -11299,9 +12781,12 @@
         <v>0.009438999999999999</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>0.009438999999999999</v>
+        <v>0.009455</v>
       </c>
       <c r="F494" s="1" t="n">
+        <v>0.009455</v>
+      </c>
+      <c r="G494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -11321,10 +12806,13 @@
         <v>0.005944</v>
       </c>
       <c r="E495" s="1" t="n">
+        <v>0.00593</v>
+      </c>
+      <c r="F495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="F495" s="1" t="n">
-        <v>0.005936</v>
+      <c r="G495" s="1" t="n">
+        <v>0.00593</v>
       </c>
     </row>
     <row r="496">
@@ -11346,6 +12834,9 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="F496" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="G496" s="1" t="n">
         <v>0.00992</v>
       </c>
     </row>
@@ -11365,9 +12856,12 @@
         <v>0.04389</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>0.04395</v>
+        <v>0.04404</v>
       </c>
       <c r="F497" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="G497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -11387,9 +12881,12 @@
         <v>0.006407</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>0.006407</v>
+        <v>0.006412</v>
       </c>
       <c r="F498" s="1" t="n">
+        <v>0.006412</v>
+      </c>
+      <c r="G498" s="1" t="n">
         <v>0.006405</v>
       </c>
     </row>
@@ -11409,9 +12906,12 @@
         <v>0.01046</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>0.01047</v>
+        <v>0.01048</v>
       </c>
       <c r="F499" s="1" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="G499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -11431,9 +12931,12 @@
         <v>0.5105</v>
       </c>
       <c r="E500" s="1" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="F500" s="1" t="n">
         <v>0.5122</v>
       </c>
-      <c r="F500" s="1" t="n">
+      <c r="G500" s="1" t="n">
         <v>0.5089</v>
       </c>
     </row>
@@ -11453,9 +12956,12 @@
         <v>0.03199</v>
       </c>
       <c r="E501" s="1" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="F501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="F501" s="1" t="n">
+      <c r="G501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -11475,9 +12981,12 @@
         <v>0.4367</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>0.4367</v>
+        <v>0.4373</v>
       </c>
       <c r="F502" s="1" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="G502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -11497,10 +13006,13 @@
         <v>0.999401</v>
       </c>
       <c r="E503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="F503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="F503" s="1" t="n">
-        <v>0.9994</v>
+      <c r="G503" s="1" t="n">
+        <v>0.999341</v>
       </c>
     </row>
     <row r="504">
@@ -11519,9 +13031,12 @@
         <v>0.03545</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>0.03545</v>
+        <v>0.03552</v>
       </c>
       <c r="F504" s="1" t="n">
+        <v>0.03552</v>
+      </c>
+      <c r="G504" s="1" t="n">
         <v>0.03525</v>
       </c>
     </row>
@@ -11541,9 +13056,12 @@
         <v>0.00495</v>
       </c>
       <c r="E505" s="1" t="n">
+        <v>0.004934</v>
+      </c>
+      <c r="F505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="F505" s="1" t="n">
+      <c r="G505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -11563,9 +13081,12 @@
         <v>0.01396</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>0.01396</v>
+        <v>0.01397</v>
       </c>
       <c r="F506" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -11585,9 +13106,12 @@
         <v>0.003472</v>
       </c>
       <c r="E507" s="1" t="n">
+        <v>0.003471</v>
+      </c>
+      <c r="F507" s="1" t="n">
         <v>0.003478</v>
       </c>
-      <c r="F507" s="1" t="n">
+      <c r="G507" s="1" t="n">
         <v>0.00347</v>
       </c>
     </row>
@@ -11607,9 +13131,12 @@
         <v>1.421</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>1.421</v>
+        <v>1.422</v>
       </c>
       <c r="F508" s="1" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="G508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -11629,10 +13156,13 @@
         <v>0.005101</v>
       </c>
       <c r="E509" s="1" t="n">
+        <v>0.005097</v>
+      </c>
+      <c r="F509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="F509" s="1" t="n">
-        <v>0.005101</v>
+      <c r="G509" s="1" t="n">
+        <v>0.005097</v>
       </c>
     </row>
     <row r="510">
@@ -11651,9 +13181,12 @@
         <v>0.01576</v>
       </c>
       <c r="E510" s="1" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="F510" s="1" t="n">
         <v>0.01576</v>
       </c>
-      <c r="F510" s="1" t="n">
+      <c r="G510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -11673,9 +13206,12 @@
         <v>0.08323999999999999</v>
       </c>
       <c r="E511" s="1" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="F511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="F511" s="1" t="n">
+      <c r="G511" s="1" t="n">
         <v>0.08319</v>
       </c>
     </row>
@@ -11695,9 +13231,12 @@
         <v>0.007114</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>0.007114</v>
+        <v>0.007121</v>
       </c>
       <c r="F512" s="1" t="n">
+        <v>0.007121</v>
+      </c>
+      <c r="G512" s="1" t="n">
         <v>0.007105</v>
       </c>
     </row>
@@ -11717,9 +13256,12 @@
         <v>0.0147</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>0.0147</v>
+        <v>0.0148</v>
       </c>
       <c r="F513" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="G513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -11739,9 +13281,12 @@
         <v>0.04758</v>
       </c>
       <c r="E514" s="1" t="n">
+        <v>0.04762</v>
+      </c>
+      <c r="F514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="F514" s="1" t="n">
+      <c r="G514" s="1" t="n">
         <v>0.04758</v>
       </c>
     </row>
@@ -11761,9 +13306,12 @@
         <v>0.01824</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>0.01826</v>
+        <v>0.01827</v>
       </c>
       <c r="F515" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="G515" s="1" t="n">
         <v>0.01824</v>
       </c>
     </row>
@@ -11786,6 +13334,9 @@
         <v>0.0005808</v>
       </c>
       <c r="F516" s="1" t="n">
+        <v>0.0005808</v>
+      </c>
+      <c r="G516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -11805,9 +13356,12 @@
         <v>0.07904</v>
       </c>
       <c r="E517" s="1" t="n">
+        <v>0.07892</v>
+      </c>
+      <c r="F517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="F517" s="1" t="n">
+      <c r="G517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -11827,9 +13381,12 @@
         <v>0.006395</v>
       </c>
       <c r="E518" s="1" t="n">
+        <v>0.006389</v>
+      </c>
+      <c r="F518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="F518" s="1" t="n">
+      <c r="G518" s="1" t="n">
         <v>0.006386</v>
       </c>
     </row>
@@ -11849,9 +13406,12 @@
         <v>0.05819</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>0.05819</v>
+        <v>0.05826</v>
       </c>
       <c r="F519" s="1" t="n">
+        <v>0.05826</v>
+      </c>
+      <c r="G519" s="1" t="n">
         <v>0.05803</v>
       </c>
     </row>
@@ -11871,9 +13431,12 @@
         <v>0.10519</v>
       </c>
       <c r="E520" s="1" t="n">
+        <v>0.10524</v>
+      </c>
+      <c r="F520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="F520" s="1" t="n">
+      <c r="G520" s="1" t="n">
         <v>0.10496</v>
       </c>
     </row>
@@ -11896,6 +13459,9 @@
         <v>0.01799</v>
       </c>
       <c r="F521" s="1" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="G521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -11915,9 +13481,12 @@
         <v>0.01653</v>
       </c>
       <c r="E522" s="1" t="n">
+        <v>0.01652</v>
+      </c>
+      <c r="F522" s="1" t="n">
         <v>0.01653</v>
       </c>
-      <c r="F522" s="1" t="n">
+      <c r="G522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -11937,9 +13506,12 @@
         <v>0.01089</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>0.01089</v>
+        <v>0.01091</v>
       </c>
       <c r="F523" s="1" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="G523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -11959,9 +13531,12 @@
         <v>0.006863</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>0.006863</v>
+        <v>0.006885</v>
       </c>
       <c r="F524" s="1" t="n">
+        <v>0.006885</v>
+      </c>
+      <c r="G524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -11981,10 +13556,13 @@
         <v>0.005964</v>
       </c>
       <c r="E525" s="1" t="n">
+        <v>0.005938</v>
+      </c>
+      <c r="F525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="F525" s="1" t="n">
-        <v>0.005964</v>
+      <c r="G525" s="1" t="n">
+        <v>0.005938</v>
       </c>
     </row>
     <row r="526">
@@ -12003,10 +13581,13 @@
         <v>0.001449</v>
       </c>
       <c r="E526" s="1" t="n">
+        <v>0.001434</v>
+      </c>
+      <c r="F526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="F526" s="1" t="n">
-        <v>0.001437</v>
+      <c r="G526" s="1" t="n">
+        <v>0.001434</v>
       </c>
     </row>
     <row r="527">
@@ -12025,9 +13606,12 @@
         <v>0.373</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="F527" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="G527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -12047,9 +13631,12 @@
         <v>0.00518</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>0.00518</v>
+        <v>0.005197</v>
       </c>
       <c r="F528" s="1" t="n">
+        <v>0.005197</v>
+      </c>
+      <c r="G528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -12069,9 +13656,12 @@
         <v>2.922</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>2.922</v>
+        <v>2.942</v>
       </c>
       <c r="F529" s="1" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="G529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -12091,9 +13681,12 @@
         <v>0.1559</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>0.1559</v>
+        <v>0.156</v>
       </c>
       <c r="F530" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="G530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -12113,10 +13706,13 @@
         <v>2537</v>
       </c>
       <c r="E531" s="1" t="n">
+        <v>2534</v>
+      </c>
+      <c r="F531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="F531" s="1" t="n">
-        <v>2537</v>
+      <c r="G531" s="1" t="n">
+        <v>2534</v>
       </c>
     </row>
     <row r="532">
@@ -12135,9 +13731,12 @@
         <v>0.03923</v>
       </c>
       <c r="E532" s="1" t="n">
+        <v>0.03925</v>
+      </c>
+      <c r="F532" s="1" t="n">
         <v>0.03928</v>
       </c>
-      <c r="F532" s="1" t="n">
+      <c r="G532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -12157,9 +13756,12 @@
         <v>0.02179</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>0.02183</v>
+        <v>0.0219</v>
       </c>
       <c r="F533" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="G533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -12179,9 +13781,12 @@
         <v>0.07273</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>0.07273</v>
+        <v>0.0731</v>
       </c>
       <c r="F534" s="1" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="G534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -12201,9 +13806,12 @@
         <v>0.007877</v>
       </c>
       <c r="E535" s="1" t="n">
+        <v>0.007853000000000001</v>
+      </c>
+      <c r="F535" s="1" t="n">
         <v>0.007877</v>
       </c>
-      <c r="F535" s="1" t="n">
+      <c r="G535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -12223,9 +13831,12 @@
         <v>0.05031</v>
       </c>
       <c r="E536" s="1" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="F536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="F536" s="1" t="n">
+      <c r="G536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -12245,9 +13856,12 @@
         <v>0.00408</v>
       </c>
       <c r="E537" s="1" t="n">
+        <v>0.00407</v>
+      </c>
+      <c r="F537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="F537" s="1" t="n">
+      <c r="G537" s="1" t="n">
         <v>0.00406</v>
       </c>
     </row>
@@ -12267,9 +13881,12 @@
         <v>0.08308</v>
       </c>
       <c r="E538" s="1" t="n">
+        <v>0.08307</v>
+      </c>
+      <c r="F538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="F538" s="1" t="n">
+      <c r="G538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -12289,10 +13906,13 @@
         <v>0.02502</v>
       </c>
       <c r="E539" s="1" t="n">
+        <v>0.02495</v>
+      </c>
+      <c r="F539" s="1" t="n">
         <v>0.02502</v>
       </c>
-      <c r="F539" s="1" t="n">
-        <v>0.02499</v>
+      <c r="G539" s="1" t="n">
+        <v>0.02495</v>
       </c>
     </row>
     <row r="540">
@@ -12311,9 +13931,12 @@
         <v>0.08488</v>
       </c>
       <c r="E540" s="1" t="n">
+        <v>0.08484</v>
+      </c>
+      <c r="F540" s="1" t="n">
         <v>0.08488</v>
       </c>
-      <c r="F540" s="1" t="n">
+      <c r="G540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -12333,9 +13956,12 @@
         <v>0.019</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>0.019</v>
+        <v>0.01901</v>
       </c>
       <c r="F541" s="1" t="n">
+        <v>0.01901</v>
+      </c>
+      <c r="G541" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -12358,6 +13984,9 @@
         <v>0.017</v>
       </c>
       <c r="F542" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G542" s="1" t="n">
         <v>0.01698</v>
       </c>
     </row>
@@ -12377,9 +14006,12 @@
         <v>0.105</v>
       </c>
       <c r="E543" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="F543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="F543" s="1" t="n">
+      <c r="G543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G543"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -424,8 +424,9 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,10 +457,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>price_01:15</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -484,9 +490,12 @@
         <v>70644.2</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>70644.2</v>
+        <v>70651.2</v>
       </c>
       <c r="G2" s="1" t="n">
+        <v>70651.2</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -509,9 +518,12 @@
         <v>2076.36</v>
       </c>
       <c r="F3" s="1" t="n">
+        <v>2076.27</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>2076.36</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="H3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -534,9 +546,12 @@
         <v>87.01000000000001</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -559,9 +574,12 @@
         <v>4.028</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>4.028</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>4.039</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -584,9 +602,12 @@
         <v>0.09528</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>0.09507</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>0.09485</v>
       </c>
     </row>
@@ -609,9 +630,12 @@
         <v>1.3922</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1.3922</v>
+        <v>1.3924</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>1.3924</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -634,9 +658,12 @@
         <v>22.35</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>22.292</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>22.657</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -659,9 +686,12 @@
         <v>0.002175</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>0.002157</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>0.002175</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>0.002119</v>
       </c>
     </row>
@@ -684,9 +714,12 @@
         <v>0.010265</v>
       </c>
       <c r="F10" s="1" t="n">
+        <v>0.010415</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -709,10 +742,13 @@
         <v>0.17111</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>0.16978</v>
+      <c r="H11" s="1" t="n">
+        <v>0.16834</v>
       </c>
     </row>
     <row r="12">
@@ -734,10 +770,13 @@
         <v>0.011847</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>0.011696</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>0.011847</v>
+      <c r="H12" s="1" t="n">
+        <v>0.011696</v>
       </c>
     </row>
     <row r="13">
@@ -759,9 +798,12 @@
         <v>38.333</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>38.192</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="H13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -784,9 +826,12 @@
         <v>654.02</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>653.84</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="H14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -809,9 +854,12 @@
         <v>209.93</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>209.79</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="H15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -834,9 +882,12 @@
         <v>0.0033537</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>0.0033453</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>0.0033417</v>
       </c>
     </row>
@@ -859,9 +910,12 @@
         <v>236.48</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>237</v>
+        <v>237.54</v>
       </c>
       <c r="G17" s="1" t="n">
+        <v>237.54</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -884,9 +938,12 @@
         <v>0.9959</v>
       </c>
       <c r="F18" s="1" t="n">
+        <v>0.9926</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="H18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -909,9 +966,12 @@
         <v>1.0555</v>
       </c>
       <c r="F19" s="1" t="n">
+        <v>1.0477</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="H19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -934,10 +994,13 @@
         <v>0.2612</v>
       </c>
       <c r="F20" s="1" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>0.2608</v>
+      <c r="H20" s="1" t="n">
+        <v>0.2605</v>
       </c>
     </row>
     <row r="21">
@@ -959,10 +1022,13 @@
         <v>0.6065700000000001</v>
       </c>
       <c r="F21" s="1" t="n">
+        <v>0.60234</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>0.60434</v>
+      <c r="H21" s="1" t="n">
+        <v>0.60234</v>
       </c>
     </row>
     <row r="22">
@@ -984,9 +1050,12 @@
         <v>9.032999999999999</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>9.032999999999999</v>
+        <v>9.037000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
+        <v>9.037000000000001</v>
+      </c>
+      <c r="H22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1009,10 +1078,13 @@
         <v>0.02422</v>
       </c>
       <c r="F23" s="1" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>0.02421</v>
+      <c r="H23" s="1" t="n">
+        <v>0.02404</v>
       </c>
     </row>
     <row r="24">
@@ -1034,9 +1106,12 @@
         <v>9.599</v>
       </c>
       <c r="F24" s="1" t="n">
+        <v>9.589</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="H24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -1059,9 +1134,12 @@
         <v>1.218</v>
       </c>
       <c r="F25" s="1" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>1.224</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="H25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1084,10 +1162,13 @@
         <v>0.07024</v>
       </c>
       <c r="F26" s="1" t="n">
+        <v>0.07023</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>0.07160999999999999</v>
       </c>
-      <c r="G26" s="1" t="n">
-        <v>0.07024</v>
+      <c r="H26" s="1" t="n">
+        <v>0.07023</v>
       </c>
     </row>
     <row r="27">
@@ -1109,9 +1190,12 @@
         <v>1.425</v>
       </c>
       <c r="F27" s="1" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>1.428</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="H27" s="1" t="n">
         <v>1.424</v>
       </c>
     </row>
@@ -1134,9 +1218,12 @@
         <v>1.312</v>
       </c>
       <c r="F28" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="H28" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -1159,9 +1246,12 @@
         <v>462.44</v>
       </c>
       <c r="F29" s="1" t="n">
+        <v>461.75</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>462.44</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="H29" s="1" t="n">
         <v>461.74</v>
       </c>
     </row>
@@ -1184,9 +1274,12 @@
         <v>1.279</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>1.279</v>
+        <v>1.2824</v>
       </c>
       <c r="G30" s="1" t="n">
+        <v>1.2824</v>
+      </c>
+      <c r="H30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1209,9 +1302,12 @@
         <v>5021.33</v>
       </c>
       <c r="F31" s="1" t="n">
+        <v>5021.91</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="G31" s="1" t="n">
+      <c r="H31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1234,9 +1330,12 @@
         <v>0.877</v>
       </c>
       <c r="F32" s="1" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.877</v>
       </c>
-      <c r="G32" s="1" t="n">
+      <c r="H32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1259,9 +1358,12 @@
         <v>0.001983</v>
       </c>
       <c r="F33" s="1" t="n">
+        <v>0.001981</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="G33" s="1" t="n">
+      <c r="H33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1284,10 +1386,13 @@
         <v>0.16806</v>
       </c>
       <c r="F34" s="1" t="n">
+        <v>0.16527</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>0.17091</v>
       </c>
-      <c r="G34" s="1" t="n">
-        <v>0.16678</v>
+      <c r="H34" s="1" t="n">
+        <v>0.16527</v>
       </c>
     </row>
     <row r="35">
@@ -1309,10 +1414,13 @@
         <v>0.29866</v>
       </c>
       <c r="F35" s="1" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="G35" s="1" t="n">
-        <v>0.2982</v>
+      <c r="H35" s="1" t="n">
+        <v>0.29802</v>
       </c>
     </row>
     <row r="36">
@@ -1334,9 +1442,12 @@
         <v>1.789</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>1.793</v>
+        <v>1.795</v>
       </c>
       <c r="G36" s="1" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="H36" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1359,9 +1470,12 @@
         <v>110.78</v>
       </c>
       <c r="F37" s="1" t="n">
+        <v>110.56</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="G37" s="1" t="n">
+      <c r="H37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1384,10 +1498,13 @@
         <v>0.22517</v>
       </c>
       <c r="F38" s="1" t="n">
+        <v>0.22414</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="G38" s="1" t="n">
-        <v>0.22488</v>
+      <c r="H38" s="1" t="n">
+        <v>0.22414</v>
       </c>
     </row>
     <row r="39">
@@ -1409,9 +1526,12 @@
         <v>0.1083</v>
       </c>
       <c r="F39" s="1" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="G39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="G39" s="1" t="n">
+      <c r="H39" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -1434,9 +1554,12 @@
         <v>0.37507</v>
       </c>
       <c r="F40" s="1" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="G40" s="1" t="n">
+      <c r="H40" s="1" t="n">
         <v>0.37042</v>
       </c>
     </row>
@@ -1459,9 +1582,12 @@
         <v>54.58</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>54.58</v>
+        <v>54.62</v>
       </c>
       <c r="G41" s="1" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="H41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1484,10 +1610,13 @@
         <v>0.0010772</v>
       </c>
       <c r="F42" s="1" t="n">
+        <v>0.0010732</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="G42" s="1" t="n">
-        <v>0.0010772</v>
+      <c r="H42" s="1" t="n">
+        <v>0.0010732</v>
       </c>
     </row>
     <row r="43">
@@ -1509,10 +1638,13 @@
         <v>6.443</v>
       </c>
       <c r="F43" s="1" t="n">
+        <v>6.438</v>
+      </c>
+      <c r="G43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="G43" s="1" t="n">
-        <v>6.443</v>
+      <c r="H43" s="1" t="n">
+        <v>6.438</v>
       </c>
     </row>
     <row r="44">
@@ -1534,10 +1666,13 @@
         <v>0.642</v>
       </c>
       <c r="F44" s="1" t="n">
+        <v>0.6399</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="G44" s="1" t="n">
-        <v>0.6401</v>
+      <c r="H44" s="1" t="n">
+        <v>0.6399</v>
       </c>
     </row>
     <row r="45">
@@ -1559,9 +1694,12 @@
         <v>0.3556</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.3556</v>
+        <v>0.3557</v>
       </c>
       <c r="G45" s="1" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="H45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -1584,10 +1722,13 @@
         <v>0.0324</v>
       </c>
       <c r="F46" s="1" t="n">
+        <v>0.03234</v>
+      </c>
+      <c r="G46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="G46" s="1" t="n">
-        <v>0.03237</v>
+      <c r="H46" s="1" t="n">
+        <v>0.03234</v>
       </c>
     </row>
     <row r="47">
@@ -1609,10 +1750,13 @@
         <v>0.07242999999999999</v>
       </c>
       <c r="F47" s="1" t="n">
+        <v>0.07163</v>
+      </c>
+      <c r="G47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="G47" s="1" t="n">
-        <v>0.07242999999999999</v>
+      <c r="H47" s="1" t="n">
+        <v>0.07163</v>
       </c>
     </row>
     <row r="48">
@@ -1634,9 +1778,12 @@
         <v>0.7057</v>
       </c>
       <c r="F48" s="1" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>0.7057</v>
       </c>
-      <c r="G48" s="1" t="n">
+      <c r="H48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -1659,9 +1806,12 @@
         <v>0.004571</v>
       </c>
       <c r="F49" s="1" t="n">
+        <v>0.004568</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="G49" s="1" t="n">
+      <c r="H49" s="1" t="n">
         <v>0.004564</v>
       </c>
     </row>
@@ -1684,9 +1834,12 @@
         <v>0.1047</v>
       </c>
       <c r="F50" s="1" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="G50" s="1" t="n">
+      <c r="H50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -1709,9 +1862,12 @@
         <v>0.04033</v>
       </c>
       <c r="F51" s="1" t="n">
+        <v>0.04044</v>
+      </c>
+      <c r="G51" s="1" t="n">
         <v>0.04047</v>
       </c>
-      <c r="G51" s="1" t="n">
+      <c r="H51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -1734,10 +1890,13 @@
         <v>0.1676</v>
       </c>
       <c r="F52" s="1" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="G52" s="1" t="n">
-        <v>0.1667</v>
+      <c r="H52" s="1" t="n">
+        <v>0.1665</v>
       </c>
     </row>
     <row r="53">
@@ -1759,10 +1918,13 @@
         <v>0.02167</v>
       </c>
       <c r="F53" s="1" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="G53" s="1" t="n">
-        <v>0.02164</v>
+      <c r="H53" s="1" t="n">
+        <v>0.02137</v>
       </c>
     </row>
     <row r="54">
@@ -1784,9 +1946,12 @@
         <v>0.007258</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>0.007246</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="G54" s="1" t="n">
+      <c r="H54" s="1" t="n">
         <v>0.007221</v>
       </c>
     </row>
@@ -1809,9 +1974,12 @@
         <v>3.929</v>
       </c>
       <c r="F55" s="1" t="n">
+        <v>3.926</v>
+      </c>
+      <c r="G55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="G55" s="1" t="n">
+      <c r="H55" s="1" t="n">
         <v>3.925</v>
       </c>
     </row>
@@ -1834,9 +2002,12 @@
         <v>0.017116</v>
       </c>
       <c r="F56" s="1" t="n">
+        <v>0.017197</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>0.017208</v>
       </c>
-      <c r="G56" s="1" t="n">
+      <c r="H56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -1859,9 +2030,12 @@
         <v>0.1117</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.1117</v>
+        <v>0.1118</v>
       </c>
       <c r="G57" s="1" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="H57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -1884,9 +2058,12 @@
         <v>2.649</v>
       </c>
       <c r="F58" s="1" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="G58" s="1" t="n">
+      <c r="H58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -1909,9 +2086,12 @@
         <v>0.1603</v>
       </c>
       <c r="F59" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="H59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -1934,9 +2114,12 @@
         <v>0.00593</v>
       </c>
       <c r="F60" s="1" t="n">
+        <v>0.005918</v>
+      </c>
+      <c r="G60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="G60" s="1" t="n">
+      <c r="H60" s="1" t="n">
         <v>0.005914</v>
       </c>
     </row>
@@ -1959,9 +2142,12 @@
         <v>0.09215</v>
       </c>
       <c r="F61" s="1" t="n">
+        <v>0.09206</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="G61" s="1" t="n">
+      <c r="H61" s="1" t="n">
         <v>0.09204</v>
       </c>
     </row>
@@ -1984,9 +2170,12 @@
         <v>0.9154</v>
       </c>
       <c r="F62" s="1" t="n">
+        <v>0.9145</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="G62" s="1" t="n">
+      <c r="H62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -2009,9 +2198,12 @@
         <v>0.779</v>
       </c>
       <c r="F63" s="1" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="G63" s="1" t="n">
         <v>0.779</v>
       </c>
-      <c r="G63" s="1" t="n">
+      <c r="H63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -2034,9 +2226,12 @@
         <v>0.04671</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.04677</v>
+        <v>0.04753</v>
       </c>
       <c r="G64" s="1" t="n">
+        <v>0.04753</v>
+      </c>
+      <c r="H64" s="1" t="n">
         <v>0.04623</v>
       </c>
     </row>
@@ -2059,10 +2254,13 @@
         <v>355.08</v>
       </c>
       <c r="F65" s="1" t="n">
+        <v>354.23</v>
+      </c>
+      <c r="G65" s="1" t="n">
         <v>357.66</v>
       </c>
-      <c r="G65" s="1" t="n">
-        <v>355.08</v>
+      <c r="H65" s="1" t="n">
+        <v>354.23</v>
       </c>
     </row>
     <row r="66">
@@ -2084,10 +2282,13 @@
         <v>0.12558</v>
       </c>
       <c r="F66" s="1" t="n">
+        <v>0.12516</v>
+      </c>
+      <c r="G66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="G66" s="1" t="n">
-        <v>0.12558</v>
+      <c r="H66" s="1" t="n">
+        <v>0.12516</v>
       </c>
     </row>
     <row r="67">
@@ -2109,10 +2310,13 @@
         <v>0.244</v>
       </c>
       <c r="F67" s="1" t="n">
+        <v>0.2398</v>
+      </c>
+      <c r="G67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="G67" s="1" t="n">
-        <v>0.2418</v>
+      <c r="H67" s="1" t="n">
+        <v>0.2398</v>
       </c>
     </row>
     <row r="68">
@@ -2134,9 +2338,12 @@
         <v>0.00343</v>
       </c>
       <c r="F68" s="1" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="G68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="G68" s="1" t="n">
+      <c r="H68" s="1" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -2159,10 +2366,13 @@
         <v>0.1761</v>
       </c>
       <c r="F69" s="1" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="G69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="G69" s="1" t="n">
-        <v>0.1759</v>
+      <c r="H69" s="1" t="n">
+        <v>0.1755</v>
       </c>
     </row>
     <row r="70">
@@ -2184,9 +2394,12 @@
         <v>0.16485</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.16485</v>
+        <v>0.1649</v>
       </c>
       <c r="G70" s="1" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="H70" s="1" t="n">
         <v>0.16421</v>
       </c>
     </row>
@@ -2209,9 +2422,12 @@
         <v>0.3554</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.3554</v>
+        <v>0.3574</v>
       </c>
       <c r="G71" s="1" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="H71" s="1" t="n">
         <v>0.3517</v>
       </c>
     </row>
@@ -2234,9 +2450,12 @@
         <v>0.7083</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.7083</v>
+        <v>0.7097</v>
       </c>
       <c r="G72" s="1" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="H72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -2259,9 +2478,12 @@
         <v>0.008630000000000001</v>
       </c>
       <c r="F73" s="1" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="G73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="G73" s="1" t="n">
+      <c r="H73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -2284,9 +2506,12 @@
         <v>0.006018</v>
       </c>
       <c r="F74" s="1" t="n">
+        <v>0.006003</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="G74" s="1" t="n">
+      <c r="H74" s="1" t="n">
         <v>0.006002</v>
       </c>
     </row>
@@ -2309,9 +2534,12 @@
         <v>0.228</v>
       </c>
       <c r="F75" s="1" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="G75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="H75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -2334,9 +2562,12 @@
         <v>0.3084</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.3084</v>
+        <v>0.3103</v>
       </c>
       <c r="G76" s="1" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="H76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -2359,9 +2590,12 @@
         <v>0.1007</v>
       </c>
       <c r="F77" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="G77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="G77" s="1" t="n">
+      <c r="H77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -2384,9 +2618,12 @@
         <v>0.1233</v>
       </c>
       <c r="F78" s="1" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="G78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="H78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -2409,9 +2646,12 @@
         <v>0.06891</v>
       </c>
       <c r="F79" s="1" t="n">
+        <v>0.06879</v>
+      </c>
+      <c r="G79" s="1" t="n">
         <v>0.06933</v>
       </c>
-      <c r="G79" s="1" t="n">
+      <c r="H79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -2434,9 +2674,12 @@
         <v>0.04699</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.04699</v>
+        <v>0.04709</v>
       </c>
       <c r="G80" s="1" t="n">
+        <v>0.04709</v>
+      </c>
+      <c r="H80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -2459,9 +2702,12 @@
         <v>0.000235</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.000235</v>
+        <v>0.000242</v>
       </c>
       <c r="G81" s="1" t="n">
+        <v>0.000242</v>
+      </c>
+      <c r="H81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -2484,9 +2730,12 @@
         <v>8.244999999999999</v>
       </c>
       <c r="F82" s="1" t="n">
+        <v>8.233000000000001</v>
+      </c>
+      <c r="G82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="G82" s="1" t="n">
+      <c r="H82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -2509,10 +2758,13 @@
         <v>0.0005892</v>
       </c>
       <c r="F83" s="1" t="n">
+        <v>0.0005831</v>
+      </c>
+      <c r="G83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="G83" s="1" t="n">
-        <v>0.0005892</v>
+      <c r="H83" s="1" t="n">
+        <v>0.0005831</v>
       </c>
     </row>
     <row r="84">
@@ -2534,9 +2786,12 @@
         <v>0.4154</v>
       </c>
       <c r="F84" s="1" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="G84" s="1" t="n">
         <v>0.4212</v>
       </c>
-      <c r="G84" s="1" t="n">
+      <c r="H84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -2559,9 +2814,12 @@
         <v>0.06279</v>
       </c>
       <c r="F85" s="1" t="n">
+        <v>0.06249</v>
+      </c>
+      <c r="G85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="G85" s="1" t="n">
+      <c r="H85" s="1" t="n">
         <v>0.06243</v>
       </c>
     </row>
@@ -2584,9 +2842,12 @@
         <v>0.05447</v>
       </c>
       <c r="F86" s="1" t="n">
+        <v>0.05465</v>
+      </c>
+      <c r="G86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="G86" s="1" t="n">
+      <c r="H86" s="1" t="n">
         <v>0.05447</v>
       </c>
     </row>
@@ -2609,9 +2870,12 @@
         <v>0.003356</v>
       </c>
       <c r="F87" s="1" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="G87" s="1" t="n">
         <v>0.003356</v>
       </c>
-      <c r="G87" s="1" t="n">
+      <c r="H87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -2634,9 +2898,12 @@
         <v>0.05045</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.05045</v>
+        <v>0.05073</v>
       </c>
       <c r="G88" s="1" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="H88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -2659,9 +2926,12 @@
         <v>0.03086</v>
       </c>
       <c r="F89" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="G89" s="1" t="n">
         <v>0.03086</v>
       </c>
-      <c r="G89" s="1" t="n">
+      <c r="H89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -2684,9 +2954,12 @@
         <v>0.3486</v>
       </c>
       <c r="F90" s="1" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="G90" s="1" t="n">
         <v>0.3491</v>
       </c>
-      <c r="G90" s="1" t="n">
+      <c r="H90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -2709,9 +2982,12 @@
         <v>0.06122</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>0.06122</v>
+        <v>0.06163</v>
       </c>
       <c r="G91" s="1" t="n">
+        <v>0.06163</v>
+      </c>
+      <c r="H91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -2734,9 +3010,12 @@
         <v>0.3494</v>
       </c>
       <c r="F92" s="1" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="G92" s="1" t="n">
         <v>0.3527</v>
       </c>
-      <c r="G92" s="1" t="n">
+      <c r="H92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -2759,9 +3038,12 @@
         <v>1.9753</v>
       </c>
       <c r="F93" s="1" t="n">
+        <v>1.9671</v>
+      </c>
+      <c r="G93" s="1" t="n">
         <v>1.9753</v>
       </c>
-      <c r="G93" s="1" t="n">
+      <c r="H93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -2784,9 +3066,12 @@
         <v>0.2599</v>
       </c>
       <c r="F94" s="1" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="G94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="G94" s="1" t="n">
+      <c r="H94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -2809,9 +3094,12 @@
         <v>0.04542</v>
       </c>
       <c r="F95" s="1" t="n">
+        <v>0.04531</v>
+      </c>
+      <c r="G95" s="1" t="n">
         <v>0.04542</v>
       </c>
-      <c r="G95" s="1" t="n">
+      <c r="H95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -2834,9 +3122,12 @@
         <v>0.006343</v>
       </c>
       <c r="F96" s="1" t="n">
+        <v>0.006205</v>
+      </c>
+      <c r="G96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="G96" s="1" t="n">
+      <c r="H96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -2859,9 +3150,12 @@
         <v>0.001732</v>
       </c>
       <c r="F97" s="1" t="n">
+        <v>0.001739</v>
+      </c>
+      <c r="G97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="G97" s="1" t="n">
+      <c r="H97" s="1" t="n">
         <v>0.001732</v>
       </c>
     </row>
@@ -2884,9 +3178,12 @@
         <v>5.221</v>
       </c>
       <c r="F98" s="1" t="n">
+        <v>5.243</v>
+      </c>
+      <c r="G98" s="1" t="n">
         <v>5.284</v>
       </c>
-      <c r="G98" s="1" t="n">
+      <c r="H98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -2909,9 +3206,12 @@
         <v>0.0153</v>
       </c>
       <c r="F99" s="1" t="n">
+        <v>0.01523</v>
+      </c>
+      <c r="G99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="G99" s="1" t="n">
+      <c r="H99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -2934,9 +3234,12 @@
         <v>0.552</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>0.552</v>
+        <v>0.5523</v>
       </c>
       <c r="G100" s="1" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="H100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -2962,6 +3265,9 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="G101" s="1" t="n">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="H101" s="1" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -2984,9 +3290,12 @@
         <v>32.55</v>
       </c>
       <c r="F102" s="1" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="G102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="G102" s="1" t="n">
+      <c r="H102" s="1" t="n">
         <v>32.48</v>
       </c>
     </row>
@@ -3009,9 +3318,12 @@
         <v>0.03258</v>
       </c>
       <c r="F103" s="1" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="G103" s="1" t="n">
+      <c r="H103" s="1" t="n">
         <v>0.032</v>
       </c>
     </row>
@@ -3034,9 +3346,12 @@
         <v>0.06612</v>
       </c>
       <c r="F104" s="1" t="n">
+        <v>0.06601</v>
+      </c>
+      <c r="G104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="G104" s="1" t="n">
+      <c r="H104" s="1" t="n">
         <v>0.06582</v>
       </c>
     </row>
@@ -3059,9 +3374,12 @@
         <v>1.3041</v>
       </c>
       <c r="F105" s="1" t="n">
+        <v>1.3037</v>
+      </c>
+      <c r="G105" s="1" t="n">
         <v>1.3041</v>
       </c>
-      <c r="G105" s="1" t="n">
+      <c r="H105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -3084,9 +3402,12 @@
         <v>0.1188</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="G106" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -3109,11 +3430,14 @@
         <v>0.12</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="G107" s="1" t="n">
         <v>0.12</v>
       </c>
+      <c r="H107" s="1" t="n">
+        <v>0.119</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3134,9 +3458,12 @@
         <v>0.09606000000000001</v>
       </c>
       <c r="F108" s="1" t="n">
+        <v>0.09597</v>
+      </c>
+      <c r="G108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="G108" s="1" t="n">
+      <c r="H108" s="1" t="n">
         <v>0.09589</v>
       </c>
     </row>
@@ -3159,9 +3486,12 @@
         <v>0.13987</v>
       </c>
       <c r="F109" s="1" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="G109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="G109" s="1" t="n">
+      <c r="H109" s="1" t="n">
         <v>0.13861</v>
       </c>
     </row>
@@ -3184,9 +3514,12 @@
         <v>5.578</v>
       </c>
       <c r="F110" s="1" t="n">
+        <v>5.566</v>
+      </c>
+      <c r="G110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="G110" s="1" t="n">
+      <c r="H110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -3212,6 +3545,9 @@
         <v>1.109</v>
       </c>
       <c r="G111" s="1" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="H111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -3234,10 +3570,13 @@
         <v>0.029477</v>
       </c>
       <c r="F112" s="1" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="G112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="G112" s="1" t="n">
-        <v>0.029477</v>
+      <c r="H112" s="1" t="n">
+        <v>0.029256</v>
       </c>
     </row>
     <row r="113">
@@ -3259,9 +3598,12 @@
         <v>1.876</v>
       </c>
       <c r="F113" s="1" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="G113" s="1" t="n">
         <v>1.879</v>
       </c>
-      <c r="G113" s="1" t="n">
+      <c r="H113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -3284,10 +3626,13 @@
         <v>0.05906</v>
       </c>
       <c r="F114" s="1" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="G114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="G114" s="1" t="n">
-        <v>0.05906</v>
+      <c r="H114" s="1" t="n">
+        <v>0.05903</v>
       </c>
     </row>
     <row r="115">
@@ -3309,10 +3654,13 @@
         <v>0.12799</v>
       </c>
       <c r="F115" s="1" t="n">
+        <v>0.12732</v>
+      </c>
+      <c r="G115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="G115" s="1" t="n">
-        <v>0.12799</v>
+      <c r="H115" s="1" t="n">
+        <v>0.12732</v>
       </c>
     </row>
     <row r="116">
@@ -3334,9 +3682,12 @@
         <v>1.1055</v>
       </c>
       <c r="F116" s="1" t="n">
+        <v>1.1064</v>
+      </c>
+      <c r="G116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="G116" s="1" t="n">
+      <c r="H116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -3359,9 +3710,12 @@
         <v>0.1612</v>
       </c>
       <c r="F117" s="1" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="G117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="G117" s="1" t="n">
+      <c r="H117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -3384,9 +3738,12 @@
         <v>0.1585</v>
       </c>
       <c r="F118" s="1" t="n">
-        <v>0.1585</v>
+        <v>0.1589</v>
       </c>
       <c r="G118" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="H118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -3409,9 +3766,12 @@
         <v>0.04573</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>0.04588</v>
+        <v>0.04596</v>
       </c>
       <c r="G119" s="1" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="H119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -3434,9 +3794,12 @@
         <v>3.033</v>
       </c>
       <c r="F120" s="1" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="G120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="G120" s="1" t="n">
+      <c r="H120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -3459,9 +3822,12 @@
         <v>0.2976</v>
       </c>
       <c r="F121" s="1" t="n">
-        <v>0.2976</v>
+        <v>0.2977</v>
       </c>
       <c r="G121" s="1" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="H121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -3484,9 +3850,12 @@
         <v>0.5857</v>
       </c>
       <c r="F122" s="1" t="n">
+        <v>0.5841</v>
+      </c>
+      <c r="G122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="G122" s="1" t="n">
+      <c r="H122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -3509,9 +3878,12 @@
         <v>0.0126</v>
       </c>
       <c r="F123" s="1" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="G123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="G123" s="1" t="n">
+      <c r="H123" s="1" t="n">
         <v>0.0126</v>
       </c>
     </row>
@@ -3534,9 +3906,12 @@
         <v>0.1592</v>
       </c>
       <c r="F124" s="1" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="G124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="G124" s="1" t="n">
+      <c r="H124" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -3559,9 +3934,12 @@
         <v>0.001785</v>
       </c>
       <c r="F125" s="1" t="n">
+        <v>0.001779</v>
+      </c>
+      <c r="G125" s="1" t="n">
         <v>0.001785</v>
       </c>
-      <c r="G125" s="1" t="n">
+      <c r="H125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -3584,10 +3962,13 @@
         <v>0.000489</v>
       </c>
       <c r="F126" s="1" t="n">
+        <v>0.0004881</v>
+      </c>
+      <c r="G126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="G126" s="1" t="n">
-        <v>0.000489</v>
+      <c r="H126" s="1" t="n">
+        <v>0.0004881</v>
       </c>
     </row>
     <row r="127">
@@ -3609,9 +3990,12 @@
         <v>0.02959</v>
       </c>
       <c r="F127" s="1" t="n">
+        <v>0.02955</v>
+      </c>
+      <c r="G127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="G127" s="1" t="n">
+      <c r="H127" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -3634,9 +4018,12 @@
         <v>0.04131</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>0.04131</v>
+        <v>0.04134</v>
       </c>
       <c r="G128" s="1" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="H128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -3659,10 +4046,13 @@
         <v>0.04858</v>
       </c>
       <c r="F129" s="1" t="n">
+        <v>0.04838</v>
+      </c>
+      <c r="G129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="G129" s="1" t="n">
-        <v>0.04858</v>
+      <c r="H129" s="1" t="n">
+        <v>0.04838</v>
       </c>
     </row>
     <row r="130">
@@ -3684,9 +4074,12 @@
         <v>1.25e-05</v>
       </c>
       <c r="F130" s="1" t="n">
+        <v>1.24e-05</v>
+      </c>
+      <c r="G130" s="1" t="n">
         <v>1.25e-05</v>
       </c>
-      <c r="G130" s="1" t="n">
+      <c r="H130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -3709,9 +4102,12 @@
         <v>6.8e-06</v>
       </c>
       <c r="F131" s="1" t="n">
+        <v>6.9e-06</v>
+      </c>
+      <c r="G131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="G131" s="1" t="n">
+      <c r="H131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -3734,9 +4130,12 @@
         <v>0.00703</v>
       </c>
       <c r="F132" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="G132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="G132" s="1" t="n">
+      <c r="H132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -3759,9 +4158,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="F133" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="G133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="G133" s="1" t="n">
+      <c r="H133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -3784,9 +4186,12 @@
         <v>0.0004108</v>
       </c>
       <c r="F134" s="1" t="n">
+        <v>0.0004103</v>
+      </c>
+      <c r="G134" s="1" t="n">
         <v>0.0004113</v>
       </c>
-      <c r="G134" s="1" t="n">
+      <c r="H134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -3809,9 +4214,12 @@
         <v>0.08426</v>
       </c>
       <c r="F135" s="1" t="n">
-        <v>0.08426</v>
+        <v>0.08468000000000001</v>
       </c>
       <c r="G135" s="1" t="n">
+        <v>0.08468000000000001</v>
+      </c>
+      <c r="H135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -3834,10 +4242,13 @@
         <v>0.007962</v>
       </c>
       <c r="F136" s="1" t="n">
+        <v>0.007891</v>
+      </c>
+      <c r="G136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="G136" s="1" t="n">
-        <v>0.007962</v>
+      <c r="H136" s="1" t="n">
+        <v>0.007891</v>
       </c>
     </row>
     <row r="137">
@@ -3859,9 +4270,12 @@
         <v>0.0008222</v>
       </c>
       <c r="F137" s="1" t="n">
+        <v>0.0008233</v>
+      </c>
+      <c r="G137" s="1" t="n">
         <v>0.0008262</v>
       </c>
-      <c r="G137" s="1" t="n">
+      <c r="H137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -3884,10 +4298,13 @@
         <v>0.1487</v>
       </c>
       <c r="F138" s="1" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="G138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="G138" s="1" t="n">
-        <v>0.1483</v>
+      <c r="H138" s="1" t="n">
+        <v>0.1482</v>
       </c>
     </row>
     <row r="139">
@@ -3909,9 +4326,12 @@
         <v>0.00674</v>
       </c>
       <c r="F139" s="1" t="n">
+        <v>0.006728</v>
+      </c>
+      <c r="G139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="G139" s="1" t="n">
+      <c r="H139" s="1" t="n">
         <v>0.006725</v>
       </c>
     </row>
@@ -3934,10 +4354,13 @@
         <v>0.01389</v>
       </c>
       <c r="F140" s="1" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="G140" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="G140" s="1" t="n">
-        <v>0.01387</v>
+      <c r="H140" s="1" t="n">
+        <v>0.01383</v>
       </c>
     </row>
     <row r="141">
@@ -3959,10 +4382,13 @@
         <v>0.09772</v>
       </c>
       <c r="F141" s="1" t="n">
+        <v>0.09758</v>
+      </c>
+      <c r="G141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="G141" s="1" t="n">
-        <v>0.09772</v>
+      <c r="H141" s="1" t="n">
+        <v>0.09758</v>
       </c>
     </row>
     <row r="142">
@@ -3984,9 +4410,12 @@
         <v>0.05413</v>
       </c>
       <c r="F142" s="1" t="n">
+        <v>0.05412</v>
+      </c>
+      <c r="G142" s="1" t="n">
         <v>0.05416</v>
       </c>
-      <c r="G142" s="1" t="n">
+      <c r="H142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -4009,9 +4438,12 @@
         <v>0.3262</v>
       </c>
       <c r="F143" s="1" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="G143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="G143" s="1" t="n">
+      <c r="H143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -4034,10 +4466,13 @@
         <v>0.02588</v>
       </c>
       <c r="F144" s="1" t="n">
+        <v>0.02572</v>
+      </c>
+      <c r="G144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="G144" s="1" t="n">
-        <v>0.02576</v>
+      <c r="H144" s="1" t="n">
+        <v>0.02572</v>
       </c>
     </row>
     <row r="145">
@@ -4059,9 +4494,12 @@
         <v>0.2379</v>
       </c>
       <c r="F145" s="1" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="G145" s="1" t="n">
         <v>0.238</v>
       </c>
-      <c r="G145" s="1" t="n">
+      <c r="H145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -4084,10 +4522,13 @@
         <v>0.007129</v>
       </c>
       <c r="F146" s="1" t="n">
+        <v>0.007052</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="G146" s="1" t="n">
-        <v>0.007066</v>
+      <c r="H146" s="1" t="n">
+        <v>0.007052</v>
       </c>
     </row>
     <row r="147">
@@ -4109,10 +4550,13 @@
         <v>0.08703</v>
       </c>
       <c r="F147" s="1" t="n">
+        <v>0.08659</v>
+      </c>
+      <c r="G147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="G147" s="1" t="n">
-        <v>0.08695</v>
+      <c r="H147" s="1" t="n">
+        <v>0.08659</v>
       </c>
     </row>
     <row r="148">
@@ -4134,9 +4578,12 @@
         <v>0.05057</v>
       </c>
       <c r="F148" s="1" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>0.05072</v>
       </c>
-      <c r="G148" s="1" t="n">
+      <c r="H148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -4159,10 +4606,13 @@
         <v>0.02393</v>
       </c>
       <c r="F149" s="1" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="G149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="G149" s="1" t="n">
-        <v>0.02391</v>
+      <c r="H149" s="1" t="n">
+        <v>0.02386</v>
       </c>
     </row>
     <row r="150">
@@ -4184,10 +4634,13 @@
         <v>0.08606999999999999</v>
       </c>
       <c r="F150" s="1" t="n">
+        <v>0.08495</v>
+      </c>
+      <c r="G150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="G150" s="1" t="n">
-        <v>0.08606999999999999</v>
+      <c r="H150" s="1" t="n">
+        <v>0.08495</v>
       </c>
     </row>
     <row r="151">
@@ -4209,10 +4662,13 @@
         <v>0.02329</v>
       </c>
       <c r="F151" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="G151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="G151" s="1" t="n">
-        <v>0.02329</v>
+      <c r="H151" s="1" t="n">
+        <v>0.0232</v>
       </c>
     </row>
     <row r="152">
@@ -4234,10 +4690,13 @@
         <v>0.02582</v>
       </c>
       <c r="F152" s="1" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="G152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="G152" s="1" t="n">
-        <v>0.02577</v>
+      <c r="H152" s="1" t="n">
+        <v>0.02571</v>
       </c>
     </row>
     <row r="153">
@@ -4259,9 +4718,12 @@
         <v>0.0002098</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>0.0002102</v>
+        <v>0.0002145</v>
       </c>
       <c r="G153" s="1" t="n">
+        <v>0.0002145</v>
+      </c>
+      <c r="H153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -4284,9 +4746,12 @@
         <v>0.4457</v>
       </c>
       <c r="F154" s="1" t="n">
-        <v>0.4457</v>
+        <v>0.4474</v>
       </c>
       <c r="G154" s="1" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="H154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -4309,9 +4774,12 @@
         <v>0.06662999999999999</v>
       </c>
       <c r="F155" s="1" t="n">
+        <v>0.06716</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="G155" s="1" t="n">
+      <c r="H155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -4334,9 +4802,12 @@
         <v>0.12848</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>0.12859</v>
+        <v>0.12938</v>
       </c>
       <c r="G156" s="1" t="n">
+        <v>0.12938</v>
+      </c>
+      <c r="H156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -4359,10 +4830,13 @@
         <v>0.4846</v>
       </c>
       <c r="F157" s="1" t="n">
+        <v>0.4843</v>
+      </c>
+      <c r="G157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="G157" s="1" t="n">
-        <v>0.4844</v>
+      <c r="H157" s="1" t="n">
+        <v>0.4843</v>
       </c>
     </row>
     <row r="158">
@@ -4384,9 +4858,12 @@
         <v>0.4523</v>
       </c>
       <c r="F158" s="1" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="G158" s="1" t="n">
+      <c r="H158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -4409,10 +4886,13 @@
         <v>0.007552</v>
       </c>
       <c r="F159" s="1" t="n">
+        <v>0.007523</v>
+      </c>
+      <c r="G159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="G159" s="1" t="n">
-        <v>0.007528</v>
+      <c r="H159" s="1" t="n">
+        <v>0.007523</v>
       </c>
     </row>
     <row r="160">
@@ -4434,9 +4914,12 @@
         <v>0.004655</v>
       </c>
       <c r="F160" s="1" t="n">
+        <v>0.004653</v>
+      </c>
+      <c r="G160" s="1" t="n">
         <v>0.004655</v>
       </c>
-      <c r="G160" s="1" t="n">
+      <c r="H160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -4459,9 +4942,12 @@
         <v>0.004314</v>
       </c>
       <c r="F161" s="1" t="n">
+        <v>0.004306</v>
+      </c>
+      <c r="G161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="G161" s="1" t="n">
+      <c r="H161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -4484,9 +4970,12 @@
         <v>0.0963</v>
       </c>
       <c r="F162" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="G162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="G162" s="1" t="n">
+      <c r="H162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -4509,9 +4998,12 @@
         <v>0.2865</v>
       </c>
       <c r="F163" s="1" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="G163" s="1" t="n">
+      <c r="H163" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -4534,10 +5026,13 @@
         <v>0.1146</v>
       </c>
       <c r="F164" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="G164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="G164" s="1" t="n">
-        <v>0.1145</v>
+      <c r="H164" s="1" t="n">
+        <v>0.1144</v>
       </c>
     </row>
     <row r="165">
@@ -4559,9 +5054,12 @@
         <v>0.1761</v>
       </c>
       <c r="F165" s="1" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="G165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="G165" s="1" t="n">
+      <c r="H165" s="1" t="n">
         <v>0.1756</v>
       </c>
     </row>
@@ -4584,9 +5082,12 @@
         <v>0.01008</v>
       </c>
       <c r="F166" s="1" t="n">
-        <v>0.01008</v>
+        <v>0.01009</v>
       </c>
       <c r="G166" s="1" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="H166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -4609,9 +5110,12 @@
         <v>1.836</v>
       </c>
       <c r="F167" s="1" t="n">
+        <v>1.835</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>1.836</v>
       </c>
-      <c r="G167" s="1" t="n">
+      <c r="H167" s="1" t="n">
         <v>1.827</v>
       </c>
     </row>
@@ -4634,9 +5138,12 @@
         <v>1.363</v>
       </c>
       <c r="F168" s="1" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="G168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="G168" s="1" t="n">
+      <c r="H168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -4659,10 +5166,13 @@
         <v>0.007335</v>
       </c>
       <c r="F169" s="1" t="n">
+        <v>0.007319</v>
+      </c>
+      <c r="G169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="G169" s="1" t="n">
-        <v>0.007321</v>
+      <c r="H169" s="1" t="n">
+        <v>0.007319</v>
       </c>
     </row>
     <row r="170">
@@ -4684,9 +5194,12 @@
         <v>0.0115</v>
       </c>
       <c r="F170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="G170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="G170" s="1" t="n">
+      <c r="H170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -4709,9 +5222,12 @@
         <v>0.005816</v>
       </c>
       <c r="F171" s="1" t="n">
+        <v>0.005826</v>
+      </c>
+      <c r="G171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="G171" s="1" t="n">
+      <c r="H171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -4734,9 +5250,12 @@
         <v>0.14796</v>
       </c>
       <c r="F172" s="1" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="G172" s="1" t="n">
         <v>0.14796</v>
       </c>
-      <c r="G172" s="1" t="n">
+      <c r="H172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -4759,9 +5278,12 @@
         <v>4.893</v>
       </c>
       <c r="F173" s="1" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="G173" s="1" t="n">
+      <c r="H173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -4784,9 +5306,12 @@
         <v>0.07924</v>
       </c>
       <c r="F174" s="1" t="n">
+        <v>0.07949000000000001</v>
+      </c>
+      <c r="G174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="G174" s="1" t="n">
+      <c r="H174" s="1" t="n">
         <v>0.07868</v>
       </c>
     </row>
@@ -4809,10 +5334,13 @@
         <v>0.00751</v>
       </c>
       <c r="F175" s="1" t="n">
+        <v>0.007485</v>
+      </c>
+      <c r="G175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="G175" s="1" t="n">
-        <v>0.007488</v>
+      <c r="H175" s="1" t="n">
+        <v>0.007485</v>
       </c>
     </row>
     <row r="176">
@@ -4834,9 +5362,12 @@
         <v>0.2018</v>
       </c>
       <c r="F176" s="1" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="G176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="G176" s="1" t="n">
+      <c r="H176" s="1" t="n">
         <v>0.2016</v>
       </c>
     </row>
@@ -4859,9 +5390,12 @@
         <v>0.05184</v>
       </c>
       <c r="F177" s="1" t="n">
+        <v>0.05184</v>
+      </c>
+      <c r="G177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="G177" s="1" t="n">
+      <c r="H177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -4884,9 +5418,12 @@
         <v>0.05464</v>
       </c>
       <c r="F178" s="1" t="n">
+        <v>0.05459</v>
+      </c>
+      <c r="G178" s="1" t="n">
         <v>0.05465</v>
       </c>
-      <c r="G178" s="1" t="n">
+      <c r="H178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -4909,9 +5446,12 @@
         <v>0.0233</v>
       </c>
       <c r="F179" s="1" t="n">
+        <v>0.02333</v>
+      </c>
+      <c r="G179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="G179" s="1" t="n">
+      <c r="H179" s="1" t="n">
         <v>0.02324</v>
       </c>
     </row>
@@ -4934,9 +5474,12 @@
         <v>0.6941000000000001</v>
       </c>
       <c r="F180" s="1" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6958</v>
       </c>
       <c r="G180" s="1" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="H180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -4959,10 +5502,13 @@
         <v>0.0003727</v>
       </c>
       <c r="F181" s="1" t="n">
+        <v>0.0003716</v>
+      </c>
+      <c r="G181" s="1" t="n">
         <v>0.0003731</v>
       </c>
-      <c r="G181" s="1" t="n">
-        <v>0.0003724</v>
+      <c r="H181" s="1" t="n">
+        <v>0.0003716</v>
       </c>
     </row>
     <row r="182">
@@ -4984,10 +5530,13 @@
         <v>0.0127</v>
       </c>
       <c r="F182" s="1" t="n">
+        <v>0.01266</v>
+      </c>
+      <c r="G182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="G182" s="1" t="n">
-        <v>0.0127</v>
+      <c r="H182" s="1" t="n">
+        <v>0.01266</v>
       </c>
     </row>
     <row r="183">
@@ -5009,10 +5558,13 @@
         <v>4.266</v>
       </c>
       <c r="F183" s="1" t="n">
+        <v>4.261</v>
+      </c>
+      <c r="G183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="G183" s="1" t="n">
-        <v>4.265</v>
+      <c r="H183" s="1" t="n">
+        <v>4.261</v>
       </c>
     </row>
     <row r="184">
@@ -5034,9 +5586,12 @@
         <v>0.2368</v>
       </c>
       <c r="F184" s="1" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="G184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="G184" s="1" t="n">
+      <c r="H184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -5059,10 +5614,13 @@
         <v>0.03774</v>
       </c>
       <c r="F185" s="1" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="G185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="G185" s="1" t="n">
-        <v>0.03769</v>
+      <c r="H185" s="1" t="n">
+        <v>0.03764</v>
       </c>
     </row>
     <row r="186">
@@ -5084,9 +5642,12 @@
         <v>0.11628</v>
       </c>
       <c r="F186" s="1" t="n">
+        <v>0.11626</v>
+      </c>
+      <c r="G186" s="1" t="n">
         <v>0.11628</v>
       </c>
-      <c r="G186" s="1" t="n">
+      <c r="H186" s="1" t="n">
         <v>0.11573</v>
       </c>
     </row>
@@ -5109,10 +5670,13 @@
         <v>0.009186</v>
       </c>
       <c r="F187" s="1" t="n">
+        <v>0.009018999999999999</v>
+      </c>
+      <c r="G187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="G187" s="1" t="n">
-        <v>0.009131</v>
+      <c r="H187" s="1" t="n">
+        <v>0.009018999999999999</v>
       </c>
     </row>
     <row r="188">
@@ -5134,9 +5698,12 @@
         <v>0.0978</v>
       </c>
       <c r="F188" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="G188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="G188" s="1" t="n">
+      <c r="H188" s="1" t="n">
         <v>0.0975</v>
       </c>
     </row>
@@ -5159,10 +5726,13 @@
         <v>0.02796</v>
       </c>
       <c r="F189" s="1" t="n">
+        <v>0.02773</v>
+      </c>
+      <c r="G189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="G189" s="1" t="n">
-        <v>0.02774</v>
+      <c r="H189" s="1" t="n">
+        <v>0.02773</v>
       </c>
     </row>
     <row r="190">
@@ -5184,9 +5754,12 @@
         <v>0.00886</v>
       </c>
       <c r="F190" s="1" t="n">
+        <v>0.008829999999999999</v>
+      </c>
+      <c r="G190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="G190" s="1" t="n">
+      <c r="H190" s="1" t="n">
         <v>0.00873</v>
       </c>
     </row>
@@ -5209,9 +5782,12 @@
         <v>0.001954</v>
       </c>
       <c r="F191" s="1" t="n">
+        <v>0.001953</v>
+      </c>
+      <c r="G191" s="1" t="n">
         <v>0.001956</v>
       </c>
-      <c r="G191" s="1" t="n">
+      <c r="H191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -5234,9 +5810,12 @@
         <v>0.1009</v>
       </c>
       <c r="F192" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="G192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="G192" s="1" t="n">
+      <c r="H192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -5259,9 +5838,12 @@
         <v>0.02333</v>
       </c>
       <c r="F193" s="1" t="n">
-        <v>0.02334</v>
+        <v>0.02336</v>
       </c>
       <c r="G193" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="H193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -5284,10 +5866,13 @@
         <v>0.01349</v>
       </c>
       <c r="F194" s="1" t="n">
+        <v>0.01346</v>
+      </c>
+      <c r="G194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="G194" s="1" t="n">
-        <v>0.01349</v>
+      <c r="H194" s="1" t="n">
+        <v>0.01346</v>
       </c>
     </row>
     <row r="195">
@@ -5309,9 +5894,12 @@
         <v>0.021</v>
       </c>
       <c r="F195" s="1" t="n">
+        <v>0.02095</v>
+      </c>
+      <c r="G195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="G195" s="1" t="n">
+      <c r="H195" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -5334,9 +5922,12 @@
         <v>0.17221</v>
       </c>
       <c r="F196" s="1" t="n">
-        <v>0.17221</v>
+        <v>0.17484</v>
       </c>
       <c r="G196" s="1" t="n">
+        <v>0.17484</v>
+      </c>
+      <c r="H196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -5359,9 +5950,12 @@
         <v>0.007292</v>
       </c>
       <c r="F197" s="1" t="n">
+        <v>0.007358</v>
+      </c>
+      <c r="G197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="G197" s="1" t="n">
+      <c r="H197" s="1" t="n">
         <v>0.007292</v>
       </c>
     </row>
@@ -5384,9 +5978,12 @@
         <v>0.0191</v>
       </c>
       <c r="F198" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="G198" s="1" t="n">
         <v>0.0191</v>
       </c>
-      <c r="G198" s="1" t="n">
+      <c r="H198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -5409,9 +6006,12 @@
         <v>0.01631</v>
       </c>
       <c r="F199" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="G199" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="G199" s="1" t="n">
+      <c r="H199" s="1" t="n">
         <v>0.01631</v>
       </c>
     </row>
@@ -5434,10 +6034,13 @@
         <v>0.2975</v>
       </c>
       <c r="F200" s="1" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="G200" s="1" t="n">
         <v>0.2975</v>
       </c>
-      <c r="G200" s="1" t="n">
-        <v>0.2966</v>
+      <c r="H200" s="1" t="n">
+        <v>0.2965</v>
       </c>
     </row>
     <row r="201">
@@ -5459,9 +6062,12 @@
         <v>0.006223</v>
       </c>
       <c r="F201" s="1" t="n">
+        <v>0.006229</v>
+      </c>
+      <c r="G201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="G201" s="1" t="n">
+      <c r="H201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -5484,9 +6090,12 @@
         <v>0.0004461</v>
       </c>
       <c r="F202" s="1" t="n">
+        <v>0.0004451</v>
+      </c>
+      <c r="G202" s="1" t="n">
         <v>0.0004463</v>
       </c>
-      <c r="G202" s="1" t="n">
+      <c r="H202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -5509,9 +6118,12 @@
         <v>0.007375</v>
       </c>
       <c r="F203" s="1" t="n">
+        <v>0.007365</v>
+      </c>
+      <c r="G203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="G203" s="1" t="n">
+      <c r="H203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -5534,9 +6146,12 @@
         <v>0.1294</v>
       </c>
       <c r="F204" s="1" t="n">
-        <v>0.1294</v>
+        <v>0.1295</v>
       </c>
       <c r="G204" s="1" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="H204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -5559,9 +6174,12 @@
         <v>0.01451</v>
       </c>
       <c r="F205" s="1" t="n">
+        <v>0.01444</v>
+      </c>
+      <c r="G205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="G205" s="1" t="n">
+      <c r="H205" s="1" t="n">
         <v>0.01444</v>
       </c>
     </row>
@@ -5584,9 +6202,12 @@
         <v>0.003566</v>
       </c>
       <c r="F206" s="1" t="n">
+        <v>0.003583</v>
+      </c>
+      <c r="G206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="G206" s="1" t="n">
+      <c r="H206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -5609,9 +6230,12 @@
         <v>0.05999</v>
       </c>
       <c r="F207" s="1" t="n">
+        <v>0.05952</v>
+      </c>
+      <c r="G207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="G207" s="1" t="n">
+      <c r="H207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -5634,9 +6258,12 @@
         <v>15.45</v>
       </c>
       <c r="F208" s="1" t="n">
-        <v>15.45</v>
+        <v>15.47</v>
       </c>
       <c r="G208" s="1" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="H208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -5659,10 +6286,13 @@
         <v>5184.2</v>
       </c>
       <c r="F209" s="1" t="n">
+        <v>5183.4</v>
+      </c>
+      <c r="G209" s="1" t="n">
         <v>5186.2</v>
       </c>
-      <c r="G209" s="1" t="n">
-        <v>5184.2</v>
+      <c r="H209" s="1" t="n">
+        <v>5183.4</v>
       </c>
     </row>
     <row r="210">
@@ -5684,9 +6314,12 @@
         <v>0.12042</v>
       </c>
       <c r="F210" s="1" t="n">
+        <v>0.11988</v>
+      </c>
+      <c r="G210" s="1" t="n">
         <v>0.12042</v>
       </c>
-      <c r="G210" s="1" t="n">
+      <c r="H210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -5709,10 +6342,13 @@
         <v>0.1828</v>
       </c>
       <c r="F211" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="G211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="G211" s="1" t="n">
-        <v>0.1828</v>
+      <c r="H211" s="1" t="n">
+        <v>0.1824</v>
       </c>
     </row>
     <row r="212">
@@ -5737,6 +6373,9 @@
         <v>0.0303</v>
       </c>
       <c r="G212" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="H212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -5759,9 +6398,12 @@
         <v>1.3976</v>
       </c>
       <c r="F213" s="1" t="n">
+        <v>1.3968</v>
+      </c>
+      <c r="G213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="G213" s="1" t="n">
+      <c r="H213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -5784,9 +6426,12 @@
         <v>0.05662</v>
       </c>
       <c r="F214" s="1" t="n">
-        <v>0.05662</v>
+        <v>0.05664</v>
       </c>
       <c r="G214" s="1" t="n">
+        <v>0.05664</v>
+      </c>
+      <c r="H214" s="1" t="n">
         <v>0.05658</v>
       </c>
     </row>
@@ -5809,9 +6454,12 @@
         <v>0.04379</v>
       </c>
       <c r="F215" s="1" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="G215" s="1" t="n">
         <v>0.04385</v>
       </c>
-      <c r="G215" s="1" t="n">
+      <c r="H215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -5834,9 +6482,12 @@
         <v>0.15123</v>
       </c>
       <c r="F216" s="1" t="n">
-        <v>0.15123</v>
+        <v>0.1517</v>
       </c>
       <c r="G216" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="H216" s="1" t="n">
         <v>0.15102</v>
       </c>
     </row>
@@ -5859,9 +6510,12 @@
         <v>0.073</v>
       </c>
       <c r="F217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="G217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="G217" s="1" t="n">
+      <c r="H217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -5884,9 +6538,12 @@
         <v>0.00268</v>
       </c>
       <c r="F218" s="1" t="n">
-        <v>0.00268</v>
+        <v>0.00269</v>
       </c>
       <c r="G218" s="1" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="H218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -5909,10 +6566,13 @@
         <v>0.01719</v>
       </c>
       <c r="F219" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="G219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="G219" s="1" t="n">
-        <v>0.01716</v>
+      <c r="H219" s="1" t="n">
+        <v>0.01715</v>
       </c>
     </row>
     <row r="220">
@@ -5934,9 +6594,12 @@
         <v>0.05535</v>
       </c>
       <c r="F220" s="1" t="n">
+        <v>0.05531</v>
+      </c>
+      <c r="G220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="G220" s="1" t="n">
+      <c r="H220" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -5959,9 +6622,12 @@
         <v>0.02196</v>
       </c>
       <c r="F221" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="G221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="G221" s="1" t="n">
+      <c r="H221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -5984,10 +6650,13 @@
         <v>0.0094</v>
       </c>
       <c r="F222" s="1" t="n">
+        <v>0.009350000000000001</v>
+      </c>
+      <c r="G222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="G222" s="1" t="n">
-        <v>0.009379999999999999</v>
+      <c r="H222" s="1" t="n">
+        <v>0.009350000000000001</v>
       </c>
     </row>
     <row r="223">
@@ -6014,6 +6683,9 @@
       <c r="G223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="H223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6034,9 +6706,12 @@
         <v>0.03841</v>
       </c>
       <c r="F224" s="1" t="n">
+        <v>0.03826</v>
+      </c>
+      <c r="G224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="G224" s="1" t="n">
+      <c r="H224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -6059,9 +6734,12 @@
         <v>0.001529</v>
       </c>
       <c r="F225" s="1" t="n">
+        <v>0.001528</v>
+      </c>
+      <c r="G225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="G225" s="1" t="n">
+      <c r="H225" s="1" t="n">
         <v>0.001526</v>
       </c>
     </row>
@@ -6084,10 +6762,13 @@
         <v>27.05</v>
       </c>
       <c r="F226" s="1" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="G226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="G226" s="1" t="n">
-        <v>27.05</v>
+      <c r="H226" s="1" t="n">
+        <v>26.99</v>
       </c>
     </row>
     <row r="227">
@@ -6109,10 +6790,13 @@
         <v>0.07023</v>
       </c>
       <c r="F227" s="1" t="n">
+        <v>0.07015</v>
+      </c>
+      <c r="G227" s="1" t="n">
         <v>0.07027</v>
       </c>
-      <c r="G227" s="1" t="n">
-        <v>0.0702</v>
+      <c r="H227" s="1" t="n">
+        <v>0.07015</v>
       </c>
     </row>
     <row r="228">
@@ -6134,9 +6818,12 @@
         <v>0.313</v>
       </c>
       <c r="F228" s="1" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="G228" s="1" t="n">
+      <c r="H228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -6159,9 +6846,12 @@
         <v>18.46</v>
       </c>
       <c r="F229" s="1" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="G229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="G229" s="1" t="n">
+      <c r="H229" s="1" t="n">
         <v>18.42</v>
       </c>
     </row>
@@ -6184,10 +6874,13 @@
         <v>0.01939</v>
       </c>
       <c r="F230" s="1" t="n">
+        <v>0.01932</v>
+      </c>
+      <c r="G230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="G230" s="1" t="n">
-        <v>0.01939</v>
+      <c r="H230" s="1" t="n">
+        <v>0.01932</v>
       </c>
     </row>
     <row r="231">
@@ -6209,9 +6902,12 @@
         <v>0.01223</v>
       </c>
       <c r="F231" s="1" t="n">
+        <v>0.01221</v>
+      </c>
+      <c r="G231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="G231" s="1" t="n">
+      <c r="H231" s="1" t="n">
         <v>0.01221</v>
       </c>
     </row>
@@ -6234,9 +6930,12 @@
         <v>0.2288</v>
       </c>
       <c r="F232" s="1" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="G232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="G232" s="1" t="n">
+      <c r="H232" s="1" t="n">
         <v>0.2285</v>
       </c>
     </row>
@@ -6259,10 +6958,13 @@
         <v>0.07136000000000001</v>
       </c>
       <c r="F233" s="1" t="n">
+        <v>0.07101</v>
+      </c>
+      <c r="G233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="G233" s="1" t="n">
-        <v>0.07113999999999999</v>
+      <c r="H233" s="1" t="n">
+        <v>0.07101</v>
       </c>
     </row>
     <row r="234">
@@ -6284,9 +6986,12 @@
         <v>0.1701</v>
       </c>
       <c r="F234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="G234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="G234" s="1" t="n">
+      <c r="H234" s="1" t="n">
         <v>0.1701</v>
       </c>
     </row>
@@ -6312,6 +7017,9 @@
         <v>0.0253</v>
       </c>
       <c r="G235" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="H235" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -6334,10 +7042,13 @@
         <v>0.03007</v>
       </c>
       <c r="F236" s="1" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="G236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="G236" s="1" t="n">
-        <v>0.03006</v>
+      <c r="H236" s="1" t="n">
+        <v>0.03005</v>
       </c>
     </row>
     <row r="237">
@@ -6359,9 +7070,12 @@
         <v>1.993</v>
       </c>
       <c r="F237" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="G237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="G237" s="1" t="n">
+      <c r="H237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -6384,9 +7098,12 @@
         <v>0.4271</v>
       </c>
       <c r="F238" s="1" t="n">
-        <v>0.4295</v>
+        <v>0.4312</v>
       </c>
       <c r="G238" s="1" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="H238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -6409,10 +7126,13 @@
         <v>0.03363</v>
       </c>
       <c r="F239" s="1" t="n">
+        <v>0.03343</v>
+      </c>
+      <c r="G239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="G239" s="1" t="n">
-        <v>0.03363</v>
+      <c r="H239" s="1" t="n">
+        <v>0.03343</v>
       </c>
     </row>
     <row r="240">
@@ -6434,9 +7154,12 @@
         <v>0.03404</v>
       </c>
       <c r="F240" s="1" t="n">
-        <v>0.03408</v>
+        <v>0.0341</v>
       </c>
       <c r="G240" s="1" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="H240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -6459,9 +7182,12 @@
         <v>0.0007534</v>
       </c>
       <c r="F241" s="1" t="n">
+        <v>0.0007531</v>
+      </c>
+      <c r="G241" s="1" t="n">
         <v>0.0007551</v>
       </c>
-      <c r="G241" s="1" t="n">
+      <c r="H241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -6484,9 +7210,12 @@
         <v>0.1847</v>
       </c>
       <c r="F242" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="G242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="G242" s="1" t="n">
+      <c r="H242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -6509,10 +7238,13 @@
         <v>0.01482</v>
       </c>
       <c r="F243" s="1" t="n">
+        <v>0.014816</v>
+      </c>
+      <c r="G243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="G243" s="1" t="n">
-        <v>0.01482</v>
+      <c r="H243" s="1" t="n">
+        <v>0.014816</v>
       </c>
     </row>
     <row r="244">
@@ -6534,9 +7266,12 @@
         <v>3.08e-05</v>
       </c>
       <c r="F244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="G244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="G244" s="1" t="n">
+      <c r="H244" s="1" t="n">
         <v>3.08e-05</v>
       </c>
     </row>
@@ -6559,9 +7294,12 @@
         <v>0.03525</v>
       </c>
       <c r="F245" s="1" t="n">
+        <v>0.03526</v>
+      </c>
+      <c r="G245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="G245" s="1" t="n">
+      <c r="H245" s="1" t="n">
         <v>0.03521</v>
       </c>
     </row>
@@ -6584,9 +7322,12 @@
         <v>0.08076</v>
       </c>
       <c r="F246" s="1" t="n">
+        <v>0.08068</v>
+      </c>
+      <c r="G246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="G246" s="1" t="n">
+      <c r="H246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -6609,9 +7350,12 @@
         <v>0.00732</v>
       </c>
       <c r="F247" s="1" t="n">
+        <v>0.007347</v>
+      </c>
+      <c r="G247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="G247" s="1" t="n">
+      <c r="H247" s="1" t="n">
         <v>0.007318</v>
       </c>
     </row>
@@ -6634,10 +7378,13 @@
         <v>0.0977</v>
       </c>
       <c r="F248" s="1" t="n">
+        <v>0.09499</v>
+      </c>
+      <c r="G248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="G248" s="1" t="n">
-        <v>0.09717000000000001</v>
+      <c r="H248" s="1" t="n">
+        <v>0.09499</v>
       </c>
     </row>
     <row r="249">
@@ -6662,6 +7409,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="G249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="H249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -6684,9 +7434,12 @@
         <v>0.03521</v>
       </c>
       <c r="F250" s="1" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="G250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="G250" s="1" t="n">
+      <c r="H250" s="1" t="n">
         <v>0.03504</v>
       </c>
     </row>
@@ -6709,9 +7462,12 @@
         <v>0.04087</v>
       </c>
       <c r="F251" s="1" t="n">
+        <v>0.04078</v>
+      </c>
+      <c r="G251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="G251" s="1" t="n">
+      <c r="H251" s="1" t="n">
         <v>0.04058</v>
       </c>
     </row>
@@ -6737,6 +7493,9 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="G252" s="1" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="H252" s="1" t="n">
         <v>0.0891</v>
       </c>
     </row>
@@ -6759,9 +7518,12 @@
         <v>4.088</v>
       </c>
       <c r="F253" s="1" t="n">
-        <v>4.088</v>
+        <v>4.095</v>
       </c>
       <c r="G253" s="1" t="n">
+        <v>4.095</v>
+      </c>
+      <c r="H253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -6784,9 +7546,12 @@
         <v>0.1875</v>
       </c>
       <c r="F254" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="G254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="G254" s="1" t="n">
+      <c r="H254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -6809,9 +7574,12 @@
         <v>0.07273</v>
       </c>
       <c r="F255" s="1" t="n">
+        <v>0.07274</v>
+      </c>
+      <c r="G255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="G255" s="1" t="n">
+      <c r="H255" s="1" t="n">
         <v>0.07273</v>
       </c>
     </row>
@@ -6834,9 +7602,12 @@
         <v>0.01828</v>
       </c>
       <c r="F256" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="G256" s="1" t="n">
         <v>0.01828</v>
       </c>
-      <c r="G256" s="1" t="n">
+      <c r="H256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -6859,9 +7630,12 @@
         <v>5.957</v>
       </c>
       <c r="F257" s="1" t="n">
-        <v>5.957</v>
+        <v>5.962</v>
       </c>
       <c r="G257" s="1" t="n">
+        <v>5.962</v>
+      </c>
+      <c r="H257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -6884,9 +7658,12 @@
         <v>0.2636</v>
       </c>
       <c r="F258" s="1" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="G258" s="1" t="n">
         <v>0.2639</v>
       </c>
-      <c r="G258" s="1" t="n">
+      <c r="H258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -6909,9 +7686,12 @@
         <v>0.1369</v>
       </c>
       <c r="F259" s="1" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="G259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="G259" s="1" t="n">
+      <c r="H259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -6934,10 +7714,13 @@
         <v>0.30606</v>
       </c>
       <c r="F260" s="1" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="G260" s="1" t="n">
         <v>0.30606</v>
       </c>
-      <c r="G260" s="1" t="n">
-        <v>0.30537</v>
+      <c r="H260" s="1" t="n">
+        <v>0.30525</v>
       </c>
     </row>
     <row r="261">
@@ -6959,9 +7742,12 @@
         <v>0.09862</v>
       </c>
       <c r="F261" s="1" t="n">
+        <v>0.09858</v>
+      </c>
+      <c r="G261" s="1" t="n">
         <v>0.09862</v>
       </c>
-      <c r="G261" s="1" t="n">
+      <c r="H261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -6984,9 +7770,12 @@
         <v>0.5434</v>
       </c>
       <c r="F262" s="1" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="G262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="G262" s="1" t="n">
+      <c r="H262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -7009,9 +7798,12 @@
         <v>0.2928</v>
       </c>
       <c r="F263" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="G263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="G263" s="1" t="n">
+      <c r="H263" s="1" t="n">
         <v>0.2923</v>
       </c>
     </row>
@@ -7034,9 +7826,12 @@
         <v>0.953</v>
       </c>
       <c r="F264" s="1" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="G264" s="1" t="n">
         <v>0.953</v>
       </c>
-      <c r="G264" s="1" t="n">
+      <c r="H264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -7059,9 +7854,12 @@
         <v>0.5413</v>
       </c>
       <c r="F265" s="1" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="G265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="G265" s="1" t="n">
+      <c r="H265" s="1" t="n">
         <v>0.5405</v>
       </c>
     </row>
@@ -7087,6 +7885,9 @@
         <v>0.074</v>
       </c>
       <c r="G266" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -7109,9 +7910,12 @@
         <v>0.02151</v>
       </c>
       <c r="F267" s="1" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="G267" s="1" t="n">
         <v>0.02151</v>
       </c>
-      <c r="G267" s="1" t="n">
+      <c r="H267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -7134,9 +7938,12 @@
         <v>0.01609</v>
       </c>
       <c r="F268" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="G268" s="1" t="n">
         <v>0.01622</v>
       </c>
-      <c r="G268" s="1" t="n">
+      <c r="H268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -7159,10 +7966,13 @@
         <v>0.003709</v>
       </c>
       <c r="F269" s="1" t="n">
+        <v>0.003702</v>
+      </c>
+      <c r="G269" s="1" t="n">
         <v>0.003717</v>
       </c>
-      <c r="G269" s="1" t="n">
-        <v>0.003708</v>
+      <c r="H269" s="1" t="n">
+        <v>0.003702</v>
       </c>
     </row>
     <row r="270">
@@ -7184,9 +7994,12 @@
         <v>0.00769</v>
       </c>
       <c r="F270" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="G270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="G270" s="1" t="n">
+      <c r="H270" s="1" t="n">
         <v>0.00769</v>
       </c>
     </row>
@@ -7209,9 +8022,12 @@
         <v>0.05508</v>
       </c>
       <c r="F271" s="1" t="n">
+        <v>0.05502</v>
+      </c>
+      <c r="G271" s="1" t="n">
         <v>0.0551</v>
       </c>
-      <c r="G271" s="1" t="n">
+      <c r="H271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -7234,9 +8050,12 @@
         <v>2.311</v>
       </c>
       <c r="F272" s="1" t="n">
-        <v>2.311</v>
+        <v>2.317</v>
       </c>
       <c r="G272" s="1" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="H272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -7259,9 +8078,12 @@
         <v>0.0547</v>
       </c>
       <c r="F273" s="1" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="G273" s="1" t="n">
         <v>0.0547</v>
       </c>
-      <c r="G273" s="1" t="n">
+      <c r="H273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -7284,10 +8106,13 @@
         <v>0.02287</v>
       </c>
       <c r="F274" s="1" t="n">
+        <v>0.02283</v>
+      </c>
+      <c r="G274" s="1" t="n">
         <v>0.02291</v>
       </c>
-      <c r="G274" s="1" t="n">
-        <v>0.02286</v>
+      <c r="H274" s="1" t="n">
+        <v>0.02283</v>
       </c>
     </row>
     <row r="275">
@@ -7309,10 +8134,13 @@
         <v>1.189</v>
       </c>
       <c r="F275" s="1" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="G275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="G275" s="1" t="n">
-        <v>1.185</v>
+      <c r="H275" s="1" t="n">
+        <v>1.182</v>
       </c>
     </row>
     <row r="276">
@@ -7334,9 +8162,12 @@
         <v>0.2723</v>
       </c>
       <c r="F276" s="1" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="G276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="G276" s="1" t="n">
+      <c r="H276" s="1" t="n">
         <v>0.2723</v>
       </c>
     </row>
@@ -7359,10 +8190,13 @@
         <v>0.946</v>
       </c>
       <c r="F277" s="1" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="G277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="G277" s="1" t="n">
-        <v>0.946</v>
+      <c r="H277" s="1" t="n">
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="278">
@@ -7384,9 +8218,12 @@
         <v>0.6257</v>
       </c>
       <c r="F278" s="1" t="n">
-        <v>0.6257</v>
+        <v>0.6274</v>
       </c>
       <c r="G278" s="1" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="H278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -7409,9 +8246,12 @@
         <v>0.001362</v>
       </c>
       <c r="F279" s="1" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="G279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="G279" s="1" t="n">
+      <c r="H279" s="1" t="n">
         <v>0.00135</v>
       </c>
     </row>
@@ -7434,9 +8274,12 @@
         <v>0.005546</v>
       </c>
       <c r="F280" s="1" t="n">
+        <v>0.005551</v>
+      </c>
+      <c r="G280" s="1" t="n">
         <v>0.005553</v>
       </c>
-      <c r="G280" s="1" t="n">
+      <c r="H280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -7459,9 +8302,12 @@
         <v>1.526</v>
       </c>
       <c r="F281" s="1" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="G281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="G281" s="1" t="n">
+      <c r="H281" s="1" t="n">
         <v>1.522</v>
       </c>
     </row>
@@ -7484,10 +8330,13 @@
         <v>28.39</v>
       </c>
       <c r="F282" s="1" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="G282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="G282" s="1" t="n">
-        <v>28.36</v>
+      <c r="H282" s="1" t="n">
+        <v>28.32</v>
       </c>
     </row>
     <row r="283">
@@ -7509,10 +8358,13 @@
         <v>0.12935</v>
       </c>
       <c r="F283" s="1" t="n">
+        <v>0.12922</v>
+      </c>
+      <c r="G283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="G283" s="1" t="n">
-        <v>0.12935</v>
+      <c r="H283" s="1" t="n">
+        <v>0.12922</v>
       </c>
     </row>
     <row r="284">
@@ -7534,9 +8386,12 @@
         <v>0.01114</v>
       </c>
       <c r="F284" s="1" t="n">
-        <v>0.01114</v>
+        <v>0.01115</v>
       </c>
       <c r="G284" s="1" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="H284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -7559,9 +8414,12 @@
         <v>6.544</v>
       </c>
       <c r="F285" s="1" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="G285" s="1" t="n">
         <v>6.544</v>
       </c>
-      <c r="G285" s="1" t="n">
+      <c r="H285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -7584,9 +8442,12 @@
         <v>0.01857</v>
       </c>
       <c r="F286" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="G286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="G286" s="1" t="n">
+      <c r="H286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -7609,10 +8470,13 @@
         <v>0.008432</v>
       </c>
       <c r="F287" s="1" t="n">
+        <v>0.008404999999999999</v>
+      </c>
+      <c r="G287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="G287" s="1" t="n">
-        <v>0.008432</v>
+      <c r="H287" s="1" t="n">
+        <v>0.008404999999999999</v>
       </c>
     </row>
     <row r="288">
@@ -7634,9 +8498,12 @@
         <v>0.3879</v>
       </c>
       <c r="F288" s="1" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="G288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="G288" s="1" t="n">
+      <c r="H288" s="1" t="n">
         <v>0.3879</v>
       </c>
     </row>
@@ -7659,10 +8526,13 @@
         <v>0.010495</v>
       </c>
       <c r="F289" s="1" t="n">
+        <v>0.010267</v>
+      </c>
+      <c r="G289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="G289" s="1" t="n">
-        <v>0.010495</v>
+      <c r="H289" s="1" t="n">
+        <v>0.010267</v>
       </c>
     </row>
     <row r="290">
@@ -7684,9 +8554,12 @@
         <v>0.0262</v>
       </c>
       <c r="F290" s="1" t="n">
+        <v>0.02617</v>
+      </c>
+      <c r="G290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="G290" s="1" t="n">
+      <c r="H290" s="1" t="n">
         <v>0.02613</v>
       </c>
     </row>
@@ -7709,9 +8582,12 @@
         <v>0.097</v>
       </c>
       <c r="F291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="G291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="G291" s="1" t="n">
+      <c r="H291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -7734,10 +8610,13 @@
         <v>0.28601</v>
       </c>
       <c r="F292" s="1" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="G292" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="G292" s="1" t="n">
-        <v>0.28557</v>
+      <c r="H292" s="1" t="n">
+        <v>0.28497</v>
       </c>
     </row>
     <row r="293">
@@ -7759,9 +8638,12 @@
         <v>0.01542</v>
       </c>
       <c r="F293" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="G293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="G293" s="1" t="n">
+      <c r="H293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -7784,9 +8666,12 @@
         <v>0.003417</v>
       </c>
       <c r="F294" s="1" t="n">
-        <v>0.003417</v>
+        <v>0.00342</v>
       </c>
       <c r="G294" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="H294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -7809,10 +8694,13 @@
         <v>0.04368</v>
       </c>
       <c r="F295" s="1" t="n">
+        <v>0.043462</v>
+      </c>
+      <c r="G295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="G295" s="1" t="n">
-        <v>0.043493</v>
+      <c r="H295" s="1" t="n">
+        <v>0.043462</v>
       </c>
     </row>
     <row r="296">
@@ -7834,9 +8722,12 @@
         <v>0.02946</v>
       </c>
       <c r="F296" s="1" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="G296" s="1" t="n">
         <v>0.03007</v>
       </c>
-      <c r="G296" s="1" t="n">
+      <c r="H296" s="1" t="n">
         <v>0.02943</v>
       </c>
     </row>
@@ -7859,10 +8750,13 @@
         <v>0.03975</v>
       </c>
       <c r="F297" s="1" t="n">
+        <v>0.03857</v>
+      </c>
+      <c r="G297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="G297" s="1" t="n">
-        <v>0.03975</v>
+      <c r="H297" s="1" t="n">
+        <v>0.03857</v>
       </c>
     </row>
     <row r="298">
@@ -7884,10 +8778,13 @@
         <v>0.08334999999999999</v>
       </c>
       <c r="F298" s="1" t="n">
+        <v>0.08305999999999999</v>
+      </c>
+      <c r="G298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="G298" s="1" t="n">
-        <v>0.08326</v>
+      <c r="H298" s="1" t="n">
+        <v>0.08305999999999999</v>
       </c>
     </row>
     <row r="299">
@@ -7909,9 +8806,12 @@
         <v>0.00766</v>
       </c>
       <c r="F299" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="G299" s="1" t="n">
         <v>0.00766</v>
       </c>
-      <c r="G299" s="1" t="n">
+      <c r="H299" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -7934,9 +8834,12 @@
         <v>0.01528</v>
       </c>
       <c r="F300" s="1" t="n">
+        <v>0.01521</v>
+      </c>
+      <c r="G300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="G300" s="1" t="n">
+      <c r="H300" s="1" t="n">
         <v>0.01519</v>
       </c>
     </row>
@@ -7959,10 +8862,13 @@
         <v>0.1413</v>
       </c>
       <c r="F301" s="1" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="G301" s="1" t="n">
-        <v>0.1413</v>
+      <c r="H301" s="1" t="n">
+        <v>0.141</v>
       </c>
     </row>
     <row r="302">
@@ -7984,10 +8890,13 @@
         <v>0.000641</v>
       </c>
       <c r="F302" s="1" t="n">
+        <v>0.0006401</v>
+      </c>
+      <c r="G302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="G302" s="1" t="n">
-        <v>0.000641</v>
+      <c r="H302" s="1" t="n">
+        <v>0.0006401</v>
       </c>
     </row>
     <row r="303">
@@ -8009,9 +8918,12 @@
         <v>0.06234</v>
       </c>
       <c r="F303" s="1" t="n">
+        <v>0.06222</v>
+      </c>
+      <c r="G303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="G303" s="1" t="n">
+      <c r="H303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -8034,10 +8946,13 @@
         <v>0.0001632</v>
       </c>
       <c r="F304" s="1" t="n">
+        <v>0.0001626</v>
+      </c>
+      <c r="G304" s="1" t="n">
         <v>0.0001639</v>
       </c>
-      <c r="G304" s="1" t="n">
-        <v>0.0001632</v>
+      <c r="H304" s="1" t="n">
+        <v>0.0001626</v>
       </c>
     </row>
     <row r="305">
@@ -8059,9 +8974,12 @@
         <v>0.06134</v>
       </c>
       <c r="F305" s="1" t="n">
+        <v>0.06121</v>
+      </c>
+      <c r="G305" s="1" t="n">
         <v>0.06134</v>
       </c>
-      <c r="G305" s="1" t="n">
+      <c r="H305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -8084,10 +9002,13 @@
         <v>0.022332</v>
       </c>
       <c r="F306" s="1" t="n">
+        <v>0.022133</v>
+      </c>
+      <c r="G306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="G306" s="1" t="n">
-        <v>0.022332</v>
+      <c r="H306" s="1" t="n">
+        <v>0.022133</v>
       </c>
     </row>
     <row r="307">
@@ -8109,10 +9030,13 @@
         <v>0.02374</v>
       </c>
       <c r="F307" s="1" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="G307" s="1" t="n">
         <v>0.02414</v>
       </c>
-      <c r="G307" s="1" t="n">
-        <v>0.02367</v>
+      <c r="H307" s="1" t="n">
+        <v>0.02346</v>
       </c>
     </row>
     <row r="308">
@@ -8137,6 +9061,9 @@
         <v>0.000412</v>
       </c>
       <c r="G308" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="H308" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -8159,10 +9086,13 @@
         <v>0.0898</v>
       </c>
       <c r="F309" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="G309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="G309" s="1" t="n">
-        <v>0.0898</v>
+      <c r="H309" s="1" t="n">
+        <v>0.0897</v>
       </c>
     </row>
     <row r="310">
@@ -8184,9 +9114,12 @@
         <v>0.3836</v>
       </c>
       <c r="F310" s="1" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="G310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="G310" s="1" t="n">
+      <c r="H310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -8212,6 +9145,9 @@
         <v>0.0358</v>
       </c>
       <c r="G311" s="1" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="H311" s="1" t="n">
         <v>0.0357</v>
       </c>
     </row>
@@ -8234,9 +9170,12 @@
         <v>0.02471</v>
       </c>
       <c r="F312" s="1" t="n">
-        <v>0.02471</v>
+        <v>0.02485</v>
       </c>
       <c r="G312" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="H312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -8259,10 +9198,13 @@
         <v>0.04141</v>
       </c>
       <c r="F313" s="1" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="G313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="G313" s="1" t="n">
-        <v>0.04139</v>
+      <c r="H313" s="1" t="n">
+        <v>0.04134</v>
       </c>
     </row>
     <row r="314">
@@ -8284,9 +9226,12 @@
         <v>4.007</v>
       </c>
       <c r="F314" s="1" t="n">
+        <v>4.014</v>
+      </c>
+      <c r="G314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="G314" s="1" t="n">
+      <c r="H314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -8309,9 +9254,12 @@
         <v>0.1602</v>
       </c>
       <c r="F315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="G315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="G315" s="1" t="n">
+      <c r="H315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -8334,9 +9282,12 @@
         <v>0.08805</v>
       </c>
       <c r="F316" s="1" t="n">
+        <v>0.08834</v>
+      </c>
+      <c r="G316" s="1" t="n">
         <v>0.08852</v>
       </c>
-      <c r="G316" s="1" t="n">
+      <c r="H316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -8359,9 +9310,12 @@
         <v>0.06827</v>
       </c>
       <c r="F317" s="1" t="n">
-        <v>0.06827999999999999</v>
+        <v>0.06837</v>
       </c>
       <c r="G317" s="1" t="n">
+        <v>0.06837</v>
+      </c>
+      <c r="H317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -8384,10 +9338,13 @@
         <v>0.012664</v>
       </c>
       <c r="F318" s="1" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="G318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="G318" s="1" t="n">
-        <v>0.012643</v>
+      <c r="H318" s="1" t="n">
+        <v>0.01261</v>
       </c>
     </row>
     <row r="319">
@@ -8409,9 +9366,12 @@
         <v>0.001138</v>
       </c>
       <c r="F319" s="1" t="n">
+        <v>0.001136</v>
+      </c>
+      <c r="G319" s="1" t="n">
         <v>0.001138</v>
       </c>
-      <c r="G319" s="1" t="n">
+      <c r="H319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -8434,9 +9394,12 @@
         <v>0.0633</v>
       </c>
       <c r="F320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="G320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="G320" s="1" t="n">
+      <c r="H320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -8459,9 +9422,12 @@
         <v>0.00525</v>
       </c>
       <c r="F321" s="1" t="n">
-        <v>0.00525</v>
+        <v>0.00526</v>
       </c>
       <c r="G321" s="1" t="n">
+        <v>0.00526</v>
+      </c>
+      <c r="H321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -8484,9 +9450,12 @@
         <v>0.1116</v>
       </c>
       <c r="F322" s="1" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="G322" s="1" t="n">
         <v>0.1116</v>
       </c>
-      <c r="G322" s="1" t="n">
+      <c r="H322" s="1" t="n">
         <v>0.1114</v>
       </c>
     </row>
@@ -8509,9 +9478,12 @@
         <v>0.04239</v>
       </c>
       <c r="F323" s="1" t="n">
-        <v>0.04246</v>
+        <v>0.04266</v>
       </c>
       <c r="G323" s="1" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="H323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -8534,9 +9506,12 @@
         <v>0.0178</v>
       </c>
       <c r="F324" s="1" t="n">
-        <v>0.0178</v>
+        <v>0.0179</v>
       </c>
       <c r="G324" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -8559,9 +9534,12 @@
         <v>0.005689</v>
       </c>
       <c r="F325" s="1" t="n">
+        <v>0.005693</v>
+      </c>
+      <c r="G325" s="1" t="n">
         <v>0.005695</v>
       </c>
-      <c r="G325" s="1" t="n">
+      <c r="H325" s="1" t="n">
         <v>0.005689</v>
       </c>
     </row>
@@ -8584,10 +9562,13 @@
         <v>0.001768</v>
       </c>
       <c r="F326" s="1" t="n">
+        <v>0.001765</v>
+      </c>
+      <c r="G326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="G326" s="1" t="n">
-        <v>0.001767</v>
+      <c r="H326" s="1" t="n">
+        <v>0.001765</v>
       </c>
     </row>
     <row r="327">
@@ -8609,10 +9590,13 @@
         <v>0.04082</v>
       </c>
       <c r="F327" s="1" t="n">
+        <v>0.04071</v>
+      </c>
+      <c r="G327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="G327" s="1" t="n">
-        <v>0.04076</v>
+      <c r="H327" s="1" t="n">
+        <v>0.04071</v>
       </c>
     </row>
     <row r="328">
@@ -8634,9 +9618,12 @@
         <v>0.054032</v>
       </c>
       <c r="F328" s="1" t="n">
+        <v>0.05398</v>
+      </c>
+      <c r="G328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="G328" s="1" t="n">
+      <c r="H328" s="1" t="n">
         <v>0.05395</v>
       </c>
     </row>
@@ -8659,9 +9646,12 @@
         <v>0.2795</v>
       </c>
       <c r="F329" s="1" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="G329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="G329" s="1" t="n">
+      <c r="H329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -8684,9 +9674,12 @@
         <v>0.16</v>
       </c>
       <c r="F330" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="G330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="G330" s="1" t="n">
+      <c r="H330" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -8709,9 +9702,12 @@
         <v>0.05354</v>
       </c>
       <c r="F331" s="1" t="n">
-        <v>0.05356</v>
+        <v>0.05358</v>
       </c>
       <c r="G331" s="1" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="H331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -8734,9 +9730,12 @@
         <v>0.361</v>
       </c>
       <c r="F332" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="G332" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="G332" s="1" t="n">
+      <c r="H332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -8759,9 +9758,12 @@
         <v>0.03048</v>
       </c>
       <c r="F333" s="1" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="G333" s="1" t="n">
         <v>0.03048</v>
       </c>
-      <c r="G333" s="1" t="n">
+      <c r="H333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -8784,9 +9786,12 @@
         <v>0.01832</v>
       </c>
       <c r="F334" s="1" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="G334" s="1" t="n">
         <v>0.01832</v>
       </c>
-      <c r="G334" s="1" t="n">
+      <c r="H334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -8809,9 +9814,12 @@
         <v>0.0581</v>
       </c>
       <c r="F335" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="G335" s="1" t="n">
         <v>0.0581</v>
       </c>
-      <c r="G335" s="1" t="n">
+      <c r="H335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -8834,9 +9842,12 @@
         <v>0.0915</v>
       </c>
       <c r="F336" s="1" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="G336" s="1" t="n">
         <v>0.09182</v>
       </c>
-      <c r="G336" s="1" t="n">
+      <c r="H336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -8859,9 +9870,12 @@
         <v>0.1777</v>
       </c>
       <c r="F337" s="1" t="n">
+        <v>0.17762</v>
+      </c>
+      <c r="G337" s="1" t="n">
         <v>0.1777</v>
       </c>
-      <c r="G337" s="1" t="n">
+      <c r="H337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -8884,10 +9898,13 @@
         <v>0.0212</v>
       </c>
       <c r="F338" s="1" t="n">
+        <v>0.02111</v>
+      </c>
+      <c r="G338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="G338" s="1" t="n">
-        <v>0.0212</v>
+      <c r="H338" s="1" t="n">
+        <v>0.02111</v>
       </c>
     </row>
     <row r="339">
@@ -8909,9 +9926,12 @@
         <v>0.1313</v>
       </c>
       <c r="F339" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="G339" s="1" t="n">
         <v>0.1315</v>
       </c>
-      <c r="G339" s="1" t="n">
+      <c r="H339" s="1" t="n">
         <v>0.1313</v>
       </c>
     </row>
@@ -8934,10 +9954,13 @@
         <v>0.008014</v>
       </c>
       <c r="F340" s="1" t="n">
+        <v>0.008005999999999999</v>
+      </c>
+      <c r="G340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="G340" s="1" t="n">
-        <v>0.008014</v>
+      <c r="H340" s="1" t="n">
+        <v>0.008005999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -8959,9 +9982,12 @@
         <v>4.403</v>
       </c>
       <c r="F341" s="1" t="n">
+        <v>4.399</v>
+      </c>
+      <c r="G341" s="1" t="n">
         <v>4.403</v>
       </c>
-      <c r="G341" s="1" t="n">
+      <c r="H341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -8984,9 +10010,12 @@
         <v>0.19423</v>
       </c>
       <c r="F342" s="1" t="n">
+        <v>0.19466</v>
+      </c>
+      <c r="G342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="G342" s="1" t="n">
+      <c r="H342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -9009,9 +10038,12 @@
         <v>0.08316999999999999</v>
       </c>
       <c r="F343" s="1" t="n">
+        <v>0.08321000000000001</v>
+      </c>
+      <c r="G343" s="1" t="n">
         <v>0.08325</v>
       </c>
-      <c r="G343" s="1" t="n">
+      <c r="H343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -9034,9 +10066,12 @@
         <v>0.1835</v>
       </c>
       <c r="F344" s="1" t="n">
-        <v>0.1835</v>
+        <v>0.1842</v>
       </c>
       <c r="G344" s="1" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="H344" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -9059,9 +10094,12 @@
         <v>0.003265</v>
       </c>
       <c r="F345" s="1" t="n">
+        <v>0.003256</v>
+      </c>
+      <c r="G345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="G345" s="1" t="n">
+      <c r="H345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -9084,9 +10122,12 @@
         <v>0.09121</v>
       </c>
       <c r="F346" s="1" t="n">
-        <v>0.09121</v>
+        <v>0.09168999999999999</v>
       </c>
       <c r="G346" s="1" t="n">
+        <v>0.09168999999999999</v>
+      </c>
+      <c r="H346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -9109,9 +10150,12 @@
         <v>2.26</v>
       </c>
       <c r="F347" s="1" t="n">
+        <v>2.254</v>
+      </c>
+      <c r="G347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="G347" s="1" t="n">
+      <c r="H347" s="1" t="n">
         <v>2.254</v>
       </c>
     </row>
@@ -9134,9 +10178,12 @@
         <v>0.3049</v>
       </c>
       <c r="F348" s="1" t="n">
-        <v>0.3049</v>
+        <v>0.3054</v>
       </c>
       <c r="G348" s="1" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="H348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -9159,10 +10206,13 @@
         <v>0.02983</v>
       </c>
       <c r="F349" s="1" t="n">
+        <v>0.02981</v>
+      </c>
+      <c r="G349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="G349" s="1" t="n">
-        <v>0.02982</v>
+      <c r="H349" s="1" t="n">
+        <v>0.02981</v>
       </c>
     </row>
     <row r="350">
@@ -9184,9 +10234,12 @@
         <v>0.128</v>
       </c>
       <c r="F350" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="G350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="G350" s="1" t="n">
+      <c r="H350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -9209,9 +10262,12 @@
         <v>0.06804</v>
       </c>
       <c r="F351" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="G351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="G351" s="1" t="n">
+      <c r="H351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -9234,9 +10290,12 @@
         <v>0.06247</v>
       </c>
       <c r="F352" s="1" t="n">
+        <v>0.06244</v>
+      </c>
+      <c r="G352" s="1" t="n">
         <v>0.06251</v>
       </c>
-      <c r="G352" s="1" t="n">
+      <c r="H352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -9259,10 +10318,13 @@
         <v>0.06388000000000001</v>
       </c>
       <c r="F353" s="1" t="n">
+        <v>0.06371</v>
+      </c>
+      <c r="G353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="G353" s="1" t="n">
-        <v>0.06375</v>
+      <c r="H353" s="1" t="n">
+        <v>0.06371</v>
       </c>
     </row>
     <row r="354">
@@ -9284,9 +10346,12 @@
         <v>0.10569</v>
       </c>
       <c r="F354" s="1" t="n">
+        <v>0.10451</v>
+      </c>
+      <c r="G354" s="1" t="n">
         <v>0.10569</v>
       </c>
-      <c r="G354" s="1" t="n">
+      <c r="H354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -9309,9 +10374,12 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="F355" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="G355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="G355" s="1" t="n">
+      <c r="H355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -9334,9 +10402,12 @@
         <v>0.06988</v>
       </c>
       <c r="F356" s="1" t="n">
+        <v>0.07003</v>
+      </c>
+      <c r="G356" s="1" t="n">
         <v>0.07054000000000001</v>
       </c>
-      <c r="G356" s="1" t="n">
+      <c r="H356" s="1" t="n">
         <v>0.06988</v>
       </c>
     </row>
@@ -9359,9 +10430,12 @@
         <v>0.4535</v>
       </c>
       <c r="F357" s="1" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="G357" s="1" t="n">
         <v>0.4541</v>
       </c>
-      <c r="G357" s="1" t="n">
+      <c r="H357" s="1" t="n">
         <v>0.4523</v>
       </c>
     </row>
@@ -9384,9 +10458,12 @@
         <v>0.03467</v>
       </c>
       <c r="F358" s="1" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="G358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="G358" s="1" t="n">
+      <c r="H358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -9409,9 +10486,12 @@
         <v>0.01482</v>
       </c>
       <c r="F359" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="G359" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="G359" s="1" t="n">
+      <c r="H359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -9434,9 +10514,12 @@
         <v>0.13282</v>
       </c>
       <c r="F360" s="1" t="n">
+        <v>0.13305</v>
+      </c>
+      <c r="G360" s="1" t="n">
         <v>0.13306</v>
       </c>
-      <c r="G360" s="1" t="n">
+      <c r="H360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -9459,9 +10542,12 @@
         <v>0.0005885</v>
       </c>
       <c r="F361" s="1" t="n">
+        <v>0.0005883</v>
+      </c>
+      <c r="G361" s="1" t="n">
         <v>0.0005885</v>
       </c>
-      <c r="G361" s="1" t="n">
+      <c r="H361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -9484,9 +10570,12 @@
         <v>0.0386</v>
       </c>
       <c r="F362" s="1" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="G362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="G362" s="1" t="n">
+      <c r="H362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -9509,10 +10598,13 @@
         <v>3.214</v>
       </c>
       <c r="F363" s="1" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="G363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="G363" s="1" t="n">
-        <v>3.208</v>
+      <c r="H363" s="1" t="n">
+        <v>3.207</v>
       </c>
     </row>
     <row r="364">
@@ -9534,10 +10626,13 @@
         <v>0.1664</v>
       </c>
       <c r="F364" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="G364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="G364" s="1" t="n">
-        <v>0.1657</v>
+      <c r="H364" s="1" t="n">
+        <v>0.1656</v>
       </c>
     </row>
     <row r="365">
@@ -9559,9 +10654,12 @@
         <v>0.1134</v>
       </c>
       <c r="F365" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="G365" s="1" t="n">
         <v>0.1135</v>
       </c>
-      <c r="G365" s="1" t="n">
+      <c r="H365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -9584,9 +10682,12 @@
         <v>0.0006437</v>
       </c>
       <c r="F366" s="1" t="n">
-        <v>0.0006438</v>
+        <v>0.0006445</v>
       </c>
       <c r="G366" s="1" t="n">
+        <v>0.0006445</v>
+      </c>
+      <c r="H366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -9609,9 +10710,12 @@
         <v>0.05998</v>
       </c>
       <c r="F367" s="1" t="n">
+        <v>0.05982</v>
+      </c>
+      <c r="G367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="G367" s="1" t="n">
+      <c r="H367" s="1" t="n">
         <v>0.05956</v>
       </c>
     </row>
@@ -9634,9 +10738,12 @@
         <v>0.08323</v>
       </c>
       <c r="F368" s="1" t="n">
-        <v>0.08323</v>
+        <v>0.08345</v>
       </c>
       <c r="G368" s="1" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="H368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -9659,9 +10766,12 @@
         <v>0.03997</v>
       </c>
       <c r="F369" s="1" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="G369" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="G369" s="1" t="n">
+      <c r="H369" s="1" t="n">
         <v>0.03979</v>
       </c>
     </row>
@@ -9684,9 +10794,12 @@
         <v>3.723</v>
       </c>
       <c r="F370" s="1" t="n">
+        <v>3.722</v>
+      </c>
+      <c r="G370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="G370" s="1" t="n">
+      <c r="H370" s="1" t="n">
         <v>3.709</v>
       </c>
     </row>
@@ -9709,10 +10822,13 @@
         <v>0.123</v>
       </c>
       <c r="F371" s="1" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="G371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="G371" s="1" t="n">
-        <v>0.1226</v>
+      <c r="H371" s="1" t="n">
+        <v>0.1222</v>
       </c>
     </row>
     <row r="372">
@@ -9734,9 +10850,12 @@
         <v>0.01473</v>
       </c>
       <c r="F372" s="1" t="n">
-        <v>0.01474</v>
+        <v>0.01479</v>
       </c>
       <c r="G372" s="1" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="H372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -9759,10 +10878,13 @@
         <v>0.02196</v>
       </c>
       <c r="F373" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="G373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="G373" s="1" t="n">
-        <v>0.02196</v>
+      <c r="H373" s="1" t="n">
+        <v>0.02192</v>
       </c>
     </row>
     <row r="374">
@@ -9784,9 +10906,12 @@
         <v>1.8566</v>
       </c>
       <c r="F374" s="1" t="n">
+        <v>1.8579</v>
+      </c>
+      <c r="G374" s="1" t="n">
         <v>1.8584</v>
       </c>
-      <c r="G374" s="1" t="n">
+      <c r="H374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -9809,9 +10934,12 @@
         <v>0.02108</v>
       </c>
       <c r="F375" s="1" t="n">
+        <v>0.02104</v>
+      </c>
+      <c r="G375" s="1" t="n">
         <v>0.02108</v>
       </c>
-      <c r="G375" s="1" t="n">
+      <c r="H375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -9834,9 +10962,12 @@
         <v>1.294</v>
       </c>
       <c r="F376" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="G376" s="1" t="n">
         <v>1.301</v>
       </c>
-      <c r="G376" s="1" t="n">
+      <c r="H376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -9859,9 +10990,12 @@
         <v>0.2841</v>
       </c>
       <c r="F377" s="1" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="G377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="G377" s="1" t="n">
+      <c r="H377" s="1" t="n">
         <v>0.2837</v>
       </c>
     </row>
@@ -9884,10 +11018,13 @@
         <v>0.01561</v>
       </c>
       <c r="F378" s="1" t="n">
+        <v>0.01558</v>
+      </c>
+      <c r="G378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="G378" s="1" t="n">
-        <v>0.01561</v>
+      <c r="H378" s="1" t="n">
+        <v>0.01558</v>
       </c>
     </row>
     <row r="379">
@@ -9909,9 +11046,12 @@
         <v>1.5291</v>
       </c>
       <c r="F379" s="1" t="n">
-        <v>1.5349</v>
+        <v>1.5387</v>
       </c>
       <c r="G379" s="1" t="n">
+        <v>1.5387</v>
+      </c>
+      <c r="H379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -9934,10 +11074,13 @@
         <v>6.969000000000001e-05</v>
       </c>
       <c r="F380" s="1" t="n">
+        <v>6.955e-05</v>
+      </c>
+      <c r="G380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="G380" s="1" t="n">
-        <v>6.962e-05</v>
+      <c r="H380" s="1" t="n">
+        <v>6.955e-05</v>
       </c>
     </row>
     <row r="381">
@@ -9959,9 +11102,12 @@
         <v>2.552</v>
       </c>
       <c r="F381" s="1" t="n">
+        <v>2.552</v>
+      </c>
+      <c r="G381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="G381" s="1" t="n">
+      <c r="H381" s="1" t="n">
         <v>2.551</v>
       </c>
     </row>
@@ -9984,9 +11130,12 @@
         <v>0.06738</v>
       </c>
       <c r="F382" s="1" t="n">
+        <v>0.06752</v>
+      </c>
+      <c r="G382" s="1" t="n">
         <v>0.06753000000000001</v>
       </c>
-      <c r="G382" s="1" t="n">
+      <c r="H382" s="1" t="n">
         <v>0.06738</v>
       </c>
     </row>
@@ -10009,9 +11158,12 @@
         <v>0.01713</v>
       </c>
       <c r="F383" s="1" t="n">
+        <v>0.01723</v>
+      </c>
+      <c r="G383" s="1" t="n">
         <v>0.01758</v>
       </c>
-      <c r="G383" s="1" t="n">
+      <c r="H383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -10034,9 +11186,12 @@
         <v>0.05068</v>
       </c>
       <c r="F384" s="1" t="n">
-        <v>0.05068</v>
+        <v>0.05086</v>
       </c>
       <c r="G384" s="1" t="n">
+        <v>0.05086</v>
+      </c>
+      <c r="H384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -10059,9 +11214,12 @@
         <v>7.585</v>
       </c>
       <c r="F385" s="1" t="n">
+        <v>7.577</v>
+      </c>
+      <c r="G385" s="1" t="n">
         <v>7.585</v>
       </c>
-      <c r="G385" s="1" t="n">
+      <c r="H385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -10084,9 +11242,12 @@
         <v>0.003295</v>
       </c>
       <c r="F386" s="1" t="n">
+        <v>0.003289</v>
+      </c>
+      <c r="G386" s="1" t="n">
         <v>0.003299</v>
       </c>
-      <c r="G386" s="1" t="n">
+      <c r="H386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -10109,9 +11270,12 @@
         <v>0.0003846</v>
       </c>
       <c r="F387" s="1" t="n">
+        <v>0.0003845</v>
+      </c>
+      <c r="G387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="G387" s="1" t="n">
+      <c r="H387" s="1" t="n">
         <v>0.0003838</v>
       </c>
     </row>
@@ -10134,10 +11298,13 @@
         <v>0.00967</v>
       </c>
       <c r="F388" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="G388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="G388" s="1" t="n">
-        <v>0.00967</v>
+      <c r="H388" s="1" t="n">
+        <v>0.00966</v>
       </c>
     </row>
     <row r="389">
@@ -10159,10 +11326,13 @@
         <v>0.2883</v>
       </c>
       <c r="F389" s="1" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="G389" s="1" t="n">
         <v>0.2891</v>
       </c>
-      <c r="G389" s="1" t="n">
-        <v>0.2883</v>
+      <c r="H389" s="1" t="n">
+        <v>0.288</v>
       </c>
     </row>
     <row r="390">
@@ -10184,9 +11354,12 @@
         <v>0.025</v>
       </c>
       <c r="F390" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="G390" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="G390" s="1" t="n">
+      <c r="H390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -10209,9 +11382,12 @@
         <v>2.829</v>
       </c>
       <c r="F391" s="1" t="n">
-        <v>2.829</v>
+        <v>2.832</v>
       </c>
       <c r="G391" s="1" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="H391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -10234,10 +11410,13 @@
         <v>0.01351</v>
       </c>
       <c r="F392" s="1" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="G392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="G392" s="1" t="n">
-        <v>0.01343</v>
+      <c r="H392" s="1" t="n">
+        <v>0.0134</v>
       </c>
     </row>
     <row r="393">
@@ -10262,6 +11441,9 @@
         <v>0.00236</v>
       </c>
       <c r="G393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="H393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -10284,9 +11466,12 @@
         <v>0.05946</v>
       </c>
       <c r="F394" s="1" t="n">
+        <v>0.05941</v>
+      </c>
+      <c r="G394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="G394" s="1" t="n">
+      <c r="H394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -10314,6 +11499,9 @@
       <c r="G395" s="1" t="n">
         <v>0.0405</v>
       </c>
+      <c r="H395" s="1" t="n">
+        <v>0.0405</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -10334,9 +11522,12 @@
         <v>0.09117</v>
       </c>
       <c r="F396" s="1" t="n">
-        <v>0.09134</v>
+        <v>0.09188</v>
       </c>
       <c r="G396" s="1" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="H396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -10359,9 +11550,12 @@
         <v>0.1522</v>
       </c>
       <c r="F397" s="1" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="G397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="G397" s="1" t="n">
+      <c r="H397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -10387,6 +11581,9 @@
         <v>0.929</v>
       </c>
       <c r="G398" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="H398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -10409,9 +11606,12 @@
         <v>0.0525</v>
       </c>
       <c r="F399" s="1" t="n">
+        <v>0.05245</v>
+      </c>
+      <c r="G399" s="1" t="n">
         <v>0.0525</v>
       </c>
-      <c r="G399" s="1" t="n">
+      <c r="H399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -10434,9 +11634,12 @@
         <v>2.525</v>
       </c>
       <c r="F400" s="1" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G400" s="1" t="n">
         <v>2.525</v>
       </c>
-      <c r="G400" s="1" t="n">
+      <c r="H400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -10459,9 +11662,12 @@
         <v>0.01819</v>
       </c>
       <c r="F401" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="G401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="G401" s="1" t="n">
+      <c r="H401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -10484,9 +11690,12 @@
         <v>0.08097</v>
       </c>
       <c r="F402" s="1" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="G402" s="1" t="n">
         <v>0.08097</v>
       </c>
-      <c r="G402" s="1" t="n">
+      <c r="H402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -10509,9 +11718,12 @@
         <v>1.2526</v>
       </c>
       <c r="F403" s="1" t="n">
+        <v>1.2512</v>
+      </c>
+      <c r="G403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="G403" s="1" t="n">
+      <c r="H403" s="1" t="n">
         <v>1.2484</v>
       </c>
     </row>
@@ -10537,6 +11749,9 @@
         <v>0.00719</v>
       </c>
       <c r="G404" s="1" t="n">
+        <v>0.00719</v>
+      </c>
+      <c r="H404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -10559,10 +11774,13 @@
         <v>0.4945</v>
       </c>
       <c r="F405" s="1" t="n">
+        <v>0.4934</v>
+      </c>
+      <c r="G405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="G405" s="1" t="n">
-        <v>0.4945</v>
+      <c r="H405" s="1" t="n">
+        <v>0.4934</v>
       </c>
     </row>
     <row r="406">
@@ -10584,9 +11802,12 @@
         <v>0.01151</v>
       </c>
       <c r="F406" s="1" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="G406" s="1" t="n">
         <v>0.01151</v>
       </c>
-      <c r="G406" s="1" t="n">
+      <c r="H406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -10609,10 +11830,13 @@
         <v>0.04647</v>
       </c>
       <c r="F407" s="1" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="G407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="G407" s="1" t="n">
-        <v>0.0464</v>
+      <c r="H407" s="1" t="n">
+        <v>0.04639</v>
       </c>
     </row>
     <row r="408">
@@ -10634,9 +11858,12 @@
         <v>0.03964</v>
       </c>
       <c r="F408" s="1" t="n">
+        <v>0.03958</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="G408" s="1" t="n">
+      <c r="H408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -10659,10 +11886,13 @@
         <v>0.05274</v>
       </c>
       <c r="F409" s="1" t="n">
+        <v>0.05262</v>
+      </c>
+      <c r="G409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="G409" s="1" t="n">
-        <v>0.05274</v>
+      <c r="H409" s="1" t="n">
+        <v>0.05262</v>
       </c>
     </row>
     <row r="410">
@@ -10684,9 +11914,12 @@
         <v>0.01256</v>
       </c>
       <c r="F410" s="1" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="G410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="G410" s="1" t="n">
+      <c r="H410" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -10709,9 +11942,12 @@
         <v>0.06399000000000001</v>
       </c>
       <c r="F411" s="1" t="n">
+        <v>0.06396</v>
+      </c>
+      <c r="G411" s="1" t="n">
         <v>0.06401</v>
       </c>
-      <c r="G411" s="1" t="n">
+      <c r="H411" s="1" t="n">
         <v>0.06378</v>
       </c>
     </row>
@@ -10734,10 +11970,13 @@
         <v>0.04141</v>
       </c>
       <c r="F412" s="1" t="n">
+        <v>0.04126</v>
+      </c>
+      <c r="G412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="G412" s="1" t="n">
-        <v>0.0414</v>
+      <c r="H412" s="1" t="n">
+        <v>0.04126</v>
       </c>
     </row>
     <row r="413">
@@ -10759,9 +11998,12 @@
         <v>1.122</v>
       </c>
       <c r="F413" s="1" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="G413" s="1" t="n">
         <v>1.122</v>
       </c>
-      <c r="G413" s="1" t="n">
+      <c r="H413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -10784,10 +12026,13 @@
         <v>0.2642</v>
       </c>
       <c r="F414" s="1" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="G414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="G414" s="1" t="n">
-        <v>0.2637</v>
+      <c r="H414" s="1" t="n">
+        <v>0.2633</v>
       </c>
     </row>
     <row r="415">
@@ -10809,9 +12054,12 @@
         <v>0.001261</v>
       </c>
       <c r="F415" s="1" t="n">
+        <v>0.001238</v>
+      </c>
+      <c r="G415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="G415" s="1" t="n">
+      <c r="H415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -10834,10 +12082,13 @@
         <v>0.03182</v>
       </c>
       <c r="F416" s="1" t="n">
+        <v>0.03175</v>
+      </c>
+      <c r="G416" s="1" t="n">
         <v>0.03196</v>
       </c>
-      <c r="G416" s="1" t="n">
-        <v>0.03179</v>
+      <c r="H416" s="1" t="n">
+        <v>0.03175</v>
       </c>
     </row>
     <row r="417">
@@ -10859,9 +12110,12 @@
         <v>0.01462</v>
       </c>
       <c r="F417" s="1" t="n">
+        <v>0.01464</v>
+      </c>
+      <c r="G417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="G417" s="1" t="n">
+      <c r="H417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -10884,9 +12138,12 @@
         <v>0.1481</v>
       </c>
       <c r="F418" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="G418" s="1" t="n">
         <v>0.1482</v>
       </c>
-      <c r="G418" s="1" t="n">
+      <c r="H418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -10909,9 +12166,12 @@
         <v>0.04887</v>
       </c>
       <c r="F419" s="1" t="n">
-        <v>0.04887</v>
+        <v>0.04894</v>
       </c>
       <c r="G419" s="1" t="n">
+        <v>0.04894</v>
+      </c>
+      <c r="H419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -10934,9 +12194,12 @@
         <v>66.38</v>
       </c>
       <c r="F420" s="1" t="n">
-        <v>66.38</v>
+        <v>66.7</v>
       </c>
       <c r="G420" s="1" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -10959,9 +12222,12 @@
         <v>0.878</v>
       </c>
       <c r="F421" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="G421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="G421" s="1" t="n">
+      <c r="H421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -10984,10 +12250,13 @@
         <v>0.012896</v>
       </c>
       <c r="F422" s="1" t="n">
+        <v>0.012813</v>
+      </c>
+      <c r="G422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="G422" s="1" t="n">
-        <v>0.012896</v>
+      <c r="H422" s="1" t="n">
+        <v>0.012813</v>
       </c>
     </row>
     <row r="423">
@@ -11009,9 +12278,12 @@
         <v>0.01599</v>
       </c>
       <c r="F423" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="G423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="G423" s="1" t="n">
+      <c r="H423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -11034,9 +12306,12 @@
         <v>0.26551</v>
       </c>
       <c r="F424" s="1" t="n">
-        <v>0.26551</v>
+        <v>0.26855</v>
       </c>
       <c r="G424" s="1" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="H424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -11059,9 +12334,12 @@
         <v>0.6018</v>
       </c>
       <c r="F425" s="1" t="n">
-        <v>0.6018</v>
+        <v>0.6019</v>
       </c>
       <c r="G425" s="1" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="H425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -11084,10 +12362,13 @@
         <v>0.005596</v>
       </c>
       <c r="F426" s="1" t="n">
+        <v>0.005577</v>
+      </c>
+      <c r="G426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="G426" s="1" t="n">
-        <v>0.005596</v>
+      <c r="H426" s="1" t="n">
+        <v>0.005577</v>
       </c>
     </row>
     <row r="427">
@@ -11109,9 +12390,12 @@
         <v>0.0489</v>
       </c>
       <c r="F427" s="1" t="n">
+        <v>0.04902</v>
+      </c>
+      <c r="G427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="G427" s="1" t="n">
+      <c r="H427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -11134,9 +12418,12 @@
         <v>0.1261</v>
       </c>
       <c r="F428" s="1" t="n">
-        <v>0.1261</v>
+        <v>0.1264</v>
       </c>
       <c r="G428" s="1" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="H428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -11159,10 +12446,13 @@
         <v>0.003193</v>
       </c>
       <c r="F429" s="1" t="n">
+        <v>0.003192</v>
+      </c>
+      <c r="G429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="G429" s="1" t="n">
-        <v>0.003193</v>
+      <c r="H429" s="1" t="n">
+        <v>0.003192</v>
       </c>
     </row>
     <row r="430">
@@ -11184,10 +12474,13 @@
         <v>0.03663</v>
       </c>
       <c r="F430" s="1" t="n">
+        <v>0.03652</v>
+      </c>
+      <c r="G430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="G430" s="1" t="n">
-        <v>0.03655</v>
+      <c r="H430" s="1" t="n">
+        <v>0.03652</v>
       </c>
     </row>
     <row r="431">
@@ -11209,10 +12502,13 @@
         <v>0.4008</v>
       </c>
       <c r="F431" s="1" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="G431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="G431" s="1" t="n">
-        <v>0.4008</v>
+      <c r="H431" s="1" t="n">
+        <v>0.4004</v>
       </c>
     </row>
     <row r="432">
@@ -11234,9 +12530,12 @@
         <v>0.004532</v>
       </c>
       <c r="F432" s="1" t="n">
-        <v>0.004542</v>
+        <v>0.004543</v>
       </c>
       <c r="G432" s="1" t="n">
+        <v>0.004543</v>
+      </c>
+      <c r="H432" s="1" t="n">
         <v>0.004519</v>
       </c>
     </row>
@@ -11259,9 +12558,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="F433" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="G433" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="G433" s="1" t="n">
+      <c r="H433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -11284,9 +12586,12 @@
         <v>0.01244</v>
       </c>
       <c r="F434" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="G434" s="1" t="n">
         <v>0.01244</v>
       </c>
-      <c r="G434" s="1" t="n">
+      <c r="H434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -11312,6 +12617,9 @@
         <v>1.981</v>
       </c>
       <c r="G435" s="1" t="n">
+        <v>1.981</v>
+      </c>
+      <c r="H435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -11334,9 +12642,12 @@
         <v>0.001844</v>
       </c>
       <c r="F436" s="1" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="G436" s="1" t="n">
         <v>0.001848</v>
       </c>
-      <c r="G436" s="1" t="n">
+      <c r="H436" s="1" t="n">
         <v>0.001833</v>
       </c>
     </row>
@@ -11359,9 +12670,12 @@
         <v>0.4427</v>
       </c>
       <c r="F437" s="1" t="n">
+        <v>0.4426</v>
+      </c>
+      <c r="G437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="G437" s="1" t="n">
+      <c r="H437" s="1" t="n">
         <v>0.4417</v>
       </c>
     </row>
@@ -11384,9 +12698,12 @@
         <v>0.00536</v>
       </c>
       <c r="F438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="G438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="G438" s="1" t="n">
+      <c r="H438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -11412,6 +12729,9 @@
         <v>0.1035</v>
       </c>
       <c r="G439" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="H439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -11434,9 +12754,12 @@
         <v>0.03417</v>
       </c>
       <c r="F440" s="1" t="n">
+        <v>0.03418</v>
+      </c>
+      <c r="G440" s="1" t="n">
         <v>0.03431</v>
       </c>
-      <c r="G440" s="1" t="n">
+      <c r="H440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -11459,9 +12782,12 @@
         <v>0.08214</v>
       </c>
       <c r="F441" s="1" t="n">
+        <v>0.08207</v>
+      </c>
+      <c r="G441" s="1" t="n">
         <v>0.08215</v>
       </c>
-      <c r="G441" s="1" t="n">
+      <c r="H441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -11484,9 +12810,12 @@
         <v>1.315</v>
       </c>
       <c r="F442" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="G442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="G442" s="1" t="n">
+      <c r="H442" s="1" t="n">
         <v>1.305</v>
       </c>
     </row>
@@ -11509,9 +12838,12 @@
         <v>0.07573000000000001</v>
       </c>
       <c r="F443" s="1" t="n">
+        <v>0.07557</v>
+      </c>
+      <c r="G443" s="1" t="n">
         <v>0.07573000000000001</v>
       </c>
-      <c r="G443" s="1" t="n">
+      <c r="H443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -11534,9 +12866,12 @@
         <v>0.07679</v>
       </c>
       <c r="F444" s="1" t="n">
+        <v>0.07688</v>
+      </c>
+      <c r="G444" s="1" t="n">
         <v>0.07692</v>
       </c>
-      <c r="G444" s="1" t="n">
+      <c r="H444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -11559,9 +12894,12 @@
         <v>0.04385</v>
       </c>
       <c r="F445" s="1" t="n">
+        <v>0.04373</v>
+      </c>
+      <c r="G445" s="1" t="n">
         <v>0.04386</v>
       </c>
-      <c r="G445" s="1" t="n">
+      <c r="H445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -11584,10 +12922,13 @@
         <v>0.02159</v>
       </c>
       <c r="F446" s="1" t="n">
+        <v>0.02153</v>
+      </c>
+      <c r="G446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="G446" s="1" t="n">
-        <v>0.02154</v>
+      <c r="H446" s="1" t="n">
+        <v>0.02153</v>
       </c>
     </row>
     <row r="447">
@@ -11609,9 +12950,12 @@
         <v>0.2811</v>
       </c>
       <c r="F447" s="1" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="G447" s="1" t="n">
         <v>0.2811</v>
       </c>
-      <c r="G447" s="1" t="n">
+      <c r="H447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -11634,10 +12978,13 @@
         <v>0.03137</v>
       </c>
       <c r="F448" s="1" t="n">
+        <v>0.03109</v>
+      </c>
+      <c r="G448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="G448" s="1" t="n">
-        <v>0.03137</v>
+      <c r="H448" s="1" t="n">
+        <v>0.03109</v>
       </c>
     </row>
     <row r="449">
@@ -11659,9 +13006,12 @@
         <v>0.00646</v>
       </c>
       <c r="F449" s="1" t="n">
+        <v>0.00643</v>
+      </c>
+      <c r="G449" s="1" t="n">
         <v>0.00646</v>
       </c>
-      <c r="G449" s="1" t="n">
+      <c r="H449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -11684,10 +13034,13 @@
         <v>0.022942</v>
       </c>
       <c r="F450" s="1" t="n">
+        <v>0.022858</v>
+      </c>
+      <c r="G450" s="1" t="n">
         <v>0.022996</v>
       </c>
-      <c r="G450" s="1" t="n">
-        <v>0.022879</v>
+      <c r="H450" s="1" t="n">
+        <v>0.022858</v>
       </c>
     </row>
     <row r="451">
@@ -11709,9 +13062,12 @@
         <v>0.04225</v>
       </c>
       <c r="F451" s="1" t="n">
-        <v>0.04232</v>
+        <v>0.04244</v>
       </c>
       <c r="G451" s="1" t="n">
+        <v>0.04244</v>
+      </c>
+      <c r="H451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -11734,10 +13090,13 @@
         <v>0.07253999999999999</v>
       </c>
       <c r="F452" s="1" t="n">
+        <v>0.07231</v>
+      </c>
+      <c r="G452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="G452" s="1" t="n">
-        <v>0.07253999999999999</v>
+      <c r="H452" s="1" t="n">
+        <v>0.07231</v>
       </c>
     </row>
     <row r="453">
@@ -11759,9 +13118,12 @@
         <v>0.0005932</v>
       </c>
       <c r="F453" s="1" t="n">
+        <v>0.0005934</v>
+      </c>
+      <c r="G453" s="1" t="n">
         <v>0.0005935</v>
       </c>
-      <c r="G453" s="1" t="n">
+      <c r="H453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -11784,9 +13146,12 @@
         <v>0.309</v>
       </c>
       <c r="F454" s="1" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="G454" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -11809,9 +13174,12 @@
         <v>0.004265</v>
       </c>
       <c r="F455" s="1" t="n">
+        <v>0.004253</v>
+      </c>
+      <c r="G455" s="1" t="n">
         <v>0.004265</v>
       </c>
-      <c r="G455" s="1" t="n">
+      <c r="H455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -11834,9 +13202,12 @@
         <v>0.1839</v>
       </c>
       <c r="F456" s="1" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="G456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="G456" s="1" t="n">
+      <c r="H456" s="1" t="n">
         <v>0.1835</v>
       </c>
     </row>
@@ -11859,9 +13230,12 @@
         <v>0.04283</v>
       </c>
       <c r="F457" s="1" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="G457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="G457" s="1" t="n">
+      <c r="H457" s="1" t="n">
         <v>0.04278</v>
       </c>
     </row>
@@ -11884,9 +13258,12 @@
         <v>0.1465</v>
       </c>
       <c r="F458" s="1" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="G458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="G458" s="1" t="n">
+      <c r="H458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -11909,9 +13286,12 @@
         <v>0.008600999999999999</v>
       </c>
       <c r="F459" s="1" t="n">
-        <v>0.008600999999999999</v>
+        <v>0.008611000000000001</v>
       </c>
       <c r="G459" s="1" t="n">
+        <v>0.008611000000000001</v>
+      </c>
+      <c r="H459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -11934,9 +13314,12 @@
         <v>0.007473</v>
       </c>
       <c r="F460" s="1" t="n">
+        <v>0.007494</v>
+      </c>
+      <c r="G460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="G460" s="1" t="n">
+      <c r="H460" s="1" t="n">
         <v>0.007458</v>
       </c>
     </row>
@@ -11959,9 +13342,12 @@
         <v>0.0001727</v>
       </c>
       <c r="F461" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="G461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="G461" s="1" t="n">
+      <c r="H461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -11984,9 +13370,12 @@
         <v>0.02262</v>
       </c>
       <c r="F462" s="1" t="n">
-        <v>0.02262</v>
+        <v>0.02265</v>
       </c>
       <c r="G462" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="H462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -12009,9 +13398,12 @@
         <v>0.03763</v>
       </c>
       <c r="F463" s="1" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="G463" s="1" t="n">
         <v>0.03777</v>
       </c>
-      <c r="G463" s="1" t="n">
+      <c r="H463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -12034,9 +13426,12 @@
         <v>0.3043</v>
       </c>
       <c r="F464" s="1" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="G464" s="1" t="n">
         <v>0.3043</v>
       </c>
-      <c r="G464" s="1" t="n">
+      <c r="H464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -12059,10 +13454,13 @@
         <v>0.03905</v>
       </c>
       <c r="F465" s="1" t="n">
+        <v>0.03892</v>
+      </c>
+      <c r="G465" s="1" t="n">
         <v>0.03923</v>
       </c>
-      <c r="G465" s="1" t="n">
-        <v>0.03905</v>
+      <c r="H465" s="1" t="n">
+        <v>0.03892</v>
       </c>
     </row>
     <row r="466">
@@ -12084,9 +13482,12 @@
         <v>2.691</v>
       </c>
       <c r="F466" s="1" t="n">
+        <v>2.683</v>
+      </c>
+      <c r="G466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="G466" s="1" t="n">
+      <c r="H466" s="1" t="n">
         <v>2.682</v>
       </c>
     </row>
@@ -12109,9 +13510,12 @@
         <v>0.03435</v>
       </c>
       <c r="F467" s="1" t="n">
+        <v>0.03418</v>
+      </c>
+      <c r="G467" s="1" t="n">
         <v>0.03435</v>
       </c>
-      <c r="G467" s="1" t="n">
+      <c r="H467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -12134,10 +13538,13 @@
         <v>0.1765</v>
       </c>
       <c r="F468" s="1" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="G468" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="G468" s="1" t="n">
-        <v>0.176</v>
+      <c r="H468" s="1" t="n">
+        <v>0.1758</v>
       </c>
     </row>
     <row r="469">
@@ -12159,9 +13566,12 @@
         <v>0.0958</v>
       </c>
       <c r="F469" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="G469" s="1" t="n">
         <v>0.0958</v>
       </c>
-      <c r="G469" s="1" t="n">
+      <c r="H469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -12184,9 +13594,12 @@
         <v>0.06753000000000001</v>
       </c>
       <c r="F470" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="G470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="G470" s="1" t="n">
+      <c r="H470" s="1" t="n">
         <v>0.06745</v>
       </c>
     </row>
@@ -12209,9 +13622,12 @@
         <v>0.03998</v>
       </c>
       <c r="F471" s="1" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="G471" s="1" t="n">
         <v>0.03998</v>
       </c>
-      <c r="G471" s="1" t="n">
+      <c r="H471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -12234,9 +13650,12 @@
         <v>0.2484</v>
       </c>
       <c r="F472" s="1" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="G472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="G472" s="1" t="n">
+      <c r="H472" s="1" t="n">
         <v>0.2475</v>
       </c>
     </row>
@@ -12259,9 +13678,12 @@
         <v>0.016554</v>
       </c>
       <c r="F473" s="1" t="n">
+        <v>0.016552</v>
+      </c>
+      <c r="G473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="G473" s="1" t="n">
+      <c r="H473" s="1" t="n">
         <v>0.016522</v>
       </c>
     </row>
@@ -12284,9 +13706,12 @@
         <v>0.1154</v>
       </c>
       <c r="F474" s="1" t="n">
-        <v>0.1154</v>
+        <v>0.1157</v>
       </c>
       <c r="G474" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="H474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -12309,9 +13734,12 @@
         <v>0.04291</v>
       </c>
       <c r="F475" s="1" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="G475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="G475" s="1" t="n">
+      <c r="H475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -12334,9 +13762,12 @@
         <v>0.2081</v>
       </c>
       <c r="F476" s="1" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="G476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="G476" s="1" t="n">
+      <c r="H476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -12359,10 +13790,13 @@
         <v>0.006826</v>
       </c>
       <c r="F477" s="1" t="n">
+        <v>0.006798</v>
+      </c>
+      <c r="G477" s="1" t="n">
         <v>0.006833</v>
       </c>
-      <c r="G477" s="1" t="n">
-        <v>0.006817</v>
+      <c r="H477" s="1" t="n">
+        <v>0.006798</v>
       </c>
     </row>
     <row r="478">
@@ -12384,10 +13818,13 @@
         <v>0.01814</v>
       </c>
       <c r="F478" s="1" t="n">
+        <v>0.01809</v>
+      </c>
+      <c r="G478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="G478" s="1" t="n">
-        <v>0.01811</v>
+      <c r="H478" s="1" t="n">
+        <v>0.01809</v>
       </c>
     </row>
     <row r="479">
@@ -12409,10 +13846,13 @@
         <v>0.04698</v>
       </c>
       <c r="F479" s="1" t="n">
+        <v>0.04692</v>
+      </c>
+      <c r="G479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="G479" s="1" t="n">
-        <v>0.04698</v>
+      <c r="H479" s="1" t="n">
+        <v>0.04692</v>
       </c>
     </row>
     <row r="480">
@@ -12434,9 +13874,12 @@
         <v>0.26166</v>
       </c>
       <c r="F480" s="1" t="n">
+        <v>0.26147</v>
+      </c>
+      <c r="G480" s="1" t="n">
         <v>0.26166</v>
       </c>
-      <c r="G480" s="1" t="n">
+      <c r="H480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -12459,9 +13902,12 @@
         <v>0.01235</v>
       </c>
       <c r="F481" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="G481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="G481" s="1" t="n">
+      <c r="H481" s="1" t="n">
         <v>0.01235</v>
       </c>
     </row>
@@ -12484,9 +13930,12 @@
         <v>0.004061</v>
       </c>
       <c r="F482" s="1" t="n">
-        <v>0.004069</v>
+        <v>0.004101</v>
       </c>
       <c r="G482" s="1" t="n">
+        <v>0.004101</v>
+      </c>
+      <c r="H482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -12509,9 +13958,12 @@
         <v>0.1231</v>
       </c>
       <c r="F483" s="1" t="n">
-        <v>0.1232</v>
+        <v>0.1233</v>
       </c>
       <c r="G483" s="1" t="n">
+        <v>0.1233</v>
+      </c>
+      <c r="H483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -12534,9 +13986,12 @@
         <v>0.02201</v>
       </c>
       <c r="F484" s="1" t="n">
-        <v>0.02201</v>
+        <v>0.02209</v>
       </c>
       <c r="G484" s="1" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="H484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -12559,10 +14014,13 @@
         <v>0.04574</v>
       </c>
       <c r="F485" s="1" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="G485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="G485" s="1" t="n">
-        <v>0.04574</v>
+      <c r="H485" s="1" t="n">
+        <v>0.0456</v>
       </c>
     </row>
     <row r="486">
@@ -12584,9 +14042,12 @@
         <v>0.1736</v>
       </c>
       <c r="F486" s="1" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="G486" s="1" t="n">
         <v>0.1736</v>
       </c>
-      <c r="G486" s="1" t="n">
+      <c r="H486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -12609,9 +14070,12 @@
         <v>0.2734</v>
       </c>
       <c r="F487" s="1" t="n">
+        <v>0.2734</v>
+      </c>
+      <c r="G487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="G487" s="1" t="n">
+      <c r="H487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -12634,10 +14098,13 @@
         <v>0.04625</v>
       </c>
       <c r="F488" s="1" t="n">
+        <v>0.04611</v>
+      </c>
+      <c r="G488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="G488" s="1" t="n">
-        <v>0.04625</v>
+      <c r="H488" s="1" t="n">
+        <v>0.04611</v>
       </c>
     </row>
     <row r="489">
@@ -12659,9 +14126,12 @@
         <v>0.0002156</v>
       </c>
       <c r="F489" s="1" t="n">
-        <v>0.0002158</v>
+        <v>0.0002159</v>
       </c>
       <c r="G489" s="1" t="n">
+        <v>0.0002159</v>
+      </c>
+      <c r="H489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -12684,9 +14154,12 @@
         <v>1.765</v>
       </c>
       <c r="F490" s="1" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="G490" s="1" t="n">
         <v>1.765</v>
       </c>
-      <c r="G490" s="1" t="n">
+      <c r="H490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -12709,9 +14182,12 @@
         <v>16.083</v>
       </c>
       <c r="F491" s="1" t="n">
+        <v>16.059</v>
+      </c>
+      <c r="G491" s="1" t="n">
         <v>16.083</v>
       </c>
-      <c r="G491" s="1" t="n">
+      <c r="H491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -12734,9 +14210,12 @@
         <v>0.06680999999999999</v>
       </c>
       <c r="F492" s="1" t="n">
+        <v>0.06679</v>
+      </c>
+      <c r="G492" s="1" t="n">
         <v>0.06680999999999999</v>
       </c>
-      <c r="G492" s="1" t="n">
+      <c r="H492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -12759,9 +14238,12 @@
         <v>0.06763</v>
       </c>
       <c r="F493" s="1" t="n">
+        <v>0.06756</v>
+      </c>
+      <c r="G493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="G493" s="1" t="n">
+      <c r="H493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -12784,9 +14266,12 @@
         <v>0.009455</v>
       </c>
       <c r="F494" s="1" t="n">
-        <v>0.009455</v>
+        <v>0.009456000000000001</v>
       </c>
       <c r="G494" s="1" t="n">
+        <v>0.009456000000000001</v>
+      </c>
+      <c r="H494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -12809,9 +14294,12 @@
         <v>0.00593</v>
       </c>
       <c r="F495" s="1" t="n">
+        <v>0.005939</v>
+      </c>
+      <c r="G495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="G495" s="1" t="n">
+      <c r="H495" s="1" t="n">
         <v>0.00593</v>
       </c>
     </row>
@@ -12834,9 +14322,12 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="F496" s="1" t="n">
+        <v>0.00993</v>
+      </c>
+      <c r="G496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="G496" s="1" t="n">
+      <c r="H496" s="1" t="n">
         <v>0.00992</v>
       </c>
     </row>
@@ -12859,9 +14350,12 @@
         <v>0.04404</v>
       </c>
       <c r="F497" s="1" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="G497" s="1" t="n">
         <v>0.04404</v>
       </c>
-      <c r="G497" s="1" t="n">
+      <c r="H497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -12884,10 +14378,13 @@
         <v>0.006412</v>
       </c>
       <c r="F498" s="1" t="n">
+        <v>0.006402</v>
+      </c>
+      <c r="G498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="G498" s="1" t="n">
-        <v>0.006405</v>
+      <c r="H498" s="1" t="n">
+        <v>0.006402</v>
       </c>
     </row>
     <row r="499">
@@ -12909,9 +14406,12 @@
         <v>0.01048</v>
       </c>
       <c r="F499" s="1" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="G499" s="1" t="n">
         <v>0.01048</v>
       </c>
-      <c r="G499" s="1" t="n">
+      <c r="H499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -12934,9 +14434,12 @@
         <v>0.5113</v>
       </c>
       <c r="F500" s="1" t="n">
-        <v>0.5122</v>
+        <v>0.5134</v>
       </c>
       <c r="G500" s="1" t="n">
+        <v>0.5134</v>
+      </c>
+      <c r="H500" s="1" t="n">
         <v>0.5089</v>
       </c>
     </row>
@@ -12959,9 +14462,12 @@
         <v>0.03205</v>
       </c>
       <c r="F501" s="1" t="n">
+        <v>0.03203</v>
+      </c>
+      <c r="G501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="G501" s="1" t="n">
+      <c r="H501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -12984,9 +14490,12 @@
         <v>0.4373</v>
       </c>
       <c r="F502" s="1" t="n">
-        <v>0.4373</v>
+        <v>0.4385</v>
       </c>
       <c r="G502" s="1" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="H502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -13009,9 +14518,12 @@
         <v>0.999341</v>
       </c>
       <c r="F503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="G503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="G503" s="1" t="n">
+      <c r="H503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -13034,9 +14546,12 @@
         <v>0.03552</v>
       </c>
       <c r="F504" s="1" t="n">
-        <v>0.03552</v>
+        <v>0.03554</v>
       </c>
       <c r="G504" s="1" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="H504" s="1" t="n">
         <v>0.03525</v>
       </c>
     </row>
@@ -13059,9 +14574,12 @@
         <v>0.004934</v>
       </c>
       <c r="F505" s="1" t="n">
+        <v>0.004932</v>
+      </c>
+      <c r="G505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="G505" s="1" t="n">
+      <c r="H505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -13084,9 +14602,12 @@
         <v>0.01397</v>
       </c>
       <c r="F506" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="G506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="G506" s="1" t="n">
+      <c r="H506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -13109,10 +14630,13 @@
         <v>0.003471</v>
       </c>
       <c r="F507" s="1" t="n">
+        <v>0.003453</v>
+      </c>
+      <c r="G507" s="1" t="n">
         <v>0.003478</v>
       </c>
-      <c r="G507" s="1" t="n">
-        <v>0.00347</v>
+      <c r="H507" s="1" t="n">
+        <v>0.003453</v>
       </c>
     </row>
     <row r="508">
@@ -13134,9 +14658,12 @@
         <v>1.422</v>
       </c>
       <c r="F508" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="G508" s="1" t="n">
+      <c r="H508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -13159,10 +14686,13 @@
         <v>0.005097</v>
       </c>
       <c r="F509" s="1" t="n">
+        <v>0.005076</v>
+      </c>
+      <c r="G509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="G509" s="1" t="n">
-        <v>0.005097</v>
+      <c r="H509" s="1" t="n">
+        <v>0.005076</v>
       </c>
     </row>
     <row r="510">
@@ -13184,9 +14714,12 @@
         <v>0.01575</v>
       </c>
       <c r="F510" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="G510" s="1" t="n">
         <v>0.01576</v>
       </c>
-      <c r="G510" s="1" t="n">
+      <c r="H510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -13209,9 +14742,12 @@
         <v>0.0832</v>
       </c>
       <c r="F511" s="1" t="n">
+        <v>0.08339000000000001</v>
+      </c>
+      <c r="G511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="G511" s="1" t="n">
+      <c r="H511" s="1" t="n">
         <v>0.08319</v>
       </c>
     </row>
@@ -13234,9 +14770,12 @@
         <v>0.007121</v>
       </c>
       <c r="F512" s="1" t="n">
+        <v>0.007117</v>
+      </c>
+      <c r="G512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="G512" s="1" t="n">
+      <c r="H512" s="1" t="n">
         <v>0.007105</v>
       </c>
     </row>
@@ -13259,9 +14798,12 @@
         <v>0.0148</v>
       </c>
       <c r="F513" s="1" t="n">
-        <v>0.0148</v>
+        <v>0.01483</v>
       </c>
       <c r="G513" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="H513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -13284,10 +14826,13 @@
         <v>0.04762</v>
       </c>
       <c r="F514" s="1" t="n">
+        <v>0.04748</v>
+      </c>
+      <c r="G514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="G514" s="1" t="n">
-        <v>0.04758</v>
+      <c r="H514" s="1" t="n">
+        <v>0.04748</v>
       </c>
     </row>
     <row r="515">
@@ -13309,10 +14854,13 @@
         <v>0.01827</v>
       </c>
       <c r="F515" s="1" t="n">
+        <v>0.01818</v>
+      </c>
+      <c r="G515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="G515" s="1" t="n">
-        <v>0.01824</v>
+      <c r="H515" s="1" t="n">
+        <v>0.01818</v>
       </c>
     </row>
     <row r="516">
@@ -13334,9 +14882,12 @@
         <v>0.0005808</v>
       </c>
       <c r="F516" s="1" t="n">
+        <v>0.0005806</v>
+      </c>
+      <c r="G516" s="1" t="n">
         <v>0.0005808</v>
       </c>
-      <c r="G516" s="1" t="n">
+      <c r="H516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -13359,9 +14910,12 @@
         <v>0.07892</v>
       </c>
       <c r="F517" s="1" t="n">
+        <v>0.07886</v>
+      </c>
+      <c r="G517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="G517" s="1" t="n">
+      <c r="H517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -13384,10 +14938,13 @@
         <v>0.006389</v>
       </c>
       <c r="F518" s="1" t="n">
+        <v>0.006378</v>
+      </c>
+      <c r="G518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="G518" s="1" t="n">
-        <v>0.006386</v>
+      <c r="H518" s="1" t="n">
+        <v>0.006378</v>
       </c>
     </row>
     <row r="519">
@@ -13409,9 +14966,12 @@
         <v>0.05826</v>
       </c>
       <c r="F519" s="1" t="n">
+        <v>0.05813</v>
+      </c>
+      <c r="G519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="G519" s="1" t="n">
+      <c r="H519" s="1" t="n">
         <v>0.05803</v>
       </c>
     </row>
@@ -13434,9 +14994,12 @@
         <v>0.10524</v>
       </c>
       <c r="F520" s="1" t="n">
+        <v>0.10513</v>
+      </c>
+      <c r="G520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="G520" s="1" t="n">
+      <c r="H520" s="1" t="n">
         <v>0.10496</v>
       </c>
     </row>
@@ -13459,9 +15022,12 @@
         <v>0.01799</v>
       </c>
       <c r="F521" s="1" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="G521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="G521" s="1" t="n">
+      <c r="H521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -13484,9 +15050,12 @@
         <v>0.01652</v>
       </c>
       <c r="F522" s="1" t="n">
+        <v>0.01651</v>
+      </c>
+      <c r="G522" s="1" t="n">
         <v>0.01653</v>
       </c>
-      <c r="G522" s="1" t="n">
+      <c r="H522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -13509,9 +15078,12 @@
         <v>0.01091</v>
       </c>
       <c r="F523" s="1" t="n">
-        <v>0.01091</v>
+        <v>0.01092</v>
       </c>
       <c r="G523" s="1" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="H523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -13534,9 +15106,12 @@
         <v>0.006885</v>
       </c>
       <c r="F524" s="1" t="n">
-        <v>0.006885</v>
+        <v>0.006993</v>
       </c>
       <c r="G524" s="1" t="n">
+        <v>0.006993</v>
+      </c>
+      <c r="H524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -13559,9 +15134,12 @@
         <v>0.005938</v>
       </c>
       <c r="F525" s="1" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="G525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="G525" s="1" t="n">
+      <c r="H525" s="1" t="n">
         <v>0.005938</v>
       </c>
     </row>
@@ -13584,9 +15162,12 @@
         <v>0.001434</v>
       </c>
       <c r="F526" s="1" t="n">
+        <v>0.001444</v>
+      </c>
+      <c r="G526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="G526" s="1" t="n">
+      <c r="H526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -13609,9 +15190,12 @@
         <v>0.374</v>
       </c>
       <c r="F527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="G527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="G527" s="1" t="n">
+      <c r="H527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -13634,9 +15218,12 @@
         <v>0.005197</v>
       </c>
       <c r="F528" s="1" t="n">
-        <v>0.005197</v>
+        <v>0.005207</v>
       </c>
       <c r="G528" s="1" t="n">
+        <v>0.005207</v>
+      </c>
+      <c r="H528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -13659,9 +15246,12 @@
         <v>2.942</v>
       </c>
       <c r="F529" s="1" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="G529" s="1" t="n">
         <v>2.942</v>
       </c>
-      <c r="G529" s="1" t="n">
+      <c r="H529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -13684,9 +15274,12 @@
         <v>0.156</v>
       </c>
       <c r="F530" s="1" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="G530" s="1" t="n">
         <v>0.156</v>
       </c>
-      <c r="G530" s="1" t="n">
+      <c r="H530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -13709,10 +15302,13 @@
         <v>2534</v>
       </c>
       <c r="F531" s="1" t="n">
+        <v>2531</v>
+      </c>
+      <c r="G531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="G531" s="1" t="n">
-        <v>2534</v>
+      <c r="H531" s="1" t="n">
+        <v>2531</v>
       </c>
     </row>
     <row r="532">
@@ -13734,9 +15330,12 @@
         <v>0.03925</v>
       </c>
       <c r="F532" s="1" t="n">
+        <v>0.03923</v>
+      </c>
+      <c r="G532" s="1" t="n">
         <v>0.03928</v>
       </c>
-      <c r="G532" s="1" t="n">
+      <c r="H532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -13762,6 +15361,9 @@
         <v>0.0219</v>
       </c>
       <c r="G533" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="H533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -13784,9 +15386,12 @@
         <v>0.0731</v>
       </c>
       <c r="F534" s="1" t="n">
-        <v>0.0731</v>
+        <v>0.07334</v>
       </c>
       <c r="G534" s="1" t="n">
+        <v>0.07334</v>
+      </c>
+      <c r="H534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -13809,9 +15414,12 @@
         <v>0.007853000000000001</v>
       </c>
       <c r="F535" s="1" t="n">
+        <v>0.007842999999999999</v>
+      </c>
+      <c r="G535" s="1" t="n">
         <v>0.007877</v>
       </c>
-      <c r="G535" s="1" t="n">
+      <c r="H535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -13834,9 +15442,12 @@
         <v>0.05032</v>
       </c>
       <c r="F536" s="1" t="n">
+        <v>0.05029</v>
+      </c>
+      <c r="G536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="G536" s="1" t="n">
+      <c r="H536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -13859,9 +15470,12 @@
         <v>0.00407</v>
       </c>
       <c r="F537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="G537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="G537" s="1" t="n">
+      <c r="H537" s="1" t="n">
         <v>0.00406</v>
       </c>
     </row>
@@ -13884,9 +15498,12 @@
         <v>0.08307</v>
       </c>
       <c r="F538" s="1" t="n">
+        <v>0.08296000000000001</v>
+      </c>
+      <c r="G538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="G538" s="1" t="n">
+      <c r="H538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -13909,10 +15526,13 @@
         <v>0.02495</v>
       </c>
       <c r="F539" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="G539" s="1" t="n">
         <v>0.02502</v>
       </c>
-      <c r="G539" s="1" t="n">
-        <v>0.02495</v>
+      <c r="H539" s="1" t="n">
+        <v>0.02485</v>
       </c>
     </row>
     <row r="540">
@@ -13934,9 +15554,12 @@
         <v>0.08484</v>
       </c>
       <c r="F540" s="1" t="n">
-        <v>0.08488</v>
+        <v>0.08498</v>
       </c>
       <c r="G540" s="1" t="n">
+        <v>0.08498</v>
+      </c>
+      <c r="H540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -13959,9 +15582,12 @@
         <v>0.01901</v>
       </c>
       <c r="F541" s="1" t="n">
+        <v>0.01898</v>
+      </c>
+      <c r="G541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="G541" s="1" t="n">
+      <c r="H541" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -13984,9 +15610,12 @@
         <v>0.017</v>
       </c>
       <c r="F542" s="1" t="n">
+        <v>0.01698</v>
+      </c>
+      <c r="G542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="G542" s="1" t="n">
+      <c r="H542" s="1" t="n">
         <v>0.01698</v>
       </c>
     </row>
@@ -14012,6 +15641,9 @@
         <v>0.105</v>
       </c>
       <c r="G543" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I543"/>
+  <dimension ref="A1:J543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,9 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,10 +469,15 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>price_01:45</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -502,9 +508,12 @@
         <v>70693.10000000001</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>70612.3</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -533,9 +542,12 @@
         <v>2076.79</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>2074.79</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -564,9 +576,12 @@
         <v>86.98</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -595,9 +610,12 @@
         <v>4.122</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>4.104</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -626,10 +644,13 @@
         <v>0.095</v>
       </c>
       <c r="H6" s="1" t="n">
+        <v>0.09476999999999999</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>0.09485</v>
+      <c r="J6" s="1" t="n">
+        <v>0.09476999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -657,9 +678,12 @@
         <v>1.3911</v>
       </c>
       <c r="H7" s="1" t="n">
+        <v>1.3896</v>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -688,9 +712,12 @@
         <v>22.43</v>
       </c>
       <c r="H8" s="1" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>22.657</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -719,9 +746,12 @@
         <v>0.002194</v>
       </c>
       <c r="H9" s="1" t="n">
+        <v>0.002154</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>0.002119</v>
       </c>
     </row>
@@ -750,9 +780,12 @@
         <v>0.01033</v>
       </c>
       <c r="H10" s="1" t="n">
+        <v>0.010215</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -781,9 +814,12 @@
         <v>0.15789</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>0.16454</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="J11" s="1" t="n">
         <v>0.15789</v>
       </c>
     </row>
@@ -812,9 +848,12 @@
         <v>0.01154</v>
       </c>
       <c r="H12" s="1" t="n">
+        <v>0.011639</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="J12" s="1" t="n">
         <v>0.01154</v>
       </c>
     </row>
@@ -843,9 +882,12 @@
         <v>38.195</v>
       </c>
       <c r="H13" s="1" t="n">
+        <v>38.067</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -874,9 +916,12 @@
         <v>653.86</v>
       </c>
       <c r="H14" s="1" t="n">
+        <v>653.5</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="J14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -905,9 +950,12 @@
         <v>209.33</v>
       </c>
       <c r="H15" s="1" t="n">
+        <v>209.47</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="J15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -936,10 +984,13 @@
         <v>0.0033487</v>
       </c>
       <c r="H16" s="1" t="n">
+        <v>0.0033394</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>0.0033417</v>
+      <c r="J16" s="1" t="n">
+        <v>0.0033394</v>
       </c>
     </row>
     <row r="17">
@@ -967,9 +1018,12 @@
         <v>238.32</v>
       </c>
       <c r="H17" s="1" t="n">
+        <v>236.78</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>238.32</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="J17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -998,9 +1052,12 @@
         <v>0.9933999999999999</v>
       </c>
       <c r="H18" s="1" t="n">
+        <v>0.9923</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="J18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1029,9 +1086,12 @@
         <v>1.0432</v>
       </c>
       <c r="H19" s="1" t="n">
+        <v>1.0495</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="I19" s="1" t="n">
+      <c r="J19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1060,10 +1120,13 @@
         <v>0.2604</v>
       </c>
       <c r="H20" s="1" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>0.2604</v>
+      <c r="J20" s="1" t="n">
+        <v>0.2598</v>
       </c>
     </row>
     <row r="21">
@@ -1091,10 +1154,13 @@
         <v>0.59972</v>
       </c>
       <c r="H21" s="1" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="I21" s="1" t="n">
-        <v>0.59972</v>
+      <c r="J21" s="1" t="n">
+        <v>0.59536</v>
       </c>
     </row>
     <row r="22">
@@ -1122,9 +1188,12 @@
         <v>9.042</v>
       </c>
       <c r="H22" s="1" t="n">
+        <v>9.028</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="J22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1153,9 +1222,12 @@
         <v>0.02408</v>
       </c>
       <c r="H23" s="1" t="n">
+        <v>0.02415</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="J23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1184,9 +1256,12 @@
         <v>9.586</v>
       </c>
       <c r="H24" s="1" t="n">
+        <v>9.576000000000001</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="J24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -1215,9 +1290,12 @@
         <v>1.222</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>1.224</v>
+        <v>1.228</v>
       </c>
       <c r="I25" s="1" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="J25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1246,9 +1324,12 @@
         <v>0.07043000000000001</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.07160999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="I26" s="1" t="n">
+        <v>0.0717</v>
+      </c>
+      <c r="J26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1277,9 +1358,12 @@
         <v>1.43</v>
       </c>
       <c r="H27" s="1" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="J27" s="1" t="n">
         <v>1.424</v>
       </c>
     </row>
@@ -1308,10 +1392,13 @@
         <v>1.311</v>
       </c>
       <c r="H28" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="I28" s="1" t="n">
-        <v>1.309</v>
+      <c r="J28" s="1" t="n">
+        <v>1.308</v>
       </c>
     </row>
     <row r="29">
@@ -1339,9 +1426,12 @@
         <v>463.21</v>
       </c>
       <c r="H29" s="1" t="n">
+        <v>462.93</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>463.21</v>
       </c>
-      <c r="I29" s="1" t="n">
+      <c r="J29" s="1" t="n">
         <v>461.74</v>
       </c>
     </row>
@@ -1370,9 +1460,12 @@
         <v>1.2887</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1.2887</v>
+        <v>1.2902</v>
       </c>
       <c r="I30" s="1" t="n">
+        <v>1.2902</v>
+      </c>
+      <c r="J30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1401,9 +1494,12 @@
         <v>5023.04</v>
       </c>
       <c r="H31" s="1" t="n">
+        <v>5024.12</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="I31" s="1" t="n">
+      <c r="J31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1432,9 +1528,12 @@
         <v>0.875</v>
       </c>
       <c r="H32" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I32" s="1" t="n">
         <v>0.877</v>
       </c>
-      <c r="I32" s="1" t="n">
+      <c r="J32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1463,9 +1562,12 @@
         <v>0.001979</v>
       </c>
       <c r="H33" s="1" t="n">
+        <v>0.001979</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="J33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1494,9 +1596,12 @@
         <v>0.16692</v>
       </c>
       <c r="H34" s="1" t="n">
+        <v>0.16824</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>0.17091</v>
       </c>
-      <c r="I34" s="1" t="n">
+      <c r="J34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -1525,10 +1630,13 @@
         <v>0.29735</v>
       </c>
       <c r="H35" s="1" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="I35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="I35" s="1" t="n">
-        <v>0.29735</v>
+      <c r="J35" s="1" t="n">
+        <v>0.2972</v>
       </c>
     </row>
     <row r="36">
@@ -1556,9 +1664,12 @@
         <v>1.793</v>
       </c>
       <c r="H36" s="1" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="I36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="I36" s="1" t="n">
+      <c r="J36" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1587,9 +1698,12 @@
         <v>110.81</v>
       </c>
       <c r="H37" s="1" t="n">
+        <v>110.77</v>
+      </c>
+      <c r="I37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="I37" s="1" t="n">
+      <c r="J37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1618,10 +1732,13 @@
         <v>0.22314</v>
       </c>
       <c r="H38" s="1" t="n">
+        <v>0.22175</v>
+      </c>
+      <c r="I38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="I38" s="1" t="n">
-        <v>0.22314</v>
+      <c r="J38" s="1" t="n">
+        <v>0.22175</v>
       </c>
     </row>
     <row r="39">
@@ -1649,9 +1766,12 @@
         <v>0.1081</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="I39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="J39" s="1" t="n">
         <v>0.1078</v>
       </c>
     </row>
@@ -1680,9 +1800,12 @@
         <v>0.37137</v>
       </c>
       <c r="H40" s="1" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="I40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="I40" s="1" t="n">
+      <c r="J40" s="1" t="n">
         <v>0.37042</v>
       </c>
     </row>
@@ -1711,9 +1834,12 @@
         <v>54.66</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="I41" s="1" t="n">
         <v>54.66</v>
       </c>
-      <c r="I41" s="1" t="n">
+      <c r="J41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1742,9 +1868,12 @@
         <v>0.0010744</v>
       </c>
       <c r="H42" s="1" t="n">
+        <v>0.0010743</v>
+      </c>
+      <c r="I42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="I42" s="1" t="n">
+      <c r="J42" s="1" t="n">
         <v>0.0010732</v>
       </c>
     </row>
@@ -1773,9 +1902,12 @@
         <v>6.414</v>
       </c>
       <c r="H43" s="1" t="n">
+        <v>6.466</v>
+      </c>
+      <c r="I43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="I43" s="1" t="n">
+      <c r="J43" s="1" t="n">
         <v>6.414</v>
       </c>
     </row>
@@ -1804,10 +1936,13 @@
         <v>0.6373</v>
       </c>
       <c r="H44" s="1" t="n">
+        <v>0.6365</v>
+      </c>
+      <c r="I44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="I44" s="1" t="n">
-        <v>0.6373</v>
+      <c r="J44" s="1" t="n">
+        <v>0.6365</v>
       </c>
     </row>
     <row r="45">
@@ -1835,9 +1970,12 @@
         <v>0.3557</v>
       </c>
       <c r="H45" s="1" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="I45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="I45" s="1" t="n">
+      <c r="J45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -1866,9 +2004,12 @@
         <v>0.03228</v>
       </c>
       <c r="H46" s="1" t="n">
+        <v>0.03228</v>
+      </c>
+      <c r="I46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="I46" s="1" t="n">
+      <c r="J46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -1897,9 +2038,12 @@
         <v>0.07151</v>
       </c>
       <c r="H47" s="1" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="I47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="I47" s="1" t="n">
+      <c r="J47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -1928,9 +2072,12 @@
         <v>0.7060999999999999</v>
       </c>
       <c r="H48" s="1" t="n">
+        <v>0.7048</v>
+      </c>
+      <c r="I48" s="1" t="n">
         <v>0.7060999999999999</v>
       </c>
-      <c r="I48" s="1" t="n">
+      <c r="J48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -1959,9 +2106,12 @@
         <v>0.004518</v>
       </c>
       <c r="H49" s="1" t="n">
+        <v>0.004536</v>
+      </c>
+      <c r="I49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="I49" s="1" t="n">
+      <c r="J49" s="1" t="n">
         <v>0.004518</v>
       </c>
     </row>
@@ -1990,9 +2140,12 @@
         <v>0.1046</v>
       </c>
       <c r="H50" s="1" t="n">
+        <v>0.1045</v>
+      </c>
+      <c r="I50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="I50" s="1" t="n">
+      <c r="J50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -2021,9 +2174,12 @@
         <v>0.04047</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>0.04047</v>
+        <v>0.0406</v>
       </c>
       <c r="I51" s="1" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="J51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -2052,10 +2208,13 @@
         <v>0.1665</v>
       </c>
       <c r="H52" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="I52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="I52" s="1" t="n">
-        <v>0.1665</v>
+      <c r="J52" s="1" t="n">
+        <v>0.166</v>
       </c>
     </row>
     <row r="53">
@@ -2083,10 +2242,13 @@
         <v>0.02128</v>
       </c>
       <c r="H53" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="I53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="I53" s="1" t="n">
-        <v>0.02128</v>
+      <c r="J53" s="1" t="n">
+        <v>0.021</v>
       </c>
     </row>
     <row r="54">
@@ -2114,9 +2276,12 @@
         <v>0.007247</v>
       </c>
       <c r="H54" s="1" t="n">
+        <v>0.007232</v>
+      </c>
+      <c r="I54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="I54" s="1" t="n">
+      <c r="J54" s="1" t="n">
         <v>0.007221</v>
       </c>
     </row>
@@ -2145,10 +2310,13 @@
         <v>3.925</v>
       </c>
       <c r="H55" s="1" t="n">
+        <v>3.921</v>
+      </c>
+      <c r="I55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="I55" s="1" t="n">
-        <v>3.925</v>
+      <c r="J55" s="1" t="n">
+        <v>3.921</v>
       </c>
     </row>
     <row r="56">
@@ -2176,9 +2344,12 @@
         <v>0.017187</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>0.017208</v>
+        <v>0.017264</v>
       </c>
       <c r="I56" s="1" t="n">
+        <v>0.017264</v>
+      </c>
+      <c r="J56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -2207,9 +2378,12 @@
         <v>0.1117</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>0.1118</v>
+        <v>0.1122</v>
       </c>
       <c r="I57" s="1" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="J57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -2241,6 +2415,9 @@
         <v>2.662</v>
       </c>
       <c r="I58" s="1" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="J58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -2269,9 +2446,12 @@
         <v>0.1603</v>
       </c>
       <c r="H59" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="I59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="I59" s="1" t="n">
+      <c r="J59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -2300,10 +2480,13 @@
         <v>0.005923</v>
       </c>
       <c r="H60" s="1" t="n">
+        <v>0.005912</v>
+      </c>
+      <c r="I60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="I60" s="1" t="n">
-        <v>0.005914</v>
+      <c r="J60" s="1" t="n">
+        <v>0.005912</v>
       </c>
     </row>
     <row r="61">
@@ -2331,9 +2514,12 @@
         <v>0.09204</v>
       </c>
       <c r="H61" s="1" t="n">
+        <v>0.09205000000000001</v>
+      </c>
+      <c r="I61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="I61" s="1" t="n">
+      <c r="J61" s="1" t="n">
         <v>0.09204</v>
       </c>
     </row>
@@ -2362,9 +2548,12 @@
         <v>0.9146</v>
       </c>
       <c r="H62" s="1" t="n">
+        <v>0.9131</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="I62" s="1" t="n">
+      <c r="J62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -2396,6 +2585,9 @@
         <v>0.78</v>
       </c>
       <c r="I63" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -2424,9 +2616,12 @@
         <v>0.04656</v>
       </c>
       <c r="H64" s="1" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="I64" s="1" t="n">
+      <c r="J64" s="1" t="n">
         <v>0.04623</v>
       </c>
     </row>
@@ -2455,9 +2650,12 @@
         <v>355.99</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>357.66</v>
+        <v>357.73</v>
       </c>
       <c r="I65" s="1" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="J65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -2486,9 +2684,12 @@
         <v>0.12495</v>
       </c>
       <c r="H66" s="1" t="n">
+        <v>0.12544</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="I66" s="1" t="n">
+      <c r="J66" s="1" t="n">
         <v>0.12495</v>
       </c>
     </row>
@@ -2517,10 +2718,13 @@
         <v>0.2383</v>
       </c>
       <c r="H67" s="1" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="I67" s="1" t="n">
-        <v>0.2383</v>
+      <c r="J67" s="1" t="n">
+        <v>0.2369</v>
       </c>
     </row>
     <row r="68">
@@ -2548,9 +2752,12 @@
         <v>0.00342</v>
       </c>
       <c r="H68" s="1" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="I68" s="1" t="n">
+      <c r="J68" s="1" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -2579,10 +2786,13 @@
         <v>0.175</v>
       </c>
       <c r="H69" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="I69" s="1" t="n">
-        <v>0.175</v>
+      <c r="J69" s="1" t="n">
+        <v>0.1748</v>
       </c>
     </row>
     <row r="70">
@@ -2610,9 +2820,12 @@
         <v>0.16506</v>
       </c>
       <c r="H70" s="1" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="I70" s="1" t="n">
+      <c r="J70" s="1" t="n">
         <v>0.16421</v>
       </c>
     </row>
@@ -2641,9 +2854,12 @@
         <v>0.3547</v>
       </c>
       <c r="H71" s="1" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="I71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="I71" s="1" t="n">
+      <c r="J71" s="1" t="n">
         <v>0.3517</v>
       </c>
     </row>
@@ -2672,9 +2888,12 @@
         <v>0.7104</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>0.7104</v>
+        <v>0.7105</v>
       </c>
       <c r="I72" s="1" t="n">
+        <v>0.7105</v>
+      </c>
+      <c r="J72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -2703,9 +2922,12 @@
         <v>0.008630000000000001</v>
       </c>
       <c r="H73" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="I73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="I73" s="1" t="n">
+      <c r="J73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -2734,10 +2956,13 @@
         <v>0.005999</v>
       </c>
       <c r="H74" s="1" t="n">
+        <v>0.005995</v>
+      </c>
+      <c r="I74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="I74" s="1" t="n">
-        <v>0.005999</v>
+      <c r="J74" s="1" t="n">
+        <v>0.005995</v>
       </c>
     </row>
     <row r="75">
@@ -2765,9 +2990,12 @@
         <v>0.227</v>
       </c>
       <c r="H75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="I75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="I75" s="1" t="n">
+      <c r="J75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -2796,9 +3024,12 @@
         <v>0.3126</v>
       </c>
       <c r="H76" s="1" t="n">
-        <v>0.3126</v>
+        <v>0.3167</v>
       </c>
       <c r="I76" s="1" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="J76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -2827,9 +3058,12 @@
         <v>0.1006</v>
       </c>
       <c r="H77" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="I77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="I77" s="1" t="n">
+      <c r="J77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -2858,9 +3092,12 @@
         <v>0.1232</v>
       </c>
       <c r="H78" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="I78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="I78" s="1" t="n">
+      <c r="J78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -2889,9 +3126,12 @@
         <v>0.06955</v>
       </c>
       <c r="H79" s="1" t="n">
-        <v>0.06955</v>
+        <v>0.07071</v>
       </c>
       <c r="I79" s="1" t="n">
+        <v>0.07071</v>
+      </c>
+      <c r="J79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -2920,9 +3160,12 @@
         <v>0.04688</v>
       </c>
       <c r="H80" s="1" t="n">
+        <v>0.04691</v>
+      </c>
+      <c r="I80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="I80" s="1" t="n">
+      <c r="J80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -2951,9 +3194,12 @@
         <v>0.000238</v>
       </c>
       <c r="H81" s="1" t="n">
+        <v>0.000238</v>
+      </c>
+      <c r="I81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="I81" s="1" t="n">
+      <c r="J81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -2982,9 +3228,12 @@
         <v>8.231999999999999</v>
       </c>
       <c r="H82" s="1" t="n">
+        <v>8.223000000000001</v>
+      </c>
+      <c r="I82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="I82" s="1" t="n">
+      <c r="J82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -3013,9 +3262,12 @@
         <v>0.000584</v>
       </c>
       <c r="H83" s="1" t="n">
+        <v>0.0005836</v>
+      </c>
+      <c r="I83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="I83" s="1" t="n">
+      <c r="J83" s="1" t="n">
         <v>0.0005831</v>
       </c>
     </row>
@@ -3044,9 +3296,12 @@
         <v>0.4268</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>0.4268</v>
+        <v>0.4342</v>
       </c>
       <c r="I84" s="1" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="J84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -3075,10 +3330,13 @@
         <v>0.06257</v>
       </c>
       <c r="H85" s="1" t="n">
+        <v>0.06235</v>
+      </c>
+      <c r="I85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="I85" s="1" t="n">
-        <v>0.06243</v>
+      <c r="J85" s="1" t="n">
+        <v>0.06235</v>
       </c>
     </row>
     <row r="86">
@@ -3106,9 +3364,12 @@
         <v>0.05472</v>
       </c>
       <c r="H86" s="1" t="n">
+        <v>0.05451</v>
+      </c>
+      <c r="I86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="I86" s="1" t="n">
+      <c r="J86" s="1" t="n">
         <v>0.05447</v>
       </c>
     </row>
@@ -3137,9 +3398,12 @@
         <v>0.003364</v>
       </c>
       <c r="H87" s="1" t="n">
+        <v>0.003348</v>
+      </c>
+      <c r="I87" s="1" t="n">
         <v>0.003364</v>
       </c>
-      <c r="I87" s="1" t="n">
+      <c r="J87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -3168,9 +3432,12 @@
         <v>0.0514</v>
       </c>
       <c r="H88" s="1" t="n">
+        <v>0.05079</v>
+      </c>
+      <c r="I88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="I88" s="1" t="n">
+      <c r="J88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -3199,9 +3466,12 @@
         <v>0.031</v>
       </c>
       <c r="H89" s="1" t="n">
-        <v>0.031</v>
+        <v>0.0313</v>
       </c>
       <c r="I89" s="1" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="J89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -3230,9 +3500,12 @@
         <v>0.3498</v>
       </c>
       <c r="H90" s="1" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="I90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="I90" s="1" t="n">
+      <c r="J90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -3261,9 +3534,12 @@
         <v>0.0625</v>
       </c>
       <c r="H91" s="1" t="n">
-        <v>0.0625</v>
+        <v>0.0653</v>
       </c>
       <c r="I91" s="1" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="J91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -3292,9 +3568,12 @@
         <v>0.3478</v>
       </c>
       <c r="H92" s="1" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="I92" s="1" t="n">
         <v>0.3527</v>
       </c>
-      <c r="I92" s="1" t="n">
+      <c r="J92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -3323,9 +3602,12 @@
         <v>1.9741</v>
       </c>
       <c r="H93" s="1" t="n">
+        <v>1.9733</v>
+      </c>
+      <c r="I93" s="1" t="n">
         <v>1.9753</v>
       </c>
-      <c r="I93" s="1" t="n">
+      <c r="J93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -3354,9 +3636,12 @@
         <v>0.2596</v>
       </c>
       <c r="H94" s="1" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="I94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="I94" s="1" t="n">
+      <c r="J94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -3385,9 +3670,12 @@
         <v>0.0452</v>
       </c>
       <c r="H95" s="1" t="n">
+        <v>0.04519</v>
+      </c>
+      <c r="I95" s="1" t="n">
         <v>0.04542</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="J95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -3416,9 +3704,12 @@
         <v>0.00623</v>
       </c>
       <c r="H96" s="1" t="n">
+        <v>0.006179</v>
+      </c>
+      <c r="I96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="I96" s="1" t="n">
+      <c r="J96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -3447,9 +3738,12 @@
         <v>0.001736</v>
       </c>
       <c r="H97" s="1" t="n">
+        <v>0.001736</v>
+      </c>
+      <c r="I97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="I97" s="1" t="n">
+      <c r="J97" s="1" t="n">
         <v>0.001732</v>
       </c>
     </row>
@@ -3478,9 +3772,12 @@
         <v>5.248</v>
       </c>
       <c r="H98" s="1" t="n">
-        <v>5.284</v>
+        <v>5.304</v>
       </c>
       <c r="I98" s="1" t="n">
+        <v>5.304</v>
+      </c>
+      <c r="J98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -3509,9 +3806,12 @@
         <v>0.0152</v>
       </c>
       <c r="H99" s="1" t="n">
+        <v>0.01524</v>
+      </c>
+      <c r="I99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="I99" s="1" t="n">
+      <c r="J99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -3540,9 +3840,12 @@
         <v>0.5533</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>0.5533</v>
+        <v>0.5535</v>
       </c>
       <c r="I100" s="1" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="J100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -3571,9 +3874,12 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="H101" s="1" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="I101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="I101" s="1" t="n">
+      <c r="J101" s="1" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -3602,9 +3908,12 @@
         <v>32.57</v>
       </c>
       <c r="H102" s="1" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="I102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="J102" s="1" t="n">
         <v>32.48</v>
       </c>
     </row>
@@ -3633,10 +3942,13 @@
         <v>0.03206</v>
       </c>
       <c r="H103" s="1" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="I103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="I103" s="1" t="n">
-        <v>0.032</v>
+      <c r="J103" s="1" t="n">
+        <v>0.03196</v>
       </c>
     </row>
     <row r="104">
@@ -3664,10 +3976,13 @@
         <v>0.06594999999999999</v>
       </c>
       <c r="H104" s="1" t="n">
+        <v>0.06577</v>
+      </c>
+      <c r="I104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="I104" s="1" t="n">
-        <v>0.06582</v>
+      <c r="J104" s="1" t="n">
+        <v>0.06577</v>
       </c>
     </row>
     <row r="105">
@@ -3695,9 +4010,12 @@
         <v>1.3023</v>
       </c>
       <c r="H105" s="1" t="n">
+        <v>1.3027</v>
+      </c>
+      <c r="I105" s="1" t="n">
         <v>1.3041</v>
       </c>
-      <c r="I105" s="1" t="n">
+      <c r="J105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -3726,9 +4044,12 @@
         <v>0.1223</v>
       </c>
       <c r="H106" s="1" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="I106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="I106" s="1" t="n">
+      <c r="J106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -3757,9 +4078,12 @@
         <v>0.121</v>
       </c>
       <c r="H107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="I107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="I107" s="1" t="n">
+      <c r="J107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -3788,10 +4112,13 @@
         <v>0.09606000000000001</v>
       </c>
       <c r="H108" s="1" t="n">
+        <v>0.09586</v>
+      </c>
+      <c r="I108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="I108" s="1" t="n">
-        <v>0.09589</v>
+      <c r="J108" s="1" t="n">
+        <v>0.09586</v>
       </c>
     </row>
     <row r="109">
@@ -3819,9 +4146,12 @@
         <v>0.14066</v>
       </c>
       <c r="H109" s="1" t="n">
+        <v>0.14091</v>
+      </c>
+      <c r="I109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="I109" s="1" t="n">
+      <c r="J109" s="1" t="n">
         <v>0.13861</v>
       </c>
     </row>
@@ -3850,9 +4180,12 @@
         <v>5.56</v>
       </c>
       <c r="H110" s="1" t="n">
+        <v>5.551</v>
+      </c>
+      <c r="I110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="I110" s="1" t="n">
+      <c r="J110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -3881,9 +4214,12 @@
         <v>1.108</v>
       </c>
       <c r="H111" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="I111" s="1" t="n">
+      <c r="J111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -3912,9 +4248,12 @@
         <v>0.029273</v>
       </c>
       <c r="H112" s="1" t="n">
+        <v>0.029308</v>
+      </c>
+      <c r="I112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="I112" s="1" t="n">
+      <c r="J112" s="1" t="n">
         <v>0.029256</v>
       </c>
     </row>
@@ -3943,9 +4282,12 @@
         <v>1.884</v>
       </c>
       <c r="H113" s="1" t="n">
-        <v>1.884</v>
+        <v>1.886</v>
       </c>
       <c r="I113" s="1" t="n">
+        <v>1.886</v>
+      </c>
+      <c r="J113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -3974,9 +4316,12 @@
         <v>0.05848</v>
       </c>
       <c r="H114" s="1" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="I114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="I114" s="1" t="n">
+      <c r="J114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -4005,9 +4350,12 @@
         <v>0.12841</v>
       </c>
       <c r="H115" s="1" t="n">
+        <v>0.12858</v>
+      </c>
+      <c r="I115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="I115" s="1" t="n">
+      <c r="J115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -4036,9 +4384,12 @@
         <v>1.1078</v>
       </c>
       <c r="H116" s="1" t="n">
+        <v>1.1079</v>
+      </c>
+      <c r="I116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="I116" s="1" t="n">
+      <c r="J116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -4067,9 +4418,12 @@
         <v>0.1575</v>
       </c>
       <c r="H117" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="I117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="I117" s="1" t="n">
+      <c r="J117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -4098,9 +4452,12 @@
         <v>0.1599</v>
       </c>
       <c r="H118" s="1" t="n">
-        <v>0.1599</v>
+        <v>0.16</v>
       </c>
       <c r="I118" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -4129,9 +4486,12 @@
         <v>0.04596</v>
       </c>
       <c r="H119" s="1" t="n">
-        <v>0.04596</v>
+        <v>0.04623</v>
       </c>
       <c r="I119" s="1" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="J119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -4160,9 +4520,12 @@
         <v>3.028</v>
       </c>
       <c r="H120" s="1" t="n">
+        <v>3.029</v>
+      </c>
+      <c r="I120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="I120" s="1" t="n">
+      <c r="J120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -4191,9 +4554,12 @@
         <v>0.2979</v>
       </c>
       <c r="H121" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="I121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="I121" s="1" t="n">
+      <c r="J121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -4222,9 +4588,12 @@
         <v>0.5846</v>
       </c>
       <c r="H122" s="1" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="I122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="I122" s="1" t="n">
+      <c r="J122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -4253,10 +4622,13 @@
         <v>0.01258</v>
       </c>
       <c r="H123" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="I123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="I123" s="1" t="n">
-        <v>0.01258</v>
+      <c r="J123" s="1" t="n">
+        <v>0.01257</v>
       </c>
     </row>
     <row r="124">
@@ -4284,9 +4656,12 @@
         <v>0.1594</v>
       </c>
       <c r="H124" s="1" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="I124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="I124" s="1" t="n">
+      <c r="J124" s="1" t="n">
         <v>0.1584</v>
       </c>
     </row>
@@ -4315,9 +4690,12 @@
         <v>0.001783</v>
       </c>
       <c r="H125" s="1" t="n">
+        <v>0.001781</v>
+      </c>
+      <c r="I125" s="1" t="n">
         <v>0.001785</v>
       </c>
-      <c r="I125" s="1" t="n">
+      <c r="J125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -4346,9 +4724,12 @@
         <v>0.0004867</v>
       </c>
       <c r="H126" s="1" t="n">
+        <v>0.000487</v>
+      </c>
+      <c r="I126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="I126" s="1" t="n">
+      <c r="J126" s="1" t="n">
         <v>0.0004867</v>
       </c>
     </row>
@@ -4377,9 +4758,12 @@
         <v>0.02957</v>
       </c>
       <c r="H127" s="1" t="n">
+        <v>0.02951</v>
+      </c>
+      <c r="I127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="I127" s="1" t="n">
+      <c r="J127" s="1" t="n">
         <v>0.02949</v>
       </c>
     </row>
@@ -4408,9 +4792,12 @@
         <v>0.04133</v>
       </c>
       <c r="H128" s="1" t="n">
+        <v>0.04132</v>
+      </c>
+      <c r="I128" s="1" t="n">
         <v>0.04134</v>
       </c>
-      <c r="I128" s="1" t="n">
+      <c r="J128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -4439,9 +4826,12 @@
         <v>0.0486</v>
       </c>
       <c r="H129" s="1" t="n">
+        <v>0.04853</v>
+      </c>
+      <c r="I129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="I129" s="1" t="n">
+      <c r="J129" s="1" t="n">
         <v>0.04838</v>
       </c>
     </row>
@@ -4473,6 +4863,9 @@
         <v>1.25e-05</v>
       </c>
       <c r="I130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="J130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -4501,9 +4894,12 @@
         <v>6.9e-06</v>
       </c>
       <c r="H131" s="1" t="n">
+        <v>6.8e-06</v>
+      </c>
+      <c r="I131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="I131" s="1" t="n">
+      <c r="J131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -4532,9 +4928,12 @@
         <v>0.00702</v>
       </c>
       <c r="H132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="I132" s="1" t="n">
+      <c r="J132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -4563,9 +4962,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="H133" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="I133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="I133" s="1" t="n">
+      <c r="J133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -4594,9 +4996,12 @@
         <v>0.0004114</v>
       </c>
       <c r="H134" s="1" t="n">
+        <v>0.0004102</v>
+      </c>
+      <c r="I134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="I134" s="1" t="n">
+      <c r="J134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -4625,9 +5030,12 @@
         <v>0.08445999999999999</v>
       </c>
       <c r="H135" s="1" t="n">
+        <v>0.08409</v>
+      </c>
+      <c r="I135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="I135" s="1" t="n">
+      <c r="J135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -4656,9 +5064,12 @@
         <v>0.007971000000000001</v>
       </c>
       <c r="H136" s="1" t="n">
+        <v>0.007936</v>
+      </c>
+      <c r="I136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="I136" s="1" t="n">
+      <c r="J136" s="1" t="n">
         <v>0.007891</v>
       </c>
     </row>
@@ -4687,9 +5098,12 @@
         <v>0.000827</v>
       </c>
       <c r="H137" s="1" t="n">
-        <v>0.000827</v>
+        <v>0.000839</v>
       </c>
       <c r="I137" s="1" t="n">
+        <v>0.000839</v>
+      </c>
+      <c r="J137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -4718,10 +5132,13 @@
         <v>0.1475</v>
       </c>
       <c r="H138" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="I138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="I138" s="1" t="n">
-        <v>0.1475</v>
+      <c r="J138" s="1" t="n">
+        <v>0.1473</v>
       </c>
     </row>
     <row r="139">
@@ -4749,9 +5166,12 @@
         <v>0.00672</v>
       </c>
       <c r="H139" s="1" t="n">
+        <v>0.006721</v>
+      </c>
+      <c r="I139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="I139" s="1" t="n">
+      <c r="J139" s="1" t="n">
         <v>0.00672</v>
       </c>
     </row>
@@ -4780,10 +5200,13 @@
         <v>0.01386</v>
       </c>
       <c r="H140" s="1" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="I140" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="I140" s="1" t="n">
-        <v>0.01383</v>
+      <c r="J140" s="1" t="n">
+        <v>0.01381</v>
       </c>
     </row>
     <row r="141">
@@ -4811,9 +5234,12 @@
         <v>0.09768</v>
       </c>
       <c r="H141" s="1" t="n">
+        <v>0.09782</v>
+      </c>
+      <c r="I141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="I141" s="1" t="n">
+      <c r="J141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -4842,9 +5268,12 @@
         <v>0.05421</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>0.05421</v>
+        <v>0.05423</v>
       </c>
       <c r="I142" s="1" t="n">
+        <v>0.05423</v>
+      </c>
+      <c r="J142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -4873,9 +5302,12 @@
         <v>0.3253</v>
       </c>
       <c r="H143" s="1" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="I143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="I143" s="1" t="n">
+      <c r="J143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -4904,9 +5336,12 @@
         <v>0.02584</v>
       </c>
       <c r="H144" s="1" t="n">
+        <v>0.02574</v>
+      </c>
+      <c r="I144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="I144" s="1" t="n">
+      <c r="J144" s="1" t="n">
         <v>0.02572</v>
       </c>
     </row>
@@ -4935,9 +5370,12 @@
         <v>0.2382</v>
       </c>
       <c r="H145" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="I145" s="1" t="n">
         <v>0.2382</v>
       </c>
-      <c r="I145" s="1" t="n">
+      <c r="J145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -4966,10 +5404,13 @@
         <v>0.007047</v>
       </c>
       <c r="H146" s="1" t="n">
+        <v>0.007032</v>
+      </c>
+      <c r="I146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="I146" s="1" t="n">
-        <v>0.007047</v>
+      <c r="J146" s="1" t="n">
+        <v>0.007032</v>
       </c>
     </row>
     <row r="147">
@@ -4997,9 +5438,12 @@
         <v>0.08655</v>
       </c>
       <c r="H147" s="1" t="n">
+        <v>0.08698</v>
+      </c>
+      <c r="I147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="I147" s="1" t="n">
+      <c r="J147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -5028,9 +5472,12 @@
         <v>0.05073</v>
       </c>
       <c r="H148" s="1" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="I148" s="1" t="n">
         <v>0.05073</v>
       </c>
-      <c r="I148" s="1" t="n">
+      <c r="J148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -5059,10 +5506,13 @@
         <v>0.02386</v>
       </c>
       <c r="H149" s="1" t="n">
+        <v>0.02385</v>
+      </c>
+      <c r="I149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="I149" s="1" t="n">
-        <v>0.02386</v>
+      <c r="J149" s="1" t="n">
+        <v>0.02385</v>
       </c>
     </row>
     <row r="150">
@@ -5090,9 +5540,12 @@
         <v>0.08556</v>
       </c>
       <c r="H150" s="1" t="n">
+        <v>0.08573</v>
+      </c>
+      <c r="I150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="I150" s="1" t="n">
+      <c r="J150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -5121,9 +5574,12 @@
         <v>0.02322</v>
       </c>
       <c r="H151" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="I151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="I151" s="1" t="n">
+      <c r="J151" s="1" t="n">
         <v>0.0232</v>
       </c>
     </row>
@@ -5152,10 +5608,13 @@
         <v>0.02572</v>
       </c>
       <c r="H152" s="1" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="I152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="I152" s="1" t="n">
-        <v>0.02571</v>
+      <c r="J152" s="1" t="n">
+        <v>0.02564</v>
       </c>
     </row>
     <row r="153">
@@ -5183,9 +5642,12 @@
         <v>0.0002183</v>
       </c>
       <c r="H153" s="1" t="n">
+        <v>0.0002157</v>
+      </c>
+      <c r="I153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="I153" s="1" t="n">
+      <c r="J153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -5214,9 +5676,12 @@
         <v>0.4444</v>
       </c>
       <c r="H154" s="1" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="I154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="I154" s="1" t="n">
+      <c r="J154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -5245,9 +5710,12 @@
         <v>0.06701</v>
       </c>
       <c r="H155" s="1" t="n">
+        <v>0.06694</v>
+      </c>
+      <c r="I155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="I155" s="1" t="n">
+      <c r="J155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -5276,9 +5744,12 @@
         <v>0.12938</v>
       </c>
       <c r="H156" s="1" t="n">
+        <v>0.12877</v>
+      </c>
+      <c r="I156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="I156" s="1" t="n">
+      <c r="J156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -5310,6 +5781,9 @@
         <v>0.4847</v>
       </c>
       <c r="I157" s="1" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="J157" s="1" t="n">
         <v>0.4843</v>
       </c>
     </row>
@@ -5338,9 +5812,12 @@
         <v>0.4485</v>
       </c>
       <c r="H158" s="1" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="I158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="I158" s="1" t="n">
+      <c r="J158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -5369,10 +5846,13 @@
         <v>0.007529</v>
       </c>
       <c r="H159" s="1" t="n">
+        <v>0.007493</v>
+      </c>
+      <c r="I159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="I159" s="1" t="n">
-        <v>0.007523</v>
+      <c r="J159" s="1" t="n">
+        <v>0.007493</v>
       </c>
     </row>
     <row r="160">
@@ -5400,9 +5880,12 @@
         <v>0.004664</v>
       </c>
       <c r="H160" s="1" t="n">
+        <v>0.004661</v>
+      </c>
+      <c r="I160" s="1" t="n">
         <v>0.004664</v>
       </c>
-      <c r="I160" s="1" t="n">
+      <c r="J160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -5431,9 +5914,12 @@
         <v>0.004304</v>
       </c>
       <c r="H161" s="1" t="n">
+        <v>0.004301</v>
+      </c>
+      <c r="I161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="I161" s="1" t="n">
+      <c r="J161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -5462,9 +5948,12 @@
         <v>0.0963</v>
       </c>
       <c r="H162" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="I162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="I162" s="1" t="n">
+      <c r="J162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -5493,9 +5982,12 @@
         <v>0.2863</v>
       </c>
       <c r="H163" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="I163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="I163" s="1" t="n">
+      <c r="J163" s="1" t="n">
         <v>0.2859</v>
       </c>
     </row>
@@ -5524,10 +6016,13 @@
         <v>0.1148</v>
       </c>
       <c r="H164" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="I164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="I164" s="1" t="n">
-        <v>0.1144</v>
+      <c r="J164" s="1" t="n">
+        <v>0.1142</v>
       </c>
     </row>
     <row r="165">
@@ -5555,10 +6050,13 @@
         <v>0.1757</v>
       </c>
       <c r="H165" s="1" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="I165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="I165" s="1" t="n">
-        <v>0.1756</v>
+      <c r="J165" s="1" t="n">
+        <v>0.1755</v>
       </c>
     </row>
     <row r="166">
@@ -5586,9 +6084,12 @@
         <v>0.01009</v>
       </c>
       <c r="H166" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="I166" s="1" t="n">
         <v>0.01009</v>
       </c>
-      <c r="I166" s="1" t="n">
+      <c r="J166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -5617,9 +6118,12 @@
         <v>1.836</v>
       </c>
       <c r="H167" s="1" t="n">
+        <v>1.834</v>
+      </c>
+      <c r="I167" s="1" t="n">
         <v>1.836</v>
       </c>
-      <c r="I167" s="1" t="n">
+      <c r="J167" s="1" t="n">
         <v>1.827</v>
       </c>
     </row>
@@ -5648,9 +6152,12 @@
         <v>1.342</v>
       </c>
       <c r="H168" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="I168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="I168" s="1" t="n">
+      <c r="J168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -5679,10 +6186,13 @@
         <v>0.00731</v>
       </c>
       <c r="H169" s="1" t="n">
+        <v>0.007304</v>
+      </c>
+      <c r="I169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="I169" s="1" t="n">
-        <v>0.00731</v>
+      <c r="J169" s="1" t="n">
+        <v>0.007304</v>
       </c>
     </row>
     <row r="170">
@@ -5710,9 +6220,12 @@
         <v>0.0116</v>
       </c>
       <c r="H170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="I170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="I170" s="1" t="n">
+      <c r="J170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -5741,9 +6254,12 @@
         <v>0.005817</v>
       </c>
       <c r="H171" s="1" t="n">
+        <v>0.005805</v>
+      </c>
+      <c r="I171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="I171" s="1" t="n">
+      <c r="J171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -5772,9 +6288,12 @@
         <v>0.14806</v>
       </c>
       <c r="H172" s="1" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="I172" s="1" t="n">
         <v>0.14806</v>
       </c>
-      <c r="I172" s="1" t="n">
+      <c r="J172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -5803,9 +6322,12 @@
         <v>4.896</v>
       </c>
       <c r="H173" s="1" t="n">
+        <v>4.874</v>
+      </c>
+      <c r="I173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="I173" s="1" t="n">
+      <c r="J173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -5834,9 +6356,12 @@
         <v>0.07906000000000001</v>
       </c>
       <c r="H174" s="1" t="n">
+        <v>0.07872</v>
+      </c>
+      <c r="I174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="I174" s="1" t="n">
+      <c r="J174" s="1" t="n">
         <v>0.07868</v>
       </c>
     </row>
@@ -5865,10 +6390,13 @@
         <v>0.007496</v>
       </c>
       <c r="H175" s="1" t="n">
+        <v>0.007479</v>
+      </c>
+      <c r="I175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="I175" s="1" t="n">
-        <v>0.007485</v>
+      <c r="J175" s="1" t="n">
+        <v>0.007479</v>
       </c>
     </row>
     <row r="176">
@@ -5896,10 +6424,13 @@
         <v>0.2017</v>
       </c>
       <c r="H176" s="1" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="I176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="I176" s="1" t="n">
-        <v>0.2016</v>
+      <c r="J176" s="1" t="n">
+        <v>0.2013</v>
       </c>
     </row>
     <row r="177">
@@ -5927,9 +6458,12 @@
         <v>0.05187</v>
       </c>
       <c r="H177" s="1" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="I177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="I177" s="1" t="n">
+      <c r="J177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -5961,6 +6495,9 @@
         <v>0.05468</v>
       </c>
       <c r="I178" s="1" t="n">
+        <v>0.05468</v>
+      </c>
+      <c r="J178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -5989,9 +6526,12 @@
         <v>0.02335</v>
       </c>
       <c r="H179" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="I179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="I179" s="1" t="n">
+      <c r="J179" s="1" t="n">
         <v>0.02324</v>
       </c>
     </row>
@@ -6020,9 +6560,12 @@
         <v>0.6962</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>0.6962</v>
+        <v>0.6964</v>
       </c>
       <c r="I180" s="1" t="n">
+        <v>0.6964</v>
+      </c>
+      <c r="J180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -6051,9 +6594,12 @@
         <v>0.0003728</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>0.0003731</v>
+        <v>0.0003734</v>
       </c>
       <c r="I181" s="1" t="n">
+        <v>0.0003734</v>
+      </c>
+      <c r="J181" s="1" t="n">
         <v>0.0003716</v>
       </c>
     </row>
@@ -6082,9 +6628,12 @@
         <v>0.01268</v>
       </c>
       <c r="H182" s="1" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="I182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="I182" s="1" t="n">
+      <c r="J182" s="1" t="n">
         <v>0.01266</v>
       </c>
     </row>
@@ -6113,10 +6662,13 @@
         <v>4.26</v>
       </c>
       <c r="H183" s="1" t="n">
+        <v>4.248</v>
+      </c>
+      <c r="I183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="I183" s="1" t="n">
-        <v>4.26</v>
+      <c r="J183" s="1" t="n">
+        <v>4.248</v>
       </c>
     </row>
     <row r="184">
@@ -6144,9 +6696,12 @@
         <v>0.2382</v>
       </c>
       <c r="H184" s="1" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="I184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="I184" s="1" t="n">
+      <c r="J184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -6175,10 +6730,13 @@
         <v>0.03755</v>
       </c>
       <c r="H185" s="1" t="n">
+        <v>0.03693</v>
+      </c>
+      <c r="I185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="I185" s="1" t="n">
-        <v>0.03755</v>
+      <c r="J185" s="1" t="n">
+        <v>0.03693</v>
       </c>
     </row>
     <row r="186">
@@ -6206,10 +6764,13 @@
         <v>0.11586</v>
       </c>
       <c r="H186" s="1" t="n">
+        <v>0.11566</v>
+      </c>
+      <c r="I186" s="1" t="n">
         <v>0.11628</v>
       </c>
-      <c r="I186" s="1" t="n">
-        <v>0.11573</v>
+      <c r="J186" s="1" t="n">
+        <v>0.11566</v>
       </c>
     </row>
     <row r="187">
@@ -6237,9 +6798,12 @@
         <v>0.009056</v>
       </c>
       <c r="H187" s="1" t="n">
+        <v>0.009117</v>
+      </c>
+      <c r="I187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="I187" s="1" t="n">
+      <c r="J187" s="1" t="n">
         <v>0.009018999999999999</v>
       </c>
     </row>
@@ -6268,10 +6832,13 @@
         <v>0.0977</v>
       </c>
       <c r="H188" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="I188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="I188" s="1" t="n">
-        <v>0.0975</v>
+      <c r="J188" s="1" t="n">
+        <v>0.0974</v>
       </c>
     </row>
     <row r="189">
@@ -6299,9 +6866,12 @@
         <v>0.02799</v>
       </c>
       <c r="H189" s="1" t="n">
+        <v>0.02792</v>
+      </c>
+      <c r="I189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="I189" s="1" t="n">
+      <c r="J189" s="1" t="n">
         <v>0.02773</v>
       </c>
     </row>
@@ -6330,10 +6900,13 @@
         <v>0.00874</v>
       </c>
       <c r="H190" s="1" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="I190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="I190" s="1" t="n">
-        <v>0.00873</v>
+      <c r="J190" s="1" t="n">
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -6361,9 +6934,12 @@
         <v>0.001956</v>
       </c>
       <c r="H191" s="1" t="n">
+        <v>0.001952</v>
+      </c>
+      <c r="I191" s="1" t="n">
         <v>0.001956</v>
       </c>
-      <c r="I191" s="1" t="n">
+      <c r="J191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -6392,9 +6968,12 @@
         <v>0.1006</v>
       </c>
       <c r="H192" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="I192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="I192" s="1" t="n">
+      <c r="J192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -6423,9 +7002,12 @@
         <v>0.02347</v>
       </c>
       <c r="H193" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="I193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="I193" s="1" t="n">
+      <c r="J193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -6454,9 +7036,12 @@
         <v>0.01349</v>
       </c>
       <c r="H194" s="1" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="I194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="I194" s="1" t="n">
+      <c r="J194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -6485,10 +7070,13 @@
         <v>0.02096</v>
       </c>
       <c r="H195" s="1" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="I195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="I195" s="1" t="n">
-        <v>0.02095</v>
+      <c r="J195" s="1" t="n">
+        <v>0.02094</v>
       </c>
     </row>
     <row r="196">
@@ -6516,9 +7104,12 @@
         <v>0.17376</v>
       </c>
       <c r="H196" s="1" t="n">
+        <v>0.17356</v>
+      </c>
+      <c r="I196" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="I196" s="1" t="n">
+      <c r="J196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -6547,9 +7138,12 @@
         <v>0.0073</v>
       </c>
       <c r="H197" s="1" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="I197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="I197" s="1" t="n">
+      <c r="J197" s="1" t="n">
         <v>0.007292</v>
       </c>
     </row>
@@ -6578,9 +7172,12 @@
         <v>0.01912</v>
       </c>
       <c r="H198" s="1" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="I198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="I198" s="1" t="n">
+      <c r="J198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -6609,10 +7206,13 @@
         <v>0.01626</v>
       </c>
       <c r="H199" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="I199" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="I199" s="1" t="n">
-        <v>0.01626</v>
+      <c r="J199" s="1" t="n">
+        <v>0.01621</v>
       </c>
     </row>
     <row r="200">
@@ -6640,9 +7240,12 @@
         <v>0.2979</v>
       </c>
       <c r="H200" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="I200" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="I200" s="1" t="n">
+      <c r="J200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -6671,9 +7274,12 @@
         <v>0.006236</v>
       </c>
       <c r="H201" s="1" t="n">
+        <v>0.006234</v>
+      </c>
+      <c r="I201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="I201" s="1" t="n">
+      <c r="J201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -6702,9 +7308,12 @@
         <v>0.0004464</v>
       </c>
       <c r="H202" s="1" t="n">
+        <v>0.0004457</v>
+      </c>
+      <c r="I202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="I202" s="1" t="n">
+      <c r="J202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -6733,9 +7342,12 @@
         <v>0.007364</v>
       </c>
       <c r="H203" s="1" t="n">
+        <v>0.007354</v>
+      </c>
+      <c r="I203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="I203" s="1" t="n">
+      <c r="J203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -6764,9 +7376,12 @@
         <v>0.1301</v>
       </c>
       <c r="H204" s="1" t="n">
-        <v>0.1301</v>
+        <v>0.1305</v>
       </c>
       <c r="I204" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="J204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -6795,9 +7410,12 @@
         <v>0.01442</v>
       </c>
       <c r="H205" s="1" t="n">
+        <v>0.01445</v>
+      </c>
+      <c r="I205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="I205" s="1" t="n">
+      <c r="J205" s="1" t="n">
         <v>0.01442</v>
       </c>
     </row>
@@ -6826,9 +7444,12 @@
         <v>0.003586</v>
       </c>
       <c r="H206" s="1" t="n">
+        <v>0.003591</v>
+      </c>
+      <c r="I206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="I206" s="1" t="n">
+      <c r="J206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -6857,9 +7478,12 @@
         <v>0.05947</v>
       </c>
       <c r="H207" s="1" t="n">
+        <v>0.05948</v>
+      </c>
+      <c r="I207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="I207" s="1" t="n">
+      <c r="J207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -6888,9 +7512,12 @@
         <v>15.49</v>
       </c>
       <c r="H208" s="1" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="I208" s="1" t="n">
         <v>15.49</v>
       </c>
-      <c r="I208" s="1" t="n">
+      <c r="J208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -6919,9 +7546,12 @@
         <v>5185.8</v>
       </c>
       <c r="H209" s="1" t="n">
-        <v>5186.2</v>
+        <v>5186.8</v>
       </c>
       <c r="I209" s="1" t="n">
+        <v>5186.8</v>
+      </c>
+      <c r="J209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -6950,9 +7580,12 @@
         <v>0.11994</v>
       </c>
       <c r="H210" s="1" t="n">
+        <v>0.11991</v>
+      </c>
+      <c r="I210" s="1" t="n">
         <v>0.12042</v>
       </c>
-      <c r="I210" s="1" t="n">
+      <c r="J210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -6981,9 +7614,12 @@
         <v>0.1822</v>
       </c>
       <c r="H211" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="I211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="I211" s="1" t="n">
+      <c r="J211" s="1" t="n">
         <v>0.1822</v>
       </c>
     </row>
@@ -7015,6 +7651,9 @@
         <v>0.0304</v>
       </c>
       <c r="I212" s="1" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="J212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -7043,9 +7682,12 @@
         <v>1.3976</v>
       </c>
       <c r="H213" s="1" t="n">
+        <v>1.3969</v>
+      </c>
+      <c r="I213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="I213" s="1" t="n">
+      <c r="J213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -7074,10 +7716,13 @@
         <v>0.05673</v>
       </c>
       <c r="H214" s="1" t="n">
+        <v>0.05655</v>
+      </c>
+      <c r="I214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="I214" s="1" t="n">
-        <v>0.05658</v>
+      <c r="J214" s="1" t="n">
+        <v>0.05655</v>
       </c>
     </row>
     <row r="215">
@@ -7105,9 +7750,12 @@
         <v>0.04375</v>
       </c>
       <c r="H215" s="1" t="n">
+        <v>0.04377</v>
+      </c>
+      <c r="I215" s="1" t="n">
         <v>0.04385</v>
       </c>
-      <c r="I215" s="1" t="n">
+      <c r="J215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -7136,10 +7784,13 @@
         <v>0.15045</v>
       </c>
       <c r="H216" s="1" t="n">
+        <v>0.15029</v>
+      </c>
+      <c r="I216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="I216" s="1" t="n">
-        <v>0.15045</v>
+      <c r="J216" s="1" t="n">
+        <v>0.15029</v>
       </c>
     </row>
     <row r="217">
@@ -7167,9 +7818,12 @@
         <v>0.073</v>
       </c>
       <c r="H217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="I217" s="1" t="n">
+      <c r="J217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -7198,9 +7852,12 @@
         <v>0.00269</v>
       </c>
       <c r="H218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="I218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="I218" s="1" t="n">
+      <c r="J218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -7229,9 +7886,12 @@
         <v>0.01715</v>
       </c>
       <c r="H219" s="1" t="n">
+        <v>0.01715</v>
+      </c>
+      <c r="I219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="I219" s="1" t="n">
+      <c r="J219" s="1" t="n">
         <v>0.01715</v>
       </c>
     </row>
@@ -7260,9 +7920,12 @@
         <v>0.05535</v>
       </c>
       <c r="H220" s="1" t="n">
+        <v>0.05514</v>
+      </c>
+      <c r="I220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="I220" s="1" t="n">
+      <c r="J220" s="1" t="n">
         <v>0.05509</v>
       </c>
     </row>
@@ -7291,9 +7954,12 @@
         <v>0.02196</v>
       </c>
       <c r="H221" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="I221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="I221" s="1" t="n">
+      <c r="J221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -7322,9 +7988,12 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="H222" s="1" t="n">
+        <v>0.00936</v>
+      </c>
+      <c r="I222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="I222" s="1" t="n">
+      <c r="J222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -7358,6 +8027,9 @@
       <c r="I223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="J223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7384,9 +8056,12 @@
         <v>0.03834</v>
       </c>
       <c r="H224" s="1" t="n">
+        <v>0.03823</v>
+      </c>
+      <c r="I224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="I224" s="1" t="n">
+      <c r="J224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -7415,10 +8090,13 @@
         <v>0.001528</v>
       </c>
       <c r="H225" s="1" t="n">
+        <v>0.001525</v>
+      </c>
+      <c r="I225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="I225" s="1" t="n">
-        <v>0.001526</v>
+      <c r="J225" s="1" t="n">
+        <v>0.001525</v>
       </c>
     </row>
     <row r="226">
@@ -7446,10 +8124,13 @@
         <v>26.95</v>
       </c>
       <c r="H226" s="1" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="I226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="I226" s="1" t="n">
-        <v>26.95</v>
+      <c r="J226" s="1" t="n">
+        <v>26.91</v>
       </c>
     </row>
     <row r="227">
@@ -7477,9 +8158,12 @@
         <v>0.0702</v>
       </c>
       <c r="H227" s="1" t="n">
-        <v>0.07027</v>
+        <v>0.07033</v>
       </c>
       <c r="I227" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="J227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -7508,9 +8192,12 @@
         <v>0.313</v>
       </c>
       <c r="H228" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="I228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="I228" s="1" t="n">
+      <c r="J228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -7539,9 +8226,12 @@
         <v>18.46</v>
       </c>
       <c r="H229" s="1" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="I229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="I229" s="1" t="n">
+      <c r="J229" s="1" t="n">
         <v>18.42</v>
       </c>
     </row>
@@ -7570,10 +8260,13 @@
         <v>0.01938</v>
       </c>
       <c r="H230" s="1" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="I230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="I230" s="1" t="n">
-        <v>0.01932</v>
+      <c r="J230" s="1" t="n">
+        <v>0.01928</v>
       </c>
     </row>
     <row r="231">
@@ -7601,10 +8294,13 @@
         <v>0.01221</v>
       </c>
       <c r="H231" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="I231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="I231" s="1" t="n">
-        <v>0.01221</v>
+      <c r="J231" s="1" t="n">
+        <v>0.01218</v>
       </c>
     </row>
     <row r="232">
@@ -7632,10 +8328,13 @@
         <v>0.2286</v>
       </c>
       <c r="H232" s="1" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="I232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="I232" s="1" t="n">
-        <v>0.2285</v>
+      <c r="J232" s="1" t="n">
+        <v>0.2284</v>
       </c>
     </row>
     <row r="233">
@@ -7663,10 +8362,13 @@
         <v>0.07103</v>
       </c>
       <c r="H233" s="1" t="n">
+        <v>0.07092</v>
+      </c>
+      <c r="I233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="I233" s="1" t="n">
-        <v>0.07101</v>
+      <c r="J233" s="1" t="n">
+        <v>0.07092</v>
       </c>
     </row>
     <row r="234">
@@ -7694,10 +8396,13 @@
         <v>0.1701</v>
       </c>
       <c r="H234" s="1" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="I234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="I234" s="1" t="n">
-        <v>0.1701</v>
+      <c r="J234" s="1" t="n">
+        <v>0.1699</v>
       </c>
     </row>
     <row r="235">
@@ -7728,6 +8433,9 @@
         <v>0.0253</v>
       </c>
       <c r="I235" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="J235" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -7756,10 +8464,13 @@
         <v>0.03004</v>
       </c>
       <c r="H236" s="1" t="n">
+        <v>0.03003</v>
+      </c>
+      <c r="I236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="I236" s="1" t="n">
-        <v>0.03004</v>
+      <c r="J236" s="1" t="n">
+        <v>0.03003</v>
       </c>
     </row>
     <row r="237">
@@ -7787,9 +8498,12 @@
         <v>1.988</v>
       </c>
       <c r="H237" s="1" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="I237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="I237" s="1" t="n">
+      <c r="J237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -7818,9 +8532,12 @@
         <v>0.4278</v>
       </c>
       <c r="H238" s="1" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="I238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="I238" s="1" t="n">
+      <c r="J238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -7849,10 +8566,13 @@
         <v>0.03351</v>
       </c>
       <c r="H239" s="1" t="n">
+        <v>0.03328</v>
+      </c>
+      <c r="I239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="I239" s="1" t="n">
-        <v>0.03343</v>
+      <c r="J239" s="1" t="n">
+        <v>0.03328</v>
       </c>
     </row>
     <row r="240">
@@ -7883,6 +8603,9 @@
         <v>0.0341</v>
       </c>
       <c r="I240" s="1" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="J240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -7911,9 +8634,12 @@
         <v>0.0007541</v>
       </c>
       <c r="H241" s="1" t="n">
+        <v>0.0007538999999999999</v>
+      </c>
+      <c r="I241" s="1" t="n">
         <v>0.0007551</v>
       </c>
-      <c r="I241" s="1" t="n">
+      <c r="J241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -7942,9 +8668,12 @@
         <v>0.184</v>
       </c>
       <c r="H242" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="I242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="I242" s="1" t="n">
+      <c r="J242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -7973,10 +8702,13 @@
         <v>0.014831</v>
       </c>
       <c r="H243" s="1" t="n">
+        <v>0.014788</v>
+      </c>
+      <c r="I243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="I243" s="1" t="n">
-        <v>0.014816</v>
+      <c r="J243" s="1" t="n">
+        <v>0.014788</v>
       </c>
     </row>
     <row r="244">
@@ -8004,9 +8736,12 @@
         <v>3.08e-05</v>
       </c>
       <c r="H244" s="1" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="I244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="I244" s="1" t="n">
+      <c r="J244" s="1" t="n">
         <v>3.08e-05</v>
       </c>
     </row>
@@ -8035,10 +8770,13 @@
         <v>0.03522</v>
       </c>
       <c r="H245" s="1" t="n">
+        <v>0.03516</v>
+      </c>
+      <c r="I245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="I245" s="1" t="n">
-        <v>0.03521</v>
+      <c r="J245" s="1" t="n">
+        <v>0.03516</v>
       </c>
     </row>
     <row r="246">
@@ -8066,9 +8804,12 @@
         <v>0.08071</v>
       </c>
       <c r="H246" s="1" t="n">
+        <v>0.08058</v>
+      </c>
+      <c r="I246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="I246" s="1" t="n">
+      <c r="J246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -8097,9 +8838,12 @@
         <v>0.00728</v>
       </c>
       <c r="H247" s="1" t="n">
+        <v>0.007333</v>
+      </c>
+      <c r="I247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="I247" s="1" t="n">
+      <c r="J247" s="1" t="n">
         <v>0.00728</v>
       </c>
     </row>
@@ -8128,9 +8872,12 @@
         <v>0.09583</v>
       </c>
       <c r="H248" s="1" t="n">
+        <v>0.09558</v>
+      </c>
+      <c r="I248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="I248" s="1" t="n">
+      <c r="J248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -8159,9 +8906,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="H249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="I249" s="1" t="n">
+      <c r="J249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -8190,10 +8940,13 @@
         <v>0.03509</v>
       </c>
       <c r="H250" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="I250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="I250" s="1" t="n">
-        <v>0.03504</v>
+      <c r="J250" s="1" t="n">
+        <v>0.03498</v>
       </c>
     </row>
     <row r="251">
@@ -8221,9 +8974,12 @@
         <v>0.04083</v>
       </c>
       <c r="H251" s="1" t="n">
+        <v>0.04058</v>
+      </c>
+      <c r="I251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="I251" s="1" t="n">
+      <c r="J251" s="1" t="n">
         <v>0.04058</v>
       </c>
     </row>
@@ -8252,10 +9008,13 @@
         <v>0.0891</v>
       </c>
       <c r="H252" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="I252" s="1" t="n">
         <v>0.08939999999999999</v>
       </c>
-      <c r="I252" s="1" t="n">
-        <v>0.0891</v>
+      <c r="J252" s="1" t="n">
+        <v>0.089</v>
       </c>
     </row>
     <row r="253">
@@ -8283,9 +9042,12 @@
         <v>4.096</v>
       </c>
       <c r="H253" s="1" t="n">
+        <v>4.093</v>
+      </c>
+      <c r="I253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="I253" s="1" t="n">
+      <c r="J253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -8314,9 +9076,12 @@
         <v>0.1875</v>
       </c>
       <c r="H254" s="1" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="I254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="I254" s="1" t="n">
+      <c r="J254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -8345,9 +9110,12 @@
         <v>0.07214</v>
       </c>
       <c r="H255" s="1" t="n">
+        <v>0.07221</v>
+      </c>
+      <c r="I255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="I255" s="1" t="n">
+      <c r="J255" s="1" t="n">
         <v>0.07214</v>
       </c>
     </row>
@@ -8376,9 +9144,12 @@
         <v>0.01831</v>
       </c>
       <c r="H256" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="I256" s="1" t="n">
         <v>0.01831</v>
       </c>
-      <c r="I256" s="1" t="n">
+      <c r="J256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -8407,9 +9178,12 @@
         <v>5.964</v>
       </c>
       <c r="H257" s="1" t="n">
+        <v>5.954</v>
+      </c>
+      <c r="I257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="I257" s="1" t="n">
+      <c r="J257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -8438,9 +9212,12 @@
         <v>0.2624</v>
       </c>
       <c r="H258" s="1" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="I258" s="1" t="n">
         <v>0.2639</v>
       </c>
-      <c r="I258" s="1" t="n">
+      <c r="J258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -8469,9 +9246,12 @@
         <v>0.1365</v>
       </c>
       <c r="H259" s="1" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="I259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="I259" s="1" t="n">
+      <c r="J259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -8500,9 +9280,12 @@
         <v>0.30612</v>
       </c>
       <c r="H260" s="1" t="n">
-        <v>0.30612</v>
+        <v>0.3062</v>
       </c>
       <c r="I260" s="1" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="J260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -8534,6 +9317,9 @@
         <v>0.09878000000000001</v>
       </c>
       <c r="I261" s="1" t="n">
+        <v>0.09878000000000001</v>
+      </c>
+      <c r="J261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -8562,9 +9348,12 @@
         <v>0.5426</v>
       </c>
       <c r="H262" s="1" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="I262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="I262" s="1" t="n">
+      <c r="J262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -8593,9 +9382,12 @@
         <v>0.2926</v>
       </c>
       <c r="H263" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="I263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="I263" s="1" t="n">
+      <c r="J263" s="1" t="n">
         <v>0.2923</v>
       </c>
     </row>
@@ -8624,9 +9416,12 @@
         <v>0.952</v>
       </c>
       <c r="H264" s="1" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="I264" s="1" t="n">
         <v>0.953</v>
       </c>
-      <c r="I264" s="1" t="n">
+      <c r="J264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -8655,10 +9450,13 @@
         <v>0.5417</v>
       </c>
       <c r="H265" s="1" t="n">
+        <v>0.5403</v>
+      </c>
+      <c r="I265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="I265" s="1" t="n">
-        <v>0.5405</v>
+      <c r="J265" s="1" t="n">
+        <v>0.5403</v>
       </c>
     </row>
     <row r="266">
@@ -8686,9 +9484,12 @@
         <v>0.07396999999999999</v>
       </c>
       <c r="H266" s="1" t="n">
+        <v>0.07384</v>
+      </c>
+      <c r="I266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="I266" s="1" t="n">
+      <c r="J266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -8717,9 +9518,12 @@
         <v>0.02151</v>
       </c>
       <c r="H267" s="1" t="n">
-        <v>0.02151</v>
+        <v>0.02159</v>
       </c>
       <c r="I267" s="1" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="J267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -8748,9 +9552,12 @@
         <v>0.01633</v>
       </c>
       <c r="H268" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="I268" s="1" t="n">
         <v>0.01633</v>
       </c>
-      <c r="I268" s="1" t="n">
+      <c r="J268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -8779,9 +9586,12 @@
         <v>0.003706</v>
       </c>
       <c r="H269" s="1" t="n">
+        <v>0.003714</v>
+      </c>
+      <c r="I269" s="1" t="n">
         <v>0.003717</v>
       </c>
-      <c r="I269" s="1" t="n">
+      <c r="J269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -8810,9 +9620,12 @@
         <v>0.0077</v>
       </c>
       <c r="H270" s="1" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="I270" s="1" t="n">
+      <c r="J270" s="1" t="n">
         <v>0.00769</v>
       </c>
     </row>
@@ -8841,9 +9654,12 @@
         <v>0.05512</v>
       </c>
       <c r="H271" s="1" t="n">
+        <v>0.05507</v>
+      </c>
+      <c r="I271" s="1" t="n">
         <v>0.05512</v>
       </c>
-      <c r="I271" s="1" t="n">
+      <c r="J271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -8872,9 +9688,12 @@
         <v>2.318</v>
       </c>
       <c r="H272" s="1" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="I272" s="1" t="n">
+      <c r="J272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -8903,9 +9722,12 @@
         <v>0.05471</v>
       </c>
       <c r="H273" s="1" t="n">
+        <v>0.05462</v>
+      </c>
+      <c r="I273" s="1" t="n">
         <v>0.05471</v>
       </c>
-      <c r="I273" s="1" t="n">
+      <c r="J273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -8934,9 +9756,12 @@
         <v>0.02286</v>
       </c>
       <c r="H274" s="1" t="n">
-        <v>0.02291</v>
+        <v>0.02303</v>
       </c>
       <c r="I274" s="1" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="J274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -8965,9 +9790,12 @@
         <v>1.183</v>
       </c>
       <c r="H275" s="1" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="I275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="I275" s="1" t="n">
+      <c r="J275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -8996,9 +9824,12 @@
         <v>0.2722</v>
       </c>
       <c r="H276" s="1" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="I276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="I276" s="1" t="n">
+      <c r="J276" s="1" t="n">
         <v>0.2722</v>
       </c>
     </row>
@@ -9027,9 +9858,12 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="H277" s="1" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="I277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="I277" s="1" t="n">
+      <c r="J277" s="1" t="n">
         <v>0.9419999999999999</v>
       </c>
     </row>
@@ -9058,9 +9892,12 @@
         <v>0.6274999999999999</v>
       </c>
       <c r="H278" s="1" t="n">
+        <v>0.6272</v>
+      </c>
+      <c r="I278" s="1" t="n">
         <v>0.6274999999999999</v>
       </c>
-      <c r="I278" s="1" t="n">
+      <c r="J278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -9089,10 +9926,13 @@
         <v>0.001354</v>
       </c>
       <c r="H279" s="1" t="n">
+        <v>0.001346</v>
+      </c>
+      <c r="I279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="I279" s="1" t="n">
-        <v>0.00135</v>
+      <c r="J279" s="1" t="n">
+        <v>0.001346</v>
       </c>
     </row>
     <row r="280">
@@ -9120,9 +9960,12 @@
         <v>0.005557</v>
       </c>
       <c r="H280" s="1" t="n">
+        <v>0.005553</v>
+      </c>
+      <c r="I280" s="1" t="n">
         <v>0.005557</v>
       </c>
-      <c r="I280" s="1" t="n">
+      <c r="J280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -9151,9 +9994,12 @@
         <v>1.522</v>
       </c>
       <c r="H281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="I281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="I281" s="1" t="n">
+      <c r="J281" s="1" t="n">
         <v>1.522</v>
       </c>
     </row>
@@ -9182,9 +10028,12 @@
         <v>28.4</v>
       </c>
       <c r="H282" s="1" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="I282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="I282" s="1" t="n">
+      <c r="J282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -9213,10 +10062,13 @@
         <v>0.12935</v>
       </c>
       <c r="H283" s="1" t="n">
+        <v>0.12892</v>
+      </c>
+      <c r="I283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="I283" s="1" t="n">
-        <v>0.12922</v>
+      <c r="J283" s="1" t="n">
+        <v>0.12892</v>
       </c>
     </row>
     <row r="284">
@@ -9244,9 +10096,12 @@
         <v>0.01116</v>
       </c>
       <c r="H284" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="I284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="I284" s="1" t="n">
+      <c r="J284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -9275,9 +10130,12 @@
         <v>6.542</v>
       </c>
       <c r="H285" s="1" t="n">
+        <v>6.542</v>
+      </c>
+      <c r="I285" s="1" t="n">
         <v>6.544</v>
       </c>
-      <c r="I285" s="1" t="n">
+      <c r="J285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -9306,9 +10164,12 @@
         <v>0.01855</v>
       </c>
       <c r="H286" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="I286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="I286" s="1" t="n">
+      <c r="J286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -9337,9 +10198,12 @@
         <v>0.008416999999999999</v>
       </c>
       <c r="H287" s="1" t="n">
+        <v>0.00842</v>
+      </c>
+      <c r="I287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="I287" s="1" t="n">
+      <c r="J287" s="1" t="n">
         <v>0.008404999999999999</v>
       </c>
     </row>
@@ -9368,10 +10232,13 @@
         <v>0.3856</v>
       </c>
       <c r="H288" s="1" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="I288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="I288" s="1" t="n">
-        <v>0.3856</v>
+      <c r="J288" s="1" t="n">
+        <v>0.3846</v>
       </c>
     </row>
     <row r="289">
@@ -9399,10 +10266,13 @@
         <v>0.010213</v>
       </c>
       <c r="H289" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="I289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="I289" s="1" t="n">
-        <v>0.010213</v>
+      <c r="J289" s="1" t="n">
+        <v>0.01008</v>
       </c>
     </row>
     <row r="290">
@@ -9430,9 +10300,12 @@
         <v>0.02622</v>
       </c>
       <c r="H290" s="1" t="n">
+        <v>0.02618</v>
+      </c>
+      <c r="I290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="I290" s="1" t="n">
+      <c r="J290" s="1" t="n">
         <v>0.02613</v>
       </c>
     </row>
@@ -9464,6 +10337,9 @@
         <v>0.097</v>
       </c>
       <c r="I291" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -9492,9 +10368,12 @@
         <v>0.28507</v>
       </c>
       <c r="H292" s="1" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="I292" s="1" t="n">
         <v>0.2861</v>
       </c>
-      <c r="I292" s="1" t="n">
+      <c r="J292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -9523,9 +10402,12 @@
         <v>0.01543</v>
       </c>
       <c r="H293" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="I293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="I293" s="1" t="n">
+      <c r="J293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -9554,9 +10436,12 @@
         <v>0.003425</v>
       </c>
       <c r="H294" s="1" t="n">
+        <v>0.003423</v>
+      </c>
+      <c r="I294" s="1" t="n">
         <v>0.003425</v>
       </c>
-      <c r="I294" s="1" t="n">
+      <c r="J294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -9585,10 +10470,13 @@
         <v>0.043361</v>
       </c>
       <c r="H295" s="1" t="n">
+        <v>0.043213</v>
+      </c>
+      <c r="I295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="I295" s="1" t="n">
-        <v>0.043361</v>
+      <c r="J295" s="1" t="n">
+        <v>0.043213</v>
       </c>
     </row>
     <row r="296">
@@ -9616,10 +10504,13 @@
         <v>0.02941</v>
       </c>
       <c r="H296" s="1" t="n">
+        <v>0.02929</v>
+      </c>
+      <c r="I296" s="1" t="n">
         <v>0.03007</v>
       </c>
-      <c r="I296" s="1" t="n">
-        <v>0.02941</v>
+      <c r="J296" s="1" t="n">
+        <v>0.02929</v>
       </c>
     </row>
     <row r="297">
@@ -9647,9 +10538,12 @@
         <v>0.03786</v>
       </c>
       <c r="H297" s="1" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="I297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="I297" s="1" t="n">
+      <c r="J297" s="1" t="n">
         <v>0.03786</v>
       </c>
     </row>
@@ -9678,9 +10572,12 @@
         <v>0.08341999999999999</v>
       </c>
       <c r="H298" s="1" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="I298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="I298" s="1" t="n">
+      <c r="J298" s="1" t="n">
         <v>0.08305999999999999</v>
       </c>
     </row>
@@ -9709,9 +10606,12 @@
         <v>0.00761</v>
       </c>
       <c r="H299" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I299" s="1" t="n">
         <v>0.00766</v>
       </c>
-      <c r="I299" s="1" t="n">
+      <c r="J299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -9740,10 +10640,13 @@
         <v>0.01522</v>
       </c>
       <c r="H300" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="I300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="I300" s="1" t="n">
-        <v>0.01519</v>
+      <c r="J300" s="1" t="n">
+        <v>0.01513</v>
       </c>
     </row>
     <row r="301">
@@ -9771,9 +10674,12 @@
         <v>0.1411</v>
       </c>
       <c r="H301" s="1" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="I301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="I301" s="1" t="n">
+      <c r="J301" s="1" t="n">
         <v>0.141</v>
       </c>
     </row>
@@ -9802,10 +10708,13 @@
         <v>0.0006305</v>
       </c>
       <c r="H302" s="1" t="n">
+        <v>0.0006304</v>
+      </c>
+      <c r="I302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="I302" s="1" t="n">
-        <v>0.0006305</v>
+      <c r="J302" s="1" t="n">
+        <v>0.0006304</v>
       </c>
     </row>
     <row r="303">
@@ -9833,9 +10742,12 @@
         <v>0.06227</v>
       </c>
       <c r="H303" s="1" t="n">
+        <v>0.06218</v>
+      </c>
+      <c r="I303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="I303" s="1" t="n">
+      <c r="J303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -9864,9 +10776,12 @@
         <v>0.0001632</v>
       </c>
       <c r="H304" s="1" t="n">
+        <v>0.0001633</v>
+      </c>
+      <c r="I304" s="1" t="n">
         <v>0.0001639</v>
       </c>
-      <c r="I304" s="1" t="n">
+      <c r="J304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -9895,9 +10810,12 @@
         <v>0.06144</v>
       </c>
       <c r="H305" s="1" t="n">
+        <v>0.06125</v>
+      </c>
+      <c r="I305" s="1" t="n">
         <v>0.06144</v>
       </c>
-      <c r="I305" s="1" t="n">
+      <c r="J305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -9926,9 +10844,12 @@
         <v>0.022443</v>
       </c>
       <c r="H306" s="1" t="n">
+        <v>0.022359</v>
+      </c>
+      <c r="I306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="I306" s="1" t="n">
+      <c r="J306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -9957,9 +10878,12 @@
         <v>0.02332</v>
       </c>
       <c r="H307" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="I307" s="1" t="n">
         <v>0.02414</v>
       </c>
-      <c r="I307" s="1" t="n">
+      <c r="J307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -9988,9 +10912,12 @@
         <v>0.000411</v>
       </c>
       <c r="H308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="I308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="I308" s="1" t="n">
+      <c r="J308" s="1" t="n">
         <v>0.000411</v>
       </c>
     </row>
@@ -10019,9 +10946,12 @@
         <v>0.0898</v>
       </c>
       <c r="H309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="I309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="I309" s="1" t="n">
+      <c r="J309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -10050,9 +10980,12 @@
         <v>0.3843</v>
       </c>
       <c r="H310" s="1" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="I310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="I310" s="1" t="n">
+      <c r="J310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -10081,10 +11014,13 @@
         <v>0.0356</v>
       </c>
       <c r="H311" s="1" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="I311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="I311" s="1" t="n">
-        <v>0.0356</v>
+      <c r="J311" s="1" t="n">
+        <v>0.0355</v>
       </c>
     </row>
     <row r="312">
@@ -10112,9 +11048,12 @@
         <v>0.02478</v>
       </c>
       <c r="H312" s="1" t="n">
+        <v>0.02472</v>
+      </c>
+      <c r="I312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="I312" s="1" t="n">
+      <c r="J312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -10143,10 +11082,13 @@
         <v>0.04131</v>
       </c>
       <c r="H313" s="1" t="n">
+        <v>0.04129</v>
+      </c>
+      <c r="I313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="I313" s="1" t="n">
-        <v>0.04131</v>
+      <c r="J313" s="1" t="n">
+        <v>0.04129</v>
       </c>
     </row>
     <row r="314">
@@ -10174,9 +11116,12 @@
         <v>4.012</v>
       </c>
       <c r="H314" s="1" t="n">
+        <v>4.004</v>
+      </c>
+      <c r="I314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="I314" s="1" t="n">
+      <c r="J314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -10205,9 +11150,12 @@
         <v>0.1603</v>
       </c>
       <c r="H315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="I315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="I315" s="1" t="n">
+      <c r="J315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -10236,9 +11184,12 @@
         <v>0.08884</v>
       </c>
       <c r="H316" s="1" t="n">
+        <v>0.08873</v>
+      </c>
+      <c r="I316" s="1" t="n">
         <v>0.08884</v>
       </c>
-      <c r="I316" s="1" t="n">
+      <c r="J316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -10267,9 +11218,12 @@
         <v>0.06847</v>
       </c>
       <c r="H317" s="1" t="n">
-        <v>0.06847</v>
+        <v>0.06849</v>
       </c>
       <c r="I317" s="1" t="n">
+        <v>0.06849</v>
+      </c>
+      <c r="J317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -10298,10 +11252,13 @@
         <v>0.012549</v>
       </c>
       <c r="H318" s="1" t="n">
+        <v>0.012534</v>
+      </c>
+      <c r="I318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="I318" s="1" t="n">
-        <v>0.012549</v>
+      <c r="J318" s="1" t="n">
+        <v>0.012534</v>
       </c>
     </row>
     <row r="319">
@@ -10329,9 +11286,12 @@
         <v>0.001137</v>
       </c>
       <c r="H319" s="1" t="n">
+        <v>0.001136</v>
+      </c>
+      <c r="I319" s="1" t="n">
         <v>0.001138</v>
       </c>
-      <c r="I319" s="1" t="n">
+      <c r="J319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -10360,9 +11320,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="H320" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="I320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="I320" s="1" t="n">
+      <c r="J320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -10394,6 +11357,9 @@
         <v>0.00527</v>
       </c>
       <c r="I321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="J321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -10422,9 +11388,12 @@
         <v>0.1114</v>
       </c>
       <c r="H322" s="1" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="I322" s="1" t="n">
         <v>0.1116</v>
       </c>
-      <c r="I322" s="1" t="n">
+      <c r="J322" s="1" t="n">
         <v>0.1114</v>
       </c>
     </row>
@@ -10453,9 +11422,12 @@
         <v>0.04274</v>
       </c>
       <c r="H323" s="1" t="n">
-        <v>0.04274</v>
+        <v>0.04277</v>
       </c>
       <c r="I323" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="J323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -10484,9 +11456,12 @@
         <v>0.0179</v>
       </c>
       <c r="H324" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="I324" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="I324" s="1" t="n">
+      <c r="J324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -10515,10 +11490,13 @@
         <v>0.005699</v>
       </c>
       <c r="H325" s="1" t="n">
+        <v>0.00568</v>
+      </c>
+      <c r="I325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="I325" s="1" t="n">
-        <v>0.005689</v>
+      <c r="J325" s="1" t="n">
+        <v>0.00568</v>
       </c>
     </row>
     <row r="326">
@@ -10546,9 +11524,12 @@
         <v>0.001769</v>
       </c>
       <c r="H326" s="1" t="n">
+        <v>0.00177</v>
+      </c>
+      <c r="I326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="I326" s="1" t="n">
+      <c r="J326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -10577,10 +11558,13 @@
         <v>0.04069</v>
       </c>
       <c r="H327" s="1" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="I327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="I327" s="1" t="n">
-        <v>0.04069</v>
+      <c r="J327" s="1" t="n">
+        <v>0.04057</v>
       </c>
     </row>
     <row r="328">
@@ -10608,10 +11592,13 @@
         <v>0.053889</v>
       </c>
       <c r="H328" s="1" t="n">
+        <v>0.053804</v>
+      </c>
+      <c r="I328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="I328" s="1" t="n">
-        <v>0.053889</v>
+      <c r="J328" s="1" t="n">
+        <v>0.053804</v>
       </c>
     </row>
     <row r="329">
@@ -10639,9 +11626,12 @@
         <v>0.2794</v>
       </c>
       <c r="H329" s="1" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="I329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="I329" s="1" t="n">
+      <c r="J329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -10670,9 +11660,12 @@
         <v>0.1601</v>
       </c>
       <c r="H330" s="1" t="n">
+        <v>0.1595</v>
+      </c>
+      <c r="I330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="I330" s="1" t="n">
+      <c r="J330" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -10701,9 +11694,12 @@
         <v>0.05357</v>
       </c>
       <c r="H331" s="1" t="n">
+        <v>0.05353</v>
+      </c>
+      <c r="I331" s="1" t="n">
         <v>0.05358</v>
       </c>
-      <c r="I331" s="1" t="n">
+      <c r="J331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -10732,9 +11728,12 @@
         <v>0.3609</v>
       </c>
       <c r="H332" s="1" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="I332" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="I332" s="1" t="n">
+      <c r="J332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -10763,9 +11762,12 @@
         <v>0.03043</v>
       </c>
       <c r="H333" s="1" t="n">
-        <v>0.03048</v>
+        <v>0.03049</v>
       </c>
       <c r="I333" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="J333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -10797,6 +11799,9 @@
         <v>0.01832</v>
       </c>
       <c r="I334" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="J334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -10828,6 +11833,9 @@
         <v>0.0582</v>
       </c>
       <c r="I335" s="1" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="J335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -10856,9 +11864,12 @@
         <v>0.0917</v>
       </c>
       <c r="H336" s="1" t="n">
+        <v>0.09175999999999999</v>
+      </c>
+      <c r="I336" s="1" t="n">
         <v>0.09182</v>
       </c>
-      <c r="I336" s="1" t="n">
+      <c r="J336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -10887,9 +11898,12 @@
         <v>0.17938</v>
       </c>
       <c r="H337" s="1" t="n">
-        <v>0.17938</v>
+        <v>0.18293</v>
       </c>
       <c r="I337" s="1" t="n">
+        <v>0.18293</v>
+      </c>
+      <c r="J337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -10918,10 +11932,13 @@
         <v>0.0211</v>
       </c>
       <c r="H338" s="1" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="I338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="I338" s="1" t="n">
-        <v>0.0211</v>
+      <c r="J338" s="1" t="n">
+        <v>0.02106</v>
       </c>
     </row>
     <row r="339">
@@ -10949,10 +11966,13 @@
         <v>0.1313</v>
       </c>
       <c r="H339" s="1" t="n">
+        <v>0.1312</v>
+      </c>
+      <c r="I339" s="1" t="n">
         <v>0.1315</v>
       </c>
-      <c r="I339" s="1" t="n">
-        <v>0.1313</v>
+      <c r="J339" s="1" t="n">
+        <v>0.1312</v>
       </c>
     </row>
     <row r="340">
@@ -10980,10 +12000,13 @@
         <v>0.008</v>
       </c>
       <c r="H340" s="1" t="n">
+        <v>0.007946</v>
+      </c>
+      <c r="I340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="I340" s="1" t="n">
-        <v>0.008</v>
+      <c r="J340" s="1" t="n">
+        <v>0.007946</v>
       </c>
     </row>
     <row r="341">
@@ -11011,9 +12034,12 @@
         <v>4.407</v>
       </c>
       <c r="H341" s="1" t="n">
+        <v>4.406</v>
+      </c>
+      <c r="I341" s="1" t="n">
         <v>4.407</v>
       </c>
-      <c r="I341" s="1" t="n">
+      <c r="J341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -11042,9 +12068,12 @@
         <v>0.19329</v>
       </c>
       <c r="H342" s="1" t="n">
+        <v>0.19251</v>
+      </c>
+      <c r="I342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="I342" s="1" t="n">
+      <c r="J342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -11073,9 +12102,12 @@
         <v>0.08325</v>
       </c>
       <c r="H343" s="1" t="n">
+        <v>0.08314000000000001</v>
+      </c>
+      <c r="I343" s="1" t="n">
         <v>0.08325</v>
       </c>
-      <c r="I343" s="1" t="n">
+      <c r="J343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -11104,9 +12136,12 @@
         <v>0.1831</v>
       </c>
       <c r="H344" s="1" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="I344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="I344" s="1" t="n">
+      <c r="J344" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -11135,9 +12170,12 @@
         <v>0.003256</v>
       </c>
       <c r="H345" s="1" t="n">
+        <v>0.00325</v>
+      </c>
+      <c r="I345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="I345" s="1" t="n">
+      <c r="J345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -11166,9 +12204,12 @@
         <v>0.09204</v>
       </c>
       <c r="H346" s="1" t="n">
+        <v>0.09168</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>0.09204</v>
       </c>
-      <c r="I346" s="1" t="n">
+      <c r="J346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -11197,10 +12238,13 @@
         <v>2.252</v>
       </c>
       <c r="H347" s="1" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="I347" s="1" t="n">
-        <v>2.252</v>
+      <c r="J347" s="1" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="348">
@@ -11228,9 +12272,12 @@
         <v>0.3059</v>
       </c>
       <c r="H348" s="1" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="I348" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="I348" s="1" t="n">
+      <c r="J348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -11259,9 +12306,12 @@
         <v>0.02991</v>
       </c>
       <c r="H349" s="1" t="n">
+        <v>0.02988</v>
+      </c>
+      <c r="I349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="I349" s="1" t="n">
+      <c r="J349" s="1" t="n">
         <v>0.02981</v>
       </c>
     </row>
@@ -11290,9 +12340,12 @@
         <v>0.1279</v>
       </c>
       <c r="H350" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="I350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="I350" s="1" t="n">
+      <c r="J350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -11321,9 +12374,12 @@
         <v>0.06729</v>
       </c>
       <c r="H351" s="1" t="n">
+        <v>0.06714000000000001</v>
+      </c>
+      <c r="I351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="I351" s="1" t="n">
+      <c r="J351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -11352,9 +12408,12 @@
         <v>0.06242</v>
       </c>
       <c r="H352" s="1" t="n">
+        <v>0.06241</v>
+      </c>
+      <c r="I352" s="1" t="n">
         <v>0.06251</v>
       </c>
-      <c r="I352" s="1" t="n">
+      <c r="J352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -11383,10 +12442,13 @@
         <v>0.06368</v>
       </c>
       <c r="H353" s="1" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="I353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="I353" s="1" t="n">
-        <v>0.06368</v>
+      <c r="J353" s="1" t="n">
+        <v>0.06353</v>
       </c>
     </row>
     <row r="354">
@@ -11414,9 +12476,12 @@
         <v>0.10509</v>
       </c>
       <c r="H354" s="1" t="n">
-        <v>0.10569</v>
+        <v>0.10603</v>
       </c>
       <c r="I354" s="1" t="n">
+        <v>0.10603</v>
+      </c>
+      <c r="J354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -11445,9 +12510,12 @@
         <v>0.0901</v>
       </c>
       <c r="H355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="I355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="I355" s="1" t="n">
+      <c r="J355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -11476,10 +12544,13 @@
         <v>0.07002</v>
       </c>
       <c r="H356" s="1" t="n">
+        <v>0.06985</v>
+      </c>
+      <c r="I356" s="1" t="n">
         <v>0.07054000000000001</v>
       </c>
-      <c r="I356" s="1" t="n">
-        <v>0.06988</v>
+      <c r="J356" s="1" t="n">
+        <v>0.06985</v>
       </c>
     </row>
     <row r="357">
@@ -11507,9 +12578,12 @@
         <v>0.4544</v>
       </c>
       <c r="H357" s="1" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="I357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="I357" s="1" t="n">
+      <c r="J357" s="1" t="n">
         <v>0.4523</v>
       </c>
     </row>
@@ -11538,9 +12612,12 @@
         <v>0.03491</v>
       </c>
       <c r="H358" s="1" t="n">
+        <v>0.03489</v>
+      </c>
+      <c r="I358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="I358" s="1" t="n">
+      <c r="J358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -11569,9 +12646,12 @@
         <v>0.01479</v>
       </c>
       <c r="H359" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="I359" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="I359" s="1" t="n">
+      <c r="J359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -11600,9 +12680,12 @@
         <v>0.13376</v>
       </c>
       <c r="H360" s="1" t="n">
-        <v>0.13376</v>
+        <v>0.13385</v>
       </c>
       <c r="I360" s="1" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="J360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -11631,9 +12714,12 @@
         <v>0.0005913</v>
       </c>
       <c r="H361" s="1" t="n">
+        <v>0.0005902</v>
+      </c>
+      <c r="I361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="I361" s="1" t="n">
+      <c r="J361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -11662,9 +12748,12 @@
         <v>0.03868</v>
       </c>
       <c r="H362" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="I362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="I362" s="1" t="n">
+      <c r="J362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -11693,10 +12782,13 @@
         <v>3.212</v>
       </c>
       <c r="H363" s="1" t="n">
+        <v>3.204</v>
+      </c>
+      <c r="I363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="I363" s="1" t="n">
-        <v>3.207</v>
+      <c r="J363" s="1" t="n">
+        <v>3.204</v>
       </c>
     </row>
     <row r="364">
@@ -11724,10 +12816,13 @@
         <v>0.1658</v>
       </c>
       <c r="H364" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="I364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="I364" s="1" t="n">
-        <v>0.1656</v>
+      <c r="J364" s="1" t="n">
+        <v>0.1655</v>
       </c>
     </row>
     <row r="365">
@@ -11755,9 +12850,12 @@
         <v>0.1136</v>
       </c>
       <c r="H365" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="I365" s="1" t="n">
         <v>0.1136</v>
       </c>
-      <c r="I365" s="1" t="n">
+      <c r="J365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -11786,9 +12884,12 @@
         <v>0.0006442</v>
       </c>
       <c r="H366" s="1" t="n">
-        <v>0.0006445</v>
+        <v>0.0006451</v>
       </c>
       <c r="I366" s="1" t="n">
+        <v>0.0006451</v>
+      </c>
+      <c r="J366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -11817,10 +12918,13 @@
         <v>0.05962</v>
       </c>
       <c r="H367" s="1" t="n">
+        <v>0.05927</v>
+      </c>
+      <c r="I367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="I367" s="1" t="n">
-        <v>0.05956</v>
+      <c r="J367" s="1" t="n">
+        <v>0.05927</v>
       </c>
     </row>
     <row r="368">
@@ -11848,9 +12952,12 @@
         <v>0.08305</v>
       </c>
       <c r="H368" s="1" t="n">
+        <v>0.08286</v>
+      </c>
+      <c r="I368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="I368" s="1" t="n">
+      <c r="J368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -11879,10 +12986,13 @@
         <v>0.03987</v>
       </c>
       <c r="H369" s="1" t="n">
+        <v>0.03976</v>
+      </c>
+      <c r="I369" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="I369" s="1" t="n">
-        <v>0.03979</v>
+      <c r="J369" s="1" t="n">
+        <v>0.03976</v>
       </c>
     </row>
     <row r="370">
@@ -11910,9 +13020,12 @@
         <v>3.718</v>
       </c>
       <c r="H370" s="1" t="n">
+        <v>3.714</v>
+      </c>
+      <c r="I370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="I370" s="1" t="n">
+      <c r="J370" s="1" t="n">
         <v>3.709</v>
       </c>
     </row>
@@ -11941,10 +13054,13 @@
         <v>0.1224</v>
       </c>
       <c r="H371" s="1" t="n">
+        <v>0.1216</v>
+      </c>
+      <c r="I371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="I371" s="1" t="n">
-        <v>0.1222</v>
+      <c r="J371" s="1" t="n">
+        <v>0.1216</v>
       </c>
     </row>
     <row r="372">
@@ -11972,9 +13088,12 @@
         <v>0.01479</v>
       </c>
       <c r="H372" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="I372" s="1" t="n">
         <v>0.01479</v>
       </c>
-      <c r="I372" s="1" t="n">
+      <c r="J372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -12003,9 +13122,12 @@
         <v>0.02202</v>
       </c>
       <c r="H373" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="I373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="I373" s="1" t="n">
+      <c r="J373" s="1" t="n">
         <v>0.02192</v>
       </c>
     </row>
@@ -12034,9 +13156,12 @@
         <v>1.859</v>
       </c>
       <c r="H374" s="1" t="n">
-        <v>1.859</v>
+        <v>1.8624</v>
       </c>
       <c r="I374" s="1" t="n">
+        <v>1.8624</v>
+      </c>
+      <c r="J374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -12065,9 +13190,12 @@
         <v>0.02112</v>
       </c>
       <c r="H375" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="I375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="I375" s="1" t="n">
+      <c r="J375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -12096,9 +13224,12 @@
         <v>1.301</v>
       </c>
       <c r="H376" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I376" s="1" t="n">
         <v>1.301</v>
       </c>
-      <c r="I376" s="1" t="n">
+      <c r="J376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -12127,9 +13258,12 @@
         <v>0.283</v>
       </c>
       <c r="H377" s="1" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="I377" s="1" t="n">
+      <c r="J377" s="1" t="n">
         <v>0.283</v>
       </c>
     </row>
@@ -12158,10 +13292,13 @@
         <v>0.01562</v>
       </c>
       <c r="H378" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="I378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="I378" s="1" t="n">
-        <v>0.01558</v>
+      <c r="J378" s="1" t="n">
+        <v>0.01554</v>
       </c>
     </row>
     <row r="379">
@@ -12189,9 +13326,12 @@
         <v>1.5328</v>
       </c>
       <c r="H379" s="1" t="n">
+        <v>1.5293</v>
+      </c>
+      <c r="I379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="I379" s="1" t="n">
+      <c r="J379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -12220,10 +13360,13 @@
         <v>6.965e-05</v>
       </c>
       <c r="H380" s="1" t="n">
+        <v>6.952999999999999e-05</v>
+      </c>
+      <c r="I380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="I380" s="1" t="n">
-        <v>6.955e-05</v>
+      <c r="J380" s="1" t="n">
+        <v>6.952999999999999e-05</v>
       </c>
     </row>
     <row r="381">
@@ -12251,10 +13394,13 @@
         <v>2.551</v>
       </c>
       <c r="H381" s="1" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="I381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="I381" s="1" t="n">
-        <v>2.551</v>
+      <c r="J381" s="1" t="n">
+        <v>2.548</v>
       </c>
     </row>
     <row r="382">
@@ -12282,9 +13428,12 @@
         <v>0.06765</v>
       </c>
       <c r="H382" s="1" t="n">
+        <v>0.06747</v>
+      </c>
+      <c r="I382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="I382" s="1" t="n">
+      <c r="J382" s="1" t="n">
         <v>0.06738</v>
       </c>
     </row>
@@ -12313,9 +13462,12 @@
         <v>0.01727</v>
       </c>
       <c r="H383" s="1" t="n">
+        <v>0.01718</v>
+      </c>
+      <c r="I383" s="1" t="n">
         <v>0.01758</v>
       </c>
-      <c r="I383" s="1" t="n">
+      <c r="J383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -12344,9 +13496,12 @@
         <v>0.05086</v>
       </c>
       <c r="H384" s="1" t="n">
-        <v>0.05086</v>
+        <v>0.05142</v>
       </c>
       <c r="I384" s="1" t="n">
+        <v>0.05142</v>
+      </c>
+      <c r="J384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -12375,9 +13530,12 @@
         <v>7.585</v>
       </c>
       <c r="H385" s="1" t="n">
+        <v>7.584</v>
+      </c>
+      <c r="I385" s="1" t="n">
         <v>7.585</v>
       </c>
-      <c r="I385" s="1" t="n">
+      <c r="J385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -12406,9 +13564,12 @@
         <v>0.003299</v>
       </c>
       <c r="H386" s="1" t="n">
+        <v>0.003293</v>
+      </c>
+      <c r="I386" s="1" t="n">
         <v>0.003299</v>
       </c>
-      <c r="I386" s="1" t="n">
+      <c r="J386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -12437,9 +13598,12 @@
         <v>0.0003843</v>
       </c>
       <c r="H387" s="1" t="n">
+        <v>0.0003839</v>
+      </c>
+      <c r="I387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="I387" s="1" t="n">
+      <c r="J387" s="1" t="n">
         <v>0.0003838</v>
       </c>
     </row>
@@ -12468,9 +13632,12 @@
         <v>0.00967</v>
       </c>
       <c r="H388" s="1" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="I388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="I388" s="1" t="n">
+      <c r="J388" s="1" t="n">
         <v>0.00966</v>
       </c>
     </row>
@@ -12499,9 +13666,12 @@
         <v>0.2884</v>
       </c>
       <c r="H389" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="I389" s="1" t="n">
         <v>0.2891</v>
       </c>
-      <c r="I389" s="1" t="n">
+      <c r="J389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -12530,9 +13700,12 @@
         <v>0.0249</v>
       </c>
       <c r="H390" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="I390" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="I390" s="1" t="n">
+      <c r="J390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -12561,9 +13734,12 @@
         <v>2.832</v>
       </c>
       <c r="H391" s="1" t="n">
-        <v>2.832</v>
+        <v>2.833</v>
       </c>
       <c r="I391" s="1" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="J391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -12592,9 +13768,12 @@
         <v>0.01341</v>
       </c>
       <c r="H392" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="I392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="I392" s="1" t="n">
+      <c r="J392" s="1" t="n">
         <v>0.0134</v>
       </c>
     </row>
@@ -12623,9 +13802,12 @@
         <v>0.00235</v>
       </c>
       <c r="H393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="I393" s="1" t="n">
         <v>0.00236</v>
       </c>
-      <c r="I393" s="1" t="n">
+      <c r="J393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -12654,9 +13836,12 @@
         <v>0.05939</v>
       </c>
       <c r="H394" s="1" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="I394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="I394" s="1" t="n">
+      <c r="J394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -12685,10 +13870,13 @@
         <v>0.0404</v>
       </c>
       <c r="H395" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="I395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="I395" s="1" t="n">
-        <v>0.0404</v>
+      <c r="J395" s="1" t="n">
+        <v>0.0403</v>
       </c>
     </row>
     <row r="396">
@@ -12716,9 +13904,12 @@
         <v>0.09182</v>
       </c>
       <c r="H396" s="1" t="n">
-        <v>0.09188</v>
+        <v>0.09217</v>
       </c>
       <c r="I396" s="1" t="n">
+        <v>0.09217</v>
+      </c>
+      <c r="J396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -12747,9 +13938,12 @@
         <v>0.1521</v>
       </c>
       <c r="H397" s="1" t="n">
+        <v>0.1517</v>
+      </c>
+      <c r="I397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="I397" s="1" t="n">
+      <c r="J397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -12778,9 +13972,12 @@
         <v>0.928</v>
       </c>
       <c r="H398" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="I398" s="1" t="n">
         <v>0.929</v>
       </c>
-      <c r="I398" s="1" t="n">
+      <c r="J398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -12809,9 +14006,12 @@
         <v>0.05249</v>
       </c>
       <c r="H399" s="1" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="I399" s="1" t="n">
         <v>0.0525</v>
       </c>
-      <c r="I399" s="1" t="n">
+      <c r="J399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -12840,9 +14040,12 @@
         <v>2.526</v>
       </c>
       <c r="H400" s="1" t="n">
+        <v>2.521</v>
+      </c>
+      <c r="I400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="I400" s="1" t="n">
+      <c r="J400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -12871,9 +14074,12 @@
         <v>0.01802</v>
       </c>
       <c r="H401" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="I401" s="1" t="n">
+      <c r="J401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -12902,9 +14108,12 @@
         <v>0.08111</v>
       </c>
       <c r="H402" s="1" t="n">
+        <v>0.08075</v>
+      </c>
+      <c r="I402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="I402" s="1" t="n">
+      <c r="J402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -12933,10 +14142,13 @@
         <v>1.249</v>
       </c>
       <c r="H403" s="1" t="n">
+        <v>1.2471</v>
+      </c>
+      <c r="I403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="I403" s="1" t="n">
-        <v>1.2484</v>
+      <c r="J403" s="1" t="n">
+        <v>1.2471</v>
       </c>
     </row>
     <row r="404">
@@ -12964,9 +14176,12 @@
         <v>0.00721</v>
       </c>
       <c r="H404" s="1" t="n">
+        <v>0.00718</v>
+      </c>
+      <c r="I404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="I404" s="1" t="n">
+      <c r="J404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -12995,9 +14210,12 @@
         <v>0.4938</v>
       </c>
       <c r="H405" s="1" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="I405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="I405" s="1" t="n">
+      <c r="J405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -13026,9 +14244,12 @@
         <v>0.01152</v>
       </c>
       <c r="H406" s="1" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="I406" s="1" t="n">
         <v>0.01152</v>
       </c>
-      <c r="I406" s="1" t="n">
+      <c r="J406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -13057,10 +14278,13 @@
         <v>0.04644</v>
       </c>
       <c r="H407" s="1" t="n">
+        <v>0.04633</v>
+      </c>
+      <c r="I407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="I407" s="1" t="n">
-        <v>0.04639</v>
+      <c r="J407" s="1" t="n">
+        <v>0.04633</v>
       </c>
     </row>
     <row r="408">
@@ -13088,9 +14312,12 @@
         <v>0.03959</v>
       </c>
       <c r="H408" s="1" t="n">
+        <v>0.03959</v>
+      </c>
+      <c r="I408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="I408" s="1" t="n">
+      <c r="J408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -13119,10 +14346,13 @@
         <v>0.05273</v>
       </c>
       <c r="H409" s="1" t="n">
+        <v>0.05258</v>
+      </c>
+      <c r="I409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="I409" s="1" t="n">
-        <v>0.05262</v>
+      <c r="J409" s="1" t="n">
+        <v>0.05258</v>
       </c>
     </row>
     <row r="410">
@@ -13150,9 +14380,12 @@
         <v>0.01245</v>
       </c>
       <c r="H410" s="1" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="I410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="I410" s="1" t="n">
+      <c r="J410" s="1" t="n">
         <v>0.01245</v>
       </c>
     </row>
@@ -13181,9 +14414,12 @@
         <v>0.06404</v>
       </c>
       <c r="H411" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="I411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="I411" s="1" t="n">
+      <c r="J411" s="1" t="n">
         <v>0.06378</v>
       </c>
     </row>
@@ -13212,9 +14448,12 @@
         <v>0.04131</v>
       </c>
       <c r="H412" s="1" t="n">
+        <v>0.04133</v>
+      </c>
+      <c r="I412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="I412" s="1" t="n">
+      <c r="J412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -13246,6 +14485,9 @@
         <v>1.122</v>
       </c>
       <c r="I413" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="J413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -13274,9 +14516,12 @@
         <v>0.2635</v>
       </c>
       <c r="H414" s="1" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="I414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="I414" s="1" t="n">
+      <c r="J414" s="1" t="n">
         <v>0.2633</v>
       </c>
     </row>
@@ -13305,9 +14550,12 @@
         <v>0.001231</v>
       </c>
       <c r="H415" s="1" t="n">
+        <v>0.001225</v>
+      </c>
+      <c r="I415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="I415" s="1" t="n">
+      <c r="J415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -13336,9 +14584,12 @@
         <v>0.03193</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>0.03196</v>
+        <v>0.03198</v>
       </c>
       <c r="I416" s="1" t="n">
+        <v>0.03198</v>
+      </c>
+      <c r="J416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -13367,9 +14618,12 @@
         <v>0.01464</v>
       </c>
       <c r="H417" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="I417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="I417" s="1" t="n">
+      <c r="J417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -13398,9 +14652,12 @@
         <v>0.1483</v>
       </c>
       <c r="H418" s="1" t="n">
-        <v>0.1483</v>
+        <v>0.1484</v>
       </c>
       <c r="I418" s="1" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="J418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -13429,9 +14686,12 @@
         <v>0.04923</v>
       </c>
       <c r="H419" s="1" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="I419" s="1" t="n">
         <v>0.04923</v>
       </c>
-      <c r="I419" s="1" t="n">
+      <c r="J419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -13460,9 +14720,12 @@
         <v>66.58</v>
       </c>
       <c r="H420" s="1" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I420" s="1" t="n">
         <v>66.7</v>
       </c>
-      <c r="I420" s="1" t="n">
+      <c r="J420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -13491,9 +14754,12 @@
         <v>0.879</v>
       </c>
       <c r="H421" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="I421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="I421" s="1" t="n">
+      <c r="J421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -13522,10 +14788,13 @@
         <v>0.01282</v>
       </c>
       <c r="H422" s="1" t="n">
+        <v>0.012788</v>
+      </c>
+      <c r="I422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="I422" s="1" t="n">
-        <v>0.012813</v>
+      <c r="J422" s="1" t="n">
+        <v>0.012788</v>
       </c>
     </row>
     <row r="423">
@@ -13553,9 +14822,12 @@
         <v>0.01595</v>
       </c>
       <c r="H423" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="I423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="I423" s="1" t="n">
+      <c r="J423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -13584,9 +14856,12 @@
         <v>0.26832</v>
       </c>
       <c r="H424" s="1" t="n">
-        <v>0.26855</v>
+        <v>0.27001</v>
       </c>
       <c r="I424" s="1" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="J424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -13615,9 +14890,12 @@
         <v>0.6022999999999999</v>
       </c>
       <c r="H425" s="1" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="I425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="I425" s="1" t="n">
+      <c r="J425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -13646,9 +14924,12 @@
         <v>0.005557</v>
       </c>
       <c r="H426" s="1" t="n">
+        <v>0.005563</v>
+      </c>
+      <c r="I426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="I426" s="1" t="n">
+      <c r="J426" s="1" t="n">
         <v>0.005557</v>
       </c>
     </row>
@@ -13677,9 +14958,12 @@
         <v>0.04902</v>
       </c>
       <c r="H427" s="1" t="n">
+        <v>0.04902</v>
+      </c>
+      <c r="I427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="I427" s="1" t="n">
+      <c r="J427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -13711,6 +14995,9 @@
         <v>0.1265</v>
       </c>
       <c r="I428" s="1" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="J428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -13739,10 +15026,13 @@
         <v>0.003192</v>
       </c>
       <c r="H429" s="1" t="n">
+        <v>0.003165</v>
+      </c>
+      <c r="I429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="I429" s="1" t="n">
-        <v>0.003192</v>
+      <c r="J429" s="1" t="n">
+        <v>0.003165</v>
       </c>
     </row>
     <row r="430">
@@ -13770,10 +15060,13 @@
         <v>0.03656</v>
       </c>
       <c r="H430" s="1" t="n">
+        <v>0.03642</v>
+      </c>
+      <c r="I430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="I430" s="1" t="n">
-        <v>0.03652</v>
+      <c r="J430" s="1" t="n">
+        <v>0.03642</v>
       </c>
     </row>
     <row r="431">
@@ -13801,10 +15094,13 @@
         <v>0.4006</v>
       </c>
       <c r="H431" s="1" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="I431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="I431" s="1" t="n">
-        <v>0.4004</v>
+      <c r="J431" s="1" t="n">
+        <v>0.3997</v>
       </c>
     </row>
     <row r="432">
@@ -13832,9 +15128,12 @@
         <v>0.004518</v>
       </c>
       <c r="H432" s="1" t="n">
+        <v>0.004522</v>
+      </c>
+      <c r="I432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="I432" s="1" t="n">
+      <c r="J432" s="1" t="n">
         <v>0.004518</v>
       </c>
     </row>
@@ -13866,6 +15165,9 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I433" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="J433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -13894,9 +15196,12 @@
         <v>0.01241</v>
       </c>
       <c r="H434" s="1" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="I434" s="1" t="n">
         <v>0.01244</v>
       </c>
-      <c r="I434" s="1" t="n">
+      <c r="J434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -13928,6 +15233,9 @@
         <v>1.983</v>
       </c>
       <c r="I435" s="1" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="J435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -13956,9 +15264,12 @@
         <v>0.001859</v>
       </c>
       <c r="H436" s="1" t="n">
-        <v>0.001859</v>
+        <v>0.001882</v>
       </c>
       <c r="I436" s="1" t="n">
+        <v>0.001882</v>
+      </c>
+      <c r="J436" s="1" t="n">
         <v>0.001833</v>
       </c>
     </row>
@@ -13987,9 +15298,12 @@
         <v>0.4422</v>
       </c>
       <c r="H437" s="1" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="I437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="I437" s="1" t="n">
+      <c r="J437" s="1" t="n">
         <v>0.4417</v>
       </c>
     </row>
@@ -14018,9 +15332,12 @@
         <v>0.00535</v>
       </c>
       <c r="H438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="I438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="I438" s="1" t="n">
+      <c r="J438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -14049,9 +15366,12 @@
         <v>0.1036</v>
       </c>
       <c r="H439" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="I439" s="1" t="n">
         <v>0.1036</v>
       </c>
-      <c r="I439" s="1" t="n">
+      <c r="J439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -14080,9 +15400,12 @@
         <v>0.03432</v>
       </c>
       <c r="H440" s="1" t="n">
+        <v>0.03419</v>
+      </c>
+      <c r="I440" s="1" t="n">
         <v>0.03432</v>
       </c>
-      <c r="I440" s="1" t="n">
+      <c r="J440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -14111,9 +15434,12 @@
         <v>0.08218</v>
       </c>
       <c r="H441" s="1" t="n">
-        <v>0.08218</v>
+        <v>0.08221000000000001</v>
       </c>
       <c r="I441" s="1" t="n">
+        <v>0.08221000000000001</v>
+      </c>
+      <c r="J441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -14142,10 +15468,13 @@
         <v>1.308</v>
       </c>
       <c r="H442" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="I442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="I442" s="1" t="n">
-        <v>1.305</v>
+      <c r="J442" s="1" t="n">
+        <v>1.304</v>
       </c>
     </row>
     <row r="443">
@@ -14176,6 +15505,9 @@
         <v>0.07573000000000001</v>
       </c>
       <c r="I443" s="1" t="n">
+        <v>0.07573000000000001</v>
+      </c>
+      <c r="J443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -14204,9 +15536,12 @@
         <v>0.07693</v>
       </c>
       <c r="H444" s="1" t="n">
+        <v>0.07689</v>
+      </c>
+      <c r="I444" s="1" t="n">
         <v>0.07693</v>
       </c>
-      <c r="I444" s="1" t="n">
+      <c r="J444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -14235,9 +15570,12 @@
         <v>0.04382</v>
       </c>
       <c r="H445" s="1" t="n">
+        <v>0.04363</v>
+      </c>
+      <c r="I445" s="1" t="n">
         <v>0.04386</v>
       </c>
-      <c r="I445" s="1" t="n">
+      <c r="J445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -14266,10 +15604,13 @@
         <v>0.02154</v>
       </c>
       <c r="H446" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="I446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="I446" s="1" t="n">
-        <v>0.02153</v>
+      <c r="J446" s="1" t="n">
+        <v>0.02144</v>
       </c>
     </row>
     <row r="447">
@@ -14297,9 +15638,12 @@
         <v>0.2811</v>
       </c>
       <c r="H447" s="1" t="n">
-        <v>0.2811</v>
+        <v>0.2816</v>
       </c>
       <c r="I447" s="1" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="J447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -14328,10 +15672,13 @@
         <v>0.03124</v>
       </c>
       <c r="H448" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="I448" s="1" t="n">
-        <v>0.03109</v>
+      <c r="J448" s="1" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="449">
@@ -14359,9 +15706,12 @@
         <v>0.00644</v>
       </c>
       <c r="H449" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="I449" s="1" t="n">
         <v>0.00646</v>
       </c>
-      <c r="I449" s="1" t="n">
+      <c r="J449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -14390,9 +15740,12 @@
         <v>0.022865</v>
       </c>
       <c r="H450" s="1" t="n">
+        <v>0.022891</v>
+      </c>
+      <c r="I450" s="1" t="n">
         <v>0.022996</v>
       </c>
-      <c r="I450" s="1" t="n">
+      <c r="J450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -14421,9 +15774,12 @@
         <v>0.04245</v>
       </c>
       <c r="H451" s="1" t="n">
-        <v>0.04245</v>
+        <v>0.0425</v>
       </c>
       <c r="I451" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="J451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -14452,10 +15808,13 @@
         <v>0.07242</v>
       </c>
       <c r="H452" s="1" t="n">
+        <v>0.07213</v>
+      </c>
+      <c r="I452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="I452" s="1" t="n">
-        <v>0.07231</v>
+      <c r="J452" s="1" t="n">
+        <v>0.07213</v>
       </c>
     </row>
     <row r="453">
@@ -14483,9 +15842,12 @@
         <v>0.0005928</v>
       </c>
       <c r="H453" s="1" t="n">
-        <v>0.0005935</v>
+        <v>0.0005939</v>
       </c>
       <c r="I453" s="1" t="n">
+        <v>0.0005939</v>
+      </c>
+      <c r="J453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -14517,6 +15879,9 @@
         <v>0.31</v>
       </c>
       <c r="I454" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -14545,9 +15910,12 @@
         <v>0.004275</v>
       </c>
       <c r="H455" s="1" t="n">
-        <v>0.004275</v>
+        <v>0.004285</v>
       </c>
       <c r="I455" s="1" t="n">
+        <v>0.004285</v>
+      </c>
+      <c r="J455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -14576,10 +15944,13 @@
         <v>0.1836</v>
       </c>
       <c r="H456" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="I456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="I456" s="1" t="n">
-        <v>0.1835</v>
+      <c r="J456" s="1" t="n">
+        <v>0.1833</v>
       </c>
     </row>
     <row r="457">
@@ -14607,10 +15978,13 @@
         <v>0.04281</v>
       </c>
       <c r="H457" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="I457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="I457" s="1" t="n">
-        <v>0.04278</v>
+      <c r="J457" s="1" t="n">
+        <v>0.04277</v>
       </c>
     </row>
     <row r="458">
@@ -14638,9 +16012,12 @@
         <v>0.146</v>
       </c>
       <c r="H458" s="1" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="I458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="I458" s="1" t="n">
+      <c r="J458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -14669,9 +16046,12 @@
         <v>0.008616</v>
       </c>
       <c r="H459" s="1" t="n">
+        <v>0.008607</v>
+      </c>
+      <c r="I459" s="1" t="n">
         <v>0.008616</v>
       </c>
-      <c r="I459" s="1" t="n">
+      <c r="J459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -14700,10 +16080,13 @@
         <v>0.007477</v>
       </c>
       <c r="H460" s="1" t="n">
+        <v>0.007423</v>
+      </c>
+      <c r="I460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="I460" s="1" t="n">
-        <v>0.007458</v>
+      <c r="J460" s="1" t="n">
+        <v>0.007423</v>
       </c>
     </row>
     <row r="461">
@@ -14731,9 +16114,12 @@
         <v>0.000173</v>
       </c>
       <c r="H461" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="I461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="I461" s="1" t="n">
+      <c r="J461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -14765,6 +16151,9 @@
         <v>0.02265</v>
       </c>
       <c r="I462" s="1" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="J462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -14793,9 +16182,12 @@
         <v>0.03748</v>
       </c>
       <c r="H463" s="1" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="I463" s="1" t="n">
         <v>0.03777</v>
       </c>
-      <c r="I463" s="1" t="n">
+      <c r="J463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -14824,9 +16216,12 @@
         <v>0.3046</v>
       </c>
       <c r="H464" s="1" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="I464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="I464" s="1" t="n">
+      <c r="J464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -14855,9 +16250,12 @@
         <v>0.03895</v>
       </c>
       <c r="H465" s="1" t="n">
+        <v>0.03898</v>
+      </c>
+      <c r="I465" s="1" t="n">
         <v>0.03923</v>
       </c>
-      <c r="I465" s="1" t="n">
+      <c r="J465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -14886,10 +16284,13 @@
         <v>2.682</v>
       </c>
       <c r="H466" s="1" t="n">
+        <v>2.675</v>
+      </c>
+      <c r="I466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="I466" s="1" t="n">
-        <v>2.682</v>
+      <c r="J466" s="1" t="n">
+        <v>2.675</v>
       </c>
     </row>
     <row r="467">
@@ -14917,9 +16318,12 @@
         <v>0.03426</v>
       </c>
       <c r="H467" s="1" t="n">
+        <v>0.03433</v>
+      </c>
+      <c r="I467" s="1" t="n">
         <v>0.03435</v>
       </c>
-      <c r="I467" s="1" t="n">
+      <c r="J467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -14948,9 +16352,12 @@
         <v>0.1763</v>
       </c>
       <c r="H468" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="I468" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="I468" s="1" t="n">
+      <c r="J468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -14979,9 +16386,12 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="H469" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="I469" s="1" t="n">
         <v>0.0958</v>
       </c>
-      <c r="I469" s="1" t="n">
+      <c r="J469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -15010,10 +16420,13 @@
         <v>0.06733</v>
       </c>
       <c r="H470" s="1" t="n">
+        <v>0.06732</v>
+      </c>
+      <c r="I470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="I470" s="1" t="n">
-        <v>0.06733</v>
+      <c r="J470" s="1" t="n">
+        <v>0.06732</v>
       </c>
     </row>
     <row r="471">
@@ -15041,9 +16454,12 @@
         <v>0.04004</v>
       </c>
       <c r="H471" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I471" s="1" t="n">
         <v>0.04004</v>
       </c>
-      <c r="I471" s="1" t="n">
+      <c r="J471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -15072,9 +16488,12 @@
         <v>0.2481</v>
       </c>
       <c r="H472" s="1" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="I472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="I472" s="1" t="n">
+      <c r="J472" s="1" t="n">
         <v>0.2475</v>
       </c>
     </row>
@@ -15103,10 +16522,13 @@
         <v>0.016538</v>
       </c>
       <c r="H473" s="1" t="n">
+        <v>0.016503</v>
+      </c>
+      <c r="I473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="I473" s="1" t="n">
-        <v>0.016522</v>
+      <c r="J473" s="1" t="n">
+        <v>0.016503</v>
       </c>
     </row>
     <row r="474">
@@ -15137,6 +16559,9 @@
         <v>0.1157</v>
       </c>
       <c r="I474" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="J474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -15165,9 +16590,12 @@
         <v>0.04286</v>
       </c>
       <c r="H475" s="1" t="n">
+        <v>0.04273</v>
+      </c>
+      <c r="I475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="I475" s="1" t="n">
+      <c r="J475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -15196,9 +16624,12 @@
         <v>0.2078</v>
       </c>
       <c r="H476" s="1" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="I476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="I476" s="1" t="n">
+      <c r="J476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -15227,10 +16658,13 @@
         <v>0.006799</v>
       </c>
       <c r="H477" s="1" t="n">
+        <v>0.006796</v>
+      </c>
+      <c r="I477" s="1" t="n">
         <v>0.006833</v>
       </c>
-      <c r="I477" s="1" t="n">
-        <v>0.006798</v>
+      <c r="J477" s="1" t="n">
+        <v>0.006796</v>
       </c>
     </row>
     <row r="478">
@@ -15258,10 +16692,13 @@
         <v>0.01809</v>
       </c>
       <c r="H478" s="1" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="I478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="I478" s="1" t="n">
-        <v>0.01809</v>
+      <c r="J478" s="1" t="n">
+        <v>0.01799</v>
       </c>
     </row>
     <row r="479">
@@ -15289,10 +16726,13 @@
         <v>0.04691</v>
       </c>
       <c r="H479" s="1" t="n">
+        <v>0.04683</v>
+      </c>
+      <c r="I479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="I479" s="1" t="n">
-        <v>0.04691</v>
+      <c r="J479" s="1" t="n">
+        <v>0.04683</v>
       </c>
     </row>
     <row r="480">
@@ -15320,9 +16760,12 @@
         <v>0.2604</v>
       </c>
       <c r="H480" s="1" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="I480" s="1" t="n">
         <v>0.26166</v>
       </c>
-      <c r="I480" s="1" t="n">
+      <c r="J480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -15351,10 +16794,13 @@
         <v>0.01236</v>
       </c>
       <c r="H481" s="1" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="I481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="I481" s="1" t="n">
-        <v>0.01235</v>
+      <c r="J481" s="1" t="n">
+        <v>0.01234</v>
       </c>
     </row>
     <row r="482">
@@ -15382,9 +16828,12 @@
         <v>0.0041</v>
       </c>
       <c r="H482" s="1" t="n">
-        <v>0.004101</v>
+        <v>0.00413</v>
       </c>
       <c r="I482" s="1" t="n">
+        <v>0.00413</v>
+      </c>
+      <c r="J482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -15413,9 +16862,12 @@
         <v>0.1233</v>
       </c>
       <c r="H483" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="I483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="I483" s="1" t="n">
+      <c r="J483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -15444,9 +16896,12 @@
         <v>0.022</v>
       </c>
       <c r="H484" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="I484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="I484" s="1" t="n">
+      <c r="J484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -15475,9 +16930,12 @@
         <v>0.04548</v>
       </c>
       <c r="H485" s="1" t="n">
+        <v>0.04558</v>
+      </c>
+      <c r="I485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="I485" s="1" t="n">
+      <c r="J485" s="1" t="n">
         <v>0.04548</v>
       </c>
     </row>
@@ -15506,9 +16964,12 @@
         <v>0.1736</v>
       </c>
       <c r="H486" s="1" t="n">
+        <v>0.1733</v>
+      </c>
+      <c r="I486" s="1" t="n">
         <v>0.1736</v>
       </c>
-      <c r="I486" s="1" t="n">
+      <c r="J486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -15537,9 +16998,12 @@
         <v>0.2733</v>
       </c>
       <c r="H487" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="I487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="I487" s="1" t="n">
+      <c r="J487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -15568,9 +17032,12 @@
         <v>0.04621</v>
       </c>
       <c r="H488" s="1" t="n">
+        <v>0.04615</v>
+      </c>
+      <c r="I488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="I488" s="1" t="n">
+      <c r="J488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -15599,9 +17066,12 @@
         <v>0.0002157</v>
       </c>
       <c r="H489" s="1" t="n">
+        <v>0.0002154</v>
+      </c>
+      <c r="I489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="I489" s="1" t="n">
+      <c r="J489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -15630,9 +17100,12 @@
         <v>1.762</v>
       </c>
       <c r="H490" s="1" t="n">
-        <v>1.765</v>
+        <v>1.768</v>
       </c>
       <c r="I490" s="1" t="n">
+        <v>1.768</v>
+      </c>
+      <c r="J490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -15661,9 +17134,12 @@
         <v>16.073</v>
       </c>
       <c r="H491" s="1" t="n">
+        <v>16.065</v>
+      </c>
+      <c r="I491" s="1" t="n">
         <v>16.083</v>
       </c>
-      <c r="I491" s="1" t="n">
+      <c r="J491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -15692,9 +17168,12 @@
         <v>0.06685000000000001</v>
       </c>
       <c r="H492" s="1" t="n">
+        <v>0.0668</v>
+      </c>
+      <c r="I492" s="1" t="n">
         <v>0.06685000000000001</v>
       </c>
-      <c r="I492" s="1" t="n">
+      <c r="J492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -15723,9 +17202,12 @@
         <v>0.06738</v>
       </c>
       <c r="H493" s="1" t="n">
+        <v>0.06736</v>
+      </c>
+      <c r="I493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="I493" s="1" t="n">
+      <c r="J493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -15754,9 +17236,12 @@
         <v>0.009457999999999999</v>
       </c>
       <c r="H494" s="1" t="n">
-        <v>0.009457999999999999</v>
+        <v>0.009471</v>
       </c>
       <c r="I494" s="1" t="n">
+        <v>0.009471</v>
+      </c>
+      <c r="J494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -15785,10 +17270,13 @@
         <v>0.005925</v>
       </c>
       <c r="H495" s="1" t="n">
+        <v>0.005907</v>
+      </c>
+      <c r="I495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="I495" s="1" t="n">
-        <v>0.005925</v>
+      <c r="J495" s="1" t="n">
+        <v>0.005907</v>
       </c>
     </row>
     <row r="496">
@@ -15816,10 +17304,13 @@
         <v>0.00993</v>
       </c>
       <c r="H496" s="1" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="I496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="I496" s="1" t="n">
-        <v>0.00992</v>
+      <c r="J496" s="1" t="n">
+        <v>0.00991</v>
       </c>
     </row>
     <row r="497">
@@ -15847,9 +17338,12 @@
         <v>0.04395</v>
       </c>
       <c r="H497" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="I497" s="1" t="n">
         <v>0.04404</v>
       </c>
-      <c r="I497" s="1" t="n">
+      <c r="J497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -15878,10 +17372,13 @@
         <v>0.006402</v>
       </c>
       <c r="H498" s="1" t="n">
+        <v>0.006394</v>
+      </c>
+      <c r="I498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="I498" s="1" t="n">
-        <v>0.006402</v>
+      <c r="J498" s="1" t="n">
+        <v>0.006394</v>
       </c>
     </row>
     <row r="499">
@@ -15909,9 +17406,12 @@
         <v>0.01049</v>
       </c>
       <c r="H499" s="1" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="I499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="I499" s="1" t="n">
+      <c r="J499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -15940,10 +17440,13 @@
         <v>0.5113</v>
       </c>
       <c r="H500" s="1" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="I500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="I500" s="1" t="n">
-        <v>0.5089</v>
+      <c r="J500" s="1" t="n">
+        <v>0.5076000000000001</v>
       </c>
     </row>
     <row r="501">
@@ -15971,9 +17474,12 @@
         <v>0.03204</v>
       </c>
       <c r="H501" s="1" t="n">
+        <v>0.03204</v>
+      </c>
+      <c r="I501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="I501" s="1" t="n">
+      <c r="J501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -16002,9 +17508,12 @@
         <v>0.4373</v>
       </c>
       <c r="H502" s="1" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="I502" s="1" t="n">
         <v>0.4385</v>
       </c>
-      <c r="I502" s="1" t="n">
+      <c r="J502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -16033,9 +17542,12 @@
         <v>0.999341</v>
       </c>
       <c r="H503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="I503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="I503" s="1" t="n">
+      <c r="J503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -16064,9 +17576,12 @@
         <v>0.03555</v>
       </c>
       <c r="H504" s="1" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="I504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="I504" s="1" t="n">
+      <c r="J504" s="1" t="n">
         <v>0.03525</v>
       </c>
     </row>
@@ -16095,9 +17610,12 @@
         <v>0.004931</v>
       </c>
       <c r="H505" s="1" t="n">
+        <v>0.00493</v>
+      </c>
+      <c r="I505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="I505" s="1" t="n">
+      <c r="J505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -16126,9 +17644,12 @@
         <v>0.01393</v>
       </c>
       <c r="H506" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="I506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="I506" s="1" t="n">
+      <c r="J506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -16157,9 +17678,12 @@
         <v>0.003466</v>
       </c>
       <c r="H507" s="1" t="n">
-        <v>0.003478</v>
+        <v>0.003486</v>
       </c>
       <c r="I507" s="1" t="n">
+        <v>0.003486</v>
+      </c>
+      <c r="J507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -16188,9 +17712,12 @@
         <v>1.421</v>
       </c>
       <c r="H508" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="I508" s="1" t="n">
+      <c r="J508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -16219,9 +17746,12 @@
         <v>0.005077</v>
       </c>
       <c r="H509" s="1" t="n">
+        <v>0.005089</v>
+      </c>
+      <c r="I509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="I509" s="1" t="n">
+      <c r="J509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -16250,9 +17780,12 @@
         <v>0.01577</v>
       </c>
       <c r="H510" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="I510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="I510" s="1" t="n">
+      <c r="J510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -16281,10 +17814,13 @@
         <v>0.08244</v>
       </c>
       <c r="H511" s="1" t="n">
+        <v>0.08212999999999999</v>
+      </c>
+      <c r="I511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="I511" s="1" t="n">
-        <v>0.08244</v>
+      <c r="J511" s="1" t="n">
+        <v>0.08212999999999999</v>
       </c>
     </row>
     <row r="512">
@@ -16312,9 +17848,12 @@
         <v>0.007117</v>
       </c>
       <c r="H512" s="1" t="n">
+        <v>0.007108</v>
+      </c>
+      <c r="I512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="I512" s="1" t="n">
+      <c r="J512" s="1" t="n">
         <v>0.007105</v>
       </c>
     </row>
@@ -16343,9 +17882,12 @@
         <v>0.01482</v>
       </c>
       <c r="H513" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="I513" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="I513" s="1" t="n">
+      <c r="J513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -16374,10 +17916,13 @@
         <v>0.04761</v>
       </c>
       <c r="H514" s="1" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="I514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="I514" s="1" t="n">
-        <v>0.04748</v>
+      <c r="J514" s="1" t="n">
+        <v>0.04736</v>
       </c>
     </row>
     <row r="515">
@@ -16405,9 +17950,12 @@
         <v>0.01822</v>
       </c>
       <c r="H515" s="1" t="n">
+        <v>0.01821</v>
+      </c>
+      <c r="I515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="I515" s="1" t="n">
+      <c r="J515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -16436,9 +17984,12 @@
         <v>0.0005807</v>
       </c>
       <c r="H516" s="1" t="n">
+        <v>0.0005806</v>
+      </c>
+      <c r="I516" s="1" t="n">
         <v>0.0005808</v>
       </c>
-      <c r="I516" s="1" t="n">
+      <c r="J516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -16467,9 +18018,12 @@
         <v>0.07894</v>
       </c>
       <c r="H517" s="1" t="n">
+        <v>0.07874</v>
+      </c>
+      <c r="I517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="I517" s="1" t="n">
+      <c r="J517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -16498,9 +18052,12 @@
         <v>0.006387</v>
       </c>
       <c r="H518" s="1" t="n">
+        <v>0.006379</v>
+      </c>
+      <c r="I518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="I518" s="1" t="n">
+      <c r="J518" s="1" t="n">
         <v>0.006378</v>
       </c>
     </row>
@@ -16529,10 +18086,13 @@
         <v>0.0582</v>
       </c>
       <c r="H519" s="1" t="n">
+        <v>0.05789</v>
+      </c>
+      <c r="I519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="I519" s="1" t="n">
-        <v>0.05803</v>
+      <c r="J519" s="1" t="n">
+        <v>0.05789</v>
       </c>
     </row>
     <row r="520">
@@ -16560,10 +18120,13 @@
         <v>0.10495</v>
       </c>
       <c r="H520" s="1" t="n">
+        <v>0.10489</v>
+      </c>
+      <c r="I520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="I520" s="1" t="n">
-        <v>0.10495</v>
+      <c r="J520" s="1" t="n">
+        <v>0.10489</v>
       </c>
     </row>
     <row r="521">
@@ -16591,9 +18154,12 @@
         <v>0.01799</v>
       </c>
       <c r="H521" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="I521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="I521" s="1" t="n">
+      <c r="J521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -16622,9 +18188,12 @@
         <v>0.01652</v>
       </c>
       <c r="H522" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="I522" s="1" t="n">
         <v>0.01653</v>
       </c>
-      <c r="I522" s="1" t="n">
+      <c r="J522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -16653,9 +18222,12 @@
         <v>0.01093</v>
       </c>
       <c r="H523" s="1" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="I523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="I523" s="1" t="n">
+      <c r="J523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -16684,9 +18256,12 @@
         <v>0.007138</v>
       </c>
       <c r="H524" s="1" t="n">
+        <v>0.007084</v>
+      </c>
+      <c r="I524" s="1" t="n">
         <v>0.007138</v>
       </c>
-      <c r="I524" s="1" t="n">
+      <c r="J524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -16715,10 +18290,13 @@
         <v>0.005946</v>
       </c>
       <c r="H525" s="1" t="n">
+        <v>0.005922</v>
+      </c>
+      <c r="I525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="I525" s="1" t="n">
-        <v>0.005938</v>
+      <c r="J525" s="1" t="n">
+        <v>0.005922</v>
       </c>
     </row>
     <row r="526">
@@ -16746,9 +18324,12 @@
         <v>0.001445</v>
       </c>
       <c r="H526" s="1" t="n">
+        <v>0.001444</v>
+      </c>
+      <c r="I526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="I526" s="1" t="n">
+      <c r="J526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -16777,9 +18358,12 @@
         <v>0.373</v>
       </c>
       <c r="H527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="I527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="I527" s="1" t="n">
+      <c r="J527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -16808,9 +18392,12 @@
         <v>0.00521</v>
       </c>
       <c r="H528" s="1" t="n">
+        <v>0.005187</v>
+      </c>
+      <c r="I528" s="1" t="n">
         <v>0.00521</v>
       </c>
-      <c r="I528" s="1" t="n">
+      <c r="J528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -16839,9 +18426,12 @@
         <v>2.938</v>
       </c>
       <c r="H529" s="1" t="n">
-        <v>2.942</v>
+        <v>2.943</v>
       </c>
       <c r="I529" s="1" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="J529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -16870,9 +18460,12 @@
         <v>0.1558</v>
       </c>
       <c r="H530" s="1" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="I530" s="1" t="n">
         <v>0.156</v>
       </c>
-      <c r="I530" s="1" t="n">
+      <c r="J530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -16901,9 +18494,12 @@
         <v>2535</v>
       </c>
       <c r="H531" s="1" t="n">
+        <v>2534</v>
+      </c>
+      <c r="I531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="I531" s="1" t="n">
+      <c r="J531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -16935,6 +18531,9 @@
         <v>0.03929</v>
       </c>
       <c r="I532" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="J532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -16963,9 +18562,12 @@
         <v>0.02191</v>
       </c>
       <c r="H533" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="I533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="I533" s="1" t="n">
+      <c r="J533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -16994,9 +18596,12 @@
         <v>0.07348</v>
       </c>
       <c r="H534" s="1" t="n">
-        <v>0.07348</v>
+        <v>0.07352</v>
       </c>
       <c r="I534" s="1" t="n">
+        <v>0.07352</v>
+      </c>
+      <c r="J534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -17025,9 +18630,12 @@
         <v>0.007837999999999999</v>
       </c>
       <c r="H535" s="1" t="n">
+        <v>0.007835</v>
+      </c>
+      <c r="I535" s="1" t="n">
         <v>0.007877</v>
       </c>
-      <c r="I535" s="1" t="n">
+      <c r="J535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -17056,9 +18664,12 @@
         <v>0.05025</v>
       </c>
       <c r="H536" s="1" t="n">
+        <v>0.05013</v>
+      </c>
+      <c r="I536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="I536" s="1" t="n">
+      <c r="J536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -17087,9 +18698,12 @@
         <v>0.00406</v>
       </c>
       <c r="H537" s="1" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="I537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="I537" s="1" t="n">
+      <c r="J537" s="1" t="n">
         <v>0.00406</v>
       </c>
     </row>
@@ -17118,9 +18732,12 @@
         <v>0.08305999999999999</v>
       </c>
       <c r="H538" s="1" t="n">
+        <v>0.08289000000000001</v>
+      </c>
+      <c r="I538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="I538" s="1" t="n">
+      <c r="J538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -17149,9 +18766,12 @@
         <v>0.02497</v>
       </c>
       <c r="H539" s="1" t="n">
+        <v>0.02496</v>
+      </c>
+      <c r="I539" s="1" t="n">
         <v>0.02502</v>
       </c>
-      <c r="I539" s="1" t="n">
+      <c r="J539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -17180,9 +18800,12 @@
         <v>0.08497</v>
       </c>
       <c r="H540" s="1" t="n">
+        <v>0.08476</v>
+      </c>
+      <c r="I540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="I540" s="1" t="n">
+      <c r="J540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -17211,10 +18834,13 @@
         <v>0.01897</v>
       </c>
       <c r="H541" s="1" t="n">
+        <v>0.01895</v>
+      </c>
+      <c r="I541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="I541" s="1" t="n">
-        <v>0.01896</v>
+      <c r="J541" s="1" t="n">
+        <v>0.01895</v>
       </c>
     </row>
     <row r="542">
@@ -17242,10 +18868,13 @@
         <v>0.01698</v>
       </c>
       <c r="H542" s="1" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="I542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="I542" s="1" t="n">
-        <v>0.01698</v>
+      <c r="J542" s="1" t="n">
+        <v>0.01694</v>
       </c>
     </row>
     <row r="543">
@@ -17273,9 +18902,12 @@
         <v>0.105</v>
       </c>
       <c r="H543" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="I543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="I543" s="1" t="n">
+      <c r="J543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J543"/>
+  <dimension ref="A1:K543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -427,8 +427,9 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,10 +475,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>price_02:00</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -511,9 +517,12 @@
         <v>70612.3</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>70586.2</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>70545.39999999999</v>
       </c>
     </row>
@@ -545,9 +554,12 @@
         <v>2074.79</v>
       </c>
       <c r="I3" s="1" t="n">
+        <v>2073.98</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -579,9 +591,12 @@
         <v>86.89</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>86.81999999999999</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -613,9 +628,12 @@
         <v>4.104</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>4.022</v>
       </c>
     </row>
@@ -647,10 +665,13 @@
         <v>0.09476999999999999</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>0.09463000000000001</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="J6" s="1" t="n">
-        <v>0.09476999999999999</v>
+      <c r="K6" s="1" t="n">
+        <v>0.09463000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -681,9 +702,12 @@
         <v>1.3896</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>1.3886</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -715,9 +739,12 @@
         <v>22.62</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>22.657</v>
+        <v>22.688</v>
       </c>
       <c r="J8" s="1" t="n">
+        <v>22.688</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -749,10 +776,13 @@
         <v>0.002154</v>
       </c>
       <c r="I9" s="1" t="n">
+        <v>0.002053</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="J9" s="1" t="n">
-        <v>0.002119</v>
+      <c r="K9" s="1" t="n">
+        <v>0.002053</v>
       </c>
     </row>
     <row r="10">
@@ -783,9 +813,12 @@
         <v>0.010215</v>
       </c>
       <c r="I10" s="1" t="n">
+        <v>0.010308</v>
+      </c>
+      <c r="J10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -817,9 +850,12 @@
         <v>0.16454</v>
       </c>
       <c r="I11" s="1" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.15789</v>
       </c>
     </row>
@@ -851,10 +887,13 @@
         <v>0.011639</v>
       </c>
       <c r="I12" s="1" t="n">
+        <v>0.011355</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>0.01154</v>
+      <c r="K12" s="1" t="n">
+        <v>0.011355</v>
       </c>
     </row>
     <row r="13">
@@ -885,9 +924,12 @@
         <v>38.067</v>
       </c>
       <c r="I13" s="1" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -919,9 +961,12 @@
         <v>653.5</v>
       </c>
       <c r="I14" s="1" t="n">
+        <v>653.01</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <v>652.8</v>
       </c>
     </row>
@@ -953,9 +998,12 @@
         <v>209.47</v>
       </c>
       <c r="I15" s="1" t="n">
+        <v>209.21</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <v>209.13</v>
       </c>
     </row>
@@ -987,10 +1035,13 @@
         <v>0.0033394</v>
       </c>
       <c r="I16" s="1" t="n">
+        <v>0.003331</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="J16" s="1" t="n">
-        <v>0.0033394</v>
+      <c r="K16" s="1" t="n">
+        <v>0.003331</v>
       </c>
     </row>
     <row r="17">
@@ -1021,9 +1072,12 @@
         <v>236.78</v>
       </c>
       <c r="I17" s="1" t="n">
+        <v>237.45</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>238.32</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="K17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1055,9 +1109,12 @@
         <v>0.9923</v>
       </c>
       <c r="I18" s="1" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1089,9 +1146,12 @@
         <v>1.0495</v>
       </c>
       <c r="I19" s="1" t="n">
+        <v>1.045</v>
+      </c>
+      <c r="J19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="K19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1123,10 +1183,13 @@
         <v>0.2598</v>
       </c>
       <c r="I20" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="J20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="J20" s="1" t="n">
-        <v>0.2598</v>
+      <c r="K20" s="1" t="n">
+        <v>0.2596</v>
       </c>
     </row>
     <row r="21">
@@ -1157,9 +1220,12 @@
         <v>0.59536</v>
       </c>
       <c r="I21" s="1" t="n">
+        <v>0.59635</v>
+      </c>
+      <c r="J21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="K21" s="1" t="n">
         <v>0.59536</v>
       </c>
     </row>
@@ -1191,9 +1257,12 @@
         <v>9.028</v>
       </c>
       <c r="I22" s="1" t="n">
+        <v>9.000999999999999</v>
+      </c>
+      <c r="J22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1225,9 +1294,12 @@
         <v>0.02415</v>
       </c>
       <c r="I23" s="1" t="n">
+        <v>0.02414</v>
+      </c>
+      <c r="J23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1259,9 +1331,12 @@
         <v>9.576000000000001</v>
       </c>
       <c r="I24" s="1" t="n">
+        <v>9.573</v>
+      </c>
+      <c r="J24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="K24" s="1" t="n">
         <v>9.555999999999999</v>
       </c>
     </row>
@@ -1293,9 +1368,12 @@
         <v>1.228</v>
       </c>
       <c r="I25" s="1" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="J25" s="1" t="n">
         <v>1.228</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="K25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1327,9 +1405,12 @@
         <v>0.0717</v>
       </c>
       <c r="I26" s="1" t="n">
+        <v>0.07152</v>
+      </c>
+      <c r="J26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="K26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1361,9 +1442,12 @@
         <v>1.429</v>
       </c>
       <c r="I27" s="1" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="J27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="K27" s="1" t="n">
         <v>1.424</v>
       </c>
     </row>
@@ -1395,10 +1479,13 @@
         <v>1.308</v>
       </c>
       <c r="I28" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="J28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="J28" s="1" t="n">
-        <v>1.308</v>
+      <c r="K28" s="1" t="n">
+        <v>1.305</v>
       </c>
     </row>
     <row r="29">
@@ -1429,10 +1516,13 @@
         <v>462.93</v>
       </c>
       <c r="I29" s="1" t="n">
+        <v>461.7</v>
+      </c>
+      <c r="J29" s="1" t="n">
         <v>463.21</v>
       </c>
-      <c r="J29" s="1" t="n">
-        <v>461.74</v>
+      <c r="K29" s="1" t="n">
+        <v>461.7</v>
       </c>
     </row>
     <row r="30">
@@ -1463,9 +1553,12 @@
         <v>1.2902</v>
       </c>
       <c r="I30" s="1" t="n">
+        <v>1.2882</v>
+      </c>
+      <c r="J30" s="1" t="n">
         <v>1.2902</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="K30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1497,9 +1590,12 @@
         <v>5024.12</v>
       </c>
       <c r="I31" s="1" t="n">
+        <v>5023.66</v>
+      </c>
+      <c r="J31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="K31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1531,9 +1627,12 @@
         <v>0.875</v>
       </c>
       <c r="I32" s="1" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="J32" s="1" t="n">
         <v>0.877</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="K32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1565,9 +1664,12 @@
         <v>0.001979</v>
       </c>
       <c r="I33" s="1" t="n">
+        <v>0.001979</v>
+      </c>
+      <c r="J33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="K33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1599,9 +1701,12 @@
         <v>0.16824</v>
       </c>
       <c r="I34" s="1" t="n">
+        <v>0.16972</v>
+      </c>
+      <c r="J34" s="1" t="n">
         <v>0.17091</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="K34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -1633,10 +1738,13 @@
         <v>0.2972</v>
       </c>
       <c r="I35" s="1" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="J35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="J35" s="1" t="n">
-        <v>0.2972</v>
+      <c r="K35" s="1" t="n">
+        <v>0.29703</v>
       </c>
     </row>
     <row r="36">
@@ -1667,10 +1775,13 @@
         <v>1.791</v>
       </c>
       <c r="I36" s="1" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="J36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="J36" s="1" t="n">
-        <v>1.787</v>
+      <c r="K36" s="1" t="n">
+        <v>1.786</v>
       </c>
     </row>
     <row r="37">
@@ -1701,9 +1812,12 @@
         <v>110.77</v>
       </c>
       <c r="I37" s="1" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="J37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="K37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1735,10 +1849,13 @@
         <v>0.22175</v>
       </c>
       <c r="I38" s="1" t="n">
+        <v>0.22169</v>
+      </c>
+      <c r="J38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="J38" s="1" t="n">
-        <v>0.22175</v>
+      <c r="K38" s="1" t="n">
+        <v>0.22169</v>
       </c>
     </row>
     <row r="39">
@@ -1769,10 +1886,13 @@
         <v>0.1079</v>
       </c>
       <c r="I39" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="J39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="J39" s="1" t="n">
-        <v>0.1078</v>
+      <c r="K39" s="1" t="n">
+        <v>0.1076</v>
       </c>
     </row>
     <row r="40">
@@ -1803,10 +1923,13 @@
         <v>0.37265</v>
       </c>
       <c r="I40" s="1" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="J40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="J40" s="1" t="n">
-        <v>0.37042</v>
+      <c r="K40" s="1" t="n">
+        <v>0.3694</v>
       </c>
     </row>
     <row r="41">
@@ -1837,9 +1960,12 @@
         <v>54.65</v>
       </c>
       <c r="I41" s="1" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="J41" s="1" t="n">
         <v>54.66</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="K41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -1871,10 +1997,13 @@
         <v>0.0010743</v>
       </c>
       <c r="I42" s="1" t="n">
+        <v>0.0010715</v>
+      </c>
+      <c r="J42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="J42" s="1" t="n">
-        <v>0.0010732</v>
+      <c r="K42" s="1" t="n">
+        <v>0.0010715</v>
       </c>
     </row>
     <row r="43">
@@ -1905,9 +2034,12 @@
         <v>6.466</v>
       </c>
       <c r="I43" s="1" t="n">
+        <v>6.465</v>
+      </c>
+      <c r="J43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="K43" s="1" t="n">
         <v>6.414</v>
       </c>
     </row>
@@ -1939,10 +2071,13 @@
         <v>0.6365</v>
       </c>
       <c r="I44" s="1" t="n">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="J44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="J44" s="1" t="n">
-        <v>0.6365</v>
+      <c r="K44" s="1" t="n">
+        <v>0.6336000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1973,9 +2108,12 @@
         <v>0.3554</v>
       </c>
       <c r="I45" s="1" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="J45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="K45" s="1" t="n">
         <v>0.3539</v>
       </c>
     </row>
@@ -2007,9 +2145,12 @@
         <v>0.03228</v>
       </c>
       <c r="I46" s="1" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="J46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="K46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2041,9 +2182,12 @@
         <v>0.0721</v>
       </c>
       <c r="I47" s="1" t="n">
+        <v>0.07269</v>
+      </c>
+      <c r="J47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="K47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -2075,9 +2219,12 @@
         <v>0.7048</v>
       </c>
       <c r="I48" s="1" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="J48" s="1" t="n">
         <v>0.7060999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="K48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -2109,10 +2256,13 @@
         <v>0.004536</v>
       </c>
       <c r="I49" s="1" t="n">
+        <v>0.004436</v>
+      </c>
+      <c r="J49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="J49" s="1" t="n">
-        <v>0.004518</v>
+      <c r="K49" s="1" t="n">
+        <v>0.004436</v>
       </c>
     </row>
     <row r="50">
@@ -2143,9 +2293,12 @@
         <v>0.1045</v>
       </c>
       <c r="I50" s="1" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="J50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="K50" s="1" t="n">
         <v>0.1041</v>
       </c>
     </row>
@@ -2177,9 +2330,12 @@
         <v>0.0406</v>
       </c>
       <c r="I51" s="1" t="n">
+        <v>0.04052</v>
+      </c>
+      <c r="J51" s="1" t="n">
         <v>0.0406</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="K51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -2211,10 +2367,13 @@
         <v>0.166</v>
       </c>
       <c r="I52" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="J52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="J52" s="1" t="n">
-        <v>0.166</v>
+      <c r="K52" s="1" t="n">
+        <v>0.165</v>
       </c>
     </row>
     <row r="53">
@@ -2245,10 +2404,13 @@
         <v>0.021</v>
       </c>
       <c r="I53" s="1" t="n">
+        <v>0.02021</v>
+      </c>
+      <c r="J53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="J53" s="1" t="n">
-        <v>0.021</v>
+      <c r="K53" s="1" t="n">
+        <v>0.02021</v>
       </c>
     </row>
     <row r="54">
@@ -2279,10 +2441,13 @@
         <v>0.007232</v>
       </c>
       <c r="I54" s="1" t="n">
+        <v>0.00721</v>
+      </c>
+      <c r="J54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="J54" s="1" t="n">
-        <v>0.007221</v>
+      <c r="K54" s="1" t="n">
+        <v>0.00721</v>
       </c>
     </row>
     <row r="55">
@@ -2313,10 +2478,13 @@
         <v>3.921</v>
       </c>
       <c r="I55" s="1" t="n">
+        <v>3.918</v>
+      </c>
+      <c r="J55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="J55" s="1" t="n">
-        <v>3.921</v>
+      <c r="K55" s="1" t="n">
+        <v>3.918</v>
       </c>
     </row>
     <row r="56">
@@ -2347,9 +2515,12 @@
         <v>0.017264</v>
       </c>
       <c r="I56" s="1" t="n">
+        <v>0.017209</v>
+      </c>
+      <c r="J56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="K56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -2381,9 +2552,12 @@
         <v>0.1122</v>
       </c>
       <c r="I57" s="1" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="J57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="K57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -2415,9 +2589,12 @@
         <v>2.662</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>2.662</v>
+        <v>2.664</v>
       </c>
       <c r="J58" s="1" t="n">
+        <v>2.664</v>
+      </c>
+      <c r="K58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -2449,9 +2626,12 @@
         <v>0.1601</v>
       </c>
       <c r="I59" s="1" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="J59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="K59" s="1" t="n">
         <v>0.1593</v>
       </c>
     </row>
@@ -2483,10 +2663,13 @@
         <v>0.005912</v>
       </c>
       <c r="I60" s="1" t="n">
+        <v>0.005893</v>
+      </c>
+      <c r="J60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="J60" s="1" t="n">
-        <v>0.005912</v>
+      <c r="K60" s="1" t="n">
+        <v>0.005893</v>
       </c>
     </row>
     <row r="61">
@@ -2517,10 +2700,13 @@
         <v>0.09205000000000001</v>
       </c>
       <c r="I61" s="1" t="n">
+        <v>0.09193</v>
+      </c>
+      <c r="J61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="J61" s="1" t="n">
-        <v>0.09204</v>
+      <c r="K61" s="1" t="n">
+        <v>0.09193</v>
       </c>
     </row>
     <row r="62">
@@ -2551,9 +2737,12 @@
         <v>0.9131</v>
       </c>
       <c r="I62" s="1" t="n">
+        <v>0.9118000000000001</v>
+      </c>
+      <c r="J62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="K62" s="1" t="n">
         <v>0.9118000000000001</v>
       </c>
     </row>
@@ -2588,6 +2777,9 @@
         <v>0.78</v>
       </c>
       <c r="J63" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -2619,10 +2811,13 @@
         <v>0.04623</v>
       </c>
       <c r="I64" s="1" t="n">
+        <v>0.04612</v>
+      </c>
+      <c r="J64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="J64" s="1" t="n">
-        <v>0.04623</v>
+      <c r="K64" s="1" t="n">
+        <v>0.04612</v>
       </c>
     </row>
     <row r="65">
@@ -2653,9 +2848,12 @@
         <v>357.73</v>
       </c>
       <c r="I65" s="1" t="n">
+        <v>356.63</v>
+      </c>
+      <c r="J65" s="1" t="n">
         <v>357.73</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="K65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -2687,10 +2885,13 @@
         <v>0.12544</v>
       </c>
       <c r="I66" s="1" t="n">
+        <v>0.12419</v>
+      </c>
+      <c r="J66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="J66" s="1" t="n">
-        <v>0.12495</v>
+      <c r="K66" s="1" t="n">
+        <v>0.12419</v>
       </c>
     </row>
     <row r="67">
@@ -2721,10 +2922,13 @@
         <v>0.2369</v>
       </c>
       <c r="I67" s="1" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="J67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="J67" s="1" t="n">
-        <v>0.2369</v>
+      <c r="K67" s="1" t="n">
+        <v>0.2357</v>
       </c>
     </row>
     <row r="68">
@@ -2755,10 +2959,13 @@
         <v>0.0034</v>
       </c>
       <c r="I68" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="J68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="J68" s="1" t="n">
-        <v>0.0034</v>
+      <c r="K68" s="1" t="n">
+        <v>0.00339</v>
       </c>
     </row>
     <row r="69">
@@ -2789,10 +2996,13 @@
         <v>0.1748</v>
       </c>
       <c r="I69" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="J69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="J69" s="1" t="n">
-        <v>0.1748</v>
+      <c r="K69" s="1" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="70">
@@ -2823,9 +3033,12 @@
         <v>0.16474</v>
       </c>
       <c r="I70" s="1" t="n">
+        <v>0.16426</v>
+      </c>
+      <c r="J70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="K70" s="1" t="n">
         <v>0.16421</v>
       </c>
     </row>
@@ -2857,10 +3070,13 @@
         <v>0.3526</v>
       </c>
       <c r="I71" s="1" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="J71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="J71" s="1" t="n">
-        <v>0.3517</v>
+      <c r="K71" s="1" t="n">
+        <v>0.3515</v>
       </c>
     </row>
     <row r="72">
@@ -2891,9 +3107,12 @@
         <v>0.7105</v>
       </c>
       <c r="I72" s="1" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="J72" s="1" t="n">
         <v>0.7105</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="K72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -2925,9 +3144,12 @@
         <v>0.00868</v>
       </c>
       <c r="I73" s="1" t="n">
+        <v>0.00869</v>
+      </c>
+      <c r="J73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="K73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -2959,10 +3181,13 @@
         <v>0.005995</v>
       </c>
       <c r="I74" s="1" t="n">
+        <v>0.005982</v>
+      </c>
+      <c r="J74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="J74" s="1" t="n">
-        <v>0.005995</v>
+      <c r="K74" s="1" t="n">
+        <v>0.005982</v>
       </c>
     </row>
     <row r="75">
@@ -2993,9 +3218,12 @@
         <v>0.226</v>
       </c>
       <c r="I75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="J75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="K75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -3027,9 +3255,12 @@
         <v>0.3167</v>
       </c>
       <c r="I76" s="1" t="n">
-        <v>0.3167</v>
+        <v>0.3189</v>
       </c>
       <c r="J76" s="1" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="K76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -3061,9 +3292,12 @@
         <v>0.1005</v>
       </c>
       <c r="I77" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="J77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="J77" s="1" t="n">
+      <c r="K77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -3095,9 +3329,12 @@
         <v>0.123</v>
       </c>
       <c r="I78" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="J78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="J78" s="1" t="n">
+      <c r="K78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -3129,9 +3366,12 @@
         <v>0.07071</v>
       </c>
       <c r="I79" s="1" t="n">
-        <v>0.07071</v>
+        <v>0.07277</v>
       </c>
       <c r="J79" s="1" t="n">
+        <v>0.07277</v>
+      </c>
+      <c r="K79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -3163,9 +3403,12 @@
         <v>0.04691</v>
       </c>
       <c r="I80" s="1" t="n">
+        <v>0.04689</v>
+      </c>
+      <c r="J80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="J80" s="1" t="n">
+      <c r="K80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -3197,9 +3440,12 @@
         <v>0.000238</v>
       </c>
       <c r="I81" s="1" t="n">
+        <v>0.000233</v>
+      </c>
+      <c r="J81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="J81" s="1" t="n">
+      <c r="K81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -3231,9 +3477,12 @@
         <v>8.223000000000001</v>
       </c>
       <c r="I82" s="1" t="n">
+        <v>8.215999999999999</v>
+      </c>
+      <c r="J82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="J82" s="1" t="n">
+      <c r="K82" s="1" t="n">
         <v>8.215</v>
       </c>
     </row>
@@ -3265,9 +3514,12 @@
         <v>0.0005836</v>
       </c>
       <c r="I83" s="1" t="n">
+        <v>0.0005831</v>
+      </c>
+      <c r="J83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="K83" s="1" t="n">
         <v>0.0005831</v>
       </c>
     </row>
@@ -3299,9 +3551,12 @@
         <v>0.4342</v>
       </c>
       <c r="I84" s="1" t="n">
-        <v>0.4342</v>
+        <v>0.4454</v>
       </c>
       <c r="J84" s="1" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="K84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -3333,9 +3588,12 @@
         <v>0.06235</v>
       </c>
       <c r="I85" s="1" t="n">
+        <v>0.06245</v>
+      </c>
+      <c r="J85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="J85" s="1" t="n">
+      <c r="K85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -3367,10 +3625,13 @@
         <v>0.05451</v>
       </c>
       <c r="I86" s="1" t="n">
+        <v>0.05424</v>
+      </c>
+      <c r="J86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="J86" s="1" t="n">
-        <v>0.05447</v>
+      <c r="K86" s="1" t="n">
+        <v>0.05424</v>
       </c>
     </row>
     <row r="87">
@@ -3401,9 +3662,12 @@
         <v>0.003348</v>
       </c>
       <c r="I87" s="1" t="n">
-        <v>0.003364</v>
+        <v>0.003366</v>
       </c>
       <c r="J87" s="1" t="n">
+        <v>0.003366</v>
+      </c>
+      <c r="K87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -3435,9 +3699,12 @@
         <v>0.05079</v>
       </c>
       <c r="I88" s="1" t="n">
+        <v>0.05082</v>
+      </c>
+      <c r="J88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="J88" s="1" t="n">
+      <c r="K88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -3469,9 +3736,12 @@
         <v>0.0313</v>
       </c>
       <c r="I89" s="1" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="J89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="K89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -3503,9 +3773,12 @@
         <v>0.3482</v>
       </c>
       <c r="I90" s="1" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="J90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="K90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -3537,9 +3810,12 @@
         <v>0.0653</v>
       </c>
       <c r="I91" s="1" t="n">
-        <v>0.0653</v>
+        <v>0.07675999999999999</v>
       </c>
       <c r="J91" s="1" t="n">
+        <v>0.07675999999999999</v>
+      </c>
+      <c r="K91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -3571,9 +3847,12 @@
         <v>0.3498</v>
       </c>
       <c r="I92" s="1" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="J92" s="1" t="n">
         <v>0.3527</v>
       </c>
-      <c r="J92" s="1" t="n">
+      <c r="K92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -3605,9 +3884,12 @@
         <v>1.9733</v>
       </c>
       <c r="I93" s="1" t="n">
+        <v>1.9746</v>
+      </c>
+      <c r="J93" s="1" t="n">
         <v>1.9753</v>
       </c>
-      <c r="J93" s="1" t="n">
+      <c r="K93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -3639,9 +3921,12 @@
         <v>0.2595</v>
       </c>
       <c r="I94" s="1" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="J94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="J94" s="1" t="n">
+      <c r="K94" s="1" t="n">
         <v>0.2589</v>
       </c>
     </row>
@@ -3673,9 +3958,12 @@
         <v>0.04519</v>
       </c>
       <c r="I95" s="1" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="J95" s="1" t="n">
         <v>0.04542</v>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="K95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -3707,9 +3995,12 @@
         <v>0.006179</v>
       </c>
       <c r="I96" s="1" t="n">
+        <v>0.006296</v>
+      </c>
+      <c r="J96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="J96" s="1" t="n">
+      <c r="K96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -3741,10 +4032,13 @@
         <v>0.001736</v>
       </c>
       <c r="I97" s="1" t="n">
+        <v>0.00173</v>
+      </c>
+      <c r="J97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="J97" s="1" t="n">
-        <v>0.001732</v>
+      <c r="K97" s="1" t="n">
+        <v>0.00173</v>
       </c>
     </row>
     <row r="98">
@@ -3775,9 +4069,12 @@
         <v>5.304</v>
       </c>
       <c r="I98" s="1" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="J98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="K98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -3809,9 +4106,12 @@
         <v>0.01524</v>
       </c>
       <c r="I99" s="1" t="n">
+        <v>0.01517</v>
+      </c>
+      <c r="J99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="K99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -3843,9 +4143,12 @@
         <v>0.5535</v>
       </c>
       <c r="I100" s="1" t="n">
-        <v>0.5535</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="J100" s="1" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="K100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -3877,9 +4180,12 @@
         <v>0.0912</v>
       </c>
       <c r="I101" s="1" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="J101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="K101" s="1" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -3911,10 +4217,13 @@
         <v>32.49</v>
       </c>
       <c r="I102" s="1" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="J102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="J102" s="1" t="n">
-        <v>32.48</v>
+      <c r="K102" s="1" t="n">
+        <v>32.44</v>
       </c>
     </row>
     <row r="103">
@@ -3945,10 +4254,13 @@
         <v>0.03196</v>
       </c>
       <c r="I103" s="1" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="J103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="J103" s="1" t="n">
-        <v>0.03196</v>
+      <c r="K103" s="1" t="n">
+        <v>0.03182</v>
       </c>
     </row>
     <row r="104">
@@ -3979,10 +4291,13 @@
         <v>0.06577</v>
       </c>
       <c r="I104" s="1" t="n">
+        <v>0.06571</v>
+      </c>
+      <c r="J104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="J104" s="1" t="n">
-        <v>0.06577</v>
+      <c r="K104" s="1" t="n">
+        <v>0.06571</v>
       </c>
     </row>
     <row r="105">
@@ -4013,9 +4328,12 @@
         <v>1.3027</v>
       </c>
       <c r="I105" s="1" t="n">
-        <v>1.3041</v>
+        <v>1.3044</v>
       </c>
       <c r="J105" s="1" t="n">
+        <v>1.3044</v>
+      </c>
+      <c r="K105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -4047,9 +4365,12 @@
         <v>0.1216</v>
       </c>
       <c r="I106" s="1" t="n">
+        <v>0.1206</v>
+      </c>
+      <c r="J106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="J106" s="1" t="n">
+      <c r="K106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -4081,9 +4402,12 @@
         <v>0.119</v>
       </c>
       <c r="I107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="J107" s="1" t="n">
+      <c r="K107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -4115,9 +4439,12 @@
         <v>0.09586</v>
       </c>
       <c r="I108" s="1" t="n">
+        <v>0.09588000000000001</v>
+      </c>
+      <c r="J108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="J108" s="1" t="n">
+      <c r="K108" s="1" t="n">
         <v>0.09586</v>
       </c>
     </row>
@@ -4149,9 +4476,12 @@
         <v>0.14091</v>
       </c>
       <c r="I109" s="1" t="n">
+        <v>0.13886</v>
+      </c>
+      <c r="J109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="J109" s="1" t="n">
+      <c r="K109" s="1" t="n">
         <v>0.13861</v>
       </c>
     </row>
@@ -4183,9 +4513,12 @@
         <v>5.551</v>
       </c>
       <c r="I110" s="1" t="n">
+        <v>5.549</v>
+      </c>
+      <c r="J110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="K110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -4217,9 +4550,12 @@
         <v>1.1</v>
       </c>
       <c r="I111" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="J111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="J111" s="1" t="n">
+      <c r="K111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -4251,10 +4587,13 @@
         <v>0.029308</v>
       </c>
       <c r="I112" s="1" t="n">
+        <v>0.029252</v>
+      </c>
+      <c r="J112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="J112" s="1" t="n">
-        <v>0.029256</v>
+      <c r="K112" s="1" t="n">
+        <v>0.029252</v>
       </c>
     </row>
     <row r="113">
@@ -4285,9 +4624,12 @@
         <v>1.886</v>
       </c>
       <c r="I113" s="1" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="J113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="J113" s="1" t="n">
+      <c r="K113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -4319,9 +4661,12 @@
         <v>0.05869</v>
       </c>
       <c r="I114" s="1" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="J114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="J114" s="1" t="n">
+      <c r="K114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -4353,9 +4698,12 @@
         <v>0.12858</v>
       </c>
       <c r="I115" s="1" t="n">
+        <v>0.12808</v>
+      </c>
+      <c r="J115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="K115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -4387,9 +4735,12 @@
         <v>1.1079</v>
       </c>
       <c r="I116" s="1" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="J116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="J116" s="1" t="n">
+      <c r="K116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -4421,9 +4772,12 @@
         <v>0.1587</v>
       </c>
       <c r="I117" s="1" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="J117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="K117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -4455,9 +4809,12 @@
         <v>0.16</v>
       </c>
       <c r="I118" s="1" t="n">
-        <v>0.16</v>
+        <v>0.1603</v>
       </c>
       <c r="J118" s="1" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="K118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -4489,9 +4846,12 @@
         <v>0.04623</v>
       </c>
       <c r="I119" s="1" t="n">
-        <v>0.04623</v>
+        <v>0.04641</v>
       </c>
       <c r="J119" s="1" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="K119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -4523,9 +4883,12 @@
         <v>3.029</v>
       </c>
       <c r="I120" s="1" t="n">
+        <v>3.023</v>
+      </c>
+      <c r="J120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="K120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -4557,9 +4920,12 @@
         <v>0.2968</v>
       </c>
       <c r="I121" s="1" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="J121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="J121" s="1" t="n">
+      <c r="K121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -4591,9 +4957,12 @@
         <v>0.5833</v>
       </c>
       <c r="I122" s="1" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="J122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="J122" s="1" t="n">
+      <c r="K122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -4625,9 +4994,12 @@
         <v>0.01257</v>
       </c>
       <c r="I123" s="1" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="J123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="J123" s="1" t="n">
+      <c r="K123" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -4659,10 +5031,13 @@
         <v>0.1586</v>
       </c>
       <c r="I124" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="J124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="J124" s="1" t="n">
-        <v>0.1584</v>
+      <c r="K124" s="1" t="n">
+        <v>0.1582</v>
       </c>
     </row>
     <row r="125">
@@ -4693,9 +5068,12 @@
         <v>0.001781</v>
       </c>
       <c r="I125" s="1" t="n">
-        <v>0.001785</v>
+        <v>0.001786</v>
       </c>
       <c r="J125" s="1" t="n">
+        <v>0.001786</v>
+      </c>
+      <c r="K125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -4727,9 +5105,12 @@
         <v>0.000487</v>
       </c>
       <c r="I126" s="1" t="n">
+        <v>0.0004868</v>
+      </c>
+      <c r="J126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="J126" s="1" t="n">
+      <c r="K126" s="1" t="n">
         <v>0.0004867</v>
       </c>
     </row>
@@ -4761,10 +5142,13 @@
         <v>0.02951</v>
       </c>
       <c r="I127" s="1" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="J127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="J127" s="1" t="n">
-        <v>0.02949</v>
+      <c r="K127" s="1" t="n">
+        <v>0.02945</v>
       </c>
     </row>
     <row r="128">
@@ -4795,9 +5179,12 @@
         <v>0.04132</v>
       </c>
       <c r="I128" s="1" t="n">
-        <v>0.04134</v>
+        <v>0.04138</v>
       </c>
       <c r="J128" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="K128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -4829,9 +5216,12 @@
         <v>0.04853</v>
       </c>
       <c r="I129" s="1" t="n">
+        <v>0.04842</v>
+      </c>
+      <c r="J129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="J129" s="1" t="n">
+      <c r="K129" s="1" t="n">
         <v>0.04838</v>
       </c>
     </row>
@@ -4863,9 +5253,12 @@
         <v>1.25e-05</v>
       </c>
       <c r="I130" s="1" t="n">
-        <v>1.25e-05</v>
+        <v>1.26e-05</v>
       </c>
       <c r="J130" s="1" t="n">
+        <v>1.26e-05</v>
+      </c>
+      <c r="K130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -4897,9 +5290,12 @@
         <v>6.8e-06</v>
       </c>
       <c r="I131" s="1" t="n">
+        <v>6.9e-06</v>
+      </c>
+      <c r="J131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="J131" s="1" t="n">
+      <c r="K131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -4931,9 +5327,12 @@
         <v>0.007</v>
       </c>
       <c r="I132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="J132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="J132" s="1" t="n">
+      <c r="K132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -4965,9 +5364,12 @@
         <v>0.0969</v>
       </c>
       <c r="I133" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="J133" s="1" t="n">
+      <c r="K133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -4999,9 +5401,12 @@
         <v>0.0004102</v>
       </c>
       <c r="I134" s="1" t="n">
+        <v>0.0004107</v>
+      </c>
+      <c r="J134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="J134" s="1" t="n">
+      <c r="K134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -5033,9 +5438,12 @@
         <v>0.08409</v>
       </c>
       <c r="I135" s="1" t="n">
+        <v>0.08391</v>
+      </c>
+      <c r="J135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="J135" s="1" t="n">
+      <c r="K135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -5067,9 +5475,12 @@
         <v>0.007936</v>
       </c>
       <c r="I136" s="1" t="n">
+        <v>0.007938000000000001</v>
+      </c>
+      <c r="J136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="J136" s="1" t="n">
+      <c r="K136" s="1" t="n">
         <v>0.007891</v>
       </c>
     </row>
@@ -5101,9 +5512,12 @@
         <v>0.000839</v>
       </c>
       <c r="I137" s="1" t="n">
+        <v>0.0008304</v>
+      </c>
+      <c r="J137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="J137" s="1" t="n">
+      <c r="K137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -5135,9 +5549,12 @@
         <v>0.1473</v>
       </c>
       <c r="I138" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="J138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="J138" s="1" t="n">
+      <c r="K138" s="1" t="n">
         <v>0.1473</v>
       </c>
     </row>
@@ -5169,9 +5586,12 @@
         <v>0.006721</v>
       </c>
       <c r="I139" s="1" t="n">
+        <v>0.006724</v>
+      </c>
+      <c r="J139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="J139" s="1" t="n">
+      <c r="K139" s="1" t="n">
         <v>0.00672</v>
       </c>
     </row>
@@ -5203,9 +5623,12 @@
         <v>0.01381</v>
       </c>
       <c r="I140" s="1" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="J140" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="J140" s="1" t="n">
+      <c r="K140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -5237,9 +5660,12 @@
         <v>0.09782</v>
       </c>
       <c r="I141" s="1" t="n">
+        <v>0.09809</v>
+      </c>
+      <c r="J141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="J141" s="1" t="n">
+      <c r="K141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -5271,9 +5697,12 @@
         <v>0.05423</v>
       </c>
       <c r="I142" s="1" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="J142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="J142" s="1" t="n">
+      <c r="K142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -5305,9 +5734,12 @@
         <v>0.3246</v>
       </c>
       <c r="I143" s="1" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="J143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="K143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -5339,9 +5771,12 @@
         <v>0.02574</v>
       </c>
       <c r="I144" s="1" t="n">
+        <v>0.02584</v>
+      </c>
+      <c r="J144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="J144" s="1" t="n">
+      <c r="K144" s="1" t="n">
         <v>0.02572</v>
       </c>
     </row>
@@ -5373,9 +5808,12 @@
         <v>0.238</v>
       </c>
       <c r="I145" s="1" t="n">
-        <v>0.2382</v>
+        <v>0.2383</v>
       </c>
       <c r="J145" s="1" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="K145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -5407,10 +5845,13 @@
         <v>0.007032</v>
       </c>
       <c r="I146" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="J146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="J146" s="1" t="n">
-        <v>0.007032</v>
+      <c r="K146" s="1" t="n">
+        <v>0.00703</v>
       </c>
     </row>
     <row r="147">
@@ -5441,9 +5882,12 @@
         <v>0.08698</v>
       </c>
       <c r="I147" s="1" t="n">
+        <v>0.08691</v>
+      </c>
+      <c r="J147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="J147" s="1" t="n">
+      <c r="K147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -5475,9 +5919,12 @@
         <v>0.05061</v>
       </c>
       <c r="I148" s="1" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="J148" s="1" t="n">
         <v>0.05073</v>
       </c>
-      <c r="J148" s="1" t="n">
+      <c r="K148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -5509,10 +5956,13 @@
         <v>0.02385</v>
       </c>
       <c r="I149" s="1" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="J149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="J149" s="1" t="n">
-        <v>0.02385</v>
+      <c r="K149" s="1" t="n">
+        <v>0.02381</v>
       </c>
     </row>
     <row r="150">
@@ -5543,9 +5993,12 @@
         <v>0.08573</v>
       </c>
       <c r="I150" s="1" t="n">
+        <v>0.08581</v>
+      </c>
+      <c r="J150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="J150" s="1" t="n">
+      <c r="K150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -5577,9 +6030,12 @@
         <v>0.02323</v>
       </c>
       <c r="I151" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="J151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="J151" s="1" t="n">
+      <c r="K151" s="1" t="n">
         <v>0.0232</v>
       </c>
     </row>
@@ -5611,10 +6067,13 @@
         <v>0.02564</v>
       </c>
       <c r="I152" s="1" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="J152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="J152" s="1" t="n">
-        <v>0.02564</v>
+      <c r="K152" s="1" t="n">
+        <v>0.02561</v>
       </c>
     </row>
     <row r="153">
@@ -5645,9 +6104,12 @@
         <v>0.0002157</v>
       </c>
       <c r="I153" s="1" t="n">
+        <v>0.0002178</v>
+      </c>
+      <c r="J153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="J153" s="1" t="n">
+      <c r="K153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -5679,9 +6141,12 @@
         <v>0.442</v>
       </c>
       <c r="I154" s="1" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="J154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="J154" s="1" t="n">
+      <c r="K154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -5713,9 +6178,12 @@
         <v>0.06694</v>
       </c>
       <c r="I155" s="1" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="J155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="J155" s="1" t="n">
+      <c r="K155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -5747,9 +6215,12 @@
         <v>0.12877</v>
       </c>
       <c r="I156" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="J156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="J156" s="1" t="n">
+      <c r="K156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -5781,9 +6252,12 @@
         <v>0.4847</v>
       </c>
       <c r="I157" s="1" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="J157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="J157" s="1" t="n">
+      <c r="K157" s="1" t="n">
         <v>0.4843</v>
       </c>
     </row>
@@ -5815,9 +6289,12 @@
         <v>0.4469</v>
       </c>
       <c r="I158" s="1" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="J158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="J158" s="1" t="n">
+      <c r="K158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -5849,9 +6326,12 @@
         <v>0.007493</v>
       </c>
       <c r="I159" s="1" t="n">
+        <v>0.007515</v>
+      </c>
+      <c r="J159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="J159" s="1" t="n">
+      <c r="K159" s="1" t="n">
         <v>0.007493</v>
       </c>
     </row>
@@ -5883,9 +6363,12 @@
         <v>0.004661</v>
       </c>
       <c r="I160" s="1" t="n">
-        <v>0.004664</v>
+        <v>0.00467</v>
       </c>
       <c r="J160" s="1" t="n">
+        <v>0.00467</v>
+      </c>
+      <c r="K160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -5917,9 +6400,12 @@
         <v>0.004301</v>
       </c>
       <c r="I161" s="1" t="n">
+        <v>0.004295</v>
+      </c>
+      <c r="J161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="J161" s="1" t="n">
+      <c r="K161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -5951,9 +6437,12 @@
         <v>0.0961</v>
       </c>
       <c r="I162" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="J162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="J162" s="1" t="n">
+      <c r="K162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -5985,10 +6474,13 @@
         <v>0.2859</v>
       </c>
       <c r="I163" s="1" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="J163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="J163" s="1" t="n">
-        <v>0.2859</v>
+      <c r="K163" s="1" t="n">
+        <v>0.2852</v>
       </c>
     </row>
     <row r="164">
@@ -6019,10 +6511,13 @@
         <v>0.1142</v>
       </c>
       <c r="I164" s="1" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="J164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="J164" s="1" t="n">
-        <v>0.1142</v>
+      <c r="K164" s="1" t="n">
+        <v>0.1139</v>
       </c>
     </row>
     <row r="165">
@@ -6053,9 +6548,12 @@
         <v>0.1755</v>
       </c>
       <c r="I165" s="1" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="J165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="J165" s="1" t="n">
+      <c r="K165" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -6087,9 +6585,12 @@
         <v>0.01008</v>
       </c>
       <c r="I166" s="1" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="J166" s="1" t="n">
         <v>0.01009</v>
       </c>
-      <c r="J166" s="1" t="n">
+      <c r="K166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -6121,9 +6622,12 @@
         <v>1.834</v>
       </c>
       <c r="I167" s="1" t="n">
-        <v>1.836</v>
+        <v>1.837</v>
       </c>
       <c r="J167" s="1" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="K167" s="1" t="n">
         <v>1.827</v>
       </c>
     </row>
@@ -6155,9 +6659,12 @@
         <v>1.343</v>
       </c>
       <c r="I168" s="1" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="J168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="J168" s="1" t="n">
+      <c r="K168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -6189,9 +6696,12 @@
         <v>0.007304</v>
       </c>
       <c r="I169" s="1" t="n">
+        <v>0.007313</v>
+      </c>
+      <c r="J169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="J169" s="1" t="n">
+      <c r="K169" s="1" t="n">
         <v>0.007304</v>
       </c>
     </row>
@@ -6223,9 +6733,12 @@
         <v>0.0116</v>
       </c>
       <c r="I170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="J170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="J170" s="1" t="n">
+      <c r="K170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -6257,9 +6770,12 @@
         <v>0.005805</v>
       </c>
       <c r="I171" s="1" t="n">
+        <v>0.005802</v>
+      </c>
+      <c r="J171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="J171" s="1" t="n">
+      <c r="K171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -6291,9 +6807,12 @@
         <v>0.1476</v>
       </c>
       <c r="I172" s="1" t="n">
+        <v>0.14729</v>
+      </c>
+      <c r="J172" s="1" t="n">
         <v>0.14806</v>
       </c>
-      <c r="J172" s="1" t="n">
+      <c r="K172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -6325,9 +6844,12 @@
         <v>4.874</v>
       </c>
       <c r="I173" s="1" t="n">
+        <v>4.879</v>
+      </c>
+      <c r="J173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="J173" s="1" t="n">
+      <c r="K173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -6359,10 +6881,13 @@
         <v>0.07872</v>
       </c>
       <c r="I174" s="1" t="n">
+        <v>0.07867</v>
+      </c>
+      <c r="J174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="J174" s="1" t="n">
-        <v>0.07868</v>
+      <c r="K174" s="1" t="n">
+        <v>0.07867</v>
       </c>
     </row>
     <row r="175">
@@ -6393,10 +6918,13 @@
         <v>0.007479</v>
       </c>
       <c r="I175" s="1" t="n">
+        <v>0.007477</v>
+      </c>
+      <c r="J175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="J175" s="1" t="n">
-        <v>0.007479</v>
+      <c r="K175" s="1" t="n">
+        <v>0.007477</v>
       </c>
     </row>
     <row r="176">
@@ -6427,10 +6955,13 @@
         <v>0.2013</v>
       </c>
       <c r="I176" s="1" t="n">
+        <v>0.2012</v>
+      </c>
+      <c r="J176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="J176" s="1" t="n">
-        <v>0.2013</v>
+      <c r="K176" s="1" t="n">
+        <v>0.2012</v>
       </c>
     </row>
     <row r="177">
@@ -6461,9 +6992,12 @@
         <v>0.05183</v>
       </c>
       <c r="I177" s="1" t="n">
+        <v>0.05181</v>
+      </c>
+      <c r="J177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="J177" s="1" t="n">
+      <c r="K177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -6495,9 +7029,12 @@
         <v>0.05468</v>
       </c>
       <c r="I178" s="1" t="n">
-        <v>0.05468</v>
+        <v>0.05485</v>
       </c>
       <c r="J178" s="1" t="n">
+        <v>0.05485</v>
+      </c>
+      <c r="K178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -6529,10 +7066,13 @@
         <v>0.02327</v>
       </c>
       <c r="I179" s="1" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="J179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="J179" s="1" t="n">
-        <v>0.02324</v>
+      <c r="K179" s="1" t="n">
+        <v>0.02321</v>
       </c>
     </row>
     <row r="180">
@@ -6563,9 +7103,12 @@
         <v>0.6964</v>
       </c>
       <c r="I180" s="1" t="n">
-        <v>0.6964</v>
+        <v>0.6976</v>
       </c>
       <c r="J180" s="1" t="n">
+        <v>0.6976</v>
+      </c>
+      <c r="K180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -6597,10 +7140,13 @@
         <v>0.0003734</v>
       </c>
       <c r="I181" s="1" t="n">
+        <v>0.000371</v>
+      </c>
+      <c r="J181" s="1" t="n">
         <v>0.0003734</v>
       </c>
-      <c r="J181" s="1" t="n">
-        <v>0.0003716</v>
+      <c r="K181" s="1" t="n">
+        <v>0.000371</v>
       </c>
     </row>
     <row r="182">
@@ -6631,10 +7177,13 @@
         <v>0.01269</v>
       </c>
       <c r="I182" s="1" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="J182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="J182" s="1" t="n">
-        <v>0.01266</v>
+      <c r="K182" s="1" t="n">
+        <v>0.01258</v>
       </c>
     </row>
     <row r="183">
@@ -6665,10 +7214,13 @@
         <v>4.248</v>
       </c>
       <c r="I183" s="1" t="n">
+        <v>4.242</v>
+      </c>
+      <c r="J183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="J183" s="1" t="n">
-        <v>4.248</v>
+      <c r="K183" s="1" t="n">
+        <v>4.242</v>
       </c>
     </row>
     <row r="184">
@@ -6699,9 +7251,12 @@
         <v>0.2376</v>
       </c>
       <c r="I184" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="J184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="J184" s="1" t="n">
+      <c r="K184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -6733,10 +7288,13 @@
         <v>0.03693</v>
       </c>
       <c r="I185" s="1" t="n">
+        <v>0.03672</v>
+      </c>
+      <c r="J185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="J185" s="1" t="n">
-        <v>0.03693</v>
+      <c r="K185" s="1" t="n">
+        <v>0.03672</v>
       </c>
     </row>
     <row r="186">
@@ -6767,9 +7325,12 @@
         <v>0.11566</v>
       </c>
       <c r="I186" s="1" t="n">
+        <v>0.11567</v>
+      </c>
+      <c r="J186" s="1" t="n">
         <v>0.11628</v>
       </c>
-      <c r="J186" s="1" t="n">
+      <c r="K186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -6801,10 +7362,13 @@
         <v>0.009117</v>
       </c>
       <c r="I187" s="1" t="n">
+        <v>0.009013</v>
+      </c>
+      <c r="J187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="J187" s="1" t="n">
-        <v>0.009018999999999999</v>
+      <c r="K187" s="1" t="n">
+        <v>0.009013</v>
       </c>
     </row>
     <row r="188">
@@ -6835,9 +7399,12 @@
         <v>0.0974</v>
       </c>
       <c r="I188" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="J188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="J188" s="1" t="n">
+      <c r="K188" s="1" t="n">
         <v>0.0974</v>
       </c>
     </row>
@@ -6869,9 +7436,12 @@
         <v>0.02792</v>
       </c>
       <c r="I189" s="1" t="n">
+        <v>0.02791</v>
+      </c>
+      <c r="J189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="J189" s="1" t="n">
+      <c r="K189" s="1" t="n">
         <v>0.02773</v>
       </c>
     </row>
@@ -6903,9 +7473,12 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="I190" s="1" t="n">
+        <v>0.00873</v>
+      </c>
+      <c r="J190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="J190" s="1" t="n">
+      <c r="K190" s="1" t="n">
         <v>0.008699999999999999</v>
       </c>
     </row>
@@ -6937,9 +7510,12 @@
         <v>0.001952</v>
       </c>
       <c r="I191" s="1" t="n">
+        <v>0.001952</v>
+      </c>
+      <c r="J191" s="1" t="n">
         <v>0.001956</v>
       </c>
-      <c r="J191" s="1" t="n">
+      <c r="K191" s="1" t="n">
         <v>0.001949</v>
       </c>
     </row>
@@ -6971,9 +7547,12 @@
         <v>0.1003</v>
       </c>
       <c r="I192" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="J192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="J192" s="1" t="n">
+      <c r="K192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -7005,9 +7584,12 @@
         <v>0.02332</v>
       </c>
       <c r="I193" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="J193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="J193" s="1" t="n">
+      <c r="K193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -7039,9 +7621,12 @@
         <v>0.01348</v>
       </c>
       <c r="I194" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="J194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="J194" s="1" t="n">
+      <c r="K194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -7073,10 +7658,13 @@
         <v>0.02094</v>
       </c>
       <c r="I195" s="1" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="J195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="J195" s="1" t="n">
-        <v>0.02094</v>
+      <c r="K195" s="1" t="n">
+        <v>0.02093</v>
       </c>
     </row>
     <row r="196">
@@ -7107,9 +7695,12 @@
         <v>0.17356</v>
       </c>
       <c r="I196" s="1" t="n">
+        <v>0.17168</v>
+      </c>
+      <c r="J196" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="J196" s="1" t="n">
+      <c r="K196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -7141,10 +7732,13 @@
         <v>0.0073</v>
       </c>
       <c r="I197" s="1" t="n">
+        <v>0.007277</v>
+      </c>
+      <c r="J197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="J197" s="1" t="n">
-        <v>0.007292</v>
+      <c r="K197" s="1" t="n">
+        <v>0.007277</v>
       </c>
     </row>
     <row r="198">
@@ -7175,9 +7769,12 @@
         <v>0.0191</v>
       </c>
       <c r="I198" s="1" t="n">
+        <v>0.01907</v>
+      </c>
+      <c r="J198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="J198" s="1" t="n">
+      <c r="K198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -7209,9 +7806,12 @@
         <v>0.01621</v>
       </c>
       <c r="I199" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="J199" s="1" t="n">
         <v>0.0164</v>
       </c>
-      <c r="J199" s="1" t="n">
+      <c r="K199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -7243,9 +7843,12 @@
         <v>0.2974</v>
       </c>
       <c r="I200" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="J200" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="J200" s="1" t="n">
+      <c r="K200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -7277,9 +7880,12 @@
         <v>0.006234</v>
       </c>
       <c r="I201" s="1" t="n">
+        <v>0.006226</v>
+      </c>
+      <c r="J201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="J201" s="1" t="n">
+      <c r="K201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -7311,9 +7917,12 @@
         <v>0.0004457</v>
       </c>
       <c r="I202" s="1" t="n">
+        <v>0.0004448</v>
+      </c>
+      <c r="J202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="J202" s="1" t="n">
+      <c r="K202" s="1" t="n">
         <v>0.0004448</v>
       </c>
     </row>
@@ -7345,9 +7954,12 @@
         <v>0.007354</v>
       </c>
       <c r="I203" s="1" t="n">
+        <v>0.007339</v>
+      </c>
+      <c r="J203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="J203" s="1" t="n">
+      <c r="K203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -7379,9 +7991,12 @@
         <v>0.1305</v>
       </c>
       <c r="I204" s="1" t="n">
-        <v>0.1305</v>
+        <v>0.1314</v>
       </c>
       <c r="J204" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="K204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -7413,9 +8028,12 @@
         <v>0.01445</v>
       </c>
       <c r="I205" s="1" t="n">
+        <v>0.01443</v>
+      </c>
+      <c r="J205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="J205" s="1" t="n">
+      <c r="K205" s="1" t="n">
         <v>0.01442</v>
       </c>
     </row>
@@ -7447,9 +8065,12 @@
         <v>0.003591</v>
       </c>
       <c r="I206" s="1" t="n">
+        <v>0.003591</v>
+      </c>
+      <c r="J206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="J206" s="1" t="n">
+      <c r="K206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -7481,9 +8102,12 @@
         <v>0.05948</v>
       </c>
       <c r="I207" s="1" t="n">
+        <v>0.05981</v>
+      </c>
+      <c r="J207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="J207" s="1" t="n">
+      <c r="K207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -7515,9 +8139,12 @@
         <v>15.48</v>
       </c>
       <c r="I208" s="1" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="J208" s="1" t="n">
         <v>15.49</v>
       </c>
-      <c r="J208" s="1" t="n">
+      <c r="K208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -7549,9 +8176,12 @@
         <v>5186.8</v>
       </c>
       <c r="I209" s="1" t="n">
-        <v>5186.8</v>
+        <v>5191.3</v>
       </c>
       <c r="J209" s="1" t="n">
+        <v>5191.3</v>
+      </c>
+      <c r="K209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -7583,9 +8213,12 @@
         <v>0.11991</v>
       </c>
       <c r="I210" s="1" t="n">
+        <v>0.11992</v>
+      </c>
+      <c r="J210" s="1" t="n">
         <v>0.12042</v>
       </c>
-      <c r="J210" s="1" t="n">
+      <c r="K210" s="1" t="n">
         <v>0.11988</v>
       </c>
     </row>
@@ -7617,10 +8250,13 @@
         <v>0.1823</v>
       </c>
       <c r="I211" s="1" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="J211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="J211" s="1" t="n">
-        <v>0.1822</v>
+      <c r="K211" s="1" t="n">
+        <v>0.182</v>
       </c>
     </row>
     <row r="212">
@@ -7651,9 +8287,12 @@
         <v>0.0304</v>
       </c>
       <c r="I212" s="1" t="n">
-        <v>0.0304</v>
+        <v>0.0305</v>
       </c>
       <c r="J212" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="K212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -7685,9 +8324,12 @@
         <v>1.3969</v>
       </c>
       <c r="I213" s="1" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="J213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="J213" s="1" t="n">
+      <c r="K213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -7719,10 +8361,13 @@
         <v>0.05655</v>
       </c>
       <c r="I214" s="1" t="n">
+        <v>0.05652</v>
+      </c>
+      <c r="J214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="J214" s="1" t="n">
-        <v>0.05655</v>
+      <c r="K214" s="1" t="n">
+        <v>0.05652</v>
       </c>
     </row>
     <row r="215">
@@ -7753,9 +8398,12 @@
         <v>0.04377</v>
       </c>
       <c r="I215" s="1" t="n">
-        <v>0.04385</v>
+        <v>0.04398</v>
       </c>
       <c r="J215" s="1" t="n">
+        <v>0.04398</v>
+      </c>
+      <c r="K215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -7787,10 +8435,13 @@
         <v>0.15029</v>
       </c>
       <c r="I216" s="1" t="n">
+        <v>0.14962</v>
+      </c>
+      <c r="J216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="J216" s="1" t="n">
-        <v>0.15029</v>
+      <c r="K216" s="1" t="n">
+        <v>0.14962</v>
       </c>
     </row>
     <row r="217">
@@ -7821,9 +8472,12 @@
         <v>0.073</v>
       </c>
       <c r="I217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="J217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="J217" s="1" t="n">
+      <c r="K217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -7855,9 +8509,12 @@
         <v>0.00268</v>
       </c>
       <c r="I218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="J218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="J218" s="1" t="n">
+      <c r="K218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -7889,9 +8546,12 @@
         <v>0.01715</v>
       </c>
       <c r="I219" s="1" t="n">
+        <v>0.01718</v>
+      </c>
+      <c r="J219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="J219" s="1" t="n">
+      <c r="K219" s="1" t="n">
         <v>0.01715</v>
       </c>
     </row>
@@ -7923,10 +8583,13 @@
         <v>0.05514</v>
       </c>
       <c r="I220" s="1" t="n">
+        <v>0.05507</v>
+      </c>
+      <c r="J220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="J220" s="1" t="n">
-        <v>0.05509</v>
+      <c r="K220" s="1" t="n">
+        <v>0.05507</v>
       </c>
     </row>
     <row r="221">
@@ -7957,9 +8620,12 @@
         <v>0.02192</v>
       </c>
       <c r="I221" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="J221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="J221" s="1" t="n">
+      <c r="K221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -7991,9 +8657,12 @@
         <v>0.00936</v>
       </c>
       <c r="I222" s="1" t="n">
+        <v>0.00937</v>
+      </c>
+      <c r="J222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="J222" s="1" t="n">
+      <c r="K222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -8030,6 +8699,9 @@
       <c r="J223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="K223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8059,9 +8731,12 @@
         <v>0.03823</v>
       </c>
       <c r="I224" s="1" t="n">
+        <v>0.03836</v>
+      </c>
+      <c r="J224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="J224" s="1" t="n">
+      <c r="K224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -8093,9 +8768,12 @@
         <v>0.001525</v>
       </c>
       <c r="I225" s="1" t="n">
+        <v>0.001527</v>
+      </c>
+      <c r="J225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="J225" s="1" t="n">
+      <c r="K225" s="1" t="n">
         <v>0.001525</v>
       </c>
     </row>
@@ -8127,9 +8805,12 @@
         <v>26.91</v>
       </c>
       <c r="I226" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="J226" s="1" t="n">
+      <c r="K226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -8161,9 +8842,12 @@
         <v>0.07033</v>
       </c>
       <c r="I227" s="1" t="n">
-        <v>0.07033</v>
+        <v>0.07059</v>
       </c>
       <c r="J227" s="1" t="n">
+        <v>0.07059</v>
+      </c>
+      <c r="K227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -8195,9 +8879,12 @@
         <v>0.313</v>
       </c>
       <c r="I228" s="1" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="J228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="J228" s="1" t="n">
+      <c r="K228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -8229,10 +8916,13 @@
         <v>18.42</v>
       </c>
       <c r="I229" s="1" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="J229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="J229" s="1" t="n">
-        <v>18.42</v>
+      <c r="K229" s="1" t="n">
+        <v>18.39</v>
       </c>
     </row>
     <row r="230">
@@ -8263,9 +8953,12 @@
         <v>0.01928</v>
       </c>
       <c r="I230" s="1" t="n">
+        <v>0.01929</v>
+      </c>
+      <c r="J230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="J230" s="1" t="n">
+      <c r="K230" s="1" t="n">
         <v>0.01928</v>
       </c>
     </row>
@@ -8297,9 +8990,12 @@
         <v>0.01218</v>
       </c>
       <c r="I231" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="J231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="J231" s="1" t="n">
+      <c r="K231" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>
@@ -8331,10 +9027,13 @@
         <v>0.2284</v>
       </c>
       <c r="I232" s="1" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="J232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="J232" s="1" t="n">
-        <v>0.2284</v>
+      <c r="K232" s="1" t="n">
+        <v>0.2279</v>
       </c>
     </row>
     <row r="233">
@@ -8365,10 +9064,13 @@
         <v>0.07092</v>
       </c>
       <c r="I233" s="1" t="n">
+        <v>0.07087</v>
+      </c>
+      <c r="J233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="J233" s="1" t="n">
-        <v>0.07092</v>
+      <c r="K233" s="1" t="n">
+        <v>0.07087</v>
       </c>
     </row>
     <row r="234">
@@ -8399,9 +9101,12 @@
         <v>0.1699</v>
       </c>
       <c r="I234" s="1" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="J234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="J234" s="1" t="n">
+      <c r="K234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -8433,10 +9138,13 @@
         <v>0.0253</v>
       </c>
       <c r="I235" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="J235" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="J235" s="1" t="n">
-        <v>0.0252</v>
+      <c r="K235" s="1" t="n">
+        <v>0.0251</v>
       </c>
     </row>
     <row r="236">
@@ -8467,9 +9175,12 @@
         <v>0.03003</v>
       </c>
       <c r="I236" s="1" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="J236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="J236" s="1" t="n">
+      <c r="K236" s="1" t="n">
         <v>0.03003</v>
       </c>
     </row>
@@ -8501,9 +9212,12 @@
         <v>1.986</v>
       </c>
       <c r="I237" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="J237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="J237" s="1" t="n">
+      <c r="K237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -8535,9 +9249,12 @@
         <v>0.428</v>
       </c>
       <c r="I238" s="1" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="J238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="J238" s="1" t="n">
+      <c r="K238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -8569,9 +9286,12 @@
         <v>0.03328</v>
       </c>
       <c r="I239" s="1" t="n">
+        <v>0.03334</v>
+      </c>
+      <c r="J239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="J239" s="1" t="n">
+      <c r="K239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -8603,9 +9323,12 @@
         <v>0.0341</v>
       </c>
       <c r="I240" s="1" t="n">
+        <v>0.03406</v>
+      </c>
+      <c r="J240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="J240" s="1" t="n">
+      <c r="K240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -8637,9 +9360,12 @@
         <v>0.0007538999999999999</v>
       </c>
       <c r="I241" s="1" t="n">
+        <v>0.0007536</v>
+      </c>
+      <c r="J241" s="1" t="n">
         <v>0.0007551</v>
       </c>
-      <c r="J241" s="1" t="n">
+      <c r="K241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -8671,9 +9397,12 @@
         <v>0.1835</v>
       </c>
       <c r="I242" s="1" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="J242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="J242" s="1" t="n">
+      <c r="K242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -8705,10 +9434,13 @@
         <v>0.014788</v>
       </c>
       <c r="I243" s="1" t="n">
+        <v>0.014772</v>
+      </c>
+      <c r="J243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="J243" s="1" t="n">
-        <v>0.014788</v>
+      <c r="K243" s="1" t="n">
+        <v>0.014772</v>
       </c>
     </row>
     <row r="244">
@@ -8739,10 +9471,13 @@
         <v>3.08e-05</v>
       </c>
       <c r="I244" s="1" t="n">
+        <v>3.06e-05</v>
+      </c>
+      <c r="J244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="J244" s="1" t="n">
-        <v>3.08e-05</v>
+      <c r="K244" s="1" t="n">
+        <v>3.06e-05</v>
       </c>
     </row>
     <row r="245">
@@ -8773,9 +9508,12 @@
         <v>0.03516</v>
       </c>
       <c r="I245" s="1" t="n">
+        <v>0.03522</v>
+      </c>
+      <c r="J245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="J245" s="1" t="n">
+      <c r="K245" s="1" t="n">
         <v>0.03516</v>
       </c>
     </row>
@@ -8807,9 +9545,12 @@
         <v>0.08058</v>
       </c>
       <c r="I246" s="1" t="n">
+        <v>0.08058</v>
+      </c>
+      <c r="J246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="J246" s="1" t="n">
+      <c r="K246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -8841,9 +9582,12 @@
         <v>0.007333</v>
       </c>
       <c r="I247" s="1" t="n">
+        <v>0.007469</v>
+      </c>
+      <c r="J247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="J247" s="1" t="n">
+      <c r="K247" s="1" t="n">
         <v>0.00728</v>
       </c>
     </row>
@@ -8875,9 +9619,12 @@
         <v>0.09558</v>
       </c>
       <c r="I248" s="1" t="n">
+        <v>0.09565</v>
+      </c>
+      <c r="J248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="J248" s="1" t="n">
+      <c r="K248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -8912,6 +9659,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="J249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="K249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -8943,9 +9693,12 @@
         <v>0.03498</v>
       </c>
       <c r="I250" s="1" t="n">
+        <v>0.03501</v>
+      </c>
+      <c r="J250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="J250" s="1" t="n">
+      <c r="K250" s="1" t="n">
         <v>0.03498</v>
       </c>
     </row>
@@ -8977,10 +9730,13 @@
         <v>0.04058</v>
       </c>
       <c r="I251" s="1" t="n">
+        <v>0.04049</v>
+      </c>
+      <c r="J251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="J251" s="1" t="n">
-        <v>0.04058</v>
+      <c r="K251" s="1" t="n">
+        <v>0.04049</v>
       </c>
     </row>
     <row r="252">
@@ -9011,9 +9767,12 @@
         <v>0.089</v>
       </c>
       <c r="I252" s="1" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0897</v>
       </c>
       <c r="J252" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="K252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -9045,9 +9804,12 @@
         <v>4.093</v>
       </c>
       <c r="I253" s="1" t="n">
+        <v>4.081</v>
+      </c>
+      <c r="J253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="J253" s="1" t="n">
+      <c r="K253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -9079,9 +9841,12 @@
         <v>0.1872</v>
       </c>
       <c r="I254" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="J254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="J254" s="1" t="n">
+      <c r="K254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -9113,9 +9878,12 @@
         <v>0.07221</v>
       </c>
       <c r="I255" s="1" t="n">
+        <v>0.07244</v>
+      </c>
+      <c r="J255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="J255" s="1" t="n">
+      <c r="K255" s="1" t="n">
         <v>0.07214</v>
       </c>
     </row>
@@ -9147,9 +9915,12 @@
         <v>0.01828</v>
       </c>
       <c r="I256" s="1" t="n">
-        <v>0.01831</v>
+        <v>0.01833</v>
       </c>
       <c r="J256" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="K256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -9181,9 +9952,12 @@
         <v>5.954</v>
       </c>
       <c r="I257" s="1" t="n">
+        <v>5.948</v>
+      </c>
+      <c r="J257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="J257" s="1" t="n">
+      <c r="K257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -9215,9 +9989,12 @@
         <v>0.2623</v>
       </c>
       <c r="I258" s="1" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="J258" s="1" t="n">
         <v>0.2639</v>
       </c>
-      <c r="J258" s="1" t="n">
+      <c r="K258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -9249,9 +10026,12 @@
         <v>0.1365</v>
       </c>
       <c r="I259" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="J259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="J259" s="1" t="n">
+      <c r="K259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -9283,9 +10063,12 @@
         <v>0.3062</v>
       </c>
       <c r="I260" s="1" t="n">
-        <v>0.3062</v>
+        <v>0.30667</v>
       </c>
       <c r="J260" s="1" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="K260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -9317,9 +10100,12 @@
         <v>0.09878000000000001</v>
       </c>
       <c r="I261" s="1" t="n">
-        <v>0.09878000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="J261" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="K261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -9351,9 +10137,12 @@
         <v>0.5425</v>
       </c>
       <c r="I262" s="1" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="J262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="J262" s="1" t="n">
+      <c r="K262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -9385,10 +10174,13 @@
         <v>0.2928</v>
       </c>
       <c r="I263" s="1" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="J263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="J263" s="1" t="n">
-        <v>0.2923</v>
+      <c r="K263" s="1" t="n">
+        <v>0.2914</v>
       </c>
     </row>
     <row r="264">
@@ -9419,9 +10211,12 @@
         <v>0.951</v>
       </c>
       <c r="I264" s="1" t="n">
-        <v>0.953</v>
+        <v>0.954</v>
       </c>
       <c r="J264" s="1" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="K264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -9453,9 +10248,12 @@
         <v>0.5403</v>
       </c>
       <c r="I265" s="1" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="J265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="J265" s="1" t="n">
+      <c r="K265" s="1" t="n">
         <v>0.5403</v>
       </c>
     </row>
@@ -9487,9 +10285,12 @@
         <v>0.07384</v>
       </c>
       <c r="I266" s="1" t="n">
+        <v>0.07382</v>
+      </c>
+      <c r="J266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="J266" s="1" t="n">
+      <c r="K266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -9521,9 +10322,12 @@
         <v>0.02159</v>
       </c>
       <c r="I267" s="1" t="n">
-        <v>0.02159</v>
+        <v>0.02163</v>
       </c>
       <c r="J267" s="1" t="n">
+        <v>0.02163</v>
+      </c>
+      <c r="K267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -9555,9 +10359,12 @@
         <v>0.01627</v>
       </c>
       <c r="I268" s="1" t="n">
+        <v>0.01619</v>
+      </c>
+      <c r="J268" s="1" t="n">
         <v>0.01633</v>
       </c>
-      <c r="J268" s="1" t="n">
+      <c r="K268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -9589,9 +10396,12 @@
         <v>0.003714</v>
       </c>
       <c r="I269" s="1" t="n">
-        <v>0.003717</v>
+        <v>0.003733</v>
       </c>
       <c r="J269" s="1" t="n">
+        <v>0.003733</v>
+      </c>
+      <c r="K269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -9623,10 +10433,13 @@
         <v>0.00771</v>
       </c>
       <c r="I270" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="J270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="J270" s="1" t="n">
-        <v>0.00769</v>
+      <c r="K270" s="1" t="n">
+        <v>0.00766</v>
       </c>
     </row>
     <row r="271">
@@ -9657,9 +10470,12 @@
         <v>0.05507</v>
       </c>
       <c r="I271" s="1" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="J271" s="1" t="n">
         <v>0.05512</v>
       </c>
-      <c r="J271" s="1" t="n">
+      <c r="K271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -9691,9 +10507,12 @@
         <v>2.31</v>
       </c>
       <c r="I272" s="1" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="J272" s="1" t="n">
+      <c r="K272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -9725,9 +10544,12 @@
         <v>0.05462</v>
       </c>
       <c r="I273" s="1" t="n">
-        <v>0.05471</v>
+        <v>0.05473</v>
       </c>
       <c r="J273" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="K273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -9759,9 +10581,12 @@
         <v>0.02303</v>
       </c>
       <c r="I274" s="1" t="n">
+        <v>0.02293</v>
+      </c>
+      <c r="J274" s="1" t="n">
         <v>0.02303</v>
       </c>
-      <c r="J274" s="1" t="n">
+      <c r="K274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -9793,9 +10618,12 @@
         <v>1.184</v>
       </c>
       <c r="I275" s="1" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="J275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="J275" s="1" t="n">
+      <c r="K275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -9827,9 +10655,12 @@
         <v>0.2724</v>
       </c>
       <c r="I276" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="J276" s="1" t="n">
+      <c r="K276" s="1" t="n">
         <v>0.2722</v>
       </c>
     </row>
@@ -9861,9 +10692,12 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="I277" s="1" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="J277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="J277" s="1" t="n">
+      <c r="K277" s="1" t="n">
         <v>0.9419999999999999</v>
       </c>
     </row>
@@ -9895,9 +10729,12 @@
         <v>0.6272</v>
       </c>
       <c r="I278" s="1" t="n">
+        <v>0.6268</v>
+      </c>
+      <c r="J278" s="1" t="n">
         <v>0.6274999999999999</v>
       </c>
-      <c r="J278" s="1" t="n">
+      <c r="K278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -9929,9 +10766,12 @@
         <v>0.001346</v>
       </c>
       <c r="I279" s="1" t="n">
+        <v>0.001346</v>
+      </c>
+      <c r="J279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="J279" s="1" t="n">
+      <c r="K279" s="1" t="n">
         <v>0.001346</v>
       </c>
     </row>
@@ -9963,9 +10803,12 @@
         <v>0.005553</v>
       </c>
       <c r="I280" s="1" t="n">
-        <v>0.005557</v>
+        <v>0.005567</v>
       </c>
       <c r="J280" s="1" t="n">
+        <v>0.005567</v>
+      </c>
+      <c r="K280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -9997,10 +10840,13 @@
         <v>1.522</v>
       </c>
       <c r="I281" s="1" t="n">
+        <v>1.521</v>
+      </c>
+      <c r="J281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="J281" s="1" t="n">
-        <v>1.522</v>
+      <c r="K281" s="1" t="n">
+        <v>1.521</v>
       </c>
     </row>
     <row r="282">
@@ -10031,9 +10877,12 @@
         <v>28.39</v>
       </c>
       <c r="I282" s="1" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="J282" s="1" t="n">
+      <c r="K282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -10065,9 +10914,12 @@
         <v>0.12892</v>
       </c>
       <c r="I283" s="1" t="n">
+        <v>0.12901</v>
+      </c>
+      <c r="J283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="J283" s="1" t="n">
+      <c r="K283" s="1" t="n">
         <v>0.12892</v>
       </c>
     </row>
@@ -10099,9 +10951,12 @@
         <v>0.01114</v>
       </c>
       <c r="I284" s="1" t="n">
+        <v>0.01113</v>
+      </c>
+      <c r="J284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="J284" s="1" t="n">
+      <c r="K284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -10133,9 +10988,12 @@
         <v>6.542</v>
       </c>
       <c r="I285" s="1" t="n">
-        <v>6.544</v>
+        <v>6.548</v>
       </c>
       <c r="J285" s="1" t="n">
+        <v>6.548</v>
+      </c>
+      <c r="K285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -10167,9 +11025,12 @@
         <v>0.01851</v>
       </c>
       <c r="I286" s="1" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="J286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="J286" s="1" t="n">
+      <c r="K286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -10201,10 +11062,13 @@
         <v>0.00842</v>
       </c>
       <c r="I287" s="1" t="n">
+        <v>0.008404</v>
+      </c>
+      <c r="J287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="J287" s="1" t="n">
-        <v>0.008404999999999999</v>
+      <c r="K287" s="1" t="n">
+        <v>0.008404</v>
       </c>
     </row>
     <row r="288">
@@ -10235,9 +11099,12 @@
         <v>0.3846</v>
       </c>
       <c r="I288" s="1" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="J288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="J288" s="1" t="n">
+      <c r="K288" s="1" t="n">
         <v>0.3846</v>
       </c>
     </row>
@@ -10269,9 +11136,12 @@
         <v>0.01008</v>
       </c>
       <c r="I289" s="1" t="n">
+        <v>0.010099</v>
+      </c>
+      <c r="J289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="J289" s="1" t="n">
+      <c r="K289" s="1" t="n">
         <v>0.01008</v>
       </c>
     </row>
@@ -10303,10 +11173,13 @@
         <v>0.02618</v>
       </c>
       <c r="I290" s="1" t="n">
+        <v>0.02611</v>
+      </c>
+      <c r="J290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="J290" s="1" t="n">
-        <v>0.02613</v>
+      <c r="K290" s="1" t="n">
+        <v>0.02611</v>
       </c>
     </row>
     <row r="291">
@@ -10340,6 +11213,9 @@
         <v>0.097</v>
       </c>
       <c r="J291" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -10371,9 +11247,12 @@
         <v>0.28523</v>
       </c>
       <c r="I292" s="1" t="n">
-        <v>0.2861</v>
+        <v>0.28632</v>
       </c>
       <c r="J292" s="1" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="K292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -10405,9 +11284,12 @@
         <v>0.01543</v>
       </c>
       <c r="I293" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="J293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="J293" s="1" t="n">
+      <c r="K293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -10439,9 +11321,12 @@
         <v>0.003423</v>
       </c>
       <c r="I294" s="1" t="n">
-        <v>0.003425</v>
+        <v>0.003443</v>
       </c>
       <c r="J294" s="1" t="n">
+        <v>0.003443</v>
+      </c>
+      <c r="K294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -10473,10 +11358,13 @@
         <v>0.043213</v>
       </c>
       <c r="I295" s="1" t="n">
+        <v>0.043008</v>
+      </c>
+      <c r="J295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="J295" s="1" t="n">
-        <v>0.043213</v>
+      <c r="K295" s="1" t="n">
+        <v>0.043008</v>
       </c>
     </row>
     <row r="296">
@@ -10507,9 +11395,12 @@
         <v>0.02929</v>
       </c>
       <c r="I296" s="1" t="n">
+        <v>0.02965</v>
+      </c>
+      <c r="J296" s="1" t="n">
         <v>0.03007</v>
       </c>
-      <c r="J296" s="1" t="n">
+      <c r="K296" s="1" t="n">
         <v>0.02929</v>
       </c>
     </row>
@@ -10541,9 +11432,12 @@
         <v>0.03821</v>
       </c>
       <c r="I297" s="1" t="n">
+        <v>0.03792</v>
+      </c>
+      <c r="J297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="J297" s="1" t="n">
+      <c r="K297" s="1" t="n">
         <v>0.03786</v>
       </c>
     </row>
@@ -10575,9 +11469,12 @@
         <v>0.08316</v>
       </c>
       <c r="I298" s="1" t="n">
+        <v>0.08312</v>
+      </c>
+      <c r="J298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="J298" s="1" t="n">
+      <c r="K298" s="1" t="n">
         <v>0.08305999999999999</v>
       </c>
     </row>
@@ -10612,6 +11509,9 @@
         <v>0.00766</v>
       </c>
       <c r="J299" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="K299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -10643,10 +11543,13 @@
         <v>0.01513</v>
       </c>
       <c r="I300" s="1" t="n">
+        <v>0.01512</v>
+      </c>
+      <c r="J300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="J300" s="1" t="n">
-        <v>0.01513</v>
+      <c r="K300" s="1" t="n">
+        <v>0.01512</v>
       </c>
     </row>
     <row r="301">
@@ -10677,9 +11580,12 @@
         <v>0.1412</v>
       </c>
       <c r="I301" s="1" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="J301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="J301" s="1" t="n">
+      <c r="K301" s="1" t="n">
         <v>0.141</v>
       </c>
     </row>
@@ -10711,10 +11617,13 @@
         <v>0.0006304</v>
       </c>
       <c r="I302" s="1" t="n">
+        <v>0.0006284</v>
+      </c>
+      <c r="J302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="J302" s="1" t="n">
-        <v>0.0006304</v>
+      <c r="K302" s="1" t="n">
+        <v>0.0006284</v>
       </c>
     </row>
     <row r="303">
@@ -10745,9 +11654,12 @@
         <v>0.06218</v>
       </c>
       <c r="I303" s="1" t="n">
+        <v>0.06222</v>
+      </c>
+      <c r="J303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="J303" s="1" t="n">
+      <c r="K303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -10779,9 +11691,12 @@
         <v>0.0001633</v>
       </c>
       <c r="I304" s="1" t="n">
+        <v>0.0001634</v>
+      </c>
+      <c r="J304" s="1" t="n">
         <v>0.0001639</v>
       </c>
-      <c r="J304" s="1" t="n">
+      <c r="K304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -10813,9 +11728,12 @@
         <v>0.06125</v>
       </c>
       <c r="I305" s="1" t="n">
-        <v>0.06144</v>
+        <v>0.06147</v>
       </c>
       <c r="J305" s="1" t="n">
+        <v>0.06147</v>
+      </c>
+      <c r="K305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -10847,9 +11765,12 @@
         <v>0.022359</v>
       </c>
       <c r="I306" s="1" t="n">
+        <v>0.022377</v>
+      </c>
+      <c r="J306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="J306" s="1" t="n">
+      <c r="K306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -10881,9 +11802,12 @@
         <v>0.02332</v>
       </c>
       <c r="I307" s="1" t="n">
-        <v>0.02414</v>
+        <v>0.02423</v>
       </c>
       <c r="J307" s="1" t="n">
+        <v>0.02423</v>
+      </c>
+      <c r="K307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -10915,10 +11839,13 @@
         <v>0.000411</v>
       </c>
       <c r="I308" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="J308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="J308" s="1" t="n">
-        <v>0.000411</v>
+      <c r="K308" s="1" t="n">
+        <v>0.00041</v>
       </c>
     </row>
     <row r="309">
@@ -10949,9 +11876,12 @@
         <v>0.0898</v>
       </c>
       <c r="I309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="J309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="J309" s="1" t="n">
+      <c r="K309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -10983,9 +11913,12 @@
         <v>0.3842</v>
       </c>
       <c r="I310" s="1" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="J310" s="1" t="n">
+      <c r="K310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -11017,9 +11950,12 @@
         <v>0.0355</v>
       </c>
       <c r="I311" s="1" t="n">
+        <v>0.0355</v>
+      </c>
+      <c r="J311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="J311" s="1" t="n">
+      <c r="K311" s="1" t="n">
         <v>0.0355</v>
       </c>
     </row>
@@ -11051,9 +11987,12 @@
         <v>0.02472</v>
       </c>
       <c r="I312" s="1" t="n">
+        <v>0.02463</v>
+      </c>
+      <c r="J312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="J312" s="1" t="n">
+      <c r="K312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -11085,9 +12024,12 @@
         <v>0.04129</v>
       </c>
       <c r="I313" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="J313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="J313" s="1" t="n">
+      <c r="K313" s="1" t="n">
         <v>0.04129</v>
       </c>
     </row>
@@ -11122,6 +12064,9 @@
         <v>4.015</v>
       </c>
       <c r="J314" s="1" t="n">
+        <v>4.015</v>
+      </c>
+      <c r="K314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -11153,9 +12098,12 @@
         <v>0.1602</v>
       </c>
       <c r="I315" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="J315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="J315" s="1" t="n">
+      <c r="K315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -11187,9 +12135,12 @@
         <v>0.08873</v>
       </c>
       <c r="I316" s="1" t="n">
+        <v>0.08848</v>
+      </c>
+      <c r="J316" s="1" t="n">
         <v>0.08884</v>
       </c>
-      <c r="J316" s="1" t="n">
+      <c r="K316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -11221,9 +12172,12 @@
         <v>0.06849</v>
       </c>
       <c r="I317" s="1" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="J317" s="1" t="n">
         <v>0.06849</v>
       </c>
-      <c r="J317" s="1" t="n">
+      <c r="K317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -11255,10 +12209,13 @@
         <v>0.012534</v>
       </c>
       <c r="I318" s="1" t="n">
+        <v>0.012463</v>
+      </c>
+      <c r="J318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="J318" s="1" t="n">
-        <v>0.012534</v>
+      <c r="K318" s="1" t="n">
+        <v>0.012463</v>
       </c>
     </row>
     <row r="319">
@@ -11289,9 +12246,12 @@
         <v>0.001136</v>
       </c>
       <c r="I319" s="1" t="n">
+        <v>0.001136</v>
+      </c>
+      <c r="J319" s="1" t="n">
         <v>0.001138</v>
       </c>
-      <c r="J319" s="1" t="n">
+      <c r="K319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -11323,9 +12283,12 @@
         <v>0.0631</v>
       </c>
       <c r="I320" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="J320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="J320" s="1" t="n">
+      <c r="K320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -11360,6 +12323,9 @@
         <v>0.00527</v>
       </c>
       <c r="J321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="K321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -11394,6 +12360,9 @@
         <v>0.1116</v>
       </c>
       <c r="J322" s="1" t="n">
+        <v>0.1116</v>
+      </c>
+      <c r="K322" s="1" t="n">
         <v>0.1114</v>
       </c>
     </row>
@@ -11425,9 +12394,12 @@
         <v>0.04277</v>
       </c>
       <c r="I323" s="1" t="n">
-        <v>0.04277</v>
+        <v>0.04304</v>
       </c>
       <c r="J323" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="K323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -11459,9 +12431,12 @@
         <v>0.01783</v>
       </c>
       <c r="I324" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="J324" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="J324" s="1" t="n">
+      <c r="K324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -11493,10 +12468,13 @@
         <v>0.00568</v>
       </c>
       <c r="I325" s="1" t="n">
+        <v>0.005663</v>
+      </c>
+      <c r="J325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="J325" s="1" t="n">
-        <v>0.00568</v>
+      <c r="K325" s="1" t="n">
+        <v>0.005663</v>
       </c>
     </row>
     <row r="326">
@@ -11527,9 +12505,12 @@
         <v>0.00177</v>
       </c>
       <c r="I326" s="1" t="n">
+        <v>0.001775</v>
+      </c>
+      <c r="J326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="J326" s="1" t="n">
+      <c r="K326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -11561,10 +12542,13 @@
         <v>0.04057</v>
       </c>
       <c r="I327" s="1" t="n">
+        <v>0.04047</v>
+      </c>
+      <c r="J327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="J327" s="1" t="n">
-        <v>0.04057</v>
+      <c r="K327" s="1" t="n">
+        <v>0.04047</v>
       </c>
     </row>
     <row r="328">
@@ -11595,10 +12579,13 @@
         <v>0.053804</v>
       </c>
       <c r="I328" s="1" t="n">
+        <v>0.053664</v>
+      </c>
+      <c r="J328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="J328" s="1" t="n">
-        <v>0.053804</v>
+      <c r="K328" s="1" t="n">
+        <v>0.053664</v>
       </c>
     </row>
     <row r="329">
@@ -11629,9 +12616,12 @@
         <v>0.2791</v>
       </c>
       <c r="I329" s="1" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="J329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="J329" s="1" t="n">
+      <c r="K329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -11663,10 +12653,13 @@
         <v>0.1595</v>
       </c>
       <c r="I330" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="J330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="J330" s="1" t="n">
-        <v>0.1593</v>
+      <c r="K330" s="1" t="n">
+        <v>0.159</v>
       </c>
     </row>
     <row r="331">
@@ -11697,9 +12690,12 @@
         <v>0.05353</v>
       </c>
       <c r="I331" s="1" t="n">
-        <v>0.05358</v>
+        <v>0.05364</v>
       </c>
       <c r="J331" s="1" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="K331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -11731,9 +12727,12 @@
         <v>0.3608</v>
       </c>
       <c r="I332" s="1" t="n">
-        <v>0.361</v>
+        <v>0.3618</v>
       </c>
       <c r="J332" s="1" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="K332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -11765,9 +12764,12 @@
         <v>0.03049</v>
       </c>
       <c r="I333" s="1" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="J333" s="1" t="n">
         <v>0.03049</v>
       </c>
-      <c r="J333" s="1" t="n">
+      <c r="K333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -11799,9 +12801,12 @@
         <v>0.01832</v>
       </c>
       <c r="I334" s="1" t="n">
-        <v>0.01832</v>
+        <v>0.01868</v>
       </c>
       <c r="J334" s="1" t="n">
+        <v>0.01868</v>
+      </c>
+      <c r="K334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -11833,9 +12838,12 @@
         <v>0.0582</v>
       </c>
       <c r="I335" s="1" t="n">
-        <v>0.0582</v>
+        <v>0.0583</v>
       </c>
       <c r="J335" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="K335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -11867,9 +12875,12 @@
         <v>0.09175999999999999</v>
       </c>
       <c r="I336" s="1" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="J336" s="1" t="n">
         <v>0.09182</v>
       </c>
-      <c r="J336" s="1" t="n">
+      <c r="K336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -11901,9 +12912,12 @@
         <v>0.18293</v>
       </c>
       <c r="I337" s="1" t="n">
+        <v>0.18085</v>
+      </c>
+      <c r="J337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="J337" s="1" t="n">
+      <c r="K337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -11935,9 +12949,12 @@
         <v>0.02106</v>
       </c>
       <c r="I338" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="J338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="J338" s="1" t="n">
+      <c r="K338" s="1" t="n">
         <v>0.02106</v>
       </c>
     </row>
@@ -11969,10 +12986,13 @@
         <v>0.1312</v>
       </c>
       <c r="I339" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="J339" s="1" t="n">
         <v>0.1315</v>
       </c>
-      <c r="J339" s="1" t="n">
-        <v>0.1312</v>
+      <c r="K339" s="1" t="n">
+        <v>0.1311</v>
       </c>
     </row>
     <row r="340">
@@ -12003,9 +13023,12 @@
         <v>0.007946</v>
       </c>
       <c r="I340" s="1" t="n">
+        <v>0.007989</v>
+      </c>
+      <c r="J340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="J340" s="1" t="n">
+      <c r="K340" s="1" t="n">
         <v>0.007946</v>
       </c>
     </row>
@@ -12037,9 +13060,12 @@
         <v>4.406</v>
       </c>
       <c r="I341" s="1" t="n">
+        <v>4.396</v>
+      </c>
+      <c r="J341" s="1" t="n">
         <v>4.407</v>
       </c>
-      <c r="J341" s="1" t="n">
+      <c r="K341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -12071,9 +13097,12 @@
         <v>0.19251</v>
       </c>
       <c r="I342" s="1" t="n">
+        <v>0.19333</v>
+      </c>
+      <c r="J342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="J342" s="1" t="n">
+      <c r="K342" s="1" t="n">
         <v>0.19148</v>
       </c>
     </row>
@@ -12105,9 +13134,12 @@
         <v>0.08314000000000001</v>
       </c>
       <c r="I343" s="1" t="n">
-        <v>0.08325</v>
+        <v>0.08334</v>
       </c>
       <c r="J343" s="1" t="n">
+        <v>0.08334</v>
+      </c>
+      <c r="K343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -12139,10 +13171,13 @@
         <v>0.1831</v>
       </c>
       <c r="I344" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="J344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="J344" s="1" t="n">
-        <v>0.1829</v>
+      <c r="K344" s="1" t="n">
+        <v>0.1821</v>
       </c>
     </row>
     <row r="345">
@@ -12173,9 +13208,12 @@
         <v>0.00325</v>
       </c>
       <c r="I345" s="1" t="n">
+        <v>0.003253</v>
+      </c>
+      <c r="J345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="J345" s="1" t="n">
+      <c r="K345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -12207,9 +13245,12 @@
         <v>0.09168</v>
       </c>
       <c r="I346" s="1" t="n">
-        <v>0.09204</v>
+        <v>0.09209000000000001</v>
       </c>
       <c r="J346" s="1" t="n">
+        <v>0.09209000000000001</v>
+      </c>
+      <c r="K346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -12241,10 +13282,13 @@
         <v>2.25</v>
       </c>
       <c r="I347" s="1" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="J347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="J347" s="1" t="n">
-        <v>2.25</v>
+      <c r="K347" s="1" t="n">
+        <v>2.247</v>
       </c>
     </row>
     <row r="348">
@@ -12275,9 +13319,12 @@
         <v>0.3054</v>
       </c>
       <c r="I348" s="1" t="n">
-        <v>0.3059</v>
+        <v>0.3061</v>
       </c>
       <c r="J348" s="1" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="K348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -12309,9 +13356,12 @@
         <v>0.02988</v>
       </c>
       <c r="I349" s="1" t="n">
+        <v>0.02981</v>
+      </c>
+      <c r="J349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="J349" s="1" t="n">
+      <c r="K349" s="1" t="n">
         <v>0.02981</v>
       </c>
     </row>
@@ -12343,9 +13393,12 @@
         <v>0.128</v>
       </c>
       <c r="I350" s="1" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="J350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="J350" s="1" t="n">
+      <c r="K350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -12377,9 +13430,12 @@
         <v>0.06714000000000001</v>
       </c>
       <c r="I351" s="1" t="n">
+        <v>0.06709</v>
+      </c>
+      <c r="J351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="J351" s="1" t="n">
+      <c r="K351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -12411,9 +13467,12 @@
         <v>0.06241</v>
       </c>
       <c r="I352" s="1" t="n">
+        <v>0.06242</v>
+      </c>
+      <c r="J352" s="1" t="n">
         <v>0.06251</v>
       </c>
-      <c r="J352" s="1" t="n">
+      <c r="K352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -12445,9 +13504,12 @@
         <v>0.06353</v>
       </c>
       <c r="I353" s="1" t="n">
+        <v>0.06358999999999999</v>
+      </c>
+      <c r="J353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="J353" s="1" t="n">
+      <c r="K353" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -12479,9 +13541,12 @@
         <v>0.10603</v>
       </c>
       <c r="I354" s="1" t="n">
+        <v>0.10487</v>
+      </c>
+      <c r="J354" s="1" t="n">
         <v>0.10603</v>
       </c>
-      <c r="J354" s="1" t="n">
+      <c r="K354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -12513,9 +13578,12 @@
         <v>0.0901</v>
       </c>
       <c r="I355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="J355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="J355" s="1" t="n">
+      <c r="K355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -12547,9 +13615,12 @@
         <v>0.06985</v>
       </c>
       <c r="I356" s="1" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="J356" s="1" t="n">
         <v>0.07054000000000001</v>
       </c>
-      <c r="J356" s="1" t="n">
+      <c r="K356" s="1" t="n">
         <v>0.06985</v>
       </c>
     </row>
@@ -12581,10 +13652,13 @@
         <v>0.4527</v>
       </c>
       <c r="I357" s="1" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="J357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="J357" s="1" t="n">
-        <v>0.4523</v>
+      <c r="K357" s="1" t="n">
+        <v>0.4521</v>
       </c>
     </row>
     <row r="358">
@@ -12615,9 +13689,12 @@
         <v>0.03489</v>
       </c>
       <c r="I358" s="1" t="n">
+        <v>0.03494</v>
+      </c>
+      <c r="J358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="J358" s="1" t="n">
+      <c r="K358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -12649,9 +13726,12 @@
         <v>0.01478</v>
       </c>
       <c r="I359" s="1" t="n">
+        <v>0.01477</v>
+      </c>
+      <c r="J359" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="J359" s="1" t="n">
+      <c r="K359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -12683,9 +13763,12 @@
         <v>0.13385</v>
       </c>
       <c r="I360" s="1" t="n">
+        <v>0.13379</v>
+      </c>
+      <c r="J360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="J360" s="1" t="n">
+      <c r="K360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -12717,9 +13800,12 @@
         <v>0.0005902</v>
       </c>
       <c r="I361" s="1" t="n">
+        <v>0.0005897</v>
+      </c>
+      <c r="J361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="J361" s="1" t="n">
+      <c r="K361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -12751,9 +13837,12 @@
         <v>0.03884</v>
       </c>
       <c r="I362" s="1" t="n">
+        <v>0.03873</v>
+      </c>
+      <c r="J362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="J362" s="1" t="n">
+      <c r="K362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -12785,9 +13874,12 @@
         <v>3.204</v>
       </c>
       <c r="I363" s="1" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="J363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="J363" s="1" t="n">
+      <c r="K363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -12819,9 +13911,12 @@
         <v>0.1655</v>
       </c>
       <c r="I364" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="J364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="J364" s="1" t="n">
+      <c r="K364" s="1" t="n">
         <v>0.1655</v>
       </c>
     </row>
@@ -12853,9 +13948,12 @@
         <v>0.1135</v>
       </c>
       <c r="I365" s="1" t="n">
+        <v>0.1134</v>
+      </c>
+      <c r="J365" s="1" t="n">
         <v>0.1136</v>
       </c>
-      <c r="J365" s="1" t="n">
+      <c r="K365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -12887,9 +13985,12 @@
         <v>0.0006451</v>
       </c>
       <c r="I366" s="1" t="n">
+        <v>0.0006436</v>
+      </c>
+      <c r="J366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="J366" s="1" t="n">
+      <c r="K366" s="1" t="n">
         <v>0.0006419</v>
       </c>
     </row>
@@ -12921,9 +14022,12 @@
         <v>0.05927</v>
       </c>
       <c r="I367" s="1" t="n">
+        <v>0.05934</v>
+      </c>
+      <c r="J367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="J367" s="1" t="n">
+      <c r="K367" s="1" t="n">
         <v>0.05927</v>
       </c>
     </row>
@@ -12955,9 +14059,12 @@
         <v>0.08286</v>
       </c>
       <c r="I368" s="1" t="n">
+        <v>0.08322</v>
+      </c>
+      <c r="J368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="J368" s="1" t="n">
+      <c r="K368" s="1" t="n">
         <v>0.0825</v>
       </c>
     </row>
@@ -12989,9 +14096,12 @@
         <v>0.03976</v>
       </c>
       <c r="I369" s="1" t="n">
-        <v>0.04</v>
+        <v>0.04038</v>
       </c>
       <c r="J369" s="1" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="K369" s="1" t="n">
         <v>0.03976</v>
       </c>
     </row>
@@ -13023,9 +14133,12 @@
         <v>3.714</v>
       </c>
       <c r="I370" s="1" t="n">
+        <v>3.712</v>
+      </c>
+      <c r="J370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="J370" s="1" t="n">
+      <c r="K370" s="1" t="n">
         <v>3.709</v>
       </c>
     </row>
@@ -13057,9 +14170,12 @@
         <v>0.1216</v>
       </c>
       <c r="I371" s="1" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="J371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="J371" s="1" t="n">
+      <c r="K371" s="1" t="n">
         <v>0.1216</v>
       </c>
     </row>
@@ -13091,9 +14207,12 @@
         <v>0.01474</v>
       </c>
       <c r="I372" s="1" t="n">
+        <v>0.01475</v>
+      </c>
+      <c r="J372" s="1" t="n">
         <v>0.01479</v>
       </c>
-      <c r="J372" s="1" t="n">
+      <c r="K372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -13125,9 +14244,12 @@
         <v>0.02195</v>
       </c>
       <c r="I373" s="1" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="J373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="J373" s="1" t="n">
+      <c r="K373" s="1" t="n">
         <v>0.02192</v>
       </c>
     </row>
@@ -13159,9 +14281,12 @@
         <v>1.8624</v>
       </c>
       <c r="I374" s="1" t="n">
-        <v>1.8624</v>
+        <v>1.863</v>
       </c>
       <c r="J374" s="1" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="K374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -13193,9 +14318,12 @@
         <v>0.02107</v>
       </c>
       <c r="I375" s="1" t="n">
+        <v>0.02108</v>
+      </c>
+      <c r="J375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="J375" s="1" t="n">
+      <c r="K375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -13227,9 +14355,12 @@
         <v>1.3</v>
       </c>
       <c r="I376" s="1" t="n">
-        <v>1.301</v>
+        <v>1.317</v>
       </c>
       <c r="J376" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="K376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -13261,10 +14392,13 @@
         <v>0.283</v>
       </c>
       <c r="I377" s="1" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="J377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="J377" s="1" t="n">
-        <v>0.283</v>
+      <c r="K377" s="1" t="n">
+        <v>0.2829</v>
       </c>
     </row>
     <row r="378">
@@ -13295,10 +14429,13 @@
         <v>0.01554</v>
       </c>
       <c r="I378" s="1" t="n">
+        <v>0.01549</v>
+      </c>
+      <c r="J378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="J378" s="1" t="n">
-        <v>0.01554</v>
+      <c r="K378" s="1" t="n">
+        <v>0.01549</v>
       </c>
     </row>
     <row r="379">
@@ -13329,9 +14466,12 @@
         <v>1.5293</v>
       </c>
       <c r="I379" s="1" t="n">
+        <v>1.5305</v>
+      </c>
+      <c r="J379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="J379" s="1" t="n">
+      <c r="K379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -13363,10 +14503,13 @@
         <v>6.952999999999999e-05</v>
       </c>
       <c r="I380" s="1" t="n">
+        <v>6.939e-05</v>
+      </c>
+      <c r="J380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="J380" s="1" t="n">
-        <v>6.952999999999999e-05</v>
+      <c r="K380" s="1" t="n">
+        <v>6.939e-05</v>
       </c>
     </row>
     <row r="381">
@@ -13397,10 +14540,13 @@
         <v>2.548</v>
       </c>
       <c r="I381" s="1" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="J381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="J381" s="1" t="n">
-        <v>2.548</v>
+      <c r="K381" s="1" t="n">
+        <v>2.545</v>
       </c>
     </row>
     <row r="382">
@@ -13431,9 +14577,12 @@
         <v>0.06747</v>
       </c>
       <c r="I382" s="1" t="n">
+        <v>0.06745</v>
+      </c>
+      <c r="J382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="J382" s="1" t="n">
+      <c r="K382" s="1" t="n">
         <v>0.06738</v>
       </c>
     </row>
@@ -13465,9 +14614,12 @@
         <v>0.01718</v>
       </c>
       <c r="I383" s="1" t="n">
+        <v>0.01734</v>
+      </c>
+      <c r="J383" s="1" t="n">
         <v>0.01758</v>
       </c>
-      <c r="J383" s="1" t="n">
+      <c r="K383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -13499,9 +14651,12 @@
         <v>0.05142</v>
       </c>
       <c r="I384" s="1" t="n">
-        <v>0.05142</v>
+        <v>0.05176</v>
       </c>
       <c r="J384" s="1" t="n">
+        <v>0.05176</v>
+      </c>
+      <c r="K384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -13533,9 +14688,12 @@
         <v>7.584</v>
       </c>
       <c r="I385" s="1" t="n">
+        <v>7.583</v>
+      </c>
+      <c r="J385" s="1" t="n">
         <v>7.585</v>
       </c>
-      <c r="J385" s="1" t="n">
+      <c r="K385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -13567,9 +14725,12 @@
         <v>0.003293</v>
       </c>
       <c r="I386" s="1" t="n">
-        <v>0.003299</v>
+        <v>0.003301</v>
       </c>
       <c r="J386" s="1" t="n">
+        <v>0.003301</v>
+      </c>
+      <c r="K386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -13601,10 +14762,13 @@
         <v>0.0003839</v>
       </c>
       <c r="I387" s="1" t="n">
+        <v>0.000383</v>
+      </c>
+      <c r="J387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="J387" s="1" t="n">
-        <v>0.0003838</v>
+      <c r="K387" s="1" t="n">
+        <v>0.000383</v>
       </c>
     </row>
     <row r="388">
@@ -13635,10 +14799,13 @@
         <v>0.00966</v>
       </c>
       <c r="I388" s="1" t="n">
+        <v>0.00962</v>
+      </c>
+      <c r="J388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="J388" s="1" t="n">
-        <v>0.00966</v>
+      <c r="K388" s="1" t="n">
+        <v>0.00962</v>
       </c>
     </row>
     <row r="389">
@@ -13669,9 +14836,12 @@
         <v>0.289</v>
       </c>
       <c r="I389" s="1" t="n">
-        <v>0.2891</v>
+        <v>0.2902</v>
       </c>
       <c r="J389" s="1" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="K389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -13703,9 +14873,12 @@
         <v>0.0249</v>
       </c>
       <c r="I390" s="1" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="J390" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="J390" s="1" t="n">
+      <c r="K390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -13737,9 +14910,12 @@
         <v>2.833</v>
       </c>
       <c r="I391" s="1" t="n">
+        <v>2.823</v>
+      </c>
+      <c r="J391" s="1" t="n">
         <v>2.833</v>
       </c>
-      <c r="J391" s="1" t="n">
+      <c r="K391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -13771,10 +14947,13 @@
         <v>0.01341</v>
       </c>
       <c r="I392" s="1" t="n">
+        <v>0.01338</v>
+      </c>
+      <c r="J392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="J392" s="1" t="n">
-        <v>0.0134</v>
+      <c r="K392" s="1" t="n">
+        <v>0.01338</v>
       </c>
     </row>
     <row r="393">
@@ -13805,9 +14984,12 @@
         <v>0.00235</v>
       </c>
       <c r="I393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="J393" s="1" t="n">
         <v>0.00236</v>
       </c>
-      <c r="J393" s="1" t="n">
+      <c r="K393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -13839,9 +15021,12 @@
         <v>0.0594</v>
       </c>
       <c r="I394" s="1" t="n">
+        <v>0.05944</v>
+      </c>
+      <c r="J394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="J394" s="1" t="n">
+      <c r="K394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -13873,10 +15058,13 @@
         <v>0.0403</v>
       </c>
       <c r="I395" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="J395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="J395" s="1" t="n">
-        <v>0.0403</v>
+      <c r="K395" s="1" t="n">
+        <v>0.0402</v>
       </c>
     </row>
     <row r="396">
@@ -13907,9 +15095,12 @@
         <v>0.09217</v>
       </c>
       <c r="I396" s="1" t="n">
+        <v>0.09211999999999999</v>
+      </c>
+      <c r="J396" s="1" t="n">
         <v>0.09217</v>
       </c>
-      <c r="J396" s="1" t="n">
+      <c r="K396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -13941,9 +15132,12 @@
         <v>0.1517</v>
       </c>
       <c r="I397" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="J397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="J397" s="1" t="n">
+      <c r="K397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -13975,9 +15169,12 @@
         <v>0.928</v>
       </c>
       <c r="I398" s="1" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="J398" s="1" t="n">
         <v>0.929</v>
       </c>
-      <c r="J398" s="1" t="n">
+      <c r="K398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -14009,9 +15206,12 @@
         <v>0.05246</v>
       </c>
       <c r="I399" s="1" t="n">
-        <v>0.0525</v>
+        <v>0.05254</v>
       </c>
       <c r="J399" s="1" t="n">
+        <v>0.05254</v>
+      </c>
+      <c r="K399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -14043,9 +15243,12 @@
         <v>2.521</v>
       </c>
       <c r="I400" s="1" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="J400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="J400" s="1" t="n">
+      <c r="K400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -14077,9 +15280,12 @@
         <v>0.018</v>
       </c>
       <c r="I401" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="J401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="J401" s="1" t="n">
+      <c r="K401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -14111,9 +15317,12 @@
         <v>0.08075</v>
       </c>
       <c r="I402" s="1" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="J402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="J402" s="1" t="n">
+      <c r="K402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -14145,9 +15354,12 @@
         <v>1.2471</v>
       </c>
       <c r="I403" s="1" t="n">
+        <v>1.2474</v>
+      </c>
+      <c r="J403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="J403" s="1" t="n">
+      <c r="K403" s="1" t="n">
         <v>1.2471</v>
       </c>
     </row>
@@ -14179,9 +15391,12 @@
         <v>0.00718</v>
       </c>
       <c r="I404" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="J404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="J404" s="1" t="n">
+      <c r="K404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -14213,9 +15428,12 @@
         <v>0.4949</v>
       </c>
       <c r="I405" s="1" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="J405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="J405" s="1" t="n">
+      <c r="K405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -14247,9 +15465,12 @@
         <v>0.01149</v>
       </c>
       <c r="I406" s="1" t="n">
-        <v>0.01152</v>
+        <v>0.01153</v>
       </c>
       <c r="J406" s="1" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="K406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -14281,10 +15502,13 @@
         <v>0.04633</v>
       </c>
       <c r="I407" s="1" t="n">
+        <v>0.04624</v>
+      </c>
+      <c r="J407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="J407" s="1" t="n">
-        <v>0.04633</v>
+      <c r="K407" s="1" t="n">
+        <v>0.04624</v>
       </c>
     </row>
     <row r="408">
@@ -14315,9 +15539,12 @@
         <v>0.03959</v>
       </c>
       <c r="I408" s="1" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="J408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="J408" s="1" t="n">
+      <c r="K408" s="1" t="n">
         <v>0.03947</v>
       </c>
     </row>
@@ -14349,10 +15576,13 @@
         <v>0.05258</v>
       </c>
       <c r="I409" s="1" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="J409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="J409" s="1" t="n">
-        <v>0.05258</v>
+      <c r="K409" s="1" t="n">
+        <v>0.05247</v>
       </c>
     </row>
     <row r="410">
@@ -14383,9 +15613,12 @@
         <v>0.01246</v>
       </c>
       <c r="I410" s="1" t="n">
+        <v>0.01253</v>
+      </c>
+      <c r="J410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="J410" s="1" t="n">
+      <c r="K410" s="1" t="n">
         <v>0.01245</v>
       </c>
     </row>
@@ -14417,10 +15650,13 @@
         <v>0.0639</v>
       </c>
       <c r="I411" s="1" t="n">
+        <v>0.06347</v>
+      </c>
+      <c r="J411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="J411" s="1" t="n">
-        <v>0.06378</v>
+      <c r="K411" s="1" t="n">
+        <v>0.06347</v>
       </c>
     </row>
     <row r="412">
@@ -14451,9 +15687,12 @@
         <v>0.04133</v>
       </c>
       <c r="I412" s="1" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="J412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="J412" s="1" t="n">
+      <c r="K412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -14488,6 +15727,9 @@
         <v>1.122</v>
       </c>
       <c r="J413" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="K413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -14519,10 +15761,13 @@
         <v>0.2633</v>
       </c>
       <c r="I414" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="J414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="J414" s="1" t="n">
-        <v>0.2633</v>
+      <c r="K414" s="1" t="n">
+        <v>0.2631</v>
       </c>
     </row>
     <row r="415">
@@ -14553,9 +15798,12 @@
         <v>0.001225</v>
       </c>
       <c r="I415" s="1" t="n">
+        <v>0.001223</v>
+      </c>
+      <c r="J415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="J415" s="1" t="n">
+      <c r="K415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -14587,9 +15835,12 @@
         <v>0.03198</v>
       </c>
       <c r="I416" s="1" t="n">
-        <v>0.03198</v>
+        <v>0.03207</v>
       </c>
       <c r="J416" s="1" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="K416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -14621,9 +15872,12 @@
         <v>0.0147</v>
       </c>
       <c r="I417" s="1" t="n">
+        <v>0.01462</v>
+      </c>
+      <c r="J417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="J417" s="1" t="n">
+      <c r="K417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -14655,9 +15909,12 @@
         <v>0.1484</v>
       </c>
       <c r="I418" s="1" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="J418" s="1" t="n">
         <v>0.1484</v>
       </c>
-      <c r="J418" s="1" t="n">
+      <c r="K418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -14689,9 +15946,12 @@
         <v>0.04921</v>
       </c>
       <c r="I419" s="1" t="n">
-        <v>0.04923</v>
+        <v>0.04943</v>
       </c>
       <c r="J419" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="K419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -14723,9 +15983,12 @@
         <v>66.40000000000001</v>
       </c>
       <c r="I420" s="1" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="J420" s="1" t="n">
         <v>66.7</v>
       </c>
-      <c r="J420" s="1" t="n">
+      <c r="K420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -14757,9 +16020,12 @@
         <v>0.877</v>
       </c>
       <c r="I421" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="J421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="J421" s="1" t="n">
+      <c r="K421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -14791,10 +16057,13 @@
         <v>0.012788</v>
       </c>
       <c r="I422" s="1" t="n">
+        <v>0.012681</v>
+      </c>
+      <c r="J422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="J422" s="1" t="n">
-        <v>0.012788</v>
+      <c r="K422" s="1" t="n">
+        <v>0.012681</v>
       </c>
     </row>
     <row r="423">
@@ -14825,9 +16094,12 @@
         <v>0.01596</v>
       </c>
       <c r="I423" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="J423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="J423" s="1" t="n">
+      <c r="K423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -14859,9 +16131,12 @@
         <v>0.27001</v>
       </c>
       <c r="I424" s="1" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="J424" s="1" t="n">
         <v>0.27001</v>
       </c>
-      <c r="J424" s="1" t="n">
+      <c r="K424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -14893,9 +16168,12 @@
         <v>0.6012999999999999</v>
       </c>
       <c r="I425" s="1" t="n">
+        <v>0.6007</v>
+      </c>
+      <c r="J425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="J425" s="1" t="n">
+      <c r="K425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -14927,9 +16205,12 @@
         <v>0.005563</v>
       </c>
       <c r="I426" s="1" t="n">
+        <v>0.00559</v>
+      </c>
+      <c r="J426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="J426" s="1" t="n">
+      <c r="K426" s="1" t="n">
         <v>0.005557</v>
       </c>
     </row>
@@ -14961,9 +16242,12 @@
         <v>0.04902</v>
       </c>
       <c r="I427" s="1" t="n">
+        <v>0.04906</v>
+      </c>
+      <c r="J427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="J427" s="1" t="n">
+      <c r="K427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -14995,9 +16279,12 @@
         <v>0.1265</v>
       </c>
       <c r="I428" s="1" t="n">
-        <v>0.1265</v>
+        <v>0.1266</v>
       </c>
       <c r="J428" s="1" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="K428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -15029,9 +16316,12 @@
         <v>0.003165</v>
       </c>
       <c r="I429" s="1" t="n">
+        <v>0.003165</v>
+      </c>
+      <c r="J429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="J429" s="1" t="n">
+      <c r="K429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -15063,10 +16353,13 @@
         <v>0.03642</v>
       </c>
       <c r="I430" s="1" t="n">
+        <v>0.03641</v>
+      </c>
+      <c r="J430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="J430" s="1" t="n">
-        <v>0.03642</v>
+      <c r="K430" s="1" t="n">
+        <v>0.03641</v>
       </c>
     </row>
     <row r="431">
@@ -15097,10 +16390,13 @@
         <v>0.3997</v>
       </c>
       <c r="I431" s="1" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="J431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="J431" s="1" t="n">
-        <v>0.3997</v>
+      <c r="K431" s="1" t="n">
+        <v>0.3982</v>
       </c>
     </row>
     <row r="432">
@@ -15131,9 +16427,12 @@
         <v>0.004522</v>
       </c>
       <c r="I432" s="1" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="J432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="J432" s="1" t="n">
+      <c r="K432" s="1" t="n">
         <v>0.004518</v>
       </c>
     </row>
@@ -15165,9 +16464,12 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I433" s="1" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="J433" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="J433" s="1" t="n">
+      <c r="K433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -15199,9 +16501,12 @@
         <v>0.0124</v>
       </c>
       <c r="I434" s="1" t="n">
-        <v>0.01244</v>
+        <v>0.01247</v>
       </c>
       <c r="J434" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="K434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -15233,9 +16538,12 @@
         <v>1.983</v>
       </c>
       <c r="I435" s="1" t="n">
-        <v>1.983</v>
+        <v>1.988</v>
       </c>
       <c r="J435" s="1" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="K435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -15267,9 +16575,12 @@
         <v>0.001882</v>
       </c>
       <c r="I436" s="1" t="n">
+        <v>0.001852</v>
+      </c>
+      <c r="J436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="J436" s="1" t="n">
+      <c r="K436" s="1" t="n">
         <v>0.001833</v>
       </c>
     </row>
@@ -15301,10 +16612,13 @@
         <v>0.4419</v>
       </c>
       <c r="I437" s="1" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="J437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="J437" s="1" t="n">
-        <v>0.4417</v>
+      <c r="K437" s="1" t="n">
+        <v>0.4415</v>
       </c>
     </row>
     <row r="438">
@@ -15335,9 +16649,12 @@
         <v>0.00535</v>
       </c>
       <c r="I438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="J438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="J438" s="1" t="n">
+      <c r="K438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -15369,9 +16686,12 @@
         <v>0.1034</v>
       </c>
       <c r="I439" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="J439" s="1" t="n">
         <v>0.1036</v>
       </c>
-      <c r="J439" s="1" t="n">
+      <c r="K439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -15403,9 +16723,12 @@
         <v>0.03419</v>
       </c>
       <c r="I440" s="1" t="n">
-        <v>0.03432</v>
+        <v>0.03445</v>
       </c>
       <c r="J440" s="1" t="n">
+        <v>0.03445</v>
+      </c>
+      <c r="K440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -15437,9 +16760,12 @@
         <v>0.08221000000000001</v>
       </c>
       <c r="I441" s="1" t="n">
+        <v>0.08205</v>
+      </c>
+      <c r="J441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="J441" s="1" t="n">
+      <c r="K441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -15471,9 +16797,12 @@
         <v>1.304</v>
       </c>
       <c r="I442" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="J442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="J442" s="1" t="n">
+      <c r="K442" s="1" t="n">
         <v>1.304</v>
       </c>
     </row>
@@ -15505,9 +16834,12 @@
         <v>0.07573000000000001</v>
       </c>
       <c r="I443" s="1" t="n">
-        <v>0.07573000000000001</v>
+        <v>0.07581</v>
       </c>
       <c r="J443" s="1" t="n">
+        <v>0.07581</v>
+      </c>
+      <c r="K443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -15539,9 +16871,12 @@
         <v>0.07689</v>
       </c>
       <c r="I444" s="1" t="n">
-        <v>0.07693</v>
+        <v>0.07701</v>
       </c>
       <c r="J444" s="1" t="n">
+        <v>0.07701</v>
+      </c>
+      <c r="K444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -15573,9 +16908,12 @@
         <v>0.04363</v>
       </c>
       <c r="I445" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="J445" s="1" t="n">
         <v>0.04386</v>
       </c>
-      <c r="J445" s="1" t="n">
+      <c r="K445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -15607,9 +16945,12 @@
         <v>0.02144</v>
       </c>
       <c r="I446" s="1" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="J446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="J446" s="1" t="n">
+      <c r="K446" s="1" t="n">
         <v>0.02144</v>
       </c>
     </row>
@@ -15644,6 +16985,9 @@
         <v>0.2816</v>
       </c>
       <c r="J447" s="1" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="K447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -15675,9 +17019,12 @@
         <v>0.031</v>
       </c>
       <c r="I448" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="J448" s="1" t="n">
+      <c r="K448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -15709,9 +17056,12 @@
         <v>0.00645</v>
       </c>
       <c r="I449" s="1" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="J449" s="1" t="n">
         <v>0.00646</v>
       </c>
-      <c r="J449" s="1" t="n">
+      <c r="K449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -15743,9 +17093,12 @@
         <v>0.022891</v>
       </c>
       <c r="I450" s="1" t="n">
-        <v>0.022996</v>
+        <v>0.023016</v>
       </c>
       <c r="J450" s="1" t="n">
+        <v>0.023016</v>
+      </c>
+      <c r="K450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -15777,9 +17130,12 @@
         <v>0.0425</v>
       </c>
       <c r="I451" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="J451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="J451" s="1" t="n">
+      <c r="K451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -15811,10 +17167,13 @@
         <v>0.07213</v>
       </c>
       <c r="I452" s="1" t="n">
+        <v>0.07205</v>
+      </c>
+      <c r="J452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="J452" s="1" t="n">
-        <v>0.07213</v>
+      <c r="K452" s="1" t="n">
+        <v>0.07205</v>
       </c>
     </row>
     <row r="453">
@@ -15845,9 +17204,12 @@
         <v>0.0005939</v>
       </c>
       <c r="I453" s="1" t="n">
-        <v>0.0005939</v>
+        <v>0.0005943</v>
       </c>
       <c r="J453" s="1" t="n">
+        <v>0.0005943</v>
+      </c>
+      <c r="K453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -15879,9 +17241,12 @@
         <v>0.31</v>
       </c>
       <c r="I454" s="1" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="J454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="J454" s="1" t="n">
+      <c r="K454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -15913,9 +17278,12 @@
         <v>0.004285</v>
       </c>
       <c r="I455" s="1" t="n">
-        <v>0.004285</v>
+        <v>0.004299</v>
       </c>
       <c r="J455" s="1" t="n">
+        <v>0.004299</v>
+      </c>
+      <c r="K455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -15947,9 +17315,12 @@
         <v>0.1833</v>
       </c>
       <c r="I456" s="1" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="J456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="J456" s="1" t="n">
+      <c r="K456" s="1" t="n">
         <v>0.1833</v>
       </c>
     </row>
@@ -15981,10 +17352,13 @@
         <v>0.04277</v>
       </c>
       <c r="I457" s="1" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="J457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="J457" s="1" t="n">
-        <v>0.04277</v>
+      <c r="K457" s="1" t="n">
+        <v>0.04274</v>
       </c>
     </row>
     <row r="458">
@@ -16015,9 +17389,12 @@
         <v>0.1459</v>
       </c>
       <c r="I458" s="1" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="J458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="J458" s="1" t="n">
+      <c r="K458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -16049,9 +17426,12 @@
         <v>0.008607</v>
       </c>
       <c r="I459" s="1" t="n">
-        <v>0.008616</v>
+        <v>0.008621</v>
       </c>
       <c r="J459" s="1" t="n">
+        <v>0.008621</v>
+      </c>
+      <c r="K459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -16083,9 +17463,12 @@
         <v>0.007423</v>
       </c>
       <c r="I460" s="1" t="n">
+        <v>0.007431</v>
+      </c>
+      <c r="J460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="J460" s="1" t="n">
+      <c r="K460" s="1" t="n">
         <v>0.007423</v>
       </c>
     </row>
@@ -16117,9 +17500,12 @@
         <v>0.000173</v>
       </c>
       <c r="I461" s="1" t="n">
+        <v>0.0001731</v>
+      </c>
+      <c r="J461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="J461" s="1" t="n">
+      <c r="K461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -16151,9 +17537,12 @@
         <v>0.02265</v>
       </c>
       <c r="I462" s="1" t="n">
-        <v>0.02265</v>
+        <v>0.0227</v>
       </c>
       <c r="J462" s="1" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="K462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -16185,9 +17574,12 @@
         <v>0.0377</v>
       </c>
       <c r="I463" s="1" t="n">
-        <v>0.03777</v>
+        <v>0.0378</v>
       </c>
       <c r="J463" s="1" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="K463" s="1" t="n">
         <v>0.0374</v>
       </c>
     </row>
@@ -16219,9 +17611,12 @@
         <v>0.3039</v>
       </c>
       <c r="I464" s="1" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="J464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="J464" s="1" t="n">
+      <c r="K464" s="1" t="n">
         <v>0.3031</v>
       </c>
     </row>
@@ -16253,9 +17648,12 @@
         <v>0.03898</v>
       </c>
       <c r="I465" s="1" t="n">
-        <v>0.03923</v>
+        <v>0.03926</v>
       </c>
       <c r="J465" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="K465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -16287,10 +17685,13 @@
         <v>2.675</v>
       </c>
       <c r="I466" s="1" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="J466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="J466" s="1" t="n">
-        <v>2.675</v>
+      <c r="K466" s="1" t="n">
+        <v>2.669</v>
       </c>
     </row>
     <row r="467">
@@ -16321,9 +17722,12 @@
         <v>0.03433</v>
       </c>
       <c r="I467" s="1" t="n">
-        <v>0.03435</v>
+        <v>0.03436</v>
       </c>
       <c r="J467" s="1" t="n">
+        <v>0.03436</v>
+      </c>
+      <c r="K467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -16355,9 +17759,12 @@
         <v>0.1763</v>
       </c>
       <c r="I468" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="J468" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="J468" s="1" t="n">
+      <c r="K468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -16389,9 +17796,12 @@
         <v>0.0956</v>
       </c>
       <c r="I469" s="1" t="n">
-        <v>0.0958</v>
+        <v>0.096</v>
       </c>
       <c r="J469" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -16423,10 +17833,13 @@
         <v>0.06732</v>
       </c>
       <c r="I470" s="1" t="n">
+        <v>0.06716999999999999</v>
+      </c>
+      <c r="J470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="J470" s="1" t="n">
-        <v>0.06732</v>
+      <c r="K470" s="1" t="n">
+        <v>0.06716999999999999</v>
       </c>
     </row>
     <row r="471">
@@ -16457,9 +17870,12 @@
         <v>0.04</v>
       </c>
       <c r="I471" s="1" t="n">
+        <v>0.03998</v>
+      </c>
+      <c r="J471" s="1" t="n">
         <v>0.04004</v>
       </c>
-      <c r="J471" s="1" t="n">
+      <c r="K471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -16491,9 +17907,12 @@
         <v>0.2477</v>
       </c>
       <c r="I472" s="1" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="J472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="J472" s="1" t="n">
+      <c r="K472" s="1" t="n">
         <v>0.2475</v>
       </c>
     </row>
@@ -16525,9 +17944,12 @@
         <v>0.016503</v>
       </c>
       <c r="I473" s="1" t="n">
+        <v>0.016505</v>
+      </c>
+      <c r="J473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="J473" s="1" t="n">
+      <c r="K473" s="1" t="n">
         <v>0.016503</v>
       </c>
     </row>
@@ -16559,9 +17981,12 @@
         <v>0.1157</v>
       </c>
       <c r="I474" s="1" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="J474" s="1" t="n">
         <v>0.1157</v>
       </c>
-      <c r="J474" s="1" t="n">
+      <c r="K474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -16593,9 +18018,12 @@
         <v>0.04273</v>
       </c>
       <c r="I475" s="1" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="J475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="J475" s="1" t="n">
+      <c r="K475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -16627,9 +18055,12 @@
         <v>0.2075</v>
       </c>
       <c r="I476" s="1" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="J476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="J476" s="1" t="n">
+      <c r="K476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -16661,9 +18092,12 @@
         <v>0.006796</v>
       </c>
       <c r="I477" s="1" t="n">
+        <v>0.006811</v>
+      </c>
+      <c r="J477" s="1" t="n">
         <v>0.006833</v>
       </c>
-      <c r="J477" s="1" t="n">
+      <c r="K477" s="1" t="n">
         <v>0.006796</v>
       </c>
     </row>
@@ -16695,10 +18129,13 @@
         <v>0.01799</v>
       </c>
       <c r="I478" s="1" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="J478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="J478" s="1" t="n">
-        <v>0.01799</v>
+      <c r="K478" s="1" t="n">
+        <v>0.01791</v>
       </c>
     </row>
     <row r="479">
@@ -16729,9 +18166,12 @@
         <v>0.04683</v>
       </c>
       <c r="I479" s="1" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="J479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="J479" s="1" t="n">
+      <c r="K479" s="1" t="n">
         <v>0.04683</v>
       </c>
     </row>
@@ -16763,9 +18203,12 @@
         <v>0.26088</v>
       </c>
       <c r="I480" s="1" t="n">
+        <v>0.26131</v>
+      </c>
+      <c r="J480" s="1" t="n">
         <v>0.26166</v>
       </c>
-      <c r="J480" s="1" t="n">
+      <c r="K480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -16797,10 +18240,13 @@
         <v>0.01234</v>
       </c>
       <c r="I481" s="1" t="n">
+        <v>0.01233</v>
+      </c>
+      <c r="J481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="J481" s="1" t="n">
-        <v>0.01234</v>
+      <c r="K481" s="1" t="n">
+        <v>0.01233</v>
       </c>
     </row>
     <row r="482">
@@ -16831,9 +18277,12 @@
         <v>0.00413</v>
       </c>
       <c r="I482" s="1" t="n">
+        <v>0.004105</v>
+      </c>
+      <c r="J482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="J482" s="1" t="n">
+      <c r="K482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -16865,9 +18314,12 @@
         <v>0.1231</v>
       </c>
       <c r="I483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="J483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="J483" s="1" t="n">
+      <c r="K483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -16899,9 +18351,12 @@
         <v>0.02198</v>
       </c>
       <c r="I484" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="J484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="J484" s="1" t="n">
+      <c r="K484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -16933,9 +18388,12 @@
         <v>0.04558</v>
       </c>
       <c r="I485" s="1" t="n">
+        <v>0.04555</v>
+      </c>
+      <c r="J485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="J485" s="1" t="n">
+      <c r="K485" s="1" t="n">
         <v>0.04548</v>
       </c>
     </row>
@@ -16967,9 +18425,12 @@
         <v>0.1733</v>
       </c>
       <c r="I486" s="1" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="J486" s="1" t="n">
         <v>0.1736</v>
       </c>
-      <c r="J486" s="1" t="n">
+      <c r="K486" s="1" t="n">
         <v>0.1732</v>
       </c>
     </row>
@@ -17001,9 +18462,12 @@
         <v>0.273</v>
       </c>
       <c r="I487" s="1" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="J487" s="1" t="n">
+      <c r="K487" s="1" t="n">
         <v>0.273</v>
       </c>
     </row>
@@ -17035,9 +18499,12 @@
         <v>0.04615</v>
       </c>
       <c r="I488" s="1" t="n">
+        <v>0.04615</v>
+      </c>
+      <c r="J488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="J488" s="1" t="n">
+      <c r="K488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -17069,9 +18536,12 @@
         <v>0.0002154</v>
       </c>
       <c r="I489" s="1" t="n">
+        <v>0.0002155</v>
+      </c>
+      <c r="J489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="J489" s="1" t="n">
+      <c r="K489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -17103,9 +18573,12 @@
         <v>1.768</v>
       </c>
       <c r="I490" s="1" t="n">
-        <v>1.768</v>
+        <v>1.769</v>
       </c>
       <c r="J490" s="1" t="n">
+        <v>1.769</v>
+      </c>
+      <c r="K490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -17137,9 +18610,12 @@
         <v>16.065</v>
       </c>
       <c r="I491" s="1" t="n">
+        <v>16.053</v>
+      </c>
+      <c r="J491" s="1" t="n">
         <v>16.083</v>
       </c>
-      <c r="J491" s="1" t="n">
+      <c r="K491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -17171,9 +18647,12 @@
         <v>0.0668</v>
       </c>
       <c r="I492" s="1" t="n">
-        <v>0.06685000000000001</v>
+        <v>0.06703000000000001</v>
       </c>
       <c r="J492" s="1" t="n">
+        <v>0.06703000000000001</v>
+      </c>
+      <c r="K492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -17205,9 +18684,12 @@
         <v>0.06736</v>
       </c>
       <c r="I493" s="1" t="n">
+        <v>0.06748</v>
+      </c>
+      <c r="J493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="J493" s="1" t="n">
+      <c r="K493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -17239,9 +18721,12 @@
         <v>0.009471</v>
       </c>
       <c r="I494" s="1" t="n">
+        <v>0.009468000000000001</v>
+      </c>
+      <c r="J494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="J494" s="1" t="n">
+      <c r="K494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -17273,9 +18758,12 @@
         <v>0.005907</v>
       </c>
       <c r="I495" s="1" t="n">
+        <v>0.005953</v>
+      </c>
+      <c r="J495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="J495" s="1" t="n">
+      <c r="K495" s="1" t="n">
         <v>0.005907</v>
       </c>
     </row>
@@ -17307,9 +18795,12 @@
         <v>0.00991</v>
       </c>
       <c r="I496" s="1" t="n">
+        <v>0.00991</v>
+      </c>
+      <c r="J496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="J496" s="1" t="n">
+      <c r="K496" s="1" t="n">
         <v>0.00991</v>
       </c>
     </row>
@@ -17341,9 +18832,12 @@
         <v>0.04394</v>
       </c>
       <c r="I497" s="1" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="J497" s="1" t="n">
         <v>0.04404</v>
       </c>
-      <c r="J497" s="1" t="n">
+      <c r="K497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -17375,10 +18869,13 @@
         <v>0.006394</v>
       </c>
       <c r="I498" s="1" t="n">
+        <v>0.006393</v>
+      </c>
+      <c r="J498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="J498" s="1" t="n">
-        <v>0.006394</v>
+      <c r="K498" s="1" t="n">
+        <v>0.006393</v>
       </c>
     </row>
     <row r="499">
@@ -17409,9 +18906,12 @@
         <v>0.01048</v>
       </c>
       <c r="I499" s="1" t="n">
+        <v>0.01047</v>
+      </c>
+      <c r="J499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="J499" s="1" t="n">
+      <c r="K499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -17443,10 +18943,13 @@
         <v>0.5076000000000001</v>
       </c>
       <c r="I500" s="1" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="J500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="J500" s="1" t="n">
-        <v>0.5076000000000001</v>
+      <c r="K500" s="1" t="n">
+        <v>0.5075</v>
       </c>
     </row>
     <row r="501">
@@ -17477,9 +18980,12 @@
         <v>0.03204</v>
       </c>
       <c r="I501" s="1" t="n">
+        <v>0.03204</v>
+      </c>
+      <c r="J501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="J501" s="1" t="n">
+      <c r="K501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -17511,9 +19017,12 @@
         <v>0.4371</v>
       </c>
       <c r="I502" s="1" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="J502" s="1" t="n">
         <v>0.4385</v>
       </c>
-      <c r="J502" s="1" t="n">
+      <c r="K502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -17545,9 +19054,12 @@
         <v>0.999342</v>
       </c>
       <c r="I503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="J503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="J503" s="1" t="n">
+      <c r="K503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -17579,9 +19091,12 @@
         <v>0.03548</v>
       </c>
       <c r="I504" s="1" t="n">
+        <v>0.03526</v>
+      </c>
+      <c r="J504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="J504" s="1" t="n">
+      <c r="K504" s="1" t="n">
         <v>0.03525</v>
       </c>
     </row>
@@ -17613,9 +19128,12 @@
         <v>0.00493</v>
       </c>
       <c r="I505" s="1" t="n">
+        <v>0.004925</v>
+      </c>
+      <c r="J505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="J505" s="1" t="n">
+      <c r="K505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -17647,9 +19165,12 @@
         <v>0.01392</v>
       </c>
       <c r="I506" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="J506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="J506" s="1" t="n">
+      <c r="K506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -17681,9 +19202,12 @@
         <v>0.003486</v>
       </c>
       <c r="I507" s="1" t="n">
-        <v>0.003486</v>
+        <v>0.003516</v>
       </c>
       <c r="J507" s="1" t="n">
+        <v>0.003516</v>
+      </c>
+      <c r="K507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -17715,9 +19239,12 @@
         <v>1.42</v>
       </c>
       <c r="I508" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="J508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="J508" s="1" t="n">
+      <c r="K508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -17749,9 +19276,12 @@
         <v>0.005089</v>
       </c>
       <c r="I509" s="1" t="n">
+        <v>0.005086</v>
+      </c>
+      <c r="J509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="J509" s="1" t="n">
+      <c r="K509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -17783,9 +19313,12 @@
         <v>0.01573</v>
       </c>
       <c r="I510" s="1" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="J510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="J510" s="1" t="n">
+      <c r="K510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -17817,9 +19350,12 @@
         <v>0.08212999999999999</v>
       </c>
       <c r="I511" s="1" t="n">
+        <v>0.08223999999999999</v>
+      </c>
+      <c r="J511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="J511" s="1" t="n">
+      <c r="K511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -17851,10 +19387,13 @@
         <v>0.007108</v>
       </c>
       <c r="I512" s="1" t="n">
+        <v>0.007099</v>
+      </c>
+      <c r="J512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="J512" s="1" t="n">
-        <v>0.007105</v>
+      <c r="K512" s="1" t="n">
+        <v>0.007099</v>
       </c>
     </row>
     <row r="513">
@@ -17885,9 +19424,12 @@
         <v>0.01482</v>
       </c>
       <c r="I513" s="1" t="n">
-        <v>0.01483</v>
+        <v>0.01485</v>
       </c>
       <c r="J513" s="1" t="n">
+        <v>0.01485</v>
+      </c>
+      <c r="K513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -17919,10 +19461,13 @@
         <v>0.04736</v>
       </c>
       <c r="I514" s="1" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="J514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="J514" s="1" t="n">
-        <v>0.04736</v>
+      <c r="K514" s="1" t="n">
+        <v>0.04721</v>
       </c>
     </row>
     <row r="515">
@@ -17953,9 +19498,12 @@
         <v>0.01821</v>
       </c>
       <c r="I515" s="1" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="J515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="J515" s="1" t="n">
+      <c r="K515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -17987,9 +19535,12 @@
         <v>0.0005806</v>
       </c>
       <c r="I516" s="1" t="n">
-        <v>0.0005808</v>
+        <v>0.0005813</v>
       </c>
       <c r="J516" s="1" t="n">
+        <v>0.0005813</v>
+      </c>
+      <c r="K516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -18021,9 +19572,12 @@
         <v>0.07874</v>
       </c>
       <c r="I517" s="1" t="n">
+        <v>0.07871</v>
+      </c>
+      <c r="J517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="J517" s="1" t="n">
+      <c r="K517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -18055,9 +19609,12 @@
         <v>0.006379</v>
       </c>
       <c r="I518" s="1" t="n">
+        <v>0.006379</v>
+      </c>
+      <c r="J518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="J518" s="1" t="n">
+      <c r="K518" s="1" t="n">
         <v>0.006378</v>
       </c>
     </row>
@@ -18089,9 +19646,12 @@
         <v>0.05789</v>
       </c>
       <c r="I519" s="1" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="J519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="J519" s="1" t="n">
+      <c r="K519" s="1" t="n">
         <v>0.05789</v>
       </c>
     </row>
@@ -18123,9 +19683,12 @@
         <v>0.10489</v>
       </c>
       <c r="I520" s="1" t="n">
+        <v>0.10498</v>
+      </c>
+      <c r="J520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="J520" s="1" t="n">
+      <c r="K520" s="1" t="n">
         <v>0.10489</v>
       </c>
     </row>
@@ -18157,9 +19720,12 @@
         <v>0.01797</v>
       </c>
       <c r="I521" s="1" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="J521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="J521" s="1" t="n">
+      <c r="K521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -18191,9 +19757,12 @@
         <v>0.0165</v>
       </c>
       <c r="I522" s="1" t="n">
-        <v>0.01653</v>
+        <v>0.01656</v>
       </c>
       <c r="J522" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="K522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -18225,9 +19794,12 @@
         <v>0.01092</v>
       </c>
       <c r="I523" s="1" t="n">
+        <v>0.01086</v>
+      </c>
+      <c r="J523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="J523" s="1" t="n">
+      <c r="K523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -18259,9 +19831,12 @@
         <v>0.007084</v>
       </c>
       <c r="I524" s="1" t="n">
-        <v>0.007138</v>
+        <v>0.007156</v>
       </c>
       <c r="J524" s="1" t="n">
+        <v>0.007156</v>
+      </c>
+      <c r="K524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -18293,10 +19868,13 @@
         <v>0.005922</v>
       </c>
       <c r="I525" s="1" t="n">
+        <v>0.005907</v>
+      </c>
+      <c r="J525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="J525" s="1" t="n">
-        <v>0.005922</v>
+      <c r="K525" s="1" t="n">
+        <v>0.005907</v>
       </c>
     </row>
     <row r="526">
@@ -18327,9 +19905,12 @@
         <v>0.001444</v>
       </c>
       <c r="I526" s="1" t="n">
+        <v>0.001442</v>
+      </c>
+      <c r="J526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="J526" s="1" t="n">
+      <c r="K526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -18361,9 +19942,12 @@
         <v>0.372</v>
       </c>
       <c r="I527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="J527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="J527" s="1" t="n">
+      <c r="K527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -18395,9 +19979,12 @@
         <v>0.005187</v>
       </c>
       <c r="I528" s="1" t="n">
+        <v>0.005181</v>
+      </c>
+      <c r="J528" s="1" t="n">
         <v>0.00521</v>
       </c>
-      <c r="J528" s="1" t="n">
+      <c r="K528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -18429,9 +20016,12 @@
         <v>2.943</v>
       </c>
       <c r="I529" s="1" t="n">
-        <v>2.943</v>
+        <v>2.951</v>
       </c>
       <c r="J529" s="1" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="K529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -18463,9 +20053,12 @@
         <v>0.1558</v>
       </c>
       <c r="I530" s="1" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="J530" s="1" t="n">
         <v>0.156</v>
       </c>
-      <c r="J530" s="1" t="n">
+      <c r="K530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -18497,9 +20090,12 @@
         <v>2534</v>
       </c>
       <c r="I531" s="1" t="n">
+        <v>2533</v>
+      </c>
+      <c r="J531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="J531" s="1" t="n">
+      <c r="K531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -18531,9 +20127,12 @@
         <v>0.03929</v>
       </c>
       <c r="I532" s="1" t="n">
+        <v>0.03924</v>
+      </c>
+      <c r="J532" s="1" t="n">
         <v>0.03929</v>
       </c>
-      <c r="J532" s="1" t="n">
+      <c r="K532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -18565,9 +20164,12 @@
         <v>0.02186</v>
       </c>
       <c r="I533" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="J533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="J533" s="1" t="n">
+      <c r="K533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -18599,9 +20201,12 @@
         <v>0.07352</v>
       </c>
       <c r="I534" s="1" t="n">
-        <v>0.07352</v>
+        <v>0.0737</v>
       </c>
       <c r="J534" s="1" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="K534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -18633,9 +20238,12 @@
         <v>0.007835</v>
       </c>
       <c r="I535" s="1" t="n">
+        <v>0.007849</v>
+      </c>
+      <c r="J535" s="1" t="n">
         <v>0.007877</v>
       </c>
-      <c r="J535" s="1" t="n">
+      <c r="K535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -18667,9 +20275,12 @@
         <v>0.05013</v>
       </c>
       <c r="I536" s="1" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="J536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="J536" s="1" t="n">
+      <c r="K536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -18701,10 +20312,13 @@
         <v>0.00406</v>
       </c>
       <c r="I537" s="1" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="J537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="J537" s="1" t="n">
-        <v>0.00406</v>
+      <c r="K537" s="1" t="n">
+        <v>0.00405</v>
       </c>
     </row>
     <row r="538">
@@ -18735,9 +20349,12 @@
         <v>0.08289000000000001</v>
       </c>
       <c r="I538" s="1" t="n">
+        <v>0.08309</v>
+      </c>
+      <c r="J538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="J538" s="1" t="n">
+      <c r="K538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -18769,9 +20386,12 @@
         <v>0.02496</v>
       </c>
       <c r="I539" s="1" t="n">
+        <v>0.02492</v>
+      </c>
+      <c r="J539" s="1" t="n">
         <v>0.02502</v>
       </c>
-      <c r="J539" s="1" t="n">
+      <c r="K539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -18803,9 +20423,12 @@
         <v>0.08476</v>
       </c>
       <c r="I540" s="1" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="J540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="J540" s="1" t="n">
+      <c r="K540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -18837,9 +20460,12 @@
         <v>0.01895</v>
       </c>
       <c r="I541" s="1" t="n">
+        <v>0.01895</v>
+      </c>
+      <c r="J541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="J541" s="1" t="n">
+      <c r="K541" s="1" t="n">
         <v>0.01895</v>
       </c>
     </row>
@@ -18871,9 +20497,12 @@
         <v>0.01694</v>
       </c>
       <c r="I542" s="1" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="J542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="J542" s="1" t="n">
+      <c r="K542" s="1" t="n">
         <v>0.01694</v>
       </c>
     </row>
@@ -18905,9 +20534,12 @@
         <v>0.1049</v>
       </c>
       <c r="I543" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="J543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="J543" s="1" t="n">
+      <c r="K543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K543"/>
+  <dimension ref="A1:L543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -428,8 +428,9 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,10 +481,15 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>price_02:15</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -520,10 +526,13 @@
         <v>70586.2</v>
       </c>
       <c r="J2" s="1" t="n">
+        <v>70544.10000000001</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="K2" s="1" t="n">
-        <v>70545.39999999999</v>
+      <c r="L2" s="1" t="n">
+        <v>70544.10000000001</v>
       </c>
     </row>
     <row r="3">
@@ -557,9 +566,12 @@
         <v>2073.98</v>
       </c>
       <c r="J3" s="1" t="n">
+        <v>2072.51</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -594,9 +606,12 @@
         <v>86.81999999999999</v>
       </c>
       <c r="J4" s="1" t="n">
+        <v>86.81</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -631,10 +646,13 @@
         <v>4.04</v>
       </c>
       <c r="J5" s="1" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="K5" s="1" t="n">
-        <v>4.022</v>
+      <c r="L5" s="1" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="6">
@@ -668,10 +686,13 @@
         <v>0.09463000000000001</v>
       </c>
       <c r="J6" s="1" t="n">
+        <v>0.09455</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>0.09463000000000001</v>
+      <c r="L6" s="1" t="n">
+        <v>0.09455</v>
       </c>
     </row>
     <row r="7">
@@ -705,9 +726,12 @@
         <v>1.3886</v>
       </c>
       <c r="J7" s="1" t="n">
+        <v>1.3883</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -742,9 +766,12 @@
         <v>22.688</v>
       </c>
       <c r="J8" s="1" t="n">
+        <v>22.422</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>22.688</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -779,10 +806,13 @@
         <v>0.002053</v>
       </c>
       <c r="J9" s="1" t="n">
+        <v>0.001977</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <v>0.002053</v>
+      <c r="L9" s="1" t="n">
+        <v>0.001977</v>
       </c>
     </row>
     <row r="10">
@@ -816,9 +846,12 @@
         <v>0.010308</v>
       </c>
       <c r="J10" s="1" t="n">
+        <v>0.010275</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -853,9 +886,12 @@
         <v>0.16075</v>
       </c>
       <c r="J11" s="1" t="n">
+        <v>0.16108</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.15789</v>
       </c>
     </row>
@@ -890,9 +926,12 @@
         <v>0.011355</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>0.01142</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -927,9 +966,12 @@
         <v>38.07</v>
       </c>
       <c r="J13" s="1" t="n">
+        <v>38.034</v>
+      </c>
+      <c r="K13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="1" t="n">
         <v>37.988</v>
       </c>
     </row>
@@ -964,10 +1006,13 @@
         <v>653.01</v>
       </c>
       <c r="J14" s="1" t="n">
+        <v>652.55</v>
+      </c>
+      <c r="K14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="K14" s="1" t="n">
-        <v>652.8</v>
+      <c r="L14" s="1" t="n">
+        <v>652.55</v>
       </c>
     </row>
     <row r="15">
@@ -1001,10 +1046,13 @@
         <v>209.21</v>
       </c>
       <c r="J15" s="1" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="K15" s="1" t="n">
-        <v>209.13</v>
+      <c r="L15" s="1" t="n">
+        <v>208.77</v>
       </c>
     </row>
     <row r="16">
@@ -1038,10 +1086,13 @@
         <v>0.003331</v>
       </c>
       <c r="J16" s="1" t="n">
+        <v>0.0033231</v>
+      </c>
+      <c r="K16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="K16" s="1" t="n">
-        <v>0.003331</v>
+      <c r="L16" s="1" t="n">
+        <v>0.0033231</v>
       </c>
     </row>
     <row r="17">
@@ -1075,9 +1126,12 @@
         <v>237.45</v>
       </c>
       <c r="J17" s="1" t="n">
+        <v>238.29</v>
+      </c>
+      <c r="K17" s="1" t="n">
         <v>238.32</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1112,9 +1166,12 @@
         <v>0.99</v>
       </c>
       <c r="J18" s="1" t="n">
+        <v>0.9885</v>
+      </c>
+      <c r="K18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="L18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1149,9 +1206,12 @@
         <v>1.045</v>
       </c>
       <c r="J19" s="1" t="n">
+        <v>1.0455</v>
+      </c>
+      <c r="K19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="K19" s="1" t="n">
+      <c r="L19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1186,10 +1246,13 @@
         <v>0.2596</v>
       </c>
       <c r="J20" s="1" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="K20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="K20" s="1" t="n">
-        <v>0.2596</v>
+      <c r="L20" s="1" t="n">
+        <v>0.2587</v>
       </c>
     </row>
     <row r="21">
@@ -1223,9 +1286,12 @@
         <v>0.59635</v>
       </c>
       <c r="J21" s="1" t="n">
+        <v>0.59554</v>
+      </c>
+      <c r="K21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="K21" s="1" t="n">
+      <c r="L21" s="1" t="n">
         <v>0.59536</v>
       </c>
     </row>
@@ -1260,9 +1326,12 @@
         <v>9.000999999999999</v>
       </c>
       <c r="J22" s="1" t="n">
+        <v>8.992000000000001</v>
+      </c>
+      <c r="K22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="L22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1297,9 +1366,12 @@
         <v>0.02414</v>
       </c>
       <c r="J23" s="1" t="n">
+        <v>0.02425</v>
+      </c>
+      <c r="K23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="K23" s="1" t="n">
+      <c r="L23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1334,10 +1406,13 @@
         <v>9.573</v>
       </c>
       <c r="J24" s="1" t="n">
+        <v>9.553000000000001</v>
+      </c>
+      <c r="K24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="K24" s="1" t="n">
-        <v>9.555999999999999</v>
+      <c r="L24" s="1" t="n">
+        <v>9.553000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1371,9 +1446,12 @@
         <v>1.224</v>
       </c>
       <c r="J25" s="1" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="K25" s="1" t="n">
         <v>1.228</v>
       </c>
-      <c r="K25" s="1" t="n">
+      <c r="L25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1408,9 +1486,12 @@
         <v>0.07152</v>
       </c>
       <c r="J26" s="1" t="n">
+        <v>0.07116</v>
+      </c>
+      <c r="K26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="K26" s="1" t="n">
+      <c r="L26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1445,9 +1526,12 @@
         <v>1.424</v>
       </c>
       <c r="J27" s="1" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="K27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="K27" s="1" t="n">
+      <c r="L27" s="1" t="n">
         <v>1.424</v>
       </c>
     </row>
@@ -1482,10 +1566,13 @@
         <v>1.305</v>
       </c>
       <c r="J28" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="K28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="K28" s="1" t="n">
-        <v>1.305</v>
+      <c r="L28" s="1" t="n">
+        <v>1.304</v>
       </c>
     </row>
     <row r="29">
@@ -1519,10 +1606,13 @@
         <v>461.7</v>
       </c>
       <c r="J29" s="1" t="n">
+        <v>461.1</v>
+      </c>
+      <c r="K29" s="1" t="n">
         <v>463.21</v>
       </c>
-      <c r="K29" s="1" t="n">
-        <v>461.7</v>
+      <c r="L29" s="1" t="n">
+        <v>461.1</v>
       </c>
     </row>
     <row r="30">
@@ -1556,9 +1646,12 @@
         <v>1.2882</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>1.2902</v>
+        <v>1.2908</v>
       </c>
       <c r="K30" s="1" t="n">
+        <v>1.2908</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1593,9 +1686,12 @@
         <v>5023.66</v>
       </c>
       <c r="J31" s="1" t="n">
+        <v>5023.98</v>
+      </c>
+      <c r="K31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="K31" s="1" t="n">
+      <c r="L31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1630,9 +1726,12 @@
         <v>0.874</v>
       </c>
       <c r="J32" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K32" s="1" t="n">
         <v>0.877</v>
       </c>
-      <c r="K32" s="1" t="n">
+      <c r="L32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1667,9 +1766,12 @@
         <v>0.001979</v>
       </c>
       <c r="J33" s="1" t="n">
+        <v>0.001978</v>
+      </c>
+      <c r="K33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="K33" s="1" t="n">
+      <c r="L33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1704,9 +1806,12 @@
         <v>0.16972</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.17091</v>
+        <v>0.17106</v>
       </c>
       <c r="K34" s="1" t="n">
+        <v>0.17106</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -1741,10 +1846,13 @@
         <v>0.29703</v>
       </c>
       <c r="J35" s="1" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="K35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="K35" s="1" t="n">
-        <v>0.29703</v>
+      <c r="L35" s="1" t="n">
+        <v>0.29701</v>
       </c>
     </row>
     <row r="36">
@@ -1778,10 +1886,13 @@
         <v>1.786</v>
       </c>
       <c r="J36" s="1" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="K36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="K36" s="1" t="n">
-        <v>1.786</v>
+      <c r="L36" s="1" t="n">
+        <v>1.784</v>
       </c>
     </row>
     <row r="37">
@@ -1815,9 +1926,12 @@
         <v>110.58</v>
       </c>
       <c r="J37" s="1" t="n">
+        <v>110.49</v>
+      </c>
+      <c r="K37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="K37" s="1" t="n">
+      <c r="L37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1852,9 +1966,12 @@
         <v>0.22169</v>
       </c>
       <c r="J38" s="1" t="n">
+        <v>0.22296</v>
+      </c>
+      <c r="K38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="K38" s="1" t="n">
+      <c r="L38" s="1" t="n">
         <v>0.22169</v>
       </c>
     </row>
@@ -1889,10 +2006,13 @@
         <v>0.1076</v>
       </c>
       <c r="J39" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="K39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="K39" s="1" t="n">
-        <v>0.1076</v>
+      <c r="L39" s="1" t="n">
+        <v>0.1074</v>
       </c>
     </row>
     <row r="40">
@@ -1926,9 +2046,12 @@
         <v>0.3694</v>
       </c>
       <c r="J40" s="1" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="K40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="K40" s="1" t="n">
+      <c r="L40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -1963,9 +2086,12 @@
         <v>54.56</v>
       </c>
       <c r="J41" s="1" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="K41" s="1" t="n">
         <v>54.66</v>
       </c>
-      <c r="K41" s="1" t="n">
+      <c r="L41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2000,10 +2126,13 @@
         <v>0.0010715</v>
       </c>
       <c r="J42" s="1" t="n">
+        <v>0.0010666</v>
+      </c>
+      <c r="K42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="K42" s="1" t="n">
-        <v>0.0010715</v>
+      <c r="L42" s="1" t="n">
+        <v>0.0010666</v>
       </c>
     </row>
     <row r="43">
@@ -2037,9 +2166,12 @@
         <v>6.465</v>
       </c>
       <c r="J43" s="1" t="n">
+        <v>6.433</v>
+      </c>
+      <c r="K43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="K43" s="1" t="n">
+      <c r="L43" s="1" t="n">
         <v>6.414</v>
       </c>
     </row>
@@ -2074,10 +2206,13 @@
         <v>0.6336000000000001</v>
       </c>
       <c r="J44" s="1" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="K44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="K44" s="1" t="n">
-        <v>0.6336000000000001</v>
+      <c r="L44" s="1" t="n">
+        <v>0.6324</v>
       </c>
     </row>
     <row r="45">
@@ -2111,10 +2246,13 @@
         <v>0.3539</v>
       </c>
       <c r="J45" s="1" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="K45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="K45" s="1" t="n">
-        <v>0.3539</v>
+      <c r="L45" s="1" t="n">
+        <v>0.3535</v>
       </c>
     </row>
     <row r="46">
@@ -2148,9 +2286,12 @@
         <v>0.0323</v>
       </c>
       <c r="J46" s="1" t="n">
+        <v>0.03247</v>
+      </c>
+      <c r="K46" s="1" t="n">
         <v>0.0326</v>
       </c>
-      <c r="K46" s="1" t="n">
+      <c r="L46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2185,9 +2326,12 @@
         <v>0.07269</v>
       </c>
       <c r="J47" s="1" t="n">
+        <v>0.07245</v>
+      </c>
+      <c r="K47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="K47" s="1" t="n">
+      <c r="L47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -2222,9 +2366,12 @@
         <v>0.7037</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7068</v>
       </c>
       <c r="K48" s="1" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -2259,10 +2406,13 @@
         <v>0.004436</v>
       </c>
       <c r="J49" s="1" t="n">
+        <v>0.004361</v>
+      </c>
+      <c r="K49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="K49" s="1" t="n">
-        <v>0.004436</v>
+      <c r="L49" s="1" t="n">
+        <v>0.004361</v>
       </c>
     </row>
     <row r="50">
@@ -2296,10 +2446,13 @@
         <v>0.1043</v>
       </c>
       <c r="J50" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="K50" s="1" t="n">
-        <v>0.1041</v>
+      <c r="L50" s="1" t="n">
+        <v>0.104</v>
       </c>
     </row>
     <row r="51">
@@ -2333,9 +2486,12 @@
         <v>0.04052</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>0.0406</v>
+        <v>0.04073</v>
       </c>
       <c r="K51" s="1" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -2370,10 +2526,13 @@
         <v>0.165</v>
       </c>
       <c r="J52" s="1" t="n">
+        <v>0.1646</v>
+      </c>
+      <c r="K52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="K52" s="1" t="n">
-        <v>0.165</v>
+      <c r="L52" s="1" t="n">
+        <v>0.1646</v>
       </c>
     </row>
     <row r="53">
@@ -2407,10 +2566,13 @@
         <v>0.02021</v>
       </c>
       <c r="J53" s="1" t="n">
+        <v>0.02003</v>
+      </c>
+      <c r="K53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="K53" s="1" t="n">
-        <v>0.02021</v>
+      <c r="L53" s="1" t="n">
+        <v>0.02003</v>
       </c>
     </row>
     <row r="54">
@@ -2444,10 +2606,13 @@
         <v>0.00721</v>
       </c>
       <c r="J54" s="1" t="n">
+        <v>0.007198</v>
+      </c>
+      <c r="K54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="K54" s="1" t="n">
-        <v>0.00721</v>
+      <c r="L54" s="1" t="n">
+        <v>0.007198</v>
       </c>
     </row>
     <row r="55">
@@ -2481,10 +2646,13 @@
         <v>3.918</v>
       </c>
       <c r="J55" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="K55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="K55" s="1" t="n">
-        <v>3.918</v>
+      <c r="L55" s="1" t="n">
+        <v>3.911</v>
       </c>
     </row>
     <row r="56">
@@ -2518,9 +2686,12 @@
         <v>0.017209</v>
       </c>
       <c r="J56" s="1" t="n">
+        <v>0.017202</v>
+      </c>
+      <c r="K56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="K56" s="1" t="n">
+      <c r="L56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -2555,9 +2726,12 @@
         <v>0.1112</v>
       </c>
       <c r="J57" s="1" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="K57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="K57" s="1" t="n">
+      <c r="L57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -2592,9 +2766,12 @@
         <v>2.664</v>
       </c>
       <c r="J58" s="1" t="n">
+        <v>2.656</v>
+      </c>
+      <c r="K58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="K58" s="1" t="n">
+      <c r="L58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -2629,10 +2806,13 @@
         <v>0.1599</v>
       </c>
       <c r="J59" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="K59" s="1" t="n">
-        <v>0.1593</v>
+      <c r="L59" s="1" t="n">
+        <v>0.159</v>
       </c>
     </row>
     <row r="60">
@@ -2666,10 +2846,13 @@
         <v>0.005893</v>
       </c>
       <c r="J60" s="1" t="n">
+        <v>0.005887</v>
+      </c>
+      <c r="K60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="K60" s="1" t="n">
-        <v>0.005893</v>
+      <c r="L60" s="1" t="n">
+        <v>0.005887</v>
       </c>
     </row>
     <row r="61">
@@ -2703,10 +2886,13 @@
         <v>0.09193</v>
       </c>
       <c r="J61" s="1" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="K61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="K61" s="1" t="n">
-        <v>0.09193</v>
+      <c r="L61" s="1" t="n">
+        <v>0.09188</v>
       </c>
     </row>
     <row r="62">
@@ -2740,10 +2926,13 @@
         <v>0.9118000000000001</v>
       </c>
       <c r="J62" s="1" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="K62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="K62" s="1" t="n">
-        <v>0.9118000000000001</v>
+      <c r="L62" s="1" t="n">
+        <v>0.9114</v>
       </c>
     </row>
     <row r="63">
@@ -2777,9 +2966,12 @@
         <v>0.78</v>
       </c>
       <c r="J63" s="1" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="K63" s="1" t="n">
         <v>0.78</v>
       </c>
-      <c r="K63" s="1" t="n">
+      <c r="L63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -2814,10 +3006,13 @@
         <v>0.04612</v>
       </c>
       <c r="J64" s="1" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="K64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="K64" s="1" t="n">
-        <v>0.04612</v>
+      <c r="L64" s="1" t="n">
+        <v>0.04563</v>
       </c>
     </row>
     <row r="65">
@@ -2851,9 +3046,12 @@
         <v>356.63</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>357.73</v>
+        <v>357.88</v>
       </c>
       <c r="K65" s="1" t="n">
+        <v>357.88</v>
+      </c>
+      <c r="L65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -2888,9 +3086,12 @@
         <v>0.12419</v>
       </c>
       <c r="J66" s="1" t="n">
+        <v>0.12428</v>
+      </c>
+      <c r="K66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="K66" s="1" t="n">
+      <c r="L66" s="1" t="n">
         <v>0.12419</v>
       </c>
     </row>
@@ -2925,10 +3126,13 @@
         <v>0.2357</v>
       </c>
       <c r="J67" s="1" t="n">
+        <v>0.2343</v>
+      </c>
+      <c r="K67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="K67" s="1" t="n">
-        <v>0.2357</v>
+      <c r="L67" s="1" t="n">
+        <v>0.2343</v>
       </c>
     </row>
     <row r="68">
@@ -2962,9 +3166,12 @@
         <v>0.00339</v>
       </c>
       <c r="J68" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="K68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="K68" s="1" t="n">
+      <c r="L68" s="1" t="n">
         <v>0.00339</v>
       </c>
     </row>
@@ -2999,10 +3206,13 @@
         <v>0.174</v>
       </c>
       <c r="J69" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="K69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="K69" s="1" t="n">
-        <v>0.174</v>
+      <c r="L69" s="1" t="n">
+        <v>0.1738</v>
       </c>
     </row>
     <row r="70">
@@ -3036,10 +3246,13 @@
         <v>0.16426</v>
       </c>
       <c r="J70" s="1" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="K70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="K70" s="1" t="n">
-        <v>0.16421</v>
+      <c r="L70" s="1" t="n">
+        <v>0.1639</v>
       </c>
     </row>
     <row r="71">
@@ -3073,10 +3286,13 @@
         <v>0.3515</v>
       </c>
       <c r="J71" s="1" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="K71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="K71" s="1" t="n">
-        <v>0.3515</v>
+      <c r="L71" s="1" t="n">
+        <v>0.3483</v>
       </c>
     </row>
     <row r="72">
@@ -3110,9 +3326,12 @@
         <v>0.7097</v>
       </c>
       <c r="J72" s="1" t="n">
-        <v>0.7105</v>
+        <v>0.7106</v>
       </c>
       <c r="K72" s="1" t="n">
+        <v>0.7106</v>
+      </c>
+      <c r="L72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -3147,9 +3366,12 @@
         <v>0.00869</v>
       </c>
       <c r="J73" s="1" t="n">
+        <v>0.008710000000000001</v>
+      </c>
+      <c r="K73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="K73" s="1" t="n">
+      <c r="L73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -3184,10 +3406,13 @@
         <v>0.005982</v>
       </c>
       <c r="J74" s="1" t="n">
+        <v>0.005972</v>
+      </c>
+      <c r="K74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="K74" s="1" t="n">
-        <v>0.005982</v>
+      <c r="L74" s="1" t="n">
+        <v>0.005972</v>
       </c>
     </row>
     <row r="75">
@@ -3221,9 +3446,12 @@
         <v>0.226</v>
       </c>
       <c r="J75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="K75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="K75" s="1" t="n">
+      <c r="L75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -3258,9 +3486,12 @@
         <v>0.3189</v>
       </c>
       <c r="J76" s="1" t="n">
-        <v>0.3189</v>
+        <v>0.3265</v>
       </c>
       <c r="K76" s="1" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="L76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -3295,9 +3526,12 @@
         <v>0.1003</v>
       </c>
       <c r="J77" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="K77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="K77" s="1" t="n">
+      <c r="L77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -3332,9 +3566,12 @@
         <v>0.1229</v>
       </c>
       <c r="J78" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="K78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="K78" s="1" t="n">
+      <c r="L78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -3369,9 +3606,12 @@
         <v>0.07277</v>
       </c>
       <c r="J79" s="1" t="n">
+        <v>0.07210999999999999</v>
+      </c>
+      <c r="K79" s="1" t="n">
         <v>0.07277</v>
       </c>
-      <c r="K79" s="1" t="n">
+      <c r="L79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -3406,9 +3646,12 @@
         <v>0.04689</v>
       </c>
       <c r="J80" s="1" t="n">
+        <v>0.04692</v>
+      </c>
+      <c r="K80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="K80" s="1" t="n">
+      <c r="L80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -3443,9 +3686,12 @@
         <v>0.000233</v>
       </c>
       <c r="J81" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="K81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="K81" s="1" t="n">
+      <c r="L81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -3480,10 +3726,13 @@
         <v>8.215999999999999</v>
       </c>
       <c r="J82" s="1" t="n">
+        <v>8.206</v>
+      </c>
+      <c r="K82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="K82" s="1" t="n">
-        <v>8.215</v>
+      <c r="L82" s="1" t="n">
+        <v>8.206</v>
       </c>
     </row>
     <row r="83">
@@ -3517,10 +3766,13 @@
         <v>0.0005831</v>
       </c>
       <c r="J83" s="1" t="n">
+        <v>0.0005795</v>
+      </c>
+      <c r="K83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="K83" s="1" t="n">
-        <v>0.0005831</v>
+      <c r="L83" s="1" t="n">
+        <v>0.0005795</v>
       </c>
     </row>
     <row r="84">
@@ -3554,9 +3806,12 @@
         <v>0.4454</v>
       </c>
       <c r="J84" s="1" t="n">
-        <v>0.4454</v>
+        <v>0.4457</v>
       </c>
       <c r="K84" s="1" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="L84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -3591,9 +3846,12 @@
         <v>0.06245</v>
       </c>
       <c r="J85" s="1" t="n">
+        <v>0.06248</v>
+      </c>
+      <c r="K85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="K85" s="1" t="n">
+      <c r="L85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -3628,9 +3886,12 @@
         <v>0.05424</v>
       </c>
       <c r="J86" s="1" t="n">
+        <v>0.05442</v>
+      </c>
+      <c r="K86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="K86" s="1" t="n">
+      <c r="L86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -3665,9 +3926,12 @@
         <v>0.003366</v>
       </c>
       <c r="J87" s="1" t="n">
+        <v>0.003331</v>
+      </c>
+      <c r="K87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="K87" s="1" t="n">
+      <c r="L87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -3702,9 +3966,12 @@
         <v>0.05082</v>
       </c>
       <c r="J88" s="1" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="K88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="K88" s="1" t="n">
+      <c r="L88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -3739,9 +4006,12 @@
         <v>0.03047</v>
       </c>
       <c r="J89" s="1" t="n">
+        <v>0.03032</v>
+      </c>
+      <c r="K89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="K89" s="1" t="n">
+      <c r="L89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -3776,9 +4046,12 @@
         <v>0.348</v>
       </c>
       <c r="J90" s="1" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="K90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="K90" s="1" t="n">
+      <c r="L90" s="1" t="n">
         <v>0.3473</v>
       </c>
     </row>
@@ -3813,9 +4086,12 @@
         <v>0.07675999999999999</v>
       </c>
       <c r="J91" s="1" t="n">
-        <v>0.07675999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="K91" s="1" t="n">
+        <v>0.0835</v>
+      </c>
+      <c r="L91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -3850,9 +4126,12 @@
         <v>0.3504</v>
       </c>
       <c r="J92" s="1" t="n">
-        <v>0.3527</v>
+        <v>0.3551</v>
       </c>
       <c r="K92" s="1" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="L92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -3887,9 +4166,12 @@
         <v>1.9746</v>
       </c>
       <c r="J93" s="1" t="n">
-        <v>1.9753</v>
+        <v>1.9779</v>
       </c>
       <c r="K93" s="1" t="n">
+        <v>1.9779</v>
+      </c>
+      <c r="L93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -3924,10 +4206,13 @@
         <v>0.259</v>
       </c>
       <c r="J94" s="1" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="K94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="K94" s="1" t="n">
-        <v>0.2589</v>
+      <c r="L94" s="1" t="n">
+        <v>0.2586</v>
       </c>
     </row>
     <row r="95">
@@ -3961,9 +4246,12 @@
         <v>0.04533</v>
       </c>
       <c r="J95" s="1" t="n">
-        <v>0.04542</v>
+        <v>0.04549</v>
       </c>
       <c r="K95" s="1" t="n">
+        <v>0.04549</v>
+      </c>
+      <c r="L95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -3998,9 +4286,12 @@
         <v>0.006296</v>
       </c>
       <c r="J96" s="1" t="n">
+        <v>0.006242</v>
+      </c>
+      <c r="K96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="K96" s="1" t="n">
+      <c r="L96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -4035,9 +4326,12 @@
         <v>0.00173</v>
       </c>
       <c r="J97" s="1" t="n">
+        <v>0.001736</v>
+      </c>
+      <c r="K97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="K97" s="1" t="n">
+      <c r="L97" s="1" t="n">
         <v>0.00173</v>
       </c>
     </row>
@@ -4072,9 +4366,12 @@
         <v>5.266</v>
       </c>
       <c r="J98" s="1" t="n">
+        <v>5.251</v>
+      </c>
+      <c r="K98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="K98" s="1" t="n">
+      <c r="L98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -4109,9 +4406,12 @@
         <v>0.01517</v>
       </c>
       <c r="J99" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="K99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="K99" s="1" t="n">
+      <c r="L99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -4146,9 +4446,12 @@
         <v>0.5538999999999999</v>
       </c>
       <c r="J100" s="1" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5545</v>
       </c>
       <c r="K100" s="1" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="L100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -4183,9 +4486,12 @@
         <v>0.0911</v>
       </c>
       <c r="J101" s="1" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="K101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="K101" s="1" t="n">
+      <c r="L101" s="1" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -4220,10 +4526,13 @@
         <v>32.44</v>
       </c>
       <c r="J102" s="1" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="K102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="K102" s="1" t="n">
-        <v>32.44</v>
+      <c r="L102" s="1" t="n">
+        <v>32.42</v>
       </c>
     </row>
     <row r="103">
@@ -4257,9 +4566,12 @@
         <v>0.03182</v>
       </c>
       <c r="J103" s="1" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="K103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="K103" s="1" t="n">
+      <c r="L103" s="1" t="n">
         <v>0.03182</v>
       </c>
     </row>
@@ -4294,10 +4606,13 @@
         <v>0.06571</v>
       </c>
       <c r="J104" s="1" t="n">
+        <v>0.06561</v>
+      </c>
+      <c r="K104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="K104" s="1" t="n">
-        <v>0.06571</v>
+      <c r="L104" s="1" t="n">
+        <v>0.06561</v>
       </c>
     </row>
     <row r="105">
@@ -4331,9 +4646,12 @@
         <v>1.3044</v>
       </c>
       <c r="J105" s="1" t="n">
-        <v>1.3044</v>
+        <v>1.3046</v>
       </c>
       <c r="K105" s="1" t="n">
+        <v>1.3046</v>
+      </c>
+      <c r="L105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -4368,9 +4686,12 @@
         <v>0.1206</v>
       </c>
       <c r="J106" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="K106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="K106" s="1" t="n">
+      <c r="L106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -4408,6 +4729,9 @@
         <v>0.121</v>
       </c>
       <c r="K107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="L107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -4442,10 +4766,13 @@
         <v>0.09588000000000001</v>
       </c>
       <c r="J108" s="1" t="n">
+        <v>0.09579</v>
+      </c>
+      <c r="K108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="K108" s="1" t="n">
-        <v>0.09586</v>
+      <c r="L108" s="1" t="n">
+        <v>0.09579</v>
       </c>
     </row>
     <row r="109">
@@ -4479,10 +4806,13 @@
         <v>0.13886</v>
       </c>
       <c r="J109" s="1" t="n">
+        <v>0.13853</v>
+      </c>
+      <c r="K109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="K109" s="1" t="n">
-        <v>0.13861</v>
+      <c r="L109" s="1" t="n">
+        <v>0.13853</v>
       </c>
     </row>
     <row r="110">
@@ -4516,9 +4846,12 @@
         <v>5.549</v>
       </c>
       <c r="J110" s="1" t="n">
+        <v>5.548</v>
+      </c>
+      <c r="K110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="K110" s="1" t="n">
+      <c r="L110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -4553,9 +4886,12 @@
         <v>1.099</v>
       </c>
       <c r="J111" s="1" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="K111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="K111" s="1" t="n">
+      <c r="L111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -4590,10 +4926,13 @@
         <v>0.029252</v>
       </c>
       <c r="J112" s="1" t="n">
+        <v>0.029118</v>
+      </c>
+      <c r="K112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="K112" s="1" t="n">
-        <v>0.029252</v>
+      <c r="L112" s="1" t="n">
+        <v>0.029118</v>
       </c>
     </row>
     <row r="113">
@@ -4627,9 +4966,12 @@
         <v>1.882</v>
       </c>
       <c r="J113" s="1" t="n">
+        <v>1.878</v>
+      </c>
+      <c r="K113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="K113" s="1" t="n">
+      <c r="L113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -4664,9 +5006,12 @@
         <v>0.05862</v>
       </c>
       <c r="J114" s="1" t="n">
+        <v>0.05913</v>
+      </c>
+      <c r="K114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="K114" s="1" t="n">
+      <c r="L114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -4701,9 +5046,12 @@
         <v>0.12808</v>
       </c>
       <c r="J115" s="1" t="n">
+        <v>0.12874</v>
+      </c>
+      <c r="K115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="K115" s="1" t="n">
+      <c r="L115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -4738,9 +5086,12 @@
         <v>1.1117</v>
       </c>
       <c r="J116" s="1" t="n">
+        <v>1.1111</v>
+      </c>
+      <c r="K116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="K116" s="1" t="n">
+      <c r="L116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -4775,9 +5126,12 @@
         <v>0.1574</v>
       </c>
       <c r="J117" s="1" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="K117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="K117" s="1" t="n">
+      <c r="L117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -4812,9 +5166,12 @@
         <v>0.1603</v>
       </c>
       <c r="J118" s="1" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="K118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="K118" s="1" t="n">
+      <c r="L118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -4849,9 +5206,12 @@
         <v>0.04641</v>
       </c>
       <c r="J119" s="1" t="n">
-        <v>0.04641</v>
+        <v>0.04683</v>
       </c>
       <c r="K119" s="1" t="n">
+        <v>0.04683</v>
+      </c>
+      <c r="L119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -4886,9 +5246,12 @@
         <v>3.023</v>
       </c>
       <c r="J120" s="1" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="K120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="K120" s="1" t="n">
+      <c r="L120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -4923,9 +5286,12 @@
         <v>0.2966</v>
       </c>
       <c r="J121" s="1" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="K121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="K121" s="1" t="n">
+      <c r="L121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -4960,9 +5326,12 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="J122" s="1" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="K122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="K122" s="1" t="n">
+      <c r="L122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -4997,9 +5366,12 @@
         <v>0.01258</v>
       </c>
       <c r="J123" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="K123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="K123" s="1" t="n">
+      <c r="L123" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -5034,10 +5406,13 @@
         <v>0.1582</v>
       </c>
       <c r="J124" s="1" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="K124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="K124" s="1" t="n">
-        <v>0.1582</v>
+      <c r="L124" s="1" t="n">
+        <v>0.1578</v>
       </c>
     </row>
     <row r="125">
@@ -5071,9 +5446,12 @@
         <v>0.001786</v>
       </c>
       <c r="J125" s="1" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="K125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="K125" s="1" t="n">
+      <c r="L125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -5108,10 +5486,13 @@
         <v>0.0004868</v>
       </c>
       <c r="J126" s="1" t="n">
+        <v>0.0004859</v>
+      </c>
+      <c r="K126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="K126" s="1" t="n">
-        <v>0.0004867</v>
+      <c r="L126" s="1" t="n">
+        <v>0.0004859</v>
       </c>
     </row>
     <row r="127">
@@ -5145,10 +5526,13 @@
         <v>0.02945</v>
       </c>
       <c r="J127" s="1" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="K127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="K127" s="1" t="n">
-        <v>0.02945</v>
+      <c r="L127" s="1" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="128">
@@ -5182,9 +5566,12 @@
         <v>0.04138</v>
       </c>
       <c r="J128" s="1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="K128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="K128" s="1" t="n">
+      <c r="L128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -5219,9 +5606,12 @@
         <v>0.04842</v>
       </c>
       <c r="J129" s="1" t="n">
+        <v>0.04841</v>
+      </c>
+      <c r="K129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="K129" s="1" t="n">
+      <c r="L129" s="1" t="n">
         <v>0.04838</v>
       </c>
     </row>
@@ -5256,9 +5646,12 @@
         <v>1.26e-05</v>
       </c>
       <c r="J130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="K130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="K130" s="1" t="n">
+      <c r="L130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -5293,9 +5686,12 @@
         <v>6.9e-06</v>
       </c>
       <c r="J131" s="1" t="n">
+        <v>6.8e-06</v>
+      </c>
+      <c r="K131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="K131" s="1" t="n">
+      <c r="L131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -5330,9 +5726,12 @@
         <v>0.007</v>
       </c>
       <c r="J132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="K132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="K132" s="1" t="n">
+      <c r="L132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -5367,9 +5766,12 @@
         <v>0.097</v>
       </c>
       <c r="J133" s="1" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="K133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="K133" s="1" t="n">
+      <c r="L133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -5404,9 +5806,12 @@
         <v>0.0004107</v>
       </c>
       <c r="J134" s="1" t="n">
+        <v>0.0004104</v>
+      </c>
+      <c r="K134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="K134" s="1" t="n">
+      <c r="L134" s="1" t="n">
         <v>0.0004099</v>
       </c>
     </row>
@@ -5441,9 +5846,12 @@
         <v>0.08391</v>
       </c>
       <c r="J135" s="1" t="n">
+        <v>0.08344</v>
+      </c>
+      <c r="K135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="K135" s="1" t="n">
+      <c r="L135" s="1" t="n">
         <v>0.08344</v>
       </c>
     </row>
@@ -5478,9 +5886,12 @@
         <v>0.007938000000000001</v>
       </c>
       <c r="J136" s="1" t="n">
+        <v>0.007939</v>
+      </c>
+      <c r="K136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="K136" s="1" t="n">
+      <c r="L136" s="1" t="n">
         <v>0.007891</v>
       </c>
     </row>
@@ -5515,9 +5926,12 @@
         <v>0.0008304</v>
       </c>
       <c r="J137" s="1" t="n">
+        <v>0.0008207000000000001</v>
+      </c>
+      <c r="K137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="K137" s="1" t="n">
+      <c r="L137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -5552,10 +5966,13 @@
         <v>0.1473</v>
       </c>
       <c r="J138" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="K138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="K138" s="1" t="n">
-        <v>0.1473</v>
+      <c r="L138" s="1" t="n">
+        <v>0.147</v>
       </c>
     </row>
     <row r="139">
@@ -5589,10 +6006,13 @@
         <v>0.006724</v>
       </c>
       <c r="J139" s="1" t="n">
+        <v>0.006714</v>
+      </c>
+      <c r="K139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="K139" s="1" t="n">
-        <v>0.00672</v>
+      <c r="L139" s="1" t="n">
+        <v>0.006714</v>
       </c>
     </row>
     <row r="140">
@@ -5626,9 +6046,12 @@
         <v>0.01381</v>
       </c>
       <c r="J140" s="1" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="K140" s="1" t="n">
         <v>0.01391</v>
       </c>
-      <c r="K140" s="1" t="n">
+      <c r="L140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -5663,9 +6086,12 @@
         <v>0.09809</v>
       </c>
       <c r="J141" s="1" t="n">
+        <v>0.09807</v>
+      </c>
+      <c r="K141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="K141" s="1" t="n">
+      <c r="L141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -5700,9 +6126,12 @@
         <v>0.05422</v>
       </c>
       <c r="J142" s="1" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="K142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="K142" s="1" t="n">
+      <c r="L142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -5737,9 +6166,12 @@
         <v>0.3244</v>
       </c>
       <c r="J143" s="1" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="K143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="K143" s="1" t="n">
+      <c r="L143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -5774,9 +6206,12 @@
         <v>0.02584</v>
       </c>
       <c r="J144" s="1" t="n">
+        <v>0.02583</v>
+      </c>
+      <c r="K144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="K144" s="1" t="n">
+      <c r="L144" s="1" t="n">
         <v>0.02572</v>
       </c>
     </row>
@@ -5811,9 +6246,12 @@
         <v>0.2383</v>
       </c>
       <c r="J145" s="1" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="K145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="K145" s="1" t="n">
+      <c r="L145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -5848,10 +6286,13 @@
         <v>0.00703</v>
       </c>
       <c r="J146" s="1" t="n">
+        <v>0.006982</v>
+      </c>
+      <c r="K146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="K146" s="1" t="n">
-        <v>0.00703</v>
+      <c r="L146" s="1" t="n">
+        <v>0.006982</v>
       </c>
     </row>
     <row r="147">
@@ -5885,9 +6326,12 @@
         <v>0.08691</v>
       </c>
       <c r="J147" s="1" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="K147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="K147" s="1" t="n">
+      <c r="L147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -5922,9 +6366,12 @@
         <v>0.05066</v>
       </c>
       <c r="J148" s="1" t="n">
-        <v>0.05073</v>
+        <v>0.05217</v>
       </c>
       <c r="K148" s="1" t="n">
+        <v>0.05217</v>
+      </c>
+      <c r="L148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -5959,9 +6406,12 @@
         <v>0.02381</v>
       </c>
       <c r="J149" s="1" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="K149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="K149" s="1" t="n">
+      <c r="L149" s="1" t="n">
         <v>0.02381</v>
       </c>
     </row>
@@ -5996,9 +6446,12 @@
         <v>0.08581</v>
       </c>
       <c r="J150" s="1" t="n">
+        <v>0.08568000000000001</v>
+      </c>
+      <c r="K150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="K150" s="1" t="n">
+      <c r="L150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -6033,9 +6486,12 @@
         <v>0.02322</v>
       </c>
       <c r="J151" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="K151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="K151" s="1" t="n">
+      <c r="L151" s="1" t="n">
         <v>0.0232</v>
       </c>
     </row>
@@ -6070,9 +6526,12 @@
         <v>0.02561</v>
       </c>
       <c r="J152" s="1" t="n">
+        <v>0.02563</v>
+      </c>
+      <c r="K152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="K152" s="1" t="n">
+      <c r="L152" s="1" t="n">
         <v>0.02561</v>
       </c>
     </row>
@@ -6107,9 +6566,12 @@
         <v>0.0002178</v>
       </c>
       <c r="J153" s="1" t="n">
+        <v>0.0002173</v>
+      </c>
+      <c r="K153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="K153" s="1" t="n">
+      <c r="L153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -6144,9 +6606,12 @@
         <v>0.4438</v>
       </c>
       <c r="J154" s="1" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="K154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="K154" s="1" t="n">
+      <c r="L154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -6181,9 +6646,12 @@
         <v>0.067</v>
       </c>
       <c r="J155" s="1" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="K155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="K155" s="1" t="n">
+      <c r="L155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -6218,9 +6686,12 @@
         <v>0.129</v>
       </c>
       <c r="J156" s="1" t="n">
+        <v>0.12839</v>
+      </c>
+      <c r="K156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="K156" s="1" t="n">
+      <c r="L156" s="1" t="n">
         <v>0.12825</v>
       </c>
     </row>
@@ -6255,10 +6726,13 @@
         <v>0.4844</v>
       </c>
       <c r="J157" s="1" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="K157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="K157" s="1" t="n">
-        <v>0.4843</v>
+      <c r="L157" s="1" t="n">
+        <v>0.484</v>
       </c>
     </row>
     <row r="158">
@@ -6292,9 +6766,12 @@
         <v>0.4494</v>
       </c>
       <c r="J158" s="1" t="n">
+        <v>0.4488</v>
+      </c>
+      <c r="K158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="K158" s="1" t="n">
+      <c r="L158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -6329,9 +6806,12 @@
         <v>0.007515</v>
       </c>
       <c r="J159" s="1" t="n">
+        <v>0.007515</v>
+      </c>
+      <c r="K159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="K159" s="1" t="n">
+      <c r="L159" s="1" t="n">
         <v>0.007493</v>
       </c>
     </row>
@@ -6366,9 +6846,12 @@
         <v>0.00467</v>
       </c>
       <c r="J160" s="1" t="n">
-        <v>0.00467</v>
+        <v>0.004681</v>
       </c>
       <c r="K160" s="1" t="n">
+        <v>0.004681</v>
+      </c>
+      <c r="L160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -6403,9 +6886,12 @@
         <v>0.004295</v>
       </c>
       <c r="J161" s="1" t="n">
+        <v>0.004296</v>
+      </c>
+      <c r="K161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="K161" s="1" t="n">
+      <c r="L161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -6440,9 +6926,12 @@
         <v>0.0959</v>
       </c>
       <c r="J162" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="K162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="K162" s="1" t="n">
+      <c r="L162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -6477,9 +6966,12 @@
         <v>0.2852</v>
       </c>
       <c r="J163" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="K163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="K163" s="1" t="n">
+      <c r="L163" s="1" t="n">
         <v>0.2852</v>
       </c>
     </row>
@@ -6514,9 +7006,12 @@
         <v>0.1139</v>
       </c>
       <c r="J164" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="K164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="K164" s="1" t="n">
+      <c r="L164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -6551,10 +7046,13 @@
         <v>0.1755</v>
       </c>
       <c r="J165" s="1" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="K165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="K165" s="1" t="n">
-        <v>0.1755</v>
+      <c r="L165" s="1" t="n">
+        <v>0.1754</v>
       </c>
     </row>
     <row r="166">
@@ -6588,9 +7086,12 @@
         <v>0.01007</v>
       </c>
       <c r="J166" s="1" t="n">
-        <v>0.01009</v>
+        <v>0.0101</v>
       </c>
       <c r="K166" s="1" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="L166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -6625,10 +7126,13 @@
         <v>1.837</v>
       </c>
       <c r="J167" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="K167" s="1" t="n">
         <v>1.837</v>
       </c>
-      <c r="K167" s="1" t="n">
-        <v>1.827</v>
+      <c r="L167" s="1" t="n">
+        <v>1.826</v>
       </c>
     </row>
     <row r="168">
@@ -6662,9 +7166,12 @@
         <v>1.343</v>
       </c>
       <c r="J168" s="1" t="n">
+        <v>1.339</v>
+      </c>
+      <c r="K168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="K168" s="1" t="n">
+      <c r="L168" s="1" t="n">
         <v>1.337</v>
       </c>
     </row>
@@ -6699,9 +7206,12 @@
         <v>0.007313</v>
       </c>
       <c r="J169" s="1" t="n">
+        <v>0.007313</v>
+      </c>
+      <c r="K169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="K169" s="1" t="n">
+      <c r="L169" s="1" t="n">
         <v>0.007304</v>
       </c>
     </row>
@@ -6736,9 +7246,12 @@
         <v>0.0116</v>
       </c>
       <c r="J170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="K170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="K170" s="1" t="n">
+      <c r="L170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -6773,9 +7286,12 @@
         <v>0.005802</v>
       </c>
       <c r="J171" s="1" t="n">
+        <v>0.005798</v>
+      </c>
+      <c r="K171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="K171" s="1" t="n">
+      <c r="L171" s="1" t="n">
         <v>0.005796</v>
       </c>
     </row>
@@ -6810,9 +7326,12 @@
         <v>0.14729</v>
       </c>
       <c r="J172" s="1" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="K172" s="1" t="n">
         <v>0.14806</v>
       </c>
-      <c r="K172" s="1" t="n">
+      <c r="L172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -6847,9 +7366,12 @@
         <v>4.879</v>
       </c>
       <c r="J173" s="1" t="n">
+        <v>4.891</v>
+      </c>
+      <c r="K173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="K173" s="1" t="n">
+      <c r="L173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -6884,10 +7406,13 @@
         <v>0.07867</v>
       </c>
       <c r="J174" s="1" t="n">
+        <v>0.07857</v>
+      </c>
+      <c r="K174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="K174" s="1" t="n">
-        <v>0.07867</v>
+      <c r="L174" s="1" t="n">
+        <v>0.07857</v>
       </c>
     </row>
     <row r="175">
@@ -6921,9 +7446,12 @@
         <v>0.007477</v>
       </c>
       <c r="J175" s="1" t="n">
+        <v>0.007478</v>
+      </c>
+      <c r="K175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="K175" s="1" t="n">
+      <c r="L175" s="1" t="n">
         <v>0.007477</v>
       </c>
     </row>
@@ -6958,9 +7486,12 @@
         <v>0.2012</v>
       </c>
       <c r="J176" s="1" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="K176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="K176" s="1" t="n">
+      <c r="L176" s="1" t="n">
         <v>0.2012</v>
       </c>
     </row>
@@ -6995,9 +7526,12 @@
         <v>0.05181</v>
       </c>
       <c r="J177" s="1" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="K177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="K177" s="1" t="n">
+      <c r="L177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -7032,9 +7566,12 @@
         <v>0.05485</v>
       </c>
       <c r="J178" s="1" t="n">
+        <v>0.05482</v>
+      </c>
+      <c r="K178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="K178" s="1" t="n">
+      <c r="L178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -7069,9 +7606,12 @@
         <v>0.02321</v>
       </c>
       <c r="J179" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="K179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="K179" s="1" t="n">
+      <c r="L179" s="1" t="n">
         <v>0.02321</v>
       </c>
     </row>
@@ -7106,9 +7646,12 @@
         <v>0.6976</v>
       </c>
       <c r="J180" s="1" t="n">
+        <v>0.6962</v>
+      </c>
+      <c r="K180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="K180" s="1" t="n">
+      <c r="L180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -7143,9 +7686,12 @@
         <v>0.000371</v>
       </c>
       <c r="J181" s="1" t="n">
+        <v>0.0003732</v>
+      </c>
+      <c r="K181" s="1" t="n">
         <v>0.0003734</v>
       </c>
-      <c r="K181" s="1" t="n">
+      <c r="L181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -7180,9 +7726,12 @@
         <v>0.01258</v>
       </c>
       <c r="J182" s="1" t="n">
+        <v>0.01261</v>
+      </c>
+      <c r="K182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="K182" s="1" t="n">
+      <c r="L182" s="1" t="n">
         <v>0.01258</v>
       </c>
     </row>
@@ -7217,10 +7766,13 @@
         <v>4.242</v>
       </c>
       <c r="J183" s="1" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="K183" s="1" t="n">
-        <v>4.242</v>
+      <c r="L183" s="1" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="184">
@@ -7254,9 +7806,12 @@
         <v>0.238</v>
       </c>
       <c r="J184" s="1" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="K184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="K184" s="1" t="n">
+      <c r="L184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -7291,9 +7846,12 @@
         <v>0.03672</v>
       </c>
       <c r="J185" s="1" t="n">
+        <v>0.03678</v>
+      </c>
+      <c r="K185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="K185" s="1" t="n">
+      <c r="L185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -7328,9 +7886,12 @@
         <v>0.11567</v>
       </c>
       <c r="J186" s="1" t="n">
+        <v>0.11584</v>
+      </c>
+      <c r="K186" s="1" t="n">
         <v>0.11628</v>
       </c>
-      <c r="K186" s="1" t="n">
+      <c r="L186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -7365,9 +7926,12 @@
         <v>0.009013</v>
       </c>
       <c r="J187" s="1" t="n">
+        <v>0.009025</v>
+      </c>
+      <c r="K187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="K187" s="1" t="n">
+      <c r="L187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -7402,10 +7966,13 @@
         <v>0.0974</v>
       </c>
       <c r="J188" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="K188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="K188" s="1" t="n">
-        <v>0.0974</v>
+      <c r="L188" s="1" t="n">
+        <v>0.0973</v>
       </c>
     </row>
     <row r="189">
@@ -7439,9 +8006,12 @@
         <v>0.02791</v>
       </c>
       <c r="J189" s="1" t="n">
+        <v>0.02778</v>
+      </c>
+      <c r="K189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="K189" s="1" t="n">
+      <c r="L189" s="1" t="n">
         <v>0.02773</v>
       </c>
     </row>
@@ -7476,9 +8046,12 @@
         <v>0.00873</v>
       </c>
       <c r="J190" s="1" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="K190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="K190" s="1" t="n">
+      <c r="L190" s="1" t="n">
         <v>0.008699999999999999</v>
       </c>
     </row>
@@ -7513,10 +8086,13 @@
         <v>0.001952</v>
       </c>
       <c r="J191" s="1" t="n">
+        <v>0.001947</v>
+      </c>
+      <c r="K191" s="1" t="n">
         <v>0.001956</v>
       </c>
-      <c r="K191" s="1" t="n">
-        <v>0.001949</v>
+      <c r="L191" s="1" t="n">
+        <v>0.001947</v>
       </c>
     </row>
     <row r="192">
@@ -7550,9 +8126,12 @@
         <v>0.1005</v>
       </c>
       <c r="J192" s="1" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="K192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="K192" s="1" t="n">
+      <c r="L192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -7587,9 +8166,12 @@
         <v>0.02336</v>
       </c>
       <c r="J193" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="K193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="K193" s="1" t="n">
+      <c r="L193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -7624,9 +8206,12 @@
         <v>0.0135</v>
       </c>
       <c r="J194" s="1" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="K194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="K194" s="1" t="n">
+      <c r="L194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -7661,10 +8246,13 @@
         <v>0.02093</v>
       </c>
       <c r="J195" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="K195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="K195" s="1" t="n">
-        <v>0.02093</v>
+      <c r="L195" s="1" t="n">
+        <v>0.0209</v>
       </c>
     </row>
     <row r="196">
@@ -7698,9 +8286,12 @@
         <v>0.17168</v>
       </c>
       <c r="J196" s="1" t="n">
+        <v>0.17208</v>
+      </c>
+      <c r="K196" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="K196" s="1" t="n">
+      <c r="L196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -7735,9 +8326,12 @@
         <v>0.007277</v>
       </c>
       <c r="J197" s="1" t="n">
+        <v>0.007305</v>
+      </c>
+      <c r="K197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="K197" s="1" t="n">
+      <c r="L197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -7772,9 +8366,12 @@
         <v>0.01907</v>
       </c>
       <c r="J198" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="K198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="K198" s="1" t="n">
+      <c r="L198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -7809,9 +8406,12 @@
         <v>0.01622</v>
       </c>
       <c r="J199" s="1" t="n">
-        <v>0.0164</v>
+        <v>0.01653</v>
       </c>
       <c r="K199" s="1" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="L199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -7846,9 +8446,12 @@
         <v>0.2975</v>
       </c>
       <c r="J200" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="K200" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="K200" s="1" t="n">
+      <c r="L200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -7883,9 +8486,12 @@
         <v>0.006226</v>
       </c>
       <c r="J201" s="1" t="n">
+        <v>0.006227</v>
+      </c>
+      <c r="K201" s="1" t="n">
         <v>0.006237</v>
       </c>
-      <c r="K201" s="1" t="n">
+      <c r="L201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -7920,10 +8526,13 @@
         <v>0.0004448</v>
       </c>
       <c r="J202" s="1" t="n">
+        <v>0.0004436</v>
+      </c>
+      <c r="K202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="K202" s="1" t="n">
-        <v>0.0004448</v>
+      <c r="L202" s="1" t="n">
+        <v>0.0004436</v>
       </c>
     </row>
     <row r="203">
@@ -7957,9 +8566,12 @@
         <v>0.007339</v>
       </c>
       <c r="J203" s="1" t="n">
+        <v>0.007317</v>
+      </c>
+      <c r="K203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="K203" s="1" t="n">
+      <c r="L203" s="1" t="n">
         <v>0.007312</v>
       </c>
     </row>
@@ -7994,9 +8606,12 @@
         <v>0.1314</v>
       </c>
       <c r="J204" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="K204" s="1" t="n">
         <v>0.1314</v>
       </c>
-      <c r="K204" s="1" t="n">
+      <c r="L204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -8031,10 +8646,13 @@
         <v>0.01443</v>
       </c>
       <c r="J205" s="1" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="K205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="K205" s="1" t="n">
-        <v>0.01442</v>
+      <c r="L205" s="1" t="n">
+        <v>0.01412</v>
       </c>
     </row>
     <row r="206">
@@ -8068,9 +8686,12 @@
         <v>0.003591</v>
       </c>
       <c r="J206" s="1" t="n">
+        <v>0.00359</v>
+      </c>
+      <c r="K206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="K206" s="1" t="n">
+      <c r="L206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -8108,6 +8729,9 @@
         <v>0.05999</v>
       </c>
       <c r="K207" s="1" t="n">
+        <v>0.05999</v>
+      </c>
+      <c r="L207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -8142,9 +8766,12 @@
         <v>15.48</v>
       </c>
       <c r="J208" s="1" t="n">
-        <v>15.49</v>
+        <v>15.55</v>
       </c>
       <c r="K208" s="1" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="L208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -8179,9 +8806,12 @@
         <v>5191.3</v>
       </c>
       <c r="J209" s="1" t="n">
+        <v>5191.1</v>
+      </c>
+      <c r="K209" s="1" t="n">
         <v>5191.3</v>
       </c>
-      <c r="K209" s="1" t="n">
+      <c r="L209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -8216,10 +8846,13 @@
         <v>0.11992</v>
       </c>
       <c r="J210" s="1" t="n">
+        <v>0.11963</v>
+      </c>
+      <c r="K210" s="1" t="n">
         <v>0.12042</v>
       </c>
-      <c r="K210" s="1" t="n">
-        <v>0.11988</v>
+      <c r="L210" s="1" t="n">
+        <v>0.11963</v>
       </c>
     </row>
     <row r="211">
@@ -8253,9 +8886,12 @@
         <v>0.182</v>
       </c>
       <c r="J211" s="1" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="K211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="K211" s="1" t="n">
+      <c r="L211" s="1" t="n">
         <v>0.182</v>
       </c>
     </row>
@@ -8290,9 +8926,12 @@
         <v>0.0305</v>
       </c>
       <c r="J212" s="1" t="n">
-        <v>0.0305</v>
+        <v>0.0306</v>
       </c>
       <c r="K212" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="L212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -8327,9 +8966,12 @@
         <v>1.395</v>
       </c>
       <c r="J213" s="1" t="n">
+        <v>1.3938</v>
+      </c>
+      <c r="K213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="K213" s="1" t="n">
+      <c r="L213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -8364,10 +9006,13 @@
         <v>0.05652</v>
       </c>
       <c r="J214" s="1" t="n">
+        <v>0.05646</v>
+      </c>
+      <c r="K214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="K214" s="1" t="n">
-        <v>0.05652</v>
+      <c r="L214" s="1" t="n">
+        <v>0.05646</v>
       </c>
     </row>
     <row r="215">
@@ -8401,9 +9046,12 @@
         <v>0.04398</v>
       </c>
       <c r="J215" s="1" t="n">
-        <v>0.04398</v>
+        <v>0.04413</v>
       </c>
       <c r="K215" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="L215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -8438,10 +9086,13 @@
         <v>0.14962</v>
       </c>
       <c r="J216" s="1" t="n">
+        <v>0.14904</v>
+      </c>
+      <c r="K216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="K216" s="1" t="n">
-        <v>0.14962</v>
+      <c r="L216" s="1" t="n">
+        <v>0.14904</v>
       </c>
     </row>
     <row r="217">
@@ -8478,6 +9129,9 @@
         <v>0.074</v>
       </c>
       <c r="K217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -8512,9 +9166,12 @@
         <v>0.00268</v>
       </c>
       <c r="J218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="K218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="K218" s="1" t="n">
+      <c r="L218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -8549,9 +9206,12 @@
         <v>0.01718</v>
       </c>
       <c r="J219" s="1" t="n">
+        <v>0.01718</v>
+      </c>
+      <c r="K219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="K219" s="1" t="n">
+      <c r="L219" s="1" t="n">
         <v>0.01715</v>
       </c>
     </row>
@@ -8586,9 +9246,12 @@
         <v>0.05507</v>
       </c>
       <c r="J220" s="1" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="K220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="K220" s="1" t="n">
+      <c r="L220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -8626,6 +9289,9 @@
         <v>0.02196</v>
       </c>
       <c r="K221" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="L221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -8660,9 +9326,12 @@
         <v>0.00937</v>
       </c>
       <c r="J222" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="K222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="K222" s="1" t="n">
+      <c r="L222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -8702,6 +9371,9 @@
       <c r="K223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="L223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8734,9 +9406,12 @@
         <v>0.03836</v>
       </c>
       <c r="J224" s="1" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="K224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="K224" s="1" t="n">
+      <c r="L224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -8771,9 +9446,12 @@
         <v>0.001527</v>
       </c>
       <c r="J225" s="1" t="n">
+        <v>0.001525</v>
+      </c>
+      <c r="K225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="K225" s="1" t="n">
+      <c r="L225" s="1" t="n">
         <v>0.001525</v>
       </c>
     </row>
@@ -8808,9 +9486,12 @@
         <v>27</v>
       </c>
       <c r="J226" s="1" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="K226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="K226" s="1" t="n">
+      <c r="L226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -8845,9 +9526,12 @@
         <v>0.07059</v>
       </c>
       <c r="J227" s="1" t="n">
-        <v>0.07059</v>
+        <v>0.07088999999999999</v>
       </c>
       <c r="K227" s="1" t="n">
+        <v>0.07088999999999999</v>
+      </c>
+      <c r="L227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -8882,9 +9566,12 @@
         <v>0.3127</v>
       </c>
       <c r="J228" s="1" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="K228" s="1" t="n">
         <v>0.3131</v>
       </c>
-      <c r="K228" s="1" t="n">
+      <c r="L228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -8919,10 +9606,13 @@
         <v>18.39</v>
       </c>
       <c r="J229" s="1" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="K229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="K229" s="1" t="n">
-        <v>18.39</v>
+      <c r="L229" s="1" t="n">
+        <v>18.38</v>
       </c>
     </row>
     <row r="230">
@@ -8956,9 +9646,12 @@
         <v>0.01929</v>
       </c>
       <c r="J230" s="1" t="n">
+        <v>0.01935</v>
+      </c>
+      <c r="K230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="K230" s="1" t="n">
+      <c r="L230" s="1" t="n">
         <v>0.01928</v>
       </c>
     </row>
@@ -8993,9 +9686,12 @@
         <v>0.01218</v>
       </c>
       <c r="J231" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="K231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="K231" s="1" t="n">
+      <c r="L231" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>
@@ -9030,9 +9726,12 @@
         <v>0.2279</v>
       </c>
       <c r="J232" s="1" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="K232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="K232" s="1" t="n">
+      <c r="L232" s="1" t="n">
         <v>0.2279</v>
       </c>
     </row>
@@ -9067,9 +9766,12 @@
         <v>0.07087</v>
       </c>
       <c r="J233" s="1" t="n">
+        <v>0.07108</v>
+      </c>
+      <c r="K233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="K233" s="1" t="n">
+      <c r="L233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -9104,9 +9806,12 @@
         <v>0.1699</v>
       </c>
       <c r="J234" s="1" t="n">
+        <v>0.1701</v>
+      </c>
+      <c r="K234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="K234" s="1" t="n">
+      <c r="L234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -9141,9 +9846,12 @@
         <v>0.0251</v>
       </c>
       <c r="J235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="K235" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="K235" s="1" t="n">
+      <c r="L235" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -9178,10 +9886,13 @@
         <v>0.03005</v>
       </c>
       <c r="J236" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="K236" s="1" t="n">
-        <v>0.03003</v>
+      <c r="L236" s="1" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="237">
@@ -9215,9 +9926,12 @@
         <v>1.988</v>
       </c>
       <c r="J237" s="1" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="K237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="K237" s="1" t="n">
+      <c r="L237" s="1" t="n">
         <v>1.984</v>
       </c>
     </row>
@@ -9252,9 +9966,12 @@
         <v>0.427</v>
       </c>
       <c r="J238" s="1" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="K238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="K238" s="1" t="n">
+      <c r="L238" s="1" t="n">
         <v>0.4268</v>
       </c>
     </row>
@@ -9289,9 +10006,12 @@
         <v>0.03334</v>
       </c>
       <c r="J239" s="1" t="n">
+        <v>0.03344</v>
+      </c>
+      <c r="K239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="K239" s="1" t="n">
+      <c r="L239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -9326,9 +10046,12 @@
         <v>0.03406</v>
       </c>
       <c r="J240" s="1" t="n">
+        <v>0.03391</v>
+      </c>
+      <c r="K240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="K240" s="1" t="n">
+      <c r="L240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -9363,9 +10086,12 @@
         <v>0.0007536</v>
       </c>
       <c r="J241" s="1" t="n">
-        <v>0.0007551</v>
+        <v>0.0007556</v>
       </c>
       <c r="K241" s="1" t="n">
+        <v>0.0007556</v>
+      </c>
+      <c r="L241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -9403,6 +10129,9 @@
         <v>0.1847</v>
       </c>
       <c r="K242" s="1" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="L242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -9437,9 +10166,12 @@
         <v>0.014772</v>
       </c>
       <c r="J243" s="1" t="n">
+        <v>0.014794</v>
+      </c>
+      <c r="K243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="K243" s="1" t="n">
+      <c r="L243" s="1" t="n">
         <v>0.014772</v>
       </c>
     </row>
@@ -9474,10 +10206,13 @@
         <v>3.06e-05</v>
       </c>
       <c r="J244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="K244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="K244" s="1" t="n">
-        <v>3.06e-05</v>
+      <c r="L244" s="1" t="n">
+        <v>3.01e-05</v>
       </c>
     </row>
     <row r="245">
@@ -9511,9 +10246,12 @@
         <v>0.03522</v>
       </c>
       <c r="J245" s="1" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="K245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="K245" s="1" t="n">
+      <c r="L245" s="1" t="n">
         <v>0.03516</v>
       </c>
     </row>
@@ -9548,9 +10286,12 @@
         <v>0.08058</v>
       </c>
       <c r="J246" s="1" t="n">
+        <v>0.08048</v>
+      </c>
+      <c r="K246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="K246" s="1" t="n">
+      <c r="L246" s="1" t="n">
         <v>0.08039</v>
       </c>
     </row>
@@ -9585,9 +10326,12 @@
         <v>0.007469</v>
       </c>
       <c r="J247" s="1" t="n">
+        <v>0.007343</v>
+      </c>
+      <c r="K247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="K247" s="1" t="n">
+      <c r="L247" s="1" t="n">
         <v>0.00728</v>
       </c>
     </row>
@@ -9622,9 +10366,12 @@
         <v>0.09565</v>
       </c>
       <c r="J248" s="1" t="n">
+        <v>0.09639</v>
+      </c>
+      <c r="K248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="K248" s="1" t="n">
+      <c r="L248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -9662,6 +10409,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="K249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -9696,9 +10446,12 @@
         <v>0.03501</v>
       </c>
       <c r="J250" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="K250" s="1" t="n">
+      <c r="L250" s="1" t="n">
         <v>0.03498</v>
       </c>
     </row>
@@ -9733,10 +10486,13 @@
         <v>0.04049</v>
       </c>
       <c r="J251" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="K251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="K251" s="1" t="n">
-        <v>0.04049</v>
+      <c r="L251" s="1" t="n">
+        <v>0.04035</v>
       </c>
     </row>
     <row r="252">
@@ -9770,9 +10526,12 @@
         <v>0.0897</v>
       </c>
       <c r="J252" s="1" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="K252" s="1" t="n">
         <v>0.0897</v>
       </c>
-      <c r="K252" s="1" t="n">
+      <c r="L252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -9807,9 +10566,12 @@
         <v>4.081</v>
       </c>
       <c r="J253" s="1" t="n">
+        <v>4.077</v>
+      </c>
+      <c r="K253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="K253" s="1" t="n">
+      <c r="L253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -9844,9 +10606,12 @@
         <v>0.1871</v>
       </c>
       <c r="J254" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="K254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="K254" s="1" t="n">
+      <c r="L254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -9881,9 +10646,12 @@
         <v>0.07244</v>
       </c>
       <c r="J255" s="1" t="n">
+        <v>0.07235999999999999</v>
+      </c>
+      <c r="K255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="K255" s="1" t="n">
+      <c r="L255" s="1" t="n">
         <v>0.07214</v>
       </c>
     </row>
@@ -9918,9 +10686,12 @@
         <v>0.01833</v>
       </c>
       <c r="J256" s="1" t="n">
+        <v>0.01832</v>
+      </c>
+      <c r="K256" s="1" t="n">
         <v>0.01833</v>
       </c>
-      <c r="K256" s="1" t="n">
+      <c r="L256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -9955,9 +10726,12 @@
         <v>5.948</v>
       </c>
       <c r="J257" s="1" t="n">
+        <v>5.942</v>
+      </c>
+      <c r="K257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="K257" s="1" t="n">
+      <c r="L257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -9992,9 +10766,12 @@
         <v>0.2633</v>
       </c>
       <c r="J258" s="1" t="n">
-        <v>0.2639</v>
+        <v>0.2645</v>
       </c>
       <c r="K258" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="L258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -10029,9 +10806,12 @@
         <v>0.1362</v>
       </c>
       <c r="J259" s="1" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="K259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="K259" s="1" t="n">
+      <c r="L259" s="1" t="n">
         <v>0.1361</v>
       </c>
     </row>
@@ -10066,9 +10846,12 @@
         <v>0.30667</v>
       </c>
       <c r="J260" s="1" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="K260" s="1" t="n">
         <v>0.30667</v>
       </c>
-      <c r="K260" s="1" t="n">
+      <c r="L260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -10103,9 +10886,12 @@
         <v>0.099</v>
       </c>
       <c r="J261" s="1" t="n">
+        <v>0.09873999999999999</v>
+      </c>
+      <c r="K261" s="1" t="n">
         <v>0.099</v>
       </c>
-      <c r="K261" s="1" t="n">
+      <c r="L261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -10140,9 +10926,12 @@
         <v>0.5417999999999999</v>
       </c>
       <c r="J262" s="1" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="K262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="K262" s="1" t="n">
+      <c r="L262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -10177,9 +10966,12 @@
         <v>0.2914</v>
       </c>
       <c r="J263" s="1" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="K263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="K263" s="1" t="n">
+      <c r="L263" s="1" t="n">
         <v>0.2914</v>
       </c>
     </row>
@@ -10214,9 +11006,12 @@
         <v>0.954</v>
       </c>
       <c r="J264" s="1" t="n">
-        <v>0.954</v>
+        <v>0.96</v>
       </c>
       <c r="K264" s="1" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -10251,9 +11046,12 @@
         <v>0.5407</v>
       </c>
       <c r="J265" s="1" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="K265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="K265" s="1" t="n">
+      <c r="L265" s="1" t="n">
         <v>0.5403</v>
       </c>
     </row>
@@ -10288,9 +11086,12 @@
         <v>0.07382</v>
       </c>
       <c r="J266" s="1" t="n">
+        <v>0.07381</v>
+      </c>
+      <c r="K266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="K266" s="1" t="n">
+      <c r="L266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -10325,9 +11126,12 @@
         <v>0.02163</v>
       </c>
       <c r="J267" s="1" t="n">
-        <v>0.02163</v>
+        <v>0.02188</v>
       </c>
       <c r="K267" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="L267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -10362,9 +11166,12 @@
         <v>0.01619</v>
       </c>
       <c r="J268" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="K268" s="1" t="n">
         <v>0.01633</v>
       </c>
-      <c r="K268" s="1" t="n">
+      <c r="L268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -10399,9 +11206,12 @@
         <v>0.003733</v>
       </c>
       <c r="J269" s="1" t="n">
-        <v>0.003733</v>
+        <v>0.003765</v>
       </c>
       <c r="K269" s="1" t="n">
+        <v>0.003765</v>
+      </c>
+      <c r="L269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -10436,10 +11246,13 @@
         <v>0.00766</v>
       </c>
       <c r="J270" s="1" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="K270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="K270" s="1" t="n">
-        <v>0.00766</v>
+      <c r="L270" s="1" t="n">
+        <v>0.00764</v>
       </c>
     </row>
     <row r="271">
@@ -10473,9 +11286,12 @@
         <v>0.05501</v>
       </c>
       <c r="J271" s="1" t="n">
+        <v>0.05506</v>
+      </c>
+      <c r="K271" s="1" t="n">
         <v>0.05512</v>
       </c>
-      <c r="K271" s="1" t="n">
+      <c r="L271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -10510,9 +11326,12 @@
         <v>2.31</v>
       </c>
       <c r="J272" s="1" t="n">
+        <v>2.306</v>
+      </c>
+      <c r="K272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="K272" s="1" t="n">
+      <c r="L272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -10547,9 +11366,12 @@
         <v>0.05473</v>
       </c>
       <c r="J273" s="1" t="n">
-        <v>0.05473</v>
+        <v>0.05481</v>
       </c>
       <c r="K273" s="1" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="L273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -10584,9 +11406,12 @@
         <v>0.02293</v>
       </c>
       <c r="J274" s="1" t="n">
+        <v>0.02298</v>
+      </c>
+      <c r="K274" s="1" t="n">
         <v>0.02303</v>
       </c>
-      <c r="K274" s="1" t="n">
+      <c r="L274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -10621,9 +11446,12 @@
         <v>1.186</v>
       </c>
       <c r="J275" s="1" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="K275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="K275" s="1" t="n">
+      <c r="L275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -10658,9 +11486,12 @@
         <v>0.273</v>
       </c>
       <c r="J276" s="1" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="K276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="K276" s="1" t="n">
+      <c r="L276" s="1" t="n">
         <v>0.2722</v>
       </c>
     </row>
@@ -10695,9 +11526,12 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="J277" s="1" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="K277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="K277" s="1" t="n">
+      <c r="L277" s="1" t="n">
         <v>0.9419999999999999</v>
       </c>
     </row>
@@ -10732,9 +11566,12 @@
         <v>0.6268</v>
       </c>
       <c r="J278" s="1" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6294</v>
       </c>
       <c r="K278" s="1" t="n">
+        <v>0.6294</v>
+      </c>
+      <c r="L278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -10769,10 +11606,13 @@
         <v>0.001346</v>
       </c>
       <c r="J279" s="1" t="n">
+        <v>0.001344</v>
+      </c>
+      <c r="K279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="K279" s="1" t="n">
-        <v>0.001346</v>
+      <c r="L279" s="1" t="n">
+        <v>0.001344</v>
       </c>
     </row>
     <row r="280">
@@ -10806,9 +11646,12 @@
         <v>0.005567</v>
       </c>
       <c r="J280" s="1" t="n">
+        <v>0.005563</v>
+      </c>
+      <c r="K280" s="1" t="n">
         <v>0.005567</v>
       </c>
-      <c r="K280" s="1" t="n">
+      <c r="L280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -10843,9 +11686,12 @@
         <v>1.521</v>
       </c>
       <c r="J281" s="1" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="K281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="K281" s="1" t="n">
+      <c r="L281" s="1" t="n">
         <v>1.521</v>
       </c>
     </row>
@@ -10880,9 +11726,12 @@
         <v>28.4</v>
       </c>
       <c r="J282" s="1" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="K282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="K282" s="1" t="n">
+      <c r="L282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -10917,10 +11766,13 @@
         <v>0.12901</v>
       </c>
       <c r="J283" s="1" t="n">
+        <v>0.12875</v>
+      </c>
+      <c r="K283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="K283" s="1" t="n">
-        <v>0.12892</v>
+      <c r="L283" s="1" t="n">
+        <v>0.12875</v>
       </c>
     </row>
     <row r="284">
@@ -10954,9 +11806,12 @@
         <v>0.01113</v>
       </c>
       <c r="J284" s="1" t="n">
+        <v>0.01115</v>
+      </c>
+      <c r="K284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="K284" s="1" t="n">
+      <c r="L284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -10991,9 +11846,12 @@
         <v>6.548</v>
       </c>
       <c r="J285" s="1" t="n">
-        <v>6.548</v>
+        <v>6.577</v>
       </c>
       <c r="K285" s="1" t="n">
+        <v>6.577</v>
+      </c>
+      <c r="L285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -11028,9 +11886,12 @@
         <v>0.01852</v>
       </c>
       <c r="J286" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="K286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="K286" s="1" t="n">
+      <c r="L286" s="1" t="n">
         <v>0.01848</v>
       </c>
     </row>
@@ -11065,10 +11926,13 @@
         <v>0.008404</v>
       </c>
       <c r="J287" s="1" t="n">
+        <v>0.008378</v>
+      </c>
+      <c r="K287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="K287" s="1" t="n">
-        <v>0.008404</v>
+      <c r="L287" s="1" t="n">
+        <v>0.008378</v>
       </c>
     </row>
     <row r="288">
@@ -11102,9 +11966,12 @@
         <v>0.3873</v>
       </c>
       <c r="J288" s="1" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="K288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="K288" s="1" t="n">
+      <c r="L288" s="1" t="n">
         <v>0.3846</v>
       </c>
     </row>
@@ -11139,9 +12006,12 @@
         <v>0.010099</v>
       </c>
       <c r="J289" s="1" t="n">
+        <v>0.010093</v>
+      </c>
+      <c r="K289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="K289" s="1" t="n">
+      <c r="L289" s="1" t="n">
         <v>0.01008</v>
       </c>
     </row>
@@ -11176,10 +12046,13 @@
         <v>0.02611</v>
       </c>
       <c r="J290" s="1" t="n">
+        <v>0.02595</v>
+      </c>
+      <c r="K290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="K290" s="1" t="n">
-        <v>0.02611</v>
+      <c r="L290" s="1" t="n">
+        <v>0.02595</v>
       </c>
     </row>
     <row r="291">
@@ -11213,9 +12086,12 @@
         <v>0.097</v>
       </c>
       <c r="J291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="K291" s="1" t="n">
+      <c r="L291" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -11250,9 +12126,12 @@
         <v>0.28632</v>
       </c>
       <c r="J292" s="1" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="K292" s="1" t="n">
         <v>0.28632</v>
       </c>
-      <c r="K292" s="1" t="n">
+      <c r="L292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -11287,9 +12166,12 @@
         <v>0.01538</v>
       </c>
       <c r="J293" s="1" t="n">
+        <v>0.01537</v>
+      </c>
+      <c r="K293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="K293" s="1" t="n">
+      <c r="L293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -11324,9 +12206,12 @@
         <v>0.003443</v>
       </c>
       <c r="J294" s="1" t="n">
-        <v>0.003443</v>
+        <v>0.003465</v>
       </c>
       <c r="K294" s="1" t="n">
+        <v>0.003465</v>
+      </c>
+      <c r="L294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -11361,10 +12246,13 @@
         <v>0.043008</v>
       </c>
       <c r="J295" s="1" t="n">
+        <v>0.04285</v>
+      </c>
+      <c r="K295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="K295" s="1" t="n">
-        <v>0.043008</v>
+      <c r="L295" s="1" t="n">
+        <v>0.04285</v>
       </c>
     </row>
     <row r="296">
@@ -11398,9 +12286,12 @@
         <v>0.02965</v>
       </c>
       <c r="J296" s="1" t="n">
-        <v>0.03007</v>
+        <v>0.03055</v>
       </c>
       <c r="K296" s="1" t="n">
+        <v>0.03055</v>
+      </c>
+      <c r="L296" s="1" t="n">
         <v>0.02929</v>
       </c>
     </row>
@@ -11435,10 +12326,13 @@
         <v>0.03792</v>
       </c>
       <c r="J297" s="1" t="n">
+        <v>0.03773</v>
+      </c>
+      <c r="K297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="K297" s="1" t="n">
-        <v>0.03786</v>
+      <c r="L297" s="1" t="n">
+        <v>0.03773</v>
       </c>
     </row>
     <row r="298">
@@ -11472,9 +12366,12 @@
         <v>0.08312</v>
       </c>
       <c r="J298" s="1" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="K298" s="1" t="n">
         <v>0.08359</v>
       </c>
-      <c r="K298" s="1" t="n">
+      <c r="L298" s="1" t="n">
         <v>0.08305999999999999</v>
       </c>
     </row>
@@ -11509,9 +12406,12 @@
         <v>0.00766</v>
       </c>
       <c r="J299" s="1" t="n">
-        <v>0.00766</v>
+        <v>0.00777</v>
       </c>
       <c r="K299" s="1" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="L299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -11546,9 +12446,12 @@
         <v>0.01512</v>
       </c>
       <c r="J300" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="K300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="K300" s="1" t="n">
+      <c r="L300" s="1" t="n">
         <v>0.01512</v>
       </c>
     </row>
@@ -11583,9 +12486,12 @@
         <v>0.1416</v>
       </c>
       <c r="J301" s="1" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="K301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="K301" s="1" t="n">
+      <c r="L301" s="1" t="n">
         <v>0.141</v>
       </c>
     </row>
@@ -11620,9 +12526,12 @@
         <v>0.0006284</v>
       </c>
       <c r="J302" s="1" t="n">
+        <v>0.0006348</v>
+      </c>
+      <c r="K302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="K302" s="1" t="n">
+      <c r="L302" s="1" t="n">
         <v>0.0006284</v>
       </c>
     </row>
@@ -11657,9 +12566,12 @@
         <v>0.06222</v>
       </c>
       <c r="J303" s="1" t="n">
+        <v>0.06224</v>
+      </c>
+      <c r="K303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="K303" s="1" t="n">
+      <c r="L303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -11694,9 +12606,12 @@
         <v>0.0001634</v>
       </c>
       <c r="J304" s="1" t="n">
-        <v>0.0001639</v>
+        <v>0.000164</v>
       </c>
       <c r="K304" s="1" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="L304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -11731,9 +12646,12 @@
         <v>0.06147</v>
       </c>
       <c r="J305" s="1" t="n">
-        <v>0.06147</v>
+        <v>0.06148</v>
       </c>
       <c r="K305" s="1" t="n">
+        <v>0.06148</v>
+      </c>
+      <c r="L305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -11768,9 +12686,12 @@
         <v>0.022377</v>
       </c>
       <c r="J306" s="1" t="n">
+        <v>0.022311</v>
+      </c>
+      <c r="K306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="K306" s="1" t="n">
+      <c r="L306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -11805,9 +12726,12 @@
         <v>0.02423</v>
       </c>
       <c r="J307" s="1" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="K307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="K307" s="1" t="n">
+      <c r="L307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -11842,9 +12766,12 @@
         <v>0.00041</v>
       </c>
       <c r="J308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="K308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="K308" s="1" t="n">
+      <c r="L308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -11879,9 +12806,12 @@
         <v>0.0898</v>
       </c>
       <c r="J309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="K309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="K309" s="1" t="n">
+      <c r="L309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -11916,9 +12846,12 @@
         <v>0.385</v>
       </c>
       <c r="J310" s="1" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="K310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="K310" s="1" t="n">
+      <c r="L310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -11953,9 +12886,12 @@
         <v>0.0355</v>
       </c>
       <c r="J311" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="K311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="K311" s="1" t="n">
+      <c r="L311" s="1" t="n">
         <v>0.0355</v>
       </c>
     </row>
@@ -11990,9 +12926,12 @@
         <v>0.02463</v>
       </c>
       <c r="J312" s="1" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="K312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="K312" s="1" t="n">
+      <c r="L312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -12027,9 +12966,12 @@
         <v>0.04131</v>
       </c>
       <c r="J313" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="K313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="K313" s="1" t="n">
+      <c r="L313" s="1" t="n">
         <v>0.04129</v>
       </c>
     </row>
@@ -12064,9 +13006,12 @@
         <v>4.015</v>
       </c>
       <c r="J314" s="1" t="n">
+        <v>4.005</v>
+      </c>
+      <c r="K314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="K314" s="1" t="n">
+      <c r="L314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -12101,9 +13046,12 @@
         <v>0.1601</v>
       </c>
       <c r="J315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="K315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="K315" s="1" t="n">
+      <c r="L315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -12138,9 +13086,12 @@
         <v>0.08848</v>
       </c>
       <c r="J316" s="1" t="n">
+        <v>0.08838</v>
+      </c>
+      <c r="K316" s="1" t="n">
         <v>0.08884</v>
       </c>
-      <c r="K316" s="1" t="n">
+      <c r="L316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -12175,9 +13126,12 @@
         <v>0.0683</v>
       </c>
       <c r="J317" s="1" t="n">
-        <v>0.06849</v>
+        <v>0.0687</v>
       </c>
       <c r="K317" s="1" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="L317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -12212,9 +13166,12 @@
         <v>0.012463</v>
       </c>
       <c r="J318" s="1" t="n">
+        <v>0.012497</v>
+      </c>
+      <c r="K318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="K318" s="1" t="n">
+      <c r="L318" s="1" t="n">
         <v>0.012463</v>
       </c>
     </row>
@@ -12249,9 +13206,12 @@
         <v>0.001136</v>
       </c>
       <c r="J319" s="1" t="n">
+        <v>0.001137</v>
+      </c>
+      <c r="K319" s="1" t="n">
         <v>0.001138</v>
       </c>
-      <c r="K319" s="1" t="n">
+      <c r="L319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -12286,9 +13246,12 @@
         <v>0.0631</v>
       </c>
       <c r="J320" s="1" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="K320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="K320" s="1" t="n">
+      <c r="L320" s="1" t="n">
         <v>0.063</v>
       </c>
     </row>
@@ -12326,6 +13289,9 @@
         <v>0.00527</v>
       </c>
       <c r="K321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="L321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -12360,9 +13326,12 @@
         <v>0.1116</v>
       </c>
       <c r="J322" s="1" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="K322" s="1" t="n">
         <v>0.1116</v>
       </c>
-      <c r="K322" s="1" t="n">
+      <c r="L322" s="1" t="n">
         <v>0.1114</v>
       </c>
     </row>
@@ -12397,9 +13366,12 @@
         <v>0.04304</v>
       </c>
       <c r="J323" s="1" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="K323" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="K323" s="1" t="n">
+      <c r="L323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -12434,9 +13406,12 @@
         <v>0.01783</v>
       </c>
       <c r="J324" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="K324" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="K324" s="1" t="n">
+      <c r="L324" s="1" t="n">
         <v>0.01768</v>
       </c>
     </row>
@@ -12471,9 +13446,12 @@
         <v>0.005663</v>
       </c>
       <c r="J325" s="1" t="n">
+        <v>0.005666</v>
+      </c>
+      <c r="K325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="K325" s="1" t="n">
+      <c r="L325" s="1" t="n">
         <v>0.005663</v>
       </c>
     </row>
@@ -12508,9 +13486,12 @@
         <v>0.001775</v>
       </c>
       <c r="J326" s="1" t="n">
+        <v>0.001775</v>
+      </c>
+      <c r="K326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="K326" s="1" t="n">
+      <c r="L326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -12545,9 +13526,12 @@
         <v>0.04047</v>
       </c>
       <c r="J327" s="1" t="n">
+        <v>0.04049</v>
+      </c>
+      <c r="K327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="K327" s="1" t="n">
+      <c r="L327" s="1" t="n">
         <v>0.04047</v>
       </c>
     </row>
@@ -12582,10 +13566,13 @@
         <v>0.053664</v>
       </c>
       <c r="J328" s="1" t="n">
+        <v>0.053612</v>
+      </c>
+      <c r="K328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="K328" s="1" t="n">
-        <v>0.053664</v>
+      <c r="L328" s="1" t="n">
+        <v>0.053612</v>
       </c>
     </row>
     <row r="329">
@@ -12619,9 +13606,12 @@
         <v>0.2787</v>
       </c>
       <c r="J329" s="1" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="K329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="K329" s="1" t="n">
+      <c r="L329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -12656,10 +13646,13 @@
         <v>0.159</v>
       </c>
       <c r="J330" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="K330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="K330" s="1" t="n">
-        <v>0.159</v>
+      <c r="L330" s="1" t="n">
+        <v>0.1587</v>
       </c>
     </row>
     <row r="331">
@@ -12696,6 +13689,9 @@
         <v>0.05364</v>
       </c>
       <c r="K331" s="1" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="L331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -12730,9 +13726,12 @@
         <v>0.3618</v>
       </c>
       <c r="J332" s="1" t="n">
-        <v>0.3618</v>
+        <v>0.3624</v>
       </c>
       <c r="K332" s="1" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="L332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -12767,9 +13766,12 @@
         <v>0.03041</v>
       </c>
       <c r="J333" s="1" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="K333" s="1" t="n">
         <v>0.03049</v>
       </c>
-      <c r="K333" s="1" t="n">
+      <c r="L333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -12804,9 +13806,12 @@
         <v>0.01868</v>
       </c>
       <c r="J334" s="1" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="K334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="K334" s="1" t="n">
+      <c r="L334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -12841,9 +13846,12 @@
         <v>0.0583</v>
       </c>
       <c r="J335" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="K335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="K335" s="1" t="n">
+      <c r="L335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -12878,9 +13886,12 @@
         <v>0.09181</v>
       </c>
       <c r="J336" s="1" t="n">
-        <v>0.09182</v>
+        <v>0.09197</v>
       </c>
       <c r="K336" s="1" t="n">
+        <v>0.09197</v>
+      </c>
+      <c r="L336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -12915,9 +13926,12 @@
         <v>0.18085</v>
       </c>
       <c r="J337" s="1" t="n">
+        <v>0.17837</v>
+      </c>
+      <c r="K337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="K337" s="1" t="n">
+      <c r="L337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -12952,10 +13966,13 @@
         <v>0.02107</v>
       </c>
       <c r="J338" s="1" t="n">
+        <v>0.02096</v>
+      </c>
+      <c r="K338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="K338" s="1" t="n">
-        <v>0.02106</v>
+      <c r="L338" s="1" t="n">
+        <v>0.02096</v>
       </c>
     </row>
     <row r="339">
@@ -12989,9 +14006,12 @@
         <v>0.1311</v>
       </c>
       <c r="J339" s="1" t="n">
-        <v>0.1315</v>
+        <v>0.1318</v>
       </c>
       <c r="K339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="L339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -13026,10 +14046,13 @@
         <v>0.007989</v>
       </c>
       <c r="J340" s="1" t="n">
+        <v>0.007929</v>
+      </c>
+      <c r="K340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="K340" s="1" t="n">
-        <v>0.007946</v>
+      <c r="L340" s="1" t="n">
+        <v>0.007929</v>
       </c>
     </row>
     <row r="341">
@@ -13063,9 +14086,12 @@
         <v>4.396</v>
       </c>
       <c r="J341" s="1" t="n">
+        <v>4.387</v>
+      </c>
+      <c r="K341" s="1" t="n">
         <v>4.407</v>
       </c>
-      <c r="K341" s="1" t="n">
+      <c r="L341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -13100,10 +14126,13 @@
         <v>0.19333</v>
       </c>
       <c r="J342" s="1" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="K342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="K342" s="1" t="n">
-        <v>0.19148</v>
+      <c r="L342" s="1" t="n">
+        <v>0.1889</v>
       </c>
     </row>
     <row r="343">
@@ -13137,9 +14166,12 @@
         <v>0.08334</v>
       </c>
       <c r="J343" s="1" t="n">
-        <v>0.08334</v>
+        <v>0.08366</v>
       </c>
       <c r="K343" s="1" t="n">
+        <v>0.08366</v>
+      </c>
+      <c r="L343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -13174,9 +14206,12 @@
         <v>0.1821</v>
       </c>
       <c r="J344" s="1" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="K344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="K344" s="1" t="n">
+      <c r="L344" s="1" t="n">
         <v>0.1821</v>
       </c>
     </row>
@@ -13211,9 +14246,12 @@
         <v>0.003253</v>
       </c>
       <c r="J345" s="1" t="n">
+        <v>0.003249</v>
+      </c>
+      <c r="K345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="K345" s="1" t="n">
+      <c r="L345" s="1" t="n">
         <v>0.003245</v>
       </c>
     </row>
@@ -13248,9 +14286,12 @@
         <v>0.09209000000000001</v>
       </c>
       <c r="J346" s="1" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="K346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="K346" s="1" t="n">
+      <c r="L346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -13285,10 +14326,13 @@
         <v>2.247</v>
       </c>
       <c r="J347" s="1" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="K347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="K347" s="1" t="n">
-        <v>2.247</v>
+      <c r="L347" s="1" t="n">
+        <v>2.244</v>
       </c>
     </row>
     <row r="348">
@@ -13322,9 +14366,12 @@
         <v>0.3061</v>
       </c>
       <c r="J348" s="1" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="K348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="K348" s="1" t="n">
+      <c r="L348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -13359,10 +14406,13 @@
         <v>0.02981</v>
       </c>
       <c r="J349" s="1" t="n">
+        <v>0.02975</v>
+      </c>
+      <c r="K349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="K349" s="1" t="n">
-        <v>0.02981</v>
+      <c r="L349" s="1" t="n">
+        <v>0.02975</v>
       </c>
     </row>
     <row r="350">
@@ -13396,9 +14446,12 @@
         <v>0.1275</v>
       </c>
       <c r="J350" s="1" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="K350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="K350" s="1" t="n">
+      <c r="L350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -13433,9 +14486,12 @@
         <v>0.06709</v>
       </c>
       <c r="J351" s="1" t="n">
+        <v>0.06707</v>
+      </c>
+      <c r="K351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="K351" s="1" t="n">
+      <c r="L351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -13470,9 +14526,12 @@
         <v>0.06242</v>
       </c>
       <c r="J352" s="1" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="K352" s="1" t="n">
         <v>0.06251</v>
       </c>
-      <c r="K352" s="1" t="n">
+      <c r="L352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -13507,9 +14566,12 @@
         <v>0.06358999999999999</v>
       </c>
       <c r="J353" s="1" t="n">
+        <v>0.06362</v>
+      </c>
+      <c r="K353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="K353" s="1" t="n">
+      <c r="L353" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -13544,9 +14606,12 @@
         <v>0.10487</v>
       </c>
       <c r="J354" s="1" t="n">
+        <v>0.10547</v>
+      </c>
+      <c r="K354" s="1" t="n">
         <v>0.10603</v>
       </c>
-      <c r="K354" s="1" t="n">
+      <c r="L354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -13581,9 +14646,12 @@
         <v>0.0901</v>
       </c>
       <c r="J355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="K355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="K355" s="1" t="n">
+      <c r="L355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -13618,9 +14686,12 @@
         <v>0.07033</v>
       </c>
       <c r="J356" s="1" t="n">
-        <v>0.07054000000000001</v>
+        <v>0.07055</v>
       </c>
       <c r="K356" s="1" t="n">
+        <v>0.07055</v>
+      </c>
+      <c r="L356" s="1" t="n">
         <v>0.06985</v>
       </c>
     </row>
@@ -13655,9 +14726,12 @@
         <v>0.4521</v>
       </c>
       <c r="J357" s="1" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="K357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="K357" s="1" t="n">
+      <c r="L357" s="1" t="n">
         <v>0.4521</v>
       </c>
     </row>
@@ -13692,9 +14766,12 @@
         <v>0.03494</v>
       </c>
       <c r="J358" s="1" t="n">
+        <v>0.03519</v>
+      </c>
+      <c r="K358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="K358" s="1" t="n">
+      <c r="L358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -13729,9 +14806,12 @@
         <v>0.01477</v>
       </c>
       <c r="J359" s="1" t="n">
-        <v>0.01482</v>
+        <v>0.01483</v>
       </c>
       <c r="K359" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="L359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -13766,9 +14846,12 @@
         <v>0.13379</v>
       </c>
       <c r="J360" s="1" t="n">
+        <v>0.13351</v>
+      </c>
+      <c r="K360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="K360" s="1" t="n">
+      <c r="L360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -13803,9 +14886,12 @@
         <v>0.0005897</v>
       </c>
       <c r="J361" s="1" t="n">
+        <v>0.0005886</v>
+      </c>
+      <c r="K361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="K361" s="1" t="n">
+      <c r="L361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -13840,9 +14926,12 @@
         <v>0.03873</v>
       </c>
       <c r="J362" s="1" t="n">
+        <v>0.03879</v>
+      </c>
+      <c r="K362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="K362" s="1" t="n">
+      <c r="L362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -13877,9 +14966,12 @@
         <v>3.208</v>
       </c>
       <c r="J363" s="1" t="n">
+        <v>3.213</v>
+      </c>
+      <c r="K363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="K363" s="1" t="n">
+      <c r="L363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -13914,10 +15006,13 @@
         <v>0.1655</v>
       </c>
       <c r="J364" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="K364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="K364" s="1" t="n">
-        <v>0.1655</v>
+      <c r="L364" s="1" t="n">
+        <v>0.1652</v>
       </c>
     </row>
     <row r="365">
@@ -13951,9 +15046,12 @@
         <v>0.1134</v>
       </c>
       <c r="J365" s="1" t="n">
-        <v>0.1136</v>
+        <v>0.1137</v>
       </c>
       <c r="K365" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="L365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -13988,10 +15086,13 @@
         <v>0.0006436</v>
       </c>
       <c r="J366" s="1" t="n">
+        <v>0.0006409</v>
+      </c>
+      <c r="K366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="K366" s="1" t="n">
-        <v>0.0006419</v>
+      <c r="L366" s="1" t="n">
+        <v>0.0006409</v>
       </c>
     </row>
     <row r="367">
@@ -14025,9 +15126,12 @@
         <v>0.05934</v>
       </c>
       <c r="J367" s="1" t="n">
+        <v>0.05951</v>
+      </c>
+      <c r="K367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="K367" s="1" t="n">
+      <c r="L367" s="1" t="n">
         <v>0.05927</v>
       </c>
     </row>
@@ -14062,10 +15166,13 @@
         <v>0.08322</v>
       </c>
       <c r="J368" s="1" t="n">
+        <v>0.08234</v>
+      </c>
+      <c r="K368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="K368" s="1" t="n">
-        <v>0.0825</v>
+      <c r="L368" s="1" t="n">
+        <v>0.08234</v>
       </c>
     </row>
     <row r="369">
@@ -14099,9 +15206,12 @@
         <v>0.04038</v>
       </c>
       <c r="J369" s="1" t="n">
-        <v>0.04038</v>
+        <v>0.0412</v>
       </c>
       <c r="K369" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="L369" s="1" t="n">
         <v>0.03976</v>
       </c>
     </row>
@@ -14136,10 +15246,13 @@
         <v>3.712</v>
       </c>
       <c r="J370" s="1" t="n">
+        <v>3.703</v>
+      </c>
+      <c r="K370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="K370" s="1" t="n">
-        <v>3.709</v>
+      <c r="L370" s="1" t="n">
+        <v>3.703</v>
       </c>
     </row>
     <row r="371">
@@ -14173,9 +15286,12 @@
         <v>0.1223</v>
       </c>
       <c r="J371" s="1" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="K371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="K371" s="1" t="n">
+      <c r="L371" s="1" t="n">
         <v>0.1216</v>
       </c>
     </row>
@@ -14210,9 +15326,12 @@
         <v>0.01475</v>
       </c>
       <c r="J372" s="1" t="n">
-        <v>0.01479</v>
+        <v>0.01481</v>
       </c>
       <c r="K372" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="L372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -14247,9 +15366,12 @@
         <v>0.02195</v>
       </c>
       <c r="J373" s="1" t="n">
+        <v>0.02196</v>
+      </c>
+      <c r="K373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="K373" s="1" t="n">
+      <c r="L373" s="1" t="n">
         <v>0.02192</v>
       </c>
     </row>
@@ -14284,9 +15406,12 @@
         <v>1.863</v>
       </c>
       <c r="J374" s="1" t="n">
-        <v>1.863</v>
+        <v>1.8633</v>
       </c>
       <c r="K374" s="1" t="n">
+        <v>1.8633</v>
+      </c>
+      <c r="L374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -14321,9 +15446,12 @@
         <v>0.02108</v>
       </c>
       <c r="J375" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="K375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="K375" s="1" t="n">
+      <c r="L375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -14358,9 +15486,12 @@
         <v>1.317</v>
       </c>
       <c r="J376" s="1" t="n">
-        <v>1.317</v>
+        <v>1.326</v>
       </c>
       <c r="K376" s="1" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="L376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -14395,9 +15526,12 @@
         <v>0.2829</v>
       </c>
       <c r="J377" s="1" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="K377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="K377" s="1" t="n">
+      <c r="L377" s="1" t="n">
         <v>0.2829</v>
       </c>
     </row>
@@ -14432,9 +15566,12 @@
         <v>0.01549</v>
       </c>
       <c r="J378" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="K378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="K378" s="1" t="n">
+      <c r="L378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -14469,9 +15606,12 @@
         <v>1.5305</v>
       </c>
       <c r="J379" s="1" t="n">
+        <v>1.5361</v>
+      </c>
+      <c r="K379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="K379" s="1" t="n">
+      <c r="L379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -14506,10 +15646,13 @@
         <v>6.939e-05</v>
       </c>
       <c r="J380" s="1" t="n">
+        <v>6.923999999999999e-05</v>
+      </c>
+      <c r="K380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="K380" s="1" t="n">
-        <v>6.939e-05</v>
+      <c r="L380" s="1" t="n">
+        <v>6.923999999999999e-05</v>
       </c>
     </row>
     <row r="381">
@@ -14543,9 +15686,12 @@
         <v>2.545</v>
       </c>
       <c r="J381" s="1" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="K381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="K381" s="1" t="n">
+      <c r="L381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -14580,10 +15726,13 @@
         <v>0.06745</v>
       </c>
       <c r="J382" s="1" t="n">
+        <v>0.06736</v>
+      </c>
+      <c r="K382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="K382" s="1" t="n">
-        <v>0.06738</v>
+      <c r="L382" s="1" t="n">
+        <v>0.06736</v>
       </c>
     </row>
     <row r="383">
@@ -14617,9 +15766,12 @@
         <v>0.01734</v>
       </c>
       <c r="J383" s="1" t="n">
-        <v>0.01758</v>
+        <v>0.01985</v>
       </c>
       <c r="K383" s="1" t="n">
+        <v>0.01985</v>
+      </c>
+      <c r="L383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -14654,9 +15806,12 @@
         <v>0.05176</v>
       </c>
       <c r="J384" s="1" t="n">
-        <v>0.05176</v>
+        <v>0.05334</v>
       </c>
       <c r="K384" s="1" t="n">
+        <v>0.05334</v>
+      </c>
+      <c r="L384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -14691,9 +15846,12 @@
         <v>7.583</v>
       </c>
       <c r="J385" s="1" t="n">
-        <v>7.585</v>
+        <v>7.591</v>
       </c>
       <c r="K385" s="1" t="n">
+        <v>7.591</v>
+      </c>
+      <c r="L385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -14728,9 +15886,12 @@
         <v>0.003301</v>
       </c>
       <c r="J386" s="1" t="n">
+        <v>0.003299</v>
+      </c>
+      <c r="K386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="K386" s="1" t="n">
+      <c r="L386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -14765,10 +15926,13 @@
         <v>0.000383</v>
       </c>
       <c r="J387" s="1" t="n">
+        <v>0.000382</v>
+      </c>
+      <c r="K387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="K387" s="1" t="n">
-        <v>0.000383</v>
+      <c r="L387" s="1" t="n">
+        <v>0.000382</v>
       </c>
     </row>
     <row r="388">
@@ -14802,9 +15966,12 @@
         <v>0.00962</v>
       </c>
       <c r="J388" s="1" t="n">
+        <v>0.009650000000000001</v>
+      </c>
+      <c r="K388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="K388" s="1" t="n">
+      <c r="L388" s="1" t="n">
         <v>0.00962</v>
       </c>
     </row>
@@ -14839,9 +16006,12 @@
         <v>0.2902</v>
       </c>
       <c r="J389" s="1" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="K389" s="1" t="n">
         <v>0.2902</v>
       </c>
-      <c r="K389" s="1" t="n">
+      <c r="L389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -14879,6 +16049,9 @@
         <v>0.025</v>
       </c>
       <c r="K390" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="L390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -14913,9 +16086,12 @@
         <v>2.823</v>
       </c>
       <c r="J391" s="1" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="K391" s="1" t="n">
         <v>2.833</v>
       </c>
-      <c r="K391" s="1" t="n">
+      <c r="L391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -14950,9 +16126,12 @@
         <v>0.01338</v>
       </c>
       <c r="J392" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="K392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="K392" s="1" t="n">
+      <c r="L392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -14990,6 +16169,9 @@
         <v>0.00236</v>
       </c>
       <c r="K393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="L393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -15024,9 +16206,12 @@
         <v>0.05944</v>
       </c>
       <c r="J394" s="1" t="n">
+        <v>0.05936</v>
+      </c>
+      <c r="K394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="K394" s="1" t="n">
+      <c r="L394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -15061,9 +16246,12 @@
         <v>0.0402</v>
       </c>
       <c r="J395" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="K395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="K395" s="1" t="n">
+      <c r="L395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -15098,9 +16286,12 @@
         <v>0.09211999999999999</v>
       </c>
       <c r="J396" s="1" t="n">
-        <v>0.09217</v>
+        <v>0.09272</v>
       </c>
       <c r="K396" s="1" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="L396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -15135,9 +16326,12 @@
         <v>0.1518</v>
       </c>
       <c r="J397" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="K397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="K397" s="1" t="n">
+      <c r="L397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -15172,9 +16366,12 @@
         <v>0.928</v>
       </c>
       <c r="J398" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="K398" s="1" t="n">
         <v>0.929</v>
       </c>
-      <c r="K398" s="1" t="n">
+      <c r="L398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -15209,9 +16406,12 @@
         <v>0.05254</v>
       </c>
       <c r="J399" s="1" t="n">
+        <v>0.05244</v>
+      </c>
+      <c r="K399" s="1" t="n">
         <v>0.05254</v>
       </c>
-      <c r="K399" s="1" t="n">
+      <c r="L399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -15246,9 +16446,12 @@
         <v>2.519</v>
       </c>
       <c r="J400" s="1" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="K400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="K400" s="1" t="n">
+      <c r="L400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -15283,9 +16486,12 @@
         <v>0.0179</v>
       </c>
       <c r="J401" s="1" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="K401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="K401" s="1" t="n">
+      <c r="L401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -15320,9 +16526,12 @@
         <v>0.0808</v>
       </c>
       <c r="J402" s="1" t="n">
+        <v>0.08067000000000001</v>
+      </c>
+      <c r="K402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="K402" s="1" t="n">
+      <c r="L402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -15357,10 +16566,13 @@
         <v>1.2474</v>
       </c>
       <c r="J403" s="1" t="n">
+        <v>1.2456</v>
+      </c>
+      <c r="K403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="K403" s="1" t="n">
-        <v>1.2471</v>
+      <c r="L403" s="1" t="n">
+        <v>1.2456</v>
       </c>
     </row>
     <row r="404">
@@ -15394,9 +16606,12 @@
         <v>0.00717</v>
       </c>
       <c r="J404" s="1" t="n">
+        <v>0.00717</v>
+      </c>
+      <c r="K404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="K404" s="1" t="n">
+      <c r="L404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -15431,9 +16646,12 @@
         <v>0.4952</v>
       </c>
       <c r="J405" s="1" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="K405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="K405" s="1" t="n">
+      <c r="L405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -15468,9 +16686,12 @@
         <v>0.01153</v>
       </c>
       <c r="J406" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="K406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="K406" s="1" t="n">
+      <c r="L406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -15505,10 +16726,13 @@
         <v>0.04624</v>
       </c>
       <c r="J407" s="1" t="n">
+        <v>0.04614</v>
+      </c>
+      <c r="K407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="K407" s="1" t="n">
-        <v>0.04624</v>
+      <c r="L407" s="1" t="n">
+        <v>0.04614</v>
       </c>
     </row>
     <row r="408">
@@ -15542,10 +16766,13 @@
         <v>0.03953</v>
       </c>
       <c r="J408" s="1" t="n">
+        <v>0.03943</v>
+      </c>
+      <c r="K408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="K408" s="1" t="n">
-        <v>0.03947</v>
+      <c r="L408" s="1" t="n">
+        <v>0.03943</v>
       </c>
     </row>
     <row r="409">
@@ -15579,10 +16806,13 @@
         <v>0.05247</v>
       </c>
       <c r="J409" s="1" t="n">
+        <v>0.05234</v>
+      </c>
+      <c r="K409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="K409" s="1" t="n">
-        <v>0.05247</v>
+      <c r="L409" s="1" t="n">
+        <v>0.05234</v>
       </c>
     </row>
     <row r="410">
@@ -15616,9 +16846,12 @@
         <v>0.01253</v>
       </c>
       <c r="J410" s="1" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="K410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="K410" s="1" t="n">
+      <c r="L410" s="1" t="n">
         <v>0.01245</v>
       </c>
     </row>
@@ -15653,9 +16886,12 @@
         <v>0.06347</v>
       </c>
       <c r="J411" s="1" t="n">
+        <v>0.06365</v>
+      </c>
+      <c r="K411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="K411" s="1" t="n">
+      <c r="L411" s="1" t="n">
         <v>0.06347</v>
       </c>
     </row>
@@ -15690,9 +16926,12 @@
         <v>0.0414</v>
       </c>
       <c r="J412" s="1" t="n">
+        <v>0.04135</v>
+      </c>
+      <c r="K412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="K412" s="1" t="n">
+      <c r="L412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -15727,9 +16966,12 @@
         <v>1.122</v>
       </c>
       <c r="J413" s="1" t="n">
-        <v>1.122</v>
+        <v>1.124</v>
       </c>
       <c r="K413" s="1" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="L413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -15764,10 +17006,13 @@
         <v>0.2631</v>
       </c>
       <c r="J414" s="1" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="K414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="K414" s="1" t="n">
-        <v>0.2631</v>
+      <c r="L414" s="1" t="n">
+        <v>0.2626</v>
       </c>
     </row>
     <row r="415">
@@ -15801,9 +17046,12 @@
         <v>0.001223</v>
       </c>
       <c r="J415" s="1" t="n">
+        <v>0.001227</v>
+      </c>
+      <c r="K415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="K415" s="1" t="n">
+      <c r="L415" s="1" t="n">
         <v>0.001221</v>
       </c>
     </row>
@@ -15838,9 +17086,12 @@
         <v>0.03207</v>
       </c>
       <c r="J416" s="1" t="n">
+        <v>0.03205</v>
+      </c>
+      <c r="K416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="K416" s="1" t="n">
+      <c r="L416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -15875,9 +17126,12 @@
         <v>0.01462</v>
       </c>
       <c r="J417" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="K417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="K417" s="1" t="n">
+      <c r="L417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -15912,9 +17166,12 @@
         <v>0.1482</v>
       </c>
       <c r="J418" s="1" t="n">
-        <v>0.1484</v>
+        <v>0.1486</v>
       </c>
       <c r="K418" s="1" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="L418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -15949,9 +17206,12 @@
         <v>0.04943</v>
       </c>
       <c r="J419" s="1" t="n">
+        <v>0.04926</v>
+      </c>
+      <c r="K419" s="1" t="n">
         <v>0.04943</v>
       </c>
-      <c r="K419" s="1" t="n">
+      <c r="L419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -15986,9 +17246,12 @@
         <v>66.3</v>
       </c>
       <c r="J420" s="1" t="n">
+        <v>66.56</v>
+      </c>
+      <c r="K420" s="1" t="n">
         <v>66.7</v>
       </c>
-      <c r="K420" s="1" t="n">
+      <c r="L420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -16023,9 +17286,12 @@
         <v>0.876</v>
       </c>
       <c r="J421" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="K421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="K421" s="1" t="n">
+      <c r="L421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -16060,10 +17326,13 @@
         <v>0.012681</v>
       </c>
       <c r="J422" s="1" t="n">
+        <v>0.012645</v>
+      </c>
+      <c r="K422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="K422" s="1" t="n">
-        <v>0.012681</v>
+      <c r="L422" s="1" t="n">
+        <v>0.012645</v>
       </c>
     </row>
     <row r="423">
@@ -16097,9 +17366,12 @@
         <v>0.01596</v>
       </c>
       <c r="J423" s="1" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="K423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="K423" s="1" t="n">
+      <c r="L423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -16134,9 +17406,12 @@
         <v>0.26794</v>
       </c>
       <c r="J424" s="1" t="n">
-        <v>0.27001</v>
+        <v>0.27049</v>
       </c>
       <c r="K424" s="1" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="L424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -16171,9 +17446,12 @@
         <v>0.6007</v>
       </c>
       <c r="J425" s="1" t="n">
+        <v>0.5999</v>
+      </c>
+      <c r="K425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="K425" s="1" t="n">
+      <c r="L425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -16208,9 +17486,12 @@
         <v>0.00559</v>
       </c>
       <c r="J426" s="1" t="n">
+        <v>0.005595</v>
+      </c>
+      <c r="K426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="K426" s="1" t="n">
+      <c r="L426" s="1" t="n">
         <v>0.005557</v>
       </c>
     </row>
@@ -16245,9 +17526,12 @@
         <v>0.04906</v>
       </c>
       <c r="J427" s="1" t="n">
+        <v>0.04911</v>
+      </c>
+      <c r="K427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="K427" s="1" t="n">
+      <c r="L427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -16285,6 +17569,9 @@
         <v>0.1266</v>
       </c>
       <c r="K428" s="1" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="L428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -16319,9 +17606,12 @@
         <v>0.003165</v>
       </c>
       <c r="J429" s="1" t="n">
+        <v>0.003191</v>
+      </c>
+      <c r="K429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="K429" s="1" t="n">
+      <c r="L429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -16356,9 +17646,12 @@
         <v>0.03641</v>
       </c>
       <c r="J430" s="1" t="n">
+        <v>0.03652</v>
+      </c>
+      <c r="K430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="K430" s="1" t="n">
+      <c r="L430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -16393,9 +17686,12 @@
         <v>0.3982</v>
       </c>
       <c r="J431" s="1" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="K431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="K431" s="1" t="n">
+      <c r="L431" s="1" t="n">
         <v>0.3982</v>
       </c>
     </row>
@@ -16430,10 +17726,13 @@
         <v>0.00452</v>
       </c>
       <c r="J432" s="1" t="n">
+        <v>0.004512</v>
+      </c>
+      <c r="K432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="K432" s="1" t="n">
-        <v>0.004518</v>
+      <c r="L432" s="1" t="n">
+        <v>0.004512</v>
       </c>
     </row>
     <row r="433">
@@ -16467,9 +17766,12 @@
         <v>0.0978</v>
       </c>
       <c r="J433" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="K433" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="K433" s="1" t="n">
+      <c r="L433" s="1" t="n">
         <v>0.0978</v>
       </c>
     </row>
@@ -16504,9 +17806,12 @@
         <v>0.01247</v>
       </c>
       <c r="J434" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="K434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="K434" s="1" t="n">
+      <c r="L434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -16541,9 +17846,12 @@
         <v>1.988</v>
       </c>
       <c r="J435" s="1" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="K435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="K435" s="1" t="n">
+      <c r="L435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -16578,10 +17886,13 @@
         <v>0.001852</v>
       </c>
       <c r="J436" s="1" t="n">
+        <v>0.001813</v>
+      </c>
+      <c r="K436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="K436" s="1" t="n">
-        <v>0.001833</v>
+      <c r="L436" s="1" t="n">
+        <v>0.001813</v>
       </c>
     </row>
     <row r="437">
@@ -16615,10 +17926,13 @@
         <v>0.4415</v>
       </c>
       <c r="J437" s="1" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="K437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="K437" s="1" t="n">
-        <v>0.4415</v>
+      <c r="L437" s="1" t="n">
+        <v>0.4413</v>
       </c>
     </row>
     <row r="438">
@@ -16652,9 +17966,12 @@
         <v>0.00535</v>
       </c>
       <c r="J438" s="1" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="K438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="K438" s="1" t="n">
+      <c r="L438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -16689,9 +18006,12 @@
         <v>0.1035</v>
       </c>
       <c r="J439" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="K439" s="1" t="n">
         <v>0.1036</v>
       </c>
-      <c r="K439" s="1" t="n">
+      <c r="L439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -16726,9 +18046,12 @@
         <v>0.03445</v>
       </c>
       <c r="J440" s="1" t="n">
-        <v>0.03445</v>
+        <v>0.03457</v>
       </c>
       <c r="K440" s="1" t="n">
+        <v>0.03457</v>
+      </c>
+      <c r="L440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -16763,9 +18086,12 @@
         <v>0.08205</v>
       </c>
       <c r="J441" s="1" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="K441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="K441" s="1" t="n">
+      <c r="L441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -16800,10 +18126,13 @@
         <v>1.304</v>
       </c>
       <c r="J442" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="K442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="K442" s="1" t="n">
-        <v>1.304</v>
+      <c r="L442" s="1" t="n">
+        <v>1.303</v>
       </c>
     </row>
     <row r="443">
@@ -16837,9 +18166,12 @@
         <v>0.07581</v>
       </c>
       <c r="J443" s="1" t="n">
+        <v>0.07575999999999999</v>
+      </c>
+      <c r="K443" s="1" t="n">
         <v>0.07581</v>
       </c>
-      <c r="K443" s="1" t="n">
+      <c r="L443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -16874,9 +18206,12 @@
         <v>0.07701</v>
       </c>
       <c r="J444" s="1" t="n">
+        <v>0.07693</v>
+      </c>
+      <c r="K444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="K444" s="1" t="n">
+      <c r="L444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -16911,9 +18246,12 @@
         <v>0.0437</v>
       </c>
       <c r="J445" s="1" t="n">
-        <v>0.04386</v>
+        <v>0.04388</v>
       </c>
       <c r="K445" s="1" t="n">
+        <v>0.04388</v>
+      </c>
+      <c r="L445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -16948,9 +18286,12 @@
         <v>0.02146</v>
       </c>
       <c r="J446" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="K446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="K446" s="1" t="n">
+      <c r="L446" s="1" t="n">
         <v>0.02144</v>
       </c>
     </row>
@@ -16985,9 +18326,12 @@
         <v>0.2816</v>
       </c>
       <c r="J447" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="K447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="K447" s="1" t="n">
+      <c r="L447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -17022,9 +18366,12 @@
         <v>0.031</v>
       </c>
       <c r="J448" s="1" t="n">
+        <v>0.03101</v>
+      </c>
+      <c r="K448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="K448" s="1" t="n">
+      <c r="L448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -17059,9 +18406,12 @@
         <v>0.00644</v>
       </c>
       <c r="J449" s="1" t="n">
+        <v>0.00644</v>
+      </c>
+      <c r="K449" s="1" t="n">
         <v>0.00646</v>
       </c>
-      <c r="K449" s="1" t="n">
+      <c r="L449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -17096,9 +18446,12 @@
         <v>0.023016</v>
       </c>
       <c r="J450" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="K450" s="1" t="n">
         <v>0.023016</v>
       </c>
-      <c r="K450" s="1" t="n">
+      <c r="L450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -17133,9 +18486,12 @@
         <v>0.04239</v>
       </c>
       <c r="J451" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="K451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="K451" s="1" t="n">
+      <c r="L451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -17170,9 +18526,12 @@
         <v>0.07205</v>
       </c>
       <c r="J452" s="1" t="n">
+        <v>0.07238</v>
+      </c>
+      <c r="K452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="K452" s="1" t="n">
+      <c r="L452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -17207,9 +18566,12 @@
         <v>0.0005943</v>
       </c>
       <c r="J453" s="1" t="n">
-        <v>0.0005943</v>
+        <v>0.000595</v>
       </c>
       <c r="K453" s="1" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="L453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -17244,9 +18606,12 @@
         <v>0.308</v>
       </c>
       <c r="J454" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="K454" s="1" t="n">
+      <c r="L454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -17281,9 +18646,12 @@
         <v>0.004299</v>
       </c>
       <c r="J455" s="1" t="n">
-        <v>0.004299</v>
+        <v>0.004324</v>
       </c>
       <c r="K455" s="1" t="n">
+        <v>0.004324</v>
+      </c>
+      <c r="L455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -17318,10 +18686,13 @@
         <v>0.1835</v>
       </c>
       <c r="J456" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="K456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="K456" s="1" t="n">
-        <v>0.1833</v>
+      <c r="L456" s="1" t="n">
+        <v>0.183</v>
       </c>
     </row>
     <row r="457">
@@ -17355,9 +18726,12 @@
         <v>0.04274</v>
       </c>
       <c r="J457" s="1" t="n">
+        <v>0.04276</v>
+      </c>
+      <c r="K457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="K457" s="1" t="n">
+      <c r="L457" s="1" t="n">
         <v>0.04274</v>
       </c>
     </row>
@@ -17392,9 +18766,12 @@
         <v>0.146</v>
       </c>
       <c r="J458" s="1" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="K458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="K458" s="1" t="n">
+      <c r="L458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -17429,9 +18806,12 @@
         <v>0.008621</v>
       </c>
       <c r="J459" s="1" t="n">
-        <v>0.008621</v>
+        <v>0.008624</v>
       </c>
       <c r="K459" s="1" t="n">
+        <v>0.008624</v>
+      </c>
+      <c r="L459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -17466,10 +18846,13 @@
         <v>0.007431</v>
       </c>
       <c r="J460" s="1" t="n">
+        <v>0.007414</v>
+      </c>
+      <c r="K460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="K460" s="1" t="n">
-        <v>0.007423</v>
+      <c r="L460" s="1" t="n">
+        <v>0.007414</v>
       </c>
     </row>
     <row r="461">
@@ -17503,9 +18886,12 @@
         <v>0.0001731</v>
       </c>
       <c r="J461" s="1" t="n">
+        <v>0.0001727</v>
+      </c>
+      <c r="K461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="K461" s="1" t="n">
+      <c r="L461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -17540,9 +18926,12 @@
         <v>0.0227</v>
       </c>
       <c r="J462" s="1" t="n">
-        <v>0.0227</v>
+        <v>0.0228</v>
       </c>
       <c r="K462" s="1" t="n">
+        <v>0.0228</v>
+      </c>
+      <c r="L462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -17577,10 +18966,13 @@
         <v>0.0378</v>
       </c>
       <c r="J463" s="1" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="K463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="K463" s="1" t="n">
-        <v>0.0374</v>
+      <c r="L463" s="1" t="n">
+        <v>0.03718</v>
       </c>
     </row>
     <row r="464">
@@ -17614,10 +19006,13 @@
         <v>0.3035</v>
       </c>
       <c r="J464" s="1" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="K464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="K464" s="1" t="n">
-        <v>0.3031</v>
+      <c r="L464" s="1" t="n">
+        <v>0.3025</v>
       </c>
     </row>
     <row r="465">
@@ -17651,9 +19046,12 @@
         <v>0.03926</v>
       </c>
       <c r="J465" s="1" t="n">
-        <v>0.03926</v>
+        <v>0.03937</v>
       </c>
       <c r="K465" s="1" t="n">
+        <v>0.03937</v>
+      </c>
+      <c r="L465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -17688,10 +19086,13 @@
         <v>2.669</v>
       </c>
       <c r="J466" s="1" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="K466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="K466" s="1" t="n">
-        <v>2.669</v>
+      <c r="L466" s="1" t="n">
+        <v>2.667</v>
       </c>
     </row>
     <row r="467">
@@ -17725,9 +19126,12 @@
         <v>0.03436</v>
       </c>
       <c r="J467" s="1" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="K467" s="1" t="n">
         <v>0.03436</v>
       </c>
-      <c r="K467" s="1" t="n">
+      <c r="L467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -17762,9 +19166,12 @@
         <v>0.1763</v>
       </c>
       <c r="J468" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="K468" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="K468" s="1" t="n">
+      <c r="L468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -17799,9 +19206,12 @@
         <v>0.096</v>
       </c>
       <c r="J469" s="1" t="n">
-        <v>0.096</v>
+        <v>0.0963</v>
       </c>
       <c r="K469" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="L469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -17836,9 +19246,12 @@
         <v>0.06716999999999999</v>
       </c>
       <c r="J470" s="1" t="n">
+        <v>0.06751</v>
+      </c>
+      <c r="K470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="K470" s="1" t="n">
+      <c r="L470" s="1" t="n">
         <v>0.06716999999999999</v>
       </c>
     </row>
@@ -17873,9 +19286,12 @@
         <v>0.03998</v>
       </c>
       <c r="J471" s="1" t="n">
-        <v>0.04004</v>
+        <v>0.04007</v>
       </c>
       <c r="K471" s="1" t="n">
+        <v>0.04007</v>
+      </c>
+      <c r="L471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -17910,10 +19326,13 @@
         <v>0.2475</v>
       </c>
       <c r="J472" s="1" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="K472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="K472" s="1" t="n">
-        <v>0.2475</v>
+      <c r="L472" s="1" t="n">
+        <v>0.2472</v>
       </c>
     </row>
     <row r="473">
@@ -17947,10 +19366,13 @@
         <v>0.016505</v>
       </c>
       <c r="J473" s="1" t="n">
+        <v>0.016397</v>
+      </c>
+      <c r="K473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="K473" s="1" t="n">
-        <v>0.016503</v>
+      <c r="L473" s="1" t="n">
+        <v>0.016397</v>
       </c>
     </row>
     <row r="474">
@@ -17984,9 +19406,12 @@
         <v>0.1155</v>
       </c>
       <c r="J474" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="K474" s="1" t="n">
         <v>0.1157</v>
       </c>
-      <c r="K474" s="1" t="n">
+      <c r="L474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -18021,9 +19446,12 @@
         <v>0.04294</v>
       </c>
       <c r="J475" s="1" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="K475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="K475" s="1" t="n">
+      <c r="L475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -18058,9 +19486,12 @@
         <v>0.2073</v>
       </c>
       <c r="J476" s="1" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="K476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="K476" s="1" t="n">
+      <c r="L476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -18095,9 +19526,12 @@
         <v>0.006811</v>
       </c>
       <c r="J477" s="1" t="n">
-        <v>0.006833</v>
+        <v>0.006837</v>
       </c>
       <c r="K477" s="1" t="n">
+        <v>0.006837</v>
+      </c>
+      <c r="L477" s="1" t="n">
         <v>0.006796</v>
       </c>
     </row>
@@ -18132,10 +19566,13 @@
         <v>0.01791</v>
       </c>
       <c r="J478" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="K478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="K478" s="1" t="n">
-        <v>0.01791</v>
+      <c r="L478" s="1" t="n">
+        <v>0.01788</v>
       </c>
     </row>
     <row r="479">
@@ -18169,9 +19606,12 @@
         <v>0.0469</v>
       </c>
       <c r="J479" s="1" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="K479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="K479" s="1" t="n">
+      <c r="L479" s="1" t="n">
         <v>0.04683</v>
       </c>
     </row>
@@ -18206,9 +19646,12 @@
         <v>0.26131</v>
       </c>
       <c r="J480" s="1" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K480" s="1" t="n">
         <v>0.26166</v>
       </c>
-      <c r="K480" s="1" t="n">
+      <c r="L480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -18243,10 +19686,13 @@
         <v>0.01233</v>
       </c>
       <c r="J481" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="K481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="K481" s="1" t="n">
-        <v>0.01233</v>
+      <c r="L481" s="1" t="n">
+        <v>0.01229</v>
       </c>
     </row>
     <row r="482">
@@ -18280,9 +19726,12 @@
         <v>0.004105</v>
       </c>
       <c r="J482" s="1" t="n">
+        <v>0.004107</v>
+      </c>
+      <c r="K482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="K482" s="1" t="n">
+      <c r="L482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -18317,9 +19766,12 @@
         <v>0.123</v>
       </c>
       <c r="J483" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="K483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="K483" s="1" t="n">
+      <c r="L483" s="1" t="n">
         <v>0.123</v>
       </c>
     </row>
@@ -18354,9 +19806,12 @@
         <v>0.02196</v>
       </c>
       <c r="J484" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="K484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="K484" s="1" t="n">
+      <c r="L484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -18391,9 +19846,12 @@
         <v>0.04555</v>
       </c>
       <c r="J485" s="1" t="n">
+        <v>0.04558</v>
+      </c>
+      <c r="K485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="K485" s="1" t="n">
+      <c r="L485" s="1" t="n">
         <v>0.04548</v>
       </c>
     </row>
@@ -18428,10 +19886,13 @@
         <v>0.1732</v>
       </c>
       <c r="J486" s="1" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="K486" s="1" t="n">
         <v>0.1736</v>
       </c>
-      <c r="K486" s="1" t="n">
-        <v>0.1732</v>
+      <c r="L486" s="1" t="n">
+        <v>0.1731</v>
       </c>
     </row>
     <row r="487">
@@ -18465,10 +19926,13 @@
         <v>0.273</v>
       </c>
       <c r="J487" s="1" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="K487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="K487" s="1" t="n">
-        <v>0.273</v>
+      <c r="L487" s="1" t="n">
+        <v>0.2729</v>
       </c>
     </row>
     <row r="488">
@@ -18502,9 +19966,12 @@
         <v>0.04615</v>
       </c>
       <c r="J488" s="1" t="n">
+        <v>0.04618</v>
+      </c>
+      <c r="K488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="K488" s="1" t="n">
+      <c r="L488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -18539,9 +20006,12 @@
         <v>0.0002155</v>
       </c>
       <c r="J489" s="1" t="n">
+        <v>0.0002155</v>
+      </c>
+      <c r="K489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="K489" s="1" t="n">
+      <c r="L489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -18576,9 +20046,12 @@
         <v>1.769</v>
       </c>
       <c r="J490" s="1" t="n">
-        <v>1.769</v>
+        <v>1.778</v>
       </c>
       <c r="K490" s="1" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="L490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -18613,9 +20086,12 @@
         <v>16.053</v>
       </c>
       <c r="J491" s="1" t="n">
+        <v>16.068</v>
+      </c>
+      <c r="K491" s="1" t="n">
         <v>16.083</v>
       </c>
-      <c r="K491" s="1" t="n">
+      <c r="L491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -18650,9 +20126,12 @@
         <v>0.06703000000000001</v>
       </c>
       <c r="J492" s="1" t="n">
+        <v>0.06695</v>
+      </c>
+      <c r="K492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="K492" s="1" t="n">
+      <c r="L492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -18687,9 +20166,12 @@
         <v>0.06748</v>
       </c>
       <c r="J493" s="1" t="n">
+        <v>0.06741</v>
+      </c>
+      <c r="K493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="K493" s="1" t="n">
+      <c r="L493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -18724,9 +20206,12 @@
         <v>0.009468000000000001</v>
       </c>
       <c r="J494" s="1" t="n">
+        <v>0.009469</v>
+      </c>
+      <c r="K494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="K494" s="1" t="n">
+      <c r="L494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -18761,10 +20246,13 @@
         <v>0.005953</v>
       </c>
       <c r="J495" s="1" t="n">
+        <v>0.005875</v>
+      </c>
+      <c r="K495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="K495" s="1" t="n">
-        <v>0.005907</v>
+      <c r="L495" s="1" t="n">
+        <v>0.005875</v>
       </c>
     </row>
     <row r="496">
@@ -18798,10 +20286,13 @@
         <v>0.00991</v>
       </c>
       <c r="J496" s="1" t="n">
+        <v>0.00987</v>
+      </c>
+      <c r="K496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="K496" s="1" t="n">
-        <v>0.00991</v>
+      <c r="L496" s="1" t="n">
+        <v>0.00987</v>
       </c>
     </row>
     <row r="497">
@@ -18835,9 +20326,12 @@
         <v>0.04396</v>
       </c>
       <c r="J497" s="1" t="n">
-        <v>0.04404</v>
+        <v>0.04411</v>
       </c>
       <c r="K497" s="1" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="L497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -18872,10 +20366,13 @@
         <v>0.006393</v>
       </c>
       <c r="J498" s="1" t="n">
+        <v>0.006388</v>
+      </c>
+      <c r="K498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="K498" s="1" t="n">
-        <v>0.006393</v>
+      <c r="L498" s="1" t="n">
+        <v>0.006388</v>
       </c>
     </row>
     <row r="499">
@@ -18912,6 +20409,9 @@
         <v>0.01049</v>
       </c>
       <c r="K499" s="1" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="L499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -18946,9 +20446,12 @@
         <v>0.5075</v>
       </c>
       <c r="J500" s="1" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="K500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="K500" s="1" t="n">
+      <c r="L500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -18983,9 +20486,12 @@
         <v>0.03204</v>
       </c>
       <c r="J501" s="1" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="K501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="K501" s="1" t="n">
+      <c r="L501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -19020,9 +20526,12 @@
         <v>0.4371</v>
       </c>
       <c r="J502" s="1" t="n">
-        <v>0.4385</v>
+        <v>0.4397</v>
       </c>
       <c r="K502" s="1" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="L502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -19057,9 +20566,12 @@
         <v>0.999341</v>
       </c>
       <c r="J503" s="1" t="n">
+        <v>0.999342</v>
+      </c>
+      <c r="K503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="K503" s="1" t="n">
+      <c r="L503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -19094,10 +20606,13 @@
         <v>0.03526</v>
       </c>
       <c r="J504" s="1" t="n">
+        <v>0.03514</v>
+      </c>
+      <c r="K504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="K504" s="1" t="n">
-        <v>0.03525</v>
+      <c r="L504" s="1" t="n">
+        <v>0.03514</v>
       </c>
     </row>
     <row r="505">
@@ -19131,9 +20646,12 @@
         <v>0.004925</v>
       </c>
       <c r="J505" s="1" t="n">
+        <v>0.004949</v>
+      </c>
+      <c r="K505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="K505" s="1" t="n">
+      <c r="L505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -19168,9 +20686,12 @@
         <v>0.01392</v>
       </c>
       <c r="J506" s="1" t="n">
+        <v>0.01395</v>
+      </c>
+      <c r="K506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="K506" s="1" t="n">
+      <c r="L506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -19205,9 +20726,12 @@
         <v>0.003516</v>
       </c>
       <c r="J507" s="1" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="K507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="K507" s="1" t="n">
+      <c r="L507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -19242,9 +20766,12 @@
         <v>1.418</v>
       </c>
       <c r="J508" s="1" t="n">
+        <v>1.419</v>
+      </c>
+      <c r="K508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="K508" s="1" t="n">
+      <c r="L508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -19279,9 +20806,12 @@
         <v>0.005086</v>
       </c>
       <c r="J509" s="1" t="n">
+        <v>0.005076</v>
+      </c>
+      <c r="K509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="K509" s="1" t="n">
+      <c r="L509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -19316,9 +20846,12 @@
         <v>0.01575</v>
       </c>
       <c r="J510" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="K510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="K510" s="1" t="n">
+      <c r="L510" s="1" t="n">
         <v>0.01572</v>
       </c>
     </row>
@@ -19353,9 +20886,12 @@
         <v>0.08223999999999999</v>
       </c>
       <c r="J511" s="1" t="n">
+        <v>0.08251</v>
+      </c>
+      <c r="K511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="K511" s="1" t="n">
+      <c r="L511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -19390,10 +20926,13 @@
         <v>0.007099</v>
       </c>
       <c r="J512" s="1" t="n">
+        <v>0.007093</v>
+      </c>
+      <c r="K512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="K512" s="1" t="n">
-        <v>0.007099</v>
+      <c r="L512" s="1" t="n">
+        <v>0.007093</v>
       </c>
     </row>
     <row r="513">
@@ -19427,9 +20966,12 @@
         <v>0.01485</v>
       </c>
       <c r="J513" s="1" t="n">
-        <v>0.01485</v>
+        <v>0.01493</v>
       </c>
       <c r="K513" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="L513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -19464,9 +21006,12 @@
         <v>0.04721</v>
       </c>
       <c r="J514" s="1" t="n">
+        <v>0.04727</v>
+      </c>
+      <c r="K514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="K514" s="1" t="n">
+      <c r="L514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -19501,9 +21046,12 @@
         <v>0.0182</v>
       </c>
       <c r="J515" s="1" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="K515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="K515" s="1" t="n">
+      <c r="L515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -19538,9 +21086,12 @@
         <v>0.0005813</v>
       </c>
       <c r="J516" s="1" t="n">
+        <v>0.0005794</v>
+      </c>
+      <c r="K516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="K516" s="1" t="n">
+      <c r="L516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -19575,9 +21126,12 @@
         <v>0.07871</v>
       </c>
       <c r="J517" s="1" t="n">
+        <v>0.07858999999999999</v>
+      </c>
+      <c r="K517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="K517" s="1" t="n">
+      <c r="L517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -19612,10 +21166,13 @@
         <v>0.006379</v>
       </c>
       <c r="J518" s="1" t="n">
+        <v>0.006373</v>
+      </c>
+      <c r="K518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="K518" s="1" t="n">
-        <v>0.006378</v>
+      <c r="L518" s="1" t="n">
+        <v>0.006373</v>
       </c>
     </row>
     <row r="519">
@@ -19649,10 +21206,13 @@
         <v>0.05797</v>
       </c>
       <c r="J519" s="1" t="n">
+        <v>0.05785</v>
+      </c>
+      <c r="K519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="K519" s="1" t="n">
-        <v>0.05789</v>
+      <c r="L519" s="1" t="n">
+        <v>0.05785</v>
       </c>
     </row>
     <row r="520">
@@ -19686,10 +21246,13 @@
         <v>0.10498</v>
       </c>
       <c r="J520" s="1" t="n">
+        <v>0.10469</v>
+      </c>
+      <c r="K520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="K520" s="1" t="n">
-        <v>0.10489</v>
+      <c r="L520" s="1" t="n">
+        <v>0.10469</v>
       </c>
     </row>
     <row r="521">
@@ -19723,9 +21286,12 @@
         <v>0.01796</v>
       </c>
       <c r="J521" s="1" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="K521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="K521" s="1" t="n">
+      <c r="L521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -19760,9 +21326,12 @@
         <v>0.01656</v>
       </c>
       <c r="J522" s="1" t="n">
+        <v>0.01655</v>
+      </c>
+      <c r="K522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="K522" s="1" t="n">
+      <c r="L522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -19797,9 +21366,12 @@
         <v>0.01086</v>
       </c>
       <c r="J523" s="1" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="K523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="K523" s="1" t="n">
+      <c r="L523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -19834,9 +21406,12 @@
         <v>0.007156</v>
       </c>
       <c r="J524" s="1" t="n">
+        <v>0.007154</v>
+      </c>
+      <c r="K524" s="1" t="n">
         <v>0.007156</v>
       </c>
-      <c r="K524" s="1" t="n">
+      <c r="L524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -19871,10 +21446,13 @@
         <v>0.005907</v>
       </c>
       <c r="J525" s="1" t="n">
+        <v>0.005892</v>
+      </c>
+      <c r="K525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="K525" s="1" t="n">
-        <v>0.005907</v>
+      <c r="L525" s="1" t="n">
+        <v>0.005892</v>
       </c>
     </row>
     <row r="526">
@@ -19908,9 +21486,12 @@
         <v>0.001442</v>
       </c>
       <c r="J526" s="1" t="n">
+        <v>0.001441</v>
+      </c>
+      <c r="K526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="K526" s="1" t="n">
+      <c r="L526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -19945,9 +21526,12 @@
         <v>0.373</v>
       </c>
       <c r="J527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="K527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="K527" s="1" t="n">
+      <c r="L527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -19982,9 +21566,12 @@
         <v>0.005181</v>
       </c>
       <c r="J528" s="1" t="n">
+        <v>0.005187</v>
+      </c>
+      <c r="K528" s="1" t="n">
         <v>0.00521</v>
       </c>
-      <c r="K528" s="1" t="n">
+      <c r="L528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -20022,6 +21609,9 @@
         <v>2.951</v>
       </c>
       <c r="K529" s="1" t="n">
+        <v>2.951</v>
+      </c>
+      <c r="L529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -20056,9 +21646,12 @@
         <v>0.1558</v>
       </c>
       <c r="J530" s="1" t="n">
-        <v>0.156</v>
+        <v>0.1562</v>
       </c>
       <c r="K530" s="1" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="L530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -20093,9 +21686,12 @@
         <v>2533</v>
       </c>
       <c r="J531" s="1" t="n">
+        <v>2535</v>
+      </c>
+      <c r="K531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="K531" s="1" t="n">
+      <c r="L531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -20130,9 +21726,12 @@
         <v>0.03924</v>
       </c>
       <c r="J532" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="K532" s="1" t="n">
         <v>0.03929</v>
       </c>
-      <c r="K532" s="1" t="n">
+      <c r="L532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -20167,9 +21766,12 @@
         <v>0.02188</v>
       </c>
       <c r="J533" s="1" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="K533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="K533" s="1" t="n">
+      <c r="L533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -20204,9 +21806,12 @@
         <v>0.0737</v>
       </c>
       <c r="J534" s="1" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="K534" s="1" t="n">
         <v>0.0737</v>
       </c>
-      <c r="K534" s="1" t="n">
+      <c r="L534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -20241,9 +21846,12 @@
         <v>0.007849</v>
       </c>
       <c r="J535" s="1" t="n">
-        <v>0.007877</v>
+        <v>0.007929</v>
       </c>
       <c r="K535" s="1" t="n">
+        <v>0.007929</v>
+      </c>
+      <c r="L535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -20278,9 +21886,12 @@
         <v>0.05025</v>
       </c>
       <c r="J536" s="1" t="n">
+        <v>0.05023</v>
+      </c>
+      <c r="K536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="K536" s="1" t="n">
+      <c r="L536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -20315,9 +21926,12 @@
         <v>0.00405</v>
       </c>
       <c r="J537" s="1" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="K537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="K537" s="1" t="n">
+      <c r="L537" s="1" t="n">
         <v>0.00405</v>
       </c>
     </row>
@@ -20352,9 +21966,12 @@
         <v>0.08309</v>
       </c>
       <c r="J538" s="1" t="n">
+        <v>0.08314000000000001</v>
+      </c>
+      <c r="K538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="K538" s="1" t="n">
+      <c r="L538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -20389,9 +22006,12 @@
         <v>0.02492</v>
       </c>
       <c r="J539" s="1" t="n">
+        <v>0.02496</v>
+      </c>
+      <c r="K539" s="1" t="n">
         <v>0.02502</v>
       </c>
-      <c r="K539" s="1" t="n">
+      <c r="L539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -20426,9 +22046,12 @@
         <v>0.08473</v>
       </c>
       <c r="J540" s="1" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="K540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="K540" s="1" t="n">
+      <c r="L540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -20463,10 +22086,13 @@
         <v>0.01895</v>
       </c>
       <c r="J541" s="1" t="n">
+        <v>0.01891</v>
+      </c>
+      <c r="K541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="K541" s="1" t="n">
-        <v>0.01895</v>
+      <c r="L541" s="1" t="n">
+        <v>0.01891</v>
       </c>
     </row>
     <row r="542">
@@ -20500,10 +22126,13 @@
         <v>0.01694</v>
       </c>
       <c r="J542" s="1" t="n">
+        <v>0.01693</v>
+      </c>
+      <c r="K542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="K542" s="1" t="n">
-        <v>0.01694</v>
+      <c r="L542" s="1" t="n">
+        <v>0.01693</v>
       </c>
     </row>
     <row r="543">
@@ -20537,9 +22166,12 @@
         <v>0.1048</v>
       </c>
       <c r="J543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="K543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="K543" s="1" t="n">
+      <c r="L543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L543"/>
+  <dimension ref="A1:M543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -429,8 +429,9 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,10 +487,15 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>price_02:30</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -529,9 +535,12 @@
         <v>70544.10000000001</v>
       </c>
       <c r="K2" s="1" t="n">
+        <v>70582.7</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -569,9 +578,12 @@
         <v>2072.51</v>
       </c>
       <c r="K3" s="1" t="n">
+        <v>2072.9</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -609,9 +621,12 @@
         <v>86.81</v>
       </c>
       <c r="K4" s="1" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -649,9 +664,12 @@
         <v>4.02</v>
       </c>
       <c r="K5" s="1" t="n">
+        <v>4.048</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>4.02</v>
       </c>
     </row>
@@ -689,10 +707,13 @@
         <v>0.09455</v>
       </c>
       <c r="K6" s="1" t="n">
+        <v>0.09444</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="L6" s="1" t="n">
-        <v>0.09455</v>
+      <c r="M6" s="1" t="n">
+        <v>0.09444</v>
       </c>
     </row>
     <row r="7">
@@ -729,9 +750,12 @@
         <v>1.3883</v>
       </c>
       <c r="K7" s="1" t="n">
+        <v>1.3894</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -769,9 +793,12 @@
         <v>22.422</v>
       </c>
       <c r="K8" s="1" t="n">
+        <v>22.518</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>22.688</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -809,9 +836,12 @@
         <v>0.001977</v>
       </c>
       <c r="K9" s="1" t="n">
+        <v>0.001987</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.001977</v>
       </c>
     </row>
@@ -849,9 +879,12 @@
         <v>0.010275</v>
       </c>
       <c r="K10" s="1" t="n">
+        <v>0.010102</v>
+      </c>
+      <c r="L10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -889,9 +922,12 @@
         <v>0.16108</v>
       </c>
       <c r="K11" s="1" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.15789</v>
       </c>
     </row>
@@ -929,9 +965,12 @@
         <v>0.01142</v>
       </c>
       <c r="K12" s="1" t="n">
+        <v>0.011387</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -969,10 +1008,13 @@
         <v>38.034</v>
       </c>
       <c r="K13" s="1" t="n">
+        <v>37.817</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="L13" s="1" t="n">
-        <v>37.988</v>
+      <c r="M13" s="1" t="n">
+        <v>37.817</v>
       </c>
     </row>
     <row r="14">
@@ -1009,10 +1051,13 @@
         <v>652.55</v>
       </c>
       <c r="K14" s="1" t="n">
+        <v>652.41</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="L14" s="1" t="n">
-        <v>652.55</v>
+      <c r="M14" s="1" t="n">
+        <v>652.41</v>
       </c>
     </row>
     <row r="15">
@@ -1049,9 +1094,12 @@
         <v>208.77</v>
       </c>
       <c r="K15" s="1" t="n">
+        <v>209.25</v>
+      </c>
+      <c r="L15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="L15" s="1" t="n">
+      <c r="M15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1089,10 +1137,13 @@
         <v>0.0033231</v>
       </c>
       <c r="K16" s="1" t="n">
+        <v>0.0033227</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="L16" s="1" t="n">
-        <v>0.0033231</v>
+      <c r="M16" s="1" t="n">
+        <v>0.0033227</v>
       </c>
     </row>
     <row r="17">
@@ -1129,9 +1180,12 @@
         <v>238.29</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>238.32</v>
+        <v>239.55</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>239.55</v>
+      </c>
+      <c r="M17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1169,9 +1223,12 @@
         <v>0.9885</v>
       </c>
       <c r="K18" s="1" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1209,9 +1266,12 @@
         <v>1.0455</v>
       </c>
       <c r="K19" s="1" t="n">
+        <v>1.0541</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="L19" s="1" t="n">
+      <c r="M19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1249,9 +1309,12 @@
         <v>0.2587</v>
       </c>
       <c r="K20" s="1" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="L20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="L20" s="1" t="n">
+      <c r="M20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1289,10 +1352,13 @@
         <v>0.59554</v>
       </c>
       <c r="K21" s="1" t="n">
+        <v>0.59476</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="L21" s="1" t="n">
-        <v>0.59536</v>
+      <c r="M21" s="1" t="n">
+        <v>0.59476</v>
       </c>
     </row>
     <row r="22">
@@ -1329,9 +1395,12 @@
         <v>8.992000000000001</v>
       </c>
       <c r="K22" s="1" t="n">
+        <v>9.002000000000001</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="M22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1369,9 +1438,12 @@
         <v>0.02425</v>
       </c>
       <c r="K23" s="1" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="L23" s="1" t="n">
+      <c r="M23" s="1" t="n">
         <v>0.02404</v>
       </c>
     </row>
@@ -1409,9 +1481,12 @@
         <v>9.553000000000001</v>
       </c>
       <c r="K24" s="1" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="M24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1449,9 +1524,12 @@
         <v>1.225</v>
       </c>
       <c r="K25" s="1" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>1.228</v>
       </c>
-      <c r="L25" s="1" t="n">
+      <c r="M25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1489,9 +1567,12 @@
         <v>0.07116</v>
       </c>
       <c r="K26" s="1" t="n">
+        <v>0.07061000000000001</v>
+      </c>
+      <c r="L26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="L26" s="1" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1529,10 +1610,13 @@
         <v>1.424</v>
       </c>
       <c r="K27" s="1" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="L27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="L27" s="1" t="n">
-        <v>1.424</v>
+      <c r="M27" s="1" t="n">
+        <v>1.423</v>
       </c>
     </row>
     <row r="28">
@@ -1569,10 +1653,13 @@
         <v>1.304</v>
       </c>
       <c r="K28" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="L28" s="1" t="n">
-        <v>1.304</v>
+      <c r="M28" s="1" t="n">
+        <v>1.302</v>
       </c>
     </row>
     <row r="29">
@@ -1609,9 +1696,12 @@
         <v>461.1</v>
       </c>
       <c r="K29" s="1" t="n">
+        <v>462.28</v>
+      </c>
+      <c r="L29" s="1" t="n">
         <v>463.21</v>
       </c>
-      <c r="L29" s="1" t="n">
+      <c r="M29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -1649,9 +1739,12 @@
         <v>1.2908</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>1.2908</v>
+        <v>1.2939</v>
       </c>
       <c r="L30" s="1" t="n">
+        <v>1.2939</v>
+      </c>
+      <c r="M30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1689,9 +1782,12 @@
         <v>5023.98</v>
       </c>
       <c r="K31" s="1" t="n">
+        <v>5023.09</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="L31" s="1" t="n">
+      <c r="M31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -1729,9 +1825,12 @@
         <v>0.875</v>
       </c>
       <c r="K32" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>0.877</v>
       </c>
-      <c r="L32" s="1" t="n">
+      <c r="M32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -1769,9 +1868,12 @@
         <v>0.001978</v>
       </c>
       <c r="K33" s="1" t="n">
+        <v>0.001974</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="L33" s="1" t="n">
+      <c r="M33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -1809,9 +1911,12 @@
         <v>0.17106</v>
       </c>
       <c r="K34" s="1" t="n">
+        <v>0.16845</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>0.17106</v>
       </c>
-      <c r="L34" s="1" t="n">
+      <c r="M34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -1849,10 +1954,13 @@
         <v>0.29701</v>
       </c>
       <c r="K35" s="1" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="L35" s="1" t="n">
-        <v>0.29701</v>
+      <c r="M35" s="1" t="n">
+        <v>0.29697</v>
       </c>
     </row>
     <row r="36">
@@ -1889,10 +1997,13 @@
         <v>1.784</v>
       </c>
       <c r="K36" s="1" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="L36" s="1" t="n">
-        <v>1.784</v>
+      <c r="M36" s="1" t="n">
+        <v>1.779</v>
       </c>
     </row>
     <row r="37">
@@ -1929,9 +2040,12 @@
         <v>110.49</v>
       </c>
       <c r="K37" s="1" t="n">
+        <v>110.27</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="L37" s="1" t="n">
+      <c r="M37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -1969,9 +2083,12 @@
         <v>0.22296</v>
       </c>
       <c r="K38" s="1" t="n">
+        <v>0.22314</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="L38" s="1" t="n">
+      <c r="M38" s="1" t="n">
         <v>0.22169</v>
       </c>
     </row>
@@ -2009,9 +2126,12 @@
         <v>0.1074</v>
       </c>
       <c r="K39" s="1" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="L39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="L39" s="1" t="n">
+      <c r="M39" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -2049,9 +2169,12 @@
         <v>0.37153</v>
       </c>
       <c r="K40" s="1" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="L40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="L40" s="1" t="n">
+      <c r="M40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2089,9 +2212,12 @@
         <v>54.58</v>
       </c>
       <c r="K41" s="1" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>54.66</v>
       </c>
-      <c r="L41" s="1" t="n">
+      <c r="M41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2129,9 +2255,12 @@
         <v>0.0010666</v>
       </c>
       <c r="K42" s="1" t="n">
+        <v>0.0010687</v>
+      </c>
+      <c r="L42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="L42" s="1" t="n">
+      <c r="M42" s="1" t="n">
         <v>0.0010666</v>
       </c>
     </row>
@@ -2169,9 +2298,12 @@
         <v>6.433</v>
       </c>
       <c r="K43" s="1" t="n">
+        <v>6.425</v>
+      </c>
+      <c r="L43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="L43" s="1" t="n">
+      <c r="M43" s="1" t="n">
         <v>6.414</v>
       </c>
     </row>
@@ -2209,9 +2341,12 @@
         <v>0.6324</v>
       </c>
       <c r="K44" s="1" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="L44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="L44" s="1" t="n">
+      <c r="M44" s="1" t="n">
         <v>0.6324</v>
       </c>
     </row>
@@ -2249,10 +2384,13 @@
         <v>0.3535</v>
       </c>
       <c r="K45" s="1" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="L45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="L45" s="1" t="n">
-        <v>0.3535</v>
+      <c r="M45" s="1" t="n">
+        <v>0.3533</v>
       </c>
     </row>
     <row r="46">
@@ -2289,9 +2427,12 @@
         <v>0.03247</v>
       </c>
       <c r="K46" s="1" t="n">
-        <v>0.0326</v>
+        <v>0.03266</v>
       </c>
       <c r="L46" s="1" t="n">
+        <v>0.03266</v>
+      </c>
+      <c r="M46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2329,9 +2470,12 @@
         <v>0.07245</v>
       </c>
       <c r="K47" s="1" t="n">
+        <v>0.07179000000000001</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="L47" s="1" t="n">
+      <c r="M47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -2369,9 +2513,12 @@
         <v>0.7068</v>
       </c>
       <c r="K48" s="1" t="n">
+        <v>0.7067</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>0.7068</v>
       </c>
-      <c r="L48" s="1" t="n">
+      <c r="M48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -2409,9 +2556,12 @@
         <v>0.004361</v>
       </c>
       <c r="K49" s="1" t="n">
+        <v>0.004374</v>
+      </c>
+      <c r="L49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="L49" s="1" t="n">
+      <c r="M49" s="1" t="n">
         <v>0.004361</v>
       </c>
     </row>
@@ -2449,9 +2599,12 @@
         <v>0.104</v>
       </c>
       <c r="K50" s="1" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="L50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="L50" s="1" t="n">
+      <c r="M50" s="1" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -2489,9 +2642,12 @@
         <v>0.04073</v>
       </c>
       <c r="K51" s="1" t="n">
+        <v>0.04069</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="L51" s="1" t="n">
+      <c r="M51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -2529,9 +2685,12 @@
         <v>0.1646</v>
       </c>
       <c r="K52" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="L52" s="1" t="n">
+      <c r="M52" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -2569,9 +2728,12 @@
         <v>0.02003</v>
       </c>
       <c r="K53" s="1" t="n">
+        <v>0.02032</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="L53" s="1" t="n">
+      <c r="M53" s="1" t="n">
         <v>0.02003</v>
       </c>
     </row>
@@ -2609,9 +2771,12 @@
         <v>0.007198</v>
       </c>
       <c r="K54" s="1" t="n">
+        <v>0.007199</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="L54" s="1" t="n">
+      <c r="M54" s="1" t="n">
         <v>0.007198</v>
       </c>
     </row>
@@ -2649,9 +2814,12 @@
         <v>3.911</v>
       </c>
       <c r="K55" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="L55" s="1" t="n">
+      <c r="M55" s="1" t="n">
         <v>3.911</v>
       </c>
     </row>
@@ -2689,9 +2857,12 @@
         <v>0.017202</v>
       </c>
       <c r="K56" s="1" t="n">
+        <v>0.017202</v>
+      </c>
+      <c r="L56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="L56" s="1" t="n">
+      <c r="M56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -2729,9 +2900,12 @@
         <v>0.1107</v>
       </c>
       <c r="K57" s="1" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="L57" s="1" t="n">
+      <c r="M57" s="1" t="n">
         <v>0.1095</v>
       </c>
     </row>
@@ -2769,9 +2943,12 @@
         <v>2.656</v>
       </c>
       <c r="K58" s="1" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="L58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="L58" s="1" t="n">
+      <c r="M58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -2809,10 +2986,13 @@
         <v>0.159</v>
       </c>
       <c r="K59" s="1" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="L59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="L59" s="1" t="n">
-        <v>0.159</v>
+      <c r="M59" s="1" t="n">
+        <v>0.1589</v>
       </c>
     </row>
     <row r="60">
@@ -2849,10 +3029,13 @@
         <v>0.005887</v>
       </c>
       <c r="K60" s="1" t="n">
+        <v>0.005883</v>
+      </c>
+      <c r="L60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="L60" s="1" t="n">
-        <v>0.005887</v>
+      <c r="M60" s="1" t="n">
+        <v>0.005883</v>
       </c>
     </row>
     <row r="61">
@@ -2889,9 +3072,12 @@
         <v>0.09188</v>
       </c>
       <c r="K61" s="1" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="L61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="L61" s="1" t="n">
+      <c r="M61" s="1" t="n">
         <v>0.09188</v>
       </c>
     </row>
@@ -2929,10 +3115,13 @@
         <v>0.9114</v>
       </c>
       <c r="K62" s="1" t="n">
+        <v>0.9112</v>
+      </c>
+      <c r="L62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="L62" s="1" t="n">
-        <v>0.9114</v>
+      <c r="M62" s="1" t="n">
+        <v>0.9112</v>
       </c>
     </row>
     <row r="63">
@@ -2972,6 +3161,9 @@
         <v>0.78</v>
       </c>
       <c r="L63" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -3009,9 +3201,12 @@
         <v>0.04563</v>
       </c>
       <c r="K64" s="1" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="L64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="L64" s="1" t="n">
+      <c r="M64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -3049,9 +3244,12 @@
         <v>357.88</v>
       </c>
       <c r="K65" s="1" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="L65" s="1" t="n">
         <v>357.88</v>
       </c>
-      <c r="L65" s="1" t="n">
+      <c r="M65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -3089,9 +3287,12 @@
         <v>0.12428</v>
       </c>
       <c r="K66" s="1" t="n">
+        <v>0.12444</v>
+      </c>
+      <c r="L66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="L66" s="1" t="n">
+      <c r="M66" s="1" t="n">
         <v>0.12419</v>
       </c>
     </row>
@@ -3129,10 +3330,13 @@
         <v>0.2343</v>
       </c>
       <c r="K67" s="1" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="L67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="L67" s="1" t="n">
-        <v>0.2343</v>
+      <c r="M67" s="1" t="n">
+        <v>0.2317</v>
       </c>
     </row>
     <row r="68">
@@ -3169,9 +3373,12 @@
         <v>0.00339</v>
       </c>
       <c r="K68" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="L68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="L68" s="1" t="n">
+      <c r="M68" s="1" t="n">
         <v>0.00339</v>
       </c>
     </row>
@@ -3209,9 +3416,12 @@
         <v>0.1738</v>
       </c>
       <c r="K69" s="1" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="L69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="L69" s="1" t="n">
+      <c r="M69" s="1" t="n">
         <v>0.1738</v>
       </c>
     </row>
@@ -3249,9 +3459,12 @@
         <v>0.1639</v>
       </c>
       <c r="K70" s="1" t="n">
+        <v>0.16403</v>
+      </c>
+      <c r="L70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="L70" s="1" t="n">
+      <c r="M70" s="1" t="n">
         <v>0.1639</v>
       </c>
     </row>
@@ -3289,9 +3502,12 @@
         <v>0.3483</v>
       </c>
       <c r="K71" s="1" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="L71" s="1" t="n">
+      <c r="M71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -3329,9 +3545,12 @@
         <v>0.7106</v>
       </c>
       <c r="K72" s="1" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="L72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="L72" s="1" t="n">
+      <c r="M72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -3369,9 +3588,12 @@
         <v>0.008710000000000001</v>
       </c>
       <c r="K73" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="L73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="L73" s="1" t="n">
+      <c r="M73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -3409,10 +3631,13 @@
         <v>0.005972</v>
       </c>
       <c r="K74" s="1" t="n">
+        <v>0.005967</v>
+      </c>
+      <c r="L74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="L74" s="1" t="n">
-        <v>0.005972</v>
+      <c r="M74" s="1" t="n">
+        <v>0.005967</v>
       </c>
     </row>
     <row r="75">
@@ -3449,9 +3674,12 @@
         <v>0.226</v>
       </c>
       <c r="K75" s="1" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="L75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="L75" s="1" t="n">
+      <c r="M75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -3489,9 +3717,12 @@
         <v>0.3265</v>
       </c>
       <c r="K76" s="1" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="L76" s="1" t="n">
         <v>0.3265</v>
       </c>
-      <c r="L76" s="1" t="n">
+      <c r="M76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -3529,9 +3760,12 @@
         <v>0.1002</v>
       </c>
       <c r="K77" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="L77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="L77" s="1" t="n">
+      <c r="M77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -3569,9 +3803,12 @@
         <v>0.1229</v>
       </c>
       <c r="K78" s="1" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="L78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="L78" s="1" t="n">
+      <c r="M78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -3609,9 +3846,12 @@
         <v>0.07210999999999999</v>
       </c>
       <c r="K79" s="1" t="n">
+        <v>0.07129000000000001</v>
+      </c>
+      <c r="L79" s="1" t="n">
         <v>0.07277</v>
       </c>
-      <c r="L79" s="1" t="n">
+      <c r="M79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -3649,9 +3889,12 @@
         <v>0.04692</v>
       </c>
       <c r="K80" s="1" t="n">
+        <v>0.04705</v>
+      </c>
+      <c r="L80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="L80" s="1" t="n">
+      <c r="M80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -3689,9 +3932,12 @@
         <v>0.000235</v>
       </c>
       <c r="K81" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="L81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="L81" s="1" t="n">
+      <c r="M81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -3729,9 +3975,12 @@
         <v>8.206</v>
       </c>
       <c r="K82" s="1" t="n">
+        <v>8.212999999999999</v>
+      </c>
+      <c r="L82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="L82" s="1" t="n">
+      <c r="M82" s="1" t="n">
         <v>8.206</v>
       </c>
     </row>
@@ -3769,10 +4018,13 @@
         <v>0.0005795</v>
       </c>
       <c r="K83" s="1" t="n">
+        <v>0.0005765</v>
+      </c>
+      <c r="L83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="L83" s="1" t="n">
-        <v>0.0005795</v>
+      <c r="M83" s="1" t="n">
+        <v>0.0005765</v>
       </c>
     </row>
     <row r="84">
@@ -3809,9 +4061,12 @@
         <v>0.4457</v>
       </c>
       <c r="K84" s="1" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="L84" s="1" t="n">
         <v>0.4457</v>
       </c>
-      <c r="L84" s="1" t="n">
+      <c r="M84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -3849,9 +4104,12 @@
         <v>0.06248</v>
       </c>
       <c r="K85" s="1" t="n">
+        <v>0.06242</v>
+      </c>
+      <c r="L85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="L85" s="1" t="n">
+      <c r="M85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -3889,9 +4147,12 @@
         <v>0.05442</v>
       </c>
       <c r="K86" s="1" t="n">
+        <v>0.05435</v>
+      </c>
+      <c r="L86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="L86" s="1" t="n">
+      <c r="M86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -3929,9 +4190,12 @@
         <v>0.003331</v>
       </c>
       <c r="K87" s="1" t="n">
+        <v>0.003334</v>
+      </c>
+      <c r="L87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="L87" s="1" t="n">
+      <c r="M87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -3969,9 +4233,12 @@
         <v>0.05089</v>
       </c>
       <c r="K88" s="1" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="L88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="L88" s="1" t="n">
+      <c r="M88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -4009,9 +4276,12 @@
         <v>0.03032</v>
       </c>
       <c r="K89" s="1" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="L89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="L89" s="1" t="n">
+      <c r="M89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -4049,10 +4319,13 @@
         <v>0.3473</v>
       </c>
       <c r="K90" s="1" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="L90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="L90" s="1" t="n">
-        <v>0.3473</v>
+      <c r="M90" s="1" t="n">
+        <v>0.3471</v>
       </c>
     </row>
     <row r="91">
@@ -4089,9 +4362,12 @@
         <v>0.0835</v>
       </c>
       <c r="K91" s="1" t="n">
+        <v>0.07622</v>
+      </c>
+      <c r="L91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="L91" s="1" t="n">
+      <c r="M91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -4129,9 +4405,12 @@
         <v>0.3551</v>
       </c>
       <c r="K92" s="1" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="L92" s="1" t="n">
         <v>0.3551</v>
       </c>
-      <c r="L92" s="1" t="n">
+      <c r="M92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -4169,9 +4448,12 @@
         <v>1.9779</v>
       </c>
       <c r="K93" s="1" t="n">
+        <v>1.9763</v>
+      </c>
+      <c r="L93" s="1" t="n">
         <v>1.9779</v>
       </c>
-      <c r="L93" s="1" t="n">
+      <c r="M93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -4209,9 +4491,12 @@
         <v>0.2586</v>
       </c>
       <c r="K94" s="1" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="L94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="L94" s="1" t="n">
+      <c r="M94" s="1" t="n">
         <v>0.2586</v>
       </c>
     </row>
@@ -4249,9 +4534,12 @@
         <v>0.04549</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>0.04549</v>
+        <v>0.0458</v>
       </c>
       <c r="L95" s="1" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="M95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -4289,9 +4577,12 @@
         <v>0.006242</v>
       </c>
       <c r="K96" s="1" t="n">
+        <v>0.006186</v>
+      </c>
+      <c r="L96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="L96" s="1" t="n">
+      <c r="M96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -4329,10 +4620,13 @@
         <v>0.001736</v>
       </c>
       <c r="K97" s="1" t="n">
+        <v>0.001729</v>
+      </c>
+      <c r="L97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="L97" s="1" t="n">
-        <v>0.00173</v>
+      <c r="M97" s="1" t="n">
+        <v>0.001729</v>
       </c>
     </row>
     <row r="98">
@@ -4369,9 +4663,12 @@
         <v>5.251</v>
       </c>
       <c r="K98" s="1" t="n">
+        <v>5.244</v>
+      </c>
+      <c r="L98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="L98" s="1" t="n">
+      <c r="M98" s="1" t="n">
         <v>5.221</v>
       </c>
     </row>
@@ -4409,9 +4706,12 @@
         <v>0.01514</v>
       </c>
       <c r="K99" s="1" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="L99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="L99" s="1" t="n">
+      <c r="M99" s="1" t="n">
         <v>0.01514</v>
       </c>
     </row>
@@ -4449,9 +4749,12 @@
         <v>0.5545</v>
       </c>
       <c r="K100" s="1" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="L100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="L100" s="1" t="n">
+      <c r="M100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -4489,10 +4792,13 @@
         <v>0.0911</v>
       </c>
       <c r="K101" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="L101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="L101" s="1" t="n">
-        <v>0.091</v>
+      <c r="M101" s="1" t="n">
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -4529,9 +4835,12 @@
         <v>32.42</v>
       </c>
       <c r="K102" s="1" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="L102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="L102" s="1" t="n">
+      <c r="M102" s="1" t="n">
         <v>32.42</v>
       </c>
     </row>
@@ -4569,10 +4878,13 @@
         <v>0.03202</v>
       </c>
       <c r="K103" s="1" t="n">
+        <v>0.03147</v>
+      </c>
+      <c r="L103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="L103" s="1" t="n">
-        <v>0.03182</v>
+      <c r="M103" s="1" t="n">
+        <v>0.03147</v>
       </c>
     </row>
     <row r="104">
@@ -4609,9 +4921,12 @@
         <v>0.06561</v>
       </c>
       <c r="K104" s="1" t="n">
+        <v>0.06562999999999999</v>
+      </c>
+      <c r="L104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="L104" s="1" t="n">
+      <c r="M104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -4649,9 +4964,12 @@
         <v>1.3046</v>
       </c>
       <c r="K105" s="1" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="L105" s="1" t="n">
         <v>1.3046</v>
       </c>
-      <c r="L105" s="1" t="n">
+      <c r="M105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -4689,9 +5007,12 @@
         <v>0.1204</v>
       </c>
       <c r="K106" s="1" t="n">
+        <v>0.1205</v>
+      </c>
+      <c r="L106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="L106" s="1" t="n">
+      <c r="M106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -4732,6 +5053,9 @@
         <v>0.121</v>
       </c>
       <c r="L107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -4769,9 +5093,12 @@
         <v>0.09579</v>
       </c>
       <c r="K108" s="1" t="n">
+        <v>0.09583</v>
+      </c>
+      <c r="L108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="L108" s="1" t="n">
+      <c r="M108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -4809,9 +5136,12 @@
         <v>0.13853</v>
       </c>
       <c r="K109" s="1" t="n">
+        <v>0.13923</v>
+      </c>
+      <c r="L109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="L109" s="1" t="n">
+      <c r="M109" s="1" t="n">
         <v>0.13853</v>
       </c>
     </row>
@@ -4849,9 +5179,12 @@
         <v>5.548</v>
       </c>
       <c r="K110" s="1" t="n">
+        <v>5.559</v>
+      </c>
+      <c r="L110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="L110" s="1" t="n">
+      <c r="M110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -4889,9 +5222,12 @@
         <v>1.103</v>
       </c>
       <c r="K111" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="L111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="L111" s="1" t="n">
+      <c r="M111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -4929,9 +5265,12 @@
         <v>0.029118</v>
       </c>
       <c r="K112" s="1" t="n">
+        <v>0.029119</v>
+      </c>
+      <c r="L112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="L112" s="1" t="n">
+      <c r="M112" s="1" t="n">
         <v>0.029118</v>
       </c>
     </row>
@@ -4969,9 +5308,12 @@
         <v>1.878</v>
       </c>
       <c r="K113" s="1" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="L113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="L113" s="1" t="n">
+      <c r="M113" s="1" t="n">
         <v>1.874</v>
       </c>
     </row>
@@ -5009,9 +5351,12 @@
         <v>0.05913</v>
       </c>
       <c r="K114" s="1" t="n">
+        <v>0.05928</v>
+      </c>
+      <c r="L114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="L114" s="1" t="n">
+      <c r="M114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -5049,9 +5394,12 @@
         <v>0.12874</v>
       </c>
       <c r="K115" s="1" t="n">
+        <v>0.12885</v>
+      </c>
+      <c r="L115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="L115" s="1" t="n">
+      <c r="M115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -5089,9 +5437,12 @@
         <v>1.1111</v>
       </c>
       <c r="K116" s="1" t="n">
+        <v>1.1106</v>
+      </c>
+      <c r="L116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="L116" s="1" t="n">
+      <c r="M116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -5129,9 +5480,12 @@
         <v>0.1542</v>
       </c>
       <c r="K117" s="1" t="n">
+        <v>0.1543</v>
+      </c>
+      <c r="L117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="L117" s="1" t="n">
+      <c r="M117" s="1" t="n">
         <v>0.1537</v>
       </c>
     </row>
@@ -5169,9 +5523,12 @@
         <v>0.1601</v>
       </c>
       <c r="K118" s="1" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="L118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="L118" s="1" t="n">
+      <c r="M118" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -5209,9 +5566,12 @@
         <v>0.04683</v>
       </c>
       <c r="K119" s="1" t="n">
-        <v>0.04683</v>
+        <v>0.04747</v>
       </c>
       <c r="L119" s="1" t="n">
+        <v>0.04747</v>
+      </c>
+      <c r="M119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -5249,9 +5609,12 @@
         <v>3.022</v>
       </c>
       <c r="K120" s="1" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="L120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="L120" s="1" t="n">
+      <c r="M120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -5289,9 +5652,12 @@
         <v>0.2969</v>
       </c>
       <c r="K121" s="1" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="L121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="L121" s="1" t="n">
+      <c r="M121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -5329,9 +5695,12 @@
         <v>0.584</v>
       </c>
       <c r="K122" s="1" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="L122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="L122" s="1" t="n">
+      <c r="M122" s="1" t="n">
         <v>0.5826</v>
       </c>
     </row>
@@ -5369,9 +5738,12 @@
         <v>0.01259</v>
       </c>
       <c r="K123" s="1" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="L123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="L123" s="1" t="n">
+      <c r="M123" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -5409,10 +5781,13 @@
         <v>0.1578</v>
       </c>
       <c r="K124" s="1" t="n">
+        <v>0.1577</v>
+      </c>
+      <c r="L124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="L124" s="1" t="n">
-        <v>0.1578</v>
+      <c r="M124" s="1" t="n">
+        <v>0.1577</v>
       </c>
     </row>
     <row r="125">
@@ -5449,9 +5824,12 @@
         <v>0.001785</v>
       </c>
       <c r="K125" s="1" t="n">
+        <v>0.001782</v>
+      </c>
+      <c r="L125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="L125" s="1" t="n">
+      <c r="M125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -5489,9 +5867,12 @@
         <v>0.0004859</v>
       </c>
       <c r="K126" s="1" t="n">
+        <v>0.0004862</v>
+      </c>
+      <c r="L126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="L126" s="1" t="n">
+      <c r="M126" s="1" t="n">
         <v>0.0004859</v>
       </c>
     </row>
@@ -5529,10 +5910,13 @@
         <v>0.0294</v>
       </c>
       <c r="K127" s="1" t="n">
+        <v>0.02938</v>
+      </c>
+      <c r="L127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="L127" s="1" t="n">
-        <v>0.0294</v>
+      <c r="M127" s="1" t="n">
+        <v>0.02938</v>
       </c>
     </row>
     <row r="128">
@@ -5569,9 +5953,12 @@
         <v>0.04125</v>
       </c>
       <c r="K128" s="1" t="n">
+        <v>0.04132</v>
+      </c>
+      <c r="L128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="L128" s="1" t="n">
+      <c r="M128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -5609,10 +5996,13 @@
         <v>0.04841</v>
       </c>
       <c r="K129" s="1" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="L129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="L129" s="1" t="n">
-        <v>0.04838</v>
+      <c r="M129" s="1" t="n">
+        <v>0.04837</v>
       </c>
     </row>
     <row r="130">
@@ -5649,9 +6039,12 @@
         <v>1.25e-05</v>
       </c>
       <c r="K130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="L130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="L130" s="1" t="n">
+      <c r="M130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -5689,9 +6082,12 @@
         <v>6.8e-06</v>
       </c>
       <c r="K131" s="1" t="n">
+        <v>6.9e-06</v>
+      </c>
+      <c r="L131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="L131" s="1" t="n">
+      <c r="M131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -5729,9 +6125,12 @@
         <v>0.007</v>
       </c>
       <c r="K132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="L132" s="1" t="n">
+      <c r="M132" s="1" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -5772,6 +6171,9 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="L133" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="M133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -5809,10 +6211,13 @@
         <v>0.0004104</v>
       </c>
       <c r="K134" s="1" t="n">
+        <v>0.0004093</v>
+      </c>
+      <c r="L134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="L134" s="1" t="n">
-        <v>0.0004099</v>
+      <c r="M134" s="1" t="n">
+        <v>0.0004093</v>
       </c>
     </row>
     <row r="135">
@@ -5849,10 +6254,13 @@
         <v>0.08344</v>
       </c>
       <c r="K135" s="1" t="n">
+        <v>0.08334</v>
+      </c>
+      <c r="L135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="L135" s="1" t="n">
-        <v>0.08344</v>
+      <c r="M135" s="1" t="n">
+        <v>0.08334</v>
       </c>
     </row>
     <row r="136">
@@ -5889,9 +6297,12 @@
         <v>0.007939</v>
       </c>
       <c r="K136" s="1" t="n">
+        <v>0.007913</v>
+      </c>
+      <c r="L136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="L136" s="1" t="n">
+      <c r="M136" s="1" t="n">
         <v>0.007891</v>
       </c>
     </row>
@@ -5929,9 +6340,12 @@
         <v>0.0008207000000000001</v>
       </c>
       <c r="K137" s="1" t="n">
+        <v>0.0008192</v>
+      </c>
+      <c r="L137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="L137" s="1" t="n">
+      <c r="M137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -5969,10 +6383,13 @@
         <v>0.147</v>
       </c>
       <c r="K138" s="1" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="L138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="L138" s="1" t="n">
-        <v>0.147</v>
+      <c r="M138" s="1" t="n">
+        <v>0.1468</v>
       </c>
     </row>
     <row r="139">
@@ -6009,9 +6426,12 @@
         <v>0.006714</v>
       </c>
       <c r="K139" s="1" t="n">
+        <v>0.006719</v>
+      </c>
+      <c r="L139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="L139" s="1" t="n">
+      <c r="M139" s="1" t="n">
         <v>0.006714</v>
       </c>
     </row>
@@ -6049,9 +6469,12 @@
         <v>0.01389</v>
       </c>
       <c r="K140" s="1" t="n">
-        <v>0.01391</v>
+        <v>0.01392</v>
       </c>
       <c r="L140" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="M140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -6089,9 +6512,12 @@
         <v>0.09807</v>
       </c>
       <c r="K141" s="1" t="n">
+        <v>0.09766</v>
+      </c>
+      <c r="L141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="L141" s="1" t="n">
+      <c r="M141" s="1" t="n">
         <v>0.09758</v>
       </c>
     </row>
@@ -6129,9 +6555,12 @@
         <v>0.05422</v>
       </c>
       <c r="K142" s="1" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="L142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="L142" s="1" t="n">
+      <c r="M142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -6169,9 +6598,12 @@
         <v>0.3242</v>
       </c>
       <c r="K143" s="1" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="L143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="L143" s="1" t="n">
+      <c r="M143" s="1" t="n">
         <v>0.3237</v>
       </c>
     </row>
@@ -6209,9 +6641,12 @@
         <v>0.02583</v>
       </c>
       <c r="K144" s="1" t="n">
+        <v>0.02581</v>
+      </c>
+      <c r="L144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="L144" s="1" t="n">
+      <c r="M144" s="1" t="n">
         <v>0.02572</v>
       </c>
     </row>
@@ -6249,9 +6684,12 @@
         <v>0.2378</v>
       </c>
       <c r="K145" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="L145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="L145" s="1" t="n">
+      <c r="M145" s="1" t="n">
         <v>0.2377</v>
       </c>
     </row>
@@ -6289,9 +6727,12 @@
         <v>0.006982</v>
       </c>
       <c r="K146" s="1" t="n">
+        <v>0.006989</v>
+      </c>
+      <c r="L146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="L146" s="1" t="n">
+      <c r="M146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -6329,9 +6770,12 @@
         <v>0.0872</v>
       </c>
       <c r="K147" s="1" t="n">
+        <v>0.08723</v>
+      </c>
+      <c r="L147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="L147" s="1" t="n">
+      <c r="M147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -6369,9 +6813,12 @@
         <v>0.05217</v>
       </c>
       <c r="K148" s="1" t="n">
+        <v>0.05203</v>
+      </c>
+      <c r="L148" s="1" t="n">
         <v>0.05217</v>
       </c>
-      <c r="L148" s="1" t="n">
+      <c r="M148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -6409,9 +6856,12 @@
         <v>0.02383</v>
       </c>
       <c r="K149" s="1" t="n">
+        <v>0.02383</v>
+      </c>
+      <c r="L149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="L149" s="1" t="n">
+      <c r="M149" s="1" t="n">
         <v>0.02381</v>
       </c>
     </row>
@@ -6449,9 +6899,12 @@
         <v>0.08568000000000001</v>
       </c>
       <c r="K150" s="1" t="n">
+        <v>0.08563</v>
+      </c>
+      <c r="L150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="L150" s="1" t="n">
+      <c r="M150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -6489,9 +6942,12 @@
         <v>0.02342</v>
       </c>
       <c r="K151" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="L151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="L151" s="1" t="n">
+      <c r="M151" s="1" t="n">
         <v>0.0232</v>
       </c>
     </row>
@@ -6529,10 +6985,13 @@
         <v>0.02563</v>
       </c>
       <c r="K152" s="1" t="n">
+        <v>0.02552</v>
+      </c>
+      <c r="L152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="L152" s="1" t="n">
-        <v>0.02561</v>
+      <c r="M152" s="1" t="n">
+        <v>0.02552</v>
       </c>
     </row>
     <row r="153">
@@ -6569,9 +7028,12 @@
         <v>0.0002173</v>
       </c>
       <c r="K153" s="1" t="n">
+        <v>0.0002152</v>
+      </c>
+      <c r="L153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="L153" s="1" t="n">
+      <c r="M153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -6609,9 +7071,12 @@
         <v>0.4412</v>
       </c>
       <c r="K154" s="1" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="L154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="L154" s="1" t="n">
+      <c r="M154" s="1" t="n">
         <v>0.4406</v>
       </c>
     </row>
@@ -6649,9 +7114,12 @@
         <v>0.0667</v>
       </c>
       <c r="K155" s="1" t="n">
+        <v>0.06673</v>
+      </c>
+      <c r="L155" s="1" t="n">
         <v>0.06741999999999999</v>
       </c>
-      <c r="L155" s="1" t="n">
+      <c r="M155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -6689,10 +7157,13 @@
         <v>0.12839</v>
       </c>
       <c r="K156" s="1" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="L156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="L156" s="1" t="n">
-        <v>0.12825</v>
+      <c r="M156" s="1" t="n">
+        <v>0.1282</v>
       </c>
     </row>
     <row r="157">
@@ -6729,10 +7200,13 @@
         <v>0.484</v>
       </c>
       <c r="K157" s="1" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="L157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="L157" s="1" t="n">
-        <v>0.484</v>
+      <c r="M157" s="1" t="n">
+        <v>0.4839</v>
       </c>
     </row>
     <row r="158">
@@ -6769,9 +7243,12 @@
         <v>0.4488</v>
       </c>
       <c r="K158" s="1" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="L158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="L158" s="1" t="n">
+      <c r="M158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -6809,9 +7286,12 @@
         <v>0.007515</v>
       </c>
       <c r="K159" s="1" t="n">
+        <v>0.007501</v>
+      </c>
+      <c r="L159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="L159" s="1" t="n">
+      <c r="M159" s="1" t="n">
         <v>0.007493</v>
       </c>
     </row>
@@ -6849,9 +7329,12 @@
         <v>0.004681</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>0.004681</v>
+        <v>0.004699</v>
       </c>
       <c r="L160" s="1" t="n">
+        <v>0.004699</v>
+      </c>
+      <c r="M160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -6889,9 +7372,12 @@
         <v>0.004296</v>
       </c>
       <c r="K161" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+      <c r="L161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="L161" s="1" t="n">
+      <c r="M161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -6929,9 +7415,12 @@
         <v>0.0959</v>
       </c>
       <c r="K162" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="L162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="L162" s="1" t="n">
+      <c r="M162" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -6969,9 +7458,12 @@
         <v>0.2861</v>
       </c>
       <c r="K163" s="1" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="L163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="L163" s="1" t="n">
+      <c r="M163" s="1" t="n">
         <v>0.2852</v>
       </c>
     </row>
@@ -7009,9 +7501,12 @@
         <v>0.1144</v>
       </c>
       <c r="K164" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="L164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="L164" s="1" t="n">
+      <c r="M164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -7049,10 +7544,13 @@
         <v>0.1754</v>
       </c>
       <c r="K165" s="1" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="L165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="L165" s="1" t="n">
-        <v>0.1754</v>
+      <c r="M165" s="1" t="n">
+        <v>0.1753</v>
       </c>
     </row>
     <row r="166">
@@ -7089,9 +7587,12 @@
         <v>0.0101</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>0.0101</v>
+        <v>0.01011</v>
       </c>
       <c r="L166" s="1" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="M166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -7129,9 +7630,12 @@
         <v>1.826</v>
       </c>
       <c r="K167" s="1" t="n">
+        <v>1.827</v>
+      </c>
+      <c r="L167" s="1" t="n">
         <v>1.837</v>
       </c>
-      <c r="L167" s="1" t="n">
+      <c r="M167" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -7169,10 +7673,13 @@
         <v>1.339</v>
       </c>
       <c r="K168" s="1" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="L168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="L168" s="1" t="n">
-        <v>1.337</v>
+      <c r="M168" s="1" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="169">
@@ -7209,9 +7716,12 @@
         <v>0.007313</v>
       </c>
       <c r="K169" s="1" t="n">
+        <v>0.007313</v>
+      </c>
+      <c r="L169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="L169" s="1" t="n">
+      <c r="M169" s="1" t="n">
         <v>0.007304</v>
       </c>
     </row>
@@ -7249,9 +7759,12 @@
         <v>0.0116</v>
       </c>
       <c r="K170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="L170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="L170" s="1" t="n">
+      <c r="M170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -7289,10 +7802,13 @@
         <v>0.005798</v>
       </c>
       <c r="K171" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="L171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="L171" s="1" t="n">
-        <v>0.005796</v>
+      <c r="M171" s="1" t="n">
+        <v>0.005794</v>
       </c>
     </row>
     <row r="172">
@@ -7329,9 +7845,12 @@
         <v>0.1474</v>
       </c>
       <c r="K172" s="1" t="n">
+        <v>0.14718</v>
+      </c>
+      <c r="L172" s="1" t="n">
         <v>0.14806</v>
       </c>
-      <c r="L172" s="1" t="n">
+      <c r="M172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -7369,9 +7888,12 @@
         <v>4.891</v>
       </c>
       <c r="K173" s="1" t="n">
+        <v>4.873</v>
+      </c>
+      <c r="L173" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="L173" s="1" t="n">
+      <c r="M173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -7409,10 +7931,13 @@
         <v>0.07857</v>
       </c>
       <c r="K174" s="1" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="L174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="L174" s="1" t="n">
-        <v>0.07857</v>
+      <c r="M174" s="1" t="n">
+        <v>0.0784</v>
       </c>
     </row>
     <row r="175">
@@ -7449,10 +7974,13 @@
         <v>0.007478</v>
       </c>
       <c r="K175" s="1" t="n">
+        <v>0.007464</v>
+      </c>
+      <c r="L175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="L175" s="1" t="n">
-        <v>0.007477</v>
+      <c r="M175" s="1" t="n">
+        <v>0.007464</v>
       </c>
     </row>
     <row r="176">
@@ -7489,10 +8017,13 @@
         <v>0.2013</v>
       </c>
       <c r="K176" s="1" t="n">
+        <v>0.2011</v>
+      </c>
+      <c r="L176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="L176" s="1" t="n">
-        <v>0.2012</v>
+      <c r="M176" s="1" t="n">
+        <v>0.2011</v>
       </c>
     </row>
     <row r="177">
@@ -7529,9 +8060,12 @@
         <v>0.05185</v>
       </c>
       <c r="K177" s="1" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="L177" s="1" t="n">
         <v>0.0519</v>
       </c>
-      <c r="L177" s="1" t="n">
+      <c r="M177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -7569,9 +8103,12 @@
         <v>0.05482</v>
       </c>
       <c r="K178" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="L178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="L178" s="1" t="n">
+      <c r="M178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -7609,9 +8146,12 @@
         <v>0.02324</v>
       </c>
       <c r="K179" s="1" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="L179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="L179" s="1" t="n">
+      <c r="M179" s="1" t="n">
         <v>0.02321</v>
       </c>
     </row>
@@ -7649,9 +8189,12 @@
         <v>0.6962</v>
       </c>
       <c r="K180" s="1" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="L180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="L180" s="1" t="n">
+      <c r="M180" s="1" t="n">
         <v>0.694</v>
       </c>
     </row>
@@ -7689,9 +8232,12 @@
         <v>0.0003732</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>0.0003734</v>
+        <v>0.0003743</v>
       </c>
       <c r="L181" s="1" t="n">
+        <v>0.0003743</v>
+      </c>
+      <c r="M181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -7729,10 +8275,13 @@
         <v>0.01261</v>
       </c>
       <c r="K182" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="L182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="L182" s="1" t="n">
-        <v>0.01258</v>
+      <c r="M182" s="1" t="n">
+        <v>0.01256</v>
       </c>
     </row>
     <row r="183">
@@ -7769,10 +8318,13 @@
         <v>4.24</v>
       </c>
       <c r="K183" s="1" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="L183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="L183" s="1" t="n">
-        <v>4.24</v>
+      <c r="M183" s="1" t="n">
+        <v>4.23</v>
       </c>
     </row>
     <row r="184">
@@ -7809,9 +8361,12 @@
         <v>0.2381</v>
       </c>
       <c r="K184" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="L184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="L184" s="1" t="n">
+      <c r="M184" s="1" t="n">
         <v>0.2368</v>
       </c>
     </row>
@@ -7849,9 +8404,12 @@
         <v>0.03678</v>
       </c>
       <c r="K185" s="1" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="L185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="L185" s="1" t="n">
+      <c r="M185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -7889,9 +8447,12 @@
         <v>0.11584</v>
       </c>
       <c r="K186" s="1" t="n">
+        <v>0.11614</v>
+      </c>
+      <c r="L186" s="1" t="n">
         <v>0.11628</v>
       </c>
-      <c r="L186" s="1" t="n">
+      <c r="M186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -7929,9 +8490,12 @@
         <v>0.009025</v>
       </c>
       <c r="K187" s="1" t="n">
+        <v>0.009063</v>
+      </c>
+      <c r="L187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="L187" s="1" t="n">
+      <c r="M187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -7969,10 +8533,13 @@
         <v>0.0973</v>
       </c>
       <c r="K188" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="L188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="L188" s="1" t="n">
-        <v>0.0973</v>
+      <c r="M188" s="1" t="n">
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -8009,10 +8576,13 @@
         <v>0.02778</v>
       </c>
       <c r="K189" s="1" t="n">
+        <v>0.02767</v>
+      </c>
+      <c r="L189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="L189" s="1" t="n">
-        <v>0.02773</v>
+      <c r="M189" s="1" t="n">
+        <v>0.02767</v>
       </c>
     </row>
     <row r="190">
@@ -8049,9 +8619,12 @@
         <v>0.00877</v>
       </c>
       <c r="K190" s="1" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="L190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="L190" s="1" t="n">
+      <c r="M190" s="1" t="n">
         <v>0.008699999999999999</v>
       </c>
     </row>
@@ -8089,9 +8662,12 @@
         <v>0.001947</v>
       </c>
       <c r="K191" s="1" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="L191" s="1" t="n">
         <v>0.001956</v>
       </c>
-      <c r="L191" s="1" t="n">
+      <c r="M191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -8129,9 +8705,12 @@
         <v>0.1006</v>
       </c>
       <c r="K192" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="L192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="L192" s="1" t="n">
+      <c r="M192" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -8169,9 +8748,12 @@
         <v>0.02342</v>
       </c>
       <c r="K193" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="L193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="L193" s="1" t="n">
+      <c r="M193" s="1" t="n">
         <v>0.02325</v>
       </c>
     </row>
@@ -8209,9 +8791,12 @@
         <v>0.01347</v>
       </c>
       <c r="K194" s="1" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="L194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="L194" s="1" t="n">
+      <c r="M194" s="1" t="n">
         <v>0.01346</v>
       </c>
     </row>
@@ -8249,10 +8834,13 @@
         <v>0.0209</v>
       </c>
       <c r="K195" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="L195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="L195" s="1" t="n">
-        <v>0.0209</v>
+      <c r="M195" s="1" t="n">
+        <v>0.02089</v>
       </c>
     </row>
     <row r="196">
@@ -8289,9 +8877,12 @@
         <v>0.17208</v>
       </c>
       <c r="K196" s="1" t="n">
+        <v>0.17201</v>
+      </c>
+      <c r="L196" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="L196" s="1" t="n">
+      <c r="M196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -8329,9 +8920,12 @@
         <v>0.007305</v>
       </c>
       <c r="K197" s="1" t="n">
+        <v>0.007345</v>
+      </c>
+      <c r="L197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="L197" s="1" t="n">
+      <c r="M197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -8369,9 +8963,12 @@
         <v>0.01904</v>
       </c>
       <c r="K198" s="1" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="L198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="L198" s="1" t="n">
+      <c r="M198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -8409,9 +9006,12 @@
         <v>0.01653</v>
       </c>
       <c r="K199" s="1" t="n">
-        <v>0.01653</v>
+        <v>0.01728</v>
       </c>
       <c r="L199" s="1" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="M199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -8449,9 +9049,12 @@
         <v>0.2975</v>
       </c>
       <c r="K200" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="L200" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="L200" s="1" t="n">
+      <c r="M200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -8489,9 +9092,12 @@
         <v>0.006227</v>
       </c>
       <c r="K201" s="1" t="n">
-        <v>0.006237</v>
+        <v>0.006242</v>
       </c>
       <c r="L201" s="1" t="n">
+        <v>0.006242</v>
+      </c>
+      <c r="M201" s="1" t="n">
         <v>0.006223</v>
       </c>
     </row>
@@ -8529,10 +9135,13 @@
         <v>0.0004436</v>
       </c>
       <c r="K202" s="1" t="n">
+        <v>0.0004435</v>
+      </c>
+      <c r="L202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="L202" s="1" t="n">
-        <v>0.0004436</v>
+      <c r="M202" s="1" t="n">
+        <v>0.0004435</v>
       </c>
     </row>
     <row r="203">
@@ -8569,10 +9178,13 @@
         <v>0.007317</v>
       </c>
       <c r="K203" s="1" t="n">
+        <v>0.007302</v>
+      </c>
+      <c r="L203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="L203" s="1" t="n">
-        <v>0.007312</v>
+      <c r="M203" s="1" t="n">
+        <v>0.007302</v>
       </c>
     </row>
     <row r="204">
@@ -8609,9 +9221,12 @@
         <v>0.1309</v>
       </c>
       <c r="K204" s="1" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="L204" s="1" t="n">
         <v>0.1314</v>
       </c>
-      <c r="L204" s="1" t="n">
+      <c r="M204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -8649,9 +9264,12 @@
         <v>0.01412</v>
       </c>
       <c r="K205" s="1" t="n">
+        <v>0.01417</v>
+      </c>
+      <c r="L205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="L205" s="1" t="n">
+      <c r="M205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -8689,9 +9307,12 @@
         <v>0.00359</v>
       </c>
       <c r="K206" s="1" t="n">
+        <v>0.003591</v>
+      </c>
+      <c r="L206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="L206" s="1" t="n">
+      <c r="M206" s="1" t="n">
         <v>0.003566</v>
       </c>
     </row>
@@ -8729,9 +9350,12 @@
         <v>0.05999</v>
       </c>
       <c r="K207" s="1" t="n">
+        <v>0.05992</v>
+      </c>
+      <c r="L207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="L207" s="1" t="n">
+      <c r="M207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -8772,6 +9396,9 @@
         <v>15.55</v>
       </c>
       <c r="L208" s="1" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="M208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -8809,9 +9436,12 @@
         <v>5191.1</v>
       </c>
       <c r="K209" s="1" t="n">
-        <v>5191.3</v>
+        <v>5192.8</v>
       </c>
       <c r="L209" s="1" t="n">
+        <v>5192.8</v>
+      </c>
+      <c r="M209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -8849,9 +9479,12 @@
         <v>0.11963</v>
       </c>
       <c r="K210" s="1" t="n">
-        <v>0.12042</v>
+        <v>0.12065</v>
       </c>
       <c r="L210" s="1" t="n">
+        <v>0.12065</v>
+      </c>
+      <c r="M210" s="1" t="n">
         <v>0.11963</v>
       </c>
     </row>
@@ -8889,10 +9522,13 @@
         <v>0.182</v>
       </c>
       <c r="K211" s="1" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="L211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="L211" s="1" t="n">
-        <v>0.182</v>
+      <c r="M211" s="1" t="n">
+        <v>0.1815</v>
       </c>
     </row>
     <row r="212">
@@ -8929,9 +9565,12 @@
         <v>0.0306</v>
       </c>
       <c r="K212" s="1" t="n">
-        <v>0.0306</v>
+        <v>0.0308</v>
       </c>
       <c r="L212" s="1" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="M212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -8969,9 +9608,12 @@
         <v>1.3938</v>
       </c>
       <c r="K213" s="1" t="n">
+        <v>1.3947</v>
+      </c>
+      <c r="L213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="L213" s="1" t="n">
+      <c r="M213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -9009,9 +9651,12 @@
         <v>0.05646</v>
       </c>
       <c r="K214" s="1" t="n">
+        <v>0.05649</v>
+      </c>
+      <c r="L214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="L214" s="1" t="n">
+      <c r="M214" s="1" t="n">
         <v>0.05646</v>
       </c>
     </row>
@@ -9049,9 +9694,12 @@
         <v>0.04413</v>
       </c>
       <c r="K215" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="L215" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="L215" s="1" t="n">
+      <c r="M215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -9089,9 +9737,12 @@
         <v>0.14904</v>
       </c>
       <c r="K216" s="1" t="n">
+        <v>0.14989</v>
+      </c>
+      <c r="L216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="L216" s="1" t="n">
+      <c r="M216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -9129,9 +9780,12 @@
         <v>0.074</v>
       </c>
       <c r="K217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="L217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="L217" s="1" t="n">
+      <c r="M217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -9169,9 +9823,12 @@
         <v>0.00268</v>
       </c>
       <c r="K218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="L218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="L218" s="1" t="n">
+      <c r="M218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -9209,9 +9866,12 @@
         <v>0.01718</v>
       </c>
       <c r="K219" s="1" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="L219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="L219" s="1" t="n">
+      <c r="M219" s="1" t="n">
         <v>0.01715</v>
       </c>
     </row>
@@ -9249,9 +9909,12 @@
         <v>0.05511</v>
       </c>
       <c r="K220" s="1" t="n">
+        <v>0.05522</v>
+      </c>
+      <c r="L220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="L220" s="1" t="n">
+      <c r="M220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -9289,9 +9952,12 @@
         <v>0.02196</v>
       </c>
       <c r="K221" s="1" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="L221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="L221" s="1" t="n">
+      <c r="M221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -9329,9 +9995,12 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="K222" s="1" t="n">
+        <v>0.009379999999999999</v>
+      </c>
+      <c r="L222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="L222" s="1" t="n">
+      <c r="M222" s="1" t="n">
         <v>0.009350000000000001</v>
       </c>
     </row>
@@ -9374,6 +10043,9 @@
       <c r="L223" s="1" t="n">
         <v>0.0164</v>
       </c>
+      <c r="M223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9409,9 +10081,12 @@
         <v>0.03833</v>
       </c>
       <c r="K224" s="1" t="n">
+        <v>0.03817</v>
+      </c>
+      <c r="L224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="L224" s="1" t="n">
+      <c r="M224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -9449,9 +10124,12 @@
         <v>0.001525</v>
       </c>
       <c r="K225" s="1" t="n">
+        <v>0.001526</v>
+      </c>
+      <c r="L225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="L225" s="1" t="n">
+      <c r="M225" s="1" t="n">
         <v>0.001525</v>
       </c>
     </row>
@@ -9489,9 +10167,12 @@
         <v>27.02</v>
       </c>
       <c r="K226" s="1" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="L226" s="1" t="n">
         <v>27.18</v>
       </c>
-      <c r="L226" s="1" t="n">
+      <c r="M226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -9529,9 +10210,12 @@
         <v>0.07088999999999999</v>
       </c>
       <c r="K227" s="1" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="L227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="L227" s="1" t="n">
+      <c r="M227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -9569,9 +10253,12 @@
         <v>0.3128</v>
       </c>
       <c r="K228" s="1" t="n">
-        <v>0.3131</v>
+        <v>0.314</v>
       </c>
       <c r="L228" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="M228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -9609,10 +10296,13 @@
         <v>18.38</v>
       </c>
       <c r="K229" s="1" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="L229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="L229" s="1" t="n">
-        <v>18.38</v>
+      <c r="M229" s="1" t="n">
+        <v>18.35</v>
       </c>
     </row>
     <row r="230">
@@ -9649,10 +10339,13 @@
         <v>0.01935</v>
       </c>
       <c r="K230" s="1" t="n">
+        <v>0.01926</v>
+      </c>
+      <c r="L230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="L230" s="1" t="n">
-        <v>0.01928</v>
+      <c r="M230" s="1" t="n">
+        <v>0.01926</v>
       </c>
     </row>
     <row r="231">
@@ -9689,10 +10382,13 @@
         <v>0.01218</v>
       </c>
       <c r="K231" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="L231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="L231" s="1" t="n">
-        <v>0.01218</v>
+      <c r="M231" s="1" t="n">
+        <v>0.01216</v>
       </c>
     </row>
     <row r="232">
@@ -9729,10 +10425,13 @@
         <v>0.2279</v>
       </c>
       <c r="K232" s="1" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="L232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="L232" s="1" t="n">
-        <v>0.2279</v>
+      <c r="M232" s="1" t="n">
+        <v>0.2274</v>
       </c>
     </row>
     <row r="233">
@@ -9769,9 +10468,12 @@
         <v>0.07108</v>
       </c>
       <c r="K233" s="1" t="n">
+        <v>0.07103</v>
+      </c>
+      <c r="L233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="L233" s="1" t="n">
+      <c r="M233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -9809,9 +10511,12 @@
         <v>0.1701</v>
       </c>
       <c r="K234" s="1" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="L234" s="1" t="n">
         <v>0.1704</v>
       </c>
-      <c r="L234" s="1" t="n">
+      <c r="M234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -9849,9 +10554,12 @@
         <v>0.0252</v>
       </c>
       <c r="K235" s="1" t="n">
-        <v>0.0253</v>
+        <v>0.0254</v>
       </c>
       <c r="L235" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="M235" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -9889,10 +10597,13 @@
         <v>0.03</v>
       </c>
       <c r="K236" s="1" t="n">
+        <v>0.02998</v>
+      </c>
+      <c r="L236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="L236" s="1" t="n">
-        <v>0.03</v>
+      <c r="M236" s="1" t="n">
+        <v>0.02998</v>
       </c>
     </row>
     <row r="237">
@@ -9929,10 +10640,13 @@
         <v>1.986</v>
       </c>
       <c r="K237" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L237" s="1" t="n">
         <v>1.993</v>
       </c>
-      <c r="L237" s="1" t="n">
-        <v>1.984</v>
+      <c r="M237" s="1" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="238">
@@ -9969,10 +10683,13 @@
         <v>0.4274</v>
       </c>
       <c r="K238" s="1" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="L238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="L238" s="1" t="n">
-        <v>0.4268</v>
+      <c r="M238" s="1" t="n">
+        <v>0.4263</v>
       </c>
     </row>
     <row r="239">
@@ -10009,9 +10726,12 @@
         <v>0.03344</v>
       </c>
       <c r="K239" s="1" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="L239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="L239" s="1" t="n">
+      <c r="M239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -10049,9 +10769,12 @@
         <v>0.03391</v>
       </c>
       <c r="K240" s="1" t="n">
+        <v>0.03401</v>
+      </c>
+      <c r="L240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="L240" s="1" t="n">
+      <c r="M240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -10089,9 +10812,12 @@
         <v>0.0007556</v>
       </c>
       <c r="K241" s="1" t="n">
+        <v>0.0007541</v>
+      </c>
+      <c r="L241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="L241" s="1" t="n">
+      <c r="M241" s="1" t="n">
         <v>0.0007509</v>
       </c>
     </row>
@@ -10129,9 +10855,12 @@
         <v>0.1847</v>
       </c>
       <c r="K242" s="1" t="n">
+        <v>0.1843</v>
+      </c>
+      <c r="L242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="L242" s="1" t="n">
+      <c r="M242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -10169,9 +10898,12 @@
         <v>0.014794</v>
       </c>
       <c r="K243" s="1" t="n">
+        <v>0.014798</v>
+      </c>
+      <c r="L243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="L243" s="1" t="n">
+      <c r="M243" s="1" t="n">
         <v>0.014772</v>
       </c>
     </row>
@@ -10209,9 +10941,12 @@
         <v>3.01e-05</v>
       </c>
       <c r="K244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="L244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="L244" s="1" t="n">
+      <c r="M244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -10249,10 +10984,13 @@
         <v>0.0352</v>
       </c>
       <c r="K245" s="1" t="n">
+        <v>0.03514</v>
+      </c>
+      <c r="L245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="L245" s="1" t="n">
-        <v>0.03516</v>
+      <c r="M245" s="1" t="n">
+        <v>0.03514</v>
       </c>
     </row>
     <row r="246">
@@ -10289,10 +11027,13 @@
         <v>0.08048</v>
       </c>
       <c r="K246" s="1" t="n">
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="L246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="L246" s="1" t="n">
-        <v>0.08039</v>
+      <c r="M246" s="1" t="n">
+        <v>0.08037999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -10329,9 +11070,12 @@
         <v>0.007343</v>
       </c>
       <c r="K247" s="1" t="n">
+        <v>0.007359</v>
+      </c>
+      <c r="L247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="L247" s="1" t="n">
+      <c r="M247" s="1" t="n">
         <v>0.00728</v>
       </c>
     </row>
@@ -10369,9 +11113,12 @@
         <v>0.09639</v>
       </c>
       <c r="K248" s="1" t="n">
+        <v>0.09596</v>
+      </c>
+      <c r="L248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="L248" s="1" t="n">
+      <c r="M248" s="1" t="n">
         <v>0.09499</v>
       </c>
     </row>
@@ -10412,6 +11159,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="L249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="M249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -10449,10 +11199,13 @@
         <v>0.035</v>
       </c>
       <c r="K250" s="1" t="n">
+        <v>0.03496</v>
+      </c>
+      <c r="L250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="L250" s="1" t="n">
-        <v>0.03498</v>
+      <c r="M250" s="1" t="n">
+        <v>0.03496</v>
       </c>
     </row>
     <row r="251">
@@ -10489,10 +11242,13 @@
         <v>0.04035</v>
       </c>
       <c r="K251" s="1" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="L251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="L251" s="1" t="n">
-        <v>0.04035</v>
+      <c r="M251" s="1" t="n">
+        <v>0.03953</v>
       </c>
     </row>
     <row r="252">
@@ -10529,9 +11285,12 @@
         <v>0.0896</v>
       </c>
       <c r="K252" s="1" t="n">
-        <v>0.0897</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L252" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="M252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -10569,9 +11328,12 @@
         <v>4.077</v>
       </c>
       <c r="K253" s="1" t="n">
+        <v>4.071</v>
+      </c>
+      <c r="L253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="L253" s="1" t="n">
+      <c r="M253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -10609,9 +11371,12 @@
         <v>0.1871</v>
       </c>
       <c r="K254" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="L254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="L254" s="1" t="n">
+      <c r="M254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -10649,9 +11414,12 @@
         <v>0.07235999999999999</v>
       </c>
       <c r="K255" s="1" t="n">
+        <v>0.07228</v>
+      </c>
+      <c r="L255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="L255" s="1" t="n">
+      <c r="M255" s="1" t="n">
         <v>0.07214</v>
       </c>
     </row>
@@ -10689,9 +11457,12 @@
         <v>0.01832</v>
       </c>
       <c r="K256" s="1" t="n">
+        <v>0.01828</v>
+      </c>
+      <c r="L256" s="1" t="n">
         <v>0.01833</v>
       </c>
-      <c r="L256" s="1" t="n">
+      <c r="M256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -10729,9 +11500,12 @@
         <v>5.942</v>
       </c>
       <c r="K257" s="1" t="n">
+        <v>5.944</v>
+      </c>
+      <c r="L257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="L257" s="1" t="n">
+      <c r="M257" s="1" t="n">
         <v>5.942</v>
       </c>
     </row>
@@ -10769,9 +11543,12 @@
         <v>0.2645</v>
       </c>
       <c r="K258" s="1" t="n">
-        <v>0.2645</v>
+        <v>0.2658</v>
       </c>
       <c r="L258" s="1" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="M258" s="1" t="n">
         <v>0.2617</v>
       </c>
     </row>
@@ -10809,10 +11586,13 @@
         <v>0.1363</v>
       </c>
       <c r="K259" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="L259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="L259" s="1" t="n">
-        <v>0.1361</v>
+      <c r="M259" s="1" t="n">
+        <v>0.136</v>
       </c>
     </row>
     <row r="260">
@@ -10849,9 +11629,12 @@
         <v>0.30664</v>
       </c>
       <c r="K260" s="1" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="L260" s="1" t="n">
         <v>0.30667</v>
       </c>
-      <c r="L260" s="1" t="n">
+      <c r="M260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -10889,9 +11672,12 @@
         <v>0.09873999999999999</v>
       </c>
       <c r="K261" s="1" t="n">
+        <v>0.09898</v>
+      </c>
+      <c r="L261" s="1" t="n">
         <v>0.099</v>
       </c>
-      <c r="L261" s="1" t="n">
+      <c r="M261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -10929,9 +11715,12 @@
         <v>0.5414</v>
       </c>
       <c r="K262" s="1" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="L262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="L262" s="1" t="n">
+      <c r="M262" s="1" t="n">
         <v>0.5409</v>
       </c>
     </row>
@@ -10969,9 +11758,12 @@
         <v>0.2917</v>
       </c>
       <c r="K263" s="1" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="L263" s="1" t="n">
         <v>0.293</v>
       </c>
-      <c r="L263" s="1" t="n">
+      <c r="M263" s="1" t="n">
         <v>0.2914</v>
       </c>
     </row>
@@ -11009,9 +11801,12 @@
         <v>0.96</v>
       </c>
       <c r="K264" s="1" t="n">
-        <v>0.96</v>
+        <v>0.964</v>
       </c>
       <c r="L264" s="1" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="M264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -11049,9 +11844,12 @@
         <v>0.5415</v>
       </c>
       <c r="K265" s="1" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="L265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="L265" s="1" t="n">
+      <c r="M265" s="1" t="n">
         <v>0.5403</v>
       </c>
     </row>
@@ -11089,9 +11887,12 @@
         <v>0.07381</v>
       </c>
       <c r="K266" s="1" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="L266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="L266" s="1" t="n">
+      <c r="M266" s="1" t="n">
         <v>0.07371</v>
       </c>
     </row>
@@ -11129,9 +11930,12 @@
         <v>0.02188</v>
       </c>
       <c r="K267" s="1" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="L267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="L267" s="1" t="n">
+      <c r="M267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -11169,9 +11973,12 @@
         <v>0.01624</v>
       </c>
       <c r="K268" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="L268" s="1" t="n">
         <v>0.01633</v>
       </c>
-      <c r="L268" s="1" t="n">
+      <c r="M268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -11209,9 +12016,12 @@
         <v>0.003765</v>
       </c>
       <c r="K269" s="1" t="n">
+        <v>0.003753</v>
+      </c>
+      <c r="L269" s="1" t="n">
         <v>0.003765</v>
       </c>
-      <c r="L269" s="1" t="n">
+      <c r="M269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -11249,10 +12059,13 @@
         <v>0.00764</v>
       </c>
       <c r="K270" s="1" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="L270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="L270" s="1" t="n">
-        <v>0.00764</v>
+      <c r="M270" s="1" t="n">
+        <v>0.00762</v>
       </c>
     </row>
     <row r="271">
@@ -11289,9 +12102,12 @@
         <v>0.05506</v>
       </c>
       <c r="K271" s="1" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="L271" s="1" t="n">
         <v>0.05512</v>
       </c>
-      <c r="L271" s="1" t="n">
+      <c r="M271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -11329,9 +12145,12 @@
         <v>2.306</v>
       </c>
       <c r="K272" s="1" t="n">
+        <v>2.303</v>
+      </c>
+      <c r="L272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="L272" s="1" t="n">
+      <c r="M272" s="1" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -11369,9 +12188,12 @@
         <v>0.05481</v>
       </c>
       <c r="K273" s="1" t="n">
-        <v>0.05481</v>
+        <v>0.05488</v>
       </c>
       <c r="L273" s="1" t="n">
+        <v>0.05488</v>
+      </c>
+      <c r="M273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -11409,9 +12231,12 @@
         <v>0.02298</v>
       </c>
       <c r="K274" s="1" t="n">
-        <v>0.02303</v>
+        <v>0.02312</v>
       </c>
       <c r="L274" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="M274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -11449,9 +12274,12 @@
         <v>1.184</v>
       </c>
       <c r="K275" s="1" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="L275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="L275" s="1" t="n">
+      <c r="M275" s="1" t="n">
         <v>1.182</v>
       </c>
     </row>
@@ -11489,9 +12317,12 @@
         <v>0.2727</v>
       </c>
       <c r="K276" s="1" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="L276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="L276" s="1" t="n">
+      <c r="M276" s="1" t="n">
         <v>0.2722</v>
       </c>
     </row>
@@ -11529,10 +12360,13 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="K277" s="1" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="L277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="L277" s="1" t="n">
-        <v>0.9419999999999999</v>
+      <c r="M277" s="1" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="278">
@@ -11569,9 +12403,12 @@
         <v>0.6294</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>0.6294</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="L278" s="1" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="M278" s="1" t="n">
         <v>0.6228</v>
       </c>
     </row>
@@ -11609,9 +12446,12 @@
         <v>0.001344</v>
       </c>
       <c r="K279" s="1" t="n">
+        <v>0.001347</v>
+      </c>
+      <c r="L279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="L279" s="1" t="n">
+      <c r="M279" s="1" t="n">
         <v>0.001344</v>
       </c>
     </row>
@@ -11649,9 +12489,12 @@
         <v>0.005563</v>
       </c>
       <c r="K280" s="1" t="n">
+        <v>0.005557</v>
+      </c>
+      <c r="L280" s="1" t="n">
         <v>0.005567</v>
       </c>
-      <c r="L280" s="1" t="n">
+      <c r="M280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -11689,9 +12532,12 @@
         <v>1.524</v>
       </c>
       <c r="K281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="L281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="L281" s="1" t="n">
+      <c r="M281" s="1" t="n">
         <v>1.521</v>
       </c>
     </row>
@@ -11729,9 +12575,12 @@
         <v>28.36</v>
       </c>
       <c r="K282" s="1" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="L282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="L282" s="1" t="n">
+      <c r="M282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -11769,10 +12618,13 @@
         <v>0.12875</v>
       </c>
       <c r="K283" s="1" t="n">
+        <v>0.12866</v>
+      </c>
+      <c r="L283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="L283" s="1" t="n">
-        <v>0.12875</v>
+      <c r="M283" s="1" t="n">
+        <v>0.12866</v>
       </c>
     </row>
     <row r="284">
@@ -11809,9 +12661,12 @@
         <v>0.01115</v>
       </c>
       <c r="K284" s="1" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="L284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="L284" s="1" t="n">
+      <c r="M284" s="1" t="n">
         <v>0.01111</v>
       </c>
     </row>
@@ -11849,9 +12704,12 @@
         <v>6.577</v>
       </c>
       <c r="K285" s="1" t="n">
+        <v>6.575</v>
+      </c>
+      <c r="L285" s="1" t="n">
         <v>6.577</v>
       </c>
-      <c r="L285" s="1" t="n">
+      <c r="M285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -11889,10 +12747,13 @@
         <v>0.01848</v>
       </c>
       <c r="K286" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="L286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="L286" s="1" t="n">
-        <v>0.01848</v>
+      <c r="M286" s="1" t="n">
+        <v>0.01844</v>
       </c>
     </row>
     <row r="287">
@@ -11929,9 +12790,12 @@
         <v>0.008378</v>
       </c>
       <c r="K287" s="1" t="n">
+        <v>0.008385</v>
+      </c>
+      <c r="L287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="L287" s="1" t="n">
+      <c r="M287" s="1" t="n">
         <v>0.008378</v>
       </c>
     </row>
@@ -11969,9 +12833,12 @@
         <v>0.3887</v>
       </c>
       <c r="K288" s="1" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="L288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="L288" s="1" t="n">
+      <c r="M288" s="1" t="n">
         <v>0.3846</v>
       </c>
     </row>
@@ -12009,10 +12876,13 @@
         <v>0.010093</v>
       </c>
       <c r="K289" s="1" t="n">
+        <v>0.010005</v>
+      </c>
+      <c r="L289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="L289" s="1" t="n">
-        <v>0.01008</v>
+      <c r="M289" s="1" t="n">
+        <v>0.010005</v>
       </c>
     </row>
     <row r="290">
@@ -12049,10 +12919,13 @@
         <v>0.02595</v>
       </c>
       <c r="K290" s="1" t="n">
+        <v>0.02591</v>
+      </c>
+      <c r="L290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="L290" s="1" t="n">
-        <v>0.02595</v>
+      <c r="M290" s="1" t="n">
+        <v>0.02591</v>
       </c>
     </row>
     <row r="291">
@@ -12089,10 +12962,13 @@
         <v>0.096</v>
       </c>
       <c r="K291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="L291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="L291" s="1" t="n">
-        <v>0.096</v>
+      <c r="M291" s="1" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="292">
@@ -12129,9 +13005,12 @@
         <v>0.28576</v>
       </c>
       <c r="K292" s="1" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="L292" s="1" t="n">
         <v>0.28632</v>
       </c>
-      <c r="L292" s="1" t="n">
+      <c r="M292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -12169,9 +13048,12 @@
         <v>0.01537</v>
       </c>
       <c r="K293" s="1" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="L293" s="1" t="n">
         <v>0.01548</v>
       </c>
-      <c r="L293" s="1" t="n">
+      <c r="M293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -12209,9 +13091,12 @@
         <v>0.003465</v>
       </c>
       <c r="K294" s="1" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="L294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="L294" s="1" t="n">
+      <c r="M294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -12249,10 +13134,13 @@
         <v>0.04285</v>
       </c>
       <c r="K295" s="1" t="n">
+        <v>0.042792</v>
+      </c>
+      <c r="L295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="L295" s="1" t="n">
-        <v>0.04285</v>
+      <c r="M295" s="1" t="n">
+        <v>0.042792</v>
       </c>
     </row>
     <row r="296">
@@ -12289,9 +13177,12 @@
         <v>0.03055</v>
       </c>
       <c r="K296" s="1" t="n">
+        <v>0.02982</v>
+      </c>
+      <c r="L296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="L296" s="1" t="n">
+      <c r="M296" s="1" t="n">
         <v>0.02929</v>
       </c>
     </row>
@@ -12329,9 +13220,12 @@
         <v>0.03773</v>
       </c>
       <c r="K297" s="1" t="n">
+        <v>0.03799</v>
+      </c>
+      <c r="L297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="L297" s="1" t="n">
+      <c r="M297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -12369,9 +13263,12 @@
         <v>0.08345</v>
       </c>
       <c r="K298" s="1" t="n">
-        <v>0.08359</v>
+        <v>0.08407000000000001</v>
       </c>
       <c r="L298" s="1" t="n">
+        <v>0.08407000000000001</v>
+      </c>
+      <c r="M298" s="1" t="n">
         <v>0.08305999999999999</v>
       </c>
     </row>
@@ -12409,9 +13306,12 @@
         <v>0.00777</v>
       </c>
       <c r="K299" s="1" t="n">
-        <v>0.00777</v>
+        <v>0.00779</v>
       </c>
       <c r="L299" s="1" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="M299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -12449,9 +13349,12 @@
         <v>0.01513</v>
       </c>
       <c r="K300" s="1" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="L300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="L300" s="1" t="n">
+      <c r="M300" s="1" t="n">
         <v>0.01512</v>
       </c>
     </row>
@@ -12489,9 +13392,12 @@
         <v>0.1418</v>
       </c>
       <c r="K301" s="1" t="n">
+        <v>0.1411</v>
+      </c>
+      <c r="L301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="L301" s="1" t="n">
+      <c r="M301" s="1" t="n">
         <v>0.141</v>
       </c>
     </row>
@@ -12529,9 +13435,12 @@
         <v>0.0006348</v>
       </c>
       <c r="K302" s="1" t="n">
+        <v>0.0006349</v>
+      </c>
+      <c r="L302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="L302" s="1" t="n">
+      <c r="M302" s="1" t="n">
         <v>0.0006284</v>
       </c>
     </row>
@@ -12569,9 +13478,12 @@
         <v>0.06224</v>
       </c>
       <c r="K303" s="1" t="n">
+        <v>0.06223</v>
+      </c>
+      <c r="L303" s="1" t="n">
         <v>0.06235</v>
       </c>
-      <c r="L303" s="1" t="n">
+      <c r="M303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -12609,9 +13521,12 @@
         <v>0.000164</v>
       </c>
       <c r="K304" s="1" t="n">
+        <v>0.0001635</v>
+      </c>
+      <c r="L304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="L304" s="1" t="n">
+      <c r="M304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -12649,9 +13564,12 @@
         <v>0.06148</v>
       </c>
       <c r="K305" s="1" t="n">
+        <v>0.06139</v>
+      </c>
+      <c r="L305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="L305" s="1" t="n">
+      <c r="M305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -12689,9 +13607,12 @@
         <v>0.022311</v>
       </c>
       <c r="K306" s="1" t="n">
+        <v>0.022229</v>
+      </c>
+      <c r="L306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="L306" s="1" t="n">
+      <c r="M306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -12729,9 +13650,12 @@
         <v>0.02381</v>
       </c>
       <c r="K307" s="1" t="n">
+        <v>0.02365</v>
+      </c>
+      <c r="L307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="L307" s="1" t="n">
+      <c r="M307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -12769,9 +13693,12 @@
         <v>0.000411</v>
       </c>
       <c r="K308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="L308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="L308" s="1" t="n">
+      <c r="M308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -12812,6 +13739,9 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="L309" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="M309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -12849,9 +13779,12 @@
         <v>0.3835</v>
       </c>
       <c r="K310" s="1" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="L310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="L310" s="1" t="n">
+      <c r="M310" s="1" t="n">
         <v>0.3831</v>
       </c>
     </row>
@@ -12889,9 +13822,12 @@
         <v>0.0356</v>
       </c>
       <c r="K311" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="L311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="L311" s="1" t="n">
+      <c r="M311" s="1" t="n">
         <v>0.0355</v>
       </c>
     </row>
@@ -12929,9 +13865,12 @@
         <v>0.02457</v>
       </c>
       <c r="K312" s="1" t="n">
+        <v>0.02452</v>
+      </c>
+      <c r="L312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="L312" s="1" t="n">
+      <c r="M312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -12969,9 +13908,12 @@
         <v>0.04138</v>
       </c>
       <c r="K313" s="1" t="n">
+        <v>0.04132</v>
+      </c>
+      <c r="L313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="L313" s="1" t="n">
+      <c r="M313" s="1" t="n">
         <v>0.04129</v>
       </c>
     </row>
@@ -13009,9 +13951,12 @@
         <v>4.005</v>
       </c>
       <c r="K314" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="L314" s="1" t="n">
+      <c r="M314" s="1" t="n">
         <v>3.998</v>
       </c>
     </row>
@@ -13049,9 +13994,12 @@
         <v>0.1602</v>
       </c>
       <c r="K315" s="1" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="L315" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="L315" s="1" t="n">
+      <c r="M315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -13089,9 +14037,12 @@
         <v>0.08838</v>
       </c>
       <c r="K316" s="1" t="n">
-        <v>0.08884</v>
+        <v>0.08977</v>
       </c>
       <c r="L316" s="1" t="n">
+        <v>0.08977</v>
+      </c>
+      <c r="M316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -13129,9 +14080,12 @@
         <v>0.0687</v>
       </c>
       <c r="K317" s="1" t="n">
+        <v>0.06852999999999999</v>
+      </c>
+      <c r="L317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="L317" s="1" t="n">
+      <c r="M317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -13169,10 +14123,13 @@
         <v>0.012497</v>
       </c>
       <c r="K318" s="1" t="n">
+        <v>0.012426</v>
+      </c>
+      <c r="L318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="L318" s="1" t="n">
-        <v>0.012463</v>
+      <c r="M318" s="1" t="n">
+        <v>0.012426</v>
       </c>
     </row>
     <row r="319">
@@ -13209,9 +14166,12 @@
         <v>0.001137</v>
       </c>
       <c r="K319" s="1" t="n">
+        <v>0.001137</v>
+      </c>
+      <c r="L319" s="1" t="n">
         <v>0.001138</v>
       </c>
-      <c r="L319" s="1" t="n">
+      <c r="M319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -13249,10 +14209,13 @@
         <v>0.0631</v>
       </c>
       <c r="K320" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="L320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="L320" s="1" t="n">
-        <v>0.063</v>
+      <c r="M320" s="1" t="n">
+        <v>0.0629</v>
       </c>
     </row>
     <row r="321">
@@ -13292,6 +14255,9 @@
         <v>0.00527</v>
       </c>
       <c r="L321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="M321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -13329,10 +14295,13 @@
         <v>0.1115</v>
       </c>
       <c r="K322" s="1" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="L322" s="1" t="n">
         <v>0.1116</v>
       </c>
-      <c r="L322" s="1" t="n">
-        <v>0.1114</v>
+      <c r="M322" s="1" t="n">
+        <v>0.1113</v>
       </c>
     </row>
     <row r="323">
@@ -13372,6 +14341,9 @@
         <v>0.04304</v>
       </c>
       <c r="L323" s="1" t="n">
+        <v>0.04304</v>
+      </c>
+      <c r="M323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -13409,10 +14381,13 @@
         <v>0.01776</v>
       </c>
       <c r="K324" s="1" t="n">
+        <v>0.01767</v>
+      </c>
+      <c r="L324" s="1" t="n">
         <v>0.0179</v>
       </c>
-      <c r="L324" s="1" t="n">
-        <v>0.01768</v>
+      <c r="M324" s="1" t="n">
+        <v>0.01767</v>
       </c>
     </row>
     <row r="325">
@@ -13449,9 +14424,12 @@
         <v>0.005666</v>
       </c>
       <c r="K325" s="1" t="n">
+        <v>0.005672</v>
+      </c>
+      <c r="L325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="L325" s="1" t="n">
+      <c r="M325" s="1" t="n">
         <v>0.005663</v>
       </c>
     </row>
@@ -13489,9 +14467,12 @@
         <v>0.001775</v>
       </c>
       <c r="K326" s="1" t="n">
+        <v>0.001776</v>
+      </c>
+      <c r="L326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="L326" s="1" t="n">
+      <c r="M326" s="1" t="n">
         <v>0.001765</v>
       </c>
     </row>
@@ -13529,9 +14510,12 @@
         <v>0.04049</v>
       </c>
       <c r="K327" s="1" t="n">
+        <v>0.04049</v>
+      </c>
+      <c r="L327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="L327" s="1" t="n">
+      <c r="M327" s="1" t="n">
         <v>0.04047</v>
       </c>
     </row>
@@ -13569,10 +14553,13 @@
         <v>0.053612</v>
       </c>
       <c r="K328" s="1" t="n">
+        <v>0.053576</v>
+      </c>
+      <c r="L328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="L328" s="1" t="n">
-        <v>0.053612</v>
+      <c r="M328" s="1" t="n">
+        <v>0.053576</v>
       </c>
     </row>
     <row r="329">
@@ -13609,9 +14596,12 @@
         <v>0.2785</v>
       </c>
       <c r="K329" s="1" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="L329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="L329" s="1" t="n">
+      <c r="M329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -13649,9 +14639,12 @@
         <v>0.1587</v>
       </c>
       <c r="K330" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="L330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="L330" s="1" t="n">
+      <c r="M330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -13689,9 +14682,12 @@
         <v>0.05364</v>
       </c>
       <c r="K331" s="1" t="n">
-        <v>0.05364</v>
+        <v>0.05368</v>
       </c>
       <c r="L331" s="1" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="M331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -13729,9 +14725,12 @@
         <v>0.3624</v>
       </c>
       <c r="K332" s="1" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="L332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="L332" s="1" t="n">
+      <c r="M332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -13769,9 +14768,12 @@
         <v>0.03043</v>
       </c>
       <c r="K333" s="1" t="n">
-        <v>0.03049</v>
+        <v>0.03051</v>
       </c>
       <c r="L333" s="1" t="n">
+        <v>0.03051</v>
+      </c>
+      <c r="M333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -13809,9 +14811,12 @@
         <v>0.0183</v>
       </c>
       <c r="K334" s="1" t="n">
+        <v>0.01796</v>
+      </c>
+      <c r="L334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="L334" s="1" t="n">
+      <c r="M334" s="1" t="n">
         <v>0.01756</v>
       </c>
     </row>
@@ -13849,9 +14854,12 @@
         <v>0.058</v>
       </c>
       <c r="K335" s="1" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="L335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="L335" s="1" t="n">
+      <c r="M335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -13889,9 +14897,12 @@
         <v>0.09197</v>
       </c>
       <c r="K336" s="1" t="n">
+        <v>0.09132999999999999</v>
+      </c>
+      <c r="L336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="L336" s="1" t="n">
+      <c r="M336" s="1" t="n">
         <v>0.09117</v>
       </c>
     </row>
@@ -13929,9 +14940,12 @@
         <v>0.17837</v>
       </c>
       <c r="K337" s="1" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="L337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="L337" s="1" t="n">
+      <c r="M337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -13969,10 +14983,13 @@
         <v>0.02096</v>
       </c>
       <c r="K338" s="1" t="n">
+        <v>0.02092</v>
+      </c>
+      <c r="L338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="L338" s="1" t="n">
-        <v>0.02096</v>
+      <c r="M338" s="1" t="n">
+        <v>0.02092</v>
       </c>
     </row>
     <row r="339">
@@ -14009,9 +15026,12 @@
         <v>0.1318</v>
       </c>
       <c r="K339" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="L339" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="L339" s="1" t="n">
+      <c r="M339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -14049,9 +15069,12 @@
         <v>0.007929</v>
       </c>
       <c r="K340" s="1" t="n">
+        <v>0.007929</v>
+      </c>
+      <c r="L340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="L340" s="1" t="n">
+      <c r="M340" s="1" t="n">
         <v>0.007929</v>
       </c>
     </row>
@@ -14089,9 +15112,12 @@
         <v>4.387</v>
       </c>
       <c r="K341" s="1" t="n">
+        <v>4.391</v>
+      </c>
+      <c r="L341" s="1" t="n">
         <v>4.407</v>
       </c>
-      <c r="L341" s="1" t="n">
+      <c r="M341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -14129,9 +15155,12 @@
         <v>0.1889</v>
       </c>
       <c r="K342" s="1" t="n">
+        <v>0.18973</v>
+      </c>
+      <c r="L342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="L342" s="1" t="n">
+      <c r="M342" s="1" t="n">
         <v>0.1889</v>
       </c>
     </row>
@@ -14169,9 +15198,12 @@
         <v>0.08366</v>
       </c>
       <c r="K343" s="1" t="n">
-        <v>0.08366</v>
+        <v>0.08373999999999999</v>
       </c>
       <c r="L343" s="1" t="n">
+        <v>0.08373999999999999</v>
+      </c>
+      <c r="M343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -14209,9 +15241,12 @@
         <v>0.1826</v>
       </c>
       <c r="K344" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="L344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="L344" s="1" t="n">
+      <c r="M344" s="1" t="n">
         <v>0.1821</v>
       </c>
     </row>
@@ -14249,10 +15284,13 @@
         <v>0.003249</v>
       </c>
       <c r="K345" s="1" t="n">
+        <v>0.003244</v>
+      </c>
+      <c r="L345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="L345" s="1" t="n">
-        <v>0.003245</v>
+      <c r="M345" s="1" t="n">
+        <v>0.003244</v>
       </c>
     </row>
     <row r="346">
@@ -14289,9 +15327,12 @@
         <v>0.09188</v>
       </c>
       <c r="K346" s="1" t="n">
+        <v>0.09163</v>
+      </c>
+      <c r="L346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="L346" s="1" t="n">
+      <c r="M346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -14329,10 +15370,13 @@
         <v>2.244</v>
       </c>
       <c r="K347" s="1" t="n">
+        <v>2.243</v>
+      </c>
+      <c r="L347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="L347" s="1" t="n">
-        <v>2.244</v>
+      <c r="M347" s="1" t="n">
+        <v>2.243</v>
       </c>
     </row>
     <row r="348">
@@ -14369,9 +15413,12 @@
         <v>0.3058</v>
       </c>
       <c r="K348" s="1" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="L348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="L348" s="1" t="n">
+      <c r="M348" s="1" t="n">
         <v>0.3038</v>
       </c>
     </row>
@@ -14409,9 +15456,12 @@
         <v>0.02975</v>
       </c>
       <c r="K349" s="1" t="n">
+        <v>0.02979</v>
+      </c>
+      <c r="L349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="L349" s="1" t="n">
+      <c r="M349" s="1" t="n">
         <v>0.02975</v>
       </c>
     </row>
@@ -14449,9 +15499,12 @@
         <v>0.1278</v>
       </c>
       <c r="K350" s="1" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="L350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="L350" s="1" t="n">
+      <c r="M350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -14489,9 +15542,12 @@
         <v>0.06707</v>
       </c>
       <c r="K351" s="1" t="n">
+        <v>0.06698999999999999</v>
+      </c>
+      <c r="L351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="L351" s="1" t="n">
+      <c r="M351" s="1" t="n">
         <v>0.06689000000000001</v>
       </c>
     </row>
@@ -14529,9 +15585,12 @@
         <v>0.0625</v>
       </c>
       <c r="K352" s="1" t="n">
-        <v>0.06251</v>
+        <v>0.06252000000000001</v>
       </c>
       <c r="L352" s="1" t="n">
+        <v>0.06252000000000001</v>
+      </c>
+      <c r="M352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -14569,9 +15628,12 @@
         <v>0.06362</v>
       </c>
       <c r="K353" s="1" t="n">
+        <v>0.06353</v>
+      </c>
+      <c r="L353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="L353" s="1" t="n">
+      <c r="M353" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -14609,9 +15671,12 @@
         <v>0.10547</v>
       </c>
       <c r="K354" s="1" t="n">
+        <v>0.10501</v>
+      </c>
+      <c r="L354" s="1" t="n">
         <v>0.10603</v>
       </c>
-      <c r="L354" s="1" t="n">
+      <c r="M354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -14649,9 +15714,12 @@
         <v>0.0901</v>
       </c>
       <c r="K355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="L355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="L355" s="1" t="n">
+      <c r="M355" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -14689,9 +15757,12 @@
         <v>0.07055</v>
       </c>
       <c r="K356" s="1" t="n">
+        <v>0.07041</v>
+      </c>
+      <c r="L356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="L356" s="1" t="n">
+      <c r="M356" s="1" t="n">
         <v>0.06985</v>
       </c>
     </row>
@@ -14729,9 +15800,12 @@
         <v>0.4529</v>
       </c>
       <c r="K357" s="1" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="L357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="L357" s="1" t="n">
+      <c r="M357" s="1" t="n">
         <v>0.4521</v>
       </c>
     </row>
@@ -14769,9 +15843,12 @@
         <v>0.03519</v>
       </c>
       <c r="K358" s="1" t="n">
+        <v>0.03523</v>
+      </c>
+      <c r="L358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="L358" s="1" t="n">
+      <c r="M358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -14809,9 +15886,12 @@
         <v>0.01483</v>
       </c>
       <c r="K359" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="L359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="L359" s="1" t="n">
+      <c r="M359" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -14849,9 +15929,12 @@
         <v>0.13351</v>
       </c>
       <c r="K360" s="1" t="n">
+        <v>0.13355</v>
+      </c>
+      <c r="L360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="L360" s="1" t="n">
+      <c r="M360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -14889,9 +15972,12 @@
         <v>0.0005886</v>
       </c>
       <c r="K361" s="1" t="n">
+        <v>0.0005872</v>
+      </c>
+      <c r="L361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="L361" s="1" t="n">
+      <c r="M361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -14929,9 +16015,12 @@
         <v>0.03879</v>
       </c>
       <c r="K362" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="L362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="L362" s="1" t="n">
+      <c r="M362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -14969,9 +16058,12 @@
         <v>3.213</v>
       </c>
       <c r="K363" s="1" t="n">
+        <v>3.213</v>
+      </c>
+      <c r="L363" s="1" t="n">
         <v>3.223</v>
       </c>
-      <c r="L363" s="1" t="n">
+      <c r="M363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -15009,10 +16101,13 @@
         <v>0.1652</v>
       </c>
       <c r="K364" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="L364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="L364" s="1" t="n">
-        <v>0.1652</v>
+      <c r="M364" s="1" t="n">
+        <v>0.165</v>
       </c>
     </row>
     <row r="365">
@@ -15052,6 +16147,9 @@
         <v>0.1137</v>
       </c>
       <c r="L365" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="M365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -15089,9 +16187,12 @@
         <v>0.0006409</v>
       </c>
       <c r="K366" s="1" t="n">
+        <v>0.0006415</v>
+      </c>
+      <c r="L366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="L366" s="1" t="n">
+      <c r="M366" s="1" t="n">
         <v>0.0006409</v>
       </c>
     </row>
@@ -15129,9 +16230,12 @@
         <v>0.05951</v>
       </c>
       <c r="K367" s="1" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="L367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="L367" s="1" t="n">
+      <c r="M367" s="1" t="n">
         <v>0.05927</v>
       </c>
     </row>
@@ -15169,10 +16273,13 @@
         <v>0.08234</v>
       </c>
       <c r="K368" s="1" t="n">
+        <v>0.08219</v>
+      </c>
+      <c r="L368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="L368" s="1" t="n">
-        <v>0.08234</v>
+      <c r="M368" s="1" t="n">
+        <v>0.08219</v>
       </c>
     </row>
     <row r="369">
@@ -15209,9 +16316,12 @@
         <v>0.0412</v>
       </c>
       <c r="K369" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="L369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="L369" s="1" t="n">
+      <c r="M369" s="1" t="n">
         <v>0.03976</v>
       </c>
     </row>
@@ -15249,10 +16359,13 @@
         <v>3.703</v>
       </c>
       <c r="K370" s="1" t="n">
+        <v>3.695</v>
+      </c>
+      <c r="L370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="L370" s="1" t="n">
-        <v>3.703</v>
+      <c r="M370" s="1" t="n">
+        <v>3.695</v>
       </c>
     </row>
     <row r="371">
@@ -15289,9 +16402,12 @@
         <v>0.1223</v>
       </c>
       <c r="K371" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="L371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="L371" s="1" t="n">
+      <c r="M371" s="1" t="n">
         <v>0.1216</v>
       </c>
     </row>
@@ -15329,9 +16445,12 @@
         <v>0.01481</v>
       </c>
       <c r="K372" s="1" t="n">
-        <v>0.01481</v>
+        <v>0.01482</v>
       </c>
       <c r="L372" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="M372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -15369,9 +16488,12 @@
         <v>0.02196</v>
       </c>
       <c r="K373" s="1" t="n">
+        <v>0.02194</v>
+      </c>
+      <c r="L373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="L373" s="1" t="n">
+      <c r="M373" s="1" t="n">
         <v>0.02192</v>
       </c>
     </row>
@@ -15409,9 +16531,12 @@
         <v>1.8633</v>
       </c>
       <c r="K374" s="1" t="n">
-        <v>1.8633</v>
+        <v>1.8671</v>
       </c>
       <c r="L374" s="1" t="n">
+        <v>1.8671</v>
+      </c>
+      <c r="M374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -15449,9 +16574,12 @@
         <v>0.02105</v>
       </c>
       <c r="K375" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="L375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="L375" s="1" t="n">
+      <c r="M375" s="1" t="n">
         <v>0.02095</v>
       </c>
     </row>
@@ -15489,9 +16617,12 @@
         <v>1.326</v>
       </c>
       <c r="K376" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="L376" s="1" t="n">
+      <c r="M376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -15529,10 +16660,13 @@
         <v>0.2831</v>
       </c>
       <c r="K377" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="L377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="L377" s="1" t="n">
-        <v>0.2829</v>
+      <c r="M377" s="1" t="n">
+        <v>0.2826</v>
       </c>
     </row>
     <row r="378">
@@ -15569,9 +16703,12 @@
         <v>0.01553</v>
       </c>
       <c r="K378" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="L378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="L378" s="1" t="n">
+      <c r="M378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -15609,9 +16746,12 @@
         <v>1.5361</v>
       </c>
       <c r="K379" s="1" t="n">
+        <v>1.5362</v>
+      </c>
+      <c r="L379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="L379" s="1" t="n">
+      <c r="M379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -15649,10 +16789,13 @@
         <v>6.923999999999999e-05</v>
       </c>
       <c r="K380" s="1" t="n">
+        <v>6.918e-05</v>
+      </c>
+      <c r="L380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="L380" s="1" t="n">
-        <v>6.923999999999999e-05</v>
+      <c r="M380" s="1" t="n">
+        <v>6.918e-05</v>
       </c>
     </row>
     <row r="381">
@@ -15689,9 +16832,12 @@
         <v>2.545</v>
       </c>
       <c r="K381" s="1" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="L381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="L381" s="1" t="n">
+      <c r="M381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -15729,10 +16875,13 @@
         <v>0.06736</v>
       </c>
       <c r="K382" s="1" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="L382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="L382" s="1" t="n">
-        <v>0.06736</v>
+      <c r="M382" s="1" t="n">
+        <v>0.0673</v>
       </c>
     </row>
     <row r="383">
@@ -15769,9 +16918,12 @@
         <v>0.01985</v>
       </c>
       <c r="K383" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="L383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="L383" s="1" t="n">
+      <c r="M383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -15809,9 +16961,12 @@
         <v>0.05334</v>
       </c>
       <c r="K384" s="1" t="n">
+        <v>0.05224</v>
+      </c>
+      <c r="L384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="L384" s="1" t="n">
+      <c r="M384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -15849,9 +17004,12 @@
         <v>7.591</v>
       </c>
       <c r="K385" s="1" t="n">
+        <v>7.585</v>
+      </c>
+      <c r="L385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="L385" s="1" t="n">
+      <c r="M385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -15889,9 +17047,12 @@
         <v>0.003299</v>
       </c>
       <c r="K386" s="1" t="n">
+        <v>0.003296</v>
+      </c>
+      <c r="L386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="L386" s="1" t="n">
+      <c r="M386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -15929,10 +17090,13 @@
         <v>0.000382</v>
       </c>
       <c r="K387" s="1" t="n">
+        <v>0.0003818</v>
+      </c>
+      <c r="L387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="L387" s="1" t="n">
-        <v>0.000382</v>
+      <c r="M387" s="1" t="n">
+        <v>0.0003818</v>
       </c>
     </row>
     <row r="388">
@@ -15969,10 +17133,13 @@
         <v>0.009650000000000001</v>
       </c>
       <c r="K388" s="1" t="n">
+        <v>0.009549999999999999</v>
+      </c>
+      <c r="L388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="L388" s="1" t="n">
-        <v>0.00962</v>
+      <c r="M388" s="1" t="n">
+        <v>0.009549999999999999</v>
       </c>
     </row>
     <row r="389">
@@ -16009,9 +17176,12 @@
         <v>0.2894</v>
       </c>
       <c r="K389" s="1" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="L389" s="1" t="n">
         <v>0.2902</v>
       </c>
-      <c r="L389" s="1" t="n">
+      <c r="M389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -16052,6 +17222,9 @@
         <v>0.025</v>
       </c>
       <c r="L390" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -16089,9 +17262,12 @@
         <v>2.815</v>
       </c>
       <c r="K391" s="1" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="L391" s="1" t="n">
         <v>2.833</v>
       </c>
-      <c r="L391" s="1" t="n">
+      <c r="M391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -16129,9 +17305,12 @@
         <v>0.01343</v>
       </c>
       <c r="K392" s="1" t="n">
+        <v>0.01346</v>
+      </c>
+      <c r="L392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="L392" s="1" t="n">
+      <c r="M392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -16172,6 +17351,9 @@
         <v>0.00236</v>
       </c>
       <c r="L393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="M393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -16209,9 +17391,12 @@
         <v>0.05936</v>
       </c>
       <c r="K394" s="1" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="L394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="L394" s="1" t="n">
+      <c r="M394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -16249,9 +17434,12 @@
         <v>0.0403</v>
       </c>
       <c r="K395" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="L395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="L395" s="1" t="n">
+      <c r="M395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -16289,9 +17477,12 @@
         <v>0.09272</v>
       </c>
       <c r="K396" s="1" t="n">
+        <v>0.09243999999999999</v>
+      </c>
+      <c r="L396" s="1" t="n">
         <v>0.09272</v>
       </c>
-      <c r="L396" s="1" t="n">
+      <c r="M396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -16329,9 +17520,12 @@
         <v>0.1519</v>
       </c>
       <c r="K397" s="1" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="L397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="L397" s="1" t="n">
+      <c r="M397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -16369,9 +17563,12 @@
         <v>0.927</v>
       </c>
       <c r="K398" s="1" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="L398" s="1" t="n">
         <v>0.929</v>
       </c>
-      <c r="L398" s="1" t="n">
+      <c r="M398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -16409,9 +17606,12 @@
         <v>0.05244</v>
       </c>
       <c r="K399" s="1" t="n">
+        <v>0.05245</v>
+      </c>
+      <c r="L399" s="1" t="n">
         <v>0.05254</v>
       </c>
-      <c r="L399" s="1" t="n">
+      <c r="M399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -16449,9 +17649,12 @@
         <v>2.519</v>
       </c>
       <c r="K400" s="1" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="L400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="L400" s="1" t="n">
+      <c r="M400" s="1" t="n">
         <v>2.517</v>
       </c>
     </row>
@@ -16489,9 +17692,12 @@
         <v>0.01806</v>
       </c>
       <c r="K401" s="1" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="L401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="L401" s="1" t="n">
+      <c r="M401" s="1" t="n">
         <v>0.01788</v>
       </c>
     </row>
@@ -16529,9 +17735,12 @@
         <v>0.08067000000000001</v>
       </c>
       <c r="K402" s="1" t="n">
+        <v>0.08078</v>
+      </c>
+      <c r="L402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="L402" s="1" t="n">
+      <c r="M402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -16569,10 +17778,13 @@
         <v>1.2456</v>
       </c>
       <c r="K403" s="1" t="n">
+        <v>1.2455</v>
+      </c>
+      <c r="L403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="L403" s="1" t="n">
-        <v>1.2456</v>
+      <c r="M403" s="1" t="n">
+        <v>1.2455</v>
       </c>
     </row>
     <row r="404">
@@ -16609,9 +17821,12 @@
         <v>0.00717</v>
       </c>
       <c r="K404" s="1" t="n">
+        <v>0.00716</v>
+      </c>
+      <c r="L404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="L404" s="1" t="n">
+      <c r="M404" s="1" t="n">
         <v>0.00715</v>
       </c>
     </row>
@@ -16649,9 +17864,12 @@
         <v>0.4987</v>
       </c>
       <c r="K405" s="1" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="L405" s="1" t="n">
         <v>0.5004999999999999</v>
       </c>
-      <c r="L405" s="1" t="n">
+      <c r="M405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -16689,9 +17907,12 @@
         <v>0.0115</v>
       </c>
       <c r="K406" s="1" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="L406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="L406" s="1" t="n">
+      <c r="M406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -16729,10 +17950,13 @@
         <v>0.04614</v>
       </c>
       <c r="K407" s="1" t="n">
+        <v>0.04612</v>
+      </c>
+      <c r="L407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="L407" s="1" t="n">
-        <v>0.04614</v>
+      <c r="M407" s="1" t="n">
+        <v>0.04612</v>
       </c>
     </row>
     <row r="408">
@@ -16769,10 +17993,13 @@
         <v>0.03943</v>
       </c>
       <c r="K408" s="1" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="L408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="L408" s="1" t="n">
-        <v>0.03943</v>
+      <c r="M408" s="1" t="n">
+        <v>0.0394</v>
       </c>
     </row>
     <row r="409">
@@ -16809,9 +18036,12 @@
         <v>0.05234</v>
       </c>
       <c r="K409" s="1" t="n">
+        <v>0.05234</v>
+      </c>
+      <c r="L409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="L409" s="1" t="n">
+      <c r="M409" s="1" t="n">
         <v>0.05234</v>
       </c>
     </row>
@@ -16849,10 +18079,13 @@
         <v>0.01246</v>
       </c>
       <c r="K410" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="L410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="L410" s="1" t="n">
-        <v>0.01245</v>
+      <c r="M410" s="1" t="n">
+        <v>0.01237</v>
       </c>
     </row>
     <row r="411">
@@ -16889,9 +18122,12 @@
         <v>0.06365</v>
       </c>
       <c r="K411" s="1" t="n">
+        <v>0.06367</v>
+      </c>
+      <c r="L411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="L411" s="1" t="n">
+      <c r="M411" s="1" t="n">
         <v>0.06347</v>
       </c>
     </row>
@@ -16929,9 +18165,12 @@
         <v>0.04135</v>
       </c>
       <c r="K412" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="L412" s="1" t="n">
         <v>0.04146</v>
       </c>
-      <c r="L412" s="1" t="n">
+      <c r="M412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -16969,9 +18208,12 @@
         <v>1.124</v>
       </c>
       <c r="K413" s="1" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="L413" s="1" t="n">
         <v>1.124</v>
       </c>
-      <c r="L413" s="1" t="n">
+      <c r="M413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -17009,10 +18251,13 @@
         <v>0.2626</v>
       </c>
       <c r="K414" s="1" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="L414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="L414" s="1" t="n">
-        <v>0.2626</v>
+      <c r="M414" s="1" t="n">
+        <v>0.2625</v>
       </c>
     </row>
     <row r="415">
@@ -17049,10 +18294,13 @@
         <v>0.001227</v>
       </c>
       <c r="K415" s="1" t="n">
+        <v>0.00122</v>
+      </c>
+      <c r="L415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="L415" s="1" t="n">
-        <v>0.001221</v>
+      <c r="M415" s="1" t="n">
+        <v>0.00122</v>
       </c>
     </row>
     <row r="416">
@@ -17089,9 +18337,12 @@
         <v>0.03205</v>
       </c>
       <c r="K416" s="1" t="n">
+        <v>0.03195</v>
+      </c>
+      <c r="L416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="L416" s="1" t="n">
+      <c r="M416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -17129,9 +18380,12 @@
         <v>0.01468</v>
       </c>
       <c r="K417" s="1" t="n">
+        <v>0.01467</v>
+      </c>
+      <c r="L417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="L417" s="1" t="n">
+      <c r="M417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -17169,9 +18423,12 @@
         <v>0.1486</v>
       </c>
       <c r="K418" s="1" t="n">
+        <v>0.1485</v>
+      </c>
+      <c r="L418" s="1" t="n">
         <v>0.1486</v>
       </c>
-      <c r="L418" s="1" t="n">
+      <c r="M418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -17212,6 +18469,9 @@
         <v>0.04943</v>
       </c>
       <c r="L419" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="M419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -17249,9 +18509,12 @@
         <v>66.56</v>
       </c>
       <c r="K420" s="1" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="L420" s="1" t="n">
         <v>66.7</v>
       </c>
-      <c r="L420" s="1" t="n">
+      <c r="M420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -17289,9 +18552,12 @@
         <v>0.877</v>
       </c>
       <c r="K421" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="L421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="L421" s="1" t="n">
+      <c r="M421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -17329,9 +18595,12 @@
         <v>0.012645</v>
       </c>
       <c r="K422" s="1" t="n">
+        <v>0.01265</v>
+      </c>
+      <c r="L422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="L422" s="1" t="n">
+      <c r="M422" s="1" t="n">
         <v>0.012645</v>
       </c>
     </row>
@@ -17369,9 +18638,12 @@
         <v>0.01597</v>
       </c>
       <c r="K423" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="L423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="L423" s="1" t="n">
+      <c r="M423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -17409,9 +18681,12 @@
         <v>0.27049</v>
       </c>
       <c r="K424" s="1" t="n">
-        <v>0.27049</v>
+        <v>0.27102</v>
       </c>
       <c r="L424" s="1" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="M424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -17449,9 +18724,12 @@
         <v>0.5999</v>
       </c>
       <c r="K425" s="1" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="L425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="L425" s="1" t="n">
+      <c r="M425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -17489,9 +18767,12 @@
         <v>0.005595</v>
       </c>
       <c r="K426" s="1" t="n">
+        <v>0.005566</v>
+      </c>
+      <c r="L426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="L426" s="1" t="n">
+      <c r="M426" s="1" t="n">
         <v>0.005557</v>
       </c>
     </row>
@@ -17529,9 +18810,12 @@
         <v>0.04911</v>
       </c>
       <c r="K427" s="1" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="L427" s="1" t="n">
         <v>0.04916</v>
       </c>
-      <c r="L427" s="1" t="n">
+      <c r="M427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -17572,6 +18856,9 @@
         <v>0.1266</v>
       </c>
       <c r="L428" s="1" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="M428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -17609,9 +18896,12 @@
         <v>0.003191</v>
       </c>
       <c r="K429" s="1" t="n">
+        <v>0.003187</v>
+      </c>
+      <c r="L429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="L429" s="1" t="n">
+      <c r="M429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -17649,9 +18939,12 @@
         <v>0.03652</v>
       </c>
       <c r="K430" s="1" t="n">
+        <v>0.03647</v>
+      </c>
+      <c r="L430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="L430" s="1" t="n">
+      <c r="M430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -17689,9 +18982,12 @@
         <v>0.3982</v>
       </c>
       <c r="K431" s="1" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="L431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="L431" s="1" t="n">
+      <c r="M431" s="1" t="n">
         <v>0.3982</v>
       </c>
     </row>
@@ -17729,10 +19025,13 @@
         <v>0.004512</v>
       </c>
       <c r="K432" s="1" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="L432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="L432" s="1" t="n">
-        <v>0.004512</v>
+      <c r="M432" s="1" t="n">
+        <v>0.0045</v>
       </c>
     </row>
     <row r="433">
@@ -17769,10 +19068,13 @@
         <v>0.0979</v>
       </c>
       <c r="K433" s="1" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="L433" s="1" t="n">
         <v>0.09810000000000001</v>
       </c>
-      <c r="L433" s="1" t="n">
-        <v>0.0978</v>
+      <c r="M433" s="1" t="n">
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="434">
@@ -17809,9 +19111,12 @@
         <v>0.01241</v>
       </c>
       <c r="K434" s="1" t="n">
+        <v>0.01243</v>
+      </c>
+      <c r="L434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="L434" s="1" t="n">
+      <c r="M434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -17849,9 +19154,12 @@
         <v>1.983</v>
       </c>
       <c r="K435" s="1" t="n">
+        <v>1.981</v>
+      </c>
+      <c r="L435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="L435" s="1" t="n">
+      <c r="M435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -17889,9 +19197,12 @@
         <v>0.001813</v>
       </c>
       <c r="K436" s="1" t="n">
+        <v>0.00182</v>
+      </c>
+      <c r="L436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="L436" s="1" t="n">
+      <c r="M436" s="1" t="n">
         <v>0.001813</v>
       </c>
     </row>
@@ -17929,9 +19240,12 @@
         <v>0.4413</v>
       </c>
       <c r="K437" s="1" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="L437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="L437" s="1" t="n">
+      <c r="M437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -17969,9 +19283,12 @@
         <v>0.00535</v>
       </c>
       <c r="K438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="L438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="L438" s="1" t="n">
+      <c r="M438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -18009,9 +19326,12 @@
         <v>0.1033</v>
       </c>
       <c r="K439" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="L439" s="1" t="n">
         <v>0.1036</v>
       </c>
-      <c r="L439" s="1" t="n">
+      <c r="M439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -18049,9 +19369,12 @@
         <v>0.03457</v>
       </c>
       <c r="K440" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="L440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="L440" s="1" t="n">
+      <c r="M440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -18089,9 +19412,12 @@
         <v>0.08201</v>
       </c>
       <c r="K441" s="1" t="n">
+        <v>0.08209</v>
+      </c>
+      <c r="L441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="L441" s="1" t="n">
+      <c r="M441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -18129,10 +19455,13 @@
         <v>1.303</v>
       </c>
       <c r="K442" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="L442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="L442" s="1" t="n">
-        <v>1.303</v>
+      <c r="M442" s="1" t="n">
+        <v>1.302</v>
       </c>
     </row>
     <row r="443">
@@ -18169,9 +19498,12 @@
         <v>0.07575999999999999</v>
       </c>
       <c r="K443" s="1" t="n">
+        <v>0.07556</v>
+      </c>
+      <c r="L443" s="1" t="n">
         <v>0.07581</v>
       </c>
-      <c r="L443" s="1" t="n">
+      <c r="M443" s="1" t="n">
         <v>0.07550999999999999</v>
       </c>
     </row>
@@ -18209,9 +19541,12 @@
         <v>0.07693</v>
       </c>
       <c r="K444" s="1" t="n">
+        <v>0.07692</v>
+      </c>
+      <c r="L444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="L444" s="1" t="n">
+      <c r="M444" s="1" t="n">
         <v>0.07661</v>
       </c>
     </row>
@@ -18249,9 +19584,12 @@
         <v>0.04388</v>
       </c>
       <c r="K445" s="1" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="L445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="L445" s="1" t="n">
+      <c r="M445" s="1" t="n">
         <v>0.04357</v>
       </c>
     </row>
@@ -18289,9 +19627,12 @@
         <v>0.02152</v>
       </c>
       <c r="K446" s="1" t="n">
+        <v>0.02145</v>
+      </c>
+      <c r="L446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="L446" s="1" t="n">
+      <c r="M446" s="1" t="n">
         <v>0.02144</v>
       </c>
     </row>
@@ -18329,9 +19670,12 @@
         <v>0.2811</v>
       </c>
       <c r="K447" s="1" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="L447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="L447" s="1" t="n">
+      <c r="M447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -18369,9 +19713,12 @@
         <v>0.03101</v>
       </c>
       <c r="K448" s="1" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="L448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="L448" s="1" t="n">
+      <c r="M448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -18409,9 +19756,12 @@
         <v>0.00644</v>
       </c>
       <c r="K449" s="1" t="n">
-        <v>0.00646</v>
+        <v>0.00647</v>
       </c>
       <c r="L449" s="1" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="M449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -18449,9 +19799,12 @@
         <v>0.02301</v>
       </c>
       <c r="K450" s="1" t="n">
+        <v>0.022915</v>
+      </c>
+      <c r="L450" s="1" t="n">
         <v>0.023016</v>
       </c>
-      <c r="L450" s="1" t="n">
+      <c r="M450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -18489,9 +19842,12 @@
         <v>0.04239</v>
       </c>
       <c r="K451" s="1" t="n">
+        <v>0.04241</v>
+      </c>
+      <c r="L451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="L451" s="1" t="n">
+      <c r="M451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -18529,9 +19885,12 @@
         <v>0.07238</v>
       </c>
       <c r="K452" s="1" t="n">
+        <v>0.07224</v>
+      </c>
+      <c r="L452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="L452" s="1" t="n">
+      <c r="M452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -18569,9 +19928,12 @@
         <v>0.000595</v>
       </c>
       <c r="K453" s="1" t="n">
-        <v>0.000595</v>
+        <v>0.0005951</v>
       </c>
       <c r="L453" s="1" t="n">
+        <v>0.0005951</v>
+      </c>
+      <c r="M453" s="1" t="n">
         <v>0.0005925</v>
       </c>
     </row>
@@ -18609,9 +19971,12 @@
         <v>0.307</v>
       </c>
       <c r="K454" s="1" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="L454" s="1" t="n">
+      <c r="M454" s="1" t="n">
         <v>0.307</v>
       </c>
     </row>
@@ -18649,9 +20014,12 @@
         <v>0.004324</v>
       </c>
       <c r="K455" s="1" t="n">
+        <v>0.004292</v>
+      </c>
+      <c r="L455" s="1" t="n">
         <v>0.004324</v>
       </c>
-      <c r="L455" s="1" t="n">
+      <c r="M455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -18689,9 +20057,12 @@
         <v>0.183</v>
       </c>
       <c r="K456" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="L456" s="1" t="n">
+      <c r="M456" s="1" t="n">
         <v>0.183</v>
       </c>
     </row>
@@ -18729,10 +20100,13 @@
         <v>0.04276</v>
       </c>
       <c r="K457" s="1" t="n">
+        <v>0.04268</v>
+      </c>
+      <c r="L457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="L457" s="1" t="n">
-        <v>0.04274</v>
+      <c r="M457" s="1" t="n">
+        <v>0.04268</v>
       </c>
     </row>
     <row r="458">
@@ -18769,9 +20143,12 @@
         <v>0.1463</v>
       </c>
       <c r="K458" s="1" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="L458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="L458" s="1" t="n">
+      <c r="M458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -18809,9 +20186,12 @@
         <v>0.008624</v>
       </c>
       <c r="K459" s="1" t="n">
+        <v>0.008618000000000001</v>
+      </c>
+      <c r="L459" s="1" t="n">
         <v>0.008624</v>
       </c>
-      <c r="L459" s="1" t="n">
+      <c r="M459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -18849,10 +20229,13 @@
         <v>0.007414</v>
       </c>
       <c r="K460" s="1" t="n">
+        <v>0.007386</v>
+      </c>
+      <c r="L460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="L460" s="1" t="n">
-        <v>0.007414</v>
+      <c r="M460" s="1" t="n">
+        <v>0.007386</v>
       </c>
     </row>
     <row r="461">
@@ -18889,9 +20272,12 @@
         <v>0.0001727</v>
       </c>
       <c r="K461" s="1" t="n">
+        <v>0.0001728</v>
+      </c>
+      <c r="L461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="L461" s="1" t="n">
+      <c r="M461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -18929,9 +20315,12 @@
         <v>0.0228</v>
       </c>
       <c r="K462" s="1" t="n">
-        <v>0.0228</v>
+        <v>0.02321</v>
       </c>
       <c r="L462" s="1" t="n">
+        <v>0.02321</v>
+      </c>
+      <c r="M462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -18969,10 +20358,13 @@
         <v>0.03718</v>
       </c>
       <c r="K463" s="1" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="L463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="L463" s="1" t="n">
-        <v>0.03718</v>
+      <c r="M463" s="1" t="n">
+        <v>0.03685</v>
       </c>
     </row>
     <row r="464">
@@ -19009,10 +20401,13 @@
         <v>0.3025</v>
       </c>
       <c r="K464" s="1" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="L464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="L464" s="1" t="n">
-        <v>0.3025</v>
+      <c r="M464" s="1" t="n">
+        <v>0.3021</v>
       </c>
     </row>
     <row r="465">
@@ -19049,9 +20444,12 @@
         <v>0.03937</v>
       </c>
       <c r="K465" s="1" t="n">
+        <v>0.03909</v>
+      </c>
+      <c r="L465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="L465" s="1" t="n">
+      <c r="M465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -19089,9 +20487,12 @@
         <v>2.667</v>
       </c>
       <c r="K466" s="1" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="L466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="L466" s="1" t="n">
+      <c r="M466" s="1" t="n">
         <v>2.667</v>
       </c>
     </row>
@@ -19129,9 +20530,12 @@
         <v>0.0341</v>
       </c>
       <c r="K467" s="1" t="n">
+        <v>0.03394</v>
+      </c>
+      <c r="L467" s="1" t="n">
         <v>0.03436</v>
       </c>
-      <c r="L467" s="1" t="n">
+      <c r="M467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -19169,9 +20573,12 @@
         <v>0.1763</v>
       </c>
       <c r="K468" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="L468" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="L468" s="1" t="n">
+      <c r="M468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -19209,9 +20616,12 @@
         <v>0.0963</v>
       </c>
       <c r="K469" s="1" t="n">
-        <v>0.0963</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="L469" s="1" t="n">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="M469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -19249,9 +20659,12 @@
         <v>0.06751</v>
       </c>
       <c r="K470" s="1" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="L470" s="1" t="n">
         <v>0.06757000000000001</v>
       </c>
-      <c r="L470" s="1" t="n">
+      <c r="M470" s="1" t="n">
         <v>0.06716999999999999</v>
       </c>
     </row>
@@ -19289,9 +20702,12 @@
         <v>0.04007</v>
       </c>
       <c r="K471" s="1" t="n">
+        <v>0.04001</v>
+      </c>
+      <c r="L471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="L471" s="1" t="n">
+      <c r="M471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -19329,9 +20745,12 @@
         <v>0.2472</v>
       </c>
       <c r="K472" s="1" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="L472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="L472" s="1" t="n">
+      <c r="M472" s="1" t="n">
         <v>0.2472</v>
       </c>
     </row>
@@ -19369,10 +20788,13 @@
         <v>0.016397</v>
       </c>
       <c r="K473" s="1" t="n">
+        <v>0.016393</v>
+      </c>
+      <c r="L473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="L473" s="1" t="n">
-        <v>0.016397</v>
+      <c r="M473" s="1" t="n">
+        <v>0.016393</v>
       </c>
     </row>
     <row r="474">
@@ -19409,9 +20831,12 @@
         <v>0.1156</v>
       </c>
       <c r="K474" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="L474" s="1" t="n">
         <v>0.1157</v>
       </c>
-      <c r="L474" s="1" t="n">
+      <c r="M474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -19449,9 +20874,12 @@
         <v>0.04274</v>
       </c>
       <c r="K475" s="1" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="L475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="L475" s="1" t="n">
+      <c r="M475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -19489,9 +20917,12 @@
         <v>0.2074</v>
       </c>
       <c r="K476" s="1" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="L476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="L476" s="1" t="n">
+      <c r="M476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -19529,9 +20960,12 @@
         <v>0.006837</v>
       </c>
       <c r="K477" s="1" t="n">
+        <v>0.006813</v>
+      </c>
+      <c r="L477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="L477" s="1" t="n">
+      <c r="M477" s="1" t="n">
         <v>0.006796</v>
       </c>
     </row>
@@ -19569,10 +21003,13 @@
         <v>0.01788</v>
       </c>
       <c r="K478" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="L478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="L478" s="1" t="n">
-        <v>0.01788</v>
+      <c r="M478" s="1" t="n">
+        <v>0.01784</v>
       </c>
     </row>
     <row r="479">
@@ -19609,9 +21046,12 @@
         <v>0.04696</v>
       </c>
       <c r="K479" s="1" t="n">
+        <v>0.04693</v>
+      </c>
+      <c r="L479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="L479" s="1" t="n">
+      <c r="M479" s="1" t="n">
         <v>0.04683</v>
       </c>
     </row>
@@ -19649,9 +21089,12 @@
         <v>0.26092</v>
       </c>
       <c r="K480" s="1" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="L480" s="1" t="n">
         <v>0.26166</v>
       </c>
-      <c r="L480" s="1" t="n">
+      <c r="M480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -19689,9 +21132,12 @@
         <v>0.01229</v>
       </c>
       <c r="K481" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="L481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="L481" s="1" t="n">
+      <c r="M481" s="1" t="n">
         <v>0.01229</v>
       </c>
     </row>
@@ -19729,9 +21175,12 @@
         <v>0.004107</v>
       </c>
       <c r="K482" s="1" t="n">
+        <v>0.004097</v>
+      </c>
+      <c r="L482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="L482" s="1" t="n">
+      <c r="M482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -19769,10 +21218,13 @@
         <v>0.123</v>
       </c>
       <c r="K483" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="L483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="L483" s="1" t="n">
-        <v>0.123</v>
+      <c r="M483" s="1" t="n">
+        <v>0.1229</v>
       </c>
     </row>
     <row r="484">
@@ -19809,9 +21261,12 @@
         <v>0.02192</v>
       </c>
       <c r="K484" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="L484" s="1" t="n">
         <v>0.02209</v>
       </c>
-      <c r="L484" s="1" t="n">
+      <c r="M484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -19849,9 +21304,12 @@
         <v>0.04558</v>
       </c>
       <c r="K485" s="1" t="n">
+        <v>0.04552</v>
+      </c>
+      <c r="L485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="L485" s="1" t="n">
+      <c r="M485" s="1" t="n">
         <v>0.04548</v>
       </c>
     </row>
@@ -19889,9 +21347,12 @@
         <v>0.1731</v>
       </c>
       <c r="K486" s="1" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="L486" s="1" t="n">
         <v>0.1736</v>
       </c>
-      <c r="L486" s="1" t="n">
+      <c r="M486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -19929,10 +21390,13 @@
         <v>0.2729</v>
       </c>
       <c r="K487" s="1" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="L487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="L487" s="1" t="n">
-        <v>0.2729</v>
+      <c r="M487" s="1" t="n">
+        <v>0.2726</v>
       </c>
     </row>
     <row r="488">
@@ -19969,9 +21433,12 @@
         <v>0.04618</v>
       </c>
       <c r="K488" s="1" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="L488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="L488" s="1" t="n">
+      <c r="M488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -20009,9 +21476,12 @@
         <v>0.0002155</v>
       </c>
       <c r="K489" s="1" t="n">
+        <v>0.0002152</v>
+      </c>
+      <c r="L489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="L489" s="1" t="n">
+      <c r="M489" s="1" t="n">
         <v>0.0002151</v>
       </c>
     </row>
@@ -20049,9 +21519,12 @@
         <v>1.778</v>
       </c>
       <c r="K490" s="1" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="L490" s="1" t="n">
         <v>1.778</v>
       </c>
-      <c r="L490" s="1" t="n">
+      <c r="M490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -20089,9 +21562,12 @@
         <v>16.068</v>
       </c>
       <c r="K491" s="1" t="n">
+        <v>16.058</v>
+      </c>
+      <c r="L491" s="1" t="n">
         <v>16.083</v>
       </c>
-      <c r="L491" s="1" t="n">
+      <c r="M491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -20129,9 +21605,12 @@
         <v>0.06695</v>
       </c>
       <c r="K492" s="1" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="L492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="L492" s="1" t="n">
+      <c r="M492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -20169,9 +21648,12 @@
         <v>0.06741</v>
       </c>
       <c r="K493" s="1" t="n">
+        <v>0.06744</v>
+      </c>
+      <c r="L493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="L493" s="1" t="n">
+      <c r="M493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -20209,9 +21691,12 @@
         <v>0.009469</v>
       </c>
       <c r="K494" s="1" t="n">
+        <v>0.009461000000000001</v>
+      </c>
+      <c r="L494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="L494" s="1" t="n">
+      <c r="M494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -20249,10 +21734,13 @@
         <v>0.005875</v>
       </c>
       <c r="K495" s="1" t="n">
+        <v>0.005874</v>
+      </c>
+      <c r="L495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="L495" s="1" t="n">
-        <v>0.005875</v>
+      <c r="M495" s="1" t="n">
+        <v>0.005874</v>
       </c>
     </row>
     <row r="496">
@@ -20292,6 +21780,9 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="L496" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="M496" s="1" t="n">
         <v>0.00987</v>
       </c>
     </row>
@@ -20329,9 +21820,12 @@
         <v>0.04411</v>
       </c>
       <c r="K497" s="1" t="n">
-        <v>0.04411</v>
+        <v>0.04412</v>
       </c>
       <c r="L497" s="1" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="M497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -20369,10 +21863,13 @@
         <v>0.006388</v>
       </c>
       <c r="K498" s="1" t="n">
+        <v>0.006384</v>
+      </c>
+      <c r="L498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="L498" s="1" t="n">
-        <v>0.006388</v>
+      <c r="M498" s="1" t="n">
+        <v>0.006384</v>
       </c>
     </row>
     <row r="499">
@@ -20409,9 +21906,12 @@
         <v>0.01049</v>
       </c>
       <c r="K499" s="1" t="n">
+        <v>0.01046</v>
+      </c>
+      <c r="L499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="L499" s="1" t="n">
+      <c r="M499" s="1" t="n">
         <v>0.01044</v>
       </c>
     </row>
@@ -20449,9 +21949,12 @@
         <v>0.5083</v>
       </c>
       <c r="K500" s="1" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="L500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="L500" s="1" t="n">
+      <c r="M500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -20489,9 +21992,12 @@
         <v>0.03207</v>
       </c>
       <c r="K501" s="1" t="n">
+        <v>0.03206</v>
+      </c>
+      <c r="L501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="L501" s="1" t="n">
+      <c r="M501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -20529,9 +22035,12 @@
         <v>0.4397</v>
       </c>
       <c r="K502" s="1" t="n">
-        <v>0.4397</v>
+        <v>0.4409</v>
       </c>
       <c r="L502" s="1" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="M502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -20569,9 +22078,12 @@
         <v>0.999342</v>
       </c>
       <c r="K503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="L503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="L503" s="1" t="n">
+      <c r="M503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -20609,9 +22121,12 @@
         <v>0.03514</v>
       </c>
       <c r="K504" s="1" t="n">
+        <v>0.03514</v>
+      </c>
+      <c r="L504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="L504" s="1" t="n">
+      <c r="M504" s="1" t="n">
         <v>0.03514</v>
       </c>
     </row>
@@ -20649,9 +22164,12 @@
         <v>0.004949</v>
       </c>
       <c r="K505" s="1" t="n">
+        <v>0.004944</v>
+      </c>
+      <c r="L505" s="1" t="n">
         <v>0.00495</v>
       </c>
-      <c r="L505" s="1" t="n">
+      <c r="M505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -20689,9 +22207,12 @@
         <v>0.01395</v>
       </c>
       <c r="K506" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="L506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="L506" s="1" t="n">
+      <c r="M506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -20729,9 +22250,12 @@
         <v>0.00349</v>
       </c>
       <c r="K507" s="1" t="n">
+        <v>0.003486</v>
+      </c>
+      <c r="L507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="L507" s="1" t="n">
+      <c r="M507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -20769,9 +22293,12 @@
         <v>1.419</v>
       </c>
       <c r="K508" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="L508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="L508" s="1" t="n">
+      <c r="M508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -20809,9 +22336,12 @@
         <v>0.005076</v>
       </c>
       <c r="K509" s="1" t="n">
+        <v>0.005076</v>
+      </c>
+      <c r="L509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="L509" s="1" t="n">
+      <c r="M509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -20849,10 +22379,13 @@
         <v>0.01573</v>
       </c>
       <c r="K510" s="1" t="n">
+        <v>0.01571</v>
+      </c>
+      <c r="L510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="L510" s="1" t="n">
-        <v>0.01572</v>
+      <c r="M510" s="1" t="n">
+        <v>0.01571</v>
       </c>
     </row>
     <row r="511">
@@ -20889,9 +22422,12 @@
         <v>0.08251</v>
       </c>
       <c r="K511" s="1" t="n">
+        <v>0.08248999999999999</v>
+      </c>
+      <c r="L511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="L511" s="1" t="n">
+      <c r="M511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -20929,9 +22465,12 @@
         <v>0.007093</v>
       </c>
       <c r="K512" s="1" t="n">
+        <v>0.007093</v>
+      </c>
+      <c r="L512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="L512" s="1" t="n">
+      <c r="M512" s="1" t="n">
         <v>0.007093</v>
       </c>
     </row>
@@ -20969,9 +22508,12 @@
         <v>0.01493</v>
       </c>
       <c r="K513" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="L513" s="1" t="n">
         <v>0.01493</v>
       </c>
-      <c r="L513" s="1" t="n">
+      <c r="M513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -21009,9 +22551,12 @@
         <v>0.04727</v>
       </c>
       <c r="K514" s="1" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="L514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="L514" s="1" t="n">
+      <c r="M514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -21049,9 +22594,12 @@
         <v>0.0182</v>
       </c>
       <c r="K515" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="L515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="L515" s="1" t="n">
+      <c r="M515" s="1" t="n">
         <v>0.01818</v>
       </c>
     </row>
@@ -21089,9 +22637,12 @@
         <v>0.0005794</v>
       </c>
       <c r="K516" s="1" t="n">
+        <v>0.0005792</v>
+      </c>
+      <c r="L516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="L516" s="1" t="n">
+      <c r="M516" s="1" t="n">
         <v>0.0005792</v>
       </c>
     </row>
@@ -21129,9 +22680,12 @@
         <v>0.07858999999999999</v>
       </c>
       <c r="K517" s="1" t="n">
+        <v>0.07857</v>
+      </c>
+      <c r="L517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="L517" s="1" t="n">
+      <c r="M517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -21169,9 +22723,12 @@
         <v>0.006373</v>
       </c>
       <c r="K518" s="1" t="n">
+        <v>0.006381</v>
+      </c>
+      <c r="L518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="L518" s="1" t="n">
+      <c r="M518" s="1" t="n">
         <v>0.006373</v>
       </c>
     </row>
@@ -21209,10 +22766,13 @@
         <v>0.05785</v>
       </c>
       <c r="K519" s="1" t="n">
+        <v>0.05784</v>
+      </c>
+      <c r="L519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="L519" s="1" t="n">
-        <v>0.05785</v>
+      <c r="M519" s="1" t="n">
+        <v>0.05784</v>
       </c>
     </row>
     <row r="520">
@@ -21249,9 +22809,12 @@
         <v>0.10469</v>
       </c>
       <c r="K520" s="1" t="n">
+        <v>0.10484</v>
+      </c>
+      <c r="L520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="L520" s="1" t="n">
+      <c r="M520" s="1" t="n">
         <v>0.10469</v>
       </c>
     </row>
@@ -21289,9 +22852,12 @@
         <v>0.01796</v>
       </c>
       <c r="K521" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="L521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="L521" s="1" t="n">
+      <c r="M521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -21329,9 +22895,12 @@
         <v>0.01655</v>
       </c>
       <c r="K522" s="1" t="n">
+        <v>0.01651</v>
+      </c>
+      <c r="L522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="L522" s="1" t="n">
+      <c r="M522" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -21369,9 +22938,12 @@
         <v>0.01092</v>
       </c>
       <c r="K523" s="1" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="L523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="L523" s="1" t="n">
+      <c r="M523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -21409,9 +22981,12 @@
         <v>0.007154</v>
       </c>
       <c r="K524" s="1" t="n">
-        <v>0.007156</v>
+        <v>0.007158</v>
       </c>
       <c r="L524" s="1" t="n">
+        <v>0.007158</v>
+      </c>
+      <c r="M524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -21449,10 +23024,13 @@
         <v>0.005892</v>
       </c>
       <c r="K525" s="1" t="n">
+        <v>0.005889</v>
+      </c>
+      <c r="L525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="L525" s="1" t="n">
-        <v>0.005892</v>
+      <c r="M525" s="1" t="n">
+        <v>0.005889</v>
       </c>
     </row>
     <row r="526">
@@ -21489,9 +23067,12 @@
         <v>0.001441</v>
       </c>
       <c r="K526" s="1" t="n">
+        <v>0.001439</v>
+      </c>
+      <c r="L526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="L526" s="1" t="n">
+      <c r="M526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -21529,9 +23110,12 @@
         <v>0.372</v>
       </c>
       <c r="K527" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="L527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="L527" s="1" t="n">
+      <c r="M527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -21569,9 +23153,12 @@
         <v>0.005187</v>
       </c>
       <c r="K528" s="1" t="n">
+        <v>0.005167</v>
+      </c>
+      <c r="L528" s="1" t="n">
         <v>0.00521</v>
       </c>
-      <c r="L528" s="1" t="n">
+      <c r="M528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -21609,9 +23196,12 @@
         <v>2.951</v>
       </c>
       <c r="K529" s="1" t="n">
+        <v>2.949</v>
+      </c>
+      <c r="L529" s="1" t="n">
         <v>2.951</v>
       </c>
-      <c r="L529" s="1" t="n">
+      <c r="M529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -21649,9 +23239,12 @@
         <v>0.1562</v>
       </c>
       <c r="K530" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="L530" s="1" t="n">
         <v>0.1562</v>
       </c>
-      <c r="L530" s="1" t="n">
+      <c r="M530" s="1" t="n">
         <v>0.1554</v>
       </c>
     </row>
@@ -21689,9 +23282,12 @@
         <v>2535</v>
       </c>
       <c r="K531" s="1" t="n">
+        <v>2539</v>
+      </c>
+      <c r="L531" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="L531" s="1" t="n">
+      <c r="M531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -21729,9 +23325,12 @@
         <v>0.03926</v>
       </c>
       <c r="K532" s="1" t="n">
+        <v>0.03925</v>
+      </c>
+      <c r="L532" s="1" t="n">
         <v>0.03929</v>
       </c>
-      <c r="L532" s="1" t="n">
+      <c r="M532" s="1" t="n">
         <v>0.03923</v>
       </c>
     </row>
@@ -21769,9 +23368,12 @@
         <v>0.02171</v>
       </c>
       <c r="K533" s="1" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="L533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="L533" s="1" t="n">
+      <c r="M533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -21809,9 +23411,12 @@
         <v>0.0736</v>
       </c>
       <c r="K534" s="1" t="n">
+        <v>0.07369000000000001</v>
+      </c>
+      <c r="L534" s="1" t="n">
         <v>0.0737</v>
       </c>
-      <c r="L534" s="1" t="n">
+      <c r="M534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -21849,9 +23454,12 @@
         <v>0.007929</v>
       </c>
       <c r="K535" s="1" t="n">
-        <v>0.007929</v>
+        <v>0.007931000000000001</v>
       </c>
       <c r="L535" s="1" t="n">
+        <v>0.007931000000000001</v>
+      </c>
+      <c r="M535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -21889,9 +23497,12 @@
         <v>0.05023</v>
       </c>
       <c r="K536" s="1" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="L536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="L536" s="1" t="n">
+      <c r="M536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -21929,10 +23540,13 @@
         <v>0.00405</v>
       </c>
       <c r="K537" s="1" t="n">
+        <v>0.00404</v>
+      </c>
+      <c r="L537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="L537" s="1" t="n">
-        <v>0.00405</v>
+      <c r="M537" s="1" t="n">
+        <v>0.00404</v>
       </c>
     </row>
     <row r="538">
@@ -21969,9 +23583,12 @@
         <v>0.08314000000000001</v>
       </c>
       <c r="K538" s="1" t="n">
+        <v>0.08298</v>
+      </c>
+      <c r="L538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="L538" s="1" t="n">
+      <c r="M538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -22009,9 +23626,12 @@
         <v>0.02496</v>
       </c>
       <c r="K539" s="1" t="n">
-        <v>0.02502</v>
+        <v>0.02505</v>
       </c>
       <c r="L539" s="1" t="n">
+        <v>0.02505</v>
+      </c>
+      <c r="M539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -22049,9 +23669,12 @@
         <v>0.08465</v>
       </c>
       <c r="K540" s="1" t="n">
+        <v>0.08463</v>
+      </c>
+      <c r="L540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="L540" s="1" t="n">
+      <c r="M540" s="1" t="n">
         <v>0.08461</v>
       </c>
     </row>
@@ -22089,9 +23712,12 @@
         <v>0.01891</v>
       </c>
       <c r="K541" s="1" t="n">
+        <v>0.01892</v>
+      </c>
+      <c r="L541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="L541" s="1" t="n">
+      <c r="M541" s="1" t="n">
         <v>0.01891</v>
       </c>
     </row>
@@ -22129,9 +23755,12 @@
         <v>0.01693</v>
       </c>
       <c r="K542" s="1" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="L542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="L542" s="1" t="n">
+      <c r="M542" s="1" t="n">
         <v>0.01693</v>
       </c>
     </row>
@@ -22169,9 +23798,12 @@
         <v>0.1047</v>
       </c>
       <c r="K543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="L543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="L543" s="1" t="n">
+      <c r="M543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:P543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -432,8 +432,9 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,10 +505,15 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>price_03:15</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -556,9 +562,12 @@
         <v>70623.5</v>
       </c>
       <c r="N2" s="1" t="n">
+        <v>70655.10000000001</v>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="P2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -605,9 +614,12 @@
         <v>2075.73</v>
       </c>
       <c r="N3" s="1" t="n">
+        <v>2076.18</v>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="P3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -654,9 +666,12 @@
         <v>86.97</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>86.91</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="P4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -703,10 +718,13 @@
         <v>4.022</v>
       </c>
       <c r="N5" s="1" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="O5" s="1" t="n">
-        <v>4.02</v>
+      <c r="P5" s="1" t="n">
+        <v>3.991</v>
       </c>
     </row>
     <row r="6">
@@ -752,9 +770,12 @@
         <v>0.09464</v>
       </c>
       <c r="N6" s="1" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -801,9 +822,12 @@
         <v>1.3903</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>1.3901</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="P7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -850,9 +874,12 @@
         <v>22.772</v>
       </c>
       <c r="N8" s="1" t="n">
+        <v>22.513</v>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="P8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -899,9 +926,12 @@
         <v>0.002003</v>
       </c>
       <c r="N9" s="1" t="n">
+        <v>0.002005</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>0.001977</v>
       </c>
     </row>
@@ -948,9 +978,12 @@
         <v>0.009712</v>
       </c>
       <c r="N10" s="1" t="n">
+        <v>0.009663</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="P10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -997,10 +1030,13 @@
         <v>0.15764</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>0.15129</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <v>0.15764</v>
+      <c r="P11" s="1" t="n">
+        <v>0.15129</v>
       </c>
     </row>
     <row r="12">
@@ -1046,9 +1082,12 @@
         <v>0.011484</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>0.011447</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="P12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -1095,9 +1134,12 @@
         <v>37.976</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>38.168</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="P13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1144,9 +1186,12 @@
         <v>653.1900000000001</v>
       </c>
       <c r="N14" s="1" t="n">
+        <v>653.22</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="P14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1193,9 +1238,12 @@
         <v>209.43</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>209.49</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="O15" s="1" t="n">
+      <c r="P15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1242,10 +1290,13 @@
         <v>0.003323</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>0.003321</v>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="O16" s="1" t="n">
-        <v>0.0033224</v>
+      <c r="P16" s="1" t="n">
+        <v>0.003321</v>
       </c>
     </row>
     <row r="17">
@@ -1291,9 +1342,12 @@
         <v>238.42</v>
       </c>
       <c r="N17" s="1" t="n">
+        <v>237.39</v>
+      </c>
+      <c r="O17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="P17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1340,9 +1394,12 @@
         <v>0.9899</v>
       </c>
       <c r="N18" s="1" t="n">
+        <v>0.9883</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="O18" s="1" t="n">
+      <c r="P18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1389,9 +1446,12 @@
         <v>1.0532</v>
       </c>
       <c r="N19" s="1" t="n">
+        <v>1.0604</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="O19" s="1" t="n">
+      <c r="P19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1438,9 +1498,12 @@
         <v>0.2588</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="P20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1487,10 +1550,13 @@
         <v>0.59712</v>
       </c>
       <c r="N21" s="1" t="n">
+        <v>0.59034</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="O21" s="1" t="n">
-        <v>0.59476</v>
+      <c r="P21" s="1" t="n">
+        <v>0.59034</v>
       </c>
     </row>
     <row r="22">
@@ -1536,9 +1602,12 @@
         <v>9.015000000000001</v>
       </c>
       <c r="N22" s="1" t="n">
+        <v>9.019</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="P22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1585,10 +1654,13 @@
         <v>0.02407</v>
       </c>
       <c r="N23" s="1" t="n">
+        <v>0.02398</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="O23" s="1" t="n">
-        <v>0.02404</v>
+      <c r="P23" s="1" t="n">
+        <v>0.02398</v>
       </c>
     </row>
     <row r="24">
@@ -1634,9 +1706,12 @@
         <v>9.564</v>
       </c>
       <c r="N24" s="1" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="O24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="O24" s="1" t="n">
+      <c r="P24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1683,9 +1758,12 @@
         <v>1.229</v>
       </c>
       <c r="N25" s="1" t="n">
-        <v>1.229</v>
+        <v>1.237</v>
       </c>
       <c r="O25" s="1" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="P25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1732,9 +1810,12 @@
         <v>0.07086000000000001</v>
       </c>
       <c r="N26" s="1" t="n">
+        <v>0.07142</v>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="O26" s="1" t="n">
+      <c r="P26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1781,9 +1862,12 @@
         <v>1.423</v>
       </c>
       <c r="N27" s="1" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="O27" s="1" t="n">
+      <c r="P27" s="1" t="n">
         <v>1.423</v>
       </c>
     </row>
@@ -1830,9 +1914,12 @@
         <v>1.305</v>
       </c>
       <c r="N28" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="O28" s="1" t="n">
+      <c r="P28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -1879,9 +1966,12 @@
         <v>462.31</v>
       </c>
       <c r="N29" s="1" t="n">
-        <v>463.21</v>
+        <v>463.26</v>
       </c>
       <c r="O29" s="1" t="n">
+        <v>463.26</v>
+      </c>
+      <c r="P29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -1928,9 +2018,12 @@
         <v>1.3093</v>
       </c>
       <c r="N30" s="1" t="n">
+        <v>1.3016</v>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="O30" s="1" t="n">
+      <c r="P30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -1977,9 +2070,12 @@
         <v>5023.33</v>
       </c>
       <c r="N31" s="1" t="n">
+        <v>5023.15</v>
+      </c>
+      <c r="O31" s="1" t="n">
         <v>5024.91</v>
       </c>
-      <c r="O31" s="1" t="n">
+      <c r="P31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -2026,9 +2122,12 @@
         <v>0.891</v>
       </c>
       <c r="N32" s="1" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="O32" s="1" t="n">
+      <c r="P32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2075,9 +2174,12 @@
         <v>0.001975</v>
       </c>
       <c r="N33" s="1" t="n">
+        <v>0.001973</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="O33" s="1" t="n">
+      <c r="P33" s="1" t="n">
         <v>0.001971</v>
       </c>
     </row>
@@ -2124,9 +2226,12 @@
         <v>0.17183</v>
       </c>
       <c r="N34" s="1" t="n">
-        <v>0.17183</v>
+        <v>0.17264</v>
       </c>
       <c r="O34" s="1" t="n">
+        <v>0.17264</v>
+      </c>
+      <c r="P34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2173,10 +2278,13 @@
         <v>0.29672</v>
       </c>
       <c r="N35" s="1" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="O35" s="1" t="n">
-        <v>0.2967</v>
+      <c r="P35" s="1" t="n">
+        <v>0.29661</v>
       </c>
     </row>
     <row r="36">
@@ -2222,9 +2330,12 @@
         <v>1.78</v>
       </c>
       <c r="N36" s="1" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="O36" s="1" t="n">
+      <c r="P36" s="1" t="n">
         <v>1.779</v>
       </c>
     </row>
@@ -2271,9 +2382,12 @@
         <v>110.32</v>
       </c>
       <c r="N37" s="1" t="n">
+        <v>110.29</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="O37" s="1" t="n">
+      <c r="P37" s="1" t="n">
         <v>110.25</v>
       </c>
     </row>
@@ -2320,9 +2434,12 @@
         <v>0.22079</v>
       </c>
       <c r="N38" s="1" t="n">
+        <v>0.2215</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="O38" s="1" t="n">
+      <c r="P38" s="1" t="n">
         <v>0.22079</v>
       </c>
     </row>
@@ -2369,10 +2486,13 @@
         <v>0.1073</v>
       </c>
       <c r="N39" s="1" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="O39" s="1" t="n">
-        <v>0.1073</v>
+      <c r="P39" s="1" t="n">
+        <v>0.1072</v>
       </c>
     </row>
     <row r="40">
@@ -2418,9 +2538,12 @@
         <v>0.37269</v>
       </c>
       <c r="N40" s="1" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="O40" s="1" t="n">
+      <c r="P40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2467,9 +2590,12 @@
         <v>54.7</v>
       </c>
       <c r="N41" s="1" t="n">
-        <v>54.7</v>
+        <v>54.72</v>
       </c>
       <c r="O41" s="1" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="P41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2516,10 +2642,13 @@
         <v>0.0010695</v>
       </c>
       <c r="N42" s="1" t="n">
+        <v>0.0010657</v>
+      </c>
+      <c r="O42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="O42" s="1" t="n">
-        <v>0.0010666</v>
+      <c r="P42" s="1" t="n">
+        <v>0.0010657</v>
       </c>
     </row>
     <row r="43">
@@ -2565,9 +2694,12 @@
         <v>6.441</v>
       </c>
       <c r="N43" s="1" t="n">
+        <v>6.414</v>
+      </c>
+      <c r="O43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="O43" s="1" t="n">
+      <c r="P43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -2614,10 +2746,13 @@
         <v>0.6356000000000001</v>
       </c>
       <c r="N44" s="1" t="n">
+        <v>0.6319</v>
+      </c>
+      <c r="O44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="O44" s="1" t="n">
-        <v>0.6324</v>
+      <c r="P44" s="1" t="n">
+        <v>0.6319</v>
       </c>
     </row>
     <row r="45">
@@ -2663,9 +2798,12 @@
         <v>0.3535</v>
       </c>
       <c r="N45" s="1" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="O45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="O45" s="1" t="n">
+      <c r="P45" s="1" t="n">
         <v>0.3533</v>
       </c>
     </row>
@@ -2712,9 +2850,12 @@
         <v>0.03298</v>
       </c>
       <c r="N46" s="1" t="n">
+        <v>0.03288</v>
+      </c>
+      <c r="O46" s="1" t="n">
         <v>0.03298</v>
       </c>
-      <c r="O46" s="1" t="n">
+      <c r="P46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2761,9 +2902,12 @@
         <v>0.07213</v>
       </c>
       <c r="N47" s="1" t="n">
+        <v>0.07154000000000001</v>
+      </c>
+      <c r="O47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="O47" s="1" t="n">
+      <c r="P47" s="1" t="n">
         <v>0.07151</v>
       </c>
     </row>
@@ -2810,9 +2954,12 @@
         <v>0.7088</v>
       </c>
       <c r="N48" s="1" t="n">
-        <v>0.7088</v>
+        <v>0.7097</v>
       </c>
       <c r="O48" s="1" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="P48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -2859,9 +3006,12 @@
         <v>0.00449</v>
       </c>
       <c r="N49" s="1" t="n">
+        <v>0.004384</v>
+      </c>
+      <c r="O49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="O49" s="1" t="n">
+      <c r="P49" s="1" t="n">
         <v>0.004361</v>
       </c>
     </row>
@@ -2908,9 +3058,12 @@
         <v>0.1039</v>
       </c>
       <c r="N50" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="O50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="O50" s="1" t="n">
+      <c r="P50" s="1" t="n">
         <v>0.1037</v>
       </c>
     </row>
@@ -2957,9 +3110,12 @@
         <v>0.0405</v>
       </c>
       <c r="N51" s="1" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="O51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="O51" s="1" t="n">
+      <c r="P51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -3006,9 +3162,12 @@
         <v>0.1652</v>
       </c>
       <c r="N52" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="O52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="O52" s="1" t="n">
+      <c r="P52" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -3055,9 +3214,12 @@
         <v>0.02002</v>
       </c>
       <c r="N53" s="1" t="n">
+        <v>0.02005</v>
+      </c>
+      <c r="O53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="O53" s="1" t="n">
+      <c r="P53" s="1" t="n">
         <v>0.02002</v>
       </c>
     </row>
@@ -3104,10 +3266,13 @@
         <v>0.007202</v>
       </c>
       <c r="N54" s="1" t="n">
+        <v>0.007191</v>
+      </c>
+      <c r="O54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="O54" s="1" t="n">
-        <v>0.007198</v>
+      <c r="P54" s="1" t="n">
+        <v>0.007191</v>
       </c>
     </row>
     <row r="55">
@@ -3153,9 +3318,12 @@
         <v>3.915</v>
       </c>
       <c r="N55" s="1" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="O55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="O55" s="1" t="n">
+      <c r="P55" s="1" t="n">
         <v>3.911</v>
       </c>
     </row>
@@ -3202,9 +3370,12 @@
         <v>0.017133</v>
       </c>
       <c r="N56" s="1" t="n">
+        <v>0.017098</v>
+      </c>
+      <c r="O56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="O56" s="1" t="n">
+      <c r="P56" s="1" t="n">
         <v>0.017082</v>
       </c>
     </row>
@@ -3251,10 +3422,13 @@
         <v>0.1094</v>
       </c>
       <c r="N57" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="O57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="O57" s="1" t="n">
-        <v>0.1094</v>
+      <c r="P57" s="1" t="n">
+        <v>0.1088</v>
       </c>
     </row>
     <row r="58">
@@ -3300,9 +3474,12 @@
         <v>2.656</v>
       </c>
       <c r="N58" s="1" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="O58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="O58" s="1" t="n">
+      <c r="P58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -3349,10 +3526,13 @@
         <v>0.159</v>
       </c>
       <c r="N59" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="O59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="O59" s="1" t="n">
-        <v>0.1589</v>
+      <c r="P59" s="1" t="n">
+        <v>0.1587</v>
       </c>
     </row>
     <row r="60">
@@ -3398,10 +3578,13 @@
         <v>0.00588</v>
       </c>
       <c r="N60" s="1" t="n">
+        <v>0.005876</v>
+      </c>
+      <c r="O60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="O60" s="1" t="n">
-        <v>0.00588</v>
+      <c r="P60" s="1" t="n">
+        <v>0.005876</v>
       </c>
     </row>
     <row r="61">
@@ -3447,9 +3630,12 @@
         <v>0.09193</v>
       </c>
       <c r="N61" s="1" t="n">
+        <v>0.09188</v>
+      </c>
+      <c r="O61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="O61" s="1" t="n">
+      <c r="P61" s="1" t="n">
         <v>0.09188</v>
       </c>
     </row>
@@ -3496,9 +3682,12 @@
         <v>0.9121</v>
       </c>
       <c r="N62" s="1" t="n">
+        <v>0.9134</v>
+      </c>
+      <c r="O62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="O62" s="1" t="n">
+      <c r="P62" s="1" t="n">
         <v>0.9112</v>
       </c>
     </row>
@@ -3545,9 +3734,12 @@
         <v>0.782</v>
       </c>
       <c r="N63" s="1" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="O63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="O63" s="1" t="n">
+      <c r="P63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -3594,9 +3786,12 @@
         <v>0.04626</v>
       </c>
       <c r="N64" s="1" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="O64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="O64" s="1" t="n">
+      <c r="P64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -3643,9 +3838,12 @@
         <v>357.45</v>
       </c>
       <c r="N65" s="1" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="O65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="O65" s="1" t="n">
+      <c r="P65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -3692,10 +3890,13 @@
         <v>0.12395</v>
       </c>
       <c r="N66" s="1" t="n">
+        <v>0.12358</v>
+      </c>
+      <c r="O66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="O66" s="1" t="n">
-        <v>0.12395</v>
+      <c r="P66" s="1" t="n">
+        <v>0.12358</v>
       </c>
     </row>
     <row r="67">
@@ -3741,10 +3942,13 @@
         <v>0.2281</v>
       </c>
       <c r="N67" s="1" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="O67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="O67" s="1" t="n">
-        <v>0.2281</v>
+      <c r="P67" s="1" t="n">
+        <v>0.2265</v>
       </c>
     </row>
     <row r="68">
@@ -3790,9 +3994,12 @@
         <v>0.0034</v>
       </c>
       <c r="N68" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="O68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="O68" s="1" t="n">
+      <c r="P68" s="1" t="n">
         <v>0.00339</v>
       </c>
     </row>
@@ -3839,9 +4046,12 @@
         <v>0.1734</v>
       </c>
       <c r="N69" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="O69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="O69" s="1" t="n">
+      <c r="P69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -3888,10 +4098,13 @@
         <v>0.16463</v>
       </c>
       <c r="N70" s="1" t="n">
+        <v>0.16386</v>
+      </c>
+      <c r="O70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="O70" s="1" t="n">
-        <v>0.1639</v>
+      <c r="P70" s="1" t="n">
+        <v>0.16386</v>
       </c>
     </row>
     <row r="71">
@@ -3937,9 +4150,12 @@
         <v>0.351</v>
       </c>
       <c r="N71" s="1" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="O71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="O71" s="1" t="n">
+      <c r="P71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -3986,9 +4202,12 @@
         <v>0.7086</v>
       </c>
       <c r="N72" s="1" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="O72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="O72" s="1" t="n">
+      <c r="P72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -4038,6 +4257,9 @@
         <v>0.00873</v>
       </c>
       <c r="O73" s="1" t="n">
+        <v>0.00873</v>
+      </c>
+      <c r="P73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -4084,9 +4306,12 @@
         <v>0.005984</v>
       </c>
       <c r="N74" s="1" t="n">
+        <v>0.005977</v>
+      </c>
+      <c r="O74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="O74" s="1" t="n">
+      <c r="P74" s="1" t="n">
         <v>0.005967</v>
       </c>
     </row>
@@ -4133,9 +4358,12 @@
         <v>0.226</v>
       </c>
       <c r="N75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="O75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="O75" s="1" t="n">
+      <c r="P75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -4182,9 +4410,12 @@
         <v>0.3235</v>
       </c>
       <c r="N76" s="1" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="O76" s="1" t="n">
         <v>0.3265</v>
       </c>
-      <c r="O76" s="1" t="n">
+      <c r="P76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -4231,9 +4462,12 @@
         <v>0.1003</v>
       </c>
       <c r="N77" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="O77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="O77" s="1" t="n">
+      <c r="P77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -4280,9 +4514,12 @@
         <v>0.1228</v>
       </c>
       <c r="N78" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="O78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="O78" s="1" t="n">
+      <c r="P78" s="1" t="n">
         <v>0.1227</v>
       </c>
     </row>
@@ -4329,9 +4566,12 @@
         <v>0.07353</v>
       </c>
       <c r="N79" s="1" t="n">
-        <v>0.07353</v>
+        <v>0.07353999999999999</v>
       </c>
       <c r="O79" s="1" t="n">
+        <v>0.07353999999999999</v>
+      </c>
+      <c r="P79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -4378,9 +4618,12 @@
         <v>0.04685</v>
       </c>
       <c r="N80" s="1" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="O80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="O80" s="1" t="n">
+      <c r="P80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -4427,9 +4670,12 @@
         <v>0.000233</v>
       </c>
       <c r="N81" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="O81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="O81" s="1" t="n">
+      <c r="P81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -4476,9 +4722,12 @@
         <v>8.220000000000001</v>
       </c>
       <c r="N82" s="1" t="n">
+        <v>8.218</v>
+      </c>
+      <c r="O82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="O82" s="1" t="n">
+      <c r="P82" s="1" t="n">
         <v>8.206</v>
       </c>
     </row>
@@ -4525,9 +4774,12 @@
         <v>0.0005816</v>
       </c>
       <c r="N83" s="1" t="n">
+        <v>0.0005843000000000001</v>
+      </c>
+      <c r="O83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="O83" s="1" t="n">
+      <c r="P83" s="1" t="n">
         <v>0.0005756</v>
       </c>
     </row>
@@ -4574,9 +4826,12 @@
         <v>0.4433</v>
       </c>
       <c r="N84" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="O84" s="1" t="n">
         <v>0.4457</v>
       </c>
-      <c r="O84" s="1" t="n">
+      <c r="P84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4623,9 +4878,12 @@
         <v>0.06251</v>
       </c>
       <c r="N85" s="1" t="n">
+        <v>0.06247</v>
+      </c>
+      <c r="O85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="O85" s="1" t="n">
+      <c r="P85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -4672,9 +4930,12 @@
         <v>0.05466</v>
       </c>
       <c r="N86" s="1" t="n">
+        <v>0.05449</v>
+      </c>
+      <c r="O86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="O86" s="1" t="n">
+      <c r="P86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -4721,9 +4982,12 @@
         <v>0.003345</v>
       </c>
       <c r="N87" s="1" t="n">
+        <v>0.003352</v>
+      </c>
+      <c r="O87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="O87" s="1" t="n">
+      <c r="P87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -4770,9 +5034,12 @@
         <v>0.05038</v>
       </c>
       <c r="N88" s="1" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="O88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="O88" s="1" t="n">
+      <c r="P88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -4819,9 +5086,12 @@
         <v>0.03037</v>
       </c>
       <c r="N89" s="1" t="n">
+        <v>0.03077</v>
+      </c>
+      <c r="O89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="O89" s="1" t="n">
+      <c r="P89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -4868,9 +5138,12 @@
         <v>0.3476</v>
       </c>
       <c r="N90" s="1" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="O90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="O90" s="1" t="n">
+      <c r="P90" s="1" t="n">
         <v>0.3471</v>
       </c>
     </row>
@@ -4917,9 +5190,12 @@
         <v>0.08159</v>
       </c>
       <c r="N91" s="1" t="n">
+        <v>0.0789</v>
+      </c>
+      <c r="O91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="O91" s="1" t="n">
+      <c r="P91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -4966,9 +5242,12 @@
         <v>0.3514</v>
       </c>
       <c r="N92" s="1" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="O92" s="1" t="n">
         <v>0.3551</v>
       </c>
-      <c r="O92" s="1" t="n">
+      <c r="P92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -5015,9 +5294,12 @@
         <v>1.978</v>
       </c>
       <c r="N93" s="1" t="n">
-        <v>1.9795</v>
+        <v>1.9809</v>
       </c>
       <c r="O93" s="1" t="n">
+        <v>1.9809</v>
+      </c>
+      <c r="P93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -5064,9 +5346,12 @@
         <v>0.2588</v>
       </c>
       <c r="N94" s="1" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="O94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="O94" s="1" t="n">
+      <c r="P94" s="1" t="n">
         <v>0.2586</v>
       </c>
     </row>
@@ -5113,9 +5398,12 @@
         <v>0.04722</v>
       </c>
       <c r="N95" s="1" t="n">
+        <v>0.04614</v>
+      </c>
+      <c r="O95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="O95" s="1" t="n">
+      <c r="P95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -5162,9 +5450,12 @@
         <v>0.006171</v>
       </c>
       <c r="N96" s="1" t="n">
+        <v>0.00618</v>
+      </c>
+      <c r="O96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="O96" s="1" t="n">
+      <c r="P96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -5211,9 +5502,12 @@
         <v>0.00173</v>
       </c>
       <c r="N97" s="1" t="n">
+        <v>0.001729</v>
+      </c>
+      <c r="O97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="O97" s="1" t="n">
+      <c r="P97" s="1" t="n">
         <v>0.001729</v>
       </c>
     </row>
@@ -5260,9 +5554,12 @@
         <v>5.188</v>
       </c>
       <c r="N98" s="1" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="O98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="O98" s="1" t="n">
+      <c r="P98" s="1" t="n">
         <v>5.188</v>
       </c>
     </row>
@@ -5309,10 +5606,13 @@
         <v>0.01511</v>
       </c>
       <c r="N99" s="1" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="O99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="O99" s="1" t="n">
-        <v>0.01511</v>
+      <c r="P99" s="1" t="n">
+        <v>0.0151</v>
       </c>
     </row>
     <row r="100">
@@ -5358,9 +5658,12 @@
         <v>0.5536</v>
       </c>
       <c r="N100" s="1" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="O100" s="1" t="n">
+      <c r="P100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -5407,10 +5710,13 @@
         <v>0.0905</v>
       </c>
       <c r="N101" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="O101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="O101" s="1" t="n">
-        <v>0.0905</v>
+      <c r="P101" s="1" t="n">
+        <v>0.0901</v>
       </c>
     </row>
     <row r="102">
@@ -5456,10 +5762,13 @@
         <v>32.45</v>
       </c>
       <c r="N102" s="1" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="O102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="O102" s="1" t="n">
-        <v>32.42</v>
+      <c r="P102" s="1" t="n">
+        <v>32.36</v>
       </c>
     </row>
     <row r="103">
@@ -5505,9 +5814,12 @@
         <v>0.03147</v>
       </c>
       <c r="N103" s="1" t="n">
+        <v>0.03164</v>
+      </c>
+      <c r="O103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="O103" s="1" t="n">
+      <c r="P103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -5554,9 +5866,12 @@
         <v>0.06571</v>
       </c>
       <c r="N104" s="1" t="n">
+        <v>0.06578000000000001</v>
+      </c>
+      <c r="O104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="O104" s="1" t="n">
+      <c r="P104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -5603,9 +5918,12 @@
         <v>1.3036</v>
       </c>
       <c r="N105" s="1" t="n">
-        <v>1.3046</v>
+        <v>1.3049</v>
       </c>
       <c r="O105" s="1" t="n">
+        <v>1.3049</v>
+      </c>
+      <c r="P105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -5652,9 +5970,12 @@
         <v>0.1205</v>
       </c>
       <c r="N106" s="1" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="O106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="O106" s="1" t="n">
+      <c r="P106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -5704,6 +6025,9 @@
         <v>0.121</v>
       </c>
       <c r="O107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="P107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -5750,9 +6074,12 @@
         <v>0.09587</v>
       </c>
       <c r="N108" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="O108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="O108" s="1" t="n">
+      <c r="P108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -5799,10 +6126,13 @@
         <v>0.13956</v>
       </c>
       <c r="N109" s="1" t="n">
+        <v>0.13782</v>
+      </c>
+      <c r="O109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="O109" s="1" t="n">
-        <v>0.13853</v>
+      <c r="P109" s="1" t="n">
+        <v>0.13782</v>
       </c>
     </row>
     <row r="110">
@@ -5848,9 +6178,12 @@
         <v>5.561</v>
       </c>
       <c r="N110" s="1" t="n">
+        <v>5.555</v>
+      </c>
+      <c r="O110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="O110" s="1" t="n">
+      <c r="P110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -5897,9 +6230,12 @@
         <v>1.1</v>
       </c>
       <c r="N111" s="1" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="O111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="O111" s="1" t="n">
+      <c r="P111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -5946,10 +6282,13 @@
         <v>0.0289</v>
       </c>
       <c r="N112" s="1" t="n">
+        <v>0.028875</v>
+      </c>
+      <c r="O112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="O112" s="1" t="n">
-        <v>0.0289</v>
+      <c r="P112" s="1" t="n">
+        <v>0.028875</v>
       </c>
     </row>
     <row r="113">
@@ -5995,9 +6334,12 @@
         <v>1.869</v>
       </c>
       <c r="N113" s="1" t="n">
+        <v>1.872</v>
+      </c>
+      <c r="O113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="O113" s="1" t="n">
+      <c r="P113" s="1" t="n">
         <v>1.869</v>
       </c>
     </row>
@@ -6044,9 +6386,12 @@
         <v>0.05942</v>
       </c>
       <c r="N114" s="1" t="n">
+        <v>0.05877</v>
+      </c>
+      <c r="O114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="O114" s="1" t="n">
+      <c r="P114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -6093,9 +6438,12 @@
         <v>0.12898</v>
       </c>
       <c r="N115" s="1" t="n">
+        <v>0.12872</v>
+      </c>
+      <c r="O115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="O115" s="1" t="n">
+      <c r="P115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -6142,9 +6490,12 @@
         <v>1.1102</v>
       </c>
       <c r="N116" s="1" t="n">
+        <v>1.1062</v>
+      </c>
+      <c r="O116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="O116" s="1" t="n">
+      <c r="P116" s="1" t="n">
         <v>1.1055</v>
       </c>
     </row>
@@ -6191,10 +6542,13 @@
         <v>0.1567</v>
       </c>
       <c r="N117" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="O117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="O117" s="1" t="n">
-        <v>0.1537</v>
+      <c r="P117" s="1" t="n">
+        <v>0.1531</v>
       </c>
     </row>
     <row r="118">
@@ -6240,10 +6594,13 @@
         <v>0.1591</v>
       </c>
       <c r="N118" s="1" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="O118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="O118" s="1" t="n">
-        <v>0.1582</v>
+      <c r="P118" s="1" t="n">
+        <v>0.158</v>
       </c>
     </row>
     <row r="119">
@@ -6289,9 +6646,12 @@
         <v>0.04769</v>
       </c>
       <c r="N119" s="1" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="O119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="O119" s="1" t="n">
+      <c r="P119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -6338,9 +6698,12 @@
         <v>3.02</v>
       </c>
       <c r="N120" s="1" t="n">
+        <v>3.019</v>
+      </c>
+      <c r="O120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="O120" s="1" t="n">
+      <c r="P120" s="1" t="n">
         <v>3.018</v>
       </c>
     </row>
@@ -6387,9 +6750,12 @@
         <v>0.2974</v>
       </c>
       <c r="N121" s="1" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="O121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="O121" s="1" t="n">
+      <c r="P121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -6436,10 +6802,13 @@
         <v>0.5833</v>
       </c>
       <c r="N122" s="1" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="O122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="O122" s="1" t="n">
-        <v>0.5826</v>
+      <c r="P122" s="1" t="n">
+        <v>0.5792</v>
       </c>
     </row>
     <row r="123">
@@ -6485,9 +6854,12 @@
         <v>0.01259</v>
       </c>
       <c r="N123" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="O123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="O123" s="1" t="n">
+      <c r="P123" s="1" t="n">
         <v>0.01257</v>
       </c>
     </row>
@@ -6534,9 +6906,12 @@
         <v>0.1579</v>
       </c>
       <c r="N124" s="1" t="n">
+        <v>0.1581</v>
+      </c>
+      <c r="O124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="O124" s="1" t="n">
+      <c r="P124" s="1" t="n">
         <v>0.1577</v>
       </c>
     </row>
@@ -6583,9 +6958,12 @@
         <v>0.001781</v>
       </c>
       <c r="N125" s="1" t="n">
+        <v>0.001779</v>
+      </c>
+      <c r="O125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="O125" s="1" t="n">
+      <c r="P125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -6632,10 +7010,13 @@
         <v>0.000486</v>
       </c>
       <c r="N126" s="1" t="n">
+        <v>0.0004845</v>
+      </c>
+      <c r="O126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="O126" s="1" t="n">
-        <v>0.0004859</v>
+      <c r="P126" s="1" t="n">
+        <v>0.0004845</v>
       </c>
     </row>
     <row r="127">
@@ -6681,10 +7062,13 @@
         <v>0.0294</v>
       </c>
       <c r="N127" s="1" t="n">
+        <v>0.02936</v>
+      </c>
+      <c r="O127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="O127" s="1" t="n">
-        <v>0.02938</v>
+      <c r="P127" s="1" t="n">
+        <v>0.02936</v>
       </c>
     </row>
     <row r="128">
@@ -6730,9 +7114,12 @@
         <v>0.04129</v>
       </c>
       <c r="N128" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="O128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="O128" s="1" t="n">
+      <c r="P128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -6779,9 +7166,12 @@
         <v>0.04857</v>
       </c>
       <c r="N129" s="1" t="n">
+        <v>0.04873</v>
+      </c>
+      <c r="O129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="O129" s="1" t="n">
+      <c r="P129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -6828,9 +7218,12 @@
         <v>1.26e-05</v>
       </c>
       <c r="N130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="O130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="O130" s="1" t="n">
+      <c r="P130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -6877,9 +7270,12 @@
         <v>7e-06</v>
       </c>
       <c r="N131" s="1" t="n">
+        <v>7.1e-06</v>
+      </c>
+      <c r="O131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="O131" s="1" t="n">
+      <c r="P131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -6926,10 +7322,13 @@
         <v>0.007</v>
       </c>
       <c r="N132" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="O132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="O132" s="1" t="n">
-        <v>0.007</v>
+      <c r="P132" s="1" t="n">
+        <v>0.00699</v>
       </c>
     </row>
     <row r="133">
@@ -6975,9 +7374,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="N133" s="1" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="O133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="O133" s="1" t="n">
+      <c r="P133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -7024,10 +7426,13 @@
         <v>0.0004086</v>
       </c>
       <c r="N134" s="1" t="n">
+        <v>0.0004079</v>
+      </c>
+      <c r="O134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="O134" s="1" t="n">
-        <v>0.0004086</v>
+      <c r="P134" s="1" t="n">
+        <v>0.0004079</v>
       </c>
     </row>
     <row r="135">
@@ -7073,10 +7478,13 @@
         <v>0.08345</v>
       </c>
       <c r="N135" s="1" t="n">
+        <v>0.08282</v>
+      </c>
+      <c r="O135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="O135" s="1" t="n">
-        <v>0.08334</v>
+      <c r="P135" s="1" t="n">
+        <v>0.08282</v>
       </c>
     </row>
     <row r="136">
@@ -7122,9 +7530,12 @@
         <v>0.007868999999999999</v>
       </c>
       <c r="N136" s="1" t="n">
+        <v>0.007891</v>
+      </c>
+      <c r="O136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="O136" s="1" t="n">
+      <c r="P136" s="1" t="n">
         <v>0.007868999999999999</v>
       </c>
     </row>
@@ -7171,9 +7582,12 @@
         <v>0.0008232</v>
       </c>
       <c r="N137" s="1" t="n">
+        <v>0.000825</v>
+      </c>
+      <c r="O137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="O137" s="1" t="n">
+      <c r="P137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -7220,9 +7634,12 @@
         <v>0.147</v>
       </c>
       <c r="N138" s="1" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="O138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="O138" s="1" t="n">
+      <c r="P138" s="1" t="n">
         <v>0.1468</v>
       </c>
     </row>
@@ -7269,10 +7686,13 @@
         <v>0.006709</v>
       </c>
       <c r="N139" s="1" t="n">
+        <v>0.006696</v>
+      </c>
+      <c r="O139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="O139" s="1" t="n">
-        <v>0.006709</v>
+      <c r="P139" s="1" t="n">
+        <v>0.006696</v>
       </c>
     </row>
     <row r="140">
@@ -7318,9 +7738,12 @@
         <v>0.01394</v>
       </c>
       <c r="N140" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="O140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="O140" s="1" t="n">
+      <c r="P140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -7367,10 +7790,13 @@
         <v>0.0977</v>
       </c>
       <c r="N141" s="1" t="n">
+        <v>0.09755</v>
+      </c>
+      <c r="O141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="O141" s="1" t="n">
-        <v>0.09758</v>
+      <c r="P141" s="1" t="n">
+        <v>0.09755</v>
       </c>
     </row>
     <row r="142">
@@ -7416,9 +7842,12 @@
         <v>0.0542</v>
       </c>
       <c r="N142" s="1" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="O142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="O142" s="1" t="n">
+      <c r="P142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -7465,10 +7894,13 @@
         <v>0.3233</v>
       </c>
       <c r="N143" s="1" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="O143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="O143" s="1" t="n">
-        <v>0.3233</v>
+      <c r="P143" s="1" t="n">
+        <v>0.3229</v>
       </c>
     </row>
     <row r="144">
@@ -7514,10 +7946,13 @@
         <v>0.0257</v>
       </c>
       <c r="N144" s="1" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="O144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="O144" s="1" t="n">
-        <v>0.0257</v>
+      <c r="P144" s="1" t="n">
+        <v>0.02567</v>
       </c>
     </row>
     <row r="145">
@@ -7563,10 +7998,13 @@
         <v>0.2373</v>
       </c>
       <c r="N145" s="1" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="O145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="O145" s="1" t="n">
-        <v>0.2373</v>
+      <c r="P145" s="1" t="n">
+        <v>0.2372</v>
       </c>
     </row>
     <row r="146">
@@ -7612,9 +8050,12 @@
         <v>0.006995</v>
       </c>
       <c r="N146" s="1" t="n">
+        <v>0.006982</v>
+      </c>
+      <c r="O146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="O146" s="1" t="n">
+      <c r="P146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -7661,9 +8102,12 @@
         <v>0.08708</v>
       </c>
       <c r="N147" s="1" t="n">
+        <v>0.08699</v>
+      </c>
+      <c r="O147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="O147" s="1" t="n">
+      <c r="P147" s="1" t="n">
         <v>0.08655</v>
       </c>
     </row>
@@ -7710,9 +8154,12 @@
         <v>0.05235</v>
       </c>
       <c r="N148" s="1" t="n">
-        <v>0.05235</v>
+        <v>0.05244</v>
       </c>
       <c r="O148" s="1" t="n">
+        <v>0.05244</v>
+      </c>
+      <c r="P148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -7759,9 +8206,12 @@
         <v>0.02379</v>
       </c>
       <c r="N149" s="1" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="O149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="O149" s="1" t="n">
+      <c r="P149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -7808,9 +8258,12 @@
         <v>0.08512</v>
       </c>
       <c r="N150" s="1" t="n">
+        <v>0.0853</v>
+      </c>
+      <c r="O150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="O150" s="1" t="n">
+      <c r="P150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -7857,9 +8310,12 @@
         <v>0.02318</v>
       </c>
       <c r="N151" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="O151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="O151" s="1" t="n">
+      <c r="P151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -7906,10 +8362,13 @@
         <v>0.0255</v>
       </c>
       <c r="N152" s="1" t="n">
+        <v>0.02534</v>
+      </c>
+      <c r="O152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="O152" s="1" t="n">
-        <v>0.0255</v>
+      <c r="P152" s="1" t="n">
+        <v>0.02534</v>
       </c>
     </row>
     <row r="153">
@@ -7955,9 +8414,12 @@
         <v>0.0002166</v>
       </c>
       <c r="N153" s="1" t="n">
+        <v>0.0002159</v>
+      </c>
+      <c r="O153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="O153" s="1" t="n">
+      <c r="P153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -8004,10 +8466,13 @@
         <v>0.4404</v>
       </c>
       <c r="N154" s="1" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="O154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="O154" s="1" t="n">
-        <v>0.4404</v>
+      <c r="P154" s="1" t="n">
+        <v>0.4393</v>
       </c>
     </row>
     <row r="155">
@@ -8053,9 +8518,12 @@
         <v>0.06744</v>
       </c>
       <c r="N155" s="1" t="n">
-        <v>0.06744</v>
+        <v>0.06813</v>
       </c>
       <c r="O155" s="1" t="n">
+        <v>0.06813</v>
+      </c>
+      <c r="P155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -8102,9 +8570,12 @@
         <v>0.12781</v>
       </c>
       <c r="N156" s="1" t="n">
+        <v>0.12874</v>
+      </c>
+      <c r="O156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="O156" s="1" t="n">
+      <c r="P156" s="1" t="n">
         <v>0.12781</v>
       </c>
     </row>
@@ -8154,6 +8625,9 @@
         <v>0.4847</v>
       </c>
       <c r="O157" s="1" t="n">
+        <v>0.4847</v>
+      </c>
+      <c r="P157" s="1" t="n">
         <v>0.4839</v>
       </c>
     </row>
@@ -8200,9 +8674,12 @@
         <v>0.4467</v>
       </c>
       <c r="N158" s="1" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="O158" s="1" t="n">
+      <c r="P158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -8249,10 +8726,13 @@
         <v>0.007504</v>
       </c>
       <c r="N159" s="1" t="n">
+        <v>0.007486</v>
+      </c>
+      <c r="O159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="O159" s="1" t="n">
-        <v>0.007493</v>
+      <c r="P159" s="1" t="n">
+        <v>0.007486</v>
       </c>
     </row>
     <row r="160">
@@ -8298,9 +8778,12 @@
         <v>0.004675</v>
       </c>
       <c r="N160" s="1" t="n">
+        <v>0.004653</v>
+      </c>
+      <c r="O160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="O160" s="1" t="n">
+      <c r="P160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -8347,9 +8830,12 @@
         <v>0.004297</v>
       </c>
       <c r="N161" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+      <c r="O161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="O161" s="1" t="n">
+      <c r="P161" s="1" t="n">
         <v>0.004294</v>
       </c>
     </row>
@@ -8396,10 +8882,13 @@
         <v>0.0959</v>
       </c>
       <c r="N162" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="O162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="O162" s="1" t="n">
-        <v>0.0958</v>
+      <c r="P162" s="1" t="n">
+        <v>0.0956</v>
       </c>
     </row>
     <row r="163">
@@ -8445,9 +8934,12 @@
         <v>0.2859</v>
       </c>
       <c r="N163" s="1" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="O163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="O163" s="1" t="n">
+      <c r="P163" s="1" t="n">
         <v>0.2852</v>
       </c>
     </row>
@@ -8494,9 +8986,12 @@
         <v>0.1141</v>
       </c>
       <c r="N164" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="O164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="O164" s="1" t="n">
+      <c r="P164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -8543,9 +9038,12 @@
         <v>0.1754</v>
       </c>
       <c r="N165" s="1" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="O165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="O165" s="1" t="n">
+      <c r="P165" s="1" t="n">
         <v>0.1753</v>
       </c>
     </row>
@@ -8592,9 +9090,12 @@
         <v>0.01013</v>
       </c>
       <c r="N166" s="1" t="n">
-        <v>0.01014</v>
+        <v>0.0102</v>
       </c>
       <c r="O166" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="P166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -8641,9 +9142,12 @@
         <v>1.837</v>
       </c>
       <c r="N167" s="1" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="O167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="O167" s="1" t="n">
+      <c r="P167" s="1" t="n">
         <v>1.826</v>
       </c>
     </row>
@@ -8690,9 +9194,12 @@
         <v>1.333</v>
       </c>
       <c r="N168" s="1" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="O168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="O168" s="1" t="n">
+      <c r="P168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -8739,10 +9246,13 @@
         <v>0.007317</v>
       </c>
       <c r="N169" s="1" t="n">
+        <v>0.007299</v>
+      </c>
+      <c r="O169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="O169" s="1" t="n">
-        <v>0.007304</v>
+      <c r="P169" s="1" t="n">
+        <v>0.007299</v>
       </c>
     </row>
     <row r="170">
@@ -8788,9 +9298,12 @@
         <v>0.0115</v>
       </c>
       <c r="N170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="O170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="O170" s="1" t="n">
+      <c r="P170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -8837,9 +9350,12 @@
         <v>0.005793</v>
       </c>
       <c r="N171" s="1" t="n">
+        <v>0.005803</v>
+      </c>
+      <c r="O171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="O171" s="1" t="n">
+      <c r="P171" s="1" t="n">
         <v>0.005793</v>
       </c>
     </row>
@@ -8886,9 +9402,12 @@
         <v>0.14733</v>
       </c>
       <c r="N172" s="1" t="n">
-        <v>0.14806</v>
+        <v>0.14822</v>
       </c>
       <c r="O172" s="1" t="n">
+        <v>0.14822</v>
+      </c>
+      <c r="P172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -8935,9 +9454,12 @@
         <v>4.893</v>
       </c>
       <c r="N173" s="1" t="n">
-        <v>4.9</v>
+        <v>4.909</v>
       </c>
       <c r="O173" s="1" t="n">
+        <v>4.909</v>
+      </c>
+      <c r="P173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -8984,10 +9506,13 @@
         <v>0.07839</v>
       </c>
       <c r="N174" s="1" t="n">
+        <v>0.07832</v>
+      </c>
+      <c r="O174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="O174" s="1" t="n">
-        <v>0.07839</v>
+      <c r="P174" s="1" t="n">
+        <v>0.07832</v>
       </c>
     </row>
     <row r="175">
@@ -9033,10 +9558,13 @@
         <v>0.007449</v>
       </c>
       <c r="N175" s="1" t="n">
+        <v>0.007413</v>
+      </c>
+      <c r="O175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="O175" s="1" t="n">
-        <v>0.007449</v>
+      <c r="P175" s="1" t="n">
+        <v>0.007413</v>
       </c>
     </row>
     <row r="176">
@@ -9082,10 +9610,13 @@
         <v>0.2013</v>
       </c>
       <c r="N176" s="1" t="n">
+        <v>0.2006</v>
+      </c>
+      <c r="O176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="O176" s="1" t="n">
-        <v>0.2011</v>
+      <c r="P176" s="1" t="n">
+        <v>0.2006</v>
       </c>
     </row>
     <row r="177">
@@ -9131,9 +9662,12 @@
         <v>0.05197</v>
       </c>
       <c r="N177" s="1" t="n">
+        <v>0.05195</v>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="O177" s="1" t="n">
+      <c r="P177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -9180,9 +9714,12 @@
         <v>0.05466</v>
       </c>
       <c r="N178" s="1" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="O178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="O178" s="1" t="n">
+      <c r="P178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -9229,9 +9766,12 @@
         <v>0.02318</v>
       </c>
       <c r="N179" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="O179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="O179" s="1" t="n">
+      <c r="P179" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -9278,9 +9818,12 @@
         <v>0.6938</v>
       </c>
       <c r="N180" s="1" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="O180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="O180" s="1" t="n">
+      <c r="P180" s="1" t="n">
         <v>0.6938</v>
       </c>
     </row>
@@ -9327,9 +9870,12 @@
         <v>0.0003749</v>
       </c>
       <c r="N181" s="1" t="n">
-        <v>0.0003749</v>
+        <v>0.0003768</v>
       </c>
       <c r="O181" s="1" t="n">
+        <v>0.0003768</v>
+      </c>
+      <c r="P181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -9376,9 +9922,12 @@
         <v>0.01261</v>
       </c>
       <c r="N182" s="1" t="n">
+        <v>0.01258</v>
+      </c>
+      <c r="O182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="O182" s="1" t="n">
+      <c r="P182" s="1" t="n">
         <v>0.01256</v>
       </c>
     </row>
@@ -9425,10 +9974,13 @@
         <v>4.238</v>
       </c>
       <c r="N183" s="1" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="O183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="O183" s="1" t="n">
-        <v>4.23</v>
+      <c r="P183" s="1" t="n">
+        <v>4.22</v>
       </c>
     </row>
     <row r="184">
@@ -9474,10 +10026,13 @@
         <v>0.2383</v>
       </c>
       <c r="N184" s="1" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="O184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="O184" s="1" t="n">
-        <v>0.2368</v>
+      <c r="P184" s="1" t="n">
+        <v>0.2363</v>
       </c>
     </row>
     <row r="185">
@@ -9523,9 +10078,12 @@
         <v>0.0369</v>
       </c>
       <c r="N185" s="1" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="O185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="O185" s="1" t="n">
+      <c r="P185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -9572,9 +10130,12 @@
         <v>0.11612</v>
       </c>
       <c r="N186" s="1" t="n">
+        <v>0.11579</v>
+      </c>
+      <c r="O186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="O186" s="1" t="n">
+      <c r="P186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -9621,9 +10182,12 @@
         <v>0.009103</v>
       </c>
       <c r="N187" s="1" t="n">
+        <v>0.009136</v>
+      </c>
+      <c r="O187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="O187" s="1" t="n">
+      <c r="P187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -9670,9 +10234,12 @@
         <v>0.0974</v>
       </c>
       <c r="N188" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="O188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="O188" s="1" t="n">
+      <c r="P188" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -9719,10 +10286,13 @@
         <v>0.02771</v>
       </c>
       <c r="N189" s="1" t="n">
+        <v>0.02762</v>
+      </c>
+      <c r="O189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="O189" s="1" t="n">
-        <v>0.02767</v>
+      <c r="P189" s="1" t="n">
+        <v>0.02762</v>
       </c>
     </row>
     <row r="190">
@@ -9768,9 +10338,12 @@
         <v>0.008829999999999999</v>
       </c>
       <c r="N190" s="1" t="n">
+        <v>0.00877</v>
+      </c>
+      <c r="O190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="O190" s="1" t="n">
+      <c r="P190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -9817,9 +10390,12 @@
         <v>0.001961</v>
       </c>
       <c r="N191" s="1" t="n">
+        <v>0.001952</v>
+      </c>
+      <c r="O191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="O191" s="1" t="n">
+      <c r="P191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -9866,10 +10442,13 @@
         <v>0.1004</v>
       </c>
       <c r="N192" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="O192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="O192" s="1" t="n">
-        <v>0.1003</v>
+      <c r="P192" s="1" t="n">
+        <v>0.1002</v>
       </c>
     </row>
     <row r="193">
@@ -9915,10 +10494,13 @@
         <v>0.02333</v>
       </c>
       <c r="N193" s="1" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="O193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="O193" s="1" t="n">
-        <v>0.02325</v>
+      <c r="P193" s="1" t="n">
+        <v>0.02319</v>
       </c>
     </row>
     <row r="194">
@@ -9964,10 +10546,13 @@
         <v>0.01349</v>
       </c>
       <c r="N194" s="1" t="n">
+        <v>0.01345</v>
+      </c>
+      <c r="O194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="O194" s="1" t="n">
-        <v>0.01346</v>
+      <c r="P194" s="1" t="n">
+        <v>0.01345</v>
       </c>
     </row>
     <row r="195">
@@ -10013,10 +10598,13 @@
         <v>0.02088</v>
       </c>
       <c r="N195" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="O195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="O195" s="1" t="n">
-        <v>0.02088</v>
+      <c r="P195" s="1" t="n">
+        <v>0.02081</v>
       </c>
     </row>
     <row r="196">
@@ -10062,9 +10650,12 @@
         <v>0.17369</v>
       </c>
       <c r="N196" s="1" t="n">
-        <v>0.17509</v>
+        <v>0.1762</v>
       </c>
       <c r="O196" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="P196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -10111,9 +10702,12 @@
         <v>0.007339</v>
       </c>
       <c r="N197" s="1" t="n">
+        <v>0.007364</v>
+      </c>
+      <c r="O197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="O197" s="1" t="n">
+      <c r="P197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -10160,9 +10754,12 @@
         <v>0.01907</v>
       </c>
       <c r="N198" s="1" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="O198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="O198" s="1" t="n">
+      <c r="P198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -10209,9 +10806,12 @@
         <v>0.01642</v>
       </c>
       <c r="N199" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="O199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="O199" s="1" t="n">
+      <c r="P199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -10258,9 +10858,12 @@
         <v>0.2981</v>
       </c>
       <c r="N200" s="1" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="O200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="O200" s="1" t="n">
+      <c r="P200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -10307,10 +10910,13 @@
         <v>0.006234</v>
       </c>
       <c r="N201" s="1" t="n">
+        <v>0.006205</v>
+      </c>
+      <c r="O201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="O201" s="1" t="n">
-        <v>0.006223</v>
+      <c r="P201" s="1" t="n">
+        <v>0.006205</v>
       </c>
     </row>
     <row r="202">
@@ -10356,10 +10962,13 @@
         <v>0.000443</v>
       </c>
       <c r="N202" s="1" t="n">
+        <v>0.0004418</v>
+      </c>
+      <c r="O202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="O202" s="1" t="n">
-        <v>0.000443</v>
+      <c r="P202" s="1" t="n">
+        <v>0.0004418</v>
       </c>
     </row>
     <row r="203">
@@ -10405,10 +11014,13 @@
         <v>0.007271</v>
       </c>
       <c r="N203" s="1" t="n">
+        <v>0.007257</v>
+      </c>
+      <c r="O203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="O203" s="1" t="n">
-        <v>0.007271</v>
+      <c r="P203" s="1" t="n">
+        <v>0.007257</v>
       </c>
     </row>
     <row r="204">
@@ -10454,9 +11066,12 @@
         <v>0.1314</v>
       </c>
       <c r="N204" s="1" t="n">
-        <v>0.1317</v>
+        <v>0.1318</v>
       </c>
       <c r="O204" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="P204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -10503,9 +11118,12 @@
         <v>0.0143</v>
       </c>
       <c r="N205" s="1" t="n">
+        <v>0.01426</v>
+      </c>
+      <c r="O205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="O205" s="1" t="n">
+      <c r="P205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -10552,10 +11170,13 @@
         <v>0.003582</v>
       </c>
       <c r="N206" s="1" t="n">
+        <v>0.003565</v>
+      </c>
+      <c r="O206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="O206" s="1" t="n">
-        <v>0.003566</v>
+      <c r="P206" s="1" t="n">
+        <v>0.003565</v>
       </c>
     </row>
     <row r="207">
@@ -10601,9 +11222,12 @@
         <v>0.05964</v>
       </c>
       <c r="N207" s="1" t="n">
+        <v>0.05957</v>
+      </c>
+      <c r="O207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="O207" s="1" t="n">
+      <c r="P207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -10650,9 +11274,12 @@
         <v>15.52</v>
       </c>
       <c r="N208" s="1" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="O208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="O208" s="1" t="n">
+      <c r="P208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -10699,9 +11326,12 @@
         <v>5190.5</v>
       </c>
       <c r="N209" s="1" t="n">
+        <v>5192.4</v>
+      </c>
+      <c r="O209" s="1" t="n">
         <v>5192.8</v>
       </c>
-      <c r="O209" s="1" t="n">
+      <c r="P209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -10748,10 +11378,13 @@
         <v>0.11977</v>
       </c>
       <c r="N210" s="1" t="n">
+        <v>0.11955</v>
+      </c>
+      <c r="O210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="O210" s="1" t="n">
-        <v>0.11963</v>
+      <c r="P210" s="1" t="n">
+        <v>0.11955</v>
       </c>
     </row>
     <row r="211">
@@ -10797,10 +11430,13 @@
         <v>0.1815</v>
       </c>
       <c r="N211" s="1" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="O211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="O211" s="1" t="n">
-        <v>0.1815</v>
+      <c r="P211" s="1" t="n">
+        <v>0.1802</v>
       </c>
     </row>
     <row r="212">
@@ -10846,9 +11482,12 @@
         <v>0.0304</v>
       </c>
       <c r="N212" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="O212" s="1" t="n">
         <v>0.0308</v>
       </c>
-      <c r="O212" s="1" t="n">
+      <c r="P212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -10898,6 +11537,9 @@
         <v>1.3976</v>
       </c>
       <c r="O213" s="1" t="n">
+        <v>1.3976</v>
+      </c>
+      <c r="P213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -10944,9 +11586,12 @@
         <v>0.05644</v>
       </c>
       <c r="N214" s="1" t="n">
+        <v>0.05646</v>
+      </c>
+      <c r="O214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="O214" s="1" t="n">
+      <c r="P214" s="1" t="n">
         <v>0.05644</v>
       </c>
     </row>
@@ -10993,9 +11638,12 @@
         <v>0.04404</v>
       </c>
       <c r="N215" s="1" t="n">
-        <v>0.04413</v>
+        <v>0.04422</v>
       </c>
       <c r="O215" s="1" t="n">
+        <v>0.04422</v>
+      </c>
+      <c r="P215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -11042,9 +11690,12 @@
         <v>0.15015</v>
       </c>
       <c r="N216" s="1" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="O216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="O216" s="1" t="n">
+      <c r="P216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -11094,6 +11745,9 @@
         <v>0.074</v>
       </c>
       <c r="O217" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="P217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -11140,9 +11794,12 @@
         <v>0.00267</v>
       </c>
       <c r="N218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="O218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="O218" s="1" t="n">
+      <c r="P218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -11189,10 +11846,13 @@
         <v>0.01713</v>
       </c>
       <c r="N219" s="1" t="n">
+        <v>0.01705</v>
+      </c>
+      <c r="O219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="O219" s="1" t="n">
-        <v>0.01713</v>
+      <c r="P219" s="1" t="n">
+        <v>0.01705</v>
       </c>
     </row>
     <row r="220">
@@ -11238,9 +11898,12 @@
         <v>0.05516</v>
       </c>
       <c r="N220" s="1" t="n">
+        <v>0.05519</v>
+      </c>
+      <c r="O220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="O220" s="1" t="n">
+      <c r="P220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -11287,9 +11950,12 @@
         <v>0.02189</v>
       </c>
       <c r="N221" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="O221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="O221" s="1" t="n">
+      <c r="P221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -11336,10 +12002,13 @@
         <v>0.00936</v>
       </c>
       <c r="N222" s="1" t="n">
+        <v>0.009339999999999999</v>
+      </c>
+      <c r="O222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="O222" s="1" t="n">
-        <v>0.009350000000000001</v>
+      <c r="P222" s="1" t="n">
+        <v>0.009339999999999999</v>
       </c>
     </row>
     <row r="223">
@@ -11385,9 +12054,12 @@
         <v>0.0164</v>
       </c>
       <c r="N223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="O223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="O223" s="1" t="n">
+      <c r="P223" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -11434,9 +12106,12 @@
         <v>0.03818</v>
       </c>
       <c r="N224" s="1" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="O224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="O224" s="1" t="n">
+      <c r="P224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -11483,10 +12158,13 @@
         <v>0.001529</v>
       </c>
       <c r="N225" s="1" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="O225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="O225" s="1" t="n">
-        <v>0.001525</v>
+      <c r="P225" s="1" t="n">
+        <v>0.001523</v>
       </c>
     </row>
     <row r="226">
@@ -11535,6 +12213,9 @@
         <v>27.18</v>
       </c>
       <c r="O226" s="1" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="P226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -11581,9 +12262,12 @@
         <v>0.07069</v>
       </c>
       <c r="N227" s="1" t="n">
+        <v>0.07059</v>
+      </c>
+      <c r="O227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="O227" s="1" t="n">
+      <c r="P227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -11630,9 +12314,12 @@
         <v>0.313</v>
       </c>
       <c r="N228" s="1" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="O228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="O228" s="1" t="n">
+      <c r="P228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -11679,9 +12366,12 @@
         <v>18.35</v>
       </c>
       <c r="N229" s="1" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="O229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="O229" s="1" t="n">
+      <c r="P229" s="1" t="n">
         <v>18.35</v>
       </c>
     </row>
@@ -11728,10 +12418,13 @@
         <v>0.01929</v>
       </c>
       <c r="N230" s="1" t="n">
+        <v>0.01923</v>
+      </c>
+      <c r="O230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="O230" s="1" t="n">
-        <v>0.01926</v>
+      <c r="P230" s="1" t="n">
+        <v>0.01923</v>
       </c>
     </row>
     <row r="231">
@@ -11777,9 +12470,12 @@
         <v>0.01218</v>
       </c>
       <c r="N231" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="O231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="O231" s="1" t="n">
+      <c r="P231" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -11826,9 +12522,12 @@
         <v>0.2278</v>
       </c>
       <c r="N232" s="1" t="n">
+        <v>0.2282</v>
+      </c>
+      <c r="O232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="O232" s="1" t="n">
+      <c r="P232" s="1" t="n">
         <v>0.2274</v>
       </c>
     </row>
@@ -11875,9 +12574,12 @@
         <v>0.0711</v>
       </c>
       <c r="N233" s="1" t="n">
+        <v>0.07109</v>
+      </c>
+      <c r="O233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="O233" s="1" t="n">
+      <c r="P233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -11924,9 +12626,12 @@
         <v>0.1706</v>
       </c>
       <c r="N234" s="1" t="n">
+        <v>0.1704</v>
+      </c>
+      <c r="O234" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="O234" s="1" t="n">
+      <c r="P234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -11973,9 +12678,12 @@
         <v>0.0251</v>
       </c>
       <c r="N235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="O235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="O235" s="1" t="n">
+      <c r="P235" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -12022,10 +12730,13 @@
         <v>0.02999</v>
       </c>
       <c r="N236" s="1" t="n">
+        <v>0.02996</v>
+      </c>
+      <c r="O236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="O236" s="1" t="n">
-        <v>0.02998</v>
+      <c r="P236" s="1" t="n">
+        <v>0.02996</v>
       </c>
     </row>
     <row r="237">
@@ -12071,9 +12782,12 @@
         <v>1.994</v>
       </c>
       <c r="N237" s="1" t="n">
-        <v>1.994</v>
+        <v>2.001</v>
       </c>
       <c r="O237" s="1" t="n">
+        <v>2.001</v>
+      </c>
+      <c r="P237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -12120,10 +12834,13 @@
         <v>0.4236</v>
       </c>
       <c r="N238" s="1" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="O238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="O238" s="1" t="n">
-        <v>0.4236</v>
+      <c r="P238" s="1" t="n">
+        <v>0.4201</v>
       </c>
     </row>
     <row r="239">
@@ -12169,9 +12886,12 @@
         <v>0.03335</v>
       </c>
       <c r="N239" s="1" t="n">
+        <v>0.03341</v>
+      </c>
+      <c r="O239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="O239" s="1" t="n">
+      <c r="P239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -12218,9 +12938,12 @@
         <v>0.03404</v>
       </c>
       <c r="N240" s="1" t="n">
+        <v>0.03396</v>
+      </c>
+      <c r="O240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="O240" s="1" t="n">
+      <c r="P240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -12267,10 +12990,13 @@
         <v>0.000752</v>
       </c>
       <c r="N241" s="1" t="n">
+        <v>0.0007489</v>
+      </c>
+      <c r="O241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="O241" s="1" t="n">
-        <v>0.0007509</v>
+      <c r="P241" s="1" t="n">
+        <v>0.0007489</v>
       </c>
     </row>
     <row r="242">
@@ -12316,9 +13042,12 @@
         <v>0.1842</v>
       </c>
       <c r="N242" s="1" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="O242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="O242" s="1" t="n">
+      <c r="P242" s="1" t="n">
         <v>0.1829</v>
       </c>
     </row>
@@ -12365,9 +13094,12 @@
         <v>0.014801</v>
       </c>
       <c r="N243" s="1" t="n">
+        <v>0.014792</v>
+      </c>
+      <c r="O243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="O243" s="1" t="n">
+      <c r="P243" s="1" t="n">
         <v>0.014772</v>
       </c>
     </row>
@@ -12414,9 +13146,12 @@
         <v>3.02e-05</v>
       </c>
       <c r="N244" s="1" t="n">
+        <v>3.02e-05</v>
+      </c>
+      <c r="O244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="O244" s="1" t="n">
+      <c r="P244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -12463,9 +13198,12 @@
         <v>0.03525</v>
       </c>
       <c r="N245" s="1" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="O245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="O245" s="1" t="n">
+      <c r="P245" s="1" t="n">
         <v>0.03514</v>
       </c>
     </row>
@@ -12512,9 +13250,12 @@
         <v>0.08044</v>
       </c>
       <c r="N246" s="1" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="O246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="O246" s="1" t="n">
+      <c r="P246" s="1" t="n">
         <v>0.08037999999999999</v>
       </c>
     </row>
@@ -12561,10 +13302,13 @@
         <v>0.007338</v>
       </c>
       <c r="N247" s="1" t="n">
+        <v>0.007242</v>
+      </c>
+      <c r="O247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="O247" s="1" t="n">
-        <v>0.00728</v>
+      <c r="P247" s="1" t="n">
+        <v>0.007242</v>
       </c>
     </row>
     <row r="248">
@@ -12610,10 +13354,13 @@
         <v>0.09499</v>
       </c>
       <c r="N248" s="1" t="n">
+        <v>0.09438000000000001</v>
+      </c>
+      <c r="O248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="O248" s="1" t="n">
-        <v>0.09499</v>
+      <c r="P248" s="1" t="n">
+        <v>0.09438000000000001</v>
       </c>
     </row>
     <row r="249">
@@ -12662,6 +13409,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="O249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="P249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -12708,10 +13458,13 @@
         <v>0.03498</v>
       </c>
       <c r="N250" s="1" t="n">
+        <v>0.03493</v>
+      </c>
+      <c r="O250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="O250" s="1" t="n">
-        <v>0.03496</v>
+      <c r="P250" s="1" t="n">
+        <v>0.03493</v>
       </c>
     </row>
     <row r="251">
@@ -12757,10 +13510,13 @@
         <v>0.03966</v>
       </c>
       <c r="N251" s="1" t="n">
+        <v>0.03945</v>
+      </c>
+      <c r="O251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="O251" s="1" t="n">
-        <v>0.03953</v>
+      <c r="P251" s="1" t="n">
+        <v>0.03945</v>
       </c>
     </row>
     <row r="252">
@@ -12806,9 +13562,12 @@
         <v>0.0896</v>
       </c>
       <c r="N252" s="1" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="O252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="O252" s="1" t="n">
+      <c r="P252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -12855,9 +13614,12 @@
         <v>4.072</v>
       </c>
       <c r="N253" s="1" t="n">
+        <v>4.073</v>
+      </c>
+      <c r="O253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="O253" s="1" t="n">
+      <c r="P253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -12904,9 +13666,12 @@
         <v>0.1869</v>
       </c>
       <c r="N254" s="1" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="O254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="O254" s="1" t="n">
+      <c r="P254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -12953,10 +13718,13 @@
         <v>0.07206</v>
       </c>
       <c r="N255" s="1" t="n">
+        <v>0.07202</v>
+      </c>
+      <c r="O255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="O255" s="1" t="n">
-        <v>0.07206</v>
+      <c r="P255" s="1" t="n">
+        <v>0.07202</v>
       </c>
     </row>
     <row r="256">
@@ -13002,9 +13770,12 @@
         <v>0.01829</v>
       </c>
       <c r="N256" s="1" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="O256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="O256" s="1" t="n">
+      <c r="P256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -13051,10 +13822,13 @@
         <v>5.949</v>
       </c>
       <c r="N257" s="1" t="n">
+        <v>5.941</v>
+      </c>
+      <c r="O257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="O257" s="1" t="n">
-        <v>5.942</v>
+      <c r="P257" s="1" t="n">
+        <v>5.941</v>
       </c>
     </row>
     <row r="258">
@@ -13100,10 +13874,13 @@
         <v>0.263</v>
       </c>
       <c r="N258" s="1" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="O258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="O258" s="1" t="n">
-        <v>0.2617</v>
+      <c r="P258" s="1" t="n">
+        <v>0.2616</v>
       </c>
     </row>
     <row r="259">
@@ -13149,10 +13926,13 @@
         <v>0.1361</v>
       </c>
       <c r="N259" s="1" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="O259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="O259" s="1" t="n">
-        <v>0.136</v>
+      <c r="P259" s="1" t="n">
+        <v>0.1356</v>
       </c>
     </row>
     <row r="260">
@@ -13198,9 +13978,12 @@
         <v>0.30601</v>
       </c>
       <c r="N260" s="1" t="n">
-        <v>0.30667</v>
+        <v>0.30784</v>
       </c>
       <c r="O260" s="1" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="P260" s="1" t="n">
         <v>0.30525</v>
       </c>
     </row>
@@ -13247,9 +14030,12 @@
         <v>0.09941999999999999</v>
       </c>
       <c r="N261" s="1" t="n">
-        <v>0.09941999999999999</v>
+        <v>0.10011</v>
       </c>
       <c r="O261" s="1" t="n">
+        <v>0.10011</v>
+      </c>
+      <c r="P261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -13296,10 +14082,13 @@
         <v>0.54</v>
       </c>
       <c r="N262" s="1" t="n">
+        <v>0.5387999999999999</v>
+      </c>
+      <c r="O262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="O262" s="1" t="n">
-        <v>0.54</v>
+      <c r="P262" s="1" t="n">
+        <v>0.5387999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -13345,9 +14134,12 @@
         <v>0.2937</v>
       </c>
       <c r="N263" s="1" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="O263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="O263" s="1" t="n">
+      <c r="P263" s="1" t="n">
         <v>0.2914</v>
       </c>
     </row>
@@ -13394,9 +14186,12 @@
         <v>0.962</v>
       </c>
       <c r="N264" s="1" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="O264" s="1" t="n">
         <v>0.972</v>
       </c>
-      <c r="O264" s="1" t="n">
+      <c r="P264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -13443,10 +14238,13 @@
         <v>0.5407</v>
       </c>
       <c r="N265" s="1" t="n">
+        <v>0.5394</v>
+      </c>
+      <c r="O265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="O265" s="1" t="n">
-        <v>0.5403</v>
+      <c r="P265" s="1" t="n">
+        <v>0.5394</v>
       </c>
     </row>
     <row r="266">
@@ -13492,10 +14290,13 @@
         <v>0.07371999999999999</v>
       </c>
       <c r="N266" s="1" t="n">
+        <v>0.0737</v>
+      </c>
+      <c r="O266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="O266" s="1" t="n">
-        <v>0.07371</v>
+      <c r="P266" s="1" t="n">
+        <v>0.0737</v>
       </c>
     </row>
     <row r="267">
@@ -13541,9 +14342,12 @@
         <v>0.02156</v>
       </c>
       <c r="N267" s="1" t="n">
+        <v>0.0216</v>
+      </c>
+      <c r="O267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="O267" s="1" t="n">
+      <c r="P267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -13590,9 +14394,12 @@
         <v>0.01634</v>
       </c>
       <c r="N268" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="O268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="O268" s="1" t="n">
+      <c r="P268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -13639,9 +14446,12 @@
         <v>0.003785</v>
       </c>
       <c r="N269" s="1" t="n">
-        <v>0.003785</v>
+        <v>0.003802</v>
       </c>
       <c r="O269" s="1" t="n">
+        <v>0.003802</v>
+      </c>
+      <c r="P269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -13688,9 +14498,12 @@
         <v>0.00766</v>
       </c>
       <c r="N270" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="O270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="O270" s="1" t="n">
+      <c r="P270" s="1" t="n">
         <v>0.00762</v>
       </c>
     </row>
@@ -13737,9 +14550,12 @@
         <v>0.05522</v>
       </c>
       <c r="N271" s="1" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="O271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="O271" s="1" t="n">
+      <c r="P271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -13786,10 +14602,13 @@
         <v>2.301</v>
       </c>
       <c r="N272" s="1" t="n">
+        <v>2.282</v>
+      </c>
+      <c r="O272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="O272" s="1" t="n">
-        <v>2.3</v>
+      <c r="P272" s="1" t="n">
+        <v>2.282</v>
       </c>
     </row>
     <row r="273">
@@ -13835,9 +14654,12 @@
         <v>0.05501</v>
       </c>
       <c r="N273" s="1" t="n">
+        <v>0.05503</v>
+      </c>
+      <c r="O273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="O273" s="1" t="n">
+      <c r="P273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -13884,9 +14706,12 @@
         <v>0.02327</v>
       </c>
       <c r="N274" s="1" t="n">
-        <v>0.02333</v>
+        <v>0.02336</v>
       </c>
       <c r="O274" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="P274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -13933,10 +14758,13 @@
         <v>1.183</v>
       </c>
       <c r="N275" s="1" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="O275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="O275" s="1" t="n">
-        <v>1.182</v>
+      <c r="P275" s="1" t="n">
+        <v>1.169</v>
       </c>
     </row>
     <row r="276">
@@ -13982,10 +14810,13 @@
         <v>0.2722</v>
       </c>
       <c r="N276" s="1" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="O276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="O276" s="1" t="n">
-        <v>0.2722</v>
+      <c r="P276" s="1" t="n">
+        <v>0.2715</v>
       </c>
     </row>
     <row r="277">
@@ -14031,10 +14862,13 @@
         <v>0.9340000000000001</v>
       </c>
       <c r="N277" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="O277" s="1" t="n">
-        <v>0.9340000000000001</v>
+      <c r="P277" s="1" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="278">
@@ -14080,9 +14914,12 @@
         <v>0.6236</v>
       </c>
       <c r="N278" s="1" t="n">
+        <v>0.6232</v>
+      </c>
+      <c r="O278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="O278" s="1" t="n">
+      <c r="P278" s="1" t="n">
         <v>0.6224</v>
       </c>
     </row>
@@ -14129,9 +14966,12 @@
         <v>0.001348</v>
       </c>
       <c r="N279" s="1" t="n">
+        <v>0.001345</v>
+      </c>
+      <c r="O279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="O279" s="1" t="n">
+      <c r="P279" s="1" t="n">
         <v>0.001344</v>
       </c>
     </row>
@@ -14178,9 +15018,12 @@
         <v>0.005565</v>
       </c>
       <c r="N280" s="1" t="n">
-        <v>0.005567</v>
+        <v>0.005581</v>
       </c>
       <c r="O280" s="1" t="n">
+        <v>0.005581</v>
+      </c>
+      <c r="P280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -14227,10 +15070,13 @@
         <v>1.522</v>
       </c>
       <c r="N281" s="1" t="n">
+        <v>1.519</v>
+      </c>
+      <c r="O281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="O281" s="1" t="n">
-        <v>1.521</v>
+      <c r="P281" s="1" t="n">
+        <v>1.519</v>
       </c>
     </row>
     <row r="282">
@@ -14276,9 +15122,12 @@
         <v>28.33</v>
       </c>
       <c r="N282" s="1" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="O282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="O282" s="1" t="n">
+      <c r="P282" s="1" t="n">
         <v>28.32</v>
       </c>
     </row>
@@ -14325,10 +15174,13 @@
         <v>0.12855</v>
       </c>
       <c r="N283" s="1" t="n">
+        <v>0.12849</v>
+      </c>
+      <c r="O283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="O283" s="1" t="n">
-        <v>0.12855</v>
+      <c r="P283" s="1" t="n">
+        <v>0.12849</v>
       </c>
     </row>
     <row r="284">
@@ -14374,10 +15226,13 @@
         <v>0.01114</v>
       </c>
       <c r="N284" s="1" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="O284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="O284" s="1" t="n">
-        <v>0.01111</v>
+      <c r="P284" s="1" t="n">
+        <v>0.0111</v>
       </c>
     </row>
     <row r="285">
@@ -14423,9 +15278,12 @@
         <v>6.601</v>
       </c>
       <c r="N285" s="1" t="n">
+        <v>6.553</v>
+      </c>
+      <c r="O285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="O285" s="1" t="n">
+      <c r="P285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -14472,10 +15330,13 @@
         <v>0.0185</v>
       </c>
       <c r="N286" s="1" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="O286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="O286" s="1" t="n">
-        <v>0.01844</v>
+      <c r="P286" s="1" t="n">
+        <v>0.01839</v>
       </c>
     </row>
     <row r="287">
@@ -14521,10 +15382,13 @@
         <v>0.008382000000000001</v>
       </c>
       <c r="N287" s="1" t="n">
+        <v>0.008361</v>
+      </c>
+      <c r="O287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="O287" s="1" t="n">
-        <v>0.008378</v>
+      <c r="P287" s="1" t="n">
+        <v>0.008361</v>
       </c>
     </row>
     <row r="288">
@@ -14570,10 +15434,13 @@
         <v>0.3827</v>
       </c>
       <c r="N288" s="1" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="O288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="O288" s="1" t="n">
-        <v>0.3827</v>
+      <c r="P288" s="1" t="n">
+        <v>0.3823</v>
       </c>
     </row>
     <row r="289">
@@ -14619,10 +15486,13 @@
         <v>0.009962</v>
       </c>
       <c r="N289" s="1" t="n">
+        <v>0.009939999999999999</v>
+      </c>
+      <c r="O289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="O289" s="1" t="n">
-        <v>0.009962</v>
+      <c r="P289" s="1" t="n">
+        <v>0.009939999999999999</v>
       </c>
     </row>
     <row r="290">
@@ -14668,10 +15538,13 @@
         <v>0.02588</v>
       </c>
       <c r="N290" s="1" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="O290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="O290" s="1" t="n">
-        <v>0.02588</v>
+      <c r="P290" s="1" t="n">
+        <v>0.02587</v>
       </c>
     </row>
     <row r="291">
@@ -14717,9 +15590,12 @@
         <v>0.096</v>
       </c>
       <c r="N291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="O291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="O291" s="1" t="n">
+      <c r="P291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -14766,9 +15642,12 @@
         <v>0.28707</v>
       </c>
       <c r="N292" s="1" t="n">
-        <v>0.28707</v>
+        <v>0.28708</v>
       </c>
       <c r="O292" s="1" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="P292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -14815,9 +15694,12 @@
         <v>0.0155</v>
       </c>
       <c r="N293" s="1" t="n">
-        <v>0.01551</v>
+        <v>0.01556</v>
       </c>
       <c r="O293" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="P293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -14864,9 +15746,12 @@
         <v>0.003456</v>
       </c>
       <c r="N294" s="1" t="n">
+        <v>0.003422</v>
+      </c>
+      <c r="O294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="O294" s="1" t="n">
+      <c r="P294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -14913,10 +15798,13 @@
         <v>0.042876</v>
       </c>
       <c r="N295" s="1" t="n">
+        <v>0.042677</v>
+      </c>
+      <c r="O295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="O295" s="1" t="n">
-        <v>0.042792</v>
+      <c r="P295" s="1" t="n">
+        <v>0.042677</v>
       </c>
     </row>
     <row r="296">
@@ -14962,9 +15850,12 @@
         <v>0.02972</v>
       </c>
       <c r="N296" s="1" t="n">
+        <v>0.02963</v>
+      </c>
+      <c r="O296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="O296" s="1" t="n">
+      <c r="P296" s="1" t="n">
         <v>0.02929</v>
       </c>
     </row>
@@ -15011,9 +15902,12 @@
         <v>0.03785</v>
       </c>
       <c r="N297" s="1" t="n">
+        <v>0.03788</v>
+      </c>
+      <c r="O297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="O297" s="1" t="n">
+      <c r="P297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -15060,9 +15954,12 @@
         <v>0.08313</v>
       </c>
       <c r="N298" s="1" t="n">
+        <v>0.08286</v>
+      </c>
+      <c r="O298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="O298" s="1" t="n">
+      <c r="P298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -15109,9 +16006,12 @@
         <v>0.00772</v>
       </c>
       <c r="N299" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="O299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="O299" s="1" t="n">
+      <c r="P299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -15158,10 +16058,13 @@
         <v>0.01513</v>
       </c>
       <c r="N300" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="O300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="O300" s="1" t="n">
-        <v>0.01512</v>
+      <c r="P300" s="1" t="n">
+        <v>0.01508</v>
       </c>
     </row>
     <row r="301">
@@ -15207,10 +16110,13 @@
         <v>0.1408</v>
       </c>
       <c r="N301" s="1" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="O301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="O301" s="1" t="n">
-        <v>0.1408</v>
+      <c r="P301" s="1" t="n">
+        <v>0.1402</v>
       </c>
     </row>
     <row r="302">
@@ -15256,9 +16162,12 @@
         <v>0.0006322</v>
       </c>
       <c r="N302" s="1" t="n">
+        <v>0.0006306</v>
+      </c>
+      <c r="O302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="O302" s="1" t="n">
+      <c r="P302" s="1" t="n">
         <v>0.0006284</v>
       </c>
     </row>
@@ -15305,9 +16214,12 @@
         <v>0.06234</v>
       </c>
       <c r="N303" s="1" t="n">
-        <v>0.0624</v>
+        <v>0.06261</v>
       </c>
       <c r="O303" s="1" t="n">
+        <v>0.06261</v>
+      </c>
+      <c r="P303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -15354,9 +16266,12 @@
         <v>0.0001633</v>
       </c>
       <c r="N304" s="1" t="n">
+        <v>0.000163</v>
+      </c>
+      <c r="O304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="O304" s="1" t="n">
+      <c r="P304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -15403,9 +16318,12 @@
         <v>0.06109</v>
       </c>
       <c r="N305" s="1" t="n">
+        <v>0.06096</v>
+      </c>
+      <c r="O305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="O305" s="1" t="n">
+      <c r="P305" s="1" t="n">
         <v>0.06078</v>
       </c>
     </row>
@@ -15452,9 +16370,12 @@
         <v>0.022267</v>
       </c>
       <c r="N306" s="1" t="n">
+        <v>0.022493</v>
+      </c>
+      <c r="O306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="O306" s="1" t="n">
+      <c r="P306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -15501,9 +16422,12 @@
         <v>0.02386</v>
       </c>
       <c r="N307" s="1" t="n">
+        <v>0.02388</v>
+      </c>
+      <c r="O307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="O307" s="1" t="n">
+      <c r="P307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -15550,9 +16474,12 @@
         <v>0.000411</v>
       </c>
       <c r="N308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="O308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="O308" s="1" t="n">
+      <c r="P308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -15599,9 +16526,12 @@
         <v>0.0898</v>
       </c>
       <c r="N309" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="O309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="O309" s="1" t="n">
+      <c r="P309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -15648,10 +16578,13 @@
         <v>0.3845</v>
       </c>
       <c r="N310" s="1" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="O310" s="1" t="n">
-        <v>0.3831</v>
+      <c r="P310" s="1" t="n">
+        <v>0.379</v>
       </c>
     </row>
     <row r="311">
@@ -15697,9 +16630,12 @@
         <v>0.0355</v>
       </c>
       <c r="N311" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="O311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="O311" s="1" t="n">
+      <c r="P311" s="1" t="n">
         <v>0.0355</v>
       </c>
     </row>
@@ -15746,9 +16682,12 @@
         <v>0.02452</v>
       </c>
       <c r="N312" s="1" t="n">
+        <v>0.02459</v>
+      </c>
+      <c r="O312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="O312" s="1" t="n">
+      <c r="P312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -15795,10 +16734,13 @@
         <v>0.04128</v>
       </c>
       <c r="N313" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="O313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="O313" s="1" t="n">
-        <v>0.04128</v>
+      <c r="P313" s="1" t="n">
+        <v>0.0412</v>
       </c>
     </row>
     <row r="314">
@@ -15844,10 +16786,13 @@
         <v>3.982</v>
       </c>
       <c r="N314" s="1" t="n">
+        <v>3.977</v>
+      </c>
+      <c r="O314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="O314" s="1" t="n">
-        <v>3.982</v>
+      <c r="P314" s="1" t="n">
+        <v>3.977</v>
       </c>
     </row>
     <row r="315">
@@ -15893,9 +16838,12 @@
         <v>0.1602</v>
       </c>
       <c r="N315" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="O315" s="1" t="n">
+      <c r="P315" s="1" t="n">
         <v>0.1595</v>
       </c>
     </row>
@@ -15942,9 +16890,12 @@
         <v>0.09137000000000001</v>
       </c>
       <c r="N316" s="1" t="n">
-        <v>0.09137000000000001</v>
+        <v>0.09374</v>
       </c>
       <c r="O316" s="1" t="n">
+        <v>0.09374</v>
+      </c>
+      <c r="P316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -15991,9 +16942,12 @@
         <v>0.06848</v>
       </c>
       <c r="N317" s="1" t="n">
+        <v>0.06826</v>
+      </c>
+      <c r="O317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="O317" s="1" t="n">
+      <c r="P317" s="1" t="n">
         <v>0.06814000000000001</v>
       </c>
     </row>
@@ -16040,9 +16994,12 @@
         <v>0.012454</v>
       </c>
       <c r="N318" s="1" t="n">
+        <v>0.012495</v>
+      </c>
+      <c r="O318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="O318" s="1" t="n">
+      <c r="P318" s="1" t="n">
         <v>0.012414</v>
       </c>
     </row>
@@ -16089,9 +17046,12 @@
         <v>0.001139</v>
       </c>
       <c r="N319" s="1" t="n">
+        <v>0.001136</v>
+      </c>
+      <c r="O319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="O319" s="1" t="n">
+      <c r="P319" s="1" t="n">
         <v>0.001135</v>
       </c>
     </row>
@@ -16138,9 +17098,12 @@
         <v>0.0631</v>
       </c>
       <c r="N320" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="O320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="O320" s="1" t="n">
+      <c r="P320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -16187,9 +17150,12 @@
         <v>0.00527</v>
       </c>
       <c r="N321" s="1" t="n">
+        <v>0.00527</v>
+      </c>
+      <c r="O321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="O321" s="1" t="n">
+      <c r="P321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -16236,9 +17202,12 @@
         <v>0.1124</v>
       </c>
       <c r="N322" s="1" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="O322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="O322" s="1" t="n">
+      <c r="P322" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
@@ -16285,9 +17254,12 @@
         <v>0.0437</v>
       </c>
       <c r="N323" s="1" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="O323" s="1" t="n">
         <v>0.0437</v>
       </c>
-      <c r="O323" s="1" t="n">
+      <c r="P323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -16334,9 +17306,12 @@
         <v>0.01779</v>
       </c>
       <c r="N324" s="1" t="n">
-        <v>0.0179</v>
+        <v>0.01794</v>
       </c>
       <c r="O324" s="1" t="n">
+        <v>0.01794</v>
+      </c>
+      <c r="P324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -16383,10 +17358,13 @@
         <v>0.005672</v>
       </c>
       <c r="N325" s="1" t="n">
+        <v>0.005658</v>
+      </c>
+      <c r="O325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="O325" s="1" t="n">
-        <v>0.005663</v>
+      <c r="P325" s="1" t="n">
+        <v>0.005658</v>
       </c>
     </row>
     <row r="326">
@@ -16432,10 +17410,13 @@
         <v>0.001772</v>
       </c>
       <c r="N326" s="1" t="n">
+        <v>0.001764</v>
+      </c>
+      <c r="O326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="O326" s="1" t="n">
-        <v>0.001765</v>
+      <c r="P326" s="1" t="n">
+        <v>0.001764</v>
       </c>
     </row>
     <row r="327">
@@ -16481,10 +17462,13 @@
         <v>0.0405</v>
       </c>
       <c r="N327" s="1" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="O327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="O327" s="1" t="n">
-        <v>0.04047</v>
+      <c r="P327" s="1" t="n">
+        <v>0.04035</v>
       </c>
     </row>
     <row r="328">
@@ -16530,9 +17514,12 @@
         <v>0.053492</v>
       </c>
       <c r="N328" s="1" t="n">
+        <v>0.053711</v>
+      </c>
+      <c r="O328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="O328" s="1" t="n">
+      <c r="P328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -16579,9 +17566,12 @@
         <v>0.2783</v>
       </c>
       <c r="N329" s="1" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="O329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="O329" s="1" t="n">
+      <c r="P329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -16628,9 +17618,12 @@
         <v>0.1591</v>
       </c>
       <c r="N330" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="O330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="O330" s="1" t="n">
+      <c r="P330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -16677,9 +17670,12 @@
         <v>0.05385</v>
       </c>
       <c r="N331" s="1" t="n">
+        <v>0.05374</v>
+      </c>
+      <c r="O331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="O331" s="1" t="n">
+      <c r="P331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -16726,9 +17722,12 @@
         <v>0.3614</v>
       </c>
       <c r="N332" s="1" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="O332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="O332" s="1" t="n">
+      <c r="P332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -16775,9 +17774,12 @@
         <v>0.03048</v>
       </c>
       <c r="N333" s="1" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="O333" s="1" t="n">
         <v>0.03051</v>
       </c>
-      <c r="O333" s="1" t="n">
+      <c r="P333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -16824,10 +17826,13 @@
         <v>0.01805</v>
       </c>
       <c r="N334" s="1" t="n">
+        <v>0.01751</v>
+      </c>
+      <c r="O334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="O334" s="1" t="n">
-        <v>0.01756</v>
+      <c r="P334" s="1" t="n">
+        <v>0.01751</v>
       </c>
     </row>
     <row r="335">
@@ -16873,9 +17878,12 @@
         <v>0.0579</v>
       </c>
       <c r="N335" s="1" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="O335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="O335" s="1" t="n">
+      <c r="P335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -16922,9 +17930,12 @@
         <v>0.09082</v>
       </c>
       <c r="N336" s="1" t="n">
+        <v>0.09102</v>
+      </c>
+      <c r="O336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="O336" s="1" t="n">
+      <c r="P336" s="1" t="n">
         <v>0.09082</v>
       </c>
     </row>
@@ -16971,9 +17982,12 @@
         <v>0.17936</v>
       </c>
       <c r="N337" s="1" t="n">
+        <v>0.17991</v>
+      </c>
+      <c r="O337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="O337" s="1" t="n">
+      <c r="P337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -17020,9 +18034,12 @@
         <v>0.02096</v>
       </c>
       <c r="N338" s="1" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="O338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="O338" s="1" t="n">
+      <c r="P338" s="1" t="n">
         <v>0.02092</v>
       </c>
     </row>
@@ -17069,9 +18086,12 @@
         <v>0.1317</v>
       </c>
       <c r="N339" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="O339" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="O339" s="1" t="n">
+      <c r="P339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -17118,10 +18138,13 @@
         <v>0.007926000000000001</v>
       </c>
       <c r="N340" s="1" t="n">
+        <v>0.007901999999999999</v>
+      </c>
+      <c r="O340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="O340" s="1" t="n">
-        <v>0.007915999999999999</v>
+      <c r="P340" s="1" t="n">
+        <v>0.007901999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -17167,9 +18190,12 @@
         <v>4.422</v>
       </c>
       <c r="N341" s="1" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="O341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="O341" s="1" t="n">
+      <c r="P341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -17216,9 +18242,12 @@
         <v>0.18981</v>
       </c>
       <c r="N342" s="1" t="n">
+        <v>0.1885</v>
+      </c>
+      <c r="O342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="O342" s="1" t="n">
+      <c r="P342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -17265,9 +18294,12 @@
         <v>0.08354</v>
       </c>
       <c r="N343" s="1" t="n">
+        <v>0.08336</v>
+      </c>
+      <c r="O343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="O343" s="1" t="n">
+      <c r="P343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -17314,9 +18346,12 @@
         <v>0.1819</v>
       </c>
       <c r="N344" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="O344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="O344" s="1" t="n">
+      <c r="P344" s="1" t="n">
         <v>0.1819</v>
       </c>
     </row>
@@ -17363,9 +18398,12 @@
         <v>0.00324</v>
       </c>
       <c r="N345" s="1" t="n">
+        <v>0.003241</v>
+      </c>
+      <c r="O345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="O345" s="1" t="n">
+      <c r="P345" s="1" t="n">
         <v>0.00324</v>
       </c>
     </row>
@@ -17412,9 +18450,12 @@
         <v>0.09127</v>
       </c>
       <c r="N346" s="1" t="n">
+        <v>0.09125999999999999</v>
+      </c>
+      <c r="O346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="O346" s="1" t="n">
+      <c r="P346" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -17461,9 +18502,12 @@
         <v>2.254</v>
       </c>
       <c r="N347" s="1" t="n">
+        <v>2.253</v>
+      </c>
+      <c r="O347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="O347" s="1" t="n">
+      <c r="P347" s="1" t="n">
         <v>2.243</v>
       </c>
     </row>
@@ -17510,10 +18554,13 @@
         <v>0.3034</v>
       </c>
       <c r="N348" s="1" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="O348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="O348" s="1" t="n">
-        <v>0.3034</v>
+      <c r="P348" s="1" t="n">
+        <v>0.303</v>
       </c>
     </row>
     <row r="349">
@@ -17559,10 +18606,13 @@
         <v>0.02969</v>
       </c>
       <c r="N349" s="1" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="O349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="O349" s="1" t="n">
-        <v>0.02969</v>
+      <c r="P349" s="1" t="n">
+        <v>0.02967</v>
       </c>
     </row>
     <row r="350">
@@ -17608,9 +18658,12 @@
         <v>0.1278</v>
       </c>
       <c r="N350" s="1" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="O350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="O350" s="1" t="n">
+      <c r="P350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -17657,10 +18710,13 @@
         <v>0.06682</v>
       </c>
       <c r="N351" s="1" t="n">
+        <v>0.06655</v>
+      </c>
+      <c r="O351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="O351" s="1" t="n">
-        <v>0.06682</v>
+      <c r="P351" s="1" t="n">
+        <v>0.06655</v>
       </c>
     </row>
     <row r="352">
@@ -17706,9 +18762,12 @@
         <v>0.06259000000000001</v>
       </c>
       <c r="N352" s="1" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="O352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="O352" s="1" t="n">
+      <c r="P352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -17755,9 +18814,12 @@
         <v>0.06346</v>
       </c>
       <c r="N353" s="1" t="n">
+        <v>0.06346</v>
+      </c>
+      <c r="O353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="O353" s="1" t="n">
+      <c r="P353" s="1" t="n">
         <v>0.06346</v>
       </c>
     </row>
@@ -17804,9 +18866,12 @@
         <v>0.10819</v>
       </c>
       <c r="N354" s="1" t="n">
-        <v>0.10819</v>
+        <v>0.10844</v>
       </c>
       <c r="O354" s="1" t="n">
+        <v>0.10844</v>
+      </c>
+      <c r="P354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -17853,10 +18918,13 @@
         <v>0.0901</v>
       </c>
       <c r="N355" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="O355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="O355" s="1" t="n">
-        <v>0.0901</v>
+      <c r="P355" s="1" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="356">
@@ -17902,9 +18970,12 @@
         <v>0.07026</v>
       </c>
       <c r="N356" s="1" t="n">
+        <v>0.07001</v>
+      </c>
+      <c r="O356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="O356" s="1" t="n">
+      <c r="P356" s="1" t="n">
         <v>0.06985</v>
       </c>
     </row>
@@ -17951,9 +19022,12 @@
         <v>0.4533</v>
       </c>
       <c r="N357" s="1" t="n">
+        <v>0.4522</v>
+      </c>
+      <c r="O357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="O357" s="1" t="n">
+      <c r="P357" s="1" t="n">
         <v>0.4521</v>
       </c>
     </row>
@@ -18000,9 +19074,12 @@
         <v>0.03496</v>
       </c>
       <c r="N358" s="1" t="n">
+        <v>0.03491</v>
+      </c>
+      <c r="O358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="O358" s="1" t="n">
+      <c r="P358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -18049,10 +19126,13 @@
         <v>0.01479</v>
       </c>
       <c r="N359" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="O359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="O359" s="1" t="n">
-        <v>0.01476</v>
+      <c r="P359" s="1" t="n">
+        <v>0.01474</v>
       </c>
     </row>
     <row r="360">
@@ -18098,9 +19178,12 @@
         <v>0.1336</v>
       </c>
       <c r="N360" s="1" t="n">
+        <v>0.13359</v>
+      </c>
+      <c r="O360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="O360" s="1" t="n">
+      <c r="P360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -18147,9 +19230,12 @@
         <v>0.0005864000000000001</v>
       </c>
       <c r="N361" s="1" t="n">
+        <v>0.0005861</v>
+      </c>
+      <c r="O361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="O361" s="1" t="n">
+      <c r="P361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -18196,9 +19282,12 @@
         <v>0.03884</v>
       </c>
       <c r="N362" s="1" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="O362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="O362" s="1" t="n">
+      <c r="P362" s="1" t="n">
         <v>0.0386</v>
       </c>
     </row>
@@ -18245,9 +19334,12 @@
         <v>3.234</v>
       </c>
       <c r="N363" s="1" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="O363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="O363" s="1" t="n">
+      <c r="P363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -18294,10 +19386,13 @@
         <v>0.165</v>
       </c>
       <c r="N364" s="1" t="n">
+        <v>0.1642</v>
+      </c>
+      <c r="O364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="O364" s="1" t="n">
-        <v>0.165</v>
+      <c r="P364" s="1" t="n">
+        <v>0.1642</v>
       </c>
     </row>
     <row r="365">
@@ -18343,9 +19438,12 @@
         <v>0.1137</v>
       </c>
       <c r="N365" s="1" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="O365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="O365" s="1" t="n">
+      <c r="P365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -18392,10 +19490,13 @@
         <v>0.0006405</v>
       </c>
       <c r="N366" s="1" t="n">
+        <v>0.0006389</v>
+      </c>
+      <c r="O366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="O366" s="1" t="n">
-        <v>0.0006405</v>
+      <c r="P366" s="1" t="n">
+        <v>0.0006389</v>
       </c>
     </row>
     <row r="367">
@@ -18441,10 +19542,13 @@
         <v>0.05944</v>
       </c>
       <c r="N367" s="1" t="n">
+        <v>0.05923</v>
+      </c>
+      <c r="O367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="O367" s="1" t="n">
-        <v>0.05927</v>
+      <c r="P367" s="1" t="n">
+        <v>0.05923</v>
       </c>
     </row>
     <row r="368">
@@ -18490,10 +19594,13 @@
         <v>0.08211</v>
       </c>
       <c r="N368" s="1" t="n">
+        <v>0.08198999999999999</v>
+      </c>
+      <c r="O368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="O368" s="1" t="n">
-        <v>0.08211</v>
+      <c r="P368" s="1" t="n">
+        <v>0.08198999999999999</v>
       </c>
     </row>
     <row r="369">
@@ -18539,10 +19646,13 @@
         <v>0.03965</v>
       </c>
       <c r="N369" s="1" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="O369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="O369" s="1" t="n">
-        <v>0.03965</v>
+      <c r="P369" s="1" t="n">
+        <v>0.03957</v>
       </c>
     </row>
     <row r="370">
@@ -18588,10 +19698,13 @@
         <v>3.704</v>
       </c>
       <c r="N370" s="1" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="O370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="O370" s="1" t="n">
-        <v>3.695</v>
+      <c r="P370" s="1" t="n">
+        <v>3.689</v>
       </c>
     </row>
     <row r="371">
@@ -18637,10 +19750,13 @@
         <v>0.1217</v>
       </c>
       <c r="N371" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="O371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="O371" s="1" t="n">
-        <v>0.1216</v>
+      <c r="P371" s="1" t="n">
+        <v>0.121</v>
       </c>
     </row>
     <row r="372">
@@ -18686,9 +19802,12 @@
         <v>0.01482</v>
       </c>
       <c r="N372" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="O372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="O372" s="1" t="n">
+      <c r="P372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -18738,6 +19857,9 @@
         <v>0.02205</v>
       </c>
       <c r="O373" s="1" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="P373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -18784,9 +19906,12 @@
         <v>1.8663</v>
       </c>
       <c r="N374" s="1" t="n">
+        <v>1.856</v>
+      </c>
+      <c r="O374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="O374" s="1" t="n">
+      <c r="P374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -18833,10 +19958,13 @@
         <v>0.02104</v>
       </c>
       <c r="N375" s="1" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="O375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="O375" s="1" t="n">
-        <v>0.02095</v>
+      <c r="P375" s="1" t="n">
+        <v>0.02094</v>
       </c>
     </row>
     <row r="376">
@@ -18882,9 +20010,12 @@
         <v>1.32</v>
       </c>
       <c r="N376" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="O376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="O376" s="1" t="n">
+      <c r="P376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -18931,9 +20062,12 @@
         <v>0.2836</v>
       </c>
       <c r="N377" s="1" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="O377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="O377" s="1" t="n">
+      <c r="P377" s="1" t="n">
         <v>0.2826</v>
       </c>
     </row>
@@ -18980,9 +20114,12 @@
         <v>0.01563</v>
       </c>
       <c r="N378" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="O378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="O378" s="1" t="n">
+      <c r="P378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -19029,9 +20166,12 @@
         <v>1.5303</v>
       </c>
       <c r="N379" s="1" t="n">
+        <v>1.5383</v>
+      </c>
+      <c r="O379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="O379" s="1" t="n">
+      <c r="P379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -19078,10 +20218,13 @@
         <v>6.931e-05</v>
       </c>
       <c r="N380" s="1" t="n">
+        <v>6.913e-05</v>
+      </c>
+      <c r="O380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="O380" s="1" t="n">
-        <v>6.918e-05</v>
+      <c r="P380" s="1" t="n">
+        <v>6.913e-05</v>
       </c>
     </row>
     <row r="381">
@@ -19127,9 +20270,12 @@
         <v>2.552</v>
       </c>
       <c r="N381" s="1" t="n">
+        <v>2.551</v>
+      </c>
+      <c r="O381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="O381" s="1" t="n">
+      <c r="P381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -19176,10 +20322,13 @@
         <v>0.06707</v>
       </c>
       <c r="N382" s="1" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="O382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="O382" s="1" t="n">
-        <v>0.06707</v>
+      <c r="P382" s="1" t="n">
+        <v>0.06697</v>
       </c>
     </row>
     <row r="383">
@@ -19225,9 +20374,12 @@
         <v>0.01728</v>
       </c>
       <c r="N383" s="1" t="n">
+        <v>0.01752</v>
+      </c>
+      <c r="O383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="O383" s="1" t="n">
+      <c r="P383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -19274,9 +20426,12 @@
         <v>0.0525</v>
       </c>
       <c r="N384" s="1" t="n">
+        <v>0.05188</v>
+      </c>
+      <c r="O384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="O384" s="1" t="n">
+      <c r="P384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -19323,9 +20478,12 @@
         <v>7.582</v>
       </c>
       <c r="N385" s="1" t="n">
+        <v>7.577</v>
+      </c>
+      <c r="O385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="O385" s="1" t="n">
+      <c r="P385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -19372,9 +20530,12 @@
         <v>0.003284</v>
       </c>
       <c r="N386" s="1" t="n">
+        <v>0.00329</v>
+      </c>
+      <c r="O386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="O386" s="1" t="n">
+      <c r="P386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -19421,10 +20582,13 @@
         <v>0.0003818</v>
       </c>
       <c r="N387" s="1" t="n">
+        <v>0.0003814</v>
+      </c>
+      <c r="O387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="O387" s="1" t="n">
-        <v>0.0003818</v>
+      <c r="P387" s="1" t="n">
+        <v>0.0003814</v>
       </c>
     </row>
     <row r="388">
@@ -19470,10 +20634,13 @@
         <v>0.00953</v>
       </c>
       <c r="N388" s="1" t="n">
+        <v>0.009520000000000001</v>
+      </c>
+      <c r="O388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="O388" s="1" t="n">
-        <v>0.00953</v>
+      <c r="P388" s="1" t="n">
+        <v>0.009520000000000001</v>
       </c>
     </row>
     <row r="389">
@@ -19519,9 +20686,12 @@
         <v>0.2886</v>
       </c>
       <c r="N389" s="1" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="O389" s="1" t="n">
         <v>0.2902</v>
       </c>
-      <c r="O389" s="1" t="n">
+      <c r="P389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -19568,9 +20738,12 @@
         <v>0.0253</v>
       </c>
       <c r="N390" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="O390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="O390" s="1" t="n">
+      <c r="P390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -19617,9 +20790,12 @@
         <v>2.815</v>
       </c>
       <c r="N391" s="1" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="O391" s="1" t="n">
         <v>2.833</v>
       </c>
-      <c r="O391" s="1" t="n">
+      <c r="P391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -19666,9 +20842,12 @@
         <v>0.01349</v>
       </c>
       <c r="N392" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="O392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="O392" s="1" t="n">
+      <c r="P392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -19718,6 +20897,9 @@
         <v>0.00237</v>
       </c>
       <c r="O393" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="P393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -19764,9 +20946,12 @@
         <v>0.05947</v>
       </c>
       <c r="N394" s="1" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="O394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="O394" s="1" t="n">
+      <c r="P394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -19813,9 +20998,12 @@
         <v>0.0404</v>
       </c>
       <c r="N395" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="O395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="O395" s="1" t="n">
+      <c r="P395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -19862,9 +21050,12 @@
         <v>0.0925</v>
       </c>
       <c r="N396" s="1" t="n">
+        <v>0.09229</v>
+      </c>
+      <c r="O396" s="1" t="n">
         <v>0.09272</v>
       </c>
-      <c r="O396" s="1" t="n">
+      <c r="P396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -19911,9 +21102,12 @@
         <v>0.1518</v>
       </c>
       <c r="N397" s="1" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="O397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="O397" s="1" t="n">
+      <c r="P397" s="1" t="n">
         <v>0.1517</v>
       </c>
     </row>
@@ -19960,9 +21154,12 @@
         <v>0.929</v>
       </c>
       <c r="N398" s="1" t="n">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
       <c r="O398" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -20009,9 +21206,12 @@
         <v>0.05247</v>
       </c>
       <c r="N399" s="1" t="n">
+        <v>0.05246</v>
+      </c>
+      <c r="O399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="O399" s="1" t="n">
+      <c r="P399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -20058,10 +21258,13 @@
         <v>2.518</v>
       </c>
       <c r="N400" s="1" t="n">
+        <v>2.516</v>
+      </c>
+      <c r="O400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="O400" s="1" t="n">
-        <v>2.517</v>
+      <c r="P400" s="1" t="n">
+        <v>2.516</v>
       </c>
     </row>
     <row r="401">
@@ -20107,9 +21310,12 @@
         <v>0.01785</v>
       </c>
       <c r="N401" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="O401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="O401" s="1" t="n">
+      <c r="P401" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -20156,9 +21362,12 @@
         <v>0.08049000000000001</v>
       </c>
       <c r="N402" s="1" t="n">
+        <v>0.08003</v>
+      </c>
+      <c r="O402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="O402" s="1" t="n">
+      <c r="P402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -20205,9 +21414,12 @@
         <v>1.2494</v>
       </c>
       <c r="N403" s="1" t="n">
+        <v>1.2484</v>
+      </c>
+      <c r="O403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="O403" s="1" t="n">
+      <c r="P403" s="1" t="n">
         <v>1.2455</v>
       </c>
     </row>
@@ -20254,9 +21466,12 @@
         <v>0.00714</v>
       </c>
       <c r="N404" s="1" t="n">
+        <v>0.00714</v>
+      </c>
+      <c r="O404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="O404" s="1" t="n">
+      <c r="P404" s="1" t="n">
         <v>0.00714</v>
       </c>
     </row>
@@ -20303,9 +21518,12 @@
         <v>0.5012</v>
       </c>
       <c r="N405" s="1" t="n">
-        <v>0.5012</v>
+        <v>0.5017</v>
       </c>
       <c r="O405" s="1" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="P405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -20352,9 +21570,12 @@
         <v>0.01151</v>
       </c>
       <c r="N406" s="1" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="O406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="O406" s="1" t="n">
+      <c r="P406" s="1" t="n">
         <v>0.01146</v>
       </c>
     </row>
@@ -20401,10 +21622,13 @@
         <v>0.04613</v>
       </c>
       <c r="N407" s="1" t="n">
+        <v>0.04603</v>
+      </c>
+      <c r="O407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="O407" s="1" t="n">
-        <v>0.04612</v>
+      <c r="P407" s="1" t="n">
+        <v>0.04603</v>
       </c>
     </row>
     <row r="408">
@@ -20450,10 +21674,13 @@
         <v>0.03951</v>
       </c>
       <c r="N408" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="O408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="O408" s="1" t="n">
-        <v>0.0394</v>
+      <c r="P408" s="1" t="n">
+        <v>0.03939</v>
       </c>
     </row>
     <row r="409">
@@ -20499,10 +21726,13 @@
         <v>0.05241</v>
       </c>
       <c r="N409" s="1" t="n">
+        <v>0.05227</v>
+      </c>
+      <c r="O409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="O409" s="1" t="n">
-        <v>0.05234</v>
+      <c r="P409" s="1" t="n">
+        <v>0.05227</v>
       </c>
     </row>
     <row r="410">
@@ -20548,10 +21778,13 @@
         <v>0.01235</v>
       </c>
       <c r="N410" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="O410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="O410" s="1" t="n">
-        <v>0.01235</v>
+      <c r="P410" s="1" t="n">
+        <v>0.01232</v>
       </c>
     </row>
     <row r="411">
@@ -20597,9 +21830,12 @@
         <v>0.06376</v>
       </c>
       <c r="N411" s="1" t="n">
+        <v>0.06362</v>
+      </c>
+      <c r="O411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="O411" s="1" t="n">
+      <c r="P411" s="1" t="n">
         <v>0.06347</v>
       </c>
     </row>
@@ -20646,9 +21882,12 @@
         <v>0.04144</v>
       </c>
       <c r="N412" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="O412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="O412" s="1" t="n">
+      <c r="P412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -20695,9 +21934,12 @@
         <v>1.126</v>
       </c>
       <c r="N413" s="1" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="O413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="O413" s="1" t="n">
+      <c r="P413" s="1" t="n">
         <v>1.117</v>
       </c>
     </row>
@@ -20744,9 +21986,12 @@
         <v>0.2628</v>
       </c>
       <c r="N414" s="1" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="O414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="O414" s="1" t="n">
+      <c r="P414" s="1" t="n">
         <v>0.2625</v>
       </c>
     </row>
@@ -20793,10 +22038,13 @@
         <v>0.001221</v>
       </c>
       <c r="N415" s="1" t="n">
+        <v>0.001214</v>
+      </c>
+      <c r="O415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="O415" s="1" t="n">
-        <v>0.00122</v>
+      <c r="P415" s="1" t="n">
+        <v>0.001214</v>
       </c>
     </row>
     <row r="416">
@@ -20842,9 +22090,12 @@
         <v>0.03195</v>
       </c>
       <c r="N416" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="O416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="O416" s="1" t="n">
+      <c r="P416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -20891,9 +22142,12 @@
         <v>0.01469</v>
       </c>
       <c r="N417" s="1" t="n">
+        <v>0.01469</v>
+      </c>
+      <c r="O417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="O417" s="1" t="n">
+      <c r="P417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -20940,9 +22194,12 @@
         <v>0.1487</v>
       </c>
       <c r="N418" s="1" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="O418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="O418" s="1" t="n">
+      <c r="P418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -20989,9 +22246,12 @@
         <v>0.04968</v>
       </c>
       <c r="N419" s="1" t="n">
+        <v>0.04952</v>
+      </c>
+      <c r="O419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="O419" s="1" t="n">
+      <c r="P419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -21038,9 +22298,12 @@
         <v>66.52</v>
       </c>
       <c r="N420" s="1" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="O420" s="1" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="O420" s="1" t="n">
+      <c r="P420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -21087,9 +22350,12 @@
         <v>0.879</v>
       </c>
       <c r="N421" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="O421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="O421" s="1" t="n">
+      <c r="P421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -21136,9 +22402,12 @@
         <v>0.012549</v>
       </c>
       <c r="N422" s="1" t="n">
+        <v>0.012561</v>
+      </c>
+      <c r="O422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="O422" s="1" t="n">
+      <c r="P422" s="1" t="n">
         <v>0.012549</v>
       </c>
     </row>
@@ -21185,9 +22454,12 @@
         <v>0.01597</v>
       </c>
       <c r="N423" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="O423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="O423" s="1" t="n">
+      <c r="P423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -21234,9 +22506,12 @@
         <v>0.27039</v>
       </c>
       <c r="N424" s="1" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="O424" s="1" t="n">
         <v>0.27102</v>
       </c>
-      <c r="O424" s="1" t="n">
+      <c r="P424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -21283,9 +22558,12 @@
         <v>0.6004</v>
       </c>
       <c r="N425" s="1" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="O425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="O425" s="1" t="n">
+      <c r="P425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -21332,10 +22610,13 @@
         <v>0.005555</v>
       </c>
       <c r="N426" s="1" t="n">
+        <v>0.005515</v>
+      </c>
+      <c r="O426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="O426" s="1" t="n">
-        <v>0.005555</v>
+      <c r="P426" s="1" t="n">
+        <v>0.005515</v>
       </c>
     </row>
     <row r="427">
@@ -21381,9 +22662,12 @@
         <v>0.0496</v>
       </c>
       <c r="N427" s="1" t="n">
-        <v>0.0496</v>
+        <v>0.04962</v>
       </c>
       <c r="O427" s="1" t="n">
+        <v>0.04962</v>
+      </c>
+      <c r="P427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -21430,9 +22714,12 @@
         <v>0.1269</v>
       </c>
       <c r="N428" s="1" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="O428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="O428" s="1" t="n">
+      <c r="P428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -21479,9 +22766,12 @@
         <v>0.003188</v>
       </c>
       <c r="N429" s="1" t="n">
+        <v>0.003196</v>
+      </c>
+      <c r="O429" s="1" t="n">
         <v>0.0032</v>
       </c>
-      <c r="O429" s="1" t="n">
+      <c r="P429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -21528,9 +22818,12 @@
         <v>0.0365</v>
       </c>
       <c r="N430" s="1" t="n">
+        <v>0.03644</v>
+      </c>
+      <c r="O430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="O430" s="1" t="n">
+      <c r="P430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -21577,10 +22870,13 @@
         <v>0.3981</v>
       </c>
       <c r="N431" s="1" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="O431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="O431" s="1" t="n">
-        <v>0.3981</v>
+      <c r="P431" s="1" t="n">
+        <v>0.3959</v>
       </c>
     </row>
     <row r="432">
@@ -21626,10 +22922,13 @@
         <v>0.004505</v>
       </c>
       <c r="N432" s="1" t="n">
+        <v>0.004486</v>
+      </c>
+      <c r="O432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="O432" s="1" t="n">
-        <v>0.0045</v>
+      <c r="P432" s="1" t="n">
+        <v>0.004486</v>
       </c>
     </row>
     <row r="433">
@@ -21675,9 +22974,12 @@
         <v>0.0983</v>
       </c>
       <c r="N433" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="O433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="O433" s="1" t="n">
+      <c r="P433" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -21724,9 +23026,12 @@
         <v>0.01241</v>
       </c>
       <c r="N434" s="1" t="n">
+        <v>0.01241</v>
+      </c>
+      <c r="O434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="O434" s="1" t="n">
+      <c r="P434" s="1" t="n">
         <v>0.01238</v>
       </c>
     </row>
@@ -21773,9 +23078,12 @@
         <v>1.982</v>
       </c>
       <c r="N435" s="1" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="O435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="O435" s="1" t="n">
+      <c r="P435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -21822,10 +23130,13 @@
         <v>0.001798</v>
       </c>
       <c r="N436" s="1" t="n">
+        <v>0.001792</v>
+      </c>
+      <c r="O436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="O436" s="1" t="n">
-        <v>0.001798</v>
+      <c r="P436" s="1" t="n">
+        <v>0.001792</v>
       </c>
     </row>
     <row r="437">
@@ -21871,9 +23182,12 @@
         <v>0.4424</v>
       </c>
       <c r="N437" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="O437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="O437" s="1" t="n">
+      <c r="P437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -21920,9 +23234,12 @@
         <v>0.00536</v>
       </c>
       <c r="N438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="O438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="O438" s="1" t="n">
+      <c r="P438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -21969,9 +23286,12 @@
         <v>0.1036</v>
       </c>
       <c r="N439" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="O439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="O439" s="1" t="n">
+      <c r="P439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -22018,9 +23338,12 @@
         <v>0.03426</v>
       </c>
       <c r="N440" s="1" t="n">
+        <v>0.03422</v>
+      </c>
+      <c r="O440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="O440" s="1" t="n">
+      <c r="P440" s="1" t="n">
         <v>0.03417</v>
       </c>
     </row>
@@ -22067,9 +23390,12 @@
         <v>0.08209</v>
       </c>
       <c r="N441" s="1" t="n">
+        <v>0.08205999999999999</v>
+      </c>
+      <c r="O441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="O441" s="1" t="n">
+      <c r="P441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -22116,9 +23442,12 @@
         <v>1.306</v>
       </c>
       <c r="N442" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="O442" s="1" t="n">
+      <c r="P442" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -22165,9 +23494,12 @@
         <v>0.07555000000000001</v>
       </c>
       <c r="N443" s="1" t="n">
-        <v>0.07581</v>
+        <v>0.07585</v>
       </c>
       <c r="O443" s="1" t="n">
+        <v>0.07585</v>
+      </c>
+      <c r="P443" s="1" t="n">
         <v>0.07549</v>
       </c>
     </row>
@@ -22214,10 +23546,13 @@
         <v>0.07692</v>
       </c>
       <c r="N444" s="1" t="n">
+        <v>0.07650999999999999</v>
+      </c>
+      <c r="O444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="O444" s="1" t="n">
-        <v>0.07661</v>
+      <c r="P444" s="1" t="n">
+        <v>0.07650999999999999</v>
       </c>
     </row>
     <row r="445">
@@ -22263,10 +23598,13 @@
         <v>0.04356</v>
       </c>
       <c r="N445" s="1" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="O445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="O445" s="1" t="n">
-        <v>0.04356</v>
+      <c r="P445" s="1" t="n">
+        <v>0.04338</v>
       </c>
     </row>
     <row r="446">
@@ -22312,10 +23650,13 @@
         <v>0.02141</v>
       </c>
       <c r="N446" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="O446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="O446" s="1" t="n">
-        <v>0.02141</v>
+      <c r="P446" s="1" t="n">
+        <v>0.02133</v>
       </c>
     </row>
     <row r="447">
@@ -22361,9 +23702,12 @@
         <v>0.2804</v>
       </c>
       <c r="N447" s="1" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="O447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="O447" s="1" t="n">
+      <c r="P447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -22410,9 +23754,12 @@
         <v>0.03119</v>
       </c>
       <c r="N448" s="1" t="n">
+        <v>0.03113</v>
+      </c>
+      <c r="O448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="O448" s="1" t="n">
+      <c r="P448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -22459,9 +23806,12 @@
         <v>0.00645</v>
       </c>
       <c r="N449" s="1" t="n">
+        <v>0.00646</v>
+      </c>
+      <c r="O449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="O449" s="1" t="n">
+      <c r="P449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -22511,6 +23861,9 @@
         <v>0.023086</v>
       </c>
       <c r="O450" s="1" t="n">
+        <v>0.023086</v>
+      </c>
+      <c r="P450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -22557,9 +23910,12 @@
         <v>0.04235</v>
       </c>
       <c r="N451" s="1" t="n">
+        <v>0.04228</v>
+      </c>
+      <c r="O451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="O451" s="1" t="n">
+      <c r="P451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -22606,9 +23962,12 @@
         <v>0.07216</v>
       </c>
       <c r="N452" s="1" t="n">
+        <v>0.07234</v>
+      </c>
+      <c r="O452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="O452" s="1" t="n">
+      <c r="P452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -22655,9 +24014,12 @@
         <v>0.0005908</v>
       </c>
       <c r="N453" s="1" t="n">
+        <v>0.0005913</v>
+      </c>
+      <c r="O453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="O453" s="1" t="n">
+      <c r="P453" s="1" t="n">
         <v>0.0005908</v>
       </c>
     </row>
@@ -22704,9 +24066,12 @@
         <v>0.307</v>
       </c>
       <c r="N454" s="1" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="O454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="O454" s="1" t="n">
+      <c r="P454" s="1" t="n">
         <v>0.306</v>
       </c>
     </row>
@@ -22753,9 +24118,12 @@
         <v>0.004293</v>
       </c>
       <c r="N455" s="1" t="n">
-        <v>0.004324</v>
+        <v>0.004338</v>
       </c>
       <c r="O455" s="1" t="n">
+        <v>0.004338</v>
+      </c>
+      <c r="P455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -22802,10 +24170,13 @@
         <v>0.183</v>
       </c>
       <c r="N456" s="1" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="O456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="O456" s="1" t="n">
-        <v>0.183</v>
+      <c r="P456" s="1" t="n">
+        <v>0.1825</v>
       </c>
     </row>
     <row r="457">
@@ -22851,9 +24222,12 @@
         <v>0.04276</v>
       </c>
       <c r="N457" s="1" t="n">
+        <v>0.04276</v>
+      </c>
+      <c r="O457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="O457" s="1" t="n">
+      <c r="P457" s="1" t="n">
         <v>0.04268</v>
       </c>
     </row>
@@ -22903,6 +24277,9 @@
         <v>0.1465</v>
       </c>
       <c r="O458" s="1" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="P458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -22949,9 +24326,12 @@
         <v>0.008665000000000001</v>
       </c>
       <c r="N459" s="1" t="n">
+        <v>0.008632000000000001</v>
+      </c>
+      <c r="O459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="O459" s="1" t="n">
+      <c r="P459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -22998,9 +24378,12 @@
         <v>0.007385</v>
       </c>
       <c r="N460" s="1" t="n">
+        <v>0.007368</v>
+      </c>
+      <c r="O460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="O460" s="1" t="n">
+      <c r="P460" s="1" t="n">
         <v>0.007357</v>
       </c>
     </row>
@@ -23047,9 +24430,12 @@
         <v>0.000173</v>
       </c>
       <c r="N461" s="1" t="n">
+        <v>0.000173</v>
+      </c>
+      <c r="O461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="O461" s="1" t="n">
+      <c r="P461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -23096,9 +24482,12 @@
         <v>0.02313</v>
       </c>
       <c r="N462" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="O462" s="1" t="n">
         <v>0.02321</v>
       </c>
-      <c r="O462" s="1" t="n">
+      <c r="P462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -23145,9 +24534,12 @@
         <v>0.03751</v>
       </c>
       <c r="N463" s="1" t="n">
+        <v>0.03717</v>
+      </c>
+      <c r="O463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="O463" s="1" t="n">
+      <c r="P463" s="1" t="n">
         <v>0.03685</v>
       </c>
     </row>
@@ -23194,9 +24586,12 @@
         <v>0.3014</v>
       </c>
       <c r="N464" s="1" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="O464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="O464" s="1" t="n">
+      <c r="P464" s="1" t="n">
         <v>0.3013</v>
       </c>
     </row>
@@ -23243,9 +24638,12 @@
         <v>0.0392</v>
       </c>
       <c r="N465" s="1" t="n">
+        <v>0.0393</v>
+      </c>
+      <c r="O465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="O465" s="1" t="n">
+      <c r="P465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -23292,9 +24690,12 @@
         <v>2.668</v>
       </c>
       <c r="N466" s="1" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="O466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="O466" s="1" t="n">
+      <c r="P466" s="1" t="n">
         <v>2.667</v>
       </c>
     </row>
@@ -23341,9 +24742,12 @@
         <v>0.03399</v>
       </c>
       <c r="N467" s="1" t="n">
+        <v>0.03395</v>
+      </c>
+      <c r="O467" s="1" t="n">
         <v>0.03436</v>
       </c>
-      <c r="O467" s="1" t="n">
+      <c r="P467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -23390,9 +24794,12 @@
         <v>0.1765</v>
       </c>
       <c r="N468" s="1" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="O468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="O468" s="1" t="n">
+      <c r="P468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -23439,9 +24846,12 @@
         <v>0.0968</v>
       </c>
       <c r="N469" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="O469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="O469" s="1" t="n">
+      <c r="P469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -23488,9 +24898,12 @@
         <v>0.06752</v>
       </c>
       <c r="N470" s="1" t="n">
+        <v>0.06741999999999999</v>
+      </c>
+      <c r="O470" s="1" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="O470" s="1" t="n">
+      <c r="P470" s="1" t="n">
         <v>0.06716999999999999</v>
       </c>
     </row>
@@ -23537,9 +24950,12 @@
         <v>0.04</v>
       </c>
       <c r="N471" s="1" t="n">
+        <v>0.03995</v>
+      </c>
+      <c r="O471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="O471" s="1" t="n">
+      <c r="P471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -23586,10 +25002,13 @@
         <v>0.2476</v>
       </c>
       <c r="N472" s="1" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="O472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="O472" s="1" t="n">
-        <v>0.2472</v>
+      <c r="P472" s="1" t="n">
+        <v>0.2471</v>
       </c>
     </row>
     <row r="473">
@@ -23635,10 +25054,13 @@
         <v>0.016379</v>
       </c>
       <c r="N473" s="1" t="n">
+        <v>0.016358</v>
+      </c>
+      <c r="O473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="O473" s="1" t="n">
-        <v>0.016367</v>
+      <c r="P473" s="1" t="n">
+        <v>0.016358</v>
       </c>
     </row>
     <row r="474">
@@ -23684,9 +25106,12 @@
         <v>0.1156</v>
       </c>
       <c r="N474" s="1" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="O474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="O474" s="1" t="n">
+      <c r="P474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -23733,9 +25158,12 @@
         <v>0.04291</v>
       </c>
       <c r="N475" s="1" t="n">
+        <v>0.04268</v>
+      </c>
+      <c r="O475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="O475" s="1" t="n">
+      <c r="P475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -23782,9 +25210,12 @@
         <v>0.2075</v>
       </c>
       <c r="N476" s="1" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="O476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="O476" s="1" t="n">
+      <c r="P476" s="1" t="n">
         <v>0.2071</v>
       </c>
     </row>
@@ -23831,9 +25262,12 @@
         <v>0.00682</v>
       </c>
       <c r="N477" s="1" t="n">
+        <v>0.006802</v>
+      </c>
+      <c r="O477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="O477" s="1" t="n">
+      <c r="P477" s="1" t="n">
         <v>0.006796</v>
       </c>
     </row>
@@ -23880,10 +25314,13 @@
         <v>0.01782</v>
       </c>
       <c r="N478" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="O478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="O478" s="1" t="n">
-        <v>0.01782</v>
+      <c r="P478" s="1" t="n">
+        <v>0.01781</v>
       </c>
     </row>
     <row r="479">
@@ -23929,10 +25366,13 @@
         <v>0.04688</v>
       </c>
       <c r="N479" s="1" t="n">
+        <v>0.04679</v>
+      </c>
+      <c r="O479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="O479" s="1" t="n">
-        <v>0.04683</v>
+      <c r="P479" s="1" t="n">
+        <v>0.04679</v>
       </c>
     </row>
     <row r="480">
@@ -23978,9 +25418,12 @@
         <v>0.26055</v>
       </c>
       <c r="N480" s="1" t="n">
+        <v>0.26006</v>
+      </c>
+      <c r="O480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="O480" s="1" t="n">
+      <c r="P480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -24027,10 +25470,13 @@
         <v>0.01227</v>
       </c>
       <c r="N481" s="1" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="O481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="O481" s="1" t="n">
-        <v>0.01227</v>
+      <c r="P481" s="1" t="n">
+        <v>0.01225</v>
       </c>
     </row>
     <row r="482">
@@ -24076,9 +25522,12 @@
         <v>0.004111</v>
       </c>
       <c r="N482" s="1" t="n">
+        <v>0.004088</v>
+      </c>
+      <c r="O482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="O482" s="1" t="n">
+      <c r="P482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -24125,9 +25574,12 @@
         <v>0.123</v>
       </c>
       <c r="N483" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="O483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="O483" s="1" t="n">
+      <c r="P483" s="1" t="n">
         <v>0.1229</v>
       </c>
     </row>
@@ -24174,9 +25626,12 @@
         <v>0.02203</v>
       </c>
       <c r="N484" s="1" t="n">
-        <v>0.02209</v>
+        <v>0.02222</v>
       </c>
       <c r="O484" s="1" t="n">
+        <v>0.02222</v>
+      </c>
+      <c r="P484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -24223,9 +25678,12 @@
         <v>0.04542</v>
       </c>
       <c r="N485" s="1" t="n">
+        <v>0.04539</v>
+      </c>
+      <c r="O485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="O485" s="1" t="n">
+      <c r="P485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -24272,9 +25730,12 @@
         <v>0.1737</v>
       </c>
       <c r="N486" s="1" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="O486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="O486" s="1" t="n">
+      <c r="P486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -24321,9 +25782,12 @@
         <v>0.2727</v>
       </c>
       <c r="N487" s="1" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="O487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="O487" s="1" t="n">
+      <c r="P487" s="1" t="n">
         <v>0.2726</v>
       </c>
     </row>
@@ -24370,9 +25834,12 @@
         <v>0.04617</v>
       </c>
       <c r="N488" s="1" t="n">
+        <v>0.04612</v>
+      </c>
+      <c r="O488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="O488" s="1" t="n">
+      <c r="P488" s="1" t="n">
         <v>0.04611</v>
       </c>
     </row>
@@ -24419,9 +25886,12 @@
         <v>0.0002151</v>
       </c>
       <c r="N489" s="1" t="n">
+        <v>0.000215</v>
+      </c>
+      <c r="O489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="O489" s="1" t="n">
+      <c r="P489" s="1" t="n">
         <v>0.0002149</v>
       </c>
     </row>
@@ -24468,9 +25938,12 @@
         <v>1.78</v>
       </c>
       <c r="N490" s="1" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="O490" s="1" t="n">
         <v>1.78</v>
       </c>
-      <c r="O490" s="1" t="n">
+      <c r="P490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -24517,9 +25990,12 @@
         <v>16.064</v>
       </c>
       <c r="N491" s="1" t="n">
+        <v>16.046</v>
+      </c>
+      <c r="O491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="O491" s="1" t="n">
+      <c r="P491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -24566,9 +26042,12 @@
         <v>0.06676</v>
       </c>
       <c r="N492" s="1" t="n">
+        <v>0.06671000000000001</v>
+      </c>
+      <c r="O492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="O492" s="1" t="n">
+      <c r="P492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -24615,9 +26094,12 @@
         <v>0.06754</v>
       </c>
       <c r="N493" s="1" t="n">
+        <v>0.06736</v>
+      </c>
+      <c r="O493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="O493" s="1" t="n">
+      <c r="P493" s="1" t="n">
         <v>0.06734999999999999</v>
       </c>
     </row>
@@ -24664,9 +26146,12 @@
         <v>0.009424</v>
       </c>
       <c r="N494" s="1" t="n">
+        <v>0.009441</v>
+      </c>
+      <c r="O494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="O494" s="1" t="n">
+      <c r="P494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -24713,9 +26198,12 @@
         <v>0.005809</v>
       </c>
       <c r="N495" s="1" t="n">
+        <v>0.005823</v>
+      </c>
+      <c r="O495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="O495" s="1" t="n">
+      <c r="P495" s="1" t="n">
         <v>0.005809</v>
       </c>
     </row>
@@ -24762,9 +26250,12 @@
         <v>0.009889999999999999</v>
       </c>
       <c r="N496" s="1" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="O496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="O496" s="1" t="n">
+      <c r="P496" s="1" t="n">
         <v>0.00987</v>
       </c>
     </row>
@@ -24811,9 +26302,12 @@
         <v>0.0455</v>
       </c>
       <c r="N497" s="1" t="n">
+        <v>0.04522</v>
+      </c>
+      <c r="O497" s="1" t="n">
         <v>0.0455</v>
       </c>
-      <c r="O497" s="1" t="n">
+      <c r="P497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -24860,10 +26354,13 @@
         <v>0.006376</v>
       </c>
       <c r="N498" s="1" t="n">
+        <v>0.006355</v>
+      </c>
+      <c r="O498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="O498" s="1" t="n">
-        <v>0.006374</v>
+      <c r="P498" s="1" t="n">
+        <v>0.006355</v>
       </c>
     </row>
     <row r="499">
@@ -24909,10 +26406,13 @@
         <v>0.01046</v>
       </c>
       <c r="N499" s="1" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="O499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="O499" s="1" t="n">
-        <v>0.01044</v>
+      <c r="P499" s="1" t="n">
+        <v>0.01041</v>
       </c>
     </row>
     <row r="500">
@@ -24958,9 +26458,12 @@
         <v>0.5097</v>
       </c>
       <c r="N500" s="1" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="O500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="O500" s="1" t="n">
+      <c r="P500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -25007,9 +26510,12 @@
         <v>0.03207</v>
       </c>
       <c r="N501" s="1" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="O501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="O501" s="1" t="n">
+      <c r="P501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -25056,9 +26562,12 @@
         <v>0.4417</v>
       </c>
       <c r="N502" s="1" t="n">
-        <v>0.4436</v>
+        <v>0.446</v>
       </c>
       <c r="O502" s="1" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="P502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -25105,9 +26614,12 @@
         <v>0.999342</v>
       </c>
       <c r="N503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="O503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="O503" s="1" t="n">
+      <c r="P503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -25154,9 +26666,12 @@
         <v>0.03501</v>
       </c>
       <c r="N504" s="1" t="n">
+        <v>0.03534</v>
+      </c>
+      <c r="O504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="O504" s="1" t="n">
+      <c r="P504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -25203,9 +26718,12 @@
         <v>0.004951</v>
       </c>
       <c r="N505" s="1" t="n">
+        <v>0.004952</v>
+      </c>
+      <c r="O505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="O505" s="1" t="n">
+      <c r="P505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -25252,9 +26770,12 @@
         <v>0.01394</v>
       </c>
       <c r="N506" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="O506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="O506" s="1" t="n">
+      <c r="P506" s="1" t="n">
         <v>0.01389</v>
       </c>
     </row>
@@ -25301,9 +26822,12 @@
         <v>0.003475</v>
       </c>
       <c r="N507" s="1" t="n">
+        <v>0.00346</v>
+      </c>
+      <c r="O507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="O507" s="1" t="n">
+      <c r="P507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -25350,9 +26874,12 @@
         <v>1.419</v>
       </c>
       <c r="N508" s="1" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="O508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="O508" s="1" t="n">
+      <c r="P508" s="1" t="n">
         <v>1.417</v>
       </c>
     </row>
@@ -25399,9 +26926,12 @@
         <v>0.0051</v>
       </c>
       <c r="N509" s="1" t="n">
+        <v>0.005082</v>
+      </c>
+      <c r="O509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="O509" s="1" t="n">
+      <c r="P509" s="1" t="n">
         <v>0.005076</v>
       </c>
     </row>
@@ -25448,9 +26978,12 @@
         <v>0.01575</v>
       </c>
       <c r="N510" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="O510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="O510" s="1" t="n">
+      <c r="P510" s="1" t="n">
         <v>0.01571</v>
       </c>
     </row>
@@ -25497,9 +27030,12 @@
         <v>0.08255</v>
       </c>
       <c r="N511" s="1" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="O511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="O511" s="1" t="n">
+      <c r="P511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -25546,10 +27082,13 @@
         <v>0.007098</v>
       </c>
       <c r="N512" s="1" t="n">
+        <v>0.007092</v>
+      </c>
+      <c r="O512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="O512" s="1" t="n">
-        <v>0.007093</v>
+      <c r="P512" s="1" t="n">
+        <v>0.007092</v>
       </c>
     </row>
     <row r="513">
@@ -25595,9 +27134,12 @@
         <v>0.01495</v>
       </c>
       <c r="N513" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="O513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="O513" s="1" t="n">
+      <c r="P513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -25644,9 +27186,12 @@
         <v>0.04748</v>
       </c>
       <c r="N514" s="1" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="O514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="O514" s="1" t="n">
+      <c r="P514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -25693,10 +27238,13 @@
         <v>0.0182</v>
       </c>
       <c r="N515" s="1" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="O515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="O515" s="1" t="n">
-        <v>0.01818</v>
+      <c r="P515" s="1" t="n">
+        <v>0.01811</v>
       </c>
     </row>
     <row r="516">
@@ -25742,10 +27290,13 @@
         <v>0.000579</v>
       </c>
       <c r="N516" s="1" t="n">
+        <v>0.0005782</v>
+      </c>
+      <c r="O516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="O516" s="1" t="n">
-        <v>0.000579</v>
+      <c r="P516" s="1" t="n">
+        <v>0.0005782</v>
       </c>
     </row>
     <row r="517">
@@ -25791,9 +27342,12 @@
         <v>0.07865</v>
       </c>
       <c r="N517" s="1" t="n">
+        <v>0.07854999999999999</v>
+      </c>
+      <c r="O517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="O517" s="1" t="n">
+      <c r="P517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -25840,9 +27394,12 @@
         <v>0.006386</v>
       </c>
       <c r="N518" s="1" t="n">
+        <v>0.006384</v>
+      </c>
+      <c r="O518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="O518" s="1" t="n">
+      <c r="P518" s="1" t="n">
         <v>0.006373</v>
       </c>
     </row>
@@ -25889,10 +27446,13 @@
         <v>0.05791</v>
       </c>
       <c r="N519" s="1" t="n">
+        <v>0.05779</v>
+      </c>
+      <c r="O519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="O519" s="1" t="n">
-        <v>0.05784</v>
+      <c r="P519" s="1" t="n">
+        <v>0.05779</v>
       </c>
     </row>
     <row r="520">
@@ -25938,10 +27498,13 @@
         <v>0.10485</v>
       </c>
       <c r="N520" s="1" t="n">
+        <v>0.10461</v>
+      </c>
+      <c r="O520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="O520" s="1" t="n">
-        <v>0.10469</v>
+      <c r="P520" s="1" t="n">
+        <v>0.10461</v>
       </c>
     </row>
     <row r="521">
@@ -25987,9 +27550,12 @@
         <v>0.01796</v>
       </c>
       <c r="N521" s="1" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="O521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="O521" s="1" t="n">
+      <c r="P521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -26036,10 +27602,13 @@
         <v>0.01644</v>
       </c>
       <c r="N522" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="O522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="O522" s="1" t="n">
-        <v>0.01644</v>
+      <c r="P522" s="1" t="n">
+        <v>0.01641</v>
       </c>
     </row>
     <row r="523">
@@ -26085,9 +27654,12 @@
         <v>0.01086</v>
       </c>
       <c r="N523" s="1" t="n">
+        <v>0.01084</v>
+      </c>
+      <c r="O523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="O523" s="1" t="n">
+      <c r="P523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -26134,9 +27706,12 @@
         <v>0.007116</v>
       </c>
       <c r="N524" s="1" t="n">
+        <v>0.00715</v>
+      </c>
+      <c r="O524" s="1" t="n">
         <v>0.007158</v>
       </c>
-      <c r="O524" s="1" t="n">
+      <c r="P524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -26183,10 +27758,13 @@
         <v>0.005885</v>
       </c>
       <c r="N525" s="1" t="n">
+        <v>0.005864</v>
+      </c>
+      <c r="O525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="O525" s="1" t="n">
-        <v>0.005885</v>
+      <c r="P525" s="1" t="n">
+        <v>0.005864</v>
       </c>
     </row>
     <row r="526">
@@ -26232,9 +27810,12 @@
         <v>0.001446</v>
       </c>
       <c r="N526" s="1" t="n">
+        <v>0.001444</v>
+      </c>
+      <c r="O526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="O526" s="1" t="n">
+      <c r="P526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -26284,6 +27865,9 @@
         <v>0.374</v>
       </c>
       <c r="O527" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="P527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -26330,9 +27914,12 @@
         <v>0.005219</v>
       </c>
       <c r="N528" s="1" t="n">
-        <v>0.005219</v>
+        <v>0.005236</v>
       </c>
       <c r="O528" s="1" t="n">
+        <v>0.005236</v>
+      </c>
+      <c r="P528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -26379,9 +27966,12 @@
         <v>2.961</v>
       </c>
       <c r="N529" s="1" t="n">
+        <v>2.954</v>
+      </c>
+      <c r="O529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="O529" s="1" t="n">
+      <c r="P529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -26428,10 +28018,13 @@
         <v>0.1558</v>
       </c>
       <c r="N530" s="1" t="n">
+        <v>0.1553</v>
+      </c>
+      <c r="O530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="O530" s="1" t="n">
-        <v>0.1554</v>
+      <c r="P530" s="1" t="n">
+        <v>0.1553</v>
       </c>
     </row>
     <row r="531">
@@ -26480,6 +28073,9 @@
         <v>2544</v>
       </c>
       <c r="O531" s="1" t="n">
+        <v>2544</v>
+      </c>
+      <c r="P531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -26526,10 +28122,13 @@
         <v>0.03923</v>
       </c>
       <c r="N532" s="1" t="n">
+        <v>0.03913</v>
+      </c>
+      <c r="O532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="O532" s="1" t="n">
-        <v>0.03923</v>
+      <c r="P532" s="1" t="n">
+        <v>0.03913</v>
       </c>
     </row>
     <row r="533">
@@ -26575,9 +28174,12 @@
         <v>0.02162</v>
       </c>
       <c r="N533" s="1" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="O533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="O533" s="1" t="n">
+      <c r="P533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -26624,9 +28226,12 @@
         <v>0.07367</v>
       </c>
       <c r="N534" s="1" t="n">
+        <v>0.07353</v>
+      </c>
+      <c r="O534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="O534" s="1" t="n">
+      <c r="P534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -26673,9 +28278,12 @@
         <v>0.008014</v>
       </c>
       <c r="N535" s="1" t="n">
+        <v>0.007913999999999999</v>
+      </c>
+      <c r="O535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="O535" s="1" t="n">
+      <c r="P535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -26722,9 +28330,12 @@
         <v>0.05015</v>
       </c>
       <c r="N536" s="1" t="n">
+        <v>0.05016</v>
+      </c>
+      <c r="O536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="O536" s="1" t="n">
+      <c r="P536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -26771,9 +28382,12 @@
         <v>0.00404</v>
       </c>
       <c r="N537" s="1" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="O537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="O537" s="1" t="n">
+      <c r="P537" s="1" t="n">
         <v>0.00404</v>
       </c>
     </row>
@@ -26820,9 +28434,12 @@
         <v>0.08296000000000001</v>
       </c>
       <c r="N538" s="1" t="n">
+        <v>0.08307</v>
+      </c>
+      <c r="O538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="O538" s="1" t="n">
+      <c r="P538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -26869,9 +28486,12 @@
         <v>0.0249</v>
       </c>
       <c r="N539" s="1" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="O539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="O539" s="1" t="n">
+      <c r="P539" s="1" t="n">
         <v>0.02485</v>
       </c>
     </row>
@@ -26918,10 +28538,13 @@
         <v>0.08433</v>
       </c>
       <c r="N540" s="1" t="n">
+        <v>0.08415</v>
+      </c>
+      <c r="O540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="O540" s="1" t="n">
-        <v>0.08433</v>
+      <c r="P540" s="1" t="n">
+        <v>0.08415</v>
       </c>
     </row>
     <row r="541">
@@ -26967,10 +28590,13 @@
         <v>0.01891</v>
       </c>
       <c r="N541" s="1" t="n">
+        <v>0.01886</v>
+      </c>
+      <c r="O541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="O541" s="1" t="n">
-        <v>0.0189</v>
+      <c r="P541" s="1" t="n">
+        <v>0.01886</v>
       </c>
     </row>
     <row r="542">
@@ -27016,10 +28642,13 @@
         <v>0.01689</v>
       </c>
       <c r="N542" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="O542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="O542" s="1" t="n">
-        <v>0.01689</v>
+      <c r="P542" s="1" t="n">
+        <v>0.01686</v>
       </c>
     </row>
     <row r="543">
@@ -27065,9 +28694,12 @@
         <v>0.105</v>
       </c>
       <c r="N543" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="O543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="O543" s="1" t="n">
+      <c r="P543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P543"/>
+  <dimension ref="A1:Q543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -433,8 +433,9 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,10 +511,15 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>price_03:30</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -565,9 +571,12 @@
         <v>70655.10000000001</v>
       </c>
       <c r="O2" s="1" t="n">
+        <v>70638.89999999999</v>
+      </c>
+      <c r="P2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -617,9 +626,12 @@
         <v>2076.18</v>
       </c>
       <c r="O3" s="1" t="n">
+        <v>2076.2</v>
+      </c>
+      <c r="P3" s="1" t="n">
         <v>2076.79</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -669,9 +681,12 @@
         <v>86.91</v>
       </c>
       <c r="O4" s="1" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="P4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -721,9 +736,12 @@
         <v>3.991</v>
       </c>
       <c r="O5" s="1" t="n">
+        <v>3.993</v>
+      </c>
+      <c r="P5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>3.991</v>
       </c>
     </row>
@@ -773,9 +791,12 @@
         <v>0.0946</v>
       </c>
       <c r="O6" s="1" t="n">
+        <v>0.09458</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -825,9 +846,12 @@
         <v>1.3901</v>
       </c>
       <c r="O7" s="1" t="n">
+        <v>1.3894</v>
+      </c>
+      <c r="P7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -877,9 +901,12 @@
         <v>22.513</v>
       </c>
       <c r="O8" s="1" t="n">
+        <v>22.416</v>
+      </c>
+      <c r="P8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -929,10 +956,13 @@
         <v>0.002005</v>
       </c>
       <c r="O9" s="1" t="n">
+        <v>0.001972</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="P9" s="1" t="n">
-        <v>0.001977</v>
+      <c r="Q9" s="1" t="n">
+        <v>0.001972</v>
       </c>
     </row>
     <row r="10">
@@ -981,9 +1011,12 @@
         <v>0.009663</v>
       </c>
       <c r="O10" s="1" t="n">
+        <v>0.009905000000000001</v>
+      </c>
+      <c r="P10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="Q10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1033,10 +1066,13 @@
         <v>0.15129</v>
       </c>
       <c r="O11" s="1" t="n">
+        <v>0.13838</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="P11" s="1" t="n">
-        <v>0.15129</v>
+      <c r="Q11" s="1" t="n">
+        <v>0.13838</v>
       </c>
     </row>
     <row r="12">
@@ -1085,9 +1121,12 @@
         <v>0.011447</v>
       </c>
       <c r="O12" s="1" t="n">
+        <v>0.011412</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="Q12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -1137,9 +1176,12 @@
         <v>38.168</v>
       </c>
       <c r="O13" s="1" t="n">
+        <v>38.139</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="Q13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1189,9 +1231,12 @@
         <v>653.22</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>653.27</v>
+      </c>
+      <c r="P14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="Q14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1241,9 +1286,12 @@
         <v>209.49</v>
       </c>
       <c r="O15" s="1" t="n">
+        <v>209.78</v>
+      </c>
+      <c r="P15" s="1" t="n">
         <v>209.93</v>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="Q15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1293,10 +1341,13 @@
         <v>0.003321</v>
       </c>
       <c r="O16" s="1" t="n">
+        <v>0.0033182</v>
+      </c>
+      <c r="P16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="P16" s="1" t="n">
-        <v>0.003321</v>
+      <c r="Q16" s="1" t="n">
+        <v>0.0033182</v>
       </c>
     </row>
     <row r="17">
@@ -1345,9 +1396,12 @@
         <v>237.39</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>237.38</v>
+      </c>
+      <c r="P17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="P17" s="1" t="n">
+      <c r="Q17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1397,9 +1451,12 @@
         <v>0.9883</v>
       </c>
       <c r="O18" s="1" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="P18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="Q18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1449,9 +1506,12 @@
         <v>1.0604</v>
       </c>
       <c r="O19" s="1" t="n">
+        <v>1.0453</v>
+      </c>
+      <c r="P19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="P19" s="1" t="n">
+      <c r="Q19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1501,9 +1561,12 @@
         <v>0.2587</v>
       </c>
       <c r="O20" s="1" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="P20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="Q20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1553,9 +1616,12 @@
         <v>0.59034</v>
       </c>
       <c r="O21" s="1" t="n">
+        <v>0.59232</v>
+      </c>
+      <c r="P21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="Q21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -1605,9 +1671,12 @@
         <v>9.019</v>
       </c>
       <c r="O22" s="1" t="n">
+        <v>9.019</v>
+      </c>
+      <c r="P22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="P22" s="1" t="n">
+      <c r="Q22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1657,10 +1726,13 @@
         <v>0.02398</v>
       </c>
       <c r="O23" s="1" t="n">
+        <v>0.02397</v>
+      </c>
+      <c r="P23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="P23" s="1" t="n">
-        <v>0.02398</v>
+      <c r="Q23" s="1" t="n">
+        <v>0.02397</v>
       </c>
     </row>
     <row r="24">
@@ -1709,9 +1781,12 @@
         <v>9.56</v>
       </c>
       <c r="O24" s="1" t="n">
+        <v>9.558</v>
+      </c>
+      <c r="P24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="Q24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1761,9 +1836,12 @@
         <v>1.237</v>
       </c>
       <c r="O25" s="1" t="n">
-        <v>1.237</v>
+        <v>1.24</v>
       </c>
       <c r="P25" s="1" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1813,9 +1891,12 @@
         <v>0.07142</v>
       </c>
       <c r="O26" s="1" t="n">
+        <v>0.07149</v>
+      </c>
+      <c r="P26" s="1" t="n">
         <v>0.0717</v>
       </c>
-      <c r="P26" s="1" t="n">
+      <c r="Q26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1865,10 +1946,13 @@
         <v>1.423</v>
       </c>
       <c r="O27" s="1" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="P27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="P27" s="1" t="n">
-        <v>1.423</v>
+      <c r="Q27" s="1" t="n">
+        <v>1.417</v>
       </c>
     </row>
     <row r="28">
@@ -1917,9 +2001,12 @@
         <v>1.306</v>
       </c>
       <c r="O28" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="P28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="P28" s="1" t="n">
+      <c r="Q28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -1972,6 +2059,9 @@
         <v>463.26</v>
       </c>
       <c r="P29" s="1" t="n">
+        <v>463.26</v>
+      </c>
+      <c r="Q29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2021,9 +2111,12 @@
         <v>1.3016</v>
       </c>
       <c r="O30" s="1" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="P30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="P30" s="1" t="n">
+      <c r="Q30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2073,9 +2166,12 @@
         <v>5023.15</v>
       </c>
       <c r="O31" s="1" t="n">
-        <v>5024.91</v>
+        <v>5025.5</v>
       </c>
       <c r="P31" s="1" t="n">
+        <v>5025.5</v>
+      </c>
+      <c r="Q31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -2125,9 +2221,12 @@
         <v>0.885</v>
       </c>
       <c r="O32" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="P32" s="1" t="n">
+      <c r="Q32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2177,10 +2276,13 @@
         <v>0.001973</v>
       </c>
       <c r="O33" s="1" t="n">
+        <v>0.001969</v>
+      </c>
+      <c r="P33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="P33" s="1" t="n">
-        <v>0.001971</v>
+      <c r="Q33" s="1" t="n">
+        <v>0.001969</v>
       </c>
     </row>
     <row r="34">
@@ -2229,9 +2331,12 @@
         <v>0.17264</v>
       </c>
       <c r="O34" s="1" t="n">
+        <v>0.17183</v>
+      </c>
+      <c r="P34" s="1" t="n">
         <v>0.17264</v>
       </c>
-      <c r="P34" s="1" t="n">
+      <c r="Q34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2281,10 +2386,13 @@
         <v>0.29661</v>
       </c>
       <c r="O35" s="1" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="P35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="P35" s="1" t="n">
-        <v>0.29661</v>
+      <c r="Q35" s="1" t="n">
+        <v>0.29656</v>
       </c>
     </row>
     <row r="36">
@@ -2333,10 +2441,13 @@
         <v>1.779</v>
       </c>
       <c r="O36" s="1" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="P36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="P36" s="1" t="n">
-        <v>1.779</v>
+      <c r="Q36" s="1" t="n">
+        <v>1.777</v>
       </c>
     </row>
     <row r="37">
@@ -2385,10 +2496,13 @@
         <v>110.29</v>
       </c>
       <c r="O37" s="1" t="n">
+        <v>110.23</v>
+      </c>
+      <c r="P37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="P37" s="1" t="n">
-        <v>110.25</v>
+      <c r="Q37" s="1" t="n">
+        <v>110.23</v>
       </c>
     </row>
     <row r="38">
@@ -2437,9 +2551,12 @@
         <v>0.2215</v>
       </c>
       <c r="O38" s="1" t="n">
+        <v>0.22151</v>
+      </c>
+      <c r="P38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="P38" s="1" t="n">
+      <c r="Q38" s="1" t="n">
         <v>0.22079</v>
       </c>
     </row>
@@ -2489,10 +2606,13 @@
         <v>0.1072</v>
       </c>
       <c r="O39" s="1" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="P39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="P39" s="1" t="n">
-        <v>0.1072</v>
+      <c r="Q39" s="1" t="n">
+        <v>0.1068</v>
       </c>
     </row>
     <row r="40">
@@ -2541,9 +2661,12 @@
         <v>0.37323</v>
       </c>
       <c r="O40" s="1" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="P40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="P40" s="1" t="n">
+      <c r="Q40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2593,9 +2716,12 @@
         <v>54.72</v>
       </c>
       <c r="O41" s="1" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="P41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="P41" s="1" t="n">
+      <c r="Q41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2645,10 +2771,13 @@
         <v>0.0010657</v>
       </c>
       <c r="O42" s="1" t="n">
+        <v>0.0010643</v>
+      </c>
+      <c r="P42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="P42" s="1" t="n">
-        <v>0.0010657</v>
+      <c r="Q42" s="1" t="n">
+        <v>0.0010643</v>
       </c>
     </row>
     <row r="43">
@@ -2697,9 +2826,12 @@
         <v>6.414</v>
       </c>
       <c r="O43" s="1" t="n">
+        <v>6.436</v>
+      </c>
+      <c r="P43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="P43" s="1" t="n">
+      <c r="Q43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -2749,10 +2881,13 @@
         <v>0.6319</v>
       </c>
       <c r="O44" s="1" t="n">
+        <v>0.6288</v>
+      </c>
+      <c r="P44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="P44" s="1" t="n">
-        <v>0.6319</v>
+      <c r="Q44" s="1" t="n">
+        <v>0.6288</v>
       </c>
     </row>
     <row r="45">
@@ -2801,9 +2936,12 @@
         <v>0.3537</v>
       </c>
       <c r="O45" s="1" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="P45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="P45" s="1" t="n">
+      <c r="Q45" s="1" t="n">
         <v>0.3533</v>
       </c>
     </row>
@@ -2853,9 +2991,12 @@
         <v>0.03288</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>0.03298</v>
+        <v>0.0331</v>
       </c>
       <c r="P46" s="1" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="Q46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -2905,10 +3046,13 @@
         <v>0.07154000000000001</v>
       </c>
       <c r="O47" s="1" t="n">
+        <v>0.0712</v>
+      </c>
+      <c r="P47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="P47" s="1" t="n">
-        <v>0.07151</v>
+      <c r="Q47" s="1" t="n">
+        <v>0.0712</v>
       </c>
     </row>
     <row r="48">
@@ -2957,9 +3101,12 @@
         <v>0.7097</v>
       </c>
       <c r="O48" s="1" t="n">
+        <v>0.7083</v>
+      </c>
+      <c r="P48" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="P48" s="1" t="n">
+      <c r="Q48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3009,10 +3156,13 @@
         <v>0.004384</v>
       </c>
       <c r="O49" s="1" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="P49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="P49" s="1" t="n">
-        <v>0.004361</v>
+      <c r="Q49" s="1" t="n">
+        <v>0.00435</v>
       </c>
     </row>
     <row r="50">
@@ -3061,9 +3211,12 @@
         <v>0.1037</v>
       </c>
       <c r="O50" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="P50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="P50" s="1" t="n">
+      <c r="Q50" s="1" t="n">
         <v>0.1037</v>
       </c>
     </row>
@@ -3113,9 +3266,12 @@
         <v>0.04043</v>
       </c>
       <c r="O51" s="1" t="n">
+        <v>0.04039</v>
+      </c>
+      <c r="P51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="P51" s="1" t="n">
+      <c r="Q51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -3165,9 +3321,12 @@
         <v>0.165</v>
       </c>
       <c r="O52" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="P52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="P52" s="1" t="n">
+      <c r="Q52" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -3217,9 +3376,12 @@
         <v>0.02005</v>
       </c>
       <c r="O53" s="1" t="n">
+        <v>0.02011</v>
+      </c>
+      <c r="P53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="P53" s="1" t="n">
+      <c r="Q53" s="1" t="n">
         <v>0.02002</v>
       </c>
     </row>
@@ -3269,10 +3431,13 @@
         <v>0.007191</v>
       </c>
       <c r="O54" s="1" t="n">
+        <v>0.007182</v>
+      </c>
+      <c r="P54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="P54" s="1" t="n">
-        <v>0.007191</v>
+      <c r="Q54" s="1" t="n">
+        <v>0.007182</v>
       </c>
     </row>
     <row r="55">
@@ -3321,9 +3486,12 @@
         <v>3.914</v>
       </c>
       <c r="O55" s="1" t="n">
+        <v>3.911</v>
+      </c>
+      <c r="P55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="P55" s="1" t="n">
+      <c r="Q55" s="1" t="n">
         <v>3.911</v>
       </c>
     </row>
@@ -3373,10 +3541,13 @@
         <v>0.017098</v>
       </c>
       <c r="O56" s="1" t="n">
+        <v>0.016965</v>
+      </c>
+      <c r="P56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="P56" s="1" t="n">
-        <v>0.017082</v>
+      <c r="Q56" s="1" t="n">
+        <v>0.016965</v>
       </c>
     </row>
     <row r="57">
@@ -3425,9 +3596,12 @@
         <v>0.1088</v>
       </c>
       <c r="O57" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="P57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="P57" s="1" t="n">
+      <c r="Q57" s="1" t="n">
         <v>0.1088</v>
       </c>
     </row>
@@ -3477,9 +3651,12 @@
         <v>2.658</v>
       </c>
       <c r="O58" s="1" t="n">
+        <v>2.654</v>
+      </c>
+      <c r="P58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="P58" s="1" t="n">
+      <c r="Q58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -3529,9 +3706,12 @@
         <v>0.1587</v>
       </c>
       <c r="O59" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="P59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="P59" s="1" t="n">
+      <c r="Q59" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -3581,10 +3761,13 @@
         <v>0.005876</v>
       </c>
       <c r="O60" s="1" t="n">
+        <v>0.005874</v>
+      </c>
+      <c r="P60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="P60" s="1" t="n">
-        <v>0.005876</v>
+      <c r="Q60" s="1" t="n">
+        <v>0.005874</v>
       </c>
     </row>
     <row r="61">
@@ -3633,10 +3816,13 @@
         <v>0.09188</v>
       </c>
       <c r="O61" s="1" t="n">
+        <v>0.09186</v>
+      </c>
+      <c r="P61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="P61" s="1" t="n">
-        <v>0.09188</v>
+      <c r="Q61" s="1" t="n">
+        <v>0.09186</v>
       </c>
     </row>
     <row r="62">
@@ -3685,9 +3871,12 @@
         <v>0.9134</v>
       </c>
       <c r="O62" s="1" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="P62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="P62" s="1" t="n">
+      <c r="Q62" s="1" t="n">
         <v>0.9112</v>
       </c>
     </row>
@@ -3737,9 +3926,12 @@
         <v>0.781</v>
       </c>
       <c r="O63" s="1" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="P63" s="1" t="n">
+      <c r="Q63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -3789,9 +3981,12 @@
         <v>0.04608</v>
       </c>
       <c r="O64" s="1" t="n">
+        <v>0.04631</v>
+      </c>
+      <c r="P64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="P64" s="1" t="n">
+      <c r="Q64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -3841,9 +4036,12 @@
         <v>355.8</v>
       </c>
       <c r="O65" s="1" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="P65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="P65" s="1" t="n">
+      <c r="Q65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -3893,9 +4091,12 @@
         <v>0.12358</v>
       </c>
       <c r="O66" s="1" t="n">
+        <v>0.12394</v>
+      </c>
+      <c r="P66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="P66" s="1" t="n">
+      <c r="Q66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -3945,10 +4146,13 @@
         <v>0.2265</v>
       </c>
       <c r="O67" s="1" t="n">
+        <v>0.2249</v>
+      </c>
+      <c r="P67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="P67" s="1" t="n">
-        <v>0.2265</v>
+      <c r="Q67" s="1" t="n">
+        <v>0.2249</v>
       </c>
     </row>
     <row r="68">
@@ -3997,10 +4201,13 @@
         <v>0.00339</v>
       </c>
       <c r="O68" s="1" t="n">
+        <v>0.00338</v>
+      </c>
+      <c r="P68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="P68" s="1" t="n">
-        <v>0.00339</v>
+      <c r="Q68" s="1" t="n">
+        <v>0.00338</v>
       </c>
     </row>
     <row r="69">
@@ -4049,9 +4256,12 @@
         <v>0.1741</v>
       </c>
       <c r="O69" s="1" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="P69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="P69" s="1" t="n">
+      <c r="Q69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -4101,10 +4311,13 @@
         <v>0.16386</v>
       </c>
       <c r="O70" s="1" t="n">
+        <v>0.16374</v>
+      </c>
+      <c r="P70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="P70" s="1" t="n">
-        <v>0.16386</v>
+      <c r="Q70" s="1" t="n">
+        <v>0.16374</v>
       </c>
     </row>
     <row r="71">
@@ -4153,9 +4366,12 @@
         <v>0.3514</v>
       </c>
       <c r="O71" s="1" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="P71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="P71" s="1" t="n">
+      <c r="Q71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -4205,9 +4421,12 @@
         <v>0.7092000000000001</v>
       </c>
       <c r="O72" s="1" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="P72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="P72" s="1" t="n">
+      <c r="Q72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -4257,9 +4476,12 @@
         <v>0.00873</v>
       </c>
       <c r="O73" s="1" t="n">
+        <v>0.00868</v>
+      </c>
+      <c r="P73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="P73" s="1" t="n">
+      <c r="Q73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -4309,9 +4531,12 @@
         <v>0.005977</v>
       </c>
       <c r="O74" s="1" t="n">
+        <v>0.005978</v>
+      </c>
+      <c r="P74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="P74" s="1" t="n">
+      <c r="Q74" s="1" t="n">
         <v>0.005967</v>
       </c>
     </row>
@@ -4361,9 +4586,12 @@
         <v>0.226</v>
       </c>
       <c r="O75" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="P75" s="1" t="n">
         <v>0.228</v>
       </c>
-      <c r="P75" s="1" t="n">
+      <c r="Q75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -4413,9 +4641,12 @@
         <v>0.3219</v>
       </c>
       <c r="O76" s="1" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="P76" s="1" t="n">
         <v>0.3265</v>
       </c>
-      <c r="P76" s="1" t="n">
+      <c r="Q76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -4465,9 +4696,12 @@
         <v>0.1004</v>
       </c>
       <c r="O77" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="P77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="P77" s="1" t="n">
+      <c r="Q77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -4517,10 +4751,13 @@
         <v>0.1228</v>
       </c>
       <c r="O78" s="1" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="P78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="P78" s="1" t="n">
-        <v>0.1227</v>
+      <c r="Q78" s="1" t="n">
+        <v>0.1225</v>
       </c>
     </row>
     <row r="79">
@@ -4569,9 +4806,12 @@
         <v>0.07353999999999999</v>
       </c>
       <c r="O79" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="P79" s="1" t="n">
         <v>0.07353999999999999</v>
       </c>
-      <c r="P79" s="1" t="n">
+      <c r="Q79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -4621,9 +4861,12 @@
         <v>0.04678</v>
       </c>
       <c r="O80" s="1" t="n">
+        <v>0.04659</v>
+      </c>
+      <c r="P80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="P80" s="1" t="n">
+      <c r="Q80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -4673,9 +4916,12 @@
         <v>0.000235</v>
       </c>
       <c r="O81" s="1" t="n">
+        <v>0.000235</v>
+      </c>
+      <c r="P81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="P81" s="1" t="n">
+      <c r="Q81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -4725,9 +4971,12 @@
         <v>8.218</v>
       </c>
       <c r="O82" s="1" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="P82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="P82" s="1" t="n">
+      <c r="Q82" s="1" t="n">
         <v>8.206</v>
       </c>
     </row>
@@ -4777,9 +5026,12 @@
         <v>0.0005843000000000001</v>
       </c>
       <c r="O83" s="1" t="n">
+        <v>0.0005802</v>
+      </c>
+      <c r="P83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="P83" s="1" t="n">
+      <c r="Q83" s="1" t="n">
         <v>0.0005756</v>
       </c>
     </row>
@@ -4829,9 +5081,12 @@
         <v>0.4423</v>
       </c>
       <c r="O84" s="1" t="n">
-        <v>0.4457</v>
+        <v>0.4505</v>
       </c>
       <c r="P84" s="1" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="Q84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4881,9 +5136,12 @@
         <v>0.06247</v>
       </c>
       <c r="O85" s="1" t="n">
+        <v>0.06262</v>
+      </c>
+      <c r="P85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="P85" s="1" t="n">
+      <c r="Q85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -4933,9 +5191,12 @@
         <v>0.05449</v>
       </c>
       <c r="O86" s="1" t="n">
+        <v>0.05436</v>
+      </c>
+      <c r="P86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="P86" s="1" t="n">
+      <c r="Q86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -4985,9 +5246,12 @@
         <v>0.003352</v>
       </c>
       <c r="O87" s="1" t="n">
+        <v>0.003345</v>
+      </c>
+      <c r="P87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="P87" s="1" t="n">
+      <c r="Q87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -5037,9 +5301,12 @@
         <v>0.05057</v>
       </c>
       <c r="O88" s="1" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="P88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="P88" s="1" t="n">
+      <c r="Q88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -5089,9 +5356,12 @@
         <v>0.03077</v>
       </c>
       <c r="O89" s="1" t="n">
+        <v>0.03087</v>
+      </c>
+      <c r="P89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="P89" s="1" t="n">
+      <c r="Q89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -5141,10 +5411,13 @@
         <v>0.3473</v>
       </c>
       <c r="O90" s="1" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="P90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="P90" s="1" t="n">
-        <v>0.3471</v>
+      <c r="Q90" s="1" t="n">
+        <v>0.3466</v>
       </c>
     </row>
     <row r="91">
@@ -5193,9 +5466,12 @@
         <v>0.0789</v>
       </c>
       <c r="O91" s="1" t="n">
+        <v>0.07742</v>
+      </c>
+      <c r="P91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="P91" s="1" t="n">
+      <c r="Q91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -5245,9 +5521,12 @@
         <v>0.3518</v>
       </c>
       <c r="O92" s="1" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="P92" s="1" t="n">
         <v>0.3551</v>
       </c>
-      <c r="P92" s="1" t="n">
+      <c r="Q92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -5297,9 +5576,12 @@
         <v>1.9809</v>
       </c>
       <c r="O93" s="1" t="n">
+        <v>1.9742</v>
+      </c>
+      <c r="P93" s="1" t="n">
         <v>1.9809</v>
       </c>
-      <c r="P93" s="1" t="n">
+      <c r="Q93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -5349,10 +5631,13 @@
         <v>0.2588</v>
       </c>
       <c r="O94" s="1" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="P94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="P94" s="1" t="n">
-        <v>0.2586</v>
+      <c r="Q94" s="1" t="n">
+        <v>0.2583</v>
       </c>
     </row>
     <row r="95">
@@ -5401,9 +5686,12 @@
         <v>0.04614</v>
       </c>
       <c r="O95" s="1" t="n">
+        <v>0.04582</v>
+      </c>
+      <c r="P95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="P95" s="1" t="n">
+      <c r="Q95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -5453,9 +5741,12 @@
         <v>0.00618</v>
       </c>
       <c r="O96" s="1" t="n">
+        <v>0.006056</v>
+      </c>
+      <c r="P96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="P96" s="1" t="n">
+      <c r="Q96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -5505,10 +5796,13 @@
         <v>0.001729</v>
       </c>
       <c r="O97" s="1" t="n">
+        <v>0.001723</v>
+      </c>
+      <c r="P97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="P97" s="1" t="n">
-        <v>0.001729</v>
+      <c r="Q97" s="1" t="n">
+        <v>0.001723</v>
       </c>
     </row>
     <row r="98">
@@ -5557,9 +5851,12 @@
         <v>5.22</v>
       </c>
       <c r="O98" s="1" t="n">
+        <v>5.194</v>
+      </c>
+      <c r="P98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="P98" s="1" t="n">
+      <c r="Q98" s="1" t="n">
         <v>5.188</v>
       </c>
     </row>
@@ -5609,10 +5906,13 @@
         <v>0.0151</v>
       </c>
       <c r="O99" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="P99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="P99" s="1" t="n">
-        <v>0.0151</v>
+      <c r="Q99" s="1" t="n">
+        <v>0.01508</v>
       </c>
     </row>
     <row r="100">
@@ -5661,9 +5961,12 @@
         <v>0.5538999999999999</v>
       </c>
       <c r="O100" s="1" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="P100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="P100" s="1" t="n">
+      <c r="Q100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -5713,10 +6016,13 @@
         <v>0.0901</v>
       </c>
       <c r="O101" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="P101" s="1" t="n">
-        <v>0.0901</v>
+      <c r="Q101" s="1" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="102">
@@ -5765,9 +6071,12 @@
         <v>32.36</v>
       </c>
       <c r="O102" s="1" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="P102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="P102" s="1" t="n">
+      <c r="Q102" s="1" t="n">
         <v>32.36</v>
       </c>
     </row>
@@ -5817,9 +6126,12 @@
         <v>0.03164</v>
       </c>
       <c r="O103" s="1" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="P103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="P103" s="1" t="n">
+      <c r="Q103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -5869,9 +6181,12 @@
         <v>0.06578000000000001</v>
       </c>
       <c r="O104" s="1" t="n">
+        <v>0.06569</v>
+      </c>
+      <c r="P104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="P104" s="1" t="n">
+      <c r="Q104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -5921,9 +6236,12 @@
         <v>1.3049</v>
       </c>
       <c r="O105" s="1" t="n">
+        <v>1.3048</v>
+      </c>
+      <c r="P105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="P105" s="1" t="n">
+      <c r="Q105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -5973,9 +6291,12 @@
         <v>0.1203</v>
       </c>
       <c r="O106" s="1" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="P106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="P106" s="1" t="n">
+      <c r="Q106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -6025,9 +6346,12 @@
         <v>0.121</v>
       </c>
       <c r="O107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="P107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="P107" s="1" t="n">
+      <c r="Q107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -6077,9 +6401,12 @@
         <v>0.096</v>
       </c>
       <c r="O108" s="1" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="P108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="P108" s="1" t="n">
+      <c r="Q108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -6129,9 +6456,12 @@
         <v>0.13782</v>
       </c>
       <c r="O109" s="1" t="n">
+        <v>0.13851</v>
+      </c>
+      <c r="P109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="P109" s="1" t="n">
+      <c r="Q109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -6181,9 +6511,12 @@
         <v>5.555</v>
       </c>
       <c r="O110" s="1" t="n">
+        <v>5.573</v>
+      </c>
+      <c r="P110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="P110" s="1" t="n">
+      <c r="Q110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -6233,9 +6566,12 @@
         <v>1.101</v>
       </c>
       <c r="O111" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="P111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="P111" s="1" t="n">
+      <c r="Q111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -6285,9 +6621,12 @@
         <v>0.028875</v>
       </c>
       <c r="O112" s="1" t="n">
+        <v>0.028959</v>
+      </c>
+      <c r="P112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="P112" s="1" t="n">
+      <c r="Q112" s="1" t="n">
         <v>0.028875</v>
       </c>
     </row>
@@ -6337,10 +6676,13 @@
         <v>1.872</v>
       </c>
       <c r="O113" s="1" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="P113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="P113" s="1" t="n">
-        <v>1.869</v>
+      <c r="Q113" s="1" t="n">
+        <v>1.868</v>
       </c>
     </row>
     <row r="114">
@@ -6389,9 +6731,12 @@
         <v>0.05877</v>
       </c>
       <c r="O114" s="1" t="n">
+        <v>0.05882</v>
+      </c>
+      <c r="P114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="P114" s="1" t="n">
+      <c r="Q114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -6441,9 +6786,12 @@
         <v>0.12872</v>
       </c>
       <c r="O115" s="1" t="n">
+        <v>0.12844</v>
+      </c>
+      <c r="P115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="P115" s="1" t="n">
+      <c r="Q115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -6493,10 +6841,13 @@
         <v>1.1062</v>
       </c>
       <c r="O116" s="1" t="n">
+        <v>1.1039</v>
+      </c>
+      <c r="P116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="P116" s="1" t="n">
-        <v>1.1055</v>
+      <c r="Q116" s="1" t="n">
+        <v>1.1039</v>
       </c>
     </row>
     <row r="117">
@@ -6545,9 +6896,12 @@
         <v>0.1531</v>
       </c>
       <c r="O117" s="1" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="P117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="P117" s="1" t="n">
+      <c r="Q117" s="1" t="n">
         <v>0.1531</v>
       </c>
     </row>
@@ -6597,9 +6951,12 @@
         <v>0.158</v>
       </c>
       <c r="O118" s="1" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="P118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="P118" s="1" t="n">
+      <c r="Q118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -6649,9 +7006,12 @@
         <v>0.0472</v>
       </c>
       <c r="O119" s="1" t="n">
+        <v>0.04686</v>
+      </c>
+      <c r="P119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="P119" s="1" t="n">
+      <c r="Q119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -6701,10 +7061,13 @@
         <v>3.019</v>
       </c>
       <c r="O120" s="1" t="n">
+        <v>3.016</v>
+      </c>
+      <c r="P120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="P120" s="1" t="n">
-        <v>3.018</v>
+      <c r="Q120" s="1" t="n">
+        <v>3.016</v>
       </c>
     </row>
     <row r="121">
@@ -6753,9 +7116,12 @@
         <v>0.2977</v>
       </c>
       <c r="O121" s="1" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="P121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="P121" s="1" t="n">
+      <c r="Q121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -6805,9 +7171,12 @@
         <v>0.5792</v>
       </c>
       <c r="O122" s="1" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="P122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="P122" s="1" t="n">
+      <c r="Q122" s="1" t="n">
         <v>0.5792</v>
       </c>
     </row>
@@ -6857,10 +7226,13 @@
         <v>0.01257</v>
       </c>
       <c r="O123" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="P123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="P123" s="1" t="n">
-        <v>0.01257</v>
+      <c r="Q123" s="1" t="n">
+        <v>0.01256</v>
       </c>
     </row>
     <row r="124">
@@ -6909,10 +7281,13 @@
         <v>0.1581</v>
       </c>
       <c r="O124" s="1" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="P124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="P124" s="1" t="n">
-        <v>0.1577</v>
+      <c r="Q124" s="1" t="n">
+        <v>0.1574</v>
       </c>
     </row>
     <row r="125">
@@ -6961,9 +7336,12 @@
         <v>0.001779</v>
       </c>
       <c r="O125" s="1" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="P125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="P125" s="1" t="n">
+      <c r="Q125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -7013,10 +7391,13 @@
         <v>0.0004845</v>
       </c>
       <c r="O126" s="1" t="n">
+        <v>0.0004831</v>
+      </c>
+      <c r="P126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="P126" s="1" t="n">
-        <v>0.0004845</v>
+      <c r="Q126" s="1" t="n">
+        <v>0.0004831</v>
       </c>
     </row>
     <row r="127">
@@ -7065,10 +7446,13 @@
         <v>0.02936</v>
       </c>
       <c r="O127" s="1" t="n">
+        <v>0.02934</v>
+      </c>
+      <c r="P127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="P127" s="1" t="n">
-        <v>0.02936</v>
+      <c r="Q127" s="1" t="n">
+        <v>0.02934</v>
       </c>
     </row>
     <row r="128">
@@ -7117,9 +7501,12 @@
         <v>0.04131</v>
       </c>
       <c r="O128" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="P128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="P128" s="1" t="n">
+      <c r="Q128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -7169,9 +7556,12 @@
         <v>0.04873</v>
       </c>
       <c r="O129" s="1" t="n">
+        <v>0.04872</v>
+      </c>
+      <c r="P129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="P129" s="1" t="n">
+      <c r="Q129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -7221,9 +7611,12 @@
         <v>1.25e-05</v>
       </c>
       <c r="O130" s="1" t="n">
+        <v>1.25e-05</v>
+      </c>
+      <c r="P130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="P130" s="1" t="n">
+      <c r="Q130" s="1" t="n">
         <v>1.24e-05</v>
       </c>
     </row>
@@ -7273,9 +7666,12 @@
         <v>7.1e-06</v>
       </c>
       <c r="O131" s="1" t="n">
+        <v>6.9e-06</v>
+      </c>
+      <c r="P131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="P131" s="1" t="n">
+      <c r="Q131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -7325,9 +7721,12 @@
         <v>0.00699</v>
       </c>
       <c r="O132" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="P132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="P132" s="1" t="n">
+      <c r="Q132" s="1" t="n">
         <v>0.00699</v>
       </c>
     </row>
@@ -7377,9 +7776,12 @@
         <v>0.0968</v>
       </c>
       <c r="O133" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="P133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="P133" s="1" t="n">
+      <c r="Q133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -7429,10 +7831,13 @@
         <v>0.0004079</v>
       </c>
       <c r="O134" s="1" t="n">
+        <v>0.0004076</v>
+      </c>
+      <c r="P134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="P134" s="1" t="n">
-        <v>0.0004079</v>
+      <c r="Q134" s="1" t="n">
+        <v>0.0004076</v>
       </c>
     </row>
     <row r="135">
@@ -7481,10 +7886,13 @@
         <v>0.08282</v>
       </c>
       <c r="O135" s="1" t="n">
+        <v>0.08221000000000001</v>
+      </c>
+      <c r="P135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="P135" s="1" t="n">
-        <v>0.08282</v>
+      <c r="Q135" s="1" t="n">
+        <v>0.08221000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7533,10 +7941,13 @@
         <v>0.007891</v>
       </c>
       <c r="O136" s="1" t="n">
+        <v>0.007851</v>
+      </c>
+      <c r="P136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="P136" s="1" t="n">
-        <v>0.007868999999999999</v>
+      <c r="Q136" s="1" t="n">
+        <v>0.007851</v>
       </c>
     </row>
     <row r="137">
@@ -7585,9 +7996,12 @@
         <v>0.000825</v>
       </c>
       <c r="O137" s="1" t="n">
+        <v>0.0008206</v>
+      </c>
+      <c r="P137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="P137" s="1" t="n">
+      <c r="Q137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -7637,9 +8051,12 @@
         <v>0.1472</v>
       </c>
       <c r="O138" s="1" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="P138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="P138" s="1" t="n">
+      <c r="Q138" s="1" t="n">
         <v>0.1468</v>
       </c>
     </row>
@@ -7689,10 +8106,13 @@
         <v>0.006696</v>
       </c>
       <c r="O139" s="1" t="n">
+        <v>0.006689</v>
+      </c>
+      <c r="P139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="P139" s="1" t="n">
-        <v>0.006696</v>
+      <c r="Q139" s="1" t="n">
+        <v>0.006689</v>
       </c>
     </row>
     <row r="140">
@@ -7741,9 +8161,12 @@
         <v>0.01386</v>
       </c>
       <c r="O140" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="P140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="P140" s="1" t="n">
+      <c r="Q140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -7793,10 +8216,13 @@
         <v>0.09755</v>
       </c>
       <c r="O141" s="1" t="n">
+        <v>0.09732</v>
+      </c>
+      <c r="P141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="P141" s="1" t="n">
-        <v>0.09755</v>
+      <c r="Q141" s="1" t="n">
+        <v>0.09732</v>
       </c>
     </row>
     <row r="142">
@@ -7845,9 +8271,12 @@
         <v>0.05418</v>
       </c>
       <c r="O142" s="1" t="n">
+        <v>0.05419</v>
+      </c>
+      <c r="P142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="P142" s="1" t="n">
+      <c r="Q142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -7897,10 +8326,13 @@
         <v>0.3229</v>
       </c>
       <c r="O143" s="1" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="P143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="P143" s="1" t="n">
-        <v>0.3229</v>
+      <c r="Q143" s="1" t="n">
+        <v>0.3222</v>
       </c>
     </row>
     <row r="144">
@@ -7949,10 +8381,13 @@
         <v>0.02567</v>
       </c>
       <c r="O144" s="1" t="n">
+        <v>0.02564</v>
+      </c>
+      <c r="P144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="P144" s="1" t="n">
-        <v>0.02567</v>
+      <c r="Q144" s="1" t="n">
+        <v>0.02564</v>
       </c>
     </row>
     <row r="145">
@@ -8001,10 +8436,13 @@
         <v>0.2372</v>
       </c>
       <c r="O145" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="P145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="P145" s="1" t="n">
-        <v>0.2372</v>
+      <c r="Q145" s="1" t="n">
+        <v>0.2368</v>
       </c>
     </row>
     <row r="146">
@@ -8053,9 +8491,12 @@
         <v>0.006982</v>
       </c>
       <c r="O146" s="1" t="n">
+        <v>0.007003</v>
+      </c>
+      <c r="P146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="P146" s="1" t="n">
+      <c r="Q146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -8105,10 +8546,13 @@
         <v>0.08699</v>
       </c>
       <c r="O147" s="1" t="n">
+        <v>0.08637</v>
+      </c>
+      <c r="P147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="P147" s="1" t="n">
-        <v>0.08655</v>
+      <c r="Q147" s="1" t="n">
+        <v>0.08637</v>
       </c>
     </row>
     <row r="148">
@@ -8157,9 +8601,12 @@
         <v>0.05244</v>
       </c>
       <c r="O148" s="1" t="n">
-        <v>0.05244</v>
+        <v>0.05284</v>
       </c>
       <c r="P148" s="1" t="n">
+        <v>0.05284</v>
+      </c>
+      <c r="Q148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -8209,9 +8656,12 @@
         <v>0.02386</v>
       </c>
       <c r="O149" s="1" t="n">
+        <v>0.02389</v>
+      </c>
+      <c r="P149" s="1" t="n">
         <v>0.02394</v>
       </c>
-      <c r="P149" s="1" t="n">
+      <c r="Q149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -8261,9 +8711,12 @@
         <v>0.0853</v>
       </c>
       <c r="O150" s="1" t="n">
+        <v>0.08592</v>
+      </c>
+      <c r="P150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="P150" s="1" t="n">
+      <c r="Q150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -8313,9 +8766,12 @@
         <v>0.02324</v>
       </c>
       <c r="O151" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="P151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="P151" s="1" t="n">
+      <c r="Q151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -8365,9 +8821,12 @@
         <v>0.02534</v>
       </c>
       <c r="O152" s="1" t="n">
+        <v>0.02543</v>
+      </c>
+      <c r="P152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="P152" s="1" t="n">
+      <c r="Q152" s="1" t="n">
         <v>0.02534</v>
       </c>
     </row>
@@ -8417,9 +8876,12 @@
         <v>0.0002159</v>
       </c>
       <c r="O153" s="1" t="n">
+        <v>0.0002152</v>
+      </c>
+      <c r="P153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="P153" s="1" t="n">
+      <c r="Q153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -8469,10 +8931,13 @@
         <v>0.4393</v>
       </c>
       <c r="O154" s="1" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="P154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="P154" s="1" t="n">
-        <v>0.4393</v>
+      <c r="Q154" s="1" t="n">
+        <v>0.4376</v>
       </c>
     </row>
     <row r="155">
@@ -8521,9 +8986,12 @@
         <v>0.06813</v>
       </c>
       <c r="O155" s="1" t="n">
+        <v>0.06766999999999999</v>
+      </c>
+      <c r="P155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="P155" s="1" t="n">
+      <c r="Q155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -8573,9 +9041,12 @@
         <v>0.12874</v>
       </c>
       <c r="O156" s="1" t="n">
+        <v>0.12826</v>
+      </c>
+      <c r="P156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="P156" s="1" t="n">
+      <c r="Q156" s="1" t="n">
         <v>0.12781</v>
       </c>
     </row>
@@ -8625,10 +9096,13 @@
         <v>0.4847</v>
       </c>
       <c r="O157" s="1" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="P157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="P157" s="1" t="n">
-        <v>0.4839</v>
+      <c r="Q157" s="1" t="n">
+        <v>0.4838</v>
       </c>
     </row>
     <row r="158">
@@ -8677,9 +9151,12 @@
         <v>0.452</v>
       </c>
       <c r="O158" s="1" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="P158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="P158" s="1" t="n">
+      <c r="Q158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -8729,10 +9206,13 @@
         <v>0.007486</v>
       </c>
       <c r="O159" s="1" t="n">
+        <v>0.007458</v>
+      </c>
+      <c r="P159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="P159" s="1" t="n">
-        <v>0.007486</v>
+      <c r="Q159" s="1" t="n">
+        <v>0.007458</v>
       </c>
     </row>
     <row r="160">
@@ -8781,9 +9261,12 @@
         <v>0.004653</v>
       </c>
       <c r="O160" s="1" t="n">
+        <v>0.004654</v>
+      </c>
+      <c r="P160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="P160" s="1" t="n">
+      <c r="Q160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -8833,10 +9316,13 @@
         <v>0.004294</v>
       </c>
       <c r="O161" s="1" t="n">
+        <v>0.00429</v>
+      </c>
+      <c r="P161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="P161" s="1" t="n">
-        <v>0.004294</v>
+      <c r="Q161" s="1" t="n">
+        <v>0.00429</v>
       </c>
     </row>
     <row r="162">
@@ -8885,9 +9371,12 @@
         <v>0.0956</v>
       </c>
       <c r="O162" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="P162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="P162" s="1" t="n">
+      <c r="Q162" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -8937,10 +9426,13 @@
         <v>0.2856</v>
       </c>
       <c r="O163" s="1" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="P163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="P163" s="1" t="n">
-        <v>0.2852</v>
+      <c r="Q163" s="1" t="n">
+        <v>0.285</v>
       </c>
     </row>
     <row r="164">
@@ -8989,9 +9481,12 @@
         <v>0.1143</v>
       </c>
       <c r="O164" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="P164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="P164" s="1" t="n">
+      <c r="Q164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -9041,9 +9536,12 @@
         <v>0.1755</v>
       </c>
       <c r="O165" s="1" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="P165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="P165" s="1" t="n">
+      <c r="Q165" s="1" t="n">
         <v>0.1753</v>
       </c>
     </row>
@@ -9093,9 +9591,12 @@
         <v>0.0102</v>
       </c>
       <c r="O166" s="1" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="P166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="P166" s="1" t="n">
+      <c r="Q166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -9145,10 +9646,13 @@
         <v>1.829</v>
       </c>
       <c r="O167" s="1" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="P167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="P167" s="1" t="n">
-        <v>1.826</v>
+      <c r="Q167" s="1" t="n">
+        <v>1.825</v>
       </c>
     </row>
     <row r="168">
@@ -9197,9 +9701,12 @@
         <v>1.338</v>
       </c>
       <c r="O168" s="1" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="P168" s="1" t="n">
+      <c r="Q168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -9249,10 +9756,13 @@
         <v>0.007299</v>
       </c>
       <c r="O169" s="1" t="n">
+        <v>0.007296</v>
+      </c>
+      <c r="P169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="P169" s="1" t="n">
-        <v>0.007299</v>
+      <c r="Q169" s="1" t="n">
+        <v>0.007296</v>
       </c>
     </row>
     <row r="170">
@@ -9301,9 +9811,12 @@
         <v>0.0115</v>
       </c>
       <c r="O170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="P170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="P170" s="1" t="n">
+      <c r="Q170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -9353,10 +9866,13 @@
         <v>0.005803</v>
       </c>
       <c r="O171" s="1" t="n">
+        <v>0.00578</v>
+      </c>
+      <c r="P171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="P171" s="1" t="n">
-        <v>0.005793</v>
+      <c r="Q171" s="1" t="n">
+        <v>0.00578</v>
       </c>
     </row>
     <row r="172">
@@ -9405,9 +9921,12 @@
         <v>0.14822</v>
       </c>
       <c r="O172" s="1" t="n">
+        <v>0.14817</v>
+      </c>
+      <c r="P172" s="1" t="n">
         <v>0.14822</v>
       </c>
-      <c r="P172" s="1" t="n">
+      <c r="Q172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -9457,9 +9976,12 @@
         <v>4.909</v>
       </c>
       <c r="O173" s="1" t="n">
+        <v>4.895</v>
+      </c>
+      <c r="P173" s="1" t="n">
         <v>4.909</v>
       </c>
-      <c r="P173" s="1" t="n">
+      <c r="Q173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -9509,10 +10031,13 @@
         <v>0.07832</v>
       </c>
       <c r="O174" s="1" t="n">
+        <v>0.07819</v>
+      </c>
+      <c r="P174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="P174" s="1" t="n">
-        <v>0.07832</v>
+      <c r="Q174" s="1" t="n">
+        <v>0.07819</v>
       </c>
     </row>
     <row r="175">
@@ -9561,10 +10086,13 @@
         <v>0.007413</v>
       </c>
       <c r="O175" s="1" t="n">
+        <v>0.007407</v>
+      </c>
+      <c r="P175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="P175" s="1" t="n">
-        <v>0.007413</v>
+      <c r="Q175" s="1" t="n">
+        <v>0.007407</v>
       </c>
     </row>
     <row r="176">
@@ -9613,10 +10141,13 @@
         <v>0.2006</v>
       </c>
       <c r="O176" s="1" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="P176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="P176" s="1" t="n">
-        <v>0.2006</v>
+      <c r="Q176" s="1" t="n">
+        <v>0.1997</v>
       </c>
     </row>
     <row r="177">
@@ -9665,9 +10196,12 @@
         <v>0.05195</v>
       </c>
       <c r="O177" s="1" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="P177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="P177" s="1" t="n">
+      <c r="Q177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -9717,9 +10251,12 @@
         <v>0.05469</v>
       </c>
       <c r="O178" s="1" t="n">
+        <v>0.05457</v>
+      </c>
+      <c r="P178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="P178" s="1" t="n">
+      <c r="Q178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -9769,10 +10306,13 @@
         <v>0.02318</v>
       </c>
       <c r="O179" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="P179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="P179" s="1" t="n">
-        <v>0.02318</v>
+      <c r="Q179" s="1" t="n">
+        <v>0.02317</v>
       </c>
     </row>
     <row r="180">
@@ -9821,9 +10361,12 @@
         <v>0.6955</v>
       </c>
       <c r="O180" s="1" t="n">
+        <v>0.6951000000000001</v>
+      </c>
+      <c r="P180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="P180" s="1" t="n">
+      <c r="Q180" s="1" t="n">
         <v>0.6938</v>
       </c>
     </row>
@@ -9873,9 +10416,12 @@
         <v>0.0003768</v>
       </c>
       <c r="O181" s="1" t="n">
+        <v>0.0003747</v>
+      </c>
+      <c r="P181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="P181" s="1" t="n">
+      <c r="Q181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -9925,10 +10471,13 @@
         <v>0.01258</v>
       </c>
       <c r="O182" s="1" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="P182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="P182" s="1" t="n">
-        <v>0.01256</v>
+      <c r="Q182" s="1" t="n">
+        <v>0.01255</v>
       </c>
     </row>
     <row r="183">
@@ -9977,9 +10526,12 @@
         <v>4.22</v>
       </c>
       <c r="O183" s="1" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="P183" s="1" t="n">
+      <c r="Q183" s="1" t="n">
         <v>4.22</v>
       </c>
     </row>
@@ -10029,10 +10581,13 @@
         <v>0.2363</v>
       </c>
       <c r="O184" s="1" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="P184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="P184" s="1" t="n">
-        <v>0.2363</v>
+      <c r="Q184" s="1" t="n">
+        <v>0.2354</v>
       </c>
     </row>
     <row r="185">
@@ -10081,9 +10636,12 @@
         <v>0.03685</v>
       </c>
       <c r="O185" s="1" t="n">
+        <v>0.03685</v>
+      </c>
+      <c r="P185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="P185" s="1" t="n">
+      <c r="Q185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -10133,9 +10691,12 @@
         <v>0.11579</v>
       </c>
       <c r="O186" s="1" t="n">
+        <v>0.11584</v>
+      </c>
+      <c r="P186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="P186" s="1" t="n">
+      <c r="Q186" s="1" t="n">
         <v>0.11566</v>
       </c>
     </row>
@@ -10185,9 +10746,12 @@
         <v>0.009136</v>
       </c>
       <c r="O187" s="1" t="n">
+        <v>0.009124999999999999</v>
+      </c>
+      <c r="P187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="P187" s="1" t="n">
+      <c r="Q187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -10237,9 +10801,12 @@
         <v>0.0974</v>
       </c>
       <c r="O188" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="P188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="P188" s="1" t="n">
+      <c r="Q188" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -10289,10 +10856,13 @@
         <v>0.02762</v>
       </c>
       <c r="O189" s="1" t="n">
+        <v>0.02754</v>
+      </c>
+      <c r="P189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="P189" s="1" t="n">
-        <v>0.02762</v>
+      <c r="Q189" s="1" t="n">
+        <v>0.02754</v>
       </c>
     </row>
     <row r="190">
@@ -10341,9 +10911,12 @@
         <v>0.00877</v>
       </c>
       <c r="O190" s="1" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="P190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="P190" s="1" t="n">
+      <c r="Q190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -10393,9 +10966,12 @@
         <v>0.001952</v>
       </c>
       <c r="O191" s="1" t="n">
+        <v>0.001951</v>
+      </c>
+      <c r="P191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="P191" s="1" t="n">
+      <c r="Q191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -10445,10 +11021,13 @@
         <v>0.1002</v>
       </c>
       <c r="O192" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="P192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="P192" s="1" t="n">
-        <v>0.1002</v>
+      <c r="Q192" s="1" t="n">
+        <v>0.1001</v>
       </c>
     </row>
     <row r="193">
@@ -10497,10 +11076,13 @@
         <v>0.02319</v>
       </c>
       <c r="O193" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="P193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="P193" s="1" t="n">
-        <v>0.02319</v>
+      <c r="Q193" s="1" t="n">
+        <v>0.02315</v>
       </c>
     </row>
     <row r="194">
@@ -10549,10 +11131,13 @@
         <v>0.01345</v>
       </c>
       <c r="O194" s="1" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="P194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="P194" s="1" t="n">
-        <v>0.01345</v>
+      <c r="Q194" s="1" t="n">
+        <v>0.01342</v>
       </c>
     </row>
     <row r="195">
@@ -10601,10 +11186,13 @@
         <v>0.02081</v>
       </c>
       <c r="O195" s="1" t="n">
+        <v>0.02079</v>
+      </c>
+      <c r="P195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="P195" s="1" t="n">
-        <v>0.02081</v>
+      <c r="Q195" s="1" t="n">
+        <v>0.02079</v>
       </c>
     </row>
     <row r="196">
@@ -10653,9 +11241,12 @@
         <v>0.1762</v>
       </c>
       <c r="O196" s="1" t="n">
+        <v>0.17602</v>
+      </c>
+      <c r="P196" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="P196" s="1" t="n">
+      <c r="Q196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -10705,9 +11296,12 @@
         <v>0.007364</v>
       </c>
       <c r="O197" s="1" t="n">
+        <v>0.00735</v>
+      </c>
+      <c r="P197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="P197" s="1" t="n">
+      <c r="Q197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -10757,9 +11351,12 @@
         <v>0.01906</v>
       </c>
       <c r="O198" s="1" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="P198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="P198" s="1" t="n">
+      <c r="Q198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -10809,9 +11406,12 @@
         <v>0.01627</v>
       </c>
       <c r="O199" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="P199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="P199" s="1" t="n">
+      <c r="Q199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -10861,9 +11461,12 @@
         <v>0.2978</v>
       </c>
       <c r="O200" s="1" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="P200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="P200" s="1" t="n">
+      <c r="Q200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -10913,9 +11516,12 @@
         <v>0.006205</v>
       </c>
       <c r="O201" s="1" t="n">
+        <v>0.006229</v>
+      </c>
+      <c r="P201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="P201" s="1" t="n">
+      <c r="Q201" s="1" t="n">
         <v>0.006205</v>
       </c>
     </row>
@@ -10965,10 +11571,13 @@
         <v>0.0004418</v>
       </c>
       <c r="O202" s="1" t="n">
+        <v>0.0004411</v>
+      </c>
+      <c r="P202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="P202" s="1" t="n">
-        <v>0.0004418</v>
+      <c r="Q202" s="1" t="n">
+        <v>0.0004411</v>
       </c>
     </row>
     <row r="203">
@@ -11017,10 +11626,13 @@
         <v>0.007257</v>
       </c>
       <c r="O203" s="1" t="n">
+        <v>0.007251</v>
+      </c>
+      <c r="P203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="P203" s="1" t="n">
-        <v>0.007257</v>
+      <c r="Q203" s="1" t="n">
+        <v>0.007251</v>
       </c>
     </row>
     <row r="204">
@@ -11069,9 +11681,12 @@
         <v>0.1318</v>
       </c>
       <c r="O204" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="P204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="P204" s="1" t="n">
+      <c r="Q204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -11121,9 +11736,12 @@
         <v>0.01426</v>
       </c>
       <c r="O205" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="P205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="P205" s="1" t="n">
+      <c r="Q205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -11173,9 +11791,12 @@
         <v>0.003565</v>
       </c>
       <c r="O206" s="1" t="n">
+        <v>0.003566</v>
+      </c>
+      <c r="P206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="P206" s="1" t="n">
+      <c r="Q206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -11225,9 +11846,12 @@
         <v>0.05957</v>
       </c>
       <c r="O207" s="1" t="n">
+        <v>0.05948</v>
+      </c>
+      <c r="P207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="P207" s="1" t="n">
+      <c r="Q207" s="1" t="n">
         <v>0.0594</v>
       </c>
     </row>
@@ -11277,9 +11901,12 @@
         <v>15.47</v>
       </c>
       <c r="O208" s="1" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="P208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="P208" s="1" t="n">
+      <c r="Q208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -11329,9 +11956,12 @@
         <v>5192.4</v>
       </c>
       <c r="O209" s="1" t="n">
-        <v>5192.8</v>
+        <v>5193.5</v>
       </c>
       <c r="P209" s="1" t="n">
+        <v>5193.5</v>
+      </c>
+      <c r="Q209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -11381,9 +12011,12 @@
         <v>0.11955</v>
       </c>
       <c r="O210" s="1" t="n">
+        <v>0.1202</v>
+      </c>
+      <c r="P210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="P210" s="1" t="n">
+      <c r="Q210" s="1" t="n">
         <v>0.11955</v>
       </c>
     </row>
@@ -11433,9 +12066,12 @@
         <v>0.1802</v>
       </c>
       <c r="O211" s="1" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="P211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="P211" s="1" t="n">
+      <c r="Q211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -11485,9 +12121,12 @@
         <v>0.0303</v>
       </c>
       <c r="O212" s="1" t="n">
-        <v>0.0308</v>
+        <v>0.0309</v>
       </c>
       <c r="P212" s="1" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="Q212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -11537,9 +12176,12 @@
         <v>1.3976</v>
       </c>
       <c r="O213" s="1" t="n">
+        <v>1.3967</v>
+      </c>
+      <c r="P213" s="1" t="n">
         <v>1.3976</v>
       </c>
-      <c r="P213" s="1" t="n">
+      <c r="Q213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -11589,10 +12231,13 @@
         <v>0.05646</v>
       </c>
       <c r="O214" s="1" t="n">
+        <v>0.05641</v>
+      </c>
+      <c r="P214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="P214" s="1" t="n">
-        <v>0.05644</v>
+      <c r="Q214" s="1" t="n">
+        <v>0.05641</v>
       </c>
     </row>
     <row r="215">
@@ -11641,9 +12286,12 @@
         <v>0.04422</v>
       </c>
       <c r="O215" s="1" t="n">
-        <v>0.04422</v>
+        <v>0.04431</v>
       </c>
       <c r="P215" s="1" t="n">
+        <v>0.04431</v>
+      </c>
+      <c r="Q215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -11693,9 +12341,12 @@
         <v>0.15086</v>
       </c>
       <c r="O216" s="1" t="n">
+        <v>0.15043</v>
+      </c>
+      <c r="P216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="P216" s="1" t="n">
+      <c r="Q216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -11745,9 +12396,12 @@
         <v>0.074</v>
       </c>
       <c r="O217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="P217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="P217" s="1" t="n">
+      <c r="Q217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -11797,9 +12451,12 @@
         <v>0.00268</v>
       </c>
       <c r="O218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="P218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="P218" s="1" t="n">
+      <c r="Q218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -11849,10 +12506,13 @@
         <v>0.01705</v>
       </c>
       <c r="O219" s="1" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="P219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="P219" s="1" t="n">
-        <v>0.01705</v>
+      <c r="Q219" s="1" t="n">
+        <v>0.01703</v>
       </c>
     </row>
     <row r="220">
@@ -11901,9 +12561,12 @@
         <v>0.05519</v>
       </c>
       <c r="O220" s="1" t="n">
+        <v>0.05516</v>
+      </c>
+      <c r="P220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="P220" s="1" t="n">
+      <c r="Q220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -11953,9 +12616,12 @@
         <v>0.02187</v>
       </c>
       <c r="O221" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="P221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="P221" s="1" t="n">
+      <c r="Q221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -12005,9 +12671,12 @@
         <v>0.009339999999999999</v>
       </c>
       <c r="O222" s="1" t="n">
+        <v>0.00936</v>
+      </c>
+      <c r="P222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="P222" s="1" t="n">
+      <c r="Q222" s="1" t="n">
         <v>0.009339999999999999</v>
       </c>
     </row>
@@ -12060,6 +12729,9 @@
         <v>0.0165</v>
       </c>
       <c r="P223" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="Q223" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -12109,9 +12781,12 @@
         <v>0.0383</v>
       </c>
       <c r="O224" s="1" t="n">
+        <v>0.03826</v>
+      </c>
+      <c r="P224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="P224" s="1" t="n">
+      <c r="Q224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -12161,10 +12836,13 @@
         <v>0.001523</v>
       </c>
       <c r="O225" s="1" t="n">
+        <v>0.001522</v>
+      </c>
+      <c r="P225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="P225" s="1" t="n">
-        <v>0.001523</v>
+      <c r="Q225" s="1" t="n">
+        <v>0.001522</v>
       </c>
     </row>
     <row r="226">
@@ -12213,9 +12891,12 @@
         <v>27.18</v>
       </c>
       <c r="O226" s="1" t="n">
-        <v>27.18</v>
+        <v>27.2</v>
       </c>
       <c r="P226" s="1" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Q226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -12265,9 +12946,12 @@
         <v>0.07059</v>
       </c>
       <c r="O227" s="1" t="n">
+        <v>0.07054000000000001</v>
+      </c>
+      <c r="P227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="P227" s="1" t="n">
+      <c r="Q227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -12317,9 +13001,12 @@
         <v>0.3138</v>
       </c>
       <c r="O228" s="1" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="P228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="P228" s="1" t="n">
+      <c r="Q228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -12369,10 +13056,13 @@
         <v>18.37</v>
       </c>
       <c r="O229" s="1" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="P229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="P229" s="1" t="n">
-        <v>18.35</v>
+      <c r="Q229" s="1" t="n">
+        <v>18.33</v>
       </c>
     </row>
     <row r="230">
@@ -12421,10 +13111,13 @@
         <v>0.01923</v>
       </c>
       <c r="O230" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="P230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="P230" s="1" t="n">
-        <v>0.01923</v>
+      <c r="Q230" s="1" t="n">
+        <v>0.01921</v>
       </c>
     </row>
     <row r="231">
@@ -12473,9 +13166,12 @@
         <v>0.01218</v>
       </c>
       <c r="O231" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="P231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="P231" s="1" t="n">
+      <c r="Q231" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -12525,9 +13221,12 @@
         <v>0.2282</v>
       </c>
       <c r="O232" s="1" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="P232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="P232" s="1" t="n">
+      <c r="Q232" s="1" t="n">
         <v>0.2274</v>
       </c>
     </row>
@@ -12577,9 +13276,12 @@
         <v>0.07109</v>
       </c>
       <c r="O233" s="1" t="n">
+        <v>0.07091</v>
+      </c>
+      <c r="P233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="P233" s="1" t="n">
+      <c r="Q233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -12629,9 +13331,12 @@
         <v>0.1704</v>
       </c>
       <c r="O234" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="P234" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="P234" s="1" t="n">
+      <c r="Q234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -12681,9 +13386,12 @@
         <v>0.0252</v>
       </c>
       <c r="O235" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="P235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="P235" s="1" t="n">
+      <c r="Q235" s="1" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -12733,9 +13441,12 @@
         <v>0.02996</v>
       </c>
       <c r="O236" s="1" t="n">
+        <v>0.02997</v>
+      </c>
+      <c r="P236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="P236" s="1" t="n">
+      <c r="Q236" s="1" t="n">
         <v>0.02996</v>
       </c>
     </row>
@@ -12785,9 +13496,12 @@
         <v>2.001</v>
       </c>
       <c r="O237" s="1" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="P237" s="1" t="n">
         <v>2.001</v>
       </c>
-      <c r="P237" s="1" t="n">
+      <c r="Q237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -12837,10 +13551,13 @@
         <v>0.4201</v>
       </c>
       <c r="O238" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="P238" s="1" t="n">
-        <v>0.4201</v>
+      <c r="Q238" s="1" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="239">
@@ -12889,9 +13606,12 @@
         <v>0.03341</v>
       </c>
       <c r="O239" s="1" t="n">
+        <v>0.03356</v>
+      </c>
+      <c r="P239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="P239" s="1" t="n">
+      <c r="Q239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -12941,9 +13661,12 @@
         <v>0.03396</v>
       </c>
       <c r="O240" s="1" t="n">
+        <v>0.03392</v>
+      </c>
+      <c r="P240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="P240" s="1" t="n">
+      <c r="Q240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -12993,9 +13716,12 @@
         <v>0.0007489</v>
       </c>
       <c r="O241" s="1" t="n">
+        <v>0.0007497</v>
+      </c>
+      <c r="P241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="P241" s="1" t="n">
+      <c r="Q241" s="1" t="n">
         <v>0.0007489</v>
       </c>
     </row>
@@ -13045,10 +13771,13 @@
         <v>0.1833</v>
       </c>
       <c r="O242" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="P242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="P242" s="1" t="n">
-        <v>0.1829</v>
+      <c r="Q242" s="1" t="n">
+        <v>0.1828</v>
       </c>
     </row>
     <row r="243">
@@ -13097,10 +13826,13 @@
         <v>0.014792</v>
       </c>
       <c r="O243" s="1" t="n">
+        <v>0.014735</v>
+      </c>
+      <c r="P243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="P243" s="1" t="n">
-        <v>0.014772</v>
+      <c r="Q243" s="1" t="n">
+        <v>0.014735</v>
       </c>
     </row>
     <row r="244">
@@ -13149,9 +13881,12 @@
         <v>3.02e-05</v>
       </c>
       <c r="O244" s="1" t="n">
+        <v>3.02e-05</v>
+      </c>
+      <c r="P244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="P244" s="1" t="n">
+      <c r="Q244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -13201,9 +13936,12 @@
         <v>0.03527</v>
       </c>
       <c r="O245" s="1" t="n">
+        <v>0.03516</v>
+      </c>
+      <c r="P245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="P245" s="1" t="n">
+      <c r="Q245" s="1" t="n">
         <v>0.03514</v>
       </c>
     </row>
@@ -13253,10 +13991,13 @@
         <v>0.0804</v>
       </c>
       <c r="O246" s="1" t="n">
+        <v>0.08033999999999999</v>
+      </c>
+      <c r="P246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="P246" s="1" t="n">
-        <v>0.08037999999999999</v>
+      <c r="Q246" s="1" t="n">
+        <v>0.08033999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -13305,10 +14046,13 @@
         <v>0.007242</v>
       </c>
       <c r="O247" s="1" t="n">
+        <v>0.007234</v>
+      </c>
+      <c r="P247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="P247" s="1" t="n">
-        <v>0.007242</v>
+      <c r="Q247" s="1" t="n">
+        <v>0.007234</v>
       </c>
     </row>
     <row r="248">
@@ -13357,9 +14101,12 @@
         <v>0.09438000000000001</v>
       </c>
       <c r="O248" s="1" t="n">
+        <v>0.09522</v>
+      </c>
+      <c r="P248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="P248" s="1" t="n">
+      <c r="Q248" s="1" t="n">
         <v>0.09438000000000001</v>
       </c>
     </row>
@@ -13409,9 +14156,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="O249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="P249" s="1" t="n">
+      <c r="Q249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -13461,10 +14211,13 @@
         <v>0.03493</v>
       </c>
       <c r="O250" s="1" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="P250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="P250" s="1" t="n">
-        <v>0.03493</v>
+      <c r="Q250" s="1" t="n">
+        <v>0.0348</v>
       </c>
     </row>
     <row r="251">
@@ -13513,10 +14266,13 @@
         <v>0.03945</v>
       </c>
       <c r="O251" s="1" t="n">
+        <v>0.03944</v>
+      </c>
+      <c r="P251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="P251" s="1" t="n">
-        <v>0.03945</v>
+      <c r="Q251" s="1" t="n">
+        <v>0.03944</v>
       </c>
     </row>
     <row r="252">
@@ -13565,9 +14321,12 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="O252" s="1" t="n">
+        <v>0.0892</v>
+      </c>
+      <c r="P252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="P252" s="1" t="n">
+      <c r="Q252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -13617,9 +14376,12 @@
         <v>4.073</v>
       </c>
       <c r="O253" s="1" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="P253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="P253" s="1" t="n">
+      <c r="Q253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -13669,9 +14431,12 @@
         <v>0.1871</v>
       </c>
       <c r="O254" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="P254" s="1" t="n">
         <v>0.1875</v>
       </c>
-      <c r="P254" s="1" t="n">
+      <c r="Q254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -13721,10 +14486,13 @@
         <v>0.07202</v>
       </c>
       <c r="O255" s="1" t="n">
+        <v>0.07185999999999999</v>
+      </c>
+      <c r="P255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="P255" s="1" t="n">
-        <v>0.07202</v>
+      <c r="Q255" s="1" t="n">
+        <v>0.07185999999999999</v>
       </c>
     </row>
     <row r="256">
@@ -13773,9 +14541,12 @@
         <v>0.01831</v>
       </c>
       <c r="O256" s="1" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="P256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="P256" s="1" t="n">
+      <c r="Q256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -13825,10 +14596,13 @@
         <v>5.941</v>
       </c>
       <c r="O257" s="1" t="n">
+        <v>5.933</v>
+      </c>
+      <c r="P257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="P257" s="1" t="n">
-        <v>5.941</v>
+      <c r="Q257" s="1" t="n">
+        <v>5.933</v>
       </c>
     </row>
     <row r="258">
@@ -13877,10 +14651,13 @@
         <v>0.2616</v>
       </c>
       <c r="O258" s="1" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="P258" s="1" t="n">
-        <v>0.2616</v>
+      <c r="Q258" s="1" t="n">
+        <v>0.261</v>
       </c>
     </row>
     <row r="259">
@@ -13929,9 +14706,12 @@
         <v>0.1356</v>
       </c>
       <c r="O259" s="1" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="P259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="P259" s="1" t="n">
+      <c r="Q259" s="1" t="n">
         <v>0.1356</v>
       </c>
     </row>
@@ -13981,10 +14761,13 @@
         <v>0.30784</v>
       </c>
       <c r="O260" s="1" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="P260" s="1" t="n">
         <v>0.30784</v>
       </c>
-      <c r="P260" s="1" t="n">
-        <v>0.30525</v>
+      <c r="Q260" s="1" t="n">
+        <v>0.30501</v>
       </c>
     </row>
     <row r="261">
@@ -14033,9 +14816,12 @@
         <v>0.10011</v>
       </c>
       <c r="O261" s="1" t="n">
+        <v>0.09961</v>
+      </c>
+      <c r="P261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="P261" s="1" t="n">
+      <c r="Q261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -14085,10 +14871,13 @@
         <v>0.5387999999999999</v>
       </c>
       <c r="O262" s="1" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="P262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="P262" s="1" t="n">
-        <v>0.5387999999999999</v>
+      <c r="Q262" s="1" t="n">
+        <v>0.538</v>
       </c>
     </row>
     <row r="263">
@@ -14137,9 +14926,12 @@
         <v>0.2926</v>
       </c>
       <c r="O263" s="1" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="P263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="P263" s="1" t="n">
+      <c r="Q263" s="1" t="n">
         <v>0.2914</v>
       </c>
     </row>
@@ -14189,9 +14981,12 @@
         <v>0.966</v>
       </c>
       <c r="O264" s="1" t="n">
-        <v>0.972</v>
+        <v>0.974</v>
       </c>
       <c r="P264" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="Q264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -14241,9 +15036,12 @@
         <v>0.5394</v>
       </c>
       <c r="O265" s="1" t="n">
+        <v>0.5399</v>
+      </c>
+      <c r="P265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="P265" s="1" t="n">
+      <c r="Q265" s="1" t="n">
         <v>0.5394</v>
       </c>
     </row>
@@ -14293,10 +15091,13 @@
         <v>0.0737</v>
       </c>
       <c r="O266" s="1" t="n">
+        <v>0.07355</v>
+      </c>
+      <c r="P266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="P266" s="1" t="n">
-        <v>0.0737</v>
+      <c r="Q266" s="1" t="n">
+        <v>0.07355</v>
       </c>
     </row>
     <row r="267">
@@ -14345,9 +15146,12 @@
         <v>0.0216</v>
       </c>
       <c r="O267" s="1" t="n">
+        <v>0.02154</v>
+      </c>
+      <c r="P267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="P267" s="1" t="n">
+      <c r="Q267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -14397,9 +15201,12 @@
         <v>0.01623</v>
       </c>
       <c r="O268" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="P268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="P268" s="1" t="n">
+      <c r="Q268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -14449,9 +15256,12 @@
         <v>0.003802</v>
       </c>
       <c r="O269" s="1" t="n">
-        <v>0.003802</v>
+        <v>0.003804</v>
       </c>
       <c r="P269" s="1" t="n">
+        <v>0.003804</v>
+      </c>
+      <c r="Q269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -14501,10 +15311,13 @@
         <v>0.00763</v>
       </c>
       <c r="O270" s="1" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="P270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="P270" s="1" t="n">
-        <v>0.00762</v>
+      <c r="Q270" s="1" t="n">
+        <v>0.00761</v>
       </c>
     </row>
     <row r="271">
@@ -14553,9 +15366,12 @@
         <v>0.05511</v>
       </c>
       <c r="O271" s="1" t="n">
+        <v>0.05504</v>
+      </c>
+      <c r="P271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="P271" s="1" t="n">
+      <c r="Q271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -14605,10 +15421,13 @@
         <v>2.282</v>
       </c>
       <c r="O272" s="1" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="P272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="P272" s="1" t="n">
-        <v>2.282</v>
+      <c r="Q272" s="1" t="n">
+        <v>2.271</v>
       </c>
     </row>
     <row r="273">
@@ -14657,9 +15476,12 @@
         <v>0.05503</v>
       </c>
       <c r="O273" s="1" t="n">
+        <v>0.05489</v>
+      </c>
+      <c r="P273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="P273" s="1" t="n">
+      <c r="Q273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -14709,9 +15531,12 @@
         <v>0.02336</v>
       </c>
       <c r="O274" s="1" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="P274" s="1" t="n">
         <v>0.02336</v>
       </c>
-      <c r="P274" s="1" t="n">
+      <c r="Q274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -14761,9 +15586,12 @@
         <v>1.169</v>
       </c>
       <c r="O275" s="1" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="P275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="P275" s="1" t="n">
+      <c r="Q275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -14813,10 +15641,13 @@
         <v>0.2715</v>
       </c>
       <c r="O276" s="1" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="P276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="P276" s="1" t="n">
-        <v>0.2715</v>
+      <c r="Q276" s="1" t="n">
+        <v>0.2706</v>
       </c>
     </row>
     <row r="277">
@@ -14865,10 +15696,13 @@
         <v>0.93</v>
       </c>
       <c r="O277" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="P277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="P277" s="1" t="n">
-        <v>0.93</v>
+      <c r="Q277" s="1" t="n">
+        <v>0.929</v>
       </c>
     </row>
     <row r="278">
@@ -14917,10 +15751,13 @@
         <v>0.6232</v>
       </c>
       <c r="O278" s="1" t="n">
+        <v>0.6221</v>
+      </c>
+      <c r="P278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="P278" s="1" t="n">
-        <v>0.6224</v>
+      <c r="Q278" s="1" t="n">
+        <v>0.6221</v>
       </c>
     </row>
     <row r="279">
@@ -14969,10 +15806,13 @@
         <v>0.001345</v>
       </c>
       <c r="O279" s="1" t="n">
+        <v>0.001341</v>
+      </c>
+      <c r="P279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="P279" s="1" t="n">
-        <v>0.001344</v>
+      <c r="Q279" s="1" t="n">
+        <v>0.001341</v>
       </c>
     </row>
     <row r="280">
@@ -15021,9 +15861,12 @@
         <v>0.005581</v>
       </c>
       <c r="O280" s="1" t="n">
+        <v>0.005579</v>
+      </c>
+      <c r="P280" s="1" t="n">
         <v>0.005581</v>
       </c>
-      <c r="P280" s="1" t="n">
+      <c r="Q280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -15073,10 +15916,13 @@
         <v>1.519</v>
       </c>
       <c r="O281" s="1" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="P281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="P281" s="1" t="n">
-        <v>1.519</v>
+      <c r="Q281" s="1" t="n">
+        <v>1.516</v>
       </c>
     </row>
     <row r="282">
@@ -15125,10 +15971,13 @@
         <v>28.32</v>
       </c>
       <c r="O282" s="1" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="P282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="P282" s="1" t="n">
-        <v>28.32</v>
+      <c r="Q282" s="1" t="n">
+        <v>28.26</v>
       </c>
     </row>
     <row r="283">
@@ -15177,10 +16026,13 @@
         <v>0.12849</v>
       </c>
       <c r="O283" s="1" t="n">
+        <v>0.12839</v>
+      </c>
+      <c r="P283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="P283" s="1" t="n">
-        <v>0.12849</v>
+      <c r="Q283" s="1" t="n">
+        <v>0.12839</v>
       </c>
     </row>
     <row r="284">
@@ -15229,10 +16081,13 @@
         <v>0.0111</v>
       </c>
       <c r="O284" s="1" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="P284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="P284" s="1" t="n">
-        <v>0.0111</v>
+      <c r="Q284" s="1" t="n">
+        <v>0.01108</v>
       </c>
     </row>
     <row r="285">
@@ -15281,9 +16136,12 @@
         <v>6.553</v>
       </c>
       <c r="O285" s="1" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="P285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="P285" s="1" t="n">
+      <c r="Q285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -15333,10 +16191,13 @@
         <v>0.01839</v>
       </c>
       <c r="O286" s="1" t="n">
+        <v>0.01838</v>
+      </c>
+      <c r="P286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="P286" s="1" t="n">
-        <v>0.01839</v>
+      <c r="Q286" s="1" t="n">
+        <v>0.01838</v>
       </c>
     </row>
     <row r="287">
@@ -15385,10 +16246,13 @@
         <v>0.008361</v>
       </c>
       <c r="O287" s="1" t="n">
+        <v>0.008356000000000001</v>
+      </c>
+      <c r="P287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="P287" s="1" t="n">
-        <v>0.008361</v>
+      <c r="Q287" s="1" t="n">
+        <v>0.008356000000000001</v>
       </c>
     </row>
     <row r="288">
@@ -15437,10 +16301,13 @@
         <v>0.3823</v>
       </c>
       <c r="O288" s="1" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="P288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="P288" s="1" t="n">
-        <v>0.3823</v>
+      <c r="Q288" s="1" t="n">
+        <v>0.3812</v>
       </c>
     </row>
     <row r="289">
@@ -15489,10 +16356,13 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="O289" s="1" t="n">
+        <v>0.009905000000000001</v>
+      </c>
+      <c r="P289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="P289" s="1" t="n">
-        <v>0.009939999999999999</v>
+      <c r="Q289" s="1" t="n">
+        <v>0.009905000000000001</v>
       </c>
     </row>
     <row r="290">
@@ -15541,10 +16411,13 @@
         <v>0.02587</v>
       </c>
       <c r="O290" s="1" t="n">
+        <v>0.02585</v>
+      </c>
+      <c r="P290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="P290" s="1" t="n">
-        <v>0.02587</v>
+      <c r="Q290" s="1" t="n">
+        <v>0.02585</v>
       </c>
     </row>
     <row r="291">
@@ -15593,9 +16466,12 @@
         <v>0.096</v>
       </c>
       <c r="O291" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="P291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="P291" s="1" t="n">
+      <c r="Q291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -15645,9 +16521,12 @@
         <v>0.28708</v>
       </c>
       <c r="O292" s="1" t="n">
-        <v>0.28708</v>
+        <v>0.28734</v>
       </c>
       <c r="P292" s="1" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="Q292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -15697,9 +16576,12 @@
         <v>0.01556</v>
       </c>
       <c r="O293" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="P293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="P293" s="1" t="n">
+      <c r="Q293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -15749,9 +16631,12 @@
         <v>0.003422</v>
       </c>
       <c r="O294" s="1" t="n">
+        <v>0.003417</v>
+      </c>
+      <c r="P294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="P294" s="1" t="n">
+      <c r="Q294" s="1" t="n">
         <v>0.003412</v>
       </c>
     </row>
@@ -15801,10 +16686,13 @@
         <v>0.042677</v>
       </c>
       <c r="O295" s="1" t="n">
+        <v>0.042629</v>
+      </c>
+      <c r="P295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="P295" s="1" t="n">
-        <v>0.042677</v>
+      <c r="Q295" s="1" t="n">
+        <v>0.042629</v>
       </c>
     </row>
     <row r="296">
@@ -15853,10 +16741,13 @@
         <v>0.02963</v>
       </c>
       <c r="O296" s="1" t="n">
+        <v>0.02902</v>
+      </c>
+      <c r="P296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="P296" s="1" t="n">
-        <v>0.02929</v>
+      <c r="Q296" s="1" t="n">
+        <v>0.02902</v>
       </c>
     </row>
     <row r="297">
@@ -15905,9 +16796,12 @@
         <v>0.03788</v>
       </c>
       <c r="O297" s="1" t="n">
+        <v>0.03797</v>
+      </c>
+      <c r="P297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="P297" s="1" t="n">
+      <c r="Q297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -15957,9 +16851,12 @@
         <v>0.08286</v>
       </c>
       <c r="O298" s="1" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="P298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="P298" s="1" t="n">
+      <c r="Q298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -16009,9 +16906,12 @@
         <v>0.0077</v>
       </c>
       <c r="O299" s="1" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="P299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="P299" s="1" t="n">
+      <c r="Q299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -16061,10 +16961,13 @@
         <v>0.01508</v>
       </c>
       <c r="O300" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="P300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="P300" s="1" t="n">
-        <v>0.01508</v>
+      <c r="Q300" s="1" t="n">
+        <v>0.01505</v>
       </c>
     </row>
     <row r="301">
@@ -16113,10 +17016,13 @@
         <v>0.1402</v>
       </c>
       <c r="O301" s="1" t="n">
+        <v>0.1399</v>
+      </c>
+      <c r="P301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="P301" s="1" t="n">
-        <v>0.1402</v>
+      <c r="Q301" s="1" t="n">
+        <v>0.1399</v>
       </c>
     </row>
     <row r="302">
@@ -16165,10 +17071,13 @@
         <v>0.0006306</v>
       </c>
       <c r="O302" s="1" t="n">
+        <v>0.0006229</v>
+      </c>
+      <c r="P302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="P302" s="1" t="n">
-        <v>0.0006284</v>
+      <c r="Q302" s="1" t="n">
+        <v>0.0006229</v>
       </c>
     </row>
     <row r="303">
@@ -16217,9 +17126,12 @@
         <v>0.06261</v>
       </c>
       <c r="O303" s="1" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="P303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="P303" s="1" t="n">
+      <c r="Q303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -16269,9 +17181,12 @@
         <v>0.000163</v>
       </c>
       <c r="O304" s="1" t="n">
+        <v>0.0001626</v>
+      </c>
+      <c r="P304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="P304" s="1" t="n">
+      <c r="Q304" s="1" t="n">
         <v>0.0001626</v>
       </c>
     </row>
@@ -16321,10 +17236,13 @@
         <v>0.06096</v>
       </c>
       <c r="O305" s="1" t="n">
+        <v>0.06076</v>
+      </c>
+      <c r="P305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="P305" s="1" t="n">
-        <v>0.06078</v>
+      <c r="Q305" s="1" t="n">
+        <v>0.06076</v>
       </c>
     </row>
     <row r="306">
@@ -16373,9 +17291,12 @@
         <v>0.022493</v>
       </c>
       <c r="O306" s="1" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="P306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="P306" s="1" t="n">
+      <c r="Q306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -16425,9 +17346,12 @@
         <v>0.02388</v>
       </c>
       <c r="O307" s="1" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="P307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="P307" s="1" t="n">
+      <c r="Q307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -16477,9 +17401,12 @@
         <v>0.000411</v>
       </c>
       <c r="O308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="P308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="P308" s="1" t="n">
+      <c r="Q308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -16529,9 +17456,12 @@
         <v>0.0897</v>
       </c>
       <c r="O309" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="P309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="P309" s="1" t="n">
+      <c r="Q309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -16581,10 +17511,13 @@
         <v>0.379</v>
       </c>
       <c r="O310" s="1" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="P310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="P310" s="1" t="n">
-        <v>0.379</v>
+      <c r="Q310" s="1" t="n">
+        <v>0.3681</v>
       </c>
     </row>
     <row r="311">
@@ -16633,10 +17566,13 @@
         <v>0.0356</v>
       </c>
       <c r="O311" s="1" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="P311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="P311" s="1" t="n">
-        <v>0.0355</v>
+      <c r="Q311" s="1" t="n">
+        <v>0.0353</v>
       </c>
     </row>
     <row r="312">
@@ -16685,9 +17621,12 @@
         <v>0.02459</v>
       </c>
       <c r="O312" s="1" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="P312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="P312" s="1" t="n">
+      <c r="Q312" s="1" t="n">
         <v>0.02445</v>
       </c>
     </row>
@@ -16737,10 +17676,13 @@
         <v>0.0412</v>
       </c>
       <c r="O313" s="1" t="n">
+        <v>0.04115</v>
+      </c>
+      <c r="P313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="P313" s="1" t="n">
-        <v>0.0412</v>
+      <c r="Q313" s="1" t="n">
+        <v>0.04115</v>
       </c>
     </row>
     <row r="314">
@@ -16789,10 +17731,13 @@
         <v>3.977</v>
       </c>
       <c r="O314" s="1" t="n">
+        <v>3.966</v>
+      </c>
+      <c r="P314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="P314" s="1" t="n">
-        <v>3.977</v>
+      <c r="Q314" s="1" t="n">
+        <v>3.966</v>
       </c>
     </row>
     <row r="315">
@@ -16841,10 +17786,13 @@
         <v>0.16</v>
       </c>
       <c r="O315" s="1" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="P315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="P315" s="1" t="n">
-        <v>0.1595</v>
+      <c r="Q315" s="1" t="n">
+        <v>0.1594</v>
       </c>
     </row>
     <row r="316">
@@ -16893,9 +17841,12 @@
         <v>0.09374</v>
       </c>
       <c r="O316" s="1" t="n">
+        <v>0.09142</v>
+      </c>
+      <c r="P316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="P316" s="1" t="n">
+      <c r="Q316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -16945,10 +17896,13 @@
         <v>0.06826</v>
       </c>
       <c r="O317" s="1" t="n">
+        <v>0.06791999999999999</v>
+      </c>
+      <c r="P317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="P317" s="1" t="n">
-        <v>0.06814000000000001</v>
+      <c r="Q317" s="1" t="n">
+        <v>0.06791999999999999</v>
       </c>
     </row>
     <row r="318">
@@ -16997,9 +17951,12 @@
         <v>0.012495</v>
       </c>
       <c r="O318" s="1" t="n">
+        <v>0.012459</v>
+      </c>
+      <c r="P318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="P318" s="1" t="n">
+      <c r="Q318" s="1" t="n">
         <v>0.012414</v>
       </c>
     </row>
@@ -17049,10 +18006,13 @@
         <v>0.001136</v>
       </c>
       <c r="O319" s="1" t="n">
+        <v>0.001134</v>
+      </c>
+      <c r="P319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="P319" s="1" t="n">
-        <v>0.001135</v>
+      <c r="Q319" s="1" t="n">
+        <v>0.001134</v>
       </c>
     </row>
     <row r="320">
@@ -17101,9 +18061,12 @@
         <v>0.0629</v>
       </c>
       <c r="O320" s="1" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="P320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="P320" s="1" t="n">
+      <c r="Q320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -17153,9 +18116,12 @@
         <v>0.00527</v>
       </c>
       <c r="O321" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="P321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="P321" s="1" t="n">
+      <c r="Q321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -17205,9 +18171,12 @@
         <v>0.1123</v>
       </c>
       <c r="O322" s="1" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="P322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="P322" s="1" t="n">
+      <c r="Q322" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
@@ -17257,9 +18226,12 @@
         <v>0.04343</v>
       </c>
       <c r="O323" s="1" t="n">
+        <v>0.04346</v>
+      </c>
+      <c r="P323" s="1" t="n">
         <v>0.0437</v>
       </c>
-      <c r="P323" s="1" t="n">
+      <c r="Q323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -17309,9 +18281,12 @@
         <v>0.01794</v>
       </c>
       <c r="O324" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="P324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="P324" s="1" t="n">
+      <c r="Q324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -17361,10 +18336,13 @@
         <v>0.005658</v>
       </c>
       <c r="O325" s="1" t="n">
+        <v>0.005652</v>
+      </c>
+      <c r="P325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="P325" s="1" t="n">
-        <v>0.005658</v>
+      <c r="Q325" s="1" t="n">
+        <v>0.005652</v>
       </c>
     </row>
     <row r="326">
@@ -17413,10 +18391,13 @@
         <v>0.001764</v>
       </c>
       <c r="O326" s="1" t="n">
+        <v>0.001757</v>
+      </c>
+      <c r="P326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="P326" s="1" t="n">
-        <v>0.001764</v>
+      <c r="Q326" s="1" t="n">
+        <v>0.001757</v>
       </c>
     </row>
     <row r="327">
@@ -17465,10 +18446,13 @@
         <v>0.04035</v>
       </c>
       <c r="O327" s="1" t="n">
+        <v>0.04029</v>
+      </c>
+      <c r="P327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="P327" s="1" t="n">
-        <v>0.04035</v>
+      <c r="Q327" s="1" t="n">
+        <v>0.04029</v>
       </c>
     </row>
     <row r="328">
@@ -17517,9 +18501,12 @@
         <v>0.053711</v>
       </c>
       <c r="O328" s="1" t="n">
+        <v>0.053569</v>
+      </c>
+      <c r="P328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="P328" s="1" t="n">
+      <c r="Q328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -17569,9 +18556,12 @@
         <v>0.2785</v>
       </c>
       <c r="O329" s="1" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="P329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="P329" s="1" t="n">
+      <c r="Q329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -17621,9 +18611,12 @@
         <v>0.1591</v>
       </c>
       <c r="O330" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="P330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="P330" s="1" t="n">
+      <c r="Q330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -17673,9 +18666,12 @@
         <v>0.05374</v>
       </c>
       <c r="O331" s="1" t="n">
+        <v>0.05366</v>
+      </c>
+      <c r="P331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="P331" s="1" t="n">
+      <c r="Q331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -17725,9 +18721,12 @@
         <v>0.3604</v>
       </c>
       <c r="O332" s="1" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="P332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="P332" s="1" t="n">
+      <c r="Q332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -17777,9 +18776,12 @@
         <v>0.03047</v>
       </c>
       <c r="O333" s="1" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="P333" s="1" t="n">
         <v>0.03051</v>
       </c>
-      <c r="P333" s="1" t="n">
+      <c r="Q333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -17829,9 +18831,12 @@
         <v>0.01751</v>
       </c>
       <c r="O334" s="1" t="n">
+        <v>0.01767</v>
+      </c>
+      <c r="P334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="P334" s="1" t="n">
+      <c r="Q334" s="1" t="n">
         <v>0.01751</v>
       </c>
     </row>
@@ -17881,9 +18886,12 @@
         <v>0.0579</v>
       </c>
       <c r="O335" s="1" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="P335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="P335" s="1" t="n">
+      <c r="Q335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -17933,10 +18941,13 @@
         <v>0.09102</v>
       </c>
       <c r="O336" s="1" t="n">
+        <v>0.09054</v>
+      </c>
+      <c r="P336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="P336" s="1" t="n">
-        <v>0.09082</v>
+      <c r="Q336" s="1" t="n">
+        <v>0.09054</v>
       </c>
     </row>
     <row r="337">
@@ -17985,9 +18996,12 @@
         <v>0.17991</v>
       </c>
       <c r="O337" s="1" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="P337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="P337" s="1" t="n">
+      <c r="Q337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -18037,10 +19051,13 @@
         <v>0.02093</v>
       </c>
       <c r="O338" s="1" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="P338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="P338" s="1" t="n">
-        <v>0.02092</v>
+      <c r="Q338" s="1" t="n">
+        <v>0.0209</v>
       </c>
     </row>
     <row r="339">
@@ -18092,6 +19109,9 @@
         <v>0.1318</v>
       </c>
       <c r="P339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="Q339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -18141,9 +19161,12 @@
         <v>0.007901999999999999</v>
       </c>
       <c r="O340" s="1" t="n">
+        <v>0.007915999999999999</v>
+      </c>
+      <c r="P340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="P340" s="1" t="n">
+      <c r="Q340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -18193,9 +19216,12 @@
         <v>4.415</v>
       </c>
       <c r="O341" s="1" t="n">
+        <v>4.414</v>
+      </c>
+      <c r="P341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="P341" s="1" t="n">
+      <c r="Q341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -18245,9 +19271,12 @@
         <v>0.1885</v>
       </c>
       <c r="O342" s="1" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="P342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="P342" s="1" t="n">
+      <c r="Q342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -18297,9 +19326,12 @@
         <v>0.08336</v>
       </c>
       <c r="O343" s="1" t="n">
+        <v>0.08326</v>
+      </c>
+      <c r="P343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="P343" s="1" t="n">
+      <c r="Q343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -18349,10 +19381,13 @@
         <v>0.1821</v>
       </c>
       <c r="O344" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="P344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="P344" s="1" t="n">
-        <v>0.1819</v>
+      <c r="Q344" s="1" t="n">
+        <v>0.1817</v>
       </c>
     </row>
     <row r="345">
@@ -18401,9 +19436,12 @@
         <v>0.003241</v>
       </c>
       <c r="O345" s="1" t="n">
+        <v>0.003241</v>
+      </c>
+      <c r="P345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="P345" s="1" t="n">
+      <c r="Q345" s="1" t="n">
         <v>0.00324</v>
       </c>
     </row>
@@ -18453,10 +19491,13 @@
         <v>0.09125999999999999</v>
       </c>
       <c r="O346" s="1" t="n">
+        <v>0.09075</v>
+      </c>
+      <c r="P346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="P346" s="1" t="n">
-        <v>0.09080000000000001</v>
+      <c r="Q346" s="1" t="n">
+        <v>0.09075</v>
       </c>
     </row>
     <row r="347">
@@ -18505,9 +19546,12 @@
         <v>2.253</v>
       </c>
       <c r="O347" s="1" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="P347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="P347" s="1" t="n">
+      <c r="Q347" s="1" t="n">
         <v>2.243</v>
       </c>
     </row>
@@ -18557,10 +19601,13 @@
         <v>0.303</v>
       </c>
       <c r="O348" s="1" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="P348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="P348" s="1" t="n">
-        <v>0.303</v>
+      <c r="Q348" s="1" t="n">
+        <v>0.3027</v>
       </c>
     </row>
     <row r="349">
@@ -18609,10 +19656,13 @@
         <v>0.02967</v>
       </c>
       <c r="O349" s="1" t="n">
+        <v>0.02953</v>
+      </c>
+      <c r="P349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="P349" s="1" t="n">
-        <v>0.02967</v>
+      <c r="Q349" s="1" t="n">
+        <v>0.02953</v>
       </c>
     </row>
     <row r="350">
@@ -18661,9 +19711,12 @@
         <v>0.1277</v>
       </c>
       <c r="O350" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="P350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="P350" s="1" t="n">
+      <c r="Q350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -18713,10 +19766,13 @@
         <v>0.06655</v>
       </c>
       <c r="O351" s="1" t="n">
+        <v>0.06651</v>
+      </c>
+      <c r="P351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="P351" s="1" t="n">
-        <v>0.06655</v>
+      <c r="Q351" s="1" t="n">
+        <v>0.06651</v>
       </c>
     </row>
     <row r="352">
@@ -18765,9 +19821,12 @@
         <v>0.06254</v>
       </c>
       <c r="O352" s="1" t="n">
+        <v>0.06241</v>
+      </c>
+      <c r="P352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="P352" s="1" t="n">
+      <c r="Q352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -18817,10 +19876,13 @@
         <v>0.06346</v>
       </c>
       <c r="O353" s="1" t="n">
+        <v>0.06329</v>
+      </c>
+      <c r="P353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="P353" s="1" t="n">
-        <v>0.06346</v>
+      <c r="Q353" s="1" t="n">
+        <v>0.06329</v>
       </c>
     </row>
     <row r="354">
@@ -18869,9 +19931,12 @@
         <v>0.10844</v>
       </c>
       <c r="O354" s="1" t="n">
+        <v>0.10602</v>
+      </c>
+      <c r="P354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="P354" s="1" t="n">
+      <c r="Q354" s="1" t="n">
         <v>0.10405</v>
       </c>
     </row>
@@ -18921,9 +19986,12 @@
         <v>0.09</v>
       </c>
       <c r="O355" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="P355" s="1" t="n">
+      <c r="Q355" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -18973,10 +20041,13 @@
         <v>0.07001</v>
       </c>
       <c r="O356" s="1" t="n">
+        <v>0.06976</v>
+      </c>
+      <c r="P356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="P356" s="1" t="n">
-        <v>0.06985</v>
+      <c r="Q356" s="1" t="n">
+        <v>0.06976</v>
       </c>
     </row>
     <row r="357">
@@ -19025,10 +20096,13 @@
         <v>0.4522</v>
       </c>
       <c r="O357" s="1" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="P357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="P357" s="1" t="n">
-        <v>0.4521</v>
+      <c r="Q357" s="1" t="n">
+        <v>0.4518</v>
       </c>
     </row>
     <row r="358">
@@ -19077,9 +20151,12 @@
         <v>0.03491</v>
       </c>
       <c r="O358" s="1" t="n">
+        <v>0.03484</v>
+      </c>
+      <c r="P358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="P358" s="1" t="n">
+      <c r="Q358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -19129,10 +20206,13 @@
         <v>0.01474</v>
       </c>
       <c r="O359" s="1" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="P359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="P359" s="1" t="n">
-        <v>0.01474</v>
+      <c r="Q359" s="1" t="n">
+        <v>0.01466</v>
       </c>
     </row>
     <row r="360">
@@ -19181,9 +20261,12 @@
         <v>0.13359</v>
       </c>
       <c r="O360" s="1" t="n">
+        <v>0.13297</v>
+      </c>
+      <c r="P360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="P360" s="1" t="n">
+      <c r="Q360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -19233,9 +20316,12 @@
         <v>0.0005861</v>
       </c>
       <c r="O361" s="1" t="n">
+        <v>0.0005865999999999999</v>
+      </c>
+      <c r="P361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="P361" s="1" t="n">
+      <c r="Q361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -19285,10 +20371,13 @@
         <v>0.0387</v>
       </c>
       <c r="O362" s="1" t="n">
+        <v>0.03855</v>
+      </c>
+      <c r="P362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="P362" s="1" t="n">
-        <v>0.0386</v>
+      <c r="Q362" s="1" t="n">
+        <v>0.03855</v>
       </c>
     </row>
     <row r="363">
@@ -19337,9 +20426,12 @@
         <v>3.22</v>
       </c>
       <c r="O363" s="1" t="n">
+        <v>3.208</v>
+      </c>
+      <c r="P363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="P363" s="1" t="n">
+      <c r="Q363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -19389,10 +20481,13 @@
         <v>0.1642</v>
       </c>
       <c r="O364" s="1" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="P364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="P364" s="1" t="n">
-        <v>0.1642</v>
+      <c r="Q364" s="1" t="n">
+        <v>0.1635</v>
       </c>
     </row>
     <row r="365">
@@ -19441,9 +20536,12 @@
         <v>0.1138</v>
       </c>
       <c r="O365" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="P365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="P365" s="1" t="n">
+      <c r="Q365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -19493,10 +20591,13 @@
         <v>0.0006389</v>
       </c>
       <c r="O366" s="1" t="n">
+        <v>0.0006386</v>
+      </c>
+      <c r="P366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="P366" s="1" t="n">
-        <v>0.0006389</v>
+      <c r="Q366" s="1" t="n">
+        <v>0.0006386</v>
       </c>
     </row>
     <row r="367">
@@ -19545,10 +20646,13 @@
         <v>0.05923</v>
       </c>
       <c r="O367" s="1" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="P367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="P367" s="1" t="n">
-        <v>0.05923</v>
+      <c r="Q367" s="1" t="n">
+        <v>0.05903</v>
       </c>
     </row>
     <row r="368">
@@ -19597,10 +20701,13 @@
         <v>0.08198999999999999</v>
       </c>
       <c r="O368" s="1" t="n">
+        <v>0.08175</v>
+      </c>
+      <c r="P368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="P368" s="1" t="n">
-        <v>0.08198999999999999</v>
+      <c r="Q368" s="1" t="n">
+        <v>0.08175</v>
       </c>
     </row>
     <row r="369">
@@ -19649,10 +20756,13 @@
         <v>0.03957</v>
       </c>
       <c r="O369" s="1" t="n">
+        <v>0.03931</v>
+      </c>
+      <c r="P369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="P369" s="1" t="n">
-        <v>0.03957</v>
+      <c r="Q369" s="1" t="n">
+        <v>0.03931</v>
       </c>
     </row>
     <row r="370">
@@ -19701,10 +20811,13 @@
         <v>3.689</v>
       </c>
       <c r="O370" s="1" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="P370" s="1" t="n">
-        <v>3.689</v>
+      <c r="Q370" s="1" t="n">
+        <v>3.68</v>
       </c>
     </row>
     <row r="371">
@@ -19753,10 +20866,13 @@
         <v>0.121</v>
       </c>
       <c r="O371" s="1" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="P371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="P371" s="1" t="n">
-        <v>0.121</v>
+      <c r="Q371" s="1" t="n">
+        <v>0.1208</v>
       </c>
     </row>
     <row r="372">
@@ -19805,9 +20921,12 @@
         <v>0.0148</v>
       </c>
       <c r="O372" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="P372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="P372" s="1" t="n">
+      <c r="Q372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -19857,9 +20976,12 @@
         <v>0.02205</v>
       </c>
       <c r="O373" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="P373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="P373" s="1" t="n">
+      <c r="Q373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -19909,9 +21031,12 @@
         <v>1.856</v>
       </c>
       <c r="O374" s="1" t="n">
+        <v>1.8579</v>
+      </c>
+      <c r="P374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="P374" s="1" t="n">
+      <c r="Q374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -19961,10 +21086,13 @@
         <v>0.02094</v>
       </c>
       <c r="O375" s="1" t="n">
+        <v>0.02092</v>
+      </c>
+      <c r="P375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="P375" s="1" t="n">
-        <v>0.02094</v>
+      <c r="Q375" s="1" t="n">
+        <v>0.02092</v>
       </c>
     </row>
     <row r="376">
@@ -20013,9 +21141,12 @@
         <v>1.308</v>
       </c>
       <c r="O376" s="1" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="P376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="P376" s="1" t="n">
+      <c r="Q376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -20065,9 +21196,12 @@
         <v>0.2832</v>
       </c>
       <c r="O377" s="1" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="P377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="P377" s="1" t="n">
+      <c r="Q377" s="1" t="n">
         <v>0.2826</v>
       </c>
     </row>
@@ -20117,9 +21251,12 @@
         <v>0.01557</v>
       </c>
       <c r="O378" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="P378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="P378" s="1" t="n">
+      <c r="Q378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -20169,9 +21306,12 @@
         <v>1.5383</v>
       </c>
       <c r="O379" s="1" t="n">
+        <v>1.5325</v>
+      </c>
+      <c r="P379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="P379" s="1" t="n">
+      <c r="Q379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -20221,10 +21361,13 @@
         <v>6.913e-05</v>
       </c>
       <c r="O380" s="1" t="n">
+        <v>6.896e-05</v>
+      </c>
+      <c r="P380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="P380" s="1" t="n">
-        <v>6.913e-05</v>
+      <c r="Q380" s="1" t="n">
+        <v>6.896e-05</v>
       </c>
     </row>
     <row r="381">
@@ -20273,9 +21416,12 @@
         <v>2.551</v>
       </c>
       <c r="O381" s="1" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="P381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="P381" s="1" t="n">
+      <c r="Q381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -20325,10 +21471,13 @@
         <v>0.06697</v>
       </c>
       <c r="O382" s="1" t="n">
+        <v>0.06683</v>
+      </c>
+      <c r="P382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="P382" s="1" t="n">
-        <v>0.06697</v>
+      <c r="Q382" s="1" t="n">
+        <v>0.06683</v>
       </c>
     </row>
     <row r="383">
@@ -20377,9 +21526,12 @@
         <v>0.01752</v>
       </c>
       <c r="O383" s="1" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="P383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="P383" s="1" t="n">
+      <c r="Q383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -20429,9 +21581,12 @@
         <v>0.05188</v>
       </c>
       <c r="O384" s="1" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="P384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="P384" s="1" t="n">
+      <c r="Q384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -20481,9 +21636,12 @@
         <v>7.577</v>
       </c>
       <c r="O385" s="1" t="n">
+        <v>7.564</v>
+      </c>
+      <c r="P385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="P385" s="1" t="n">
+      <c r="Q385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -20533,9 +21691,12 @@
         <v>0.00329</v>
       </c>
       <c r="O386" s="1" t="n">
+        <v>0.00328</v>
+      </c>
+      <c r="P386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="P386" s="1" t="n">
+      <c r="Q386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -20585,10 +21746,13 @@
         <v>0.0003814</v>
       </c>
       <c r="O387" s="1" t="n">
+        <v>0.0003801</v>
+      </c>
+      <c r="P387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="P387" s="1" t="n">
-        <v>0.0003814</v>
+      <c r="Q387" s="1" t="n">
+        <v>0.0003801</v>
       </c>
     </row>
     <row r="388">
@@ -20637,10 +21801,13 @@
         <v>0.009520000000000001</v>
       </c>
       <c r="O388" s="1" t="n">
+        <v>0.00946</v>
+      </c>
+      <c r="P388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="P388" s="1" t="n">
-        <v>0.009520000000000001</v>
+      <c r="Q388" s="1" t="n">
+        <v>0.00946</v>
       </c>
     </row>
     <row r="389">
@@ -20689,9 +21856,12 @@
         <v>0.2886</v>
       </c>
       <c r="O389" s="1" t="n">
-        <v>0.2902</v>
+        <v>0.2904</v>
       </c>
       <c r="P389" s="1" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="Q389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -20741,9 +21911,12 @@
         <v>0.0252</v>
       </c>
       <c r="O390" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="P390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="P390" s="1" t="n">
+      <c r="Q390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -20793,9 +21966,12 @@
         <v>2.819</v>
       </c>
       <c r="O391" s="1" t="n">
-        <v>2.833</v>
+        <v>2.834</v>
       </c>
       <c r="P391" s="1" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Q391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -20845,9 +22021,12 @@
         <v>0.0135</v>
       </c>
       <c r="O392" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="P392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="P392" s="1" t="n">
+      <c r="Q392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -20897,9 +22076,12 @@
         <v>0.00237</v>
       </c>
       <c r="O393" s="1" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="P393" s="1" t="n">
         <v>0.00237</v>
       </c>
-      <c r="P393" s="1" t="n">
+      <c r="Q393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -20949,9 +22131,12 @@
         <v>0.05935</v>
       </c>
       <c r="O394" s="1" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="P394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="P394" s="1" t="n">
+      <c r="Q394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -21001,9 +22186,12 @@
         <v>0.0403</v>
       </c>
       <c r="O395" s="1" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="P395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="P395" s="1" t="n">
+      <c r="Q395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -21053,9 +22241,12 @@
         <v>0.09229</v>
       </c>
       <c r="O396" s="1" t="n">
+        <v>0.09246</v>
+      </c>
+      <c r="P396" s="1" t="n">
         <v>0.09272</v>
       </c>
-      <c r="P396" s="1" t="n">
+      <c r="Q396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -21105,10 +22296,13 @@
         <v>0.1518</v>
       </c>
       <c r="O397" s="1" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="P397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="P397" s="1" t="n">
-        <v>0.1517</v>
+      <c r="Q397" s="1" t="n">
+        <v>0.1515</v>
       </c>
     </row>
     <row r="398">
@@ -21157,9 +22351,12 @@
         <v>0.93</v>
       </c>
       <c r="O398" s="1" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="P398" s="1" t="n">
         <v>0.93</v>
       </c>
-      <c r="P398" s="1" t="n">
+      <c r="Q398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -21209,9 +22406,12 @@
         <v>0.05246</v>
       </c>
       <c r="O399" s="1" t="n">
+        <v>0.05237</v>
+      </c>
+      <c r="P399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="P399" s="1" t="n">
+      <c r="Q399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -21261,10 +22461,13 @@
         <v>2.516</v>
       </c>
       <c r="O400" s="1" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="P400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="P400" s="1" t="n">
-        <v>2.516</v>
+      <c r="Q400" s="1" t="n">
+        <v>2.512</v>
       </c>
     </row>
     <row r="401">
@@ -21313,9 +22516,12 @@
         <v>0.0179</v>
       </c>
       <c r="O401" s="1" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="P401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="P401" s="1" t="n">
+      <c r="Q401" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -21365,9 +22571,12 @@
         <v>0.08003</v>
       </c>
       <c r="O402" s="1" t="n">
+        <v>0.07985</v>
+      </c>
+      <c r="P402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="P402" s="1" t="n">
+      <c r="Q402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -21417,9 +22626,12 @@
         <v>1.2484</v>
       </c>
       <c r="O403" s="1" t="n">
+        <v>1.2485</v>
+      </c>
+      <c r="P403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="P403" s="1" t="n">
+      <c r="Q403" s="1" t="n">
         <v>1.2455</v>
       </c>
     </row>
@@ -21469,10 +22681,13 @@
         <v>0.00714</v>
       </c>
       <c r="O404" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="P404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="P404" s="1" t="n">
-        <v>0.00714</v>
+      <c r="Q404" s="1" t="n">
+        <v>0.00711</v>
       </c>
     </row>
     <row r="405">
@@ -21521,9 +22736,12 @@
         <v>0.5017</v>
       </c>
       <c r="O405" s="1" t="n">
-        <v>0.5017</v>
+        <v>0.5041</v>
       </c>
       <c r="P405" s="1" t="n">
+        <v>0.5041</v>
+      </c>
+      <c r="Q405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -21573,10 +22791,13 @@
         <v>0.01149</v>
       </c>
       <c r="O406" s="1" t="n">
+        <v>0.01145</v>
+      </c>
+      <c r="P406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="P406" s="1" t="n">
-        <v>0.01146</v>
+      <c r="Q406" s="1" t="n">
+        <v>0.01145</v>
       </c>
     </row>
     <row r="407">
@@ -21625,10 +22846,13 @@
         <v>0.04603</v>
       </c>
       <c r="O407" s="1" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="P407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="P407" s="1" t="n">
-        <v>0.04603</v>
+      <c r="Q407" s="1" t="n">
+        <v>0.04596</v>
       </c>
     </row>
     <row r="408">
@@ -21677,10 +22901,13 @@
         <v>0.03939</v>
       </c>
       <c r="O408" s="1" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="P408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="P408" s="1" t="n">
-        <v>0.03939</v>
+      <c r="Q408" s="1" t="n">
+        <v>0.03927</v>
       </c>
     </row>
     <row r="409">
@@ -21729,10 +22956,13 @@
         <v>0.05227</v>
       </c>
       <c r="O409" s="1" t="n">
+        <v>0.05226</v>
+      </c>
+      <c r="P409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="P409" s="1" t="n">
-        <v>0.05227</v>
+      <c r="Q409" s="1" t="n">
+        <v>0.05226</v>
       </c>
     </row>
     <row r="410">
@@ -21781,10 +23011,13 @@
         <v>0.01232</v>
       </c>
       <c r="O410" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="P410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="P410" s="1" t="n">
-        <v>0.01232</v>
+      <c r="Q410" s="1" t="n">
+        <v>0.01229</v>
       </c>
     </row>
     <row r="411">
@@ -21833,9 +23066,12 @@
         <v>0.06362</v>
       </c>
       <c r="O411" s="1" t="n">
+        <v>0.06349</v>
+      </c>
+      <c r="P411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="P411" s="1" t="n">
+      <c r="Q411" s="1" t="n">
         <v>0.06347</v>
       </c>
     </row>
@@ -21885,9 +23121,12 @@
         <v>0.04139</v>
       </c>
       <c r="O412" s="1" t="n">
+        <v>0.04131</v>
+      </c>
+      <c r="P412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="P412" s="1" t="n">
+      <c r="Q412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -21937,10 +23176,13 @@
         <v>1.123</v>
       </c>
       <c r="O413" s="1" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="P413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="P413" s="1" t="n">
-        <v>1.117</v>
+      <c r="Q413" s="1" t="n">
+        <v>1.114</v>
       </c>
     </row>
     <row r="414">
@@ -21989,10 +23231,13 @@
         <v>0.2627</v>
       </c>
       <c r="O414" s="1" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="P414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="P414" s="1" t="n">
-        <v>0.2625</v>
+      <c r="Q414" s="1" t="n">
+        <v>0.2624</v>
       </c>
     </row>
     <row r="415">
@@ -22041,9 +23286,12 @@
         <v>0.001214</v>
       </c>
       <c r="O415" s="1" t="n">
+        <v>0.001214</v>
+      </c>
+      <c r="P415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="P415" s="1" t="n">
+      <c r="Q415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -22093,9 +23341,12 @@
         <v>0.032</v>
       </c>
       <c r="O416" s="1" t="n">
+        <v>0.03193</v>
+      </c>
+      <c r="P416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="P416" s="1" t="n">
+      <c r="Q416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -22145,9 +23396,12 @@
         <v>0.01469</v>
       </c>
       <c r="O417" s="1" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="P417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="P417" s="1" t="n">
+      <c r="Q417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -22197,9 +23451,12 @@
         <v>0.1483</v>
       </c>
       <c r="O418" s="1" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="P418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="P418" s="1" t="n">
+      <c r="Q418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -22249,9 +23506,12 @@
         <v>0.04952</v>
       </c>
       <c r="O419" s="1" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="P419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="P419" s="1" t="n">
+      <c r="Q419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -22301,9 +23561,12 @@
         <v>66.87</v>
       </c>
       <c r="O420" s="1" t="n">
-        <v>66.90000000000001</v>
+        <v>66.94</v>
       </c>
       <c r="P420" s="1" t="n">
+        <v>66.94</v>
+      </c>
+      <c r="Q420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -22353,9 +23616,12 @@
         <v>0.877</v>
       </c>
       <c r="O421" s="1" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="P421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="P421" s="1" t="n">
+      <c r="Q421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -22405,10 +23671,13 @@
         <v>0.012561</v>
       </c>
       <c r="O422" s="1" t="n">
+        <v>0.012415</v>
+      </c>
+      <c r="P422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="P422" s="1" t="n">
-        <v>0.012549</v>
+      <c r="Q422" s="1" t="n">
+        <v>0.012415</v>
       </c>
     </row>
     <row r="423">
@@ -22457,9 +23726,12 @@
         <v>0.01596</v>
       </c>
       <c r="O423" s="1" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="P423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="P423" s="1" t="n">
+      <c r="Q423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -22509,9 +23781,12 @@
         <v>0.26901</v>
       </c>
       <c r="O424" s="1" t="n">
-        <v>0.27102</v>
+        <v>0.2716</v>
       </c>
       <c r="P424" s="1" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="Q424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -22561,9 +23836,12 @@
         <v>0.6004</v>
       </c>
       <c r="O425" s="1" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="P425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="P425" s="1" t="n">
+      <c r="Q425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -22613,10 +23891,13 @@
         <v>0.005515</v>
       </c>
       <c r="O426" s="1" t="n">
+        <v>0.005512</v>
+      </c>
+      <c r="P426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="P426" s="1" t="n">
-        <v>0.005515</v>
+      <c r="Q426" s="1" t="n">
+        <v>0.005512</v>
       </c>
     </row>
     <row r="427">
@@ -22665,9 +23946,12 @@
         <v>0.04962</v>
       </c>
       <c r="O427" s="1" t="n">
+        <v>0.04955</v>
+      </c>
+      <c r="P427" s="1" t="n">
         <v>0.04962</v>
       </c>
-      <c r="P427" s="1" t="n">
+      <c r="Q427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -22717,9 +24001,12 @@
         <v>0.1263</v>
       </c>
       <c r="O428" s="1" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="P428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="P428" s="1" t="n">
+      <c r="Q428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -22769,9 +24056,12 @@
         <v>0.003196</v>
       </c>
       <c r="O429" s="1" t="n">
-        <v>0.0032</v>
+        <v>0.003205</v>
       </c>
       <c r="P429" s="1" t="n">
+        <v>0.003205</v>
+      </c>
+      <c r="Q429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -22821,9 +24111,12 @@
         <v>0.03644</v>
       </c>
       <c r="O430" s="1" t="n">
+        <v>0.03644</v>
+      </c>
+      <c r="P430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="P430" s="1" t="n">
+      <c r="Q430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -22873,10 +24166,13 @@
         <v>0.3959</v>
       </c>
       <c r="O431" s="1" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="P431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="P431" s="1" t="n">
-        <v>0.3959</v>
+      <c r="Q431" s="1" t="n">
+        <v>0.3952</v>
       </c>
     </row>
     <row r="432">
@@ -22925,10 +24221,13 @@
         <v>0.004486</v>
       </c>
       <c r="O432" s="1" t="n">
+        <v>0.004483</v>
+      </c>
+      <c r="P432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="P432" s="1" t="n">
-        <v>0.004486</v>
+      <c r="Q432" s="1" t="n">
+        <v>0.004483</v>
       </c>
     </row>
     <row r="433">
@@ -22977,9 +24276,12 @@
         <v>0.0982</v>
       </c>
       <c r="O433" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="P433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="P433" s="1" t="n">
+      <c r="Q433" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -23029,10 +24331,13 @@
         <v>0.01241</v>
       </c>
       <c r="O434" s="1" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="P434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="P434" s="1" t="n">
-        <v>0.01238</v>
+      <c r="Q434" s="1" t="n">
+        <v>0.01237</v>
       </c>
     </row>
     <row r="435">
@@ -23081,9 +24386,12 @@
         <v>1.986</v>
       </c>
       <c r="O435" s="1" t="n">
+        <v>1.982</v>
+      </c>
+      <c r="P435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="P435" s="1" t="n">
+      <c r="Q435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -23133,9 +24441,12 @@
         <v>0.001792</v>
       </c>
       <c r="O436" s="1" t="n">
+        <v>0.001792</v>
+      </c>
+      <c r="P436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="P436" s="1" t="n">
+      <c r="Q436" s="1" t="n">
         <v>0.001792</v>
       </c>
     </row>
@@ -23185,9 +24496,12 @@
         <v>0.4422</v>
       </c>
       <c r="O437" s="1" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="P437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="P437" s="1" t="n">
+      <c r="Q437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -23237,9 +24551,12 @@
         <v>0.00534</v>
       </c>
       <c r="O438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="P438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="P438" s="1" t="n">
+      <c r="Q438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -23289,9 +24606,12 @@
         <v>0.1037</v>
       </c>
       <c r="O439" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="P439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="P439" s="1" t="n">
+      <c r="Q439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -23341,10 +24661,13 @@
         <v>0.03422</v>
       </c>
       <c r="O440" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="P440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="P440" s="1" t="n">
-        <v>0.03417</v>
+      <c r="Q440" s="1" t="n">
+        <v>0.034</v>
       </c>
     </row>
     <row r="441">
@@ -23393,9 +24716,12 @@
         <v>0.08205999999999999</v>
       </c>
       <c r="O441" s="1" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="P441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="P441" s="1" t="n">
+      <c r="Q441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -23445,9 +24771,12 @@
         <v>1.31</v>
       </c>
       <c r="O442" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="P442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="P442" s="1" t="n">
+      <c r="Q442" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -23497,9 +24826,12 @@
         <v>0.07585</v>
       </c>
       <c r="O443" s="1" t="n">
+        <v>0.07566000000000001</v>
+      </c>
+      <c r="P443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="P443" s="1" t="n">
+      <c r="Q443" s="1" t="n">
         <v>0.07549</v>
       </c>
     </row>
@@ -23549,9 +24881,12 @@
         <v>0.07650999999999999</v>
       </c>
       <c r="O444" s="1" t="n">
+        <v>0.07652</v>
+      </c>
+      <c r="P444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="P444" s="1" t="n">
+      <c r="Q444" s="1" t="n">
         <v>0.07650999999999999</v>
       </c>
     </row>
@@ -23601,10 +24936,13 @@
         <v>0.04338</v>
       </c>
       <c r="O445" s="1" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="P445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="P445" s="1" t="n">
-        <v>0.04338</v>
+      <c r="Q445" s="1" t="n">
+        <v>0.0433</v>
       </c>
     </row>
     <row r="446">
@@ -23653,10 +24991,13 @@
         <v>0.02133</v>
       </c>
       <c r="O446" s="1" t="n">
+        <v>0.02132</v>
+      </c>
+      <c r="P446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="P446" s="1" t="n">
-        <v>0.02133</v>
+      <c r="Q446" s="1" t="n">
+        <v>0.02132</v>
       </c>
     </row>
     <row r="447">
@@ -23705,9 +25046,12 @@
         <v>0.2802</v>
       </c>
       <c r="O447" s="1" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="P447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="P447" s="1" t="n">
+      <c r="Q447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -23757,9 +25101,12 @@
         <v>0.03113</v>
       </c>
       <c r="O448" s="1" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="P448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="P448" s="1" t="n">
+      <c r="Q448" s="1" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -23809,9 +25156,12 @@
         <v>0.00646</v>
       </c>
       <c r="O449" s="1" t="n">
+        <v>0.00645</v>
+      </c>
+      <c r="P449" s="1" t="n">
         <v>0.00647</v>
       </c>
-      <c r="P449" s="1" t="n">
+      <c r="Q449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -23861,9 +25211,12 @@
         <v>0.023086</v>
       </c>
       <c r="O450" s="1" t="n">
+        <v>0.023072</v>
+      </c>
+      <c r="P450" s="1" t="n">
         <v>0.023086</v>
       </c>
-      <c r="P450" s="1" t="n">
+      <c r="Q450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -23913,9 +25266,12 @@
         <v>0.04228</v>
       </c>
       <c r="O451" s="1" t="n">
+        <v>0.04227</v>
+      </c>
+      <c r="P451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="P451" s="1" t="n">
+      <c r="Q451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -23965,9 +25321,12 @@
         <v>0.07234</v>
       </c>
       <c r="O452" s="1" t="n">
+        <v>0.07223</v>
+      </c>
+      <c r="P452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="P452" s="1" t="n">
+      <c r="Q452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -24017,10 +25376,13 @@
         <v>0.0005913</v>
       </c>
       <c r="O453" s="1" t="n">
+        <v>0.0005904</v>
+      </c>
+      <c r="P453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="P453" s="1" t="n">
-        <v>0.0005908</v>
+      <c r="Q453" s="1" t="n">
+        <v>0.0005904</v>
       </c>
     </row>
     <row r="454">
@@ -24069,10 +25431,13 @@
         <v>0.306</v>
       </c>
       <c r="O454" s="1" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="P454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="P454" s="1" t="n">
-        <v>0.306</v>
+      <c r="Q454" s="1" t="n">
+        <v>0.305</v>
       </c>
     </row>
     <row r="455">
@@ -24121,9 +25486,12 @@
         <v>0.004338</v>
       </c>
       <c r="O455" s="1" t="n">
+        <v>0.004277</v>
+      </c>
+      <c r="P455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="P455" s="1" t="n">
+      <c r="Q455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -24173,10 +25541,13 @@
         <v>0.1825</v>
       </c>
       <c r="O456" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="P456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="P456" s="1" t="n">
-        <v>0.1825</v>
+      <c r="Q456" s="1" t="n">
+        <v>0.1821</v>
       </c>
     </row>
     <row r="457">
@@ -24225,10 +25596,13 @@
         <v>0.04276</v>
       </c>
       <c r="O457" s="1" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="P457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="P457" s="1" t="n">
-        <v>0.04268</v>
+      <c r="Q457" s="1" t="n">
+        <v>0.04267</v>
       </c>
     </row>
     <row r="458">
@@ -24277,9 +25651,12 @@
         <v>0.1465</v>
       </c>
       <c r="O458" s="1" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="P458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="P458" s="1" t="n">
+      <c r="Q458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -24329,9 +25706,12 @@
         <v>0.008632000000000001</v>
       </c>
       <c r="O459" s="1" t="n">
+        <v>0.008625000000000001</v>
+      </c>
+      <c r="P459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="P459" s="1" t="n">
+      <c r="Q459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -24381,9 +25761,12 @@
         <v>0.007368</v>
       </c>
       <c r="O460" s="1" t="n">
+        <v>0.007357</v>
+      </c>
+      <c r="P460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="P460" s="1" t="n">
+      <c r="Q460" s="1" t="n">
         <v>0.007357</v>
       </c>
     </row>
@@ -24433,9 +25816,12 @@
         <v>0.000173</v>
       </c>
       <c r="O461" s="1" t="n">
+        <v>0.0001733</v>
+      </c>
+      <c r="P461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="P461" s="1" t="n">
+      <c r="Q461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -24485,9 +25871,12 @@
         <v>0.02311</v>
       </c>
       <c r="O462" s="1" t="n">
-        <v>0.02321</v>
+        <v>0.02331</v>
       </c>
       <c r="P462" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="Q462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -24537,9 +25926,12 @@
         <v>0.03717</v>
       </c>
       <c r="O463" s="1" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="P463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="P463" s="1" t="n">
+      <c r="Q463" s="1" t="n">
         <v>0.03685</v>
       </c>
     </row>
@@ -24589,10 +25981,13 @@
         <v>0.302</v>
       </c>
       <c r="O464" s="1" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="P464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="P464" s="1" t="n">
-        <v>0.3013</v>
+      <c r="Q464" s="1" t="n">
+        <v>0.3012</v>
       </c>
     </row>
     <row r="465">
@@ -24641,9 +26036,12 @@
         <v>0.0393</v>
       </c>
       <c r="O465" s="1" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="P465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="P465" s="1" t="n">
+      <c r="Q465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -24693,10 +26091,13 @@
         <v>2.667</v>
       </c>
       <c r="O466" s="1" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="P466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="P466" s="1" t="n">
-        <v>2.667</v>
+      <c r="Q466" s="1" t="n">
+        <v>2.662</v>
       </c>
     </row>
     <row r="467">
@@ -24745,9 +26146,12 @@
         <v>0.03395</v>
       </c>
       <c r="O467" s="1" t="n">
+        <v>0.03393</v>
+      </c>
+      <c r="P467" s="1" t="n">
         <v>0.03436</v>
       </c>
-      <c r="P467" s="1" t="n">
+      <c r="Q467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -24797,9 +26201,12 @@
         <v>0.1766</v>
       </c>
       <c r="O468" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="P468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="P468" s="1" t="n">
+      <c r="Q468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -24849,9 +26256,12 @@
         <v>0.0965</v>
       </c>
       <c r="O469" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="P469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="P469" s="1" t="n">
+      <c r="Q469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -24901,10 +26311,13 @@
         <v>0.06741999999999999</v>
       </c>
       <c r="O470" s="1" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="P470" s="1" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="P470" s="1" t="n">
-        <v>0.06716999999999999</v>
+      <c r="Q470" s="1" t="n">
+        <v>0.06708</v>
       </c>
     </row>
     <row r="471">
@@ -24953,9 +26366,12 @@
         <v>0.03995</v>
       </c>
       <c r="O471" s="1" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="P471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="P471" s="1" t="n">
+      <c r="Q471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -25005,10 +26421,13 @@
         <v>0.2471</v>
       </c>
       <c r="O472" s="1" t="n">
+        <v>0.2466</v>
+      </c>
+      <c r="P472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="P472" s="1" t="n">
-        <v>0.2471</v>
+      <c r="Q472" s="1" t="n">
+        <v>0.2466</v>
       </c>
     </row>
     <row r="473">
@@ -25057,9 +26476,12 @@
         <v>0.016358</v>
       </c>
       <c r="O473" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="P473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="P473" s="1" t="n">
+      <c r="Q473" s="1" t="n">
         <v>0.016358</v>
       </c>
     </row>
@@ -25109,9 +26531,12 @@
         <v>0.1155</v>
       </c>
       <c r="O474" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="P474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="P474" s="1" t="n">
+      <c r="Q474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -25161,9 +26586,12 @@
         <v>0.04268</v>
       </c>
       <c r="O475" s="1" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="P475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="P475" s="1" t="n">
+      <c r="Q475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -25213,10 +26641,13 @@
         <v>0.2072</v>
       </c>
       <c r="O476" s="1" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="P476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="P476" s="1" t="n">
-        <v>0.2071</v>
+      <c r="Q476" s="1" t="n">
+        <v>0.2066</v>
       </c>
     </row>
     <row r="477">
@@ -25265,10 +26696,13 @@
         <v>0.006802</v>
       </c>
       <c r="O477" s="1" t="n">
+        <v>0.006789</v>
+      </c>
+      <c r="P477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="P477" s="1" t="n">
-        <v>0.006796</v>
+      <c r="Q477" s="1" t="n">
+        <v>0.006789</v>
       </c>
     </row>
     <row r="478">
@@ -25317,9 +26751,12 @@
         <v>0.01781</v>
       </c>
       <c r="O478" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="P478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="P478" s="1" t="n">
+      <c r="Q478" s="1" t="n">
         <v>0.01781</v>
       </c>
     </row>
@@ -25369,10 +26806,13 @@
         <v>0.04679</v>
       </c>
       <c r="O479" s="1" t="n">
+        <v>0.04672</v>
+      </c>
+      <c r="P479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="P479" s="1" t="n">
-        <v>0.04679</v>
+      <c r="Q479" s="1" t="n">
+        <v>0.04672</v>
       </c>
     </row>
     <row r="480">
@@ -25421,9 +26861,12 @@
         <v>0.26006</v>
       </c>
       <c r="O480" s="1" t="n">
+        <v>0.25998</v>
+      </c>
+      <c r="P480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="P480" s="1" t="n">
+      <c r="Q480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -25473,10 +26916,13 @@
         <v>0.01225</v>
       </c>
       <c r="O481" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="P481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="P481" s="1" t="n">
-        <v>0.01225</v>
+      <c r="Q481" s="1" t="n">
+        <v>0.01218</v>
       </c>
     </row>
     <row r="482">
@@ -25525,9 +26971,12 @@
         <v>0.004088</v>
       </c>
       <c r="O482" s="1" t="n">
+        <v>0.004084</v>
+      </c>
+      <c r="P482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="P482" s="1" t="n">
+      <c r="Q482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -25577,9 +27026,12 @@
         <v>0.1229</v>
       </c>
       <c r="O483" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="P483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="P483" s="1" t="n">
+      <c r="Q483" s="1" t="n">
         <v>0.1229</v>
       </c>
     </row>
@@ -25629,9 +27081,12 @@
         <v>0.02222</v>
       </c>
       <c r="O484" s="1" t="n">
+        <v>0.02218</v>
+      </c>
+      <c r="P484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="P484" s="1" t="n">
+      <c r="Q484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -25681,9 +27136,12 @@
         <v>0.04539</v>
       </c>
       <c r="O485" s="1" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="P485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="P485" s="1" t="n">
+      <c r="Q485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -25733,9 +27191,12 @@
         <v>0.1735</v>
       </c>
       <c r="O486" s="1" t="n">
+        <v>0.1732</v>
+      </c>
+      <c r="P486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="P486" s="1" t="n">
+      <c r="Q486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -25785,10 +27246,13 @@
         <v>0.2726</v>
       </c>
       <c r="O487" s="1" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="P487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="P487" s="1" t="n">
-        <v>0.2726</v>
+      <c r="Q487" s="1" t="n">
+        <v>0.2725</v>
       </c>
     </row>
     <row r="488">
@@ -25837,10 +27301,13 @@
         <v>0.04612</v>
       </c>
       <c r="O488" s="1" t="n">
+        <v>0.04604</v>
+      </c>
+      <c r="P488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="P488" s="1" t="n">
-        <v>0.04611</v>
+      <c r="Q488" s="1" t="n">
+        <v>0.04604</v>
       </c>
     </row>
     <row r="489">
@@ -25889,10 +27356,13 @@
         <v>0.000215</v>
       </c>
       <c r="O489" s="1" t="n">
+        <v>0.0002144</v>
+      </c>
+      <c r="P489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="P489" s="1" t="n">
-        <v>0.0002149</v>
+      <c r="Q489" s="1" t="n">
+        <v>0.0002144</v>
       </c>
     </row>
     <row r="490">
@@ -25944,6 +27414,9 @@
         <v>1.78</v>
       </c>
       <c r="P490" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -25993,9 +27466,12 @@
         <v>16.046</v>
       </c>
       <c r="O491" s="1" t="n">
+        <v>16.019</v>
+      </c>
+      <c r="P491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="P491" s="1" t="n">
+      <c r="Q491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -26045,9 +27521,12 @@
         <v>0.06671000000000001</v>
       </c>
       <c r="O492" s="1" t="n">
+        <v>0.06668</v>
+      </c>
+      <c r="P492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="P492" s="1" t="n">
+      <c r="Q492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -26097,10 +27576,13 @@
         <v>0.06736</v>
       </c>
       <c r="O493" s="1" t="n">
+        <v>0.06728000000000001</v>
+      </c>
+      <c r="P493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="P493" s="1" t="n">
-        <v>0.06734999999999999</v>
+      <c r="Q493" s="1" t="n">
+        <v>0.06728000000000001</v>
       </c>
     </row>
     <row r="494">
@@ -26149,9 +27631,12 @@
         <v>0.009441</v>
       </c>
       <c r="O494" s="1" t="n">
+        <v>0.009450999999999999</v>
+      </c>
+      <c r="P494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="P494" s="1" t="n">
+      <c r="Q494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -26201,9 +27686,12 @@
         <v>0.005823</v>
       </c>
       <c r="O495" s="1" t="n">
+        <v>0.005829</v>
+      </c>
+      <c r="P495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="P495" s="1" t="n">
+      <c r="Q495" s="1" t="n">
         <v>0.005809</v>
       </c>
     </row>
@@ -26253,10 +27741,13 @@
         <v>0.009889999999999999</v>
       </c>
       <c r="O496" s="1" t="n">
+        <v>0.009849999999999999</v>
+      </c>
+      <c r="P496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="P496" s="1" t="n">
-        <v>0.00987</v>
+      <c r="Q496" s="1" t="n">
+        <v>0.009849999999999999</v>
       </c>
     </row>
     <row r="497">
@@ -26305,9 +27796,12 @@
         <v>0.04522</v>
       </c>
       <c r="O497" s="1" t="n">
-        <v>0.0455</v>
+        <v>0.04578</v>
       </c>
       <c r="P497" s="1" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="Q497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -26357,10 +27851,13 @@
         <v>0.006355</v>
       </c>
       <c r="O498" s="1" t="n">
+        <v>0.006353</v>
+      </c>
+      <c r="P498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="P498" s="1" t="n">
-        <v>0.006355</v>
+      <c r="Q498" s="1" t="n">
+        <v>0.006353</v>
       </c>
     </row>
     <row r="499">
@@ -26409,10 +27906,13 @@
         <v>0.01041</v>
       </c>
       <c r="O499" s="1" t="n">
+        <v>0.01039</v>
+      </c>
+      <c r="P499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="P499" s="1" t="n">
-        <v>0.01041</v>
+      <c r="Q499" s="1" t="n">
+        <v>0.01039</v>
       </c>
     </row>
     <row r="500">
@@ -26461,9 +27961,12 @@
         <v>0.5084</v>
       </c>
       <c r="O500" s="1" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="P500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="P500" s="1" t="n">
+      <c r="Q500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -26513,9 +28016,12 @@
         <v>0.03207</v>
       </c>
       <c r="O501" s="1" t="n">
+        <v>0.03206</v>
+      </c>
+      <c r="P501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="P501" s="1" t="n">
+      <c r="Q501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -26565,9 +28071,12 @@
         <v>0.446</v>
       </c>
       <c r="O502" s="1" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="P502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="P502" s="1" t="n">
+      <c r="Q502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -26617,9 +28126,12 @@
         <v>0.999341</v>
       </c>
       <c r="O503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="P503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="P503" s="1" t="n">
+      <c r="Q503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -26669,9 +28181,12 @@
         <v>0.03534</v>
       </c>
       <c r="O504" s="1" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="P504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="P504" s="1" t="n">
+      <c r="Q504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -26721,9 +28236,12 @@
         <v>0.004952</v>
       </c>
       <c r="O505" s="1" t="n">
+        <v>0.004941</v>
+      </c>
+      <c r="P505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="P505" s="1" t="n">
+      <c r="Q505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -26773,10 +28291,13 @@
         <v>0.01391</v>
       </c>
       <c r="O506" s="1" t="n">
+        <v>0.01388</v>
+      </c>
+      <c r="P506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="P506" s="1" t="n">
-        <v>0.01389</v>
+      <c r="Q506" s="1" t="n">
+        <v>0.01388</v>
       </c>
     </row>
     <row r="507">
@@ -26825,9 +28346,12 @@
         <v>0.00346</v>
       </c>
       <c r="O507" s="1" t="n">
+        <v>0.003464</v>
+      </c>
+      <c r="P507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="P507" s="1" t="n">
+      <c r="Q507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -26877,10 +28401,13 @@
         <v>1.418</v>
       </c>
       <c r="O508" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="P508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="P508" s="1" t="n">
-        <v>1.417</v>
+      <c r="Q508" s="1" t="n">
+        <v>1.413</v>
       </c>
     </row>
     <row r="509">
@@ -26929,10 +28456,13 @@
         <v>0.005082</v>
       </c>
       <c r="O509" s="1" t="n">
+        <v>0.005067</v>
+      </c>
+      <c r="P509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="P509" s="1" t="n">
-        <v>0.005076</v>
+      <c r="Q509" s="1" t="n">
+        <v>0.005067</v>
       </c>
     </row>
     <row r="510">
@@ -26981,9 +28511,12 @@
         <v>0.01573</v>
       </c>
       <c r="O510" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="P510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="P510" s="1" t="n">
+      <c r="Q510" s="1" t="n">
         <v>0.01571</v>
       </c>
     </row>
@@ -27033,9 +28566,12 @@
         <v>0.0823</v>
       </c>
       <c r="O511" s="1" t="n">
+        <v>0.08234</v>
+      </c>
+      <c r="P511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="P511" s="1" t="n">
+      <c r="Q511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -27085,10 +28621,13 @@
         <v>0.007092</v>
       </c>
       <c r="O512" s="1" t="n">
+        <v>0.007089</v>
+      </c>
+      <c r="P512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="P512" s="1" t="n">
-        <v>0.007092</v>
+      <c r="Q512" s="1" t="n">
+        <v>0.007089</v>
       </c>
     </row>
     <row r="513">
@@ -27137,9 +28676,12 @@
         <v>0.01491</v>
       </c>
       <c r="O513" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="P513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="P513" s="1" t="n">
+      <c r="Q513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -27189,9 +28731,12 @@
         <v>0.0475</v>
       </c>
       <c r="O514" s="1" t="n">
+        <v>0.04746</v>
+      </c>
+      <c r="P514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="P514" s="1" t="n">
+      <c r="Q514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -27241,9 +28786,12 @@
         <v>0.01811</v>
       </c>
       <c r="O515" s="1" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="P515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="P515" s="1" t="n">
+      <c r="Q515" s="1" t="n">
         <v>0.01811</v>
       </c>
     </row>
@@ -27293,9 +28841,12 @@
         <v>0.0005782</v>
       </c>
       <c r="O516" s="1" t="n">
+        <v>0.0005787</v>
+      </c>
+      <c r="P516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="P516" s="1" t="n">
+      <c r="Q516" s="1" t="n">
         <v>0.0005782</v>
       </c>
     </row>
@@ -27345,9 +28896,12 @@
         <v>0.07854999999999999</v>
       </c>
       <c r="O517" s="1" t="n">
+        <v>0.07849</v>
+      </c>
+      <c r="P517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="P517" s="1" t="n">
+      <c r="Q517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -27397,9 +28951,12 @@
         <v>0.006384</v>
       </c>
       <c r="O518" s="1" t="n">
+        <v>0.006376</v>
+      </c>
+      <c r="P518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="P518" s="1" t="n">
+      <c r="Q518" s="1" t="n">
         <v>0.006373</v>
       </c>
     </row>
@@ -27449,10 +29006,13 @@
         <v>0.05779</v>
       </c>
       <c r="O519" s="1" t="n">
+        <v>0.05765</v>
+      </c>
+      <c r="P519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="P519" s="1" t="n">
-        <v>0.05779</v>
+      <c r="Q519" s="1" t="n">
+        <v>0.05765</v>
       </c>
     </row>
     <row r="520">
@@ -27501,9 +29061,12 @@
         <v>0.10461</v>
       </c>
       <c r="O520" s="1" t="n">
+        <v>0.10462</v>
+      </c>
+      <c r="P520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="P520" s="1" t="n">
+      <c r="Q520" s="1" t="n">
         <v>0.10461</v>
       </c>
     </row>
@@ -27553,9 +29116,12 @@
         <v>0.01795</v>
       </c>
       <c r="O521" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="P521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="P521" s="1" t="n">
+      <c r="Q521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -27605,10 +29171,13 @@
         <v>0.01641</v>
       </c>
       <c r="O522" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="P522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="P522" s="1" t="n">
-        <v>0.01641</v>
+      <c r="Q522" s="1" t="n">
+        <v>0.01635</v>
       </c>
     </row>
     <row r="523">
@@ -27657,9 +29226,12 @@
         <v>0.01084</v>
       </c>
       <c r="O523" s="1" t="n">
+        <v>0.01084</v>
+      </c>
+      <c r="P523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="P523" s="1" t="n">
+      <c r="Q523" s="1" t="n">
         <v>0.01083</v>
       </c>
     </row>
@@ -27709,9 +29281,12 @@
         <v>0.00715</v>
       </c>
       <c r="O524" s="1" t="n">
-        <v>0.007158</v>
+        <v>0.007196</v>
       </c>
       <c r="P524" s="1" t="n">
+        <v>0.007196</v>
+      </c>
+      <c r="Q524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -27761,10 +29336,13 @@
         <v>0.005864</v>
       </c>
       <c r="O525" s="1" t="n">
+        <v>0.005837</v>
+      </c>
+      <c r="P525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="P525" s="1" t="n">
-        <v>0.005864</v>
+      <c r="Q525" s="1" t="n">
+        <v>0.005837</v>
       </c>
     </row>
     <row r="526">
@@ -27813,9 +29391,12 @@
         <v>0.001444</v>
       </c>
       <c r="O526" s="1" t="n">
+        <v>0.001443</v>
+      </c>
+      <c r="P526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="P526" s="1" t="n">
+      <c r="Q526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -27865,9 +29446,12 @@
         <v>0.374</v>
       </c>
       <c r="O527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="P527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="P527" s="1" t="n">
+      <c r="Q527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -27917,9 +29501,12 @@
         <v>0.005236</v>
       </c>
       <c r="O528" s="1" t="n">
-        <v>0.005236</v>
+        <v>0.00548</v>
       </c>
       <c r="P528" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="Q528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -27969,9 +29556,12 @@
         <v>2.954</v>
       </c>
       <c r="O529" s="1" t="n">
+        <v>2.952</v>
+      </c>
+      <c r="P529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="P529" s="1" t="n">
+      <c r="Q529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -28021,10 +29611,13 @@
         <v>0.1553</v>
       </c>
       <c r="O530" s="1" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="P530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="P530" s="1" t="n">
-        <v>0.1553</v>
+      <c r="Q530" s="1" t="n">
+        <v>0.1546</v>
       </c>
     </row>
     <row r="531">
@@ -28073,9 +29666,12 @@
         <v>2544</v>
       </c>
       <c r="O531" s="1" t="n">
-        <v>2544</v>
+        <v>2561</v>
       </c>
       <c r="P531" s="1" t="n">
+        <v>2561</v>
+      </c>
+      <c r="Q531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -28125,10 +29721,13 @@
         <v>0.03913</v>
       </c>
       <c r="O532" s="1" t="n">
+        <v>0.03905</v>
+      </c>
+      <c r="P532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="P532" s="1" t="n">
-        <v>0.03913</v>
+      <c r="Q532" s="1" t="n">
+        <v>0.03905</v>
       </c>
     </row>
     <row r="533">
@@ -28177,9 +29776,12 @@
         <v>0.02164</v>
       </c>
       <c r="O533" s="1" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="P533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="P533" s="1" t="n">
+      <c r="Q533" s="1" t="n">
         <v>0.02157</v>
       </c>
     </row>
@@ -28229,9 +29831,12 @@
         <v>0.07353</v>
       </c>
       <c r="O534" s="1" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="P534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="P534" s="1" t="n">
+      <c r="Q534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -28281,9 +29886,12 @@
         <v>0.007913999999999999</v>
       </c>
       <c r="O535" s="1" t="n">
+        <v>0.007863</v>
+      </c>
+      <c r="P535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="P535" s="1" t="n">
+      <c r="Q535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -28333,9 +29941,12 @@
         <v>0.05016</v>
       </c>
       <c r="O536" s="1" t="n">
+        <v>0.05008</v>
+      </c>
+      <c r="P536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="P536" s="1" t="n">
+      <c r="Q536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -28385,10 +29996,13 @@
         <v>0.00405</v>
       </c>
       <c r="O537" s="1" t="n">
+        <v>0.00403</v>
+      </c>
+      <c r="P537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="P537" s="1" t="n">
-        <v>0.00404</v>
+      <c r="Q537" s="1" t="n">
+        <v>0.00403</v>
       </c>
     </row>
     <row r="538">
@@ -28437,9 +30051,12 @@
         <v>0.08307</v>
       </c>
       <c r="O538" s="1" t="n">
+        <v>0.08284</v>
+      </c>
+      <c r="P538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="P538" s="1" t="n">
+      <c r="Q538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -28489,10 +30106,13 @@
         <v>0.02489</v>
       </c>
       <c r="O539" s="1" t="n">
+        <v>0.02484</v>
+      </c>
+      <c r="P539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="P539" s="1" t="n">
-        <v>0.02485</v>
+      <c r="Q539" s="1" t="n">
+        <v>0.02484</v>
       </c>
     </row>
     <row r="540">
@@ -28541,10 +30161,13 @@
         <v>0.08415</v>
       </c>
       <c r="O540" s="1" t="n">
+        <v>0.08406</v>
+      </c>
+      <c r="P540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="P540" s="1" t="n">
-        <v>0.08415</v>
+      <c r="Q540" s="1" t="n">
+        <v>0.08406</v>
       </c>
     </row>
     <row r="541">
@@ -28593,10 +30216,13 @@
         <v>0.01886</v>
       </c>
       <c r="O541" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="P541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="P541" s="1" t="n">
-        <v>0.01886</v>
+      <c r="Q541" s="1" t="n">
+        <v>0.01882</v>
       </c>
     </row>
     <row r="542">
@@ -28645,10 +30271,13 @@
         <v>0.01686</v>
       </c>
       <c r="O542" s="1" t="n">
+        <v>0.01685</v>
+      </c>
+      <c r="P542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="P542" s="1" t="n">
-        <v>0.01686</v>
+      <c r="Q542" s="1" t="n">
+        <v>0.01685</v>
       </c>
     </row>
     <row r="543">
@@ -28697,9 +30326,12 @@
         <v>0.1049</v>
       </c>
       <c r="O543" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="P543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="P543" s="1" t="n">
+      <c r="Q543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q543"/>
+  <dimension ref="A1:R543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -434,8 +434,9 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,10 +517,15 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>price_03:45</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -574,9 +580,12 @@
         <v>70638.89999999999</v>
       </c>
       <c r="P2" s="1" t="n">
+        <v>70690.2</v>
+      </c>
+      <c r="Q2" s="1" t="n">
         <v>70693.10000000001</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="R2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -629,9 +638,12 @@
         <v>2076.2</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>2076.79</v>
+        <v>2077.45</v>
       </c>
       <c r="Q3" s="1" t="n">
+        <v>2077.45</v>
+      </c>
+      <c r="R3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -684,9 +696,12 @@
         <v>86.92</v>
       </c>
       <c r="P4" s="1" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="Q4" s="1" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="R4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -739,9 +754,12 @@
         <v>3.993</v>
       </c>
       <c r="P5" s="1" t="n">
+        <v>4.002</v>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="R5" s="1" t="n">
         <v>3.991</v>
       </c>
     </row>
@@ -794,9 +812,12 @@
         <v>0.09458</v>
       </c>
       <c r="P6" s="1" t="n">
+        <v>0.09471</v>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -849,9 +870,12 @@
         <v>1.3894</v>
       </c>
       <c r="P7" s="1" t="n">
+        <v>1.3895</v>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>1.3924</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="R7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -904,9 +928,12 @@
         <v>22.416</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>22.497</v>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="R8" s="1" t="n">
         <v>22.204</v>
       </c>
     </row>
@@ -959,9 +986,12 @@
         <v>0.001972</v>
       </c>
       <c r="P9" s="1" t="n">
+        <v>0.002026</v>
+      </c>
+      <c r="Q9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="R9" s="1" t="n">
         <v>0.001972</v>
       </c>
     </row>
@@ -1014,9 +1044,12 @@
         <v>0.009905000000000001</v>
       </c>
       <c r="P10" s="1" t="n">
+        <v>0.009991999999999999</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="R10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1069,9 +1102,12 @@
         <v>0.13838</v>
       </c>
       <c r="P11" s="1" t="n">
+        <v>0.14433</v>
+      </c>
+      <c r="Q11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="R11" s="1" t="n">
         <v>0.13838</v>
       </c>
     </row>
@@ -1124,9 +1160,12 @@
         <v>0.011412</v>
       </c>
       <c r="P12" s="1" t="n">
+        <v>0.011403</v>
+      </c>
+      <c r="Q12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="R12" s="1" t="n">
         <v>0.011355</v>
       </c>
     </row>
@@ -1179,9 +1218,12 @@
         <v>38.139</v>
       </c>
       <c r="P13" s="1" t="n">
+        <v>38.157</v>
+      </c>
+      <c r="Q13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="R13" s="1" t="n">
         <v>37.812</v>
       </c>
     </row>
@@ -1234,9 +1276,12 @@
         <v>653.27</v>
       </c>
       <c r="P14" s="1" t="n">
+        <v>653.76</v>
+      </c>
+      <c r="Q14" s="1" t="n">
         <v>654.02</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="R14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1289,9 +1334,12 @@
         <v>209.78</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>209.93</v>
+        <v>210.04</v>
       </c>
       <c r="Q15" s="1" t="n">
+        <v>210.04</v>
+      </c>
+      <c r="R15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1344,9 +1392,12 @@
         <v>0.0033182</v>
       </c>
       <c r="P16" s="1" t="n">
+        <v>0.0033226</v>
+      </c>
+      <c r="Q16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="R16" s="1" t="n">
         <v>0.0033182</v>
       </c>
     </row>
@@ -1399,9 +1450,12 @@
         <v>237.38</v>
       </c>
       <c r="P17" s="1" t="n">
+        <v>238.41</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>239.55</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="R17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1454,9 +1508,12 @@
         <v>0.9871</v>
       </c>
       <c r="P18" s="1" t="n">
+        <v>0.9881</v>
+      </c>
+      <c r="Q18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="R18" s="1" t="n">
         <v>0.987</v>
       </c>
     </row>
@@ -1509,9 +1566,12 @@
         <v>1.0453</v>
       </c>
       <c r="P19" s="1" t="n">
+        <v>1.0264</v>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="Q19" s="1" t="n">
+      <c r="R19" s="1" t="n">
         <v>1.0184</v>
       </c>
     </row>
@@ -1564,9 +1624,12 @@
         <v>0.2587</v>
       </c>
       <c r="P20" s="1" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="Q20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="R20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1619,9 +1682,12 @@
         <v>0.59232</v>
       </c>
       <c r="P21" s="1" t="n">
+        <v>0.59271</v>
+      </c>
+      <c r="Q21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="Q21" s="1" t="n">
+      <c r="R21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -1674,9 +1740,12 @@
         <v>9.019</v>
       </c>
       <c r="P22" s="1" t="n">
+        <v>9.032999999999999</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="R22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -1729,9 +1798,12 @@
         <v>0.02397</v>
       </c>
       <c r="P23" s="1" t="n">
+        <v>0.02399</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="Q23" s="1" t="n">
+      <c r="R23" s="1" t="n">
         <v>0.02397</v>
       </c>
     </row>
@@ -1784,9 +1856,12 @@
         <v>9.558</v>
       </c>
       <c r="P24" s="1" t="n">
+        <v>9.565</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="Q24" s="1" t="n">
+      <c r="R24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -1842,6 +1917,9 @@
         <v>1.24</v>
       </c>
       <c r="Q25" s="1" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -1894,9 +1972,12 @@
         <v>0.07149</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>0.0717</v>
+        <v>0.07242</v>
       </c>
       <c r="Q26" s="1" t="n">
+        <v>0.07242</v>
+      </c>
+      <c r="R26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -1949,10 +2030,13 @@
         <v>1.417</v>
       </c>
       <c r="P27" s="1" t="n">
+        <v>1.416</v>
+      </c>
+      <c r="Q27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q27" s="1" t="n">
-        <v>1.417</v>
+      <c r="R27" s="1" t="n">
+        <v>1.416</v>
       </c>
     </row>
     <row r="28">
@@ -2004,9 +2088,12 @@
         <v>1.305</v>
       </c>
       <c r="P28" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="Q28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="Q28" s="1" t="n">
+      <c r="R28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2059,9 +2146,12 @@
         <v>463.26</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>463.26</v>
+        <v>463.55</v>
       </c>
       <c r="Q29" s="1" t="n">
+        <v>463.55</v>
+      </c>
+      <c r="R29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2114,9 +2204,12 @@
         <v>1.3045</v>
       </c>
       <c r="P30" s="1" t="n">
+        <v>1.2972</v>
+      </c>
+      <c r="Q30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="Q30" s="1" t="n">
+      <c r="R30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2172,6 +2265,9 @@
         <v>5025.5</v>
       </c>
       <c r="Q31" s="1" t="n">
+        <v>5025.5</v>
+      </c>
+      <c r="R31" s="1" t="n">
         <v>5021.33</v>
       </c>
     </row>
@@ -2224,9 +2320,12 @@
         <v>0.88</v>
       </c>
       <c r="P32" s="1" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="Q32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="Q32" s="1" t="n">
+      <c r="R32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2279,9 +2378,12 @@
         <v>0.001969</v>
       </c>
       <c r="P33" s="1" t="n">
+        <v>0.001975</v>
+      </c>
+      <c r="Q33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="Q33" s="1" t="n">
+      <c r="R33" s="1" t="n">
         <v>0.001969</v>
       </c>
     </row>
@@ -2334,9 +2436,12 @@
         <v>0.17183</v>
       </c>
       <c r="P34" s="1" t="n">
+        <v>0.17141</v>
+      </c>
+      <c r="Q34" s="1" t="n">
         <v>0.17264</v>
       </c>
-      <c r="Q34" s="1" t="n">
+      <c r="R34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2389,9 +2494,12 @@
         <v>0.29656</v>
       </c>
       <c r="P35" s="1" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="Q35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="Q35" s="1" t="n">
+      <c r="R35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -2444,9 +2552,12 @@
         <v>1.777</v>
       </c>
       <c r="P36" s="1" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="Q36" s="1" t="n">
         <v>1.795</v>
       </c>
-      <c r="Q36" s="1" t="n">
+      <c r="R36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -2499,9 +2610,12 @@
         <v>110.23</v>
       </c>
       <c r="P37" s="1" t="n">
+        <v>110.38</v>
+      </c>
+      <c r="Q37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="Q37" s="1" t="n">
+      <c r="R37" s="1" t="n">
         <v>110.23</v>
       </c>
     </row>
@@ -2554,10 +2668,13 @@
         <v>0.22151</v>
       </c>
       <c r="P38" s="1" t="n">
+        <v>0.21964</v>
+      </c>
+      <c r="Q38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="Q38" s="1" t="n">
-        <v>0.22079</v>
+      <c r="R38" s="1" t="n">
+        <v>0.21964</v>
       </c>
     </row>
     <row r="39">
@@ -2609,9 +2726,12 @@
         <v>0.1068</v>
       </c>
       <c r="P39" s="1" t="n">
+        <v>0.1069</v>
+      </c>
+      <c r="Q39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="Q39" s="1" t="n">
+      <c r="R39" s="1" t="n">
         <v>0.1068</v>
       </c>
     </row>
@@ -2664,9 +2784,12 @@
         <v>0.37301</v>
       </c>
       <c r="P40" s="1" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="Q40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="Q40" s="1" t="n">
+      <c r="R40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -2719,9 +2842,12 @@
         <v>54.63</v>
       </c>
       <c r="P41" s="1" t="n">
+        <v>54.66</v>
+      </c>
+      <c r="Q41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="Q41" s="1" t="n">
+      <c r="R41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -2774,9 +2900,12 @@
         <v>0.0010643</v>
       </c>
       <c r="P42" s="1" t="n">
+        <v>0.0010645</v>
+      </c>
+      <c r="Q42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="Q42" s="1" t="n">
+      <c r="R42" s="1" t="n">
         <v>0.0010643</v>
       </c>
     </row>
@@ -2829,9 +2958,12 @@
         <v>6.436</v>
       </c>
       <c r="P43" s="1" t="n">
+        <v>6.478</v>
+      </c>
+      <c r="Q43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="Q43" s="1" t="n">
+      <c r="R43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -2884,10 +3016,13 @@
         <v>0.6288</v>
       </c>
       <c r="P44" s="1" t="n">
+        <v>0.6276</v>
+      </c>
+      <c r="Q44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="Q44" s="1" t="n">
-        <v>0.6288</v>
+      <c r="R44" s="1" t="n">
+        <v>0.6276</v>
       </c>
     </row>
     <row r="45">
@@ -2939,10 +3074,13 @@
         <v>0.3536</v>
       </c>
       <c r="P45" s="1" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="Q45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="Q45" s="1" t="n">
-        <v>0.3533</v>
+      <c r="R45" s="1" t="n">
+        <v>0.3528</v>
       </c>
     </row>
     <row r="46">
@@ -2994,9 +3132,12 @@
         <v>0.0331</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>0.0331</v>
+        <v>0.03321</v>
       </c>
       <c r="Q46" s="1" t="n">
+        <v>0.03321</v>
+      </c>
+      <c r="R46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3049,9 +3190,12 @@
         <v>0.0712</v>
       </c>
       <c r="P47" s="1" t="n">
+        <v>0.07126</v>
+      </c>
+      <c r="Q47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="Q47" s="1" t="n">
+      <c r="R47" s="1" t="n">
         <v>0.0712</v>
       </c>
     </row>
@@ -3104,9 +3248,12 @@
         <v>0.7083</v>
       </c>
       <c r="P48" s="1" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="Q48" s="1" t="n">
         <v>0.7097</v>
       </c>
-      <c r="Q48" s="1" t="n">
+      <c r="R48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3159,10 +3306,13 @@
         <v>0.00435</v>
       </c>
       <c r="P49" s="1" t="n">
+        <v>0.004326</v>
+      </c>
+      <c r="Q49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="Q49" s="1" t="n">
-        <v>0.00435</v>
+      <c r="R49" s="1" t="n">
+        <v>0.004326</v>
       </c>
     </row>
     <row r="50">
@@ -3214,10 +3364,13 @@
         <v>0.1037</v>
       </c>
       <c r="P50" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="Q50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="Q50" s="1" t="n">
-        <v>0.1037</v>
+      <c r="R50" s="1" t="n">
+        <v>0.1035</v>
       </c>
     </row>
     <row r="51">
@@ -3269,9 +3422,12 @@
         <v>0.04039</v>
       </c>
       <c r="P51" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="Q51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="Q51" s="1" t="n">
+      <c r="R51" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -3324,9 +3480,12 @@
         <v>0.1647</v>
       </c>
       <c r="P52" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="Q52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="Q52" s="1" t="n">
+      <c r="R52" s="1" t="n">
         <v>0.1646</v>
       </c>
     </row>
@@ -3379,9 +3538,12 @@
         <v>0.02011</v>
       </c>
       <c r="P53" s="1" t="n">
+        <v>0.02067</v>
+      </c>
+      <c r="Q53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="Q53" s="1" t="n">
+      <c r="R53" s="1" t="n">
         <v>0.02002</v>
       </c>
     </row>
@@ -3434,9 +3596,12 @@
         <v>0.007182</v>
       </c>
       <c r="P54" s="1" t="n">
+        <v>0.00719</v>
+      </c>
+      <c r="Q54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="Q54" s="1" t="n">
+      <c r="R54" s="1" t="n">
         <v>0.007182</v>
       </c>
     </row>
@@ -3489,9 +3654,12 @@
         <v>3.911</v>
       </c>
       <c r="P55" s="1" t="n">
+        <v>3.913</v>
+      </c>
+      <c r="Q55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="Q55" s="1" t="n">
+      <c r="R55" s="1" t="n">
         <v>3.911</v>
       </c>
     </row>
@@ -3544,9 +3712,12 @@
         <v>0.016965</v>
       </c>
       <c r="P56" s="1" t="n">
+        <v>0.017032</v>
+      </c>
+      <c r="Q56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="Q56" s="1" t="n">
+      <c r="R56" s="1" t="n">
         <v>0.016965</v>
       </c>
     </row>
@@ -3599,9 +3770,12 @@
         <v>0.1088</v>
       </c>
       <c r="P57" s="1" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="Q57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="Q57" s="1" t="n">
+      <c r="R57" s="1" t="n">
         <v>0.1088</v>
       </c>
     </row>
@@ -3654,9 +3828,12 @@
         <v>2.654</v>
       </c>
       <c r="P58" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="Q58" s="1" t="n">
+      <c r="R58" s="1" t="n">
         <v>2.643</v>
       </c>
     </row>
@@ -3709,9 +3886,12 @@
         <v>0.1587</v>
       </c>
       <c r="P59" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="Q59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="Q59" s="1" t="n">
+      <c r="R59" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -3764,9 +3944,12 @@
         <v>0.005874</v>
       </c>
       <c r="P60" s="1" t="n">
+        <v>0.005879</v>
+      </c>
+      <c r="Q60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="Q60" s="1" t="n">
+      <c r="R60" s="1" t="n">
         <v>0.005874</v>
       </c>
     </row>
@@ -3819,9 +4002,12 @@
         <v>0.09186</v>
       </c>
       <c r="P61" s="1" t="n">
+        <v>0.09186999999999999</v>
+      </c>
+      <c r="Q61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="Q61" s="1" t="n">
+      <c r="R61" s="1" t="n">
         <v>0.09186</v>
       </c>
     </row>
@@ -3874,9 +4060,12 @@
         <v>0.9135</v>
       </c>
       <c r="P62" s="1" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="Q62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="Q62" s="1" t="n">
+      <c r="R62" s="1" t="n">
         <v>0.9112</v>
       </c>
     </row>
@@ -3929,9 +4118,12 @@
         <v>0.78</v>
       </c>
       <c r="P63" s="1" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="Q63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="Q63" s="1" t="n">
+      <c r="R63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -3984,9 +4176,12 @@
         <v>0.04631</v>
       </c>
       <c r="P64" s="1" t="n">
+        <v>0.04652</v>
+      </c>
+      <c r="Q64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="Q64" s="1" t="n">
+      <c r="R64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -4039,9 +4234,12 @@
         <v>354.81</v>
       </c>
       <c r="P65" s="1" t="n">
+        <v>355.13</v>
+      </c>
+      <c r="Q65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="Q65" s="1" t="n">
+      <c r="R65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -4094,9 +4292,12 @@
         <v>0.12394</v>
       </c>
       <c r="P66" s="1" t="n">
+        <v>0.12439</v>
+      </c>
+      <c r="Q66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="Q66" s="1" t="n">
+      <c r="R66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -4149,9 +4350,12 @@
         <v>0.2249</v>
       </c>
       <c r="P67" s="1" t="n">
+        <v>0.2258</v>
+      </c>
+      <c r="Q67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="Q67" s="1" t="n">
+      <c r="R67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -4204,9 +4408,12 @@
         <v>0.00338</v>
       </c>
       <c r="P68" s="1" t="n">
+        <v>0.00339</v>
+      </c>
+      <c r="Q68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="Q68" s="1" t="n">
+      <c r="R68" s="1" t="n">
         <v>0.00338</v>
       </c>
     </row>
@@ -4259,9 +4466,12 @@
         <v>0.1742</v>
       </c>
       <c r="P69" s="1" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="Q69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="Q69" s="1" t="n">
+      <c r="R69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -4314,9 +4524,12 @@
         <v>0.16374</v>
       </c>
       <c r="P70" s="1" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="Q70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="Q70" s="1" t="n">
+      <c r="R70" s="1" t="n">
         <v>0.16374</v>
       </c>
     </row>
@@ -4369,9 +4582,12 @@
         <v>0.3543</v>
       </c>
       <c r="P71" s="1" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="Q71" s="1" t="n">
         <v>0.3574</v>
       </c>
-      <c r="Q71" s="1" t="n">
+      <c r="R71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -4424,9 +4640,12 @@
         <v>0.7068</v>
       </c>
       <c r="P72" s="1" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="Q72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="Q72" s="1" t="n">
+      <c r="R72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -4479,9 +4698,12 @@
         <v>0.00868</v>
       </c>
       <c r="P73" s="1" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="Q73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="Q73" s="1" t="n">
+      <c r="R73" s="1" t="n">
         <v>0.00859</v>
       </c>
     </row>
@@ -4534,9 +4756,12 @@
         <v>0.005978</v>
       </c>
       <c r="P74" s="1" t="n">
+        <v>0.005986</v>
+      </c>
+      <c r="Q74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="Q74" s="1" t="n">
+      <c r="R74" s="1" t="n">
         <v>0.005967</v>
       </c>
     </row>
@@ -4589,9 +4814,12 @@
         <v>0.226</v>
       </c>
       <c r="P75" s="1" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="Q75" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="R75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -4644,9 +4872,12 @@
         <v>0.3222</v>
       </c>
       <c r="P76" s="1" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="Q76" s="1" t="n">
         <v>0.3265</v>
       </c>
-      <c r="Q76" s="1" t="n">
+      <c r="R76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -4699,9 +4930,12 @@
         <v>0.1002</v>
       </c>
       <c r="P77" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="Q77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="Q77" s="1" t="n">
+      <c r="R77" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -4754,9 +4988,12 @@
         <v>0.1225</v>
       </c>
       <c r="P78" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="Q78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="Q78" s="1" t="n">
+      <c r="R78" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -4809,9 +5046,12 @@
         <v>0.073</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>0.07353999999999999</v>
+        <v>0.07373</v>
       </c>
       <c r="Q79" s="1" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="R79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -4864,9 +5104,12 @@
         <v>0.04659</v>
       </c>
       <c r="P80" s="1" t="n">
+        <v>0.04676</v>
+      </c>
+      <c r="Q80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="Q80" s="1" t="n">
+      <c r="R80" s="1" t="n">
         <v>0.04655</v>
       </c>
     </row>
@@ -4919,9 +5162,12 @@
         <v>0.000235</v>
       </c>
       <c r="P81" s="1" t="n">
+        <v>0.000233</v>
+      </c>
+      <c r="Q81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="Q81" s="1" t="n">
+      <c r="R81" s="1" t="n">
         <v>0.000231</v>
       </c>
     </row>
@@ -4974,9 +5220,12 @@
         <v>8.208</v>
       </c>
       <c r="P82" s="1" t="n">
+        <v>8.215999999999999</v>
+      </c>
+      <c r="Q82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="Q82" s="1" t="n">
+      <c r="R82" s="1" t="n">
         <v>8.206</v>
       </c>
     </row>
@@ -5029,9 +5278,12 @@
         <v>0.0005802</v>
       </c>
       <c r="P83" s="1" t="n">
+        <v>0.0005787</v>
+      </c>
+      <c r="Q83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="Q83" s="1" t="n">
+      <c r="R83" s="1" t="n">
         <v>0.0005756</v>
       </c>
     </row>
@@ -5084,9 +5336,12 @@
         <v>0.4505</v>
       </c>
       <c r="P84" s="1" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="Q84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="Q84" s="1" t="n">
+      <c r="R84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -5139,9 +5394,12 @@
         <v>0.06262</v>
       </c>
       <c r="P85" s="1" t="n">
+        <v>0.06265</v>
+      </c>
+      <c r="Q85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="Q85" s="1" t="n">
+      <c r="R85" s="1" t="n">
         <v>0.06235</v>
       </c>
     </row>
@@ -5194,9 +5452,12 @@
         <v>0.05436</v>
       </c>
       <c r="P86" s="1" t="n">
+        <v>0.05432</v>
+      </c>
+      <c r="Q86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="Q86" s="1" t="n">
+      <c r="R86" s="1" t="n">
         <v>0.05424</v>
       </c>
     </row>
@@ -5249,9 +5510,12 @@
         <v>0.003345</v>
       </c>
       <c r="P87" s="1" t="n">
+        <v>0.003346</v>
+      </c>
+      <c r="Q87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="Q87" s="1" t="n">
+      <c r="R87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -5304,9 +5568,12 @@
         <v>0.05038</v>
       </c>
       <c r="P88" s="1" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="Q88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="Q88" s="1" t="n">
+      <c r="R88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -5359,9 +5626,12 @@
         <v>0.03087</v>
       </c>
       <c r="P89" s="1" t="n">
+        <v>0.03108</v>
+      </c>
+      <c r="Q89" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="Q89" s="1" t="n">
+      <c r="R89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -5414,10 +5684,13 @@
         <v>0.3466</v>
       </c>
       <c r="P90" s="1" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="Q90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="Q90" s="1" t="n">
-        <v>0.3466</v>
+      <c r="R90" s="1" t="n">
+        <v>0.346</v>
       </c>
     </row>
     <row r="91">
@@ -5469,9 +5742,12 @@
         <v>0.07742</v>
       </c>
       <c r="P91" s="1" t="n">
+        <v>0.07739</v>
+      </c>
+      <c r="Q91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="Q91" s="1" t="n">
+      <c r="R91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -5524,9 +5800,12 @@
         <v>0.3535</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>0.3551</v>
+        <v>0.361</v>
       </c>
       <c r="Q92" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="R92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -5579,9 +5858,12 @@
         <v>1.9742</v>
       </c>
       <c r="P93" s="1" t="n">
+        <v>1.9722</v>
+      </c>
+      <c r="Q93" s="1" t="n">
         <v>1.9809</v>
       </c>
-      <c r="Q93" s="1" t="n">
+      <c r="R93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -5634,9 +5916,12 @@
         <v>0.2583</v>
       </c>
       <c r="P94" s="1" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="Q94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="Q94" s="1" t="n">
+      <c r="R94" s="1" t="n">
         <v>0.2583</v>
       </c>
     </row>
@@ -5689,9 +5974,12 @@
         <v>0.04582</v>
       </c>
       <c r="P95" s="1" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="Q95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="Q95" s="1" t="n">
+      <c r="R95" s="1" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -5744,9 +6032,12 @@
         <v>0.006056</v>
       </c>
       <c r="P96" s="1" t="n">
+        <v>0.006101</v>
+      </c>
+      <c r="Q96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="Q96" s="1" t="n">
+      <c r="R96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -5799,9 +6090,12 @@
         <v>0.001723</v>
       </c>
       <c r="P97" s="1" t="n">
+        <v>0.001724</v>
+      </c>
+      <c r="Q97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="Q97" s="1" t="n">
+      <c r="R97" s="1" t="n">
         <v>0.001723</v>
       </c>
     </row>
@@ -5854,9 +6148,12 @@
         <v>5.194</v>
       </c>
       <c r="P98" s="1" t="n">
+        <v>5.198</v>
+      </c>
+      <c r="Q98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="Q98" s="1" t="n">
+      <c r="R98" s="1" t="n">
         <v>5.188</v>
       </c>
     </row>
@@ -5909,9 +6206,12 @@
         <v>0.01508</v>
       </c>
       <c r="P99" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="Q99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="Q99" s="1" t="n">
+      <c r="R99" s="1" t="n">
         <v>0.01508</v>
       </c>
     </row>
@@ -5964,9 +6264,12 @@
         <v>0.5528999999999999</v>
       </c>
       <c r="P100" s="1" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="Q100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="Q100" s="1" t="n">
+      <c r="R100" s="1" t="n">
         <v>0.5508999999999999</v>
       </c>
     </row>
@@ -6019,9 +6322,12 @@
         <v>0.09</v>
       </c>
       <c r="P101" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="Q101" s="1" t="n">
+      <c r="R101" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6074,9 +6380,12 @@
         <v>32.39</v>
       </c>
       <c r="P102" s="1" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="Q102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="Q102" s="1" t="n">
+      <c r="R102" s="1" t="n">
         <v>32.36</v>
       </c>
     </row>
@@ -6129,9 +6438,12 @@
         <v>0.03166</v>
       </c>
       <c r="P103" s="1" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="Q103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="Q103" s="1" t="n">
+      <c r="R103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -6184,9 +6496,12 @@
         <v>0.06569</v>
       </c>
       <c r="P104" s="1" t="n">
+        <v>0.06572</v>
+      </c>
+      <c r="Q104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="Q104" s="1" t="n">
+      <c r="R104" s="1" t="n">
         <v>0.06561</v>
       </c>
     </row>
@@ -6239,9 +6554,12 @@
         <v>1.3048</v>
       </c>
       <c r="P105" s="1" t="n">
+        <v>1.3034</v>
+      </c>
+      <c r="Q105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="Q105" s="1" t="n">
+      <c r="R105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -6294,9 +6612,12 @@
         <v>0.1209</v>
       </c>
       <c r="P106" s="1" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="Q106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="Q106" s="1" t="n">
+      <c r="R106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -6349,9 +6670,12 @@
         <v>0.119</v>
       </c>
       <c r="P107" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="Q107" s="1" t="n">
+      <c r="R107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -6404,9 +6728,12 @@
         <v>0.09594</v>
       </c>
       <c r="P108" s="1" t="n">
+        <v>0.09596</v>
+      </c>
+      <c r="Q108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="Q108" s="1" t="n">
+      <c r="R108" s="1" t="n">
         <v>0.09579</v>
       </c>
     </row>
@@ -6459,9 +6786,12 @@
         <v>0.13851</v>
       </c>
       <c r="P109" s="1" t="n">
+        <v>0.13863</v>
+      </c>
+      <c r="Q109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="Q109" s="1" t="n">
+      <c r="R109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -6514,9 +6844,12 @@
         <v>5.573</v>
       </c>
       <c r="P110" s="1" t="n">
+        <v>5.565</v>
+      </c>
+      <c r="Q110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="Q110" s="1" t="n">
+      <c r="R110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -6569,9 +6902,12 @@
         <v>1.099</v>
       </c>
       <c r="P111" s="1" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="Q111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="Q111" s="1" t="n">
+      <c r="R111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -6624,10 +6960,13 @@
         <v>0.028959</v>
       </c>
       <c r="P112" s="1" t="n">
+        <v>0.028821</v>
+      </c>
+      <c r="Q112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="Q112" s="1" t="n">
-        <v>0.028875</v>
+      <c r="R112" s="1" t="n">
+        <v>0.028821</v>
       </c>
     </row>
     <row r="113">
@@ -6679,9 +7018,12 @@
         <v>1.868</v>
       </c>
       <c r="P113" s="1" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="Q113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="Q113" s="1" t="n">
+      <c r="R113" s="1" t="n">
         <v>1.868</v>
       </c>
     </row>
@@ -6734,9 +7076,12 @@
         <v>0.05882</v>
       </c>
       <c r="P114" s="1" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="Q114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="Q114" s="1" t="n">
+      <c r="R114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -6789,9 +7134,12 @@
         <v>0.12844</v>
       </c>
       <c r="P115" s="1" t="n">
+        <v>0.12859</v>
+      </c>
+      <c r="Q115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="Q115" s="1" t="n">
+      <c r="R115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -6844,9 +7192,12 @@
         <v>1.1039</v>
       </c>
       <c r="P116" s="1" t="n">
+        <v>1.1066</v>
+      </c>
+      <c r="Q116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="Q116" s="1" t="n">
+      <c r="R116" s="1" t="n">
         <v>1.1039</v>
       </c>
     </row>
@@ -6899,10 +7250,13 @@
         <v>0.1535</v>
       </c>
       <c r="P117" s="1" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="Q117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="Q117" s="1" t="n">
-        <v>0.1531</v>
+      <c r="R117" s="1" t="n">
+        <v>0.1515</v>
       </c>
     </row>
     <row r="118">
@@ -6954,9 +7308,12 @@
         <v>0.158</v>
       </c>
       <c r="P118" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="Q118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="Q118" s="1" t="n">
+      <c r="R118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -7009,9 +7366,12 @@
         <v>0.04686</v>
       </c>
       <c r="P119" s="1" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="Q119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="Q119" s="1" t="n">
+      <c r="R119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -7064,9 +7424,12 @@
         <v>3.016</v>
       </c>
       <c r="P120" s="1" t="n">
+        <v>3.018</v>
+      </c>
+      <c r="Q120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="Q120" s="1" t="n">
+      <c r="R120" s="1" t="n">
         <v>3.016</v>
       </c>
     </row>
@@ -7119,9 +7482,12 @@
         <v>0.2962</v>
       </c>
       <c r="P121" s="1" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="Q121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="Q121" s="1" t="n">
+      <c r="R121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -7174,9 +7540,12 @@
         <v>0.5792</v>
       </c>
       <c r="P122" s="1" t="n">
+        <v>0.5793</v>
+      </c>
+      <c r="Q122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="Q122" s="1" t="n">
+      <c r="R122" s="1" t="n">
         <v>0.5792</v>
       </c>
     </row>
@@ -7229,10 +7598,13 @@
         <v>0.01256</v>
       </c>
       <c r="P123" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="Q123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="Q123" s="1" t="n">
-        <v>0.01256</v>
+      <c r="R123" s="1" t="n">
+        <v>0.01254</v>
       </c>
     </row>
     <row r="124">
@@ -7284,9 +7656,12 @@
         <v>0.1574</v>
       </c>
       <c r="P124" s="1" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="Q124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="Q124" s="1" t="n">
+      <c r="R124" s="1" t="n">
         <v>0.1574</v>
       </c>
     </row>
@@ -7339,9 +7714,12 @@
         <v>0.00178</v>
       </c>
       <c r="P125" s="1" t="n">
+        <v>0.001783</v>
+      </c>
+      <c r="Q125" s="1" t="n">
         <v>0.001786</v>
       </c>
-      <c r="Q125" s="1" t="n">
+      <c r="R125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -7394,9 +7772,12 @@
         <v>0.0004831</v>
       </c>
       <c r="P126" s="1" t="n">
+        <v>0.0004842</v>
+      </c>
+      <c r="Q126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="Q126" s="1" t="n">
+      <c r="R126" s="1" t="n">
         <v>0.0004831</v>
       </c>
     </row>
@@ -7449,9 +7830,12 @@
         <v>0.02934</v>
       </c>
       <c r="P127" s="1" t="n">
+        <v>0.02935</v>
+      </c>
+      <c r="Q127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="Q127" s="1" t="n">
+      <c r="R127" s="1" t="n">
         <v>0.02934</v>
       </c>
     </row>
@@ -7504,9 +7888,12 @@
         <v>0.0412</v>
       </c>
       <c r="P128" s="1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="Q128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="Q128" s="1" t="n">
+      <c r="R128" s="1" t="n">
         <v>0.04119</v>
       </c>
     </row>
@@ -7559,9 +7946,12 @@
         <v>0.04872</v>
       </c>
       <c r="P129" s="1" t="n">
+        <v>0.04868</v>
+      </c>
+      <c r="Q129" s="1" t="n">
         <v>0.04887</v>
       </c>
-      <c r="Q129" s="1" t="n">
+      <c r="R129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -7614,10 +8004,13 @@
         <v>1.25e-05</v>
       </c>
       <c r="P130" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="Q130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="Q130" s="1" t="n">
-        <v>1.24e-05</v>
+      <c r="R130" s="1" t="n">
+        <v>1.22e-05</v>
       </c>
     </row>
     <row r="131">
@@ -7669,9 +8062,12 @@
         <v>6.9e-06</v>
       </c>
       <c r="P131" s="1" t="n">
+        <v>6.9e-06</v>
+      </c>
+      <c r="Q131" s="1" t="n">
         <v>7.2e-06</v>
       </c>
-      <c r="Q131" s="1" t="n">
+      <c r="R131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -7724,9 +8120,12 @@
         <v>0.00699</v>
       </c>
       <c r="P132" s="1" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="Q132" s="1" t="n">
         <v>0.00703</v>
       </c>
-      <c r="Q132" s="1" t="n">
+      <c r="R132" s="1" t="n">
         <v>0.00699</v>
       </c>
     </row>
@@ -7779,9 +8178,12 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="P133" s="1" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="Q133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="Q133" s="1" t="n">
+      <c r="R133" s="1" t="n">
         <v>0.09660000000000001</v>
       </c>
     </row>
@@ -7834,9 +8236,12 @@
         <v>0.0004076</v>
       </c>
       <c r="P134" s="1" t="n">
+        <v>0.0004106</v>
+      </c>
+      <c r="Q134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="Q134" s="1" t="n">
+      <c r="R134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -7889,10 +8294,13 @@
         <v>0.08221000000000001</v>
       </c>
       <c r="P135" s="1" t="n">
+        <v>0.08195</v>
+      </c>
+      <c r="Q135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="Q135" s="1" t="n">
-        <v>0.08221000000000001</v>
+      <c r="R135" s="1" t="n">
+        <v>0.08195</v>
       </c>
     </row>
     <row r="136">
@@ -7944,9 +8352,12 @@
         <v>0.007851</v>
       </c>
       <c r="P136" s="1" t="n">
+        <v>0.007875999999999999</v>
+      </c>
+      <c r="Q136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="Q136" s="1" t="n">
+      <c r="R136" s="1" t="n">
         <v>0.007851</v>
       </c>
     </row>
@@ -7999,9 +8410,12 @@
         <v>0.0008206</v>
       </c>
       <c r="P137" s="1" t="n">
+        <v>0.0008207000000000001</v>
+      </c>
+      <c r="Q137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="Q137" s="1" t="n">
+      <c r="R137" s="1" t="n">
         <v>0.000816</v>
       </c>
     </row>
@@ -8054,9 +8468,12 @@
         <v>0.1468</v>
       </c>
       <c r="P138" s="1" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="Q138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="Q138" s="1" t="n">
+      <c r="R138" s="1" t="n">
         <v>0.1468</v>
       </c>
     </row>
@@ -8109,9 +8526,12 @@
         <v>0.006689</v>
       </c>
       <c r="P139" s="1" t="n">
+        <v>0.006693</v>
+      </c>
+      <c r="Q139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="Q139" s="1" t="n">
+      <c r="R139" s="1" t="n">
         <v>0.006689</v>
       </c>
     </row>
@@ -8164,9 +8584,12 @@
         <v>0.01384</v>
       </c>
       <c r="P140" s="1" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="Q140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="Q140" s="1" t="n">
+      <c r="R140" s="1" t="n">
         <v>0.01381</v>
       </c>
     </row>
@@ -8219,10 +8642,13 @@
         <v>0.09732</v>
       </c>
       <c r="P141" s="1" t="n">
+        <v>0.09718</v>
+      </c>
+      <c r="Q141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="Q141" s="1" t="n">
-        <v>0.09732</v>
+      <c r="R141" s="1" t="n">
+        <v>0.09718</v>
       </c>
     </row>
     <row r="142">
@@ -8274,9 +8700,12 @@
         <v>0.05419</v>
       </c>
       <c r="P142" s="1" t="n">
+        <v>0.05417</v>
+      </c>
+      <c r="Q142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="Q142" s="1" t="n">
+      <c r="R142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -8329,9 +8758,12 @@
         <v>0.3222</v>
       </c>
       <c r="P143" s="1" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Q143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="Q143" s="1" t="n">
+      <c r="R143" s="1" t="n">
         <v>0.3222</v>
       </c>
     </row>
@@ -8384,9 +8816,12 @@
         <v>0.02564</v>
       </c>
       <c r="P144" s="1" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="Q144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="Q144" s="1" t="n">
+      <c r="R144" s="1" t="n">
         <v>0.02564</v>
       </c>
     </row>
@@ -8439,10 +8874,13 @@
         <v>0.2368</v>
       </c>
       <c r="P145" s="1" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="Q145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="Q145" s="1" t="n">
-        <v>0.2368</v>
+      <c r="R145" s="1" t="n">
+        <v>0.2367</v>
       </c>
     </row>
     <row r="146">
@@ -8494,9 +8932,12 @@
         <v>0.007003</v>
       </c>
       <c r="P146" s="1" t="n">
+        <v>0.00702</v>
+      </c>
+      <c r="Q146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="Q146" s="1" t="n">
+      <c r="R146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -8549,9 +8990,12 @@
         <v>0.08637</v>
       </c>
       <c r="P147" s="1" t="n">
+        <v>0.08656999999999999</v>
+      </c>
+      <c r="Q147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="Q147" s="1" t="n">
+      <c r="R147" s="1" t="n">
         <v>0.08637</v>
       </c>
     </row>
@@ -8604,9 +9048,12 @@
         <v>0.05284</v>
       </c>
       <c r="P148" s="1" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="Q148" s="1" t="n">
         <v>0.05284</v>
       </c>
-      <c r="Q148" s="1" t="n">
+      <c r="R148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -8659,9 +9106,12 @@
         <v>0.02389</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>0.02394</v>
+        <v>0.02398</v>
       </c>
       <c r="Q149" s="1" t="n">
+        <v>0.02398</v>
+      </c>
+      <c r="R149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -8714,9 +9164,12 @@
         <v>0.08592</v>
       </c>
       <c r="P150" s="1" t="n">
+        <v>0.08567</v>
+      </c>
+      <c r="Q150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="Q150" s="1" t="n">
+      <c r="R150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -8769,9 +9222,12 @@
         <v>0.0232</v>
       </c>
       <c r="P151" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="Q151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="Q151" s="1" t="n">
+      <c r="R151" s="1" t="n">
         <v>0.02318</v>
       </c>
     </row>
@@ -8824,9 +9280,12 @@
         <v>0.02543</v>
       </c>
       <c r="P152" s="1" t="n">
+        <v>0.02541</v>
+      </c>
+      <c r="Q152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="Q152" s="1" t="n">
+      <c r="R152" s="1" t="n">
         <v>0.02534</v>
       </c>
     </row>
@@ -8879,9 +9338,12 @@
         <v>0.0002152</v>
       </c>
       <c r="P153" s="1" t="n">
+        <v>0.0002131</v>
+      </c>
+      <c r="Q153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="Q153" s="1" t="n">
+      <c r="R153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -8934,9 +9396,12 @@
         <v>0.4376</v>
       </c>
       <c r="P154" s="1" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="Q154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="Q154" s="1" t="n">
+      <c r="R154" s="1" t="n">
         <v>0.4376</v>
       </c>
     </row>
@@ -8989,9 +9454,12 @@
         <v>0.06766999999999999</v>
       </c>
       <c r="P155" s="1" t="n">
+        <v>0.06759</v>
+      </c>
+      <c r="Q155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="Q155" s="1" t="n">
+      <c r="R155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -9044,10 +9512,13 @@
         <v>0.12826</v>
       </c>
       <c r="P156" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="Q156" s="1" t="n">
         <v>0.12938</v>
       </c>
-      <c r="Q156" s="1" t="n">
-        <v>0.12781</v>
+      <c r="R156" s="1" t="n">
+        <v>0.1276</v>
       </c>
     </row>
     <row r="157">
@@ -9099,9 +9570,12 @@
         <v>0.4838</v>
       </c>
       <c r="P157" s="1" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="Q157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="Q157" s="1" t="n">
+      <c r="R157" s="1" t="n">
         <v>0.4838</v>
       </c>
     </row>
@@ -9154,9 +9628,12 @@
         <v>0.4514</v>
       </c>
       <c r="P158" s="1" t="n">
+        <v>0.4517</v>
+      </c>
+      <c r="Q158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="Q158" s="1" t="n">
+      <c r="R158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -9209,10 +9686,13 @@
         <v>0.007458</v>
       </c>
       <c r="P159" s="1" t="n">
+        <v>0.007456</v>
+      </c>
+      <c r="Q159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="Q159" s="1" t="n">
-        <v>0.007458</v>
+      <c r="R159" s="1" t="n">
+        <v>0.007456</v>
       </c>
     </row>
     <row r="160">
@@ -9264,9 +9744,12 @@
         <v>0.004654</v>
       </c>
       <c r="P160" s="1" t="n">
+        <v>0.004658</v>
+      </c>
+      <c r="Q160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="Q160" s="1" t="n">
+      <c r="R160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -9319,9 +9802,12 @@
         <v>0.00429</v>
       </c>
       <c r="P161" s="1" t="n">
+        <v>0.004294</v>
+      </c>
+      <c r="Q161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="Q161" s="1" t="n">
+      <c r="R161" s="1" t="n">
         <v>0.00429</v>
       </c>
     </row>
@@ -9374,9 +9860,12 @@
         <v>0.0956</v>
       </c>
       <c r="P162" s="1" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="Q162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="Q162" s="1" t="n">
+      <c r="R162" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -9429,9 +9918,12 @@
         <v>0.285</v>
       </c>
       <c r="P163" s="1" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="Q163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="Q163" s="1" t="n">
+      <c r="R163" s="1" t="n">
         <v>0.285</v>
       </c>
     </row>
@@ -9484,9 +9976,12 @@
         <v>0.1144</v>
       </c>
       <c r="P164" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="Q164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="Q164" s="1" t="n">
+      <c r="R164" s="1" t="n">
         <v>0.1139</v>
       </c>
     </row>
@@ -9539,9 +10034,12 @@
         <v>0.1753</v>
       </c>
       <c r="P165" s="1" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="Q165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="Q165" s="1" t="n">
+      <c r="R165" s="1" t="n">
         <v>0.1753</v>
       </c>
     </row>
@@ -9594,9 +10092,12 @@
         <v>0.01012</v>
       </c>
       <c r="P166" s="1" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="Q166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="Q166" s="1" t="n">
+      <c r="R166" s="1" t="n">
         <v>0.01006</v>
       </c>
     </row>
@@ -9649,10 +10150,13 @@
         <v>1.825</v>
       </c>
       <c r="P167" s="1" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="Q167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="Q167" s="1" t="n">
-        <v>1.825</v>
+      <c r="R167" s="1" t="n">
+        <v>1.823</v>
       </c>
     </row>
     <row r="168">
@@ -9704,9 +10208,12 @@
         <v>1.34</v>
       </c>
       <c r="P168" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="Q168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="Q168" s="1" t="n">
+      <c r="R168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -9759,9 +10266,12 @@
         <v>0.007296</v>
       </c>
       <c r="P169" s="1" t="n">
+        <v>0.007305</v>
+      </c>
+      <c r="Q169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="Q169" s="1" t="n">
+      <c r="R169" s="1" t="n">
         <v>0.007296</v>
       </c>
     </row>
@@ -9814,9 +10324,12 @@
         <v>0.0116</v>
       </c>
       <c r="P170" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="Q170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="Q170" s="1" t="n">
+      <c r="R170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -9869,9 +10382,12 @@
         <v>0.00578</v>
       </c>
       <c r="P171" s="1" t="n">
+        <v>0.005794</v>
+      </c>
+      <c r="Q171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="Q171" s="1" t="n">
+      <c r="R171" s="1" t="n">
         <v>0.00578</v>
       </c>
     </row>
@@ -9924,9 +10440,12 @@
         <v>0.14817</v>
       </c>
       <c r="P172" s="1" t="n">
-        <v>0.14822</v>
+        <v>0.14898</v>
       </c>
       <c r="Q172" s="1" t="n">
+        <v>0.14898</v>
+      </c>
+      <c r="R172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -9979,9 +10498,12 @@
         <v>4.895</v>
       </c>
       <c r="P173" s="1" t="n">
+        <v>4.886</v>
+      </c>
+      <c r="Q173" s="1" t="n">
         <v>4.909</v>
       </c>
-      <c r="Q173" s="1" t="n">
+      <c r="R173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -10034,9 +10556,12 @@
         <v>0.07819</v>
       </c>
       <c r="P174" s="1" t="n">
+        <v>0.07822</v>
+      </c>
+      <c r="Q174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="Q174" s="1" t="n">
+      <c r="R174" s="1" t="n">
         <v>0.07819</v>
       </c>
     </row>
@@ -10089,9 +10614,12 @@
         <v>0.007407</v>
       </c>
       <c r="P175" s="1" t="n">
+        <v>0.007421</v>
+      </c>
+      <c r="Q175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="Q175" s="1" t="n">
+      <c r="R175" s="1" t="n">
         <v>0.007407</v>
       </c>
     </row>
@@ -10144,9 +10672,12 @@
         <v>0.1997</v>
       </c>
       <c r="P176" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="Q176" s="1" t="n">
+      <c r="R176" s="1" t="n">
         <v>0.1997</v>
       </c>
     </row>
@@ -10199,9 +10730,12 @@
         <v>0.05185</v>
       </c>
       <c r="P177" s="1" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="Q177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="Q177" s="1" t="n">
+      <c r="R177" s="1" t="n">
         <v>0.05175</v>
       </c>
     </row>
@@ -10254,9 +10788,12 @@
         <v>0.05457</v>
       </c>
       <c r="P178" s="1" t="n">
+        <v>0.05473</v>
+      </c>
+      <c r="Q178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="Q178" s="1" t="n">
+      <c r="R178" s="1" t="n">
         <v>0.05455</v>
       </c>
     </row>
@@ -10309,9 +10846,12 @@
         <v>0.02317</v>
       </c>
       <c r="P179" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="Q179" s="1" t="n">
         <v>0.02338</v>
       </c>
-      <c r="Q179" s="1" t="n">
+      <c r="R179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -10364,9 +10904,12 @@
         <v>0.6951000000000001</v>
       </c>
       <c r="P180" s="1" t="n">
+        <v>0.6951000000000001</v>
+      </c>
+      <c r="Q180" s="1" t="n">
         <v>0.6976</v>
       </c>
-      <c r="Q180" s="1" t="n">
+      <c r="R180" s="1" t="n">
         <v>0.6938</v>
       </c>
     </row>
@@ -10419,9 +10962,12 @@
         <v>0.0003747</v>
       </c>
       <c r="P181" s="1" t="n">
+        <v>0.0003745</v>
+      </c>
+      <c r="Q181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="Q181" s="1" t="n">
+      <c r="R181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -10474,9 +11020,12 @@
         <v>0.01255</v>
       </c>
       <c r="P182" s="1" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="Q182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="Q182" s="1" t="n">
+      <c r="R182" s="1" t="n">
         <v>0.01255</v>
       </c>
     </row>
@@ -10529,9 +11078,12 @@
         <v>4.22</v>
       </c>
       <c r="P183" s="1" t="n">
+        <v>4.228</v>
+      </c>
+      <c r="Q183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="Q183" s="1" t="n">
+      <c r="R183" s="1" t="n">
         <v>4.22</v>
       </c>
     </row>
@@ -10584,9 +11136,12 @@
         <v>0.2354</v>
       </c>
       <c r="P184" s="1" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="Q184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="Q184" s="1" t="n">
+      <c r="R184" s="1" t="n">
         <v>0.2354</v>
       </c>
     </row>
@@ -10639,9 +11194,12 @@
         <v>0.03685</v>
       </c>
       <c r="P185" s="1" t="n">
+        <v>0.03684</v>
+      </c>
+      <c r="Q185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="Q185" s="1" t="n">
+      <c r="R185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -10694,10 +11252,13 @@
         <v>0.11584</v>
       </c>
       <c r="P186" s="1" t="n">
+        <v>0.11557</v>
+      </c>
+      <c r="Q186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="Q186" s="1" t="n">
-        <v>0.11566</v>
+      <c r="R186" s="1" t="n">
+        <v>0.11557</v>
       </c>
     </row>
     <row r="187">
@@ -10749,9 +11310,12 @@
         <v>0.009124999999999999</v>
       </c>
       <c r="P187" s="1" t="n">
+        <v>0.009169999999999999</v>
+      </c>
+      <c r="Q187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="Q187" s="1" t="n">
+      <c r="R187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -10804,9 +11368,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="P188" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="Q188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="Q188" s="1" t="n">
+      <c r="R188" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -10859,10 +11426,13 @@
         <v>0.02754</v>
       </c>
       <c r="P189" s="1" t="n">
+        <v>0.02749</v>
+      </c>
+      <c r="Q189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="Q189" s="1" t="n">
-        <v>0.02754</v>
+      <c r="R189" s="1" t="n">
+        <v>0.02749</v>
       </c>
     </row>
     <row r="190">
@@ -10914,9 +11484,12 @@
         <v>0.008670000000000001</v>
       </c>
       <c r="P190" s="1" t="n">
+        <v>0.008659999999999999</v>
+      </c>
+      <c r="Q190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="Q190" s="1" t="n">
+      <c r="R190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -10969,9 +11542,12 @@
         <v>0.001951</v>
       </c>
       <c r="P191" s="1" t="n">
+        <v>0.001951</v>
+      </c>
+      <c r="Q191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="Q191" s="1" t="n">
+      <c r="R191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -11024,9 +11600,12 @@
         <v>0.1001</v>
       </c>
       <c r="P192" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="Q192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="Q192" s="1" t="n">
+      <c r="R192" s="1" t="n">
         <v>0.1001</v>
       </c>
     </row>
@@ -11079,10 +11658,13 @@
         <v>0.02315</v>
       </c>
       <c r="P193" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="Q193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="Q193" s="1" t="n">
-        <v>0.02315</v>
+      <c r="R193" s="1" t="n">
+        <v>0.02312</v>
       </c>
     </row>
     <row r="194">
@@ -11134,9 +11716,12 @@
         <v>0.01342</v>
       </c>
       <c r="P194" s="1" t="n">
+        <v>0.01343</v>
+      </c>
+      <c r="Q194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="Q194" s="1" t="n">
+      <c r="R194" s="1" t="n">
         <v>0.01342</v>
       </c>
     </row>
@@ -11189,9 +11774,12 @@
         <v>0.02079</v>
       </c>
       <c r="P195" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Q195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="Q195" s="1" t="n">
+      <c r="R195" s="1" t="n">
         <v>0.02079</v>
       </c>
     </row>
@@ -11244,9 +11832,12 @@
         <v>0.17602</v>
       </c>
       <c r="P196" s="1" t="n">
-        <v>0.1762</v>
+        <v>0.17643</v>
       </c>
       <c r="Q196" s="1" t="n">
+        <v>0.17643</v>
+      </c>
+      <c r="R196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -11299,9 +11890,12 @@
         <v>0.00735</v>
       </c>
       <c r="P197" s="1" t="n">
+        <v>0.00734</v>
+      </c>
+      <c r="Q197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="Q197" s="1" t="n">
+      <c r="R197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -11354,9 +11948,12 @@
         <v>0.01906</v>
       </c>
       <c r="P198" s="1" t="n">
+        <v>0.01908</v>
+      </c>
+      <c r="Q198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="Q198" s="1" t="n">
+      <c r="R198" s="1" t="n">
         <v>0.01904</v>
       </c>
     </row>
@@ -11409,9 +12006,12 @@
         <v>0.01634</v>
       </c>
       <c r="P199" s="1" t="n">
+        <v>0.01657</v>
+      </c>
+      <c r="Q199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="Q199" s="1" t="n">
+      <c r="R199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -11464,9 +12064,12 @@
         <v>0.2972</v>
       </c>
       <c r="P200" s="1" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="Q200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="Q200" s="1" t="n">
+      <c r="R200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -11519,9 +12122,12 @@
         <v>0.006229</v>
       </c>
       <c r="P201" s="1" t="n">
+        <v>0.006224</v>
+      </c>
+      <c r="Q201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="Q201" s="1" t="n">
+      <c r="R201" s="1" t="n">
         <v>0.006205</v>
       </c>
     </row>
@@ -11574,9 +12180,12 @@
         <v>0.0004411</v>
       </c>
       <c r="P202" s="1" t="n">
+        <v>0.0004411</v>
+      </c>
+      <c r="Q202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="Q202" s="1" t="n">
+      <c r="R202" s="1" t="n">
         <v>0.0004411</v>
       </c>
     </row>
@@ -11629,9 +12238,12 @@
         <v>0.007251</v>
       </c>
       <c r="P203" s="1" t="n">
+        <v>0.007276</v>
+      </c>
+      <c r="Q203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="Q203" s="1" t="n">
+      <c r="R203" s="1" t="n">
         <v>0.007251</v>
       </c>
     </row>
@@ -11684,9 +12296,12 @@
         <v>0.131</v>
       </c>
       <c r="P204" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="Q204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="Q204" s="1" t="n">
+      <c r="R204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -11739,9 +12354,12 @@
         <v>0.01421</v>
       </c>
       <c r="P205" s="1" t="n">
+        <v>0.01415</v>
+      </c>
+      <c r="Q205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="Q205" s="1" t="n">
+      <c r="R205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -11794,9 +12412,12 @@
         <v>0.003566</v>
       </c>
       <c r="P206" s="1" t="n">
+        <v>0.003565</v>
+      </c>
+      <c r="Q206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="Q206" s="1" t="n">
+      <c r="R206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -11849,10 +12470,13 @@
         <v>0.05948</v>
       </c>
       <c r="P207" s="1" t="n">
+        <v>0.05937</v>
+      </c>
+      <c r="Q207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="Q207" s="1" t="n">
-        <v>0.0594</v>
+      <c r="R207" s="1" t="n">
+        <v>0.05937</v>
       </c>
     </row>
     <row r="208">
@@ -11904,9 +12528,12 @@
         <v>15.42</v>
       </c>
       <c r="P208" s="1" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="Q208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="Q208" s="1" t="n">
+      <c r="R208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -11959,9 +12586,12 @@
         <v>5193.5</v>
       </c>
       <c r="P209" s="1" t="n">
+        <v>5192.1</v>
+      </c>
+      <c r="Q209" s="1" t="n">
         <v>5193.5</v>
       </c>
-      <c r="Q209" s="1" t="n">
+      <c r="R209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -12014,9 +12644,12 @@
         <v>0.1202</v>
       </c>
       <c r="P210" s="1" t="n">
+        <v>0.12027</v>
+      </c>
+      <c r="Q210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="Q210" s="1" t="n">
+      <c r="R210" s="1" t="n">
         <v>0.11955</v>
       </c>
     </row>
@@ -12069,9 +12702,12 @@
         <v>0.1804</v>
       </c>
       <c r="P211" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="Q211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="Q211" s="1" t="n">
+      <c r="R211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -12124,9 +12760,12 @@
         <v>0.0309</v>
       </c>
       <c r="P212" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="Q212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="Q212" s="1" t="n">
+      <c r="R212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -12179,9 +12818,12 @@
         <v>1.3967</v>
       </c>
       <c r="P213" s="1" t="n">
-        <v>1.3976</v>
+        <v>1.3979</v>
       </c>
       <c r="Q213" s="1" t="n">
+        <v>1.3979</v>
+      </c>
+      <c r="R213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -12234,9 +12876,12 @@
         <v>0.05641</v>
       </c>
       <c r="P214" s="1" t="n">
+        <v>0.05641</v>
+      </c>
+      <c r="Q214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="Q214" s="1" t="n">
+      <c r="R214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -12289,9 +12934,12 @@
         <v>0.04431</v>
       </c>
       <c r="P215" s="1" t="n">
-        <v>0.04431</v>
+        <v>0.04437</v>
       </c>
       <c r="Q215" s="1" t="n">
+        <v>0.04437</v>
+      </c>
+      <c r="R215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -12344,9 +12992,12 @@
         <v>0.15043</v>
       </c>
       <c r="P216" s="1" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="Q216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="Q216" s="1" t="n">
+      <c r="R216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -12399,9 +13050,12 @@
         <v>0.073</v>
       </c>
       <c r="P217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="Q217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="Q217" s="1" t="n">
+      <c r="R217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -12454,9 +13108,12 @@
         <v>0.00268</v>
       </c>
       <c r="P218" s="1" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="Q218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="Q218" s="1" t="n">
+      <c r="R218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -12509,9 +13166,12 @@
         <v>0.01703</v>
       </c>
       <c r="P219" s="1" t="n">
+        <v>0.01703</v>
+      </c>
+      <c r="Q219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="Q219" s="1" t="n">
+      <c r="R219" s="1" t="n">
         <v>0.01703</v>
       </c>
     </row>
@@ -12564,9 +13224,12 @@
         <v>0.05516</v>
       </c>
       <c r="P220" s="1" t="n">
+        <v>0.05512</v>
+      </c>
+      <c r="Q220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="Q220" s="1" t="n">
+      <c r="R220" s="1" t="n">
         <v>0.05507</v>
       </c>
     </row>
@@ -12619,9 +13282,12 @@
         <v>0.02184</v>
       </c>
       <c r="P221" s="1" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="Q221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="Q221" s="1" t="n">
+      <c r="R221" s="1" t="n">
         <v>0.02182</v>
       </c>
     </row>
@@ -12674,9 +13340,12 @@
         <v>0.00936</v>
       </c>
       <c r="P222" s="1" t="n">
+        <v>0.00937</v>
+      </c>
+      <c r="Q222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="Q222" s="1" t="n">
+      <c r="R222" s="1" t="n">
         <v>0.009339999999999999</v>
       </c>
     </row>
@@ -12729,9 +13398,12 @@
         <v>0.0165</v>
       </c>
       <c r="P223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="Q223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="Q223" s="1" t="n">
+      <c r="R223" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -12784,9 +13456,12 @@
         <v>0.03826</v>
       </c>
       <c r="P224" s="1" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="Q224" s="1" t="n">
         <v>0.03841</v>
       </c>
-      <c r="Q224" s="1" t="n">
+      <c r="R224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -12839,9 +13514,12 @@
         <v>0.001522</v>
       </c>
       <c r="P225" s="1" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="Q225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="Q225" s="1" t="n">
+      <c r="R225" s="1" t="n">
         <v>0.001522</v>
       </c>
     </row>
@@ -12894,9 +13572,12 @@
         <v>27.2</v>
       </c>
       <c r="P226" s="1" t="n">
+        <v>27.11</v>
+      </c>
+      <c r="Q226" s="1" t="n">
         <v>27.2</v>
       </c>
-      <c r="Q226" s="1" t="n">
+      <c r="R226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -12949,9 +13630,12 @@
         <v>0.07054000000000001</v>
       </c>
       <c r="P227" s="1" t="n">
+        <v>0.07043000000000001</v>
+      </c>
+      <c r="Q227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="Q227" s="1" t="n">
+      <c r="R227" s="1" t="n">
         <v>0.07015</v>
       </c>
     </row>
@@ -13004,9 +13688,12 @@
         <v>0.3126</v>
       </c>
       <c r="P228" s="1" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="Q228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="Q228" s="1" t="n">
+      <c r="R228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -13059,9 +13746,12 @@
         <v>18.33</v>
       </c>
       <c r="P229" s="1" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="Q229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="Q229" s="1" t="n">
+      <c r="R229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -13114,9 +13804,12 @@
         <v>0.01921</v>
       </c>
       <c r="P230" s="1" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="Q230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="Q230" s="1" t="n">
+      <c r="R230" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -13169,9 +13862,12 @@
         <v>0.01216</v>
       </c>
       <c r="P231" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="Q231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="Q231" s="1" t="n">
+      <c r="R231" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -13224,9 +13920,12 @@
         <v>0.228</v>
       </c>
       <c r="P232" s="1" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="Q232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="Q232" s="1" t="n">
+      <c r="R232" s="1" t="n">
         <v>0.2274</v>
       </c>
     </row>
@@ -13279,9 +13978,12 @@
         <v>0.07091</v>
       </c>
       <c r="P233" s="1" t="n">
+        <v>0.07091</v>
+      </c>
+      <c r="Q233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="Q233" s="1" t="n">
+      <c r="R233" s="1" t="n">
         <v>0.07087</v>
       </c>
     </row>
@@ -13334,9 +14036,12 @@
         <v>0.1703</v>
       </c>
       <c r="P234" s="1" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="Q234" s="1" t="n">
         <v>0.1706</v>
       </c>
-      <c r="Q234" s="1" t="n">
+      <c r="R234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -13389,10 +14094,13 @@
         <v>0.0252</v>
       </c>
       <c r="P235" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="Q235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="Q235" s="1" t="n">
-        <v>0.0251</v>
+      <c r="R235" s="1" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="236">
@@ -13444,10 +14152,13 @@
         <v>0.02997</v>
       </c>
       <c r="P236" s="1" t="n">
+        <v>0.02995</v>
+      </c>
+      <c r="Q236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="Q236" s="1" t="n">
-        <v>0.02996</v>
+      <c r="R236" s="1" t="n">
+        <v>0.02995</v>
       </c>
     </row>
     <row r="237">
@@ -13499,9 +14210,12 @@
         <v>1.997</v>
       </c>
       <c r="P237" s="1" t="n">
-        <v>2.001</v>
+        <v>2.006</v>
       </c>
       <c r="Q237" s="1" t="n">
+        <v>2.006</v>
+      </c>
+      <c r="R237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -13554,9 +14268,12 @@
         <v>0.42</v>
       </c>
       <c r="P238" s="1" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="Q238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="Q238" s="1" t="n">
+      <c r="R238" s="1" t="n">
         <v>0.42</v>
       </c>
     </row>
@@ -13609,9 +14326,12 @@
         <v>0.03356</v>
       </c>
       <c r="P239" s="1" t="n">
+        <v>0.03354</v>
+      </c>
+      <c r="Q239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="Q239" s="1" t="n">
+      <c r="R239" s="1" t="n">
         <v>0.03328</v>
       </c>
     </row>
@@ -13664,9 +14384,12 @@
         <v>0.03392</v>
       </c>
       <c r="P240" s="1" t="n">
+        <v>0.03401</v>
+      </c>
+      <c r="Q240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="Q240" s="1" t="n">
+      <c r="R240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -13719,9 +14442,12 @@
         <v>0.0007497</v>
       </c>
       <c r="P241" s="1" t="n">
+        <v>0.0007507</v>
+      </c>
+      <c r="Q241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="Q241" s="1" t="n">
+      <c r="R241" s="1" t="n">
         <v>0.0007489</v>
       </c>
     </row>
@@ -13774,9 +14500,12 @@
         <v>0.1828</v>
       </c>
       <c r="P242" s="1" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="Q242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="Q242" s="1" t="n">
+      <c r="R242" s="1" t="n">
         <v>0.1828</v>
       </c>
     </row>
@@ -13829,9 +14558,12 @@
         <v>0.014735</v>
       </c>
       <c r="P243" s="1" t="n">
+        <v>0.014755</v>
+      </c>
+      <c r="Q243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="Q243" s="1" t="n">
+      <c r="R243" s="1" t="n">
         <v>0.014735</v>
       </c>
     </row>
@@ -13884,9 +14616,12 @@
         <v>3.02e-05</v>
       </c>
       <c r="P244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="Q244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="Q244" s="1" t="n">
+      <c r="R244" s="1" t="n">
         <v>3.01e-05</v>
       </c>
     </row>
@@ -13939,9 +14674,12 @@
         <v>0.03516</v>
       </c>
       <c r="P245" s="1" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="Q245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="Q245" s="1" t="n">
+      <c r="R245" s="1" t="n">
         <v>0.03514</v>
       </c>
     </row>
@@ -13994,9 +14732,12 @@
         <v>0.08033999999999999</v>
       </c>
       <c r="P246" s="1" t="n">
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="Q246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="Q246" s="1" t="n">
+      <c r="R246" s="1" t="n">
         <v>0.08033999999999999</v>
       </c>
     </row>
@@ -14049,10 +14790,13 @@
         <v>0.007234</v>
       </c>
       <c r="P247" s="1" t="n">
+        <v>0.007229</v>
+      </c>
+      <c r="Q247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="Q247" s="1" t="n">
-        <v>0.007234</v>
+      <c r="R247" s="1" t="n">
+        <v>0.007229</v>
       </c>
     </row>
     <row r="248">
@@ -14104,9 +14848,12 @@
         <v>0.09522</v>
       </c>
       <c r="P248" s="1" t="n">
+        <v>0.09452000000000001</v>
+      </c>
+      <c r="Q248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="Q248" s="1" t="n">
+      <c r="R248" s="1" t="n">
         <v>0.09438000000000001</v>
       </c>
     </row>
@@ -14162,6 +14909,9 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="Q249" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="R249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -14214,9 +14964,12 @@
         <v>0.0348</v>
       </c>
       <c r="P250" s="1" t="n">
+        <v>0.03483</v>
+      </c>
+      <c r="Q250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="Q250" s="1" t="n">
+      <c r="R250" s="1" t="n">
         <v>0.0348</v>
       </c>
     </row>
@@ -14269,10 +15022,13 @@
         <v>0.03944</v>
       </c>
       <c r="P251" s="1" t="n">
+        <v>0.03916</v>
+      </c>
+      <c r="Q251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="Q251" s="1" t="n">
-        <v>0.03944</v>
+      <c r="R251" s="1" t="n">
+        <v>0.03916</v>
       </c>
     </row>
     <row r="252">
@@ -14324,9 +15080,12 @@
         <v>0.0892</v>
       </c>
       <c r="P252" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="Q252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="Q252" s="1" t="n">
+      <c r="R252" s="1" t="n">
         <v>0.089</v>
       </c>
     </row>
@@ -14379,9 +15138,12 @@
         <v>4.07</v>
       </c>
       <c r="P253" s="1" t="n">
+        <v>4.083</v>
+      </c>
+      <c r="Q253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="Q253" s="1" t="n">
+      <c r="R253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -14434,9 +15196,12 @@
         <v>0.187</v>
       </c>
       <c r="P254" s="1" t="n">
-        <v>0.1875</v>
+        <v>0.1877</v>
       </c>
       <c r="Q254" s="1" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="R254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -14489,10 +15254,13 @@
         <v>0.07185999999999999</v>
       </c>
       <c r="P255" s="1" t="n">
+        <v>0.07185</v>
+      </c>
+      <c r="Q255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="Q255" s="1" t="n">
-        <v>0.07185999999999999</v>
+      <c r="R255" s="1" t="n">
+        <v>0.07185</v>
       </c>
     </row>
     <row r="256">
@@ -14544,9 +15312,12 @@
         <v>0.01824</v>
       </c>
       <c r="P256" s="1" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="Q256" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="Q256" s="1" t="n">
+      <c r="R256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -14599,9 +15370,12 @@
         <v>5.933</v>
       </c>
       <c r="P257" s="1" t="n">
+        <v>5.942</v>
+      </c>
+      <c r="Q257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="Q257" s="1" t="n">
+      <c r="R257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -14654,9 +15428,12 @@
         <v>0.261</v>
       </c>
       <c r="P258" s="1" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="Q258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="Q258" s="1" t="n">
+      <c r="R258" s="1" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -14709,9 +15486,12 @@
         <v>0.1357</v>
       </c>
       <c r="P259" s="1" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="Q259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="Q259" s="1" t="n">
+      <c r="R259" s="1" t="n">
         <v>0.1356</v>
       </c>
     </row>
@@ -14764,9 +15544,12 @@
         <v>0.30501</v>
       </c>
       <c r="P260" s="1" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="Q260" s="1" t="n">
         <v>0.30784</v>
       </c>
-      <c r="Q260" s="1" t="n">
+      <c r="R260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -14819,9 +15602,12 @@
         <v>0.09961</v>
       </c>
       <c r="P261" s="1" t="n">
+        <v>0.09927999999999999</v>
+      </c>
+      <c r="Q261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="Q261" s="1" t="n">
+      <c r="R261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -14874,9 +15660,12 @@
         <v>0.538</v>
       </c>
       <c r="P262" s="1" t="n">
+        <v>0.5389</v>
+      </c>
+      <c r="Q262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="Q262" s="1" t="n">
+      <c r="R262" s="1" t="n">
         <v>0.538</v>
       </c>
     </row>
@@ -14929,10 +15718,13 @@
         <v>0.2915</v>
       </c>
       <c r="P263" s="1" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="Q263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="Q263" s="1" t="n">
-        <v>0.2914</v>
+      <c r="R263" s="1" t="n">
+        <v>0.2903</v>
       </c>
     </row>
     <row r="264">
@@ -14984,9 +15776,12 @@
         <v>0.974</v>
       </c>
       <c r="P264" s="1" t="n">
-        <v>0.974</v>
+        <v>0.983</v>
       </c>
       <c r="Q264" s="1" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="R264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -15039,9 +15834,12 @@
         <v>0.5399</v>
       </c>
       <c r="P265" s="1" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="Q265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="Q265" s="1" t="n">
+      <c r="R265" s="1" t="n">
         <v>0.5394</v>
       </c>
     </row>
@@ -15094,9 +15892,12 @@
         <v>0.07355</v>
       </c>
       <c r="P266" s="1" t="n">
+        <v>0.07356</v>
+      </c>
+      <c r="Q266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="Q266" s="1" t="n">
+      <c r="R266" s="1" t="n">
         <v>0.07355</v>
       </c>
     </row>
@@ -15149,9 +15950,12 @@
         <v>0.02154</v>
       </c>
       <c r="P267" s="1" t="n">
+        <v>0.02167</v>
+      </c>
+      <c r="Q267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="Q267" s="1" t="n">
+      <c r="R267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -15204,9 +16008,12 @@
         <v>0.01624</v>
       </c>
       <c r="P268" s="1" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="Q268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="Q268" s="1" t="n">
+      <c r="R268" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -15259,9 +16066,12 @@
         <v>0.003804</v>
       </c>
       <c r="P269" s="1" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="Q269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="Q269" s="1" t="n">
+      <c r="R269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -15314,9 +16124,12 @@
         <v>0.00761</v>
       </c>
       <c r="P270" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="Q270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="Q270" s="1" t="n">
+      <c r="R270" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -15369,9 +16182,12 @@
         <v>0.05504</v>
       </c>
       <c r="P271" s="1" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="Q271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="Q271" s="1" t="n">
+      <c r="R271" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -15424,9 +16240,12 @@
         <v>2.271</v>
       </c>
       <c r="P272" s="1" t="n">
+        <v>2.273</v>
+      </c>
+      <c r="Q272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="Q272" s="1" t="n">
+      <c r="R272" s="1" t="n">
         <v>2.271</v>
       </c>
     </row>
@@ -15479,9 +16298,12 @@
         <v>0.05489</v>
       </c>
       <c r="P273" s="1" t="n">
+        <v>0.05494</v>
+      </c>
+      <c r="Q273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="Q273" s="1" t="n">
+      <c r="R273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -15534,9 +16356,12 @@
         <v>0.02325</v>
       </c>
       <c r="P274" s="1" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="Q274" s="1" t="n">
         <v>0.02336</v>
       </c>
-      <c r="Q274" s="1" t="n">
+      <c r="R274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -15589,9 +16414,12 @@
         <v>1.178</v>
       </c>
       <c r="P275" s="1" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="Q275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="Q275" s="1" t="n">
+      <c r="R275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -15644,9 +16472,12 @@
         <v>0.2706</v>
       </c>
       <c r="P276" s="1" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="Q276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="Q276" s="1" t="n">
+      <c r="R276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -15699,9 +16530,12 @@
         <v>0.929</v>
       </c>
       <c r="P277" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="Q277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="Q277" s="1" t="n">
+      <c r="R277" s="1" t="n">
         <v>0.929</v>
       </c>
     </row>
@@ -15754,9 +16588,12 @@
         <v>0.6221</v>
       </c>
       <c r="P278" s="1" t="n">
+        <v>0.6236</v>
+      </c>
+      <c r="Q278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="Q278" s="1" t="n">
+      <c r="R278" s="1" t="n">
         <v>0.6221</v>
       </c>
     </row>
@@ -15809,9 +16646,12 @@
         <v>0.001341</v>
       </c>
       <c r="P279" s="1" t="n">
+        <v>0.001343</v>
+      </c>
+      <c r="Q279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="Q279" s="1" t="n">
+      <c r="R279" s="1" t="n">
         <v>0.001341</v>
       </c>
     </row>
@@ -15864,9 +16704,12 @@
         <v>0.005579</v>
       </c>
       <c r="P280" s="1" t="n">
-        <v>0.005581</v>
+        <v>0.005601</v>
       </c>
       <c r="Q280" s="1" t="n">
+        <v>0.005601</v>
+      </c>
+      <c r="R280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -15919,9 +16762,12 @@
         <v>1.516</v>
       </c>
       <c r="P281" s="1" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="Q281" s="1" t="n">
+      <c r="R281" s="1" t="n">
         <v>1.516</v>
       </c>
     </row>
@@ -15974,9 +16820,12 @@
         <v>28.26</v>
       </c>
       <c r="P282" s="1" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="Q282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="Q282" s="1" t="n">
+      <c r="R282" s="1" t="n">
         <v>28.26</v>
       </c>
     </row>
@@ -16029,9 +16878,12 @@
         <v>0.12839</v>
       </c>
       <c r="P283" s="1" t="n">
+        <v>0.12846</v>
+      </c>
+      <c r="Q283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="Q283" s="1" t="n">
+      <c r="R283" s="1" t="n">
         <v>0.12839</v>
       </c>
     </row>
@@ -16084,9 +16936,12 @@
         <v>0.01108</v>
       </c>
       <c r="P284" s="1" t="n">
+        <v>0.01109</v>
+      </c>
+      <c r="Q284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="Q284" s="1" t="n">
+      <c r="R284" s="1" t="n">
         <v>0.01108</v>
       </c>
     </row>
@@ -16139,9 +16994,12 @@
         <v>6.55</v>
       </c>
       <c r="P285" s="1" t="n">
+        <v>6.549</v>
+      </c>
+      <c r="Q285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="Q285" s="1" t="n">
+      <c r="R285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -16194,9 +17052,12 @@
         <v>0.01838</v>
       </c>
       <c r="P286" s="1" t="n">
+        <v>0.01842</v>
+      </c>
+      <c r="Q286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="Q286" s="1" t="n">
+      <c r="R286" s="1" t="n">
         <v>0.01838</v>
       </c>
     </row>
@@ -16249,10 +17110,13 @@
         <v>0.008356000000000001</v>
       </c>
       <c r="P287" s="1" t="n">
+        <v>0.008348</v>
+      </c>
+      <c r="Q287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="Q287" s="1" t="n">
-        <v>0.008356000000000001</v>
+      <c r="R287" s="1" t="n">
+        <v>0.008348</v>
       </c>
     </row>
     <row r="288">
@@ -16304,10 +17168,13 @@
         <v>0.3812</v>
       </c>
       <c r="P288" s="1" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="Q288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="Q288" s="1" t="n">
-        <v>0.3812</v>
+      <c r="R288" s="1" t="n">
+        <v>0.3803</v>
       </c>
     </row>
     <row r="289">
@@ -16359,10 +17226,13 @@
         <v>0.009905000000000001</v>
       </c>
       <c r="P289" s="1" t="n">
+        <v>0.009882999999999999</v>
+      </c>
+      <c r="Q289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="Q289" s="1" t="n">
-        <v>0.009905000000000001</v>
+      <c r="R289" s="1" t="n">
+        <v>0.009882999999999999</v>
       </c>
     </row>
     <row r="290">
@@ -16414,9 +17284,12 @@
         <v>0.02585</v>
       </c>
       <c r="P290" s="1" t="n">
+        <v>0.02593</v>
+      </c>
+      <c r="Q290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="Q290" s="1" t="n">
+      <c r="R290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -16469,9 +17342,12 @@
         <v>0.096</v>
       </c>
       <c r="P291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="Q291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="Q291" s="1" t="n">
+      <c r="R291" s="1" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -16524,9 +17400,12 @@
         <v>0.28734</v>
       </c>
       <c r="P292" s="1" t="n">
-        <v>0.28734</v>
+        <v>0.28764</v>
       </c>
       <c r="Q292" s="1" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="R292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -16579,9 +17458,12 @@
         <v>0.01538</v>
       </c>
       <c r="P293" s="1" t="n">
+        <v>0.01536</v>
+      </c>
+      <c r="Q293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="Q293" s="1" t="n">
+      <c r="R293" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -16634,10 +17516,13 @@
         <v>0.003417</v>
       </c>
       <c r="P294" s="1" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="Q294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="Q294" s="1" t="n">
-        <v>0.003412</v>
+      <c r="R294" s="1" t="n">
+        <v>0.00341</v>
       </c>
     </row>
     <row r="295">
@@ -16689,9 +17574,12 @@
         <v>0.042629</v>
       </c>
       <c r="P295" s="1" t="n">
+        <v>0.042856</v>
+      </c>
+      <c r="Q295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="Q295" s="1" t="n">
+      <c r="R295" s="1" t="n">
         <v>0.042629</v>
       </c>
     </row>
@@ -16744,10 +17632,13 @@
         <v>0.02902</v>
       </c>
       <c r="P296" s="1" t="n">
+        <v>0.02894</v>
+      </c>
+      <c r="Q296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="Q296" s="1" t="n">
-        <v>0.02902</v>
+      <c r="R296" s="1" t="n">
+        <v>0.02894</v>
       </c>
     </row>
     <row r="297">
@@ -16799,9 +17690,12 @@
         <v>0.03797</v>
       </c>
       <c r="P297" s="1" t="n">
+        <v>0.03791</v>
+      </c>
+      <c r="Q297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="Q297" s="1" t="n">
+      <c r="R297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -16854,9 +17748,12 @@
         <v>0.08255</v>
       </c>
       <c r="P298" s="1" t="n">
+        <v>0.08298999999999999</v>
+      </c>
+      <c r="Q298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="Q298" s="1" t="n">
+      <c r="R298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -16909,9 +17806,12 @@
         <v>0.00766</v>
       </c>
       <c r="P299" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="Q299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="Q299" s="1" t="n">
+      <c r="R299" s="1" t="n">
         <v>0.00761</v>
       </c>
     </row>
@@ -16964,9 +17864,12 @@
         <v>0.01505</v>
       </c>
       <c r="P300" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="Q300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="Q300" s="1" t="n">
+      <c r="R300" s="1" t="n">
         <v>0.01505</v>
       </c>
     </row>
@@ -17019,9 +17922,12 @@
         <v>0.1399</v>
       </c>
       <c r="P301" s="1" t="n">
+        <v>0.1403</v>
+      </c>
+      <c r="Q301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="Q301" s="1" t="n">
+      <c r="R301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -17074,9 +17980,12 @@
         <v>0.0006229</v>
       </c>
       <c r="P302" s="1" t="n">
+        <v>0.0006288</v>
+      </c>
+      <c r="Q302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="Q302" s="1" t="n">
+      <c r="R302" s="1" t="n">
         <v>0.0006229</v>
       </c>
     </row>
@@ -17129,9 +18038,12 @@
         <v>0.06239</v>
       </c>
       <c r="P303" s="1" t="n">
+        <v>0.06234</v>
+      </c>
+      <c r="Q303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="Q303" s="1" t="n">
+      <c r="R303" s="1" t="n">
         <v>0.0621</v>
       </c>
     </row>
@@ -17184,10 +18096,13 @@
         <v>0.0001626</v>
       </c>
       <c r="P304" s="1" t="n">
+        <v>0.0001624</v>
+      </c>
+      <c r="Q304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="Q304" s="1" t="n">
-        <v>0.0001626</v>
+      <c r="R304" s="1" t="n">
+        <v>0.0001624</v>
       </c>
     </row>
     <row r="305">
@@ -17239,9 +18154,12 @@
         <v>0.06076</v>
       </c>
       <c r="P305" s="1" t="n">
+        <v>0.06081</v>
+      </c>
+      <c r="Q305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="Q305" s="1" t="n">
+      <c r="R305" s="1" t="n">
         <v>0.06076</v>
       </c>
     </row>
@@ -17294,9 +18212,12 @@
         <v>0.02249</v>
       </c>
       <c r="P306" s="1" t="n">
+        <v>0.022482</v>
+      </c>
+      <c r="Q306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="Q306" s="1" t="n">
+      <c r="R306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -17349,9 +18270,12 @@
         <v>0.02417</v>
       </c>
       <c r="P307" s="1" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="Q307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="Q307" s="1" t="n">
+      <c r="R307" s="1" t="n">
         <v>0.02332</v>
       </c>
     </row>
@@ -17404,9 +18328,12 @@
         <v>0.000411</v>
       </c>
       <c r="P308" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="Q308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="Q308" s="1" t="n">
+      <c r="R308" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -17459,9 +18386,12 @@
         <v>0.0897</v>
       </c>
       <c r="P309" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="Q309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="Q309" s="1" t="n">
+      <c r="R309" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -17514,10 +18444,13 @@
         <v>0.3681</v>
       </c>
       <c r="P310" s="1" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="Q310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="Q310" s="1" t="n">
-        <v>0.3681</v>
+      <c r="R310" s="1" t="n">
+        <v>0.3664</v>
       </c>
     </row>
     <row r="311">
@@ -17569,9 +18502,12 @@
         <v>0.0353</v>
       </c>
       <c r="P311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="Q311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="Q311" s="1" t="n">
+      <c r="R311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -17624,10 +18560,13 @@
         <v>0.0245</v>
       </c>
       <c r="P312" s="1" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="Q312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="Q312" s="1" t="n">
-        <v>0.02445</v>
+      <c r="R312" s="1" t="n">
+        <v>0.0244</v>
       </c>
     </row>
     <row r="313">
@@ -17679,10 +18618,13 @@
         <v>0.04115</v>
       </c>
       <c r="P313" s="1" t="n">
+        <v>0.04106</v>
+      </c>
+      <c r="Q313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="Q313" s="1" t="n">
-        <v>0.04115</v>
+      <c r="R313" s="1" t="n">
+        <v>0.04106</v>
       </c>
     </row>
     <row r="314">
@@ -17734,10 +18676,13 @@
         <v>3.966</v>
       </c>
       <c r="P314" s="1" t="n">
+        <v>3.964</v>
+      </c>
+      <c r="Q314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="Q314" s="1" t="n">
-        <v>3.966</v>
+      <c r="R314" s="1" t="n">
+        <v>3.964</v>
       </c>
     </row>
     <row r="315">
@@ -17789,9 +18734,12 @@
         <v>0.1594</v>
       </c>
       <c r="P315" s="1" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="Q315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="Q315" s="1" t="n">
+      <c r="R315" s="1" t="n">
         <v>0.1594</v>
       </c>
     </row>
@@ -17844,9 +18792,12 @@
         <v>0.09142</v>
       </c>
       <c r="P316" s="1" t="n">
+        <v>0.09016</v>
+      </c>
+      <c r="Q316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="Q316" s="1" t="n">
+      <c r="R316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -17899,9 +18850,12 @@
         <v>0.06791999999999999</v>
       </c>
       <c r="P317" s="1" t="n">
+        <v>0.06796000000000001</v>
+      </c>
+      <c r="Q317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="Q317" s="1" t="n">
+      <c r="R317" s="1" t="n">
         <v>0.06791999999999999</v>
       </c>
     </row>
@@ -17954,9 +18908,12 @@
         <v>0.012459</v>
       </c>
       <c r="P318" s="1" t="n">
+        <v>0.012421</v>
+      </c>
+      <c r="Q318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="Q318" s="1" t="n">
+      <c r="R318" s="1" t="n">
         <v>0.012414</v>
       </c>
     </row>
@@ -18009,10 +18966,13 @@
         <v>0.001134</v>
       </c>
       <c r="P319" s="1" t="n">
+        <v>0.001133</v>
+      </c>
+      <c r="Q319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="Q319" s="1" t="n">
-        <v>0.001134</v>
+      <c r="R319" s="1" t="n">
+        <v>0.001133</v>
       </c>
     </row>
     <row r="320">
@@ -18064,9 +19024,12 @@
         <v>0.0629</v>
       </c>
       <c r="P320" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="Q320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="Q320" s="1" t="n">
+      <c r="R320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -18119,9 +19082,12 @@
         <v>0.00524</v>
       </c>
       <c r="P321" s="1" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="Q321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="Q321" s="1" t="n">
+      <c r="R321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -18174,9 +19140,12 @@
         <v>0.1122</v>
       </c>
       <c r="P322" s="1" t="n">
+        <v>0.1117</v>
+      </c>
+      <c r="Q322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="Q322" s="1" t="n">
+      <c r="R322" s="1" t="n">
         <v>0.1113</v>
       </c>
     </row>
@@ -18229,9 +19198,12 @@
         <v>0.04346</v>
       </c>
       <c r="P323" s="1" t="n">
-        <v>0.0437</v>
+        <v>0.04376</v>
       </c>
       <c r="Q323" s="1" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="R323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -18284,9 +19256,12 @@
         <v>0.01787</v>
       </c>
       <c r="P324" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="Q324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="Q324" s="1" t="n">
+      <c r="R324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -18339,10 +19314,13 @@
         <v>0.005652</v>
       </c>
       <c r="P325" s="1" t="n">
+        <v>0.005638</v>
+      </c>
+      <c r="Q325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="Q325" s="1" t="n">
-        <v>0.005652</v>
+      <c r="R325" s="1" t="n">
+        <v>0.005638</v>
       </c>
     </row>
     <row r="326">
@@ -18394,9 +19372,12 @@
         <v>0.001757</v>
       </c>
       <c r="P326" s="1" t="n">
+        <v>0.001757</v>
+      </c>
+      <c r="Q326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="Q326" s="1" t="n">
+      <c r="R326" s="1" t="n">
         <v>0.001757</v>
       </c>
     </row>
@@ -18449,10 +19430,13 @@
         <v>0.04029</v>
       </c>
       <c r="P327" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="Q327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="Q327" s="1" t="n">
-        <v>0.04029</v>
+      <c r="R327" s="1" t="n">
+        <v>0.04022</v>
       </c>
     </row>
     <row r="328">
@@ -18504,9 +19488,12 @@
         <v>0.053569</v>
       </c>
       <c r="P328" s="1" t="n">
+        <v>0.053699</v>
+      </c>
+      <c r="Q328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="Q328" s="1" t="n">
+      <c r="R328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -18559,9 +19546,12 @@
         <v>0.278</v>
       </c>
       <c r="P329" s="1" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="Q329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="Q329" s="1" t="n">
+      <c r="R329" s="1" t="n">
         <v>0.2779</v>
       </c>
     </row>
@@ -18614,9 +19604,12 @@
         <v>0.1588</v>
       </c>
       <c r="P330" s="1" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="Q330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="Q330" s="1" t="n">
+      <c r="R330" s="1" t="n">
         <v>0.1587</v>
       </c>
     </row>
@@ -18669,9 +19662,12 @@
         <v>0.05366</v>
       </c>
       <c r="P331" s="1" t="n">
+        <v>0.05366</v>
+      </c>
+      <c r="Q331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="Q331" s="1" t="n">
+      <c r="R331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -18724,9 +19720,12 @@
         <v>0.3602</v>
       </c>
       <c r="P332" s="1" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="Q332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="Q332" s="1" t="n">
+      <c r="R332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -18779,9 +19778,12 @@
         <v>0.03044</v>
       </c>
       <c r="P333" s="1" t="n">
-        <v>0.03051</v>
+        <v>0.03054</v>
       </c>
       <c r="Q333" s="1" t="n">
+        <v>0.03054</v>
+      </c>
+      <c r="R333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -18834,9 +19836,12 @@
         <v>0.01767</v>
       </c>
       <c r="P334" s="1" t="n">
+        <v>0.01767</v>
+      </c>
+      <c r="Q334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="Q334" s="1" t="n">
+      <c r="R334" s="1" t="n">
         <v>0.01751</v>
       </c>
     </row>
@@ -18889,9 +19894,12 @@
         <v>0.0579</v>
       </c>
       <c r="P335" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="Q335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="Q335" s="1" t="n">
+      <c r="R335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -18944,10 +19952,13 @@
         <v>0.09054</v>
       </c>
       <c r="P336" s="1" t="n">
+        <v>0.09045</v>
+      </c>
+      <c r="Q336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="Q336" s="1" t="n">
-        <v>0.09054</v>
+      <c r="R336" s="1" t="n">
+        <v>0.09045</v>
       </c>
     </row>
     <row r="337">
@@ -18999,9 +20010,12 @@
         <v>0.1802</v>
       </c>
       <c r="P337" s="1" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="Q337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="Q337" s="1" t="n">
+      <c r="R337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -19054,10 +20068,13 @@
         <v>0.0209</v>
       </c>
       <c r="P338" s="1" t="n">
+        <v>0.02089</v>
+      </c>
+      <c r="Q338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="Q338" s="1" t="n">
-        <v>0.0209</v>
+      <c r="R338" s="1" t="n">
+        <v>0.02089</v>
       </c>
     </row>
     <row r="339">
@@ -19109,9 +20126,12 @@
         <v>0.1318</v>
       </c>
       <c r="P339" s="1" t="n">
-        <v>0.1318</v>
+        <v>0.1319</v>
       </c>
       <c r="Q339" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="R339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -19164,9 +20184,12 @@
         <v>0.007915999999999999</v>
       </c>
       <c r="P340" s="1" t="n">
+        <v>0.007952000000000001</v>
+      </c>
+      <c r="Q340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="Q340" s="1" t="n">
+      <c r="R340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -19219,9 +20242,12 @@
         <v>4.414</v>
       </c>
       <c r="P341" s="1" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="Q341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="Q341" s="1" t="n">
+      <c r="R341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -19274,9 +20300,12 @@
         <v>0.1891</v>
       </c>
       <c r="P342" s="1" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="Q342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="Q342" s="1" t="n">
+      <c r="R342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -19329,9 +20358,12 @@
         <v>0.08326</v>
       </c>
       <c r="P343" s="1" t="n">
+        <v>0.08311</v>
+      </c>
+      <c r="Q343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="Q343" s="1" t="n">
+      <c r="R343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -19384,9 +20416,12 @@
         <v>0.1817</v>
       </c>
       <c r="P344" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="Q344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="Q344" s="1" t="n">
+      <c r="R344" s="1" t="n">
         <v>0.1817</v>
       </c>
     </row>
@@ -19439,9 +20474,12 @@
         <v>0.003241</v>
       </c>
       <c r="P345" s="1" t="n">
+        <v>0.003242</v>
+      </c>
+      <c r="Q345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="Q345" s="1" t="n">
+      <c r="R345" s="1" t="n">
         <v>0.00324</v>
       </c>
     </row>
@@ -19494,9 +20532,12 @@
         <v>0.09075</v>
       </c>
       <c r="P346" s="1" t="n">
+        <v>0.09111</v>
+      </c>
+      <c r="Q346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="Q346" s="1" t="n">
+      <c r="R346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -19549,9 +20590,12 @@
         <v>2.244</v>
       </c>
       <c r="P347" s="1" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="Q347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q347" s="1" t="n">
+      <c r="R347" s="1" t="n">
         <v>2.243</v>
       </c>
     </row>
@@ -19604,9 +20648,12 @@
         <v>0.3027</v>
       </c>
       <c r="P348" s="1" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="Q348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="Q348" s="1" t="n">
+      <c r="R348" s="1" t="n">
         <v>0.3027</v>
       </c>
     </row>
@@ -19659,10 +20706,13 @@
         <v>0.02953</v>
       </c>
       <c r="P349" s="1" t="n">
+        <v>0.02945</v>
+      </c>
+      <c r="Q349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="Q349" s="1" t="n">
-        <v>0.02953</v>
+      <c r="R349" s="1" t="n">
+        <v>0.02945</v>
       </c>
     </row>
     <row r="350">
@@ -19714,9 +20764,12 @@
         <v>0.1274</v>
       </c>
       <c r="P350" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="Q350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="Q350" s="1" t="n">
+      <c r="R350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -19769,9 +20822,12 @@
         <v>0.06651</v>
       </c>
       <c r="P351" s="1" t="n">
+        <v>0.06655999999999999</v>
+      </c>
+      <c r="Q351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="Q351" s="1" t="n">
+      <c r="R351" s="1" t="n">
         <v>0.06651</v>
       </c>
     </row>
@@ -19824,9 +20880,12 @@
         <v>0.06241</v>
       </c>
       <c r="P352" s="1" t="n">
+        <v>0.06244</v>
+      </c>
+      <c r="Q352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="Q352" s="1" t="n">
+      <c r="R352" s="1" t="n">
         <v>0.06236</v>
       </c>
     </row>
@@ -19879,9 +20938,12 @@
         <v>0.06329</v>
       </c>
       <c r="P353" s="1" t="n">
+        <v>0.06337</v>
+      </c>
+      <c r="Q353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="Q353" s="1" t="n">
+      <c r="R353" s="1" t="n">
         <v>0.06329</v>
       </c>
     </row>
@@ -19934,10 +20996,13 @@
         <v>0.10602</v>
       </c>
       <c r="P354" s="1" t="n">
+        <v>0.10393</v>
+      </c>
+      <c r="Q354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="Q354" s="1" t="n">
-        <v>0.10405</v>
+      <c r="R354" s="1" t="n">
+        <v>0.10393</v>
       </c>
     </row>
     <row r="355">
@@ -19989,9 +21054,12 @@
         <v>0.09</v>
       </c>
       <c r="P355" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="Q355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="Q355" s="1" t="n">
+      <c r="R355" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -20044,10 +21112,13 @@
         <v>0.06976</v>
       </c>
       <c r="P356" s="1" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="Q356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="Q356" s="1" t="n">
-        <v>0.06976</v>
+      <c r="R356" s="1" t="n">
+        <v>0.06958</v>
       </c>
     </row>
     <row r="357">
@@ -20099,9 +21170,12 @@
         <v>0.4518</v>
       </c>
       <c r="P357" s="1" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="Q357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="Q357" s="1" t="n">
+      <c r="R357" s="1" t="n">
         <v>0.4518</v>
       </c>
     </row>
@@ -20154,9 +21228,12 @@
         <v>0.03484</v>
       </c>
       <c r="P358" s="1" t="n">
+        <v>0.03483</v>
+      </c>
+      <c r="Q358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="Q358" s="1" t="n">
+      <c r="R358" s="1" t="n">
         <v>0.03467</v>
       </c>
     </row>
@@ -20209,10 +21286,13 @@
         <v>0.01466</v>
       </c>
       <c r="P359" s="1" t="n">
+        <v>0.01463</v>
+      </c>
+      <c r="Q359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="Q359" s="1" t="n">
-        <v>0.01466</v>
+      <c r="R359" s="1" t="n">
+        <v>0.01463</v>
       </c>
     </row>
     <row r="360">
@@ -20264,9 +21344,12 @@
         <v>0.13297</v>
       </c>
       <c r="P360" s="1" t="n">
+        <v>0.13325</v>
+      </c>
+      <c r="Q360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="Q360" s="1" t="n">
+      <c r="R360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -20319,9 +21402,12 @@
         <v>0.0005865999999999999</v>
       </c>
       <c r="P361" s="1" t="n">
+        <v>0.0005886</v>
+      </c>
+      <c r="Q361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="Q361" s="1" t="n">
+      <c r="R361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -20374,9 +21460,12 @@
         <v>0.03855</v>
       </c>
       <c r="P362" s="1" t="n">
+        <v>0.03863</v>
+      </c>
+      <c r="Q362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="Q362" s="1" t="n">
+      <c r="R362" s="1" t="n">
         <v>0.03855</v>
       </c>
     </row>
@@ -20429,9 +21518,12 @@
         <v>3.208</v>
       </c>
       <c r="P363" s="1" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="Q363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="Q363" s="1" t="n">
+      <c r="R363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -20484,9 +21576,12 @@
         <v>0.1635</v>
       </c>
       <c r="P364" s="1" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="Q364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="Q364" s="1" t="n">
+      <c r="R364" s="1" t="n">
         <v>0.1635</v>
       </c>
     </row>
@@ -20539,9 +21634,12 @@
         <v>0.1136</v>
       </c>
       <c r="P365" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="Q365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="Q365" s="1" t="n">
+      <c r="R365" s="1" t="n">
         <v>0.1129</v>
       </c>
     </row>
@@ -20594,10 +21692,13 @@
         <v>0.0006386</v>
       </c>
       <c r="P366" s="1" t="n">
+        <v>0.0006375</v>
+      </c>
+      <c r="Q366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="Q366" s="1" t="n">
-        <v>0.0006386</v>
+      <c r="R366" s="1" t="n">
+        <v>0.0006375</v>
       </c>
     </row>
     <row r="367">
@@ -20649,9 +21750,12 @@
         <v>0.05903</v>
       </c>
       <c r="P367" s="1" t="n">
+        <v>0.05939</v>
+      </c>
+      <c r="Q367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="Q367" s="1" t="n">
+      <c r="R367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -20704,10 +21808,13 @@
         <v>0.08175</v>
       </c>
       <c r="P368" s="1" t="n">
+        <v>0.08162999999999999</v>
+      </c>
+      <c r="Q368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="Q368" s="1" t="n">
-        <v>0.08175</v>
+      <c r="R368" s="1" t="n">
+        <v>0.08162999999999999</v>
       </c>
     </row>
     <row r="369">
@@ -20759,9 +21866,12 @@
         <v>0.03931</v>
       </c>
       <c r="P369" s="1" t="n">
+        <v>0.03939</v>
+      </c>
+      <c r="Q369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="Q369" s="1" t="n">
+      <c r="R369" s="1" t="n">
         <v>0.03931</v>
       </c>
     </row>
@@ -20814,9 +21924,12 @@
         <v>3.68</v>
       </c>
       <c r="P370" s="1" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="Q370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="Q370" s="1" t="n">
+      <c r="R370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -20869,9 +21982,12 @@
         <v>0.1208</v>
       </c>
       <c r="P371" s="1" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="Q371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="Q371" s="1" t="n">
+      <c r="R371" s="1" t="n">
         <v>0.1208</v>
       </c>
     </row>
@@ -20924,9 +22040,12 @@
         <v>0.0148</v>
       </c>
       <c r="P372" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="Q372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="Q372" s="1" t="n">
+      <c r="R372" s="1" t="n">
         <v>0.01471</v>
       </c>
     </row>
@@ -20979,9 +22098,12 @@
         <v>0.02198</v>
       </c>
       <c r="P373" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="Q373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="Q373" s="1" t="n">
+      <c r="R373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -21034,9 +22156,12 @@
         <v>1.8579</v>
       </c>
       <c r="P374" s="1" t="n">
+        <v>1.8612</v>
+      </c>
+      <c r="Q374" s="1" t="n">
         <v>1.8671</v>
       </c>
-      <c r="Q374" s="1" t="n">
+      <c r="R374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -21089,10 +22214,13 @@
         <v>0.02092</v>
       </c>
       <c r="P375" s="1" t="n">
+        <v>0.02087</v>
+      </c>
+      <c r="Q375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="Q375" s="1" t="n">
-        <v>0.02092</v>
+      <c r="R375" s="1" t="n">
+        <v>0.02087</v>
       </c>
     </row>
     <row r="376">
@@ -21144,9 +22272,12 @@
         <v>1.304</v>
       </c>
       <c r="P376" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="Q376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="Q376" s="1" t="n">
+      <c r="R376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -21199,9 +22330,12 @@
         <v>0.2829</v>
       </c>
       <c r="P377" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="Q377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="Q377" s="1" t="n">
+      <c r="R377" s="1" t="n">
         <v>0.2826</v>
       </c>
     </row>
@@ -21254,9 +22388,12 @@
         <v>0.01553</v>
       </c>
       <c r="P378" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="Q378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="Q378" s="1" t="n">
+      <c r="R378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -21309,9 +22446,12 @@
         <v>1.5325</v>
       </c>
       <c r="P379" s="1" t="n">
+        <v>1.5325</v>
+      </c>
+      <c r="Q379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="Q379" s="1" t="n">
+      <c r="R379" s="1" t="n">
         <v>1.5275</v>
       </c>
     </row>
@@ -21364,9 +22504,12 @@
         <v>6.896e-05</v>
       </c>
       <c r="P380" s="1" t="n">
+        <v>6.905e-05</v>
+      </c>
+      <c r="Q380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="Q380" s="1" t="n">
+      <c r="R380" s="1" t="n">
         <v>6.896e-05</v>
       </c>
     </row>
@@ -21419,9 +22562,12 @@
         <v>2.548</v>
       </c>
       <c r="P381" s="1" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="Q381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="Q381" s="1" t="n">
+      <c r="R381" s="1" t="n">
         <v>2.545</v>
       </c>
     </row>
@@ -21474,9 +22620,12 @@
         <v>0.06683</v>
       </c>
       <c r="P382" s="1" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="Q382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="Q382" s="1" t="n">
+      <c r="R382" s="1" t="n">
         <v>0.06683</v>
       </c>
     </row>
@@ -21529,9 +22678,12 @@
         <v>0.0172</v>
       </c>
       <c r="P383" s="1" t="n">
+        <v>0.01744</v>
+      </c>
+      <c r="Q383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="Q383" s="1" t="n">
+      <c r="R383" s="1" t="n">
         <v>0.01713</v>
       </c>
     </row>
@@ -21584,9 +22736,12 @@
         <v>0.05177</v>
       </c>
       <c r="P384" s="1" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="Q384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="Q384" s="1" t="n">
+      <c r="R384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -21639,9 +22794,12 @@
         <v>7.564</v>
       </c>
       <c r="P385" s="1" t="n">
+        <v>7.571</v>
+      </c>
+      <c r="Q385" s="1" t="n">
         <v>7.591</v>
       </c>
-      <c r="Q385" s="1" t="n">
+      <c r="R385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -21694,9 +22852,12 @@
         <v>0.00328</v>
       </c>
       <c r="P386" s="1" t="n">
+        <v>0.003278</v>
+      </c>
+      <c r="Q386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="Q386" s="1" t="n">
+      <c r="R386" s="1" t="n">
         <v>0.00327</v>
       </c>
     </row>
@@ -21749,9 +22910,12 @@
         <v>0.0003801</v>
       </c>
       <c r="P387" s="1" t="n">
+        <v>0.0003802</v>
+      </c>
+      <c r="Q387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="Q387" s="1" t="n">
+      <c r="R387" s="1" t="n">
         <v>0.0003801</v>
       </c>
     </row>
@@ -21804,10 +22968,13 @@
         <v>0.00946</v>
       </c>
       <c r="P388" s="1" t="n">
+        <v>0.00945</v>
+      </c>
+      <c r="Q388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="Q388" s="1" t="n">
-        <v>0.00946</v>
+      <c r="R388" s="1" t="n">
+        <v>0.00945</v>
       </c>
     </row>
     <row r="389">
@@ -21859,9 +23026,12 @@
         <v>0.2904</v>
       </c>
       <c r="P389" s="1" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="Q389" s="1" t="n">
         <v>0.2904</v>
       </c>
-      <c r="Q389" s="1" t="n">
+      <c r="R389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -21917,6 +23087,9 @@
         <v>0.0253</v>
       </c>
       <c r="Q390" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="R390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -21969,9 +23142,12 @@
         <v>2.834</v>
       </c>
       <c r="P391" s="1" t="n">
-        <v>2.834</v>
+        <v>2.845</v>
       </c>
       <c r="Q391" s="1" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="R391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -22024,9 +23200,12 @@
         <v>0.0135</v>
       </c>
       <c r="P392" s="1" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="Q392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="Q392" s="1" t="n">
+      <c r="R392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -22082,6 +23261,9 @@
         <v>0.00237</v>
       </c>
       <c r="Q393" s="1" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="R393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -22134,9 +23316,12 @@
         <v>0.05933</v>
       </c>
       <c r="P394" s="1" t="n">
+        <v>0.05935</v>
+      </c>
+      <c r="Q394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="Q394" s="1" t="n">
+      <c r="R394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -22189,9 +23374,12 @@
         <v>0.0402</v>
       </c>
       <c r="P395" s="1" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="Q395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="Q395" s="1" t="n">
+      <c r="R395" s="1" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -22244,9 +23432,12 @@
         <v>0.09246</v>
       </c>
       <c r="P396" s="1" t="n">
-        <v>0.09272</v>
+        <v>0.09273000000000001</v>
       </c>
       <c r="Q396" s="1" t="n">
+        <v>0.09273000000000001</v>
+      </c>
+      <c r="R396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -22299,9 +23490,12 @@
         <v>0.1515</v>
       </c>
       <c r="P397" s="1" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="Q397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="Q397" s="1" t="n">
+      <c r="R397" s="1" t="n">
         <v>0.1515</v>
       </c>
     </row>
@@ -22354,9 +23548,12 @@
         <v>0.929</v>
       </c>
       <c r="P398" s="1" t="n">
-        <v>0.93</v>
+        <v>0.931</v>
       </c>
       <c r="Q398" s="1" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="R398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -22409,9 +23606,12 @@
         <v>0.05237</v>
       </c>
       <c r="P399" s="1" t="n">
+        <v>0.05239</v>
+      </c>
+      <c r="Q399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="Q399" s="1" t="n">
+      <c r="R399" s="1" t="n">
         <v>0.05215</v>
       </c>
     </row>
@@ -22464,9 +23664,12 @@
         <v>2.512</v>
       </c>
       <c r="P400" s="1" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="Q400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="Q400" s="1" t="n">
+      <c r="R400" s="1" t="n">
         <v>2.512</v>
       </c>
     </row>
@@ -22519,10 +23722,13 @@
         <v>0.01788</v>
       </c>
       <c r="P401" s="1" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="Q401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="Q401" s="1" t="n">
-        <v>0.01785</v>
+      <c r="R401" s="1" t="n">
+        <v>0.0178</v>
       </c>
     </row>
     <row r="402">
@@ -22574,9 +23780,12 @@
         <v>0.07985</v>
       </c>
       <c r="P402" s="1" t="n">
+        <v>0.07973</v>
+      </c>
+      <c r="Q402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="Q402" s="1" t="n">
+      <c r="R402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -22629,9 +23838,12 @@
         <v>1.2485</v>
       </c>
       <c r="P403" s="1" t="n">
+        <v>1.2496</v>
+      </c>
+      <c r="Q403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="Q403" s="1" t="n">
+      <c r="R403" s="1" t="n">
         <v>1.2455</v>
       </c>
     </row>
@@ -22684,9 +23896,12 @@
         <v>0.00711</v>
       </c>
       <c r="P404" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="Q404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="Q404" s="1" t="n">
+      <c r="R404" s="1" t="n">
         <v>0.00711</v>
       </c>
     </row>
@@ -22739,9 +23954,12 @@
         <v>0.5041</v>
       </c>
       <c r="P405" s="1" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="Q405" s="1" t="n">
         <v>0.5041</v>
       </c>
-      <c r="Q405" s="1" t="n">
+      <c r="R405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -22794,10 +24012,13 @@
         <v>0.01145</v>
       </c>
       <c r="P406" s="1" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="Q406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="Q406" s="1" t="n">
-        <v>0.01145</v>
+      <c r="R406" s="1" t="n">
+        <v>0.01144</v>
       </c>
     </row>
     <row r="407">
@@ -22849,9 +24070,12 @@
         <v>0.04596</v>
       </c>
       <c r="P407" s="1" t="n">
+        <v>0.04602</v>
+      </c>
+      <c r="Q407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="Q407" s="1" t="n">
+      <c r="R407" s="1" t="n">
         <v>0.04596</v>
       </c>
     </row>
@@ -22904,9 +24128,12 @@
         <v>0.03927</v>
       </c>
       <c r="P408" s="1" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="Q408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="Q408" s="1" t="n">
+      <c r="R408" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -22959,9 +24186,12 @@
         <v>0.05226</v>
       </c>
       <c r="P409" s="1" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="Q409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="Q409" s="1" t="n">
+      <c r="R409" s="1" t="n">
         <v>0.05226</v>
       </c>
     </row>
@@ -23014,10 +24244,13 @@
         <v>0.01229</v>
       </c>
       <c r="P410" s="1" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="Q410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="Q410" s="1" t="n">
-        <v>0.01229</v>
+      <c r="R410" s="1" t="n">
+        <v>0.01227</v>
       </c>
     </row>
     <row r="411">
@@ -23069,10 +24302,13 @@
         <v>0.06349</v>
       </c>
       <c r="P411" s="1" t="n">
+        <v>0.06342</v>
+      </c>
+      <c r="Q411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="Q411" s="1" t="n">
-        <v>0.06347</v>
+      <c r="R411" s="1" t="n">
+        <v>0.06342</v>
       </c>
     </row>
     <row r="412">
@@ -23124,9 +24360,12 @@
         <v>0.04131</v>
       </c>
       <c r="P412" s="1" t="n">
+        <v>0.04136</v>
+      </c>
+      <c r="Q412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="Q412" s="1" t="n">
+      <c r="R412" s="1" t="n">
         <v>0.04126</v>
       </c>
     </row>
@@ -23179,10 +24418,13 @@
         <v>1.114</v>
       </c>
       <c r="P413" s="1" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="Q413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="Q413" s="1" t="n">
-        <v>1.114</v>
+      <c r="R413" s="1" t="n">
+        <v>1.112</v>
       </c>
     </row>
     <row r="414">
@@ -23234,9 +24476,12 @@
         <v>0.2624</v>
       </c>
       <c r="P414" s="1" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="Q414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="Q414" s="1" t="n">
+      <c r="R414" s="1" t="n">
         <v>0.2624</v>
       </c>
     </row>
@@ -23289,9 +24534,12 @@
         <v>0.001214</v>
       </c>
       <c r="P415" s="1" t="n">
+        <v>0.001218</v>
+      </c>
+      <c r="Q415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="Q415" s="1" t="n">
+      <c r="R415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -23344,9 +24592,12 @@
         <v>0.03193</v>
       </c>
       <c r="P416" s="1" t="n">
+        <v>0.03203</v>
+      </c>
+      <c r="Q416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="Q416" s="1" t="n">
+      <c r="R416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -23399,9 +24650,12 @@
         <v>0.01465</v>
       </c>
       <c r="P417" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="Q417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="Q417" s="1" t="n">
+      <c r="R417" s="1" t="n">
         <v>0.01454</v>
       </c>
     </row>
@@ -23454,9 +24708,12 @@
         <v>0.1481</v>
       </c>
       <c r="P418" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="Q418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="Q418" s="1" t="n">
+      <c r="R418" s="1" t="n">
         <v>0.1479</v>
       </c>
     </row>
@@ -23509,9 +24766,12 @@
         <v>0.04904</v>
       </c>
       <c r="P419" s="1" t="n">
+        <v>0.04914</v>
+      </c>
+      <c r="Q419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="Q419" s="1" t="n">
+      <c r="R419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -23564,9 +24824,12 @@
         <v>66.94</v>
       </c>
       <c r="P420" s="1" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="Q420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="Q420" s="1" t="n">
+      <c r="R420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -23619,9 +24882,12 @@
         <v>0.875</v>
       </c>
       <c r="P421" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="Q421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="Q421" s="1" t="n">
+      <c r="R421" s="1" t="n">
         <v>0.875</v>
       </c>
     </row>
@@ -23674,10 +24940,13 @@
         <v>0.012415</v>
       </c>
       <c r="P422" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="Q422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="Q422" s="1" t="n">
-        <v>0.012415</v>
+      <c r="R422" s="1" t="n">
+        <v>0.01239</v>
       </c>
     </row>
     <row r="423">
@@ -23729,9 +24998,12 @@
         <v>0.01595</v>
       </c>
       <c r="P423" s="1" t="n">
+        <v>0.01596</v>
+      </c>
+      <c r="Q423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="Q423" s="1" t="n">
+      <c r="R423" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -23784,9 +25056,12 @@
         <v>0.2716</v>
       </c>
       <c r="P424" s="1" t="n">
-        <v>0.2716</v>
+        <v>0.27462</v>
       </c>
       <c r="Q424" s="1" t="n">
+        <v>0.27462</v>
+      </c>
+      <c r="R424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -23839,9 +25114,12 @@
         <v>0.6002999999999999</v>
       </c>
       <c r="P425" s="1" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="Q425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="Q425" s="1" t="n">
+      <c r="R425" s="1" t="n">
         <v>0.599</v>
       </c>
     </row>
@@ -23894,10 +25172,13 @@
         <v>0.005512</v>
       </c>
       <c r="P426" s="1" t="n">
+        <v>0.005501</v>
+      </c>
+      <c r="Q426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="Q426" s="1" t="n">
-        <v>0.005512</v>
+      <c r="R426" s="1" t="n">
+        <v>0.005501</v>
       </c>
     </row>
     <row r="427">
@@ -23949,9 +25230,12 @@
         <v>0.04955</v>
       </c>
       <c r="P427" s="1" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="Q427" s="1" t="n">
         <v>0.04962</v>
       </c>
-      <c r="Q427" s="1" t="n">
+      <c r="R427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -24004,9 +25288,12 @@
         <v>0.1259</v>
       </c>
       <c r="P428" s="1" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="Q428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="Q428" s="1" t="n">
+      <c r="R428" s="1" t="n">
         <v>0.1254</v>
       </c>
     </row>
@@ -24059,9 +25346,12 @@
         <v>0.003205</v>
       </c>
       <c r="P429" s="1" t="n">
+        <v>0.003198</v>
+      </c>
+      <c r="Q429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="Q429" s="1" t="n">
+      <c r="R429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -24114,9 +25404,12 @@
         <v>0.03644</v>
       </c>
       <c r="P430" s="1" t="n">
+        <v>0.03641</v>
+      </c>
+      <c r="Q430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="Q430" s="1" t="n">
+      <c r="R430" s="1" t="n">
         <v>0.03641</v>
       </c>
     </row>
@@ -24169,9 +25462,12 @@
         <v>0.3952</v>
       </c>
       <c r="P431" s="1" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="Q431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="Q431" s="1" t="n">
+      <c r="R431" s="1" t="n">
         <v>0.3952</v>
       </c>
     </row>
@@ -24224,10 +25520,13 @@
         <v>0.004483</v>
       </c>
       <c r="P432" s="1" t="n">
+        <v>0.00448</v>
+      </c>
+      <c r="Q432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="Q432" s="1" t="n">
-        <v>0.004483</v>
+      <c r="R432" s="1" t="n">
+        <v>0.00448</v>
       </c>
     </row>
     <row r="433">
@@ -24279,9 +25578,12 @@
         <v>0.098</v>
       </c>
       <c r="P433" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="Q433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="Q433" s="1" t="n">
+      <c r="R433" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -24334,9 +25636,12 @@
         <v>0.01237</v>
       </c>
       <c r="P434" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="Q434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="Q434" s="1" t="n">
+      <c r="R434" s="1" t="n">
         <v>0.01237</v>
       </c>
     </row>
@@ -24389,9 +25694,12 @@
         <v>1.982</v>
       </c>
       <c r="P435" s="1" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="Q435" s="1" t="n">
         <v>1.988</v>
       </c>
-      <c r="Q435" s="1" t="n">
+      <c r="R435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -24444,10 +25752,13 @@
         <v>0.001792</v>
       </c>
       <c r="P436" s="1" t="n">
+        <v>0.001777</v>
+      </c>
+      <c r="Q436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="Q436" s="1" t="n">
-        <v>0.001792</v>
+      <c r="R436" s="1" t="n">
+        <v>0.001777</v>
       </c>
     </row>
     <row r="437">
@@ -24499,9 +25810,12 @@
         <v>0.4419</v>
       </c>
       <c r="P437" s="1" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="Q437" s="1" t="n">
         <v>0.4427</v>
       </c>
-      <c r="Q437" s="1" t="n">
+      <c r="R437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -24554,9 +25868,12 @@
         <v>0.00534</v>
       </c>
       <c r="P438" s="1" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="Q438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="Q438" s="1" t="n">
+      <c r="R438" s="1" t="n">
         <v>0.00534</v>
       </c>
     </row>
@@ -24609,9 +25926,12 @@
         <v>0.1034</v>
       </c>
       <c r="P439" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="Q439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="Q439" s="1" t="n">
+      <c r="R439" s="1" t="n">
         <v>0.1033</v>
       </c>
     </row>
@@ -24664,10 +25984,13 @@
         <v>0.034</v>
       </c>
       <c r="P440" s="1" t="n">
+        <v>0.03399</v>
+      </c>
+      <c r="Q440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="Q440" s="1" t="n">
-        <v>0.034</v>
+      <c r="R440" s="1" t="n">
+        <v>0.03399</v>
       </c>
     </row>
     <row r="441">
@@ -24719,9 +26042,12 @@
         <v>0.08201</v>
       </c>
       <c r="P441" s="1" t="n">
+        <v>0.08212999999999999</v>
+      </c>
+      <c r="Q441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="Q441" s="1" t="n">
+      <c r="R441" s="1" t="n">
         <v>0.08201</v>
       </c>
     </row>
@@ -24774,9 +26100,12 @@
         <v>1.308</v>
       </c>
       <c r="P442" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="Q442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="Q442" s="1" t="n">
+      <c r="R442" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -24829,10 +26158,13 @@
         <v>0.07566000000000001</v>
       </c>
       <c r="P443" s="1" t="n">
+        <v>0.07543999999999999</v>
+      </c>
+      <c r="Q443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="Q443" s="1" t="n">
-        <v>0.07549</v>
+      <c r="R443" s="1" t="n">
+        <v>0.07543999999999999</v>
       </c>
     </row>
     <row r="444">
@@ -24884,10 +26216,13 @@
         <v>0.07652</v>
       </c>
       <c r="P444" s="1" t="n">
+        <v>0.07638</v>
+      </c>
+      <c r="Q444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="Q444" s="1" t="n">
-        <v>0.07650999999999999</v>
+      <c r="R444" s="1" t="n">
+        <v>0.07638</v>
       </c>
     </row>
     <row r="445">
@@ -24939,9 +26274,12 @@
         <v>0.0433</v>
       </c>
       <c r="P445" s="1" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="Q445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="Q445" s="1" t="n">
+      <c r="R445" s="1" t="n">
         <v>0.0433</v>
       </c>
     </row>
@@ -24994,9 +26332,12 @@
         <v>0.02132</v>
       </c>
       <c r="P446" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="Q446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="Q446" s="1" t="n">
+      <c r="R446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -25049,9 +26390,12 @@
         <v>0.2804</v>
       </c>
       <c r="P447" s="1" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="Q447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="Q447" s="1" t="n">
+      <c r="R447" s="1" t="n">
         <v>0.2795</v>
       </c>
     </row>
@@ -25104,10 +26448,13 @@
         <v>0.031</v>
       </c>
       <c r="P448" s="1" t="n">
+        <v>0.03097</v>
+      </c>
+      <c r="Q448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="Q448" s="1" t="n">
-        <v>0.031</v>
+      <c r="R448" s="1" t="n">
+        <v>0.03097</v>
       </c>
     </row>
     <row r="449">
@@ -25162,6 +26509,9 @@
         <v>0.00647</v>
       </c>
       <c r="Q449" s="1" t="n">
+        <v>0.00647</v>
+      </c>
+      <c r="R449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -25214,9 +26564,12 @@
         <v>0.023072</v>
       </c>
       <c r="P450" s="1" t="n">
+        <v>0.023057</v>
+      </c>
+      <c r="Q450" s="1" t="n">
         <v>0.023086</v>
       </c>
-      <c r="Q450" s="1" t="n">
+      <c r="R450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -25269,9 +26622,12 @@
         <v>0.04227</v>
       </c>
       <c r="P451" s="1" t="n">
+        <v>0.04236</v>
+      </c>
+      <c r="Q451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="Q451" s="1" t="n">
+      <c r="R451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -25324,9 +26680,12 @@
         <v>0.07223</v>
       </c>
       <c r="P452" s="1" t="n">
+        <v>0.07239</v>
+      </c>
+      <c r="Q452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="Q452" s="1" t="n">
+      <c r="R452" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -25379,9 +26738,12 @@
         <v>0.0005904</v>
       </c>
       <c r="P453" s="1" t="n">
+        <v>0.0005910000000000001</v>
+      </c>
+      <c r="Q453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="Q453" s="1" t="n">
+      <c r="R453" s="1" t="n">
         <v>0.0005904</v>
       </c>
     </row>
@@ -25434,9 +26796,12 @@
         <v>0.305</v>
       </c>
       <c r="P454" s="1" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="Q454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="Q454" s="1" t="n">
+      <c r="R454" s="1" t="n">
         <v>0.305</v>
       </c>
     </row>
@@ -25489,9 +26854,12 @@
         <v>0.004277</v>
       </c>
       <c r="P455" s="1" t="n">
+        <v>0.004277</v>
+      </c>
+      <c r="Q455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="Q455" s="1" t="n">
+      <c r="R455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -25544,9 +26912,12 @@
         <v>0.1821</v>
       </c>
       <c r="P456" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="Q456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="Q456" s="1" t="n">
+      <c r="R456" s="1" t="n">
         <v>0.1821</v>
       </c>
     </row>
@@ -25599,9 +26970,12 @@
         <v>0.04267</v>
       </c>
       <c r="P457" s="1" t="n">
+        <v>0.04275</v>
+      </c>
+      <c r="Q457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="Q457" s="1" t="n">
+      <c r="R457" s="1" t="n">
         <v>0.04267</v>
       </c>
     </row>
@@ -25654,9 +27028,12 @@
         <v>0.1464</v>
       </c>
       <c r="P458" s="1" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="Q458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="Q458" s="1" t="n">
+      <c r="R458" s="1" t="n">
         <v>0.1459</v>
       </c>
     </row>
@@ -25709,9 +27086,12 @@
         <v>0.008625000000000001</v>
       </c>
       <c r="P459" s="1" t="n">
+        <v>0.008626</v>
+      </c>
+      <c r="Q459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="Q459" s="1" t="n">
+      <c r="R459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -25764,9 +27144,12 @@
         <v>0.007357</v>
       </c>
       <c r="P460" s="1" t="n">
+        <v>0.007414</v>
+      </c>
+      <c r="Q460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="Q460" s="1" t="n">
+      <c r="R460" s="1" t="n">
         <v>0.007357</v>
       </c>
     </row>
@@ -25819,9 +27202,12 @@
         <v>0.0001733</v>
       </c>
       <c r="P461" s="1" t="n">
+        <v>0.0001735</v>
+      </c>
+      <c r="Q461" s="1" t="n">
         <v>0.0001736</v>
       </c>
-      <c r="Q461" s="1" t="n">
+      <c r="R461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -25874,9 +27260,12 @@
         <v>0.02331</v>
       </c>
       <c r="P462" s="1" t="n">
-        <v>0.02331</v>
+        <v>0.02337</v>
       </c>
       <c r="Q462" s="1" t="n">
+        <v>0.02337</v>
+      </c>
+      <c r="R462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -25929,9 +27318,12 @@
         <v>0.03704</v>
       </c>
       <c r="P463" s="1" t="n">
+        <v>0.03694</v>
+      </c>
+      <c r="Q463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="Q463" s="1" t="n">
+      <c r="R463" s="1" t="n">
         <v>0.03685</v>
       </c>
     </row>
@@ -25984,9 +27376,12 @@
         <v>0.3012</v>
       </c>
       <c r="P464" s="1" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="Q464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="Q464" s="1" t="n">
+      <c r="R464" s="1" t="n">
         <v>0.3012</v>
       </c>
     </row>
@@ -26039,9 +27434,12 @@
         <v>0.0391</v>
       </c>
       <c r="P465" s="1" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="Q465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="Q465" s="1" t="n">
+      <c r="R465" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -26094,9 +27492,12 @@
         <v>2.662</v>
       </c>
       <c r="P466" s="1" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="Q466" s="1" t="n">
+      <c r="R466" s="1" t="n">
         <v>2.662</v>
       </c>
     </row>
@@ -26149,9 +27550,12 @@
         <v>0.03393</v>
       </c>
       <c r="P467" s="1" t="n">
-        <v>0.03436</v>
+        <v>0.03438</v>
       </c>
       <c r="Q467" s="1" t="n">
+        <v>0.03438</v>
+      </c>
+      <c r="R467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -26204,9 +27608,12 @@
         <v>0.1762</v>
       </c>
       <c r="P468" s="1" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="Q468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="Q468" s="1" t="n">
+      <c r="R468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -26259,9 +27666,12 @@
         <v>0.0961</v>
       </c>
       <c r="P469" s="1" t="n">
+        <v>0.0965</v>
+      </c>
+      <c r="Q469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="Q469" s="1" t="n">
+      <c r="R469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -26314,9 +27724,12 @@
         <v>0.06708</v>
       </c>
       <c r="P470" s="1" t="n">
+        <v>0.06713</v>
+      </c>
+      <c r="Q470" s="1" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="Q470" s="1" t="n">
+      <c r="R470" s="1" t="n">
         <v>0.06708</v>
       </c>
     </row>
@@ -26369,9 +27782,12 @@
         <v>0.03994</v>
       </c>
       <c r="P471" s="1" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="Q471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="Q471" s="1" t="n">
+      <c r="R471" s="1" t="n">
         <v>0.03978</v>
       </c>
     </row>
@@ -26424,9 +27840,12 @@
         <v>0.2466</v>
       </c>
       <c r="P472" s="1" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="Q472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="Q472" s="1" t="n">
+      <c r="R472" s="1" t="n">
         <v>0.2466</v>
       </c>
     </row>
@@ -26479,10 +27898,13 @@
         <v>0.01636</v>
       </c>
       <c r="P473" s="1" t="n">
+        <v>0.016346</v>
+      </c>
+      <c r="Q473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="Q473" s="1" t="n">
-        <v>0.016358</v>
+      <c r="R473" s="1" t="n">
+        <v>0.016346</v>
       </c>
     </row>
     <row r="474">
@@ -26534,9 +27956,12 @@
         <v>0.1154</v>
       </c>
       <c r="P474" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="Q474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="Q474" s="1" t="n">
+      <c r="R474" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -26589,9 +28014,12 @@
         <v>0.04266</v>
       </c>
       <c r="P475" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="Q475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="Q475" s="1" t="n">
+      <c r="R475" s="1" t="n">
         <v>0.04264</v>
       </c>
     </row>
@@ -26644,9 +28072,12 @@
         <v>0.2066</v>
       </c>
       <c r="P476" s="1" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="Q476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="Q476" s="1" t="n">
+      <c r="R476" s="1" t="n">
         <v>0.2066</v>
       </c>
     </row>
@@ -26699,9 +28130,12 @@
         <v>0.006789</v>
       </c>
       <c r="P477" s="1" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="Q477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="Q477" s="1" t="n">
+      <c r="R477" s="1" t="n">
         <v>0.006789</v>
       </c>
     </row>
@@ -26754,9 +28188,12 @@
         <v>0.01781</v>
       </c>
       <c r="P478" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="Q478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="Q478" s="1" t="n">
+      <c r="R478" s="1" t="n">
         <v>0.01781</v>
       </c>
     </row>
@@ -26809,9 +28246,12 @@
         <v>0.04672</v>
       </c>
       <c r="P479" s="1" t="n">
+        <v>0.04673</v>
+      </c>
+      <c r="Q479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="Q479" s="1" t="n">
+      <c r="R479" s="1" t="n">
         <v>0.04672</v>
       </c>
     </row>
@@ -26864,9 +28304,12 @@
         <v>0.25998</v>
       </c>
       <c r="P480" s="1" t="n">
+        <v>0.26029</v>
+      </c>
+      <c r="Q480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="Q480" s="1" t="n">
+      <c r="R480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -26919,9 +28362,12 @@
         <v>0.01218</v>
       </c>
       <c r="P481" s="1" t="n">
+        <v>0.01222</v>
+      </c>
+      <c r="Q481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="Q481" s="1" t="n">
+      <c r="R481" s="1" t="n">
         <v>0.01218</v>
       </c>
     </row>
@@ -26974,9 +28420,12 @@
         <v>0.004084</v>
       </c>
       <c r="P482" s="1" t="n">
+        <v>0.004085</v>
+      </c>
+      <c r="Q482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="Q482" s="1" t="n">
+      <c r="R482" s="1" t="n">
         <v>0.004061</v>
       </c>
     </row>
@@ -27029,9 +28478,12 @@
         <v>0.1229</v>
       </c>
       <c r="P483" s="1" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="Q483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="Q483" s="1" t="n">
+      <c r="R483" s="1" t="n">
         <v>0.1229</v>
       </c>
     </row>
@@ -27084,9 +28536,12 @@
         <v>0.02218</v>
       </c>
       <c r="P484" s="1" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="Q484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="Q484" s="1" t="n">
+      <c r="R484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -27139,9 +28594,12 @@
         <v>0.0453</v>
       </c>
       <c r="P485" s="1" t="n">
+        <v>0.04517</v>
+      </c>
+      <c r="Q485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="Q485" s="1" t="n">
+      <c r="R485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -27194,9 +28652,12 @@
         <v>0.1732</v>
       </c>
       <c r="P486" s="1" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="Q486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="Q486" s="1" t="n">
+      <c r="R486" s="1" t="n">
         <v>0.1731</v>
       </c>
     </row>
@@ -27249,9 +28710,12 @@
         <v>0.2725</v>
       </c>
       <c r="P487" s="1" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="Q487" s="1" t="n">
         <v>0.2735</v>
       </c>
-      <c r="Q487" s="1" t="n">
+      <c r="R487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -27304,9 +28768,12 @@
         <v>0.04604</v>
       </c>
       <c r="P488" s="1" t="n">
+        <v>0.04609</v>
+      </c>
+      <c r="Q488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="Q488" s="1" t="n">
+      <c r="R488" s="1" t="n">
         <v>0.04604</v>
       </c>
     </row>
@@ -27359,9 +28826,12 @@
         <v>0.0002144</v>
       </c>
       <c r="P489" s="1" t="n">
+        <v>0.0002146</v>
+      </c>
+      <c r="Q489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="Q489" s="1" t="n">
+      <c r="R489" s="1" t="n">
         <v>0.0002144</v>
       </c>
     </row>
@@ -27417,6 +28887,9 @@
         <v>1.78</v>
       </c>
       <c r="Q490" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -27469,9 +28942,12 @@
         <v>16.019</v>
       </c>
       <c r="P491" s="1" t="n">
+        <v>16.044</v>
+      </c>
+      <c r="Q491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="Q491" s="1" t="n">
+      <c r="R491" s="1" t="n">
         <v>15.996</v>
       </c>
     </row>
@@ -27524,9 +29000,12 @@
         <v>0.06668</v>
       </c>
       <c r="P492" s="1" t="n">
+        <v>0.06671000000000001</v>
+      </c>
+      <c r="Q492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="Q492" s="1" t="n">
+      <c r="R492" s="1" t="n">
         <v>0.06648</v>
       </c>
     </row>
@@ -27579,9 +29058,12 @@
         <v>0.06728000000000001</v>
       </c>
       <c r="P493" s="1" t="n">
+        <v>0.06734</v>
+      </c>
+      <c r="Q493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="Q493" s="1" t="n">
+      <c r="R493" s="1" t="n">
         <v>0.06728000000000001</v>
       </c>
     </row>
@@ -27634,9 +29116,12 @@
         <v>0.009450999999999999</v>
       </c>
       <c r="P494" s="1" t="n">
+        <v>0.009427</v>
+      </c>
+      <c r="Q494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="Q494" s="1" t="n">
+      <c r="R494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -27689,9 +29174,12 @@
         <v>0.005829</v>
       </c>
       <c r="P495" s="1" t="n">
+        <v>0.005885</v>
+      </c>
+      <c r="Q495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="Q495" s="1" t="n">
+      <c r="R495" s="1" t="n">
         <v>0.005809</v>
       </c>
     </row>
@@ -27744,9 +29232,12 @@
         <v>0.009849999999999999</v>
       </c>
       <c r="P496" s="1" t="n">
+        <v>0.00988</v>
+      </c>
+      <c r="Q496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="Q496" s="1" t="n">
+      <c r="R496" s="1" t="n">
         <v>0.009849999999999999</v>
       </c>
     </row>
@@ -27799,9 +29290,12 @@
         <v>0.04578</v>
       </c>
       <c r="P497" s="1" t="n">
-        <v>0.04578</v>
+        <v>0.04613</v>
       </c>
       <c r="Q497" s="1" t="n">
+        <v>0.04613</v>
+      </c>
+      <c r="R497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -27854,9 +29348,12 @@
         <v>0.006353</v>
       </c>
       <c r="P498" s="1" t="n">
+        <v>0.006366</v>
+      </c>
+      <c r="Q498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="Q498" s="1" t="n">
+      <c r="R498" s="1" t="n">
         <v>0.006353</v>
       </c>
     </row>
@@ -27909,10 +29406,13 @@
         <v>0.01039</v>
       </c>
       <c r="P499" s="1" t="n">
+        <v>0.01038</v>
+      </c>
+      <c r="Q499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="Q499" s="1" t="n">
-        <v>0.01039</v>
+      <c r="R499" s="1" t="n">
+        <v>0.01038</v>
       </c>
     </row>
     <row r="500">
@@ -27964,9 +29464,12 @@
         <v>0.5084</v>
       </c>
       <c r="P500" s="1" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="Q500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="Q500" s="1" t="n">
+      <c r="R500" s="1" t="n">
         <v>0.5075</v>
       </c>
     </row>
@@ -28019,9 +29522,12 @@
         <v>0.03206</v>
       </c>
       <c r="P501" s="1" t="n">
+        <v>0.03201</v>
+      </c>
+      <c r="Q501" s="1" t="n">
         <v>0.03212</v>
       </c>
-      <c r="Q501" s="1" t="n">
+      <c r="R501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -28074,9 +29580,12 @@
         <v>0.4432</v>
       </c>
       <c r="P502" s="1" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="Q502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="Q502" s="1" t="n">
+      <c r="R502" s="1" t="n">
         <v>0.4356</v>
       </c>
     </row>
@@ -28129,9 +29638,12 @@
         <v>0.999341</v>
       </c>
       <c r="P503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="Q503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="Q503" s="1" t="n">
+      <c r="R503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -28184,9 +29696,12 @@
         <v>0.03512</v>
       </c>
       <c r="P504" s="1" t="n">
+        <v>0.03513</v>
+      </c>
+      <c r="Q504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="Q504" s="1" t="n">
+      <c r="R504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -28239,9 +29754,12 @@
         <v>0.004941</v>
       </c>
       <c r="P505" s="1" t="n">
+        <v>0.004943</v>
+      </c>
+      <c r="Q505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="Q505" s="1" t="n">
+      <c r="R505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -28294,9 +29812,12 @@
         <v>0.01388</v>
       </c>
       <c r="P506" s="1" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="Q506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="Q506" s="1" t="n">
+      <c r="R506" s="1" t="n">
         <v>0.01388</v>
       </c>
     </row>
@@ -28349,9 +29870,12 @@
         <v>0.003464</v>
       </c>
       <c r="P507" s="1" t="n">
+        <v>0.003478</v>
+      </c>
+      <c r="Q507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="Q507" s="1" t="n">
+      <c r="R507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -28404,9 +29928,12 @@
         <v>1.413</v>
       </c>
       <c r="P508" s="1" t="n">
+        <v>1.414</v>
+      </c>
+      <c r="Q508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="Q508" s="1" t="n">
+      <c r="R508" s="1" t="n">
         <v>1.413</v>
       </c>
     </row>
@@ -28459,9 +29986,12 @@
         <v>0.005067</v>
       </c>
       <c r="P509" s="1" t="n">
+        <v>0.005074</v>
+      </c>
+      <c r="Q509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="Q509" s="1" t="n">
+      <c r="R509" s="1" t="n">
         <v>0.005067</v>
       </c>
     </row>
@@ -28514,10 +30044,13 @@
         <v>0.01572</v>
       </c>
       <c r="P510" s="1" t="n">
+        <v>0.01568</v>
+      </c>
+      <c r="Q510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="Q510" s="1" t="n">
-        <v>0.01571</v>
+      <c r="R510" s="1" t="n">
+        <v>0.01568</v>
       </c>
     </row>
     <row r="511">
@@ -28569,9 +30102,12 @@
         <v>0.08234</v>
       </c>
       <c r="P511" s="1" t="n">
+        <v>0.08227</v>
+      </c>
+      <c r="Q511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="Q511" s="1" t="n">
+      <c r="R511" s="1" t="n">
         <v>0.08212999999999999</v>
       </c>
     </row>
@@ -28624,9 +30160,12 @@
         <v>0.007089</v>
       </c>
       <c r="P512" s="1" t="n">
+        <v>0.007092</v>
+      </c>
+      <c r="Q512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="Q512" s="1" t="n">
+      <c r="R512" s="1" t="n">
         <v>0.007089</v>
       </c>
     </row>
@@ -28679,9 +30218,12 @@
         <v>0.01482</v>
       </c>
       <c r="P513" s="1" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="Q513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="Q513" s="1" t="n">
+      <c r="R513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -28734,9 +30276,12 @@
         <v>0.04746</v>
       </c>
       <c r="P514" s="1" t="n">
+        <v>0.04745</v>
+      </c>
+      <c r="Q514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="Q514" s="1" t="n">
+      <c r="R514" s="1" t="n">
         <v>0.04721</v>
       </c>
     </row>
@@ -28789,10 +30334,13 @@
         <v>0.01811</v>
       </c>
       <c r="P515" s="1" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="Q515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="Q515" s="1" t="n">
-        <v>0.01811</v>
+      <c r="R515" s="1" t="n">
+        <v>0.01808</v>
       </c>
     </row>
     <row r="516">
@@ -28844,9 +30392,12 @@
         <v>0.0005787</v>
       </c>
       <c r="P516" s="1" t="n">
+        <v>0.0005795</v>
+      </c>
+      <c r="Q516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="Q516" s="1" t="n">
+      <c r="R516" s="1" t="n">
         <v>0.0005782</v>
       </c>
     </row>
@@ -28899,9 +30450,12 @@
         <v>0.07849</v>
       </c>
       <c r="P517" s="1" t="n">
+        <v>0.07853</v>
+      </c>
+      <c r="Q517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="Q517" s="1" t="n">
+      <c r="R517" s="1" t="n">
         <v>0.07829</v>
       </c>
     </row>
@@ -28954,9 +30508,12 @@
         <v>0.006376</v>
       </c>
       <c r="P518" s="1" t="n">
+        <v>0.006374</v>
+      </c>
+      <c r="Q518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="Q518" s="1" t="n">
+      <c r="R518" s="1" t="n">
         <v>0.006373</v>
       </c>
     </row>
@@ -29009,9 +30566,12 @@
         <v>0.05765</v>
       </c>
       <c r="P519" s="1" t="n">
+        <v>0.05776</v>
+      </c>
+      <c r="Q519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="Q519" s="1" t="n">
+      <c r="R519" s="1" t="n">
         <v>0.05765</v>
       </c>
     </row>
@@ -29064,10 +30624,13 @@
         <v>0.10462</v>
       </c>
       <c r="P520" s="1" t="n">
+        <v>0.10448</v>
+      </c>
+      <c r="Q520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="Q520" s="1" t="n">
-        <v>0.10461</v>
+      <c r="R520" s="1" t="n">
+        <v>0.10448</v>
       </c>
     </row>
     <row r="521">
@@ -29119,9 +30682,12 @@
         <v>0.01792</v>
       </c>
       <c r="P521" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="Q521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="Q521" s="1" t="n">
+      <c r="R521" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -29174,9 +30740,12 @@
         <v>0.01635</v>
       </c>
       <c r="P522" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="Q522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="Q522" s="1" t="n">
+      <c r="R522" s="1" t="n">
         <v>0.01635</v>
       </c>
     </row>
@@ -29229,10 +30798,13 @@
         <v>0.01084</v>
       </c>
       <c r="P523" s="1" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="Q523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="Q523" s="1" t="n">
-        <v>0.01083</v>
+      <c r="R523" s="1" t="n">
+        <v>0.01079</v>
       </c>
     </row>
     <row r="524">
@@ -29284,9 +30856,12 @@
         <v>0.007196</v>
       </c>
       <c r="P524" s="1" t="n">
-        <v>0.007196</v>
+        <v>0.007244</v>
       </c>
       <c r="Q524" s="1" t="n">
+        <v>0.007244</v>
+      </c>
+      <c r="R524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -29339,10 +30914,13 @@
         <v>0.005837</v>
       </c>
       <c r="P525" s="1" t="n">
+        <v>0.005828</v>
+      </c>
+      <c r="Q525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="Q525" s="1" t="n">
-        <v>0.005837</v>
+      <c r="R525" s="1" t="n">
+        <v>0.005828</v>
       </c>
     </row>
     <row r="526">
@@ -29394,9 +30972,12 @@
         <v>0.001443</v>
       </c>
       <c r="P526" s="1" t="n">
+        <v>0.001437</v>
+      </c>
+      <c r="Q526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="Q526" s="1" t="n">
+      <c r="R526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -29449,9 +31030,12 @@
         <v>0.373</v>
       </c>
       <c r="P527" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="Q527" s="1" t="n">
         <v>0.374</v>
       </c>
-      <c r="Q527" s="1" t="n">
+      <c r="R527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -29504,9 +31088,12 @@
         <v>0.00548</v>
       </c>
       <c r="P528" s="1" t="n">
+        <v>0.005323</v>
+      </c>
+      <c r="Q528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="Q528" s="1" t="n">
+      <c r="R528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -29559,9 +31146,12 @@
         <v>2.952</v>
       </c>
       <c r="P529" s="1" t="n">
+        <v>2.952</v>
+      </c>
+      <c r="Q529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="Q529" s="1" t="n">
+      <c r="R529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -29614,10 +31204,13 @@
         <v>0.1546</v>
       </c>
       <c r="P530" s="1" t="n">
+        <v>0.1545</v>
+      </c>
+      <c r="Q530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="Q530" s="1" t="n">
-        <v>0.1546</v>
+      <c r="R530" s="1" t="n">
+        <v>0.1545</v>
       </c>
     </row>
     <row r="531">
@@ -29669,9 +31262,12 @@
         <v>2561</v>
       </c>
       <c r="P531" s="1" t="n">
+        <v>2559</v>
+      </c>
+      <c r="Q531" s="1" t="n">
         <v>2561</v>
       </c>
-      <c r="Q531" s="1" t="n">
+      <c r="R531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -29724,9 +31320,12 @@
         <v>0.03905</v>
       </c>
       <c r="P532" s="1" t="n">
+        <v>0.03909</v>
+      </c>
+      <c r="Q532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="Q532" s="1" t="n">
+      <c r="R532" s="1" t="n">
         <v>0.03905</v>
       </c>
     </row>
@@ -29779,10 +31378,13 @@
         <v>0.02158</v>
       </c>
       <c r="P533" s="1" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="Q533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="Q533" s="1" t="n">
-        <v>0.02157</v>
+      <c r="R533" s="1" t="n">
+        <v>0.02156</v>
       </c>
     </row>
     <row r="534">
@@ -29834,9 +31436,12 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="P534" s="1" t="n">
+        <v>0.07335999999999999</v>
+      </c>
+      <c r="Q534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="Q534" s="1" t="n">
+      <c r="R534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -29889,9 +31494,12 @@
         <v>0.007863</v>
       </c>
       <c r="P535" s="1" t="n">
+        <v>0.007837999999999999</v>
+      </c>
+      <c r="Q535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="Q535" s="1" t="n">
+      <c r="R535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -29944,9 +31552,12 @@
         <v>0.05008</v>
       </c>
       <c r="P536" s="1" t="n">
+        <v>0.05009</v>
+      </c>
+      <c r="Q536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="Q536" s="1" t="n">
+      <c r="R536" s="1" t="n">
         <v>0.05002</v>
       </c>
     </row>
@@ -29999,10 +31610,13 @@
         <v>0.00403</v>
       </c>
       <c r="P537" s="1" t="n">
+        <v>0.00402</v>
+      </c>
+      <c r="Q537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="Q537" s="1" t="n">
-        <v>0.00403</v>
+      <c r="R537" s="1" t="n">
+        <v>0.00402</v>
       </c>
     </row>
     <row r="538">
@@ -30054,9 +31668,12 @@
         <v>0.08284</v>
       </c>
       <c r="P538" s="1" t="n">
+        <v>0.08289000000000001</v>
+      </c>
+      <c r="Q538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="Q538" s="1" t="n">
+      <c r="R538" s="1" t="n">
         <v>0.08284</v>
       </c>
     </row>
@@ -30109,10 +31726,13 @@
         <v>0.02484</v>
       </c>
       <c r="P539" s="1" t="n">
+        <v>0.02483</v>
+      </c>
+      <c r="Q539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="Q539" s="1" t="n">
-        <v>0.02484</v>
+      <c r="R539" s="1" t="n">
+        <v>0.02483</v>
       </c>
     </row>
     <row r="540">
@@ -30164,9 +31784,12 @@
         <v>0.08406</v>
       </c>
       <c r="P540" s="1" t="n">
+        <v>0.08424</v>
+      </c>
+      <c r="Q540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="Q540" s="1" t="n">
+      <c r="R540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -30219,9 +31842,12 @@
         <v>0.01882</v>
       </c>
       <c r="P541" s="1" t="n">
+        <v>0.01883</v>
+      </c>
+      <c r="Q541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="Q541" s="1" t="n">
+      <c r="R541" s="1" t="n">
         <v>0.01882</v>
       </c>
     </row>
@@ -30274,9 +31900,12 @@
         <v>0.01685</v>
       </c>
       <c r="P542" s="1" t="n">
+        <v>0.01687</v>
+      </c>
+      <c r="Q542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="Q542" s="1" t="n">
+      <c r="R542" s="1" t="n">
         <v>0.01685</v>
       </c>
     </row>
@@ -30329,9 +31958,12 @@
         <v>0.1048</v>
       </c>
       <c r="P543" s="1" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="Q543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="Q543" s="1" t="n">
+      <c r="R543" s="1" t="n">
         <v>0.1047</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V543"/>
+  <dimension ref="A1:W543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -439,8 +439,9 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,10 +547,15 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>price_05:00</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -619,9 +625,12 @@
         <v>70796.5</v>
       </c>
       <c r="U2" s="1" t="n">
+        <v>70765.3</v>
+      </c>
+      <c r="V2" s="1" t="n">
         <v>70796.5</v>
       </c>
-      <c r="V2" s="1" t="n">
+      <c r="W2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -689,9 +698,12 @@
         <v>2083.29</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>2083.29</v>
+        <v>2084.79</v>
       </c>
       <c r="V3" s="1" t="n">
+        <v>2084.79</v>
+      </c>
+      <c r="W3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -759,9 +771,12 @@
         <v>87.05</v>
       </c>
       <c r="U4" s="1" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="V4" s="1" t="n">
         <v>87.05</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="W4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -829,10 +844,13 @@
         <v>3.994</v>
       </c>
       <c r="U5" s="1" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="V5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="V5" s="1" t="n">
-        <v>3.991</v>
+      <c r="W5" s="1" t="n">
+        <v>3.967</v>
       </c>
     </row>
     <row r="6">
@@ -899,9 +917,12 @@
         <v>0.09483</v>
       </c>
       <c r="U6" s="1" t="n">
+        <v>0.09478</v>
+      </c>
+      <c r="V6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="W6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -969,9 +990,12 @@
         <v>1.3929</v>
       </c>
       <c r="U7" s="1" t="n">
+        <v>1.3923</v>
+      </c>
+      <c r="V7" s="1" t="n">
         <v>1.3929</v>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="W7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -1039,9 +1063,12 @@
         <v>21.944</v>
       </c>
       <c r="U8" s="1" t="n">
+        <v>21.923</v>
+      </c>
+      <c r="V8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="V8" s="1" t="n">
+      <c r="W8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1109,9 +1136,12 @@
         <v>0.001951</v>
       </c>
       <c r="U9" s="1" t="n">
+        <v>0.002045</v>
+      </c>
+      <c r="V9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="V9" s="1" t="n">
+      <c r="W9" s="1" t="n">
         <v>0.001951</v>
       </c>
     </row>
@@ -1179,9 +1209,12 @@
         <v>0.009974</v>
       </c>
       <c r="U10" s="1" t="n">
+        <v>0.010015</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="V10" s="1" t="n">
+      <c r="W10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1249,9 +1282,12 @@
         <v>0.15083</v>
       </c>
       <c r="U11" s="1" t="n">
+        <v>0.14558</v>
+      </c>
+      <c r="V11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="V11" s="1" t="n">
+      <c r="W11" s="1" t="n">
         <v>0.13631</v>
       </c>
     </row>
@@ -1319,10 +1355,13 @@
         <v>0.011307</v>
       </c>
       <c r="U12" s="1" t="n">
+        <v>0.011051</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="V12" s="1" t="n">
-        <v>0.011225</v>
+      <c r="W12" s="1" t="n">
+        <v>0.011051</v>
       </c>
     </row>
     <row r="13">
@@ -1389,9 +1428,12 @@
         <v>37.748</v>
       </c>
       <c r="U13" s="1" t="n">
+        <v>37.761</v>
+      </c>
+      <c r="V13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="V13" s="1" t="n">
+      <c r="W13" s="1" t="n">
         <v>37.748</v>
       </c>
     </row>
@@ -1459,9 +1501,12 @@
         <v>654.13</v>
       </c>
       <c r="U14" s="1" t="n">
+        <v>653.89</v>
+      </c>
+      <c r="V14" s="1" t="n">
         <v>654.13</v>
       </c>
-      <c r="V14" s="1" t="n">
+      <c r="W14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1529,9 +1574,12 @@
         <v>209.96</v>
       </c>
       <c r="U15" s="1" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>210.26</v>
       </c>
-      <c r="V15" s="1" t="n">
+      <c r="W15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1599,9 +1647,12 @@
         <v>0.0033231</v>
       </c>
       <c r="U16" s="1" t="n">
+        <v>0.0033203</v>
+      </c>
+      <c r="V16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="V16" s="1" t="n">
+      <c r="W16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1669,9 +1720,12 @@
         <v>240.32</v>
       </c>
       <c r="U17" s="1" t="n">
+        <v>239.37</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>240.32</v>
       </c>
-      <c r="V17" s="1" t="n">
+      <c r="W17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1739,9 +1793,12 @@
         <v>0.9878</v>
       </c>
       <c r="U18" s="1" t="n">
+        <v>0.9876</v>
+      </c>
+      <c r="V18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="V18" s="1" t="n">
+      <c r="W18" s="1" t="n">
         <v>0.9858</v>
       </c>
     </row>
@@ -1809,9 +1866,12 @@
         <v>1</v>
       </c>
       <c r="U19" s="1" t="n">
+        <v>1.0006</v>
+      </c>
+      <c r="V19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="V19" s="1" t="n">
+      <c r="W19" s="1" t="n">
         <v>0.9972</v>
       </c>
     </row>
@@ -1879,9 +1939,12 @@
         <v>0.2596</v>
       </c>
       <c r="U20" s="1" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="V20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="V20" s="1" t="n">
+      <c r="W20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -1949,9 +2012,12 @@
         <v>0.59321</v>
       </c>
       <c r="U21" s="1" t="n">
+        <v>0.59222</v>
+      </c>
+      <c r="V21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="V21" s="1" t="n">
+      <c r="W21" s="1" t="n">
         <v>0.59034</v>
       </c>
     </row>
@@ -2019,9 +2085,12 @@
         <v>9.029999999999999</v>
       </c>
       <c r="U22" s="1" t="n">
+        <v>9.036</v>
+      </c>
+      <c r="V22" s="1" t="n">
         <v>9.042</v>
       </c>
-      <c r="V22" s="1" t="n">
+      <c r="W22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -2089,10 +2158,13 @@
         <v>0.02367</v>
       </c>
       <c r="U23" s="1" t="n">
+        <v>0.02359</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="V23" s="1" t="n">
-        <v>0.02367</v>
+      <c r="W23" s="1" t="n">
+        <v>0.02359</v>
       </c>
     </row>
     <row r="24">
@@ -2159,9 +2231,12 @@
         <v>9.593</v>
       </c>
       <c r="U24" s="1" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="V24" s="1" t="n">
+      <c r="W24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2229,9 +2304,12 @@
         <v>1.227</v>
       </c>
       <c r="U25" s="1" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="V25" s="1" t="n">
+      <c r="W25" s="1" t="n">
         <v>1.218</v>
       </c>
     </row>
@@ -2299,9 +2377,12 @@
         <v>0.07269</v>
       </c>
       <c r="U26" s="1" t="n">
+        <v>0.07284</v>
+      </c>
+      <c r="V26" s="1" t="n">
         <v>0.07317</v>
       </c>
-      <c r="V26" s="1" t="n">
+      <c r="W26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2369,9 +2450,12 @@
         <v>1.415</v>
       </c>
       <c r="U27" s="1" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="V27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="V27" s="1" t="n">
+      <c r="W27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2439,9 +2523,12 @@
         <v>1.307</v>
       </c>
       <c r="U28" s="1" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="V28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="V28" s="1" t="n">
+      <c r="W28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2509,9 +2596,12 @@
         <v>464.27</v>
       </c>
       <c r="U29" s="1" t="n">
+        <v>464.14</v>
+      </c>
+      <c r="V29" s="1" t="n">
         <v>464.27</v>
       </c>
-      <c r="V29" s="1" t="n">
+      <c r="W29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2579,9 +2669,12 @@
         <v>1.2937</v>
       </c>
       <c r="U30" s="1" t="n">
+        <v>1.2889</v>
+      </c>
+      <c r="V30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="V30" s="1" t="n">
+      <c r="W30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2649,10 +2742,13 @@
         <v>5019.42</v>
       </c>
       <c r="U31" s="1" t="n">
+        <v>5019.32</v>
+      </c>
+      <c r="V31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="V31" s="1" t="n">
-        <v>5019.42</v>
+      <c r="W31" s="1" t="n">
+        <v>5019.32</v>
       </c>
     </row>
     <row r="32">
@@ -2719,9 +2815,12 @@
         <v>0.877</v>
       </c>
       <c r="U32" s="1" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="V32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="V32" s="1" t="n">
+      <c r="W32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2789,9 +2888,12 @@
         <v>0.001972</v>
       </c>
       <c r="U33" s="1" t="n">
+        <v>0.00197</v>
+      </c>
+      <c r="V33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="V33" s="1" t="n">
+      <c r="W33" s="1" t="n">
         <v>0.001966</v>
       </c>
     </row>
@@ -2859,9 +2961,12 @@
         <v>0.17484</v>
       </c>
       <c r="U34" s="1" t="n">
+        <v>0.17388</v>
+      </c>
+      <c r="V34" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="V34" s="1" t="n">
+      <c r="W34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -2929,9 +3034,12 @@
         <v>0.29695</v>
       </c>
       <c r="U35" s="1" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="V35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="V35" s="1" t="n">
+      <c r="W35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -2999,9 +3107,12 @@
         <v>1.795</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>1.795</v>
+        <v>1.798</v>
       </c>
       <c r="V36" s="1" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="W36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -3069,9 +3180,12 @@
         <v>110.49</v>
       </c>
       <c r="U37" s="1" t="n">
+        <v>110.44</v>
+      </c>
+      <c r="V37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="V37" s="1" t="n">
+      <c r="W37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -3139,9 +3253,12 @@
         <v>0.22043</v>
       </c>
       <c r="U38" s="1" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="V38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="V38" s="1" t="n">
+      <c r="W38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -3209,9 +3326,12 @@
         <v>0.1068</v>
       </c>
       <c r="U39" s="1" t="n">
+        <v>0.1067</v>
+      </c>
+      <c r="V39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="V39" s="1" t="n">
+      <c r="W39" s="1" t="n">
         <v>0.1066</v>
       </c>
     </row>
@@ -3279,9 +3399,12 @@
         <v>0.37429</v>
       </c>
       <c r="U40" s="1" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="V40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="V40" s="1" t="n">
+      <c r="W40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -3349,9 +3472,12 @@
         <v>54.64</v>
       </c>
       <c r="U41" s="1" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="V41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="V41" s="1" t="n">
+      <c r="W41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3419,9 +3545,12 @@
         <v>0.001058</v>
       </c>
       <c r="U42" s="1" t="n">
+        <v>0.0010552</v>
+      </c>
+      <c r="V42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="V42" s="1" t="n">
+      <c r="W42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -3489,9 +3618,12 @@
         <v>6.519</v>
       </c>
       <c r="U43" s="1" t="n">
+        <v>6.482</v>
+      </c>
+      <c r="V43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="V43" s="1" t="n">
+      <c r="W43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3559,9 +3691,12 @@
         <v>0.6259</v>
       </c>
       <c r="U44" s="1" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="V44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="V44" s="1" t="n">
+      <c r="W44" s="1" t="n">
         <v>0.6213</v>
       </c>
     </row>
@@ -3629,9 +3764,12 @@
         <v>0.3522</v>
       </c>
       <c r="U45" s="1" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="V45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="V45" s="1" t="n">
+      <c r="W45" s="1" t="n">
         <v>0.3512</v>
       </c>
     </row>
@@ -3699,9 +3837,12 @@
         <v>0.0328</v>
       </c>
       <c r="U46" s="1" t="n">
+        <v>0.03278</v>
+      </c>
+      <c r="V46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="V46" s="1" t="n">
+      <c r="W46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -3769,10 +3910,13 @@
         <v>0.06927999999999999</v>
       </c>
       <c r="U47" s="1" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="V47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="V47" s="1" t="n">
-        <v>0.06920999999999999</v>
+      <c r="W47" s="1" t="n">
+        <v>0.0687</v>
       </c>
     </row>
     <row r="48">
@@ -3839,9 +3983,12 @@
         <v>0.7065</v>
       </c>
       <c r="U48" s="1" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="V48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="V48" s="1" t="n">
+      <c r="W48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -3909,9 +4056,12 @@
         <v>0.004267</v>
       </c>
       <c r="U49" s="1" t="n">
+        <v>0.004246</v>
+      </c>
+      <c r="V49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="V49" s="1" t="n">
+      <c r="W49" s="1" t="n">
         <v>0.004224</v>
       </c>
     </row>
@@ -3979,9 +4129,12 @@
         <v>0.1034</v>
       </c>
       <c r="U50" s="1" t="n">
+        <v>0.1031</v>
+      </c>
+      <c r="V50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="V50" s="1" t="n">
+      <c r="W50" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -4049,9 +4202,12 @@
         <v>0.04033</v>
       </c>
       <c r="U51" s="1" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="V51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="V51" s="1" t="n">
+      <c r="W51" s="1" t="n">
         <v>0.04021</v>
       </c>
     </row>
@@ -4119,9 +4275,12 @@
         <v>0.1647</v>
       </c>
       <c r="U52" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="V52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="V52" s="1" t="n">
+      <c r="W52" s="1" t="n">
         <v>0.1645</v>
       </c>
     </row>
@@ -4189,9 +4348,12 @@
         <v>0.01922</v>
       </c>
       <c r="U53" s="1" t="n">
+        <v>0.01932</v>
+      </c>
+      <c r="V53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="V53" s="1" t="n">
+      <c r="W53" s="1" t="n">
         <v>0.01922</v>
       </c>
     </row>
@@ -4259,9 +4421,12 @@
         <v>0.007188</v>
       </c>
       <c r="U54" s="1" t="n">
+        <v>0.007178</v>
+      </c>
+      <c r="V54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="V54" s="1" t="n">
+      <c r="W54" s="1" t="n">
         <v>0.00717</v>
       </c>
     </row>
@@ -4329,9 +4494,12 @@
         <v>3.926</v>
       </c>
       <c r="U55" s="1" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="V55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="V55" s="1" t="n">
+      <c r="W55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -4399,9 +4567,12 @@
         <v>0.016874</v>
       </c>
       <c r="U56" s="1" t="n">
+        <v>0.01692</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="V56" s="1" t="n">
+      <c r="W56" s="1" t="n">
         <v>0.016808</v>
       </c>
     </row>
@@ -4469,9 +4640,12 @@
         <v>0.1084</v>
       </c>
       <c r="U57" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="V57" s="1" t="n">
+      <c r="W57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -4539,9 +4713,12 @@
         <v>2.647</v>
       </c>
       <c r="U58" s="1" t="n">
+        <v>2.643</v>
+      </c>
+      <c r="V58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="V58" s="1" t="n">
+      <c r="W58" s="1" t="n">
         <v>2.639</v>
       </c>
     </row>
@@ -4609,9 +4786,12 @@
         <v>0.1589</v>
       </c>
       <c r="U59" s="1" t="n">
+        <v>0.1584</v>
+      </c>
+      <c r="V59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="V59" s="1" t="n">
+      <c r="W59" s="1" t="n">
         <v>0.1582</v>
       </c>
     </row>
@@ -4679,9 +4859,12 @@
         <v>0.005845</v>
       </c>
       <c r="U60" s="1" t="n">
+        <v>0.005843</v>
+      </c>
+      <c r="V60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="V60" s="1" t="n">
+      <c r="W60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -4749,9 +4932,12 @@
         <v>0.09182</v>
       </c>
       <c r="U61" s="1" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="V61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="V61" s="1" t="n">
+      <c r="W61" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -4819,9 +5005,12 @@
         <v>0.9125</v>
       </c>
       <c r="U62" s="1" t="n">
+        <v>0.9122</v>
+      </c>
+      <c r="V62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="V62" s="1" t="n">
+      <c r="W62" s="1" t="n">
         <v>0.9101</v>
       </c>
     </row>
@@ -4889,9 +5078,12 @@
         <v>0.779</v>
       </c>
       <c r="U63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="V63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="V63" s="1" t="n">
+      <c r="W63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -4959,9 +5151,12 @@
         <v>0.04595</v>
       </c>
       <c r="U64" s="1" t="n">
+        <v>0.04599</v>
+      </c>
+      <c r="V64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="V64" s="1" t="n">
+      <c r="W64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -5029,9 +5224,12 @@
         <v>356.47</v>
       </c>
       <c r="U65" s="1" t="n">
+        <v>356.31</v>
+      </c>
+      <c r="V65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="V65" s="1" t="n">
+      <c r="W65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -5099,9 +5297,12 @@
         <v>0.12519</v>
       </c>
       <c r="U66" s="1" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="V66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="V66" s="1" t="n">
+      <c r="W66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -5169,9 +5370,12 @@
         <v>0.2324</v>
       </c>
       <c r="U67" s="1" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="V67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="V67" s="1" t="n">
+      <c r="W67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -5239,9 +5443,12 @@
         <v>0.00338</v>
       </c>
       <c r="U68" s="1" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="V68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="V68" s="1" t="n">
+      <c r="W68" s="1" t="n">
         <v>0.00337</v>
       </c>
     </row>
@@ -5309,9 +5516,12 @@
         <v>0.1748</v>
       </c>
       <c r="U69" s="1" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="V69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="V69" s="1" t="n">
+      <c r="W69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -5379,9 +5589,12 @@
         <v>0.16409</v>
       </c>
       <c r="U70" s="1" t="n">
+        <v>0.16395</v>
+      </c>
+      <c r="V70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="V70" s="1" t="n">
+      <c r="W70" s="1" t="n">
         <v>0.16358</v>
       </c>
     </row>
@@ -5449,9 +5662,12 @@
         <v>0.3573</v>
       </c>
       <c r="U71" s="1" t="n">
-        <v>0.3574</v>
+        <v>0.3599</v>
       </c>
       <c r="V71" s="1" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="W71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -5519,9 +5735,12 @@
         <v>0.7099</v>
       </c>
       <c r="U72" s="1" t="n">
+        <v>0.7078</v>
+      </c>
+      <c r="V72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="V72" s="1" t="n">
+      <c r="W72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -5589,9 +5808,12 @@
         <v>0.008630000000000001</v>
       </c>
       <c r="U73" s="1" t="n">
+        <v>0.008580000000000001</v>
+      </c>
+      <c r="V73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="V73" s="1" t="n">
+      <c r="W73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -5659,9 +5881,12 @@
         <v>0.005976</v>
       </c>
       <c r="U74" s="1" t="n">
+        <v>0.005965</v>
+      </c>
+      <c r="V74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="V74" s="1" t="n">
+      <c r="W74" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -5732,6 +5957,9 @@
         <v>0.229</v>
       </c>
       <c r="V75" s="1" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="W75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -5799,9 +6027,12 @@
         <v>0.3269</v>
       </c>
       <c r="U76" s="1" t="n">
-        <v>0.3278</v>
+        <v>0.3287</v>
       </c>
       <c r="V76" s="1" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="W76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -5869,9 +6100,12 @@
         <v>0.1002</v>
       </c>
       <c r="U77" s="1" t="n">
+        <v>0.1001</v>
+      </c>
+      <c r="V77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="V77" s="1" t="n">
+      <c r="W77" s="1" t="n">
         <v>0.0999</v>
       </c>
     </row>
@@ -5939,9 +6173,12 @@
         <v>0.1226</v>
       </c>
       <c r="U78" s="1" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="V78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="V78" s="1" t="n">
+      <c r="W78" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -6009,9 +6246,12 @@
         <v>0.07549</v>
       </c>
       <c r="U79" s="1" t="n">
+        <v>0.07439</v>
+      </c>
+      <c r="V79" s="1" t="n">
         <v>0.07549</v>
       </c>
-      <c r="V79" s="1" t="n">
+      <c r="W79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -6079,10 +6319,13 @@
         <v>0.04628</v>
       </c>
       <c r="U80" s="1" t="n">
+        <v>0.04623</v>
+      </c>
+      <c r="V80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="V80" s="1" t="n">
-        <v>0.04628</v>
+      <c r="W80" s="1" t="n">
+        <v>0.04623</v>
       </c>
     </row>
     <row r="81">
@@ -6149,9 +6392,12 @@
         <v>0.000232</v>
       </c>
       <c r="U81" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="V81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="V81" s="1" t="n">
+      <c r="W81" s="1" t="n">
         <v>0.000228</v>
       </c>
     </row>
@@ -6219,9 +6465,12 @@
         <v>8.212</v>
       </c>
       <c r="U82" s="1" t="n">
+        <v>8.206</v>
+      </c>
+      <c r="V82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="V82" s="1" t="n">
+      <c r="W82" s="1" t="n">
         <v>8.194000000000001</v>
       </c>
     </row>
@@ -6289,9 +6538,12 @@
         <v>0.0005761</v>
       </c>
       <c r="U83" s="1" t="n">
+        <v>0.0005734</v>
+      </c>
+      <c r="V83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="V83" s="1" t="n">
+      <c r="W83" s="1" t="n">
         <v>0.0005713</v>
       </c>
     </row>
@@ -6359,9 +6611,12 @@
         <v>0.4474</v>
       </c>
       <c r="U84" s="1" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="V84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="V84" s="1" t="n">
+      <c r="W84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6429,9 +6684,12 @@
         <v>0.06241</v>
       </c>
       <c r="U85" s="1" t="n">
+        <v>0.06242</v>
+      </c>
+      <c r="V85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="V85" s="1" t="n">
+      <c r="W85" s="1" t="n">
         <v>0.0623</v>
       </c>
     </row>
@@ -6499,9 +6757,12 @@
         <v>0.05425</v>
       </c>
       <c r="U86" s="1" t="n">
+        <v>0.05413</v>
+      </c>
+      <c r="V86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="V86" s="1" t="n">
+      <c r="W86" s="1" t="n">
         <v>0.05403</v>
       </c>
     </row>
@@ -6569,9 +6830,12 @@
         <v>0.003355</v>
       </c>
       <c r="U87" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="V87" s="1" t="n">
         <v>0.003366</v>
       </c>
-      <c r="V87" s="1" t="n">
+      <c r="W87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -6639,9 +6903,12 @@
         <v>0.05009</v>
       </c>
       <c r="U88" s="1" t="n">
+        <v>0.05011</v>
+      </c>
+      <c r="V88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="V88" s="1" t="n">
+      <c r="W88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -6709,9 +6976,12 @@
         <v>0.03192</v>
       </c>
       <c r="U89" s="1" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="V89" s="1" t="n">
         <v>0.03192</v>
       </c>
-      <c r="V89" s="1" t="n">
+      <c r="W89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -6779,9 +7049,12 @@
         <v>0.3444</v>
       </c>
       <c r="U90" s="1" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="V90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="V90" s="1" t="n">
+      <c r="W90" s="1" t="n">
         <v>0.3442</v>
       </c>
     </row>
@@ -6849,9 +7122,12 @@
         <v>0.07452</v>
       </c>
       <c r="U91" s="1" t="n">
+        <v>0.07434</v>
+      </c>
+      <c r="V91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="V91" s="1" t="n">
+      <c r="W91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -6919,9 +7195,12 @@
         <v>0.3595</v>
       </c>
       <c r="U92" s="1" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="V92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="V92" s="1" t="n">
+      <c r="W92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -6989,9 +7268,12 @@
         <v>1.9759</v>
       </c>
       <c r="U93" s="1" t="n">
-        <v>1.9809</v>
+        <v>1.9816</v>
       </c>
       <c r="V93" s="1" t="n">
+        <v>1.9816</v>
+      </c>
+      <c r="W93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -7059,9 +7341,12 @@
         <v>0.2589</v>
       </c>
       <c r="U94" s="1" t="n">
+        <v>0.2587</v>
+      </c>
+      <c r="V94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="V94" s="1" t="n">
+      <c r="W94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -7129,9 +7414,12 @@
         <v>0.04529</v>
       </c>
       <c r="U95" s="1" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="V95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="V95" s="1" t="n">
+      <c r="W95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -7199,9 +7487,12 @@
         <v>0.006202</v>
       </c>
       <c r="U96" s="1" t="n">
+        <v>0.006176</v>
+      </c>
+      <c r="V96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="V96" s="1" t="n">
+      <c r="W96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -7269,9 +7560,12 @@
         <v>0.001707</v>
       </c>
       <c r="U97" s="1" t="n">
+        <v>0.001708</v>
+      </c>
+      <c r="V97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="V97" s="1" t="n">
+      <c r="W97" s="1" t="n">
         <v>0.001706</v>
       </c>
     </row>
@@ -7339,9 +7633,12 @@
         <v>5.215</v>
       </c>
       <c r="U98" s="1" t="n">
+        <v>5.198</v>
+      </c>
+      <c r="V98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="V98" s="1" t="n">
+      <c r="W98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -7409,10 +7706,13 @@
         <v>0.01507</v>
       </c>
       <c r="U99" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="V99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="V99" s="1" t="n">
-        <v>0.01503</v>
+      <c r="W99" s="1" t="n">
+        <v>0.01501</v>
       </c>
     </row>
     <row r="100">
@@ -7479,9 +7779,12 @@
         <v>0.551</v>
       </c>
       <c r="U100" s="1" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="V100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="V100" s="1" t="n">
+      <c r="W100" s="1" t="n">
         <v>0.5508</v>
       </c>
     </row>
@@ -7549,9 +7852,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="U101" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="V101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="V101" s="1" t="n">
+      <c r="W101" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -7619,9 +7925,12 @@
         <v>32.36</v>
       </c>
       <c r="U102" s="1" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="V102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="V102" s="1" t="n">
+      <c r="W102" s="1" t="n">
         <v>32.29</v>
       </c>
     </row>
@@ -7689,9 +7998,12 @@
         <v>0.03223</v>
       </c>
       <c r="U103" s="1" t="n">
+        <v>0.03226</v>
+      </c>
+      <c r="V103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="V103" s="1" t="n">
+      <c r="W103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -7759,10 +8071,13 @@
         <v>0.06571</v>
       </c>
       <c r="U104" s="1" t="n">
+        <v>0.06558</v>
+      </c>
+      <c r="V104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="V104" s="1" t="n">
-        <v>0.06559</v>
+      <c r="W104" s="1" t="n">
+        <v>0.06558</v>
       </c>
     </row>
     <row r="105">
@@ -7829,9 +8144,12 @@
         <v>1.3024</v>
       </c>
       <c r="U105" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="V105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="V105" s="1" t="n">
+      <c r="W105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -7899,9 +8217,12 @@
         <v>0.1201</v>
       </c>
       <c r="U106" s="1" t="n">
+        <v>0.1201</v>
+      </c>
+      <c r="V106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="V106" s="1" t="n">
+      <c r="W106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -7969,9 +8290,12 @@
         <v>0.119</v>
       </c>
       <c r="U107" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="V107" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="V107" s="1" t="n">
+      <c r="W107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -8039,9 +8363,12 @@
         <v>0.09574000000000001</v>
       </c>
       <c r="U108" s="1" t="n">
+        <v>0.09574000000000001</v>
+      </c>
+      <c r="V108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="V108" s="1" t="n">
+      <c r="W108" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -8109,9 +8436,12 @@
         <v>0.13981</v>
       </c>
       <c r="U109" s="1" t="n">
+        <v>0.14021</v>
+      </c>
+      <c r="V109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="V109" s="1" t="n">
+      <c r="W109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -8179,9 +8509,12 @@
         <v>5.569</v>
       </c>
       <c r="U110" s="1" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="V110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="V110" s="1" t="n">
+      <c r="W110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -8249,9 +8582,12 @@
         <v>1.1</v>
       </c>
       <c r="U111" s="1" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="V111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="V111" s="1" t="n">
+      <c r="W111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -8319,9 +8655,12 @@
         <v>0.02881</v>
       </c>
       <c r="U112" s="1" t="n">
+        <v>0.028749</v>
+      </c>
+      <c r="V112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="V112" s="1" t="n">
+      <c r="W112" s="1" t="n">
         <v>0.028743</v>
       </c>
     </row>
@@ -8389,9 +8728,12 @@
         <v>1.865</v>
       </c>
       <c r="U113" s="1" t="n">
+        <v>1.863</v>
+      </c>
+      <c r="V113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="V113" s="1" t="n">
+      <c r="W113" s="1" t="n">
         <v>1.862</v>
       </c>
     </row>
@@ -8459,9 +8801,12 @@
         <v>0.05912</v>
       </c>
       <c r="U114" s="1" t="n">
+        <v>0.05924</v>
+      </c>
+      <c r="V114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="V114" s="1" t="n">
+      <c r="W114" s="1" t="n">
         <v>0.05848</v>
       </c>
     </row>
@@ -8529,9 +8874,12 @@
         <v>0.12769</v>
       </c>
       <c r="U115" s="1" t="n">
+        <v>0.12783</v>
+      </c>
+      <c r="V115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="V115" s="1" t="n">
+      <c r="W115" s="1" t="n">
         <v>0.12732</v>
       </c>
     </row>
@@ -8599,9 +8947,12 @@
         <v>1.0959</v>
       </c>
       <c r="U116" s="1" t="n">
+        <v>1.0959</v>
+      </c>
+      <c r="V116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="V116" s="1" t="n">
+      <c r="W116" s="1" t="n">
         <v>1.0959</v>
       </c>
     </row>
@@ -8669,9 +9020,12 @@
         <v>0.1496</v>
       </c>
       <c r="U117" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="V117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="V117" s="1" t="n">
+      <c r="W117" s="1" t="n">
         <v>0.1484</v>
       </c>
     </row>
@@ -8739,9 +9093,12 @@
         <v>0.1585</v>
       </c>
       <c r="U118" s="1" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="V118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="V118" s="1" t="n">
+      <c r="W118" s="1" t="n">
         <v>0.158</v>
       </c>
     </row>
@@ -8809,9 +9166,12 @@
         <v>0.04685</v>
       </c>
       <c r="U119" s="1" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="V119" s="1" t="n">
         <v>0.04769</v>
       </c>
-      <c r="V119" s="1" t="n">
+      <c r="W119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -8879,9 +9239,12 @@
         <v>3.013</v>
       </c>
       <c r="U120" s="1" t="n">
+        <v>3.016</v>
+      </c>
+      <c r="V120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="V120" s="1" t="n">
+      <c r="W120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -8949,9 +9312,12 @@
         <v>0.2975</v>
       </c>
       <c r="U121" s="1" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="V121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="V121" s="1" t="n">
+      <c r="W121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -9019,9 +9385,12 @@
         <v>0.5785</v>
       </c>
       <c r="U122" s="1" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="V122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="V122" s="1" t="n">
+      <c r="W122" s="1" t="n">
         <v>0.5770999999999999</v>
       </c>
     </row>
@@ -9089,9 +9458,12 @@
         <v>0.01251</v>
       </c>
       <c r="U123" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="V123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="V123" s="1" t="n">
+      <c r="W123" s="1" t="n">
         <v>0.01251</v>
       </c>
     </row>
@@ -9159,9 +9531,12 @@
         <v>0.1571</v>
       </c>
       <c r="U124" s="1" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="V124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="V124" s="1" t="n">
+      <c r="W124" s="1" t="n">
         <v>0.1569</v>
       </c>
     </row>
@@ -9232,6 +9607,9 @@
         <v>0.001786</v>
       </c>
       <c r="V125" s="1" t="n">
+        <v>0.001786</v>
+      </c>
+      <c r="W125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -9299,9 +9677,12 @@
         <v>0.0004844</v>
       </c>
       <c r="U126" s="1" t="n">
+        <v>0.0004831</v>
+      </c>
+      <c r="V126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="V126" s="1" t="n">
+      <c r="W126" s="1" t="n">
         <v>0.0004824</v>
       </c>
     </row>
@@ -9369,9 +9750,12 @@
         <v>0.02932</v>
       </c>
       <c r="U127" s="1" t="n">
+        <v>0.02926</v>
+      </c>
+      <c r="V127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="V127" s="1" t="n">
+      <c r="W127" s="1" t="n">
         <v>0.02924</v>
       </c>
     </row>
@@ -9439,9 +9823,12 @@
         <v>0.0413</v>
       </c>
       <c r="U128" s="1" t="n">
+        <v>0.04125</v>
+      </c>
+      <c r="V128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="V128" s="1" t="n">
+      <c r="W128" s="1" t="n">
         <v>0.04116</v>
       </c>
     </row>
@@ -9509,9 +9896,12 @@
         <v>0.04906</v>
       </c>
       <c r="U129" s="1" t="n">
+        <v>0.04913</v>
+      </c>
+      <c r="V129" s="1" t="n">
         <v>0.04935</v>
       </c>
-      <c r="V129" s="1" t="n">
+      <c r="W129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -9579,9 +9969,12 @@
         <v>1.21e-05</v>
       </c>
       <c r="U130" s="1" t="n">
+        <v>1.22e-05</v>
+      </c>
+      <c r="V130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="V130" s="1" t="n">
+      <c r="W130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -9652,6 +10045,9 @@
         <v>7.5e-06</v>
       </c>
       <c r="V131" s="1" t="n">
+        <v>7.5e-06</v>
+      </c>
+      <c r="W131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -9719,9 +10115,12 @@
         <v>0.00699</v>
       </c>
       <c r="U132" s="1" t="n">
-        <v>0.00703</v>
+        <v>0.00705</v>
       </c>
       <c r="V132" s="1" t="n">
+        <v>0.00705</v>
+      </c>
+      <c r="W132" s="1" t="n">
         <v>0.00697</v>
       </c>
     </row>
@@ -9789,9 +10188,12 @@
         <v>0.0963</v>
       </c>
       <c r="U133" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="V133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="V133" s="1" t="n">
+      <c r="W133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -9859,9 +10261,12 @@
         <v>0.0004107</v>
       </c>
       <c r="U134" s="1" t="n">
+        <v>0.0004099</v>
+      </c>
+      <c r="V134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="V134" s="1" t="n">
+      <c r="W134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -9929,9 +10334,12 @@
         <v>0.08183</v>
       </c>
       <c r="U135" s="1" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="V135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="V135" s="1" t="n">
+      <c r="W135" s="1" t="n">
         <v>0.08148</v>
       </c>
     </row>
@@ -9999,10 +10407,13 @@
         <v>0.007844</v>
       </c>
       <c r="U136" s="1" t="n">
+        <v>0.007757</v>
+      </c>
+      <c r="V136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="V136" s="1" t="n">
-        <v>0.0078</v>
+      <c r="W136" s="1" t="n">
+        <v>0.007757</v>
       </c>
     </row>
     <row r="137">
@@ -10069,10 +10480,13 @@
         <v>0.0008079</v>
       </c>
       <c r="U137" s="1" t="n">
+        <v>0.000802</v>
+      </c>
+      <c r="V137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="V137" s="1" t="n">
-        <v>0.0008066</v>
+      <c r="W137" s="1" t="n">
+        <v>0.000802</v>
       </c>
     </row>
     <row r="138">
@@ -10139,9 +10553,12 @@
         <v>0.1454</v>
       </c>
       <c r="U138" s="1" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="V138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="V138" s="1" t="n">
+      <c r="W138" s="1" t="n">
         <v>0.1453</v>
       </c>
     </row>
@@ -10209,10 +10626,13 @@
         <v>0.006679</v>
       </c>
       <c r="U139" s="1" t="n">
+        <v>0.00667</v>
+      </c>
+      <c r="V139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="V139" s="1" t="n">
-        <v>0.006677</v>
+      <c r="W139" s="1" t="n">
+        <v>0.00667</v>
       </c>
     </row>
     <row r="140">
@@ -10279,10 +10699,13 @@
         <v>0.01378</v>
       </c>
       <c r="U140" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="V140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="V140" s="1" t="n">
-        <v>0.01377</v>
+      <c r="W140" s="1" t="n">
+        <v>0.01374</v>
       </c>
     </row>
     <row r="141">
@@ -10349,10 +10772,13 @@
         <v>0.09668</v>
       </c>
       <c r="U141" s="1" t="n">
+        <v>0.09646</v>
+      </c>
+      <c r="V141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="V141" s="1" t="n">
-        <v>0.09667000000000001</v>
+      <c r="W141" s="1" t="n">
+        <v>0.09646</v>
       </c>
     </row>
     <row r="142">
@@ -10419,9 +10845,12 @@
         <v>0.0541</v>
       </c>
       <c r="U142" s="1" t="n">
+        <v>0.05411</v>
+      </c>
+      <c r="V142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="V142" s="1" t="n">
+      <c r="W142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -10489,9 +10918,12 @@
         <v>0.3225</v>
       </c>
       <c r="U143" s="1" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="V143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="V143" s="1" t="n">
+      <c r="W143" s="1" t="n">
         <v>0.3219</v>
       </c>
     </row>
@@ -10559,9 +10991,12 @@
         <v>0.02557</v>
       </c>
       <c r="U144" s="1" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="V144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="V144" s="1" t="n">
+      <c r="W144" s="1" t="n">
         <v>0.02557</v>
       </c>
     </row>
@@ -10629,10 +11064,13 @@
         <v>0.2359</v>
       </c>
       <c r="U145" s="1" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="V145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="V145" s="1" t="n">
-        <v>0.2352</v>
+      <c r="W145" s="1" t="n">
+        <v>0.2351</v>
       </c>
     </row>
     <row r="146">
@@ -10699,9 +11137,12 @@
         <v>0.007053</v>
       </c>
       <c r="U146" s="1" t="n">
+        <v>0.007043</v>
+      </c>
+      <c r="V146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="V146" s="1" t="n">
+      <c r="W146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -10769,9 +11210,12 @@
         <v>0.08667999999999999</v>
       </c>
       <c r="U147" s="1" t="n">
+        <v>0.08641</v>
+      </c>
+      <c r="V147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="V147" s="1" t="n">
+      <c r="W147" s="1" t="n">
         <v>0.08597</v>
       </c>
     </row>
@@ -10839,9 +11283,12 @@
         <v>0.05224</v>
       </c>
       <c r="U148" s="1" t="n">
+        <v>0.05264</v>
+      </c>
+      <c r="V148" s="1" t="n">
         <v>0.05284</v>
       </c>
-      <c r="V148" s="1" t="n">
+      <c r="W148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -10909,9 +11356,12 @@
         <v>0.02392</v>
       </c>
       <c r="U149" s="1" t="n">
-        <v>0.02399</v>
+        <v>0.02402</v>
       </c>
       <c r="V149" s="1" t="n">
+        <v>0.02402</v>
+      </c>
+      <c r="W149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -10979,9 +11429,12 @@
         <v>0.08653</v>
       </c>
       <c r="U150" s="1" t="n">
+        <v>0.08631999999999999</v>
+      </c>
+      <c r="V150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="V150" s="1" t="n">
+      <c r="W150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -11049,10 +11502,13 @@
         <v>0.02319</v>
       </c>
       <c r="U151" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="V151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="V151" s="1" t="n">
-        <v>0.02318</v>
+      <c r="W151" s="1" t="n">
+        <v>0.02312</v>
       </c>
     </row>
     <row r="152">
@@ -11119,10 +11575,13 @@
         <v>0.02524</v>
       </c>
       <c r="U152" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="V152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="V152" s="1" t="n">
-        <v>0.02524</v>
+      <c r="W152" s="1" t="n">
+        <v>0.0252</v>
       </c>
     </row>
     <row r="153">
@@ -11189,9 +11648,12 @@
         <v>0.0002118</v>
       </c>
       <c r="U153" s="1" t="n">
+        <v>0.0002123</v>
+      </c>
+      <c r="V153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="V153" s="1" t="n">
+      <c r="W153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -11259,9 +11721,12 @@
         <v>0.4417</v>
       </c>
       <c r="U154" s="1" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="V154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="V154" s="1" t="n">
+      <c r="W154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -11329,9 +11794,12 @@
         <v>0.06796000000000001</v>
       </c>
       <c r="U155" s="1" t="n">
+        <v>0.06784</v>
+      </c>
+      <c r="V155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="V155" s="1" t="n">
+      <c r="W155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -11399,9 +11867,12 @@
         <v>0.13403</v>
       </c>
       <c r="U156" s="1" t="n">
+        <v>0.13064</v>
+      </c>
+      <c r="V156" s="1" t="n">
         <v>0.13403</v>
       </c>
-      <c r="V156" s="1" t="n">
+      <c r="W156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -11469,9 +11940,12 @@
         <v>0.4823</v>
       </c>
       <c r="U157" s="1" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="V157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="V157" s="1" t="n">
+      <c r="W157" s="1" t="n">
         <v>0.4823</v>
       </c>
     </row>
@@ -11539,9 +12013,12 @@
         <v>0.4491</v>
       </c>
       <c r="U158" s="1" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="V158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="V158" s="1" t="n">
+      <c r="W158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -11609,9 +12086,12 @@
         <v>0.007433</v>
       </c>
       <c r="U159" s="1" t="n">
+        <v>0.007431</v>
+      </c>
+      <c r="V159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="V159" s="1" t="n">
+      <c r="W159" s="1" t="n">
         <v>0.007417</v>
       </c>
     </row>
@@ -11679,9 +12159,12 @@
         <v>0.004657</v>
       </c>
       <c r="U160" s="1" t="n">
+        <v>0.004652</v>
+      </c>
+      <c r="V160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="V160" s="1" t="n">
+      <c r="W160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -11749,9 +12232,12 @@
         <v>0.004291</v>
       </c>
       <c r="U161" s="1" t="n">
+        <v>0.004287</v>
+      </c>
+      <c r="V161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="V161" s="1" t="n">
+      <c r="W161" s="1" t="n">
         <v>0.004276</v>
       </c>
     </row>
@@ -11819,10 +12305,13 @@
         <v>0.0955</v>
       </c>
       <c r="U162" s="1" t="n">
+        <v>0.0953</v>
+      </c>
+      <c r="V162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="V162" s="1" t="n">
-        <v>0.0954</v>
+      <c r="W162" s="1" t="n">
+        <v>0.0953</v>
       </c>
     </row>
     <row r="163">
@@ -11889,9 +12378,12 @@
         <v>0.2848</v>
       </c>
       <c r="U163" s="1" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="V163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="V163" s="1" t="n">
+      <c r="W163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -11959,9 +12451,12 @@
         <v>0.1135</v>
       </c>
       <c r="U164" s="1" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="V164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="V164" s="1" t="n">
+      <c r="W164" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -12029,9 +12524,12 @@
         <v>0.1751</v>
       </c>
       <c r="U165" s="1" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="V165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="V165" s="1" t="n">
+      <c r="W165" s="1" t="n">
         <v>0.1748</v>
       </c>
     </row>
@@ -12099,9 +12597,12 @@
         <v>0.01008</v>
       </c>
       <c r="U166" s="1" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="V166" s="1" t="n">
         <v>0.0102</v>
       </c>
-      <c r="V166" s="1" t="n">
+      <c r="W166" s="1" t="n">
         <v>0.01004</v>
       </c>
     </row>
@@ -12169,9 +12670,12 @@
         <v>1.819</v>
       </c>
       <c r="U167" s="1" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="V167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="V167" s="1" t="n">
+      <c r="W167" s="1" t="n">
         <v>1.814</v>
       </c>
     </row>
@@ -12239,9 +12743,12 @@
         <v>1.343</v>
       </c>
       <c r="U168" s="1" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="V168" s="1" t="n">
+      <c r="W168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -12309,9 +12816,12 @@
         <v>0.0073</v>
       </c>
       <c r="U169" s="1" t="n">
+        <v>0.007299</v>
+      </c>
+      <c r="V169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="V169" s="1" t="n">
+      <c r="W169" s="1" t="n">
         <v>0.007284</v>
       </c>
     </row>
@@ -12379,9 +12889,12 @@
         <v>0.0115</v>
       </c>
       <c r="U170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="V170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="V170" s="1" t="n">
+      <c r="W170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -12449,9 +12962,12 @@
         <v>0.005778</v>
       </c>
       <c r="U171" s="1" t="n">
+        <v>0.005778</v>
+      </c>
+      <c r="V171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="V171" s="1" t="n">
+      <c r="W171" s="1" t="n">
         <v>0.00576</v>
       </c>
     </row>
@@ -12519,9 +13035,12 @@
         <v>0.14854</v>
       </c>
       <c r="U172" s="1" t="n">
+        <v>0.14879</v>
+      </c>
+      <c r="V172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="V172" s="1" t="n">
+      <c r="W172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -12589,9 +13108,12 @@
         <v>4.877</v>
       </c>
       <c r="U173" s="1" t="n">
+        <v>4.886</v>
+      </c>
+      <c r="V173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="V173" s="1" t="n">
+      <c r="W173" s="1" t="n">
         <v>4.871</v>
       </c>
     </row>
@@ -12659,10 +13181,13 @@
         <v>0.07790999999999999</v>
       </c>
       <c r="U174" s="1" t="n">
+        <v>0.07788</v>
+      </c>
+      <c r="V174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="V174" s="1" t="n">
-        <v>0.07789</v>
+      <c r="W174" s="1" t="n">
+        <v>0.07788</v>
       </c>
     </row>
     <row r="175">
@@ -12729,9 +13254,12 @@
         <v>0.007417</v>
       </c>
       <c r="U175" s="1" t="n">
+        <v>0.007413</v>
+      </c>
+      <c r="V175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="V175" s="1" t="n">
+      <c r="W175" s="1" t="n">
         <v>0.007403</v>
       </c>
     </row>
@@ -12799,9 +13327,12 @@
         <v>0.199</v>
       </c>
       <c r="U176" s="1" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="V176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="V176" s="1" t="n">
+      <c r="W176" s="1" t="n">
         <v>0.1985</v>
       </c>
     </row>
@@ -12872,6 +13403,9 @@
         <v>0.05197</v>
       </c>
       <c r="V177" s="1" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="W177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -12939,9 +13473,12 @@
         <v>0.05464</v>
       </c>
       <c r="U178" s="1" t="n">
+        <v>0.05455</v>
+      </c>
+      <c r="V178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="V178" s="1" t="n">
+      <c r="W178" s="1" t="n">
         <v>0.05447</v>
       </c>
     </row>
@@ -13009,9 +13546,12 @@
         <v>0.02341</v>
       </c>
       <c r="U179" s="1" t="n">
-        <v>0.02341</v>
+        <v>0.02349</v>
       </c>
       <c r="V179" s="1" t="n">
+        <v>0.02349</v>
+      </c>
+      <c r="W179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -13079,9 +13619,12 @@
         <v>0.6971000000000001</v>
       </c>
       <c r="U180" s="1" t="n">
-        <v>0.6976</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="V180" s="1" t="n">
+        <v>0.6991000000000001</v>
+      </c>
+      <c r="W180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -13149,9 +13692,12 @@
         <v>0.0003754</v>
       </c>
       <c r="U181" s="1" t="n">
+        <v>0.0003724</v>
+      </c>
+      <c r="V181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="V181" s="1" t="n">
+      <c r="W181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -13219,9 +13765,12 @@
         <v>0.01264</v>
       </c>
       <c r="U182" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="V182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="V182" s="1" t="n">
+      <c r="W182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -13289,9 +13838,12 @@
         <v>4.238</v>
       </c>
       <c r="U183" s="1" t="n">
+        <v>4.222</v>
+      </c>
+      <c r="V183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="V183" s="1" t="n">
+      <c r="W183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -13359,9 +13911,12 @@
         <v>0.234</v>
       </c>
       <c r="U184" s="1" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="V184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="V184" s="1" t="n">
+      <c r="W184" s="1" t="n">
         <v>0.2335</v>
       </c>
     </row>
@@ -13429,9 +13984,12 @@
         <v>0.03709</v>
       </c>
       <c r="U185" s="1" t="n">
+        <v>0.03713</v>
+      </c>
+      <c r="V185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="V185" s="1" t="n">
+      <c r="W185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -13499,10 +14057,13 @@
         <v>0.11543</v>
       </c>
       <c r="U186" s="1" t="n">
+        <v>0.11535</v>
+      </c>
+      <c r="V186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="V186" s="1" t="n">
-        <v>0.11543</v>
+      <c r="W186" s="1" t="n">
+        <v>0.11535</v>
       </c>
     </row>
     <row r="187">
@@ -13569,9 +14130,12 @@
         <v>0.009168000000000001</v>
       </c>
       <c r="U187" s="1" t="n">
+        <v>0.009145</v>
+      </c>
+      <c r="V187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="V187" s="1" t="n">
+      <c r="W187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -13639,9 +14203,12 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="U188" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="V188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="V188" s="1" t="n">
+      <c r="W188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -13709,10 +14276,13 @@
         <v>0.02727</v>
       </c>
       <c r="U189" s="1" t="n">
+        <v>0.02708</v>
+      </c>
+      <c r="V189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="V189" s="1" t="n">
-        <v>0.02727</v>
+      <c r="W189" s="1" t="n">
+        <v>0.02708</v>
       </c>
     </row>
     <row r="190">
@@ -13779,9 +14349,12 @@
         <v>0.008659999999999999</v>
       </c>
       <c r="U190" s="1" t="n">
+        <v>0.008670000000000001</v>
+      </c>
+      <c r="V190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="V190" s="1" t="n">
+      <c r="W190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -13849,9 +14422,12 @@
         <v>0.001958</v>
       </c>
       <c r="U191" s="1" t="n">
+        <v>0.001957</v>
+      </c>
+      <c r="V191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="V191" s="1" t="n">
+      <c r="W191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -13919,9 +14495,12 @@
         <v>0.0998</v>
       </c>
       <c r="U192" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="V192" s="1" t="n">
         <v>0.1009</v>
       </c>
-      <c r="V192" s="1" t="n">
+      <c r="W192" s="1" t="n">
         <v>0.09959999999999999</v>
       </c>
     </row>
@@ -13989,9 +14568,12 @@
         <v>0.0232</v>
       </c>
       <c r="U193" s="1" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="V193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="V193" s="1" t="n">
+      <c r="W193" s="1" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -14059,9 +14641,12 @@
         <v>0.01345</v>
       </c>
       <c r="U194" s="1" t="n">
+        <v>0.01342</v>
+      </c>
+      <c r="V194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="V194" s="1" t="n">
+      <c r="W194" s="1" t="n">
         <v>0.01341</v>
       </c>
     </row>
@@ -14129,10 +14714,13 @@
         <v>0.02082</v>
       </c>
       <c r="U195" s="1" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="V195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="V195" s="1" t="n">
-        <v>0.02076</v>
+      <c r="W195" s="1" t="n">
+        <v>0.02073</v>
       </c>
     </row>
     <row r="196">
@@ -14199,9 +14787,12 @@
         <v>0.17448</v>
       </c>
       <c r="U196" s="1" t="n">
-        <v>0.17659</v>
+        <v>0.17767</v>
       </c>
       <c r="V196" s="1" t="n">
+        <v>0.17767</v>
+      </c>
+      <c r="W196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -14269,9 +14860,12 @@
         <v>0.007349</v>
       </c>
       <c r="U197" s="1" t="n">
+        <v>0.007352</v>
+      </c>
+      <c r="V197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="V197" s="1" t="n">
+      <c r="W197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -14339,9 +14933,12 @@
         <v>0.01902</v>
       </c>
       <c r="U198" s="1" t="n">
+        <v>0.01905</v>
+      </c>
+      <c r="V198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="V198" s="1" t="n">
+      <c r="W198" s="1" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -14409,9 +15006,12 @@
         <v>0.01622</v>
       </c>
       <c r="U199" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="V199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="V199" s="1" t="n">
+      <c r="W199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -14479,9 +15079,12 @@
         <v>0.2975</v>
       </c>
       <c r="U200" s="1" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="V200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="V200" s="1" t="n">
+      <c r="W200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -14549,9 +15152,12 @@
         <v>0.00621</v>
       </c>
       <c r="U201" s="1" t="n">
+        <v>0.006204</v>
+      </c>
+      <c r="V201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="V201" s="1" t="n">
+      <c r="W201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -14619,9 +15225,12 @@
         <v>0.0004399</v>
       </c>
       <c r="U202" s="1" t="n">
+        <v>0.0004389</v>
+      </c>
+      <c r="V202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="V202" s="1" t="n">
+      <c r="W202" s="1" t="n">
         <v>0.0004386</v>
       </c>
     </row>
@@ -14689,9 +15298,12 @@
         <v>0.007275</v>
       </c>
       <c r="U203" s="1" t="n">
+        <v>0.007282</v>
+      </c>
+      <c r="V203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="V203" s="1" t="n">
+      <c r="W203" s="1" t="n">
         <v>0.007245</v>
       </c>
     </row>
@@ -14759,9 +15371,12 @@
         <v>0.1304</v>
       </c>
       <c r="U204" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="V204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="V204" s="1" t="n">
+      <c r="W204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -14829,9 +15444,12 @@
         <v>0.01419</v>
       </c>
       <c r="U205" s="1" t="n">
+        <v>0.01414</v>
+      </c>
+      <c r="V205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="V205" s="1" t="n">
+      <c r="W205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -14899,9 +15517,12 @@
         <v>0.003571</v>
       </c>
       <c r="U206" s="1" t="n">
+        <v>0.003578</v>
+      </c>
+      <c r="V206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="V206" s="1" t="n">
+      <c r="W206" s="1" t="n">
         <v>0.003565</v>
       </c>
     </row>
@@ -14969,9 +15590,12 @@
         <v>0.05952</v>
       </c>
       <c r="U207" s="1" t="n">
+        <v>0.05923</v>
+      </c>
+      <c r="V207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="V207" s="1" t="n">
+      <c r="W207" s="1" t="n">
         <v>0.05914</v>
       </c>
     </row>
@@ -15039,9 +15663,12 @@
         <v>15.47</v>
       </c>
       <c r="U208" s="1" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="V208" s="1" t="n">
         <v>15.55</v>
       </c>
-      <c r="V208" s="1" t="n">
+      <c r="W208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -15109,9 +15736,12 @@
         <v>5192.3</v>
       </c>
       <c r="U209" s="1" t="n">
+        <v>5188.1</v>
+      </c>
+      <c r="V209" s="1" t="n">
         <v>5194.4</v>
       </c>
-      <c r="V209" s="1" t="n">
+      <c r="W209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -15179,9 +15809,12 @@
         <v>0.11941</v>
       </c>
       <c r="U210" s="1" t="n">
+        <v>0.11974</v>
+      </c>
+      <c r="V210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="V210" s="1" t="n">
+      <c r="W210" s="1" t="n">
         <v>0.11941</v>
       </c>
     </row>
@@ -15249,9 +15882,12 @@
         <v>0.1816</v>
       </c>
       <c r="U211" s="1" t="n">
+        <v>0.1814</v>
+      </c>
+      <c r="V211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="V211" s="1" t="n">
+      <c r="W211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -15319,9 +15955,12 @@
         <v>0.0302</v>
       </c>
       <c r="U212" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="V212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="V212" s="1" t="n">
+      <c r="W212" s="1" t="n">
         <v>0.0298</v>
       </c>
     </row>
@@ -15389,9 +16028,12 @@
         <v>1.3995</v>
       </c>
       <c r="U213" s="1" t="n">
-        <v>1.3995</v>
+        <v>1.3997</v>
       </c>
       <c r="V213" s="1" t="n">
+        <v>1.3997</v>
+      </c>
+      <c r="W213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -15459,9 +16101,12 @@
         <v>0.05653</v>
       </c>
       <c r="U214" s="1" t="n">
+        <v>0.05649</v>
+      </c>
+      <c r="V214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="V214" s="1" t="n">
+      <c r="W214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -15529,9 +16174,12 @@
         <v>0.04399</v>
       </c>
       <c r="U215" s="1" t="n">
+        <v>0.04391</v>
+      </c>
+      <c r="V215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="V215" s="1" t="n">
+      <c r="W215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -15599,9 +16247,12 @@
         <v>0.15096</v>
       </c>
       <c r="U216" s="1" t="n">
+        <v>0.15088</v>
+      </c>
+      <c r="V216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="V216" s="1" t="n">
+      <c r="W216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -15669,9 +16320,12 @@
         <v>0.073</v>
       </c>
       <c r="U217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="V217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="V217" s="1" t="n">
+      <c r="W217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -15739,9 +16393,12 @@
         <v>0.00267</v>
       </c>
       <c r="U218" s="1" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="V218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="V218" s="1" t="n">
+      <c r="W218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -15809,9 +16466,12 @@
         <v>0.01698</v>
       </c>
       <c r="U219" s="1" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="V219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="V219" s="1" t="n">
+      <c r="W219" s="1" t="n">
         <v>0.01696</v>
       </c>
     </row>
@@ -15879,9 +16539,12 @@
         <v>0.05519</v>
       </c>
       <c r="U220" s="1" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="V220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="V220" s="1" t="n">
+      <c r="W220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -15949,9 +16612,12 @@
         <v>0.0219</v>
       </c>
       <c r="U221" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="V221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="V221" s="1" t="n">
+      <c r="W221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -16019,9 +16685,12 @@
         <v>0.00928</v>
       </c>
       <c r="U222" s="1" t="n">
+        <v>0.009259999999999999</v>
+      </c>
+      <c r="V222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="V222" s="1" t="n">
+      <c r="W222" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -16089,9 +16758,12 @@
         <v>0.0164</v>
       </c>
       <c r="U223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="V223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="V223" s="1" t="n">
+      <c r="W223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -16159,9 +16831,12 @@
         <v>0.03846</v>
       </c>
       <c r="U224" s="1" t="n">
+        <v>0.03825</v>
+      </c>
+      <c r="V224" s="1" t="n">
         <v>0.03846</v>
       </c>
-      <c r="V224" s="1" t="n">
+      <c r="W224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -16229,9 +16904,12 @@
         <v>0.001517</v>
       </c>
       <c r="U225" s="1" t="n">
+        <v>0.001517</v>
+      </c>
+      <c r="V225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="V225" s="1" t="n">
+      <c r="W225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -16299,9 +16977,12 @@
         <v>27.28</v>
       </c>
       <c r="U226" s="1" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="V226" s="1" t="n">
         <v>27.31</v>
       </c>
-      <c r="V226" s="1" t="n">
+      <c r="W226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -16369,9 +17050,12 @@
         <v>0.07018000000000001</v>
       </c>
       <c r="U227" s="1" t="n">
+        <v>0.07027</v>
+      </c>
+      <c r="V227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="V227" s="1" t="n">
+      <c r="W227" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -16439,9 +17123,12 @@
         <v>0.3121</v>
       </c>
       <c r="U228" s="1" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="V228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="V228" s="1" t="n">
+      <c r="W228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -16509,9 +17196,12 @@
         <v>18.38</v>
       </c>
       <c r="U229" s="1" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="V229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="V229" s="1" t="n">
+      <c r="W229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -16579,9 +17269,12 @@
         <v>0.01921</v>
       </c>
       <c r="U230" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="V230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="V230" s="1" t="n">
+      <c r="W230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -16649,9 +17342,12 @@
         <v>0.01215</v>
       </c>
       <c r="U231" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="V231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="V231" s="1" t="n">
+      <c r="W231" s="1" t="n">
         <v>0.01214</v>
       </c>
     </row>
@@ -16719,9 +17415,12 @@
         <v>0.2276</v>
       </c>
       <c r="U232" s="1" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="V232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="V232" s="1" t="n">
+      <c r="W232" s="1" t="n">
         <v>0.2269</v>
       </c>
     </row>
@@ -16789,9 +17488,12 @@
         <v>0.07081999999999999</v>
       </c>
       <c r="U233" s="1" t="n">
+        <v>0.07086000000000001</v>
+      </c>
+      <c r="V233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="V233" s="1" t="n">
+      <c r="W233" s="1" t="n">
         <v>0.07073</v>
       </c>
     </row>
@@ -16859,9 +17561,12 @@
         <v>0.1709</v>
       </c>
       <c r="U234" s="1" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="V234" s="1" t="n">
         <v>0.1709</v>
       </c>
-      <c r="V234" s="1" t="n">
+      <c r="W234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -16929,9 +17634,12 @@
         <v>0.0251</v>
       </c>
       <c r="U235" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="V235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="V235" s="1" t="n">
+      <c r="W235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -16999,9 +17707,12 @@
         <v>0.02999</v>
       </c>
       <c r="U236" s="1" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="V236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="V236" s="1" t="n">
+      <c r="W236" s="1" t="n">
         <v>0.02993</v>
       </c>
     </row>
@@ -17069,9 +17780,12 @@
         <v>2.039</v>
       </c>
       <c r="U237" s="1" t="n">
-        <v>2.039</v>
+        <v>2.049</v>
       </c>
       <c r="V237" s="1" t="n">
+        <v>2.049</v>
+      </c>
+      <c r="W237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -17139,10 +17853,13 @@
         <v>0.4198</v>
       </c>
       <c r="U238" s="1" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="V238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="V238" s="1" t="n">
-        <v>0.4198</v>
+      <c r="W238" s="1" t="n">
+        <v>0.4187</v>
       </c>
     </row>
     <row r="239">
@@ -17209,9 +17926,12 @@
         <v>0.03308</v>
       </c>
       <c r="U239" s="1" t="n">
+        <v>0.03323</v>
+      </c>
+      <c r="V239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="V239" s="1" t="n">
+      <c r="W239" s="1" t="n">
         <v>0.03308</v>
       </c>
     </row>
@@ -17279,9 +17999,12 @@
         <v>0.03399</v>
       </c>
       <c r="U240" s="1" t="n">
+        <v>0.03385</v>
+      </c>
+      <c r="V240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="V240" s="1" t="n">
+      <c r="W240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -17349,9 +18072,12 @@
         <v>0.0007463</v>
       </c>
       <c r="U241" s="1" t="n">
+        <v>0.0007464</v>
+      </c>
+      <c r="V241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="V241" s="1" t="n">
+      <c r="W241" s="1" t="n">
         <v>0.0007463</v>
       </c>
     </row>
@@ -17419,9 +18145,12 @@
         <v>0.1822</v>
       </c>
       <c r="U242" s="1" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="V242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="V242" s="1" t="n">
+      <c r="W242" s="1" t="n">
         <v>0.1822</v>
       </c>
     </row>
@@ -17489,9 +18218,12 @@
         <v>0.014728</v>
       </c>
       <c r="U243" s="1" t="n">
+        <v>0.014718</v>
+      </c>
+      <c r="V243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="V243" s="1" t="n">
+      <c r="W243" s="1" t="n">
         <v>0.014706</v>
       </c>
     </row>
@@ -17559,9 +18291,12 @@
         <v>3e-05</v>
       </c>
       <c r="U244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="V244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="V244" s="1" t="n">
+      <c r="W244" s="1" t="n">
         <v>2.99e-05</v>
       </c>
     </row>
@@ -17629,9 +18364,12 @@
         <v>0.03517</v>
       </c>
       <c r="U245" s="1" t="n">
+        <v>0.03526</v>
+      </c>
+      <c r="V245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="V245" s="1" t="n">
+      <c r="W245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -17699,9 +18437,12 @@
         <v>0.08036</v>
       </c>
       <c r="U246" s="1" t="n">
+        <v>0.08032</v>
+      </c>
+      <c r="V246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="V246" s="1" t="n">
+      <c r="W246" s="1" t="n">
         <v>0.08018</v>
       </c>
     </row>
@@ -17769,9 +18510,12 @@
         <v>0.007129</v>
       </c>
       <c r="U247" s="1" t="n">
+        <v>0.007131</v>
+      </c>
+      <c r="V247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="V247" s="1" t="n">
+      <c r="W247" s="1" t="n">
         <v>0.007129</v>
       </c>
     </row>
@@ -17839,9 +18583,12 @@
         <v>0.09317</v>
       </c>
       <c r="U248" s="1" t="n">
+        <v>0.09275</v>
+      </c>
+      <c r="V248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="V248" s="1" t="n">
+      <c r="W248" s="1" t="n">
         <v>0.09239</v>
       </c>
     </row>
@@ -17909,9 +18656,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="U249" s="1" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="V249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="V249" s="1" t="n">
+      <c r="W249" s="1" t="n">
         <v>0.08699999999999999</v>
       </c>
     </row>
@@ -17979,9 +18729,12 @@
         <v>0.03481</v>
       </c>
       <c r="U250" s="1" t="n">
+        <v>0.03482</v>
+      </c>
+      <c r="V250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="V250" s="1" t="n">
+      <c r="W250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -18049,10 +18802,13 @@
         <v>0.03896</v>
       </c>
       <c r="U251" s="1" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="V251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="V251" s="1" t="n">
-        <v>0.03896</v>
+      <c r="W251" s="1" t="n">
+        <v>0.0388</v>
       </c>
     </row>
     <row r="252">
@@ -18119,9 +18875,12 @@
         <v>0.0877</v>
       </c>
       <c r="U252" s="1" t="n">
+        <v>0.08790000000000001</v>
+      </c>
+      <c r="V252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="V252" s="1" t="n">
+      <c r="W252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -18189,9 +18948,12 @@
         <v>4.081</v>
       </c>
       <c r="U253" s="1" t="n">
+        <v>4.071</v>
+      </c>
+      <c r="V253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="V253" s="1" t="n">
+      <c r="W253" s="1" t="n">
         <v>4.058</v>
       </c>
     </row>
@@ -18259,9 +19021,12 @@
         <v>0.1872</v>
       </c>
       <c r="U254" s="1" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="V254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="V254" s="1" t="n">
+      <c r="W254" s="1" t="n">
         <v>0.1866</v>
       </c>
     </row>
@@ -18329,9 +19094,12 @@
         <v>0.07192999999999999</v>
       </c>
       <c r="U255" s="1" t="n">
+        <v>0.07183</v>
+      </c>
+      <c r="V255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="V255" s="1" t="n">
+      <c r="W255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -18399,9 +19167,12 @@
         <v>0.01845</v>
       </c>
       <c r="U256" s="1" t="n">
-        <v>0.01845</v>
+        <v>0.01848</v>
       </c>
       <c r="V256" s="1" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="W256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -18469,9 +19240,12 @@
         <v>5.947</v>
       </c>
       <c r="U257" s="1" t="n">
+        <v>5.949</v>
+      </c>
+      <c r="V257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="V257" s="1" t="n">
+      <c r="W257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -18539,9 +19313,12 @@
         <v>0.2596</v>
       </c>
       <c r="U258" s="1" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="V258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="V258" s="1" t="n">
+      <c r="W258" s="1" t="n">
         <v>0.2596</v>
       </c>
     </row>
@@ -18609,9 +19386,12 @@
         <v>0.1358</v>
       </c>
       <c r="U259" s="1" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="V259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="V259" s="1" t="n">
+      <c r="W259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -18679,9 +19459,12 @@
         <v>0.30774</v>
       </c>
       <c r="U260" s="1" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="V260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="V260" s="1" t="n">
+      <c r="W260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -18749,9 +19532,12 @@
         <v>0.09876</v>
       </c>
       <c r="U261" s="1" t="n">
+        <v>0.09859</v>
+      </c>
+      <c r="V261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="V261" s="1" t="n">
+      <c r="W261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -18819,9 +19605,12 @@
         <v>0.5396</v>
       </c>
       <c r="U262" s="1" t="n">
+        <v>0.5395</v>
+      </c>
+      <c r="V262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="V262" s="1" t="n">
+      <c r="W262" s="1" t="n">
         <v>0.5377999999999999</v>
       </c>
     </row>
@@ -18889,9 +19678,12 @@
         <v>0.2887</v>
       </c>
       <c r="U263" s="1" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="V263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="V263" s="1" t="n">
+      <c r="W263" s="1" t="n">
         <v>0.2877</v>
       </c>
     </row>
@@ -18959,9 +19751,12 @@
         <v>0.989</v>
       </c>
       <c r="U264" s="1" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="V264" s="1" t="n">
         <v>0.989</v>
       </c>
-      <c r="V264" s="1" t="n">
+      <c r="W264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -19029,10 +19824,13 @@
         <v>0.5382</v>
       </c>
       <c r="U265" s="1" t="n">
+        <v>0.5364</v>
+      </c>
+      <c r="V265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="V265" s="1" t="n">
-        <v>0.5367</v>
+      <c r="W265" s="1" t="n">
+        <v>0.5364</v>
       </c>
     </row>
     <row r="266">
@@ -19099,10 +19897,13 @@
         <v>0.07346999999999999</v>
       </c>
       <c r="U266" s="1" t="n">
+        <v>0.07339</v>
+      </c>
+      <c r="V266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="V266" s="1" t="n">
-        <v>0.07341</v>
+      <c r="W266" s="1" t="n">
+        <v>0.07339</v>
       </c>
     </row>
     <row r="267">
@@ -19169,9 +19970,12 @@
         <v>0.02138</v>
       </c>
       <c r="U267" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="V267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="V267" s="1" t="n">
+      <c r="W267" s="1" t="n">
         <v>0.02127</v>
       </c>
     </row>
@@ -19239,9 +20043,12 @@
         <v>0.01605</v>
       </c>
       <c r="U268" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="V268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="V268" s="1" t="n">
+      <c r="W268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -19309,9 +20116,12 @@
         <v>0.003781</v>
       </c>
       <c r="U269" s="1" t="n">
+        <v>0.003787</v>
+      </c>
+      <c r="V269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="V269" s="1" t="n">
+      <c r="W269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -19379,9 +20189,12 @@
         <v>0.00767</v>
       </c>
       <c r="U270" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="V270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="V270" s="1" t="n">
+      <c r="W270" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -19449,9 +20262,12 @@
         <v>0.05488</v>
       </c>
       <c r="U271" s="1" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="V271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="V271" s="1" t="n">
+      <c r="W271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -19519,9 +20335,12 @@
         <v>2.275</v>
       </c>
       <c r="U272" s="1" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="V272" s="1" t="n">
+      <c r="W272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -19589,9 +20408,12 @@
         <v>0.05484</v>
       </c>
       <c r="U273" s="1" t="n">
+        <v>0.05476</v>
+      </c>
+      <c r="V273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="V273" s="1" t="n">
+      <c r="W273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -19659,9 +20481,12 @@
         <v>0.02349</v>
       </c>
       <c r="U274" s="1" t="n">
+        <v>0.02329</v>
+      </c>
+      <c r="V274" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="V274" s="1" t="n">
+      <c r="W274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -19729,9 +20554,12 @@
         <v>1.177</v>
       </c>
       <c r="U275" s="1" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="V275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="V275" s="1" t="n">
+      <c r="W275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -19799,9 +20627,12 @@
         <v>0.2718</v>
       </c>
       <c r="U276" s="1" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="V276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="V276" s="1" t="n">
+      <c r="W276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -19869,9 +20700,12 @@
         <v>0.922</v>
       </c>
       <c r="U277" s="1" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="V277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="V277" s="1" t="n">
+      <c r="W277" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -19939,9 +20773,12 @@
         <v>0.6237</v>
       </c>
       <c r="U278" s="1" t="n">
+        <v>0.6263</v>
+      </c>
+      <c r="V278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="V278" s="1" t="n">
+      <c r="W278" s="1" t="n">
         <v>0.6218</v>
       </c>
     </row>
@@ -20009,9 +20846,12 @@
         <v>0.001329</v>
       </c>
       <c r="U279" s="1" t="n">
+        <v>0.001328</v>
+      </c>
+      <c r="V279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="V279" s="1" t="n">
+      <c r="W279" s="1" t="n">
         <v>0.001326</v>
       </c>
     </row>
@@ -20079,9 +20919,12 @@
         <v>0.005613</v>
       </c>
       <c r="U280" s="1" t="n">
+        <v>0.005597</v>
+      </c>
+      <c r="V280" s="1" t="n">
         <v>0.005613</v>
       </c>
-      <c r="V280" s="1" t="n">
+      <c r="W280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -20149,9 +20992,12 @@
         <v>1.52</v>
       </c>
       <c r="U281" s="1" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="V281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="V281" s="1" t="n">
+      <c r="W281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -20219,9 +21065,12 @@
         <v>28.36</v>
       </c>
       <c r="U282" s="1" t="n">
+        <v>28.27</v>
+      </c>
+      <c r="V282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="V282" s="1" t="n">
+      <c r="W282" s="1" t="n">
         <v>28.25</v>
       </c>
     </row>
@@ -20289,9 +21138,12 @@
         <v>0.12814</v>
       </c>
       <c r="U283" s="1" t="n">
+        <v>0.12888</v>
+      </c>
+      <c r="V283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="V283" s="1" t="n">
+      <c r="W283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -20359,9 +21211,12 @@
         <v>0.01104</v>
       </c>
       <c r="U284" s="1" t="n">
+        <v>0.01103</v>
+      </c>
+      <c r="V284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="V284" s="1" t="n">
+      <c r="W284" s="1" t="n">
         <v>0.01102</v>
       </c>
     </row>
@@ -20429,9 +21284,12 @@
         <v>6.554</v>
       </c>
       <c r="U285" s="1" t="n">
+        <v>6.548</v>
+      </c>
+      <c r="V285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="V285" s="1" t="n">
+      <c r="W285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -20499,9 +21357,12 @@
         <v>0.01834</v>
       </c>
       <c r="U286" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="V286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="V286" s="1" t="n">
+      <c r="W286" s="1" t="n">
         <v>0.01831</v>
       </c>
     </row>
@@ -20569,9 +21430,12 @@
         <v>0.008343</v>
       </c>
       <c r="U287" s="1" t="n">
+        <v>0.008362</v>
+      </c>
+      <c r="V287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="V287" s="1" t="n">
+      <c r="W287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -20639,10 +21503,13 @@
         <v>0.3791</v>
       </c>
       <c r="U288" s="1" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="V288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="V288" s="1" t="n">
-        <v>0.3791</v>
+      <c r="W288" s="1" t="n">
+        <v>0.3774</v>
       </c>
     </row>
     <row r="289">
@@ -20709,9 +21576,12 @@
         <v>0.009797999999999999</v>
       </c>
       <c r="U289" s="1" t="n">
+        <v>0.009789000000000001</v>
+      </c>
+      <c r="V289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="V289" s="1" t="n">
+      <c r="W289" s="1" t="n">
         <v>0.00974</v>
       </c>
     </row>
@@ -20779,9 +21649,12 @@
         <v>0.02597</v>
       </c>
       <c r="U290" s="1" t="n">
+        <v>0.02592</v>
+      </c>
+      <c r="V290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="V290" s="1" t="n">
+      <c r="W290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -20849,9 +21722,12 @@
         <v>0.094</v>
       </c>
       <c r="U291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="V291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="V291" s="1" t="n">
+      <c r="W291" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -20919,9 +21795,12 @@
         <v>0.28683</v>
       </c>
       <c r="U292" s="1" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="V292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="V292" s="1" t="n">
+      <c r="W292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -20989,10 +21868,13 @@
         <v>0.01528</v>
       </c>
       <c r="U293" s="1" t="n">
+        <v>0.01525</v>
+      </c>
+      <c r="V293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="V293" s="1" t="n">
-        <v>0.01528</v>
+      <c r="W293" s="1" t="n">
+        <v>0.01525</v>
       </c>
     </row>
     <row r="294">
@@ -21059,9 +21941,12 @@
         <v>0.003399</v>
       </c>
       <c r="U294" s="1" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="V294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="V294" s="1" t="n">
+      <c r="W294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -21129,9 +22014,12 @@
         <v>0.04246</v>
       </c>
       <c r="U295" s="1" t="n">
+        <v>0.042602</v>
+      </c>
+      <c r="V295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="V295" s="1" t="n">
+      <c r="W295" s="1" t="n">
         <v>0.042232</v>
       </c>
     </row>
@@ -21199,10 +22087,13 @@
         <v>0.02897</v>
       </c>
       <c r="U296" s="1" t="n">
+        <v>0.02886</v>
+      </c>
+      <c r="V296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="V296" s="1" t="n">
-        <v>0.02894</v>
+      <c r="W296" s="1" t="n">
+        <v>0.02886</v>
       </c>
     </row>
     <row r="297">
@@ -21269,9 +22160,12 @@
         <v>0.03799</v>
       </c>
       <c r="U297" s="1" t="n">
+        <v>0.03797</v>
+      </c>
+      <c r="V297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="V297" s="1" t="n">
+      <c r="W297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -21339,9 +22233,12 @@
         <v>0.08282</v>
       </c>
       <c r="U298" s="1" t="n">
+        <v>0.08283</v>
+      </c>
+      <c r="V298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="V298" s="1" t="n">
+      <c r="W298" s="1" t="n">
         <v>0.08248</v>
       </c>
     </row>
@@ -21409,9 +22306,12 @@
         <v>0.0076</v>
       </c>
       <c r="U299" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="V299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="V299" s="1" t="n">
+      <c r="W299" s="1" t="n">
         <v>0.0076</v>
       </c>
     </row>
@@ -21479,9 +22379,12 @@
         <v>0.01498</v>
       </c>
       <c r="U300" s="1" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="V300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="V300" s="1" t="n">
+      <c r="W300" s="1" t="n">
         <v>0.01496</v>
       </c>
     </row>
@@ -21549,9 +22452,12 @@
         <v>0.1406</v>
       </c>
       <c r="U301" s="1" t="n">
+        <v>0.1405</v>
+      </c>
+      <c r="V301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="V301" s="1" t="n">
+      <c r="W301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -21619,9 +22525,12 @@
         <v>0.0006269</v>
       </c>
       <c r="U302" s="1" t="n">
+        <v>0.0006228</v>
+      </c>
+      <c r="V302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="V302" s="1" t="n">
+      <c r="W302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -21689,9 +22598,12 @@
         <v>0.06231</v>
       </c>
       <c r="U303" s="1" t="n">
+        <v>0.06254</v>
+      </c>
+      <c r="V303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="V303" s="1" t="n">
+      <c r="W303" s="1" t="n">
         <v>0.06207</v>
       </c>
     </row>
@@ -21759,9 +22671,12 @@
         <v>0.0001623</v>
       </c>
       <c r="U304" s="1" t="n">
+        <v>0.0001624</v>
+      </c>
+      <c r="V304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="V304" s="1" t="n">
+      <c r="W304" s="1" t="n">
         <v>0.000162</v>
       </c>
     </row>
@@ -21829,9 +22744,12 @@
         <v>0.06098</v>
       </c>
       <c r="U305" s="1" t="n">
+        <v>0.06083</v>
+      </c>
+      <c r="V305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="V305" s="1" t="n">
+      <c r="W305" s="1" t="n">
         <v>0.06071</v>
       </c>
     </row>
@@ -21899,9 +22817,12 @@
         <v>0.02232</v>
       </c>
       <c r="U306" s="1" t="n">
+        <v>0.022335</v>
+      </c>
+      <c r="V306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="V306" s="1" t="n">
+      <c r="W306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -21969,9 +22890,12 @@
         <v>0.02297</v>
       </c>
       <c r="U307" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="V307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="V307" s="1" t="n">
+      <c r="W307" s="1" t="n">
         <v>0.02278</v>
       </c>
     </row>
@@ -22039,10 +22963,13 @@
         <v>0.00041</v>
       </c>
       <c r="U308" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="V308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="V308" s="1" t="n">
-        <v>0.00041</v>
+      <c r="W308" s="1" t="n">
+        <v>0.000409</v>
       </c>
     </row>
     <row r="309">
@@ -22109,9 +23036,12 @@
         <v>0.0898</v>
       </c>
       <c r="U309" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="V309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="V309" s="1" t="n">
+      <c r="W309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -22179,9 +23109,12 @@
         <v>0.3701</v>
       </c>
       <c r="U310" s="1" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="V310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="V310" s="1" t="n">
+      <c r="W310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -22249,9 +23182,12 @@
         <v>0.0354</v>
       </c>
       <c r="U311" s="1" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="V311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="V311" s="1" t="n">
+      <c r="W311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -22319,9 +23255,12 @@
         <v>0.02426</v>
       </c>
       <c r="U312" s="1" t="n">
+        <v>0.02426</v>
+      </c>
+      <c r="V312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="V312" s="1" t="n">
+      <c r="W312" s="1" t="n">
         <v>0.02415</v>
       </c>
     </row>
@@ -22389,9 +23328,12 @@
         <v>0.04094</v>
       </c>
       <c r="U313" s="1" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="V313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="V313" s="1" t="n">
+      <c r="W313" s="1" t="n">
         <v>0.04087</v>
       </c>
     </row>
@@ -22459,9 +23401,12 @@
         <v>3.937</v>
       </c>
       <c r="U314" s="1" t="n">
+        <v>3.932</v>
+      </c>
+      <c r="V314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="V314" s="1" t="n">
+      <c r="W314" s="1" t="n">
         <v>3.932</v>
       </c>
     </row>
@@ -22529,9 +23474,12 @@
         <v>0.1594</v>
       </c>
       <c r="U315" s="1" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="V315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="V315" s="1" t="n">
+      <c r="W315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -22599,9 +23547,12 @@
         <v>0.09067</v>
       </c>
       <c r="U316" s="1" t="n">
+        <v>0.09016</v>
+      </c>
+      <c r="V316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="V316" s="1" t="n">
+      <c r="W316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -22669,9 +23620,12 @@
         <v>0.06808</v>
       </c>
       <c r="U317" s="1" t="n">
+        <v>0.06802999999999999</v>
+      </c>
+      <c r="V317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="V317" s="1" t="n">
+      <c r="W317" s="1" t="n">
         <v>0.06791999999999999</v>
       </c>
     </row>
@@ -22739,9 +23693,12 @@
         <v>0.012463</v>
       </c>
       <c r="U318" s="1" t="n">
+        <v>0.012477</v>
+      </c>
+      <c r="V318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="V318" s="1" t="n">
+      <c r="W318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -22809,9 +23766,12 @@
         <v>0.001133</v>
       </c>
       <c r="U319" s="1" t="n">
+        <v>0.00113</v>
+      </c>
+      <c r="V319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="V319" s="1" t="n">
+      <c r="W319" s="1" t="n">
         <v>0.00113</v>
       </c>
     </row>
@@ -22879,9 +23839,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="U320" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="V320" s="1" t="n">
         <v>0.0633</v>
       </c>
-      <c r="V320" s="1" t="n">
+      <c r="W320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -22949,9 +23912,12 @@
         <v>0.00525</v>
       </c>
       <c r="U321" s="1" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="V321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="V321" s="1" t="n">
+      <c r="W321" s="1" t="n">
         <v>0.00523</v>
       </c>
     </row>
@@ -23019,9 +23985,12 @@
         <v>0.1114</v>
       </c>
       <c r="U322" s="1" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="V322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="V322" s="1" t="n">
+      <c r="W322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -23089,9 +24058,12 @@
         <v>0.04368</v>
       </c>
       <c r="U323" s="1" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="V323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="V323" s="1" t="n">
+      <c r="W323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -23159,9 +24131,12 @@
         <v>0.01781</v>
       </c>
       <c r="U324" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="V324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="V324" s="1" t="n">
+      <c r="W324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -23229,9 +24204,12 @@
         <v>0.005656</v>
       </c>
       <c r="U325" s="1" t="n">
+        <v>0.005646</v>
+      </c>
+      <c r="V325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="V325" s="1" t="n">
+      <c r="W325" s="1" t="n">
         <v>0.005633</v>
       </c>
     </row>
@@ -23299,9 +24277,12 @@
         <v>0.00176</v>
       </c>
       <c r="U326" s="1" t="n">
+        <v>0.001757</v>
+      </c>
+      <c r="V326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="V326" s="1" t="n">
+      <c r="W326" s="1" t="n">
         <v>0.001751</v>
       </c>
     </row>
@@ -23369,9 +24350,12 @@
         <v>0.04025</v>
       </c>
       <c r="U327" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="V327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="V327" s="1" t="n">
+      <c r="W327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -23439,9 +24423,12 @@
         <v>0.053583</v>
       </c>
       <c r="U328" s="1" t="n">
+        <v>0.053606</v>
+      </c>
+      <c r="V328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="V328" s="1" t="n">
+      <c r="W328" s="1" t="n">
         <v>0.053492</v>
       </c>
     </row>
@@ -23509,9 +24496,12 @@
         <v>0.2776</v>
       </c>
       <c r="U329" s="1" t="n">
+        <v>0.2771</v>
+      </c>
+      <c r="V329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="V329" s="1" t="n">
+      <c r="W329" s="1" t="n">
         <v>0.2771</v>
       </c>
     </row>
@@ -23579,9 +24569,12 @@
         <v>0.159</v>
       </c>
       <c r="U330" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="V330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="V330" s="1" t="n">
+      <c r="W330" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -23649,9 +24642,12 @@
         <v>0.05365</v>
       </c>
       <c r="U331" s="1" t="n">
+        <v>0.05369</v>
+      </c>
+      <c r="V331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="V331" s="1" t="n">
+      <c r="W331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -23719,9 +24715,12 @@
         <v>0.3624</v>
       </c>
       <c r="U332" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="V332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="V332" s="1" t="n">
+      <c r="W332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -23789,9 +24788,12 @@
         <v>0.03063</v>
       </c>
       <c r="U333" s="1" t="n">
+        <v>0.03059</v>
+      </c>
+      <c r="V333" s="1" t="n">
         <v>0.03063</v>
       </c>
-      <c r="V333" s="1" t="n">
+      <c r="W333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -23859,10 +24861,13 @@
         <v>0.01774</v>
       </c>
       <c r="U334" s="1" t="n">
+        <v>0.01729</v>
+      </c>
+      <c r="V334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="V334" s="1" t="n">
-        <v>0.01751</v>
+      <c r="W334" s="1" t="n">
+        <v>0.01729</v>
       </c>
     </row>
     <row r="335">
@@ -23929,9 +24934,12 @@
         <v>0.0577</v>
       </c>
       <c r="U335" s="1" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="V335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="V335" s="1" t="n">
+      <c r="W335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -23999,10 +25007,13 @@
         <v>0.09023</v>
       </c>
       <c r="U336" s="1" t="n">
+        <v>0.08994000000000001</v>
+      </c>
+      <c r="V336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="V336" s="1" t="n">
-        <v>0.09023</v>
+      <c r="W336" s="1" t="n">
+        <v>0.08994000000000001</v>
       </c>
     </row>
     <row r="337">
@@ -24069,9 +25080,12 @@
         <v>0.18091</v>
       </c>
       <c r="U337" s="1" t="n">
+        <v>0.18025</v>
+      </c>
+      <c r="V337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="V337" s="1" t="n">
+      <c r="W337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -24139,9 +25153,12 @@
         <v>0.02084</v>
       </c>
       <c r="U338" s="1" t="n">
+        <v>0.02079</v>
+      </c>
+      <c r="V338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="V338" s="1" t="n">
+      <c r="W338" s="1" t="n">
         <v>0.02074</v>
       </c>
     </row>
@@ -24212,6 +25229,9 @@
         <v>0.1319</v>
       </c>
       <c r="V339" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="W339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -24279,9 +25299,12 @@
         <v>0.007971000000000001</v>
       </c>
       <c r="U340" s="1" t="n">
+        <v>0.007936</v>
+      </c>
+      <c r="V340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="V340" s="1" t="n">
+      <c r="W340" s="1" t="n">
         <v>0.007901999999999999</v>
       </c>
     </row>
@@ -24349,9 +25372,12 @@
         <v>4.416</v>
       </c>
       <c r="U341" s="1" t="n">
+        <v>4.413</v>
+      </c>
+      <c r="V341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="V341" s="1" t="n">
+      <c r="W341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -24419,9 +25445,12 @@
         <v>0.19001</v>
       </c>
       <c r="U342" s="1" t="n">
+        <v>0.18893</v>
+      </c>
+      <c r="V342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="V342" s="1" t="n">
+      <c r="W342" s="1" t="n">
         <v>0.18839</v>
       </c>
     </row>
@@ -24489,9 +25518,12 @@
         <v>0.08318</v>
       </c>
       <c r="U343" s="1" t="n">
+        <v>0.08312</v>
+      </c>
+      <c r="V343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="V343" s="1" t="n">
+      <c r="W343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -24559,9 +25591,12 @@
         <v>0.1831</v>
       </c>
       <c r="U344" s="1" t="n">
+        <v>0.1829</v>
+      </c>
+      <c r="V344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="V344" s="1" t="n">
+      <c r="W344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -24629,10 +25664,13 @@
         <v>0.003231</v>
       </c>
       <c r="U345" s="1" t="n">
+        <v>0.003221</v>
+      </c>
+      <c r="V345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="V345" s="1" t="n">
-        <v>0.003222</v>
+      <c r="W345" s="1" t="n">
+        <v>0.003221</v>
       </c>
     </row>
     <row r="346">
@@ -24699,9 +25737,12 @@
         <v>0.09137000000000001</v>
       </c>
       <c r="U346" s="1" t="n">
+        <v>0.09103</v>
+      </c>
+      <c r="V346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="V346" s="1" t="n">
+      <c r="W346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -24769,9 +25810,12 @@
         <v>2.243</v>
       </c>
       <c r="U347" s="1" t="n">
+        <v>2.242</v>
+      </c>
+      <c r="V347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="V347" s="1" t="n">
+      <c r="W347" s="1" t="n">
         <v>2.235</v>
       </c>
     </row>
@@ -24839,10 +25883,13 @@
         <v>0.3032</v>
       </c>
       <c r="U348" s="1" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="V348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="V348" s="1" t="n">
-        <v>0.3027</v>
+      <c r="W348" s="1" t="n">
+        <v>0.3026</v>
       </c>
     </row>
     <row r="349">
@@ -24909,9 +25956,12 @@
         <v>0.02987</v>
       </c>
       <c r="U349" s="1" t="n">
+        <v>0.02987</v>
+      </c>
+      <c r="V349" s="1" t="n">
         <v>0.02991</v>
       </c>
-      <c r="V349" s="1" t="n">
+      <c r="W349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -24979,9 +26029,12 @@
         <v>0.1278</v>
       </c>
       <c r="U350" s="1" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="V350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="V350" s="1" t="n">
+      <c r="W350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -25049,10 +26102,13 @@
         <v>0.06591</v>
       </c>
       <c r="U351" s="1" t="n">
+        <v>0.06578000000000001</v>
+      </c>
+      <c r="V351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="V351" s="1" t="n">
-        <v>0.06591</v>
+      <c r="W351" s="1" t="n">
+        <v>0.06578000000000001</v>
       </c>
     </row>
     <row r="352">
@@ -25119,10 +26175,13 @@
         <v>0.06224</v>
       </c>
       <c r="U352" s="1" t="n">
+        <v>0.06218</v>
+      </c>
+      <c r="V352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="V352" s="1" t="n">
-        <v>0.06224</v>
+      <c r="W352" s="1" t="n">
+        <v>0.06218</v>
       </c>
     </row>
     <row r="353">
@@ -25189,9 +26248,12 @@
         <v>0.06288000000000001</v>
       </c>
       <c r="U353" s="1" t="n">
+        <v>0.06282</v>
+      </c>
+      <c r="V353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="V353" s="1" t="n">
+      <c r="W353" s="1" t="n">
         <v>0.06270000000000001</v>
       </c>
     </row>
@@ -25259,10 +26321,13 @@
         <v>0.10498</v>
       </c>
       <c r="U354" s="1" t="n">
+        <v>0.10348</v>
+      </c>
+      <c r="V354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="V354" s="1" t="n">
-        <v>0.10393</v>
+      <c r="W354" s="1" t="n">
+        <v>0.10348</v>
       </c>
     </row>
     <row r="355">
@@ -25329,9 +26394,12 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="U355" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="V355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="V355" s="1" t="n">
+      <c r="W355" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -25399,9 +26467,12 @@
         <v>0.0696</v>
       </c>
       <c r="U356" s="1" t="n">
+        <v>0.06947</v>
+      </c>
+      <c r="V356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="V356" s="1" t="n">
+      <c r="W356" s="1" t="n">
         <v>0.06905</v>
       </c>
     </row>
@@ -25469,9 +26540,12 @@
         <v>0.4514</v>
       </c>
       <c r="U357" s="1" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="V357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="V357" s="1" t="n">
+      <c r="W357" s="1" t="n">
         <v>0.4504</v>
       </c>
     </row>
@@ -25539,9 +26613,12 @@
         <v>0.03447</v>
       </c>
       <c r="U358" s="1" t="n">
+        <v>0.03458</v>
+      </c>
+      <c r="V358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="V358" s="1" t="n">
+      <c r="W358" s="1" t="n">
         <v>0.03441</v>
       </c>
     </row>
@@ -25609,10 +26686,13 @@
         <v>0.01457</v>
       </c>
       <c r="U359" s="1" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="V359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="V359" s="1" t="n">
-        <v>0.01454</v>
+      <c r="W359" s="1" t="n">
+        <v>0.01451</v>
       </c>
     </row>
     <row r="360">
@@ -25679,9 +26759,12 @@
         <v>0.13341</v>
       </c>
       <c r="U360" s="1" t="n">
+        <v>0.13339</v>
+      </c>
+      <c r="V360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="V360" s="1" t="n">
+      <c r="W360" s="1" t="n">
         <v>0.13282</v>
       </c>
     </row>
@@ -25749,9 +26832,12 @@
         <v>0.0005862</v>
       </c>
       <c r="U361" s="1" t="n">
+        <v>0.0005865</v>
+      </c>
+      <c r="V361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="V361" s="1" t="n">
+      <c r="W361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -25819,9 +26905,12 @@
         <v>0.03847</v>
       </c>
       <c r="U362" s="1" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="V362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="V362" s="1" t="n">
+      <c r="W362" s="1" t="n">
         <v>0.03824</v>
       </c>
     </row>
@@ -25889,9 +26978,12 @@
         <v>3.229</v>
       </c>
       <c r="U363" s="1" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V363" s="1" t="n">
         <v>3.234</v>
       </c>
-      <c r="V363" s="1" t="n">
+      <c r="W363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -25959,9 +27051,12 @@
         <v>0.1636</v>
       </c>
       <c r="U364" s="1" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="V364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="V364" s="1" t="n">
+      <c r="W364" s="1" t="n">
         <v>0.1632</v>
       </c>
     </row>
@@ -26029,9 +27124,12 @@
         <v>0.113</v>
       </c>
       <c r="U365" s="1" t="n">
+        <v>0.1129</v>
+      </c>
+      <c r="V365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="V365" s="1" t="n">
+      <c r="W365" s="1" t="n">
         <v>0.1128</v>
       </c>
     </row>
@@ -26099,9 +27197,12 @@
         <v>0.0006361</v>
       </c>
       <c r="U366" s="1" t="n">
+        <v>0.0006353</v>
+      </c>
+      <c r="V366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="V366" s="1" t="n">
+      <c r="W366" s="1" t="n">
         <v>0.000634</v>
       </c>
     </row>
@@ -26169,9 +27270,12 @@
         <v>0.05982</v>
       </c>
       <c r="U367" s="1" t="n">
+        <v>0.05937</v>
+      </c>
+      <c r="V367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="V367" s="1" t="n">
+      <c r="W367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -26239,9 +27343,12 @@
         <v>0.08111</v>
       </c>
       <c r="U368" s="1" t="n">
+        <v>0.08112999999999999</v>
+      </c>
+      <c r="V368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="V368" s="1" t="n">
+      <c r="W368" s="1" t="n">
         <v>0.08111</v>
       </c>
     </row>
@@ -26309,9 +27416,12 @@
         <v>0.03935</v>
       </c>
       <c r="U369" s="1" t="n">
+        <v>0.03944</v>
+      </c>
+      <c r="V369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="V369" s="1" t="n">
+      <c r="W369" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -26379,9 +27489,12 @@
         <v>3.708</v>
       </c>
       <c r="U370" s="1" t="n">
+        <v>3.706</v>
+      </c>
+      <c r="V370" s="1" t="n">
         <v>3.727</v>
       </c>
-      <c r="V370" s="1" t="n">
+      <c r="W370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -26449,9 +27562,12 @@
         <v>0.121</v>
       </c>
       <c r="U371" s="1" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="V371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="V371" s="1" t="n">
+      <c r="W371" s="1" t="n">
         <v>0.1206</v>
       </c>
     </row>
@@ -26519,10 +27635,13 @@
         <v>0.01468</v>
       </c>
       <c r="U372" s="1" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="V372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="V372" s="1" t="n">
-        <v>0.01467</v>
+      <c r="W372" s="1" t="n">
+        <v>0.01465</v>
       </c>
     </row>
     <row r="373">
@@ -26589,9 +27708,12 @@
         <v>0.02193</v>
       </c>
       <c r="U373" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="V373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="V373" s="1" t="n">
+      <c r="W373" s="1" t="n">
         <v>0.02191</v>
       </c>
     </row>
@@ -26659,9 +27781,12 @@
         <v>1.8723</v>
       </c>
       <c r="U374" s="1" t="n">
-        <v>1.8723</v>
+        <v>1.8728</v>
       </c>
       <c r="V374" s="1" t="n">
+        <v>1.8728</v>
+      </c>
+      <c r="W374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -26729,9 +27854,12 @@
         <v>0.02089</v>
       </c>
       <c r="U375" s="1" t="n">
+        <v>0.02082</v>
+      </c>
+      <c r="V375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="V375" s="1" t="n">
+      <c r="W375" s="1" t="n">
         <v>0.02081</v>
       </c>
     </row>
@@ -26799,9 +27927,12 @@
         <v>1.308</v>
       </c>
       <c r="U376" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="V376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="V376" s="1" t="n">
+      <c r="W376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -26869,9 +28000,12 @@
         <v>0.2828</v>
       </c>
       <c r="U377" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="V377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="V377" s="1" t="n">
+      <c r="W377" s="1" t="n">
         <v>0.2819</v>
       </c>
     </row>
@@ -26939,9 +28073,12 @@
         <v>0.01558</v>
       </c>
       <c r="U378" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="V378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="V378" s="1" t="n">
+      <c r="W378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -27009,10 +28146,13 @@
         <v>1.5302</v>
       </c>
       <c r="U379" s="1" t="n">
+        <v>1.5218</v>
+      </c>
+      <c r="V379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="V379" s="1" t="n">
-        <v>1.5275</v>
+      <c r="W379" s="1" t="n">
+        <v>1.5218</v>
       </c>
     </row>
     <row r="380">
@@ -27079,9 +28219,12 @@
         <v>6.886e-05</v>
       </c>
       <c r="U380" s="1" t="n">
+        <v>6.872000000000001e-05</v>
+      </c>
+      <c r="V380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="V380" s="1" t="n">
+      <c r="W380" s="1" t="n">
         <v>6.871e-05</v>
       </c>
     </row>
@@ -27149,9 +28292,12 @@
         <v>2.543</v>
       </c>
       <c r="U381" s="1" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="V381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="V381" s="1" t="n">
+      <c r="W381" s="1" t="n">
         <v>2.536</v>
       </c>
     </row>
@@ -27219,9 +28365,12 @@
         <v>0.06655999999999999</v>
       </c>
       <c r="U382" s="1" t="n">
+        <v>0.06661</v>
+      </c>
+      <c r="V382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="V382" s="1" t="n">
+      <c r="W382" s="1" t="n">
         <v>0.06646000000000001</v>
       </c>
     </row>
@@ -27289,9 +28438,12 @@
         <v>0.01664</v>
       </c>
       <c r="U383" s="1" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="V383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="V383" s="1" t="n">
+      <c r="W383" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -27359,9 +28511,12 @@
         <v>0.05171</v>
       </c>
       <c r="U384" s="1" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="V384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="V384" s="1" t="n">
+      <c r="W384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -27429,9 +28584,12 @@
         <v>7.597</v>
       </c>
       <c r="U385" s="1" t="n">
-        <v>7.597</v>
+        <v>7.61</v>
       </c>
       <c r="V385" s="1" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="W385" s="1" t="n">
         <v>7.554</v>
       </c>
     </row>
@@ -27499,9 +28657,12 @@
         <v>0.003267</v>
       </c>
       <c r="U386" s="1" t="n">
+        <v>0.003265</v>
+      </c>
+      <c r="V386" s="1" t="n">
         <v>0.003301</v>
       </c>
-      <c r="V386" s="1" t="n">
+      <c r="W386" s="1" t="n">
         <v>0.003258</v>
       </c>
     </row>
@@ -27569,10 +28730,13 @@
         <v>0.0003796</v>
       </c>
       <c r="U387" s="1" t="n">
+        <v>0.0003792</v>
+      </c>
+      <c r="V387" s="1" t="n">
         <v>0.0003848</v>
       </c>
-      <c r="V387" s="1" t="n">
-        <v>0.0003793</v>
+      <c r="W387" s="1" t="n">
+        <v>0.0003792</v>
       </c>
     </row>
     <row r="388">
@@ -27639,9 +28803,12 @@
         <v>0.009560000000000001</v>
       </c>
       <c r="U388" s="1" t="n">
+        <v>0.00953</v>
+      </c>
+      <c r="V388" s="1" t="n">
         <v>0.009889999999999999</v>
       </c>
-      <c r="V388" s="1" t="n">
+      <c r="W388" s="1" t="n">
         <v>0.00942</v>
       </c>
     </row>
@@ -27709,9 +28876,12 @@
         <v>0.2897</v>
       </c>
       <c r="U389" s="1" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="V389" s="1" t="n">
         <v>0.2904</v>
       </c>
-      <c r="V389" s="1" t="n">
+      <c r="W389" s="1" t="n">
         <v>0.288</v>
       </c>
     </row>
@@ -27779,9 +28949,12 @@
         <v>0.0251</v>
       </c>
       <c r="U390" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="V390" s="1" t="n">
         <v>0.0253</v>
       </c>
-      <c r="V390" s="1" t="n">
+      <c r="W390" s="1" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -27849,9 +29022,12 @@
         <v>2.836</v>
       </c>
       <c r="U391" s="1" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="V391" s="1" t="n">
         <v>2.859</v>
       </c>
-      <c r="V391" s="1" t="n">
+      <c r="W391" s="1" t="n">
         <v>2.815</v>
       </c>
     </row>
@@ -27919,9 +29095,12 @@
         <v>0.01346</v>
       </c>
       <c r="U392" s="1" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="V392" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="V392" s="1" t="n">
+      <c r="W392" s="1" t="n">
         <v>0.01338</v>
       </c>
     </row>
@@ -27989,9 +29168,12 @@
         <v>0.00235</v>
       </c>
       <c r="U393" s="1" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="V393" s="1" t="n">
         <v>0.00237</v>
       </c>
-      <c r="V393" s="1" t="n">
+      <c r="W393" s="1" t="n">
         <v>0.00235</v>
       </c>
     </row>
@@ -28059,9 +29241,12 @@
         <v>0.05933</v>
       </c>
       <c r="U394" s="1" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="V394" s="1" t="n">
         <v>0.05951</v>
       </c>
-      <c r="V394" s="1" t="n">
+      <c r="W394" s="1" t="n">
         <v>0.05922</v>
       </c>
     </row>
@@ -28129,10 +29314,13 @@
         <v>0.0401</v>
       </c>
       <c r="U395" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="V395" s="1" t="n">
         <v>0.0405</v>
       </c>
-      <c r="V395" s="1" t="n">
-        <v>0.0401</v>
+      <c r="W395" s="1" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="396">
@@ -28199,9 +29387,12 @@
         <v>0.09447</v>
       </c>
       <c r="U396" s="1" t="n">
+        <v>0.09411</v>
+      </c>
+      <c r="V396" s="1" t="n">
         <v>0.09447</v>
       </c>
-      <c r="V396" s="1" t="n">
+      <c r="W396" s="1" t="n">
         <v>0.09107999999999999</v>
       </c>
     </row>
@@ -28269,10 +29460,13 @@
         <v>0.1516</v>
       </c>
       <c r="U397" s="1" t="n">
+        <v>0.1511</v>
+      </c>
+      <c r="V397" s="1" t="n">
         <v>0.1522</v>
       </c>
-      <c r="V397" s="1" t="n">
-        <v>0.1512</v>
+      <c r="W397" s="1" t="n">
+        <v>0.1511</v>
       </c>
     </row>
     <row r="398">
@@ -28339,9 +29533,12 @@
         <v>0.931</v>
       </c>
       <c r="U398" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="V398" s="1" t="n">
         <v>0.931</v>
       </c>
-      <c r="V398" s="1" t="n">
+      <c r="W398" s="1" t="n">
         <v>0.925</v>
       </c>
     </row>
@@ -28409,9 +29606,12 @@
         <v>0.05221</v>
       </c>
       <c r="U399" s="1" t="n">
+        <v>0.05225</v>
+      </c>
+      <c r="V399" s="1" t="n">
         <v>0.05255</v>
       </c>
-      <c r="V399" s="1" t="n">
+      <c r="W399" s="1" t="n">
         <v>0.05213</v>
       </c>
     </row>
@@ -28479,10 +29679,13 @@
         <v>2.506</v>
       </c>
       <c r="U400" s="1" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="V400" s="1" t="n">
         <v>2.526</v>
       </c>
-      <c r="V400" s="1" t="n">
-        <v>2.504</v>
+      <c r="W400" s="1" t="n">
+        <v>2.502</v>
       </c>
     </row>
     <row r="401">
@@ -28549,10 +29752,13 @@
         <v>0.01773</v>
       </c>
       <c r="U401" s="1" t="n">
+        <v>0.01768</v>
+      </c>
+      <c r="V401" s="1" t="n">
         <v>0.01819</v>
       </c>
-      <c r="V401" s="1" t="n">
-        <v>0.01769</v>
+      <c r="W401" s="1" t="n">
+        <v>0.01768</v>
       </c>
     </row>
     <row r="402">
@@ -28619,9 +29825,12 @@
         <v>0.07997</v>
       </c>
       <c r="U402" s="1" t="n">
+        <v>0.07989</v>
+      </c>
+      <c r="V402" s="1" t="n">
         <v>0.08111</v>
       </c>
-      <c r="V402" s="1" t="n">
+      <c r="W402" s="1" t="n">
         <v>0.07953</v>
       </c>
     </row>
@@ -28689,9 +29898,12 @@
         <v>1.252</v>
       </c>
       <c r="U403" s="1" t="n">
+        <v>1.2509</v>
+      </c>
+      <c r="V403" s="1" t="n">
         <v>1.2526</v>
       </c>
-      <c r="V403" s="1" t="n">
+      <c r="W403" s="1" t="n">
         <v>1.2451</v>
       </c>
     </row>
@@ -28759,10 +29971,13 @@
         <v>0.00708</v>
       </c>
       <c r="U404" s="1" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="V404" s="1" t="n">
         <v>0.00721</v>
       </c>
-      <c r="V404" s="1" t="n">
-        <v>0.00708</v>
+      <c r="W404" s="1" t="n">
+        <v>0.00707</v>
       </c>
     </row>
     <row r="405">
@@ -28829,9 +30044,12 @@
         <v>0.5065</v>
       </c>
       <c r="U405" s="1" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="V405" s="1" t="n">
         <v>0.5065</v>
       </c>
-      <c r="V405" s="1" t="n">
+      <c r="W405" s="1" t="n">
         <v>0.4934</v>
       </c>
     </row>
@@ -28899,10 +30117,13 @@
         <v>0.01145</v>
       </c>
       <c r="U406" s="1" t="n">
+        <v>0.01139</v>
+      </c>
+      <c r="V406" s="1" t="n">
         <v>0.01153</v>
       </c>
-      <c r="V406" s="1" t="n">
-        <v>0.01142</v>
+      <c r="W406" s="1" t="n">
+        <v>0.01139</v>
       </c>
     </row>
     <row r="407">
@@ -28969,9 +30190,12 @@
         <v>0.04593</v>
       </c>
       <c r="U407" s="1" t="n">
+        <v>0.04588</v>
+      </c>
+      <c r="V407" s="1" t="n">
         <v>0.0465</v>
       </c>
-      <c r="V407" s="1" t="n">
+      <c r="W407" s="1" t="n">
         <v>0.04583</v>
       </c>
     </row>
@@ -29039,9 +30263,12 @@
         <v>0.0393</v>
       </c>
       <c r="U408" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="V408" s="1" t="n">
         <v>0.03964</v>
       </c>
-      <c r="V408" s="1" t="n">
+      <c r="W408" s="1" t="n">
         <v>0.03922</v>
       </c>
     </row>
@@ -29109,9 +30336,12 @@
         <v>0.05221</v>
       </c>
       <c r="U409" s="1" t="n">
+        <v>0.05219</v>
+      </c>
+      <c r="V409" s="1" t="n">
         <v>0.05285</v>
       </c>
-      <c r="V409" s="1" t="n">
+      <c r="W409" s="1" t="n">
         <v>0.05209</v>
       </c>
     </row>
@@ -29179,9 +30409,12 @@
         <v>0.01216</v>
       </c>
       <c r="U410" s="1" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="V410" s="1" t="n">
         <v>0.01256</v>
       </c>
-      <c r="V410" s="1" t="n">
+      <c r="W410" s="1" t="n">
         <v>0.01216</v>
       </c>
     </row>
@@ -29249,9 +30482,12 @@
         <v>0.06349</v>
       </c>
       <c r="U411" s="1" t="n">
+        <v>0.06347</v>
+      </c>
+      <c r="V411" s="1" t="n">
         <v>0.06404</v>
       </c>
-      <c r="V411" s="1" t="n">
+      <c r="W411" s="1" t="n">
         <v>0.06333</v>
       </c>
     </row>
@@ -29319,9 +30555,12 @@
         <v>0.04142</v>
       </c>
       <c r="U412" s="1" t="n">
+        <v>0.04127</v>
+      </c>
+      <c r="V412" s="1" t="n">
         <v>0.04154</v>
       </c>
-      <c r="V412" s="1" t="n">
+      <c r="W412" s="1" t="n">
         <v>0.04114</v>
       </c>
     </row>
@@ -29389,10 +30628,13 @@
         <v>1.111</v>
       </c>
       <c r="U413" s="1" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="V413" s="1" t="n">
         <v>1.126</v>
       </c>
-      <c r="V413" s="1" t="n">
-        <v>1.11</v>
+      <c r="W413" s="1" t="n">
+        <v>1.106</v>
       </c>
     </row>
     <row r="414">
@@ -29459,9 +30701,12 @@
         <v>0.2623</v>
       </c>
       <c r="U414" s="1" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="V414" s="1" t="n">
         <v>0.2644</v>
       </c>
-      <c r="V414" s="1" t="n">
+      <c r="W414" s="1" t="n">
         <v>0.2614</v>
       </c>
     </row>
@@ -29529,9 +30774,12 @@
         <v>0.001221</v>
       </c>
       <c r="U415" s="1" t="n">
+        <v>0.001219</v>
+      </c>
+      <c r="V415" s="1" t="n">
         <v>0.001261</v>
       </c>
-      <c r="V415" s="1" t="n">
+      <c r="W415" s="1" t="n">
         <v>0.001214</v>
       </c>
     </row>
@@ -29599,9 +30847,12 @@
         <v>0.032</v>
       </c>
       <c r="U416" s="1" t="n">
+        <v>0.03187</v>
+      </c>
+      <c r="V416" s="1" t="n">
         <v>0.03207</v>
       </c>
-      <c r="V416" s="1" t="n">
+      <c r="W416" s="1" t="n">
         <v>0.03175</v>
       </c>
     </row>
@@ -29669,9 +30920,12 @@
         <v>0.01454</v>
       </c>
       <c r="U417" s="1" t="n">
+        <v>0.01459</v>
+      </c>
+      <c r="V417" s="1" t="n">
         <v>0.01473</v>
       </c>
-      <c r="V417" s="1" t="n">
+      <c r="W417" s="1" t="n">
         <v>0.01451</v>
       </c>
     </row>
@@ -29739,9 +30993,12 @@
         <v>0.1481</v>
       </c>
       <c r="U418" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="V418" s="1" t="n">
         <v>0.1488</v>
       </c>
-      <c r="V418" s="1" t="n">
+      <c r="W418" s="1" t="n">
         <v>0.1478</v>
       </c>
     </row>
@@ -29809,9 +31066,12 @@
         <v>0.04888</v>
       </c>
       <c r="U419" s="1" t="n">
+        <v>0.04884</v>
+      </c>
+      <c r="V419" s="1" t="n">
         <v>0.04968</v>
       </c>
-      <c r="V419" s="1" t="n">
+      <c r="W419" s="1" t="n">
         <v>0.04862</v>
       </c>
     </row>
@@ -29879,9 +31139,12 @@
         <v>66.34</v>
       </c>
       <c r="U420" s="1" t="n">
+        <v>66.37</v>
+      </c>
+      <c r="V420" s="1" t="n">
         <v>66.94</v>
       </c>
-      <c r="V420" s="1" t="n">
+      <c r="W420" s="1" t="n">
         <v>65.70999999999999</v>
       </c>
     </row>
@@ -29949,9 +31212,12 @@
         <v>0.877</v>
       </c>
       <c r="U421" s="1" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="V421" s="1" t="n">
         <v>0.879</v>
       </c>
-      <c r="V421" s="1" t="n">
+      <c r="W421" s="1" t="n">
         <v>0.874</v>
       </c>
     </row>
@@ -30019,9 +31285,12 @@
         <v>0.012429</v>
       </c>
       <c r="U422" s="1" t="n">
+        <v>0.012434</v>
+      </c>
+      <c r="V422" s="1" t="n">
         <v>0.012972</v>
       </c>
-      <c r="V422" s="1" t="n">
+      <c r="W422" s="1" t="n">
         <v>0.01239</v>
       </c>
     </row>
@@ -30089,9 +31358,12 @@
         <v>0.01593</v>
       </c>
       <c r="U423" s="1" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="V423" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="V423" s="1" t="n">
+      <c r="W423" s="1" t="n">
         <v>0.01592</v>
       </c>
     </row>
@@ -30159,9 +31431,12 @@
         <v>0.27302</v>
       </c>
       <c r="U424" s="1" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="V424" s="1" t="n">
         <v>0.27462</v>
       </c>
-      <c r="V424" s="1" t="n">
+      <c r="W424" s="1" t="n">
         <v>0.25951</v>
       </c>
     </row>
@@ -30229,9 +31504,12 @@
         <v>0.5991</v>
       </c>
       <c r="U425" s="1" t="n">
+        <v>0.5993000000000001</v>
+      </c>
+      <c r="V425" s="1" t="n">
         <v>0.6022999999999999</v>
       </c>
-      <c r="V425" s="1" t="n">
+      <c r="W425" s="1" t="n">
         <v>0.5984</v>
       </c>
     </row>
@@ -30299,9 +31577,12 @@
         <v>0.005494</v>
       </c>
       <c r="U426" s="1" t="n">
+        <v>0.005495</v>
+      </c>
+      <c r="V426" s="1" t="n">
         <v>0.005657</v>
       </c>
-      <c r="V426" s="1" t="n">
+      <c r="W426" s="1" t="n">
         <v>0.005493</v>
       </c>
     </row>
@@ -30369,9 +31650,12 @@
         <v>0.04986</v>
       </c>
       <c r="U427" s="1" t="n">
-        <v>0.04986</v>
+        <v>0.05022</v>
       </c>
       <c r="V427" s="1" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="W427" s="1" t="n">
         <v>0.0489</v>
       </c>
     </row>
@@ -30439,9 +31723,12 @@
         <v>0.1254</v>
       </c>
       <c r="U428" s="1" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="V428" s="1" t="n">
         <v>0.1272</v>
       </c>
-      <c r="V428" s="1" t="n">
+      <c r="W428" s="1" t="n">
         <v>0.1249</v>
       </c>
     </row>
@@ -30509,9 +31796,12 @@
         <v>0.003186</v>
       </c>
       <c r="U429" s="1" t="n">
+        <v>0.003181</v>
+      </c>
+      <c r="V429" s="1" t="n">
         <v>0.003205</v>
       </c>
-      <c r="V429" s="1" t="n">
+      <c r="W429" s="1" t="n">
         <v>0.003165</v>
       </c>
     </row>
@@ -30579,10 +31869,13 @@
         <v>0.03626</v>
       </c>
       <c r="U430" s="1" t="n">
+        <v>0.03622</v>
+      </c>
+      <c r="V430" s="1" t="n">
         <v>0.03678</v>
       </c>
-      <c r="V430" s="1" t="n">
-        <v>0.03626</v>
+      <c r="W430" s="1" t="n">
+        <v>0.03622</v>
       </c>
     </row>
     <row r="431">
@@ -30649,9 +31942,12 @@
         <v>0.3922</v>
       </c>
       <c r="U431" s="1" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="V431" s="1" t="n">
         <v>0.4011</v>
       </c>
-      <c r="V431" s="1" t="n">
+      <c r="W431" s="1" t="n">
         <v>0.3914</v>
       </c>
     </row>
@@ -30719,9 +32015,12 @@
         <v>0.004468</v>
       </c>
       <c r="U432" s="1" t="n">
+        <v>0.004457</v>
+      </c>
+      <c r="V432" s="1" t="n">
         <v>0.004543</v>
       </c>
-      <c r="V432" s="1" t="n">
+      <c r="W432" s="1" t="n">
         <v>0.004446</v>
       </c>
     </row>
@@ -30789,9 +32088,12 @@
         <v>0.0975</v>
       </c>
       <c r="U433" s="1" t="n">
+        <v>0.0975</v>
+      </c>
+      <c r="V433" s="1" t="n">
         <v>0.0983</v>
       </c>
-      <c r="V433" s="1" t="n">
+      <c r="W433" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
     </row>
@@ -30859,9 +32161,12 @@
         <v>0.0124</v>
       </c>
       <c r="U434" s="1" t="n">
+        <v>0.01239</v>
+      </c>
+      <c r="V434" s="1" t="n">
         <v>0.01247</v>
       </c>
-      <c r="V434" s="1" t="n">
+      <c r="W434" s="1" t="n">
         <v>0.01234</v>
       </c>
     </row>
@@ -30929,9 +32234,12 @@
         <v>2.004</v>
       </c>
       <c r="U435" s="1" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V435" s="1" t="n">
         <v>2.004</v>
       </c>
-      <c r="V435" s="1" t="n">
+      <c r="W435" s="1" t="n">
         <v>1.968</v>
       </c>
     </row>
@@ -30999,10 +32307,13 @@
         <v>0.001771</v>
       </c>
       <c r="U436" s="1" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="V436" s="1" t="n">
         <v>0.001882</v>
       </c>
-      <c r="V436" s="1" t="n">
-        <v>0.001771</v>
+      <c r="W436" s="1" t="n">
+        <v>0.001767</v>
       </c>
     </row>
     <row r="437">
@@ -31072,6 +32383,9 @@
         <v>0.4427</v>
       </c>
       <c r="V437" s="1" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="W437" s="1" t="n">
         <v>0.4413</v>
       </c>
     </row>
@@ -31139,9 +32453,12 @@
         <v>0.00534</v>
       </c>
       <c r="U438" s="1" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="V438" s="1" t="n">
         <v>0.00537</v>
       </c>
-      <c r="V438" s="1" t="n">
+      <c r="W438" s="1" t="n">
         <v>0.00533</v>
       </c>
     </row>
@@ -31209,9 +32526,12 @@
         <v>0.1034</v>
       </c>
       <c r="U439" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="V439" s="1" t="n">
         <v>0.1038</v>
       </c>
-      <c r="V439" s="1" t="n">
+      <c r="W439" s="1" t="n">
         <v>0.1032</v>
       </c>
     </row>
@@ -31279,10 +32599,13 @@
         <v>0.03363</v>
       </c>
       <c r="U440" s="1" t="n">
+        <v>0.03356</v>
+      </c>
+      <c r="V440" s="1" t="n">
         <v>0.03457</v>
       </c>
-      <c r="V440" s="1" t="n">
-        <v>0.03361</v>
+      <c r="W440" s="1" t="n">
+        <v>0.03356</v>
       </c>
     </row>
     <row r="441">
@@ -31349,9 +32672,12 @@
         <v>0.08196000000000001</v>
       </c>
       <c r="U441" s="1" t="n">
+        <v>0.08184</v>
+      </c>
+      <c r="V441" s="1" t="n">
         <v>0.08221000000000001</v>
       </c>
-      <c r="V441" s="1" t="n">
+      <c r="W441" s="1" t="n">
         <v>0.08179</v>
       </c>
     </row>
@@ -31419,10 +32745,13 @@
         <v>1.299</v>
       </c>
       <c r="U442" s="1" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="V442" s="1" t="n">
         <v>1.315</v>
       </c>
-      <c r="V442" s="1" t="n">
-        <v>1.299</v>
+      <c r="W442" s="1" t="n">
+        <v>1.296</v>
       </c>
     </row>
     <row r="443">
@@ -31489,9 +32818,12 @@
         <v>0.07519000000000001</v>
       </c>
       <c r="U443" s="1" t="n">
+        <v>0.07514999999999999</v>
+      </c>
+      <c r="V443" s="1" t="n">
         <v>0.07585</v>
       </c>
-      <c r="V443" s="1" t="n">
+      <c r="W443" s="1" t="n">
         <v>0.07491</v>
       </c>
     </row>
@@ -31559,9 +32891,12 @@
         <v>0.07633</v>
       </c>
       <c r="U444" s="1" t="n">
+        <v>0.07633</v>
+      </c>
+      <c r="V444" s="1" t="n">
         <v>0.07701</v>
       </c>
-      <c r="V444" s="1" t="n">
+      <c r="W444" s="1" t="n">
         <v>0.07616000000000001</v>
       </c>
     </row>
@@ -31629,9 +32964,12 @@
         <v>0.04298</v>
       </c>
       <c r="U445" s="1" t="n">
+        <v>0.04299</v>
+      </c>
+      <c r="V445" s="1" t="n">
         <v>0.04388</v>
       </c>
-      <c r="V445" s="1" t="n">
+      <c r="W445" s="1" t="n">
         <v>0.04298</v>
       </c>
     </row>
@@ -31699,9 +33037,12 @@
         <v>0.02141</v>
       </c>
       <c r="U446" s="1" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="V446" s="1" t="n">
         <v>0.0217</v>
       </c>
-      <c r="V446" s="1" t="n">
+      <c r="W446" s="1" t="n">
         <v>0.02132</v>
       </c>
     </row>
@@ -31769,9 +33110,12 @@
         <v>0.2781</v>
       </c>
       <c r="U447" s="1" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="V447" s="1" t="n">
         <v>0.2816</v>
       </c>
-      <c r="V447" s="1" t="n">
+      <c r="W447" s="1" t="n">
         <v>0.2781</v>
       </c>
     </row>
@@ -31839,10 +33183,13 @@
         <v>0.03065</v>
       </c>
       <c r="U448" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="V448" s="1" t="n">
         <v>0.03146</v>
       </c>
-      <c r="V448" s="1" t="n">
-        <v>0.03065</v>
+      <c r="W448" s="1" t="n">
+        <v>0.03061</v>
       </c>
     </row>
     <row r="449">
@@ -31909,9 +33256,12 @@
         <v>0.00646</v>
       </c>
       <c r="U449" s="1" t="n">
-        <v>0.00647</v>
+        <v>0.00655</v>
       </c>
       <c r="V449" s="1" t="n">
+        <v>0.00655</v>
+      </c>
+      <c r="W449" s="1" t="n">
         <v>0.00642</v>
       </c>
     </row>
@@ -31979,9 +33329,12 @@
         <v>0.022993</v>
       </c>
       <c r="U450" s="1" t="n">
+        <v>0.023004</v>
+      </c>
+      <c r="V450" s="1" t="n">
         <v>0.02312</v>
       </c>
-      <c r="V450" s="1" t="n">
+      <c r="W450" s="1" t="n">
         <v>0.022858</v>
       </c>
     </row>
@@ -32049,9 +33402,12 @@
         <v>0.0424</v>
       </c>
       <c r="U451" s="1" t="n">
+        <v>0.04238</v>
+      </c>
+      <c r="V451" s="1" t="n">
         <v>0.0425</v>
       </c>
-      <c r="V451" s="1" t="n">
+      <c r="W451" s="1" t="n">
         <v>0.04223</v>
       </c>
     </row>
@@ -32119,9 +33475,12 @@
         <v>0.07224999999999999</v>
       </c>
       <c r="U452" s="1" t="n">
+        <v>0.07242999999999999</v>
+      </c>
+      <c r="V452" s="1" t="n">
         <v>0.07363</v>
       </c>
-      <c r="V452" s="1" t="n">
+      <c r="W452" s="1" t="n">
         <v>0.07204000000000001</v>
       </c>
     </row>
@@ -32189,9 +33548,12 @@
         <v>0.0005921</v>
       </c>
       <c r="U453" s="1" t="n">
+        <v>0.0005919</v>
+      </c>
+      <c r="V453" s="1" t="n">
         <v>0.0005951</v>
       </c>
-      <c r="V453" s="1" t="n">
+      <c r="W453" s="1" t="n">
         <v>0.0005904</v>
       </c>
     </row>
@@ -32259,9 +33621,12 @@
         <v>0.304</v>
       </c>
       <c r="U454" s="1" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="V454" s="1" t="n">
         <v>0.31</v>
       </c>
-      <c r="V454" s="1" t="n">
+      <c r="W454" s="1" t="n">
         <v>0.304</v>
       </c>
     </row>
@@ -32329,9 +33694,12 @@
         <v>0.00429</v>
       </c>
       <c r="U455" s="1" t="n">
+        <v>0.004292</v>
+      </c>
+      <c r="V455" s="1" t="n">
         <v>0.004338</v>
       </c>
-      <c r="V455" s="1" t="n">
+      <c r="W455" s="1" t="n">
         <v>0.004208</v>
       </c>
     </row>
@@ -32399,10 +33767,13 @@
         <v>0.1823</v>
       </c>
       <c r="U456" s="1" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="V456" s="1" t="n">
         <v>0.1844</v>
       </c>
-      <c r="V456" s="1" t="n">
-        <v>0.1817</v>
+      <c r="W456" s="1" t="n">
+        <v>0.1816</v>
       </c>
     </row>
     <row r="457">
@@ -32469,9 +33840,12 @@
         <v>0.04264</v>
       </c>
       <c r="U457" s="1" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="V457" s="1" t="n">
         <v>0.04284</v>
       </c>
-      <c r="V457" s="1" t="n">
+      <c r="W457" s="1" t="n">
         <v>0.04254</v>
       </c>
     </row>
@@ -32539,10 +33913,13 @@
         <v>0.1452</v>
       </c>
       <c r="U458" s="1" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="V458" s="1" t="n">
         <v>0.1465</v>
       </c>
-      <c r="V458" s="1" t="n">
-        <v>0.1452</v>
+      <c r="W458" s="1" t="n">
+        <v>0.1448</v>
       </c>
     </row>
     <row r="459">
@@ -32609,9 +33986,12 @@
         <v>0.008588</v>
       </c>
       <c r="U459" s="1" t="n">
+        <v>0.008576</v>
+      </c>
+      <c r="V459" s="1" t="n">
         <v>0.008665000000000001</v>
       </c>
-      <c r="V459" s="1" t="n">
+      <c r="W459" s="1" t="n">
         <v>0.008574</v>
       </c>
     </row>
@@ -32679,9 +34059,12 @@
         <v>0.007438</v>
       </c>
       <c r="U460" s="1" t="n">
+        <v>0.007446</v>
+      </c>
+      <c r="V460" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="V460" s="1" t="n">
+      <c r="W460" s="1" t="n">
         <v>0.007353</v>
       </c>
     </row>
@@ -32749,9 +34132,12 @@
         <v>0.0001749</v>
       </c>
       <c r="U461" s="1" t="n">
-        <v>0.0001749</v>
+        <v>0.0001899</v>
       </c>
       <c r="V461" s="1" t="n">
+        <v>0.0001899</v>
+      </c>
+      <c r="W461" s="1" t="n">
         <v>0.0001722</v>
       </c>
     </row>
@@ -32819,9 +34205,12 @@
         <v>0.02425</v>
       </c>
       <c r="U462" s="1" t="n">
+        <v>0.02392</v>
+      </c>
+      <c r="V462" s="1" t="n">
         <v>0.02585</v>
       </c>
-      <c r="V462" s="1" t="n">
+      <c r="W462" s="1" t="n">
         <v>0.02244</v>
       </c>
     </row>
@@ -32889,9 +34278,12 @@
         <v>0.03652</v>
       </c>
       <c r="U463" s="1" t="n">
+        <v>0.03658</v>
+      </c>
+      <c r="V463" s="1" t="n">
         <v>0.0378</v>
       </c>
-      <c r="V463" s="1" t="n">
+      <c r="W463" s="1" t="n">
         <v>0.03652</v>
       </c>
     </row>
@@ -32959,9 +34351,12 @@
         <v>0.3015</v>
       </c>
       <c r="U464" s="1" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="V464" s="1" t="n">
         <v>0.3046</v>
       </c>
-      <c r="V464" s="1" t="n">
+      <c r="W464" s="1" t="n">
         <v>0.3003</v>
       </c>
     </row>
@@ -33029,10 +34424,13 @@
         <v>0.03889</v>
       </c>
       <c r="U465" s="1" t="n">
+        <v>0.03887</v>
+      </c>
+      <c r="V465" s="1" t="n">
         <v>0.03937</v>
       </c>
-      <c r="V465" s="1" t="n">
-        <v>0.03889</v>
+      <c r="W465" s="1" t="n">
+        <v>0.03887</v>
       </c>
     </row>
     <row r="466">
@@ -33099,9 +34497,12 @@
         <v>2.669</v>
       </c>
       <c r="U466" s="1" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="V466" s="1" t="n">
         <v>2.691</v>
       </c>
-      <c r="V466" s="1" t="n">
+      <c r="W466" s="1" t="n">
         <v>2.66</v>
       </c>
     </row>
@@ -33169,9 +34570,12 @@
         <v>0.03434</v>
       </c>
       <c r="U467" s="1" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="V467" s="1" t="n">
         <v>0.03438</v>
       </c>
-      <c r="V467" s="1" t="n">
+      <c r="W467" s="1" t="n">
         <v>0.0337</v>
       </c>
     </row>
@@ -33239,9 +34643,12 @@
         <v>0.1761</v>
       </c>
       <c r="U468" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="V468" s="1" t="n">
         <v>0.1767</v>
       </c>
-      <c r="V468" s="1" t="n">
+      <c r="W468" s="1" t="n">
         <v>0.1758</v>
       </c>
     </row>
@@ -33309,9 +34716,12 @@
         <v>0.0961</v>
       </c>
       <c r="U469" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="V469" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="V469" s="1" t="n">
+      <c r="W469" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -33379,9 +34789,12 @@
         <v>0.06815</v>
       </c>
       <c r="U470" s="1" t="n">
-        <v>0.06815</v>
+        <v>0.06838</v>
       </c>
       <c r="V470" s="1" t="n">
+        <v>0.06838</v>
+      </c>
+      <c r="W470" s="1" t="n">
         <v>0.06696000000000001</v>
       </c>
     </row>
@@ -33449,10 +34862,13 @@
         <v>0.03979</v>
       </c>
       <c r="U471" s="1" t="n">
+        <v>0.03967</v>
+      </c>
+      <c r="V471" s="1" t="n">
         <v>0.04007</v>
       </c>
-      <c r="V471" s="1" t="n">
-        <v>0.03969</v>
+      <c r="W471" s="1" t="n">
+        <v>0.03967</v>
       </c>
     </row>
     <row r="472">
@@ -33519,9 +34935,12 @@
         <v>0.2465</v>
       </c>
       <c r="U472" s="1" t="n">
+        <v>0.2464</v>
+      </c>
+      <c r="V472" s="1" t="n">
         <v>0.2484</v>
       </c>
-      <c r="V472" s="1" t="n">
+      <c r="W472" s="1" t="n">
         <v>0.2457</v>
       </c>
     </row>
@@ -33589,9 +35008,12 @@
         <v>0.016239</v>
       </c>
       <c r="U473" s="1" t="n">
+        <v>0.016273</v>
+      </c>
+      <c r="V473" s="1" t="n">
         <v>0.016588</v>
       </c>
-      <c r="V473" s="1" t="n">
+      <c r="W473" s="1" t="n">
         <v>0.016238</v>
       </c>
     </row>
@@ -33659,9 +35081,12 @@
         <v>0.1148</v>
       </c>
       <c r="U474" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="V474" s="1" t="n">
         <v>0.1158</v>
       </c>
-      <c r="V474" s="1" t="n">
+      <c r="W474" s="1" t="n">
         <v>0.1146</v>
       </c>
     </row>
@@ -33729,9 +35154,12 @@
         <v>0.04279</v>
       </c>
       <c r="U475" s="1" t="n">
+        <v>0.04298</v>
+      </c>
+      <c r="V475" s="1" t="n">
         <v>0.04304</v>
       </c>
-      <c r="V475" s="1" t="n">
+      <c r="W475" s="1" t="n">
         <v>0.04258</v>
       </c>
     </row>
@@ -33799,9 +35227,12 @@
         <v>0.2067</v>
       </c>
       <c r="U476" s="1" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="V476" s="1" t="n">
         <v>0.2081</v>
       </c>
-      <c r="V476" s="1" t="n">
+      <c r="W476" s="1" t="n">
         <v>0.2062</v>
       </c>
     </row>
@@ -33869,9 +35300,12 @@
         <v>0.006817</v>
       </c>
       <c r="U477" s="1" t="n">
+        <v>0.006791</v>
+      </c>
+      <c r="V477" s="1" t="n">
         <v>0.006837</v>
       </c>
-      <c r="V477" s="1" t="n">
+      <c r="W477" s="1" t="n">
         <v>0.006763</v>
       </c>
     </row>
@@ -33939,9 +35373,12 @@
         <v>0.01778</v>
       </c>
       <c r="U478" s="1" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="V478" s="1" t="n">
         <v>0.01814</v>
       </c>
-      <c r="V478" s="1" t="n">
+      <c r="W478" s="1" t="n">
         <v>0.01776</v>
       </c>
     </row>
@@ -34009,10 +35446,13 @@
         <v>0.04667</v>
       </c>
       <c r="U479" s="1" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="V479" s="1" t="n">
         <v>0.04738</v>
       </c>
-      <c r="V479" s="1" t="n">
-        <v>0.04647</v>
+      <c r="W479" s="1" t="n">
+        <v>0.04639</v>
       </c>
     </row>
     <row r="480">
@@ -34079,9 +35519,12 @@
         <v>0.26079</v>
       </c>
       <c r="U480" s="1" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="V480" s="1" t="n">
         <v>0.2618</v>
       </c>
-      <c r="V480" s="1" t="n">
+      <c r="W480" s="1" t="n">
         <v>0.25884</v>
       </c>
     </row>
@@ -34149,10 +35592,13 @@
         <v>0.01207</v>
       </c>
       <c r="U481" s="1" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="V481" s="1" t="n">
         <v>0.01253</v>
       </c>
-      <c r="V481" s="1" t="n">
-        <v>0.01207</v>
+      <c r="W481" s="1" t="n">
+        <v>0.01206</v>
       </c>
     </row>
     <row r="482">
@@ -34219,9 +35665,12 @@
         <v>0.004055</v>
       </c>
       <c r="U482" s="1" t="n">
+        <v>0.004064</v>
+      </c>
+      <c r="V482" s="1" t="n">
         <v>0.00413</v>
       </c>
-      <c r="V482" s="1" t="n">
+      <c r="W482" s="1" t="n">
         <v>0.004055</v>
       </c>
     </row>
@@ -34289,9 +35738,12 @@
         <v>0.1228</v>
       </c>
       <c r="U483" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="V483" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="V483" s="1" t="n">
+      <c r="W483" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -34359,9 +35811,12 @@
         <v>0.02198</v>
       </c>
       <c r="U484" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="V484" s="1" t="n">
         <v>0.02222</v>
       </c>
-      <c r="V484" s="1" t="n">
+      <c r="W484" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -34429,9 +35884,12 @@
         <v>0.04526</v>
       </c>
       <c r="U485" s="1" t="n">
+        <v>0.04553</v>
+      </c>
+      <c r="V485" s="1" t="n">
         <v>0.04638</v>
       </c>
-      <c r="V485" s="1" t="n">
+      <c r="W485" s="1" t="n">
         <v>0.04514</v>
       </c>
     </row>
@@ -34499,10 +35957,13 @@
         <v>0.1724</v>
       </c>
       <c r="U486" s="1" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="V486" s="1" t="n">
         <v>0.1738</v>
       </c>
-      <c r="V486" s="1" t="n">
-        <v>0.1724</v>
+      <c r="W486" s="1" t="n">
+        <v>0.1721</v>
       </c>
     </row>
     <row r="487">
@@ -34569,9 +36030,12 @@
         <v>0.2767</v>
       </c>
       <c r="U487" s="1" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="V487" s="1" t="n">
         <v>0.2767</v>
       </c>
-      <c r="V487" s="1" t="n">
+      <c r="W487" s="1" t="n">
         <v>0.2725</v>
       </c>
     </row>
@@ -34639,9 +36103,12 @@
         <v>0.04594</v>
       </c>
       <c r="U488" s="1" t="n">
+        <v>0.04582</v>
+      </c>
+      <c r="V488" s="1" t="n">
         <v>0.0463</v>
       </c>
-      <c r="V488" s="1" t="n">
+      <c r="W488" s="1" t="n">
         <v>0.04578</v>
       </c>
     </row>
@@ -34709,9 +36176,12 @@
         <v>0.0002141</v>
       </c>
       <c r="U489" s="1" t="n">
+        <v>0.0002142</v>
+      </c>
+      <c r="V489" s="1" t="n">
         <v>0.0002159</v>
       </c>
-      <c r="V489" s="1" t="n">
+      <c r="W489" s="1" t="n">
         <v>0.0002139</v>
       </c>
     </row>
@@ -34779,9 +36249,12 @@
         <v>1.783</v>
       </c>
       <c r="U490" s="1" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="V490" s="1" t="n">
         <v>1.783</v>
       </c>
-      <c r="V490" s="1" t="n">
+      <c r="W490" s="1" t="n">
         <v>1.759</v>
       </c>
     </row>
@@ -34849,9 +36322,12 @@
         <v>16.034</v>
       </c>
       <c r="U491" s="1" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="V491" s="1" t="n">
         <v>16.087</v>
       </c>
-      <c r="V491" s="1" t="n">
+      <c r="W491" s="1" t="n">
         <v>15.99</v>
       </c>
     </row>
@@ -34919,9 +36395,12 @@
         <v>0.06652</v>
       </c>
       <c r="U492" s="1" t="n">
+        <v>0.06645</v>
+      </c>
+      <c r="V492" s="1" t="n">
         <v>0.06703000000000001</v>
       </c>
-      <c r="V492" s="1" t="n">
+      <c r="W492" s="1" t="n">
         <v>0.06637</v>
       </c>
     </row>
@@ -34989,9 +36468,12 @@
         <v>0.06739000000000001</v>
       </c>
       <c r="U493" s="1" t="n">
+        <v>0.06726</v>
+      </c>
+      <c r="V493" s="1" t="n">
         <v>0.06768</v>
       </c>
-      <c r="V493" s="1" t="n">
+      <c r="W493" s="1" t="n">
         <v>0.06709</v>
       </c>
     </row>
@@ -35059,9 +36541,12 @@
         <v>0.009408</v>
       </c>
       <c r="U494" s="1" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="V494" s="1" t="n">
         <v>0.009471</v>
       </c>
-      <c r="V494" s="1" t="n">
+      <c r="W494" s="1" t="n">
         <v>0.009375</v>
       </c>
     </row>
@@ -35129,9 +36614,12 @@
         <v>0.005774</v>
       </c>
       <c r="U495" s="1" t="n">
+        <v>0.005776</v>
+      </c>
+      <c r="V495" s="1" t="n">
         <v>0.006116</v>
       </c>
-      <c r="V495" s="1" t="n">
+      <c r="W495" s="1" t="n">
         <v>0.005774</v>
       </c>
     </row>
@@ -35199,10 +36687,13 @@
         <v>0.009820000000000001</v>
       </c>
       <c r="U496" s="1" t="n">
+        <v>0.009809999999999999</v>
+      </c>
+      <c r="V496" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
-      <c r="V496" s="1" t="n">
-        <v>0.009820000000000001</v>
+      <c r="W496" s="1" t="n">
+        <v>0.009809999999999999</v>
       </c>
     </row>
     <row r="497">
@@ -35269,9 +36760,12 @@
         <v>0.04655</v>
       </c>
       <c r="U497" s="1" t="n">
+        <v>0.04551</v>
+      </c>
+      <c r="V497" s="1" t="n">
         <v>0.04665</v>
       </c>
-      <c r="V497" s="1" t="n">
+      <c r="W497" s="1" t="n">
         <v>0.04389</v>
       </c>
     </row>
@@ -35339,9 +36833,12 @@
         <v>0.006353</v>
       </c>
       <c r="U498" s="1" t="n">
+        <v>0.006361</v>
+      </c>
+      <c r="V498" s="1" t="n">
         <v>0.006412</v>
       </c>
-      <c r="V498" s="1" t="n">
+      <c r="W498" s="1" t="n">
         <v>0.006338</v>
       </c>
     </row>
@@ -35409,10 +36906,13 @@
         <v>0.01035</v>
       </c>
       <c r="U499" s="1" t="n">
+        <v>0.01029</v>
+      </c>
+      <c r="V499" s="1" t="n">
         <v>0.01049</v>
       </c>
-      <c r="V499" s="1" t="n">
-        <v>0.01032</v>
+      <c r="W499" s="1" t="n">
+        <v>0.01029</v>
       </c>
     </row>
     <row r="500">
@@ -35479,9 +36979,12 @@
         <v>0.5076000000000001</v>
       </c>
       <c r="U500" s="1" t="n">
+        <v>0.5071</v>
+      </c>
+      <c r="V500" s="1" t="n">
         <v>0.5134</v>
       </c>
-      <c r="V500" s="1" t="n">
+      <c r="W500" s="1" t="n">
         <v>0.5067</v>
       </c>
     </row>
@@ -35549,9 +37052,12 @@
         <v>0.03208</v>
       </c>
       <c r="U501" s="1" t="n">
+        <v>0.03209</v>
+      </c>
+      <c r="V501" s="1" t="n">
         <v>0.03213</v>
       </c>
-      <c r="V501" s="1" t="n">
+      <c r="W501" s="1" t="n">
         <v>0.03199</v>
       </c>
     </row>
@@ -35619,10 +37125,13 @@
         <v>0.4353</v>
       </c>
       <c r="U502" s="1" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="V502" s="1" t="n">
         <v>0.446</v>
       </c>
-      <c r="V502" s="1" t="n">
-        <v>0.4353</v>
+      <c r="W502" s="1" t="n">
+        <v>0.4326</v>
       </c>
     </row>
     <row r="503">
@@ -35689,9 +37198,12 @@
         <v>0.999342</v>
       </c>
       <c r="U503" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="V503" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="V503" s="1" t="n">
+      <c r="W503" s="1" t="n">
         <v>0.999341</v>
       </c>
     </row>
@@ -35759,9 +37271,12 @@
         <v>0.03535</v>
       </c>
       <c r="U504" s="1" t="n">
+        <v>0.03522</v>
+      </c>
+      <c r="V504" s="1" t="n">
         <v>0.03555</v>
       </c>
-      <c r="V504" s="1" t="n">
+      <c r="W504" s="1" t="n">
         <v>0.03501</v>
       </c>
     </row>
@@ -35829,9 +37344,12 @@
         <v>0.004915</v>
       </c>
       <c r="U505" s="1" t="n">
+        <v>0.00491</v>
+      </c>
+      <c r="V505" s="1" t="n">
         <v>0.004962</v>
       </c>
-      <c r="V505" s="1" t="n">
+      <c r="W505" s="1" t="n">
         <v>0.004893</v>
       </c>
     </row>
@@ -35899,9 +37417,12 @@
         <v>0.01383</v>
       </c>
       <c r="U506" s="1" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="V506" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="V506" s="1" t="n">
+      <c r="W506" s="1" t="n">
         <v>0.0138</v>
       </c>
     </row>
@@ -35969,9 +37490,12 @@
         <v>0.003488</v>
       </c>
       <c r="U507" s="1" t="n">
+        <v>0.003477</v>
+      </c>
+      <c r="V507" s="1" t="n">
         <v>0.003516</v>
       </c>
-      <c r="V507" s="1" t="n">
+      <c r="W507" s="1" t="n">
         <v>0.003453</v>
       </c>
     </row>
@@ -36039,9 +37563,12 @@
         <v>1.413</v>
       </c>
       <c r="U508" s="1" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="V508" s="1" t="n">
         <v>1.422</v>
       </c>
-      <c r="V508" s="1" t="n">
+      <c r="W508" s="1" t="n">
         <v>1.411</v>
       </c>
     </row>
@@ -36109,10 +37636,13 @@
         <v>0.005059</v>
       </c>
       <c r="U509" s="1" t="n">
+        <v>0.005026</v>
+      </c>
+      <c r="V509" s="1" t="n">
         <v>0.005124</v>
       </c>
-      <c r="V509" s="1" t="n">
-        <v>0.005056</v>
+      <c r="W509" s="1" t="n">
+        <v>0.005026</v>
       </c>
     </row>
     <row r="510">
@@ -36179,9 +37709,12 @@
         <v>0.0156</v>
       </c>
       <c r="U510" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="V510" s="1" t="n">
         <v>0.01577</v>
       </c>
-      <c r="V510" s="1" t="n">
+      <c r="W510" s="1" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -36249,9 +37782,12 @@
         <v>0.08175</v>
       </c>
       <c r="U511" s="1" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="V511" s="1" t="n">
         <v>0.08361</v>
       </c>
-      <c r="V511" s="1" t="n">
+      <c r="W511" s="1" t="n">
         <v>0.08119</v>
       </c>
     </row>
@@ -36319,9 +37855,12 @@
         <v>0.00709</v>
       </c>
       <c r="U512" s="1" t="n">
+        <v>0.007082</v>
+      </c>
+      <c r="V512" s="1" t="n">
         <v>0.007121</v>
       </c>
-      <c r="V512" s="1" t="n">
+      <c r="W512" s="1" t="n">
         <v>0.007067</v>
       </c>
     </row>
@@ -36389,9 +37928,12 @@
         <v>0.01478</v>
       </c>
       <c r="U513" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="V513" s="1" t="n">
         <v>0.01495</v>
       </c>
-      <c r="V513" s="1" t="n">
+      <c r="W513" s="1" t="n">
         <v>0.01468</v>
       </c>
     </row>
@@ -36459,10 +38001,13 @@
         <v>0.04712</v>
       </c>
       <c r="U514" s="1" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="V514" s="1" t="n">
         <v>0.04787</v>
       </c>
-      <c r="V514" s="1" t="n">
-        <v>0.04712</v>
+      <c r="W514" s="1" t="n">
+        <v>0.0471</v>
       </c>
     </row>
     <row r="515">
@@ -36529,9 +38074,12 @@
         <v>0.01803</v>
       </c>
       <c r="U515" s="1" t="n">
+        <v>0.01806</v>
+      </c>
+      <c r="V515" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="V515" s="1" t="n">
+      <c r="W515" s="1" t="n">
         <v>0.01796</v>
       </c>
     </row>
@@ -36599,9 +38147,12 @@
         <v>0.000579</v>
       </c>
       <c r="U516" s="1" t="n">
+        <v>0.000579</v>
+      </c>
+      <c r="V516" s="1" t="n">
         <v>0.0005813</v>
       </c>
-      <c r="V516" s="1" t="n">
+      <c r="W516" s="1" t="n">
         <v>0.000578</v>
       </c>
     </row>
@@ -36669,9 +38220,12 @@
         <v>0.07838000000000001</v>
       </c>
       <c r="U517" s="1" t="n">
+        <v>0.07825</v>
+      </c>
+      <c r="V517" s="1" t="n">
         <v>0.07904</v>
       </c>
-      <c r="V517" s="1" t="n">
+      <c r="W517" s="1" t="n">
         <v>0.07817</v>
       </c>
     </row>
@@ -36739,9 +38293,12 @@
         <v>0.006363</v>
       </c>
       <c r="U518" s="1" t="n">
+        <v>0.006361</v>
+      </c>
+      <c r="V518" s="1" t="n">
         <v>0.006395</v>
       </c>
-      <c r="V518" s="1" t="n">
+      <c r="W518" s="1" t="n">
         <v>0.00635</v>
       </c>
     </row>
@@ -36809,9 +38366,12 @@
         <v>0.05759</v>
       </c>
       <c r="U519" s="1" t="n">
+        <v>0.05752</v>
+      </c>
+      <c r="V519" s="1" t="n">
         <v>0.05826</v>
       </c>
-      <c r="V519" s="1" t="n">
+      <c r="W519" s="1" t="n">
         <v>0.05746</v>
       </c>
     </row>
@@ -36879,10 +38439,13 @@
         <v>0.10376</v>
       </c>
       <c r="U520" s="1" t="n">
+        <v>0.10333</v>
+      </c>
+      <c r="V520" s="1" t="n">
         <v>0.10531</v>
       </c>
-      <c r="V520" s="1" t="n">
-        <v>0.10341</v>
+      <c r="W520" s="1" t="n">
+        <v>0.10333</v>
       </c>
     </row>
     <row r="521">
@@ -36949,9 +38512,12 @@
         <v>0.01791</v>
       </c>
       <c r="U521" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="V521" s="1" t="n">
         <v>0.01799</v>
       </c>
-      <c r="V521" s="1" t="n">
+      <c r="W521" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -37019,9 +38585,12 @@
         <v>0.01612</v>
       </c>
       <c r="U522" s="1" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="V522" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="V522" s="1" t="n">
+      <c r="W522" s="1" t="n">
         <v>0.01602</v>
       </c>
     </row>
@@ -37089,9 +38658,12 @@
         <v>0.01077</v>
       </c>
       <c r="U523" s="1" t="n">
+        <v>0.01077</v>
+      </c>
+      <c r="V523" s="1" t="n">
         <v>0.01093</v>
       </c>
-      <c r="V523" s="1" t="n">
+      <c r="W523" s="1" t="n">
         <v>0.01077</v>
       </c>
     </row>
@@ -37159,9 +38731,12 @@
         <v>0.007331</v>
       </c>
       <c r="U524" s="1" t="n">
+        <v>0.00733</v>
+      </c>
+      <c r="V524" s="1" t="n">
         <v>0.007331</v>
       </c>
-      <c r="V524" s="1" t="n">
+      <c r="W524" s="1" t="n">
         <v>0.006771</v>
       </c>
     </row>
@@ -37229,9 +38804,12 @@
         <v>0.005794</v>
       </c>
       <c r="U525" s="1" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="V525" s="1" t="n">
         <v>0.005998</v>
       </c>
-      <c r="V525" s="1" t="n">
+      <c r="W525" s="1" t="n">
         <v>0.005794</v>
       </c>
     </row>
@@ -37299,9 +38877,12 @@
         <v>0.001441</v>
       </c>
       <c r="U526" s="1" t="n">
+        <v>0.001439</v>
+      </c>
+      <c r="V526" s="1" t="n">
         <v>0.001449</v>
       </c>
-      <c r="V526" s="1" t="n">
+      <c r="W526" s="1" t="n">
         <v>0.001434</v>
       </c>
     </row>
@@ -37372,6 +38953,9 @@
         <v>0.375</v>
       </c>
       <c r="V527" s="1" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="W527" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -37439,9 +39023,12 @@
         <v>0.005239</v>
       </c>
       <c r="U528" s="1" t="n">
+        <v>0.005196</v>
+      </c>
+      <c r="V528" s="1" t="n">
         <v>0.00548</v>
       </c>
-      <c r="V528" s="1" t="n">
+      <c r="W528" s="1" t="n">
         <v>0.005138</v>
       </c>
     </row>
@@ -37509,9 +39096,12 @@
         <v>2.945</v>
       </c>
       <c r="U529" s="1" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="V529" s="1" t="n">
         <v>2.961</v>
       </c>
-      <c r="V529" s="1" t="n">
+      <c r="W529" s="1" t="n">
         <v>2.917</v>
       </c>
     </row>
@@ -37579,10 +39169,13 @@
         <v>0.1527</v>
       </c>
       <c r="U530" s="1" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="V530" s="1" t="n">
         <v>0.1565</v>
       </c>
-      <c r="V530" s="1" t="n">
-        <v>0.1526</v>
+      <c r="W530" s="1" t="n">
+        <v>0.1522</v>
       </c>
     </row>
     <row r="531">
@@ -37652,6 +39245,9 @@
         <v>2584</v>
       </c>
       <c r="V531" s="1" t="n">
+        <v>2584</v>
+      </c>
+      <c r="W531" s="1" t="n">
         <v>2531</v>
       </c>
     </row>
@@ -37719,9 +39315,12 @@
         <v>0.03904</v>
       </c>
       <c r="U532" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="V532" s="1" t="n">
         <v>0.0393</v>
       </c>
-      <c r="V532" s="1" t="n">
+      <c r="W532" s="1" t="n">
         <v>0.03893</v>
       </c>
     </row>
@@ -37789,9 +39388,12 @@
         <v>0.02191</v>
       </c>
       <c r="U533" s="1" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="V533" s="1" t="n">
         <v>0.02191</v>
       </c>
-      <c r="V533" s="1" t="n">
+      <c r="W533" s="1" t="n">
         <v>0.02156</v>
       </c>
     </row>
@@ -37859,9 +39461,12 @@
         <v>0.07307</v>
       </c>
       <c r="U534" s="1" t="n">
+        <v>0.07287</v>
+      </c>
+      <c r="V534" s="1" t="n">
         <v>0.07374</v>
       </c>
-      <c r="V534" s="1" t="n">
+      <c r="W534" s="1" t="n">
         <v>0.07267</v>
       </c>
     </row>
@@ -37929,9 +39534,12 @@
         <v>0.007865</v>
       </c>
       <c r="U535" s="1" t="n">
+        <v>0.007839</v>
+      </c>
+      <c r="V535" s="1" t="n">
         <v>0.008029</v>
       </c>
-      <c r="V535" s="1" t="n">
+      <c r="W535" s="1" t="n">
         <v>0.007766</v>
       </c>
     </row>
@@ -37999,9 +39607,12 @@
         <v>0.04997</v>
       </c>
       <c r="U536" s="1" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="V536" s="1" t="n">
         <v>0.0504</v>
       </c>
-      <c r="V536" s="1" t="n">
+      <c r="W536" s="1" t="n">
         <v>0.04985</v>
       </c>
     </row>
@@ -38069,9 +39680,12 @@
         <v>0.004</v>
       </c>
       <c r="U537" s="1" t="n">
+        <v>0.00401</v>
+      </c>
+      <c r="V537" s="1" t="n">
         <v>0.00408</v>
       </c>
-      <c r="V537" s="1" t="n">
+      <c r="W537" s="1" t="n">
         <v>0.00397</v>
       </c>
     </row>
@@ -38139,9 +39753,12 @@
         <v>0.08261</v>
       </c>
       <c r="U538" s="1" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="V538" s="1" t="n">
         <v>0.0832</v>
       </c>
-      <c r="V538" s="1" t="n">
+      <c r="W538" s="1" t="n">
         <v>0.08252</v>
       </c>
     </row>
@@ -38209,9 +39826,12 @@
         <v>0.02473</v>
       </c>
       <c r="U539" s="1" t="n">
+        <v>0.02476</v>
+      </c>
+      <c r="V539" s="1" t="n">
         <v>0.02505</v>
       </c>
-      <c r="V539" s="1" t="n">
+      <c r="W539" s="1" t="n">
         <v>0.02473</v>
       </c>
     </row>
@@ -38279,9 +39899,12 @@
         <v>0.08452</v>
       </c>
       <c r="U540" s="1" t="n">
+        <v>0.08427999999999999</v>
+      </c>
+      <c r="V540" s="1" t="n">
         <v>0.08498</v>
       </c>
-      <c r="V540" s="1" t="n">
+      <c r="W540" s="1" t="n">
         <v>0.08406</v>
       </c>
     </row>
@@ -38349,9 +39972,12 @@
         <v>0.01888</v>
       </c>
       <c r="U541" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="V541" s="1" t="n">
         <v>0.01901</v>
       </c>
-      <c r="V541" s="1" t="n">
+      <c r="W541" s="1" t="n">
         <v>0.0188</v>
       </c>
     </row>
@@ -38419,9 +40045,12 @@
         <v>0.0168</v>
       </c>
       <c r="U542" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="V542" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="V542" s="1" t="n">
+      <c r="W542" s="1" t="n">
         <v>0.01679</v>
       </c>
     </row>
@@ -38489,9 +40118,12 @@
         <v>0.1047</v>
       </c>
       <c r="U543" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="V543" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="V543" s="1" t="n">
+      <c r="W543" s="1" t="n">
         <v>0.1044</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-15.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X543"/>
+  <dimension ref="A1:Y543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -441,8 +441,9 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,10 +559,15 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>price_05:30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -637,9 +643,12 @@
         <v>70627.3</v>
       </c>
       <c r="W2" s="1" t="n">
+        <v>70656.10000000001</v>
+      </c>
+      <c r="X2" s="1" t="n">
         <v>70796.5</v>
       </c>
-      <c r="X2" s="1" t="n">
+      <c r="Y2" s="1" t="n">
         <v>70544.10000000001</v>
       </c>
     </row>
@@ -713,9 +722,12 @@
         <v>2081.89</v>
       </c>
       <c r="W3" s="1" t="n">
+        <v>2082.15</v>
+      </c>
+      <c r="X3" s="1" t="n">
         <v>2084.79</v>
       </c>
-      <c r="X3" s="1" t="n">
+      <c r="Y3" s="1" t="n">
         <v>2072.31</v>
       </c>
     </row>
@@ -789,9 +801,12 @@
         <v>86.86</v>
       </c>
       <c r="W4" s="1" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="X4" s="1" t="n">
         <v>87.05</v>
       </c>
-      <c r="X4" s="1" t="n">
+      <c r="Y4" s="1" t="n">
         <v>86.72</v>
       </c>
     </row>
@@ -865,9 +880,12 @@
         <v>3.969</v>
       </c>
       <c r="W5" s="1" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="X5" s="1" t="n">
         <v>4.122</v>
       </c>
-      <c r="X5" s="1" t="n">
+      <c r="Y5" s="1" t="n">
         <v>3.967</v>
       </c>
     </row>
@@ -941,9 +959,12 @@
         <v>0.09467</v>
       </c>
       <c r="W6" s="1" t="n">
+        <v>0.09475</v>
+      </c>
+      <c r="X6" s="1" t="n">
         <v>0.09528</v>
       </c>
-      <c r="X6" s="1" t="n">
+      <c r="Y6" s="1" t="n">
         <v>0.09444</v>
       </c>
     </row>
@@ -1017,9 +1038,12 @@
         <v>1.3911</v>
       </c>
       <c r="W7" s="1" t="n">
+        <v>1.3916</v>
+      </c>
+      <c r="X7" s="1" t="n">
         <v>1.3929</v>
       </c>
-      <c r="X7" s="1" t="n">
+      <c r="Y7" s="1" t="n">
         <v>1.388</v>
       </c>
     </row>
@@ -1093,9 +1117,12 @@
         <v>22.193</v>
       </c>
       <c r="W8" s="1" t="n">
+        <v>22.046</v>
+      </c>
+      <c r="X8" s="1" t="n">
         <v>22.772</v>
       </c>
-      <c r="X8" s="1" t="n">
+      <c r="Y8" s="1" t="n">
         <v>21.772</v>
       </c>
     </row>
@@ -1169,9 +1196,12 @@
         <v>0.002004</v>
       </c>
       <c r="W9" s="1" t="n">
+        <v>0.001987</v>
+      </c>
+      <c r="X9" s="1" t="n">
         <v>0.002194</v>
       </c>
-      <c r="X9" s="1" t="n">
+      <c r="Y9" s="1" t="n">
         <v>0.001951</v>
       </c>
     </row>
@@ -1245,9 +1275,12 @@
         <v>0.010003</v>
       </c>
       <c r="W10" s="1" t="n">
+        <v>0.009858</v>
+      </c>
+      <c r="X10" s="1" t="n">
         <v>0.01067</v>
       </c>
-      <c r="X10" s="1" t="n">
+      <c r="Y10" s="1" t="n">
         <v>0.009129</v>
       </c>
     </row>
@@ -1321,9 +1354,12 @@
         <v>0.14484</v>
       </c>
       <c r="W11" s="1" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="X11" s="1" t="n">
         <v>0.17111</v>
       </c>
-      <c r="X11" s="1" t="n">
+      <c r="Y11" s="1" t="n">
         <v>0.13631</v>
       </c>
     </row>
@@ -1397,10 +1433,13 @@
         <v>0.010936</v>
       </c>
       <c r="W12" s="1" t="n">
+        <v>0.010924</v>
+      </c>
+      <c r="X12" s="1" t="n">
         <v>0.012009</v>
       </c>
-      <c r="X12" s="1" t="n">
-        <v>0.010936</v>
+      <c r="Y12" s="1" t="n">
+        <v>0.010924</v>
       </c>
     </row>
     <row r="13">
@@ -1473,9 +1512,12 @@
         <v>37.884</v>
       </c>
       <c r="W13" s="1" t="n">
+        <v>37.894</v>
+      </c>
+      <c r="X13" s="1" t="n">
         <v>38.402</v>
       </c>
-      <c r="X13" s="1" t="n">
+      <c r="Y13" s="1" t="n">
         <v>37.748</v>
       </c>
     </row>
@@ -1549,9 +1591,12 @@
         <v>653.3099999999999</v>
       </c>
       <c r="W14" s="1" t="n">
+        <v>653.21</v>
+      </c>
+      <c r="X14" s="1" t="n">
         <v>654.13</v>
       </c>
-      <c r="X14" s="1" t="n">
+      <c r="Y14" s="1" t="n">
         <v>652.41</v>
       </c>
     </row>
@@ -1625,9 +1670,12 @@
         <v>209.32</v>
       </c>
       <c r="W15" s="1" t="n">
+        <v>209.69</v>
+      </c>
+      <c r="X15" s="1" t="n">
         <v>210.26</v>
       </c>
-      <c r="X15" s="1" t="n">
+      <c r="Y15" s="1" t="n">
         <v>208.77</v>
       </c>
     </row>
@@ -1701,9 +1749,12 @@
         <v>0.0033181</v>
       </c>
       <c r="W16" s="1" t="n">
+        <v>0.0033217</v>
+      </c>
+      <c r="X16" s="1" t="n">
         <v>0.0033537</v>
       </c>
-      <c r="X16" s="1" t="n">
+      <c r="Y16" s="1" t="n">
         <v>0.0033084</v>
       </c>
     </row>
@@ -1777,9 +1828,12 @@
         <v>241.69</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>241.69</v>
+        <v>243.3</v>
       </c>
       <c r="X17" s="1" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="Y17" s="1" t="n">
         <v>234.47</v>
       </c>
     </row>
@@ -1853,9 +1907,12 @@
         <v>0.9872</v>
       </c>
       <c r="W18" s="1" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="X18" s="1" t="n">
         <v>0.9959</v>
       </c>
-      <c r="X18" s="1" t="n">
+      <c r="Y18" s="1" t="n">
         <v>0.9858</v>
       </c>
     </row>
@@ -1929,10 +1986,13 @@
         <v>0.9988</v>
       </c>
       <c r="W19" s="1" t="n">
+        <v>0.9968</v>
+      </c>
+      <c r="X19" s="1" t="n">
         <v>1.0722</v>
       </c>
-      <c r="X19" s="1" t="n">
-        <v>0.9972</v>
+      <c r="Y19" s="1" t="n">
+        <v>0.9968</v>
       </c>
     </row>
     <row r="20">
@@ -2005,9 +2065,12 @@
         <v>0.2588</v>
       </c>
       <c r="W20" s="1" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="X20" s="1" t="n">
         <v>0.2612</v>
       </c>
-      <c r="X20" s="1" t="n">
+      <c r="Y20" s="1" t="n">
         <v>0.2587</v>
       </c>
     </row>
@@ -2081,10 +2144,13 @@
         <v>0.5868100000000001</v>
       </c>
       <c r="W21" s="1" t="n">
+        <v>0.58568</v>
+      </c>
+      <c r="X21" s="1" t="n">
         <v>0.60985</v>
       </c>
-      <c r="X21" s="1" t="n">
-        <v>0.5868100000000001</v>
+      <c r="Y21" s="1" t="n">
+        <v>0.58568</v>
       </c>
     </row>
     <row r="22">
@@ -2157,9 +2223,12 @@
         <v>9.026999999999999</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>9.042</v>
+        <v>9.042999999999999</v>
       </c>
       <c r="X22" s="1" t="n">
+        <v>9.042999999999999</v>
+      </c>
+      <c r="Y22" s="1" t="n">
         <v>8.991</v>
       </c>
     </row>
@@ -2233,9 +2302,12 @@
         <v>0.02376</v>
       </c>
       <c r="W23" s="1" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="X23" s="1" t="n">
         <v>0.02441</v>
       </c>
-      <c r="X23" s="1" t="n">
+      <c r="Y23" s="1" t="n">
         <v>0.02359</v>
       </c>
     </row>
@@ -2309,9 +2381,12 @@
         <v>9.574999999999999</v>
       </c>
       <c r="W24" s="1" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="X24" s="1" t="n">
         <v>9.599</v>
       </c>
-      <c r="X24" s="1" t="n">
+      <c r="Y24" s="1" t="n">
         <v>9.553000000000001</v>
       </c>
     </row>
@@ -2385,9 +2460,12 @@
         <v>1.216</v>
       </c>
       <c r="W25" s="1" t="n">
+        <v>1.218</v>
+      </c>
+      <c r="X25" s="1" t="n">
         <v>1.24</v>
       </c>
-      <c r="X25" s="1" t="n">
+      <c r="Y25" s="1" t="n">
         <v>1.216</v>
       </c>
     </row>
@@ -2461,9 +2539,12 @@
         <v>0.07282</v>
       </c>
       <c r="W26" s="1" t="n">
+        <v>0.07215000000000001</v>
+      </c>
+      <c r="X26" s="1" t="n">
         <v>0.07317</v>
       </c>
-      <c r="X26" s="1" t="n">
+      <c r="Y26" s="1" t="n">
         <v>0.07023</v>
       </c>
     </row>
@@ -2537,9 +2618,12 @@
         <v>1.407</v>
       </c>
       <c r="W27" s="1" t="n">
+        <v>1.409</v>
+      </c>
+      <c r="X27" s="1" t="n">
         <v>1.43</v>
       </c>
-      <c r="X27" s="1" t="n">
+      <c r="Y27" s="1" t="n">
         <v>1.405</v>
       </c>
     </row>
@@ -2613,9 +2697,12 @@
         <v>1.304</v>
       </c>
       <c r="W28" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="X28" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="X28" s="1" t="n">
+      <c r="Y28" s="1" t="n">
         <v>1.302</v>
       </c>
     </row>
@@ -2689,9 +2776,12 @@
         <v>463.35</v>
       </c>
       <c r="W29" s="1" t="n">
+        <v>463.75</v>
+      </c>
+      <c r="X29" s="1" t="n">
         <v>464.27</v>
       </c>
-      <c r="X29" s="1" t="n">
+      <c r="Y29" s="1" t="n">
         <v>461.1</v>
       </c>
     </row>
@@ -2765,9 +2855,12 @@
         <v>1.2856</v>
       </c>
       <c r="W30" s="1" t="n">
+        <v>1.2906</v>
+      </c>
+      <c r="X30" s="1" t="n">
         <v>1.3093</v>
       </c>
-      <c r="X30" s="1" t="n">
+      <c r="Y30" s="1" t="n">
         <v>1.2764</v>
       </c>
     </row>
@@ -2841,9 +2934,12 @@
         <v>5020.62</v>
       </c>
       <c r="W31" s="1" t="n">
+        <v>5020.26</v>
+      </c>
+      <c r="X31" s="1" t="n">
         <v>5025.5</v>
       </c>
-      <c r="X31" s="1" t="n">
+      <c r="Y31" s="1" t="n">
         <v>5019.32</v>
       </c>
     </row>
@@ -2917,9 +3013,12 @@
         <v>0.878</v>
       </c>
       <c r="W32" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="X32" s="1" t="n">
         <v>0.903</v>
       </c>
-      <c r="X32" s="1" t="n">
+      <c r="Y32" s="1" t="n">
         <v>0.867</v>
       </c>
     </row>
@@ -2993,10 +3092,13 @@
         <v>0.001968</v>
       </c>
       <c r="W33" s="1" t="n">
+        <v>0.001965</v>
+      </c>
+      <c r="X33" s="1" t="n">
         <v>0.001983</v>
       </c>
-      <c r="X33" s="1" t="n">
-        <v>0.001966</v>
+      <c r="Y33" s="1" t="n">
+        <v>0.001965</v>
       </c>
     </row>
     <row r="34">
@@ -3069,9 +3171,12 @@
         <v>0.1729</v>
       </c>
       <c r="W34" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="X34" s="1" t="n">
         <v>0.17484</v>
       </c>
-      <c r="X34" s="1" t="n">
+      <c r="Y34" s="1" t="n">
         <v>0.16527</v>
       </c>
     </row>
@@ -3145,9 +3250,12 @@
         <v>0.297</v>
       </c>
       <c r="W35" s="1" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="X35" s="1" t="n">
         <v>0.29866</v>
       </c>
-      <c r="X35" s="1" t="n">
+      <c r="Y35" s="1" t="n">
         <v>0.29656</v>
       </c>
     </row>
@@ -3221,9 +3329,12 @@
         <v>1.791</v>
       </c>
       <c r="W36" s="1" t="n">
+        <v>1.787</v>
+      </c>
+      <c r="X36" s="1" t="n">
         <v>1.798</v>
       </c>
-      <c r="X36" s="1" t="n">
+      <c r="Y36" s="1" t="n">
         <v>1.777</v>
       </c>
     </row>
@@ -3297,9 +3408,12 @@
         <v>110.24</v>
       </c>
       <c r="W37" s="1" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="X37" s="1" t="n">
         <v>110.86</v>
       </c>
-      <c r="X37" s="1" t="n">
+      <c r="Y37" s="1" t="n">
         <v>110.17</v>
       </c>
     </row>
@@ -3373,9 +3487,12 @@
         <v>0.22094</v>
       </c>
       <c r="W38" s="1" t="n">
+        <v>0.21981</v>
+      </c>
+      <c r="X38" s="1" t="n">
         <v>0.22687</v>
       </c>
-      <c r="X38" s="1" t="n">
+      <c r="Y38" s="1" t="n">
         <v>0.21964</v>
       </c>
     </row>
@@ -3449,9 +3566,12 @@
         <v>0.1063</v>
       </c>
       <c r="W39" s="1" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="X39" s="1" t="n">
         <v>0.1083</v>
       </c>
-      <c r="X39" s="1" t="n">
+      <c r="Y39" s="1" t="n">
         <v>0.1063</v>
       </c>
     </row>
@@ -3525,9 +3645,12 @@
         <v>0.37236</v>
       </c>
       <c r="W40" s="1" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="X40" s="1" t="n">
         <v>0.37507</v>
       </c>
-      <c r="X40" s="1" t="n">
+      <c r="Y40" s="1" t="n">
         <v>0.3694</v>
       </c>
     </row>
@@ -3601,9 +3724,12 @@
         <v>54.54</v>
       </c>
       <c r="W41" s="1" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="X41" s="1" t="n">
         <v>54.72</v>
       </c>
-      <c r="X41" s="1" t="n">
+      <c r="Y41" s="1" t="n">
         <v>54.45</v>
       </c>
     </row>
@@ -3677,9 +3803,12 @@
         <v>0.001054</v>
       </c>
       <c r="W42" s="1" t="n">
+        <v>0.0010547</v>
+      </c>
+      <c r="X42" s="1" t="n">
         <v>0.0010838</v>
       </c>
-      <c r="X42" s="1" t="n">
+      <c r="Y42" s="1" t="n">
         <v>0.001053</v>
       </c>
     </row>
@@ -3753,9 +3882,12 @@
         <v>6.475</v>
       </c>
       <c r="W43" s="1" t="n">
+        <v>6.477</v>
+      </c>
+      <c r="X43" s="1" t="n">
         <v>6.588</v>
       </c>
-      <c r="X43" s="1" t="n">
+      <c r="Y43" s="1" t="n">
         <v>6.41</v>
       </c>
     </row>
@@ -3829,9 +3961,12 @@
         <v>0.6246</v>
       </c>
       <c r="W44" s="1" t="n">
+        <v>0.6274999999999999</v>
+      </c>
+      <c r="X44" s="1" t="n">
         <v>0.6451</v>
       </c>
-      <c r="X44" s="1" t="n">
+      <c r="Y44" s="1" t="n">
         <v>0.6213</v>
       </c>
     </row>
@@ -3905,9 +4040,12 @@
         <v>0.3518</v>
       </c>
       <c r="W45" s="1" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="X45" s="1" t="n">
         <v>0.3557</v>
       </c>
-      <c r="X45" s="1" t="n">
+      <c r="Y45" s="1" t="n">
         <v>0.3512</v>
       </c>
     </row>
@@ -3981,9 +4119,12 @@
         <v>0.03286</v>
       </c>
       <c r="W46" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="X46" s="1" t="n">
         <v>0.03321</v>
       </c>
-      <c r="X46" s="1" t="n">
+      <c r="Y46" s="1" t="n">
         <v>0.03228</v>
       </c>
     </row>
@@ -4057,10 +4198,13 @@
         <v>0.06844</v>
       </c>
       <c r="W47" s="1" t="n">
+        <v>0.06813</v>
+      </c>
+      <c r="X47" s="1" t="n">
         <v>0.07371</v>
       </c>
-      <c r="X47" s="1" t="n">
-        <v>0.06844</v>
+      <c r="Y47" s="1" t="n">
+        <v>0.06813</v>
       </c>
     </row>
     <row r="48">
@@ -4133,9 +4277,12 @@
         <v>0.7073</v>
       </c>
       <c r="W48" s="1" t="n">
+        <v>0.7087</v>
+      </c>
+      <c r="X48" s="1" t="n">
         <v>0.7112000000000001</v>
       </c>
-      <c r="X48" s="1" t="n">
+      <c r="Y48" s="1" t="n">
         <v>0.7008</v>
       </c>
     </row>
@@ -4209,9 +4356,12 @@
         <v>0.004259</v>
       </c>
       <c r="W49" s="1" t="n">
+        <v>0.004283</v>
+      </c>
+      <c r="X49" s="1" t="n">
         <v>0.00463</v>
       </c>
-      <c r="X49" s="1" t="n">
+      <c r="Y49" s="1" t="n">
         <v>0.004224</v>
       </c>
     </row>
@@ -4285,9 +4435,12 @@
         <v>0.1032</v>
       </c>
       <c r="W50" s="1" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="X50" s="1" t="n">
         <v>0.1049</v>
       </c>
-      <c r="X50" s="1" t="n">
+      <c r="Y50" s="1" t="n">
         <v>0.1031</v>
       </c>
     </row>
@@ -4361,10 +4514,13 @@
         <v>0.04019</v>
       </c>
       <c r="W51" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="X51" s="1" t="n">
         <v>0.04073</v>
       </c>
-      <c r="X51" s="1" t="n">
-        <v>0.04019</v>
+      <c r="Y51" s="1" t="n">
+        <v>0.04015</v>
       </c>
     </row>
     <row r="52">
@@ -4437,9 +4593,12 @@
         <v>0.1641</v>
       </c>
       <c r="W52" s="1" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="X52" s="1" t="n">
         <v>0.1688</v>
       </c>
-      <c r="X52" s="1" t="n">
+      <c r="Y52" s="1" t="n">
         <v>0.1641</v>
       </c>
     </row>
@@ -4513,9 +4672,12 @@
         <v>0.01953</v>
       </c>
       <c r="W53" s="1" t="n">
+        <v>0.01938</v>
+      </c>
+      <c r="X53" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="X53" s="1" t="n">
+      <c r="Y53" s="1" t="n">
         <v>0.01922</v>
       </c>
     </row>
@@ -4589,10 +4751,13 @@
         <v>0.007169</v>
       </c>
       <c r="W54" s="1" t="n">
+        <v>0.007168</v>
+      </c>
+      <c r="X54" s="1" t="n">
         <v>0.007261</v>
       </c>
-      <c r="X54" s="1" t="n">
-        <v>0.007169</v>
+      <c r="Y54" s="1" t="n">
+        <v>0.007168</v>
       </c>
     </row>
     <row r="55">
@@ -4665,9 +4830,12 @@
         <v>3.911</v>
       </c>
       <c r="W55" s="1" t="n">
+        <v>3.912</v>
+      </c>
+      <c r="X55" s="1" t="n">
         <v>3.933</v>
       </c>
-      <c r="X55" s="1" t="n">
+      <c r="Y55" s="1" t="n">
         <v>3.909</v>
       </c>
     </row>
@@ -4741,10 +4909,13 @@
         <v>0.016829</v>
       </c>
       <c r="W56" s="1" t="n">
+        <v>0.016778</v>
+      </c>
+      <c r="X56" s="1" t="n">
         <v>0.017264</v>
       </c>
-      <c r="X56" s="1" t="n">
-        <v>0.016808</v>
+      <c r="Y56" s="1" t="n">
+        <v>0.016778</v>
       </c>
     </row>
     <row r="57">
@@ -4817,9 +4988,12 @@
         <v>0.1085</v>
       </c>
       <c r="W57" s="1" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="X57" s="1" t="n">
         <v>0.1122</v>
       </c>
-      <c r="X57" s="1" t="n">
+      <c r="Y57" s="1" t="n">
         <v>0.1075</v>
       </c>
     </row>
@@ -4893,9 +5067,12 @@
         <v>2.646</v>
       </c>
       <c r="W58" s="1" t="n">
+        <v>2.649</v>
+      </c>
+      <c r="X58" s="1" t="n">
         <v>2.664</v>
       </c>
-      <c r="X58" s="1" t="n">
+      <c r="Y58" s="1" t="n">
         <v>2.639</v>
       </c>
     </row>
@@ -4969,10 +5146,13 @@
         <v>0.1579</v>
       </c>
       <c r="W59" s="1" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="X59" s="1" t="n">
         <v>0.1604</v>
       </c>
-      <c r="X59" s="1" t="n">
-        <v>0.1579</v>
+      <c r="Y59" s="1" t="n">
+        <v>0.157</v>
       </c>
     </row>
     <row r="60">
@@ -5045,9 +5225,12 @@
         <v>0.005836</v>
       </c>
       <c r="W60" s="1" t="n">
+        <v>0.005837</v>
+      </c>
+      <c r="X60" s="1" t="n">
         <v>0.00593</v>
       </c>
-      <c r="X60" s="1" t="n">
+      <c r="Y60" s="1" t="n">
         <v>0.005834</v>
       </c>
     </row>
@@ -5121,9 +5304,12 @@
         <v>0.0917</v>
       </c>
       <c r="W61" s="1" t="n">
+        <v>0.09182</v>
+      </c>
+      <c r="X61" s="1" t="n">
         <v>0.09215</v>
       </c>
-      <c r="X61" s="1" t="n">
+      <c r="Y61" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
     </row>
@@ -5197,9 +5383,12 @@
         <v>0.9106</v>
       </c>
       <c r="W62" s="1" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="X62" s="1" t="n">
         <v>0.9154</v>
       </c>
-      <c r="X62" s="1" t="n">
+      <c r="Y62" s="1" t="n">
         <v>0.9101</v>
       </c>
     </row>
@@ -5273,9 +5462,12 @@
         <v>0.778</v>
       </c>
       <c r="W63" s="1" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="X63" s="1" t="n">
         <v>0.782</v>
       </c>
-      <c r="X63" s="1" t="n">
+      <c r="Y63" s="1" t="n">
         <v>0.774</v>
       </c>
     </row>
@@ -5349,9 +5541,12 @@
         <v>0.0461</v>
       </c>
       <c r="W64" s="1" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="X64" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="X64" s="1" t="n">
+      <c r="Y64" s="1" t="n">
         <v>0.04563</v>
       </c>
     </row>
@@ -5425,9 +5620,12 @@
         <v>355.29</v>
       </c>
       <c r="W65" s="1" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="X65" s="1" t="n">
         <v>358.18</v>
       </c>
-      <c r="X65" s="1" t="n">
+      <c r="Y65" s="1" t="n">
         <v>354.23</v>
       </c>
     </row>
@@ -5501,9 +5699,12 @@
         <v>0.12492</v>
       </c>
       <c r="W66" s="1" t="n">
+        <v>0.12469</v>
+      </c>
+      <c r="X66" s="1" t="n">
         <v>0.12814</v>
       </c>
-      <c r="X66" s="1" t="n">
+      <c r="Y66" s="1" t="n">
         <v>0.12358</v>
       </c>
     </row>
@@ -5577,9 +5778,12 @@
         <v>0.2302</v>
       </c>
       <c r="W67" s="1" t="n">
+        <v>0.2294</v>
+      </c>
+      <c r="X67" s="1" t="n">
         <v>0.2446</v>
       </c>
-      <c r="X67" s="1" t="n">
+      <c r="Y67" s="1" t="n">
         <v>0.2249</v>
       </c>
     </row>
@@ -5653,9 +5857,12 @@
         <v>0.00335</v>
       </c>
       <c r="W68" s="1" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="X68" s="1" t="n">
         <v>0.00343</v>
       </c>
-      <c r="X68" s="1" t="n">
+      <c r="Y68" s="1" t="n">
         <v>0.00335</v>
       </c>
     </row>
@@ -5729,9 +5936,12 @@
         <v>0.1741</v>
       </c>
       <c r="W69" s="1" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="X69" s="1" t="n">
         <v>0.1762</v>
       </c>
-      <c r="X69" s="1" t="n">
+      <c r="Y69" s="1" t="n">
         <v>0.1734</v>
       </c>
     </row>
@@ -5805,9 +6015,12 @@
         <v>0.16359</v>
       </c>
       <c r="W70" s="1" t="n">
+        <v>0.16365</v>
+      </c>
+      <c r="X70" s="1" t="n">
         <v>0.16506</v>
       </c>
-      <c r="X70" s="1" t="n">
+      <c r="Y70" s="1" t="n">
         <v>0.16358</v>
       </c>
     </row>
@@ -5881,9 +6094,12 @@
         <v>0.3563</v>
       </c>
       <c r="W71" s="1" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="X71" s="1" t="n">
         <v>0.3599</v>
       </c>
-      <c r="X71" s="1" t="n">
+      <c r="Y71" s="1" t="n">
         <v>0.3483</v>
       </c>
     </row>
@@ -5957,9 +6173,12 @@
         <v>0.7071</v>
       </c>
       <c r="W72" s="1" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="X72" s="1" t="n">
         <v>0.7106</v>
       </c>
-      <c r="X72" s="1" t="n">
+      <c r="Y72" s="1" t="n">
         <v>0.7043</v>
       </c>
     </row>
@@ -6033,9 +6252,12 @@
         <v>0.0086</v>
       </c>
       <c r="W73" s="1" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="X73" s="1" t="n">
         <v>0.00873</v>
       </c>
-      <c r="X73" s="1" t="n">
+      <c r="Y73" s="1" t="n">
         <v>0.008569999999999999</v>
       </c>
     </row>
@@ -6109,9 +6331,12 @@
         <v>0.00596</v>
       </c>
       <c r="W74" s="1" t="n">
+        <v>0.005969</v>
+      </c>
+      <c r="X74" s="1" t="n">
         <v>0.006018</v>
       </c>
-      <c r="X74" s="1" t="n">
+      <c r="Y74" s="1" t="n">
         <v>0.005958</v>
       </c>
     </row>
@@ -6188,6 +6413,9 @@
         <v>0.23</v>
       </c>
       <c r="X75" s="1" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Y75" s="1" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -6261,9 +6489,12 @@
         <v>0.3273</v>
       </c>
       <c r="W76" s="1" t="n">
-        <v>0.3287</v>
+        <v>0.33</v>
       </c>
       <c r="X76" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y76" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -6337,9 +6568,12 @@
         <v>0.0999</v>
       </c>
       <c r="W77" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="X77" s="1" t="n">
         <v>0.1007</v>
       </c>
-      <c r="X77" s="1" t="n">
+      <c r="Y77" s="1" t="n">
         <v>0.0999</v>
       </c>
     </row>
@@ -6413,9 +6647,12 @@
         <v>0.1224</v>
       </c>
       <c r="W78" s="1" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="X78" s="1" t="n">
         <v>0.1233</v>
       </c>
-      <c r="X78" s="1" t="n">
+      <c r="Y78" s="1" t="n">
         <v>0.1222</v>
       </c>
     </row>
@@ -6489,9 +6726,12 @@
         <v>0.07296999999999999</v>
       </c>
       <c r="W79" s="1" t="n">
+        <v>0.07353</v>
+      </c>
+      <c r="X79" s="1" t="n">
         <v>0.07549</v>
       </c>
-      <c r="X79" s="1" t="n">
+      <c r="Y79" s="1" t="n">
         <v>0.06873</v>
       </c>
     </row>
@@ -6565,9 +6805,12 @@
         <v>0.04605</v>
       </c>
       <c r="W80" s="1" t="n">
+        <v>0.04617</v>
+      </c>
+      <c r="X80" s="1" t="n">
         <v>0.04709</v>
       </c>
-      <c r="X80" s="1" t="n">
+      <c r="Y80" s="1" t="n">
         <v>0.04605</v>
       </c>
     </row>
@@ -6641,9 +6884,12 @@
         <v>0.000229</v>
       </c>
       <c r="W81" s="1" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="X81" s="1" t="n">
         <v>0.000242</v>
       </c>
-      <c r="X81" s="1" t="n">
+      <c r="Y81" s="1" t="n">
         <v>0.000228</v>
       </c>
     </row>
@@ -6717,10 +6963,13 @@
         <v>8.186</v>
       </c>
       <c r="W82" s="1" t="n">
+        <v>8.183999999999999</v>
+      </c>
+      <c r="X82" s="1" t="n">
         <v>8.244999999999999</v>
       </c>
-      <c r="X82" s="1" t="n">
-        <v>8.186</v>
+      <c r="Y82" s="1" t="n">
+        <v>8.183999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -6793,10 +7042,13 @@
         <v>0.0005731999999999999</v>
       </c>
       <c r="W83" s="1" t="n">
+        <v>0.0005668</v>
+      </c>
+      <c r="X83" s="1" t="n">
         <v>0.0006002</v>
       </c>
-      <c r="X83" s="1" t="n">
-        <v>0.0005713</v>
+      <c r="Y83" s="1" t="n">
+        <v>0.0005668</v>
       </c>
     </row>
     <row r="84">
@@ -6869,9 +7121,12 @@
         <v>0.4449</v>
       </c>
       <c r="W84" s="1" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="X84" s="1" t="n">
         <v>0.4505</v>
       </c>
-      <c r="X84" s="1" t="n">
+      <c r="Y84" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6945,9 +7200,12 @@
         <v>0.06234</v>
       </c>
       <c r="W85" s="1" t="n">
+        <v>0.06257</v>
+      </c>
+      <c r="X85" s="1" t="n">
         <v>0.06279</v>
       </c>
-      <c r="X85" s="1" t="n">
+      <c r="Y85" s="1" t="n">
         <v>0.0623</v>
       </c>
     </row>
@@ -7021,9 +7279,12 @@
         <v>0.05417</v>
       </c>
       <c r="W86" s="1" t="n">
+        <v>0.05411</v>
+      </c>
+      <c r="X86" s="1" t="n">
         <v>0.05509</v>
       </c>
-      <c r="X86" s="1" t="n">
+      <c r="Y86" s="1" t="n">
         <v>0.05403</v>
       </c>
     </row>
@@ -7097,9 +7358,12 @@
         <v>0.003362</v>
       </c>
       <c r="W87" s="1" t="n">
-        <v>0.003366</v>
+        <v>0.003368</v>
       </c>
       <c r="X87" s="1" t="n">
+        <v>0.003368</v>
+      </c>
+      <c r="Y87" s="1" t="n">
         <v>0.003329</v>
       </c>
     </row>
@@ -7173,9 +7437,12 @@
         <v>0.04992</v>
       </c>
       <c r="W88" s="1" t="n">
+        <v>0.04992</v>
+      </c>
+      <c r="X88" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="X88" s="1" t="n">
+      <c r="Y88" s="1" t="n">
         <v>0.04964</v>
       </c>
     </row>
@@ -7249,9 +7516,12 @@
         <v>0.03198</v>
       </c>
       <c r="W89" s="1" t="n">
+        <v>0.03178</v>
+      </c>
+      <c r="X89" s="1" t="n">
         <v>0.03198</v>
       </c>
-      <c r="X89" s="1" t="n">
+      <c r="Y89" s="1" t="n">
         <v>0.03031</v>
       </c>
     </row>
@@ -7325,9 +7595,12 @@
         <v>0.3436</v>
       </c>
       <c r="W90" s="1" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="X90" s="1" t="n">
         <v>0.3498</v>
       </c>
-      <c r="X90" s="1" t="n">
+      <c r="Y90" s="1" t="n">
         <v>0.3436</v>
       </c>
     </row>
@@ -7401,9 +7674,12 @@
         <v>0.0766</v>
       </c>
       <c r="W91" s="1" t="n">
+        <v>0.07764</v>
+      </c>
+      <c r="X91" s="1" t="n">
         <v>0.0835</v>
       </c>
-      <c r="X91" s="1" t="n">
+      <c r="Y91" s="1" t="n">
         <v>0.06074</v>
       </c>
     </row>
@@ -7477,9 +7753,12 @@
         <v>0.361</v>
       </c>
       <c r="W92" s="1" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="X92" s="1" t="n">
         <v>0.361</v>
       </c>
-      <c r="X92" s="1" t="n">
+      <c r="Y92" s="1" t="n">
         <v>0.3421</v>
       </c>
     </row>
@@ -7553,9 +7832,12 @@
         <v>1.9759</v>
       </c>
       <c r="W93" s="1" t="n">
+        <v>1.9782</v>
+      </c>
+      <c r="X93" s="1" t="n">
         <v>1.9816</v>
       </c>
-      <c r="X93" s="1" t="n">
+      <c r="Y93" s="1" t="n">
         <v>1.966</v>
       </c>
     </row>
@@ -7629,9 +7911,12 @@
         <v>0.2584</v>
       </c>
       <c r="W94" s="1" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="X94" s="1" t="n">
         <v>0.2599</v>
       </c>
-      <c r="X94" s="1" t="n">
+      <c r="Y94" s="1" t="n">
         <v>0.2581</v>
       </c>
     </row>
@@ -7705,9 +7990,12 @@
         <v>0.04518</v>
       </c>
       <c r="W95" s="1" t="n">
+        <v>0.04543</v>
+      </c>
+      <c r="X95" s="1" t="n">
         <v>0.04722</v>
       </c>
-      <c r="X95" s="1" t="n">
+      <c r="Y95" s="1" t="n">
         <v>0.04483</v>
       </c>
     </row>
@@ -7781,9 +8069,12 @@
         <v>0.006287</v>
       </c>
       <c r="W96" s="1" t="n">
+        <v>0.006215</v>
+      </c>
+      <c r="X96" s="1" t="n">
         <v>0.006343</v>
       </c>
-      <c r="X96" s="1" t="n">
+      <c r="Y96" s="1" t="n">
         <v>0.005831</v>
       </c>
     </row>
@@ -7857,9 +8148,12 @@
         <v>0.001708</v>
       </c>
       <c r="W97" s="1" t="n">
+        <v>0.001714</v>
+      </c>
+      <c r="X97" s="1" t="n">
         <v>0.001748</v>
       </c>
-      <c r="X97" s="1" t="n">
+      <c r="Y97" s="1" t="n">
         <v>0.001706</v>
       </c>
     </row>
@@ -7933,9 +8227,12 @@
         <v>5.203</v>
       </c>
       <c r="W98" s="1" t="n">
+        <v>5.204</v>
+      </c>
+      <c r="X98" s="1" t="n">
         <v>5.304</v>
       </c>
-      <c r="X98" s="1" t="n">
+      <c r="Y98" s="1" t="n">
         <v>5.179</v>
       </c>
     </row>
@@ -8009,9 +8306,12 @@
         <v>0.01501</v>
       </c>
       <c r="W99" s="1" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="X99" s="1" t="n">
         <v>0.0153</v>
       </c>
-      <c r="X99" s="1" t="n">
+      <c r="Y99" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -8085,9 +8385,12 @@
         <v>0.551</v>
       </c>
       <c r="W100" s="1" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="X100" s="1" t="n">
         <v>0.5545</v>
       </c>
-      <c r="X100" s="1" t="n">
+      <c r="Y100" s="1" t="n">
         <v>0.5508</v>
       </c>
     </row>
@@ -8161,9 +8464,12 @@
         <v>0.0898</v>
       </c>
       <c r="W101" s="1" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="X101" s="1" t="n">
         <v>0.09130000000000001</v>
       </c>
-      <c r="X101" s="1" t="n">
+      <c r="Y101" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -8237,9 +8543,12 @@
         <v>32.25</v>
       </c>
       <c r="W102" s="1" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="X102" s="1" t="n">
         <v>32.59</v>
       </c>
-      <c r="X102" s="1" t="n">
+      <c r="Y102" s="1" t="n">
         <v>32.25</v>
       </c>
     </row>
@@ -8313,9 +8622,12 @@
         <v>0.03211</v>
       </c>
       <c r="W103" s="1" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="X103" s="1" t="n">
         <v>0.03258</v>
       </c>
-      <c r="X103" s="1" t="n">
+      <c r="Y103" s="1" t="n">
         <v>0.03147</v>
       </c>
     </row>
@@ -8389,9 +8701,12 @@
         <v>0.06548</v>
       </c>
       <c r="W104" s="1" t="n">
+        <v>0.06548</v>
+      </c>
+      <c r="X104" s="1" t="n">
         <v>0.06614</v>
       </c>
-      <c r="X104" s="1" t="n">
+      <c r="Y104" s="1" t="n">
         <v>0.06548</v>
       </c>
     </row>
@@ -8465,9 +8780,12 @@
         <v>1.3002</v>
       </c>
       <c r="W105" s="1" t="n">
+        <v>1.2999</v>
+      </c>
+      <c r="X105" s="1" t="n">
         <v>1.3049</v>
       </c>
-      <c r="X105" s="1" t="n">
+      <c r="Y105" s="1" t="n">
         <v>1.2981</v>
       </c>
     </row>
@@ -8541,9 +8859,12 @@
         <v>0.119</v>
       </c>
       <c r="W106" s="1" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="X106" s="1" t="n">
         <v>0.1223</v>
       </c>
-      <c r="X106" s="1" t="n">
+      <c r="Y106" s="1" t="n">
         <v>0.1183</v>
       </c>
     </row>
@@ -8620,6 +8941,9 @@
         <v>0.121</v>
       </c>
       <c r="X107" s="1" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="Y107" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -8693,10 +9017,13 @@
         <v>0.09569</v>
       </c>
       <c r="W108" s="1" t="n">
+        <v>0.09566</v>
+      </c>
+      <c r="X108" s="1" t="n">
         <v>0.09616</v>
       </c>
-      <c r="X108" s="1" t="n">
-        <v>0.09569</v>
+      <c r="Y108" s="1" t="n">
+        <v>0.09566</v>
       </c>
     </row>
     <row r="109">
@@ -8769,9 +9096,12 @@
         <v>0.13988</v>
       </c>
       <c r="W109" s="1" t="n">
+        <v>0.13948</v>
+      </c>
+      <c r="X109" s="1" t="n">
         <v>0.14276</v>
       </c>
-      <c r="X109" s="1" t="n">
+      <c r="Y109" s="1" t="n">
         <v>0.13782</v>
       </c>
     </row>
@@ -8845,9 +9175,12 @@
         <v>5.552</v>
       </c>
       <c r="W110" s="1" t="n">
+        <v>5.561</v>
+      </c>
+      <c r="X110" s="1" t="n">
         <v>5.578</v>
       </c>
-      <c r="X110" s="1" t="n">
+      <c r="Y110" s="1" t="n">
         <v>5.546</v>
       </c>
     </row>
@@ -8921,9 +9254,12 @@
         <v>1.093</v>
       </c>
       <c r="W111" s="1" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="X111" s="1" t="n">
         <v>1.109</v>
       </c>
-      <c r="X111" s="1" t="n">
+      <c r="Y111" s="1" t="n">
         <v>1.082</v>
       </c>
     </row>
@@ -8997,9 +9333,12 @@
         <v>0.028712</v>
       </c>
       <c r="W112" s="1" t="n">
+        <v>0.028741</v>
+      </c>
+      <c r="X112" s="1" t="n">
         <v>0.029743</v>
       </c>
-      <c r="X112" s="1" t="n">
+      <c r="Y112" s="1" t="n">
         <v>0.028712</v>
       </c>
     </row>
@@ -9073,9 +9412,12 @@
         <v>1.859</v>
       </c>
       <c r="W113" s="1" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="X113" s="1" t="n">
         <v>1.886</v>
       </c>
-      <c r="X113" s="1" t="n">
+      <c r="Y113" s="1" t="n">
         <v>1.859</v>
       </c>
     </row>
@@ -9149,10 +9491,13 @@
         <v>0.05876</v>
       </c>
       <c r="W114" s="1" t="n">
+        <v>0.0584</v>
+      </c>
+      <c r="X114" s="1" t="n">
         <v>0.06108</v>
       </c>
-      <c r="X114" s="1" t="n">
-        <v>0.05848</v>
+      <c r="Y114" s="1" t="n">
+        <v>0.0584</v>
       </c>
     </row>
     <row r="115">
@@ -9225,10 +9570,13 @@
         <v>0.12727</v>
       </c>
       <c r="W115" s="1" t="n">
+        <v>0.12718</v>
+      </c>
+      <c r="X115" s="1" t="n">
         <v>0.12981</v>
       </c>
-      <c r="X115" s="1" t="n">
-        <v>0.12727</v>
+      <c r="Y115" s="1" t="n">
+        <v>0.12718</v>
       </c>
     </row>
     <row r="116">
@@ -9301,9 +9649,12 @@
         <v>1.0937</v>
       </c>
       <c r="W116" s="1" t="n">
+        <v>1.0951</v>
+      </c>
+      <c r="X116" s="1" t="n">
         <v>1.1135</v>
       </c>
-      <c r="X116" s="1" t="n">
+      <c r="Y116" s="1" t="n">
         <v>1.0937</v>
       </c>
     </row>
@@ -9377,9 +9728,12 @@
         <v>0.1534</v>
       </c>
       <c r="W117" s="1" t="n">
+        <v>0.1543</v>
+      </c>
+      <c r="X117" s="1" t="n">
         <v>0.1612</v>
       </c>
-      <c r="X117" s="1" t="n">
+      <c r="Y117" s="1" t="n">
         <v>0.1484</v>
       </c>
     </row>
@@ -9453,9 +9807,12 @@
         <v>0.1572</v>
       </c>
       <c r="W118" s="1" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="X118" s="1" t="n">
         <v>0.1603</v>
       </c>
-      <c r="X118" s="1" t="n">
+      <c r="Y118" s="1" t="n">
         <v>0.1572</v>
       </c>
     </row>
@@ -9529,9 +9886,12 @@
         <v>0.04753</v>
       </c>
       <c r="W119" s="1" t="n">
-        <v>0.04769</v>
+        <v>0.0478</v>
       </c>
       <c r="X119" s="1" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="Y119" s="1" t="n">
         <v>0.04566</v>
       </c>
     </row>
@@ -9605,9 +9965,12 @@
         <v>3.012</v>
       </c>
       <c r="W120" s="1" t="n">
+        <v>3.014</v>
+      </c>
+      <c r="X120" s="1" t="n">
         <v>3.033</v>
       </c>
-      <c r="X120" s="1" t="n">
+      <c r="Y120" s="1" t="n">
         <v>3.006</v>
       </c>
     </row>
@@ -9681,9 +10044,12 @@
         <v>0.297</v>
       </c>
       <c r="W121" s="1" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="X121" s="1" t="n">
         <v>0.2979</v>
       </c>
-      <c r="X121" s="1" t="n">
+      <c r="Y121" s="1" t="n">
         <v>0.2957</v>
       </c>
     </row>
@@ -9757,10 +10123,13 @@
         <v>0.5768</v>
       </c>
       <c r="W122" s="1" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="X122" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="X122" s="1" t="n">
-        <v>0.5768</v>
+      <c r="Y122" s="1" t="n">
+        <v>0.5767</v>
       </c>
     </row>
     <row r="123">
@@ -9833,9 +10202,12 @@
         <v>0.01247</v>
       </c>
       <c r="W123" s="1" t="n">
+        <v>0.01247</v>
+      </c>
+      <c r="X123" s="1" t="n">
         <v>0.01263</v>
       </c>
-      <c r="X123" s="1" t="n">
+      <c r="Y123" s="1" t="n">
         <v>0.01247</v>
       </c>
     </row>
@@ -9909,9 +10281,12 @@
         <v>0.1566</v>
       </c>
       <c r="W124" s="1" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="X124" s="1" t="n">
         <v>0.1595</v>
       </c>
-      <c r="X124" s="1" t="n">
+      <c r="Y124" s="1" t="n">
         <v>0.1566</v>
       </c>
     </row>
@@ -9985,9 +10360,12 @@
         <v>0.001786</v>
       </c>
       <c r="W125" s="1" t="n">
-        <v>0.001786</v>
+        <v>0.001788</v>
       </c>
       <c r="X125" s="1" t="n">
+        <v>0.001788</v>
+      </c>
+      <c r="Y125" s="1" t="n">
         <v>0.001778</v>
       </c>
     </row>
@@ -10061,10 +10439,13 @@
         <v>0.0004816</v>
       </c>
       <c r="W126" s="1" t="n">
+        <v>0.0004808</v>
+      </c>
+      <c r="X126" s="1" t="n">
         <v>0.0004906</v>
       </c>
-      <c r="X126" s="1" t="n">
-        <v>0.0004816</v>
+      <c r="Y126" s="1" t="n">
+        <v>0.0004808</v>
       </c>
     </row>
     <row r="127">
@@ -10137,9 +10518,12 @@
         <v>0.02922</v>
       </c>
       <c r="W127" s="1" t="n">
+        <v>0.02924</v>
+      </c>
+      <c r="X127" s="1" t="n">
         <v>0.02959</v>
       </c>
-      <c r="X127" s="1" t="n">
+      <c r="Y127" s="1" t="n">
         <v>0.02922</v>
       </c>
     </row>
@@ -10213,9 +10597,12 @@
         <v>0.04123</v>
       </c>
       <c r="W128" s="1" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="X128" s="1" t="n">
         <v>0.04138</v>
       </c>
-      <c r="X128" s="1" t="n">
+      <c r="Y128" s="1" t="n">
         <v>0.04116</v>
       </c>
     </row>
@@ -10292,6 +10679,9 @@
         <v>0.04935</v>
       </c>
       <c r="X129" s="1" t="n">
+        <v>0.04935</v>
+      </c>
+      <c r="Y129" s="1" t="n">
         <v>0.04837</v>
       </c>
     </row>
@@ -10365,9 +10755,12 @@
         <v>1.21e-05</v>
       </c>
       <c r="W130" s="1" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="X130" s="1" t="n">
         <v>1.26e-05</v>
       </c>
-      <c r="X130" s="1" t="n">
+      <c r="Y130" s="1" t="n">
         <v>1.21e-05</v>
       </c>
     </row>
@@ -10441,9 +10834,12 @@
         <v>7.3e-06</v>
       </c>
       <c r="W131" s="1" t="n">
+        <v>7.3e-06</v>
+      </c>
+      <c r="X131" s="1" t="n">
         <v>7.5e-06</v>
       </c>
-      <c r="X131" s="1" t="n">
+      <c r="Y131" s="1" t="n">
         <v>6.7e-06</v>
       </c>
     </row>
@@ -10517,9 +10913,12 @@
         <v>0.00701</v>
       </c>
       <c r="W132" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="X132" s="1" t="n">
         <v>0.00705</v>
       </c>
-      <c r="X132" s="1" t="n">
+      <c r="Y132" s="1" t="n">
         <v>0.00697</v>
       </c>
     </row>
@@ -10593,9 +10992,12 @@
         <v>0.0964</v>
       </c>
       <c r="W133" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="X133" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
-      <c r="X133" s="1" t="n">
+      <c r="Y133" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -10669,9 +11071,12 @@
         <v>0.0004104</v>
       </c>
       <c r="W134" s="1" t="n">
+        <v>0.0004104</v>
+      </c>
+      <c r="X134" s="1" t="n">
         <v>0.0004114</v>
       </c>
-      <c r="X134" s="1" t="n">
+      <c r="Y134" s="1" t="n">
         <v>0.0004076</v>
       </c>
     </row>
@@ -10745,9 +11150,12 @@
         <v>0.08191</v>
       </c>
       <c r="W135" s="1" t="n">
+        <v>0.08193</v>
+      </c>
+      <c r="X135" s="1" t="n">
         <v>0.08468000000000001</v>
       </c>
-      <c r="X135" s="1" t="n">
+      <c r="Y135" s="1" t="n">
         <v>0.08148</v>
       </c>
     </row>
@@ -10821,9 +11229,12 @@
         <v>0.007748</v>
       </c>
       <c r="W136" s="1" t="n">
+        <v>0.007786</v>
+      </c>
+      <c r="X136" s="1" t="n">
         <v>0.008005</v>
       </c>
-      <c r="X136" s="1" t="n">
+      <c r="Y136" s="1" t="n">
         <v>0.007748</v>
       </c>
     </row>
@@ -10897,9 +11308,12 @@
         <v>0.0007981</v>
       </c>
       <c r="W137" s="1" t="n">
+        <v>0.0007982</v>
+      </c>
+      <c r="X137" s="1" t="n">
         <v>0.000839</v>
       </c>
-      <c r="X137" s="1" t="n">
+      <c r="Y137" s="1" t="n">
         <v>0.0007981</v>
       </c>
     </row>
@@ -10973,9 +11387,12 @@
         <v>0.1455</v>
       </c>
       <c r="W138" s="1" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="X138" s="1" t="n">
         <v>0.1487</v>
       </c>
-      <c r="X138" s="1" t="n">
+      <c r="Y138" s="1" t="n">
         <v>0.1453</v>
       </c>
     </row>
@@ -11049,9 +11466,12 @@
         <v>0.006661</v>
       </c>
       <c r="W139" s="1" t="n">
+        <v>0.006661</v>
+      </c>
+      <c r="X139" s="1" t="n">
         <v>0.00674</v>
       </c>
-      <c r="X139" s="1" t="n">
+      <c r="Y139" s="1" t="n">
         <v>0.006661</v>
       </c>
     </row>
@@ -11125,9 +11545,12 @@
         <v>0.01373</v>
       </c>
       <c r="W140" s="1" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="X140" s="1" t="n">
         <v>0.01394</v>
       </c>
-      <c r="X140" s="1" t="n">
+      <c r="Y140" s="1" t="n">
         <v>0.01373</v>
       </c>
     </row>
@@ -11201,10 +11624,13 @@
         <v>0.09601</v>
       </c>
       <c r="W141" s="1" t="n">
+        <v>0.09591</v>
+      </c>
+      <c r="X141" s="1" t="n">
         <v>0.09848999999999999</v>
       </c>
-      <c r="X141" s="1" t="n">
-        <v>0.09601</v>
+      <c r="Y141" s="1" t="n">
+        <v>0.09591</v>
       </c>
     </row>
     <row r="142">
@@ -11277,9 +11703,12 @@
         <v>0.05412</v>
       </c>
       <c r="W142" s="1" t="n">
+        <v>0.05416</v>
+      </c>
+      <c r="X142" s="1" t="n">
         <v>0.05423</v>
       </c>
-      <c r="X142" s="1" t="n">
+      <c r="Y142" s="1" t="n">
         <v>0.05405</v>
       </c>
     </row>
@@ -11353,9 +11782,12 @@
         <v>0.3221</v>
       </c>
       <c r="W143" s="1" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="X143" s="1" t="n">
         <v>0.3262</v>
       </c>
-      <c r="X143" s="1" t="n">
+      <c r="Y143" s="1" t="n">
         <v>0.3219</v>
       </c>
     </row>
@@ -11429,9 +11861,12 @@
         <v>0.02553</v>
       </c>
       <c r="W144" s="1" t="n">
+        <v>0.02557</v>
+      </c>
+      <c r="X144" s="1" t="n">
         <v>0.02588</v>
       </c>
-      <c r="X144" s="1" t="n">
+      <c r="Y144" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -11505,9 +11940,12 @@
         <v>0.2359</v>
       </c>
       <c r="W145" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="X145" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="X145" s="1" t="n">
+      <c r="Y145" s="1" t="n">
         <v>0.2351</v>
       </c>
     </row>
@@ -11581,9 +12019,12 @@
         <v>0.007037</v>
       </c>
       <c r="W146" s="1" t="n">
+        <v>0.007021</v>
+      </c>
+      <c r="X146" s="1" t="n">
         <v>0.007129</v>
       </c>
-      <c r="X146" s="1" t="n">
+      <c r="Y146" s="1" t="n">
         <v>0.006982</v>
       </c>
     </row>
@@ -11657,9 +12098,12 @@
         <v>0.08624999999999999</v>
       </c>
       <c r="W147" s="1" t="n">
+        <v>0.08608</v>
+      </c>
+      <c r="X147" s="1" t="n">
         <v>0.08734</v>
       </c>
-      <c r="X147" s="1" t="n">
+      <c r="Y147" s="1" t="n">
         <v>0.08597</v>
       </c>
     </row>
@@ -11733,9 +12177,12 @@
         <v>0.05289</v>
       </c>
       <c r="W148" s="1" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="X148" s="1" t="n">
         <v>0.05289</v>
       </c>
-      <c r="X148" s="1" t="n">
+      <c r="Y148" s="1" t="n">
         <v>0.05024</v>
       </c>
     </row>
@@ -11809,9 +12256,12 @@
         <v>0.02401</v>
       </c>
       <c r="W149" s="1" t="n">
+        <v>0.02391</v>
+      </c>
+      <c r="X149" s="1" t="n">
         <v>0.02402</v>
       </c>
-      <c r="X149" s="1" t="n">
+      <c r="Y149" s="1" t="n">
         <v>0.02379</v>
       </c>
     </row>
@@ -11885,9 +12335,12 @@
         <v>0.08595</v>
       </c>
       <c r="W150" s="1" t="n">
+        <v>0.08628</v>
+      </c>
+      <c r="X150" s="1" t="n">
         <v>0.0867</v>
       </c>
-      <c r="X150" s="1" t="n">
+      <c r="Y150" s="1" t="n">
         <v>0.08495</v>
       </c>
     </row>
@@ -11961,10 +12414,13 @@
         <v>0.02314</v>
       </c>
       <c r="W151" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="X151" s="1" t="n">
         <v>0.02352</v>
       </c>
-      <c r="X151" s="1" t="n">
-        <v>0.02312</v>
+      <c r="Y151" s="1" t="n">
+        <v>0.02308</v>
       </c>
     </row>
     <row r="152">
@@ -12037,9 +12493,12 @@
         <v>0.02515</v>
       </c>
       <c r="W152" s="1" t="n">
+        <v>0.02515</v>
+      </c>
+      <c r="X152" s="1" t="n">
         <v>0.02586</v>
       </c>
-      <c r="X152" s="1" t="n">
+      <c r="Y152" s="1" t="n">
         <v>0.02515</v>
       </c>
     </row>
@@ -12113,9 +12572,12 @@
         <v>0.0002109</v>
       </c>
       <c r="W153" s="1" t="n">
+        <v>0.000212</v>
+      </c>
+      <c r="X153" s="1" t="n">
         <v>0.0002183</v>
       </c>
-      <c r="X153" s="1" t="n">
+      <c r="Y153" s="1" t="n">
         <v>0.0002082</v>
       </c>
     </row>
@@ -12189,9 +12651,12 @@
         <v>0.4448</v>
       </c>
       <c r="W154" s="1" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="X154" s="1" t="n">
         <v>0.4474</v>
       </c>
-      <c r="X154" s="1" t="n">
+      <c r="Y154" s="1" t="n">
         <v>0.437</v>
       </c>
     </row>
@@ -12265,9 +12730,12 @@
         <v>0.06769</v>
       </c>
       <c r="W155" s="1" t="n">
+        <v>0.06752</v>
+      </c>
+      <c r="X155" s="1" t="n">
         <v>0.06813</v>
       </c>
-      <c r="X155" s="1" t="n">
+      <c r="Y155" s="1" t="n">
         <v>0.06662999999999999</v>
       </c>
     </row>
@@ -12341,9 +12809,12 @@
         <v>0.13161</v>
       </c>
       <c r="W156" s="1" t="n">
+        <v>0.13384</v>
+      </c>
+      <c r="X156" s="1" t="n">
         <v>0.13403</v>
       </c>
-      <c r="X156" s="1" t="n">
+      <c r="Y156" s="1" t="n">
         <v>0.1276</v>
       </c>
     </row>
@@ -12417,10 +12888,13 @@
         <v>0.4825</v>
       </c>
       <c r="W157" s="1" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="X157" s="1" t="n">
         <v>0.4847</v>
       </c>
-      <c r="X157" s="1" t="n">
-        <v>0.4823</v>
+      <c r="Y157" s="1" t="n">
+        <v>0.4818</v>
       </c>
     </row>
     <row r="158">
@@ -12493,9 +12967,12 @@
         <v>0.4485</v>
       </c>
       <c r="W158" s="1" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="X158" s="1" t="n">
         <v>0.4523</v>
       </c>
-      <c r="X158" s="1" t="n">
+      <c r="Y158" s="1" t="n">
         <v>0.4465</v>
       </c>
     </row>
@@ -12569,9 +13046,12 @@
         <v>0.007426</v>
       </c>
       <c r="W159" s="1" t="n">
+        <v>0.007419</v>
+      </c>
+      <c r="X159" s="1" t="n">
         <v>0.007557</v>
       </c>
-      <c r="X159" s="1" t="n">
+      <c r="Y159" s="1" t="n">
         <v>0.007417</v>
       </c>
     </row>
@@ -12645,9 +13125,12 @@
         <v>0.004649</v>
       </c>
       <c r="W160" s="1" t="n">
+        <v>0.004653</v>
+      </c>
+      <c r="X160" s="1" t="n">
         <v>0.004699</v>
       </c>
-      <c r="X160" s="1" t="n">
+      <c r="Y160" s="1" t="n">
         <v>0.004628</v>
       </c>
     </row>
@@ -12721,9 +13204,12 @@
         <v>0.004295</v>
       </c>
       <c r="W161" s="1" t="n">
+        <v>0.004298</v>
+      </c>
+      <c r="X161" s="1" t="n">
         <v>0.004314</v>
       </c>
-      <c r="X161" s="1" t="n">
+      <c r="Y161" s="1" t="n">
         <v>0.004276</v>
       </c>
     </row>
@@ -12797,9 +13283,12 @@
         <v>0.0951</v>
       </c>
       <c r="W162" s="1" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="X162" s="1" t="n">
         <v>0.0964</v>
       </c>
-      <c r="X162" s="1" t="n">
+      <c r="Y162" s="1" t="n">
         <v>0.0951</v>
       </c>
     </row>
@@ -12873,9 +13362,12 @@
         <v>0.2845</v>
       </c>
       <c r="W163" s="1" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="X163" s="1" t="n">
         <v>0.2865</v>
       </c>
-      <c r="X163" s="1" t="n">
+      <c r="Y163" s="1" t="n">
         <v>0.2843</v>
       </c>
     </row>
@@ -12949,9 +13441,12 @@
         <v>0.1131</v>
       </c>
       <c r="W164" s="1" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="X164" s="1" t="n">
         <v>0.1148</v>
       </c>
-      <c r="X164" s="1" t="n">
+      <c r="Y164" s="1" t="n">
         <v>0.1131</v>
       </c>
     </row>
@@ -13025,9 +13520,12 @@
         <v>0.1747</v>
       </c>
       <c r="W165" s="1" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="X165" s="1" t="n">
         <v>0.1761</v>
       </c>
-      <c r="X165" s="1" t="n">
+      <c r="Y165" s="1" t="n">
         <v>0.1747</v>
       </c>
     </row>
@@ -13101,9 +13599,12 @@
         <v>0.01055</v>
       </c>
       <c r="W166" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="X166" s="1" t="n">
         <v>0.01055</v>
       </c>
-      <c r="X166" s="1" t="n">
+      <c r="Y166" s="1" t="n">
         <v>0.01004</v>
       </c>
     </row>
@@ -13177,9 +13678,12 @@
         <v>1.813</v>
       </c>
       <c r="W167" s="1" t="n">
+        <v>1.813</v>
+      </c>
+      <c r="X167" s="1" t="n">
         <v>1.842</v>
       </c>
-      <c r="X167" s="1" t="n">
+      <c r="Y167" s="1" t="n">
         <v>1.813</v>
       </c>
     </row>
@@ -13253,9 +13757,12 @@
         <v>1.336</v>
       </c>
       <c r="W168" s="1" t="n">
+        <v>1.335</v>
+      </c>
+      <c r="X168" s="1" t="n">
         <v>1.363</v>
       </c>
-      <c r="X168" s="1" t="n">
+      <c r="Y168" s="1" t="n">
         <v>1.333</v>
       </c>
     </row>
@@ -13329,9 +13836,12 @@
         <v>0.007276</v>
       </c>
       <c r="W169" s="1" t="n">
+        <v>0.007287</v>
+      </c>
+      <c r="X169" s="1" t="n">
         <v>0.007335</v>
       </c>
-      <c r="X169" s="1" t="n">
+      <c r="Y169" s="1" t="n">
         <v>0.007276</v>
       </c>
     </row>
@@ -13405,9 +13915,12 @@
         <v>0.0116</v>
       </c>
       <c r="W170" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="X170" s="1" t="n">
         <v>0.0117</v>
       </c>
-      <c r="X170" s="1" t="n">
+      <c r="Y170" s="1" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -13481,10 +13994,13 @@
         <v>0.005751</v>
       </c>
       <c r="W171" s="1" t="n">
+        <v>0.005737</v>
+      </c>
+      <c r="X171" s="1" t="n">
         <v>0.005827</v>
       </c>
-      <c r="X171" s="1" t="n">
-        <v>0.005751</v>
+      <c r="Y171" s="1" t="n">
+        <v>0.005737</v>
       </c>
     </row>
     <row r="172">
@@ -13557,9 +14073,12 @@
         <v>0.14863</v>
       </c>
       <c r="W172" s="1" t="n">
+        <v>0.14899</v>
+      </c>
+      <c r="X172" s="1" t="n">
         <v>0.14905</v>
       </c>
-      <c r="X172" s="1" t="n">
+      <c r="Y172" s="1" t="n">
         <v>0.14615</v>
       </c>
     </row>
@@ -13633,9 +14152,12 @@
         <v>4.868</v>
       </c>
       <c r="W173" s="1" t="n">
+        <v>4.869</v>
+      </c>
+      <c r="X173" s="1" t="n">
         <v>4.917</v>
       </c>
-      <c r="X173" s="1" t="n">
+      <c r="Y173" s="1" t="n">
         <v>4.868</v>
       </c>
     </row>
@@ -13709,9 +14231,12 @@
         <v>0.07785</v>
       </c>
       <c r="W174" s="1" t="n">
+        <v>0.07792</v>
+      </c>
+      <c r="X174" s="1" t="n">
         <v>0.07982</v>
       </c>
-      <c r="X174" s="1" t="n">
+      <c r="Y174" s="1" t="n">
         <v>0.07785</v>
       </c>
     </row>
@@ -13785,9 +14310,12 @@
         <v>0.007404</v>
       </c>
       <c r="W175" s="1" t="n">
+        <v>0.007403</v>
+      </c>
+      <c r="X175" s="1" t="n">
         <v>0.007513</v>
       </c>
-      <c r="X175" s="1" t="n">
+      <c r="Y175" s="1" t="n">
         <v>0.007403</v>
       </c>
     </row>
@@ -13861,9 +14389,12 @@
         <v>0.1983</v>
       </c>
       <c r="W176" s="1" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="X176" s="1" t="n">
         <v>0.2023</v>
       </c>
-      <c r="X176" s="1" t="n">
+      <c r="Y176" s="1" t="n">
         <v>0.1983</v>
       </c>
     </row>
@@ -13937,9 +14468,12 @@
         <v>0.05196</v>
       </c>
       <c r="W177" s="1" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="X177" s="1" t="n">
         <v>0.05197</v>
       </c>
-      <c r="X177" s="1" t="n">
+      <c r="Y177" s="1" t="n">
         <v>0.05171</v>
       </c>
     </row>
@@ -14013,10 +14547,13 @@
         <v>0.05444</v>
       </c>
       <c r="W178" s="1" t="n">
+        <v>0.05442</v>
+      </c>
+      <c r="X178" s="1" t="n">
         <v>0.05485</v>
       </c>
-      <c r="X178" s="1" t="n">
-        <v>0.05444</v>
+      <c r="Y178" s="1" t="n">
+        <v>0.05442</v>
       </c>
     </row>
     <row r="179">
@@ -14089,9 +14626,12 @@
         <v>0.02341</v>
       </c>
       <c r="W179" s="1" t="n">
+        <v>0.02332</v>
+      </c>
+      <c r="X179" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="X179" s="1" t="n">
+      <c r="Y179" s="1" t="n">
         <v>0.02317</v>
       </c>
     </row>
@@ -14165,9 +14705,12 @@
         <v>0.6994</v>
       </c>
       <c r="W180" s="1" t="n">
+        <v>0.6973</v>
+      </c>
+      <c r="X180" s="1" t="n">
         <v>0.6994</v>
       </c>
-      <c r="X180" s="1" t="n">
+      <c r="Y180" s="1" t="n">
         <v>0.6936</v>
       </c>
     </row>
@@ -14241,9 +14784,12 @@
         <v>0.0003732</v>
       </c>
       <c r="W181" s="1" t="n">
+        <v>0.0003741</v>
+      </c>
+      <c r="X181" s="1" t="n">
         <v>0.0003768</v>
       </c>
-      <c r="X181" s="1" t="n">
+      <c r="Y181" s="1" t="n">
         <v>0.000371</v>
       </c>
     </row>
@@ -14317,9 +14863,12 @@
         <v>0.01263</v>
       </c>
       <c r="W182" s="1" t="n">
+        <v>0.01264</v>
+      </c>
+      <c r="X182" s="1" t="n">
         <v>0.01287</v>
       </c>
-      <c r="X182" s="1" t="n">
+      <c r="Y182" s="1" t="n">
         <v>0.01254</v>
       </c>
     </row>
@@ -14393,9 +14942,12 @@
         <v>4.217</v>
       </c>
       <c r="W183" s="1" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="X183" s="1" t="n">
         <v>4.277</v>
       </c>
-      <c r="X183" s="1" t="n">
+      <c r="Y183" s="1" t="n">
         <v>4.182</v>
       </c>
     </row>
@@ -14469,9 +15021,12 @@
         <v>0.234</v>
       </c>
       <c r="W184" s="1" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="X184" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="X184" s="1" t="n">
+      <c r="Y184" s="1" t="n">
         <v>0.2335</v>
       </c>
     </row>
@@ -14545,9 +15100,12 @@
         <v>0.03706</v>
       </c>
       <c r="W185" s="1" t="n">
+        <v>0.03679</v>
+      </c>
+      <c r="X185" s="1" t="n">
         <v>0.03782</v>
       </c>
-      <c r="X185" s="1" t="n">
+      <c r="Y185" s="1" t="n">
         <v>0.03672</v>
       </c>
     </row>
@@ -14621,9 +15179,12 @@
         <v>0.11568</v>
       </c>
       <c r="W186" s="1" t="n">
+        <v>0.11545</v>
+      </c>
+      <c r="X186" s="1" t="n">
         <v>0.11632</v>
       </c>
-      <c r="X186" s="1" t="n">
+      <c r="Y186" s="1" t="n">
         <v>0.11535</v>
       </c>
     </row>
@@ -14697,9 +15258,12 @@
         <v>0.009133</v>
       </c>
       <c r="W187" s="1" t="n">
+        <v>0.009056</v>
+      </c>
+      <c r="X187" s="1" t="n">
         <v>0.009277000000000001</v>
       </c>
-      <c r="X187" s="1" t="n">
+      <c r="Y187" s="1" t="n">
         <v>0.009013</v>
       </c>
     </row>
@@ -14773,9 +15337,12 @@
         <v>0.0969</v>
       </c>
       <c r="W188" s="1" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="X188" s="1" t="n">
         <v>0.0978</v>
       </c>
-      <c r="X188" s="1" t="n">
+      <c r="Y188" s="1" t="n">
         <v>0.0968</v>
       </c>
     </row>
@@ -14849,9 +15416,12 @@
         <v>0.02702</v>
       </c>
       <c r="W189" s="1" t="n">
+        <v>0.02713</v>
+      </c>
+      <c r="X189" s="1" t="n">
         <v>0.02808</v>
       </c>
-      <c r="X189" s="1" t="n">
+      <c r="Y189" s="1" t="n">
         <v>0.02702</v>
       </c>
     </row>
@@ -14925,9 +15495,12 @@
         <v>0.008710000000000001</v>
       </c>
       <c r="W190" s="1" t="n">
+        <v>0.00865</v>
+      </c>
+      <c r="X190" s="1" t="n">
         <v>0.00886</v>
       </c>
-      <c r="X190" s="1" t="n">
+      <c r="Y190" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -15001,9 +15574,12 @@
         <v>0.001957</v>
       </c>
       <c r="W191" s="1" t="n">
+        <v>0.001957</v>
+      </c>
+      <c r="X191" s="1" t="n">
         <v>0.001961</v>
       </c>
-      <c r="X191" s="1" t="n">
+      <c r="Y191" s="1" t="n">
         <v>0.001947</v>
       </c>
     </row>
@@ -15077,9 +15653,12 @@
         <v>0.1019</v>
       </c>
       <c r="W192" s="1" t="n">
+        <v>0.0998</v>
+      </c>
+      <c r="X192" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="X192" s="1" t="n">
+      <c r="Y192" s="1" t="n">
         <v>0.09959999999999999</v>
       </c>
     </row>
@@ -15153,9 +15732,12 @@
         <v>0.0234</v>
       </c>
       <c r="W193" s="1" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="X193" s="1" t="n">
         <v>0.02347</v>
       </c>
-      <c r="X193" s="1" t="n">
+      <c r="Y193" s="1" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -15229,9 +15811,12 @@
         <v>0.0134</v>
       </c>
       <c r="W194" s="1" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="X194" s="1" t="n">
         <v>0.01351</v>
       </c>
-      <c r="X194" s="1" t="n">
+      <c r="Y194" s="1" t="n">
         <v>0.0134</v>
       </c>
     </row>
@@ -15305,9 +15890,12 @@
         <v>0.02071</v>
       </c>
       <c r="W195" s="1" t="n">
+        <v>0.02071</v>
+      </c>
+      <c r="X195" s="1" t="n">
         <v>0.02105</v>
       </c>
-      <c r="X195" s="1" t="n">
+      <c r="Y195" s="1" t="n">
         <v>0.02071</v>
       </c>
     </row>
@@ -15381,9 +15969,12 @@
         <v>0.17655</v>
       </c>
       <c r="W196" s="1" t="n">
+        <v>0.17687</v>
+      </c>
+      <c r="X196" s="1" t="n">
         <v>0.17767</v>
       </c>
-      <c r="X196" s="1" t="n">
+      <c r="Y196" s="1" t="n">
         <v>0.1698</v>
       </c>
     </row>
@@ -15457,9 +16048,12 @@
         <v>0.007365</v>
       </c>
       <c r="W197" s="1" t="n">
+        <v>0.007306</v>
+      </c>
+      <c r="X197" s="1" t="n">
         <v>0.007482</v>
       </c>
-      <c r="X197" s="1" t="n">
+      <c r="Y197" s="1" t="n">
         <v>0.007277</v>
       </c>
     </row>
@@ -15533,9 +16127,12 @@
         <v>0.01896</v>
       </c>
       <c r="W198" s="1" t="n">
+        <v>0.01899</v>
+      </c>
+      <c r="X198" s="1" t="n">
         <v>0.01912</v>
       </c>
-      <c r="X198" s="1" t="n">
+      <c r="Y198" s="1" t="n">
         <v>0.01896</v>
       </c>
     </row>
@@ -15609,9 +16206,12 @@
         <v>0.01647</v>
       </c>
       <c r="W199" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="X199" s="1" t="n">
         <v>0.01728</v>
       </c>
-      <c r="X199" s="1" t="n">
+      <c r="Y199" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -15685,9 +16285,12 @@
         <v>0.2973</v>
       </c>
       <c r="W200" s="1" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="X200" s="1" t="n">
         <v>0.2981</v>
       </c>
-      <c r="X200" s="1" t="n">
+      <c r="Y200" s="1" t="n">
         <v>0.2965</v>
       </c>
     </row>
@@ -15761,9 +16364,12 @@
         <v>0.006204</v>
       </c>
       <c r="W201" s="1" t="n">
+        <v>0.006233</v>
+      </c>
+      <c r="X201" s="1" t="n">
         <v>0.006258</v>
       </c>
-      <c r="X201" s="1" t="n">
+      <c r="Y201" s="1" t="n">
         <v>0.006203</v>
       </c>
     </row>
@@ -15837,9 +16443,12 @@
         <v>0.0004378</v>
       </c>
       <c r="W202" s="1" t="n">
+        <v>0.000438</v>
+      </c>
+      <c r="X202" s="1" t="n">
         <v>0.0004464</v>
       </c>
-      <c r="X202" s="1" t="n">
+      <c r="Y202" s="1" t="n">
         <v>0.0004378</v>
       </c>
     </row>
@@ -15913,9 +16522,12 @@
         <v>0.007252</v>
       </c>
       <c r="W203" s="1" t="n">
+        <v>0.007254</v>
+      </c>
+      <c r="X203" s="1" t="n">
         <v>0.007385</v>
       </c>
-      <c r="X203" s="1" t="n">
+      <c r="Y203" s="1" t="n">
         <v>0.007245</v>
       </c>
     </row>
@@ -15989,9 +16601,12 @@
         <v>0.1298</v>
       </c>
       <c r="W204" s="1" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="X204" s="1" t="n">
         <v>0.1318</v>
       </c>
-      <c r="X204" s="1" t="n">
+      <c r="Y204" s="1" t="n">
         <v>0.1282</v>
       </c>
     </row>
@@ -16065,9 +16680,12 @@
         <v>0.01416</v>
       </c>
       <c r="W205" s="1" t="n">
+        <v>0.01419</v>
+      </c>
+      <c r="X205" s="1" t="n">
         <v>0.01457</v>
       </c>
-      <c r="X205" s="1" t="n">
+      <c r="Y205" s="1" t="n">
         <v>0.01412</v>
       </c>
     </row>
@@ -16141,9 +16759,12 @@
         <v>0.00356</v>
       </c>
       <c r="W206" s="1" t="n">
+        <v>0.003567</v>
+      </c>
+      <c r="X206" s="1" t="n">
         <v>0.00361</v>
       </c>
-      <c r="X206" s="1" t="n">
+      <c r="Y206" s="1" t="n">
         <v>0.00356</v>
       </c>
     </row>
@@ -16217,9 +16838,12 @@
         <v>0.05883</v>
       </c>
       <c r="W207" s="1" t="n">
+        <v>0.05887</v>
+      </c>
+      <c r="X207" s="1" t="n">
         <v>0.05999</v>
       </c>
-      <c r="X207" s="1" t="n">
+      <c r="Y207" s="1" t="n">
         <v>0.05883</v>
       </c>
     </row>
@@ -16293,9 +16917,12 @@
         <v>15.52</v>
       </c>
       <c r="W208" s="1" t="n">
-        <v>15.55</v>
+        <v>15.56</v>
       </c>
       <c r="X208" s="1" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="Y208" s="1" t="n">
         <v>15.35</v>
       </c>
     </row>
@@ -16369,9 +16996,12 @@
         <v>5183.8</v>
       </c>
       <c r="W209" s="1" t="n">
+        <v>5184.5</v>
+      </c>
+      <c r="X209" s="1" t="n">
         <v>5194.4</v>
       </c>
-      <c r="X209" s="1" t="n">
+      <c r="Y209" s="1" t="n">
         <v>5183.4</v>
       </c>
     </row>
@@ -16445,9 +17075,12 @@
         <v>0.11992</v>
       </c>
       <c r="W210" s="1" t="n">
+        <v>0.11981</v>
+      </c>
+      <c r="X210" s="1" t="n">
         <v>0.12065</v>
       </c>
-      <c r="X210" s="1" t="n">
+      <c r="Y210" s="1" t="n">
         <v>0.11941</v>
       </c>
     </row>
@@ -16521,9 +17154,12 @@
         <v>0.1807</v>
       </c>
       <c r="W211" s="1" t="n">
+        <v>0.1812</v>
+      </c>
+      <c r="X211" s="1" t="n">
         <v>0.1839</v>
       </c>
-      <c r="X211" s="1" t="n">
+      <c r="Y211" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -16597,9 +17233,12 @@
         <v>0.0297</v>
       </c>
       <c r="W212" s="1" t="n">
+        <v>0.0298</v>
+      </c>
+      <c r="X212" s="1" t="n">
         <v>0.0309</v>
       </c>
-      <c r="X212" s="1" t="n">
+      <c r="Y212" s="1" t="n">
         <v>0.0297</v>
       </c>
     </row>
@@ -16673,9 +17312,12 @@
         <v>1.3982</v>
       </c>
       <c r="W213" s="1" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="X213" s="1" t="n">
         <v>1.3997</v>
       </c>
-      <c r="X213" s="1" t="n">
+      <c r="Y213" s="1" t="n">
         <v>1.3921</v>
       </c>
     </row>
@@ -16749,9 +17391,12 @@
         <v>0.05653</v>
       </c>
       <c r="W214" s="1" t="n">
+        <v>0.0565</v>
+      </c>
+      <c r="X214" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="X214" s="1" t="n">
+      <c r="Y214" s="1" t="n">
         <v>0.05641</v>
       </c>
     </row>
@@ -16825,9 +17470,12 @@
         <v>0.04389</v>
       </c>
       <c r="W215" s="1" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="X215" s="1" t="n">
         <v>0.04447</v>
       </c>
-      <c r="X215" s="1" t="n">
+      <c r="Y215" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -16901,9 +17549,12 @@
         <v>0.15103</v>
       </c>
       <c r="W216" s="1" t="n">
+        <v>0.15118</v>
+      </c>
+      <c r="X216" s="1" t="n">
         <v>0.1517</v>
       </c>
-      <c r="X216" s="1" t="n">
+      <c r="Y216" s="1" t="n">
         <v>0.14904</v>
       </c>
     </row>
@@ -16977,9 +17628,12 @@
         <v>0.074</v>
       </c>
       <c r="W217" s="1" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="X217" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="X217" s="1" t="n">
+      <c r="Y217" s="1" t="n">
         <v>0.073</v>
       </c>
     </row>
@@ -17053,9 +17707,12 @@
         <v>0.00266</v>
       </c>
       <c r="W218" s="1" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="X218" s="1" t="n">
         <v>0.00269</v>
       </c>
-      <c r="X218" s="1" t="n">
+      <c r="Y218" s="1" t="n">
         <v>0.00266</v>
       </c>
     </row>
@@ -17129,9 +17786,12 @@
         <v>0.01693</v>
       </c>
       <c r="W219" s="1" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="X219" s="1" t="n">
         <v>0.01721</v>
       </c>
-      <c r="X219" s="1" t="n">
+      <c r="Y219" s="1" t="n">
         <v>0.01693</v>
       </c>
     </row>
@@ -17205,9 +17865,12 @@
         <v>0.05512</v>
       </c>
       <c r="W220" s="1" t="n">
+        <v>0.05513</v>
+      </c>
+      <c r="X220" s="1" t="n">
         <v>0.05535</v>
       </c>
-      <c r="X220" s="1" t="n">
+      <c r="Y220" s="1" t="n">
         <v>0.05504</v>
       </c>
     </row>
@@ -17281,9 +17944,12 @@
         <v>0.02181</v>
       </c>
       <c r="W221" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="X221" s="1" t="n">
         <v>0.02196</v>
       </c>
-      <c r="X221" s="1" t="n">
+      <c r="Y221" s="1" t="n">
         <v>0.02179</v>
       </c>
     </row>
@@ -17357,9 +18023,12 @@
         <v>0.00925</v>
       </c>
       <c r="W222" s="1" t="n">
+        <v>0.009259999999999999</v>
+      </c>
+      <c r="X222" s="1" t="n">
         <v>0.00942</v>
       </c>
-      <c r="X222" s="1" t="n">
+      <c r="Y222" s="1" t="n">
         <v>0.00923</v>
       </c>
     </row>
@@ -17433,9 +18102,12 @@
         <v>0.0163</v>
       </c>
       <c r="W223" s="1" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="X223" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="X223" s="1" t="n">
+      <c r="Y223" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -17509,9 +18181,12 @@
         <v>0.03811</v>
       </c>
       <c r="W224" s="1" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="X224" s="1" t="n">
         <v>0.03846</v>
       </c>
-      <c r="X224" s="1" t="n">
+      <c r="Y224" s="1" t="n">
         <v>0.03797</v>
       </c>
     </row>
@@ -17585,9 +18260,12 @@
         <v>0.001515</v>
       </c>
       <c r="W225" s="1" t="n">
+        <v>0.001517</v>
+      </c>
+      <c r="X225" s="1" t="n">
         <v>0.00153</v>
       </c>
-      <c r="X225" s="1" t="n">
+      <c r="Y225" s="1" t="n">
         <v>0.001513</v>
       </c>
     </row>
@@ -17661,9 +18339,12 @@
         <v>27.05</v>
       </c>
       <c r="W226" s="1" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="X226" s="1" t="n">
         <v>27.31</v>
       </c>
-      <c r="X226" s="1" t="n">
+      <c r="Y226" s="1" t="n">
         <v>26.91</v>
       </c>
     </row>
@@ -17737,9 +18418,12 @@
         <v>0.0702</v>
       </c>
       <c r="W227" s="1" t="n">
+        <v>0.07020999999999999</v>
+      </c>
+      <c r="X227" s="1" t="n">
         <v>0.07088999999999999</v>
       </c>
-      <c r="X227" s="1" t="n">
+      <c r="Y227" s="1" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -17813,9 +18497,12 @@
         <v>0.3112</v>
       </c>
       <c r="W228" s="1" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="X228" s="1" t="n">
         <v>0.314</v>
       </c>
-      <c r="X228" s="1" t="n">
+      <c r="Y228" s="1" t="n">
         <v>0.3111</v>
       </c>
     </row>
@@ -17889,9 +18576,12 @@
         <v>18.39</v>
       </c>
       <c r="W229" s="1" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="X229" s="1" t="n">
         <v>18.46</v>
       </c>
-      <c r="X229" s="1" t="n">
+      <c r="Y229" s="1" t="n">
         <v>18.33</v>
       </c>
     </row>
@@ -17965,9 +18655,12 @@
         <v>0.01918</v>
       </c>
       <c r="W230" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="X230" s="1" t="n">
         <v>0.01952</v>
       </c>
-      <c r="X230" s="1" t="n">
+      <c r="Y230" s="1" t="n">
         <v>0.01914</v>
       </c>
     </row>
@@ -18041,9 +18734,12 @@
         <v>0.01212</v>
       </c>
       <c r="W231" s="1" t="n">
+        <v>0.01213</v>
+      </c>
+      <c r="X231" s="1" t="n">
         <v>0.01224</v>
       </c>
-      <c r="X231" s="1" t="n">
+      <c r="Y231" s="1" t="n">
         <v>0.01212</v>
       </c>
     </row>
@@ -18117,9 +18813,12 @@
         <v>0.2274</v>
       </c>
       <c r="W232" s="1" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="X232" s="1" t="n">
         <v>0.2293</v>
       </c>
-      <c r="X232" s="1" t="n">
+      <c r="Y232" s="1" t="n">
         <v>0.2269</v>
       </c>
     </row>
@@ -18193,9 +18892,12 @@
         <v>0.07077</v>
       </c>
       <c r="W233" s="1" t="n">
+        <v>0.07078</v>
+      </c>
+      <c r="X233" s="1" t="n">
         <v>0.07136000000000001</v>
       </c>
-      <c r="X233" s="1" t="n">
+      <c r="Y233" s="1" t="n">
         <v>0.07073</v>
       </c>
     </row>
@@ -18269,9 +18971,12 @@
         <v>0.1707</v>
       </c>
       <c r="W234" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="X234" s="1" t="n">
         <v>0.1709</v>
       </c>
-      <c r="X234" s="1" t="n">
+      <c r="Y234" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -18345,9 +19050,12 @@
         <v>0.025</v>
       </c>
       <c r="W235" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="X235" s="1" t="n">
         <v>0.0254</v>
       </c>
-      <c r="X235" s="1" t="n">
+      <c r="Y235" s="1" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -18421,9 +19129,12 @@
         <v>0.03003</v>
       </c>
       <c r="W236" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X236" s="1" t="n">
         <v>0.03013</v>
       </c>
-      <c r="X236" s="1" t="n">
+      <c r="Y236" s="1" t="n">
         <v>0.02993</v>
       </c>
     </row>
@@ -18497,9 +19208,12 @@
         <v>2.042</v>
       </c>
       <c r="W237" s="1" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="X237" s="1" t="n">
         <v>2.049</v>
       </c>
-      <c r="X237" s="1" t="n">
+      <c r="Y237" s="1" t="n">
         <v>1.98</v>
       </c>
     </row>
@@ -18573,9 +19287,12 @@
         <v>0.4172</v>
       </c>
       <c r="W238" s="1" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="X238" s="1" t="n">
         <v>0.4312</v>
       </c>
-      <c r="X238" s="1" t="n">
+      <c r="Y238" s="1" t="n">
         <v>0.4172</v>
       </c>
     </row>
@@ -18649,10 +19366,13 @@
         <v>0.03303</v>
       </c>
       <c r="W239" s="1" t="n">
+        <v>0.03297</v>
+      </c>
+      <c r="X239" s="1" t="n">
         <v>0.03376</v>
       </c>
-      <c r="X239" s="1" t="n">
-        <v>0.03303</v>
+      <c r="Y239" s="1" t="n">
+        <v>0.03297</v>
       </c>
     </row>
     <row r="240">
@@ -18725,9 +19445,12 @@
         <v>0.03384</v>
       </c>
       <c r="W240" s="1" t="n">
+        <v>0.03402</v>
+      </c>
+      <c r="X240" s="1" t="n">
         <v>0.0341</v>
       </c>
-      <c r="X240" s="1" t="n">
+      <c r="Y240" s="1" t="n">
         <v>0.0338</v>
       </c>
     </row>
@@ -18801,10 +19524,13 @@
         <v>0.0007466</v>
       </c>
       <c r="W241" s="1" t="n">
+        <v>0.0007452</v>
+      </c>
+      <c r="X241" s="1" t="n">
         <v>0.0007556</v>
       </c>
-      <c r="X241" s="1" t="n">
-        <v>0.0007463</v>
+      <c r="Y241" s="1" t="n">
+        <v>0.0007452</v>
       </c>
     </row>
     <row r="242">
@@ -18877,10 +19603,13 @@
         <v>0.1816</v>
       </c>
       <c r="W242" s="1" t="n">
+        <v>0.1815</v>
+      </c>
+      <c r="X242" s="1" t="n">
         <v>0.1847</v>
       </c>
-      <c r="X242" s="1" t="n">
-        <v>0.1816</v>
+      <c r="Y242" s="1" t="n">
+        <v>0.1815</v>
       </c>
     </row>
     <row r="243">
@@ -18953,10 +19682,13 @@
         <v>0.014715</v>
       </c>
       <c r="W243" s="1" t="n">
+        <v>0.014696</v>
+      </c>
+      <c r="X243" s="1" t="n">
         <v>0.014839</v>
       </c>
-      <c r="X243" s="1" t="n">
-        <v>0.014706</v>
+      <c r="Y243" s="1" t="n">
+        <v>0.014696</v>
       </c>
     </row>
     <row r="244">
@@ -19029,9 +19761,12 @@
         <v>3e-05</v>
       </c>
       <c r="W244" s="1" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="X244" s="1" t="n">
         <v>3.09e-05</v>
       </c>
-      <c r="X244" s="1" t="n">
+      <c r="Y244" s="1" t="n">
         <v>2.99e-05</v>
       </c>
     </row>
@@ -19105,9 +19840,12 @@
         <v>0.03509</v>
       </c>
       <c r="W245" s="1" t="n">
+        <v>0.03513</v>
+      </c>
+      <c r="X245" s="1" t="n">
         <v>0.03543</v>
       </c>
-      <c r="X245" s="1" t="n">
+      <c r="Y245" s="1" t="n">
         <v>0.03502</v>
       </c>
     </row>
@@ -19181,10 +19919,13 @@
         <v>0.08019</v>
       </c>
       <c r="W246" s="1" t="n">
+        <v>0.07982</v>
+      </c>
+      <c r="X246" s="1" t="n">
         <v>0.08076</v>
       </c>
-      <c r="X246" s="1" t="n">
-        <v>0.08018</v>
+      <c r="Y246" s="1" t="n">
+        <v>0.07982</v>
       </c>
     </row>
     <row r="247">
@@ -19257,10 +19998,13 @@
         <v>0.00709</v>
       </c>
       <c r="W247" s="1" t="n">
+        <v>0.00707</v>
+      </c>
+      <c r="X247" s="1" t="n">
         <v>0.007522</v>
       </c>
-      <c r="X247" s="1" t="n">
-        <v>0.00709</v>
+      <c r="Y247" s="1" t="n">
+        <v>0.00707</v>
       </c>
     </row>
     <row r="248">
@@ -19333,9 +20077,12 @@
         <v>0.09371</v>
       </c>
       <c r="W248" s="1" t="n">
+        <v>0.09372</v>
+      </c>
+      <c r="X248" s="1" t="n">
         <v>0.09855999999999999</v>
       </c>
-      <c r="X248" s="1" t="n">
+      <c r="Y248" s="1" t="n">
         <v>0.09239</v>
       </c>
     </row>
@@ -19409,10 +20156,13 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="W249" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="X249" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="X249" s="1" t="n">
-        <v>0.08699999999999999</v>
+      <c r="Y249" s="1" t="n">
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -19485,9 +20235,12 @@
         <v>0.03474</v>
       </c>
       <c r="W250" s="1" t="n">
+        <v>0.03478</v>
+      </c>
+      <c r="X250" s="1" t="n">
         <v>0.03521</v>
       </c>
-      <c r="X250" s="1" t="n">
+      <c r="Y250" s="1" t="n">
         <v>0.03469</v>
       </c>
     </row>
@@ -19561,10 +20314,13 @@
         <v>0.03875</v>
       </c>
       <c r="W251" s="1" t="n">
+        <v>0.03859</v>
+      </c>
+      <c r="X251" s="1" t="n">
         <v>0.04087</v>
       </c>
-      <c r="X251" s="1" t="n">
-        <v>0.03875</v>
+      <c r="Y251" s="1" t="n">
+        <v>0.03859</v>
       </c>
     </row>
     <row r="252">
@@ -19637,9 +20393,12 @@
         <v>0.0881</v>
       </c>
       <c r="W252" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="X252" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="X252" s="1" t="n">
+      <c r="Y252" s="1" t="n">
         <v>0.0876</v>
       </c>
     </row>
@@ -19713,10 +20472,13 @@
         <v>4.059</v>
       </c>
       <c r="W253" s="1" t="n">
+        <v>4.056</v>
+      </c>
+      <c r="X253" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="X253" s="1" t="n">
-        <v>4.058</v>
+      <c r="Y253" s="1" t="n">
+        <v>4.056</v>
       </c>
     </row>
     <row r="254">
@@ -19789,9 +20551,12 @@
         <v>0.1865</v>
       </c>
       <c r="W254" s="1" t="n">
+        <v>0.1865</v>
+      </c>
+      <c r="X254" s="1" t="n">
         <v>0.1877</v>
       </c>
-      <c r="X254" s="1" t="n">
+      <c r="Y254" s="1" t="n">
         <v>0.1865</v>
       </c>
     </row>
@@ -19865,9 +20630,12 @@
         <v>0.07192999999999999</v>
       </c>
       <c r="W255" s="1" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="X255" s="1" t="n">
         <v>0.07283000000000001</v>
       </c>
-      <c r="X255" s="1" t="n">
+      <c r="Y255" s="1" t="n">
         <v>0.07174</v>
       </c>
     </row>
@@ -19941,9 +20709,12 @@
         <v>0.0183</v>
       </c>
       <c r="W256" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="X256" s="1" t="n">
         <v>0.01848</v>
       </c>
-      <c r="X256" s="1" t="n">
+      <c r="Y256" s="1" t="n">
         <v>0.01816</v>
       </c>
     </row>
@@ -20017,9 +20788,12 @@
         <v>5.938</v>
       </c>
       <c r="W257" s="1" t="n">
+        <v>5.938</v>
+      </c>
+      <c r="X257" s="1" t="n">
         <v>5.964</v>
       </c>
-      <c r="X257" s="1" t="n">
+      <c r="Y257" s="1" t="n">
         <v>5.933</v>
       </c>
     </row>
@@ -20093,9 +20867,12 @@
         <v>0.2582</v>
       </c>
       <c r="W258" s="1" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="X258" s="1" t="n">
         <v>0.2658</v>
       </c>
-      <c r="X258" s="1" t="n">
+      <c r="Y258" s="1" t="n">
         <v>0.2582</v>
       </c>
     </row>
@@ -20169,9 +20946,12 @@
         <v>0.1357</v>
       </c>
       <c r="W259" s="1" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="X259" s="1" t="n">
         <v>0.1369</v>
       </c>
-      <c r="X259" s="1" t="n">
+      <c r="Y259" s="1" t="n">
         <v>0.1352</v>
       </c>
     </row>
@@ -20245,9 +21025,12 @@
         <v>0.30691</v>
       </c>
       <c r="W260" s="1" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="X260" s="1" t="n">
         <v>0.30794</v>
       </c>
-      <c r="X260" s="1" t="n">
+      <c r="Y260" s="1" t="n">
         <v>0.30501</v>
       </c>
     </row>
@@ -20321,9 +21104,12 @@
         <v>0.09872</v>
       </c>
       <c r="W261" s="1" t="n">
+        <v>0.09863</v>
+      </c>
+      <c r="X261" s="1" t="n">
         <v>0.10011</v>
       </c>
-      <c r="X261" s="1" t="n">
+      <c r="Y261" s="1" t="n">
         <v>0.09787</v>
       </c>
     </row>
@@ -20397,9 +21183,12 @@
         <v>0.5403</v>
       </c>
       <c r="W262" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X262" s="1" t="n">
         <v>0.544</v>
       </c>
-      <c r="X262" s="1" t="n">
+      <c r="Y262" s="1" t="n">
         <v>0.5377999999999999</v>
       </c>
     </row>
@@ -20473,9 +21262,12 @@
         <v>0.2891</v>
       </c>
       <c r="W263" s="1" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="X263" s="1" t="n">
         <v>0.2937</v>
       </c>
-      <c r="X263" s="1" t="n">
+      <c r="Y263" s="1" t="n">
         <v>0.2877</v>
       </c>
     </row>
@@ -20549,9 +21341,12 @@
         <v>0.967</v>
       </c>
       <c r="W264" s="1" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="X264" s="1" t="n">
         <v>0.989</v>
       </c>
-      <c r="X264" s="1" t="n">
+      <c r="Y264" s="1" t="n">
         <v>0.948</v>
       </c>
     </row>
@@ -20625,9 +21420,12 @@
         <v>0.5339</v>
       </c>
       <c r="W265" s="1" t="n">
+        <v>0.5347</v>
+      </c>
+      <c r="X265" s="1" t="n">
         <v>0.5431</v>
       </c>
-      <c r="X265" s="1" t="n">
+      <c r="Y265" s="1" t="n">
         <v>0.5339</v>
       </c>
     </row>
@@ -20701,9 +21499,12 @@
         <v>0.07359</v>
       </c>
       <c r="W266" s="1" t="n">
+        <v>0.07346999999999999</v>
+      </c>
+      <c r="X266" s="1" t="n">
         <v>0.074</v>
       </c>
-      <c r="X266" s="1" t="n">
+      <c r="Y266" s="1" t="n">
         <v>0.07339</v>
       </c>
     </row>
@@ -20777,10 +21578,13 @@
         <v>0.02126</v>
       </c>
       <c r="W267" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="X267" s="1" t="n">
         <v>0.02188</v>
       </c>
-      <c r="X267" s="1" t="n">
-        <v>0.02126</v>
+      <c r="Y267" s="1" t="n">
+        <v>0.02116</v>
       </c>
     </row>
     <row r="268">
@@ -20853,9 +21657,12 @@
         <v>0.01612</v>
       </c>
       <c r="W268" s="1" t="n">
+        <v>0.01609</v>
+      </c>
+      <c r="X268" s="1" t="n">
         <v>0.01634</v>
       </c>
-      <c r="X268" s="1" t="n">
+      <c r="Y268" s="1" t="n">
         <v>0.01603</v>
       </c>
     </row>
@@ -20929,9 +21736,12 @@
         <v>0.003796</v>
       </c>
       <c r="W269" s="1" t="n">
+        <v>0.003794</v>
+      </c>
+      <c r="X269" s="1" t="n">
         <v>0.003804</v>
       </c>
-      <c r="X269" s="1" t="n">
+      <c r="Y269" s="1" t="n">
         <v>0.003702</v>
       </c>
     </row>
@@ -21005,9 +21815,12 @@
         <v>0.00762</v>
       </c>
       <c r="W270" s="1" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="X270" s="1" t="n">
         <v>0.00787</v>
       </c>
-      <c r="X270" s="1" t="n">
+      <c r="Y270" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -21081,9 +21894,12 @@
         <v>0.05474</v>
       </c>
       <c r="W271" s="1" t="n">
+        <v>0.05474</v>
+      </c>
+      <c r="X271" s="1" t="n">
         <v>0.05525</v>
       </c>
-      <c r="X271" s="1" t="n">
+      <c r="Y271" s="1" t="n">
         <v>0.0547</v>
       </c>
     </row>
@@ -21157,9 +21973,12 @@
         <v>2.281</v>
       </c>
       <c r="W272" s="1" t="n">
+        <v>2.292</v>
+      </c>
+      <c r="X272" s="1" t="n">
         <v>2.318</v>
       </c>
-      <c r="X272" s="1" t="n">
+      <c r="Y272" s="1" t="n">
         <v>2.267</v>
       </c>
     </row>
@@ -21233,9 +22052,12 @@
         <v>0.05448</v>
       </c>
       <c r="W273" s="1" t="n">
+        <v>0.05445</v>
+      </c>
+      <c r="X273" s="1" t="n">
         <v>0.05504</v>
       </c>
-      <c r="X273" s="1" t="n">
+      <c r="Y273" s="1" t="n">
         <v>0.05431</v>
       </c>
     </row>
@@ -21309,9 +22131,12 @@
         <v>0.02346</v>
       </c>
       <c r="W274" s="1" t="n">
+        <v>0.02346</v>
+      </c>
+      <c r="X274" s="1" t="n">
         <v>0.02349</v>
       </c>
-      <c r="X274" s="1" t="n">
+      <c r="Y274" s="1" t="n">
         <v>0.02283</v>
       </c>
     </row>
@@ -21385,9 +22210,12 @@
         <v>1.174</v>
       </c>
       <c r="W275" s="1" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="X275" s="1" t="n">
         <v>1.193</v>
       </c>
-      <c r="X275" s="1" t="n">
+      <c r="Y275" s="1" t="n">
         <v>1.169</v>
       </c>
     </row>
@@ -21461,9 +22289,12 @@
         <v>0.2716</v>
       </c>
       <c r="W276" s="1" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="X276" s="1" t="n">
         <v>0.2732</v>
       </c>
-      <c r="X276" s="1" t="n">
+      <c r="Y276" s="1" t="n">
         <v>0.2706</v>
       </c>
     </row>
@@ -21537,9 +22368,12 @@
         <v>0.922</v>
       </c>
       <c r="W277" s="1" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="X277" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="X277" s="1" t="n">
+      <c r="Y277" s="1" t="n">
         <v>0.919</v>
       </c>
     </row>
@@ -21613,9 +22447,12 @@
         <v>0.6262</v>
       </c>
       <c r="W278" s="1" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="X278" s="1" t="n">
         <v>0.6294999999999999</v>
       </c>
-      <c r="X278" s="1" t="n">
+      <c r="Y278" s="1" t="n">
         <v>0.6218</v>
       </c>
     </row>
@@ -21689,10 +22526,13 @@
         <v>0.001325</v>
       </c>
       <c r="W279" s="1" t="n">
+        <v>0.001324</v>
+      </c>
+      <c r="X279" s="1" t="n">
         <v>0.001362</v>
       </c>
-      <c r="X279" s="1" t="n">
-        <v>0.001325</v>
+      <c r="Y279" s="1" t="n">
+        <v>0.001324</v>
       </c>
     </row>
     <row r="280">
@@ -21765,9 +22605,12 @@
         <v>0.005588</v>
       </c>
       <c r="W280" s="1" t="n">
+        <v>0.005579</v>
+      </c>
+      <c r="X280" s="1" t="n">
         <v>0.005613</v>
       </c>
-      <c r="X280" s="1" t="n">
+      <c r="Y280" s="1" t="n">
         <v>0.00554</v>
       </c>
     </row>
@@ -21841,9 +22684,12 @@
         <v>1.525</v>
       </c>
       <c r="W281" s="1" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="X281" s="1" t="n">
         <v>1.526</v>
       </c>
-      <c r="X281" s="1" t="n">
+      <c r="Y281" s="1" t="n">
         <v>1.515</v>
       </c>
     </row>
@@ -21917,9 +22763,12 @@
         <v>28.2</v>
       </c>
       <c r="W282" s="1" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="X282" s="1" t="n">
         <v>28.47</v>
       </c>
-      <c r="X282" s="1" t="n">
+      <c r="Y282" s="1" t="n">
         <v>28.2</v>
       </c>
     </row>
@@ -21993,9 +22842,12 @@
         <v>0.12893</v>
       </c>
       <c r="W283" s="1" t="n">
+        <v>0.12886</v>
+      </c>
+      <c r="X283" s="1" t="n">
         <v>0.12942</v>
       </c>
-      <c r="X283" s="1" t="n">
+      <c r="Y283" s="1" t="n">
         <v>0.12788</v>
       </c>
     </row>
@@ -22069,10 +22921,13 @@
         <v>0.01101</v>
       </c>
       <c r="W284" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="X284" s="1" t="n">
         <v>0.01116</v>
       </c>
-      <c r="X284" s="1" t="n">
-        <v>0.01101</v>
+      <c r="Y284" s="1" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="285">
@@ -22145,9 +23000,12 @@
         <v>6.553</v>
       </c>
       <c r="W285" s="1" t="n">
+        <v>6.552</v>
+      </c>
+      <c r="X285" s="1" t="n">
         <v>6.601</v>
       </c>
-      <c r="X285" s="1" t="n">
+      <c r="Y285" s="1" t="n">
         <v>6.487</v>
       </c>
     </row>
@@ -22221,9 +23079,12 @@
         <v>0.0183</v>
       </c>
       <c r="W286" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="X286" s="1" t="n">
         <v>0.01857</v>
       </c>
-      <c r="X286" s="1" t="n">
+      <c r="Y286" s="1" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -22297,9 +23158,12 @@
         <v>0.008363000000000001</v>
       </c>
       <c r="W287" s="1" t="n">
+        <v>0.008364999999999999</v>
+      </c>
+      <c r="X287" s="1" t="n">
         <v>0.008486</v>
       </c>
-      <c r="X287" s="1" t="n">
+      <c r="Y287" s="1" t="n">
         <v>0.008312999999999999</v>
       </c>
     </row>
@@ -22373,9 +23237,12 @@
         <v>0.3743</v>
       </c>
       <c r="W288" s="1" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="X288" s="1" t="n">
         <v>0.3929</v>
       </c>
-      <c r="X288" s="1" t="n">
+      <c r="Y288" s="1" t="n">
         <v>0.3743</v>
       </c>
     </row>
@@ -22449,9 +23316,12 @@
         <v>0.009773</v>
       </c>
       <c r="W289" s="1" t="n">
+        <v>0.009790999999999999</v>
+      </c>
+      <c r="X289" s="1" t="n">
         <v>0.010539</v>
       </c>
-      <c r="X289" s="1" t="n">
+      <c r="Y289" s="1" t="n">
         <v>0.00974</v>
       </c>
     </row>
@@ -22525,9 +23395,12 @@
         <v>0.02586</v>
       </c>
       <c r="W290" s="1" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="X290" s="1" t="n">
         <v>0.02626</v>
       </c>
-      <c r="X290" s="1" t="n">
+      <c r="Y290" s="1" t="n">
         <v>0.02585</v>
       </c>
     </row>
@@ -22601,9 +23474,12 @@
         <v>0.095</v>
       </c>
       <c r="W291" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="X291" s="1" t="n">
         <v>0.097</v>
       </c>
-      <c r="X291" s="1" t="n">
+      <c r="Y291" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -22677,9 +23553,12 @@
         <v>0.28671</v>
       </c>
       <c r="W292" s="1" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="X292" s="1" t="n">
         <v>0.28799</v>
       </c>
-      <c r="X292" s="1" t="n">
+      <c r="Y292" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -22753,9 +23632,12 @@
         <v>0.01516</v>
       </c>
       <c r="W293" s="1" t="n">
+        <v>0.01517</v>
+      </c>
+      <c r="X293" s="1" t="n">
         <v>0.01556</v>
       </c>
-      <c r="X293" s="1" t="n">
+      <c r="Y293" s="1" t="n">
         <v>0.01516</v>
       </c>
     </row>
@@ -22829,9 +23711,12 @@
         <v>0.00343</v>
       </c>
       <c r="W294" s="1" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="X294" s="1" t="n">
         <v>0.003465</v>
       </c>
-      <c r="X294" s="1" t="n">
+      <c r="Y294" s="1" t="n">
         <v>0.003381</v>
       </c>
     </row>
@@ -22905,10 +23790,13 @@
         <v>0.042352</v>
       </c>
       <c r="W295" s="1" t="n">
+        <v>0.042061</v>
+      </c>
+      <c r="X295" s="1" t="n">
         <v>0.043723</v>
       </c>
-      <c r="X295" s="1" t="n">
-        <v>0.042232</v>
+      <c r="Y295" s="1" t="n">
+        <v>0.042061</v>
       </c>
     </row>
     <row r="296">
@@ -22981,9 +23869,12 @@
         <v>0.02844</v>
       </c>
       <c r="W296" s="1" t="n">
+        <v>0.02845</v>
+      </c>
+      <c r="X296" s="1" t="n">
         <v>0.03055</v>
       </c>
-      <c r="X296" s="1" t="n">
+      <c r="Y296" s="1" t="n">
         <v>0.02844</v>
       </c>
     </row>
@@ -23057,9 +23948,12 @@
         <v>0.03806</v>
       </c>
       <c r="W297" s="1" t="n">
+        <v>0.03785</v>
+      </c>
+      <c r="X297" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="X297" s="1" t="n">
+      <c r="Y297" s="1" t="n">
         <v>0.03773</v>
       </c>
     </row>
@@ -23133,10 +24027,13 @@
         <v>0.08271000000000001</v>
       </c>
       <c r="W298" s="1" t="n">
+        <v>0.08239</v>
+      </c>
+      <c r="X298" s="1" t="n">
         <v>0.08407000000000001</v>
       </c>
-      <c r="X298" s="1" t="n">
-        <v>0.08248</v>
+      <c r="Y298" s="1" t="n">
+        <v>0.08239</v>
       </c>
     </row>
     <row r="299">
@@ -23209,9 +24106,12 @@
         <v>0.00762</v>
       </c>
       <c r="W299" s="1" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="X299" s="1" t="n">
         <v>0.00779</v>
       </c>
-      <c r="X299" s="1" t="n">
+      <c r="Y299" s="1" t="n">
         <v>0.0076</v>
       </c>
     </row>
@@ -23285,10 +24185,13 @@
         <v>0.01489</v>
       </c>
       <c r="W300" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="X300" s="1" t="n">
         <v>0.01532</v>
       </c>
-      <c r="X300" s="1" t="n">
-        <v>0.01489</v>
+      <c r="Y300" s="1" t="n">
+        <v>0.01486</v>
       </c>
     </row>
     <row r="301">
@@ -23361,9 +24264,12 @@
         <v>0.1403</v>
       </c>
       <c r="W301" s="1" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="X301" s="1" t="n">
         <v>0.142</v>
       </c>
-      <c r="X301" s="1" t="n">
+      <c r="Y301" s="1" t="n">
         <v>0.1399</v>
       </c>
     </row>
@@ -23437,9 +24343,12 @@
         <v>0.000624</v>
       </c>
       <c r="W302" s="1" t="n">
+        <v>0.0006228</v>
+      </c>
+      <c r="X302" s="1" t="n">
         <v>0.0006538</v>
       </c>
-      <c r="X302" s="1" t="n">
+      <c r="Y302" s="1" t="n">
         <v>0.0006217</v>
       </c>
     </row>
@@ -23513,9 +24422,12 @@
         <v>0.0622</v>
       </c>
       <c r="W303" s="1" t="n">
+        <v>0.06214</v>
+      </c>
+      <c r="X303" s="1" t="n">
         <v>0.06261</v>
       </c>
-      <c r="X303" s="1" t="n">
+      <c r="Y303" s="1" t="n">
         <v>0.06207</v>
       </c>
     </row>
@@ -23589,9 +24501,12 @@
         <v>0.0001618</v>
       </c>
       <c r="W304" s="1" t="n">
+        <v>0.0001618</v>
+      </c>
+      <c r="X304" s="1" t="n">
         <v>0.000164</v>
       </c>
-      <c r="X304" s="1" t="n">
+      <c r="Y304" s="1" t="n">
         <v>0.0001618</v>
       </c>
     </row>
@@ -23665,9 +24580,12 @@
         <v>0.0606</v>
       </c>
       <c r="W305" s="1" t="n">
+        <v>0.06075</v>
+      </c>
+      <c r="X305" s="1" t="n">
         <v>0.06148</v>
       </c>
-      <c r="X305" s="1" t="n">
+      <c r="Y305" s="1" t="n">
         <v>0.0606</v>
       </c>
     </row>
@@ -23741,9 +24659,12 @@
         <v>0.022281</v>
       </c>
       <c r="W306" s="1" t="n">
+        <v>0.022322</v>
+      </c>
+      <c r="X306" s="1" t="n">
         <v>0.022667</v>
       </c>
-      <c r="X306" s="1" t="n">
+      <c r="Y306" s="1" t="n">
         <v>0.022133</v>
       </c>
     </row>
@@ -23817,9 +24738,12 @@
         <v>0.02303</v>
       </c>
       <c r="W307" s="1" t="n">
+        <v>0.02281</v>
+      </c>
+      <c r="X307" s="1" t="n">
         <v>0.02423</v>
       </c>
-      <c r="X307" s="1" t="n">
+      <c r="Y307" s="1" t="n">
         <v>0.02278</v>
       </c>
     </row>
@@ -23893,9 +24817,12 @@
         <v>0.000409</v>
       </c>
       <c r="W308" s="1" t="n">
+        <v>0.000409</v>
+      </c>
+      <c r="X308" s="1" t="n">
         <v>0.000412</v>
       </c>
-      <c r="X308" s="1" t="n">
+      <c r="Y308" s="1" t="n">
         <v>0.000409</v>
       </c>
     </row>
@@ -23969,9 +24896,12 @@
         <v>0.0896</v>
       </c>
       <c r="W309" s="1" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="X309" s="1" t="n">
         <v>0.08989999999999999</v>
       </c>
-      <c r="X309" s="1" t="n">
+      <c r="Y309" s="1" t="n">
         <v>0.0896</v>
       </c>
     </row>
@@ -24045,9 +24975,12 @@
         <v>0.3704</v>
       </c>
       <c r="W310" s="1" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X310" s="1" t="n">
         <v>0.3882</v>
       </c>
-      <c r="X310" s="1" t="n">
+      <c r="Y310" s="1" t="n">
         <v>0.3664</v>
       </c>
     </row>
@@ -24121,9 +25054,12 @@
         <v>0.0353</v>
       </c>
       <c r="W311" s="1" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="X311" s="1" t="n">
         <v>0.0358</v>
       </c>
-      <c r="X311" s="1" t="n">
+      <c r="Y311" s="1" t="n">
         <v>0.0353</v>
       </c>
     </row>
@@ -24197,9 +25133,12 @@
         <v>0.02433</v>
       </c>
       <c r="W312" s="1" t="n">
+        <v>0.02432</v>
+      </c>
+      <c r="X312" s="1" t="n">
         <v>0.02485</v>
       </c>
-      <c r="X312" s="1" t="n">
+      <c r="Y312" s="1" t="n">
         <v>0.02415</v>
       </c>
     </row>
@@ -24273,9 +25212,12 @@
         <v>0.0408</v>
       </c>
       <c r="W313" s="1" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="X313" s="1" t="n">
         <v>0.04147</v>
       </c>
-      <c r="X313" s="1" t="n">
+      <c r="Y313" s="1" t="n">
         <v>0.0408</v>
       </c>
     </row>
@@ -24349,9 +25291,12 @@
         <v>3.932</v>
       </c>
       <c r="W314" s="1" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="X314" s="1" t="n">
         <v>4.015</v>
       </c>
-      <c r="X314" s="1" t="n">
+      <c r="Y314" s="1" t="n">
         <v>3.932</v>
       </c>
     </row>
@@ -24425,9 +25370,12 @@
         <v>0.159</v>
       </c>
       <c r="W315" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="X315" s="1" t="n">
         <v>0.1605</v>
       </c>
-      <c r="X315" s="1" t="n">
+      <c r="Y315" s="1" t="n">
         <v>0.1589</v>
       </c>
     </row>
@@ -24501,9 +25449,12 @@
         <v>0.08993</v>
       </c>
       <c r="W316" s="1" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="X316" s="1" t="n">
         <v>0.09374</v>
       </c>
-      <c r="X316" s="1" t="n">
+      <c r="Y316" s="1" t="n">
         <v>0.08805</v>
       </c>
     </row>
@@ -24577,9 +25528,12 @@
         <v>0.06783</v>
       </c>
       <c r="W317" s="1" t="n">
+        <v>0.06791999999999999</v>
+      </c>
+      <c r="X317" s="1" t="n">
         <v>0.0687</v>
       </c>
-      <c r="X317" s="1" t="n">
+      <c r="Y317" s="1" t="n">
         <v>0.06783</v>
       </c>
     </row>
@@ -24653,9 +25607,12 @@
         <v>0.012456</v>
       </c>
       <c r="W318" s="1" t="n">
+        <v>0.012511</v>
+      </c>
+      <c r="X318" s="1" t="n">
         <v>0.01272</v>
       </c>
-      <c r="X318" s="1" t="n">
+      <c r="Y318" s="1" t="n">
         <v>0.012382</v>
       </c>
     </row>
@@ -24729,10 +25686,13 @@
         <v>0.001129</v>
       </c>
       <c r="W319" s="1" t="n">
+        <v>0.001128</v>
+      </c>
+      <c r="X319" s="1" t="n">
         <v>0.00114</v>
       </c>
-      <c r="X319" s="1" t="n">
-        <v>0.001129</v>
+      <c r="Y319" s="1" t="n">
+        <v>0.001128</v>
       </c>
     </row>
     <row r="320">
@@ -24808,6 +25768,9 @@
         <v>0.0633</v>
       </c>
       <c r="X320" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="Y320" s="1" t="n">
         <v>0.0629</v>
       </c>
     </row>
@@ -24881,10 +25844,13 @@
         <v>0.00523</v>
       </c>
       <c r="W321" s="1" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="X321" s="1" t="n">
         <v>0.00528</v>
       </c>
-      <c r="X321" s="1" t="n">
-        <v>0.00523</v>
+      <c r="Y321" s="1" t="n">
+        <v>0.0052</v>
       </c>
     </row>
     <row r="322">
@@ -24957,9 +25923,12 @@
         <v>0.111</v>
       </c>
       <c r="W322" s="1" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="X322" s="1" t="n">
         <v>0.1124</v>
       </c>
-      <c r="X322" s="1" t="n">
+      <c r="Y322" s="1" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -25033,9 +26002,12 @@
         <v>0.04336</v>
       </c>
       <c r="W323" s="1" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="X323" s="1" t="n">
         <v>0.04413</v>
       </c>
-      <c r="X323" s="1" t="n">
+      <c r="Y323" s="1" t="n">
         <v>0.04171</v>
       </c>
     </row>
@@ -25109,9 +26081,12 @@
         <v>0.01776</v>
       </c>
       <c r="W324" s="1" t="n">
+        <v>0.01778</v>
+      </c>
+      <c r="X324" s="1" t="n">
         <v>0.01794</v>
       </c>
-      <c r="X324" s="1" t="n">
+      <c r="Y324" s="1" t="n">
         <v>0.01767</v>
       </c>
     </row>
@@ -25185,9 +26160,12 @@
         <v>0.005628</v>
       </c>
       <c r="W325" s="1" t="n">
+        <v>0.005636</v>
+      </c>
+      <c r="X325" s="1" t="n">
         <v>0.005699</v>
       </c>
-      <c r="X325" s="1" t="n">
+      <c r="Y325" s="1" t="n">
         <v>0.005628</v>
       </c>
     </row>
@@ -25261,10 +26239,13 @@
         <v>0.00175</v>
       </c>
       <c r="W326" s="1" t="n">
+        <v>0.001733</v>
+      </c>
+      <c r="X326" s="1" t="n">
         <v>0.001779</v>
       </c>
-      <c r="X326" s="1" t="n">
-        <v>0.00175</v>
+      <c r="Y326" s="1" t="n">
+        <v>0.001733</v>
       </c>
     </row>
     <row r="327">
@@ -25337,9 +26318,12 @@
         <v>0.04034</v>
       </c>
       <c r="W327" s="1" t="n">
+        <v>0.04032</v>
+      </c>
+      <c r="X327" s="1" t="n">
         <v>0.04085</v>
       </c>
-      <c r="X327" s="1" t="n">
+      <c r="Y327" s="1" t="n">
         <v>0.04011</v>
       </c>
     </row>
@@ -25413,10 +26397,13 @@
         <v>0.053537</v>
       </c>
       <c r="W328" s="1" t="n">
+        <v>0.053472</v>
+      </c>
+      <c r="X328" s="1" t="n">
         <v>0.054034</v>
       </c>
-      <c r="X328" s="1" t="n">
-        <v>0.053492</v>
+      <c r="Y328" s="1" t="n">
+        <v>0.053472</v>
       </c>
     </row>
     <row r="329">
@@ -25489,9 +26476,12 @@
         <v>0.2769</v>
       </c>
       <c r="W329" s="1" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="X329" s="1" t="n">
         <v>0.2795</v>
       </c>
-      <c r="X329" s="1" t="n">
+      <c r="Y329" s="1" t="n">
         <v>0.2769</v>
       </c>
     </row>
@@ -25565,9 +26555,12 @@
         <v>0.1585</v>
       </c>
       <c r="W330" s="1" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="X330" s="1" t="n">
         <v>0.1601</v>
       </c>
-      <c r="X330" s="1" t="n">
+      <c r="Y330" s="1" t="n">
         <v>0.1585</v>
       </c>
     </row>
@@ -25641,9 +26634,12 @@
         <v>0.05352</v>
       </c>
       <c r="W331" s="1" t="n">
+        <v>0.05372</v>
+      </c>
+      <c r="X331" s="1" t="n">
         <v>0.05385</v>
       </c>
-      <c r="X331" s="1" t="n">
+      <c r="Y331" s="1" t="n">
         <v>0.05348</v>
       </c>
     </row>
@@ -25717,9 +26713,12 @@
         <v>0.3616</v>
       </c>
       <c r="W332" s="1" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="X332" s="1" t="n">
         <v>0.3624</v>
       </c>
-      <c r="X332" s="1" t="n">
+      <c r="Y332" s="1" t="n">
         <v>0.3594</v>
       </c>
     </row>
@@ -25793,9 +26792,12 @@
         <v>0.0306</v>
       </c>
       <c r="W333" s="1" t="n">
+        <v>0.03057</v>
+      </c>
+      <c r="X333" s="1" t="n">
         <v>0.03063</v>
       </c>
-      <c r="X333" s="1" t="n">
+      <c r="Y333" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -25869,9 +26871,12 @@
         <v>0.01737</v>
       </c>
       <c r="W334" s="1" t="n">
+        <v>0.01741</v>
+      </c>
+      <c r="X334" s="1" t="n">
         <v>0.01868</v>
       </c>
-      <c r="X334" s="1" t="n">
+      <c r="Y334" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -25945,9 +26950,12 @@
         <v>0.0578</v>
       </c>
       <c r="W335" s="1" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="X335" s="1" t="n">
         <v>0.0583</v>
       </c>
-      <c r="X335" s="1" t="n">
+      <c r="Y335" s="1" t="n">
         <v>0.0574</v>
       </c>
     </row>
@@ -26021,9 +27029,12 @@
         <v>0.08910999999999999</v>
       </c>
       <c r="W336" s="1" t="n">
+        <v>0.08962000000000001</v>
+      </c>
+      <c r="X336" s="1" t="n">
         <v>0.09197</v>
       </c>
-      <c r="X336" s="1" t="n">
+      <c r="Y336" s="1" t="n">
         <v>0.08910999999999999</v>
       </c>
     </row>
@@ -26097,9 +27108,12 @@
         <v>0.17945</v>
       </c>
       <c r="W337" s="1" t="n">
+        <v>0.17892</v>
+      </c>
+      <c r="X337" s="1" t="n">
         <v>0.18293</v>
       </c>
-      <c r="X337" s="1" t="n">
+      <c r="Y337" s="1" t="n">
         <v>0.17441</v>
       </c>
     </row>
@@ -26173,9 +27187,12 @@
         <v>0.02078</v>
       </c>
       <c r="W338" s="1" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="X338" s="1" t="n">
         <v>0.02135</v>
       </c>
-      <c r="X338" s="1" t="n">
+      <c r="Y338" s="1" t="n">
         <v>0.02074</v>
       </c>
     </row>
@@ -26249,9 +27266,12 @@
         <v>0.1318</v>
       </c>
       <c r="W339" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="X339" s="1" t="n">
         <v>0.1319</v>
       </c>
-      <c r="X339" s="1" t="n">
+      <c r="Y339" s="1" t="n">
         <v>0.1311</v>
       </c>
     </row>
@@ -26325,10 +27345,13 @@
         <v>0.007908999999999999</v>
       </c>
       <c r="W340" s="1" t="n">
+        <v>0.007889</v>
+      </c>
+      <c r="X340" s="1" t="n">
         <v>0.008114</v>
       </c>
-      <c r="X340" s="1" t="n">
-        <v>0.007901999999999999</v>
+      <c r="Y340" s="1" t="n">
+        <v>0.007889</v>
       </c>
     </row>
     <row r="341">
@@ -26401,9 +27424,12 @@
         <v>4.404</v>
       </c>
       <c r="W341" s="1" t="n">
+        <v>4.402</v>
+      </c>
+      <c r="X341" s="1" t="n">
         <v>4.422</v>
       </c>
-      <c r="X341" s="1" t="n">
+      <c r="Y341" s="1" t="n">
         <v>4.382</v>
       </c>
     </row>
@@ -26477,9 +27503,12 @@
         <v>0.18732</v>
       </c>
       <c r="W342" s="1" t="n">
+        <v>0.18789</v>
+      </c>
+      <c r="X342" s="1" t="n">
         <v>0.19496</v>
       </c>
-      <c r="X342" s="1" t="n">
+      <c r="Y342" s="1" t="n">
         <v>0.18732</v>
       </c>
     </row>
@@ -26553,9 +27582,12 @@
         <v>0.08329</v>
       </c>
       <c r="W343" s="1" t="n">
+        <v>0.08323999999999999</v>
+      </c>
+      <c r="X343" s="1" t="n">
         <v>0.08373999999999999</v>
       </c>
-      <c r="X343" s="1" t="n">
+      <c r="Y343" s="1" t="n">
         <v>0.08266999999999999</v>
       </c>
     </row>
@@ -26629,9 +27661,12 @@
         <v>0.182</v>
       </c>
       <c r="W344" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="X344" s="1" t="n">
         <v>0.1842</v>
       </c>
-      <c r="X344" s="1" t="n">
+      <c r="Y344" s="1" t="n">
         <v>0.1813</v>
       </c>
     </row>
@@ -26705,9 +27740,12 @@
         <v>0.003214</v>
       </c>
       <c r="W345" s="1" t="n">
+        <v>0.003214</v>
+      </c>
+      <c r="X345" s="1" t="n">
         <v>0.003265</v>
       </c>
-      <c r="X345" s="1" t="n">
+      <c r="Y345" s="1" t="n">
         <v>0.003214</v>
       </c>
     </row>
@@ -26781,9 +27819,12 @@
         <v>0.09093999999999999</v>
       </c>
       <c r="W346" s="1" t="n">
+        <v>0.09117</v>
+      </c>
+      <c r="X346" s="1" t="n">
         <v>0.09209000000000001</v>
       </c>
-      <c r="X346" s="1" t="n">
+      <c r="Y346" s="1" t="n">
         <v>0.09075</v>
       </c>
     </row>
@@ -26857,9 +27898,12 @@
         <v>2.24</v>
       </c>
       <c r="W347" s="1" t="n">
+        <v>2.238</v>
+      </c>
+      <c r="X347" s="1" t="n">
         <v>2.26</v>
       </c>
-      <c r="X347" s="1" t="n">
+      <c r="Y347" s="1" t="n">
         <v>2.235</v>
       </c>
     </row>
@@ -26933,10 +27977,13 @@
         <v>0.3014</v>
       </c>
       <c r="W348" s="1" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="X348" s="1" t="n">
         <v>0.3061</v>
       </c>
-      <c r="X348" s="1" t="n">
-        <v>0.3014</v>
+      <c r="Y348" s="1" t="n">
+        <v>0.3012</v>
       </c>
     </row>
     <row r="349">
@@ -27009,9 +28056,12 @@
         <v>0.03002</v>
       </c>
       <c r="W349" s="1" t="n">
+        <v>0.02988</v>
+      </c>
+      <c r="X349" s="1" t="n">
         <v>0.03002</v>
       </c>
-      <c r="X349" s="1" t="n">
+      <c r="Y349" s="1" t="n">
         <v>0.02945</v>
       </c>
     </row>
@@ -27085,9 +28135,12 @@
         <v>0.1276</v>
       </c>
       <c r="W350" s="1" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="X350" s="1" t="n">
         <v>0.1281</v>
       </c>
-      <c r="X350" s="1" t="n">
+      <c r="Y350" s="1" t="n">
         <v>0.1271</v>
       </c>
     </row>
@@ -27161,10 +28214,13 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="W351" s="1" t="n">
+        <v>0.06559</v>
+      </c>
+      <c r="X351" s="1" t="n">
         <v>0.06804</v>
       </c>
-      <c r="X351" s="1" t="n">
-        <v>0.06569999999999999</v>
+      <c r="Y351" s="1" t="n">
+        <v>0.06559</v>
       </c>
     </row>
     <row r="352">
@@ -27237,10 +28293,13 @@
         <v>0.06208</v>
       </c>
       <c r="W352" s="1" t="n">
+        <v>0.06203</v>
+      </c>
+      <c r="X352" s="1" t="n">
         <v>0.06259000000000001</v>
       </c>
-      <c r="X352" s="1" t="n">
-        <v>0.06208</v>
+      <c r="Y352" s="1" t="n">
+        <v>0.06203</v>
       </c>
     </row>
     <row r="353">
@@ -27313,9 +28372,12 @@
         <v>0.06294</v>
       </c>
       <c r="W353" s="1" t="n">
+        <v>0.06292</v>
+      </c>
+      <c r="X353" s="1" t="n">
         <v>0.0639</v>
       </c>
-      <c r="X353" s="1" t="n">
+      <c r="Y353" s="1" t="n">
         <v>0.06270000000000001</v>
       </c>
     </row>
@@ -27389,10 +28451,13 @@
         <v>0.10311</v>
       </c>
       <c r="W354" s="1" t="n">
+        <v>0.10261</v>
+      </c>
+      <c r="X354" s="1" t="n">
         <v>0.10844</v>
       </c>
-      <c r="X354" s="1" t="n">
-        <v>0.10311</v>
+      <c r="Y354" s="1" t="n">
+        <v>0.10261</v>
       </c>
     </row>
     <row r="355">
@@ -27465,9 +28530,12 @@
         <v>0.0897</v>
       </c>
       <c r="W355" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="X355" s="1" t="n">
         <v>0.09039999999999999</v>
       </c>
-      <c r="X355" s="1" t="n">
+      <c r="Y355" s="1" t="n">
         <v>0.0897</v>
       </c>
     </row>
@@ -27541,9 +28609,12 @@
         <v>0.0697</v>
       </c>
       <c r="W356" s="1" t="n">
+        <v>0.06972</v>
+      </c>
+      <c r="X356" s="1" t="n">
         <v>0.07055</v>
       </c>
-      <c r="X356" s="1" t="n">
+      <c r="Y356" s="1" t="n">
         <v>0.06905</v>
       </c>
     </row>
@@ -27617,9 +28688,12 @@
         <v>0.4507</v>
       </c>
       <c r="W357" s="1" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="X357" s="1" t="n">
         <v>0.4544</v>
       </c>
-      <c r="X357" s="1" t="n">
+      <c r="Y357" s="1" t="n">
         <v>0.4504</v>
       </c>
     </row>
@@ -27693,9 +28767,12 @@
         <v>0.03455</v>
       </c>
       <c r="W358" s="1" t="n">
+        <v>0.03449</v>
+      </c>
+      <c r="X358" s="1" t="n">
         <v>0.03527</v>
       </c>
-      <c r="X358" s="1" t="n">
+      <c r="Y358" s="1" t="n">
         <v>0.03441</v>
       </c>
     </row>
@@ -27769,9 +28846,12 @@
         <v>0.01446</v>
       </c>
       <c r="W359" s="1" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="X359" s="1" t="n">
         <v>0.01483</v>
       </c>
-      <c r="X359" s="1" t="n">
+      <c r="Y359" s="1" t="n">
         <v>0.01446</v>
       </c>
     </row>
@@ -27845,9 +28925,12 @@
         <v>0.13239</v>
       </c>
       <c r="W360" s="1" t="n">
+        <v>0.13253</v>
+      </c>
+      <c r="X360" s="1" t="n">
         <v>0.13385</v>
       </c>
-      <c r="X360" s="1" t="n">
+      <c r="Y360" s="1" t="n">
         <v>0.13239</v>
       </c>
     </row>
@@ -27921,9 +29004,12 @@
         <v>0.0005881</v>
       </c>
       <c r="W361" s="1" t="n">
+        <v>0.0005865999999999999</v>
+      </c>
+      <c r="X361" s="1" t="n">
         <v>0.0005913</v>
       </c>
-      <c r="X361" s="1" t="n">
+      <c r="Y361" s="1" t="n">
         <v>0.0005848</v>
       </c>
     </row>
@@ -27997,9 +29083,12 @@
         <v>0.03838</v>
       </c>
       <c r="W362" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="X362" s="1" t="n">
         <v>0.03893</v>
       </c>
-      <c r="X362" s="1" t="n">
+      <c r="Y362" s="1" t="n">
         <v>0.03824</v>
       </c>
     </row>
@@ -28073,9 +29162,12 @@
         <v>3.244</v>
       </c>
       <c r="W363" s="1" t="n">
+        <v>3.243</v>
+      </c>
+      <c r="X363" s="1" t="n">
         <v>3.244</v>
       </c>
-      <c r="X363" s="1" t="n">
+      <c r="Y363" s="1" t="n">
         <v>3.204</v>
       </c>
     </row>
@@ -28149,9 +29241,12 @@
         <v>0.1627</v>
       </c>
       <c r="W364" s="1" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="X364" s="1" t="n">
         <v>0.1664</v>
       </c>
-      <c r="X364" s="1" t="n">
+      <c r="Y364" s="1" t="n">
         <v>0.1627</v>
       </c>
     </row>
@@ -28225,9 +29320,12 @@
         <v>0.1127</v>
       </c>
       <c r="W365" s="1" t="n">
+        <v>0.1127</v>
+      </c>
+      <c r="X365" s="1" t="n">
         <v>0.1139</v>
       </c>
-      <c r="X365" s="1" t="n">
+      <c r="Y365" s="1" t="n">
         <v>0.1127</v>
       </c>
     </row>
@@ -28301,9 +29399,12 @@
         <v>0.0006339</v>
       </c>
       <c r="W366" s="1" t="n">
+        <v>0.0006342</v>
+      </c>
+      <c r="X366" s="1" t="n">
         <v>0.0006451</v>
       </c>
-      <c r="X366" s="1" t="n">
+      <c r="Y366" s="1" t="n">
         <v>0.0006339</v>
       </c>
     </row>
@@ -28377,9 +29478,12 @@
         <v>0.0595</v>
       </c>
       <c r="W367" s="1" t="n">
+        <v>0.05982</v>
+      </c>
+      <c r="X367" s="1" t="n">
         <v>0.05998</v>
       </c>
-      <c r="X367" s="1" t="n">
+      <c r="Y367" s="1" t="n">
         <v>0.05903</v>
       </c>
     </row>
@@ -28453,9 +29557,12 @@
         <v>0.08114</v>
       </c>
       <c r="W368" s="1" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="X368" s="1" t="n">
         <v>0.08345</v>
       </c>
-      <c r="X368" s="1" t="n">
+      <c r="Y368" s="1" t="n">
         <v>0.08111</v>
       </c>
     </row>
@@ -28529,9 +29636,12 @@
         <v>0.03929</v>
       </c>
       <c r="W369" s="1" t="n">
+        <v>0.03935</v>
+      </c>
+      <c r="X369" s="1" t="n">
         <v>0.0412</v>
       </c>
-      <c r="X369" s="1" t="n">
+      <c r="Y369" s="1" t="n">
         <v>0.03927</v>
       </c>
     </row>
@@ -28605,9 +29715,12 @@
         <v>3.759</v>
       </c>
       <c r="W370" s="1" t="n">
+        <v>3.691</v>
+      </c>
+      <c r="X370" s="1" t="n">
         <v>3.759</v>
       </c>
-      <c r="X370" s="1" t="n">
+      <c r="Y370" s="1" t="n">
         <v>3.68</v>
       </c>
     </row>
@@ -28681,9 +29794,12 @@
         <v>0.1204</v>
       </c>
       <c r="W371" s="1" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="X371" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="X371" s="1" t="n">
+      <c r="Y371" s="1" t="n">
         <v>0.1204</v>
       </c>
     </row>
@@ -28757,9 +29873,12 @@
         <v>0.0146</v>
       </c>
       <c r="W372" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="X372" s="1" t="n">
         <v>0.01482</v>
       </c>
-      <c r="X372" s="1" t="n">
+      <c r="Y372" s="1" t="n">
         <v>0.0146</v>
       </c>
     </row>
@@ -28833,9 +29952,12 @@
         <v>0.02187</v>
       </c>
       <c r="W373" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="X373" s="1" t="n">
         <v>0.02205</v>
       </c>
-      <c r="X373" s="1" t="n">
+      <c r="Y373" s="1" t="n">
         <v>0.02187</v>
       </c>
     </row>
@@ -28909,9 +30031,12 @@
         <v>1.875</v>
       </c>
       <c r="W374" s="1" t="n">
+        <v>1.8718</v>
+      </c>
+      <c r="X374" s="1" t="n">
         <v>1.875</v>
       </c>
-      <c r="X374" s="1" t="n">
+      <c r="Y374" s="1" t="n">
         <v>1.8537</v>
       </c>
     </row>
@@ -28985,9 +30110,12 @@
         <v>0.02081</v>
       </c>
       <c r="W375" s="1" t="n">
+        <v>0.02081</v>
+      </c>
+      <c r="X375" s="1" t="n">
         <v>0.02112</v>
       </c>
-      <c r="X375" s="1" t="n">
+      <c r="Y375" s="1" t="n">
         <v>0.02081</v>
       </c>
     </row>
@@ -29061,9 +30189,12 @@
         <v>1.304</v>
       </c>
       <c r="W376" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="X376" s="1" t="n">
         <v>1.326</v>
       </c>
-      <c r="X376" s="1" t="n">
+      <c r="Y376" s="1" t="n">
         <v>1.294</v>
       </c>
     </row>
@@ -29137,9 +30268,12 @@
         <v>0.282</v>
       </c>
       <c r="W377" s="1" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="X377" s="1" t="n">
         <v>0.2845</v>
       </c>
-      <c r="X377" s="1" t="n">
+      <c r="Y377" s="1" t="n">
         <v>0.2819</v>
       </c>
     </row>
@@ -29213,9 +30347,12 @@
         <v>0.01552</v>
       </c>
       <c r="W378" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="X378" s="1" t="n">
         <v>0.01573</v>
       </c>
-      <c r="X378" s="1" t="n">
+      <c r="Y378" s="1" t="n">
         <v>0.01549</v>
       </c>
     </row>
@@ -29289,9 +30426,12 @@
         <v>1.5181</v>
       </c>
       <c r="W379" s="1" t="n">
+        <v>1.5215</v>
+      </c>
+      <c r="X379" s="1" t="n">
         <v>1.5387</v>
       </c>
-      <c r="X379" s="1" t="n">
+      <c r="Y379" s="1" t="n">
         <v>1.5181</v>
       </c>
     </row>
@@ -29365,9 +30505,12 @@
         <v>6.858e-05</v>
       </c>
       <c r="W380" s="1" t="n">
+        <v>6.861e-05</v>
+      </c>
+      <c r="X380" s="1" t="n">
         <v>6.972e-05</v>
       </c>
-      <c r="X380" s="1" t="n">
+      <c r="Y380" s="1" t="n">
         <v>6.858e-05</v>
       </c>
     </row>
@@ -29441,9 +30584,12 @@
         <v>2.538</v>
       </c>
       <c r="W381" s="1" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="X381" s="1" t="n">
         <v>2.559</v>
       </c>
-      <c r="X381" s="1" t="n">
+      <c r="Y381" s="1" t="n">
         <v>2.536</v>
       </c>
     </row>
@@ -29517,9 +30663,12 @@
         <v>0.06658</v>
       </c>
       <c r="W382" s="1" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="X382" s="1" t="n">
         <v>0.06765</v>
       </c>
-      <c r="X382" s="1" t="n">
+      <c r="Y382" s="1" t="n">
         <v>0.06646000000000001</v>
       </c>
     </row>
@@ -29593,9 +30742,12 @@
         <v>0.01662</v>
       </c>
       <c r="W383" s="1" t="n">
+        <v>0.01672</v>
+      </c>
+      <c r="X383" s="1" t="n">
         <v>0.01985</v>
       </c>
-      <c r="X383" s="1" t="n">
+      <c r="Y383" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -29669,9 +30821,12 @@
         <v>0.05126</v>
       </c>
       <c r="W384" s="1" t="n">
+        <v>0.05126</v>
+      </c>
+      <c r="X384" s="1" t="n">
         <v>0.05334</v>
       </c>
-      <c r="X384" s="1" t="n">
+      <c r="Y384" s="1" t="n">
         <v>0.05055</v>
       </c>
     </row>
@@ -29745,9 +30900,12 @@
         <v>7.607</v>
       </c>
       <c r="W385" s="1" t="n">
+        <v>7.605</v>
+      </c>
+      <c r="X385" s="1